--- a/Screener/data/rs_rating_top_30.xlsx
+++ b/Screener/data/rs_rating_top_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="370">
   <si>
     <t>Symbol</t>
   </si>
@@ -22,1071 +22,1077 @@
     <t>RS Rating</t>
   </si>
   <si>
+    <t>CLH</t>
+  </si>
+  <si>
+    <t>CCS</t>
+  </si>
+  <si>
+    <t>ABNB</t>
+  </si>
+  <si>
+    <t>ABG</t>
+  </si>
+  <si>
+    <t>AFRM</t>
+  </si>
+  <si>
+    <t>RKT</t>
+  </si>
+  <si>
+    <t>FTDR</t>
+  </si>
+  <si>
+    <t>PAM</t>
+  </si>
+  <si>
+    <t>MTZ</t>
+  </si>
+  <si>
+    <t>LSCC</t>
+  </si>
+  <si>
+    <t>THO</t>
+  </si>
+  <si>
+    <t>KBAL</t>
+  </si>
+  <si>
+    <t>GPI</t>
+  </si>
+  <si>
+    <t>APPN</t>
+  </si>
+  <si>
+    <t>MWA</t>
+  </si>
+  <si>
+    <t>FLEX</t>
+  </si>
+  <si>
+    <t>WDFC</t>
+  </si>
+  <si>
+    <t>TEX</t>
+  </si>
+  <si>
+    <t>NOW</t>
+  </si>
+  <si>
+    <t>CWH</t>
+  </si>
+  <si>
+    <t>LASR</t>
+  </si>
+  <si>
+    <t>VIPS</t>
+  </si>
+  <si>
+    <t>CRMT</t>
+  </si>
+  <si>
+    <t>PLTK</t>
+  </si>
+  <si>
+    <t>ORCL</t>
+  </si>
+  <si>
+    <t>ACCD</t>
+  </si>
+  <si>
+    <t>CRNC</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>FORM</t>
+  </si>
+  <si>
+    <t>FDX</t>
+  </si>
+  <si>
+    <t>CPRT</t>
+  </si>
+  <si>
+    <t>CNM</t>
+  </si>
+  <si>
+    <t>SSD</t>
+  </si>
+  <si>
+    <t>HEAR</t>
+  </si>
+  <si>
+    <t>AMZN</t>
+  </si>
+  <si>
+    <t>PATH</t>
+  </si>
+  <si>
+    <t>LRCX</t>
+  </si>
+  <si>
+    <t>HUBB</t>
+  </si>
+  <si>
+    <t>DBRG</t>
+  </si>
+  <si>
+    <t>TWN</t>
+  </si>
+  <si>
+    <t>LPRO</t>
+  </si>
+  <si>
     <t>ADDYY</t>
   </si>
   <si>
-    <t>IPGP</t>
-  </si>
-  <si>
-    <t>PHG</t>
-  </si>
-  <si>
-    <t>WDAY</t>
-  </si>
-  <si>
-    <t>KE</t>
+    <t>NPO</t>
+  </si>
+  <si>
+    <t>FCAP</t>
+  </si>
+  <si>
+    <t>IGT</t>
+  </si>
+  <si>
+    <t>FDMT</t>
+  </si>
+  <si>
+    <t>MLNK</t>
+  </si>
+  <si>
+    <t>GNRC</t>
+  </si>
+  <si>
+    <t>ARCO</t>
+  </si>
+  <si>
+    <t>TA</t>
+  </si>
+  <si>
+    <t>SPSC</t>
+  </si>
+  <si>
+    <t>GSHD</t>
+  </si>
+  <si>
+    <t>FND</t>
+  </si>
+  <si>
+    <t>MATW</t>
+  </si>
+  <si>
+    <t>ATI</t>
+  </si>
+  <si>
+    <t>KRNT</t>
+  </si>
+  <si>
+    <t>VLRS</t>
+  </si>
+  <si>
+    <t>Z</t>
+  </si>
+  <si>
+    <t>FTNT</t>
+  </si>
+  <si>
+    <t>ZEUS</t>
+  </si>
+  <si>
+    <t>DELL</t>
+  </si>
+  <si>
+    <t>CVAC</t>
+  </si>
+  <si>
+    <t>BLX</t>
+  </si>
+  <si>
+    <t>NEO</t>
+  </si>
+  <si>
+    <t>ZG</t>
+  </si>
+  <si>
+    <t>ADDDF</t>
+  </si>
+  <si>
+    <t>RELY</t>
+  </si>
+  <si>
+    <t>CAMT</t>
+  </si>
+  <si>
+    <t>BSY</t>
+  </si>
+  <si>
+    <t>PATK</t>
+  </si>
+  <si>
+    <t>MRUS</t>
+  </si>
+  <si>
+    <t>ON</t>
+  </si>
+  <si>
+    <t>BCC</t>
+  </si>
+  <si>
+    <t>MPX</t>
+  </si>
+  <si>
+    <t>TMDX</t>
+  </si>
+  <si>
+    <t>MTH</t>
+  </si>
+  <si>
+    <t>PEGA</t>
+  </si>
+  <si>
+    <t>PEN</t>
+  </si>
+  <si>
+    <t>SSYS</t>
+  </si>
+  <si>
+    <t>ONTO</t>
+  </si>
+  <si>
+    <t>OII</t>
+  </si>
+  <si>
+    <t>AZEK</t>
+  </si>
+  <si>
+    <t>SNAP</t>
+  </si>
+  <si>
+    <t>LPG</t>
+  </si>
+  <si>
+    <t>VEON</t>
+  </si>
+  <si>
+    <t>TREX</t>
+  </si>
+  <si>
+    <t>GXO</t>
+  </si>
+  <si>
+    <t>LZ</t>
+  </si>
+  <si>
+    <t>HQI</t>
+  </si>
+  <si>
+    <t>GTLB</t>
+  </si>
+  <si>
+    <t>DT</t>
+  </si>
+  <si>
+    <t>IESC</t>
+  </si>
+  <si>
+    <t>MPWR</t>
+  </si>
+  <si>
+    <t>BOOT</t>
+  </si>
+  <si>
+    <t>DDOG</t>
+  </si>
+  <si>
+    <t>NEOG</t>
+  </si>
+  <si>
+    <t>OC</t>
+  </si>
+  <si>
+    <t>GKOS</t>
+  </si>
+  <si>
+    <t>UBER</t>
+  </si>
+  <si>
+    <t>NET</t>
+  </si>
+  <si>
+    <t>COTY</t>
+  </si>
+  <si>
+    <t>URBN</t>
+  </si>
+  <si>
+    <t>TPH</t>
+  </si>
+  <si>
+    <t>ALGM</t>
+  </si>
+  <si>
+    <t>VNT</t>
+  </si>
+  <si>
+    <t>CNMD</t>
+  </si>
+  <si>
+    <t>ALGN</t>
+  </si>
+  <si>
+    <t>SMHI</t>
+  </si>
+  <si>
+    <t>TRDA</t>
+  </si>
+  <si>
+    <t>PKOH</t>
+  </si>
+  <si>
+    <t>APG</t>
+  </si>
+  <si>
+    <t>DICE</t>
+  </si>
+  <si>
+    <t>CARG</t>
+  </si>
+  <si>
+    <t>INMB</t>
+  </si>
+  <si>
+    <t>SGRY</t>
+  </si>
+  <si>
+    <t>CYD</t>
+  </si>
+  <si>
+    <t>APPF</t>
+  </si>
+  <si>
+    <t>PAG</t>
+  </si>
+  <si>
+    <t>SHAK</t>
+  </si>
+  <si>
+    <t>ATEC</t>
+  </si>
+  <si>
+    <t>ERO</t>
+  </si>
+  <si>
+    <t>GE</t>
+  </si>
+  <si>
+    <t>ASMIY</t>
+  </si>
+  <si>
+    <t>CPS</t>
+  </si>
+  <si>
+    <t>ASAN</t>
+  </si>
+  <si>
+    <t>TMHC</t>
+  </si>
+  <si>
+    <t>FIVN</t>
+  </si>
+  <si>
+    <t>RH</t>
+  </si>
+  <si>
+    <t>ENS</t>
+  </si>
+  <si>
+    <t>CLS</t>
+  </si>
+  <si>
+    <t>WFRD</t>
+  </si>
+  <si>
+    <t>BWMN</t>
+  </si>
+  <si>
+    <t>MACK</t>
+  </si>
+  <si>
+    <t>FTAI</t>
+  </si>
+  <si>
+    <t>JELD</t>
+  </si>
+  <si>
+    <t>RDNT</t>
+  </si>
+  <si>
+    <t>ZUO</t>
+  </si>
+  <si>
+    <t>SHOP</t>
+  </si>
+  <si>
+    <t>AXR</t>
+  </si>
+  <si>
+    <t>TSQ</t>
+  </si>
+  <si>
+    <t>MTW</t>
+  </si>
+  <si>
+    <t>RCMT</t>
+  </si>
+  <si>
+    <t>MTR</t>
+  </si>
+  <si>
+    <t>FTI</t>
+  </si>
+  <si>
+    <t>DAL</t>
+  </si>
+  <si>
+    <t>SIBN</t>
+  </si>
+  <si>
+    <t>BMA</t>
+  </si>
+  <si>
+    <t>CELH</t>
+  </si>
+  <si>
+    <t>CPSS</t>
+  </si>
+  <si>
+    <t>ROKU</t>
+  </si>
+  <si>
+    <t>MANH</t>
+  </si>
+  <si>
+    <t>IBP</t>
+  </si>
+  <si>
+    <t>KBH</t>
+  </si>
+  <si>
+    <t>GBX</t>
+  </si>
+  <si>
+    <t>PRG</t>
+  </si>
+  <si>
+    <t>NFLX</t>
+  </si>
+  <si>
+    <t>NATR</t>
+  </si>
+  <si>
+    <t>ETNB</t>
+  </si>
+  <si>
+    <t>ALGT</t>
+  </si>
+  <si>
+    <t>USLM</t>
+  </si>
+  <si>
+    <t>ARCT</t>
+  </si>
+  <si>
+    <t>HSKA</t>
+  </si>
+  <si>
+    <t>DASH</t>
+  </si>
+  <si>
+    <t>SWDAF</t>
+  </si>
+  <si>
+    <t>PACB</t>
+  </si>
+  <si>
+    <t>CAAP</t>
+  </si>
+  <si>
+    <t>TXG</t>
+  </si>
+  <si>
+    <t>DXPE</t>
+  </si>
+  <si>
+    <t>YEXT</t>
+  </si>
+  <si>
+    <t>DUOL</t>
+  </si>
+  <si>
+    <t>BECN</t>
+  </si>
+  <si>
+    <t>PETQ</t>
+  </si>
+  <si>
+    <t>YPF</t>
+  </si>
+  <si>
+    <t>AN</t>
+  </si>
+  <si>
+    <t>LSANF</t>
+  </si>
+  <si>
+    <t>UFPT</t>
+  </si>
+  <si>
+    <t>CXM</t>
+  </si>
+  <si>
+    <t>PANW</t>
+  </si>
+  <si>
+    <t>MOMO</t>
+  </si>
+  <si>
+    <t>LTH</t>
+  </si>
+  <si>
+    <t>NETI</t>
+  </si>
+  <si>
+    <t>AMD</t>
+  </si>
+  <si>
+    <t>TDC</t>
+  </si>
+  <si>
+    <t>FLNC</t>
+  </si>
+  <si>
+    <t>FOR</t>
+  </si>
+  <si>
+    <t>IIVI</t>
+  </si>
+  <si>
+    <t>TOL</t>
+  </si>
+  <si>
+    <t>EBIX</t>
+  </si>
+  <si>
+    <t>ENTG</t>
+  </si>
+  <si>
+    <t>SAIA</t>
+  </si>
+  <si>
+    <t>ONON</t>
+  </si>
+  <si>
+    <t>IDCC</t>
+  </si>
+  <si>
+    <t>NNOX</t>
+  </si>
+  <si>
+    <t>ALPN</t>
+  </si>
+  <si>
+    <t>TDW</t>
+  </si>
+  <si>
+    <t>BLD</t>
+  </si>
+  <si>
+    <t>MNDY</t>
+  </si>
+  <si>
+    <t>BELFB</t>
+  </si>
+  <si>
+    <t>ACMR</t>
+  </si>
+  <si>
+    <t>PCTTU</t>
+  </si>
+  <si>
+    <t>BMEA</t>
+  </si>
+  <si>
+    <t>CVGI</t>
+  </si>
+  <si>
+    <t>THC</t>
+  </si>
+  <si>
+    <t>PDFS</t>
+  </si>
+  <si>
+    <t>BLU</t>
+  </si>
+  <si>
+    <t>ABCM</t>
+  </si>
+  <si>
+    <t>RIVN</t>
+  </si>
+  <si>
+    <t>FCNCA</t>
   </si>
   <si>
     <t>PHAT</t>
   </si>
   <si>
-    <t>GTLB</t>
-  </si>
-  <si>
-    <t>AAL</t>
-  </si>
-  <si>
-    <t>NXPI</t>
-  </si>
-  <si>
-    <t>LEGN</t>
-  </si>
-  <si>
-    <t>HY</t>
-  </si>
-  <si>
-    <t>VIPS</t>
-  </si>
-  <si>
-    <t>CAR</t>
-  </si>
-  <si>
-    <t>CNM</t>
-  </si>
-  <si>
-    <t>MPX</t>
-  </si>
-  <si>
-    <t>GHRS</t>
-  </si>
-  <si>
-    <t>IGT</t>
-  </si>
-  <si>
-    <t>MTR</t>
-  </si>
-  <si>
-    <t>SSD</t>
-  </si>
-  <si>
-    <t>VEL</t>
-  </si>
-  <si>
-    <t>WST</t>
-  </si>
-  <si>
-    <t>BLX</t>
-  </si>
-  <si>
-    <t>LINK</t>
-  </si>
-  <si>
-    <t>CDNS</t>
-  </si>
-  <si>
-    <t>FMS</t>
-  </si>
-  <si>
-    <t>ORCL</t>
-  </si>
-  <si>
-    <t>ASAN</t>
-  </si>
-  <si>
-    <t>APPN</t>
-  </si>
-  <si>
-    <t>CCS</t>
-  </si>
-  <si>
-    <t>ZS</t>
-  </si>
-  <si>
-    <t>AMZN</t>
-  </si>
-  <si>
-    <t>PLTK</t>
-  </si>
-  <si>
-    <t>PAM</t>
-  </si>
-  <si>
-    <t>BSY</t>
-  </si>
-  <si>
-    <t>OII</t>
-  </si>
-  <si>
-    <t>CNK</t>
-  </si>
-  <si>
-    <t>PATK</t>
-  </si>
-  <si>
-    <t>DT</t>
-  </si>
-  <si>
-    <t>NVMI</t>
-  </si>
-  <si>
-    <t>FORM</t>
-  </si>
-  <si>
-    <t>PEGA</t>
-  </si>
-  <si>
-    <t>DDOG</t>
-  </si>
-  <si>
-    <t>SMHI</t>
-  </si>
-  <si>
-    <t>ATI</t>
-  </si>
-  <si>
-    <t>DELL</t>
-  </si>
-  <si>
-    <t>NPO</t>
-  </si>
-  <si>
-    <t>NET</t>
-  </si>
-  <si>
-    <t>MTZ</t>
-  </si>
-  <si>
-    <t>TWN</t>
-  </si>
-  <si>
-    <t>SNPS</t>
-  </si>
-  <si>
-    <t>FLEX</t>
-  </si>
-  <si>
-    <t>HELE</t>
-  </si>
-  <si>
-    <t>CPRT</t>
-  </si>
-  <si>
-    <t>BOOT</t>
-  </si>
-  <si>
-    <t>FSTR</t>
-  </si>
-  <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>ACAD</t>
-  </si>
-  <si>
-    <t>AZEK</t>
-  </si>
-  <si>
-    <t>UBER</t>
-  </si>
-  <si>
-    <t>FTNT</t>
-  </si>
-  <si>
-    <t>MLNK</t>
-  </si>
-  <si>
-    <t>FCAP</t>
-  </si>
-  <si>
-    <t>IRMD</t>
-  </si>
-  <si>
-    <t>RH</t>
-  </si>
-  <si>
-    <t>BCC</t>
-  </si>
-  <si>
-    <t>WCC</t>
-  </si>
-  <si>
-    <t>HUBB</t>
-  </si>
-  <si>
-    <t>WFRD</t>
-  </si>
-  <si>
-    <t>NOW</t>
-  </si>
-  <si>
-    <t>PKOH</t>
-  </si>
-  <si>
-    <t>VLRS</t>
-  </si>
-  <si>
-    <t>CWCO</t>
-  </si>
-  <si>
-    <t>ARCO</t>
-  </si>
-  <si>
-    <t>CLH</t>
-  </si>
-  <si>
-    <t>GH</t>
-  </si>
-  <si>
-    <t>TMDX</t>
-  </si>
-  <si>
-    <t>CVAC</t>
-  </si>
-  <si>
-    <t>CAMT</t>
-  </si>
-  <si>
-    <t>URBN</t>
-  </si>
-  <si>
-    <t>LZRFY</t>
-  </si>
-  <si>
-    <t>AMAT</t>
-  </si>
-  <si>
-    <t>ALGN</t>
-  </si>
-  <si>
-    <t>APG</t>
-  </si>
-  <si>
-    <t>MTH</t>
-  </si>
-  <si>
-    <t>DBRG</t>
-  </si>
-  <si>
-    <t>USLM</t>
-  </si>
-  <si>
-    <t>LASR</t>
-  </si>
-  <si>
-    <t>LSCC</t>
-  </si>
-  <si>
-    <t>AXR</t>
-  </si>
-  <si>
-    <t>FTI</t>
-  </si>
-  <si>
-    <t>OC</t>
-  </si>
-  <si>
-    <t>VSH</t>
-  </si>
-  <si>
-    <t>GXO</t>
-  </si>
-  <si>
-    <t>CLS</t>
-  </si>
-  <si>
-    <t>NEOG</t>
-  </si>
-  <si>
-    <t>CRNC</t>
-  </si>
-  <si>
-    <t>TRDA</t>
-  </si>
-  <si>
-    <t>VEON</t>
-  </si>
-  <si>
-    <t>MNDY</t>
-  </si>
-  <si>
-    <t>ON</t>
-  </si>
-  <si>
-    <t>PAG</t>
-  </si>
-  <si>
-    <t>LRCX</t>
-  </si>
-  <si>
-    <t>CNMD</t>
-  </si>
-  <si>
-    <t>COTY</t>
-  </si>
-  <si>
-    <t>ATEC</t>
-  </si>
-  <si>
-    <t>MATW</t>
-  </si>
-  <si>
-    <t>MPWR</t>
-  </si>
-  <si>
-    <t>VNT</t>
+    <t>AMWD</t>
+  </si>
+  <si>
+    <t>ATLC</t>
+  </si>
+  <si>
+    <t>ROIV</t>
+  </si>
+  <si>
+    <t>PHM</t>
+  </si>
+  <si>
+    <t>LAD</t>
+  </si>
+  <si>
+    <t>MLP</t>
+  </si>
+  <si>
+    <t>DOCN</t>
+  </si>
+  <si>
+    <t>RMBS</t>
+  </si>
+  <si>
+    <t>MORF</t>
+  </si>
+  <si>
+    <t>MRNS</t>
+  </si>
+  <si>
+    <t>BELFA</t>
+  </si>
+  <si>
+    <t>OPAD</t>
   </si>
   <si>
     <t>TTD</t>
   </si>
   <si>
-    <t>ALGM</t>
-  </si>
-  <si>
-    <t>SSYS</t>
-  </si>
-  <si>
-    <t>DICE</t>
-  </si>
-  <si>
-    <t>DUOL</t>
-  </si>
-  <si>
-    <t>GKOS</t>
-  </si>
-  <si>
-    <t>PEN</t>
-  </si>
-  <si>
-    <t>CXM</t>
-  </si>
-  <si>
-    <t>IBP</t>
-  </si>
-  <si>
-    <t>RDNT</t>
-  </si>
-  <si>
-    <t>NEO</t>
-  </si>
-  <si>
-    <t>JELD</t>
-  </si>
-  <si>
-    <t>ZUO</t>
-  </si>
-  <si>
-    <t>MACK</t>
-  </si>
-  <si>
-    <t>CAAP</t>
-  </si>
-  <si>
-    <t>VYGR</t>
-  </si>
-  <si>
-    <t>KRNT</t>
-  </si>
-  <si>
-    <t>TPH</t>
-  </si>
-  <si>
-    <t>SHOP</t>
-  </si>
-  <si>
-    <t>ENS</t>
-  </si>
-  <si>
-    <t>APPF</t>
-  </si>
-  <si>
-    <t>SHAK</t>
-  </si>
-  <si>
-    <t>TMHC</t>
-  </si>
-  <si>
-    <t>IESC</t>
-  </si>
-  <si>
-    <t>FIVN</t>
-  </si>
-  <si>
-    <t>NATR</t>
-  </si>
-  <si>
-    <t>GE</t>
-  </si>
-  <si>
-    <t>MANH</t>
-  </si>
-  <si>
-    <t>DXPE</t>
-  </si>
-  <si>
-    <t>AN</t>
-  </si>
-  <si>
-    <t>DASH</t>
-  </si>
-  <si>
-    <t>BMA</t>
-  </si>
-  <si>
-    <t>MTW</t>
-  </si>
-  <si>
-    <t>PACB</t>
-  </si>
-  <si>
-    <t>HSKA</t>
-  </si>
-  <si>
-    <t>BWMN</t>
-  </si>
-  <si>
-    <t>DAL</t>
-  </si>
-  <si>
-    <t>OPAD</t>
-  </si>
-  <si>
-    <t>CYD</t>
-  </si>
-  <si>
-    <t>HQI</t>
-  </si>
-  <si>
-    <t>TSQ</t>
-  </si>
-  <si>
-    <t>KBH</t>
-  </si>
-  <si>
-    <t>SGRY</t>
-  </si>
-  <si>
-    <t>SAIA</t>
-  </si>
-  <si>
-    <t>ASMIY</t>
-  </si>
-  <si>
-    <t>LSANF</t>
+    <t>DV</t>
+  </si>
+  <si>
+    <t>KRYS</t>
+  </si>
+  <si>
+    <t>PSTG</t>
+  </si>
+  <si>
+    <t>DMRC</t>
+  </si>
+  <si>
+    <t>MNSO</t>
+  </si>
+  <si>
+    <t>BLBD</t>
+  </si>
+  <si>
+    <t>MDWT</t>
+  </si>
+  <si>
+    <t>BRZE</t>
+  </si>
+  <si>
+    <t>ADBE</t>
+  </si>
+  <si>
+    <t>CMT</t>
+  </si>
+  <si>
+    <t>PLPC</t>
+  </si>
+  <si>
+    <t>COHR</t>
+  </si>
+  <si>
+    <t>SPOT</t>
+  </si>
+  <si>
+    <t>BWMX</t>
+  </si>
+  <si>
+    <t>VIST</t>
+  </si>
+  <si>
+    <t>HUBS</t>
+  </si>
+  <si>
+    <t>ISEE</t>
+  </si>
+  <si>
+    <t>XP</t>
+  </si>
+  <si>
+    <t>STVN</t>
+  </si>
+  <si>
+    <t>MHO</t>
+  </si>
+  <si>
+    <t>CUBI</t>
+  </si>
+  <si>
+    <t>JBL</t>
+  </si>
+  <si>
+    <t>GGAL</t>
+  </si>
+  <si>
+    <t>CRCT</t>
+  </si>
+  <si>
+    <t>EXTR</t>
+  </si>
+  <si>
+    <t>COCO</t>
+  </si>
+  <si>
+    <t>BBIO</t>
+  </si>
+  <si>
+    <t>PTGX</t>
+  </si>
+  <si>
+    <t>TGLS</t>
+  </si>
+  <si>
+    <t>TAYD</t>
+  </si>
+  <si>
+    <t>ATRO</t>
   </si>
   <si>
     <t>U</t>
   </si>
   <si>
-    <t>ENTG</t>
-  </si>
-  <si>
-    <t>ONON</t>
-  </si>
-  <si>
-    <t>RCMT</t>
-  </si>
-  <si>
-    <t>TXG</t>
-  </si>
-  <si>
-    <t>PANW</t>
-  </si>
-  <si>
-    <t>IIVI</t>
-  </si>
-  <si>
-    <t>GBX</t>
-  </si>
-  <si>
-    <t>SWDAF</t>
-  </si>
-  <si>
-    <t>MRUS</t>
-  </si>
-  <si>
-    <t>ONTO</t>
-  </si>
-  <si>
-    <t>LTH</t>
-  </si>
-  <si>
-    <t>MLP</t>
-  </si>
-  <si>
-    <t>CARG</t>
-  </si>
-  <si>
-    <t>SIBN</t>
-  </si>
-  <si>
-    <t>NETI</t>
-  </si>
-  <si>
-    <t>FTAI</t>
-  </si>
-  <si>
-    <t>YPF</t>
-  </si>
-  <si>
-    <t>NFLX</t>
-  </si>
-  <si>
-    <t>BWMX</t>
-  </si>
-  <si>
-    <t>FLNC</t>
-  </si>
-  <si>
-    <t>TOL</t>
-  </si>
-  <si>
-    <t>NNOX</t>
-  </si>
-  <si>
-    <t>PRG</t>
-  </si>
-  <si>
-    <t>LPRO</t>
-  </si>
-  <si>
-    <t>LAD</t>
-  </si>
-  <si>
-    <t>ALGT</t>
-  </si>
-  <si>
-    <t>TDC</t>
-  </si>
-  <si>
-    <t>ACMR</t>
-  </si>
-  <si>
-    <t>FOR</t>
-  </si>
-  <si>
-    <t>ATLC</t>
-  </si>
-  <si>
-    <t>KALV</t>
-  </si>
-  <si>
-    <t>BECN</t>
-  </si>
-  <si>
-    <t>BLU</t>
-  </si>
-  <si>
-    <t>PCTTU</t>
-  </si>
-  <si>
-    <t>CUBI</t>
-  </si>
-  <si>
-    <t>VIST</t>
-  </si>
-  <si>
-    <t>BLD</t>
-  </si>
-  <si>
-    <t>YEXT</t>
-  </si>
-  <si>
-    <t>TDW</t>
+    <t>POWL</t>
   </si>
   <si>
     <t>OSTK</t>
   </si>
   <si>
-    <t>KBAL</t>
-  </si>
-  <si>
-    <t>ETNB</t>
-  </si>
-  <si>
-    <t>EBIX</t>
-  </si>
-  <si>
-    <t>DOCN</t>
-  </si>
-  <si>
-    <t>THC</t>
-  </si>
-  <si>
-    <t>SPOT</t>
-  </si>
-  <si>
-    <t>IDCC</t>
-  </si>
-  <si>
-    <t>LZ</t>
-  </si>
-  <si>
-    <t>PHM</t>
-  </si>
-  <si>
-    <t>HUBS</t>
-  </si>
-  <si>
-    <t>BMEA</t>
-  </si>
-  <si>
-    <t>ROIV</t>
-  </si>
-  <si>
-    <t>BRZE</t>
+    <t>GRBK</t>
+  </si>
+  <si>
+    <t>AVGO</t>
+  </si>
+  <si>
+    <t>NCLH</t>
+  </si>
+  <si>
+    <t>MRVL</t>
   </si>
   <si>
     <t>PROF</t>
   </si>
   <si>
-    <t>ADBE</t>
-  </si>
-  <si>
-    <t>CVGI</t>
-  </si>
-  <si>
-    <t>CRCT</t>
-  </si>
-  <si>
-    <t>PDFS</t>
-  </si>
-  <si>
-    <t>AMWD</t>
-  </si>
-  <si>
-    <t>ALPN</t>
-  </si>
-  <si>
-    <t>KRYS</t>
-  </si>
-  <si>
-    <t>AMD</t>
-  </si>
-  <si>
-    <t>PLPC</t>
-  </si>
-  <si>
-    <t>ISEE</t>
-  </si>
-  <si>
-    <t>PSTG</t>
-  </si>
-  <si>
-    <t>ABCM</t>
-  </si>
-  <si>
-    <t>PETQ</t>
+    <t>STRL</t>
+  </si>
+  <si>
+    <t>XPO</t>
+  </si>
+  <si>
+    <t>RRGB</t>
+  </si>
+  <si>
+    <t>BVH</t>
+  </si>
+  <si>
+    <t>PLAB</t>
+  </si>
+  <si>
+    <t>CFLT</t>
+  </si>
+  <si>
+    <t>WRLD</t>
+  </si>
+  <si>
+    <t>RCL</t>
+  </si>
+  <si>
+    <t>ANF</t>
+  </si>
+  <si>
+    <t>SG</t>
+  </si>
+  <si>
+    <t>AMPH</t>
+  </si>
+  <si>
+    <t>GRVY</t>
   </si>
   <si>
     <t>IAS</t>
   </si>
   <si>
-    <t>DV</t>
-  </si>
-  <si>
-    <t>COHR</t>
-  </si>
-  <si>
-    <t>BELFB</t>
-  </si>
-  <si>
-    <t>CFLT</t>
-  </si>
-  <si>
-    <t>JBL</t>
-  </si>
-  <si>
-    <t>FCNCA</t>
-  </si>
-  <si>
-    <t>BBIO</t>
-  </si>
-  <si>
-    <t>STVN</t>
-  </si>
-  <si>
-    <t>BELFA</t>
-  </si>
-  <si>
-    <t>DMRC</t>
-  </si>
-  <si>
-    <t>MHO</t>
-  </si>
-  <si>
-    <t>TAYD</t>
-  </si>
-  <si>
-    <t>GGAL</t>
-  </si>
-  <si>
-    <t>MDWT</t>
-  </si>
-  <si>
-    <t>CELH</t>
-  </si>
-  <si>
-    <t>MORF</t>
-  </si>
-  <si>
-    <t>ATRO</t>
-  </si>
-  <si>
-    <t>RMBS</t>
-  </si>
-  <si>
-    <t>RIVN</t>
-  </si>
-  <si>
-    <t>MRVL</t>
-  </si>
-  <si>
-    <t>UFPT</t>
-  </si>
-  <si>
-    <t>BVH</t>
-  </si>
-  <si>
-    <t>IMRX</t>
-  </si>
-  <si>
-    <t>ARCT</t>
-  </si>
-  <si>
-    <t>AVGO</t>
+    <t>MOD</t>
+  </si>
+  <si>
+    <t>FSLY</t>
+  </si>
+  <si>
+    <t>AVDL</t>
   </si>
   <si>
     <t>COIN</t>
   </si>
   <si>
-    <t>XP</t>
-  </si>
-  <si>
-    <t>TGLS</t>
+    <t>ACVA</t>
+  </si>
+  <si>
+    <t>DKNG</t>
+  </si>
+  <si>
+    <t>PCT</t>
+  </si>
+  <si>
+    <t>CBAY</t>
+  </si>
+  <si>
+    <t>GBTC</t>
+  </si>
+  <si>
+    <t>TYRA</t>
+  </si>
+  <si>
+    <t>LI</t>
+  </si>
+  <si>
+    <t>CLXT</t>
+  </si>
+  <si>
+    <t>AZUL</t>
+  </si>
+  <si>
+    <t>AEHR</t>
+  </si>
+  <si>
+    <t>GLBE</t>
+  </si>
+  <si>
+    <t>KRUS</t>
+  </si>
+  <si>
+    <t>XPEV</t>
+  </si>
+  <si>
+    <t>EDTX</t>
+  </si>
+  <si>
+    <t>BLDR</t>
+  </si>
+  <si>
+    <t>GOCO</t>
+  </si>
+  <si>
+    <t>KDNY</t>
+  </si>
+  <si>
+    <t>INTT</t>
+  </si>
+  <si>
+    <t>NWLI</t>
+  </si>
+  <si>
+    <t>VKTX</t>
+  </si>
+  <si>
+    <t>MGNI</t>
+  </si>
+  <si>
+    <t>BHVN</t>
+  </si>
+  <si>
+    <t>MSTR</t>
+  </si>
+  <si>
+    <t>VRT</t>
+  </si>
+  <si>
+    <t>SGH</t>
+  </si>
+  <si>
+    <t>SHC</t>
+  </si>
+  <si>
+    <t>EDTXU</t>
+  </si>
+  <si>
+    <t>EDN</t>
+  </si>
+  <si>
+    <t>HOV</t>
+  </si>
+  <si>
+    <t>EXAS</t>
+  </si>
+  <si>
+    <t>ELF</t>
+  </si>
+  <si>
+    <t>RCEL</t>
+  </si>
+  <si>
+    <t>ODC</t>
+  </si>
+  <si>
+    <t>VECT</t>
+  </si>
+  <si>
+    <t>USAP</t>
+  </si>
+  <si>
+    <t>QTRX</t>
+  </si>
+  <si>
+    <t>EXPI</t>
+  </si>
+  <si>
+    <t>LSEA</t>
+  </si>
+  <si>
+    <t>IOT</t>
+  </si>
+  <si>
+    <t>GHL</t>
+  </si>
+  <si>
+    <t>MDB</t>
+  </si>
+  <si>
+    <t>CMPR</t>
+  </si>
+  <si>
+    <t>BZH</t>
+  </si>
+  <si>
+    <t>ACLS</t>
+  </si>
+  <si>
+    <t>NGMS</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>RXDX</t>
+  </si>
+  <si>
+    <t>TGTX</t>
+  </si>
+  <si>
+    <t>DFH</t>
+  </si>
+  <si>
+    <t>APP</t>
+  </si>
+  <si>
+    <t>LTRPB</t>
+  </si>
+  <si>
+    <t>EH</t>
+  </si>
+  <si>
+    <t>CCL</t>
+  </si>
+  <si>
+    <t>TCMD</t>
   </si>
   <si>
     <t>ENVX</t>
   </si>
   <si>
-    <t>ANF</t>
-  </si>
-  <si>
-    <t>MGNI</t>
-  </si>
-  <si>
-    <t>POWL</t>
-  </si>
-  <si>
-    <t>CMT</t>
-  </si>
-  <si>
-    <t>STRL</t>
-  </si>
-  <si>
-    <t>PTGX</t>
-  </si>
-  <si>
-    <t>NCLH</t>
-  </si>
-  <si>
-    <t>ACVA</t>
-  </si>
-  <si>
-    <t>BLBD</t>
-  </si>
-  <si>
-    <t>GRBK</t>
-  </si>
-  <si>
-    <t>EXTR</t>
-  </si>
-  <si>
-    <t>WRLD</t>
-  </si>
-  <si>
-    <t>TYRA</t>
-  </si>
-  <si>
-    <t>FSLY</t>
-  </si>
-  <si>
-    <t>GRVY</t>
-  </si>
-  <si>
-    <t>SG</t>
-  </si>
-  <si>
-    <t>XPO</t>
-  </si>
-  <si>
-    <t>MOD</t>
-  </si>
-  <si>
-    <t>RRGB</t>
-  </si>
-  <si>
-    <t>BHVN</t>
-  </si>
-  <si>
-    <t>MNSO</t>
-  </si>
-  <si>
-    <t>COCO</t>
-  </si>
-  <si>
-    <t>PLAB</t>
-  </si>
-  <si>
-    <t>XPEV</t>
-  </si>
-  <si>
-    <t>EDTX</t>
+    <t>CUK</t>
+  </si>
+  <si>
+    <t>PLTR</t>
+  </si>
+  <si>
+    <t>LMB</t>
+  </si>
+  <si>
+    <t>SKYW</t>
+  </si>
+  <si>
+    <t>RXST</t>
+  </si>
+  <si>
+    <t>NVTS</t>
+  </si>
+  <si>
+    <t>RETA</t>
   </si>
   <si>
     <t>VERA</t>
   </si>
   <si>
-    <t>MRNS</t>
-  </si>
-  <si>
-    <t>ICVX</t>
-  </si>
-  <si>
-    <t>CBAY</t>
-  </si>
-  <si>
-    <t>RCL</t>
-  </si>
-  <si>
-    <t>BLDR</t>
-  </si>
-  <si>
-    <t>GBTC</t>
-  </si>
-  <si>
-    <t>GLBE</t>
-  </si>
-  <si>
-    <t>DKNG</t>
-  </si>
-  <si>
-    <t>NWLI</t>
-  </si>
-  <si>
-    <t>PCT</t>
-  </si>
-  <si>
-    <t>TSLA</t>
-  </si>
-  <si>
-    <t>EXPI</t>
-  </si>
-  <si>
-    <t>AEHR</t>
-  </si>
-  <si>
-    <t>AVDL</t>
-  </si>
-  <si>
-    <t>VKTX</t>
-  </si>
-  <si>
-    <t>HOV</t>
-  </si>
-  <si>
-    <t>KRUS</t>
-  </si>
-  <si>
-    <t>EDTXU</t>
-  </si>
-  <si>
-    <t>VRT</t>
-  </si>
-  <si>
-    <t>ODC</t>
-  </si>
-  <si>
-    <t>CLXT</t>
-  </si>
-  <si>
-    <t>AMPH</t>
-  </si>
-  <si>
-    <t>LI</t>
-  </si>
-  <si>
-    <t>INTT</t>
-  </si>
-  <si>
-    <t>AZUL</t>
-  </si>
-  <si>
-    <t>KDNY</t>
-  </si>
-  <si>
-    <t>LSEA</t>
-  </si>
-  <si>
-    <t>GOCO</t>
-  </si>
-  <si>
-    <t>ELF</t>
-  </si>
-  <si>
-    <t>IOT</t>
-  </si>
-  <si>
-    <t>EDN</t>
-  </si>
-  <si>
-    <t>EXAS</t>
-  </si>
-  <si>
-    <t>QTRX</t>
-  </si>
-  <si>
-    <t>RCEL</t>
-  </si>
-  <si>
-    <t>MSTR</t>
-  </si>
-  <si>
-    <t>SGH</t>
-  </si>
-  <si>
-    <t>USAP</t>
-  </si>
-  <si>
-    <t>PESI</t>
-  </si>
-  <si>
-    <t>GHL</t>
-  </si>
-  <si>
-    <t>W</t>
-  </si>
-  <si>
-    <t>VECT</t>
-  </si>
-  <si>
-    <t>CMPR</t>
-  </si>
-  <si>
-    <t>MDB</t>
-  </si>
-  <si>
-    <t>BZH</t>
-  </si>
-  <si>
-    <t>APP</t>
-  </si>
-  <si>
-    <t>DFH</t>
-  </si>
-  <si>
-    <t>NGMS</t>
-  </si>
-  <si>
-    <t>RXDX</t>
-  </si>
-  <si>
-    <t>RETA</t>
-  </si>
-  <si>
-    <t>TCMD</t>
-  </si>
-  <si>
-    <t>TGTX</t>
-  </si>
-  <si>
-    <t>ACLS</t>
-  </si>
-  <si>
-    <t>LTRPB</t>
-  </si>
-  <si>
-    <t>PLTR</t>
+    <t>ROOT</t>
+  </si>
+  <si>
+    <t>MEDS</t>
+  </si>
+  <si>
+    <t>PHVS</t>
+  </si>
+  <si>
+    <t>ARLO</t>
+  </si>
+  <si>
+    <t>WEAV</t>
+  </si>
+  <si>
+    <t>CABA</t>
+  </si>
+  <si>
+    <t>NVDA</t>
+  </si>
+  <si>
+    <t>SDGR</t>
+  </si>
+  <si>
+    <t>CIR</t>
+  </si>
+  <si>
+    <t>INOD</t>
   </si>
   <si>
     <t>RDFN</t>
   </si>
   <si>
-    <t>LMB</t>
-  </si>
-  <si>
-    <t>CCL</t>
-  </si>
-  <si>
-    <t>CUK</t>
-  </si>
-  <si>
-    <t>SKYW</t>
-  </si>
-  <si>
-    <t>NVTS</t>
-  </si>
-  <si>
-    <t>ROOT</t>
-  </si>
-  <si>
-    <t>EH</t>
-  </si>
-  <si>
-    <t>RXST</t>
-  </si>
-  <si>
-    <t>WEAV</t>
-  </si>
-  <si>
-    <t>MEDS</t>
-  </si>
-  <si>
-    <t>SDGR</t>
-  </si>
-  <si>
-    <t>NVDA</t>
-  </si>
-  <si>
-    <t>PHVS</t>
-  </si>
-  <si>
-    <t>CIR</t>
-  </si>
-  <si>
-    <t>CABA</t>
-  </si>
-  <si>
-    <t>ARLO</t>
-  </si>
-  <si>
-    <t>INOD</t>
+    <t>MARA</t>
   </si>
   <si>
     <t>JOBY</t>
   </si>
   <si>
+    <t>UPST</t>
+  </si>
+  <si>
     <t>MEOA</t>
   </si>
   <si>
     <t>AI</t>
   </si>
   <si>
-    <t>MARA</t>
-  </si>
-  <si>
-    <t>UPST</t>
-  </si>
-  <si>
     <t>RIOT</t>
   </si>
   <si>
@@ -1115,6 +1121,9 @@
   </si>
   <si>
     <t>AMAM</t>
+  </si>
+  <si>
+    <t>PRFX</t>
   </si>
 </sst>
 </file>
@@ -1465,7 +1474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B366"/>
+  <dimension ref="A1:B369"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1481,7 +1490,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1">
-        <v>129.0541782735251</v>
+        <v>130.4868752401933</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1489,7 +1498,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1">
-        <v>129.0765076832348</v>
+        <v>130.6365249875919</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1497,7 +1506,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1">
-        <v>129.2761272824234</v>
+        <v>130.753545722488</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1505,7 +1514,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="1">
-        <v>129.2945600354264</v>
+        <v>130.7908382444955</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1513,7 +1522,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="1">
-        <v>129.3882778015979</v>
+        <v>130.858766897102</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1521,7 +1530,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="1">
-        <v>129.4462806633313</v>
+        <v>130.8619019629713</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1529,7 +1538,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="1">
-        <v>129.4727121617203</v>
+        <v>131.0526229500746</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1537,7 +1546,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="1">
-        <v>129.5095367035595</v>
+        <v>131.1146976475468</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1545,7 +1554,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="1">
-        <v>129.5621637786964</v>
+        <v>131.1214552648555</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1553,7 +1562,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="1">
-        <v>129.5747556567092</v>
+        <v>131.1754539126597</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1561,7 +1570,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="1">
-        <v>129.6558408696833</v>
+        <v>131.1863471049425</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1569,7 +1578,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="1">
-        <v>129.6784040440995</v>
+        <v>131.206139358947</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1577,7 +1586,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="1">
-        <v>129.8519277136384</v>
+        <v>131.3486170871375</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1585,7 +1594,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="1">
-        <v>129.9525571302814</v>
+        <v>131.3604288071017</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1593,7 +1602,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="1">
-        <v>130.1113510644884</v>
+        <v>131.3772977476627</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1601,7 +1610,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="1">
-        <v>130.1578294384928</v>
+        <v>131.3927541689931</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1609,7 +1618,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="1">
-        <v>130.1654200669369</v>
+        <v>131.5673931847554</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1617,7 +1626,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="1">
-        <v>130.185106340813</v>
+        <v>131.6172117675589</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1625,7 +1634,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="1">
-        <v>130.200231266295</v>
+        <v>131.6785135826206</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1633,7 +1642,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="1">
-        <v>130.2273909541179</v>
+        <v>131.7347077714464</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1641,7 +1650,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="1">
-        <v>130.2507194747586</v>
+        <v>131.7381011056909</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1649,7 +1658,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="1">
-        <v>130.3334489712824</v>
+        <v>131.7786720867366</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1657,7 +1666,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="1">
-        <v>130.3853616497115</v>
+        <v>131.820844093639</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1665,7 +1674,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="1">
-        <v>130.3899336678149</v>
+        <v>131.83420335031</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1673,7 +1682,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="1">
-        <v>130.4545807337651</v>
+        <v>131.8973423673471</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1681,7 +1690,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="1">
-        <v>130.4695965536535</v>
+        <v>132.0285160122253</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1689,7 +1698,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="1">
-        <v>130.4714270505242</v>
+        <v>132.0626904336166</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1697,7 +1706,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="1">
-        <v>130.7160676105698</v>
+        <v>132.0634086592961</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1705,7 +1714,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="1">
-        <v>130.7169508966288</v>
+        <v>132.1209965567197</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1713,7 +1722,7 @@
         <v>31</v>
       </c>
       <c r="B31" s="1">
-        <v>130.7660396780781</v>
+        <v>132.249905584196</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1721,7 +1730,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="1">
-        <v>130.7700291824453</v>
+        <v>132.2735329667315</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1729,7 +1738,7 @@
         <v>33</v>
       </c>
       <c r="B33" s="1">
-        <v>130.7785997878308</v>
+        <v>132.2912562670783</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1737,7 +1746,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="1">
-        <v>130.8083080663185</v>
+        <v>132.3193679302368</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1745,7 +1754,7 @@
         <v>35</v>
       </c>
       <c r="B35" s="1">
-        <v>130.9535412994788</v>
+        <v>132.3773624863019</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1753,7 +1762,7 @@
         <v>36</v>
       </c>
       <c r="B36" s="1">
-        <v>130.9730752415662</v>
+        <v>132.3822147989913</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1761,7 +1770,7 @@
         <v>37</v>
       </c>
       <c r="B37" s="1">
-        <v>131.0300670700483</v>
+        <v>132.4826299610886</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1769,7 +1778,7 @@
         <v>38</v>
       </c>
       <c r="B38" s="1">
-        <v>131.0822682777914</v>
+        <v>132.7425174485702</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1777,7 +1786,7 @@
         <v>39</v>
       </c>
       <c r="B39" s="1">
-        <v>131.1165998299188</v>
+        <v>132.7518171058426</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1785,7 +1794,7 @@
         <v>40</v>
       </c>
       <c r="B40" s="1">
-        <v>131.2215194125996</v>
+        <v>132.8343214352512</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1793,7 +1802,7 @@
         <v>41</v>
       </c>
       <c r="B41" s="1">
-        <v>131.2598386985846</v>
+        <v>132.8597500739698</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -1801,7 +1810,7 @@
         <v>42</v>
       </c>
       <c r="B42" s="1">
-        <v>131.3347234044867</v>
+        <v>132.8863501378605</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -1809,7 +1818,7 @@
         <v>43</v>
       </c>
       <c r="B43" s="1">
-        <v>131.3614813108385</v>
+        <v>132.9428204710456</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1817,7 +1826,7 @@
         <v>44</v>
       </c>
       <c r="B44" s="1">
-        <v>131.3640238934641</v>
+        <v>132.9561192295088</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1825,7 +1834,7 @@
         <v>45</v>
       </c>
       <c r="B45" s="1">
-        <v>131.4518276635724</v>
+        <v>132.9756114919859</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1833,7 +1842,7 @@
         <v>46</v>
       </c>
       <c r="B46" s="1">
-        <v>131.474687678503</v>
+        <v>132.9784173760003</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -1841,7 +1850,7 @@
         <v>47</v>
       </c>
       <c r="B47" s="1">
-        <v>131.5170175142346</v>
+        <v>133.0447153959948</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -1849,7 +1858,7 @@
         <v>48</v>
       </c>
       <c r="B48" s="1">
-        <v>131.5276174997704</v>
+        <v>133.4053318417248</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1857,7 +1866,7 @@
         <v>49</v>
       </c>
       <c r="B49" s="1">
-        <v>131.627284462856</v>
+        <v>133.4180233629538</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1865,7 +1874,7 @@
         <v>50</v>
       </c>
       <c r="B50" s="1">
-        <v>131.6825042733848</v>
+        <v>133.455391248564</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1873,7 +1882,7 @@
         <v>51</v>
       </c>
       <c r="B51" s="1">
-        <v>131.7621215225137</v>
+        <v>133.5429766101482</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1881,7 +1890,7 @@
         <v>52</v>
       </c>
       <c r="B52" s="1">
-        <v>131.7737900562671</v>
+        <v>133.606933024094</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1889,7 +1898,7 @@
         <v>53</v>
       </c>
       <c r="B53" s="1">
-        <v>131.8094739899263</v>
+        <v>133.618076345044</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1897,7 +1906,7 @@
         <v>54</v>
       </c>
       <c r="B54" s="1">
-        <v>131.8318607482259</v>
+        <v>133.7349871025708</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1905,7 +1914,7 @@
         <v>55</v>
       </c>
       <c r="B55" s="1">
-        <v>131.8434556029215</v>
+        <v>133.7816468891679</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1913,7 +1922,7 @@
         <v>56</v>
       </c>
       <c r="B56" s="1">
-        <v>131.8624299761792</v>
+        <v>133.8624181634548</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1921,7 +1930,7 @@
         <v>57</v>
       </c>
       <c r="B57" s="1">
-        <v>131.9066363066477</v>
+        <v>133.8859581649071</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1929,7 +1938,7 @@
         <v>58</v>
       </c>
       <c r="B58" s="1">
-        <v>132.1574824477047</v>
+        <v>133.9265330193475</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1937,7 +1946,7 @@
         <v>59</v>
       </c>
       <c r="B59" s="1">
-        <v>132.3215704706583</v>
+        <v>133.9531972985087</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1945,7 +1954,7 @@
         <v>60</v>
       </c>
       <c r="B60" s="1">
-        <v>132.3668843475561</v>
+        <v>133.9592665205222</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1953,7 +1962,7 @@
         <v>61</v>
       </c>
       <c r="B61" s="1">
-        <v>132.3920078004651</v>
+        <v>133.9702946478169</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1961,7 +1970,7 @@
         <v>62</v>
       </c>
       <c r="B62" s="1">
-        <v>132.4042769704868</v>
+        <v>134.2274858842702</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1969,7 +1978,7 @@
         <v>63</v>
       </c>
       <c r="B63" s="1">
-        <v>132.4299553743191</v>
+        <v>134.234666218901</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1977,7 +1986,7 @@
         <v>64</v>
       </c>
       <c r="B64" s="1">
-        <v>132.4926302961666</v>
+        <v>134.2590563251207</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1985,7 +1994,7 @@
         <v>65</v>
       </c>
       <c r="B65" s="1">
-        <v>132.6075685454143</v>
+        <v>134.2925010407556</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -1993,7 +2002,7 @@
         <v>66</v>
       </c>
       <c r="B66" s="1">
-        <v>132.7107225812265</v>
+        <v>134.3144102796159</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -2001,7 +2010,7 @@
         <v>67</v>
       </c>
       <c r="B67" s="1">
-        <v>132.9599851253658</v>
+        <v>134.3637573665926</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -2009,7 +2018,7 @@
         <v>68</v>
       </c>
       <c r="B68" s="1">
-        <v>133.0115536420186</v>
+        <v>134.6983784481088</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -2017,7 +2026,7 @@
         <v>69</v>
       </c>
       <c r="B69" s="1">
-        <v>133.0372350179966</v>
+        <v>134.7637511300891</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -2025,7 +2034,7 @@
         <v>70</v>
       </c>
       <c r="B70" s="1">
-        <v>133.0570377765718</v>
+        <v>134.7965283158647</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -2033,7 +2042,7 @@
         <v>71</v>
       </c>
       <c r="B71" s="1">
-        <v>133.0665878993779</v>
+        <v>134.8774251289209</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -2041,7 +2050,7 @@
         <v>72</v>
       </c>
       <c r="B72" s="1">
-        <v>133.1027139999721</v>
+        <v>134.8831153423669</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2049,7 +2058,7 @@
         <v>73</v>
       </c>
       <c r="B73" s="1">
-        <v>133.1347396113473</v>
+        <v>134.8857080482051</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -2057,7 +2066,7 @@
         <v>74</v>
       </c>
       <c r="B74" s="1">
-        <v>133.2039684936054</v>
+        <v>134.9456555725604</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -2065,7 +2074,7 @@
         <v>75</v>
       </c>
       <c r="B75" s="1">
-        <v>133.2340922805791</v>
+        <v>134.9804635848764</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -2073,7 +2082,7 @@
         <v>76</v>
       </c>
       <c r="B76" s="1">
-        <v>133.2423659981355</v>
+        <v>134.9960291967982</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -2081,7 +2090,7 @@
         <v>77</v>
       </c>
       <c r="B77" s="1">
-        <v>133.4669688683025</v>
+        <v>135.0001188985055</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -2089,7 +2098,7 @@
         <v>78</v>
       </c>
       <c r="B78" s="1">
-        <v>133.6082060207949</v>
+        <v>135.1495570380197</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -2097,7 +2106,7 @@
         <v>79</v>
       </c>
       <c r="B79" s="1">
-        <v>133.6732742923475</v>
+        <v>135.1770809495814</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -2105,7 +2114,7 @@
         <v>80</v>
       </c>
       <c r="B80" s="1">
-        <v>133.7595732259513</v>
+        <v>135.2455553364134</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -2113,7 +2122,7 @@
         <v>81</v>
       </c>
       <c r="B81" s="1">
-        <v>133.9131433373756</v>
+        <v>135.2549302624207</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -2121,7 +2130,7 @@
         <v>82</v>
       </c>
       <c r="B82" s="1">
-        <v>133.9169893006235</v>
+        <v>135.339802845216</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -2129,7 +2138,7 @@
         <v>83</v>
       </c>
       <c r="B83" s="1">
-        <v>133.9320699866089</v>
+        <v>135.6991349137823</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -2137,7 +2146,7 @@
         <v>84</v>
       </c>
       <c r="B84" s="1">
-        <v>133.9699338545227</v>
+        <v>135.7399790156825</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -2145,7 +2154,7 @@
         <v>85</v>
       </c>
       <c r="B85" s="1">
-        <v>134.0907184415566</v>
+        <v>135.8850515203913</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -2153,7 +2162,7 @@
         <v>86</v>
       </c>
       <c r="B86" s="1">
-        <v>134.0965271647891</v>
+        <v>136.0162257766625</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -2161,7 +2170,7 @@
         <v>87</v>
       </c>
       <c r="B87" s="1">
-        <v>134.1887680409995</v>
+        <v>136.0288388457031</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -2169,7 +2178,7 @@
         <v>88</v>
       </c>
       <c r="B88" s="1">
-        <v>134.3968473154001</v>
+        <v>136.03792622528</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -2177,7 +2186,7 @@
         <v>89</v>
       </c>
       <c r="B89" s="1">
-        <v>134.5089402255208</v>
+        <v>136.2258795480038</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -2185,7 +2194,7 @@
         <v>90</v>
       </c>
       <c r="B90" s="1">
-        <v>134.7292807626116</v>
+        <v>136.2417280438983</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -2193,7 +2202,7 @@
         <v>91</v>
       </c>
       <c r="B91" s="1">
-        <v>134.7559745652222</v>
+        <v>136.3445799288037</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -2201,7 +2210,7 @@
         <v>92</v>
       </c>
       <c r="B92" s="1">
-        <v>134.7659670129065</v>
+        <v>136.4104708009492</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -2209,7 +2218,7 @@
         <v>93</v>
       </c>
       <c r="B93" s="1">
-        <v>134.7724130379996</v>
+        <v>136.4110338826474</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -2217,7 +2226,7 @@
         <v>94</v>
       </c>
       <c r="B94" s="1">
-        <v>134.7958381022236</v>
+        <v>136.5423472406811</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -2225,7 +2234,7 @@
         <v>95</v>
       </c>
       <c r="B95" s="1">
-        <v>134.8505689492338</v>
+        <v>136.5851697461995</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -2233,7 +2242,7 @@
         <v>96</v>
       </c>
       <c r="B96" s="1">
-        <v>134.9413391612674</v>
+        <v>136.6338766729932</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -2241,7 +2250,7 @@
         <v>97</v>
       </c>
       <c r="B97" s="1">
-        <v>134.9760855322643</v>
+        <v>136.7180529667098</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -2249,7 +2258,7 @@
         <v>98</v>
       </c>
       <c r="B98" s="1">
-        <v>135.0317507146535</v>
+        <v>136.8625057143158</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -2257,7 +2266,7 @@
         <v>99</v>
       </c>
       <c r="B99" s="1">
-        <v>135.0667098991066</v>
+        <v>136.8634580301458</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -2265,7 +2274,7 @@
         <v>100</v>
       </c>
       <c r="B100" s="1">
-        <v>135.1410144121253</v>
+        <v>136.8666648679079</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -2273,7 +2282,7 @@
         <v>101</v>
       </c>
       <c r="B101" s="1">
-        <v>135.3549501790971</v>
+        <v>136.9105009036798</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -2281,7 +2290,7 @@
         <v>102</v>
       </c>
       <c r="B102" s="1">
-        <v>135.3582461828401</v>
+        <v>136.929867671959</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -2289,7 +2298,7 @@
         <v>103</v>
       </c>
       <c r="B103" s="1">
-        <v>135.5605300596975</v>
+        <v>136.9530740749764</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -2297,7 +2306,7 @@
         <v>104</v>
       </c>
       <c r="B104" s="1">
-        <v>135.618279899029</v>
+        <v>137.0017119680191</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -2305,7 +2314,7 @@
         <v>105</v>
       </c>
       <c r="B105" s="1">
-        <v>135.6942966103652</v>
+        <v>137.0375592317531</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -2313,7 +2322,7 @@
         <v>106</v>
       </c>
       <c r="B106" s="1">
-        <v>135.7585485985758</v>
+        <v>137.1420559203621</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -2321,7 +2330,7 @@
         <v>107</v>
       </c>
       <c r="B107" s="1">
-        <v>136.2904369250405</v>
+        <v>137.2149423636228</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -2329,7 +2338,7 @@
         <v>108</v>
       </c>
       <c r="B108" s="1">
-        <v>136.7267366446388</v>
+        <v>137.2206070891754</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -2337,7 +2346,7 @@
         <v>109</v>
       </c>
       <c r="B109" s="1">
-        <v>136.7361507041445</v>
+        <v>137.4940630864616</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -2345,7 +2354,7 @@
         <v>110</v>
       </c>
       <c r="B110" s="1">
-        <v>136.7852893489572</v>
+        <v>137.5950422409416</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -2353,7 +2362,7 @@
         <v>111</v>
       </c>
       <c r="B111" s="1">
-        <v>136.8622751029824</v>
+        <v>137.6240168590841</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -2361,7 +2370,7 @@
         <v>112</v>
       </c>
       <c r="B112" s="1">
-        <v>137.010361641743</v>
+        <v>137.6807078737178</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -2369,7 +2378,7 @@
         <v>113</v>
       </c>
       <c r="B113" s="1">
-        <v>137.1383258340364</v>
+        <v>137.6989336084455</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -2377,7 +2386,7 @@
         <v>114</v>
       </c>
       <c r="B114" s="1">
-        <v>137.1948058403123</v>
+        <v>138.1877945363265</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -2385,7 +2394,7 @@
         <v>115</v>
       </c>
       <c r="B115" s="1">
-        <v>137.2915717849057</v>
+        <v>138.2756585823726</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -2393,7 +2402,7 @@
         <v>116</v>
       </c>
       <c r="B116" s="1">
-        <v>137.3059790948429</v>
+        <v>138.3407139438463</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -2401,7 +2410,7 @@
         <v>117</v>
       </c>
       <c r="B117" s="1">
-        <v>137.3208651143143</v>
+        <v>138.4211582361048</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -2409,7 +2418,7 @@
         <v>118</v>
       </c>
       <c r="B118" s="1">
-        <v>137.4231051544072</v>
+        <v>138.4866970059065</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -2417,7 +2426,7 @@
         <v>119</v>
       </c>
       <c r="B119" s="1">
-        <v>137.5215493880937</v>
+        <v>138.51020449617</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -2425,7 +2434,7 @@
         <v>120</v>
       </c>
       <c r="B120" s="1">
-        <v>137.5375174228025</v>
+        <v>138.5965974405061</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -2433,7 +2442,7 @@
         <v>121</v>
       </c>
       <c r="B121" s="1">
-        <v>137.7966835759719</v>
+        <v>138.6439061493694</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -2441,7 +2450,7 @@
         <v>122</v>
       </c>
       <c r="B122" s="1">
-        <v>137.8308243575617</v>
+        <v>138.7571141646627</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -2449,7 +2458,7 @@
         <v>123</v>
       </c>
       <c r="B123" s="1">
-        <v>137.8723860770333</v>
+        <v>138.7685782053862</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -2457,7 +2466,7 @@
         <v>124</v>
       </c>
       <c r="B124" s="1">
-        <v>138.0121732832238</v>
+        <v>138.8035104356895</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -2465,7 +2474,7 @@
         <v>125</v>
       </c>
       <c r="B125" s="1">
-        <v>138.0366628906603</v>
+        <v>138.8507674410837</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -2473,7 +2482,7 @@
         <v>126</v>
       </c>
       <c r="B126" s="1">
-        <v>138.0932626351901</v>
+        <v>139.0786717999565</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -2481,7 +2490,7 @@
         <v>127</v>
       </c>
       <c r="B127" s="1">
-        <v>138.1100957343923</v>
+        <v>139.3553137449881</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -2489,7 +2498,7 @@
         <v>128</v>
       </c>
       <c r="B128" s="1">
-        <v>138.1708829183355</v>
+        <v>139.4509394224665</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -2497,7 +2506,7 @@
         <v>129</v>
       </c>
       <c r="B129" s="1">
-        <v>138.2025283365322</v>
+        <v>139.5995800162935</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -2505,7 +2514,7 @@
         <v>130</v>
       </c>
       <c r="B130" s="1">
-        <v>138.230698904134</v>
+        <v>139.6430871945962</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -2513,7 +2522,7 @@
         <v>131</v>
       </c>
       <c r="B131" s="1">
-        <v>138.3080844545077</v>
+        <v>139.7111430905039</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -2521,7 +2530,7 @@
         <v>132</v>
       </c>
       <c r="B132" s="1">
-        <v>138.3471213178586</v>
+        <v>139.8026609577829</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -2529,7 +2538,7 @@
         <v>133</v>
       </c>
       <c r="B133" s="1">
-        <v>138.3620910840152</v>
+        <v>139.8209585202318</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -2537,7 +2546,7 @@
         <v>134</v>
       </c>
       <c r="B134" s="1">
-        <v>138.4579857363187</v>
+        <v>139.8939504467421</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -2545,7 +2554,7 @@
         <v>135</v>
       </c>
       <c r="B135" s="1">
-        <v>138.6741190977717</v>
+        <v>139.906775555251</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -2553,7 +2562,7 @@
         <v>136</v>
       </c>
       <c r="B136" s="1">
-        <v>138.8931213808955</v>
+        <v>139.9770606935549</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -2561,7 +2570,7 @@
         <v>137</v>
       </c>
       <c r="B137" s="1">
-        <v>138.9938848082165</v>
+        <v>139.9960415506373</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -2569,7 +2578,7 @@
         <v>138</v>
       </c>
       <c r="B138" s="1">
-        <v>139.0227745618324</v>
+        <v>140.087531310638</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -2577,7 +2586,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="1">
-        <v>139.3020539666354</v>
+        <v>140.2232973664062</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -2585,7 +2594,7 @@
         <v>140</v>
       </c>
       <c r="B140" s="1">
-        <v>139.3298571680106</v>
+        <v>140.3483678496279</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -2593,7 +2602,7 @@
         <v>141</v>
       </c>
       <c r="B141" s="1">
-        <v>139.3469161688852</v>
+        <v>140.3485557404363</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -2601,7 +2610,7 @@
         <v>142</v>
       </c>
       <c r="B142" s="1">
-        <v>139.4663992319676</v>
+        <v>140.3746133548444</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -2609,7 +2618,7 @@
         <v>143</v>
       </c>
       <c r="B143" s="1">
-        <v>139.4732893119663</v>
+        <v>140.440653367782</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -2617,7 +2626,7 @@
         <v>144</v>
       </c>
       <c r="B144" s="1">
-        <v>139.7258361550442</v>
+        <v>140.5065422606641</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -2625,7 +2634,7 @@
         <v>145</v>
       </c>
       <c r="B145" s="1">
-        <v>139.7704585671699</v>
+        <v>140.628437593084</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -2633,7 +2642,7 @@
         <v>146</v>
       </c>
       <c r="B146" s="1">
-        <v>140.0255653767337</v>
+        <v>140.7356501155672</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -2641,7 +2650,7 @@
         <v>147</v>
       </c>
       <c r="B147" s="1">
-        <v>140.0733594361162</v>
+        <v>140.8256862916625</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -2649,7 +2658,7 @@
         <v>148</v>
       </c>
       <c r="B148" s="1">
-        <v>140.0942322587645</v>
+        <v>140.8795660121339</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -2657,7 +2666,7 @@
         <v>149</v>
       </c>
       <c r="B149" s="1">
-        <v>140.4745500912956</v>
+        <v>141.0569639842882</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -2665,7 +2674,7 @@
         <v>150</v>
       </c>
       <c r="B150" s="1">
-        <v>140.7731238744024</v>
+        <v>141.1069128464913</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -2673,7 +2682,7 @@
         <v>151</v>
       </c>
       <c r="B151" s="1">
-        <v>140.7824265539416</v>
+        <v>141.1958154670565</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -2681,7 +2690,7 @@
         <v>152</v>
       </c>
       <c r="B152" s="1">
-        <v>140.8014762385119</v>
+        <v>141.2256668516544</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -2689,7 +2698,7 @@
         <v>153</v>
       </c>
       <c r="B153" s="1">
-        <v>140.8550692950035</v>
+        <v>141.2625708093179</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -2697,7 +2706,7 @@
         <v>154</v>
       </c>
       <c r="B154" s="1">
-        <v>140.9523518989892</v>
+        <v>141.3006451766136</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -2705,7 +2714,7 @@
         <v>155</v>
       </c>
       <c r="B155" s="1">
-        <v>141.0061295971914</v>
+        <v>141.4046324341625</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -2713,7 +2722,7 @@
         <v>156</v>
       </c>
       <c r="B156" s="1">
-        <v>141.0823220491047</v>
+        <v>141.4206552982397</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -2721,7 +2730,7 @@
         <v>157</v>
       </c>
       <c r="B157" s="1">
-        <v>141.2848569737029</v>
+        <v>141.4387792454595</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -2729,7 +2738,7 @@
         <v>158</v>
       </c>
       <c r="B158" s="1">
-        <v>141.3987694528706</v>
+        <v>141.5684044089679</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -2737,7 +2746,7 @@
         <v>159</v>
       </c>
       <c r="B159" s="1">
-        <v>141.677379946394</v>
+        <v>141.6161116867899</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -2745,7 +2754,7 @@
         <v>160</v>
       </c>
       <c r="B160" s="1">
-        <v>141.6773805136064</v>
+        <v>141.6510644034684</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -2753,7 +2762,7 @@
         <v>161</v>
       </c>
       <c r="B161" s="1">
-        <v>141.7159359795624</v>
+        <v>141.6587707806821</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -2761,7 +2770,7 @@
         <v>162</v>
       </c>
       <c r="B162" s="1">
-        <v>141.7755210299212</v>
+        <v>141.6771197644478</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -2769,7 +2778,7 @@
         <v>163</v>
       </c>
       <c r="B163" s="1">
-        <v>141.8287523964997</v>
+        <v>141.7247944877044</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -2777,7 +2786,7 @@
         <v>164</v>
       </c>
       <c r="B164" s="1">
-        <v>141.9495193624487</v>
+        <v>141.9242505662458</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -2785,7 +2794,7 @@
         <v>165</v>
       </c>
       <c r="B165" s="1">
-        <v>141.9648787757141</v>
+        <v>142.2461284043449</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -2793,7 +2802,7 @@
         <v>166</v>
       </c>
       <c r="B166" s="1">
-        <v>141.9695973795569</v>
+        <v>142.2660657866045</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -2801,7 +2810,7 @@
         <v>167</v>
       </c>
       <c r="B167" s="1">
-        <v>142.0221432201896</v>
+        <v>142.5913577275146</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -2809,7 +2818,7 @@
         <v>168</v>
       </c>
       <c r="B168" s="1">
-        <v>142.0509508483756</v>
+        <v>142.7682149389013</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -2817,7 +2826,7 @@
         <v>169</v>
       </c>
       <c r="B169" s="1">
-        <v>142.1380508605765</v>
+        <v>142.7769740796847</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -2825,7 +2834,7 @@
         <v>170</v>
       </c>
       <c r="B170" s="1">
-        <v>142.1444172833621</v>
+        <v>142.7772072341252</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -2833,7 +2842,7 @@
         <v>171</v>
       </c>
       <c r="B171" s="1">
-        <v>142.2609144419021</v>
+        <v>142.8030582252101</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -2841,7 +2850,7 @@
         <v>172</v>
       </c>
       <c r="B172" s="1">
-        <v>142.3935181723166</v>
+        <v>142.9079512128387</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -2849,7 +2858,7 @@
         <v>173</v>
       </c>
       <c r="B173" s="1">
-        <v>142.482238625309</v>
+        <v>142.9207598073575</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -2857,7 +2866,7 @@
         <v>174</v>
       </c>
       <c r="B174" s="1">
-        <v>142.5939375856896</v>
+        <v>142.9239304007165</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -2865,7 +2874,7 @@
         <v>175</v>
       </c>
       <c r="B175" s="1">
-        <v>142.6625444332851</v>
+        <v>143.4652562835982</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -2873,7 +2882,7 @@
         <v>176</v>
       </c>
       <c r="B176" s="1">
-        <v>142.7229339007058</v>
+        <v>143.4667154973108</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -2881,7 +2890,7 @@
         <v>177</v>
       </c>
       <c r="B177" s="1">
-        <v>142.7243839431673</v>
+        <v>143.6060919567858</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -2889,7 +2898,7 @@
         <v>178</v>
       </c>
       <c r="B178" s="1">
-        <v>142.8564829569304</v>
+        <v>143.7159331385198</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -2897,7 +2906,7 @@
         <v>179</v>
       </c>
       <c r="B179" s="1">
-        <v>142.9816703532855</v>
+        <v>143.8215703284683</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -2905,7 +2914,7 @@
         <v>180</v>
       </c>
       <c r="B180" s="1">
-        <v>143.2603215906651</v>
+        <v>143.8592658683947</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -2913,7 +2922,7 @@
         <v>181</v>
       </c>
       <c r="B181" s="1">
-        <v>143.2760351851946</v>
+        <v>143.9441540201111</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -2921,7 +2930,7 @@
         <v>182</v>
       </c>
       <c r="B182" s="1">
-        <v>143.3770062161605</v>
+        <v>144.0310599305928</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -2929,7 +2938,7 @@
         <v>183</v>
       </c>
       <c r="B183" s="1">
-        <v>143.7455009493513</v>
+        <v>144.3812576173013</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -2937,7 +2946,7 @@
         <v>184</v>
       </c>
       <c r="B184" s="1">
-        <v>143.8196059864518</v>
+        <v>144.6296193322121</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -2945,7 +2954,7 @@
         <v>185</v>
       </c>
       <c r="B185" s="1">
-        <v>144.030936886486</v>
+        <v>144.7082894170406</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -2953,7 +2962,7 @@
         <v>186</v>
       </c>
       <c r="B186" s="1">
-        <v>144.3628565063497</v>
+        <v>144.7619218793243</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -2961,7 +2970,7 @@
         <v>187</v>
       </c>
       <c r="B187" s="1">
-        <v>144.3667618166908</v>
+        <v>144.900531498821</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -2969,7 +2978,7 @@
         <v>188</v>
       </c>
       <c r="B188" s="1">
-        <v>144.3793005371247</v>
+        <v>144.9718432923428</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -2977,7 +2986,7 @@
         <v>189</v>
       </c>
       <c r="B189" s="1">
-        <v>144.4817672926994</v>
+        <v>145.0110270938888</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -2985,7 +2994,7 @@
         <v>190</v>
       </c>
       <c r="B190" s="1">
-        <v>144.7418221849207</v>
+        <v>145.1315401574591</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -2993,7 +3002,7 @@
         <v>191</v>
       </c>
       <c r="B191" s="1">
-        <v>144.9305695976536</v>
+        <v>145.3445901710574</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -3001,7 +3010,7 @@
         <v>192</v>
       </c>
       <c r="B192" s="1">
-        <v>145.0637348273295</v>
+        <v>145.4620563240676</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -3009,7 +3018,7 @@
         <v>193</v>
       </c>
       <c r="B193" s="1">
-        <v>145.4113956062375</v>
+        <v>145.4778827199088</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -3017,7 +3026,7 @@
         <v>194</v>
       </c>
       <c r="B194" s="1">
-        <v>145.5367128931396</v>
+        <v>145.549133276064</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -3025,7 +3034,7 @@
         <v>195</v>
       </c>
       <c r="B195" s="1">
-        <v>145.5514675908328</v>
+        <v>145.6312400891725</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -3033,7 +3042,7 @@
         <v>196</v>
       </c>
       <c r="B196" s="1">
-        <v>145.5615527780312</v>
+        <v>145.7469695643437</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -3041,7 +3050,7 @@
         <v>197</v>
       </c>
       <c r="B197" s="1">
-        <v>145.7099542041203</v>
+        <v>145.8880896327759</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -3049,7 +3058,7 @@
         <v>198</v>
       </c>
       <c r="B198" s="1">
-        <v>146.0710362074236</v>
+        <v>145.9411713567546</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -3057,7 +3066,7 @@
         <v>199</v>
       </c>
       <c r="B199" s="1">
-        <v>146.2230723208792</v>
+        <v>145.9649249741741</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -3065,7 +3074,7 @@
         <v>200</v>
       </c>
       <c r="B200" s="1">
-        <v>146.3253037090889</v>
+        <v>146.0232557876939</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -3073,7 +3082,7 @@
         <v>201</v>
       </c>
       <c r="B201" s="1">
-        <v>146.3628011893166</v>
+        <v>146.0960268006589</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -3081,7 +3090,7 @@
         <v>202</v>
       </c>
       <c r="B202" s="1">
-        <v>146.4267373914498</v>
+        <v>146.4210553002168</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -3089,7 +3098,7 @@
         <v>203</v>
       </c>
       <c r="B203" s="1">
-        <v>146.4474740806352</v>
+        <v>146.609469287127</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -3097,7 +3106,7 @@
         <v>204</v>
       </c>
       <c r="B204" s="1">
-        <v>146.6590373641567</v>
+        <v>146.618830036765</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -3105,7 +3114,7 @@
         <v>205</v>
       </c>
       <c r="B205" s="1">
-        <v>146.7193950997101</v>
+        <v>146.6300595650501</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -3113,7 +3122,7 @@
         <v>206</v>
       </c>
       <c r="B206" s="1">
-        <v>146.7477045455248</v>
+        <v>146.9177979031219</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -3121,7 +3130,7 @@
         <v>207</v>
       </c>
       <c r="B207" s="1">
-        <v>146.7655707104884</v>
+        <v>146.9470351554011</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -3129,7 +3138,7 @@
         <v>208</v>
       </c>
       <c r="B208" s="1">
-        <v>147.2278414277113</v>
+        <v>147.1261494758413</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -3137,7 +3146,7 @@
         <v>209</v>
       </c>
       <c r="B209" s="1">
-        <v>147.2736635748718</v>
+        <v>147.1620940082197</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -3145,7 +3154,7 @@
         <v>210</v>
       </c>
       <c r="B210" s="1">
-        <v>147.5735103663524</v>
+        <v>147.5055430759965</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -3153,7 +3162,7 @@
         <v>211</v>
       </c>
       <c r="B211" s="1">
-        <v>147.6096504960536</v>
+        <v>147.5892701251681</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -3161,7 +3170,7 @@
         <v>212</v>
       </c>
       <c r="B212" s="1">
-        <v>147.7790905503738</v>
+        <v>147.6484443731759</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -3169,7 +3178,7 @@
         <v>213</v>
       </c>
       <c r="B213" s="1">
-        <v>148.2476676268066</v>
+        <v>147.7218641037902</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -3177,7 +3186,7 @@
         <v>214</v>
       </c>
       <c r="B214" s="1">
-        <v>148.4148102379007</v>
+        <v>148.1669075477361</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -3185,7 +3194,7 @@
         <v>215</v>
       </c>
       <c r="B215" s="1">
-        <v>148.4459551111864</v>
+        <v>148.2450341450622</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -3193,7 +3202,7 @@
         <v>216</v>
       </c>
       <c r="B216" s="1">
-        <v>148.5112389921572</v>
+        <v>148.3966703136136</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -3201,7 +3210,7 @@
         <v>217</v>
       </c>
       <c r="B217" s="1">
-        <v>148.5855292328461</v>
+        <v>148.4067976949974</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -3209,7 +3218,7 @@
         <v>218</v>
       </c>
       <c r="B218" s="1">
-        <v>149.0167295649792</v>
+        <v>148.4136434324771</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -3217,7 +3226,7 @@
         <v>219</v>
       </c>
       <c r="B219" s="1">
-        <v>149.3698512375906</v>
+        <v>148.9468252019111</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -3225,7 +3234,7 @@
         <v>220</v>
       </c>
       <c r="B220" s="1">
-        <v>149.3865368499017</v>
+        <v>149.0213623652791</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -3233,7 +3242,7 @@
         <v>221</v>
       </c>
       <c r="B221" s="1">
-        <v>149.4358592524264</v>
+        <v>149.473024430074</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -3241,7 +3250,7 @@
         <v>222</v>
       </c>
       <c r="B222" s="1">
-        <v>149.6003248189962</v>
+        <v>149.6824656618896</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -3249,7 +3258,7 @@
         <v>223</v>
       </c>
       <c r="B223" s="1">
-        <v>149.7566817109066</v>
+        <v>150.0492026666304</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -3257,7 +3266,7 @@
         <v>224</v>
       </c>
       <c r="B224" s="1">
-        <v>149.7654752724847</v>
+        <v>150.1477084628251</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -3265,7 +3274,7 @@
         <v>225</v>
       </c>
       <c r="B225" s="1">
-        <v>149.8420154480939</v>
+        <v>150.1993502467734</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -3273,7 +3282,7 @@
         <v>226</v>
       </c>
       <c r="B226" s="1">
-        <v>149.8486033662496</v>
+        <v>150.3101217111794</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -3281,7 +3290,7 @@
         <v>227</v>
       </c>
       <c r="B227" s="1">
-        <v>150.0146496484822</v>
+        <v>150.5355141758329</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -3289,7 +3298,7 @@
         <v>228</v>
       </c>
       <c r="B228" s="1">
-        <v>150.0827551102319</v>
+        <v>150.645477427521</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -3297,7 +3306,7 @@
         <v>229</v>
       </c>
       <c r="B229" s="1">
-        <v>150.5905981147945</v>
+        <v>150.6899197247542</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -3305,7 +3314,7 @@
         <v>230</v>
       </c>
       <c r="B230" s="1">
-        <v>150.6541503549409</v>
+        <v>150.8105142178837</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -3313,7 +3322,7 @@
         <v>231</v>
       </c>
       <c r="B231" s="1">
-        <v>150.8627972903009</v>
+        <v>150.8894088828394</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -3321,7 +3330,7 @@
         <v>232</v>
       </c>
       <c r="B232" s="1">
-        <v>150.9685591017775</v>
+        <v>150.9575199558835</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -3329,7 +3338,7 @@
         <v>233</v>
       </c>
       <c r="B233" s="1">
-        <v>151.251362440944</v>
+        <v>150.9637031554629</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -3337,7 +3346,7 @@
         <v>234</v>
       </c>
       <c r="B234" s="1">
-        <v>151.2517859533364</v>
+        <v>150.9791037994039</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -3345,7 +3354,7 @@
         <v>235</v>
       </c>
       <c r="B235" s="1">
-        <v>151.3026948622085</v>
+        <v>150.9853885011604</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -3353,7 +3362,7 @@
         <v>236</v>
       </c>
       <c r="B236" s="1">
-        <v>151.355385670096</v>
+        <v>151.0763943520546</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -3361,7 +3370,7 @@
         <v>237</v>
       </c>
       <c r="B237" s="1">
-        <v>151.7779392263806</v>
+        <v>151.1001345514663</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -3369,7 +3378,7 @@
         <v>238</v>
       </c>
       <c r="B238" s="1">
-        <v>151.8960436055272</v>
+        <v>151.3124496785799</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -3377,7 +3386,7 @@
         <v>239</v>
       </c>
       <c r="B239" s="1">
-        <v>152.1464460765735</v>
+        <v>151.4253227512033</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -3385,7 +3394,7 @@
         <v>240</v>
       </c>
       <c r="B240" s="1">
-        <v>152.4041496548522</v>
+        <v>151.4766083595992</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -3393,7 +3402,7 @@
         <v>241</v>
       </c>
       <c r="B241" s="1">
-        <v>152.9261279415256</v>
+        <v>151.5086337840906</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -3401,7 +3410,7 @@
         <v>242</v>
       </c>
       <c r="B242" s="1">
-        <v>153.0475889807217</v>
+        <v>151.708502569371</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -3409,7 +3418,7 @@
         <v>243</v>
       </c>
       <c r="B243" s="1">
-        <v>153.1339100849972</v>
+        <v>151.7300167863497</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -3417,7 +3426,7 @@
         <v>244</v>
       </c>
       <c r="B244" s="1">
-        <v>153.4821112917333</v>
+        <v>151.905518121769</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -3425,7 +3434,7 @@
         <v>245</v>
       </c>
       <c r="B245" s="1">
-        <v>153.4916157469542</v>
+        <v>152.2920661871823</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -3433,7 +3442,7 @@
         <v>246</v>
       </c>
       <c r="B246" s="1">
-        <v>153.5855467526802</v>
+        <v>152.3520721129422</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -3441,7 +3450,7 @@
         <v>247</v>
       </c>
       <c r="B247" s="1">
-        <v>153.9688831577192</v>
+        <v>152.6078582155396</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -3449,7 +3458,7 @@
         <v>248</v>
       </c>
       <c r="B248" s="1">
-        <v>153.979192738138</v>
+        <v>153.8756735686069</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -3457,7 +3466,7 @@
         <v>249</v>
       </c>
       <c r="B249" s="1">
-        <v>154.0793954262433</v>
+        <v>154.1600892758226</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -3465,7 +3474,7 @@
         <v>250</v>
       </c>
       <c r="B250" s="1">
-        <v>154.1966146608536</v>
+        <v>154.2327565694047</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -3473,7 +3482,7 @@
         <v>251</v>
       </c>
       <c r="B251" s="1">
-        <v>154.5572063984703</v>
+        <v>154.252015360337</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -3481,7 +3490,7 @@
         <v>252</v>
       </c>
       <c r="B252" s="1">
-        <v>154.5965599773032</v>
+        <v>154.3948777935419</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -3489,7 +3498,7 @@
         <v>253</v>
       </c>
       <c r="B253" s="1">
-        <v>154.7370324124328</v>
+        <v>154.4685559462872</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -3497,7 +3506,7 @@
         <v>254</v>
       </c>
       <c r="B254" s="1">
-        <v>154.9331759795698</v>
+        <v>154.6003353282635</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -3505,7 +3514,7 @@
         <v>255</v>
       </c>
       <c r="B255" s="1">
-        <v>155.0298207201392</v>
+        <v>154.6018814657929</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -3513,7 +3522,7 @@
         <v>256</v>
       </c>
       <c r="B256" s="1">
-        <v>155.4781320560821</v>
+        <v>154.6083710380927</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -3521,7 +3530,7 @@
         <v>257</v>
       </c>
       <c r="B257" s="1">
-        <v>155.8074803280858</v>
+        <v>155.3026895802803</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -3529,7 +3538,7 @@
         <v>258</v>
       </c>
       <c r="B258" s="1">
-        <v>156.1443324953716</v>
+        <v>155.6617700295029</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -3537,7 +3546,7 @@
         <v>259</v>
       </c>
       <c r="B259" s="1">
-        <v>156.6042721855946</v>
+        <v>156.269461302709</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -3545,7 +3554,7 @@
         <v>260</v>
       </c>
       <c r="B260" s="1">
-        <v>156.8636856267785</v>
+        <v>156.3811840841785</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -3553,7 +3562,7 @@
         <v>261</v>
       </c>
       <c r="B261" s="1">
-        <v>157.1364734993087</v>
+        <v>156.4844871611789</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -3561,7 +3570,7 @@
         <v>262</v>
       </c>
       <c r="B262" s="1">
-        <v>157.3222944623957</v>
+        <v>156.71448965825</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -3569,7 +3578,7 @@
         <v>263</v>
       </c>
       <c r="B263" s="1">
-        <v>157.3720598656632</v>
+        <v>156.9596804566893</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -3577,7 +3586,7 @@
         <v>264</v>
       </c>
       <c r="B264" s="1">
-        <v>157.7552494244354</v>
+        <v>156.9924778239875</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -3585,7 +3594,7 @@
         <v>265</v>
       </c>
       <c r="B265" s="1">
-        <v>157.8519975762594</v>
+        <v>157.3207984664355</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -3593,7 +3602,7 @@
         <v>266</v>
       </c>
       <c r="B266" s="1">
-        <v>157.8719826700831</v>
+        <v>157.5136453359733</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -3601,7 +3610,7 @@
         <v>267</v>
       </c>
       <c r="B267" s="1">
-        <v>158.053578720336</v>
+        <v>157.9963212041921</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -3609,7 +3618,7 @@
         <v>268</v>
       </c>
       <c r="B268" s="1">
-        <v>158.2882085888576</v>
+        <v>158.1300521386454</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -3617,7 +3626,7 @@
         <v>269</v>
       </c>
       <c r="B269" s="1">
-        <v>158.7565528062396</v>
+        <v>159.0841880240827</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -3625,7 +3634,7 @@
         <v>270</v>
       </c>
       <c r="B270" s="1">
-        <v>158.8872798948115</v>
+        <v>159.8288978874638</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -3633,7 +3642,7 @@
         <v>271</v>
       </c>
       <c r="B271" s="1">
-        <v>159.2822738705949</v>
+        <v>159.9539834285392</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -3641,7 +3650,7 @@
         <v>272</v>
       </c>
       <c r="B272" s="1">
-        <v>159.4616811743895</v>
+        <v>159.9647300892068</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -3649,7 +3658,7 @@
         <v>273</v>
       </c>
       <c r="B273" s="1">
-        <v>159.9735762629195</v>
+        <v>160.2053683329975</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -3657,7 +3666,7 @@
         <v>274</v>
       </c>
       <c r="B274" s="1">
-        <v>160.2379715636833</v>
+        <v>160.7580139054633</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -3665,7 +3674,7 @@
         <v>275</v>
       </c>
       <c r="B275" s="1">
-        <v>160.3328479595493</v>
+        <v>161.2535662379121</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -3673,7 +3682,7 @@
         <v>276</v>
       </c>
       <c r="B276" s="1">
-        <v>160.8054733595782</v>
+        <v>161.4619054436921</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -3681,7 +3690,7 @@
         <v>277</v>
       </c>
       <c r="B277" s="1">
-        <v>160.837095377664</v>
+        <v>161.5597999942993</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -3689,7 +3698,7 @@
         <v>278</v>
       </c>
       <c r="B278" s="1">
-        <v>161.0776537017498</v>
+        <v>161.8455923485839</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -3697,7 +3706,7 @@
         <v>279</v>
       </c>
       <c r="B279" s="1">
-        <v>161.0886095780536</v>
+        <v>161.8891411155313</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -3705,7 +3714,7 @@
         <v>280</v>
       </c>
       <c r="B280" s="1">
-        <v>162.5170134959479</v>
+        <v>161.927401454433</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -3713,7 +3722,7 @@
         <v>281</v>
       </c>
       <c r="B281" s="1">
-        <v>163.1024209838261</v>
+        <v>163.0371095703058</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -3721,7 +3730,7 @@
         <v>282</v>
       </c>
       <c r="B282" s="1">
-        <v>163.3549563776196</v>
+        <v>163.17444214829</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -3729,7 +3738,7 @@
         <v>283</v>
       </c>
       <c r="B283" s="1">
-        <v>163.8926870827923</v>
+        <v>163.2382418676684</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -3737,7 +3746,7 @@
         <v>284</v>
       </c>
       <c r="B284" s="1">
-        <v>163.8988138492714</v>
+        <v>163.2795561388018</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -3745,7 +3754,7 @@
         <v>285</v>
       </c>
       <c r="B285" s="1">
-        <v>164.0419552831832</v>
+        <v>163.3710721380043</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -3753,7 +3762,7 @@
         <v>286</v>
       </c>
       <c r="B286" s="1">
-        <v>164.1004582460421</v>
+        <v>163.4535082713533</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -3761,7 +3770,7 @@
         <v>287</v>
       </c>
       <c r="B287" s="1">
-        <v>164.4877783613834</v>
+        <v>164.004901331472</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -3769,7 +3778,7 @@
         <v>288</v>
       </c>
       <c r="B288" s="1">
-        <v>165.2762431757478</v>
+        <v>164.0599612611061</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -3777,7 +3786,7 @@
         <v>289</v>
       </c>
       <c r="B289" s="1">
-        <v>165.4509884250156</v>
+        <v>164.5686930407567</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -3785,7 +3794,7 @@
         <v>290</v>
       </c>
       <c r="B290" s="1">
-        <v>166.0329249503166</v>
+        <v>164.7311626574242</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -3793,7 +3802,7 @@
         <v>291</v>
       </c>
       <c r="B291" s="1">
-        <v>166.1027834432078</v>
+        <v>164.8394018521705</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -3801,7 +3810,7 @@
         <v>292</v>
       </c>
       <c r="B292" s="1">
-        <v>166.7644048742971</v>
+        <v>164.8731496656783</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -3809,7 +3818,7 @@
         <v>293</v>
       </c>
       <c r="B293" s="1">
-        <v>166.8264988593442</v>
+        <v>165.4870833950229</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -3817,7 +3826,7 @@
         <v>294</v>
       </c>
       <c r="B294" s="1">
-        <v>167.3271997739132</v>
+        <v>165.5519884010992</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -3825,7 +3834,7 @@
         <v>295</v>
       </c>
       <c r="B295" s="1">
-        <v>167.7014381730259</v>
+        <v>167.2323068177305</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -3833,7 +3842,7 @@
         <v>296</v>
       </c>
       <c r="B296" s="1">
-        <v>170.1953737706039</v>
+        <v>167.7348610695898</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -3841,7 +3850,7 @@
         <v>297</v>
       </c>
       <c r="B297" s="1">
-        <v>170.3538145342497</v>
+        <v>168.0790200670218</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -3849,7 +3858,7 @@
         <v>298</v>
       </c>
       <c r="B298" s="1">
-        <v>170.9425796010347</v>
+        <v>168.1558165004512</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -3857,7 +3866,7 @@
         <v>299</v>
       </c>
       <c r="B299" s="1">
-        <v>171.2141206355402</v>
+        <v>168.6291700609935</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -3865,7 +3874,7 @@
         <v>300</v>
       </c>
       <c r="B300" s="1">
-        <v>171.3953756361307</v>
+        <v>168.9476128216828</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -3873,7 +3882,7 @@
         <v>301</v>
       </c>
       <c r="B301" s="1">
-        <v>171.5646357721439</v>
+        <v>170.7109438438289</v>
       </c>
     </row>
     <row r="302" spans="1:2">
@@ -3881,7 +3890,7 @@
         <v>302</v>
       </c>
       <c r="B302" s="1">
-        <v>171.7067482698571</v>
+        <v>170.9471991350086</v>
       </c>
     </row>
     <row r="303" spans="1:2">
@@ -3889,7 +3898,7 @@
         <v>303</v>
       </c>
       <c r="B303" s="1">
-        <v>172.4094727159224</v>
+        <v>171.8213109448897</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -3897,7 +3906,7 @@
         <v>304</v>
       </c>
       <c r="B304" s="1">
-        <v>172.498187496699</v>
+        <v>172.0525568004913</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -3905,7 +3914,7 @@
         <v>305</v>
       </c>
       <c r="B305" s="1">
-        <v>172.5736008757729</v>
+        <v>172.9739813215777</v>
       </c>
     </row>
     <row r="306" spans="1:2">
@@ -3913,7 +3922,7 @@
         <v>306</v>
       </c>
       <c r="B306" s="1">
-        <v>173.3870445201975</v>
+        <v>173.5287224213129</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -3921,7 +3930,7 @@
         <v>307</v>
       </c>
       <c r="B307" s="1">
-        <v>174.3356896242827</v>
+        <v>173.8469730188513</v>
       </c>
     </row>
     <row r="308" spans="1:2">
@@ -3929,7 +3938,7 @@
         <v>308</v>
       </c>
       <c r="B308" s="1">
-        <v>174.418983046675</v>
+        <v>174.2487607349872</v>
       </c>
     </row>
     <row r="309" spans="1:2">
@@ -3937,7 +3946,7 @@
         <v>309</v>
       </c>
       <c r="B309" s="1">
-        <v>174.4687727168251</v>
+        <v>174.4171073700907</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -3945,7 +3954,7 @@
         <v>310</v>
       </c>
       <c r="B310" s="1">
-        <v>174.9169322670169</v>
+        <v>177.0189177543051</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -3953,7 +3962,7 @@
         <v>311</v>
       </c>
       <c r="B311" s="1">
-        <v>176.1239357824899</v>
+        <v>177.0984002931595</v>
       </c>
     </row>
     <row r="312" spans="1:2">
@@ -3961,7 +3970,7 @@
         <v>312</v>
       </c>
       <c r="B312" s="1">
-        <v>176.3085306488119</v>
+        <v>177.1582505079601</v>
       </c>
     </row>
     <row r="313" spans="1:2">
@@ -3969,7 +3978,7 @@
         <v>313</v>
       </c>
       <c r="B313" s="1">
-        <v>176.6667899350075</v>
+        <v>179.3192113113045</v>
       </c>
     </row>
     <row r="314" spans="1:2">
@@ -3977,7 +3986,7 @@
         <v>314</v>
       </c>
       <c r="B314" s="1">
-        <v>176.9111186190079</v>
+        <v>179.3939986394354</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -3985,7 +3994,7 @@
         <v>315</v>
       </c>
       <c r="B315" s="1">
-        <v>177.0189668669418</v>
+        <v>179.480617254217</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -3993,7 +4002,7 @@
         <v>316</v>
       </c>
       <c r="B316" s="1">
-        <v>178.6847351000755</v>
+        <v>180.1643099701507</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -4001,7 +4010,7 @@
         <v>317</v>
       </c>
       <c r="B317" s="1">
-        <v>179.1372387705821</v>
+        <v>180.1858302979921</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -4009,7 +4018,7 @@
         <v>318</v>
       </c>
       <c r="B318" s="1">
-        <v>179.3819351570838</v>
+        <v>181.3191028228078</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -4017,7 +4026,7 @@
         <v>319</v>
       </c>
       <c r="B319" s="1">
-        <v>179.6034849603488</v>
+        <v>181.4447829658757</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -4025,7 +4034,7 @@
         <v>320</v>
       </c>
       <c r="B320" s="1">
-        <v>180.7429718743477</v>
+        <v>185.0771514550568</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -4033,7 +4042,7 @@
         <v>321</v>
       </c>
       <c r="B321" s="1">
-        <v>181.1433756901792</v>
+        <v>185.8814126436308</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -4041,7 +4050,7 @@
         <v>322</v>
       </c>
       <c r="B322" s="1">
-        <v>183.2295331935385</v>
+        <v>186.0158227849384</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -4049,7 +4058,7 @@
         <v>323</v>
       </c>
       <c r="B323" s="1">
-        <v>183.950223457789</v>
+        <v>186.7020197528608</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -4057,7 +4066,7 @@
         <v>324</v>
       </c>
       <c r="B324" s="1">
-        <v>184.9127653256874</v>
+        <v>186.8708048136772</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -4065,7 +4074,7 @@
         <v>325</v>
       </c>
       <c r="B325" s="1">
-        <v>186.0535372051724</v>
+        <v>187.2069071719741</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -4073,7 +4082,7 @@
         <v>326</v>
       </c>
       <c r="B326" s="1">
-        <v>186.8369671361897</v>
+        <v>189.7452927007889</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -4081,7 +4090,7 @@
         <v>327</v>
       </c>
       <c r="B327" s="1">
-        <v>188.1703394893809</v>
+        <v>190.0556527108427</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -4089,7 +4098,7 @@
         <v>328</v>
       </c>
       <c r="B328" s="1">
-        <v>188.3346797334197</v>
+        <v>190.1349517280545</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -4097,7 +4106,7 @@
         <v>329</v>
       </c>
       <c r="B329" s="1">
-        <v>189.2093642739584</v>
+        <v>191.8613798621345</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -4105,7 +4114,7 @@
         <v>330</v>
       </c>
       <c r="B330" s="1">
-        <v>193.0958122157078</v>
+        <v>192.0021883266455</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -4113,7 +4122,7 @@
         <v>331</v>
       </c>
       <c r="B331" s="1">
-        <v>193.2290239152157</v>
+        <v>192.5943176259993</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -4121,7 +4130,7 @@
         <v>332</v>
       </c>
       <c r="B332" s="1">
-        <v>193.8543287823771</v>
+        <v>194.7137762758161</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -4129,7 +4138,7 @@
         <v>333</v>
       </c>
       <c r="B333" s="1">
-        <v>196.3493010982699</v>
+        <v>195.5035144903562</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -4137,7 +4146,7 @@
         <v>334</v>
       </c>
       <c r="B334" s="1">
-        <v>196.7873957383791</v>
+        <v>196.0315747740466</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -4145,7 +4154,7 @@
         <v>335</v>
       </c>
       <c r="B335" s="1">
-        <v>197.9796522460255</v>
+        <v>196.7304819544939</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -4153,7 +4162,7 @@
         <v>336</v>
       </c>
       <c r="B336" s="1">
-        <v>199.082390235406</v>
+        <v>197.1671883711335</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -4161,7 +4170,7 @@
         <v>337</v>
       </c>
       <c r="B337" s="1">
-        <v>201.2703406423917</v>
+        <v>197.7721212007041</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -4169,7 +4178,7 @@
         <v>338</v>
       </c>
       <c r="B338" s="1">
-        <v>201.8110857938627</v>
+        <v>199.1188109960168</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -4177,7 +4186,7 @@
         <v>339</v>
       </c>
       <c r="B339" s="1">
-        <v>202.9816004424655</v>
+        <v>199.2145124429223</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -4185,7 +4194,7 @@
         <v>340</v>
       </c>
       <c r="B340" s="1">
-        <v>204.0515126185103</v>
+        <v>199.4448679790632</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -4193,7 +4202,7 @@
         <v>341</v>
       </c>
       <c r="B341" s="1">
-        <v>206.5388326169519</v>
+        <v>201.0842312111908</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -4201,7 +4210,7 @@
         <v>342</v>
       </c>
       <c r="B342" s="1">
-        <v>207.7500756598931</v>
+        <v>202.1831157205901</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -4209,7 +4218,7 @@
         <v>343</v>
       </c>
       <c r="B343" s="1">
-        <v>207.9032889763585</v>
+        <v>203.1752825231409</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -4217,7 +4226,7 @@
         <v>344</v>
       </c>
       <c r="B344" s="1">
-        <v>211.8565612456653</v>
+        <v>203.8219671485625</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -4225,7 +4234,7 @@
         <v>345</v>
       </c>
       <c r="B345" s="1">
-        <v>214.5281051660122</v>
+        <v>205.202990436334</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -4233,7 +4242,7 @@
         <v>346</v>
       </c>
       <c r="B346" s="1">
-        <v>216.4992247055354</v>
+        <v>206.8254515770182</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -4241,7 +4250,7 @@
         <v>347</v>
       </c>
       <c r="B347" s="1">
-        <v>219.0776468395092</v>
+        <v>210.8055761729698</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -4249,7 +4258,7 @@
         <v>348</v>
       </c>
       <c r="B348" s="1">
-        <v>223.2657737352902</v>
+        <v>213.8394836447769</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -4257,7 +4266,7 @@
         <v>349</v>
       </c>
       <c r="B349" s="1">
-        <v>226.2214757404459</v>
+        <v>215.514735130629</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -4265,7 +4274,7 @@
         <v>350</v>
       </c>
       <c r="B350" s="1">
-        <v>231.5400678363424</v>
+        <v>217.5750621378892</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -4273,7 +4282,7 @@
         <v>351</v>
       </c>
       <c r="B351" s="1">
-        <v>236.6186016987529</v>
+        <v>225.4136844092101</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -4281,7 +4290,7 @@
         <v>352</v>
       </c>
       <c r="B352" s="1">
-        <v>242.8801622928327</v>
+        <v>226.7055263452704</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -4289,7 +4298,7 @@
         <v>353</v>
       </c>
       <c r="B353" s="1">
-        <v>246.7788468966484</v>
+        <v>234.3649565056661</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -4297,7 +4306,7 @@
         <v>354</v>
       </c>
       <c r="B354" s="1">
-        <v>250.1797147678629</v>
+        <v>238.6078132078231</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -4305,7 +4314,7 @@
         <v>355</v>
       </c>
       <c r="B355" s="1">
-        <v>254.9417355238852</v>
+        <v>239.3360672016524</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -4313,7 +4322,7 @@
         <v>356</v>
       </c>
       <c r="B356" s="1">
-        <v>265.6965223112458</v>
+        <v>244.2000430188477</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -4321,7 +4330,7 @@
         <v>357</v>
       </c>
       <c r="B357" s="1">
-        <v>265.9410216655157</v>
+        <v>246.6848878556057</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -4329,7 +4338,7 @@
         <v>358</v>
       </c>
       <c r="B358" s="1">
-        <v>275.8800835152222</v>
+        <v>256.1870265265885</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -4337,7 +4346,7 @@
         <v>359</v>
       </c>
       <c r="B359" s="1">
-        <v>275.9478690241664</v>
+        <v>262.5401501524642</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -4345,7 +4354,7 @@
         <v>360</v>
       </c>
       <c r="B360" s="1">
-        <v>289.7904230059646</v>
+        <v>263.3466004210608</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -4353,7 +4362,7 @@
         <v>361</v>
       </c>
       <c r="B361" s="1">
-        <v>296.7502076119106</v>
+        <v>266.5758812525153</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -4361,7 +4370,7 @@
         <v>362</v>
       </c>
       <c r="B362" s="1">
-        <v>310.3115013690099</v>
+        <v>294.3008197005457</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -4369,7 +4378,7 @@
         <v>363</v>
       </c>
       <c r="B363" s="1">
-        <v>314.4204001179268</v>
+        <v>296.4510310708426</v>
       </c>
     </row>
     <row r="364" spans="1:2">
@@ -4377,7 +4386,7 @@
         <v>364</v>
       </c>
       <c r="B364" s="1">
-        <v>385.7545853160398</v>
+        <v>320.8465976510635</v>
       </c>
     </row>
     <row r="365" spans="1:2">
@@ -4385,7 +4394,7 @@
         <v>365</v>
       </c>
       <c r="B365" s="1">
-        <v>407.8159374801271</v>
+        <v>325.9014186056987</v>
       </c>
     </row>
     <row r="366" spans="1:2">
@@ -4393,7 +4402,31 @@
         <v>366</v>
       </c>
       <c r="B366" s="1">
-        <v>542.8471944563681</v>
+        <v>382.5463494712144</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2">
+      <c r="A367" t="s">
+        <v>367</v>
+      </c>
+      <c r="B367" s="1">
+        <v>386.4418995890168</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2">
+      <c r="A368" t="s">
+        <v>368</v>
+      </c>
+      <c r="B368" s="1">
+        <v>538.5505230327528</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2">
+      <c r="A369" t="s">
+        <v>369</v>
+      </c>
+      <c r="B369" s="1">
+        <v>2948.165655424706</v>
       </c>
     </row>
   </sheetData>

--- a/Screener/data/rs_rating_top_30.xlsx
+++ b/Screener/data/rs_rating_top_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="369">
   <si>
     <t>Symbol</t>
   </si>
@@ -22,1108 +22,1105 @@
     <t>RS Rating</t>
   </si>
   <si>
-    <t>CLH</t>
+    <t>ORCL</t>
+  </si>
+  <si>
+    <t>SNPS</t>
+  </si>
+  <si>
+    <t>MTR</t>
+  </si>
+  <si>
+    <t>LSCC</t>
+  </si>
+  <si>
+    <t>DELL</t>
+  </si>
+  <si>
+    <t>MLCO</t>
+  </si>
+  <si>
+    <t>PUBM</t>
+  </si>
+  <si>
+    <t>AEIS</t>
+  </si>
+  <si>
+    <t>HOOD</t>
+  </si>
+  <si>
+    <t>WCC</t>
+  </si>
+  <si>
+    <t>CSTM</t>
+  </si>
+  <si>
+    <t>RAMP</t>
+  </si>
+  <si>
+    <t>CRMT</t>
+  </si>
+  <si>
+    <t>MACK</t>
+  </si>
+  <si>
+    <t>PRO</t>
+  </si>
+  <si>
+    <t>MOMO</t>
+  </si>
+  <si>
+    <t>GE</t>
+  </si>
+  <si>
+    <t>WST</t>
+  </si>
+  <si>
+    <t>TSM</t>
+  </si>
+  <si>
+    <t>RCMT</t>
+  </si>
+  <si>
+    <t>IGT</t>
+  </si>
+  <si>
+    <t>CDNS</t>
+  </si>
+  <si>
+    <t>PAM</t>
+  </si>
+  <si>
+    <t>NPO</t>
+  </si>
+  <si>
+    <t>TXG</t>
+  </si>
+  <si>
+    <t>PHG</t>
+  </si>
+  <si>
+    <t>MPX</t>
+  </si>
+  <si>
+    <t>BOOT</t>
+  </si>
+  <si>
+    <t>GH</t>
+  </si>
+  <si>
+    <t>RKT</t>
   </si>
   <si>
     <t>CCS</t>
   </si>
   <si>
+    <t>TEX</t>
+  </si>
+  <si>
+    <t>GNRC</t>
+  </si>
+  <si>
+    <t>SPSC</t>
+  </si>
+  <si>
+    <t>OII</t>
+  </si>
+  <si>
+    <t>FND</t>
+  </si>
+  <si>
+    <t>LASR</t>
+  </si>
+  <si>
+    <t>TWN</t>
+  </si>
+  <si>
+    <t>TMDX</t>
+  </si>
+  <si>
+    <t>PKOH</t>
+  </si>
+  <si>
+    <t>RCLFU</t>
+  </si>
+  <si>
+    <t>ATI</t>
+  </si>
+  <si>
+    <t>ZEUS</t>
+  </si>
+  <si>
+    <t>VCEL</t>
+  </si>
+  <si>
+    <t>PAG</t>
+  </si>
+  <si>
+    <t>CNM</t>
+  </si>
+  <si>
     <t>ABNB</t>
   </si>
   <si>
-    <t>ABG</t>
+    <t>AUPH</t>
+  </si>
+  <si>
+    <t>APLS</t>
+  </si>
+  <si>
+    <t>MATW</t>
+  </si>
+  <si>
+    <t>MLNK</t>
+  </si>
+  <si>
+    <t>CRM</t>
+  </si>
+  <si>
+    <t>LPRO</t>
+  </si>
+  <si>
+    <t>FTNT</t>
+  </si>
+  <si>
+    <t>SSD</t>
+  </si>
+  <si>
+    <t>PATK</t>
+  </si>
+  <si>
+    <t>ACAD</t>
+  </si>
+  <si>
+    <t>TSQ</t>
+  </si>
+  <si>
+    <t>FMS</t>
+  </si>
+  <si>
+    <t>USLM</t>
+  </si>
+  <si>
+    <t>KRNT</t>
+  </si>
+  <si>
+    <t>APG</t>
+  </si>
+  <si>
+    <t>DAL</t>
+  </si>
+  <si>
+    <t>CPS</t>
+  </si>
+  <si>
+    <t>BLBD</t>
+  </si>
+  <si>
+    <t>BYND</t>
+  </si>
+  <si>
+    <t>AMZN</t>
+  </si>
+  <si>
+    <t>CNMD</t>
+  </si>
+  <si>
+    <t>CVGI</t>
+  </si>
+  <si>
+    <t>SITM</t>
+  </si>
+  <si>
+    <t>DMRC</t>
+  </si>
+  <si>
+    <t>ZG</t>
+  </si>
+  <si>
+    <t>Z</t>
+  </si>
+  <si>
+    <t>BSY</t>
+  </si>
+  <si>
+    <t>PCOR</t>
+  </si>
+  <si>
+    <t>DT</t>
+  </si>
+  <si>
+    <t>DBRG</t>
+  </si>
+  <si>
+    <t>ONTO</t>
+  </si>
+  <si>
+    <t>CAAP</t>
+  </si>
+  <si>
+    <t>TOST</t>
+  </si>
+  <si>
+    <t>RDNT</t>
+  </si>
+  <si>
+    <t>LSANF</t>
+  </si>
+  <si>
+    <t>NEOG</t>
+  </si>
+  <si>
+    <t>BWMN</t>
+  </si>
+  <si>
+    <t>SRAD</t>
+  </si>
+  <si>
+    <t>TWST</t>
+  </si>
+  <si>
+    <t>RILY</t>
+  </si>
+  <si>
+    <t>RH</t>
+  </si>
+  <si>
+    <t>OC</t>
+  </si>
+  <si>
+    <t>MTH</t>
+  </si>
+  <si>
+    <t>VNT</t>
+  </si>
+  <si>
+    <t>ACCD</t>
+  </si>
+  <si>
+    <t>ON</t>
+  </si>
+  <si>
+    <t>CYD</t>
+  </si>
+  <si>
+    <t>VEON</t>
+  </si>
+  <si>
+    <t>GXO</t>
+  </si>
+  <si>
+    <t>GKOS</t>
+  </si>
+  <si>
+    <t>FROG</t>
+  </si>
+  <si>
+    <t>NEO</t>
+  </si>
+  <si>
+    <t>PTGX</t>
+  </si>
+  <si>
+    <t>WMS</t>
+  </si>
+  <si>
+    <t>NOW</t>
+  </si>
+  <si>
+    <t>CARG</t>
+  </si>
+  <si>
+    <t>BILL</t>
+  </si>
+  <si>
+    <t>SWDAF</t>
+  </si>
+  <si>
+    <t>ENS</t>
+  </si>
+  <si>
+    <t>GSHD</t>
+  </si>
+  <si>
+    <t>TWLO</t>
+  </si>
+  <si>
+    <t>FTAI</t>
+  </si>
+  <si>
+    <t>TREX</t>
+  </si>
+  <si>
+    <t>PANW</t>
+  </si>
+  <si>
+    <t>IESC</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>PROF</t>
+  </si>
+  <si>
+    <t>SHAK</t>
+  </si>
+  <si>
+    <t>UBER</t>
+  </si>
+  <si>
+    <t>PATH</t>
+  </si>
+  <si>
+    <t>PRG</t>
+  </si>
+  <si>
+    <t>WFRD</t>
+  </si>
+  <si>
+    <t>SMHI</t>
+  </si>
+  <si>
+    <t>APPN</t>
+  </si>
+  <si>
+    <t>FORM</t>
+  </si>
+  <si>
+    <t>AZEK</t>
+  </si>
+  <si>
+    <t>ALGT</t>
+  </si>
+  <si>
+    <t>MRUS</t>
+  </si>
+  <si>
+    <t>ATEC</t>
+  </si>
+  <si>
+    <t>KBH</t>
+  </si>
+  <si>
+    <t>TPH</t>
+  </si>
+  <si>
+    <t>SAIA</t>
+  </si>
+  <si>
+    <t>BCC</t>
+  </si>
+  <si>
+    <t>ENTG</t>
+  </si>
+  <si>
+    <t>BECN</t>
+  </si>
+  <si>
+    <t>AN</t>
+  </si>
+  <si>
+    <t>MANH</t>
+  </si>
+  <si>
+    <t>AZUL</t>
+  </si>
+  <si>
+    <t>PACB</t>
+  </si>
+  <si>
+    <t>DICE</t>
+  </si>
+  <si>
+    <t>PETQ</t>
+  </si>
+  <si>
+    <t>TMHC</t>
+  </si>
+  <si>
+    <t>ALPN</t>
+  </si>
+  <si>
+    <t>ARCT</t>
+  </si>
+  <si>
+    <t>NATR</t>
+  </si>
+  <si>
+    <t>MPWR</t>
+  </si>
+  <si>
+    <t>SGRY</t>
+  </si>
+  <si>
+    <t>PEGA</t>
+  </si>
+  <si>
+    <t>ZUO</t>
+  </si>
+  <si>
+    <t>HSKA</t>
+  </si>
+  <si>
+    <t>MLP</t>
+  </si>
+  <si>
+    <t>CLS</t>
+  </si>
+  <si>
+    <t>IBP</t>
+  </si>
+  <si>
+    <t>ONON</t>
+  </si>
+  <si>
+    <t>CELH</t>
+  </si>
+  <si>
+    <t>LZ</t>
+  </si>
+  <si>
+    <t>NFLX</t>
+  </si>
+  <si>
+    <t>SIBN</t>
+  </si>
+  <si>
+    <t>ETNB</t>
+  </si>
+  <si>
+    <t>NET</t>
+  </si>
+  <si>
+    <t>UFPT</t>
+  </si>
+  <si>
+    <t>ALGN</t>
+  </si>
+  <si>
+    <t>PDFS</t>
+  </si>
+  <si>
+    <t>RELY</t>
+  </si>
+  <si>
+    <t>AMWD</t>
+  </si>
+  <si>
+    <t>ASAN</t>
+  </si>
+  <si>
+    <t>SSYS</t>
+  </si>
+  <si>
+    <t>ERO</t>
+  </si>
+  <si>
+    <t>NNOX</t>
+  </si>
+  <si>
+    <t>SNAP</t>
+  </si>
+  <si>
+    <t>ROKU</t>
+  </si>
+  <si>
+    <t>BWMX</t>
+  </si>
+  <si>
+    <t>ANF</t>
+  </si>
+  <si>
+    <t>ROIV</t>
+  </si>
+  <si>
+    <t>NETI</t>
+  </si>
+  <si>
+    <t>DDOG</t>
+  </si>
+  <si>
+    <t>MDWT</t>
+  </si>
+  <si>
+    <t>IDCC</t>
+  </si>
+  <si>
+    <t>TDW</t>
+  </si>
+  <si>
+    <t>TOL</t>
+  </si>
+  <si>
+    <t>PHAT</t>
+  </si>
+  <si>
+    <t>DASH</t>
+  </si>
+  <si>
+    <t>JELD</t>
+  </si>
+  <si>
+    <t>LAD</t>
+  </si>
+  <si>
+    <t>LTH</t>
+  </si>
+  <si>
+    <t>BLU</t>
+  </si>
+  <si>
+    <t>BVH</t>
+  </si>
+  <si>
+    <t>GBX</t>
+  </si>
+  <si>
+    <t>AMD</t>
+  </si>
+  <si>
+    <t>FCNCA</t>
+  </si>
+  <si>
+    <t>EB</t>
+  </si>
+  <si>
+    <t>THC</t>
+  </si>
+  <si>
+    <t>BMA</t>
+  </si>
+  <si>
+    <t>IIVI</t>
+  </si>
+  <si>
+    <t>APPF</t>
+  </si>
+  <si>
+    <t>DUOL</t>
+  </si>
+  <si>
+    <t>ATRO</t>
+  </si>
+  <si>
+    <t>ALGM</t>
   </si>
   <si>
     <t>AFRM</t>
   </si>
   <si>
-    <t>RKT</t>
-  </si>
-  <si>
-    <t>FTDR</t>
-  </si>
-  <si>
-    <t>PAM</t>
-  </si>
-  <si>
-    <t>MTZ</t>
-  </si>
-  <si>
-    <t>LSCC</t>
-  </si>
-  <si>
-    <t>THO</t>
-  </si>
-  <si>
-    <t>KBAL</t>
-  </si>
-  <si>
-    <t>GPI</t>
-  </si>
-  <si>
-    <t>APPN</t>
-  </si>
-  <si>
-    <t>MWA</t>
-  </si>
-  <si>
-    <t>FLEX</t>
-  </si>
-  <si>
-    <t>WDFC</t>
-  </si>
-  <si>
-    <t>TEX</t>
-  </si>
-  <si>
-    <t>NOW</t>
-  </si>
-  <si>
-    <t>CWH</t>
-  </si>
-  <si>
-    <t>LASR</t>
-  </si>
-  <si>
-    <t>VIPS</t>
-  </si>
-  <si>
-    <t>CRMT</t>
-  </si>
-  <si>
-    <t>PLTK</t>
-  </si>
-  <si>
-    <t>ORCL</t>
-  </si>
-  <si>
-    <t>ACCD</t>
-  </si>
-  <si>
-    <t>CRNC</t>
-  </si>
-  <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>FORM</t>
-  </si>
-  <si>
-    <t>FDX</t>
-  </si>
-  <si>
-    <t>CPRT</t>
-  </si>
-  <si>
-    <t>CNM</t>
-  </si>
-  <si>
-    <t>SSD</t>
-  </si>
-  <si>
-    <t>HEAR</t>
-  </si>
-  <si>
-    <t>AMZN</t>
-  </si>
-  <si>
-    <t>PATH</t>
-  </si>
-  <si>
-    <t>LRCX</t>
-  </si>
-  <si>
-    <t>HUBB</t>
-  </si>
-  <si>
-    <t>DBRG</t>
-  </si>
-  <si>
-    <t>TWN</t>
-  </si>
-  <si>
-    <t>LPRO</t>
-  </si>
-  <si>
-    <t>ADDYY</t>
-  </si>
-  <si>
-    <t>NPO</t>
-  </si>
-  <si>
-    <t>FCAP</t>
-  </si>
-  <si>
-    <t>IGT</t>
-  </si>
-  <si>
-    <t>FDMT</t>
-  </si>
-  <si>
-    <t>MLNK</t>
-  </si>
-  <si>
-    <t>GNRC</t>
-  </si>
-  <si>
-    <t>ARCO</t>
-  </si>
-  <si>
-    <t>TA</t>
-  </si>
-  <si>
-    <t>SPSC</t>
-  </si>
-  <si>
-    <t>GSHD</t>
-  </si>
-  <si>
-    <t>FND</t>
-  </si>
-  <si>
-    <t>MATW</t>
-  </si>
-  <si>
-    <t>ATI</t>
-  </si>
-  <si>
-    <t>KRNT</t>
-  </si>
-  <si>
-    <t>VLRS</t>
-  </si>
-  <si>
-    <t>Z</t>
-  </si>
-  <si>
-    <t>FTNT</t>
-  </si>
-  <si>
-    <t>ZEUS</t>
-  </si>
-  <si>
-    <t>DELL</t>
-  </si>
-  <si>
-    <t>CVAC</t>
-  </si>
-  <si>
-    <t>BLX</t>
-  </si>
-  <si>
-    <t>NEO</t>
-  </si>
-  <si>
-    <t>ZG</t>
-  </si>
-  <si>
-    <t>ADDDF</t>
-  </si>
-  <si>
-    <t>RELY</t>
+    <t>YPF</t>
+  </si>
+  <si>
+    <t>ATLC</t>
+  </si>
+  <si>
+    <t>STVN</t>
+  </si>
+  <si>
+    <t>FOR</t>
+  </si>
+  <si>
+    <t>ASMIY</t>
+  </si>
+  <si>
+    <t>PHM</t>
+  </si>
+  <si>
+    <t>BLD</t>
+  </si>
+  <si>
+    <t>TAYD</t>
+  </si>
+  <si>
+    <t>YEXT</t>
+  </si>
+  <si>
+    <t>TGLS</t>
+  </si>
+  <si>
+    <t>ABCM</t>
+  </si>
+  <si>
+    <t>PSTG</t>
+  </si>
+  <si>
+    <t>TDC</t>
+  </si>
+  <si>
+    <t>JBL</t>
+  </si>
+  <si>
+    <t>CRCT</t>
+  </si>
+  <si>
+    <t>EBIX</t>
+  </si>
+  <si>
+    <t>MTW</t>
+  </si>
+  <si>
+    <t>NCLH</t>
+  </si>
+  <si>
+    <t>POWL</t>
+  </si>
+  <si>
+    <t>LUNG</t>
+  </si>
+  <si>
+    <t>BELFB</t>
+  </si>
+  <si>
+    <t>XPEV</t>
+  </si>
+  <si>
+    <t>RCL</t>
+  </si>
+  <si>
+    <t>MORF</t>
+  </si>
+  <si>
+    <t>ACMR</t>
+  </si>
+  <si>
+    <t>KRYS</t>
+  </si>
+  <si>
+    <t>AVGO</t>
+  </si>
+  <si>
+    <t>RMBS</t>
+  </si>
+  <si>
+    <t>MNSO</t>
+  </si>
+  <si>
+    <t>ETHE</t>
+  </si>
+  <si>
+    <t>XPO</t>
+  </si>
+  <si>
+    <t>COCO</t>
+  </si>
+  <si>
+    <t>GTLB</t>
+  </si>
+  <si>
+    <t>EXTR</t>
+  </si>
+  <si>
+    <t>XP</t>
+  </si>
+  <si>
+    <t>STRL</t>
+  </si>
+  <si>
+    <t>CMT</t>
+  </si>
+  <si>
+    <t>BBIO</t>
+  </si>
+  <si>
+    <t>FIVN</t>
+  </si>
+  <si>
+    <t>ISEE</t>
+  </si>
+  <si>
+    <t>VIST</t>
+  </si>
+  <si>
+    <t>QS</t>
+  </si>
+  <si>
+    <t>GRVY</t>
+  </si>
+  <si>
+    <t>FLNC</t>
+  </si>
+  <si>
+    <t>HUBS</t>
+  </si>
+  <si>
+    <t>AMPH</t>
+  </si>
+  <si>
+    <t>CPSS</t>
   </si>
   <si>
     <t>CAMT</t>
   </si>
   <si>
-    <t>BSY</t>
-  </si>
-  <si>
-    <t>PATK</t>
-  </si>
-  <si>
-    <t>MRUS</t>
-  </si>
-  <si>
-    <t>ON</t>
-  </si>
-  <si>
-    <t>BCC</t>
-  </si>
-  <si>
-    <t>MPX</t>
-  </si>
-  <si>
-    <t>TMDX</t>
-  </si>
-  <si>
-    <t>MTH</t>
-  </si>
-  <si>
-    <t>PEGA</t>
-  </si>
-  <si>
-    <t>PEN</t>
-  </si>
-  <si>
-    <t>SSYS</t>
-  </si>
-  <si>
-    <t>ONTO</t>
-  </si>
-  <si>
-    <t>OII</t>
-  </si>
-  <si>
-    <t>AZEK</t>
-  </si>
-  <si>
-    <t>SNAP</t>
-  </si>
-  <si>
-    <t>LPG</t>
-  </si>
-  <si>
-    <t>VEON</t>
-  </si>
-  <si>
-    <t>TREX</t>
-  </si>
-  <si>
-    <t>GXO</t>
-  </si>
-  <si>
-    <t>LZ</t>
-  </si>
-  <si>
-    <t>HQI</t>
-  </si>
-  <si>
-    <t>GTLB</t>
-  </si>
-  <si>
-    <t>DT</t>
-  </si>
-  <si>
-    <t>IESC</t>
-  </si>
-  <si>
-    <t>MPWR</t>
-  </si>
-  <si>
-    <t>BOOT</t>
-  </si>
-  <si>
-    <t>DDOG</t>
-  </si>
-  <si>
-    <t>NEOG</t>
-  </si>
-  <si>
-    <t>OC</t>
-  </si>
-  <si>
-    <t>GKOS</t>
-  </si>
-  <si>
-    <t>UBER</t>
-  </si>
-  <si>
-    <t>NET</t>
-  </si>
-  <si>
-    <t>COTY</t>
-  </si>
-  <si>
-    <t>URBN</t>
-  </si>
-  <si>
-    <t>TPH</t>
-  </si>
-  <si>
-    <t>ALGM</t>
-  </si>
-  <si>
-    <t>VNT</t>
-  </si>
-  <si>
-    <t>CNMD</t>
-  </si>
-  <si>
-    <t>ALGN</t>
-  </si>
-  <si>
-    <t>SMHI</t>
-  </si>
-  <si>
-    <t>TRDA</t>
-  </si>
-  <si>
-    <t>PKOH</t>
-  </si>
-  <si>
-    <t>APG</t>
-  </si>
-  <si>
-    <t>DICE</t>
-  </si>
-  <si>
-    <t>CARG</t>
-  </si>
-  <si>
-    <t>INMB</t>
-  </si>
-  <si>
-    <t>SGRY</t>
-  </si>
-  <si>
-    <t>CYD</t>
-  </si>
-  <si>
-    <t>APPF</t>
-  </si>
-  <si>
-    <t>PAG</t>
-  </si>
-  <si>
-    <t>SHAK</t>
-  </si>
-  <si>
-    <t>ATEC</t>
-  </si>
-  <si>
-    <t>ERO</t>
-  </si>
-  <si>
-    <t>GE</t>
-  </si>
-  <si>
-    <t>ASMIY</t>
-  </si>
-  <si>
-    <t>CPS</t>
-  </si>
-  <si>
-    <t>ASAN</t>
-  </si>
-  <si>
-    <t>TMHC</t>
-  </si>
-  <si>
-    <t>FIVN</t>
-  </si>
-  <si>
-    <t>RH</t>
-  </si>
-  <si>
-    <t>ENS</t>
-  </si>
-  <si>
-    <t>CLS</t>
-  </si>
-  <si>
-    <t>WFRD</t>
-  </si>
-  <si>
-    <t>BWMN</t>
-  </si>
-  <si>
-    <t>MACK</t>
-  </si>
-  <si>
-    <t>FTAI</t>
-  </si>
-  <si>
-    <t>JELD</t>
-  </si>
-  <si>
-    <t>RDNT</t>
-  </si>
-  <si>
-    <t>ZUO</t>
+    <t>CXM</t>
+  </si>
+  <si>
+    <t>PLPC</t>
+  </si>
+  <si>
+    <t>DV</t>
+  </si>
+  <si>
+    <t>BELFA</t>
+  </si>
+  <si>
+    <t>ADBE</t>
+  </si>
+  <si>
+    <t>GGAL</t>
+  </si>
+  <si>
+    <t>ACVA</t>
   </si>
   <si>
     <t>SHOP</t>
   </si>
   <si>
-    <t>AXR</t>
-  </si>
-  <si>
-    <t>TSQ</t>
-  </si>
-  <si>
-    <t>MTW</t>
-  </si>
-  <si>
-    <t>RCMT</t>
-  </si>
-  <si>
-    <t>MTR</t>
-  </si>
-  <si>
-    <t>FTI</t>
-  </si>
-  <si>
-    <t>DAL</t>
-  </si>
-  <si>
-    <t>SIBN</t>
-  </si>
-  <si>
-    <t>BMA</t>
-  </si>
-  <si>
-    <t>CELH</t>
-  </si>
-  <si>
-    <t>CPSS</t>
-  </si>
-  <si>
-    <t>ROKU</t>
-  </si>
-  <si>
-    <t>MANH</t>
-  </si>
-  <si>
-    <t>IBP</t>
-  </si>
-  <si>
-    <t>KBH</t>
-  </si>
-  <si>
-    <t>GBX</t>
-  </si>
-  <si>
-    <t>PRG</t>
-  </si>
-  <si>
-    <t>NFLX</t>
-  </si>
-  <si>
-    <t>NATR</t>
-  </si>
-  <si>
-    <t>ETNB</t>
-  </si>
-  <si>
-    <t>ALGT</t>
-  </si>
-  <si>
-    <t>USLM</t>
-  </si>
-  <si>
-    <t>ARCT</t>
-  </si>
-  <si>
-    <t>HSKA</t>
-  </si>
-  <si>
-    <t>DASH</t>
-  </si>
-  <si>
-    <t>SWDAF</t>
-  </si>
-  <si>
-    <t>PACB</t>
-  </si>
-  <si>
-    <t>CAAP</t>
-  </si>
-  <si>
-    <t>TXG</t>
-  </si>
-  <si>
-    <t>DXPE</t>
-  </si>
-  <si>
-    <t>YEXT</t>
-  </si>
-  <si>
-    <t>DUOL</t>
-  </si>
-  <si>
-    <t>BECN</t>
-  </si>
-  <si>
-    <t>PETQ</t>
-  </si>
-  <si>
-    <t>YPF</t>
-  </si>
-  <si>
-    <t>AN</t>
-  </si>
-  <si>
-    <t>LSANF</t>
-  </si>
-  <si>
-    <t>UFPT</t>
-  </si>
-  <si>
-    <t>CXM</t>
-  </si>
-  <si>
-    <t>PANW</t>
-  </si>
-  <si>
-    <t>MOMO</t>
-  </si>
-  <si>
-    <t>LTH</t>
-  </si>
-  <si>
-    <t>NETI</t>
-  </si>
-  <si>
-    <t>AMD</t>
-  </si>
-  <si>
-    <t>TDC</t>
-  </si>
-  <si>
-    <t>FLNC</t>
-  </si>
-  <si>
-    <t>FOR</t>
-  </si>
-  <si>
-    <t>IIVI</t>
-  </si>
-  <si>
-    <t>TOL</t>
-  </si>
-  <si>
-    <t>EBIX</t>
-  </si>
-  <si>
-    <t>ENTG</t>
-  </si>
-  <si>
-    <t>SAIA</t>
-  </si>
-  <si>
-    <t>ONON</t>
-  </si>
-  <si>
-    <t>IDCC</t>
-  </si>
-  <si>
-    <t>NNOX</t>
-  </si>
-  <si>
-    <t>ALPN</t>
-  </si>
-  <si>
-    <t>TDW</t>
-  </si>
-  <si>
-    <t>BLD</t>
+    <t>PCTTU</t>
   </si>
   <si>
     <t>MNDY</t>
   </si>
   <si>
-    <t>BELFB</t>
-  </si>
-  <si>
-    <t>ACMR</t>
-  </si>
-  <si>
-    <t>PCTTU</t>
+    <t>RIVN</t>
+  </si>
+  <si>
+    <t>LI</t>
   </si>
   <si>
     <t>BMEA</t>
   </si>
   <si>
-    <t>CVGI</t>
-  </si>
-  <si>
-    <t>THC</t>
-  </si>
-  <si>
-    <t>PDFS</t>
-  </si>
-  <si>
-    <t>BLU</t>
-  </si>
-  <si>
-    <t>ABCM</t>
-  </si>
-  <si>
-    <t>RIVN</t>
-  </si>
-  <si>
-    <t>FCNCA</t>
-  </si>
-  <si>
-    <t>PHAT</t>
-  </si>
-  <si>
-    <t>AMWD</t>
-  </si>
-  <si>
-    <t>ATLC</t>
-  </si>
-  <si>
-    <t>ROIV</t>
-  </si>
-  <si>
-    <t>PHM</t>
-  </si>
-  <si>
-    <t>LAD</t>
-  </si>
-  <si>
-    <t>MLP</t>
+    <t>PLAB</t>
   </si>
   <si>
     <t>DOCN</t>
   </si>
   <si>
-    <t>RMBS</t>
-  </si>
-  <si>
-    <t>MORF</t>
-  </si>
-  <si>
-    <t>MRNS</t>
-  </si>
-  <si>
-    <t>BELFA</t>
+    <t>RRGB</t>
+  </si>
+  <si>
+    <t>CUBI</t>
+  </si>
+  <si>
+    <t>COHR</t>
+  </si>
+  <si>
+    <t>OSTK</t>
+  </si>
+  <si>
+    <t>BRZE</t>
+  </si>
+  <si>
+    <t>MHO</t>
+  </si>
+  <si>
+    <t>SPOT</t>
+  </si>
+  <si>
+    <t>WRLD</t>
+  </si>
+  <si>
+    <t>MGNI</t>
+  </si>
+  <si>
+    <t>SG</t>
+  </si>
+  <si>
+    <t>AEHR</t>
+  </si>
+  <si>
+    <t>TTD</t>
+  </si>
+  <si>
+    <t>PCT</t>
+  </si>
+  <si>
+    <t>TYRA</t>
+  </si>
+  <si>
+    <t>FSLY</t>
+  </si>
+  <si>
+    <t>NWLI</t>
+  </si>
+  <si>
+    <t>MRVL</t>
+  </si>
+  <si>
+    <t>U</t>
+  </si>
+  <si>
+    <t>VKTX</t>
+  </si>
+  <si>
+    <t>KDNY</t>
+  </si>
+  <si>
+    <t>MOD</t>
+  </si>
+  <si>
+    <t>USAP</t>
+  </si>
+  <si>
+    <t>ELF</t>
+  </si>
+  <si>
+    <t>ODC</t>
+  </si>
+  <si>
+    <t>GHL</t>
+  </si>
+  <si>
+    <t>BLDR</t>
+  </si>
+  <si>
+    <t>TGTX</t>
+  </si>
+  <si>
+    <t>TSLA</t>
+  </si>
+  <si>
+    <t>BHVN</t>
+  </si>
+  <si>
+    <t>VECT</t>
+  </si>
+  <si>
+    <t>AVDL</t>
+  </si>
+  <si>
+    <t>GRBK</t>
+  </si>
+  <si>
+    <t>CFLT</t>
+  </si>
+  <si>
+    <t>EXAS</t>
+  </si>
+  <si>
+    <t>IAS</t>
+  </si>
+  <si>
+    <t>SGH</t>
+  </si>
+  <si>
+    <t>GLBE</t>
+  </si>
+  <si>
+    <t>SHC</t>
+  </si>
+  <si>
+    <t>LSEA</t>
+  </si>
+  <si>
+    <t>LTRPB</t>
+  </si>
+  <si>
+    <t>GBTC</t>
+  </si>
+  <si>
+    <t>VRT</t>
+  </si>
+  <si>
+    <t>KRUS</t>
+  </si>
+  <si>
+    <t>MEDS</t>
+  </si>
+  <si>
+    <t>CBAY</t>
+  </si>
+  <si>
+    <t>ACLS</t>
+  </si>
+  <si>
+    <t>CCL</t>
+  </si>
+  <si>
+    <t>CMPR</t>
+  </si>
+  <si>
+    <t>RXRX</t>
+  </si>
+  <si>
+    <t>QTRX</t>
+  </si>
+  <si>
+    <t>CUK</t>
+  </si>
+  <si>
+    <t>HOV</t>
   </si>
   <si>
     <t>OPAD</t>
   </si>
   <si>
-    <t>TTD</t>
-  </si>
-  <si>
-    <t>DV</t>
-  </si>
-  <si>
-    <t>KRYS</t>
-  </si>
-  <si>
-    <t>PSTG</t>
-  </si>
-  <si>
-    <t>DMRC</t>
-  </si>
-  <si>
-    <t>MNSO</t>
-  </si>
-  <si>
-    <t>BLBD</t>
-  </si>
-  <si>
-    <t>MDWT</t>
-  </si>
-  <si>
-    <t>BRZE</t>
-  </si>
-  <si>
-    <t>ADBE</t>
-  </si>
-  <si>
-    <t>CMT</t>
-  </si>
-  <si>
-    <t>PLPC</t>
-  </si>
-  <si>
-    <t>COHR</t>
-  </si>
-  <si>
-    <t>SPOT</t>
-  </si>
-  <si>
-    <t>BWMX</t>
-  </si>
-  <si>
-    <t>VIST</t>
-  </si>
-  <si>
-    <t>HUBS</t>
-  </si>
-  <si>
-    <t>ISEE</t>
-  </si>
-  <si>
-    <t>XP</t>
-  </si>
-  <si>
-    <t>STVN</t>
-  </si>
-  <si>
-    <t>MHO</t>
-  </si>
-  <si>
-    <t>CUBI</t>
-  </si>
-  <si>
-    <t>JBL</t>
-  </si>
-  <si>
-    <t>GGAL</t>
-  </si>
-  <si>
-    <t>CRCT</t>
-  </si>
-  <si>
-    <t>EXTR</t>
-  </si>
-  <si>
-    <t>COCO</t>
-  </si>
-  <si>
-    <t>BBIO</t>
-  </si>
-  <si>
-    <t>PTGX</t>
-  </si>
-  <si>
-    <t>TGLS</t>
-  </si>
-  <si>
-    <t>TAYD</t>
-  </si>
-  <si>
-    <t>ATRO</t>
-  </si>
-  <si>
-    <t>U</t>
-  </si>
-  <si>
-    <t>POWL</t>
-  </si>
-  <si>
-    <t>OSTK</t>
-  </si>
-  <si>
-    <t>GRBK</t>
-  </si>
-  <si>
-    <t>AVGO</t>
-  </si>
-  <si>
-    <t>NCLH</t>
-  </si>
-  <si>
-    <t>MRVL</t>
-  </si>
-  <si>
-    <t>PROF</t>
-  </si>
-  <si>
-    <t>STRL</t>
-  </si>
-  <si>
-    <t>XPO</t>
-  </si>
-  <si>
-    <t>RRGB</t>
-  </si>
-  <si>
-    <t>BVH</t>
-  </si>
-  <si>
-    <t>PLAB</t>
-  </si>
-  <si>
-    <t>CFLT</t>
-  </si>
-  <si>
-    <t>WRLD</t>
-  </si>
-  <si>
-    <t>RCL</t>
-  </si>
-  <si>
-    <t>ANF</t>
-  </si>
-  <si>
-    <t>SG</t>
-  </si>
-  <si>
-    <t>AMPH</t>
-  </si>
-  <si>
-    <t>GRVY</t>
-  </si>
-  <si>
-    <t>IAS</t>
-  </si>
-  <si>
-    <t>MOD</t>
-  </si>
-  <si>
-    <t>FSLY</t>
-  </si>
-  <si>
-    <t>AVDL</t>
+    <t>BZH</t>
+  </si>
+  <si>
+    <t>TCMD</t>
+  </si>
+  <si>
+    <t>EDN</t>
+  </si>
+  <si>
+    <t>IOT</t>
+  </si>
+  <si>
+    <t>CLXT</t>
+  </si>
+  <si>
+    <t>RXDX</t>
+  </si>
+  <si>
+    <t>DKNG</t>
+  </si>
+  <si>
+    <t>ARLO</t>
+  </si>
+  <si>
+    <t>RXST</t>
+  </si>
+  <si>
+    <t>SKYW</t>
+  </si>
+  <si>
+    <t>NGMS</t>
+  </si>
+  <si>
+    <t>APP</t>
+  </si>
+  <si>
+    <t>ENVX</t>
+  </si>
+  <si>
+    <t>RETA</t>
+  </si>
+  <si>
+    <t>LMB</t>
+  </si>
+  <si>
+    <t>DFH</t>
+  </si>
+  <si>
+    <t>MSTR</t>
+  </si>
+  <si>
+    <t>MDB</t>
+  </si>
+  <si>
+    <t>EXPI</t>
+  </si>
+  <si>
+    <t>CABA</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>NVTS</t>
+  </si>
+  <si>
+    <t>PLTR</t>
+  </si>
+  <si>
+    <t>WEAV</t>
+  </si>
+  <si>
+    <t>EBON</t>
   </si>
   <si>
     <t>COIN</t>
   </si>
   <si>
-    <t>ACVA</t>
-  </si>
-  <si>
-    <t>DKNG</t>
-  </si>
-  <si>
-    <t>PCT</t>
-  </si>
-  <si>
-    <t>CBAY</t>
-  </si>
-  <si>
-    <t>GBTC</t>
-  </si>
-  <si>
-    <t>TYRA</t>
-  </si>
-  <si>
-    <t>LI</t>
-  </si>
-  <si>
-    <t>CLXT</t>
-  </si>
-  <si>
-    <t>AZUL</t>
-  </si>
-  <si>
-    <t>AEHR</t>
-  </si>
-  <si>
-    <t>GLBE</t>
-  </si>
-  <si>
-    <t>KRUS</t>
-  </si>
-  <si>
-    <t>XPEV</t>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>CIR</t>
+  </si>
+  <si>
+    <t>ROOT</t>
+  </si>
+  <si>
+    <t>GGAAU</t>
+  </si>
+  <si>
+    <t>NVDA</t>
+  </si>
+  <si>
+    <t>EH</t>
+  </si>
+  <si>
+    <t>PHVS</t>
+  </si>
+  <si>
+    <t>SDGR</t>
+  </si>
+  <si>
+    <t>RCEL</t>
+  </si>
+  <si>
+    <t>MEOA</t>
+  </si>
+  <si>
+    <t>JOBY</t>
+  </si>
+  <si>
+    <t>AI</t>
+  </si>
+  <si>
+    <t>RDFN</t>
+  </si>
+  <si>
+    <t>EYPT</t>
+  </si>
+  <si>
+    <t>IONQ</t>
+  </si>
+  <si>
+    <t>MARA</t>
+  </si>
+  <si>
+    <t>MEOAU</t>
+  </si>
+  <si>
+    <t>SMCI</t>
+  </si>
+  <si>
+    <t>UPST</t>
+  </si>
+  <si>
+    <t>IMGN</t>
+  </si>
+  <si>
+    <t>RIOT</t>
+  </si>
+  <si>
+    <t>SGTX</t>
+  </si>
+  <si>
+    <t>OPRA</t>
+  </si>
+  <si>
+    <t>EDTXU</t>
   </si>
   <si>
     <t>EDTX</t>
   </si>
   <si>
-    <t>BLDR</t>
-  </si>
-  <si>
-    <t>GOCO</t>
-  </si>
-  <si>
-    <t>KDNY</t>
-  </si>
-  <si>
-    <t>INTT</t>
-  </si>
-  <si>
-    <t>NWLI</t>
-  </si>
-  <si>
-    <t>VKTX</t>
-  </si>
-  <si>
-    <t>MGNI</t>
-  </si>
-  <si>
-    <t>BHVN</t>
-  </si>
-  <si>
-    <t>MSTR</t>
-  </si>
-  <si>
-    <t>VRT</t>
-  </si>
-  <si>
-    <t>SGH</t>
-  </si>
-  <si>
-    <t>SHC</t>
-  </si>
-  <si>
-    <t>EDTXU</t>
-  </si>
-  <si>
-    <t>EDN</t>
-  </si>
-  <si>
-    <t>HOV</t>
-  </si>
-  <si>
-    <t>EXAS</t>
-  </si>
-  <si>
-    <t>ELF</t>
-  </si>
-  <si>
-    <t>RCEL</t>
-  </si>
-  <si>
-    <t>ODC</t>
-  </si>
-  <si>
-    <t>VECT</t>
-  </si>
-  <si>
-    <t>USAP</t>
-  </si>
-  <si>
-    <t>QTRX</t>
-  </si>
-  <si>
-    <t>EXPI</t>
-  </si>
-  <si>
-    <t>LSEA</t>
-  </si>
-  <si>
-    <t>IOT</t>
-  </si>
-  <si>
-    <t>GHL</t>
-  </si>
-  <si>
-    <t>MDB</t>
-  </si>
-  <si>
-    <t>CMPR</t>
-  </si>
-  <si>
-    <t>BZH</t>
-  </si>
-  <si>
-    <t>ACLS</t>
-  </si>
-  <si>
-    <t>NGMS</t>
-  </si>
-  <si>
-    <t>W</t>
-  </si>
-  <si>
-    <t>RXDX</t>
-  </si>
-  <si>
-    <t>TGTX</t>
-  </si>
-  <si>
-    <t>DFH</t>
-  </si>
-  <si>
-    <t>APP</t>
-  </si>
-  <si>
-    <t>LTRPB</t>
-  </si>
-  <si>
-    <t>EH</t>
-  </si>
-  <si>
-    <t>CCL</t>
-  </si>
-  <si>
-    <t>TCMD</t>
-  </si>
-  <si>
-    <t>ENVX</t>
-  </si>
-  <si>
-    <t>CUK</t>
-  </si>
-  <si>
-    <t>PLTR</t>
-  </si>
-  <si>
-    <t>LMB</t>
-  </si>
-  <si>
-    <t>SKYW</t>
-  </si>
-  <si>
-    <t>RXST</t>
-  </si>
-  <si>
-    <t>NVTS</t>
-  </si>
-  <si>
-    <t>RETA</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>ROOT</t>
-  </si>
-  <si>
-    <t>MEDS</t>
-  </si>
-  <si>
-    <t>PHVS</t>
-  </si>
-  <si>
-    <t>ARLO</t>
-  </si>
-  <si>
-    <t>WEAV</t>
-  </si>
-  <si>
-    <t>CABA</t>
-  </si>
-  <si>
-    <t>NVDA</t>
-  </si>
-  <si>
-    <t>SDGR</t>
-  </si>
-  <si>
-    <t>CIR</t>
-  </si>
-  <si>
-    <t>INOD</t>
-  </si>
-  <si>
-    <t>RDFN</t>
-  </si>
-  <si>
-    <t>MARA</t>
-  </si>
-  <si>
-    <t>JOBY</t>
-  </si>
-  <si>
-    <t>UPST</t>
-  </si>
-  <si>
-    <t>MEOA</t>
-  </si>
-  <si>
-    <t>AI</t>
-  </si>
-  <si>
-    <t>RIOT</t>
-  </si>
-  <si>
-    <t>IONQ</t>
-  </si>
-  <si>
-    <t>SMCI</t>
-  </si>
-  <si>
-    <t>IMGN</t>
-  </si>
-  <si>
-    <t>MEOAU</t>
-  </si>
-  <si>
-    <t>SGTX</t>
-  </si>
-  <si>
-    <t>OPRA</t>
+    <t>NERV</t>
   </si>
   <si>
     <t>CVNA</t>
   </si>
   <si>
-    <t>NERV</t>
+    <t>AAOI</t>
   </si>
   <si>
     <t>AMAM</t>
-  </si>
-  <si>
-    <t>PRFX</t>
   </si>
 </sst>
 </file>
@@ -1474,7 +1471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B369"/>
+  <dimension ref="A1:B368"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1490,7 +1487,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1">
-        <v>130.4868752401933</v>
+        <v>134.2835236400988</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1498,7 +1495,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1">
-        <v>130.6365249875919</v>
+        <v>134.4090806296152</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1506,7 +1503,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1">
-        <v>130.753545722488</v>
+        <v>134.5074545593008</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1514,7 +1511,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="1">
-        <v>130.7908382444955</v>
+        <v>134.6267962054363</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1522,7 +1519,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="1">
-        <v>130.858766897102</v>
+        <v>134.794220677352</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1530,7 +1527,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="1">
-        <v>130.8619019629713</v>
+        <v>134.838672284857</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1538,7 +1535,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="1">
-        <v>131.0526229500746</v>
+        <v>134.8795606266485</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1546,7 +1543,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="1">
-        <v>131.1146976475468</v>
+        <v>135.0579725884918</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1554,7 +1551,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="1">
-        <v>131.1214552648555</v>
+        <v>135.0740553864142</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1562,7 +1559,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="1">
-        <v>131.1754539126597</v>
+        <v>135.0922309856031</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1570,7 +1567,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="1">
-        <v>131.1863471049425</v>
+        <v>135.1179799764997</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1578,7 +1575,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="1">
-        <v>131.206139358947</v>
+        <v>135.2522703815308</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1586,7 +1583,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="1">
-        <v>131.3486170871375</v>
+        <v>135.2825036268666</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1594,7 +1591,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="1">
-        <v>131.3604288071017</v>
+        <v>135.2903612742539</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1602,7 +1599,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="1">
-        <v>131.3772977476627</v>
+        <v>135.4775005488728</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1610,7 +1607,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="1">
-        <v>131.3927541689931</v>
+        <v>135.5518128408808</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1618,7 +1615,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="1">
-        <v>131.5673931847554</v>
+        <v>135.6137227690266</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1626,7 +1623,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="1">
-        <v>131.6172117675589</v>
+        <v>135.615381869454</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1634,7 +1631,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="1">
-        <v>131.6785135826206</v>
+        <v>135.6524869215367</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1642,7 +1639,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="1">
-        <v>131.7347077714464</v>
+        <v>135.7164462646808</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1650,7 +1647,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="1">
-        <v>131.7381011056909</v>
+        <v>135.7444515766796</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1658,7 +1655,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="1">
-        <v>131.7786720867366</v>
+        <v>135.7459673196028</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1666,7 +1663,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="1">
-        <v>131.820844093639</v>
+        <v>135.7515814062836</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1674,7 +1671,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="1">
-        <v>131.83420335031</v>
+        <v>135.8470754974519</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1682,7 +1679,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="1">
-        <v>131.8973423673471</v>
+        <v>136.0100649800785</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1690,7 +1687,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="1">
-        <v>132.0285160122253</v>
+        <v>136.0627919805756</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1698,7 +1695,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="1">
-        <v>132.0626904336166</v>
+        <v>136.1359688902318</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1706,7 +1703,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="1">
-        <v>132.0634086592961</v>
+        <v>136.2592481787247</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1714,7 +1711,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="1">
-        <v>132.1209965567197</v>
+        <v>136.3427528796899</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1722,7 +1719,7 @@
         <v>31</v>
       </c>
       <c r="B31" s="1">
-        <v>132.249905584196</v>
+        <v>136.5207991693276</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1730,7 +1727,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="1">
-        <v>132.2735329667315</v>
+        <v>136.6546915932336</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1738,7 +1735,7 @@
         <v>33</v>
       </c>
       <c r="B33" s="1">
-        <v>132.2912562670783</v>
+        <v>136.73714903327</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1746,7 +1743,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="1">
-        <v>132.3193679302368</v>
+        <v>136.7436129471768</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1754,7 +1751,7 @@
         <v>35</v>
       </c>
       <c r="B35" s="1">
-        <v>132.3773624863019</v>
+        <v>136.9114519031462</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1762,7 +1759,7 @@
         <v>36</v>
       </c>
       <c r="B36" s="1">
-        <v>132.3822147989913</v>
+        <v>136.9903375655236</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1770,7 +1767,7 @@
         <v>37</v>
       </c>
       <c r="B37" s="1">
-        <v>132.4826299610886</v>
+        <v>137.0128111628075</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1778,7 +1775,7 @@
         <v>38</v>
       </c>
       <c r="B38" s="1">
-        <v>132.7425174485702</v>
+        <v>137.1838954294745</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1786,7 +1783,7 @@
         <v>39</v>
       </c>
       <c r="B39" s="1">
-        <v>132.7518171058426</v>
+        <v>137.2234880281013</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1794,7 +1791,7 @@
         <v>40</v>
       </c>
       <c r="B40" s="1">
-        <v>132.8343214352512</v>
+        <v>137.5029928601381</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1802,7 +1799,7 @@
         <v>41</v>
       </c>
       <c r="B41" s="1">
-        <v>132.8597500739698</v>
+        <v>137.5053776597617</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -1810,7 +1807,7 @@
         <v>42</v>
       </c>
       <c r="B42" s="1">
-        <v>132.8863501378605</v>
+        <v>137.5362062907868</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -1818,7 +1815,7 @@
         <v>43</v>
       </c>
       <c r="B43" s="1">
-        <v>132.9428204710456</v>
+        <v>137.6322726301878</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1826,7 +1823,7 @@
         <v>44</v>
       </c>
       <c r="B44" s="1">
-        <v>132.9561192295088</v>
+        <v>137.6372561036121</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1834,7 +1831,7 @@
         <v>45</v>
       </c>
       <c r="B45" s="1">
-        <v>132.9756114919859</v>
+        <v>137.7009035953743</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1842,7 +1839,7 @@
         <v>46</v>
       </c>
       <c r="B46" s="1">
-        <v>132.9784173760003</v>
+        <v>137.702695166012</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -1850,7 +1847,7 @@
         <v>47</v>
       </c>
       <c r="B47" s="1">
-        <v>133.0447153959948</v>
+        <v>137.7196691233726</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -1858,7 +1855,7 @@
         <v>48</v>
       </c>
       <c r="B48" s="1">
-        <v>133.4053318417248</v>
+        <v>137.7217488850168</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1866,7 +1863,7 @@
         <v>49</v>
       </c>
       <c r="B49" s="1">
-        <v>133.4180233629538</v>
+        <v>137.7289779971502</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1874,7 +1871,7 @@
         <v>50</v>
       </c>
       <c r="B50" s="1">
-        <v>133.455391248564</v>
+        <v>137.75173437534</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1882,7 +1879,7 @@
         <v>51</v>
       </c>
       <c r="B51" s="1">
-        <v>133.5429766101482</v>
+        <v>137.753678478699</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1890,7 +1887,7 @@
         <v>52</v>
       </c>
       <c r="B52" s="1">
-        <v>133.606933024094</v>
+        <v>137.901019166253</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1898,7 +1895,7 @@
         <v>53</v>
       </c>
       <c r="B53" s="1">
-        <v>133.618076345044</v>
+        <v>138.0201619343431</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1906,7 +1903,7 @@
         <v>54</v>
       </c>
       <c r="B54" s="1">
-        <v>133.7349871025708</v>
+        <v>138.1337370944594</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1914,7 +1911,7 @@
         <v>55</v>
       </c>
       <c r="B55" s="1">
-        <v>133.7816468891679</v>
+        <v>138.1886972162805</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1922,7 +1919,7 @@
         <v>56</v>
       </c>
       <c r="B56" s="1">
-        <v>133.8624181634548</v>
+        <v>138.3774628840076</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1930,7 +1927,7 @@
         <v>57</v>
       </c>
       <c r="B57" s="1">
-        <v>133.8859581649071</v>
+        <v>138.3845550404653</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1938,7 +1935,7 @@
         <v>58</v>
       </c>
       <c r="B58" s="1">
-        <v>133.9265330193475</v>
+        <v>138.3988512516472</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1946,7 +1943,7 @@
         <v>59</v>
       </c>
       <c r="B59" s="1">
-        <v>133.9531972985087</v>
+        <v>138.4152102175942</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1954,7 +1951,7 @@
         <v>60</v>
       </c>
       <c r="B60" s="1">
-        <v>133.9592665205222</v>
+        <v>138.5544138887973</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1962,7 +1959,7 @@
         <v>61</v>
       </c>
       <c r="B61" s="1">
-        <v>133.9702946478169</v>
+        <v>138.5728180292637</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1970,7 +1967,7 @@
         <v>62</v>
       </c>
       <c r="B62" s="1">
-        <v>134.2274858842702</v>
+        <v>138.6129087262043</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1978,7 +1975,7 @@
         <v>63</v>
       </c>
       <c r="B63" s="1">
-        <v>134.234666218901</v>
+        <v>138.6466069282945</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1986,7 +1983,7 @@
         <v>64</v>
       </c>
       <c r="B64" s="1">
-        <v>134.2590563251207</v>
+        <v>138.6566111160424</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1994,7 +1991,7 @@
         <v>65</v>
       </c>
       <c r="B65" s="1">
-        <v>134.2925010407556</v>
+        <v>138.7145361217494</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -2002,7 +1999,7 @@
         <v>66</v>
       </c>
       <c r="B66" s="1">
-        <v>134.3144102796159</v>
+        <v>138.7206221345322</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -2010,7 +2007,7 @@
         <v>67</v>
       </c>
       <c r="B67" s="1">
-        <v>134.3637573665926</v>
+        <v>139.0038417832344</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -2018,7 +2015,7 @@
         <v>68</v>
       </c>
       <c r="B68" s="1">
-        <v>134.6983784481088</v>
+        <v>139.0520279849854</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -2026,7 +2023,7 @@
         <v>69</v>
       </c>
       <c r="B69" s="1">
-        <v>134.7637511300891</v>
+        <v>139.0980624397909</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -2034,7 +2031,7 @@
         <v>70</v>
       </c>
       <c r="B70" s="1">
-        <v>134.7965283158647</v>
+        <v>139.2433355030488</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -2042,7 +2039,7 @@
         <v>71</v>
       </c>
       <c r="B71" s="1">
-        <v>134.8774251289209</v>
+        <v>139.4211249010141</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -2050,7 +2047,7 @@
         <v>72</v>
       </c>
       <c r="B72" s="1">
-        <v>134.8831153423669</v>
+        <v>139.4519999900984</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2058,7 +2055,7 @@
         <v>73</v>
       </c>
       <c r="B73" s="1">
-        <v>134.8857080482051</v>
+        <v>139.4895798489713</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -2066,7 +2063,7 @@
         <v>74</v>
       </c>
       <c r="B74" s="1">
-        <v>134.9456555725604</v>
+        <v>139.492215786882</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -2074,7 +2071,7 @@
         <v>75</v>
       </c>
       <c r="B75" s="1">
-        <v>134.9804635848764</v>
+        <v>139.8322253529184</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -2082,7 +2079,7 @@
         <v>76</v>
       </c>
       <c r="B76" s="1">
-        <v>134.9960291967982</v>
+        <v>139.8387754335597</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -2090,7 +2087,7 @@
         <v>77</v>
       </c>
       <c r="B77" s="1">
-        <v>135.0001188985055</v>
+        <v>139.8753344526066</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -2098,7 +2095,7 @@
         <v>78</v>
       </c>
       <c r="B78" s="1">
-        <v>135.1495570380197</v>
+        <v>139.8774673855234</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -2106,7 +2103,7 @@
         <v>79</v>
       </c>
       <c r="B79" s="1">
-        <v>135.1770809495814</v>
+        <v>139.902384881612</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -2114,7 +2111,7 @@
         <v>80</v>
       </c>
       <c r="B80" s="1">
-        <v>135.2455553364134</v>
+        <v>139.9709000227226</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -2122,7 +2119,7 @@
         <v>81</v>
       </c>
       <c r="B81" s="1">
-        <v>135.2549302624207</v>
+        <v>140.0962879492597</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -2130,7 +2127,7 @@
         <v>82</v>
       </c>
       <c r="B82" s="1">
-        <v>135.339802845216</v>
+        <v>140.4424059594698</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -2138,7 +2135,7 @@
         <v>83</v>
       </c>
       <c r="B83" s="1">
-        <v>135.6991349137823</v>
+        <v>140.4785186798393</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -2146,7 +2143,7 @@
         <v>84</v>
       </c>
       <c r="B84" s="1">
-        <v>135.7399790156825</v>
+        <v>140.5017802836973</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -2154,7 +2151,7 @@
         <v>85</v>
       </c>
       <c r="B85" s="1">
-        <v>135.8850515203913</v>
+        <v>140.5300424257138</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -2162,7 +2159,7 @@
         <v>86</v>
       </c>
       <c r="B86" s="1">
-        <v>136.0162257766625</v>
+        <v>140.5582369388532</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -2170,7 +2167,7 @@
         <v>87</v>
       </c>
       <c r="B87" s="1">
-        <v>136.0288388457031</v>
+        <v>140.6288336266411</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -2178,7 +2175,7 @@
         <v>88</v>
       </c>
       <c r="B88" s="1">
-        <v>136.03792622528</v>
+        <v>140.6503886462164</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -2186,7 +2183,7 @@
         <v>89</v>
       </c>
       <c r="B89" s="1">
-        <v>136.2258795480038</v>
+        <v>140.7618817293612</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -2194,7 +2191,7 @@
         <v>90</v>
       </c>
       <c r="B90" s="1">
-        <v>136.2417280438983</v>
+        <v>140.8107844466733</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -2202,7 +2199,7 @@
         <v>91</v>
       </c>
       <c r="B91" s="1">
-        <v>136.3445799288037</v>
+        <v>140.8376763186334</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -2210,7 +2207,7 @@
         <v>92</v>
       </c>
       <c r="B92" s="1">
-        <v>136.4104708009492</v>
+        <v>140.8652637658371</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -2218,7 +2215,7 @@
         <v>93</v>
       </c>
       <c r="B93" s="1">
-        <v>136.4110338826474</v>
+        <v>140.8772633598947</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -2226,7 +2223,7 @@
         <v>94</v>
       </c>
       <c r="B94" s="1">
-        <v>136.5423472406811</v>
+        <v>141.1814826649681</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -2234,7 +2231,7 @@
         <v>95</v>
       </c>
       <c r="B95" s="1">
-        <v>136.5851697461995</v>
+        <v>141.2644634174211</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -2242,7 +2239,7 @@
         <v>96</v>
       </c>
       <c r="B96" s="1">
-        <v>136.6338766729932</v>
+        <v>141.3895818733996</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -2250,7 +2247,7 @@
         <v>97</v>
       </c>
       <c r="B97" s="1">
-        <v>136.7180529667098</v>
+        <v>141.4206778902169</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -2258,7 +2255,7 @@
         <v>98</v>
       </c>
       <c r="B98" s="1">
-        <v>136.8625057143158</v>
+        <v>141.4729560545239</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -2266,7 +2263,7 @@
         <v>99</v>
       </c>
       <c r="B99" s="1">
-        <v>136.8634580301458</v>
+        <v>141.7029639219962</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -2274,7 +2271,7 @@
         <v>100</v>
       </c>
       <c r="B100" s="1">
-        <v>136.8666648679079</v>
+        <v>141.7037312654739</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -2282,7 +2279,7 @@
         <v>101</v>
       </c>
       <c r="B101" s="1">
-        <v>136.9105009036798</v>
+        <v>141.8174532363149</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -2290,7 +2287,7 @@
         <v>102</v>
       </c>
       <c r="B102" s="1">
-        <v>136.929867671959</v>
+        <v>141.9139327928566</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -2298,7 +2295,7 @@
         <v>103</v>
       </c>
       <c r="B103" s="1">
-        <v>136.9530740749764</v>
+        <v>142.0004653050219</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -2306,7 +2303,7 @@
         <v>104</v>
       </c>
       <c r="B104" s="1">
-        <v>137.0017119680191</v>
+        <v>142.096405374987</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -2314,7 +2311,7 @@
         <v>105</v>
       </c>
       <c r="B105" s="1">
-        <v>137.0375592317531</v>
+        <v>142.2134529377515</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -2322,7 +2319,7 @@
         <v>106</v>
       </c>
       <c r="B106" s="1">
-        <v>137.1420559203621</v>
+        <v>142.2461284043449</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -2330,7 +2327,7 @@
         <v>107</v>
       </c>
       <c r="B107" s="1">
-        <v>137.2149423636228</v>
+        <v>142.5062305314136</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -2338,7 +2335,7 @@
         <v>108</v>
       </c>
       <c r="B108" s="1">
-        <v>137.2206070891754</v>
+        <v>142.508821428502</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -2346,7 +2343,7 @@
         <v>109</v>
       </c>
       <c r="B109" s="1">
-        <v>137.4940630864616</v>
+        <v>142.5733996680439</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -2354,7 +2351,7 @@
         <v>110</v>
       </c>
       <c r="B110" s="1">
-        <v>137.5950422409416</v>
+        <v>142.6908856879183</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -2362,7 +2359,7 @@
         <v>111</v>
       </c>
       <c r="B111" s="1">
-        <v>137.6240168590841</v>
+        <v>142.7422779553292</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -2370,7 +2367,7 @@
         <v>112</v>
       </c>
       <c r="B112" s="1">
-        <v>137.6807078737178</v>
+        <v>142.7719647448292</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -2378,7 +2375,7 @@
         <v>113</v>
       </c>
       <c r="B113" s="1">
-        <v>137.6989336084455</v>
+        <v>142.9807977658342</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -2386,7 +2383,7 @@
         <v>114</v>
       </c>
       <c r="B114" s="1">
-        <v>138.1877945363265</v>
+        <v>142.9952913677558</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -2394,7 +2391,7 @@
         <v>115</v>
       </c>
       <c r="B115" s="1">
-        <v>138.2756585823726</v>
+        <v>143.0307616765038</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -2402,7 +2399,7 @@
         <v>116</v>
       </c>
       <c r="B116" s="1">
-        <v>138.3407139438463</v>
+        <v>143.5420306916623</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -2410,7 +2407,7 @@
         <v>117</v>
       </c>
       <c r="B117" s="1">
-        <v>138.4211582361048</v>
+        <v>143.5488134326128</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -2418,7 +2415,7 @@
         <v>118</v>
       </c>
       <c r="B118" s="1">
-        <v>138.4866970059065</v>
+        <v>143.7207333775848</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -2426,7 +2423,7 @@
         <v>119</v>
       </c>
       <c r="B119" s="1">
-        <v>138.51020449617</v>
+        <v>143.9316867177185</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -2434,7 +2431,7 @@
         <v>120</v>
       </c>
       <c r="B120" s="1">
-        <v>138.5965974405061</v>
+        <v>143.9628823579038</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -2442,7 +2439,7 @@
         <v>121</v>
       </c>
       <c r="B121" s="1">
-        <v>138.6439061493694</v>
+        <v>144.0735431454528</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -2450,7 +2447,7 @@
         <v>122</v>
       </c>
       <c r="B122" s="1">
-        <v>138.7571141646627</v>
+        <v>144.2799161089162</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -2458,7 +2455,7 @@
         <v>123</v>
       </c>
       <c r="B123" s="1">
-        <v>138.7685782053862</v>
+        <v>144.3157882588583</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -2466,7 +2463,7 @@
         <v>124</v>
       </c>
       <c r="B124" s="1">
-        <v>138.8035104356895</v>
+        <v>144.7166642338104</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -2474,7 +2471,7 @@
         <v>125</v>
       </c>
       <c r="B125" s="1">
-        <v>138.8507674410837</v>
+        <v>144.7863083684602</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -2482,7 +2479,7 @@
         <v>126</v>
       </c>
       <c r="B126" s="1">
-        <v>139.0786717999565</v>
+        <v>144.8172267752956</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -2490,7 +2487,7 @@
         <v>127</v>
       </c>
       <c r="B127" s="1">
-        <v>139.3553137449881</v>
+        <v>145.1111024547492</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -2498,7 +2495,7 @@
         <v>128</v>
       </c>
       <c r="B128" s="1">
-        <v>139.4509394224665</v>
+        <v>145.1199216672256</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -2506,7 +2503,7 @@
         <v>129</v>
       </c>
       <c r="B129" s="1">
-        <v>139.5995800162935</v>
+        <v>145.1313097846991</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -2514,7 +2511,7 @@
         <v>130</v>
       </c>
       <c r="B130" s="1">
-        <v>139.6430871945962</v>
+        <v>145.2735781460551</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -2522,7 +2519,7 @@
         <v>131</v>
       </c>
       <c r="B131" s="1">
-        <v>139.7111430905039</v>
+        <v>145.2793893797502</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -2530,7 +2527,7 @@
         <v>132</v>
       </c>
       <c r="B132" s="1">
-        <v>139.8026609577829</v>
+        <v>145.414547803106</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -2538,7 +2535,7 @@
         <v>133</v>
       </c>
       <c r="B133" s="1">
-        <v>139.8209585202318</v>
+        <v>145.4521356941933</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -2546,7 +2543,7 @@
         <v>134</v>
       </c>
       <c r="B134" s="1">
-        <v>139.8939504467421</v>
+        <v>145.4928880053916</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -2554,7 +2551,7 @@
         <v>135</v>
       </c>
       <c r="B135" s="1">
-        <v>139.906775555251</v>
+        <v>145.5406891148138</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -2562,7 +2559,7 @@
         <v>136</v>
       </c>
       <c r="B136" s="1">
-        <v>139.9770606935549</v>
+        <v>145.5586697850432</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -2570,7 +2567,7 @@
         <v>137</v>
       </c>
       <c r="B137" s="1">
-        <v>139.9960415506373</v>
+        <v>145.6874196520826</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -2578,7 +2575,7 @@
         <v>138</v>
       </c>
       <c r="B138" s="1">
-        <v>140.087531310638</v>
+        <v>145.7771804789558</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -2586,7 +2583,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="1">
-        <v>140.2232973664062</v>
+        <v>145.8478560641873</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -2594,7 +2591,7 @@
         <v>140</v>
       </c>
       <c r="B140" s="1">
-        <v>140.3483678496279</v>
+        <v>145.8673501442741</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -2602,7 +2599,7 @@
         <v>141</v>
       </c>
       <c r="B141" s="1">
-        <v>140.3485557404363</v>
+        <v>145.9514855728845</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -2610,7 +2607,7 @@
         <v>142</v>
       </c>
       <c r="B142" s="1">
-        <v>140.3746133548444</v>
+        <v>146.0115969721941</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -2618,7 +2615,7 @@
         <v>143</v>
       </c>
       <c r="B143" s="1">
-        <v>140.440653367782</v>
+        <v>146.0122492886034</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -2626,7 +2623,7 @@
         <v>144</v>
       </c>
       <c r="B144" s="1">
-        <v>140.5065422606641</v>
+        <v>146.0291730023319</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -2634,7 +2631,7 @@
         <v>145</v>
       </c>
       <c r="B145" s="1">
-        <v>140.628437593084</v>
+        <v>146.0523272408333</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -2642,7 +2639,7 @@
         <v>146</v>
       </c>
       <c r="B146" s="1">
-        <v>140.7356501155672</v>
+        <v>146.1333484083241</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -2650,7 +2647,7 @@
         <v>147</v>
       </c>
       <c r="B147" s="1">
-        <v>140.8256862916625</v>
+        <v>146.2582220024996</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -2658,7 +2655,7 @@
         <v>148</v>
       </c>
       <c r="B148" s="1">
-        <v>140.8795660121339</v>
+        <v>146.2697088410681</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -2666,7 +2663,7 @@
         <v>149</v>
       </c>
       <c r="B149" s="1">
-        <v>141.0569639842882</v>
+        <v>146.4657448102584</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -2674,7 +2671,7 @@
         <v>150</v>
       </c>
       <c r="B150" s="1">
-        <v>141.1069128464913</v>
+        <v>146.5310366576604</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -2682,7 +2679,7 @@
         <v>151</v>
       </c>
       <c r="B151" s="1">
-        <v>141.1958154670565</v>
+        <v>146.632406937648</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -2690,7 +2687,7 @@
         <v>152</v>
       </c>
       <c r="B152" s="1">
-        <v>141.2256668516544</v>
+        <v>146.7111077489883</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -2698,7 +2695,7 @@
         <v>153</v>
       </c>
       <c r="B153" s="1">
-        <v>141.2625708093179</v>
+        <v>146.7136265496125</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -2706,7 +2703,7 @@
         <v>154</v>
       </c>
       <c r="B154" s="1">
-        <v>141.3006451766136</v>
+        <v>146.8226257200928</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -2714,7 +2711,7 @@
         <v>155</v>
       </c>
       <c r="B155" s="1">
-        <v>141.4046324341625</v>
+        <v>146.8562748736842</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -2722,7 +2719,7 @@
         <v>156</v>
       </c>
       <c r="B156" s="1">
-        <v>141.4206552982397</v>
+        <v>147.0311818369598</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -2730,7 +2727,7 @@
         <v>157</v>
       </c>
       <c r="B157" s="1">
-        <v>141.4387792454595</v>
+        <v>147.1558314162329</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -2738,7 +2735,7 @@
         <v>158</v>
       </c>
       <c r="B158" s="1">
-        <v>141.5684044089679</v>
+        <v>147.1801675964391</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -2746,7 +2743,7 @@
         <v>159</v>
       </c>
       <c r="B159" s="1">
-        <v>141.6161116867899</v>
+        <v>147.3171115334467</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -2754,7 +2751,7 @@
         <v>160</v>
       </c>
       <c r="B160" s="1">
-        <v>141.6510644034684</v>
+        <v>147.4876510778121</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -2762,7 +2759,7 @@
         <v>161</v>
       </c>
       <c r="B161" s="1">
-        <v>141.6587707806821</v>
+        <v>147.7443310395245</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -2770,7 +2767,7 @@
         <v>162</v>
       </c>
       <c r="B162" s="1">
-        <v>141.6771197644478</v>
+        <v>147.9050371506544</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -2778,7 +2775,7 @@
         <v>163</v>
       </c>
       <c r="B163" s="1">
-        <v>141.7247944877044</v>
+        <v>148.00676430756</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -2786,7 +2783,7 @@
         <v>164</v>
       </c>
       <c r="B164" s="1">
-        <v>141.9242505662458</v>
+        <v>148.0199508661514</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -2794,7 +2791,7 @@
         <v>165</v>
       </c>
       <c r="B165" s="1">
-        <v>142.2461284043449</v>
+        <v>148.1034868633982</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -2802,7 +2799,7 @@
         <v>166</v>
       </c>
       <c r="B166" s="1">
-        <v>142.2660657866045</v>
+        <v>148.1228045553516</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -2810,7 +2807,7 @@
         <v>167</v>
       </c>
       <c r="B167" s="1">
-        <v>142.5913577275146</v>
+        <v>148.168000310745</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -2818,7 +2815,7 @@
         <v>168</v>
       </c>
       <c r="B168" s="1">
-        <v>142.7682149389013</v>
+        <v>148.204425236508</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -2826,7 +2823,7 @@
         <v>169</v>
       </c>
       <c r="B169" s="1">
-        <v>142.7769740796847</v>
+        <v>148.2258314562386</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -2834,7 +2831,7 @@
         <v>170</v>
       </c>
       <c r="B170" s="1">
-        <v>142.7772072341252</v>
+        <v>148.4803374113282</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -2842,7 +2839,7 @@
         <v>171</v>
       </c>
       <c r="B171" s="1">
-        <v>142.8030582252101</v>
+        <v>148.5213253562977</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -2850,7 +2847,7 @@
         <v>172</v>
       </c>
       <c r="B172" s="1">
-        <v>142.9079512128387</v>
+        <v>148.5227436888644</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -2858,7 +2855,7 @@
         <v>173</v>
       </c>
       <c r="B173" s="1">
-        <v>142.9207598073575</v>
+        <v>148.5504024193307</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -2866,7 +2863,7 @@
         <v>174</v>
       </c>
       <c r="B174" s="1">
-        <v>142.9239304007165</v>
+        <v>148.6592715474537</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -2874,7 +2871,7 @@
         <v>175</v>
       </c>
       <c r="B175" s="1">
-        <v>143.4652562835982</v>
+        <v>148.6772576143061</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -2882,7 +2879,7 @@
         <v>176</v>
       </c>
       <c r="B176" s="1">
-        <v>143.4667154973108</v>
+        <v>148.7165859347409</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -2890,7 +2887,7 @@
         <v>177</v>
       </c>
       <c r="B177" s="1">
-        <v>143.6060919567858</v>
+        <v>148.7397161833984</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -2898,7 +2895,7 @@
         <v>178</v>
       </c>
       <c r="B178" s="1">
-        <v>143.7159331385198</v>
+        <v>148.8116249814337</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -2906,7 +2903,7 @@
         <v>179</v>
       </c>
       <c r="B179" s="1">
-        <v>143.8215703284683</v>
+        <v>148.8484754637867</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -2914,7 +2911,7 @@
         <v>180</v>
       </c>
       <c r="B180" s="1">
-        <v>143.8592658683947</v>
+        <v>148.8786873545211</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -2922,7 +2919,7 @@
         <v>181</v>
       </c>
       <c r="B181" s="1">
-        <v>143.9441540201111</v>
+        <v>148.9753596639122</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -2930,7 +2927,7 @@
         <v>182</v>
       </c>
       <c r="B182" s="1">
-        <v>144.0310599305928</v>
+        <v>148.9902393566263</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -2938,7 +2935,7 @@
         <v>183</v>
       </c>
       <c r="B183" s="1">
-        <v>144.3812576173013</v>
+        <v>149.4288426412054</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -2946,7 +2943,7 @@
         <v>184</v>
       </c>
       <c r="B184" s="1">
-        <v>144.6296193322121</v>
+        <v>149.8001924499408</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -2954,7 +2951,7 @@
         <v>185</v>
       </c>
       <c r="B185" s="1">
-        <v>144.7082894170406</v>
+        <v>149.9903368779129</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -2962,7 +2959,7 @@
         <v>186</v>
       </c>
       <c r="B186" s="1">
-        <v>144.7619218793243</v>
+        <v>150.1433452796223</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -2970,7 +2967,7 @@
         <v>187</v>
       </c>
       <c r="B187" s="1">
-        <v>144.900531498821</v>
+        <v>150.2461938227445</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -2978,7 +2975,7 @@
         <v>188</v>
       </c>
       <c r="B188" s="1">
-        <v>144.9718432923428</v>
+        <v>150.2610035622114</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -2986,7 +2983,7 @@
         <v>189</v>
       </c>
       <c r="B189" s="1">
-        <v>145.0110270938888</v>
+        <v>150.4429086668608</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -2994,7 +2991,7 @@
         <v>190</v>
       </c>
       <c r="B190" s="1">
-        <v>145.1315401574591</v>
+        <v>150.4442443375513</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -3002,7 +2999,7 @@
         <v>191</v>
       </c>
       <c r="B191" s="1">
-        <v>145.3445901710574</v>
+        <v>150.565669745216</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -3010,7 +3007,7 @@
         <v>192</v>
       </c>
       <c r="B192" s="1">
-        <v>145.4620563240676</v>
+        <v>150.6715356849958</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -3018,7 +3015,7 @@
         <v>193</v>
       </c>
       <c r="B193" s="1">
-        <v>145.4778827199088</v>
+        <v>150.7232644936856</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -3026,7 +3023,7 @@
         <v>194</v>
       </c>
       <c r="B194" s="1">
-        <v>145.549133276064</v>
+        <v>150.8990004468832</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -3034,7 +3031,7 @@
         <v>195</v>
       </c>
       <c r="B195" s="1">
-        <v>145.6312400891725</v>
+        <v>151.1941754507485</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -3042,7 +3039,7 @@
         <v>196</v>
       </c>
       <c r="B196" s="1">
-        <v>145.7469695643437</v>
+        <v>151.1944962367647</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -3050,7 +3047,7 @@
         <v>197</v>
       </c>
       <c r="B197" s="1">
-        <v>145.8880896327759</v>
+        <v>151.6552032242236</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -3058,7 +3055,7 @@
         <v>198</v>
       </c>
       <c r="B198" s="1">
-        <v>145.9411713567546</v>
+        <v>151.7458986072924</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -3066,7 +3063,7 @@
         <v>199</v>
       </c>
       <c r="B199" s="1">
-        <v>145.9649249741741</v>
+        <v>151.7930480175272</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -3074,7 +3071,7 @@
         <v>200</v>
       </c>
       <c r="B200" s="1">
-        <v>146.0232557876939</v>
+        <v>151.8357553472608</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -3082,7 +3079,7 @@
         <v>201</v>
       </c>
       <c r="B201" s="1">
-        <v>146.0960268006589</v>
+        <v>151.8627797313298</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -3090,7 +3087,7 @@
         <v>202</v>
       </c>
       <c r="B202" s="1">
-        <v>146.4210553002168</v>
+        <v>152.0898108056934</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -3098,7 +3095,7 @@
         <v>203</v>
       </c>
       <c r="B203" s="1">
-        <v>146.609469287127</v>
+        <v>152.2883628158504</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -3106,7 +3103,7 @@
         <v>204</v>
       </c>
       <c r="B204" s="1">
-        <v>146.618830036765</v>
+        <v>152.3298878902208</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -3114,7 +3111,7 @@
         <v>205</v>
       </c>
       <c r="B205" s="1">
-        <v>146.6300595650501</v>
+        <v>152.333804973313</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -3122,7 +3119,7 @@
         <v>206</v>
       </c>
       <c r="B206" s="1">
-        <v>146.9177979031219</v>
+        <v>152.4224023976398</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -3130,7 +3127,7 @@
         <v>207</v>
       </c>
       <c r="B207" s="1">
-        <v>146.9470351554011</v>
+        <v>152.4422426524919</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -3138,7 +3135,7 @@
         <v>208</v>
       </c>
       <c r="B208" s="1">
-        <v>147.1261494758413</v>
+        <v>152.4592499398751</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -3146,7 +3143,7 @@
         <v>209</v>
       </c>
       <c r="B209" s="1">
-        <v>147.1620940082197</v>
+        <v>152.6343407855723</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -3154,7 +3151,7 @@
         <v>210</v>
       </c>
       <c r="B210" s="1">
-        <v>147.5055430759965</v>
+        <v>152.7597854337902</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -3162,7 +3159,7 @@
         <v>211</v>
       </c>
       <c r="B211" s="1">
-        <v>147.5892701251681</v>
+        <v>152.7614276342225</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -3170,7 +3167,7 @@
         <v>212</v>
       </c>
       <c r="B212" s="1">
-        <v>147.6484443731759</v>
+        <v>152.8238586764627</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -3178,7 +3175,7 @@
         <v>213</v>
       </c>
       <c r="B213" s="1">
-        <v>147.7218641037902</v>
+        <v>153.3339948378739</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -3186,7 +3183,7 @@
         <v>214</v>
       </c>
       <c r="B214" s="1">
-        <v>148.1669075477361</v>
+        <v>153.7322509652283</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -3194,7 +3191,7 @@
         <v>215</v>
       </c>
       <c r="B215" s="1">
-        <v>148.2450341450622</v>
+        <v>153.8254827358357</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -3202,7 +3199,7 @@
         <v>216</v>
       </c>
       <c r="B216" s="1">
-        <v>148.3966703136136</v>
+        <v>153.9885365552946</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -3210,7 +3207,7 @@
         <v>217</v>
       </c>
       <c r="B217" s="1">
-        <v>148.4067976949974</v>
+        <v>154.1222109275584</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -3218,7 +3215,7 @@
         <v>218</v>
       </c>
       <c r="B218" s="1">
-        <v>148.4136434324771</v>
+        <v>154.1747385777701</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -3226,7 +3223,7 @@
         <v>219</v>
       </c>
       <c r="B219" s="1">
-        <v>148.9468252019111</v>
+        <v>154.926036710481</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -3234,7 +3231,7 @@
         <v>220</v>
       </c>
       <c r="B220" s="1">
-        <v>149.0213623652791</v>
+        <v>154.9622470014539</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -3242,7 +3239,7 @@
         <v>221</v>
       </c>
       <c r="B221" s="1">
-        <v>149.473024430074</v>
+        <v>155.4703577851581</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -3250,7 +3247,7 @@
         <v>222</v>
       </c>
       <c r="B222" s="1">
-        <v>149.6824656618896</v>
+        <v>155.6121883410259</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -3258,7 +3255,7 @@
         <v>223</v>
       </c>
       <c r="B223" s="1">
-        <v>150.0492026666304</v>
+        <v>155.7155336731865</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -3266,7 +3263,7 @@
         <v>224</v>
       </c>
       <c r="B224" s="1">
-        <v>150.1477084628251</v>
+        <v>155.7719984672208</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -3274,7 +3271,7 @@
         <v>225</v>
       </c>
       <c r="B225" s="1">
-        <v>150.1993502467734</v>
+        <v>155.8151466070369</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -3282,7 +3279,7 @@
         <v>226</v>
       </c>
       <c r="B226" s="1">
-        <v>150.3101217111794</v>
+        <v>156.0587005592275</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -3290,7 +3287,7 @@
         <v>227</v>
       </c>
       <c r="B227" s="1">
-        <v>150.5355141758329</v>
+        <v>156.8233377591846</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -3298,7 +3295,7 @@
         <v>228</v>
       </c>
       <c r="B228" s="1">
-        <v>150.645477427521</v>
+        <v>156.8422495088006</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -3306,7 +3303,7 @@
         <v>229</v>
       </c>
       <c r="B229" s="1">
-        <v>150.6899197247542</v>
+        <v>156.8889817059661</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -3314,7 +3311,7 @@
         <v>230</v>
       </c>
       <c r="B230" s="1">
-        <v>150.8105142178837</v>
+        <v>157.1591824532886</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -3322,7 +3319,7 @@
         <v>231</v>
       </c>
       <c r="B231" s="1">
-        <v>150.8894088828394</v>
+        <v>157.5731518526055</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -3330,7 +3327,7 @@
         <v>232</v>
       </c>
       <c r="B232" s="1">
-        <v>150.9575199558835</v>
+        <v>157.6506861245939</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -3338,7 +3335,7 @@
         <v>233</v>
       </c>
       <c r="B233" s="1">
-        <v>150.9637031554629</v>
+        <v>157.690312310653</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -3346,7 +3343,7 @@
         <v>234</v>
       </c>
       <c r="B234" s="1">
-        <v>150.9791037994039</v>
+        <v>157.7221212123568</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -3354,7 +3351,7 @@
         <v>235</v>
       </c>
       <c r="B235" s="1">
-        <v>150.9853885011604</v>
+        <v>157.7715499085963</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -3362,7 +3359,7 @@
         <v>236</v>
       </c>
       <c r="B236" s="1">
-        <v>151.0763943520546</v>
+        <v>157.8852617638525</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -3370,7 +3367,7 @@
         <v>237</v>
       </c>
       <c r="B237" s="1">
-        <v>151.1001345514663</v>
+        <v>158.1512341091337</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -3378,7 +3375,7 @@
         <v>238</v>
       </c>
       <c r="B238" s="1">
-        <v>151.3124496785799</v>
+        <v>158.1967608879753</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -3386,7 +3383,7 @@
         <v>239</v>
       </c>
       <c r="B239" s="1">
-        <v>151.4253227512033</v>
+        <v>158.4279467545706</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -3394,7 +3391,7 @@
         <v>240</v>
       </c>
       <c r="B240" s="1">
-        <v>151.4766083595992</v>
+        <v>159.0880236059803</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -3402,7 +3399,7 @@
         <v>241</v>
       </c>
       <c r="B241" s="1">
-        <v>151.5086337840906</v>
+        <v>159.1537021783387</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -3410,7 +3407,7 @@
         <v>242</v>
       </c>
       <c r="B242" s="1">
-        <v>151.708502569371</v>
+        <v>159.4552300614482</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -3418,7 +3415,7 @@
         <v>243</v>
       </c>
       <c r="B243" s="1">
-        <v>151.7300167863497</v>
+        <v>159.544380796584</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -3426,7 +3423,7 @@
         <v>244</v>
       </c>
       <c r="B244" s="1">
-        <v>151.905518121769</v>
+        <v>159.6581088213393</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -3434,7 +3431,7 @@
         <v>245</v>
       </c>
       <c r="B245" s="1">
-        <v>152.2920661871823</v>
+        <v>159.8192609539429</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -3442,7 +3439,7 @@
         <v>246</v>
       </c>
       <c r="B246" s="1">
-        <v>152.3520721129422</v>
+        <v>159.9366583040839</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -3450,7 +3447,7 @@
         <v>247</v>
       </c>
       <c r="B247" s="1">
-        <v>152.6078582155396</v>
+        <v>160.0755362125547</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -3458,7 +3455,7 @@
         <v>248</v>
       </c>
       <c r="B248" s="1">
-        <v>153.8756735686069</v>
+        <v>160.3321714190521</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -3466,7 +3463,7 @@
         <v>249</v>
       </c>
       <c r="B249" s="1">
-        <v>154.1600892758226</v>
+        <v>160.3863162968006</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -3474,7 +3471,7 @@
         <v>250</v>
       </c>
       <c r="B250" s="1">
-        <v>154.2327565694047</v>
+        <v>160.3951568308797</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -3482,7 +3479,7 @@
         <v>251</v>
       </c>
       <c r="B251" s="1">
-        <v>154.252015360337</v>
+        <v>160.5210859226177</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -3490,7 +3487,7 @@
         <v>252</v>
       </c>
       <c r="B252" s="1">
-        <v>154.3948777935419</v>
+        <v>161.318755584536</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -3498,7 +3495,7 @@
         <v>253</v>
       </c>
       <c r="B253" s="1">
-        <v>154.4685559462872</v>
+        <v>161.8106725925103</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -3506,7 +3503,7 @@
         <v>254</v>
       </c>
       <c r="B254" s="1">
-        <v>154.6003353282635</v>
+        <v>162.0789813233197</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -3514,7 +3511,7 @@
         <v>255</v>
       </c>
       <c r="B255" s="1">
-        <v>154.6018814657929</v>
+        <v>162.1404218765388</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -3522,7 +3519,7 @@
         <v>256</v>
       </c>
       <c r="B256" s="1">
-        <v>154.6083710380927</v>
+        <v>162.1926279569011</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -3530,7 +3527,7 @@
         <v>257</v>
       </c>
       <c r="B257" s="1">
-        <v>155.3026895802803</v>
+        <v>162.2340283588514</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -3538,7 +3535,7 @@
         <v>258</v>
       </c>
       <c r="B258" s="1">
-        <v>155.6617700295029</v>
+        <v>162.5719384447257</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -3546,7 +3543,7 @@
         <v>259</v>
       </c>
       <c r="B259" s="1">
-        <v>156.269461302709</v>
+        <v>162.6360116283743</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -3554,7 +3551,7 @@
         <v>260</v>
       </c>
       <c r="B260" s="1">
-        <v>156.3811840841785</v>
+        <v>162.775587843783</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -3562,7 +3559,7 @@
         <v>261</v>
       </c>
       <c r="B261" s="1">
-        <v>156.4844871611789</v>
+        <v>163.2059727441025</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -3570,7 +3567,7 @@
         <v>262</v>
       </c>
       <c r="B262" s="1">
-        <v>156.71448965825</v>
+        <v>163.6008492178738</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -3578,7 +3575,7 @@
         <v>263</v>
       </c>
       <c r="B263" s="1">
-        <v>156.9596804566893</v>
+        <v>163.61173686411</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -3586,7 +3583,7 @@
         <v>264</v>
       </c>
       <c r="B264" s="1">
-        <v>156.9924778239875</v>
+        <v>163.8870313627493</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -3594,7 +3591,7 @@
         <v>265</v>
       </c>
       <c r="B265" s="1">
-        <v>157.3207984664355</v>
+        <v>164.7343138404654</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -3602,7 +3599,7 @@
         <v>266</v>
       </c>
       <c r="B266" s="1">
-        <v>157.5136453359733</v>
+        <v>164.7862566176076</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -3610,7 +3607,7 @@
         <v>267</v>
       </c>
       <c r="B267" s="1">
-        <v>157.9963212041921</v>
+        <v>165.2712112287705</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -3618,7 +3615,7 @@
         <v>268</v>
       </c>
       <c r="B268" s="1">
-        <v>158.1300521386454</v>
+        <v>165.7478693885261</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -3626,7 +3623,7 @@
         <v>269</v>
       </c>
       <c r="B269" s="1">
-        <v>159.0841880240827</v>
+        <v>165.9362414392656</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -3634,7 +3631,7 @@
         <v>270</v>
       </c>
       <c r="B270" s="1">
-        <v>159.8288978874638</v>
+        <v>166.7672638145179</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -3642,7 +3639,7 @@
         <v>271</v>
       </c>
       <c r="B271" s="1">
-        <v>159.9539834285392</v>
+        <v>167.1012778048138</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -3650,7 +3647,7 @@
         <v>272</v>
       </c>
       <c r="B272" s="1">
-        <v>159.9647300892068</v>
+        <v>167.2588838695628</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -3658,7 +3655,7 @@
         <v>273</v>
       </c>
       <c r="B273" s="1">
-        <v>160.2053683329975</v>
+        <v>167.8767839534319</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -3666,7 +3663,7 @@
         <v>274</v>
       </c>
       <c r="B274" s="1">
-        <v>160.7580139054633</v>
+        <v>167.9573475553624</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -3674,7 +3671,7 @@
         <v>275</v>
       </c>
       <c r="B275" s="1">
-        <v>161.2535662379121</v>
+        <v>168.1062429415455</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -3682,7 +3679,7 @@
         <v>276</v>
       </c>
       <c r="B276" s="1">
-        <v>161.4619054436921</v>
+        <v>168.4439175777551</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -3690,7 +3687,7 @@
         <v>277</v>
       </c>
       <c r="B277" s="1">
-        <v>161.5597999942993</v>
+        <v>168.7398494976057</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -3698,7 +3695,7 @@
         <v>278</v>
       </c>
       <c r="B278" s="1">
-        <v>161.8455923485839</v>
+        <v>169.0202118435182</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -3706,7 +3703,7 @@
         <v>279</v>
       </c>
       <c r="B279" s="1">
-        <v>161.8891411155313</v>
+        <v>169.9042838465698</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -3714,7 +3711,7 @@
         <v>280</v>
       </c>
       <c r="B280" s="1">
-        <v>161.927401454433</v>
+        <v>169.9495084841492</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -3722,7 +3719,7 @@
         <v>281</v>
       </c>
       <c r="B281" s="1">
-        <v>163.0371095703058</v>
+        <v>171.4245788359831</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -3730,7 +3727,7 @@
         <v>282</v>
       </c>
       <c r="B282" s="1">
-        <v>163.17444214829</v>
+        <v>171.7541414008859</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -3738,7 +3735,7 @@
         <v>283</v>
       </c>
       <c r="B283" s="1">
-        <v>163.2382418676684</v>
+        <v>171.8209673604115</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -3746,7 +3743,7 @@
         <v>284</v>
       </c>
       <c r="B284" s="1">
-        <v>163.2795561388018</v>
+        <v>172.5877198703604</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -3754,7 +3751,7 @@
         <v>285</v>
       </c>
       <c r="B285" s="1">
-        <v>163.3710721380043</v>
+        <v>173.0898488938615</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -3762,7 +3759,7 @@
         <v>286</v>
       </c>
       <c r="B286" s="1">
-        <v>163.4535082713533</v>
+        <v>173.5201968164739</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -3770,7 +3767,7 @@
         <v>287</v>
       </c>
       <c r="B287" s="1">
-        <v>164.004901331472</v>
+        <v>173.8234180936929</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -3778,7 +3775,7 @@
         <v>288</v>
       </c>
       <c r="B288" s="1">
-        <v>164.0599612611061</v>
+        <v>174.1693606352181</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -3786,7 +3783,7 @@
         <v>289</v>
       </c>
       <c r="B289" s="1">
-        <v>164.5686930407567</v>
+        <v>174.6461847681058</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -3794,7 +3791,7 @@
         <v>290</v>
       </c>
       <c r="B290" s="1">
-        <v>164.7311626574242</v>
+        <v>174.6466723000609</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -3802,7 +3799,7 @@
         <v>291</v>
       </c>
       <c r="B291" s="1">
-        <v>164.8394018521705</v>
+        <v>175.1609691669011</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -3810,7 +3807,7 @@
         <v>292</v>
       </c>
       <c r="B292" s="1">
-        <v>164.8731496656783</v>
+        <v>175.1686566000805</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -3818,7 +3815,7 @@
         <v>293</v>
       </c>
       <c r="B293" s="1">
-        <v>165.4870833950229</v>
+        <v>175.4405520769</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -3826,7 +3823,7 @@
         <v>294</v>
       </c>
       <c r="B294" s="1">
-        <v>165.5519884010992</v>
+        <v>175.9644073922579</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -3834,7 +3831,7 @@
         <v>295</v>
       </c>
       <c r="B295" s="1">
-        <v>167.2323068177305</v>
+        <v>176.6277490172018</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -3842,7 +3839,7 @@
         <v>296</v>
       </c>
       <c r="B296" s="1">
-        <v>167.7348610695898</v>
+        <v>176.9675882803405</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -3850,7 +3847,7 @@
         <v>297</v>
       </c>
       <c r="B297" s="1">
-        <v>168.0790200670218</v>
+        <v>177.6893531672492</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -3858,7 +3855,7 @@
         <v>298</v>
       </c>
       <c r="B298" s="1">
-        <v>168.1558165004512</v>
+        <v>178.0355224079531</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -3866,7 +3863,7 @@
         <v>299</v>
       </c>
       <c r="B299" s="1">
-        <v>168.6291700609935</v>
+        <v>178.1942045041361</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -3874,7 +3871,7 @@
         <v>300</v>
       </c>
       <c r="B300" s="1">
-        <v>168.9476128216828</v>
+        <v>182.1629781173368</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -3882,7 +3879,7 @@
         <v>301</v>
       </c>
       <c r="B301" s="1">
-        <v>170.7109438438289</v>
+        <v>182.3767807966469</v>
       </c>
     </row>
     <row r="302" spans="1:2">
@@ -3890,7 +3887,7 @@
         <v>302</v>
       </c>
       <c r="B302" s="1">
-        <v>170.9471991350086</v>
+        <v>182.3985777141801</v>
       </c>
     </row>
     <row r="303" spans="1:2">
@@ -3898,7 +3895,7 @@
         <v>303</v>
       </c>
       <c r="B303" s="1">
-        <v>171.8213109448897</v>
+        <v>184.6303764313633</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -3906,7 +3903,7 @@
         <v>304</v>
       </c>
       <c r="B304" s="1">
-        <v>172.0525568004913</v>
+        <v>184.8996760724754</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -3914,7 +3911,7 @@
         <v>305</v>
       </c>
       <c r="B305" s="1">
-        <v>172.9739813215777</v>
+        <v>186.3484364629211</v>
       </c>
     </row>
     <row r="306" spans="1:2">
@@ -3922,7 +3919,7 @@
         <v>306</v>
       </c>
       <c r="B306" s="1">
-        <v>173.5287224213129</v>
+        <v>186.6565012692695</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -3930,7 +3927,7 @@
         <v>307</v>
       </c>
       <c r="B307" s="1">
-        <v>173.8469730188513</v>
+        <v>186.8949846831205</v>
       </c>
     </row>
     <row r="308" spans="1:2">
@@ -3938,7 +3935,7 @@
         <v>308</v>
       </c>
       <c r="B308" s="1">
-        <v>174.2487607349872</v>
+        <v>187.8209017506827</v>
       </c>
     </row>
     <row r="309" spans="1:2">
@@ -3946,7 +3943,7 @@
         <v>309</v>
       </c>
       <c r="B309" s="1">
-        <v>174.4171073700907</v>
+        <v>188.4294479710993</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -3954,7 +3951,7 @@
         <v>310</v>
       </c>
       <c r="B310" s="1">
-        <v>177.0189177543051</v>
+        <v>189.8091139521081</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -3962,7 +3959,7 @@
         <v>311</v>
       </c>
       <c r="B311" s="1">
-        <v>177.0984002931595</v>
+        <v>189.9161194093101</v>
       </c>
     </row>
     <row r="312" spans="1:2">
@@ -3970,7 +3967,7 @@
         <v>312</v>
       </c>
       <c r="B312" s="1">
-        <v>177.1582505079601</v>
+        <v>190.5096572645835</v>
       </c>
     </row>
     <row r="313" spans="1:2">
@@ -3978,7 +3975,7 @@
         <v>313</v>
       </c>
       <c r="B313" s="1">
-        <v>179.3192113113045</v>
+        <v>191.1506418617892</v>
       </c>
     </row>
     <row r="314" spans="1:2">
@@ -3986,7 +3983,7 @@
         <v>314</v>
       </c>
       <c r="B314" s="1">
-        <v>179.3939986394354</v>
+        <v>192.4061441295251</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -3994,7 +3991,7 @@
         <v>315</v>
       </c>
       <c r="B315" s="1">
-        <v>179.480617254217</v>
+        <v>192.5412637843312</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -4002,7 +3999,7 @@
         <v>316</v>
       </c>
       <c r="B316" s="1">
-        <v>180.1643099701507</v>
+        <v>193.145301612815</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -4010,7 +4007,7 @@
         <v>317</v>
       </c>
       <c r="B317" s="1">
-        <v>180.1858302979921</v>
+        <v>193.7785972366965</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -4018,7 +4015,7 @@
         <v>318</v>
       </c>
       <c r="B318" s="1">
-        <v>181.3191028228078</v>
+        <v>194.2755384076055</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -4026,7 +4023,7 @@
         <v>319</v>
       </c>
       <c r="B319" s="1">
-        <v>181.4447829658757</v>
+        <v>194.968050850363</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -4034,7 +4031,7 @@
         <v>320</v>
       </c>
       <c r="B320" s="1">
-        <v>185.0771514550568</v>
+        <v>196.1308526990321</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -4042,7 +4039,7 @@
         <v>321</v>
       </c>
       <c r="B321" s="1">
-        <v>185.8814126436308</v>
+        <v>196.2843049805526</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -4050,7 +4047,7 @@
         <v>322</v>
       </c>
       <c r="B322" s="1">
-        <v>186.0158227849384</v>
+        <v>197.4678031685473</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -4058,7 +4055,7 @@
         <v>323</v>
       </c>
       <c r="B323" s="1">
-        <v>186.7020197528608</v>
+        <v>198.7689075072755</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -4066,7 +4063,7 @@
         <v>324</v>
       </c>
       <c r="B324" s="1">
-        <v>186.8708048136772</v>
+        <v>199.2509332174167</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -4074,7 +4071,7 @@
         <v>325</v>
       </c>
       <c r="B325" s="1">
-        <v>187.2069071719741</v>
+        <v>199.730008983556</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -4082,7 +4079,7 @@
         <v>326</v>
       </c>
       <c r="B326" s="1">
-        <v>189.7452927007889</v>
+        <v>199.8787038733008</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -4090,7 +4087,7 @@
         <v>327</v>
       </c>
       <c r="B327" s="1">
-        <v>190.0556527108427</v>
+        <v>202.8675769825743</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -4098,7 +4095,7 @@
         <v>328</v>
       </c>
       <c r="B328" s="1">
-        <v>190.1349517280545</v>
+        <v>202.9991148398219</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -4106,7 +4103,7 @@
         <v>329</v>
       </c>
       <c r="B329" s="1">
-        <v>191.8613798621345</v>
+        <v>204.7653652253236</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -4114,7 +4111,7 @@
         <v>330</v>
       </c>
       <c r="B330" s="1">
-        <v>192.0021883266455</v>
+        <v>207.1715075900056</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -4122,7 +4119,7 @@
         <v>331</v>
       </c>
       <c r="B331" s="1">
-        <v>192.5943176259993</v>
+        <v>207.7331301217209</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -4130,7 +4127,7 @@
         <v>332</v>
       </c>
       <c r="B332" s="1">
-        <v>194.7137762758161</v>
+        <v>208.864419466937</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -4138,7 +4135,7 @@
         <v>333</v>
       </c>
       <c r="B333" s="1">
-        <v>195.5035144903562</v>
+        <v>209.0820684720069</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -4146,7 +4143,7 @@
         <v>334</v>
       </c>
       <c r="B334" s="1">
-        <v>196.0315747740466</v>
+        <v>209.6265159623706</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -4154,7 +4151,7 @@
         <v>335</v>
       </c>
       <c r="B335" s="1">
-        <v>196.7304819544939</v>
+        <v>209.6996280418062</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -4162,7 +4159,7 @@
         <v>336</v>
       </c>
       <c r="B336" s="1">
-        <v>197.1671883711335</v>
+        <v>210.5671487052272</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -4170,7 +4167,7 @@
         <v>337</v>
       </c>
       <c r="B337" s="1">
-        <v>197.7721212007041</v>
+        <v>211.975948228974</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -4178,7 +4175,7 @@
         <v>338</v>
       </c>
       <c r="B338" s="1">
-        <v>199.1188109960168</v>
+        <v>212.7715625230339</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -4186,7 +4183,7 @@
         <v>339</v>
       </c>
       <c r="B339" s="1">
-        <v>199.2145124429223</v>
+        <v>215.4111322220793</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -4194,7 +4191,7 @@
         <v>340</v>
       </c>
       <c r="B340" s="1">
-        <v>199.4448679790632</v>
+        <v>215.6268381402093</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -4202,7 +4199,7 @@
         <v>341</v>
       </c>
       <c r="B341" s="1">
-        <v>201.0842312111908</v>
+        <v>217.5381073886436</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -4210,7 +4207,7 @@
         <v>342</v>
       </c>
       <c r="B342" s="1">
-        <v>202.1831157205901</v>
+        <v>220.7439310483481</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -4218,7 +4215,7 @@
         <v>343</v>
       </c>
       <c r="B343" s="1">
-        <v>203.1752825231409</v>
+        <v>226.7871563241533</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -4226,7 +4223,7 @@
         <v>344</v>
       </c>
       <c r="B344" s="1">
-        <v>203.8219671485625</v>
+        <v>231.7763632427629</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -4234,7 +4231,7 @@
         <v>345</v>
       </c>
       <c r="B345" s="1">
-        <v>205.202990436334</v>
+        <v>233.3880892230295</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -4242,7 +4239,7 @@
         <v>346</v>
       </c>
       <c r="B346" s="1">
-        <v>206.8254515770182</v>
+        <v>239.0976489638589</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -4250,7 +4247,7 @@
         <v>347</v>
       </c>
       <c r="B347" s="1">
-        <v>210.8055761729698</v>
+        <v>240.1459983451321</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -4258,7 +4255,7 @@
         <v>348</v>
       </c>
       <c r="B348" s="1">
-        <v>213.8394836447769</v>
+        <v>244.739497990157</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -4266,7 +4263,7 @@
         <v>349</v>
       </c>
       <c r="B349" s="1">
-        <v>215.514735130629</v>
+        <v>245.878696221241</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -4274,7 +4271,7 @@
         <v>350</v>
       </c>
       <c r="B350" s="1">
-        <v>217.5750621378892</v>
+        <v>252.7612858151726</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -4282,7 +4279,7 @@
         <v>351</v>
       </c>
       <c r="B351" s="1">
-        <v>225.4136844092101</v>
+        <v>256.962439075991</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -4290,7 +4287,7 @@
         <v>352</v>
       </c>
       <c r="B352" s="1">
-        <v>226.7055263452704</v>
+        <v>270.6698224521361</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -4298,7 +4295,7 @@
         <v>353</v>
       </c>
       <c r="B353" s="1">
-        <v>234.3649565056661</v>
+        <v>271.423862128658</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -4306,7 +4303,7 @@
         <v>354</v>
       </c>
       <c r="B354" s="1">
-        <v>238.6078132078231</v>
+        <v>287.2650587313971</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -4314,7 +4311,7 @@
         <v>355</v>
       </c>
       <c r="B355" s="1">
-        <v>239.3360672016524</v>
+        <v>288.9527169235999</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -4322,7 +4319,7 @@
         <v>356</v>
       </c>
       <c r="B356" s="1">
-        <v>244.2000430188477</v>
+        <v>296.2171892448593</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -4330,7 +4327,7 @@
         <v>357</v>
       </c>
       <c r="B357" s="1">
-        <v>246.6848878556057</v>
+        <v>297.2837277422557</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -4338,7 +4335,7 @@
         <v>358</v>
       </c>
       <c r="B358" s="1">
-        <v>256.1870265265885</v>
+        <v>298.165518083229</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -4346,7 +4343,7 @@
         <v>359</v>
       </c>
       <c r="B359" s="1">
-        <v>262.5401501524642</v>
+        <v>307.7277061033978</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -4354,7 +4351,7 @@
         <v>360</v>
       </c>
       <c r="B360" s="1">
-        <v>263.3466004210608</v>
+        <v>317.9593612186261</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -4362,7 +4359,7 @@
         <v>361</v>
       </c>
       <c r="B361" s="1">
-        <v>266.5758812525153</v>
+        <v>322.2189265119928</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -4370,7 +4367,7 @@
         <v>362</v>
       </c>
       <c r="B362" s="1">
-        <v>294.3008197005457</v>
+        <v>355.1290127954948</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -4378,7 +4375,7 @@
         <v>363</v>
       </c>
       <c r="B363" s="1">
-        <v>296.4510310708426</v>
+        <v>386.9422677527307</v>
       </c>
     </row>
     <row r="364" spans="1:2">
@@ -4386,7 +4383,7 @@
         <v>364</v>
       </c>
       <c r="B364" s="1">
-        <v>320.8465976510635</v>
+        <v>408.3573055448696</v>
       </c>
     </row>
     <row r="365" spans="1:2">
@@ -4394,7 +4391,7 @@
         <v>365</v>
       </c>
       <c r="B365" s="1">
-        <v>325.9014186056987</v>
+        <v>439.6913150972075</v>
       </c>
     </row>
     <row r="366" spans="1:2">
@@ -4402,7 +4399,7 @@
         <v>366</v>
       </c>
       <c r="B366" s="1">
-        <v>382.5463494712144</v>
+        <v>503.5462719615929</v>
       </c>
     </row>
     <row r="367" spans="1:2">
@@ -4410,7 +4407,7 @@
         <v>367</v>
       </c>
       <c r="B367" s="1">
-        <v>386.4418995890168</v>
+        <v>549.581708043965</v>
       </c>
     </row>
     <row r="368" spans="1:2">
@@ -4418,15 +4415,7 @@
         <v>368</v>
       </c>
       <c r="B368" s="1">
-        <v>538.5505230327528</v>
-      </c>
-    </row>
-    <row r="369" spans="1:2">
-      <c r="A369" t="s">
-        <v>369</v>
-      </c>
-      <c r="B369" s="1">
-        <v>2948.165655424706</v>
+        <v>575.1362957276335</v>
       </c>
     </row>
   </sheetData>

--- a/Screener/data/rs_rating_top_30.xlsx
+++ b/Screener/data/rs_rating_top_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="329">
   <si>
     <t>Symbol</t>
   </si>
@@ -22,1102 +22,982 @@
     <t>RS Rating</t>
   </si>
   <si>
-    <t>ORCL</t>
-  </si>
-  <si>
-    <t>SNPS</t>
-  </si>
-  <si>
-    <t>MTR</t>
-  </si>
-  <si>
-    <t>LSCC</t>
-  </si>
-  <si>
-    <t>DELL</t>
-  </si>
-  <si>
-    <t>MLCO</t>
-  </si>
-  <si>
-    <t>PUBM</t>
-  </si>
-  <si>
-    <t>AEIS</t>
+    <t>LUNG</t>
+  </si>
+  <si>
+    <t>ZUO</t>
+  </si>
+  <si>
+    <t>WOR</t>
+  </si>
+  <si>
+    <t>ANGN</t>
+  </si>
+  <si>
+    <t>SCX</t>
+  </si>
+  <si>
+    <t>RELY</t>
+  </si>
+  <si>
+    <t>LTH</t>
+  </si>
+  <si>
+    <t>TWST</t>
+  </si>
+  <si>
+    <t>ASMIY</t>
+  </si>
+  <si>
+    <t>URBN</t>
+  </si>
+  <si>
+    <t>GNRC</t>
+  </si>
+  <si>
+    <t>IMTX</t>
+  </si>
+  <si>
+    <t>WCC</t>
+  </si>
+  <si>
+    <t>DECK</t>
+  </si>
+  <si>
+    <t>ABR</t>
+  </si>
+  <si>
+    <t>NYCB</t>
+  </si>
+  <si>
+    <t>SPSC</t>
+  </si>
+  <si>
+    <t>FND</t>
+  </si>
+  <si>
+    <t>GXO</t>
+  </si>
+  <si>
+    <t>AGRO</t>
+  </si>
+  <si>
+    <t>ALSN</t>
+  </si>
+  <si>
+    <t>MYRG</t>
+  </si>
+  <si>
+    <t>CARS</t>
+  </si>
+  <si>
+    <t>AAN</t>
+  </si>
+  <si>
+    <t>CPA</t>
+  </si>
+  <si>
+    <t>FTNT</t>
+  </si>
+  <si>
+    <t>LECO</t>
+  </si>
+  <si>
+    <t>HELE</t>
+  </si>
+  <si>
+    <t>MTH</t>
+  </si>
+  <si>
+    <t>CNMD</t>
+  </si>
+  <si>
+    <t>CLH</t>
+  </si>
+  <si>
+    <t>PATK</t>
+  </si>
+  <si>
+    <t>PHG</t>
+  </si>
+  <si>
+    <t>GPI</t>
+  </si>
+  <si>
+    <t>GT</t>
+  </si>
+  <si>
+    <t>PRI</t>
+  </si>
+  <si>
+    <t>MLNK</t>
+  </si>
+  <si>
+    <t>NNOX</t>
+  </si>
+  <si>
+    <t>EXP</t>
+  </si>
+  <si>
+    <t>CRS</t>
+  </si>
+  <si>
+    <t>AUPH</t>
+  </si>
+  <si>
+    <t>ERII</t>
+  </si>
+  <si>
+    <t>EDU</t>
+  </si>
+  <si>
+    <t>CSWI</t>
+  </si>
+  <si>
+    <t>ENVA</t>
+  </si>
+  <si>
+    <t>MOMO</t>
+  </si>
+  <si>
+    <t>ARHS</t>
+  </si>
+  <si>
+    <t>IGT</t>
+  </si>
+  <si>
+    <t>ATI</t>
+  </si>
+  <si>
+    <t>HSKA</t>
+  </si>
+  <si>
+    <t>HUBB</t>
+  </si>
+  <si>
+    <t>LZRFY</t>
+  </si>
+  <si>
+    <t>ROKU</t>
+  </si>
+  <si>
+    <t>ATEC</t>
+  </si>
+  <si>
+    <t>ARCB</t>
+  </si>
+  <si>
+    <t>NEWT</t>
+  </si>
+  <si>
+    <t>IESC</t>
+  </si>
+  <si>
+    <t>ASUR</t>
+  </si>
+  <si>
+    <t>NFLX</t>
+  </si>
+  <si>
+    <t>NEOG</t>
+  </si>
+  <si>
+    <t>FCAP</t>
+  </si>
+  <si>
+    <t>THO</t>
+  </si>
+  <si>
+    <t>PEGA</t>
+  </si>
+  <si>
+    <t>ACCD</t>
+  </si>
+  <si>
+    <t>NVT</t>
+  </si>
+  <si>
+    <t>EVO</t>
+  </si>
+  <si>
+    <t>AVDX</t>
+  </si>
+  <si>
+    <t>NUVL</t>
+  </si>
+  <si>
+    <t>AFRM</t>
+  </si>
+  <si>
+    <t>CVGI</t>
+  </si>
+  <si>
+    <t>PCYO</t>
+  </si>
+  <si>
+    <t>HROW</t>
+  </si>
+  <si>
+    <t>CNM</t>
+  </si>
+  <si>
+    <t>CIX</t>
+  </si>
+  <si>
+    <t>ATKR</t>
+  </si>
+  <si>
+    <t>WMS</t>
+  </si>
+  <si>
+    <t>VCEL</t>
+  </si>
+  <si>
+    <t>GTLB</t>
+  </si>
+  <si>
+    <t>NE</t>
+  </si>
+  <si>
+    <t>BILL</t>
+  </si>
+  <si>
+    <t>FROG</t>
+  </si>
+  <si>
+    <t>PETQ</t>
+  </si>
+  <si>
+    <t>AZEK</t>
+  </si>
+  <si>
+    <t>OC</t>
+  </si>
+  <si>
+    <t>APG</t>
+  </si>
+  <si>
+    <t>CELH</t>
+  </si>
+  <si>
+    <t>ABNB</t>
+  </si>
+  <si>
+    <t>NPO</t>
+  </si>
+  <si>
+    <t>IMVT</t>
+  </si>
+  <si>
+    <t>DXPE</t>
+  </si>
+  <si>
+    <t>PKOH</t>
+  </si>
+  <si>
+    <t>ZEUS</t>
+  </si>
+  <si>
+    <t>FTI</t>
+  </si>
+  <si>
+    <t>BWMN</t>
+  </si>
+  <si>
+    <t>FIVN</t>
+  </si>
+  <si>
+    <t>COHR</t>
+  </si>
+  <si>
+    <t>CLS</t>
+  </si>
+  <si>
+    <t>CARG</t>
+  </si>
+  <si>
+    <t>INMD</t>
+  </si>
+  <si>
+    <t>PROF</t>
+  </si>
+  <si>
+    <t>VMW</t>
+  </si>
+  <si>
+    <t>ARGX</t>
+  </si>
+  <si>
+    <t>PAG</t>
+  </si>
+  <si>
+    <t>MLP</t>
+  </si>
+  <si>
+    <t>TGLS</t>
+  </si>
+  <si>
+    <t>EB</t>
+  </si>
+  <si>
+    <t>YELP</t>
+  </si>
+  <si>
+    <t>LAD</t>
+  </si>
+  <si>
+    <t>MATW</t>
+  </si>
+  <si>
+    <t>TMHC</t>
+  </si>
+  <si>
+    <t>ERO</t>
+  </si>
+  <si>
+    <t>DAL</t>
+  </si>
+  <si>
+    <t>JELD</t>
+  </si>
+  <si>
+    <t>ENS</t>
+  </si>
+  <si>
+    <t>MORF</t>
+  </si>
+  <si>
+    <t>NOVA</t>
+  </si>
+  <si>
+    <t>DASH</t>
+  </si>
+  <si>
+    <t>WFRD</t>
+  </si>
+  <si>
+    <t>CXM</t>
+  </si>
+  <si>
+    <t>AZUL</t>
+  </si>
+  <si>
+    <t>ETNB</t>
+  </si>
+  <si>
+    <t>KBH</t>
+  </si>
+  <si>
+    <t>PAM</t>
+  </si>
+  <si>
+    <t>RCMT</t>
+  </si>
+  <si>
+    <t>GTLS</t>
+  </si>
+  <si>
+    <t>CLBR</t>
+  </si>
+  <si>
+    <t>ALGM</t>
+  </si>
+  <si>
+    <t>PHM</t>
+  </si>
+  <si>
+    <t>DDOG</t>
+  </si>
+  <si>
+    <t>HCCI</t>
+  </si>
+  <si>
+    <t>SMID</t>
+  </si>
+  <si>
+    <t>RH</t>
+  </si>
+  <si>
+    <t>BVH</t>
+  </si>
+  <si>
+    <t>BWMX</t>
+  </si>
+  <si>
+    <t>MNDY</t>
+  </si>
+  <si>
+    <t>OII</t>
+  </si>
+  <si>
+    <t>CYD</t>
+  </si>
+  <si>
+    <t>IMRX</t>
+  </si>
+  <si>
+    <t>SHOP</t>
+  </si>
+  <si>
+    <t>IDCC</t>
+  </si>
+  <si>
+    <t>DUOL</t>
+  </si>
+  <si>
+    <t>AEL</t>
+  </si>
+  <si>
+    <t>LPRO</t>
+  </si>
+  <si>
+    <t>NETI</t>
+  </si>
+  <si>
+    <t>BOOT</t>
+  </si>
+  <si>
+    <t>DBRG</t>
+  </si>
+  <si>
+    <t>MRUS</t>
+  </si>
+  <si>
+    <t>MGNI</t>
+  </si>
+  <si>
+    <t>BCC</t>
+  </si>
+  <si>
+    <t>LSANF</t>
+  </si>
+  <si>
+    <t>CAAP</t>
+  </si>
+  <si>
+    <t>GSHD</t>
+  </si>
+  <si>
+    <t>FRD</t>
+  </si>
+  <si>
+    <t>NATR</t>
+  </si>
+  <si>
+    <t>EVI</t>
+  </si>
+  <si>
+    <t>FTAI</t>
+  </si>
+  <si>
+    <t>BLD</t>
+  </si>
+  <si>
+    <t>IIVI</t>
+  </si>
+  <si>
+    <t>LMND</t>
+  </si>
+  <si>
+    <t>PANW</t>
   </si>
   <si>
     <t>HOOD</t>
   </si>
   <si>
-    <t>WCC</t>
-  </si>
-  <si>
-    <t>CSTM</t>
-  </si>
-  <si>
-    <t>RAMP</t>
+    <t>BECN</t>
+  </si>
+  <si>
+    <t>MNSO</t>
+  </si>
+  <si>
+    <t>MTW</t>
+  </si>
+  <si>
+    <t>HUBS</t>
+  </si>
+  <si>
+    <t>TSQ</t>
+  </si>
+  <si>
+    <t>NCLH</t>
+  </si>
+  <si>
+    <t>BRZE</t>
+  </si>
+  <si>
+    <t>FMS</t>
+  </si>
+  <si>
+    <t>SSYS</t>
+  </si>
+  <si>
+    <t>MANH</t>
+  </si>
+  <si>
+    <t>IBP</t>
+  </si>
+  <si>
+    <t>AN</t>
+  </si>
+  <si>
+    <t>AMWD</t>
+  </si>
+  <si>
+    <t>SRDX</t>
+  </si>
+  <si>
+    <t>TDC</t>
+  </si>
+  <si>
+    <t>EXAS</t>
+  </si>
+  <si>
+    <t>ACVA</t>
+  </si>
+  <si>
+    <t>PLAB</t>
+  </si>
+  <si>
+    <t>INTT</t>
+  </si>
+  <si>
+    <t>SGH</t>
+  </si>
+  <si>
+    <t>ETHE</t>
+  </si>
+  <si>
+    <t>AVDL</t>
+  </si>
+  <si>
+    <t>GRVY</t>
+  </si>
+  <si>
+    <t>LZ</t>
+  </si>
+  <si>
+    <t>MDWT</t>
+  </si>
+  <si>
+    <t>RRGB</t>
+  </si>
+  <si>
+    <t>GKOS</t>
+  </si>
+  <si>
+    <t>CRCT</t>
+  </si>
+  <si>
+    <t>PHAT</t>
+  </si>
+  <si>
+    <t>ADBE</t>
+  </si>
+  <si>
+    <t>QS</t>
+  </si>
+  <si>
+    <t>GLBE</t>
+  </si>
+  <si>
+    <t>KRYS</t>
+  </si>
+  <si>
+    <t>ALPN</t>
+  </si>
+  <si>
+    <t>JBL</t>
+  </si>
+  <si>
+    <t>CPS</t>
+  </si>
+  <si>
+    <t>APPF</t>
+  </si>
+  <si>
+    <t>ATLC</t>
+  </si>
+  <si>
+    <t>PSTG</t>
+  </si>
+  <si>
+    <t>ABCM</t>
+  </si>
+  <si>
+    <t>AVGO</t>
+  </si>
+  <si>
+    <t>FOR</t>
+  </si>
+  <si>
+    <t>ALGT</t>
+  </si>
+  <si>
+    <t>BMA</t>
   </si>
   <si>
     <t>CRMT</t>
   </si>
   <si>
-    <t>MACK</t>
-  </si>
-  <si>
-    <t>PRO</t>
-  </si>
-  <si>
-    <t>MOMO</t>
-  </si>
-  <si>
-    <t>GE</t>
-  </si>
-  <si>
-    <t>WST</t>
-  </si>
-  <si>
-    <t>TSM</t>
-  </si>
-  <si>
-    <t>RCMT</t>
-  </si>
-  <si>
-    <t>IGT</t>
-  </si>
-  <si>
-    <t>CDNS</t>
-  </si>
-  <si>
-    <t>PAM</t>
-  </si>
-  <si>
-    <t>NPO</t>
-  </si>
-  <si>
-    <t>TXG</t>
-  </si>
-  <si>
-    <t>PHG</t>
-  </si>
-  <si>
-    <t>MPX</t>
-  </si>
-  <si>
-    <t>BOOT</t>
-  </si>
-  <si>
-    <t>GH</t>
-  </si>
-  <si>
-    <t>RKT</t>
-  </si>
-  <si>
-    <t>CCS</t>
-  </si>
-  <si>
-    <t>TEX</t>
-  </si>
-  <si>
-    <t>GNRC</t>
-  </si>
-  <si>
-    <t>SPSC</t>
-  </si>
-  <si>
-    <t>OII</t>
-  </si>
-  <si>
-    <t>FND</t>
-  </si>
-  <si>
-    <t>LASR</t>
-  </si>
-  <si>
-    <t>TWN</t>
-  </si>
-  <si>
-    <t>TMDX</t>
-  </si>
-  <si>
-    <t>PKOH</t>
-  </si>
-  <si>
-    <t>RCLFU</t>
-  </si>
-  <si>
-    <t>ATI</t>
-  </si>
-  <si>
-    <t>ZEUS</t>
-  </si>
-  <si>
-    <t>VCEL</t>
-  </si>
-  <si>
-    <t>PAG</t>
-  </si>
-  <si>
-    <t>CNM</t>
-  </si>
-  <si>
-    <t>ABNB</t>
-  </si>
-  <si>
-    <t>AUPH</t>
-  </si>
-  <si>
-    <t>APLS</t>
-  </si>
-  <si>
-    <t>MATW</t>
-  </si>
-  <si>
-    <t>MLNK</t>
-  </si>
-  <si>
-    <t>CRM</t>
-  </si>
-  <si>
-    <t>LPRO</t>
-  </si>
-  <si>
-    <t>FTNT</t>
-  </si>
-  <si>
-    <t>SSD</t>
-  </si>
-  <si>
-    <t>PATK</t>
+    <t>CMT</t>
+  </si>
+  <si>
+    <t>EBIX</t>
+  </si>
+  <si>
+    <t>BLU</t>
+  </si>
+  <si>
+    <t>MRVL</t>
+  </si>
+  <si>
+    <t>KRUS</t>
+  </si>
+  <si>
+    <t>PRG</t>
+  </si>
+  <si>
+    <t>DICE</t>
+  </si>
+  <si>
+    <t>FSLY</t>
+  </si>
+  <si>
+    <t>RCL</t>
+  </si>
+  <si>
+    <t>DOCN</t>
+  </si>
+  <si>
+    <t>NGMS</t>
+  </si>
+  <si>
+    <t>RDNT</t>
+  </si>
+  <si>
+    <t>NWLI</t>
+  </si>
+  <si>
+    <t>DV</t>
+  </si>
+  <si>
+    <t>RILY</t>
+  </si>
+  <si>
+    <t>EXTR</t>
+  </si>
+  <si>
+    <t>AXR</t>
+  </si>
+  <si>
+    <t>WRLD</t>
+  </si>
+  <si>
+    <t>GOCO</t>
+  </si>
+  <si>
+    <t>POWL</t>
+  </si>
+  <si>
+    <t>GBX</t>
+  </si>
+  <si>
+    <t>BELFB</t>
+  </si>
+  <si>
+    <t>XP</t>
+  </si>
+  <si>
+    <t>ONON</t>
+  </si>
+  <si>
+    <t>LTRPB</t>
+  </si>
+  <si>
+    <t>STVN</t>
+  </si>
+  <si>
+    <t>MHO</t>
+  </si>
+  <si>
+    <t>SAIA</t>
+  </si>
+  <si>
+    <t>STRL</t>
   </si>
   <si>
     <t>ACAD</t>
   </si>
   <si>
-    <t>TSQ</t>
-  </si>
-  <si>
-    <t>FMS</t>
-  </si>
-  <si>
-    <t>USLM</t>
-  </si>
-  <si>
-    <t>KRNT</t>
-  </si>
-  <si>
-    <t>APG</t>
-  </si>
-  <si>
-    <t>DAL</t>
-  </si>
-  <si>
-    <t>CPS</t>
-  </si>
-  <si>
-    <t>BLBD</t>
-  </si>
-  <si>
-    <t>BYND</t>
-  </si>
-  <si>
-    <t>AMZN</t>
-  </si>
-  <si>
-    <t>CNMD</t>
-  </si>
-  <si>
-    <t>CVGI</t>
-  </si>
-  <si>
-    <t>SITM</t>
-  </si>
-  <si>
-    <t>DMRC</t>
-  </si>
-  <si>
-    <t>ZG</t>
-  </si>
-  <si>
-    <t>Z</t>
-  </si>
-  <si>
-    <t>BSY</t>
-  </si>
-  <si>
-    <t>PCOR</t>
-  </si>
-  <si>
-    <t>DT</t>
-  </si>
-  <si>
-    <t>DBRG</t>
-  </si>
-  <si>
-    <t>ONTO</t>
-  </si>
-  <si>
-    <t>CAAP</t>
-  </si>
-  <si>
-    <t>TOST</t>
-  </si>
-  <si>
-    <t>RDNT</t>
-  </si>
-  <si>
-    <t>LSANF</t>
-  </si>
-  <si>
-    <t>NEOG</t>
-  </si>
-  <si>
-    <t>BWMN</t>
-  </si>
-  <si>
-    <t>SRAD</t>
-  </si>
-  <si>
-    <t>TWST</t>
-  </si>
-  <si>
-    <t>RILY</t>
-  </si>
-  <si>
-    <t>RH</t>
-  </si>
-  <si>
-    <t>OC</t>
-  </si>
-  <si>
-    <t>MTH</t>
-  </si>
-  <si>
-    <t>VNT</t>
-  </si>
-  <si>
-    <t>ACCD</t>
-  </si>
-  <si>
-    <t>ON</t>
-  </si>
-  <si>
-    <t>CYD</t>
-  </si>
-  <si>
-    <t>VEON</t>
-  </si>
-  <si>
-    <t>GXO</t>
-  </si>
-  <si>
-    <t>GKOS</t>
-  </si>
-  <si>
-    <t>FROG</t>
-  </si>
-  <si>
-    <t>NEO</t>
-  </si>
-  <si>
-    <t>PTGX</t>
-  </si>
-  <si>
-    <t>WMS</t>
-  </si>
-  <si>
-    <t>NOW</t>
-  </si>
-  <si>
-    <t>CARG</t>
-  </si>
-  <si>
-    <t>BILL</t>
-  </si>
-  <si>
-    <t>SWDAF</t>
-  </si>
-  <si>
-    <t>ENS</t>
-  </si>
-  <si>
-    <t>GSHD</t>
-  </si>
-  <si>
-    <t>TWLO</t>
-  </si>
-  <si>
-    <t>FTAI</t>
-  </si>
-  <si>
-    <t>TREX</t>
-  </si>
-  <si>
-    <t>PANW</t>
-  </si>
-  <si>
-    <t>IESC</t>
-  </si>
-  <si>
     <t>PKX</t>
   </si>
   <si>
-    <t>PROF</t>
-  </si>
-  <si>
-    <t>SHAK</t>
-  </si>
-  <si>
-    <t>UBER</t>
-  </si>
-  <si>
-    <t>PATH</t>
-  </si>
-  <si>
-    <t>PRG</t>
-  </si>
-  <si>
-    <t>WFRD</t>
-  </si>
-  <si>
-    <t>SMHI</t>
-  </si>
-  <si>
-    <t>APPN</t>
-  </si>
-  <si>
-    <t>FORM</t>
-  </si>
-  <si>
-    <t>AZEK</t>
-  </si>
-  <si>
-    <t>ALGT</t>
-  </si>
-  <si>
-    <t>MRUS</t>
-  </si>
-  <si>
-    <t>ATEC</t>
-  </si>
-  <si>
-    <t>KBH</t>
-  </si>
-  <si>
-    <t>TPH</t>
-  </si>
-  <si>
-    <t>SAIA</t>
-  </si>
-  <si>
-    <t>BCC</t>
-  </si>
-  <si>
-    <t>ENTG</t>
-  </si>
-  <si>
-    <t>BECN</t>
-  </si>
-  <si>
-    <t>AN</t>
-  </si>
-  <si>
-    <t>MANH</t>
-  </si>
-  <si>
-    <t>AZUL</t>
-  </si>
-  <si>
-    <t>PACB</t>
-  </si>
-  <si>
-    <t>DICE</t>
-  </si>
-  <si>
-    <t>PETQ</t>
-  </si>
-  <si>
-    <t>TMHC</t>
-  </si>
-  <si>
-    <t>ALPN</t>
+    <t>FLNC</t>
+  </si>
+  <si>
+    <t>CFLT</t>
+  </si>
+  <si>
+    <t>EBON</t>
+  </si>
+  <si>
+    <t>ACLS</t>
+  </si>
+  <si>
+    <t>LI</t>
+  </si>
+  <si>
+    <t>YPF</t>
+  </si>
+  <si>
+    <t>CAMT</t>
+  </si>
+  <si>
+    <t>PCT</t>
+  </si>
+  <si>
+    <t>ANF</t>
+  </si>
+  <si>
+    <t>SNBR</t>
+  </si>
+  <si>
+    <t>PCTTU</t>
+  </si>
+  <si>
+    <t>AEHR</t>
+  </si>
+  <si>
+    <t>RIVN</t>
+  </si>
+  <si>
+    <t>COCO</t>
+  </si>
+  <si>
+    <t>FCNCA</t>
+  </si>
+  <si>
+    <t>PLPC</t>
+  </si>
+  <si>
+    <t>GBTC</t>
+  </si>
+  <si>
+    <t>VKTX</t>
+  </si>
+  <si>
+    <t>HOV</t>
+  </si>
+  <si>
+    <t>ISEE</t>
+  </si>
+  <si>
+    <t>OSTK</t>
+  </si>
+  <si>
+    <t>BLDR</t>
+  </si>
+  <si>
+    <t>GGAL</t>
+  </si>
+  <si>
+    <t>BMEA</t>
+  </si>
+  <si>
+    <t>QTRX</t>
+  </si>
+  <si>
+    <t>CUBI</t>
+  </si>
+  <si>
+    <t>IAS</t>
+  </si>
+  <si>
+    <t>GRBK</t>
+  </si>
+  <si>
+    <t>EXPI</t>
+  </si>
+  <si>
+    <t>BHVN</t>
+  </si>
+  <si>
+    <t>CLXT</t>
   </si>
   <si>
     <t>ARCT</t>
   </si>
   <si>
-    <t>NATR</t>
-  </si>
-  <si>
-    <t>MPWR</t>
-  </si>
-  <si>
-    <t>SGRY</t>
-  </si>
-  <si>
-    <t>PEGA</t>
-  </si>
-  <si>
-    <t>ZUO</t>
-  </si>
-  <si>
-    <t>HSKA</t>
-  </si>
-  <si>
-    <t>MLP</t>
-  </si>
-  <si>
-    <t>CLS</t>
-  </si>
-  <si>
-    <t>IBP</t>
-  </si>
-  <si>
-    <t>ONON</t>
-  </si>
-  <si>
-    <t>CELH</t>
-  </si>
-  <si>
-    <t>LZ</t>
-  </si>
-  <si>
-    <t>NFLX</t>
-  </si>
-  <si>
-    <t>SIBN</t>
-  </si>
-  <si>
-    <t>ETNB</t>
-  </si>
-  <si>
-    <t>NET</t>
-  </si>
-  <si>
-    <t>UFPT</t>
-  </si>
-  <si>
-    <t>ALGN</t>
-  </si>
-  <si>
-    <t>PDFS</t>
-  </si>
-  <si>
-    <t>RELY</t>
-  </si>
-  <si>
-    <t>AMWD</t>
-  </si>
-  <si>
-    <t>ASAN</t>
-  </si>
-  <si>
-    <t>SSYS</t>
-  </si>
-  <si>
-    <t>ERO</t>
-  </si>
-  <si>
-    <t>NNOX</t>
-  </si>
-  <si>
-    <t>SNAP</t>
-  </si>
-  <si>
-    <t>ROKU</t>
-  </si>
-  <si>
-    <t>BWMX</t>
-  </si>
-  <si>
-    <t>ANF</t>
-  </si>
-  <si>
-    <t>ROIV</t>
-  </si>
-  <si>
-    <t>NETI</t>
-  </si>
-  <si>
-    <t>DDOG</t>
-  </si>
-  <si>
-    <t>MDWT</t>
-  </si>
-  <si>
-    <t>IDCC</t>
-  </si>
-  <si>
-    <t>TDW</t>
-  </si>
-  <si>
-    <t>TOL</t>
-  </si>
-  <si>
-    <t>PHAT</t>
-  </si>
-  <si>
-    <t>DASH</t>
-  </si>
-  <si>
-    <t>JELD</t>
-  </si>
-  <si>
-    <t>LAD</t>
-  </si>
-  <si>
-    <t>LTH</t>
-  </si>
-  <si>
-    <t>BLU</t>
-  </si>
-  <si>
-    <t>BVH</t>
-  </si>
-  <si>
-    <t>GBX</t>
-  </si>
-  <si>
-    <t>AMD</t>
-  </si>
-  <si>
-    <t>FCNCA</t>
-  </si>
-  <si>
-    <t>EB</t>
-  </si>
-  <si>
-    <t>THC</t>
-  </si>
-  <si>
-    <t>BMA</t>
-  </si>
-  <si>
-    <t>IIVI</t>
-  </si>
-  <si>
-    <t>APPF</t>
-  </si>
-  <si>
-    <t>DUOL</t>
+    <t>APP</t>
+  </si>
+  <si>
+    <t>ELF</t>
+  </si>
+  <si>
+    <t>GHL</t>
+  </si>
+  <si>
+    <t>DKNG</t>
+  </si>
+  <si>
+    <t>MOD</t>
+  </si>
+  <si>
+    <t>BZH</t>
+  </si>
+  <si>
+    <t>XPO</t>
+  </si>
+  <si>
+    <t>ODC</t>
+  </si>
+  <si>
+    <t>BELFA</t>
+  </si>
+  <si>
+    <t>KDNY</t>
+  </si>
+  <si>
+    <t>CCL</t>
   </si>
   <si>
     <t>ATRO</t>
   </si>
   <si>
-    <t>ALGM</t>
-  </si>
-  <si>
-    <t>AFRM</t>
-  </si>
-  <si>
-    <t>YPF</t>
-  </si>
-  <si>
-    <t>ATLC</t>
-  </si>
-  <si>
-    <t>STVN</t>
-  </si>
-  <si>
-    <t>FOR</t>
-  </si>
-  <si>
-    <t>ASMIY</t>
-  </si>
-  <si>
-    <t>PHM</t>
-  </si>
-  <si>
-    <t>BLD</t>
-  </si>
-  <si>
-    <t>TAYD</t>
-  </si>
-  <si>
-    <t>YEXT</t>
-  </si>
-  <si>
-    <t>TGLS</t>
-  </si>
-  <si>
-    <t>ABCM</t>
-  </si>
-  <si>
-    <t>PSTG</t>
-  </si>
-  <si>
-    <t>TDC</t>
-  </si>
-  <si>
-    <t>JBL</t>
-  </si>
-  <si>
-    <t>CRCT</t>
-  </si>
-  <si>
-    <t>EBIX</t>
-  </si>
-  <si>
-    <t>MTW</t>
-  </si>
-  <si>
-    <t>NCLH</t>
-  </si>
-  <si>
-    <t>POWL</t>
-  </si>
-  <si>
-    <t>LUNG</t>
-  </si>
-  <si>
-    <t>BELFB</t>
-  </si>
-  <si>
-    <t>XPEV</t>
-  </si>
-  <si>
-    <t>RCL</t>
-  </si>
-  <si>
-    <t>MORF</t>
-  </si>
-  <si>
-    <t>ACMR</t>
-  </si>
-  <si>
-    <t>KRYS</t>
-  </si>
-  <si>
-    <t>AVGO</t>
-  </si>
-  <si>
-    <t>RMBS</t>
-  </si>
-  <si>
-    <t>MNSO</t>
-  </si>
-  <si>
-    <t>ETHE</t>
-  </si>
-  <si>
-    <t>XPO</t>
-  </si>
-  <si>
-    <t>COCO</t>
-  </si>
-  <si>
-    <t>GTLB</t>
-  </si>
-  <si>
-    <t>EXTR</t>
-  </si>
-  <si>
-    <t>XP</t>
-  </si>
-  <si>
-    <t>STRL</t>
-  </si>
-  <si>
-    <t>CMT</t>
+    <t>CMPR</t>
+  </si>
+  <si>
+    <t>VRT</t>
+  </si>
+  <si>
+    <t>CUK</t>
+  </si>
+  <si>
+    <t>CBAY</t>
+  </si>
+  <si>
+    <t>AMPH</t>
+  </si>
+  <si>
+    <t>COIN</t>
+  </si>
+  <si>
+    <t>RXST</t>
+  </si>
+  <si>
+    <t>LMB</t>
+  </si>
+  <si>
+    <t>IOT</t>
+  </si>
+  <si>
+    <t>MSTR</t>
+  </si>
+  <si>
+    <t>MDB</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>RXRX</t>
+  </si>
+  <si>
+    <t>SKYW</t>
+  </si>
+  <si>
+    <t>PLTR</t>
+  </si>
+  <si>
+    <t>RCEL</t>
+  </si>
+  <si>
+    <t>ENVX</t>
+  </si>
+  <si>
+    <t>DFH</t>
+  </si>
+  <si>
+    <t>ARLO</t>
+  </si>
+  <si>
+    <t>SDGR</t>
+  </si>
+  <si>
+    <t>RDFN</t>
+  </si>
+  <si>
+    <t>MARA</t>
+  </si>
+  <si>
+    <t>EDN</t>
+  </si>
+  <si>
+    <t>NVDA</t>
+  </si>
+  <si>
+    <t>CIR</t>
+  </si>
+  <si>
+    <t>EH</t>
+  </si>
+  <si>
+    <t>AI</t>
+  </si>
+  <si>
+    <t>CABA</t>
+  </si>
+  <si>
+    <t>INOD</t>
+  </si>
+  <si>
+    <t>GGAAU</t>
+  </si>
+  <si>
+    <t>RIOT</t>
+  </si>
+  <si>
+    <t>OPRA</t>
+  </si>
+  <si>
+    <t>MEOA</t>
+  </si>
+  <si>
+    <t>IONQ</t>
+  </si>
+  <si>
+    <t>ROOT</t>
+  </si>
+  <si>
+    <t>PHVS</t>
+  </si>
+  <si>
+    <t>EYPT</t>
+  </si>
+  <si>
+    <t>SGTX</t>
+  </si>
+  <si>
+    <t>SMCI</t>
   </si>
   <si>
     <t>BBIO</t>
   </si>
   <si>
-    <t>FIVN</t>
-  </si>
-  <si>
-    <t>ISEE</t>
-  </si>
-  <si>
-    <t>VIST</t>
-  </si>
-  <si>
-    <t>QS</t>
-  </si>
-  <si>
-    <t>GRVY</t>
-  </si>
-  <si>
-    <t>FLNC</t>
-  </si>
-  <si>
-    <t>HUBS</t>
-  </si>
-  <si>
-    <t>AMPH</t>
-  </si>
-  <si>
-    <t>CPSS</t>
-  </si>
-  <si>
-    <t>CAMT</t>
-  </si>
-  <si>
-    <t>CXM</t>
-  </si>
-  <si>
-    <t>PLPC</t>
-  </si>
-  <si>
-    <t>DV</t>
-  </si>
-  <si>
-    <t>BELFA</t>
-  </si>
-  <si>
-    <t>ADBE</t>
-  </si>
-  <si>
-    <t>GGAL</t>
-  </si>
-  <si>
-    <t>ACVA</t>
-  </si>
-  <si>
-    <t>SHOP</t>
-  </si>
-  <si>
-    <t>PCTTU</t>
-  </si>
-  <si>
-    <t>MNDY</t>
-  </si>
-  <si>
-    <t>RIVN</t>
-  </si>
-  <si>
-    <t>LI</t>
-  </si>
-  <si>
-    <t>BMEA</t>
-  </si>
-  <si>
-    <t>PLAB</t>
-  </si>
-  <si>
-    <t>DOCN</t>
-  </si>
-  <si>
-    <t>RRGB</t>
-  </si>
-  <si>
-    <t>CUBI</t>
-  </si>
-  <si>
-    <t>COHR</t>
-  </si>
-  <si>
-    <t>OSTK</t>
-  </si>
-  <si>
-    <t>BRZE</t>
-  </si>
-  <si>
-    <t>MHO</t>
-  </si>
-  <si>
-    <t>SPOT</t>
-  </si>
-  <si>
-    <t>WRLD</t>
-  </si>
-  <si>
-    <t>MGNI</t>
-  </si>
-  <si>
-    <t>SG</t>
-  </si>
-  <si>
-    <t>AEHR</t>
-  </si>
-  <si>
-    <t>TTD</t>
-  </si>
-  <si>
-    <t>PCT</t>
-  </si>
-  <si>
-    <t>TYRA</t>
-  </si>
-  <si>
-    <t>FSLY</t>
-  </si>
-  <si>
-    <t>NWLI</t>
-  </si>
-  <si>
-    <t>MRVL</t>
-  </si>
-  <si>
-    <t>U</t>
-  </si>
-  <si>
-    <t>VKTX</t>
-  </si>
-  <si>
-    <t>KDNY</t>
-  </si>
-  <si>
-    <t>MOD</t>
-  </si>
-  <si>
-    <t>USAP</t>
-  </si>
-  <si>
-    <t>ELF</t>
-  </si>
-  <si>
-    <t>ODC</t>
-  </si>
-  <si>
-    <t>GHL</t>
-  </si>
-  <si>
-    <t>BLDR</t>
-  </si>
-  <si>
-    <t>TGTX</t>
-  </si>
-  <si>
-    <t>TSLA</t>
-  </si>
-  <si>
-    <t>BHVN</t>
-  </si>
-  <si>
-    <t>VECT</t>
-  </si>
-  <si>
-    <t>AVDL</t>
-  </si>
-  <si>
-    <t>GRBK</t>
-  </si>
-  <si>
-    <t>CFLT</t>
-  </si>
-  <si>
-    <t>EXAS</t>
-  </si>
-  <si>
-    <t>IAS</t>
-  </si>
-  <si>
-    <t>SGH</t>
-  </si>
-  <si>
-    <t>GLBE</t>
-  </si>
-  <si>
-    <t>SHC</t>
-  </si>
-  <si>
-    <t>LSEA</t>
-  </si>
-  <si>
-    <t>LTRPB</t>
-  </si>
-  <si>
-    <t>GBTC</t>
-  </si>
-  <si>
-    <t>VRT</t>
-  </si>
-  <si>
-    <t>KRUS</t>
-  </si>
-  <si>
-    <t>MEDS</t>
-  </si>
-  <si>
-    <t>CBAY</t>
-  </si>
-  <si>
-    <t>ACLS</t>
-  </si>
-  <si>
-    <t>CCL</t>
-  </si>
-  <si>
-    <t>CMPR</t>
-  </si>
-  <si>
-    <t>RXRX</t>
-  </si>
-  <si>
-    <t>QTRX</t>
-  </si>
-  <si>
-    <t>CUK</t>
-  </si>
-  <si>
-    <t>HOV</t>
-  </si>
-  <si>
-    <t>OPAD</t>
-  </si>
-  <si>
-    <t>BZH</t>
-  </si>
-  <si>
-    <t>TCMD</t>
-  </si>
-  <si>
-    <t>EDN</t>
-  </si>
-  <si>
-    <t>IOT</t>
-  </si>
-  <si>
-    <t>CLXT</t>
-  </si>
-  <si>
-    <t>RXDX</t>
-  </si>
-  <si>
-    <t>DKNG</t>
-  </si>
-  <si>
-    <t>ARLO</t>
-  </si>
-  <si>
-    <t>RXST</t>
-  </si>
-  <si>
-    <t>SKYW</t>
-  </si>
-  <si>
-    <t>NGMS</t>
-  </si>
-  <si>
-    <t>APP</t>
-  </si>
-  <si>
-    <t>ENVX</t>
-  </si>
-  <si>
-    <t>RETA</t>
-  </si>
-  <si>
-    <t>LMB</t>
-  </si>
-  <si>
-    <t>DFH</t>
-  </si>
-  <si>
-    <t>MSTR</t>
-  </si>
-  <si>
-    <t>MDB</t>
-  </si>
-  <si>
-    <t>EXPI</t>
-  </si>
-  <si>
-    <t>CABA</t>
-  </si>
-  <si>
-    <t>W</t>
-  </si>
-  <si>
-    <t>NVTS</t>
-  </si>
-  <si>
-    <t>PLTR</t>
-  </si>
-  <si>
-    <t>WEAV</t>
-  </si>
-  <si>
-    <t>EBON</t>
-  </si>
-  <si>
-    <t>COIN</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>CIR</t>
-  </si>
-  <si>
-    <t>ROOT</t>
-  </si>
-  <si>
-    <t>GGAAU</t>
-  </si>
-  <si>
-    <t>NVDA</t>
-  </si>
-  <si>
-    <t>EH</t>
-  </si>
-  <si>
-    <t>PHVS</t>
-  </si>
-  <si>
-    <t>SDGR</t>
-  </si>
-  <si>
-    <t>RCEL</t>
-  </si>
-  <si>
-    <t>MEOA</t>
-  </si>
-  <si>
-    <t>JOBY</t>
-  </si>
-  <si>
-    <t>AI</t>
-  </si>
-  <si>
-    <t>RDFN</t>
-  </si>
-  <si>
-    <t>EYPT</t>
-  </si>
-  <si>
-    <t>IONQ</t>
-  </si>
-  <si>
-    <t>MARA</t>
-  </si>
-  <si>
     <t>MEOAU</t>
   </si>
   <si>
-    <t>SMCI</t>
-  </si>
-  <si>
-    <t>UPST</t>
-  </si>
-  <si>
     <t>IMGN</t>
   </si>
   <si>
-    <t>RIOT</t>
-  </si>
-  <si>
-    <t>SGTX</t>
-  </si>
-  <si>
-    <t>OPRA</t>
+    <t>CVNA</t>
   </si>
   <si>
     <t>EDTXU</t>
   </si>
   <si>
     <t>EDTX</t>
-  </si>
-  <si>
-    <t>NERV</t>
-  </si>
-  <si>
-    <t>CVNA</t>
-  </si>
-  <si>
-    <t>AAOI</t>
   </si>
   <si>
     <t>AMAM</t>
@@ -1471,7 +1351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B368"/>
+  <dimension ref="A1:B328"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1487,7 +1367,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1">
-        <v>134.2835236400988</v>
+        <v>129.3043216204136</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1495,7 +1375,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1">
-        <v>134.4090806296152</v>
+        <v>129.3114315654894</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1503,7 +1383,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1">
-        <v>134.5074545593008</v>
+        <v>129.3287087482267</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1511,7 +1391,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="1">
-        <v>134.6267962054363</v>
+        <v>129.3506528893776</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1519,7 +1399,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="1">
-        <v>134.794220677352</v>
+        <v>129.4125982492894</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1527,7 +1407,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="1">
-        <v>134.838672284857</v>
+        <v>129.4624789743012</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1535,7 +1415,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="1">
-        <v>134.8795606266485</v>
+        <v>129.4868683213205</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1543,7 +1423,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="1">
-        <v>135.0579725884918</v>
+        <v>129.5396776430732</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1551,7 +1431,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="1">
-        <v>135.0740553864142</v>
+        <v>129.575620789456</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1559,7 +1439,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="1">
-        <v>135.0922309856031</v>
+        <v>129.5900908197025</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1567,7 +1447,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="1">
-        <v>135.1179799764997</v>
+        <v>129.6078078035002</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1575,7 +1455,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="1">
-        <v>135.2522703815308</v>
+        <v>129.6715054552926</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1583,7 +1463,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="1">
-        <v>135.2825036268666</v>
+        <v>129.8066822040929</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1591,7 +1471,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="1">
-        <v>135.2903612742539</v>
+        <v>129.8882548185674</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1599,7 +1479,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="1">
-        <v>135.4775005488728</v>
+        <v>129.9746166181891</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1607,7 +1487,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="1">
-        <v>135.5518128408808</v>
+        <v>129.975827554942</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1615,7 +1495,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="1">
-        <v>135.6137227690266</v>
+        <v>130.0090426890373</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1623,7 +1503,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="1">
-        <v>135.615381869454</v>
+        <v>130.1841690912718</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1631,7 +1511,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="1">
-        <v>135.6524869215367</v>
+        <v>130.2149878261212</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1639,7 +1519,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="1">
-        <v>135.7164462646808</v>
+        <v>130.4110664730868</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1647,7 +1527,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="1">
-        <v>135.7444515766796</v>
+        <v>130.4462988901802</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1655,7 +1535,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="1">
-        <v>135.7459673196028</v>
+        <v>130.4615372731179</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1663,7 +1543,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="1">
-        <v>135.7515814062836</v>
+        <v>130.5342828725076</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1671,7 +1551,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="1">
-        <v>135.8470754974519</v>
+        <v>130.5861050978399</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1679,7 +1559,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="1">
-        <v>136.0100649800785</v>
+        <v>130.5898247616127</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1687,7 +1567,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="1">
-        <v>136.0627919805756</v>
+        <v>130.6708815481005</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1695,7 +1575,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="1">
-        <v>136.1359688902318</v>
+        <v>130.8122296140773</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1703,7 +1583,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="1">
-        <v>136.2592481787247</v>
+        <v>130.8290588905969</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1711,7 +1591,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="1">
-        <v>136.3427528796899</v>
+        <v>130.8533008730499</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1719,7 +1599,7 @@
         <v>31</v>
       </c>
       <c r="B31" s="1">
-        <v>136.5207991693276</v>
+        <v>130.8667562300924</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1727,7 +1607,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="1">
-        <v>136.6546915932336</v>
+        <v>130.8676609889043</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1735,7 +1615,7 @@
         <v>33</v>
       </c>
       <c r="B33" s="1">
-        <v>136.73714903327</v>
+        <v>131.0102265267315</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1743,7 +1623,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="1">
-        <v>136.7436129471768</v>
+        <v>131.0149450411747</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1751,7 +1631,7 @@
         <v>35</v>
       </c>
       <c r="B35" s="1">
-        <v>136.9114519031462</v>
+        <v>131.0656181703646</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1759,7 +1639,7 @@
         <v>36</v>
       </c>
       <c r="B36" s="1">
-        <v>136.9903375655236</v>
+        <v>131.0947552017941</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1767,7 +1647,7 @@
         <v>37</v>
       </c>
       <c r="B37" s="1">
-        <v>137.0128111628075</v>
+        <v>131.1027162330343</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1775,7 +1655,7 @@
         <v>38</v>
       </c>
       <c r="B38" s="1">
-        <v>137.1838954294745</v>
+        <v>131.1505026907606</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1783,7 +1663,7 @@
         <v>39</v>
       </c>
       <c r="B39" s="1">
-        <v>137.2234880281013</v>
+        <v>131.2029885890086</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1791,7 +1671,7 @@
         <v>40</v>
       </c>
       <c r="B40" s="1">
-        <v>137.5029928601381</v>
+        <v>131.285423583404</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1799,7 +1679,7 @@
         <v>41</v>
       </c>
       <c r="B41" s="1">
-        <v>137.5053776597617</v>
+        <v>131.2882493284291</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -1807,7 +1687,7 @@
         <v>42</v>
       </c>
       <c r="B42" s="1">
-        <v>137.5362062907868</v>
+        <v>131.2895864505632</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -1815,7 +1695,7 @@
         <v>43</v>
       </c>
       <c r="B43" s="1">
-        <v>137.6322726301878</v>
+        <v>131.3394859647028</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1823,7 +1703,7 @@
         <v>44</v>
       </c>
       <c r="B44" s="1">
-        <v>137.6372561036121</v>
+        <v>131.3422661324374</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1831,7 +1711,7 @@
         <v>45</v>
       </c>
       <c r="B45" s="1">
-        <v>137.7009035953743</v>
+        <v>131.5884913372849</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1839,7 +1719,7 @@
         <v>46</v>
       </c>
       <c r="B46" s="1">
-        <v>137.702695166012</v>
+        <v>131.6714472756249</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -1847,7 +1727,7 @@
         <v>47</v>
       </c>
       <c r="B47" s="1">
-        <v>137.7196691233726</v>
+        <v>131.6945200779809</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -1855,7 +1735,7 @@
         <v>48</v>
       </c>
       <c r="B48" s="1">
-        <v>137.7217488850168</v>
+        <v>131.709476200069</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1863,7 +1743,7 @@
         <v>49</v>
       </c>
       <c r="B49" s="1">
-        <v>137.7289779971502</v>
+        <v>131.8958813002955</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1871,7 +1751,7 @@
         <v>50</v>
       </c>
       <c r="B50" s="1">
-        <v>137.75173437534</v>
+        <v>131.9265019844602</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1879,7 +1759,7 @@
         <v>51</v>
       </c>
       <c r="B51" s="1">
-        <v>137.753678478699</v>
+        <v>132.0107733209298</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1887,7 +1767,7 @@
         <v>52</v>
       </c>
       <c r="B52" s="1">
-        <v>137.901019166253</v>
+        <v>132.0441989208849</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1895,7 +1775,7 @@
         <v>53</v>
       </c>
       <c r="B53" s="1">
-        <v>138.0201619343431</v>
+        <v>132.0672152996668</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1903,7 +1783,7 @@
         <v>54</v>
       </c>
       <c r="B54" s="1">
-        <v>138.1337370944594</v>
+        <v>132.1555821994835</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1911,7 +1791,7 @@
         <v>55</v>
       </c>
       <c r="B55" s="1">
-        <v>138.1886972162805</v>
+        <v>132.1712714347813</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1919,7 +1799,7 @@
         <v>56</v>
       </c>
       <c r="B56" s="1">
-        <v>138.3774628840076</v>
+        <v>132.2656353334257</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1927,7 +1807,7 @@
         <v>57</v>
       </c>
       <c r="B57" s="1">
-        <v>138.3845550404653</v>
+        <v>132.2788736914969</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1935,7 +1815,7 @@
         <v>58</v>
       </c>
       <c r="B58" s="1">
-        <v>138.3988512516472</v>
+        <v>132.3970325788387</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1943,7 +1823,7 @@
         <v>59</v>
       </c>
       <c r="B59" s="1">
-        <v>138.4152102175942</v>
+        <v>132.4039222663605</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1951,7 +1831,7 @@
         <v>60</v>
       </c>
       <c r="B60" s="1">
-        <v>138.5544138887973</v>
+        <v>132.4276086023096</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1959,7 +1839,7 @@
         <v>61</v>
       </c>
       <c r="B61" s="1">
-        <v>138.5728180292637</v>
+        <v>132.4789364577125</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1967,7 +1847,7 @@
         <v>62</v>
       </c>
       <c r="B62" s="1">
-        <v>138.6129087262043</v>
+        <v>132.5014495467844</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1975,7 +1855,7 @@
         <v>63</v>
       </c>
       <c r="B63" s="1">
-        <v>138.6466069282945</v>
+        <v>132.5753701458476</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1983,7 +1863,7 @@
         <v>64</v>
       </c>
       <c r="B64" s="1">
-        <v>138.6566111160424</v>
+        <v>132.7533229758515</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1991,7 +1871,7 @@
         <v>65</v>
       </c>
       <c r="B65" s="1">
-        <v>138.7145361217494</v>
+        <v>132.8497064269368</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -1999,7 +1879,7 @@
         <v>66</v>
       </c>
       <c r="B66" s="1">
-        <v>138.7206221345322</v>
+        <v>132.9399198677628</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -2007,7 +1887,7 @@
         <v>67</v>
       </c>
       <c r="B67" s="1">
-        <v>139.0038417832344</v>
+        <v>133.0024800145635</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -2015,7 +1895,7 @@
         <v>68</v>
       </c>
       <c r="B68" s="1">
-        <v>139.0520279849854</v>
+        <v>133.054804113083</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -2023,7 +1903,7 @@
         <v>69</v>
       </c>
       <c r="B69" s="1">
-        <v>139.0980624397909</v>
+        <v>133.0969648937134</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -2031,7 +1911,7 @@
         <v>70</v>
       </c>
       <c r="B70" s="1">
-        <v>139.2433355030488</v>
+        <v>133.2575781261514</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -2039,7 +1919,7 @@
         <v>71</v>
       </c>
       <c r="B71" s="1">
-        <v>139.4211249010141</v>
+        <v>133.381640451391</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -2047,7 +1927,7 @@
         <v>72</v>
       </c>
       <c r="B72" s="1">
-        <v>139.4519999900984</v>
+        <v>133.4098969419445</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2055,7 +1935,7 @@
         <v>73</v>
       </c>
       <c r="B73" s="1">
-        <v>139.4895798489713</v>
+        <v>133.4211383982439</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -2063,7 +1943,7 @@
         <v>74</v>
       </c>
       <c r="B74" s="1">
-        <v>139.492215786882</v>
+        <v>133.5006517207393</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -2071,7 +1951,7 @@
         <v>75</v>
       </c>
       <c r="B75" s="1">
-        <v>139.8322253529184</v>
+        <v>133.5302571188829</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -2079,7 +1959,7 @@
         <v>76</v>
       </c>
       <c r="B76" s="1">
-        <v>139.8387754335597</v>
+        <v>133.636013709772</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -2087,7 +1967,7 @@
         <v>77</v>
       </c>
       <c r="B77" s="1">
-        <v>139.8753344526066</v>
+        <v>133.7618897390375</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -2095,7 +1975,7 @@
         <v>78</v>
       </c>
       <c r="B78" s="1">
-        <v>139.8774673855234</v>
+        <v>133.7738544489832</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -2103,7 +1983,7 @@
         <v>79</v>
       </c>
       <c r="B79" s="1">
-        <v>139.902384881612</v>
+        <v>133.8071425626298</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -2111,7 +1991,7 @@
         <v>80</v>
       </c>
       <c r="B80" s="1">
-        <v>139.9709000227226</v>
+        <v>133.8731011160293</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -2119,7 +1999,7 @@
         <v>81</v>
       </c>
       <c r="B81" s="1">
-        <v>140.0962879492597</v>
+        <v>134.0183325265511</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -2127,7 +2007,7 @@
         <v>82</v>
       </c>
       <c r="B82" s="1">
-        <v>140.4424059594698</v>
+        <v>134.0783290884218</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -2135,7 +2015,7 @@
         <v>83</v>
       </c>
       <c r="B83" s="1">
-        <v>140.4785186798393</v>
+        <v>134.1396896680948</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -2143,7 +2023,7 @@
         <v>84</v>
       </c>
       <c r="B84" s="1">
-        <v>140.5017802836973</v>
+        <v>134.1896704876501</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -2151,7 +2031,7 @@
         <v>85</v>
       </c>
       <c r="B85" s="1">
-        <v>140.5300424257138</v>
+        <v>134.5546856509591</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -2159,7 +2039,7 @@
         <v>86</v>
       </c>
       <c r="B86" s="1">
-        <v>140.5582369388532</v>
+        <v>134.705240307926</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -2167,7 +2047,7 @@
         <v>87</v>
       </c>
       <c r="B87" s="1">
-        <v>140.6288336266411</v>
+        <v>134.7462261557664</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -2175,7 +2055,7 @@
         <v>88</v>
       </c>
       <c r="B88" s="1">
-        <v>140.6503886462164</v>
+        <v>134.7779695032455</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -2183,7 +2063,7 @@
         <v>89</v>
       </c>
       <c r="B89" s="1">
-        <v>140.7618817293612</v>
+        <v>134.894014021914</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -2191,7 +2071,7 @@
         <v>90</v>
       </c>
       <c r="B90" s="1">
-        <v>140.8107844466733</v>
+        <v>135.0252094399987</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -2199,7 +2079,7 @@
         <v>91</v>
       </c>
       <c r="B91" s="1">
-        <v>140.8376763186334</v>
+        <v>135.1007661315249</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -2207,7 +2087,7 @@
         <v>92</v>
       </c>
       <c r="B92" s="1">
-        <v>140.8652637658371</v>
+        <v>135.2443449262809</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -2215,7 +2095,7 @@
         <v>93</v>
       </c>
       <c r="B93" s="1">
-        <v>140.8772633598947</v>
+        <v>135.314083586221</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -2223,7 +2103,7 @@
         <v>94</v>
       </c>
       <c r="B94" s="1">
-        <v>141.1814826649681</v>
+        <v>135.3634489636169</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -2231,7 +2111,7 @@
         <v>95</v>
       </c>
       <c r="B95" s="1">
-        <v>141.2644634174211</v>
+        <v>135.5501486661843</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -2239,7 +2119,7 @@
         <v>96</v>
       </c>
       <c r="B96" s="1">
-        <v>141.3895818733996</v>
+        <v>135.5854465331853</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -2247,7 +2127,7 @@
         <v>97</v>
       </c>
       <c r="B97" s="1">
-        <v>141.4206778902169</v>
+        <v>135.5889344255435</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -2255,7 +2135,7 @@
         <v>98</v>
       </c>
       <c r="B98" s="1">
-        <v>141.4729560545239</v>
+        <v>135.6521333983807</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -2263,7 +2143,7 @@
         <v>99</v>
       </c>
       <c r="B99" s="1">
-        <v>141.7029639219962</v>
+        <v>135.7108241577782</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -2271,7 +2151,7 @@
         <v>100</v>
       </c>
       <c r="B100" s="1">
-        <v>141.7037312654739</v>
+        <v>135.7145360260231</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -2279,7 +2159,7 @@
         <v>101</v>
       </c>
       <c r="B101" s="1">
-        <v>141.8174532363149</v>
+        <v>135.7333710742167</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -2287,7 +2167,7 @@
         <v>102</v>
       </c>
       <c r="B102" s="1">
-        <v>141.9139327928566</v>
+        <v>135.757906767528</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -2295,7 +2175,7 @@
         <v>103</v>
       </c>
       <c r="B103" s="1">
-        <v>142.0004653050219</v>
+        <v>135.8865009065889</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -2303,7 +2183,7 @@
         <v>104</v>
       </c>
       <c r="B104" s="1">
-        <v>142.096405374987</v>
+        <v>136.0717000616034</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -2311,7 +2191,7 @@
         <v>105</v>
       </c>
       <c r="B105" s="1">
-        <v>142.2134529377515</v>
+        <v>136.4170002511934</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -2319,7 +2199,7 @@
         <v>106</v>
       </c>
       <c r="B106" s="1">
-        <v>142.2461284043449</v>
+        <v>136.5712369630736</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -2327,7 +2207,7 @@
         <v>107</v>
       </c>
       <c r="B107" s="1">
-        <v>142.5062305314136</v>
+        <v>136.6111800547159</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -2335,7 +2215,7 @@
         <v>108</v>
       </c>
       <c r="B108" s="1">
-        <v>142.508821428502</v>
+        <v>136.7123648198388</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -2343,7 +2223,7 @@
         <v>109</v>
       </c>
       <c r="B109" s="1">
-        <v>142.5733996680439</v>
+        <v>136.896599543079</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -2351,7 +2231,7 @@
         <v>110</v>
       </c>
       <c r="B110" s="1">
-        <v>142.6908856879183</v>
+        <v>137.0549753175946</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -2359,7 +2239,7 @@
         <v>111</v>
       </c>
       <c r="B111" s="1">
-        <v>142.7422779553292</v>
+        <v>137.2437111400247</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -2367,7 +2247,7 @@
         <v>112</v>
       </c>
       <c r="B112" s="1">
-        <v>142.7719647448292</v>
+        <v>137.2530481192849</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -2375,7 +2255,7 @@
         <v>113</v>
       </c>
       <c r="B113" s="1">
-        <v>142.9807977658342</v>
+        <v>137.3786489652296</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -2383,7 +2263,7 @@
         <v>114</v>
       </c>
       <c r="B114" s="1">
-        <v>142.9952913677558</v>
+        <v>137.4432195334991</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -2391,7 +2271,7 @@
         <v>115</v>
       </c>
       <c r="B115" s="1">
-        <v>143.0307616765038</v>
+        <v>137.4730221182488</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -2399,7 +2279,7 @@
         <v>116</v>
       </c>
       <c r="B116" s="1">
-        <v>143.5420306916623</v>
+        <v>137.5938378011265</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -2407,7 +2287,7 @@
         <v>117</v>
       </c>
       <c r="B117" s="1">
-        <v>143.5488134326128</v>
+        <v>137.6827006167127</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -2415,7 +2295,7 @@
         <v>118</v>
       </c>
       <c r="B118" s="1">
-        <v>143.7207333775848</v>
+        <v>137.7058672374596</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -2423,7 +2303,7 @@
         <v>119</v>
       </c>
       <c r="B119" s="1">
-        <v>143.9316867177185</v>
+        <v>137.7799672732077</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -2431,7 +2311,7 @@
         <v>120</v>
       </c>
       <c r="B120" s="1">
-        <v>143.9628823579038</v>
+        <v>137.9504968617209</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -2439,7 +2319,7 @@
         <v>121</v>
       </c>
       <c r="B121" s="1">
-        <v>144.0735431454528</v>
+        <v>138.0037934228926</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -2447,7 +2327,7 @@
         <v>122</v>
       </c>
       <c r="B122" s="1">
-        <v>144.2799161089162</v>
+        <v>138.0842294583706</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -2455,7 +2335,7 @@
         <v>123</v>
       </c>
       <c r="B123" s="1">
-        <v>144.3157882588583</v>
+        <v>138.2355758941389</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -2463,7 +2343,7 @@
         <v>124</v>
       </c>
       <c r="B124" s="1">
-        <v>144.7166642338104</v>
+        <v>138.3006960726211</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -2471,7 +2351,7 @@
         <v>125</v>
       </c>
       <c r="B125" s="1">
-        <v>144.7863083684602</v>
+        <v>138.3211440201763</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -2479,7 +2359,7 @@
         <v>126</v>
       </c>
       <c r="B126" s="1">
-        <v>144.8172267752956</v>
+        <v>138.3261628600382</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -2487,7 +2367,7 @@
         <v>127</v>
       </c>
       <c r="B127" s="1">
-        <v>145.1111024547492</v>
+        <v>138.3628761265203</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -2495,7 +2375,7 @@
         <v>128</v>
       </c>
       <c r="B128" s="1">
-        <v>145.1199216672256</v>
+        <v>138.4859910937689</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -2503,7 +2383,7 @@
         <v>129</v>
       </c>
       <c r="B129" s="1">
-        <v>145.1313097846991</v>
+        <v>138.5925791322447</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -2511,7 +2391,7 @@
         <v>130</v>
       </c>
       <c r="B130" s="1">
-        <v>145.2735781460551</v>
+        <v>138.5998150846503</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -2519,7 +2399,7 @@
         <v>131</v>
       </c>
       <c r="B131" s="1">
-        <v>145.2793893797502</v>
+        <v>138.8862481300656</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -2527,7 +2407,7 @@
         <v>132</v>
       </c>
       <c r="B132" s="1">
-        <v>145.414547803106</v>
+        <v>138.9874086537829</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -2535,7 +2415,7 @@
         <v>133</v>
       </c>
       <c r="B133" s="1">
-        <v>145.4521356941933</v>
+        <v>139.1265820166901</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -2543,7 +2423,7 @@
         <v>134</v>
       </c>
       <c r="B134" s="1">
-        <v>145.4928880053916</v>
+        <v>139.1970130722525</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -2551,7 +2431,7 @@
         <v>135</v>
       </c>
       <c r="B135" s="1">
-        <v>145.5406891148138</v>
+        <v>139.3336595626849</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -2559,7 +2439,7 @@
         <v>136</v>
       </c>
       <c r="B136" s="1">
-        <v>145.5586697850432</v>
+        <v>139.4561407932709</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -2567,7 +2447,7 @@
         <v>137</v>
       </c>
       <c r="B137" s="1">
-        <v>145.6874196520826</v>
+        <v>139.5540873336665</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -2575,7 +2455,7 @@
         <v>138</v>
       </c>
       <c r="B138" s="1">
-        <v>145.7771804789558</v>
+        <v>139.7528622364796</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -2583,7 +2463,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="1">
-        <v>145.8478560641873</v>
+        <v>139.788460901412</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -2591,7 +2471,7 @@
         <v>140</v>
       </c>
       <c r="B140" s="1">
-        <v>145.8673501442741</v>
+        <v>139.8476427138656</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -2599,7 +2479,7 @@
         <v>141</v>
       </c>
       <c r="B141" s="1">
-        <v>145.9514855728845</v>
+        <v>139.8646952363676</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -2607,7 +2487,7 @@
         <v>142</v>
       </c>
       <c r="B142" s="1">
-        <v>146.0115969721941</v>
+        <v>139.8849269611022</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -2615,7 +2495,7 @@
         <v>143</v>
       </c>
       <c r="B143" s="1">
-        <v>146.0122492886034</v>
+        <v>139.8974090851178</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -2623,7 +2503,7 @@
         <v>144</v>
       </c>
       <c r="B144" s="1">
-        <v>146.0291730023319</v>
+        <v>139.9685033086227</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -2631,7 +2511,7 @@
         <v>145</v>
       </c>
       <c r="B145" s="1">
-        <v>146.0523272408333</v>
+        <v>140.1688639990773</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -2639,7 +2519,7 @@
         <v>146</v>
       </c>
       <c r="B146" s="1">
-        <v>146.1333484083241</v>
+        <v>140.1817840078584</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -2647,7 +2527,7 @@
         <v>147</v>
       </c>
       <c r="B147" s="1">
-        <v>146.2582220024996</v>
+        <v>140.2858128916649</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -2655,7 +2535,7 @@
         <v>148</v>
       </c>
       <c r="B148" s="1">
-        <v>146.2697088410681</v>
+        <v>140.3016246725128</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -2663,7 +2543,7 @@
         <v>149</v>
       </c>
       <c r="B149" s="1">
-        <v>146.4657448102584</v>
+        <v>140.4803939385575</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -2671,7 +2551,7 @@
         <v>150</v>
       </c>
       <c r="B150" s="1">
-        <v>146.5310366576604</v>
+        <v>140.4886364878397</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -2679,7 +2559,7 @@
         <v>151</v>
       </c>
       <c r="B151" s="1">
-        <v>146.632406937648</v>
+        <v>140.5491983858017</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -2687,7 +2567,7 @@
         <v>152</v>
       </c>
       <c r="B152" s="1">
-        <v>146.7111077489883</v>
+        <v>140.5505632835069</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -2695,7 +2575,7 @@
         <v>153</v>
       </c>
       <c r="B153" s="1">
-        <v>146.7136265496125</v>
+        <v>140.570388717293</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -2703,7 +2583,7 @@
         <v>154</v>
       </c>
       <c r="B154" s="1">
-        <v>146.8226257200928</v>
+        <v>140.6029818792996</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -2711,7 +2591,7 @@
         <v>155</v>
       </c>
       <c r="B155" s="1">
-        <v>146.8562748736842</v>
+        <v>140.6600489712138</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -2719,7 +2599,7 @@
         <v>156</v>
       </c>
       <c r="B156" s="1">
-        <v>147.0311818369598</v>
+        <v>140.6831709030577</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -2727,7 +2607,7 @@
         <v>157</v>
       </c>
       <c r="B157" s="1">
-        <v>147.1558314162329</v>
+        <v>140.8047689722629</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -2735,7 +2615,7 @@
         <v>158</v>
       </c>
       <c r="B158" s="1">
-        <v>147.1801675964391</v>
+        <v>140.8481574014934</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -2743,7 +2623,7 @@
         <v>159</v>
       </c>
       <c r="B159" s="1">
-        <v>147.3171115334467</v>
+        <v>140.9299930550523</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -2751,7 +2631,7 @@
         <v>160</v>
       </c>
       <c r="B160" s="1">
-        <v>147.4876510778121</v>
+        <v>141.1436295670682</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -2759,7 +2639,7 @@
         <v>161</v>
       </c>
       <c r="B161" s="1">
-        <v>147.7443310395245</v>
+        <v>141.1498074200022</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -2767,7 +2647,7 @@
         <v>162</v>
       </c>
       <c r="B162" s="1">
-        <v>147.9050371506544</v>
+        <v>141.3738995696563</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -2775,7 +2655,7 @@
         <v>163</v>
       </c>
       <c r="B163" s="1">
-        <v>148.00676430756</v>
+        <v>141.4944955319837</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -2783,7 +2663,7 @@
         <v>164</v>
       </c>
       <c r="B164" s="1">
-        <v>148.0199508661514</v>
+        <v>141.6149379342257</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -2791,7 +2671,7 @@
         <v>165</v>
       </c>
       <c r="B165" s="1">
-        <v>148.1034868633982</v>
+        <v>141.7445417132864</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -2799,7 +2679,7 @@
         <v>166</v>
       </c>
       <c r="B166" s="1">
-        <v>148.1228045553516</v>
+        <v>141.9971175891156</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -2807,7 +2687,7 @@
         <v>167</v>
       </c>
       <c r="B167" s="1">
-        <v>148.168000310745</v>
+        <v>142.1378061528011</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -2815,7 +2695,7 @@
         <v>168</v>
       </c>
       <c r="B168" s="1">
-        <v>148.204425236508</v>
+        <v>142.2859130021646</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -2823,7 +2703,7 @@
         <v>169</v>
       </c>
       <c r="B169" s="1">
-        <v>148.2258314562386</v>
+        <v>142.4279189917299</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -2831,7 +2711,7 @@
         <v>170</v>
       </c>
       <c r="B170" s="1">
-        <v>148.4803374113282</v>
+        <v>142.4451775676185</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -2839,7 +2719,7 @@
         <v>171</v>
       </c>
       <c r="B171" s="1">
-        <v>148.5213253562977</v>
+        <v>142.5328823474679</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -2847,7 +2727,7 @@
         <v>172</v>
       </c>
       <c r="B172" s="1">
-        <v>148.5227436888644</v>
+        <v>142.6311346826648</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -2855,7 +2735,7 @@
         <v>173</v>
       </c>
       <c r="B173" s="1">
-        <v>148.5504024193307</v>
+        <v>142.7016844730109</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -2863,7 +2743,7 @@
         <v>174</v>
       </c>
       <c r="B174" s="1">
-        <v>148.6592715474537</v>
+        <v>142.8766548099713</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -2871,7 +2751,7 @@
         <v>175</v>
       </c>
       <c r="B175" s="1">
-        <v>148.6772576143061</v>
+        <v>142.8936100139529</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -2879,7 +2759,7 @@
         <v>176</v>
       </c>
       <c r="B176" s="1">
-        <v>148.7165859347409</v>
+        <v>143.4293799926538</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -2887,7 +2767,7 @@
         <v>177</v>
       </c>
       <c r="B177" s="1">
-        <v>148.7397161833984</v>
+        <v>143.4965607302162</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -2895,7 +2775,7 @@
         <v>178</v>
       </c>
       <c r="B178" s="1">
-        <v>148.8116249814337</v>
+        <v>143.8696326440162</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -2903,7 +2783,7 @@
         <v>179</v>
       </c>
       <c r="B179" s="1">
-        <v>148.8484754637867</v>
+        <v>144.0590301591415</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -2911,7 +2791,7 @@
         <v>180</v>
       </c>
       <c r="B180" s="1">
-        <v>148.8786873545211</v>
+        <v>144.0800158428473</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -2919,7 +2799,7 @@
         <v>181</v>
       </c>
       <c r="B181" s="1">
-        <v>148.9753596639122</v>
+        <v>144.1902679147018</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -2927,7 +2807,7 @@
         <v>182</v>
       </c>
       <c r="B182" s="1">
-        <v>148.9902393566263</v>
+        <v>144.2222542109978</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -2935,7 +2815,7 @@
         <v>183</v>
       </c>
       <c r="B183" s="1">
-        <v>149.4288426412054</v>
+        <v>144.5482721205284</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -2943,7 +2823,7 @@
         <v>184</v>
       </c>
       <c r="B184" s="1">
-        <v>149.8001924499408</v>
+        <v>144.6415685083634</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -2951,7 +2831,7 @@
         <v>185</v>
       </c>
       <c r="B185" s="1">
-        <v>149.9903368779129</v>
+        <v>144.692163104913</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -2959,7 +2839,7 @@
         <v>186</v>
       </c>
       <c r="B186" s="1">
-        <v>150.1433452796223</v>
+        <v>144.6949912863568</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -2967,7 +2847,7 @@
         <v>187</v>
       </c>
       <c r="B187" s="1">
-        <v>150.2461938227445</v>
+        <v>144.7546683844614</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -2975,7 +2855,7 @@
         <v>188</v>
       </c>
       <c r="B188" s="1">
-        <v>150.2610035622114</v>
+        <v>144.8602175815853</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -2983,7 +2863,7 @@
         <v>189</v>
       </c>
       <c r="B189" s="1">
-        <v>150.4429086668608</v>
+        <v>144.9035588150722</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -2991,7 +2871,7 @@
         <v>190</v>
       </c>
       <c r="B190" s="1">
-        <v>150.4442443375513</v>
+        <v>145.0186326059533</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -2999,7 +2879,7 @@
         <v>191</v>
       </c>
       <c r="B191" s="1">
-        <v>150.565669745216</v>
+        <v>145.2248402289466</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -3007,7 +2887,7 @@
         <v>192</v>
       </c>
       <c r="B192" s="1">
-        <v>150.6715356849958</v>
+        <v>145.2708806659446</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -3015,7 +2895,7 @@
         <v>193</v>
       </c>
       <c r="B193" s="1">
-        <v>150.7232644936856</v>
+        <v>145.2712689674481</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -3023,7 +2903,7 @@
         <v>194</v>
       </c>
       <c r="B194" s="1">
-        <v>150.8990004468832</v>
+        <v>146.0692451850791</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -3031,7 +2911,7 @@
         <v>195</v>
       </c>
       <c r="B195" s="1">
-        <v>151.1941754507485</v>
+        <v>146.1780301231503</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -3039,7 +2919,7 @@
         <v>196</v>
       </c>
       <c r="B196" s="1">
-        <v>151.1944962367647</v>
+        <v>146.259727358538</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -3047,7 +2927,7 @@
         <v>197</v>
       </c>
       <c r="B197" s="1">
-        <v>151.6552032242236</v>
+        <v>146.4094264237745</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -3055,7 +2935,7 @@
         <v>198</v>
       </c>
       <c r="B198" s="1">
-        <v>151.7458986072924</v>
+        <v>146.5809838733086</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -3063,7 +2943,7 @@
         <v>199</v>
       </c>
       <c r="B199" s="1">
-        <v>151.7930480175272</v>
+        <v>146.7402127489977</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -3071,7 +2951,7 @@
         <v>200</v>
       </c>
       <c r="B200" s="1">
-        <v>151.8357553472608</v>
+        <v>146.8285661738778</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -3079,7 +2959,7 @@
         <v>201</v>
       </c>
       <c r="B201" s="1">
-        <v>151.8627797313298</v>
+        <v>147.1379470526188</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -3087,7 +2967,7 @@
         <v>202</v>
       </c>
       <c r="B202" s="1">
-        <v>152.0898108056934</v>
+        <v>147.2667966495009</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -3095,7 +2975,7 @@
         <v>203</v>
       </c>
       <c r="B203" s="1">
-        <v>152.2883628158504</v>
+        <v>147.3335984920871</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -3103,7 +2983,7 @@
         <v>204</v>
       </c>
       <c r="B204" s="1">
-        <v>152.3298878902208</v>
+        <v>147.4765492979953</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -3111,7 +2991,7 @@
         <v>205</v>
       </c>
       <c r="B205" s="1">
-        <v>152.333804973313</v>
+        <v>147.7309661794874</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -3119,7 +2999,7 @@
         <v>206</v>
       </c>
       <c r="B206" s="1">
-        <v>152.4224023976398</v>
+        <v>148.2026101301634</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -3127,7 +3007,7 @@
         <v>207</v>
       </c>
       <c r="B207" s="1">
-        <v>152.4422426524919</v>
+        <v>148.3987471328047</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -3135,7 +3015,7 @@
         <v>208</v>
       </c>
       <c r="B208" s="1">
-        <v>152.4592499398751</v>
+        <v>148.4293495016097</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -3143,7 +3023,7 @@
         <v>209</v>
       </c>
       <c r="B209" s="1">
-        <v>152.6343407855723</v>
+        <v>148.4463954505772</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -3151,7 +3031,7 @@
         <v>210</v>
       </c>
       <c r="B210" s="1">
-        <v>152.7597854337902</v>
+        <v>148.5809303255238</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -3159,7 +3039,7 @@
         <v>211</v>
       </c>
       <c r="B211" s="1">
-        <v>152.7614276342225</v>
+        <v>149.045523877299</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -3167,7 +3047,7 @@
         <v>212</v>
       </c>
       <c r="B212" s="1">
-        <v>152.8238586764627</v>
+        <v>149.0990341524744</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -3175,7 +3055,7 @@
         <v>213</v>
       </c>
       <c r="B213" s="1">
-        <v>153.3339948378739</v>
+        <v>149.1724738286315</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -3183,7 +3063,7 @@
         <v>214</v>
       </c>
       <c r="B214" s="1">
-        <v>153.7322509652283</v>
+        <v>149.2954192871287</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -3191,7 +3071,7 @@
         <v>215</v>
       </c>
       <c r="B215" s="1">
-        <v>153.8254827358357</v>
+        <v>149.8172701293772</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -3199,7 +3079,7 @@
         <v>216</v>
       </c>
       <c r="B216" s="1">
-        <v>153.9885365552946</v>
+        <v>150.5165850579068</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -3207,7 +3087,7 @@
         <v>217</v>
       </c>
       <c r="B217" s="1">
-        <v>154.1222109275584</v>
+        <v>150.7083323887239</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -3215,7 +3095,7 @@
         <v>218</v>
       </c>
       <c r="B218" s="1">
-        <v>154.1747385777701</v>
+        <v>150.9576870764507</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -3223,7 +3103,7 @@
         <v>219</v>
       </c>
       <c r="B219" s="1">
-        <v>154.926036710481</v>
+        <v>151.070099883861</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -3231,7 +3111,7 @@
         <v>220</v>
       </c>
       <c r="B220" s="1">
-        <v>154.9622470014539</v>
+        <v>151.1869210444988</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -3239,7 +3119,7 @@
         <v>221</v>
       </c>
       <c r="B221" s="1">
-        <v>155.4703577851581</v>
+        <v>151.1949273850225</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -3247,7 +3127,7 @@
         <v>222</v>
       </c>
       <c r="B222" s="1">
-        <v>155.6121883410259</v>
+        <v>151.6349094459205</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -3255,7 +3135,7 @@
         <v>223</v>
       </c>
       <c r="B223" s="1">
-        <v>155.7155336731865</v>
+        <v>151.7560628001356</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -3263,7 +3143,7 @@
         <v>224</v>
       </c>
       <c r="B224" s="1">
-        <v>155.7719984672208</v>
+        <v>151.8489983692553</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -3271,7 +3151,7 @@
         <v>225</v>
       </c>
       <c r="B225" s="1">
-        <v>155.8151466070369</v>
+        <v>151.9613245333938</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -3279,7 +3159,7 @@
         <v>226</v>
       </c>
       <c r="B226" s="1">
-        <v>156.0587005592275</v>
+        <v>152.0263027182713</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -3287,7 +3167,7 @@
         <v>227</v>
       </c>
       <c r="B227" s="1">
-        <v>156.8233377591846</v>
+        <v>152.4634264696241</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -3295,7 +3175,7 @@
         <v>228</v>
       </c>
       <c r="B228" s="1">
-        <v>156.8422495088006</v>
+        <v>152.7081929577312</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -3303,7 +3183,7 @@
         <v>229</v>
       </c>
       <c r="B229" s="1">
-        <v>156.8889817059661</v>
+        <v>152.8384239407649</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -3311,7 +3191,7 @@
         <v>230</v>
       </c>
       <c r="B230" s="1">
-        <v>157.1591824532886</v>
+        <v>153.2000983220264</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -3319,7 +3199,7 @@
         <v>231</v>
       </c>
       <c r="B231" s="1">
-        <v>157.5731518526055</v>
+        <v>153.3548575012401</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -3327,7 +3207,7 @@
         <v>232</v>
       </c>
       <c r="B232" s="1">
-        <v>157.6506861245939</v>
+        <v>153.4386380464938</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -3335,7 +3215,7 @@
         <v>233</v>
       </c>
       <c r="B233" s="1">
-        <v>157.690312310653</v>
+        <v>153.4393796479383</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -3343,7 +3223,7 @@
         <v>234</v>
       </c>
       <c r="B234" s="1">
-        <v>157.7221212123568</v>
+        <v>154.0481122143651</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -3351,7 +3231,7 @@
         <v>235</v>
       </c>
       <c r="B235" s="1">
-        <v>157.7715499085963</v>
+        <v>154.420228958684</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -3359,7 +3239,7 @@
         <v>236</v>
       </c>
       <c r="B236" s="1">
-        <v>157.8852617638525</v>
+        <v>155.026275051384</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -3367,7 +3247,7 @@
         <v>237</v>
       </c>
       <c r="B237" s="1">
-        <v>158.1512341091337</v>
+        <v>155.3333619187437</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -3375,7 +3255,7 @@
         <v>238</v>
       </c>
       <c r="B238" s="1">
-        <v>158.1967608879753</v>
+        <v>156.2186758695682</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -3383,7 +3263,7 @@
         <v>239</v>
       </c>
       <c r="B239" s="1">
-        <v>158.4279467545706</v>
+        <v>156.2233337826705</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -3391,7 +3271,7 @@
         <v>240</v>
       </c>
       <c r="B240" s="1">
-        <v>159.0880236059803</v>
+        <v>156.572011137729</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -3399,7 +3279,7 @@
         <v>241</v>
       </c>
       <c r="B241" s="1">
-        <v>159.1537021783387</v>
+        <v>156.8845963151284</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -3407,7 +3287,7 @@
         <v>242</v>
       </c>
       <c r="B242" s="1">
-        <v>159.4552300614482</v>
+        <v>157.6286106981774</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -3415,7 +3295,7 @@
         <v>243</v>
       </c>
       <c r="B243" s="1">
-        <v>159.544380796584</v>
+        <v>157.6522101953819</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -3423,7 +3303,7 @@
         <v>244</v>
       </c>
       <c r="B244" s="1">
-        <v>159.6581088213393</v>
+        <v>157.6821916766821</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -3431,7 +3311,7 @@
         <v>245</v>
       </c>
       <c r="B245" s="1">
-        <v>159.8192609539429</v>
+        <v>157.9975906530497</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -3439,7 +3319,7 @@
         <v>246</v>
       </c>
       <c r="B246" s="1">
-        <v>159.9366583040839</v>
+        <v>158.1026241464933</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -3447,7 +3327,7 @@
         <v>247</v>
       </c>
       <c r="B247" s="1">
-        <v>160.0755362125547</v>
+        <v>158.3176885435086</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -3455,7 +3335,7 @@
         <v>248</v>
       </c>
       <c r="B248" s="1">
-        <v>160.3321714190521</v>
+        <v>158.5063885319229</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -3463,7 +3343,7 @@
         <v>249</v>
       </c>
       <c r="B249" s="1">
-        <v>160.3863162968006</v>
+        <v>158.7304330762128</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -3471,7 +3351,7 @@
         <v>250</v>
       </c>
       <c r="B250" s="1">
-        <v>160.3951568308797</v>
+        <v>159.2256496329512</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -3479,7 +3359,7 @@
         <v>251</v>
       </c>
       <c r="B251" s="1">
-        <v>160.5210859226177</v>
+        <v>159.3176407482934</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -3487,7 +3367,7 @@
         <v>252</v>
       </c>
       <c r="B252" s="1">
-        <v>161.318755584536</v>
+        <v>159.3722911180282</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -3495,7 +3375,7 @@
         <v>253</v>
       </c>
       <c r="B253" s="1">
-        <v>161.8106725925103</v>
+        <v>159.4702308581652</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -3503,7 +3383,7 @@
         <v>254</v>
       </c>
       <c r="B254" s="1">
-        <v>162.0789813233197</v>
+        <v>159.788525686778</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -3511,7 +3391,7 @@
         <v>255</v>
       </c>
       <c r="B255" s="1">
-        <v>162.1404218765388</v>
+        <v>159.8438640635044</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -3519,7 +3399,7 @@
         <v>256</v>
       </c>
       <c r="B256" s="1">
-        <v>162.1926279569011</v>
+        <v>160.2191192407651</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -3527,7 +3407,7 @@
         <v>257</v>
       </c>
       <c r="B257" s="1">
-        <v>162.2340283588514</v>
+        <v>160.2359330108084</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -3535,7 +3415,7 @@
         <v>258</v>
       </c>
       <c r="B258" s="1">
-        <v>162.5719384447257</v>
+        <v>160.3795810929254</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -3543,7 +3423,7 @@
         <v>259</v>
       </c>
       <c r="B259" s="1">
-        <v>162.6360116283743</v>
+        <v>160.6792091524873</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -3551,7 +3431,7 @@
         <v>260</v>
       </c>
       <c r="B260" s="1">
-        <v>162.775587843783</v>
+        <v>162.1359849282519</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -3559,7 +3439,7 @@
         <v>261</v>
       </c>
       <c r="B261" s="1">
-        <v>163.2059727441025</v>
+        <v>163.6335494742071</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -3567,7 +3447,7 @@
         <v>262</v>
       </c>
       <c r="B262" s="1">
-        <v>163.6008492178738</v>
+        <v>164.0314532066326</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -3575,7 +3455,7 @@
         <v>263</v>
       </c>
       <c r="B263" s="1">
-        <v>163.61173686411</v>
+        <v>164.1479663058912</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -3583,7 +3463,7 @@
         <v>264</v>
       </c>
       <c r="B264" s="1">
-        <v>163.8870313627493</v>
+        <v>164.1738063820643</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -3591,7 +3471,7 @@
         <v>265</v>
       </c>
       <c r="B265" s="1">
-        <v>164.7343138404654</v>
+        <v>164.6609273103286</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -3599,7 +3479,7 @@
         <v>266</v>
       </c>
       <c r="B266" s="1">
-        <v>164.7862566176076</v>
+        <v>164.6637264434003</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -3607,7 +3487,7 @@
         <v>267</v>
       </c>
       <c r="B267" s="1">
-        <v>165.2712112287705</v>
+        <v>164.7581313450536</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -3615,7 +3495,7 @@
         <v>268</v>
       </c>
       <c r="B268" s="1">
-        <v>165.7478693885261</v>
+        <v>165.6903873191379</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -3623,7 +3503,7 @@
         <v>269</v>
       </c>
       <c r="B269" s="1">
-        <v>165.9362414392656</v>
+        <v>166.8936676425027</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -3631,7 +3511,7 @@
         <v>270</v>
       </c>
       <c r="B270" s="1">
-        <v>166.7672638145179</v>
+        <v>167.9518987616215</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -3639,7 +3519,7 @@
         <v>271</v>
       </c>
       <c r="B271" s="1">
-        <v>167.1012778048138</v>
+        <v>168.7930115340081</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -3647,7 +3527,7 @@
         <v>272</v>
       </c>
       <c r="B272" s="1">
-        <v>167.2588838695628</v>
+        <v>170.0064407452977</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -3655,7 +3535,7 @@
         <v>273</v>
       </c>
       <c r="B273" s="1">
-        <v>167.8767839534319</v>
+        <v>170.1096312798175</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -3663,7 +3543,7 @@
         <v>274</v>
       </c>
       <c r="B274" s="1">
-        <v>167.9573475553624</v>
+        <v>170.4589471201529</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -3671,7 +3551,7 @@
         <v>275</v>
       </c>
       <c r="B275" s="1">
-        <v>168.1062429415455</v>
+        <v>170.963041427082</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -3679,7 +3559,7 @@
         <v>276</v>
       </c>
       <c r="B276" s="1">
-        <v>168.4439175777551</v>
+        <v>171.573049160733</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -3687,7 +3567,7 @@
         <v>277</v>
       </c>
       <c r="B277" s="1">
-        <v>168.7398494976057</v>
+        <v>171.5766682443286</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -3695,7 +3575,7 @@
         <v>278</v>
       </c>
       <c r="B278" s="1">
-        <v>169.0202118435182</v>
+        <v>171.696215708971</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -3703,7 +3583,7 @@
         <v>279</v>
       </c>
       <c r="B279" s="1">
-        <v>169.9042838465698</v>
+        <v>173.083899162879</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -3711,7 +3591,7 @@
         <v>280</v>
       </c>
       <c r="B280" s="1">
-        <v>169.9495084841492</v>
+        <v>174.9834226493426</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -3719,7 +3599,7 @@
         <v>281</v>
       </c>
       <c r="B281" s="1">
-        <v>171.4245788359831</v>
+        <v>175.2341086455913</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -3727,7 +3607,7 @@
         <v>282</v>
       </c>
       <c r="B282" s="1">
-        <v>171.7541414008859</v>
+        <v>175.274495622687</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -3735,7 +3615,7 @@
         <v>283</v>
       </c>
       <c r="B283" s="1">
-        <v>171.8209673604115</v>
+        <v>176.085008564365</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -3743,7 +3623,7 @@
         <v>284</v>
       </c>
       <c r="B284" s="1">
-        <v>172.5877198703604</v>
+        <v>176.4818509157336</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -3751,7 +3631,7 @@
         <v>285</v>
       </c>
       <c r="B285" s="1">
-        <v>173.0898488938615</v>
+        <v>176.6500411554718</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -3759,7 +3639,7 @@
         <v>286</v>
       </c>
       <c r="B286" s="1">
-        <v>173.5201968164739</v>
+        <v>176.8736102167953</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -3767,7 +3647,7 @@
         <v>287</v>
       </c>
       <c r="B287" s="1">
-        <v>173.8234180936929</v>
+        <v>177.9745074336391</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -3775,7 +3655,7 @@
         <v>288</v>
       </c>
       <c r="B288" s="1">
-        <v>174.1693606352181</v>
+        <v>179.2773584895475</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -3783,7 +3663,7 @@
         <v>289</v>
       </c>
       <c r="B289" s="1">
-        <v>174.6461847681058</v>
+        <v>182.1067917868554</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -3791,7 +3671,7 @@
         <v>290</v>
       </c>
       <c r="B290" s="1">
-        <v>174.6466723000609</v>
+        <v>182.8578568114873</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -3799,7 +3679,7 @@
         <v>291</v>
       </c>
       <c r="B291" s="1">
-        <v>175.1609691669011</v>
+        <v>183.9838616740865</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -3807,7 +3687,7 @@
         <v>292</v>
       </c>
       <c r="B292" s="1">
-        <v>175.1686566000805</v>
+        <v>185.1375559245426</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -3815,7 +3695,7 @@
         <v>293</v>
       </c>
       <c r="B293" s="1">
-        <v>175.4405520769</v>
+        <v>187.1541375601494</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -3823,7 +3703,7 @@
         <v>294</v>
       </c>
       <c r="B294" s="1">
-        <v>175.9644073922579</v>
+        <v>190.2099952632329</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -3831,7 +3711,7 @@
         <v>295</v>
       </c>
       <c r="B295" s="1">
-        <v>176.6277490172018</v>
+        <v>190.4605564406618</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -3839,7 +3719,7 @@
         <v>296</v>
       </c>
       <c r="B296" s="1">
-        <v>176.9675882803405</v>
+        <v>192.2999812711404</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -3847,7 +3727,7 @@
         <v>297</v>
       </c>
       <c r="B297" s="1">
-        <v>177.6893531672492</v>
+        <v>192.8770640342961</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -3855,7 +3735,7 @@
         <v>298</v>
       </c>
       <c r="B298" s="1">
-        <v>178.0355224079531</v>
+        <v>192.8927852217686</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -3863,7 +3743,7 @@
         <v>299</v>
       </c>
       <c r="B299" s="1">
-        <v>178.1942045041361</v>
+        <v>193.4235826684304</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -3871,7 +3751,7 @@
         <v>300</v>
       </c>
       <c r="B300" s="1">
-        <v>182.1629781173368</v>
+        <v>194.3385198777316</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -3879,7 +3759,7 @@
         <v>301</v>
       </c>
       <c r="B301" s="1">
-        <v>182.3767807966469</v>
+        <v>194.8419474346039</v>
       </c>
     </row>
     <row r="302" spans="1:2">
@@ -3887,7 +3767,7 @@
         <v>302</v>
       </c>
       <c r="B302" s="1">
-        <v>182.3985777141801</v>
+        <v>195.4219817739837</v>
       </c>
     </row>
     <row r="303" spans="1:2">
@@ -3895,7 +3775,7 @@
         <v>303</v>
       </c>
       <c r="B303" s="1">
-        <v>184.6303764313633</v>
+        <v>195.7388368344477</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -3903,7 +3783,7 @@
         <v>304</v>
       </c>
       <c r="B304" s="1">
-        <v>184.8996760724754</v>
+        <v>196.4221822485067</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -3911,7 +3791,7 @@
         <v>305</v>
       </c>
       <c r="B305" s="1">
-        <v>186.3484364629211</v>
+        <v>200.8887125565817</v>
       </c>
     </row>
     <row r="306" spans="1:2">
@@ -3919,7 +3799,7 @@
         <v>306</v>
       </c>
       <c r="B306" s="1">
-        <v>186.6565012692695</v>
+        <v>205.2429945071746</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -3927,7 +3807,7 @@
         <v>307</v>
       </c>
       <c r="B307" s="1">
-        <v>186.8949846831205</v>
+        <v>206.6701527454403</v>
       </c>
     </row>
     <row r="308" spans="1:2">
@@ -3935,7 +3815,7 @@
         <v>308</v>
       </c>
       <c r="B308" s="1">
-        <v>187.8209017506827</v>
+        <v>209.0189939958908</v>
       </c>
     </row>
     <row r="309" spans="1:2">
@@ -3943,7 +3823,7 @@
         <v>309</v>
       </c>
       <c r="B309" s="1">
-        <v>188.4294479710993</v>
+        <v>213.5306501931515</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -3951,7 +3831,7 @@
         <v>310</v>
       </c>
       <c r="B310" s="1">
-        <v>189.8091139521081</v>
+        <v>218.6491159861113</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -3959,7 +3839,7 @@
         <v>311</v>
       </c>
       <c r="B311" s="1">
-        <v>189.9161194093101</v>
+        <v>226.9743659900273</v>
       </c>
     </row>
     <row r="312" spans="1:2">
@@ -3967,7 +3847,7 @@
         <v>312</v>
       </c>
       <c r="B312" s="1">
-        <v>190.5096572645835</v>
+        <v>229.8417410344738</v>
       </c>
     </row>
     <row r="313" spans="1:2">
@@ -3975,7 +3855,7 @@
         <v>313</v>
       </c>
       <c r="B313" s="1">
-        <v>191.1506418617892</v>
+        <v>245.6483509512667</v>
       </c>
     </row>
     <row r="314" spans="1:2">
@@ -3983,7 +3863,7 @@
         <v>314</v>
       </c>
       <c r="B314" s="1">
-        <v>192.4061441295251</v>
+        <v>246.3015896134957</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -3991,7 +3871,7 @@
         <v>315</v>
       </c>
       <c r="B315" s="1">
-        <v>192.5412637843312</v>
+        <v>247.6318496368786</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -3999,7 +3879,7 @@
         <v>316</v>
       </c>
       <c r="B316" s="1">
-        <v>193.145301612815</v>
+        <v>249.4757856638007</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -4007,7 +3887,7 @@
         <v>317</v>
       </c>
       <c r="B317" s="1">
-        <v>193.7785972366965</v>
+        <v>249.7076333205924</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -4015,7 +3895,7 @@
         <v>318</v>
       </c>
       <c r="B318" s="1">
-        <v>194.2755384076055</v>
+        <v>265.5535118419622</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -4023,7 +3903,7 @@
         <v>319</v>
       </c>
       <c r="B319" s="1">
-        <v>194.968050850363</v>
+        <v>267.3953710487986</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -4031,7 +3911,7 @@
         <v>320</v>
       </c>
       <c r="B320" s="1">
-        <v>196.1308526990321</v>
+        <v>277.1603816110563</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -4039,7 +3919,7 @@
         <v>321</v>
       </c>
       <c r="B321" s="1">
-        <v>196.2843049805526</v>
+        <v>280.1621561560102</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -4047,7 +3927,7 @@
         <v>322</v>
       </c>
       <c r="B322" s="1">
-        <v>197.4678031685473</v>
+        <v>295.1944893761822</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -4055,7 +3935,7 @@
         <v>323</v>
       </c>
       <c r="B323" s="1">
-        <v>198.7689075072755</v>
+        <v>296.7704629716832</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -4063,7 +3943,7 @@
         <v>324</v>
       </c>
       <c r="B324" s="1">
-        <v>199.2509332174167</v>
+        <v>305.7540545322861</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -4071,7 +3951,7 @@
         <v>325</v>
       </c>
       <c r="B325" s="1">
-        <v>199.730008983556</v>
+        <v>512.3633645654282</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -4079,7 +3959,7 @@
         <v>326</v>
       </c>
       <c r="B326" s="1">
-        <v>199.8787038733008</v>
+        <v>567.1717836405109</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -4087,7 +3967,7 @@
         <v>327</v>
       </c>
       <c r="B327" s="1">
-        <v>202.8675769825743</v>
+        <v>594.5424739133769</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -4095,327 +3975,7 @@
         <v>328</v>
       </c>
       <c r="B328" s="1">
-        <v>202.9991148398219</v>
-      </c>
-    </row>
-    <row r="329" spans="1:2">
-      <c r="A329" t="s">
-        <v>329</v>
-      </c>
-      <c r="B329" s="1">
-        <v>204.7653652253236</v>
-      </c>
-    </row>
-    <row r="330" spans="1:2">
-      <c r="A330" t="s">
-        <v>330</v>
-      </c>
-      <c r="B330" s="1">
-        <v>207.1715075900056</v>
-      </c>
-    </row>
-    <row r="331" spans="1:2">
-      <c r="A331" t="s">
-        <v>331</v>
-      </c>
-      <c r="B331" s="1">
-        <v>207.7331301217209</v>
-      </c>
-    </row>
-    <row r="332" spans="1:2">
-      <c r="A332" t="s">
-        <v>332</v>
-      </c>
-      <c r="B332" s="1">
-        <v>208.864419466937</v>
-      </c>
-    </row>
-    <row r="333" spans="1:2">
-      <c r="A333" t="s">
-        <v>333</v>
-      </c>
-      <c r="B333" s="1">
-        <v>209.0820684720069</v>
-      </c>
-    </row>
-    <row r="334" spans="1:2">
-      <c r="A334" t="s">
-        <v>334</v>
-      </c>
-      <c r="B334" s="1">
-        <v>209.6265159623706</v>
-      </c>
-    </row>
-    <row r="335" spans="1:2">
-      <c r="A335" t="s">
-        <v>335</v>
-      </c>
-      <c r="B335" s="1">
-        <v>209.6996280418062</v>
-      </c>
-    </row>
-    <row r="336" spans="1:2">
-      <c r="A336" t="s">
-        <v>336</v>
-      </c>
-      <c r="B336" s="1">
-        <v>210.5671487052272</v>
-      </c>
-    </row>
-    <row r="337" spans="1:2">
-      <c r="A337" t="s">
-        <v>337</v>
-      </c>
-      <c r="B337" s="1">
-        <v>211.975948228974</v>
-      </c>
-    </row>
-    <row r="338" spans="1:2">
-      <c r="A338" t="s">
-        <v>338</v>
-      </c>
-      <c r="B338" s="1">
-        <v>212.7715625230339</v>
-      </c>
-    </row>
-    <row r="339" spans="1:2">
-      <c r="A339" t="s">
-        <v>339</v>
-      </c>
-      <c r="B339" s="1">
-        <v>215.4111322220793</v>
-      </c>
-    </row>
-    <row r="340" spans="1:2">
-      <c r="A340" t="s">
-        <v>340</v>
-      </c>
-      <c r="B340" s="1">
-        <v>215.6268381402093</v>
-      </c>
-    </row>
-    <row r="341" spans="1:2">
-      <c r="A341" t="s">
-        <v>341</v>
-      </c>
-      <c r="B341" s="1">
-        <v>217.5381073886436</v>
-      </c>
-    </row>
-    <row r="342" spans="1:2">
-      <c r="A342" t="s">
-        <v>342</v>
-      </c>
-      <c r="B342" s="1">
-        <v>220.7439310483481</v>
-      </c>
-    </row>
-    <row r="343" spans="1:2">
-      <c r="A343" t="s">
-        <v>343</v>
-      </c>
-      <c r="B343" s="1">
-        <v>226.7871563241533</v>
-      </c>
-    </row>
-    <row r="344" spans="1:2">
-      <c r="A344" t="s">
-        <v>344</v>
-      </c>
-      <c r="B344" s="1">
-        <v>231.7763632427629</v>
-      </c>
-    </row>
-    <row r="345" spans="1:2">
-      <c r="A345" t="s">
-        <v>345</v>
-      </c>
-      <c r="B345" s="1">
-        <v>233.3880892230295</v>
-      </c>
-    </row>
-    <row r="346" spans="1:2">
-      <c r="A346" t="s">
-        <v>346</v>
-      </c>
-      <c r="B346" s="1">
-        <v>239.0976489638589</v>
-      </c>
-    </row>
-    <row r="347" spans="1:2">
-      <c r="A347" t="s">
-        <v>347</v>
-      </c>
-      <c r="B347" s="1">
-        <v>240.1459983451321</v>
-      </c>
-    </row>
-    <row r="348" spans="1:2">
-      <c r="A348" t="s">
-        <v>348</v>
-      </c>
-      <c r="B348" s="1">
-        <v>244.739497990157</v>
-      </c>
-    </row>
-    <row r="349" spans="1:2">
-      <c r="A349" t="s">
-        <v>349</v>
-      </c>
-      <c r="B349" s="1">
-        <v>245.878696221241</v>
-      </c>
-    </row>
-    <row r="350" spans="1:2">
-      <c r="A350" t="s">
-        <v>350</v>
-      </c>
-      <c r="B350" s="1">
-        <v>252.7612858151726</v>
-      </c>
-    </row>
-    <row r="351" spans="1:2">
-      <c r="A351" t="s">
-        <v>351</v>
-      </c>
-      <c r="B351" s="1">
-        <v>256.962439075991</v>
-      </c>
-    </row>
-    <row r="352" spans="1:2">
-      <c r="A352" t="s">
-        <v>352</v>
-      </c>
-      <c r="B352" s="1">
-        <v>270.6698224521361</v>
-      </c>
-    </row>
-    <row r="353" spans="1:2">
-      <c r="A353" t="s">
-        <v>353</v>
-      </c>
-      <c r="B353" s="1">
-        <v>271.423862128658</v>
-      </c>
-    </row>
-    <row r="354" spans="1:2">
-      <c r="A354" t="s">
-        <v>354</v>
-      </c>
-      <c r="B354" s="1">
-        <v>287.2650587313971</v>
-      </c>
-    </row>
-    <row r="355" spans="1:2">
-      <c r="A355" t="s">
-        <v>355</v>
-      </c>
-      <c r="B355" s="1">
-        <v>288.9527169235999</v>
-      </c>
-    </row>
-    <row r="356" spans="1:2">
-      <c r="A356" t="s">
-        <v>356</v>
-      </c>
-      <c r="B356" s="1">
-        <v>296.2171892448593</v>
-      </c>
-    </row>
-    <row r="357" spans="1:2">
-      <c r="A357" t="s">
-        <v>357</v>
-      </c>
-      <c r="B357" s="1">
-        <v>297.2837277422557</v>
-      </c>
-    </row>
-    <row r="358" spans="1:2">
-      <c r="A358" t="s">
-        <v>358</v>
-      </c>
-      <c r="B358" s="1">
-        <v>298.165518083229</v>
-      </c>
-    </row>
-    <row r="359" spans="1:2">
-      <c r="A359" t="s">
-        <v>359</v>
-      </c>
-      <c r="B359" s="1">
-        <v>307.7277061033978</v>
-      </c>
-    </row>
-    <row r="360" spans="1:2">
-      <c r="A360" t="s">
-        <v>360</v>
-      </c>
-      <c r="B360" s="1">
-        <v>317.9593612186261</v>
-      </c>
-    </row>
-    <row r="361" spans="1:2">
-      <c r="A361" t="s">
-        <v>361</v>
-      </c>
-      <c r="B361" s="1">
-        <v>322.2189265119928</v>
-      </c>
-    </row>
-    <row r="362" spans="1:2">
-      <c r="A362" t="s">
-        <v>362</v>
-      </c>
-      <c r="B362" s="1">
-        <v>355.1290127954948</v>
-      </c>
-    </row>
-    <row r="363" spans="1:2">
-      <c r="A363" t="s">
-        <v>363</v>
-      </c>
-      <c r="B363" s="1">
-        <v>386.9422677527307</v>
-      </c>
-    </row>
-    <row r="364" spans="1:2">
-      <c r="A364" t="s">
-        <v>364</v>
-      </c>
-      <c r="B364" s="1">
-        <v>408.3573055448696</v>
-      </c>
-    </row>
-    <row r="365" spans="1:2">
-      <c r="A365" t="s">
-        <v>365</v>
-      </c>
-      <c r="B365" s="1">
-        <v>439.6913150972075</v>
-      </c>
-    </row>
-    <row r="366" spans="1:2">
-      <c r="A366" t="s">
-        <v>366</v>
-      </c>
-      <c r="B366" s="1">
-        <v>503.5462719615929</v>
-      </c>
-    </row>
-    <row r="367" spans="1:2">
-      <c r="A367" t="s">
-        <v>367</v>
-      </c>
-      <c r="B367" s="1">
-        <v>549.581708043965</v>
-      </c>
-    </row>
-    <row r="368" spans="1:2">
-      <c r="A368" t="s">
-        <v>368</v>
-      </c>
-      <c r="B368" s="1">
-        <v>575.1362957276335</v>
+        <v>652.0128981926437</v>
       </c>
     </row>
   </sheetData>

--- a/Screener/data/rs_rating_top_30.xlsx
+++ b/Screener/data/rs_rating_top_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="371">
   <si>
     <t>Symbol</t>
   </si>
@@ -22,826 +22,937 @@
     <t>RS Rating</t>
   </si>
   <si>
+    <t>FTNT</t>
+  </si>
+  <si>
+    <t>IMTX</t>
+  </si>
+  <si>
+    <t>TARO</t>
+  </si>
+  <si>
+    <t>DECK</t>
+  </si>
+  <si>
+    <t>GNRC</t>
+  </si>
+  <si>
+    <t>TREX</t>
+  </si>
+  <si>
+    <t>MTR</t>
+  </si>
+  <si>
+    <t>URBN</t>
+  </si>
+  <si>
+    <t>TWST</t>
+  </si>
+  <si>
+    <t>FND</t>
+  </si>
+  <si>
     <t>LUNG</t>
   </si>
   <si>
+    <t>VEL</t>
+  </si>
+  <si>
+    <t>WCC</t>
+  </si>
+  <si>
+    <t>LZRFY</t>
+  </si>
+  <si>
+    <t>BUR</t>
+  </si>
+  <si>
+    <t>CPA</t>
+  </si>
+  <si>
+    <t>EXP</t>
+  </si>
+  <si>
+    <t>ALSN</t>
+  </si>
+  <si>
+    <t>EDU</t>
+  </si>
+  <si>
+    <t>CNMD</t>
+  </si>
+  <si>
+    <t>HOFV</t>
+  </si>
+  <si>
+    <t>LECO</t>
+  </si>
+  <si>
+    <t>PHG</t>
+  </si>
+  <si>
+    <t>ALBY</t>
+  </si>
+  <si>
+    <t>NYCB</t>
+  </si>
+  <si>
+    <t>MTH</t>
+  </si>
+  <si>
+    <t>CPSS</t>
+  </si>
+  <si>
+    <t>HROW</t>
+  </si>
+  <si>
+    <t>GCBC</t>
+  </si>
+  <si>
+    <t>SIBN</t>
+  </si>
+  <si>
     <t>ZUO</t>
   </si>
   <si>
-    <t>WOR</t>
-  </si>
-  <si>
-    <t>ANGN</t>
-  </si>
-  <si>
-    <t>SCX</t>
-  </si>
-  <si>
-    <t>RELY</t>
-  </si>
-  <si>
-    <t>LTH</t>
-  </si>
-  <si>
-    <t>TWST</t>
-  </si>
-  <si>
-    <t>ASMIY</t>
-  </si>
-  <si>
-    <t>URBN</t>
-  </si>
-  <si>
-    <t>GNRC</t>
-  </si>
-  <si>
-    <t>IMTX</t>
-  </si>
-  <si>
-    <t>WCC</t>
-  </si>
-  <si>
-    <t>DECK</t>
+    <t>PRI</t>
+  </si>
+  <si>
+    <t>NEOG</t>
+  </si>
+  <si>
+    <t>CARS</t>
+  </si>
+  <si>
+    <t>GPI</t>
+  </si>
+  <si>
+    <t>ATEC</t>
+  </si>
+  <si>
+    <t>MYRG</t>
+  </si>
+  <si>
+    <t>NUVL</t>
+  </si>
+  <si>
+    <t>GTLB</t>
+  </si>
+  <si>
+    <t>ARHS</t>
+  </si>
+  <si>
+    <t>TEX</t>
+  </si>
+  <si>
+    <t>CVRX</t>
+  </si>
+  <si>
+    <t>NVT</t>
+  </si>
+  <si>
+    <t>ROKU</t>
+  </si>
+  <si>
+    <t>USLM</t>
+  </si>
+  <si>
+    <t>PATK</t>
+  </si>
+  <si>
+    <t>CLH</t>
+  </si>
+  <si>
+    <t>TGTX</t>
+  </si>
+  <si>
+    <t>ERII</t>
+  </si>
+  <si>
+    <t>ENVA</t>
+  </si>
+  <si>
+    <t>HSKA</t>
+  </si>
+  <si>
+    <t>IESC</t>
+  </si>
+  <si>
+    <t>ARCB</t>
+  </si>
+  <si>
+    <t>MOMO</t>
+  </si>
+  <si>
+    <t>ACCD</t>
+  </si>
+  <si>
+    <t>MLNK</t>
+  </si>
+  <si>
+    <t>LEGN</t>
+  </si>
+  <si>
+    <t>CRS</t>
+  </si>
+  <si>
+    <t>GT</t>
+  </si>
+  <si>
+    <t>EVO</t>
+  </si>
+  <si>
+    <t>HUBB</t>
+  </si>
+  <si>
+    <t>AFRM</t>
+  </si>
+  <si>
+    <t>VCEL</t>
+  </si>
+  <si>
+    <t>ATI</t>
+  </si>
+  <si>
+    <t>AGRO</t>
+  </si>
+  <si>
+    <t>IGT</t>
+  </si>
+  <si>
+    <t>AUPH</t>
+  </si>
+  <si>
+    <t>CNM</t>
+  </si>
+  <si>
+    <t>PEGA</t>
+  </si>
+  <si>
+    <t>CSWI</t>
+  </si>
+  <si>
+    <t>THO</t>
+  </si>
+  <si>
+    <t>NE</t>
+  </si>
+  <si>
+    <t>CVGI</t>
+  </si>
+  <si>
+    <t>ASUR</t>
+  </si>
+  <si>
+    <t>NFLX</t>
+  </si>
+  <si>
+    <t>AZEK</t>
+  </si>
+  <si>
+    <t>AVDX</t>
+  </si>
+  <si>
+    <t>AAN</t>
+  </si>
+  <si>
+    <t>PFSI</t>
+  </si>
+  <si>
+    <t>HELE</t>
+  </si>
+  <si>
+    <t>SHAK</t>
+  </si>
+  <si>
+    <t>OC</t>
+  </si>
+  <si>
+    <t>ATKR</t>
+  </si>
+  <si>
+    <t>RYI</t>
+  </si>
+  <si>
+    <t>PCYO</t>
+  </si>
+  <si>
+    <t>CIX</t>
+  </si>
+  <si>
+    <t>NPO</t>
   </si>
   <si>
     <t>ABR</t>
   </si>
   <si>
-    <t>NYCB</t>
-  </si>
-  <si>
-    <t>SPSC</t>
-  </si>
-  <si>
-    <t>FND</t>
-  </si>
-  <si>
-    <t>GXO</t>
-  </si>
-  <si>
-    <t>AGRO</t>
-  </si>
-  <si>
-    <t>ALSN</t>
-  </si>
-  <si>
-    <t>MYRG</t>
-  </si>
-  <si>
-    <t>CARS</t>
-  </si>
-  <si>
-    <t>AAN</t>
-  </si>
-  <si>
-    <t>CPA</t>
-  </si>
-  <si>
-    <t>FTNT</t>
-  </si>
-  <si>
-    <t>LECO</t>
-  </si>
-  <si>
-    <t>HELE</t>
-  </si>
-  <si>
-    <t>MTH</t>
-  </si>
-  <si>
-    <t>CNMD</t>
-  </si>
-  <si>
-    <t>CLH</t>
-  </si>
-  <si>
-    <t>PATK</t>
-  </si>
-  <si>
-    <t>PHG</t>
-  </si>
-  <si>
-    <t>GPI</t>
-  </si>
-  <si>
-    <t>GT</t>
-  </si>
-  <si>
-    <t>PRI</t>
-  </si>
-  <si>
-    <t>MLNK</t>
-  </si>
-  <si>
-    <t>NNOX</t>
-  </si>
-  <si>
-    <t>EXP</t>
-  </si>
-  <si>
-    <t>CRS</t>
-  </si>
-  <si>
-    <t>AUPH</t>
-  </si>
-  <si>
-    <t>ERII</t>
-  </si>
-  <si>
-    <t>EDU</t>
-  </si>
-  <si>
-    <t>CSWI</t>
-  </si>
-  <si>
-    <t>ENVA</t>
-  </si>
-  <si>
-    <t>MOMO</t>
-  </si>
-  <si>
-    <t>ARHS</t>
-  </si>
-  <si>
-    <t>IGT</t>
-  </si>
-  <si>
-    <t>ATI</t>
-  </si>
-  <si>
-    <t>HSKA</t>
-  </si>
-  <si>
-    <t>HUBB</t>
-  </si>
-  <si>
-    <t>LZRFY</t>
-  </si>
-  <si>
-    <t>ROKU</t>
-  </si>
-  <si>
-    <t>ATEC</t>
-  </si>
-  <si>
-    <t>ARCB</t>
+    <t>WMS</t>
+  </si>
+  <si>
+    <t>ABNB</t>
+  </si>
+  <si>
+    <t>VMW</t>
+  </si>
+  <si>
+    <t>FIVN</t>
+  </si>
+  <si>
+    <t>CELH</t>
+  </si>
+  <si>
+    <t>FROG</t>
+  </si>
+  <si>
+    <t>COHR</t>
   </si>
   <si>
     <t>NEWT</t>
   </si>
   <si>
-    <t>IESC</t>
-  </si>
-  <si>
-    <t>ASUR</t>
-  </si>
-  <si>
-    <t>NFLX</t>
-  </si>
-  <si>
-    <t>NEOG</t>
+    <t>APG</t>
+  </si>
+  <si>
+    <t>SRAD</t>
+  </si>
+  <si>
+    <t>CARG</t>
+  </si>
+  <si>
+    <t>PETQ</t>
+  </si>
+  <si>
+    <t>TPH</t>
+  </si>
+  <si>
+    <t>FTI</t>
+  </si>
+  <si>
+    <t>BILL</t>
+  </si>
+  <si>
+    <t>CLS</t>
+  </si>
+  <si>
+    <t>PAG</t>
+  </si>
+  <si>
+    <t>IMVT</t>
+  </si>
+  <si>
+    <t>DXPE</t>
+  </si>
+  <si>
+    <t>ENS</t>
+  </si>
+  <si>
+    <t>TOL</t>
+  </si>
+  <si>
+    <t>TYRA</t>
+  </si>
+  <si>
+    <t>BWMN</t>
+  </si>
+  <si>
+    <t>SMID</t>
+  </si>
+  <si>
+    <t>ERO</t>
+  </si>
+  <si>
+    <t>TMDX</t>
+  </si>
+  <si>
+    <t>RCMT</t>
+  </si>
+  <si>
+    <t>INMD</t>
+  </si>
+  <si>
+    <t>LAD</t>
+  </si>
+  <si>
+    <t>DASH</t>
+  </si>
+  <si>
+    <t>ARGX</t>
+  </si>
+  <si>
+    <t>RCM</t>
+  </si>
+  <si>
+    <t>ZEUS</t>
+  </si>
+  <si>
+    <t>PROF</t>
+  </si>
+  <si>
+    <t>EB</t>
+  </si>
+  <si>
+    <t>TGLS</t>
+  </si>
+  <si>
+    <t>YELP</t>
+  </si>
+  <si>
+    <t>ALGM</t>
+  </si>
+  <si>
+    <t>DAL</t>
+  </si>
+  <si>
+    <t>TMHC</t>
+  </si>
+  <si>
+    <t>AZUL</t>
+  </si>
+  <si>
+    <t>BWMX</t>
+  </si>
+  <si>
+    <t>DDOG</t>
+  </si>
+  <si>
+    <t>PKOH</t>
+  </si>
+  <si>
+    <t>ETNB</t>
+  </si>
+  <si>
+    <t>KBH</t>
+  </si>
+  <si>
+    <t>FRD</t>
+  </si>
+  <si>
+    <t>MATW</t>
+  </si>
+  <si>
+    <t>WPRT</t>
+  </si>
+  <si>
+    <t>PHM</t>
+  </si>
+  <si>
+    <t>MNDY</t>
+  </si>
+  <si>
+    <t>CLBR</t>
+  </si>
+  <si>
+    <t>CXM</t>
+  </si>
+  <si>
+    <t>PAM</t>
+  </si>
+  <si>
+    <t>RH</t>
+  </si>
+  <si>
+    <t>THC</t>
+  </si>
+  <si>
+    <t>DUOL</t>
+  </si>
+  <si>
+    <t>JELD</t>
+  </si>
+  <si>
+    <t>LPRO</t>
+  </si>
+  <si>
+    <t>MLP</t>
+  </si>
+  <si>
+    <t>MGNI</t>
+  </si>
+  <si>
+    <t>MRUS</t>
+  </si>
+  <si>
+    <t>ROIV</t>
+  </si>
+  <si>
+    <t>EVI</t>
   </si>
   <si>
     <t>FCAP</t>
   </si>
   <si>
-    <t>THO</t>
-  </si>
-  <si>
-    <t>PEGA</t>
-  </si>
-  <si>
-    <t>ACCD</t>
-  </si>
-  <si>
-    <t>NVT</t>
-  </si>
-  <si>
-    <t>EVO</t>
-  </si>
-  <si>
-    <t>AVDX</t>
-  </si>
-  <si>
-    <t>NUVL</t>
-  </si>
-  <si>
-    <t>AFRM</t>
-  </si>
-  <si>
-    <t>CVGI</t>
-  </si>
-  <si>
-    <t>PCYO</t>
-  </si>
-  <si>
-    <t>HROW</t>
-  </si>
-  <si>
-    <t>CNM</t>
-  </si>
-  <si>
-    <t>CIX</t>
-  </si>
-  <si>
-    <t>ATKR</t>
-  </si>
-  <si>
-    <t>WMS</t>
-  </si>
-  <si>
-    <t>VCEL</t>
-  </si>
-  <si>
-    <t>GTLB</t>
-  </si>
-  <si>
-    <t>NE</t>
-  </si>
-  <si>
-    <t>BILL</t>
-  </si>
-  <si>
-    <t>FROG</t>
-  </si>
-  <si>
-    <t>PETQ</t>
-  </si>
-  <si>
-    <t>AZEK</t>
-  </si>
-  <si>
-    <t>OC</t>
-  </si>
-  <si>
-    <t>APG</t>
-  </si>
-  <si>
-    <t>CELH</t>
-  </si>
-  <si>
-    <t>ABNB</t>
-  </si>
-  <si>
-    <t>NPO</t>
-  </si>
-  <si>
-    <t>IMVT</t>
-  </si>
-  <si>
-    <t>DXPE</t>
-  </si>
-  <si>
-    <t>PKOH</t>
-  </si>
-  <si>
-    <t>ZEUS</t>
-  </si>
-  <si>
-    <t>FTI</t>
-  </si>
-  <si>
-    <t>BWMN</t>
-  </si>
-  <si>
-    <t>FIVN</t>
-  </si>
-  <si>
-    <t>COHR</t>
-  </si>
-  <si>
-    <t>CLS</t>
-  </si>
-  <si>
-    <t>CARG</t>
-  </si>
-  <si>
-    <t>INMD</t>
-  </si>
-  <si>
-    <t>PROF</t>
-  </si>
-  <si>
-    <t>VMW</t>
-  </si>
-  <si>
-    <t>ARGX</t>
-  </si>
-  <si>
-    <t>PAG</t>
-  </si>
-  <si>
-    <t>MLP</t>
-  </si>
-  <si>
-    <t>TGLS</t>
-  </si>
-  <si>
-    <t>EB</t>
-  </si>
-  <si>
-    <t>YELP</t>
-  </si>
-  <si>
-    <t>LAD</t>
-  </si>
-  <si>
-    <t>MATW</t>
-  </si>
-  <si>
-    <t>TMHC</t>
-  </si>
-  <si>
-    <t>ERO</t>
-  </si>
-  <si>
-    <t>DAL</t>
-  </si>
-  <si>
-    <t>JELD</t>
-  </si>
-  <si>
-    <t>ENS</t>
+    <t>NOVA</t>
+  </si>
+  <si>
+    <t>GTLS</t>
+  </si>
+  <si>
+    <t>SHOP</t>
+  </si>
+  <si>
+    <t>SSD</t>
+  </si>
+  <si>
+    <t>DBRG</t>
+  </si>
+  <si>
+    <t>BCC</t>
+  </si>
+  <si>
+    <t>IDCC</t>
+  </si>
+  <si>
+    <t>BOOT</t>
+  </si>
+  <si>
+    <t>WFRD</t>
+  </si>
+  <si>
+    <t>AEL</t>
+  </si>
+  <si>
+    <t>SWDAF</t>
+  </si>
+  <si>
+    <t>FTAI</t>
+  </si>
+  <si>
+    <t>HOOD</t>
+  </si>
+  <si>
+    <t>BRZE</t>
+  </si>
+  <si>
+    <t>UBER</t>
+  </si>
+  <si>
+    <t>HCCI</t>
+  </si>
+  <si>
+    <t>IMRX</t>
+  </si>
+  <si>
+    <t>CYD</t>
+  </si>
+  <si>
+    <t>LSANF</t>
+  </si>
+  <si>
+    <t>NATR</t>
+  </si>
+  <si>
+    <t>NETI</t>
+  </si>
+  <si>
+    <t>BLD</t>
+  </si>
+  <si>
+    <t>IIVI</t>
+  </si>
+  <si>
+    <t>MANH</t>
+  </si>
+  <si>
+    <t>NCLH</t>
+  </si>
+  <si>
+    <t>PANW</t>
+  </si>
+  <si>
+    <t>OII</t>
+  </si>
+  <si>
+    <t>SSYS</t>
   </si>
   <si>
     <t>MORF</t>
   </si>
   <si>
-    <t>NOVA</t>
-  </si>
-  <si>
-    <t>DASH</t>
-  </si>
-  <si>
-    <t>WFRD</t>
-  </si>
-  <si>
-    <t>CXM</t>
-  </si>
-  <si>
-    <t>AZUL</t>
-  </si>
-  <si>
-    <t>ETNB</t>
-  </si>
-  <si>
-    <t>KBH</t>
-  </si>
-  <si>
-    <t>PAM</t>
-  </si>
-  <si>
-    <t>RCMT</t>
-  </si>
-  <si>
-    <t>GTLS</t>
-  </si>
-  <si>
-    <t>CLBR</t>
-  </si>
-  <si>
-    <t>ALGM</t>
-  </si>
-  <si>
-    <t>PHM</t>
-  </si>
-  <si>
-    <t>DDOG</t>
-  </si>
-  <si>
-    <t>HCCI</t>
-  </si>
-  <si>
-    <t>SMID</t>
-  </si>
-  <si>
-    <t>RH</t>
+    <t>BECN</t>
+  </si>
+  <si>
+    <t>MTW</t>
+  </si>
+  <si>
+    <t>MNSO</t>
+  </si>
+  <si>
+    <t>LMND</t>
+  </si>
+  <si>
+    <t>HUBS</t>
   </si>
   <si>
     <t>BVH</t>
   </si>
   <si>
-    <t>BWMX</t>
-  </si>
-  <si>
-    <t>MNDY</t>
-  </si>
-  <si>
-    <t>OII</t>
-  </si>
-  <si>
-    <t>CYD</t>
-  </si>
-  <si>
-    <t>IMRX</t>
-  </si>
-  <si>
-    <t>SHOP</t>
-  </si>
-  <si>
-    <t>IDCC</t>
-  </si>
-  <si>
-    <t>DUOL</t>
-  </si>
-  <si>
-    <t>AEL</t>
-  </si>
-  <si>
-    <t>LPRO</t>
-  </si>
-  <si>
-    <t>NETI</t>
-  </si>
-  <si>
-    <t>BOOT</t>
-  </si>
-  <si>
-    <t>DBRG</t>
-  </si>
-  <si>
-    <t>MRUS</t>
-  </si>
-  <si>
-    <t>MGNI</t>
-  </si>
-  <si>
-    <t>BCC</t>
-  </si>
-  <si>
-    <t>LSANF</t>
+    <t>FMS</t>
+  </si>
+  <si>
+    <t>AN</t>
+  </si>
+  <si>
+    <t>IBP</t>
   </si>
   <si>
     <t>CAAP</t>
   </si>
   <si>
+    <t>TDC</t>
+  </si>
+  <si>
+    <t>PLAB</t>
+  </si>
+  <si>
+    <t>SRDX</t>
+  </si>
+  <si>
+    <t>TSQ</t>
+  </si>
+  <si>
+    <t>GKOS</t>
+  </si>
+  <si>
     <t>GSHD</t>
   </si>
   <si>
-    <t>FRD</t>
-  </si>
-  <si>
-    <t>NATR</t>
-  </si>
-  <si>
-    <t>EVI</t>
-  </si>
-  <si>
-    <t>FTAI</t>
-  </si>
-  <si>
-    <t>BLD</t>
-  </si>
-  <si>
-    <t>IIVI</t>
-  </si>
-  <si>
-    <t>LMND</t>
-  </si>
-  <si>
-    <t>PANW</t>
-  </si>
-  <si>
-    <t>HOOD</t>
-  </si>
-  <si>
-    <t>BECN</t>
-  </si>
-  <si>
-    <t>MNSO</t>
-  </si>
-  <si>
-    <t>MTW</t>
-  </si>
-  <si>
-    <t>HUBS</t>
-  </si>
-  <si>
-    <t>TSQ</t>
-  </si>
-  <si>
-    <t>NCLH</t>
-  </si>
-  <si>
-    <t>BRZE</t>
-  </si>
-  <si>
-    <t>FMS</t>
-  </si>
-  <si>
-    <t>SSYS</t>
-  </si>
-  <si>
-    <t>MANH</t>
-  </si>
-  <si>
-    <t>IBP</t>
-  </si>
-  <si>
-    <t>AN</t>
+    <t>EXAS</t>
+  </si>
+  <si>
+    <t>LZ</t>
+  </si>
+  <si>
+    <t>GRVY</t>
+  </si>
+  <si>
+    <t>MDWT</t>
   </si>
   <si>
     <t>AMWD</t>
   </si>
   <si>
-    <t>SRDX</t>
-  </si>
-  <si>
-    <t>TDC</t>
-  </si>
-  <si>
-    <t>EXAS</t>
+    <t>SGH</t>
+  </si>
+  <si>
+    <t>SHC</t>
+  </si>
+  <si>
+    <t>INTT</t>
+  </si>
+  <si>
+    <t>ADBE</t>
+  </si>
+  <si>
+    <t>CRCT</t>
+  </si>
+  <si>
+    <t>RRGB</t>
+  </si>
+  <si>
+    <t>ALPN</t>
+  </si>
+  <si>
+    <t>QS</t>
+  </si>
+  <si>
+    <t>PHAT</t>
+  </si>
+  <si>
+    <t>ETHE</t>
+  </si>
+  <si>
+    <t>AVDL</t>
+  </si>
+  <si>
+    <t>JBL</t>
+  </si>
+  <si>
+    <t>PSTG</t>
+  </si>
+  <si>
+    <t>KRYS</t>
   </si>
   <si>
     <t>ACVA</t>
   </si>
   <si>
-    <t>PLAB</t>
-  </si>
-  <si>
-    <t>INTT</t>
-  </si>
-  <si>
-    <t>SGH</t>
-  </si>
-  <si>
-    <t>ETHE</t>
-  </si>
-  <si>
-    <t>AVDL</t>
-  </si>
-  <si>
-    <t>GRVY</t>
-  </si>
-  <si>
-    <t>LZ</t>
-  </si>
-  <si>
-    <t>MDWT</t>
-  </si>
-  <si>
-    <t>RRGB</t>
-  </si>
-  <si>
-    <t>GKOS</t>
-  </si>
-  <si>
-    <t>CRCT</t>
-  </si>
-  <si>
-    <t>PHAT</t>
-  </si>
-  <si>
-    <t>ADBE</t>
-  </si>
-  <si>
-    <t>QS</t>
-  </si>
-  <si>
     <t>GLBE</t>
   </si>
   <si>
-    <t>KRYS</t>
-  </si>
-  <si>
-    <t>ALPN</t>
-  </si>
-  <si>
-    <t>JBL</t>
+    <t>ATLC</t>
+  </si>
+  <si>
+    <t>APPF</t>
+  </si>
+  <si>
+    <t>AVGO</t>
+  </si>
+  <si>
+    <t>TDW</t>
+  </si>
+  <si>
+    <t>ALGT</t>
+  </si>
+  <si>
+    <t>ABCM</t>
+  </si>
+  <si>
+    <t>KRUS</t>
+  </si>
+  <si>
+    <t>MRVL</t>
+  </si>
+  <si>
+    <t>U</t>
+  </si>
+  <si>
+    <t>SMHI</t>
+  </si>
+  <si>
+    <t>BLU</t>
+  </si>
+  <si>
+    <t>PRG</t>
+  </si>
+  <si>
+    <t>CMT</t>
+  </si>
+  <si>
+    <t>DICE</t>
+  </si>
+  <si>
+    <t>CRMT</t>
+  </si>
+  <si>
+    <t>EXTR</t>
   </si>
   <si>
     <t>CPS</t>
   </si>
   <si>
-    <t>APPF</t>
-  </si>
-  <si>
-    <t>ATLC</t>
-  </si>
-  <si>
-    <t>PSTG</t>
-  </si>
-  <si>
-    <t>ABCM</t>
-  </si>
-  <si>
-    <t>AVGO</t>
+    <t>FSLY</t>
+  </si>
+  <si>
+    <t>TTD</t>
+  </si>
+  <si>
+    <t>RCL</t>
+  </si>
+  <si>
+    <t>STVN</t>
+  </si>
+  <si>
+    <t>DOCN</t>
+  </si>
+  <si>
+    <t>EBIX</t>
+  </si>
+  <si>
+    <t>RDNT</t>
   </si>
   <si>
     <t>FOR</t>
   </si>
   <si>
-    <t>ALGT</t>
+    <t>WRLD</t>
+  </si>
+  <si>
+    <t>NWLI</t>
+  </si>
+  <si>
+    <t>ONON</t>
+  </si>
+  <si>
+    <t>DV</t>
+  </si>
+  <si>
+    <t>TARS</t>
+  </si>
+  <si>
+    <t>AXR</t>
+  </si>
+  <si>
+    <t>SPOT</t>
+  </si>
+  <si>
+    <t>GBX</t>
+  </si>
+  <si>
+    <t>TAYD</t>
+  </si>
+  <si>
+    <t>VIST</t>
+  </si>
+  <si>
+    <t>RILY</t>
+  </si>
+  <si>
+    <t>UFPT</t>
+  </si>
+  <si>
+    <t>SNBR</t>
+  </si>
+  <si>
+    <t>NGMS</t>
+  </si>
+  <si>
+    <t>BELFB</t>
+  </si>
+  <si>
+    <t>GOCO</t>
+  </si>
+  <si>
+    <t>POWL</t>
+  </si>
+  <si>
+    <t>MHO</t>
+  </si>
+  <si>
+    <t>ACAD</t>
+  </si>
+  <si>
+    <t>CLXT</t>
+  </si>
+  <si>
+    <t>EBON</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>STRL</t>
+  </si>
+  <si>
+    <t>ANF</t>
+  </si>
+  <si>
+    <t>CAMT</t>
+  </si>
+  <si>
+    <t>CFLT</t>
   </si>
   <si>
     <t>BMA</t>
   </si>
   <si>
-    <t>CRMT</t>
-  </si>
-  <si>
-    <t>CMT</t>
-  </si>
-  <si>
-    <t>EBIX</t>
-  </si>
-  <si>
-    <t>BLU</t>
-  </si>
-  <si>
-    <t>MRVL</t>
-  </si>
-  <si>
-    <t>KRUS</t>
-  </si>
-  <si>
-    <t>PRG</t>
-  </si>
-  <si>
-    <t>DICE</t>
-  </si>
-  <si>
-    <t>FSLY</t>
-  </si>
-  <si>
-    <t>RCL</t>
-  </si>
-  <si>
-    <t>DOCN</t>
-  </si>
-  <si>
-    <t>NGMS</t>
-  </si>
-  <si>
-    <t>RDNT</t>
-  </si>
-  <si>
-    <t>NWLI</t>
-  </si>
-  <si>
-    <t>DV</t>
-  </si>
-  <si>
-    <t>RILY</t>
-  </si>
-  <si>
-    <t>EXTR</t>
-  </si>
-  <si>
-    <t>AXR</t>
-  </si>
-  <si>
-    <t>WRLD</t>
-  </si>
-  <si>
-    <t>GOCO</t>
-  </si>
-  <si>
-    <t>POWL</t>
-  </si>
-  <si>
-    <t>GBX</t>
-  </si>
-  <si>
-    <t>BELFB</t>
+    <t>SAIA</t>
   </si>
   <si>
     <t>XP</t>
   </si>
   <si>
-    <t>ONON</t>
+    <t>TSLA</t>
+  </si>
+  <si>
+    <t>YPF</t>
+  </si>
+  <si>
+    <t>LI</t>
+  </si>
+  <si>
+    <t>ACLS</t>
+  </si>
+  <si>
+    <t>GBTC</t>
+  </si>
+  <si>
+    <t>PCTTU</t>
+  </si>
+  <si>
+    <t>OSTK</t>
+  </si>
+  <si>
+    <t>VKTX</t>
+  </si>
+  <si>
+    <t>SG</t>
+  </si>
+  <si>
+    <t>COCO</t>
+  </si>
+  <si>
+    <t>PCT</t>
+  </si>
+  <si>
+    <t>AEHR</t>
+  </si>
+  <si>
+    <t>TCMD</t>
+  </si>
+  <si>
+    <t>FLNC</t>
+  </si>
+  <si>
+    <t>HOV</t>
+  </si>
+  <si>
+    <t>ISEE</t>
+  </si>
+  <si>
+    <t>PLPC</t>
+  </si>
+  <si>
+    <t>BLDR</t>
+  </si>
+  <si>
+    <t>FCNCA</t>
+  </si>
+  <si>
+    <t>RIVN</t>
+  </si>
+  <si>
+    <t>BHVN</t>
+  </si>
+  <si>
+    <t>GRBK</t>
+  </si>
+  <si>
+    <t>CUBI</t>
+  </si>
+  <si>
+    <t>QTRX</t>
   </si>
   <si>
     <t>LTRPB</t>
   </si>
   <si>
-    <t>STVN</t>
-  </si>
-  <si>
-    <t>MHO</t>
-  </si>
-  <si>
-    <t>SAIA</t>
-  </si>
-  <si>
-    <t>STRL</t>
-  </si>
-  <si>
-    <t>ACAD</t>
-  </si>
-  <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>FLNC</t>
-  </si>
-  <si>
-    <t>CFLT</t>
-  </si>
-  <si>
-    <t>EBON</t>
-  </si>
-  <si>
-    <t>ACLS</t>
-  </si>
-  <si>
-    <t>LI</t>
-  </si>
-  <si>
-    <t>YPF</t>
-  </si>
-  <si>
-    <t>CAMT</t>
-  </si>
-  <si>
-    <t>PCT</t>
-  </si>
-  <si>
-    <t>ANF</t>
-  </si>
-  <si>
-    <t>SNBR</t>
-  </si>
-  <si>
-    <t>PCTTU</t>
-  </si>
-  <si>
-    <t>AEHR</t>
-  </si>
-  <si>
-    <t>RIVN</t>
-  </si>
-  <si>
-    <t>COCO</t>
-  </si>
-  <si>
-    <t>FCNCA</t>
-  </si>
-  <si>
-    <t>PLPC</t>
-  </si>
-  <si>
-    <t>GBTC</t>
-  </si>
-  <si>
-    <t>VKTX</t>
-  </si>
-  <si>
-    <t>HOV</t>
-  </si>
-  <si>
-    <t>ISEE</t>
-  </si>
-  <si>
-    <t>OSTK</t>
-  </si>
-  <si>
-    <t>BLDR</t>
+    <t>BMEA</t>
   </si>
   <si>
     <t>GGAL</t>
   </si>
   <si>
-    <t>BMEA</t>
-  </si>
-  <si>
-    <t>QTRX</t>
-  </si>
-  <si>
-    <t>CUBI</t>
+    <t>USAP</t>
   </si>
   <si>
     <t>IAS</t>
   </si>
   <si>
-    <t>GRBK</t>
+    <t>XPEV</t>
   </si>
   <si>
     <t>EXPI</t>
   </si>
   <si>
-    <t>BHVN</t>
-  </si>
-  <si>
-    <t>CLXT</t>
-  </si>
-  <si>
     <t>ARCT</t>
   </si>
   <si>
+    <t>MOD</t>
+  </si>
+  <si>
+    <t>DKNG</t>
+  </si>
+  <si>
+    <t>GHL</t>
+  </si>
+  <si>
+    <t>ELF</t>
+  </si>
+  <si>
     <t>APP</t>
   </si>
   <si>
-    <t>ELF</t>
-  </si>
-  <si>
-    <t>GHL</t>
-  </si>
-  <si>
-    <t>DKNG</t>
-  </si>
-  <si>
-    <t>MOD</t>
+    <t>CBAY</t>
   </si>
   <si>
     <t>BZH</t>
@@ -856,55 +967,64 @@
     <t>BELFA</t>
   </si>
   <si>
+    <t>CCL</t>
+  </si>
+  <si>
+    <t>COIN</t>
+  </si>
+  <si>
+    <t>ATRO</t>
+  </si>
+  <si>
     <t>KDNY</t>
   </si>
   <si>
-    <t>CCL</t>
-  </si>
-  <si>
-    <t>ATRO</t>
+    <t>CUK</t>
+  </si>
+  <si>
+    <t>VRT</t>
   </si>
   <si>
     <t>CMPR</t>
   </si>
   <si>
-    <t>VRT</t>
-  </si>
-  <si>
-    <t>CUK</t>
-  </si>
-  <si>
-    <t>CBAY</t>
+    <t>RXST</t>
   </si>
   <si>
     <t>AMPH</t>
   </si>
   <si>
-    <t>COIN</t>
-  </si>
-  <si>
-    <t>RXST</t>
+    <t>IOT</t>
+  </si>
+  <si>
+    <t>VECT</t>
   </si>
   <si>
     <t>LMB</t>
   </si>
   <si>
-    <t>IOT</t>
-  </si>
-  <si>
     <t>MSTR</t>
   </si>
   <si>
     <t>MDB</t>
   </si>
   <si>
+    <t>RXRX</t>
+  </si>
+  <si>
+    <t>RXDX</t>
+  </si>
+  <si>
+    <t>RETA</t>
+  </si>
+  <si>
+    <t>SKYW</t>
+  </si>
+  <si>
     <t>W</t>
   </si>
   <si>
-    <t>RXRX</t>
-  </si>
-  <si>
-    <t>SKYW</t>
+    <t>ENVX</t>
   </si>
   <si>
     <t>PLTR</t>
@@ -913,30 +1033,33 @@
     <t>RCEL</t>
   </si>
   <si>
-    <t>ENVX</t>
+    <t>WEAV</t>
+  </si>
+  <si>
+    <t>ARLO</t>
+  </si>
+  <si>
+    <t>SDGR</t>
   </si>
   <si>
     <t>DFH</t>
   </si>
   <si>
-    <t>ARLO</t>
-  </si>
-  <si>
-    <t>SDGR</t>
+    <t>MARA</t>
   </si>
   <si>
     <t>RDFN</t>
   </si>
   <si>
-    <t>MARA</t>
-  </si>
-  <si>
     <t>EDN</t>
   </si>
   <si>
     <t>NVDA</t>
   </si>
   <si>
+    <t>VERA</t>
+  </si>
+  <si>
     <t>CIR</t>
   </si>
   <si>
@@ -949,34 +1072,37 @@
     <t>CABA</t>
   </si>
   <si>
+    <t>GGAAU</t>
+  </si>
+  <si>
     <t>INOD</t>
   </si>
   <si>
-    <t>GGAAU</t>
+    <t>ROOT</t>
   </si>
   <si>
     <t>RIOT</t>
   </si>
   <si>
+    <t>MEOA</t>
+  </si>
+  <si>
+    <t>IONQ</t>
+  </si>
+  <si>
     <t>OPRA</t>
   </si>
   <si>
-    <t>MEOA</t>
-  </si>
-  <si>
-    <t>IONQ</t>
-  </si>
-  <si>
-    <t>ROOT</t>
-  </si>
-  <si>
     <t>PHVS</t>
   </si>
   <si>
+    <t>SGTX</t>
+  </si>
+  <si>
     <t>EYPT</t>
   </si>
   <si>
-    <t>SGTX</t>
+    <t>UPST</t>
   </si>
   <si>
     <t>SMCI</t>
@@ -1351,7 +1477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B328"/>
+  <dimension ref="A1:B370"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1367,7 +1493,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1">
-        <v>129.3043216204136</v>
+        <v>129.5041696416307</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1375,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1">
-        <v>129.3114315654894</v>
+        <v>129.5078439438456</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1383,7 +1509,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1">
-        <v>129.3287087482267</v>
+        <v>129.5151782409129</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1391,7 +1517,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="1">
-        <v>129.3506528893776</v>
+        <v>129.5422814584203</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1399,7 +1525,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="1">
-        <v>129.4125982492894</v>
+        <v>129.546229958598</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1407,7 +1533,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="1">
-        <v>129.4624789743012</v>
+        <v>129.6156884039016</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1415,7 +1541,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="1">
-        <v>129.4868683213205</v>
+        <v>129.6809833616088</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1423,7 +1549,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="1">
-        <v>129.5396776430732</v>
+        <v>129.7396789207368</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1431,7 +1557,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="1">
-        <v>129.575620789456</v>
+        <v>130.151241766338</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1439,7 +1565,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="1">
-        <v>129.5900908197025</v>
+        <v>130.1726682983</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1447,7 +1573,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="1">
-        <v>129.6078078035002</v>
+        <v>130.1762670920081</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1455,7 +1581,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="1">
-        <v>129.6715054552926</v>
+        <v>130.2639627350479</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1463,7 +1589,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="1">
-        <v>129.8066822040929</v>
+        <v>130.3096314529034</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1471,7 +1597,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="1">
-        <v>129.8882548185674</v>
+        <v>130.3921341076695</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1479,7 +1605,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="1">
-        <v>129.9746166181891</v>
+        <v>130.4638773668084</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1487,7 +1613,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="1">
-        <v>129.975827554942</v>
+        <v>130.5843744718494</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1495,7 +1621,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="1">
-        <v>130.0090426890373</v>
+        <v>130.745163982922</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1503,7 +1629,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="1">
-        <v>130.1841690912718</v>
+        <v>130.7567255714332</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1511,7 +1637,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="1">
-        <v>130.2149878261212</v>
+        <v>130.8687253381991</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1519,7 +1645,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="1">
-        <v>130.4110664730868</v>
+        <v>130.9410934740915</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1527,7 +1653,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="1">
-        <v>130.4462988901802</v>
+        <v>130.9779864593487</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1535,7 +1661,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="1">
-        <v>130.4615372731179</v>
+        <v>130.9805943188987</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1543,7 +1669,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="1">
-        <v>130.5342828725076</v>
+        <v>131.0149450411747</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1551,7 +1677,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="1">
-        <v>130.5861050978399</v>
+        <v>131.0511188431077</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1559,7 +1685,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="1">
-        <v>130.5898247616127</v>
+        <v>131.0535645309364</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1567,7 +1693,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="1">
-        <v>130.6708815481005</v>
+        <v>131.0620902907002</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1575,7 +1701,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="1">
-        <v>130.8122296140773</v>
+        <v>131.0667126937048</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1583,7 +1709,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="1">
-        <v>130.8290588905969</v>
+        <v>131.0815020142404</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1591,7 +1717,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="1">
-        <v>130.8533008730499</v>
+        <v>131.1298412912091</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1599,7 +1725,7 @@
         <v>31</v>
       </c>
       <c r="B31" s="1">
-        <v>130.8667562300924</v>
+        <v>131.1400515440482</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1607,7 +1733,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="1">
-        <v>130.8676609889043</v>
+        <v>131.1657972763583</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1615,7 +1741,7 @@
         <v>33</v>
       </c>
       <c r="B33" s="1">
-        <v>131.0102265267315</v>
+        <v>131.189530632868</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1623,7 +1749,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="1">
-        <v>131.0149450411747</v>
+        <v>131.2032748108403</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1631,7 +1757,7 @@
         <v>35</v>
       </c>
       <c r="B35" s="1">
-        <v>131.0656181703646</v>
+        <v>131.2578036008879</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1639,7 +1765,7 @@
         <v>36</v>
       </c>
       <c r="B36" s="1">
-        <v>131.0947552017941</v>
+        <v>131.2616524550107</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1647,7 +1773,7 @@
         <v>37</v>
       </c>
       <c r="B37" s="1">
-        <v>131.1027162330343</v>
+        <v>131.3581467639494</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1655,7 +1781,7 @@
         <v>38</v>
       </c>
       <c r="B38" s="1">
-        <v>131.1505026907606</v>
+        <v>131.3692720811365</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1663,7 +1789,7 @@
         <v>39</v>
       </c>
       <c r="B39" s="1">
-        <v>131.2029885890086</v>
+        <v>131.4447710369079</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1671,7 +1797,7 @@
         <v>40</v>
       </c>
       <c r="B40" s="1">
-        <v>131.285423583404</v>
+        <v>131.5315992569605</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1679,7 +1805,7 @@
         <v>41</v>
       </c>
       <c r="B41" s="1">
-        <v>131.2882493284291</v>
+        <v>131.592916475673</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -1687,7 +1813,7 @@
         <v>42</v>
       </c>
       <c r="B42" s="1">
-        <v>131.2895864505632</v>
+        <v>131.6018868009316</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -1695,7 +1821,7 @@
         <v>43</v>
       </c>
       <c r="B43" s="1">
-        <v>131.3394859647028</v>
+        <v>131.7052664509743</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1703,7 +1829,7 @@
         <v>44</v>
       </c>
       <c r="B44" s="1">
-        <v>131.3422661324374</v>
+        <v>131.7160208021559</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1711,7 +1837,7 @@
         <v>45</v>
       </c>
       <c r="B45" s="1">
-        <v>131.5884913372849</v>
+        <v>131.8331198677894</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1719,7 +1845,7 @@
         <v>46</v>
       </c>
       <c r="B46" s="1">
-        <v>131.6714472756249</v>
+        <v>131.8353805036161</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -1727,7 +1853,7 @@
         <v>47</v>
       </c>
       <c r="B47" s="1">
-        <v>131.6945200779809</v>
+        <v>131.8413548160303</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -1735,7 +1861,7 @@
         <v>48</v>
       </c>
       <c r="B48" s="1">
-        <v>131.709476200069</v>
+        <v>131.8522145756976</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1743,7 +1869,7 @@
         <v>49</v>
       </c>
       <c r="B49" s="1">
-        <v>131.8958813002955</v>
+        <v>131.9117486318892</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1751,7 +1877,7 @@
         <v>50</v>
       </c>
       <c r="B50" s="1">
-        <v>131.9265019844602</v>
+        <v>131.9561005877736</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1759,7 +1885,7 @@
         <v>51</v>
       </c>
       <c r="B51" s="1">
-        <v>132.0107733209298</v>
+        <v>131.9738219197082</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1767,7 +1893,7 @@
         <v>52</v>
       </c>
       <c r="B52" s="1">
-        <v>132.0441989208849</v>
+        <v>132.0107733209298</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1775,7 +1901,7 @@
         <v>53</v>
       </c>
       <c r="B53" s="1">
-        <v>132.0672152996668</v>
+        <v>132.1370583861681</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1783,7 +1909,7 @@
         <v>54</v>
       </c>
       <c r="B54" s="1">
-        <v>132.1555821994835</v>
+        <v>132.1592788019431</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1791,7 +1917,7 @@
         <v>55</v>
       </c>
       <c r="B55" s="1">
-        <v>132.1712714347813</v>
+        <v>132.2064516424999</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1799,7 +1925,7 @@
         <v>56</v>
       </c>
       <c r="B56" s="1">
-        <v>132.2656353334257</v>
+        <v>132.2273514596001</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1807,7 +1933,7 @@
         <v>57</v>
       </c>
       <c r="B57" s="1">
-        <v>132.2788736914969</v>
+        <v>132.2940737947747</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1815,7 +1941,7 @@
         <v>58</v>
       </c>
       <c r="B58" s="1">
-        <v>132.3970325788387</v>
+        <v>132.3070468560089</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1823,7 +1949,7 @@
         <v>59</v>
       </c>
       <c r="B59" s="1">
-        <v>132.4039222663605</v>
+        <v>132.4417219139188</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1831,7 +1957,7 @@
         <v>60</v>
       </c>
       <c r="B60" s="1">
-        <v>132.4276086023096</v>
+        <v>132.5061623227492</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1839,7 +1965,7 @@
         <v>61</v>
       </c>
       <c r="B61" s="1">
-        <v>132.4789364577125</v>
+        <v>132.5065702871506</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1847,7 +1973,7 @@
         <v>62</v>
       </c>
       <c r="B62" s="1">
-        <v>132.5014495467844</v>
+        <v>132.546431750187</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1855,7 +1981,7 @@
         <v>63</v>
       </c>
       <c r="B63" s="1">
-        <v>132.5753701458476</v>
+        <v>132.5607188098132</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1863,7 +1989,7 @@
         <v>64</v>
       </c>
       <c r="B64" s="1">
-        <v>132.7533229758515</v>
+        <v>132.5621400164259</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1871,7 +1997,7 @@
         <v>65</v>
       </c>
       <c r="B65" s="1">
-        <v>132.8497064269368</v>
+        <v>132.5635407760574</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -1879,7 +2005,7 @@
         <v>66</v>
       </c>
       <c r="B66" s="1">
-        <v>132.9399198677628</v>
+        <v>132.5669008861021</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -1887,7 +2013,7 @@
         <v>67</v>
       </c>
       <c r="B67" s="1">
-        <v>133.0024800145635</v>
+        <v>132.6971959526612</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -1895,7 +2021,7 @@
         <v>68</v>
       </c>
       <c r="B68" s="1">
-        <v>133.054804113083</v>
+        <v>132.7102118006441</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -1903,7 +2029,7 @@
         <v>69</v>
       </c>
       <c r="B69" s="1">
-        <v>133.0969648937134</v>
+        <v>132.7282262119174</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -1911,7 +2037,7 @@
         <v>70</v>
       </c>
       <c r="B70" s="1">
-        <v>133.2575781261514</v>
+        <v>132.7533229758515</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -1919,7 +2045,7 @@
         <v>71</v>
       </c>
       <c r="B71" s="1">
-        <v>133.381640451391</v>
+        <v>132.8464630169053</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -1927,7 +2053,7 @@
         <v>72</v>
       </c>
       <c r="B72" s="1">
-        <v>133.4098969419445</v>
+        <v>132.8608687368259</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -1935,7 +2061,7 @@
         <v>73</v>
       </c>
       <c r="B73" s="1">
-        <v>133.4211383982439</v>
+        <v>132.9788599874957</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -1943,7 +2069,7 @@
         <v>74</v>
       </c>
       <c r="B74" s="1">
-        <v>133.5006517207393</v>
+        <v>133.0041366159721</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -1951,7 +2077,7 @@
         <v>75</v>
       </c>
       <c r="B75" s="1">
-        <v>133.5302571188829</v>
+        <v>133.0659420131744</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -1959,7 +2085,7 @@
         <v>76</v>
       </c>
       <c r="B76" s="1">
-        <v>133.636013709772</v>
+        <v>133.1533107418949</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1967,7 +2093,7 @@
         <v>77</v>
       </c>
       <c r="B77" s="1">
-        <v>133.7618897390375</v>
+        <v>133.252533532742</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1975,7 +2101,7 @@
         <v>78</v>
       </c>
       <c r="B78" s="1">
-        <v>133.7738544489832</v>
+        <v>133.3318819402165</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1983,7 +2109,7 @@
         <v>79</v>
       </c>
       <c r="B79" s="1">
-        <v>133.8071425626298</v>
+        <v>133.3568548726421</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1991,7 +2117,7 @@
         <v>80</v>
       </c>
       <c r="B80" s="1">
-        <v>133.8731011160293</v>
+        <v>133.4221717413834</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1999,7 +2125,7 @@
         <v>81</v>
       </c>
       <c r="B81" s="1">
-        <v>134.0183325265511</v>
+        <v>133.5832599106051</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -2007,7 +2133,7 @@
         <v>82</v>
       </c>
       <c r="B82" s="1">
-        <v>134.0783290884218</v>
+        <v>133.6094031839723</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -2015,7 +2141,7 @@
         <v>83</v>
       </c>
       <c r="B83" s="1">
-        <v>134.1396896680948</v>
+        <v>133.7068860678006</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -2023,7 +2149,7 @@
         <v>84</v>
       </c>
       <c r="B84" s="1">
-        <v>134.1896704876501</v>
+        <v>133.7779560852961</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -2031,7 +2157,7 @@
         <v>85</v>
       </c>
       <c r="B85" s="1">
-        <v>134.5546856509591</v>
+        <v>133.8115269632842</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -2039,7 +2165,7 @@
         <v>86</v>
       </c>
       <c r="B86" s="1">
-        <v>134.705240307926</v>
+        <v>133.945039704926</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -2047,7 +2173,7 @@
         <v>87</v>
       </c>
       <c r="B87" s="1">
-        <v>134.7462261557664</v>
+        <v>133.9958213364256</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -2055,7 +2181,7 @@
         <v>88</v>
       </c>
       <c r="B88" s="1">
-        <v>134.7779695032455</v>
+        <v>133.9979397295292</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -2063,7 +2189,7 @@
         <v>89</v>
       </c>
       <c r="B89" s="1">
-        <v>134.894014021914</v>
+        <v>134.0511119367338</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -2071,7 +2197,7 @@
         <v>90</v>
       </c>
       <c r="B90" s="1">
-        <v>135.0252094399987</v>
+        <v>134.1516131960995</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -2079,7 +2205,7 @@
         <v>91</v>
       </c>
       <c r="B91" s="1">
-        <v>135.1007661315249</v>
+        <v>134.1776483769894</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -2087,7 +2213,7 @@
         <v>92</v>
       </c>
       <c r="B92" s="1">
-        <v>135.2443449262809</v>
+        <v>134.2536369368789</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -2095,7 +2221,7 @@
         <v>93</v>
       </c>
       <c r="B93" s="1">
-        <v>135.314083586221</v>
+        <v>134.5794808378749</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -2103,7 +2229,7 @@
         <v>94</v>
       </c>
       <c r="B94" s="1">
-        <v>135.3634489636169</v>
+        <v>134.6523925440123</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -2111,7 +2237,7 @@
         <v>95</v>
       </c>
       <c r="B95" s="1">
-        <v>135.5501486661843</v>
+        <v>134.6549604604534</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -2119,7 +2245,7 @@
         <v>96</v>
       </c>
       <c r="B96" s="1">
-        <v>135.5854465331853</v>
+        <v>134.7091415218411</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -2127,7 +2253,7 @@
         <v>97</v>
       </c>
       <c r="B97" s="1">
-        <v>135.5889344255435</v>
+        <v>134.7675861172457</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -2135,7 +2261,7 @@
         <v>98</v>
       </c>
       <c r="B98" s="1">
-        <v>135.6521333983807</v>
+        <v>134.7999295686369</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -2143,7 +2269,7 @@
         <v>99</v>
       </c>
       <c r="B99" s="1">
-        <v>135.7108241577782</v>
+        <v>134.8063599657798</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -2151,7 +2277,7 @@
         <v>100</v>
       </c>
       <c r="B100" s="1">
-        <v>135.7145360260231</v>
+        <v>134.8097741384794</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -2159,7 +2285,7 @@
         <v>101</v>
       </c>
       <c r="B101" s="1">
-        <v>135.7333710742167</v>
+        <v>134.9378843621292</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -2167,7 +2293,7 @@
         <v>102</v>
       </c>
       <c r="B102" s="1">
-        <v>135.757906767528</v>
+        <v>135.1678951673446</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -2175,7 +2301,7 @@
         <v>103</v>
       </c>
       <c r="B103" s="1">
-        <v>135.8865009065889</v>
+        <v>135.3247100901519</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -2183,7 +2309,7 @@
         <v>104</v>
       </c>
       <c r="B104" s="1">
-        <v>136.0717000616034</v>
+        <v>135.3797784874333</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -2191,7 +2317,7 @@
         <v>105</v>
       </c>
       <c r="B105" s="1">
-        <v>136.4170002511934</v>
+        <v>135.6943987034581</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -2199,7 +2325,7 @@
         <v>106</v>
       </c>
       <c r="B106" s="1">
-        <v>136.5712369630736</v>
+        <v>135.8714516044884</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -2207,7 +2333,7 @@
         <v>107</v>
       </c>
       <c r="B107" s="1">
-        <v>136.6111800547159</v>
+        <v>135.8803619530791</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -2215,7 +2341,7 @@
         <v>108</v>
       </c>
       <c r="B108" s="1">
-        <v>136.7123648198388</v>
+        <v>135.982199941777</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -2223,7 +2349,7 @@
         <v>109</v>
       </c>
       <c r="B109" s="1">
-        <v>136.896599543079</v>
+        <v>136.0198934161041</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -2231,7 +2357,7 @@
         <v>110</v>
       </c>
       <c r="B110" s="1">
-        <v>137.0549753175946</v>
+        <v>136.0794957799257</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -2239,7 +2365,7 @@
         <v>111</v>
       </c>
       <c r="B111" s="1">
-        <v>137.2437111400247</v>
+        <v>136.1305420682012</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -2247,7 +2373,7 @@
         <v>112</v>
       </c>
       <c r="B112" s="1">
-        <v>137.2530481192849</v>
+        <v>136.1796449390421</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -2255,7 +2381,7 @@
         <v>113</v>
       </c>
       <c r="B113" s="1">
-        <v>137.3786489652296</v>
+        <v>136.1914353845972</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -2263,7 +2389,7 @@
         <v>114</v>
       </c>
       <c r="B114" s="1">
-        <v>137.4432195334991</v>
+        <v>136.2557517387488</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -2271,7 +2397,7 @@
         <v>115</v>
       </c>
       <c r="B115" s="1">
-        <v>137.4730221182488</v>
+        <v>136.2884174726703</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -2279,7 +2405,7 @@
         <v>116</v>
       </c>
       <c r="B116" s="1">
-        <v>137.5938378011265</v>
+        <v>136.3571606111927</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -2287,7 +2413,7 @@
         <v>117</v>
       </c>
       <c r="B117" s="1">
-        <v>137.6827006167127</v>
+        <v>136.377279041235</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -2295,7 +2421,7 @@
         <v>118</v>
       </c>
       <c r="B118" s="1">
-        <v>137.7058672374596</v>
+        <v>136.4858997175197</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -2303,7 +2429,7 @@
         <v>119</v>
       </c>
       <c r="B119" s="1">
-        <v>137.7799672732077</v>
+        <v>136.5143804284009</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -2311,7 +2437,7 @@
         <v>120</v>
       </c>
       <c r="B120" s="1">
-        <v>137.9504968617209</v>
+        <v>136.5322257842773</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -2319,7 +2445,7 @@
         <v>121</v>
       </c>
       <c r="B121" s="1">
-        <v>138.0037934228926</v>
+        <v>136.6410404452078</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -2327,7 +2453,7 @@
         <v>122</v>
       </c>
       <c r="B122" s="1">
-        <v>138.0842294583706</v>
+        <v>136.7135627119306</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -2335,7 +2461,7 @@
         <v>123</v>
       </c>
       <c r="B123" s="1">
-        <v>138.2355758941389</v>
+        <v>136.7979505946554</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -2343,7 +2469,7 @@
         <v>124</v>
       </c>
       <c r="B124" s="1">
-        <v>138.3006960726211</v>
+        <v>136.8094591640515</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -2351,7 +2477,7 @@
         <v>125</v>
       </c>
       <c r="B125" s="1">
-        <v>138.3211440201763</v>
+        <v>137.0045257630852</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -2359,7 +2485,7 @@
         <v>126</v>
       </c>
       <c r="B126" s="1">
-        <v>138.3261628600382</v>
+        <v>137.0375557707843</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -2367,7 +2493,7 @@
         <v>127</v>
       </c>
       <c r="B127" s="1">
-        <v>138.3628761265203</v>
+        <v>137.1742319709355</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -2375,7 +2501,7 @@
         <v>128</v>
       </c>
       <c r="B128" s="1">
-        <v>138.4859910937689</v>
+        <v>137.2377102812316</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -2383,7 +2509,7 @@
         <v>129</v>
       </c>
       <c r="B129" s="1">
-        <v>138.5925791322447</v>
+        <v>137.2434354799232</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -2391,7 +2517,7 @@
         <v>130</v>
       </c>
       <c r="B130" s="1">
-        <v>138.5998150846503</v>
+        <v>137.2860516470156</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -2399,7 +2525,7 @@
         <v>131</v>
       </c>
       <c r="B131" s="1">
-        <v>138.8862481300656</v>
+        <v>137.3574201471104</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -2407,7 +2533,7 @@
         <v>132</v>
       </c>
       <c r="B132" s="1">
-        <v>138.9874086537829</v>
+        <v>137.6489215062962</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -2415,7 +2541,7 @@
         <v>133</v>
       </c>
       <c r="B133" s="1">
-        <v>139.1265820166901</v>
+        <v>137.8190697868271</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -2423,7 +2549,7 @@
         <v>134</v>
       </c>
       <c r="B134" s="1">
-        <v>139.1970130722525</v>
+        <v>137.9663664457507</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -2431,7 +2557,7 @@
         <v>135</v>
       </c>
       <c r="B135" s="1">
-        <v>139.3336595626849</v>
+        <v>138.1623398619516</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -2439,7 +2565,7 @@
         <v>136</v>
       </c>
       <c r="B136" s="1">
-        <v>139.4561407932709</v>
+        <v>138.1787925365531</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -2447,7 +2573,7 @@
         <v>137</v>
       </c>
       <c r="B137" s="1">
-        <v>139.5540873336665</v>
+        <v>138.252964129571</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -2455,7 +2581,7 @@
         <v>138</v>
       </c>
       <c r="B138" s="1">
-        <v>139.7528622364796</v>
+        <v>138.2686004963132</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -2463,7 +2589,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="1">
-        <v>139.788460901412</v>
+        <v>138.2959609121969</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -2471,7 +2597,7 @@
         <v>140</v>
       </c>
       <c r="B140" s="1">
-        <v>139.8476427138656</v>
+        <v>138.3364122056973</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -2479,7 +2605,7 @@
         <v>141</v>
       </c>
       <c r="B141" s="1">
-        <v>139.8646952363676</v>
+        <v>138.3628761265203</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -2487,7 +2613,7 @@
         <v>142</v>
       </c>
       <c r="B142" s="1">
-        <v>139.8849269611022</v>
+        <v>138.3921747520643</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -2495,7 +2621,7 @@
         <v>143</v>
       </c>
       <c r="B143" s="1">
-        <v>139.8974090851178</v>
+        <v>138.4268569541144</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -2503,7 +2629,7 @@
         <v>144</v>
       </c>
       <c r="B144" s="1">
-        <v>139.9685033086227</v>
+        <v>138.4857070895515</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -2511,7 +2637,7 @@
         <v>145</v>
       </c>
       <c r="B145" s="1">
-        <v>140.1688639990773</v>
+        <v>138.5554492694773</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -2519,7 +2645,7 @@
         <v>146</v>
       </c>
       <c r="B146" s="1">
-        <v>140.1817840078584</v>
+        <v>138.6040974571663</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -2527,7 +2653,7 @@
         <v>147</v>
       </c>
       <c r="B147" s="1">
-        <v>140.2858128916649</v>
+        <v>138.7210322862707</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -2535,7 +2661,7 @@
         <v>148</v>
       </c>
       <c r="B148" s="1">
-        <v>140.3016246725128</v>
+        <v>138.8036285618528</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -2543,7 +2669,7 @@
         <v>149</v>
       </c>
       <c r="B149" s="1">
-        <v>140.4803939385575</v>
+        <v>138.9506380652648</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -2551,7 +2677,7 @@
         <v>150</v>
       </c>
       <c r="B150" s="1">
-        <v>140.4886364878397</v>
+        <v>138.9657819868425</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -2559,7 +2685,7 @@
         <v>151</v>
       </c>
       <c r="B151" s="1">
-        <v>140.5491983858017</v>
+        <v>138.9738533995165</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -2567,7 +2693,7 @@
         <v>152</v>
       </c>
       <c r="B152" s="1">
-        <v>140.5505632835069</v>
+        <v>139.0471787049581</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -2575,7 +2701,7 @@
         <v>153</v>
       </c>
       <c r="B153" s="1">
-        <v>140.570388717293</v>
+        <v>139.3514483385379</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -2583,7 +2709,7 @@
         <v>154</v>
       </c>
       <c r="B154" s="1">
-        <v>140.6029818792996</v>
+        <v>139.473113660091</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -2591,7 +2717,7 @@
         <v>155</v>
       </c>
       <c r="B155" s="1">
-        <v>140.6600489712138</v>
+        <v>139.5052901372149</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -2599,7 +2725,7 @@
         <v>156</v>
       </c>
       <c r="B156" s="1">
-        <v>140.6831709030577</v>
+        <v>139.5530960254365</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -2607,7 +2733,7 @@
         <v>157</v>
       </c>
       <c r="B157" s="1">
-        <v>140.8047689722629</v>
+        <v>139.6129619306686</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -2615,7 +2741,7 @@
         <v>158</v>
       </c>
       <c r="B158" s="1">
-        <v>140.8481574014934</v>
+        <v>139.7491917296005</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -2623,7 +2749,7 @@
         <v>159</v>
       </c>
       <c r="B159" s="1">
-        <v>140.9299930550523</v>
+        <v>139.8627620082344</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -2631,7 +2757,7 @@
         <v>160</v>
       </c>
       <c r="B160" s="1">
-        <v>141.1436295670682</v>
+        <v>139.9250453788258</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -2639,7 +2765,7 @@
         <v>161</v>
       </c>
       <c r="B161" s="1">
-        <v>141.1498074200022</v>
+        <v>140.0252524516203</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -2647,7 +2773,7 @@
         <v>162</v>
       </c>
       <c r="B162" s="1">
-        <v>141.3738995696563</v>
+        <v>140.0492812086558</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -2655,7 +2781,7 @@
         <v>163</v>
       </c>
       <c r="B163" s="1">
-        <v>141.4944955319837</v>
+        <v>140.0703042997551</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -2663,7 +2789,7 @@
         <v>164</v>
       </c>
       <c r="B164" s="1">
-        <v>141.6149379342257</v>
+        <v>140.1327069464381</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -2671,7 +2797,7 @@
         <v>165</v>
       </c>
       <c r="B165" s="1">
-        <v>141.7445417132864</v>
+        <v>140.1753285683016</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -2679,7 +2805,7 @@
         <v>166</v>
       </c>
       <c r="B166" s="1">
-        <v>141.9971175891156</v>
+        <v>140.2568859897513</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -2687,7 +2813,7 @@
         <v>167</v>
       </c>
       <c r="B167" s="1">
-        <v>142.1378061528011</v>
+        <v>140.3331848340294</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -2695,7 +2821,7 @@
         <v>168</v>
       </c>
       <c r="B168" s="1">
-        <v>142.2859130021646</v>
+        <v>140.3659880481158</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -2703,7 +2829,7 @@
         <v>169</v>
       </c>
       <c r="B169" s="1">
-        <v>142.4279189917299</v>
+        <v>140.441605100127</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -2711,7 +2837,7 @@
         <v>170</v>
       </c>
       <c r="B170" s="1">
-        <v>142.4451775676185</v>
+        <v>140.4687757735928</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -2719,7 +2845,7 @@
         <v>171</v>
       </c>
       <c r="B171" s="1">
-        <v>142.5328823474679</v>
+        <v>140.4763988750906</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -2727,7 +2853,7 @@
         <v>172</v>
       </c>
       <c r="B172" s="1">
-        <v>142.6311346826648</v>
+        <v>140.5201545733592</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -2735,7 +2861,7 @@
         <v>173</v>
       </c>
       <c r="B173" s="1">
-        <v>142.7016844730109</v>
+        <v>140.5491983858017</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -2743,7 +2869,7 @@
         <v>174</v>
       </c>
       <c r="B174" s="1">
-        <v>142.8766548099713</v>
+        <v>140.6600489712138</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -2751,7 +2877,7 @@
         <v>175</v>
       </c>
       <c r="B175" s="1">
-        <v>142.8936100139529</v>
+        <v>140.8158017419343</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -2759,7 +2885,7 @@
         <v>176</v>
       </c>
       <c r="B176" s="1">
-        <v>143.4293799926538</v>
+        <v>140.895600393904</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -2767,7 +2893,7 @@
         <v>177</v>
       </c>
       <c r="B177" s="1">
-        <v>143.4965607302162</v>
+        <v>140.9299930550523</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -2775,7 +2901,7 @@
         <v>178</v>
       </c>
       <c r="B178" s="1">
-        <v>143.8696326440162</v>
+        <v>140.930478172524</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -2783,7 +2909,7 @@
         <v>179</v>
       </c>
       <c r="B179" s="1">
-        <v>144.0590301591415</v>
+        <v>140.9567772123103</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -2791,7 +2917,7 @@
         <v>180</v>
       </c>
       <c r="B180" s="1">
-        <v>144.0800158428473</v>
+        <v>141.0623936715724</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -2799,7 +2925,7 @@
         <v>181</v>
       </c>
       <c r="B181" s="1">
-        <v>144.1902679147018</v>
+        <v>141.3121475469277</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -2807,7 +2933,7 @@
         <v>182</v>
       </c>
       <c r="B182" s="1">
-        <v>144.2222542109978</v>
+        <v>141.3696273804869</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -2815,7 +2941,7 @@
         <v>183</v>
       </c>
       <c r="B183" s="1">
-        <v>144.5482721205284</v>
+        <v>141.4622320104278</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -2823,7 +2949,7 @@
         <v>184</v>
       </c>
       <c r="B184" s="1">
-        <v>144.6415685083634</v>
+        <v>141.5112658511021</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -2831,7 +2957,7 @@
         <v>185</v>
       </c>
       <c r="B185" s="1">
-        <v>144.692163104913</v>
+        <v>141.5286429455035</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -2839,7 +2965,7 @@
         <v>186</v>
       </c>
       <c r="B186" s="1">
-        <v>144.6949912863568</v>
+        <v>141.5757119060466</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -2847,7 +2973,7 @@
         <v>187</v>
       </c>
       <c r="B187" s="1">
-        <v>144.7546683844614</v>
+        <v>141.6027755463067</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -2855,7 +2981,7 @@
         <v>188</v>
       </c>
       <c r="B188" s="1">
-        <v>144.8602175815853</v>
+        <v>141.6430658677874</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -2863,7 +2989,7 @@
         <v>189</v>
       </c>
       <c r="B189" s="1">
-        <v>144.9035588150722</v>
+        <v>141.7545822615294</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -2871,7 +2997,7 @@
         <v>190</v>
       </c>
       <c r="B190" s="1">
-        <v>145.0186326059533</v>
+        <v>142.3418792077396</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -2879,7 +3005,7 @@
         <v>191</v>
       </c>
       <c r="B191" s="1">
-        <v>145.2248402289466</v>
+        <v>142.4579416116289</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -2887,7 +3013,7 @@
         <v>192</v>
       </c>
       <c r="B192" s="1">
-        <v>145.2708806659446</v>
+        <v>142.672246456289</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -2895,7 +3021,7 @@
         <v>193</v>
       </c>
       <c r="B193" s="1">
-        <v>145.2712689674481</v>
+        <v>142.8191737892882</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -2903,7 +3029,7 @@
         <v>194</v>
       </c>
       <c r="B194" s="1">
-        <v>146.0692451850791</v>
+        <v>143.1831952383566</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -2911,7 +3037,7 @@
         <v>195</v>
       </c>
       <c r="B195" s="1">
-        <v>146.1780301231503</v>
+        <v>143.4318272509059</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -2919,7 +3045,7 @@
         <v>196</v>
       </c>
       <c r="B196" s="1">
-        <v>146.259727358538</v>
+        <v>143.5289072942551</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -2927,7 +3053,7 @@
         <v>197</v>
       </c>
       <c r="B197" s="1">
-        <v>146.4094264237745</v>
+        <v>143.6165598158398</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -2935,7 +3061,7 @@
         <v>198</v>
       </c>
       <c r="B198" s="1">
-        <v>146.5809838733086</v>
+        <v>143.7889229291555</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -2943,7 +3069,7 @@
         <v>199</v>
       </c>
       <c r="B199" s="1">
-        <v>146.7402127489977</v>
+        <v>143.8617578340204</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -2951,7 +3077,7 @@
         <v>200</v>
       </c>
       <c r="B200" s="1">
-        <v>146.8285661738778</v>
+        <v>144.0897161273375</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -2959,7 +3085,7 @@
         <v>201</v>
       </c>
       <c r="B201" s="1">
-        <v>147.1379470526188</v>
+        <v>144.1771117570505</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -2967,7 +3093,7 @@
         <v>202</v>
       </c>
       <c r="B202" s="1">
-        <v>147.2667966495009</v>
+        <v>144.1862384531083</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -2975,7 +3101,7 @@
         <v>203</v>
       </c>
       <c r="B203" s="1">
-        <v>147.3335984920871</v>
+        <v>144.2920244813407</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -2983,7 +3109,7 @@
         <v>204</v>
       </c>
       <c r="B204" s="1">
-        <v>147.4765492979953</v>
+        <v>144.4758057949878</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -2991,7 +3117,7 @@
         <v>205</v>
       </c>
       <c r="B205" s="1">
-        <v>147.7309661794874</v>
+        <v>144.7344888127104</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -2999,7 +3125,7 @@
         <v>206</v>
       </c>
       <c r="B206" s="1">
-        <v>148.2026101301634</v>
+        <v>144.7506357718072</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -3007,7 +3133,7 @@
         <v>207</v>
       </c>
       <c r="B207" s="1">
-        <v>148.3987471328047</v>
+        <v>144.7745608750327</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -3015,7 +3141,7 @@
         <v>208</v>
       </c>
       <c r="B208" s="1">
-        <v>148.4293495016097</v>
+        <v>144.8756809725201</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -3023,7 +3149,7 @@
         <v>209</v>
       </c>
       <c r="B209" s="1">
-        <v>148.4463954505772</v>
+        <v>145.1363452320988</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -3031,7 +3157,7 @@
         <v>210</v>
       </c>
       <c r="B210" s="1">
-        <v>148.5809303255238</v>
+        <v>145.2811876163065</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -3039,7 +3165,7 @@
         <v>211</v>
       </c>
       <c r="B211" s="1">
-        <v>149.045523877299</v>
+        <v>145.5222898953698</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -3047,7 +3173,7 @@
         <v>212</v>
       </c>
       <c r="B212" s="1">
-        <v>149.0990341524744</v>
+        <v>145.5586568980044</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -3055,7 +3181,7 @@
         <v>213</v>
       </c>
       <c r="B213" s="1">
-        <v>149.1724738286315</v>
+        <v>145.6391760263504</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -3063,7 +3189,7 @@
         <v>214</v>
       </c>
       <c r="B214" s="1">
-        <v>149.2954192871287</v>
+        <v>146.2009803093625</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -3071,7 +3197,7 @@
         <v>215</v>
       </c>
       <c r="B215" s="1">
-        <v>149.8172701293772</v>
+        <v>146.2114902536547</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -3079,7 +3205,7 @@
         <v>216</v>
       </c>
       <c r="B216" s="1">
-        <v>150.5165850579068</v>
+        <v>146.241795428917</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -3087,7 +3213,7 @@
         <v>217</v>
       </c>
       <c r="B217" s="1">
-        <v>150.7083323887239</v>
+        <v>146.3215973718292</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -3095,7 +3221,7 @@
         <v>218</v>
       </c>
       <c r="B218" s="1">
-        <v>150.9576870764507</v>
+        <v>146.3561530138102</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -3103,7 +3229,7 @@
         <v>219</v>
       </c>
       <c r="B219" s="1">
-        <v>151.070099883861</v>
+        <v>146.3798949065404</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -3111,7 +3237,7 @@
         <v>220</v>
       </c>
       <c r="B220" s="1">
-        <v>151.1869210444988</v>
+        <v>146.3833731381108</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -3119,7 +3245,7 @@
         <v>221</v>
       </c>
       <c r="B221" s="1">
-        <v>151.1949273850225</v>
+        <v>146.4602246996432</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -3127,7 +3253,7 @@
         <v>222</v>
       </c>
       <c r="B222" s="1">
-        <v>151.6349094459205</v>
+        <v>146.8890423374388</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -3135,7 +3261,7 @@
         <v>223</v>
       </c>
       <c r="B223" s="1">
-        <v>151.7560628001356</v>
+        <v>146.9563941813576</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -3143,7 +3269,7 @@
         <v>224</v>
       </c>
       <c r="B224" s="1">
-        <v>151.8489983692553</v>
+        <v>147.0040493194154</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -3151,7 +3277,7 @@
         <v>225</v>
       </c>
       <c r="B225" s="1">
-        <v>151.9613245333938</v>
+        <v>147.2026916411549</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -3159,7 +3285,7 @@
         <v>226</v>
       </c>
       <c r="B226" s="1">
-        <v>152.0263027182713</v>
+        <v>147.3925610959904</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -3167,7 +3293,7 @@
         <v>227</v>
       </c>
       <c r="B227" s="1">
-        <v>152.4634264696241</v>
+        <v>147.4288005275747</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -3175,7 +3301,7 @@
         <v>228</v>
       </c>
       <c r="B228" s="1">
-        <v>152.7081929577312</v>
+        <v>147.5171538389538</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -3183,7 +3309,7 @@
         <v>229</v>
       </c>
       <c r="B229" s="1">
-        <v>152.8384239407649</v>
+        <v>147.9542697098937</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -3191,7 +3317,7 @@
         <v>230</v>
       </c>
       <c r="B230" s="1">
-        <v>153.2000983220264</v>
+        <v>148.1032779929752</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -3199,7 +3325,7 @@
         <v>231</v>
       </c>
       <c r="B231" s="1">
-        <v>153.3548575012401</v>
+        <v>148.5809303255238</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -3207,7 +3333,7 @@
         <v>232</v>
       </c>
       <c r="B232" s="1">
-        <v>153.4386380464938</v>
+        <v>149.1724738286315</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -3215,7 +3341,7 @@
         <v>233</v>
       </c>
       <c r="B233" s="1">
-        <v>153.4393796479383</v>
+        <v>149.2199115458932</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -3223,7 +3349,7 @@
         <v>234</v>
       </c>
       <c r="B234" s="1">
-        <v>154.0481122143651</v>
+        <v>149.2954192871287</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -3231,7 +3357,7 @@
         <v>235</v>
       </c>
       <c r="B235" s="1">
-        <v>154.420228958684</v>
+        <v>149.3354932960714</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -3239,7 +3365,7 @@
         <v>236</v>
       </c>
       <c r="B236" s="1">
-        <v>155.026275051384</v>
+        <v>149.5527536541209</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -3247,7 +3373,7 @@
         <v>237</v>
       </c>
       <c r="B237" s="1">
-        <v>155.3333619187437</v>
+        <v>149.6061067117918</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -3255,7 +3381,7 @@
         <v>238</v>
       </c>
       <c r="B238" s="1">
-        <v>156.2186758695682</v>
+        <v>149.6476937869576</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -3263,7 +3389,7 @@
         <v>239</v>
       </c>
       <c r="B239" s="1">
-        <v>156.2233337826705</v>
+        <v>149.8769942158445</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -3271,7 +3397,7 @@
         <v>240</v>
       </c>
       <c r="B240" s="1">
-        <v>156.572011137729</v>
+        <v>149.9234724342617</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -3279,7 +3405,7 @@
         <v>241</v>
       </c>
       <c r="B241" s="1">
-        <v>156.8845963151284</v>
+        <v>149.9361973014729</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -3287,7 +3413,7 @@
         <v>242</v>
       </c>
       <c r="B242" s="1">
-        <v>157.6286106981774</v>
+        <v>149.9668465598864</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -3295,7 +3421,7 @@
         <v>243</v>
       </c>
       <c r="B243" s="1">
-        <v>157.6522101953819</v>
+        <v>150.4791268300617</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -3303,7 +3429,7 @@
         <v>244</v>
       </c>
       <c r="B244" s="1">
-        <v>157.6821916766821</v>
+        <v>150.5797545462281</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -3311,7 +3437,7 @@
         <v>245</v>
       </c>
       <c r="B245" s="1">
-        <v>157.9975906530497</v>
+        <v>150.8113412185874</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -3319,7 +3445,7 @@
         <v>246</v>
       </c>
       <c r="B246" s="1">
-        <v>158.1026241464933</v>
+        <v>151.0555355352025</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -3327,7 +3453,7 @@
         <v>247</v>
       </c>
       <c r="B247" s="1">
-        <v>158.3176885435086</v>
+        <v>151.3257899262815</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -3335,7 +3461,7 @@
         <v>248</v>
       </c>
       <c r="B248" s="1">
-        <v>158.5063885319229</v>
+        <v>151.4136627383538</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -3343,7 +3469,7 @@
         <v>249</v>
       </c>
       <c r="B249" s="1">
-        <v>158.7304330762128</v>
+        <v>151.6408852951403</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -3351,7 +3477,7 @@
         <v>250</v>
       </c>
       <c r="B250" s="1">
-        <v>159.2256496329512</v>
+        <v>151.7688634109338</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -3359,7 +3485,7 @@
         <v>251</v>
       </c>
       <c r="B251" s="1">
-        <v>159.3176407482934</v>
+        <v>151.9271519830134</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -3367,7 +3493,7 @@
         <v>252</v>
       </c>
       <c r="B252" s="1">
-        <v>159.3722911180282</v>
+        <v>151.993233406547</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -3375,7 +3501,7 @@
         <v>253</v>
       </c>
       <c r="B253" s="1">
-        <v>159.4702308581652</v>
+        <v>152.0300900607988</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -3383,7 +3509,7 @@
         <v>254</v>
       </c>
       <c r="B254" s="1">
-        <v>159.788525686778</v>
+        <v>152.0541038522017</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -3391,7 +3517,7 @@
         <v>255</v>
       </c>
       <c r="B255" s="1">
-        <v>159.8438640635044</v>
+        <v>152.3051063990928</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -3399,7 +3525,7 @@
         <v>256</v>
       </c>
       <c r="B256" s="1">
-        <v>160.2191192407651</v>
+        <v>152.7862323762343</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -3407,7 +3533,7 @@
         <v>257</v>
       </c>
       <c r="B257" s="1">
-        <v>160.2359330108084</v>
+        <v>152.8112999019221</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -3415,7 +3541,7 @@
         <v>258</v>
       </c>
       <c r="B258" s="1">
-        <v>160.3795810929254</v>
+        <v>152.8725595941941</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -3423,7 +3549,7 @@
         <v>259</v>
       </c>
       <c r="B259" s="1">
-        <v>160.6792091524873</v>
+        <v>153.3142307288645</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -3431,7 +3557,7 @@
         <v>260</v>
       </c>
       <c r="B260" s="1">
-        <v>162.1359849282519</v>
+        <v>153.9490286603791</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -3439,7 +3565,7 @@
         <v>261</v>
       </c>
       <c r="B261" s="1">
-        <v>163.6335494742071</v>
+        <v>153.9570580387928</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -3447,7 +3573,7 @@
         <v>262</v>
       </c>
       <c r="B262" s="1">
-        <v>164.0314532066326</v>
+        <v>154.22770273795</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -3455,7 +3581,7 @@
         <v>263</v>
       </c>
       <c r="B263" s="1">
-        <v>164.1479663058912</v>
+        <v>154.7986553136977</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -3463,7 +3589,7 @@
         <v>264</v>
       </c>
       <c r="B264" s="1">
-        <v>164.1738063820643</v>
+        <v>155.1348577473296</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -3471,7 +3597,7 @@
         <v>265</v>
       </c>
       <c r="B265" s="1">
-        <v>164.6609273103286</v>
+        <v>155.154464663835</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -3479,7 +3605,7 @@
         <v>266</v>
       </c>
       <c r="B266" s="1">
-        <v>164.6637264434003</v>
+        <v>155.4439609630959</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -3487,7 +3613,7 @@
         <v>267</v>
       </c>
       <c r="B267" s="1">
-        <v>164.7581313450536</v>
+        <v>155.6722940343043</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -3495,7 +3621,7 @@
         <v>268</v>
       </c>
       <c r="B268" s="1">
-        <v>165.6903873191379</v>
+        <v>155.7991435937746</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -3503,7 +3629,7 @@
         <v>269</v>
       </c>
       <c r="B269" s="1">
-        <v>166.8936676425027</v>
+        <v>155.8299089258133</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -3511,7 +3637,7 @@
         <v>270</v>
       </c>
       <c r="B270" s="1">
-        <v>167.9518987616215</v>
+        <v>155.837329146129</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -3519,7 +3645,7 @@
         <v>271</v>
       </c>
       <c r="B271" s="1">
-        <v>168.7930115340081</v>
+        <v>155.862225665689</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -3527,7 +3653,7 @@
         <v>272</v>
       </c>
       <c r="B272" s="1">
-        <v>170.0064407452977</v>
+        <v>156.0321215288868</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -3535,7 +3661,7 @@
         <v>273</v>
       </c>
       <c r="B273" s="1">
-        <v>170.1096312798175</v>
+        <v>156.691976783327</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -3543,7 +3669,7 @@
         <v>274</v>
       </c>
       <c r="B274" s="1">
-        <v>170.4589471201529</v>
+        <v>157.0659587497863</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -3551,7 +3677,7 @@
         <v>275</v>
       </c>
       <c r="B275" s="1">
-        <v>170.963041427082</v>
+        <v>157.3549961866462</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -3559,7 +3685,7 @@
         <v>276</v>
       </c>
       <c r="B276" s="1">
-        <v>171.573049160733</v>
+        <v>157.5272433008002</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -3567,7 +3693,7 @@
         <v>277</v>
       </c>
       <c r="B277" s="1">
-        <v>171.5766682443286</v>
+        <v>157.5891602857081</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -3575,7 +3701,7 @@
         <v>278</v>
       </c>
       <c r="B278" s="1">
-        <v>171.696215708971</v>
+        <v>157.6857350589274</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -3583,7 +3709,7 @@
         <v>279</v>
       </c>
       <c r="B279" s="1">
-        <v>173.083899162879</v>
+        <v>158.6292481105189</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -3591,7 +3717,7 @@
         <v>280</v>
       </c>
       <c r="B280" s="1">
-        <v>174.9834226493426</v>
+        <v>158.7304330762128</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -3599,7 +3725,7 @@
         <v>281</v>
       </c>
       <c r="B281" s="1">
-        <v>175.2341086455913</v>
+        <v>158.8277161252772</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -3607,7 +3733,7 @@
         <v>282</v>
       </c>
       <c r="B282" s="1">
-        <v>175.274495622687</v>
+        <v>158.860443184628</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -3615,7 +3741,7 @@
         <v>283</v>
       </c>
       <c r="B283" s="1">
-        <v>176.085008564365</v>
+        <v>159.2486625100511</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -3623,7 +3749,7 @@
         <v>284</v>
       </c>
       <c r="B284" s="1">
-        <v>176.4818509157336</v>
+        <v>159.2495998619324</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -3631,7 +3757,7 @@
         <v>285</v>
       </c>
       <c r="B285" s="1">
-        <v>176.6500411554718</v>
+        <v>159.2737535581665</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -3639,7 +3765,7 @@
         <v>286</v>
       </c>
       <c r="B286" s="1">
-        <v>176.8736102167953</v>
+        <v>159.6253757457039</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -3647,7 +3773,7 @@
         <v>287</v>
       </c>
       <c r="B287" s="1">
-        <v>177.9745074336391</v>
+        <v>159.9132493247502</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -3655,7 +3781,7 @@
         <v>288</v>
       </c>
       <c r="B288" s="1">
-        <v>179.2773584895475</v>
+        <v>160.1558497188078</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -3663,7 +3789,7 @@
         <v>289</v>
       </c>
       <c r="B289" s="1">
-        <v>182.1067917868554</v>
+        <v>160.1572191334164</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -3671,7 +3797,7 @@
         <v>290</v>
       </c>
       <c r="B290" s="1">
-        <v>182.8578568114873</v>
+        <v>160.3795810929254</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -3679,7 +3805,7 @@
         <v>291</v>
       </c>
       <c r="B291" s="1">
-        <v>183.9838616740865</v>
+        <v>161.4683344869864</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -3687,7 +3813,7 @@
         <v>292</v>
       </c>
       <c r="B292" s="1">
-        <v>185.1375559245426</v>
+        <v>161.9613894130539</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -3695,7 +3821,7 @@
         <v>293</v>
       </c>
       <c r="B293" s="1">
-        <v>187.1541375601494</v>
+        <v>162.001681167397</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -3703,7 +3829,7 @@
         <v>294</v>
       </c>
       <c r="B294" s="1">
-        <v>190.2099952632329</v>
+        <v>162.4923288318841</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -3711,7 +3837,7 @@
         <v>295</v>
       </c>
       <c r="B295" s="1">
-        <v>190.4605564406618</v>
+        <v>163.0551550039471</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -3719,7 +3845,7 @@
         <v>296</v>
       </c>
       <c r="B296" s="1">
-        <v>192.2999812711404</v>
+        <v>163.3062862203633</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -3727,7 +3853,7 @@
         <v>297</v>
       </c>
       <c r="B297" s="1">
-        <v>192.8770640342961</v>
+        <v>164.0482643519483</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -3735,7 +3861,7 @@
         <v>298</v>
       </c>
       <c r="B298" s="1">
-        <v>192.8927852217686</v>
+        <v>164.6311583671043</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -3743,7 +3869,7 @@
         <v>299</v>
       </c>
       <c r="B299" s="1">
-        <v>193.4235826684304</v>
+        <v>165.325340420979</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -3751,7 +3877,7 @@
         <v>300</v>
       </c>
       <c r="B300" s="1">
-        <v>194.3385198777316</v>
+        <v>165.3542881051458</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -3759,7 +3885,7 @@
         <v>301</v>
       </c>
       <c r="B301" s="1">
-        <v>194.8419474346039</v>
+        <v>165.3920228401474</v>
       </c>
     </row>
     <row r="302" spans="1:2">
@@ -3767,7 +3893,7 @@
         <v>302</v>
       </c>
       <c r="B302" s="1">
-        <v>195.4219817739837</v>
+        <v>165.4876222953312</v>
       </c>
     </row>
     <row r="303" spans="1:2">
@@ -3775,7 +3901,7 @@
         <v>303</v>
       </c>
       <c r="B303" s="1">
-        <v>195.7388368344477</v>
+        <v>165.8135487764482</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -3783,7 +3909,7 @@
         <v>304</v>
       </c>
       <c r="B304" s="1">
-        <v>196.4221822485067</v>
+        <v>166.2634048312421</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -3791,7 +3917,7 @@
         <v>305</v>
       </c>
       <c r="B305" s="1">
-        <v>200.8887125565817</v>
+        <v>166.606024173428</v>
       </c>
     </row>
     <row r="306" spans="1:2">
@@ -3799,7 +3925,7 @@
         <v>306</v>
       </c>
       <c r="B306" s="1">
-        <v>205.2429945071746</v>
+        <v>166.9026561958634</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -3807,7 +3933,7 @@
         <v>307</v>
       </c>
       <c r="B307" s="1">
-        <v>206.6701527454403</v>
+        <v>169.823757781311</v>
       </c>
     </row>
     <row r="308" spans="1:2">
@@ -3815,7 +3941,7 @@
         <v>308</v>
       </c>
       <c r="B308" s="1">
-        <v>209.0189939958908</v>
+        <v>169.9603663264398</v>
       </c>
     </row>
     <row r="309" spans="1:2">
@@ -3823,7 +3949,7 @@
         <v>309</v>
       </c>
       <c r="B309" s="1">
-        <v>213.5306501931515</v>
+        <v>170.1096312798175</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -3831,7 +3957,7 @@
         <v>310</v>
       </c>
       <c r="B310" s="1">
-        <v>218.6491159861113</v>
+        <v>171.0138448975905</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -3839,7 +3965,7 @@
         <v>311</v>
       </c>
       <c r="B311" s="1">
-        <v>226.9743659900273</v>
+        <v>171.0509130621659</v>
       </c>
     </row>
     <row r="312" spans="1:2">
@@ -3847,7 +3973,7 @@
         <v>312</v>
       </c>
       <c r="B312" s="1">
-        <v>229.8417410344738</v>
+        <v>171.104354796629</v>
       </c>
     </row>
     <row r="313" spans="1:2">
@@ -3855,7 +3981,7 @@
         <v>313</v>
       </c>
       <c r="B313" s="1">
-        <v>245.6483509512667</v>
+        <v>172.3800202223545</v>
       </c>
     </row>
     <row r="314" spans="1:2">
@@ -3863,7 +3989,7 @@
         <v>314</v>
       </c>
       <c r="B314" s="1">
-        <v>246.3015896134957</v>
+        <v>172.5097052467621</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -3871,7 +3997,7 @@
         <v>315</v>
       </c>
       <c r="B315" s="1">
-        <v>247.6318496368786</v>
+        <v>172.9983819872432</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -3879,7 +4005,7 @@
         <v>316</v>
       </c>
       <c r="B316" s="1">
-        <v>249.4757856638007</v>
+        <v>173.2591193859789</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -3887,7 +4013,7 @@
         <v>317</v>
       </c>
       <c r="B317" s="1">
-        <v>249.7076333205924</v>
+        <v>173.5137065002932</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -3895,7 +4021,7 @@
         <v>318</v>
       </c>
       <c r="B318" s="1">
-        <v>265.5535118419622</v>
+        <v>174.1104475125682</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -3903,7 +4029,7 @@
         <v>319</v>
       </c>
       <c r="B319" s="1">
-        <v>267.3953710487986</v>
+        <v>174.7109145043558</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -3911,7 +4037,7 @@
         <v>320</v>
       </c>
       <c r="B320" s="1">
-        <v>277.1603816110563</v>
+        <v>174.8268886405918</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -3919,7 +4045,7 @@
         <v>321</v>
       </c>
       <c r="B321" s="1">
-        <v>280.1621561560102</v>
+        <v>175.0072984297854</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -3927,7 +4053,7 @@
         <v>322</v>
       </c>
       <c r="B322" s="1">
-        <v>295.1944893761822</v>
+        <v>176.2071368220628</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -3935,7 +4061,7 @@
         <v>323</v>
       </c>
       <c r="B323" s="1">
-        <v>296.7704629716832</v>
+        <v>177.7401978707017</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -3943,7 +4069,7 @@
         <v>324</v>
       </c>
       <c r="B324" s="1">
-        <v>305.7540545322861</v>
+        <v>178.9708259968874</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -3951,7 +4077,7 @@
         <v>325</v>
       </c>
       <c r="B325" s="1">
-        <v>512.3633645654282</v>
+        <v>180.5145523572857</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -3959,7 +4085,7 @@
         <v>326</v>
       </c>
       <c r="B326" s="1">
-        <v>567.1717836405109</v>
+        <v>180.7115548644201</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -3967,7 +4093,7 @@
         <v>327</v>
       </c>
       <c r="B327" s="1">
-        <v>594.5424739133769</v>
+        <v>182.440083913593</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -3975,7 +4101,343 @@
         <v>328</v>
       </c>
       <c r="B328" s="1">
-        <v>652.0128981926437</v>
+        <v>184.3330769999656</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2">
+      <c r="A329" t="s">
+        <v>329</v>
+      </c>
+      <c r="B329" s="1">
+        <v>185.0703827741358</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2">
+      <c r="A330" t="s">
+        <v>330</v>
+      </c>
+      <c r="B330" s="1">
+        <v>186.2199793966167</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2">
+      <c r="A331" t="s">
+        <v>331</v>
+      </c>
+      <c r="B331" s="1">
+        <v>189.8836087329821</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2">
+      <c r="A332" t="s">
+        <v>332</v>
+      </c>
+      <c r="B332" s="1">
+        <v>190.4077779152403</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2">
+      <c r="A333" t="s">
+        <v>333</v>
+      </c>
+      <c r="B333" s="1">
+        <v>190.9393094179592</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2">
+      <c r="A334" t="s">
+        <v>334</v>
+      </c>
+      <c r="B334" s="1">
+        <v>190.9658384088822</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2">
+      <c r="A335" t="s">
+        <v>335</v>
+      </c>
+      <c r="B335" s="1">
+        <v>191.7132577440073</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2">
+      <c r="A336" t="s">
+        <v>336</v>
+      </c>
+      <c r="B336" s="1">
+        <v>191.7851683668534</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2">
+      <c r="A337" t="s">
+        <v>337</v>
+      </c>
+      <c r="B337" s="1">
+        <v>191.9525936536076</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2">
+      <c r="A338" t="s">
+        <v>338</v>
+      </c>
+      <c r="B338" s="1">
+        <v>192.5770778551727</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2">
+      <c r="A339" t="s">
+        <v>339</v>
+      </c>
+      <c r="B339" s="1">
+        <v>192.8906642561781</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2">
+      <c r="A340" t="s">
+        <v>340</v>
+      </c>
+      <c r="B340" s="1">
+        <v>194.1189724199648</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2">
+      <c r="A341" t="s">
+        <v>341</v>
+      </c>
+      <c r="B341" s="1">
+        <v>194.3939312410436</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2">
+      <c r="A342" t="s">
+        <v>342</v>
+      </c>
+      <c r="B342" s="1">
+        <v>195.0951526572358</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2">
+      <c r="A343" t="s">
+        <v>343</v>
+      </c>
+      <c r="B343" s="1">
+        <v>195.4483659836453</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2">
+      <c r="A344" t="s">
+        <v>344</v>
+      </c>
+      <c r="B344" s="1">
+        <v>200.6891681168601</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2">
+      <c r="A345" t="s">
+        <v>345</v>
+      </c>
+      <c r="B345" s="1">
+        <v>202.9980715578714</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2">
+      <c r="A346" t="s">
+        <v>346</v>
+      </c>
+      <c r="B346" s="1">
+        <v>203.2626140744005</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2">
+      <c r="A347" t="s">
+        <v>347</v>
+      </c>
+      <c r="B347" s="1">
+        <v>204.9186447907497</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2">
+      <c r="A348" t="s">
+        <v>348</v>
+      </c>
+      <c r="B348" s="1">
+        <v>206.4117559679477</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2">
+      <c r="A349" t="s">
+        <v>349</v>
+      </c>
+      <c r="B349" s="1">
+        <v>207.2253572575597</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2">
+      <c r="A350" t="s">
+        <v>350</v>
+      </c>
+      <c r="B350" s="1">
+        <v>211.4229301278048</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2">
+      <c r="A351" t="s">
+        <v>351</v>
+      </c>
+      <c r="B351" s="1">
+        <v>225.1710975298583</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2">
+      <c r="A352" t="s">
+        <v>352</v>
+      </c>
+      <c r="B352" s="1">
+        <v>229.8417410344738</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2">
+      <c r="A353" t="s">
+        <v>353</v>
+      </c>
+      <c r="B353" s="1">
+        <v>230.7730965867328</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2">
+      <c r="A354" t="s">
+        <v>354</v>
+      </c>
+      <c r="B354" s="1">
+        <v>238.4912574059636</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2">
+      <c r="A355" t="s">
+        <v>355</v>
+      </c>
+      <c r="B355" s="1">
+        <v>242.8217823429158</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2">
+      <c r="A356" t="s">
+        <v>356</v>
+      </c>
+      <c r="B356" s="1">
+        <v>247.6318496368786</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2">
+      <c r="A357" t="s">
+        <v>357</v>
+      </c>
+      <c r="B357" s="1">
+        <v>249.1418236734584</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2">
+      <c r="A358" t="s">
+        <v>358</v>
+      </c>
+      <c r="B358" s="1">
+        <v>251.7635329189505</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2">
+      <c r="A359" t="s">
+        <v>359</v>
+      </c>
+      <c r="B359" s="1">
+        <v>256.3798499807854</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2">
+      <c r="A360" t="s">
+        <v>360</v>
+      </c>
+      <c r="B360" s="1">
+        <v>270.7130728670858</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2">
+      <c r="A361" t="s">
+        <v>361</v>
+      </c>
+      <c r="B361" s="1">
+        <v>270.8382431497024</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2">
+      <c r="A362" t="s">
+        <v>362</v>
+      </c>
+      <c r="B362" s="1">
+        <v>283.2107348903979</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2">
+      <c r="A363" t="s">
+        <v>363</v>
+      </c>
+      <c r="B363" s="1">
+        <v>285.0310817466313</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2">
+      <c r="A364" t="s">
+        <v>364</v>
+      </c>
+      <c r="B364" s="1">
+        <v>291.017814961712</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2">
+      <c r="A365" t="s">
+        <v>365</v>
+      </c>
+      <c r="B365" s="1">
+        <v>296.7704629716832</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2">
+      <c r="A366" t="s">
+        <v>366</v>
+      </c>
+      <c r="B366" s="1">
+        <v>305.5140061517363</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2">
+      <c r="A367" t="s">
+        <v>367</v>
+      </c>
+      <c r="B367" s="1">
+        <v>508.0148366005249</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2">
+      <c r="A368" t="s">
+        <v>368</v>
+      </c>
+      <c r="B368" s="1">
+        <v>567.1717836405109</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2">
+      <c r="A369" t="s">
+        <v>369</v>
+      </c>
+      <c r="B369" s="1">
+        <v>594.5424739133769</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2">
+      <c r="A370" t="s">
+        <v>370</v>
+      </c>
+      <c r="B370" s="1">
+        <v>638.6554122789598</v>
       </c>
     </row>
   </sheetData>

--- a/Screener/data/rs_rating_top_30.xlsx
+++ b/Screener/data/rs_rating_top_30.xlsx
@@ -22,1099 +22,1099 @@
     <t>RS Rating</t>
   </si>
   <si>
+    <t>BOSSY</t>
+  </si>
+  <si>
+    <t>ACDVF</t>
+  </si>
+  <si>
+    <t>KRT</t>
+  </si>
+  <si>
+    <t>NE</t>
+  </si>
+  <si>
+    <t>MLNK</t>
+  </si>
+  <si>
+    <t>NOW</t>
+  </si>
+  <si>
+    <t>PAG</t>
+  </si>
+  <si>
+    <t>NVT</t>
+  </si>
+  <si>
+    <t>MOMO</t>
+  </si>
+  <si>
+    <t>LZRFY</t>
+  </si>
+  <si>
+    <t>BSAC</t>
+  </si>
+  <si>
+    <t>NPO</t>
+  </si>
+  <si>
+    <t>WCC</t>
+  </si>
+  <si>
+    <t>VNT</t>
+  </si>
+  <si>
+    <t>DRD</t>
+  </si>
+  <si>
+    <t>PRI</t>
+  </si>
+  <si>
+    <t>CLH</t>
+  </si>
+  <si>
+    <t>TWST</t>
+  </si>
+  <si>
+    <t>ROKU</t>
+  </si>
+  <si>
+    <t>ARCB</t>
+  </si>
+  <si>
     <t>FTNT</t>
   </si>
   <si>
+    <t>NUVL</t>
+  </si>
+  <si>
+    <t>EVO</t>
+  </si>
+  <si>
+    <t>COHR</t>
+  </si>
+  <si>
+    <t>ORCL</t>
+  </si>
+  <si>
+    <t>NFLX</t>
+  </si>
+  <si>
+    <t>ALSN</t>
+  </si>
+  <si>
+    <t>APAM</t>
+  </si>
+  <si>
+    <t>ASUR</t>
+  </si>
+  <si>
+    <t>BLX</t>
+  </si>
+  <si>
+    <t>ATI</t>
+  </si>
+  <si>
     <t>IMTX</t>
   </si>
   <si>
+    <t>RYI</t>
+  </si>
+  <si>
+    <t>HZO</t>
+  </si>
+  <si>
+    <t>PEGA</t>
+  </si>
+  <si>
+    <t>ARCO</t>
+  </si>
+  <si>
+    <t>ATKR</t>
+  </si>
+  <si>
+    <t>TEX</t>
+  </si>
+  <si>
+    <t>TREX</t>
+  </si>
+  <si>
+    <t>AFRM</t>
+  </si>
+  <si>
+    <t>LAD</t>
+  </si>
+  <si>
+    <t>TWN</t>
+  </si>
+  <si>
+    <t>HUBB</t>
+  </si>
+  <si>
+    <t>IGT</t>
+  </si>
+  <si>
+    <t>CVRX</t>
+  </si>
+  <si>
+    <t>VCEL</t>
+  </si>
+  <si>
+    <t>CIX</t>
+  </si>
+  <si>
     <t>TARO</t>
   </si>
   <si>
+    <t>EXP</t>
+  </si>
+  <si>
+    <t>THO</t>
+  </si>
+  <si>
+    <t>SIBN</t>
+  </si>
+  <si>
+    <t>TGS</t>
+  </si>
+  <si>
+    <t>ABR</t>
+  </si>
+  <si>
+    <t>ALBY</t>
+  </si>
+  <si>
+    <t>ERII</t>
+  </si>
+  <si>
+    <t>AGRO</t>
+  </si>
+  <si>
+    <t>CVGI</t>
+  </si>
+  <si>
+    <t>CSAN</t>
+  </si>
+  <si>
+    <t>RMBS</t>
+  </si>
+  <si>
+    <t>AUPH</t>
+  </si>
+  <si>
+    <t>LEGN</t>
+  </si>
+  <si>
+    <t>PTGX</t>
+  </si>
+  <si>
+    <t>CRCT</t>
+  </si>
+  <si>
+    <t>VEL</t>
+  </si>
+  <si>
+    <t>ENVA</t>
+  </si>
+  <si>
+    <t>NEWT</t>
+  </si>
+  <si>
+    <t>ZEUS</t>
+  </si>
+  <si>
     <t>DECK</t>
   </si>
   <si>
-    <t>GNRC</t>
-  </si>
-  <si>
-    <t>TREX</t>
-  </si>
-  <si>
-    <t>MTR</t>
-  </si>
-  <si>
-    <t>URBN</t>
-  </si>
-  <si>
-    <t>TWST</t>
-  </si>
-  <si>
-    <t>FND</t>
+    <t>ATEC</t>
+  </si>
+  <si>
+    <t>MNSO</t>
+  </si>
+  <si>
+    <t>GT</t>
+  </si>
+  <si>
+    <t>DHI</t>
+  </si>
+  <si>
+    <t>DXPE</t>
+  </si>
+  <si>
+    <t>CPA</t>
+  </si>
+  <si>
+    <t>VMW</t>
+  </si>
+  <si>
+    <t>CARS</t>
+  </si>
+  <si>
+    <t>ENS</t>
+  </si>
+  <si>
+    <t>SHAK</t>
+  </si>
+  <si>
+    <t>HSKA</t>
+  </si>
+  <si>
+    <t>HOFV</t>
+  </si>
+  <si>
+    <t>MYRG</t>
+  </si>
+  <si>
+    <t>CSWI</t>
+  </si>
+  <si>
+    <t>TMDX</t>
+  </si>
+  <si>
+    <t>BMI</t>
+  </si>
+  <si>
+    <t>CNM</t>
+  </si>
+  <si>
+    <t>APG</t>
+  </si>
+  <si>
+    <t>FTI</t>
   </si>
   <si>
     <t>LUNG</t>
   </si>
   <si>
-    <t>VEL</t>
-  </si>
-  <si>
-    <t>WCC</t>
-  </si>
-  <si>
-    <t>LZRFY</t>
+    <t>HROW</t>
+  </si>
+  <si>
+    <t>PHG</t>
+  </si>
+  <si>
+    <t>AVDX</t>
+  </si>
+  <si>
+    <t>WPRT</t>
+  </si>
+  <si>
+    <t>RELY</t>
+  </si>
+  <si>
+    <t>MATX</t>
+  </si>
+  <si>
+    <t>RCMT</t>
+  </si>
+  <si>
+    <t>MANH</t>
+  </si>
+  <si>
+    <t>PFSI</t>
+  </si>
+  <si>
+    <t>CXM</t>
   </si>
   <si>
     <t>BUR</t>
   </si>
   <si>
-    <t>CPA</t>
-  </si>
-  <si>
-    <t>EXP</t>
-  </si>
-  <si>
-    <t>ALSN</t>
+    <t>NEOG</t>
+  </si>
+  <si>
+    <t>FIVN</t>
+  </si>
+  <si>
+    <t>INMD</t>
+  </si>
+  <si>
+    <t>NETI</t>
+  </si>
+  <si>
+    <t>USLM</t>
+  </si>
+  <si>
+    <t>RCM</t>
+  </si>
+  <si>
+    <t>CARG</t>
+  </si>
+  <si>
+    <t>OC</t>
+  </si>
+  <si>
+    <t>HELE</t>
+  </si>
+  <si>
+    <t>AZEK</t>
+  </si>
+  <si>
+    <t>EB</t>
+  </si>
+  <si>
+    <t>YELP</t>
+  </si>
+  <si>
+    <t>FROG</t>
+  </si>
+  <si>
+    <t>KRYS</t>
+  </si>
+  <si>
+    <t>PETQ</t>
+  </si>
+  <si>
+    <t>BWMN</t>
+  </si>
+  <si>
+    <t>MNDY</t>
+  </si>
+  <si>
+    <t>MLP</t>
+  </si>
+  <si>
+    <t>PKOH</t>
+  </si>
+  <si>
+    <t>PCYO</t>
+  </si>
+  <si>
+    <t>TGLS</t>
+  </si>
+  <si>
+    <t>MATW</t>
+  </si>
+  <si>
+    <t>MTH</t>
+  </si>
+  <si>
+    <t>CELH</t>
+  </si>
+  <si>
+    <t>THC</t>
+  </si>
+  <si>
+    <t>EVI</t>
+  </si>
+  <si>
+    <t>SRAD</t>
+  </si>
+  <si>
+    <t>CLS</t>
+  </si>
+  <si>
+    <t>SMID</t>
+  </si>
+  <si>
+    <t>MRUS</t>
+  </si>
+  <si>
+    <t>ERO</t>
+  </si>
+  <si>
+    <t>ALGM</t>
+  </si>
+  <si>
+    <t>IESC</t>
+  </si>
+  <si>
+    <t>PROF</t>
+  </si>
+  <si>
+    <t>NATR</t>
+  </si>
+  <si>
+    <t>MGNI</t>
+  </si>
+  <si>
+    <t>GTLS</t>
+  </si>
+  <si>
+    <t>AAN</t>
+  </si>
+  <si>
+    <t>TGTX</t>
+  </si>
+  <si>
+    <t>WMS</t>
+  </si>
+  <si>
+    <t>GHRS</t>
+  </si>
+  <si>
+    <t>ROIV</t>
+  </si>
+  <si>
+    <t>ABNB</t>
+  </si>
+  <si>
+    <t>TPH</t>
+  </si>
+  <si>
+    <t>JELD</t>
+  </si>
+  <si>
+    <t>LPRO</t>
+  </si>
+  <si>
+    <t>DBRG</t>
+  </si>
+  <si>
+    <t>DAL</t>
+  </si>
+  <si>
+    <t>ETNB</t>
+  </si>
+  <si>
+    <t>BOOT</t>
   </si>
   <si>
     <t>EDU</t>
   </si>
   <si>
-    <t>CNMD</t>
-  </si>
-  <si>
-    <t>HOFV</t>
-  </si>
-  <si>
-    <t>LECO</t>
-  </si>
-  <si>
-    <t>PHG</t>
-  </si>
-  <si>
-    <t>ALBY</t>
-  </si>
-  <si>
-    <t>NYCB</t>
-  </si>
-  <si>
-    <t>MTH</t>
-  </si>
-  <si>
-    <t>CPSS</t>
-  </si>
-  <si>
-    <t>HROW</t>
-  </si>
-  <si>
-    <t>GCBC</t>
-  </si>
-  <si>
-    <t>SIBN</t>
-  </si>
-  <si>
-    <t>ZUO</t>
-  </si>
-  <si>
-    <t>PRI</t>
-  </si>
-  <si>
-    <t>NEOG</t>
-  </si>
-  <si>
-    <t>CARS</t>
-  </si>
-  <si>
-    <t>GPI</t>
-  </si>
-  <si>
-    <t>ATEC</t>
-  </si>
-  <si>
-    <t>MYRG</t>
-  </si>
-  <si>
-    <t>NUVL</t>
-  </si>
-  <si>
-    <t>GTLB</t>
-  </si>
-  <si>
-    <t>ARHS</t>
-  </si>
-  <si>
-    <t>TEX</t>
-  </si>
-  <si>
-    <t>CVRX</t>
-  </si>
-  <si>
-    <t>NVT</t>
-  </si>
-  <si>
-    <t>ROKU</t>
-  </si>
-  <si>
-    <t>USLM</t>
-  </si>
-  <si>
-    <t>PATK</t>
-  </si>
-  <si>
-    <t>CLH</t>
-  </si>
-  <si>
-    <t>TGTX</t>
-  </si>
-  <si>
-    <t>ERII</t>
-  </si>
-  <si>
-    <t>ENVA</t>
-  </si>
-  <si>
-    <t>HSKA</t>
-  </si>
-  <si>
-    <t>IESC</t>
-  </si>
-  <si>
-    <t>ARCB</t>
-  </si>
-  <si>
-    <t>MOMO</t>
-  </si>
-  <si>
-    <t>ACCD</t>
-  </si>
-  <si>
-    <t>MLNK</t>
-  </si>
-  <si>
-    <t>LEGN</t>
-  </si>
-  <si>
-    <t>CRS</t>
-  </si>
-  <si>
-    <t>GT</t>
-  </si>
-  <si>
-    <t>EVO</t>
-  </si>
-  <si>
-    <t>HUBB</t>
-  </si>
-  <si>
-    <t>AFRM</t>
-  </si>
-  <si>
-    <t>VCEL</t>
-  </si>
-  <si>
-    <t>ATI</t>
-  </si>
-  <si>
-    <t>AGRO</t>
-  </si>
-  <si>
-    <t>IGT</t>
-  </si>
-  <si>
-    <t>AUPH</t>
-  </si>
-  <si>
-    <t>CNM</t>
-  </si>
-  <si>
-    <t>PEGA</t>
-  </si>
-  <si>
-    <t>CSWI</t>
-  </si>
-  <si>
-    <t>THO</t>
-  </si>
-  <si>
-    <t>NE</t>
-  </si>
-  <si>
-    <t>CVGI</t>
-  </si>
-  <si>
-    <t>ASUR</t>
-  </si>
-  <si>
-    <t>NFLX</t>
-  </si>
-  <si>
-    <t>AZEK</t>
-  </si>
-  <si>
-    <t>AVDX</t>
-  </si>
-  <si>
-    <t>AAN</t>
-  </si>
-  <si>
-    <t>PFSI</t>
-  </si>
-  <si>
-    <t>HELE</t>
-  </si>
-  <si>
-    <t>SHAK</t>
-  </si>
-  <si>
-    <t>OC</t>
-  </si>
-  <si>
-    <t>ATKR</t>
-  </si>
-  <si>
-    <t>RYI</t>
-  </si>
-  <si>
-    <t>PCYO</t>
-  </si>
-  <si>
-    <t>CIX</t>
-  </si>
-  <si>
-    <t>NPO</t>
-  </si>
-  <si>
-    <t>ABR</t>
-  </si>
-  <si>
-    <t>WMS</t>
-  </si>
-  <si>
-    <t>ABNB</t>
-  </si>
-  <si>
-    <t>VMW</t>
-  </si>
-  <si>
-    <t>FIVN</t>
-  </si>
-  <si>
-    <t>CELH</t>
-  </si>
-  <si>
-    <t>FROG</t>
-  </si>
-  <si>
-    <t>COHR</t>
-  </si>
-  <si>
-    <t>NEWT</t>
-  </si>
-  <si>
-    <t>APG</t>
-  </si>
-  <si>
-    <t>SRAD</t>
-  </si>
-  <si>
-    <t>CARG</t>
-  </si>
-  <si>
-    <t>PETQ</t>
-  </si>
-  <si>
-    <t>TPH</t>
-  </si>
-  <si>
-    <t>FTI</t>
-  </si>
-  <si>
-    <t>BILL</t>
-  </si>
-  <si>
-    <t>CLS</t>
-  </si>
-  <si>
-    <t>PAG</t>
-  </si>
-  <si>
-    <t>IMVT</t>
-  </si>
-  <si>
-    <t>DXPE</t>
-  </si>
-  <si>
-    <t>ENS</t>
+    <t>IDCC</t>
+  </si>
+  <si>
+    <t>DDOG</t>
+  </si>
+  <si>
+    <t>DASH</t>
+  </si>
+  <si>
+    <t>CLBR</t>
+  </si>
+  <si>
+    <t>INTT</t>
+  </si>
+  <si>
+    <t>DUOL</t>
+  </si>
+  <si>
+    <t>IIVI</t>
+  </si>
+  <si>
+    <t>OII</t>
+  </si>
+  <si>
+    <t>FCAP</t>
   </si>
   <si>
     <t>TOL</t>
   </si>
   <si>
+    <t>SSYS</t>
+  </si>
+  <si>
+    <t>HCCI</t>
+  </si>
+  <si>
+    <t>LMND</t>
+  </si>
+  <si>
+    <t>SHOP</t>
+  </si>
+  <si>
+    <t>ATLC</t>
+  </si>
+  <si>
+    <t>BCC</t>
+  </si>
+  <si>
+    <t>BRZE</t>
+  </si>
+  <si>
+    <t>TMHC</t>
+  </si>
+  <si>
+    <t>BECN</t>
+  </si>
+  <si>
+    <t>FMS</t>
+  </si>
+  <si>
+    <t>ACVA</t>
+  </si>
+  <si>
+    <t>SSD</t>
+  </si>
+  <si>
+    <t>AEL</t>
+  </si>
+  <si>
+    <t>AMWD</t>
+  </si>
+  <si>
+    <t>WFRD</t>
+  </si>
+  <si>
+    <t>BVH</t>
+  </si>
+  <si>
+    <t>CYD</t>
+  </si>
+  <si>
+    <t>RH</t>
+  </si>
+  <si>
+    <t>SWDAF</t>
+  </si>
+  <si>
+    <t>BWMX</t>
+  </si>
+  <si>
+    <t>PAM</t>
+  </si>
+  <si>
+    <t>ARGX</t>
+  </si>
+  <si>
+    <t>RRGB</t>
+  </si>
+  <si>
+    <t>HOOD</t>
+  </si>
+  <si>
+    <t>PANW</t>
+  </si>
+  <si>
+    <t>MORF</t>
+  </si>
+  <si>
+    <t>MTW</t>
+  </si>
+  <si>
+    <t>FTAI</t>
+  </si>
+  <si>
+    <t>PSTG</t>
+  </si>
+  <si>
+    <t>GKOS</t>
+  </si>
+  <si>
+    <t>PHM</t>
+  </si>
+  <si>
+    <t>KBH</t>
+  </si>
+  <si>
+    <t>TDW</t>
+  </si>
+  <si>
+    <t>LSANF</t>
+  </si>
+  <si>
+    <t>PHAT</t>
+  </si>
+  <si>
+    <t>NCLH</t>
+  </si>
+  <si>
+    <t>ANGN</t>
+  </si>
+  <si>
+    <t>UBER</t>
+  </si>
+  <si>
+    <t>HUBS</t>
+  </si>
+  <si>
+    <t>SGH</t>
+  </si>
+  <si>
+    <t>FRD</t>
+  </si>
+  <si>
+    <t>BLD</t>
+  </si>
+  <si>
+    <t>FSLY</t>
+  </si>
+  <si>
+    <t>JBL</t>
+  </si>
+  <si>
+    <t>SRDX</t>
+  </si>
+  <si>
+    <t>TDC</t>
+  </si>
+  <si>
+    <t>MDWT</t>
+  </si>
+  <si>
+    <t>APPF</t>
+  </si>
+  <si>
+    <t>EBIX</t>
+  </si>
+  <si>
+    <t>GRVY</t>
+  </si>
+  <si>
+    <t>PLAB</t>
+  </si>
+  <si>
+    <t>IBP</t>
+  </si>
+  <si>
+    <t>EXTR</t>
+  </si>
+  <si>
+    <t>CAAP</t>
+  </si>
+  <si>
+    <t>CRMT</t>
+  </si>
+  <si>
+    <t>ETHE</t>
+  </si>
+  <si>
+    <t>SMHI</t>
+  </si>
+  <si>
+    <t>AXR</t>
+  </si>
+  <si>
+    <t>U</t>
+  </si>
+  <si>
+    <t>TSQ</t>
+  </si>
+  <si>
+    <t>ADBE</t>
+  </si>
+  <si>
+    <t>CMT</t>
+  </si>
+  <si>
+    <t>GLBE</t>
+  </si>
+  <si>
+    <t>EXAS</t>
+  </si>
+  <si>
+    <t>GSHD</t>
+  </si>
+  <si>
+    <t>AZUL</t>
+  </si>
+  <si>
+    <t>KRUS</t>
+  </si>
+  <si>
+    <t>MRVL</t>
+  </si>
+  <si>
+    <t>TAYD</t>
+  </si>
+  <si>
+    <t>BELFB</t>
+  </si>
+  <si>
     <t>TYRA</t>
   </si>
   <si>
-    <t>BWMN</t>
-  </si>
-  <si>
-    <t>SMID</t>
-  </si>
-  <si>
-    <t>ERO</t>
-  </si>
-  <si>
-    <t>TMDX</t>
-  </si>
-  <si>
-    <t>RCMT</t>
-  </si>
-  <si>
-    <t>INMD</t>
-  </si>
-  <si>
-    <t>LAD</t>
-  </si>
-  <si>
-    <t>DASH</t>
-  </si>
-  <si>
-    <t>ARGX</t>
-  </si>
-  <si>
-    <t>RCM</t>
-  </si>
-  <si>
-    <t>ZEUS</t>
-  </si>
-  <si>
-    <t>PROF</t>
-  </si>
-  <si>
-    <t>EB</t>
-  </si>
-  <si>
-    <t>TGLS</t>
-  </si>
-  <si>
-    <t>YELP</t>
-  </si>
-  <si>
-    <t>ALGM</t>
-  </si>
-  <si>
-    <t>DAL</t>
-  </si>
-  <si>
-    <t>TMHC</t>
-  </si>
-  <si>
-    <t>AZUL</t>
-  </si>
-  <si>
-    <t>BWMX</t>
-  </si>
-  <si>
-    <t>DDOG</t>
-  </si>
-  <si>
-    <t>PKOH</t>
-  </si>
-  <si>
-    <t>ETNB</t>
-  </si>
-  <si>
-    <t>KBH</t>
-  </si>
-  <si>
-    <t>FRD</t>
-  </si>
-  <si>
-    <t>MATW</t>
-  </si>
-  <si>
-    <t>WPRT</t>
-  </si>
-  <si>
-    <t>PHM</t>
-  </si>
-  <si>
-    <t>MNDY</t>
-  </si>
-  <si>
-    <t>CLBR</t>
-  </si>
-  <si>
-    <t>CXM</t>
-  </si>
-  <si>
-    <t>PAM</t>
-  </si>
-  <si>
-    <t>RH</t>
-  </si>
-  <si>
-    <t>THC</t>
-  </si>
-  <si>
-    <t>DUOL</t>
-  </si>
-  <si>
-    <t>JELD</t>
-  </si>
-  <si>
-    <t>LPRO</t>
-  </si>
-  <si>
-    <t>MLP</t>
-  </si>
-  <si>
-    <t>MGNI</t>
-  </si>
-  <si>
-    <t>MRUS</t>
-  </si>
-  <si>
-    <t>ROIV</t>
-  </si>
-  <si>
-    <t>EVI</t>
-  </si>
-  <si>
-    <t>FCAP</t>
-  </si>
-  <si>
-    <t>NOVA</t>
-  </si>
-  <si>
-    <t>GTLS</t>
-  </si>
-  <si>
-    <t>SHOP</t>
-  </si>
-  <si>
-    <t>SSD</t>
-  </si>
-  <si>
-    <t>DBRG</t>
-  </si>
-  <si>
-    <t>BCC</t>
-  </si>
-  <si>
-    <t>IDCC</t>
-  </si>
-  <si>
-    <t>BOOT</t>
-  </si>
-  <si>
-    <t>WFRD</t>
-  </si>
-  <si>
-    <t>AEL</t>
-  </si>
-  <si>
-    <t>SWDAF</t>
-  </si>
-  <si>
-    <t>FTAI</t>
-  </si>
-  <si>
-    <t>HOOD</t>
-  </si>
-  <si>
-    <t>BRZE</t>
-  </si>
-  <si>
-    <t>UBER</t>
-  </si>
-  <si>
-    <t>HCCI</t>
+    <t>LZ</t>
+  </si>
+  <si>
+    <t>NWLI</t>
+  </si>
+  <si>
+    <t>AVDL</t>
+  </si>
+  <si>
+    <t>ALGT</t>
+  </si>
+  <si>
+    <t>POWL</t>
+  </si>
+  <si>
+    <t>AVGO</t>
+  </si>
+  <si>
+    <t>LTRPB</t>
+  </si>
+  <si>
+    <t>GOCO</t>
+  </si>
+  <si>
+    <t>CPS</t>
+  </si>
+  <si>
+    <t>DICE</t>
+  </si>
+  <si>
+    <t>BLU</t>
+  </si>
+  <si>
+    <t>VIST</t>
+  </si>
+  <si>
+    <t>PRG</t>
+  </si>
+  <si>
+    <t>UFPT</t>
+  </si>
+  <si>
+    <t>TTD</t>
+  </si>
+  <si>
+    <t>GBX</t>
+  </si>
+  <si>
+    <t>ONON</t>
+  </si>
+  <si>
+    <t>TSLA</t>
+  </si>
+  <si>
+    <t>SHC</t>
+  </si>
+  <si>
+    <t>DOCN</t>
   </si>
   <si>
     <t>IMRX</t>
   </si>
   <si>
-    <t>CYD</t>
-  </si>
-  <si>
-    <t>LSANF</t>
-  </si>
-  <si>
-    <t>NATR</t>
-  </si>
-  <si>
-    <t>NETI</t>
-  </si>
-  <si>
-    <t>BLD</t>
-  </si>
-  <si>
-    <t>IIVI</t>
-  </si>
-  <si>
-    <t>MANH</t>
-  </si>
-  <si>
-    <t>NCLH</t>
-  </si>
-  <si>
-    <t>PANW</t>
-  </si>
-  <si>
-    <t>OII</t>
-  </si>
-  <si>
-    <t>SSYS</t>
-  </si>
-  <si>
-    <t>MORF</t>
-  </si>
-  <si>
-    <t>BECN</t>
-  </si>
-  <si>
-    <t>MTW</t>
-  </si>
-  <si>
-    <t>MNSO</t>
-  </si>
-  <si>
-    <t>LMND</t>
-  </si>
-  <si>
-    <t>HUBS</t>
-  </si>
-  <si>
-    <t>BVH</t>
-  </si>
-  <si>
-    <t>FMS</t>
-  </si>
-  <si>
-    <t>AN</t>
-  </si>
-  <si>
-    <t>IBP</t>
-  </si>
-  <si>
-    <t>CAAP</t>
-  </si>
-  <si>
-    <t>TDC</t>
-  </si>
-  <si>
-    <t>PLAB</t>
-  </si>
-  <si>
-    <t>SRDX</t>
-  </si>
-  <si>
-    <t>TSQ</t>
-  </si>
-  <si>
-    <t>GKOS</t>
-  </si>
-  <si>
-    <t>GSHD</t>
-  </si>
-  <si>
-    <t>EXAS</t>
-  </si>
-  <si>
-    <t>LZ</t>
-  </si>
-  <si>
-    <t>GRVY</t>
-  </si>
-  <si>
-    <t>MDWT</t>
-  </si>
-  <si>
-    <t>AMWD</t>
-  </si>
-  <si>
-    <t>SGH</t>
-  </si>
-  <si>
-    <t>SHC</t>
-  </si>
-  <si>
-    <t>INTT</t>
-  </si>
-  <si>
-    <t>ADBE</t>
-  </si>
-  <si>
-    <t>CRCT</t>
-  </si>
-  <si>
-    <t>RRGB</t>
+    <t>ABCM</t>
+  </si>
+  <si>
+    <t>RILY</t>
+  </si>
+  <si>
+    <t>DV</t>
+  </si>
+  <si>
+    <t>NGMS</t>
   </si>
   <si>
     <t>ALPN</t>
   </si>
   <si>
-    <t>QS</t>
-  </si>
-  <si>
-    <t>PHAT</t>
-  </si>
-  <si>
-    <t>ETHE</t>
-  </si>
-  <si>
-    <t>AVDL</t>
-  </si>
-  <si>
-    <t>JBL</t>
-  </si>
-  <si>
-    <t>PSTG</t>
-  </si>
-  <si>
-    <t>KRYS</t>
-  </si>
-  <si>
-    <t>ACVA</t>
-  </si>
-  <si>
-    <t>GLBE</t>
-  </si>
-  <si>
-    <t>ATLC</t>
-  </si>
-  <si>
-    <t>APPF</t>
-  </si>
-  <si>
-    <t>AVGO</t>
-  </si>
-  <si>
-    <t>TDW</t>
-  </si>
-  <si>
-    <t>ALGT</t>
-  </si>
-  <si>
-    <t>ABCM</t>
-  </si>
-  <si>
-    <t>KRUS</t>
-  </si>
-  <si>
-    <t>MRVL</t>
-  </si>
-  <si>
-    <t>U</t>
-  </si>
-  <si>
-    <t>SMHI</t>
-  </si>
-  <si>
-    <t>BLU</t>
-  </si>
-  <si>
-    <t>PRG</t>
-  </si>
-  <si>
-    <t>CMT</t>
-  </si>
-  <si>
-    <t>DICE</t>
-  </si>
-  <si>
-    <t>CRMT</t>
-  </si>
-  <si>
-    <t>EXTR</t>
-  </si>
-  <si>
-    <t>CPS</t>
-  </si>
-  <si>
-    <t>FSLY</t>
-  </si>
-  <si>
-    <t>TTD</t>
-  </si>
-  <si>
     <t>RCL</t>
   </si>
   <si>
+    <t>SNBR</t>
+  </si>
+  <si>
+    <t>FLNC</t>
+  </si>
+  <si>
+    <t>SPOT</t>
+  </si>
+  <si>
+    <t>CFLT</t>
+  </si>
+  <si>
+    <t>PLPC</t>
+  </si>
+  <si>
+    <t>ACAD</t>
+  </si>
+  <si>
+    <t>SAIA</t>
+  </si>
+  <si>
     <t>STVN</t>
   </si>
   <si>
-    <t>DOCN</t>
-  </si>
-  <si>
-    <t>EBIX</t>
+    <t>RIVN</t>
+  </si>
+  <si>
+    <t>PCTTU</t>
+  </si>
+  <si>
+    <t>PCT</t>
+  </si>
+  <si>
+    <t>YPF</t>
+  </si>
+  <si>
+    <t>ACLS</t>
+  </si>
+  <si>
+    <t>ANF</t>
+  </si>
+  <si>
+    <t>VKTX</t>
+  </si>
+  <si>
+    <t>STRL</t>
+  </si>
+  <si>
+    <t>FCNCA</t>
   </si>
   <si>
     <t>RDNT</t>
   </si>
   <si>
+    <t>LI</t>
+  </si>
+  <si>
+    <t>XPEV</t>
+  </si>
+  <si>
+    <t>MHO</t>
+  </si>
+  <si>
+    <t>GBTC</t>
+  </si>
+  <si>
+    <t>SG</t>
+  </si>
+  <si>
+    <t>TARS</t>
+  </si>
+  <si>
+    <t>ISEE</t>
+  </si>
+  <si>
+    <t>OSTK</t>
+  </si>
+  <si>
+    <t>BMA</t>
+  </si>
+  <si>
+    <t>HOV</t>
+  </si>
+  <si>
+    <t>COCO</t>
+  </si>
+  <si>
+    <t>TCMD</t>
+  </si>
+  <si>
+    <t>BMEA</t>
+  </si>
+  <si>
+    <t>BHVN</t>
+  </si>
+  <si>
+    <t>GRBK</t>
+  </si>
+  <si>
+    <t>EXPI</t>
+  </si>
+  <si>
+    <t>BLDR</t>
+  </si>
+  <si>
     <t>FOR</t>
   </si>
   <si>
+    <t>CUBI</t>
+  </si>
+  <si>
+    <t>USAP</t>
+  </si>
+  <si>
+    <t>AEHR</t>
+  </si>
+  <si>
+    <t>BELFA</t>
+  </si>
+  <si>
+    <t>XP</t>
+  </si>
+  <si>
+    <t>CAMT</t>
+  </si>
+  <si>
+    <t>ARCT</t>
+  </si>
+  <si>
+    <t>IAS</t>
+  </si>
+  <si>
+    <t>XPO</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>COIN</t>
+  </si>
+  <si>
+    <t>ELF</t>
+  </si>
+  <si>
+    <t>QTRX</t>
+  </si>
+  <si>
     <t>WRLD</t>
   </si>
   <si>
-    <t>NWLI</t>
-  </si>
-  <si>
-    <t>ONON</t>
-  </si>
-  <si>
-    <t>DV</t>
-  </si>
-  <si>
-    <t>TARS</t>
-  </si>
-  <si>
-    <t>AXR</t>
-  </si>
-  <si>
-    <t>SPOT</t>
-  </si>
-  <si>
-    <t>GBX</t>
-  </si>
-  <si>
-    <t>TAYD</t>
-  </si>
-  <si>
-    <t>VIST</t>
-  </si>
-  <si>
-    <t>RILY</t>
-  </si>
-  <si>
-    <t>UFPT</t>
-  </si>
-  <si>
-    <t>SNBR</t>
-  </si>
-  <si>
-    <t>NGMS</t>
-  </si>
-  <si>
-    <t>BELFB</t>
-  </si>
-  <si>
-    <t>GOCO</t>
-  </si>
-  <si>
-    <t>POWL</t>
-  </si>
-  <si>
-    <t>MHO</t>
-  </si>
-  <si>
-    <t>ACAD</t>
-  </si>
-  <si>
-    <t>CLXT</t>
-  </si>
-  <si>
-    <t>EBON</t>
-  </si>
-  <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>STRL</t>
-  </si>
-  <si>
-    <t>ANF</t>
-  </si>
-  <si>
-    <t>CAMT</t>
-  </si>
-  <si>
-    <t>CFLT</t>
-  </si>
-  <si>
-    <t>BMA</t>
-  </si>
-  <si>
-    <t>SAIA</t>
-  </si>
-  <si>
-    <t>XP</t>
-  </si>
-  <si>
-    <t>TSLA</t>
-  </si>
-  <si>
-    <t>YPF</t>
-  </si>
-  <si>
-    <t>LI</t>
-  </si>
-  <si>
-    <t>ACLS</t>
-  </si>
-  <si>
-    <t>GBTC</t>
-  </si>
-  <si>
-    <t>PCTTU</t>
-  </si>
-  <si>
-    <t>OSTK</t>
-  </si>
-  <si>
-    <t>VKTX</t>
-  </si>
-  <si>
-    <t>SG</t>
-  </si>
-  <si>
-    <t>COCO</t>
-  </si>
-  <si>
-    <t>PCT</t>
-  </si>
-  <si>
-    <t>AEHR</t>
-  </si>
-  <si>
-    <t>TCMD</t>
-  </si>
-  <si>
-    <t>FLNC</t>
-  </si>
-  <si>
-    <t>HOV</t>
-  </si>
-  <si>
-    <t>ISEE</t>
-  </si>
-  <si>
-    <t>PLPC</t>
-  </si>
-  <si>
-    <t>BLDR</t>
-  </si>
-  <si>
-    <t>FCNCA</t>
-  </si>
-  <si>
-    <t>RIVN</t>
-  </si>
-  <si>
-    <t>BHVN</t>
-  </si>
-  <si>
-    <t>GRBK</t>
-  </si>
-  <si>
-    <t>CUBI</t>
-  </si>
-  <si>
-    <t>QTRX</t>
-  </si>
-  <si>
-    <t>LTRPB</t>
-  </si>
-  <si>
-    <t>BMEA</t>
+    <t>VRT</t>
+  </si>
+  <si>
+    <t>VECT</t>
   </si>
   <si>
     <t>GGAL</t>
   </si>
   <si>
-    <t>USAP</t>
-  </si>
-  <si>
-    <t>IAS</t>
-  </si>
-  <si>
-    <t>XPEV</t>
-  </si>
-  <si>
-    <t>EXPI</t>
-  </si>
-  <si>
-    <t>ARCT</t>
-  </si>
-  <si>
     <t>MOD</t>
   </si>
   <si>
+    <t>KDNY</t>
+  </si>
+  <si>
     <t>DKNG</t>
   </si>
   <si>
-    <t>GHL</t>
-  </si>
-  <si>
-    <t>ELF</t>
+    <t>CCL</t>
+  </si>
+  <si>
+    <t>CUK</t>
+  </si>
+  <si>
+    <t>CMPR</t>
   </si>
   <si>
     <t>APP</t>
   </si>
   <si>
+    <t>ODC</t>
+  </si>
+  <si>
+    <t>LMB</t>
+  </si>
+  <si>
+    <t>AMPH</t>
+  </si>
+  <si>
+    <t>ENVX</t>
+  </si>
+  <si>
     <t>CBAY</t>
   </si>
   <si>
+    <t>ATRO</t>
+  </si>
+  <si>
+    <t>RXRX</t>
+  </si>
+  <si>
     <t>BZH</t>
   </si>
   <si>
-    <t>XPO</t>
-  </si>
-  <si>
-    <t>ODC</t>
-  </si>
-  <si>
-    <t>BELFA</t>
-  </si>
-  <si>
-    <t>CCL</t>
-  </si>
-  <si>
-    <t>COIN</t>
-  </si>
-  <si>
-    <t>ATRO</t>
-  </si>
-  <si>
-    <t>KDNY</t>
-  </si>
-  <si>
-    <t>CUK</t>
-  </si>
-  <si>
-    <t>VRT</t>
-  </si>
-  <si>
-    <t>CMPR</t>
+    <t>IOT</t>
   </si>
   <si>
     <t>RXST</t>
   </si>
   <si>
-    <t>AMPH</t>
-  </si>
-  <si>
-    <t>IOT</t>
-  </si>
-  <si>
-    <t>VECT</t>
-  </si>
-  <si>
-    <t>LMB</t>
-  </si>
-  <si>
     <t>MSTR</t>
   </si>
   <si>
+    <t>PLTR</t>
+  </si>
+  <si>
     <t>MDB</t>
   </si>
   <si>
-    <t>RXRX</t>
+    <t>MARA</t>
+  </si>
+  <si>
+    <t>SKYW</t>
+  </si>
+  <si>
+    <t>RETA</t>
   </si>
   <si>
     <t>RXDX</t>
   </si>
   <si>
-    <t>RETA</t>
-  </si>
-  <si>
-    <t>SKYW</t>
+    <t>WEAV</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>RDFN</t>
+  </si>
+  <si>
+    <t>SDGR</t>
+  </si>
+  <si>
+    <t>RCEL</t>
+  </si>
+  <si>
+    <t>ARLO</t>
+  </si>
+  <si>
+    <t>CABA</t>
+  </si>
+  <si>
+    <t>NVDA</t>
+  </si>
+  <si>
+    <t>DFH</t>
   </si>
   <si>
     <t>W</t>
   </si>
   <si>
-    <t>ENVX</t>
-  </si>
-  <si>
-    <t>PLTR</t>
-  </si>
-  <si>
-    <t>RCEL</t>
-  </si>
-  <si>
-    <t>WEAV</t>
-  </si>
-  <si>
-    <t>ARLO</t>
-  </si>
-  <si>
-    <t>SDGR</t>
-  </si>
-  <si>
-    <t>DFH</t>
-  </si>
-  <si>
-    <t>MARA</t>
-  </si>
-  <si>
-    <t>RDFN</t>
+    <t>CIR</t>
+  </si>
+  <si>
+    <t>AI</t>
   </si>
   <si>
     <t>EDN</t>
   </si>
   <si>
-    <t>NVDA</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>CIR</t>
-  </si>
-  <si>
     <t>EH</t>
   </si>
   <si>
-    <t>AI</t>
-  </si>
-  <si>
-    <t>CABA</t>
+    <t>EVLO</t>
+  </si>
+  <si>
+    <t>INOD</t>
+  </si>
+  <si>
+    <t>ROOT</t>
+  </si>
+  <si>
+    <t>IONQ</t>
+  </si>
+  <si>
+    <t>OPRA</t>
+  </si>
+  <si>
+    <t>RIOT</t>
   </si>
   <si>
     <t>GGAAU</t>
   </si>
   <si>
-    <t>INOD</t>
-  </si>
-  <si>
-    <t>ROOT</t>
-  </si>
-  <si>
-    <t>RIOT</t>
-  </si>
-  <si>
     <t>MEOA</t>
   </si>
   <si>
-    <t>IONQ</t>
-  </si>
-  <si>
-    <t>OPRA</t>
+    <t>EYPT</t>
+  </si>
+  <si>
+    <t>UPST</t>
   </si>
   <si>
     <t>PHVS</t>
   </si>
   <si>
+    <t>SMCI</t>
+  </si>
+  <si>
+    <t>BBIO</t>
+  </si>
+  <si>
+    <t>MEOAU</t>
+  </si>
+  <si>
+    <t>IMGN</t>
+  </si>
+  <si>
     <t>SGTX</t>
-  </si>
-  <si>
-    <t>EYPT</t>
-  </si>
-  <si>
-    <t>UPST</t>
-  </si>
-  <si>
-    <t>SMCI</t>
-  </si>
-  <si>
-    <t>BBIO</t>
-  </si>
-  <si>
-    <t>MEOAU</t>
-  </si>
-  <si>
-    <t>IMGN</t>
   </si>
   <si>
     <t>CVNA</t>
@@ -1493,7 +1493,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1">
-        <v>129.5041696416307</v>
+        <v>128.8418385144505</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1">
-        <v>129.5078439438456</v>
+        <v>128.8556541746105</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1509,7 +1509,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1">
-        <v>129.5151782409129</v>
+        <v>128.9595671831721</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1517,7 +1517,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="1">
-        <v>129.5422814584203</v>
+        <v>129.0741997172067</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1525,7 +1525,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="1">
-        <v>129.546229958598</v>
+        <v>129.1621229715601</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1533,7 +1533,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="1">
-        <v>129.6156884039016</v>
+        <v>129.1786661590297</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1541,7 +1541,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="1">
-        <v>129.6809833616088</v>
+        <v>129.1884133486842</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1549,7 +1549,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="1">
-        <v>129.7396789207368</v>
+        <v>129.2540680974793</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1557,7 +1557,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="1">
-        <v>130.151241766338</v>
+        <v>129.2571143782511</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1565,7 +1565,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="1">
-        <v>130.1726682983</v>
+        <v>129.3188096352597</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1573,7 +1573,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="1">
-        <v>130.1762670920081</v>
+        <v>129.3204917730164</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1581,7 +1581,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="1">
-        <v>130.2639627350479</v>
+        <v>129.3302272878408</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1589,7 +1589,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="1">
-        <v>130.3096314529034</v>
+        <v>129.3666034014301</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1597,7 +1597,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="1">
-        <v>130.3921341076695</v>
+        <v>129.487426634305</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1605,7 +1605,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="1">
-        <v>130.4638773668084</v>
+        <v>129.4893937245052</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1613,7 +1613,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="1">
-        <v>130.5843744718494</v>
+        <v>129.4925279782775</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1621,7 +1621,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="1">
-        <v>130.745163982922</v>
+        <v>129.5557468372629</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1629,7 +1629,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="1">
-        <v>130.7567255714332</v>
+        <v>129.5722875188654</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1637,7 +1637,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="1">
-        <v>130.8687253381991</v>
+        <v>129.6257393373202</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1645,7 +1645,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="1">
-        <v>130.9410934740915</v>
+        <v>129.6553316219292</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1653,7 +1653,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="1">
-        <v>130.9779864593487</v>
+        <v>129.72982125931</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1661,7 +1661,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="1">
-        <v>130.9805943188987</v>
+        <v>129.7338095871469</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1669,7 +1669,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="1">
-        <v>131.0149450411747</v>
+        <v>129.7636734794255</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1677,7 +1677,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="1">
-        <v>131.0511188431077</v>
+        <v>129.7665234427931</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1685,7 +1685,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="1">
-        <v>131.0535645309364</v>
+        <v>129.8205806021168</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1693,7 +1693,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="1">
-        <v>131.0620902907002</v>
+        <v>129.9058089028698</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1701,7 +1701,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="1">
-        <v>131.0667126937048</v>
+        <v>129.9080589662269</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1709,7 +1709,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="1">
-        <v>131.0815020142404</v>
+        <v>129.9448220482373</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1717,7 +1717,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="1">
-        <v>131.1298412912091</v>
+        <v>130.013122092222</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1725,7 +1725,7 @@
         <v>31</v>
       </c>
       <c r="B31" s="1">
-        <v>131.1400515440482</v>
+        <v>130.0462272830487</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1733,7 +1733,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="1">
-        <v>131.1657972763583</v>
+        <v>130.1508189669505</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1741,7 +1741,7 @@
         <v>33</v>
       </c>
       <c r="B33" s="1">
-        <v>131.189530632868</v>
+        <v>130.1701778527836</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1749,7 +1749,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="1">
-        <v>131.2032748108403</v>
+        <v>130.2012318739947</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1757,7 +1757,7 @@
         <v>35</v>
       </c>
       <c r="B35" s="1">
-        <v>131.2578036008879</v>
+        <v>130.2394848516819</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1765,7 +1765,7 @@
         <v>36</v>
       </c>
       <c r="B36" s="1">
-        <v>131.2616524550107</v>
+        <v>130.3166227565701</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1773,7 +1773,7 @@
         <v>37</v>
       </c>
       <c r="B37" s="1">
-        <v>131.3581467639494</v>
+        <v>130.3244016258064</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1781,7 +1781,7 @@
         <v>38</v>
       </c>
       <c r="B38" s="1">
-        <v>131.3692720811365</v>
+        <v>130.4018084857356</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1789,7 +1789,7 @@
         <v>39</v>
       </c>
       <c r="B39" s="1">
-        <v>131.4447710369079</v>
+        <v>130.4499804997209</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1797,7 +1797,7 @@
         <v>40</v>
       </c>
       <c r="B40" s="1">
-        <v>131.5315992569605</v>
+        <v>130.4534305281069</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1805,7 +1805,7 @@
         <v>41</v>
       </c>
       <c r="B41" s="1">
-        <v>131.592916475673</v>
+        <v>130.4761080022428</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -1813,7 +1813,7 @@
         <v>42</v>
       </c>
       <c r="B42" s="1">
-        <v>131.6018868009316</v>
+        <v>130.6119230774536</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -1821,7 +1821,7 @@
         <v>43</v>
       </c>
       <c r="B43" s="1">
-        <v>131.7052664509743</v>
+        <v>130.6507983271327</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1829,7 +1829,7 @@
         <v>44</v>
       </c>
       <c r="B44" s="1">
-        <v>131.7160208021559</v>
+        <v>130.6846452065481</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1837,7 +1837,7 @@
         <v>45</v>
       </c>
       <c r="B45" s="1">
-        <v>131.8331198677894</v>
+        <v>130.7137570071686</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1845,7 +1845,7 @@
         <v>46</v>
       </c>
       <c r="B46" s="1">
-        <v>131.8353805036161</v>
+        <v>130.7264746475709</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -1853,7 +1853,7 @@
         <v>47</v>
       </c>
       <c r="B47" s="1">
-        <v>131.8413548160303</v>
+        <v>130.7363037076441</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -1861,7 +1861,7 @@
         <v>48</v>
       </c>
       <c r="B48" s="1">
-        <v>131.8522145756976</v>
+        <v>130.752981702612</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1869,7 +1869,7 @@
         <v>49</v>
       </c>
       <c r="B49" s="1">
-        <v>131.9117486318892</v>
+        <v>130.7554090838864</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1877,7 +1877,7 @@
         <v>50</v>
       </c>
       <c r="B50" s="1">
-        <v>131.9561005877736</v>
+        <v>130.797735246736</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1885,7 +1885,7 @@
         <v>51</v>
       </c>
       <c r="B51" s="1">
-        <v>131.9738219197082</v>
+        <v>130.8406668280275</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1893,7 +1893,7 @@
         <v>52</v>
       </c>
       <c r="B52" s="1">
-        <v>132.0107733209298</v>
+        <v>130.8922317118607</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1901,7 +1901,7 @@
         <v>53</v>
       </c>
       <c r="B53" s="1">
-        <v>132.1370583861681</v>
+        <v>130.9605400406355</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1909,7 +1909,7 @@
         <v>54</v>
       </c>
       <c r="B54" s="1">
-        <v>132.1592788019431</v>
+        <v>131.0332404735889</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1917,7 +1917,7 @@
         <v>55</v>
       </c>
       <c r="B55" s="1">
-        <v>132.2064516424999</v>
+        <v>131.0511188431077</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1925,7 +1925,7 @@
         <v>56</v>
       </c>
       <c r="B56" s="1">
-        <v>132.2273514596001</v>
+        <v>131.0944142963648</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1933,7 +1933,7 @@
         <v>57</v>
       </c>
       <c r="B57" s="1">
-        <v>132.2940737947747</v>
+        <v>131.1129378658328</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1941,7 +1941,7 @@
         <v>58</v>
       </c>
       <c r="B58" s="1">
-        <v>132.3070468560089</v>
+        <v>131.1198384261066</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1949,7 +1949,7 @@
         <v>59</v>
       </c>
       <c r="B59" s="1">
-        <v>132.4417219139188</v>
+        <v>131.1528715465286</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1957,7 +1957,7 @@
         <v>60</v>
       </c>
       <c r="B60" s="1">
-        <v>132.5061623227492</v>
+        <v>131.1613884924556</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1965,7 +1965,7 @@
         <v>61</v>
       </c>
       <c r="B61" s="1">
-        <v>132.5065702871506</v>
+        <v>131.1761450682014</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1973,7 +1973,7 @@
         <v>62</v>
       </c>
       <c r="B62" s="1">
-        <v>132.546431750187</v>
+        <v>131.2217491777038</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1981,7 +1981,7 @@
         <v>63</v>
       </c>
       <c r="B63" s="1">
-        <v>132.5607188098132</v>
+        <v>131.2788015348657</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1989,7 +1989,7 @@
         <v>64</v>
       </c>
       <c r="B64" s="1">
-        <v>132.5621400164259</v>
+        <v>131.29059742464</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1997,7 +1997,7 @@
         <v>65</v>
       </c>
       <c r="B65" s="1">
-        <v>132.5635407760574</v>
+        <v>131.3489952740695</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -2005,7 +2005,7 @@
         <v>66</v>
       </c>
       <c r="B66" s="1">
-        <v>132.5669008861021</v>
+        <v>131.4177534453752</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -2013,7 +2013,7 @@
         <v>67</v>
       </c>
       <c r="B67" s="1">
-        <v>132.6971959526612</v>
+        <v>131.4738915251514</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -2021,7 +2021,7 @@
         <v>68</v>
       </c>
       <c r="B68" s="1">
-        <v>132.7102118006441</v>
+        <v>131.5117688873351</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -2029,7 +2029,7 @@
         <v>69</v>
       </c>
       <c r="B69" s="1">
-        <v>132.7282262119174</v>
+        <v>131.5599533617691</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -2037,7 +2037,7 @@
         <v>70</v>
       </c>
       <c r="B70" s="1">
-        <v>132.7533229758515</v>
+        <v>131.5729226327164</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -2045,7 +2045,7 @@
         <v>71</v>
       </c>
       <c r="B71" s="1">
-        <v>132.8464630169053</v>
+        <v>131.6646478757366</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -2053,7 +2053,7 @@
         <v>72</v>
       </c>
       <c r="B72" s="1">
-        <v>132.8608687368259</v>
+        <v>131.6683093529969</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2061,7 +2061,7 @@
         <v>73</v>
       </c>
       <c r="B73" s="1">
-        <v>132.9788599874957</v>
+        <v>131.6921247062887</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -2069,7 +2069,7 @@
         <v>74</v>
       </c>
       <c r="B74" s="1">
-        <v>133.0041366159721</v>
+        <v>131.7129202798213</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -2077,7 +2077,7 @@
         <v>75</v>
       </c>
       <c r="B75" s="1">
-        <v>133.0659420131744</v>
+        <v>131.7506249114107</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -2085,7 +2085,7 @@
         <v>76</v>
       </c>
       <c r="B76" s="1">
-        <v>133.1533107418949</v>
+        <v>132.090161416676</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -2093,7 +2093,7 @@
         <v>77</v>
       </c>
       <c r="B77" s="1">
-        <v>133.252533532742</v>
+        <v>132.1289174533914</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -2101,7 +2101,7 @@
         <v>78</v>
       </c>
       <c r="B78" s="1">
-        <v>133.3318819402165</v>
+        <v>132.1881413205918</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -2109,7 +2109,7 @@
         <v>79</v>
       </c>
       <c r="B79" s="1">
-        <v>133.3568548726421</v>
+        <v>132.2472489961463</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -2117,7 +2117,7 @@
         <v>80</v>
       </c>
       <c r="B80" s="1">
-        <v>133.4221717413834</v>
+        <v>132.2623030844752</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -2125,7 +2125,7 @@
         <v>81</v>
       </c>
       <c r="B81" s="1">
-        <v>133.5832599106051</v>
+        <v>132.2770881616839</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -2133,7 +2133,7 @@
         <v>82</v>
       </c>
       <c r="B82" s="1">
-        <v>133.6094031839723</v>
+        <v>132.344175140894</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -2141,7 +2141,7 @@
         <v>83</v>
       </c>
       <c r="B83" s="1">
-        <v>133.7068860678006</v>
+        <v>132.3587879234781</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -2149,7 +2149,7 @@
         <v>84</v>
       </c>
       <c r="B84" s="1">
-        <v>133.7779560852961</v>
+        <v>132.4402992601575</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -2157,7 +2157,7 @@
         <v>85</v>
       </c>
       <c r="B85" s="1">
-        <v>133.8115269632842</v>
+        <v>132.6424068405293</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -2165,7 +2165,7 @@
         <v>86</v>
       </c>
       <c r="B86" s="1">
-        <v>133.945039704926</v>
+        <v>132.7275798955153</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -2173,7 +2173,7 @@
         <v>87</v>
       </c>
       <c r="B87" s="1">
-        <v>133.9958213364256</v>
+        <v>132.79375217751</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -2181,7 +2181,7 @@
         <v>88</v>
       </c>
       <c r="B88" s="1">
-        <v>133.9979397295292</v>
+        <v>132.8583350676296</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -2189,7 +2189,7 @@
         <v>89</v>
       </c>
       <c r="B89" s="1">
-        <v>134.0511119367338</v>
+        <v>132.8633142148722</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -2197,7 +2197,7 @@
         <v>90</v>
       </c>
       <c r="B90" s="1">
-        <v>134.1516131960995</v>
+        <v>132.8916369482114</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -2205,7 +2205,7 @@
         <v>91</v>
       </c>
       <c r="B91" s="1">
-        <v>134.1776483769894</v>
+        <v>132.904225112107</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -2213,7 +2213,7 @@
         <v>92</v>
       </c>
       <c r="B92" s="1">
-        <v>134.2536369368789</v>
+        <v>133.0443574550879</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -2221,7 +2221,7 @@
         <v>93</v>
       </c>
       <c r="B93" s="1">
-        <v>134.5794808378749</v>
+        <v>133.0627705678469</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -2229,7 +2229,7 @@
         <v>94</v>
       </c>
       <c r="B94" s="1">
-        <v>134.6523925440123</v>
+        <v>133.0676272411874</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -2237,7 +2237,7 @@
         <v>95</v>
       </c>
       <c r="B95" s="1">
-        <v>134.6549604604534</v>
+        <v>133.0815307442033</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -2245,7 +2245,7 @@
         <v>96</v>
       </c>
       <c r="B96" s="1">
-        <v>134.7091415218411</v>
+        <v>133.0834432155956</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -2253,7 +2253,7 @@
         <v>97</v>
       </c>
       <c r="B97" s="1">
-        <v>134.7675861172457</v>
+        <v>133.0840597101596</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -2261,7 +2261,7 @@
         <v>98</v>
       </c>
       <c r="B98" s="1">
-        <v>134.7999295686369</v>
+        <v>133.1632653398787</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -2269,7 +2269,7 @@
         <v>99</v>
       </c>
       <c r="B99" s="1">
-        <v>134.8063599657798</v>
+        <v>133.1932124828586</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -2277,7 +2277,7 @@
         <v>100</v>
       </c>
       <c r="B100" s="1">
-        <v>134.8097741384794</v>
+        <v>133.2223612200225</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -2285,7 +2285,7 @@
         <v>101</v>
       </c>
       <c r="B101" s="1">
-        <v>134.9378843621292</v>
+        <v>133.2731592054614</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -2293,7 +2293,7 @@
         <v>102</v>
       </c>
       <c r="B102" s="1">
-        <v>135.1678951673446</v>
+        <v>133.3192752461155</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -2301,7 +2301,7 @@
         <v>103</v>
       </c>
       <c r="B103" s="1">
-        <v>135.3247100901519</v>
+        <v>133.3684546803613</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -2309,7 +2309,7 @@
         <v>104</v>
       </c>
       <c r="B104" s="1">
-        <v>135.3797784874333</v>
+        <v>133.5371447841513</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -2317,7 +2317,7 @@
         <v>105</v>
       </c>
       <c r="B105" s="1">
-        <v>135.6943987034581</v>
+        <v>133.6051835902513</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -2325,7 +2325,7 @@
         <v>106</v>
       </c>
       <c r="B106" s="1">
-        <v>135.8714516044884</v>
+        <v>133.6164386524803</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -2333,7 +2333,7 @@
         <v>107</v>
       </c>
       <c r="B107" s="1">
-        <v>135.8803619530791</v>
+        <v>133.7015679893385</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -2341,7 +2341,7 @@
         <v>108</v>
       </c>
       <c r="B108" s="1">
-        <v>135.982199941777</v>
+        <v>133.7351266929983</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -2349,7 +2349,7 @@
         <v>109</v>
       </c>
       <c r="B109" s="1">
-        <v>136.0198934161041</v>
+        <v>133.7534013755708</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -2357,7 +2357,7 @@
         <v>110</v>
       </c>
       <c r="B110" s="1">
-        <v>136.0794957799257</v>
+        <v>133.8914131423229</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -2365,7 +2365,7 @@
         <v>111</v>
       </c>
       <c r="B111" s="1">
-        <v>136.1305420682012</v>
+        <v>133.8998698297357</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -2373,7 +2373,7 @@
         <v>112</v>
       </c>
       <c r="B112" s="1">
-        <v>136.1796449390421</v>
+        <v>133.9140724462457</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -2381,7 +2381,7 @@
         <v>113</v>
       </c>
       <c r="B113" s="1">
-        <v>136.1914353845972</v>
+        <v>133.9344621349694</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -2389,7 +2389,7 @@
         <v>114</v>
       </c>
       <c r="B114" s="1">
-        <v>136.2557517387488</v>
+        <v>134.0711538924853</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -2397,7 +2397,7 @@
         <v>115</v>
       </c>
       <c r="B115" s="1">
-        <v>136.2884174726703</v>
+        <v>134.2774978452899</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -2405,7 +2405,7 @@
         <v>116</v>
       </c>
       <c r="B116" s="1">
-        <v>136.3571606111927</v>
+        <v>134.2917374529565</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -2413,7 +2413,7 @@
         <v>117</v>
       </c>
       <c r="B117" s="1">
-        <v>136.377279041235</v>
+        <v>134.5317276677093</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -2421,7 +2421,7 @@
         <v>118</v>
       </c>
       <c r="B118" s="1">
-        <v>136.4858997175197</v>
+        <v>134.5527021709759</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -2429,7 +2429,7 @@
         <v>119</v>
       </c>
       <c r="B119" s="1">
-        <v>136.5143804284009</v>
+        <v>134.6102728017987</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -2437,7 +2437,7 @@
         <v>120</v>
       </c>
       <c r="B120" s="1">
-        <v>136.5322257842773</v>
+        <v>134.6618931575434</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -2445,7 +2445,7 @@
         <v>121</v>
       </c>
       <c r="B121" s="1">
-        <v>136.6410404452078</v>
+        <v>134.6681814640669</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -2453,7 +2453,7 @@
         <v>122</v>
       </c>
       <c r="B122" s="1">
-        <v>136.7135627119306</v>
+        <v>134.6859473975873</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -2461,7 +2461,7 @@
         <v>123</v>
       </c>
       <c r="B123" s="1">
-        <v>136.7979505946554</v>
+        <v>134.7560234718916</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -2469,7 +2469,7 @@
         <v>124</v>
       </c>
       <c r="B124" s="1">
-        <v>136.8094591640515</v>
+        <v>134.8321626036516</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -2477,7 +2477,7 @@
         <v>125</v>
       </c>
       <c r="B125" s="1">
-        <v>137.0045257630852</v>
+        <v>134.9281150433661</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -2485,7 +2485,7 @@
         <v>126</v>
       </c>
       <c r="B126" s="1">
-        <v>137.0375557707843</v>
+        <v>134.992647692306</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -2493,7 +2493,7 @@
         <v>127</v>
       </c>
       <c r="B127" s="1">
-        <v>137.1742319709355</v>
+        <v>135.1280750654117</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -2501,7 +2501,7 @@
         <v>128</v>
       </c>
       <c r="B128" s="1">
-        <v>137.2377102812316</v>
+        <v>135.1839653936904</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -2509,7 +2509,7 @@
         <v>129</v>
       </c>
       <c r="B129" s="1">
-        <v>137.2434354799232</v>
+        <v>135.2015680536632</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -2517,7 +2517,7 @@
         <v>130</v>
       </c>
       <c r="B130" s="1">
-        <v>137.2860516470156</v>
+        <v>135.3487446386117</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -2525,7 +2525,7 @@
         <v>131</v>
       </c>
       <c r="B131" s="1">
-        <v>137.3574201471104</v>
+        <v>135.3603826579791</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -2533,7 +2533,7 @@
         <v>132</v>
       </c>
       <c r="B132" s="1">
-        <v>137.6489215062962</v>
+        <v>135.6260725025899</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -2541,7 +2541,7 @@
         <v>133</v>
       </c>
       <c r="B133" s="1">
-        <v>137.8190697868271</v>
+        <v>135.8753332925177</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -2549,7 +2549,7 @@
         <v>134</v>
       </c>
       <c r="B134" s="1">
-        <v>137.9663664457507</v>
+        <v>136.0843606382982</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -2557,7 +2557,7 @@
         <v>135</v>
       </c>
       <c r="B135" s="1">
-        <v>138.1623398619516</v>
+        <v>136.153461452649</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -2565,7 +2565,7 @@
         <v>136</v>
       </c>
       <c r="B136" s="1">
-        <v>138.1787925365531</v>
+        <v>136.1568302880125</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -2573,7 +2573,7 @@
         <v>137</v>
       </c>
       <c r="B137" s="1">
-        <v>138.252964129571</v>
+        <v>136.2511674197416</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -2581,7 +2581,7 @@
         <v>138</v>
       </c>
       <c r="B138" s="1">
-        <v>138.2686004963132</v>
+        <v>136.3692061226469</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -2589,7 +2589,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="1">
-        <v>138.2959609121969</v>
+        <v>136.4724314863476</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -2597,7 +2597,7 @@
         <v>140</v>
       </c>
       <c r="B140" s="1">
-        <v>138.3364122056973</v>
+        <v>136.5898630081201</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -2605,7 +2605,7 @@
         <v>141</v>
       </c>
       <c r="B141" s="1">
-        <v>138.3628761265203</v>
+        <v>136.6599260102346</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -2613,7 +2613,7 @@
         <v>142</v>
       </c>
       <c r="B142" s="1">
-        <v>138.3921747520643</v>
+        <v>136.9102226201362</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -2621,7 +2621,7 @@
         <v>143</v>
       </c>
       <c r="B143" s="1">
-        <v>138.4268569541144</v>
+        <v>136.937592057036</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -2629,7 +2629,7 @@
         <v>144</v>
       </c>
       <c r="B144" s="1">
-        <v>138.4857070895515</v>
+        <v>137.2029525483879</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -2637,7 +2637,7 @@
         <v>145</v>
       </c>
       <c r="B145" s="1">
-        <v>138.5554492694773</v>
+        <v>137.2720616111737</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -2645,7 +2645,7 @@
         <v>146</v>
       </c>
       <c r="B146" s="1">
-        <v>138.6040974571663</v>
+        <v>137.30659375389</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -2653,7 +2653,7 @@
         <v>147</v>
       </c>
       <c r="B147" s="1">
-        <v>138.7210322862707</v>
+        <v>137.3294162431843</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -2661,7 +2661,7 @@
         <v>148</v>
       </c>
       <c r="B148" s="1">
-        <v>138.8036285618528</v>
+        <v>137.4356364370926</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -2669,7 +2669,7 @@
         <v>149</v>
       </c>
       <c r="B149" s="1">
-        <v>138.9506380652648</v>
+        <v>137.5842499055375</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -2677,7 +2677,7 @@
         <v>150</v>
       </c>
       <c r="B150" s="1">
-        <v>138.9657819868425</v>
+        <v>137.6203336428015</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -2685,7 +2685,7 @@
         <v>151</v>
       </c>
       <c r="B151" s="1">
-        <v>138.9738533995165</v>
+        <v>137.70985573285</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -2693,7 +2693,7 @@
         <v>152</v>
       </c>
       <c r="B152" s="1">
-        <v>139.0471787049581</v>
+        <v>138.157100233013</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -2701,7 +2701,7 @@
         <v>153</v>
       </c>
       <c r="B153" s="1">
-        <v>139.3514483385379</v>
+        <v>138.2114519485719</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -2709,7 +2709,7 @@
         <v>154</v>
       </c>
       <c r="B154" s="1">
-        <v>139.473113660091</v>
+        <v>138.2659150607776</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -2717,7 +2717,7 @@
         <v>155</v>
       </c>
       <c r="B155" s="1">
-        <v>139.5052901372149</v>
+        <v>138.3680107024486</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -2725,7 +2725,7 @@
         <v>156</v>
       </c>
       <c r="B156" s="1">
-        <v>139.5530960254365</v>
+        <v>138.3683271950471</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -2733,7 +2733,7 @@
         <v>157</v>
       </c>
       <c r="B157" s="1">
-        <v>139.6129619306686</v>
+        <v>138.4165200910626</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -2741,7 +2741,7 @@
         <v>158</v>
       </c>
       <c r="B158" s="1">
-        <v>139.7491917296005</v>
+        <v>138.4806178251586</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -2749,7 +2749,7 @@
         <v>159</v>
       </c>
       <c r="B159" s="1">
-        <v>139.8627620082344</v>
+        <v>138.5245130158287</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -2757,7 +2757,7 @@
         <v>160</v>
       </c>
       <c r="B160" s="1">
-        <v>139.9250453788258</v>
+        <v>138.5869038382817</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -2765,7 +2765,7 @@
         <v>161</v>
       </c>
       <c r="B161" s="1">
-        <v>140.0252524516203</v>
+        <v>138.790548646384</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -2773,7 +2773,7 @@
         <v>162</v>
       </c>
       <c r="B162" s="1">
-        <v>140.0492812086558</v>
+        <v>138.8252676037534</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -2781,7 +2781,7 @@
         <v>163</v>
       </c>
       <c r="B163" s="1">
-        <v>140.0703042997551</v>
+        <v>139.0306735924999</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -2789,7 +2789,7 @@
         <v>164</v>
       </c>
       <c r="B164" s="1">
-        <v>140.1327069464381</v>
+        <v>139.0757638213322</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -2797,7 +2797,7 @@
         <v>165</v>
       </c>
       <c r="B165" s="1">
-        <v>140.1753285683016</v>
+        <v>139.1008187274686</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -2805,7 +2805,7 @@
         <v>166</v>
       </c>
       <c r="B166" s="1">
-        <v>140.2568859897513</v>
+        <v>139.2108177691146</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -2813,7 +2813,7 @@
         <v>167</v>
       </c>
       <c r="B167" s="1">
-        <v>140.3331848340294</v>
+        <v>139.4100820864048</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -2821,7 +2821,7 @@
         <v>168</v>
       </c>
       <c r="B168" s="1">
-        <v>140.3659880481158</v>
+        <v>139.5383241409109</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -2829,7 +2829,7 @@
         <v>169</v>
       </c>
       <c r="B169" s="1">
-        <v>140.441605100127</v>
+        <v>139.5528490673355</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -2837,7 +2837,7 @@
         <v>170</v>
       </c>
       <c r="B170" s="1">
-        <v>140.4687757735928</v>
+        <v>139.5773766729721</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -2845,7 +2845,7 @@
         <v>171</v>
       </c>
       <c r="B171" s="1">
-        <v>140.4763988750906</v>
+        <v>139.5849337419351</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -2853,7 +2853,7 @@
         <v>172</v>
       </c>
       <c r="B172" s="1">
-        <v>140.5201545733592</v>
+        <v>139.7209003481764</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -2861,7 +2861,7 @@
         <v>173</v>
       </c>
       <c r="B173" s="1">
-        <v>140.5491983858017</v>
+        <v>139.8590903114757</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -2869,7 +2869,7 @@
         <v>174</v>
       </c>
       <c r="B174" s="1">
-        <v>140.6600489712138</v>
+        <v>139.9984411375982</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -2877,7 +2877,7 @@
         <v>175</v>
       </c>
       <c r="B175" s="1">
-        <v>140.8158017419343</v>
+        <v>140.002300868927</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -2885,7 +2885,7 @@
         <v>176</v>
       </c>
       <c r="B176" s="1">
-        <v>140.895600393904</v>
+        <v>140.0336240038694</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -2893,7 +2893,7 @@
         <v>177</v>
       </c>
       <c r="B177" s="1">
-        <v>140.9299930550523</v>
+        <v>140.0374472226139</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -2901,7 +2901,7 @@
         <v>178</v>
       </c>
       <c r="B178" s="1">
-        <v>140.930478172524</v>
+        <v>140.1458049237871</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -2909,7 +2909,7 @@
         <v>179</v>
       </c>
       <c r="B179" s="1">
-        <v>140.9567772123103</v>
+        <v>140.1585614462658</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -2917,7 +2917,7 @@
         <v>180</v>
       </c>
       <c r="B180" s="1">
-        <v>141.0623936715724</v>
+        <v>140.1753285683016</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -2925,7 +2925,7 @@
         <v>181</v>
       </c>
       <c r="B181" s="1">
-        <v>141.3121475469277</v>
+        <v>140.1811070515768</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -2933,7 +2933,7 @@
         <v>182</v>
       </c>
       <c r="B182" s="1">
-        <v>141.3696273804869</v>
+        <v>140.2548441357495</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -2941,7 +2941,7 @@
         <v>183</v>
       </c>
       <c r="B183" s="1">
-        <v>141.4622320104278</v>
+        <v>140.2991611482426</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -2949,7 +2949,7 @@
         <v>184</v>
       </c>
       <c r="B184" s="1">
-        <v>141.5112658511021</v>
+        <v>140.3015975689732</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -2957,7 +2957,7 @@
         <v>185</v>
       </c>
       <c r="B185" s="1">
-        <v>141.5286429455035</v>
+        <v>140.7661214545707</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -2965,7 +2965,7 @@
         <v>186</v>
       </c>
       <c r="B186" s="1">
-        <v>141.5757119060466</v>
+        <v>141.0015768298448</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -2973,7 +2973,7 @@
         <v>187</v>
       </c>
       <c r="B187" s="1">
-        <v>141.6027755463067</v>
+        <v>141.2326048854281</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -2981,7 +2981,7 @@
         <v>188</v>
       </c>
       <c r="B188" s="1">
-        <v>141.6430658677874</v>
+        <v>141.2457605171266</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -2989,7 +2989,7 @@
         <v>189</v>
       </c>
       <c r="B189" s="1">
-        <v>141.7545822615294</v>
+        <v>141.255027362186</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -2997,7 +2997,7 @@
         <v>190</v>
       </c>
       <c r="B190" s="1">
-        <v>142.3418792077396</v>
+        <v>141.3590978575441</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -3005,7 +3005,7 @@
         <v>191</v>
       </c>
       <c r="B191" s="1">
-        <v>142.4579416116289</v>
+        <v>141.5275681285418</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -3013,7 +3013,7 @@
         <v>192</v>
       </c>
       <c r="B192" s="1">
-        <v>142.672246456289</v>
+        <v>141.8633122806268</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -3021,7 +3021,7 @@
         <v>193</v>
       </c>
       <c r="B193" s="1">
-        <v>142.8191737892882</v>
+        <v>142.0374083714284</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -3029,7 +3029,7 @@
         <v>194</v>
       </c>
       <c r="B194" s="1">
-        <v>143.1831952383566</v>
+        <v>142.0566562986901</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -3037,7 +3037,7 @@
         <v>195</v>
       </c>
       <c r="B195" s="1">
-        <v>143.4318272509059</v>
+        <v>142.0699288390356</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -3045,7 +3045,7 @@
         <v>196</v>
       </c>
       <c r="B196" s="1">
-        <v>143.5289072942551</v>
+        <v>142.4801150665665</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -3053,7 +3053,7 @@
         <v>197</v>
       </c>
       <c r="B197" s="1">
-        <v>143.6165598158398</v>
+        <v>142.5277983261064</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -3061,7 +3061,7 @@
         <v>198</v>
       </c>
       <c r="B198" s="1">
-        <v>143.7889229291555</v>
+        <v>142.5791099732033</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -3069,7 +3069,7 @@
         <v>199</v>
       </c>
       <c r="B199" s="1">
-        <v>143.8617578340204</v>
+        <v>142.6575478978992</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -3077,7 +3077,7 @@
         <v>200</v>
       </c>
       <c r="B200" s="1">
-        <v>144.0897161273375</v>
+        <v>142.947661851444</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -3085,7 +3085,7 @@
         <v>201</v>
       </c>
       <c r="B201" s="1">
-        <v>144.1771117570505</v>
+        <v>142.9785131609205</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -3093,7 +3093,7 @@
         <v>202</v>
       </c>
       <c r="B202" s="1">
-        <v>144.1862384531083</v>
+        <v>142.9900420111261</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -3101,7 +3101,7 @@
         <v>203</v>
       </c>
       <c r="B203" s="1">
-        <v>144.2920244813407</v>
+        <v>143.1452118896332</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -3109,7 +3109,7 @@
         <v>204</v>
       </c>
       <c r="B204" s="1">
-        <v>144.4758057949878</v>
+        <v>143.3122389975256</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -3117,7 +3117,7 @@
         <v>205</v>
       </c>
       <c r="B205" s="1">
-        <v>144.7344888127104</v>
+        <v>143.3792457521962</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -3125,7 +3125,7 @@
         <v>206</v>
       </c>
       <c r="B206" s="1">
-        <v>144.7506357718072</v>
+        <v>143.5917415394537</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -3133,7 +3133,7 @@
         <v>207</v>
       </c>
       <c r="B207" s="1">
-        <v>144.7745608750327</v>
+        <v>143.6601432684386</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -3141,7 +3141,7 @@
         <v>208</v>
       </c>
       <c r="B208" s="1">
-        <v>144.8756809725201</v>
+        <v>144.026328370385</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -3149,7 +3149,7 @@
         <v>209</v>
       </c>
       <c r="B209" s="1">
-        <v>145.1363452320988</v>
+        <v>144.2857142866729</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -3157,7 +3157,7 @@
         <v>210</v>
       </c>
       <c r="B210" s="1">
-        <v>145.2811876163065</v>
+        <v>144.3100865234969</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -3165,7 +3165,7 @@
         <v>211</v>
       </c>
       <c r="B211" s="1">
-        <v>145.5222898953698</v>
+        <v>144.3139079130871</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -3173,7 +3173,7 @@
         <v>212</v>
       </c>
       <c r="B212" s="1">
-        <v>145.5586568980044</v>
+        <v>144.4026151359955</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -3181,7 +3181,7 @@
         <v>213</v>
       </c>
       <c r="B213" s="1">
-        <v>145.6391760263504</v>
+        <v>144.5231043531464</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -3189,7 +3189,7 @@
         <v>214</v>
       </c>
       <c r="B214" s="1">
-        <v>146.2009803093625</v>
+        <v>144.5719921245901</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -3197,7 +3197,7 @@
         <v>215</v>
       </c>
       <c r="B215" s="1">
-        <v>146.2114902536547</v>
+        <v>144.5745447768692</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -3205,7 +3205,7 @@
         <v>216</v>
       </c>
       <c r="B216" s="1">
-        <v>146.241795428917</v>
+        <v>144.7086678215231</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -3213,7 +3213,7 @@
         <v>217</v>
       </c>
       <c r="B217" s="1">
-        <v>146.3215973718292</v>
+        <v>144.750001885976</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -3221,7 +3221,7 @@
         <v>218</v>
       </c>
       <c r="B218" s="1">
-        <v>146.3561530138102</v>
+        <v>145.107215349144</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -3229,7 +3229,7 @@
         <v>219</v>
       </c>
       <c r="B219" s="1">
-        <v>146.3798949065404</v>
+        <v>145.1915621715714</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -3237,7 +3237,7 @@
         <v>220</v>
       </c>
       <c r="B220" s="1">
-        <v>146.3833731381108</v>
+        <v>145.2130689022475</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -3245,7 +3245,7 @@
         <v>221</v>
       </c>
       <c r="B221" s="1">
-        <v>146.4602246996432</v>
+        <v>145.2663788448963</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -3253,7 +3253,7 @@
         <v>222</v>
       </c>
       <c r="B222" s="1">
-        <v>146.8890423374388</v>
+        <v>145.3845312890374</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -3261,7 +3261,7 @@
         <v>223</v>
       </c>
       <c r="B223" s="1">
-        <v>146.9563941813576</v>
+        <v>145.4580950517498</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -3269,7 +3269,7 @@
         <v>224</v>
       </c>
       <c r="B224" s="1">
-        <v>147.0040493194154</v>
+        <v>145.5427046338095</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -3277,7 +3277,7 @@
         <v>225</v>
       </c>
       <c r="B225" s="1">
-        <v>147.2026916411549</v>
+        <v>145.6317923598297</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -3285,7 +3285,7 @@
         <v>226</v>
       </c>
       <c r="B226" s="1">
-        <v>147.3925610959904</v>
+        <v>145.9730067349331</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -3293,7 +3293,7 @@
         <v>227</v>
       </c>
       <c r="B227" s="1">
-        <v>147.4288005275747</v>
+        <v>146.2684867575076</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -3301,7 +3301,7 @@
         <v>228</v>
       </c>
       <c r="B228" s="1">
-        <v>147.5171538389538</v>
+        <v>146.3141348464204</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -3309,7 +3309,7 @@
         <v>229</v>
       </c>
       <c r="B229" s="1">
-        <v>147.9542697098937</v>
+        <v>146.3394803260355</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -3317,7 +3317,7 @@
         <v>230</v>
       </c>
       <c r="B230" s="1">
-        <v>148.1032779929752</v>
+        <v>147.0418590179065</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -3325,7 +3325,7 @@
         <v>231</v>
       </c>
       <c r="B231" s="1">
-        <v>148.5809303255238</v>
+        <v>147.315689092545</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -3333,7 +3333,7 @@
         <v>232</v>
       </c>
       <c r="B232" s="1">
-        <v>149.1724738286315</v>
+        <v>147.509124761938</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -3341,7 +3341,7 @@
         <v>233</v>
       </c>
       <c r="B233" s="1">
-        <v>149.2199115458932</v>
+        <v>147.7849905491536</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -3349,7 +3349,7 @@
         <v>234</v>
       </c>
       <c r="B234" s="1">
-        <v>149.2954192871287</v>
+        <v>147.8863702366639</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -3357,7 +3357,7 @@
         <v>235</v>
       </c>
       <c r="B235" s="1">
-        <v>149.3354932960714</v>
+        <v>148.0600612074248</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -3365,7 +3365,7 @@
         <v>236</v>
       </c>
       <c r="B236" s="1">
-        <v>149.5527536541209</v>
+        <v>148.1575291827062</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -3373,7 +3373,7 @@
         <v>237</v>
       </c>
       <c r="B237" s="1">
-        <v>149.6061067117918</v>
+        <v>148.3581299354677</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -3381,7 +3381,7 @@
         <v>238</v>
       </c>
       <c r="B238" s="1">
-        <v>149.6476937869576</v>
+        <v>148.4027206241158</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -3389,7 +3389,7 @@
         <v>239</v>
       </c>
       <c r="B239" s="1">
-        <v>149.8769942158445</v>
+        <v>148.5288233549315</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -3397,7 +3397,7 @@
         <v>240</v>
       </c>
       <c r="B240" s="1">
-        <v>149.9234724342617</v>
+        <v>148.6293282844493</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -3405,7 +3405,7 @@
         <v>241</v>
       </c>
       <c r="B241" s="1">
-        <v>149.9361973014729</v>
+        <v>148.7276898000317</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -3413,7 +3413,7 @@
         <v>242</v>
       </c>
       <c r="B242" s="1">
-        <v>149.9668465598864</v>
+        <v>148.9975435545929</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -3421,7 +3421,7 @@
         <v>243</v>
       </c>
       <c r="B243" s="1">
-        <v>150.4791268300617</v>
+        <v>149.2551820554246</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -3429,7 +3429,7 @@
         <v>244</v>
       </c>
       <c r="B244" s="1">
-        <v>150.5797545462281</v>
+        <v>149.5480256104833</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -3437,7 +3437,7 @@
         <v>245</v>
       </c>
       <c r="B245" s="1">
-        <v>150.8113412185874</v>
+        <v>149.5525551561696</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -3445,7 +3445,7 @@
         <v>246</v>
       </c>
       <c r="B246" s="1">
-        <v>151.0555355352025</v>
+        <v>149.7412946608287</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -3453,7 +3453,7 @@
         <v>247</v>
       </c>
       <c r="B247" s="1">
-        <v>151.3257899262815</v>
+        <v>149.7455280997524</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -3461,7 +3461,7 @@
         <v>248</v>
       </c>
       <c r="B248" s="1">
-        <v>151.4136627383538</v>
+        <v>149.9758647453591</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -3469,7 +3469,7 @@
         <v>249</v>
       </c>
       <c r="B249" s="1">
-        <v>151.6408852951403</v>
+        <v>150.163461834323</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -3477,7 +3477,7 @@
         <v>250</v>
       </c>
       <c r="B250" s="1">
-        <v>151.7688634109338</v>
+        <v>150.231407329553</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -3485,7 +3485,7 @@
         <v>251</v>
       </c>
       <c r="B251" s="1">
-        <v>151.9271519830134</v>
+        <v>150.2597636048207</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -3493,7 +3493,7 @@
         <v>252</v>
       </c>
       <c r="B252" s="1">
-        <v>151.993233406547</v>
+        <v>150.492622845637</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -3501,7 +3501,7 @@
         <v>253</v>
       </c>
       <c r="B253" s="1">
-        <v>152.0300900607988</v>
+        <v>150.6169915384697</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -3509,7 +3509,7 @@
         <v>254</v>
       </c>
       <c r="B254" s="1">
-        <v>152.0541038522017</v>
+        <v>150.6253082630952</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -3517,7 +3517,7 @@
         <v>255</v>
       </c>
       <c r="B255" s="1">
-        <v>152.3051063990928</v>
+        <v>150.7752059259454</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -3525,7 +3525,7 @@
         <v>256</v>
       </c>
       <c r="B256" s="1">
-        <v>152.7862323762343</v>
+        <v>150.8002880020072</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -3533,7 +3533,7 @@
         <v>257</v>
       </c>
       <c r="B257" s="1">
-        <v>152.8112999019221</v>
+        <v>151.0958229307504</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -3541,7 +3541,7 @@
         <v>258</v>
       </c>
       <c r="B258" s="1">
-        <v>152.8725595941941</v>
+        <v>151.4720875157562</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -3549,7 +3549,7 @@
         <v>259</v>
       </c>
       <c r="B259" s="1">
-        <v>153.3142307288645</v>
+        <v>151.530272903834</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -3557,7 +3557,7 @@
         <v>260</v>
       </c>
       <c r="B260" s="1">
-        <v>153.9490286603791</v>
+        <v>151.8405378713438</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -3565,7 +3565,7 @@
         <v>261</v>
       </c>
       <c r="B261" s="1">
-        <v>153.9570580387928</v>
+        <v>152.0138559852837</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -3573,7 +3573,7 @@
         <v>262</v>
       </c>
       <c r="B262" s="1">
-        <v>154.22770273795</v>
+        <v>152.4445239743982</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -3581,7 +3581,7 @@
         <v>263</v>
       </c>
       <c r="B263" s="1">
-        <v>154.7986553136977</v>
+        <v>152.9723042712538</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -3589,7 +3589,7 @@
         <v>264</v>
       </c>
       <c r="B264" s="1">
-        <v>155.1348577473296</v>
+        <v>153.6186168570916</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -3597,7 +3597,7 @@
         <v>265</v>
       </c>
       <c r="B265" s="1">
-        <v>155.154464663835</v>
+        <v>153.6723982007186</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -3605,7 +3605,7 @@
         <v>266</v>
       </c>
       <c r="B266" s="1">
-        <v>155.4439609630959</v>
+        <v>153.9990183026713</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -3613,7 +3613,7 @@
         <v>267</v>
       </c>
       <c r="B267" s="1">
-        <v>155.6722940343043</v>
+        <v>154.3822503406911</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -3621,7 +3621,7 @@
         <v>268</v>
       </c>
       <c r="B268" s="1">
-        <v>155.7991435937746</v>
+        <v>154.4029761858587</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -3629,7 +3629,7 @@
         <v>269</v>
       </c>
       <c r="B269" s="1">
-        <v>155.8299089258133</v>
+        <v>154.6251071266665</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -3637,7 +3637,7 @@
         <v>270</v>
       </c>
       <c r="B270" s="1">
-        <v>155.837329146129</v>
+        <v>154.8805995051191</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -3645,7 +3645,7 @@
         <v>271</v>
       </c>
       <c r="B271" s="1">
-        <v>155.862225665689</v>
+        <v>154.8861261913671</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -3653,7 +3653,7 @@
         <v>272</v>
       </c>
       <c r="B272" s="1">
-        <v>156.0321215288868</v>
+        <v>155.8126763513131</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -3661,7 +3661,7 @@
         <v>273</v>
       </c>
       <c r="B273" s="1">
-        <v>156.691976783327</v>
+        <v>155.9522572522366</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -3669,7 +3669,7 @@
         <v>274</v>
       </c>
       <c r="B274" s="1">
-        <v>157.0659587497863</v>
+        <v>156.057408752954</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -3677,7 +3677,7 @@
         <v>275</v>
       </c>
       <c r="B275" s="1">
-        <v>157.3549961866462</v>
+        <v>156.6337107524481</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -3685,7 +3685,7 @@
         <v>276</v>
       </c>
       <c r="B276" s="1">
-        <v>157.5272433008002</v>
+        <v>156.979236574529</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -3693,7 +3693,7 @@
         <v>277</v>
       </c>
       <c r="B277" s="1">
-        <v>157.5891602857081</v>
+        <v>157.2876128717563</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -3701,7 +3701,7 @@
         <v>278</v>
       </c>
       <c r="B278" s="1">
-        <v>157.6857350589274</v>
+        <v>157.5805582354955</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -3709,7 +3709,7 @@
         <v>279</v>
       </c>
       <c r="B279" s="1">
-        <v>158.6292481105189</v>
+        <v>158.5315628038649</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -3717,7 +3717,7 @@
         <v>280</v>
       </c>
       <c r="B280" s="1">
-        <v>158.7304330762128</v>
+        <v>158.7937128666052</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -3725,7 +3725,7 @@
         <v>281</v>
       </c>
       <c r="B281" s="1">
-        <v>158.8277161252772</v>
+        <v>159.1741132088299</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -3733,7 +3733,7 @@
         <v>282</v>
       </c>
       <c r="B282" s="1">
-        <v>158.860443184628</v>
+        <v>159.228682454758</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -3741,7 +3741,7 @@
         <v>283</v>
       </c>
       <c r="B283" s="1">
-        <v>159.2486625100511</v>
+        <v>159.6691538481873</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -3749,7 +3749,7 @@
         <v>284</v>
       </c>
       <c r="B284" s="1">
-        <v>159.2495998619324</v>
+        <v>159.8052336803059</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -3757,7 +3757,7 @@
         <v>285</v>
       </c>
       <c r="B285" s="1">
-        <v>159.2737535581665</v>
+        <v>160.3185316215196</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -3765,7 +3765,7 @@
         <v>286</v>
       </c>
       <c r="B286" s="1">
-        <v>159.6253757457039</v>
+        <v>160.6563359116057</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -3773,7 +3773,7 @@
         <v>287</v>
       </c>
       <c r="B287" s="1">
-        <v>159.9132493247502</v>
+        <v>160.6963734713058</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -3781,7 +3781,7 @@
         <v>288</v>
       </c>
       <c r="B288" s="1">
-        <v>160.1558497188078</v>
+        <v>160.8439863953792</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -3789,7 +3789,7 @@
         <v>289</v>
       </c>
       <c r="B289" s="1">
-        <v>160.1572191334164</v>
+        <v>160.8922175724327</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -3797,7 +3797,7 @@
         <v>290</v>
       </c>
       <c r="B290" s="1">
-        <v>160.3795810929254</v>
+        <v>161.4757060938436</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -3805,7 +3805,7 @@
         <v>291</v>
       </c>
       <c r="B291" s="1">
-        <v>161.4683344869864</v>
+        <v>161.8455249057803</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -3813,7 +3813,7 @@
         <v>292</v>
       </c>
       <c r="B292" s="1">
-        <v>161.9613894130539</v>
+        <v>161.9213773783305</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -3821,7 +3821,7 @@
         <v>293</v>
       </c>
       <c r="B293" s="1">
-        <v>162.001681167397</v>
+        <v>162.4919905167188</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -3829,7 +3829,7 @@
         <v>294</v>
       </c>
       <c r="B294" s="1">
-        <v>162.4923288318841</v>
+        <v>162.7442720400813</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -3837,7 +3837,7 @@
         <v>295</v>
       </c>
       <c r="B295" s="1">
-        <v>163.0551550039471</v>
+        <v>162.8974042011984</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -3845,7 +3845,7 @@
         <v>296</v>
       </c>
       <c r="B296" s="1">
-        <v>163.3062862203633</v>
+        <v>163.1674429312644</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -3853,7 +3853,7 @@
         <v>297</v>
       </c>
       <c r="B297" s="1">
-        <v>164.0482643519483</v>
+        <v>163.2103317871596</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -3861,7 +3861,7 @@
         <v>298</v>
       </c>
       <c r="B298" s="1">
-        <v>164.6311583671043</v>
+        <v>163.2518567240724</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -3869,7 +3869,7 @@
         <v>299</v>
       </c>
       <c r="B299" s="1">
-        <v>165.325340420979</v>
+        <v>165.0838455007558</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -3877,7 +3877,7 @@
         <v>300</v>
       </c>
       <c r="B300" s="1">
-        <v>165.3542881051458</v>
+        <v>165.2986414332055</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -3885,7 +3885,7 @@
         <v>301</v>
       </c>
       <c r="B301" s="1">
-        <v>165.3920228401474</v>
+        <v>165.7174624479791</v>
       </c>
     </row>
     <row r="302" spans="1:2">
@@ -3893,7 +3893,7 @@
         <v>302</v>
       </c>
       <c r="B302" s="1">
-        <v>165.4876222953312</v>
+        <v>166.1765459885423</v>
       </c>
     </row>
     <row r="303" spans="1:2">
@@ -3901,7 +3901,7 @@
         <v>303</v>
       </c>
       <c r="B303" s="1">
-        <v>165.8135487764482</v>
+        <v>166.2453553767382</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -3909,7 +3909,7 @@
         <v>304</v>
       </c>
       <c r="B304" s="1">
-        <v>166.2634048312421</v>
+        <v>166.2590691865597</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -3917,7 +3917,7 @@
         <v>305</v>
       </c>
       <c r="B305" s="1">
-        <v>166.606024173428</v>
+        <v>167.1716717773506</v>
       </c>
     </row>
     <row r="306" spans="1:2">
@@ -3925,7 +3925,7 @@
         <v>306</v>
       </c>
       <c r="B306" s="1">
-        <v>166.9026561958634</v>
+        <v>168.0031309919731</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -3933,7 +3933,7 @@
         <v>307</v>
       </c>
       <c r="B307" s="1">
-        <v>169.823757781311</v>
+        <v>168.0379970789592</v>
       </c>
     </row>
     <row r="308" spans="1:2">
@@ -3941,7 +3941,7 @@
         <v>308</v>
       </c>
       <c r="B308" s="1">
-        <v>169.9603663264398</v>
+        <v>168.4993846761335</v>
       </c>
     </row>
     <row r="309" spans="1:2">
@@ -3949,7 +3949,7 @@
         <v>309</v>
       </c>
       <c r="B309" s="1">
-        <v>170.1096312798175</v>
+        <v>168.7811235943186</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -3957,7 +3957,7 @@
         <v>310</v>
       </c>
       <c r="B310" s="1">
-        <v>171.0138448975905</v>
+        <v>169.7991514246532</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -3965,7 +3965,7 @@
         <v>311</v>
       </c>
       <c r="B311" s="1">
-        <v>171.0509130621659</v>
+        <v>169.9284707352504</v>
       </c>
     </row>
     <row r="312" spans="1:2">
@@ -3973,7 +3973,7 @@
         <v>312</v>
       </c>
       <c r="B312" s="1">
-        <v>171.104354796629</v>
+        <v>169.9536084477205</v>
       </c>
     </row>
     <row r="313" spans="1:2">
@@ -3981,7 +3981,7 @@
         <v>313</v>
       </c>
       <c r="B313" s="1">
-        <v>172.3800202223545</v>
+        <v>170.1413980151002</v>
       </c>
     </row>
     <row r="314" spans="1:2">
@@ -3989,7 +3989,7 @@
         <v>314</v>
       </c>
       <c r="B314" s="1">
-        <v>172.5097052467621</v>
+        <v>170.9368387755291</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -3997,7 +3997,7 @@
         <v>315</v>
       </c>
       <c r="B315" s="1">
-        <v>172.9983819872432</v>
+        <v>171.4091125053183</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -4005,7 +4005,7 @@
         <v>316</v>
       </c>
       <c r="B316" s="1">
-        <v>173.2591193859789</v>
+        <v>171.8799031805035</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -4013,7 +4013,7 @@
         <v>317</v>
       </c>
       <c r="B317" s="1">
-        <v>173.5137065002932</v>
+        <v>173.0735070953451</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -4021,7 +4021,7 @@
         <v>318</v>
       </c>
       <c r="B318" s="1">
-        <v>174.1104475125682</v>
+        <v>173.5397684771616</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -4029,7 +4029,7 @@
         <v>319</v>
       </c>
       <c r="B319" s="1">
-        <v>174.7109145043558</v>
+        <v>174.270432253941</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -4037,7 +4037,7 @@
         <v>320</v>
       </c>
       <c r="B320" s="1">
-        <v>174.8268886405918</v>
+        <v>174.312954340026</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -4045,7 +4045,7 @@
         <v>321</v>
       </c>
       <c r="B321" s="1">
-        <v>175.0072984297854</v>
+        <v>174.6701501176942</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -4053,7 +4053,7 @@
         <v>322</v>
       </c>
       <c r="B322" s="1">
-        <v>176.2071368220628</v>
+        <v>174.8399856620773</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -4061,7 +4061,7 @@
         <v>323</v>
       </c>
       <c r="B323" s="1">
-        <v>177.7401978707017</v>
+        <v>175.2058538885997</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -4069,7 +4069,7 @@
         <v>324</v>
       </c>
       <c r="B324" s="1">
-        <v>178.9708259968874</v>
+        <v>175.4941320170654</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -4077,7 +4077,7 @@
         <v>325</v>
       </c>
       <c r="B325" s="1">
-        <v>180.5145523572857</v>
+        <v>175.7294847983877</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -4085,7 +4085,7 @@
         <v>326</v>
       </c>
       <c r="B326" s="1">
-        <v>180.7115548644201</v>
+        <v>176.8898868988804</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -4093,7 +4093,7 @@
         <v>327</v>
       </c>
       <c r="B327" s="1">
-        <v>182.440083913593</v>
+        <v>177.6907565266278</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -4101,7 +4101,7 @@
         <v>328</v>
       </c>
       <c r="B328" s="1">
-        <v>184.3330769999656</v>
+        <v>179.5037574449794</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -4109,7 +4109,7 @@
         <v>329</v>
       </c>
       <c r="B329" s="1">
-        <v>185.0703827741358</v>
+        <v>180.2701622626164</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -4117,7 +4117,7 @@
         <v>330</v>
       </c>
       <c r="B330" s="1">
-        <v>186.2199793966167</v>
+        <v>182.1254149464945</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -4125,7 +4125,7 @@
         <v>331</v>
       </c>
       <c r="B331" s="1">
-        <v>189.8836087329821</v>
+        <v>183.2210512348921</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -4133,7 +4133,7 @@
         <v>332</v>
       </c>
       <c r="B332" s="1">
-        <v>190.4077779152403</v>
+        <v>185.0259131984018</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -4141,7 +4141,7 @@
         <v>333</v>
       </c>
       <c r="B333" s="1">
-        <v>190.9393094179592</v>
+        <v>188.6272703691708</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -4149,7 +4149,7 @@
         <v>334</v>
       </c>
       <c r="B334" s="1">
-        <v>190.9658384088822</v>
+        <v>189.8403916355152</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -4157,7 +4157,7 @@
         <v>335</v>
       </c>
       <c r="B335" s="1">
-        <v>191.7132577440073</v>
+        <v>190.2180863895166</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -4165,7 +4165,7 @@
         <v>336</v>
       </c>
       <c r="B336" s="1">
-        <v>191.7851683668534</v>
+        <v>190.3591316243511</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -4173,7 +4173,7 @@
         <v>337</v>
       </c>
       <c r="B337" s="1">
-        <v>191.9525936536076</v>
+        <v>190.9046495749268</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -4181,7 +4181,7 @@
         <v>338</v>
       </c>
       <c r="B338" s="1">
-        <v>192.5770778551727</v>
+        <v>191.3358092495296</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -4189,7 +4189,7 @@
         <v>339</v>
       </c>
       <c r="B339" s="1">
-        <v>192.8906642561781</v>
+        <v>192.2526722383186</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -4197,7 +4197,7 @@
         <v>340</v>
       </c>
       <c r="B340" s="1">
-        <v>194.1189724199648</v>
+        <v>193.0051279855795</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -4205,7 +4205,7 @@
         <v>341</v>
       </c>
       <c r="B341" s="1">
-        <v>194.3939312410436</v>
+        <v>194.4275386577478</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -4213,7 +4213,7 @@
         <v>342</v>
       </c>
       <c r="B342" s="1">
-        <v>195.0951526572358</v>
+        <v>194.4608533668435</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -4221,7 +4221,7 @@
         <v>343</v>
       </c>
       <c r="B343" s="1">
-        <v>195.4483659836453</v>
+        <v>194.814206693846</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -4229,7 +4229,7 @@
         <v>344</v>
       </c>
       <c r="B344" s="1">
-        <v>200.6891681168601</v>
+        <v>195.5101448557973</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -4237,7 +4237,7 @@
         <v>345</v>
       </c>
       <c r="B345" s="1">
-        <v>202.9980715578714</v>
+        <v>195.8499428123625</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -4245,7 +4245,7 @@
         <v>346</v>
       </c>
       <c r="B346" s="1">
-        <v>203.2626140744005</v>
+        <v>195.920310549299</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -4253,7 +4253,7 @@
         <v>347</v>
       </c>
       <c r="B347" s="1">
-        <v>204.9186447907497</v>
+        <v>199.1697998367451</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -4261,7 +4261,7 @@
         <v>348</v>
       </c>
       <c r="B348" s="1">
-        <v>206.4117559679477</v>
+        <v>201.3320814964501</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -4269,7 +4269,7 @@
         <v>349</v>
       </c>
       <c r="B349" s="1">
-        <v>207.2253572575597</v>
+        <v>209.0816026061022</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -4277,7 +4277,7 @@
         <v>350</v>
       </c>
       <c r="B350" s="1">
-        <v>211.4229301278048</v>
+        <v>209.3396769346014</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -4285,7 +4285,7 @@
         <v>351</v>
       </c>
       <c r="B351" s="1">
-        <v>225.1710975298583</v>
+        <v>214.8798189099198</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -4293,7 +4293,7 @@
         <v>352</v>
       </c>
       <c r="B352" s="1">
-        <v>229.8417410344738</v>
+        <v>219.2488041077693</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -4301,7 +4301,7 @@
         <v>353</v>
       </c>
       <c r="B353" s="1">
-        <v>230.7730965867328</v>
+        <v>228.9059760541909</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -4309,7 +4309,7 @@
         <v>354</v>
       </c>
       <c r="B354" s="1">
-        <v>238.4912574059636</v>
+        <v>230.1177582584917</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -4317,7 +4317,7 @@
         <v>355</v>
       </c>
       <c r="B355" s="1">
-        <v>242.8217823429158</v>
+        <v>231.8242440066284</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -4325,7 +4325,7 @@
         <v>356</v>
       </c>
       <c r="B356" s="1">
-        <v>247.6318496368786</v>
+        <v>232.1218433792926</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -4333,7 +4333,7 @@
         <v>357</v>
       </c>
       <c r="B357" s="1">
-        <v>249.1418236734584</v>
+        <v>232.789031730069</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -4341,7 +4341,7 @@
         <v>358</v>
       </c>
       <c r="B358" s="1">
-        <v>251.7635329189505</v>
+        <v>246.5086808950119</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -4349,7 +4349,7 @@
         <v>359</v>
       </c>
       <c r="B359" s="1">
-        <v>256.3798499807854</v>
+        <v>260.7997735028497</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -4357,7 +4357,7 @@
         <v>360</v>
       </c>
       <c r="B360" s="1">
-        <v>270.7130728670858</v>
+        <v>270.1776239673481</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -4365,7 +4365,7 @@
         <v>361</v>
       </c>
       <c r="B361" s="1">
-        <v>270.8382431497024</v>
+        <v>271.9297759370343</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -4373,7 +4373,7 @@
         <v>362</v>
       </c>
       <c r="B362" s="1">
-        <v>283.2107348903979</v>
+        <v>280.5909856384841</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -4381,7 +4381,7 @@
         <v>363</v>
       </c>
       <c r="B363" s="1">
-        <v>285.0310817466313</v>
+        <v>290.5314514084259</v>
       </c>
     </row>
     <row r="364" spans="1:2">
@@ -4389,7 +4389,7 @@
         <v>364</v>
       </c>
       <c r="B364" s="1">
-        <v>291.017814961712</v>
+        <v>296.7704629716832</v>
       </c>
     </row>
     <row r="365" spans="1:2">
@@ -4397,7 +4397,7 @@
         <v>365</v>
       </c>
       <c r="B365" s="1">
-        <v>296.7704629716832</v>
+        <v>299.2567598894694</v>
       </c>
     </row>
     <row r="366" spans="1:2">
@@ -4405,7 +4405,7 @@
         <v>366</v>
       </c>
       <c r="B366" s="1">
-        <v>305.5140061517363</v>
+        <v>310.3700664470173</v>
       </c>
     </row>
     <row r="367" spans="1:2">
@@ -4413,7 +4413,7 @@
         <v>367</v>
       </c>
       <c r="B367" s="1">
-        <v>508.0148366005249</v>
+        <v>506.6364912782456</v>
       </c>
     </row>
     <row r="368" spans="1:2">
@@ -4429,7 +4429,7 @@
         <v>369</v>
       </c>
       <c r="B369" s="1">
-        <v>594.5424739133769</v>
+        <v>594.6581873627458</v>
       </c>
     </row>
     <row r="370" spans="1:2">
@@ -4437,7 +4437,7 @@
         <v>370</v>
       </c>
       <c r="B370" s="1">
-        <v>638.6554122789598</v>
+        <v>648.9755435686895</v>
       </c>
     </row>
   </sheetData>

--- a/Screener/data/rs_rating_top_30.xlsx
+++ b/Screener/data/rs_rating_top_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="373">
   <si>
     <t>Symbol</t>
   </si>
@@ -22,1099 +22,1105 @@
     <t>RS Rating</t>
   </si>
   <si>
-    <t>BOSSY</t>
-  </si>
-  <si>
-    <t>ACDVF</t>
+    <t>VEL</t>
+  </si>
+  <si>
+    <t>ARGX</t>
+  </si>
+  <si>
+    <t>GXO</t>
+  </si>
+  <si>
+    <t>QTWO</t>
+  </si>
+  <si>
+    <t>BELFB</t>
+  </si>
+  <si>
+    <t>CXM</t>
+  </si>
+  <si>
+    <t>NTES</t>
+  </si>
+  <si>
+    <t>NE</t>
+  </si>
+  <si>
+    <t>ODFL</t>
+  </si>
+  <si>
+    <t>TNET</t>
+  </si>
+  <si>
+    <t>PBR</t>
+  </si>
+  <si>
+    <t>AMNB</t>
+  </si>
+  <si>
+    <t>PNR</t>
+  </si>
+  <si>
+    <t>FORM</t>
+  </si>
+  <si>
+    <t>CRH</t>
+  </si>
+  <si>
+    <t>GT</t>
+  </si>
+  <si>
+    <t>IMTX</t>
+  </si>
+  <si>
+    <t>NRP</t>
+  </si>
+  <si>
+    <t>THC</t>
+  </si>
+  <si>
+    <t>NEWR</t>
+  </si>
+  <si>
+    <t>RKT</t>
+  </si>
+  <si>
+    <t>HZO</t>
+  </si>
+  <si>
+    <t>CARG</t>
+  </si>
+  <si>
+    <t>GRFS</t>
+  </si>
+  <si>
+    <t>MLNK</t>
+  </si>
+  <si>
+    <t>SPOT</t>
+  </si>
+  <si>
+    <t>TMHC</t>
+  </si>
+  <si>
+    <t>LAD</t>
+  </si>
+  <si>
+    <t>ITRI</t>
+  </si>
+  <si>
+    <t>TWST</t>
+  </si>
+  <si>
+    <t>BATRA</t>
+  </si>
+  <si>
+    <t>ZEUS</t>
+  </si>
+  <si>
+    <t>JBL</t>
+  </si>
+  <si>
+    <t>JHX</t>
+  </si>
+  <si>
+    <t>CSTM</t>
+  </si>
+  <si>
+    <t>AEL</t>
+  </si>
+  <si>
+    <t>ERII</t>
+  </si>
+  <si>
+    <t>MLCO</t>
+  </si>
+  <si>
+    <t>INTT</t>
+  </si>
+  <si>
+    <t>AGRO</t>
+  </si>
+  <si>
+    <t>CNM</t>
+  </si>
+  <si>
+    <t>IAC</t>
+  </si>
+  <si>
+    <t>ZUO</t>
+  </si>
+  <si>
+    <t>MRVL</t>
+  </si>
+  <si>
+    <t>APG</t>
+  </si>
+  <si>
+    <t>BOOT</t>
+  </si>
+  <si>
+    <t>ADDDF</t>
+  </si>
+  <si>
+    <t>ASMIY</t>
+  </si>
+  <si>
+    <t>ARHS</t>
+  </si>
+  <si>
+    <t>EME</t>
+  </si>
+  <si>
+    <t>IMVT</t>
+  </si>
+  <si>
+    <t>TPH</t>
+  </si>
+  <si>
+    <t>EVO</t>
+  </si>
+  <si>
+    <t>ATLC</t>
+  </si>
+  <si>
+    <t>AXR</t>
+  </si>
+  <si>
+    <t>ATEC</t>
+  </si>
+  <si>
+    <t>PATK</t>
+  </si>
+  <si>
+    <t>ABR</t>
+  </si>
+  <si>
+    <t>ANGN</t>
+  </si>
+  <si>
+    <t>IDCC</t>
+  </si>
+  <si>
+    <t>CSWI</t>
+  </si>
+  <si>
+    <t>BLX</t>
+  </si>
+  <si>
+    <t>PANW</t>
+  </si>
+  <si>
+    <t>TRDA</t>
+  </si>
+  <si>
+    <t>LPRO</t>
+  </si>
+  <si>
+    <t>INBK</t>
+  </si>
+  <si>
+    <t>BPMC</t>
+  </si>
+  <si>
+    <t>GOCO</t>
+  </si>
+  <si>
+    <t>VNO</t>
+  </si>
+  <si>
+    <t>TXG</t>
+  </si>
+  <si>
+    <t>KALV</t>
+  </si>
+  <si>
+    <t>HCCI</t>
+  </si>
+  <si>
+    <t>FUTU</t>
+  </si>
+  <si>
+    <t>CCJ</t>
+  </si>
+  <si>
+    <t>ARCB</t>
+  </si>
+  <si>
+    <t>AMWD</t>
+  </si>
+  <si>
+    <t>LRCX</t>
+  </si>
+  <si>
+    <t>OII</t>
+  </si>
+  <si>
+    <t>TMDX</t>
+  </si>
+  <si>
+    <t>AAN</t>
+  </si>
+  <si>
+    <t>ZGN</t>
+  </si>
+  <si>
+    <t>RRGB</t>
+  </si>
+  <si>
+    <t>IGT</t>
+  </si>
+  <si>
+    <t>NATR</t>
+  </si>
+  <si>
+    <t>PCOR</t>
+  </si>
+  <si>
+    <t>IESC</t>
+  </si>
+  <si>
+    <t>ETHE</t>
+  </si>
+  <si>
+    <t>BELFA</t>
+  </si>
+  <si>
+    <t>RCM</t>
+  </si>
+  <si>
+    <t>BYND</t>
+  </si>
+  <si>
+    <t>MTW</t>
+  </si>
+  <si>
+    <t>MDC</t>
+  </si>
+  <si>
+    <t>CARS</t>
+  </si>
+  <si>
+    <t>ZWS</t>
+  </si>
+  <si>
+    <t>TOL</t>
+  </si>
+  <si>
+    <t>FROG</t>
+  </si>
+  <si>
+    <t>CELH</t>
+  </si>
+  <si>
+    <t>DOMO</t>
+  </si>
+  <si>
+    <t>SHAK</t>
+  </si>
+  <si>
+    <t>HROW</t>
+  </si>
+  <si>
+    <t>MNDY</t>
+  </si>
+  <si>
+    <t>BUR</t>
+  </si>
+  <si>
+    <t>FMS</t>
+  </si>
+  <si>
+    <t>GNRC</t>
+  </si>
+  <si>
+    <t>FTI</t>
+  </si>
+  <si>
+    <t>CYD</t>
+  </si>
+  <si>
+    <t>CLBR</t>
+  </si>
+  <si>
+    <t>LEGN</t>
+  </si>
+  <si>
+    <t>EXTR</t>
+  </si>
+  <si>
+    <t>CRS</t>
+  </si>
+  <si>
+    <t>ONTO</t>
+  </si>
+  <si>
+    <t>AVDX</t>
+  </si>
+  <si>
+    <t>FIVN</t>
+  </si>
+  <si>
+    <t>CSAN</t>
+  </si>
+  <si>
+    <t>RELY</t>
+  </si>
+  <si>
+    <t>CARR</t>
+  </si>
+  <si>
+    <t>ALGM</t>
+  </si>
+  <si>
+    <t>TREX</t>
+  </si>
+  <si>
+    <t>MOMO</t>
+  </si>
+  <si>
+    <t>ATI</t>
+  </si>
+  <si>
+    <t>LII</t>
+  </si>
+  <si>
+    <t>ON</t>
+  </si>
+  <si>
+    <t>PKOH</t>
+  </si>
+  <si>
+    <t>ARCO</t>
+  </si>
+  <si>
+    <t>AVGO</t>
+  </si>
+  <si>
+    <t>WPRT</t>
+  </si>
+  <si>
+    <t>BWMN</t>
+  </si>
+  <si>
+    <t>PLAB</t>
+  </si>
+  <si>
+    <t>FTAI</t>
+  </si>
+  <si>
+    <t>MLP</t>
   </si>
   <si>
     <t>KRT</t>
   </si>
   <si>
-    <t>NE</t>
-  </si>
-  <si>
-    <t>MLNK</t>
-  </si>
-  <si>
-    <t>NOW</t>
-  </si>
-  <si>
-    <t>PAG</t>
-  </si>
-  <si>
-    <t>NVT</t>
-  </si>
-  <si>
-    <t>MOMO</t>
-  </si>
-  <si>
-    <t>LZRFY</t>
-  </si>
-  <si>
-    <t>BSAC</t>
-  </si>
-  <si>
-    <t>NPO</t>
-  </si>
-  <si>
-    <t>WCC</t>
-  </si>
-  <si>
-    <t>VNT</t>
-  </si>
-  <si>
-    <t>DRD</t>
-  </si>
-  <si>
-    <t>PRI</t>
-  </si>
-  <si>
-    <t>CLH</t>
-  </si>
-  <si>
-    <t>TWST</t>
+    <t>KRNT</t>
+  </si>
+  <si>
+    <t>TGTX</t>
+  </si>
+  <si>
+    <t>KBH</t>
+  </si>
+  <si>
+    <t>NEX</t>
+  </si>
+  <si>
+    <t>KNSA</t>
+  </si>
+  <si>
+    <t>AZEK</t>
+  </si>
+  <si>
+    <t>THO</t>
+  </si>
+  <si>
+    <t>SRDX</t>
+  </si>
+  <si>
+    <t>MTH</t>
+  </si>
+  <si>
+    <t>SBOW</t>
+  </si>
+  <si>
+    <t>CFLT</t>
+  </si>
+  <si>
+    <t>ALGT</t>
+  </si>
+  <si>
+    <t>SLG</t>
+  </si>
+  <si>
+    <t>CAAP</t>
+  </si>
+  <si>
+    <t>MATX</t>
+  </si>
+  <si>
+    <t>PETQ</t>
+  </si>
+  <si>
+    <t>BECN</t>
+  </si>
+  <si>
+    <t>NYCB</t>
+  </si>
+  <si>
+    <t>VIPS</t>
+  </si>
+  <si>
+    <t>SMHI</t>
+  </si>
+  <si>
+    <t>ACCD</t>
+  </si>
+  <si>
+    <t>MGNI</t>
+  </si>
+  <si>
+    <t>KRYS</t>
+  </si>
+  <si>
+    <t>HOOD</t>
+  </si>
+  <si>
+    <t>SIBN</t>
+  </si>
+  <si>
+    <t>APPF</t>
+  </si>
+  <si>
+    <t>TYRA</t>
+  </si>
+  <si>
+    <t>AZUL</t>
+  </si>
+  <si>
+    <t>MDWT</t>
+  </si>
+  <si>
+    <t>LPG</t>
+  </si>
+  <si>
+    <t>OC</t>
+  </si>
+  <si>
+    <t>SGH</t>
+  </si>
+  <si>
+    <t>ABNB</t>
+  </si>
+  <si>
+    <t>ETRN</t>
+  </si>
+  <si>
+    <t>RDNT</t>
+  </si>
+  <si>
+    <t>BCC</t>
+  </si>
+  <si>
+    <t>ANF</t>
+  </si>
+  <si>
+    <t>TSQ</t>
+  </si>
+  <si>
+    <t>ADBE</t>
+  </si>
+  <si>
+    <t>YPF</t>
+  </si>
+  <si>
+    <t>PRO</t>
+  </si>
+  <si>
+    <t>RCMT</t>
+  </si>
+  <si>
+    <t>HELE</t>
+  </si>
+  <si>
+    <t>STVN</t>
+  </si>
+  <si>
+    <t>GSHD</t>
+  </si>
+  <si>
+    <t>YELP</t>
+  </si>
+  <si>
+    <t>FWAC</t>
+  </si>
+  <si>
+    <t>DV</t>
+  </si>
+  <si>
+    <t>CVLG</t>
+  </si>
+  <si>
+    <t>DUOL</t>
+  </si>
+  <si>
+    <t>TDC</t>
+  </si>
+  <si>
+    <t>LMND</t>
+  </si>
+  <si>
+    <t>TARS</t>
+  </si>
+  <si>
+    <t>MORF</t>
+  </si>
+  <si>
+    <t>SHC</t>
+  </si>
+  <si>
+    <t>BLD</t>
+  </si>
+  <si>
+    <t>KRUS</t>
+  </si>
+  <si>
+    <t>AVDL</t>
+  </si>
+  <si>
+    <t>SHOP</t>
+  </si>
+  <si>
+    <t>POWL</t>
+  </si>
+  <si>
+    <t>LOB</t>
+  </si>
+  <si>
+    <t>TAYD</t>
+  </si>
+  <si>
+    <t>ALGN</t>
+  </si>
+  <si>
+    <t>SSD</t>
+  </si>
+  <si>
+    <t>MRUS</t>
+  </si>
+  <si>
+    <t>UFPT</t>
+  </si>
+  <si>
+    <t>GRVY</t>
+  </si>
+  <si>
+    <t>BVH</t>
+  </si>
+  <si>
+    <t>FCNCA</t>
+  </si>
+  <si>
+    <t>RH</t>
+  </si>
+  <si>
+    <t>VIST</t>
+  </si>
+  <si>
+    <t>DDOG</t>
+  </si>
+  <si>
+    <t>IBP</t>
+  </si>
+  <si>
+    <t>FSLY</t>
+  </si>
+  <si>
+    <t>FLNC</t>
+  </si>
+  <si>
+    <t>FCAP</t>
+  </si>
+  <si>
+    <t>CRMT</t>
+  </si>
+  <si>
+    <t>SPOK</t>
+  </si>
+  <si>
+    <t>ONON</t>
+  </si>
+  <si>
+    <t>JELD</t>
+  </si>
+  <si>
+    <t>DICE</t>
+  </si>
+  <si>
+    <t>NUVL</t>
+  </si>
+  <si>
+    <t>TSLA</t>
+  </si>
+  <si>
+    <t>ERO</t>
+  </si>
+  <si>
+    <t>AUPH</t>
+  </si>
+  <si>
+    <t>HUBS</t>
+  </si>
+  <si>
+    <t>BLU</t>
+  </si>
+  <si>
+    <t>ACAD</t>
+  </si>
+  <si>
+    <t>U</t>
+  </si>
+  <si>
+    <t>ABCM</t>
+  </si>
+  <si>
+    <t>JOE</t>
+  </si>
+  <si>
+    <t>DASH</t>
+  </si>
+  <si>
+    <t>BMEA</t>
+  </si>
+  <si>
+    <t>NCLH</t>
+  </si>
+  <si>
+    <t>ISEE</t>
+  </si>
+  <si>
+    <t>BMA</t>
+  </si>
+  <si>
+    <t>EB</t>
+  </si>
+  <si>
+    <t>AFRM</t>
+  </si>
+  <si>
+    <t>GKOS</t>
+  </si>
+  <si>
+    <t>PHM</t>
+  </si>
+  <si>
+    <t>GTLS</t>
+  </si>
+  <si>
+    <t>VKTX</t>
+  </si>
+  <si>
+    <t>BWMX</t>
+  </si>
+  <si>
+    <t>RILY</t>
+  </si>
+  <si>
+    <t>NWLI</t>
+  </si>
+  <si>
+    <t>ACVA</t>
+  </si>
+  <si>
+    <t>NOA</t>
+  </si>
+  <si>
+    <t>PLPC</t>
+  </si>
+  <si>
+    <t>GBX</t>
+  </si>
+  <si>
+    <t>CVRX</t>
+  </si>
+  <si>
+    <t>EXAS</t>
+  </si>
+  <si>
+    <t>BRZE</t>
+  </si>
+  <si>
+    <t>UBER</t>
+  </si>
+  <si>
+    <t>DOCN</t>
+  </si>
+  <si>
+    <t>TDW</t>
+  </si>
+  <si>
+    <t>WFRD</t>
+  </si>
+  <si>
+    <t>MNSO</t>
+  </si>
+  <si>
+    <t>STRL</t>
+  </si>
+  <si>
+    <t>ALPN</t>
+  </si>
+  <si>
+    <t>GBTC</t>
+  </si>
+  <si>
+    <t>COCO</t>
+  </si>
+  <si>
+    <t>MOD</t>
+  </si>
+  <si>
+    <t>EDU</t>
+  </si>
+  <si>
+    <t>GGAL</t>
+  </si>
+  <si>
+    <t>NGMS</t>
+  </si>
+  <si>
+    <t>VSTM</t>
+  </si>
+  <si>
+    <t>IMRX</t>
+  </si>
+  <si>
+    <t>ELF</t>
+  </si>
+  <si>
+    <t>SAIA</t>
+  </si>
+  <si>
+    <t>TTD</t>
+  </si>
+  <si>
+    <t>LUNG</t>
+  </si>
+  <si>
+    <t>CMT</t>
+  </si>
+  <si>
+    <t>PHAT</t>
+  </si>
+  <si>
+    <t>LZ</t>
+  </si>
+  <si>
+    <t>RCL</t>
+  </si>
+  <si>
+    <t>IAS</t>
+  </si>
+  <si>
+    <t>AEHR</t>
+  </si>
+  <si>
+    <t>ROIV</t>
+  </si>
+  <si>
+    <t>ATRO</t>
+  </si>
+  <si>
+    <t>TCMD</t>
+  </si>
+  <si>
+    <t>VRT</t>
+  </si>
+  <si>
+    <t>VICR</t>
+  </si>
+  <si>
+    <t>GRBK</t>
+  </si>
+  <si>
+    <t>HOV</t>
+  </si>
+  <si>
+    <t>SG</t>
+  </si>
+  <si>
+    <t>GLBE</t>
+  </si>
+  <si>
+    <t>CUBI</t>
+  </si>
+  <si>
+    <t>VECT</t>
+  </si>
+  <si>
+    <t>RIVN</t>
+  </si>
+  <si>
+    <t>PCT</t>
+  </si>
+  <si>
+    <t>PRG</t>
+  </si>
+  <si>
+    <t>LTRPB</t>
+  </si>
+  <si>
+    <t>KDNY</t>
+  </si>
+  <si>
+    <t>XP</t>
+  </si>
+  <si>
+    <t>AMPH</t>
+  </si>
+  <si>
+    <t>MHO</t>
+  </si>
+  <si>
+    <t>BLDR</t>
+  </si>
+  <si>
+    <t>ACLS</t>
   </si>
   <si>
     <t>ROKU</t>
   </si>
   <si>
-    <t>ARCB</t>
-  </si>
-  <si>
-    <t>FTNT</t>
-  </si>
-  <si>
-    <t>NUVL</t>
-  </si>
-  <si>
-    <t>EVO</t>
-  </si>
-  <si>
-    <t>COHR</t>
-  </si>
-  <si>
-    <t>ORCL</t>
-  </si>
-  <si>
-    <t>NFLX</t>
-  </si>
-  <si>
-    <t>ALSN</t>
-  </si>
-  <si>
-    <t>APAM</t>
-  </si>
-  <si>
-    <t>ASUR</t>
-  </si>
-  <si>
-    <t>BLX</t>
-  </si>
-  <si>
-    <t>ATI</t>
-  </si>
-  <si>
-    <t>IMTX</t>
-  </si>
-  <si>
-    <t>RYI</t>
-  </si>
-  <si>
-    <t>HZO</t>
-  </si>
-  <si>
-    <t>PEGA</t>
-  </si>
-  <si>
-    <t>ARCO</t>
-  </si>
-  <si>
-    <t>ATKR</t>
-  </si>
-  <si>
-    <t>TEX</t>
-  </si>
-  <si>
-    <t>TREX</t>
-  </si>
-  <si>
-    <t>AFRM</t>
-  </si>
-  <si>
-    <t>LAD</t>
-  </si>
-  <si>
-    <t>TWN</t>
-  </si>
-  <si>
-    <t>HUBB</t>
-  </si>
-  <si>
-    <t>IGT</t>
-  </si>
-  <si>
-    <t>CVRX</t>
-  </si>
-  <si>
-    <t>VCEL</t>
-  </si>
-  <si>
-    <t>CIX</t>
-  </si>
-  <si>
-    <t>TARO</t>
-  </si>
-  <si>
-    <t>EXP</t>
-  </si>
-  <si>
-    <t>THO</t>
-  </si>
-  <si>
-    <t>SIBN</t>
-  </si>
-  <si>
-    <t>TGS</t>
-  </si>
-  <si>
-    <t>ABR</t>
-  </si>
-  <si>
-    <t>ALBY</t>
-  </si>
-  <si>
-    <t>ERII</t>
-  </si>
-  <si>
-    <t>AGRO</t>
-  </si>
-  <si>
-    <t>CVGI</t>
-  </si>
-  <si>
-    <t>CSAN</t>
-  </si>
-  <si>
-    <t>RMBS</t>
-  </si>
-  <si>
-    <t>AUPH</t>
-  </si>
-  <si>
-    <t>LEGN</t>
-  </si>
-  <si>
-    <t>PTGX</t>
-  </si>
-  <si>
-    <t>CRCT</t>
-  </si>
-  <si>
-    <t>VEL</t>
-  </si>
-  <si>
-    <t>ENVA</t>
-  </si>
-  <si>
-    <t>NEWT</t>
-  </si>
-  <si>
-    <t>ZEUS</t>
-  </si>
-  <si>
-    <t>DECK</t>
-  </si>
-  <si>
-    <t>ATEC</t>
-  </si>
-  <si>
-    <t>MNSO</t>
-  </si>
-  <si>
-    <t>GT</t>
-  </si>
-  <si>
-    <t>DHI</t>
-  </si>
-  <si>
-    <t>DXPE</t>
-  </si>
-  <si>
-    <t>CPA</t>
-  </si>
-  <si>
-    <t>VMW</t>
-  </si>
-  <si>
-    <t>CARS</t>
-  </si>
-  <si>
-    <t>ENS</t>
-  </si>
-  <si>
-    <t>SHAK</t>
-  </si>
-  <si>
-    <t>HSKA</t>
-  </si>
-  <si>
-    <t>HOFV</t>
-  </si>
-  <si>
-    <t>MYRG</t>
-  </si>
-  <si>
-    <t>CSWI</t>
-  </si>
-  <si>
-    <t>TMDX</t>
-  </si>
-  <si>
-    <t>BMI</t>
-  </si>
-  <si>
-    <t>CNM</t>
-  </si>
-  <si>
-    <t>APG</t>
-  </si>
-  <si>
-    <t>FTI</t>
-  </si>
-  <si>
-    <t>LUNG</t>
-  </si>
-  <si>
-    <t>HROW</t>
-  </si>
-  <si>
-    <t>PHG</t>
-  </si>
-  <si>
-    <t>AVDX</t>
-  </si>
-  <si>
-    <t>WPRT</t>
-  </si>
-  <si>
-    <t>RELY</t>
-  </si>
-  <si>
-    <t>MATX</t>
-  </si>
-  <si>
-    <t>RCMT</t>
-  </si>
-  <si>
-    <t>MANH</t>
-  </si>
-  <si>
-    <t>PFSI</t>
-  </si>
-  <si>
-    <t>CXM</t>
-  </si>
-  <si>
-    <t>BUR</t>
-  </si>
-  <si>
-    <t>NEOG</t>
-  </si>
-  <si>
-    <t>FIVN</t>
-  </si>
-  <si>
-    <t>INMD</t>
-  </si>
-  <si>
-    <t>NETI</t>
-  </si>
-  <si>
-    <t>USLM</t>
-  </si>
-  <si>
-    <t>RCM</t>
-  </si>
-  <si>
-    <t>CARG</t>
-  </si>
-  <si>
-    <t>OC</t>
-  </si>
-  <si>
-    <t>HELE</t>
-  </si>
-  <si>
-    <t>AZEK</t>
-  </si>
-  <si>
-    <t>EB</t>
-  </si>
-  <si>
-    <t>YELP</t>
-  </si>
-  <si>
-    <t>FROG</t>
-  </si>
-  <si>
-    <t>KRYS</t>
-  </si>
-  <si>
-    <t>PETQ</t>
-  </si>
-  <si>
-    <t>BWMN</t>
-  </si>
-  <si>
-    <t>MNDY</t>
-  </si>
-  <si>
-    <t>MLP</t>
-  </si>
-  <si>
-    <t>PKOH</t>
-  </si>
-  <si>
-    <t>PCYO</t>
-  </si>
-  <si>
-    <t>TGLS</t>
-  </si>
-  <si>
-    <t>MATW</t>
-  </si>
-  <si>
-    <t>MTH</t>
-  </si>
-  <si>
-    <t>CELH</t>
-  </si>
-  <si>
-    <t>THC</t>
-  </si>
-  <si>
-    <t>EVI</t>
-  </si>
-  <si>
-    <t>SRAD</t>
+    <t>RXRX</t>
+  </si>
+  <si>
+    <t>NIO</t>
+  </si>
+  <si>
+    <t>NVTS</t>
+  </si>
+  <si>
+    <t>EBIX</t>
+  </si>
+  <si>
+    <t>LMB</t>
+  </si>
+  <si>
+    <t>QTRX</t>
+  </si>
+  <si>
+    <t>XPO</t>
+  </si>
+  <si>
+    <t>CAMT</t>
+  </si>
+  <si>
+    <t>ODC</t>
+  </si>
+  <si>
+    <t>USAP</t>
+  </si>
+  <si>
+    <t>EDN</t>
   </si>
   <si>
     <t>CLS</t>
   </si>
   <si>
-    <t>SMID</t>
-  </si>
-  <si>
-    <t>MRUS</t>
-  </si>
-  <si>
-    <t>ERO</t>
-  </si>
-  <si>
-    <t>ALGM</t>
-  </si>
-  <si>
-    <t>IESC</t>
-  </si>
-  <si>
-    <t>PROF</t>
-  </si>
-  <si>
-    <t>NATR</t>
-  </si>
-  <si>
-    <t>MGNI</t>
-  </si>
-  <si>
-    <t>GTLS</t>
-  </si>
-  <si>
-    <t>AAN</t>
-  </si>
-  <si>
-    <t>TGTX</t>
-  </si>
-  <si>
-    <t>WMS</t>
-  </si>
-  <si>
-    <t>GHRS</t>
-  </si>
-  <si>
-    <t>ROIV</t>
-  </si>
-  <si>
-    <t>ABNB</t>
-  </si>
-  <si>
-    <t>TPH</t>
-  </si>
-  <si>
-    <t>JELD</t>
-  </si>
-  <si>
-    <t>LPRO</t>
-  </si>
-  <si>
-    <t>DBRG</t>
-  </si>
-  <si>
-    <t>DAL</t>
-  </si>
-  <si>
-    <t>ETNB</t>
-  </si>
-  <si>
-    <t>BOOT</t>
-  </si>
-  <si>
-    <t>EDU</t>
-  </si>
-  <si>
-    <t>IDCC</t>
-  </si>
-  <si>
-    <t>DDOG</t>
-  </si>
-  <si>
-    <t>DASH</t>
-  </si>
-  <si>
-    <t>CLBR</t>
-  </si>
-  <si>
-    <t>INTT</t>
-  </si>
-  <si>
-    <t>DUOL</t>
-  </si>
-  <si>
-    <t>IIVI</t>
-  </si>
-  <si>
-    <t>OII</t>
-  </si>
-  <si>
-    <t>FCAP</t>
-  </si>
-  <si>
-    <t>TOL</t>
-  </si>
-  <si>
-    <t>SSYS</t>
-  </si>
-  <si>
-    <t>HCCI</t>
-  </si>
-  <si>
-    <t>LMND</t>
-  </si>
-  <si>
-    <t>SHOP</t>
-  </si>
-  <si>
-    <t>ATLC</t>
-  </si>
-  <si>
-    <t>BCC</t>
-  </si>
-  <si>
-    <t>BRZE</t>
-  </si>
-  <si>
-    <t>TMHC</t>
-  </si>
-  <si>
-    <t>BECN</t>
-  </si>
-  <si>
-    <t>FMS</t>
-  </si>
-  <si>
-    <t>ACVA</t>
-  </si>
-  <si>
-    <t>SSD</t>
-  </si>
-  <si>
-    <t>AEL</t>
-  </si>
-  <si>
-    <t>AMWD</t>
-  </si>
-  <si>
-    <t>WFRD</t>
-  </si>
-  <si>
-    <t>BVH</t>
-  </si>
-  <si>
-    <t>CYD</t>
-  </si>
-  <si>
-    <t>RH</t>
-  </si>
-  <si>
-    <t>SWDAF</t>
-  </si>
-  <si>
-    <t>BWMX</t>
-  </si>
-  <si>
-    <t>PAM</t>
-  </si>
-  <si>
-    <t>ARGX</t>
-  </si>
-  <si>
-    <t>RRGB</t>
-  </si>
-  <si>
-    <t>HOOD</t>
-  </si>
-  <si>
-    <t>PANW</t>
-  </si>
-  <si>
-    <t>MORF</t>
-  </si>
-  <si>
-    <t>MTW</t>
-  </si>
-  <si>
-    <t>FTAI</t>
-  </si>
-  <si>
-    <t>PSTG</t>
-  </si>
-  <si>
-    <t>GKOS</t>
-  </si>
-  <si>
-    <t>PHM</t>
-  </si>
-  <si>
-    <t>KBH</t>
-  </si>
-  <si>
-    <t>TDW</t>
-  </si>
-  <si>
-    <t>LSANF</t>
-  </si>
-  <si>
-    <t>PHAT</t>
-  </si>
-  <si>
-    <t>NCLH</t>
-  </si>
-  <si>
-    <t>ANGN</t>
-  </si>
-  <si>
-    <t>UBER</t>
-  </si>
-  <si>
-    <t>HUBS</t>
-  </si>
-  <si>
-    <t>SGH</t>
+    <t>ARCT</t>
   </si>
   <si>
     <t>FRD</t>
   </si>
   <si>
-    <t>BLD</t>
-  </si>
-  <si>
-    <t>FSLY</t>
-  </si>
-  <si>
-    <t>JBL</t>
-  </si>
-  <si>
-    <t>SRDX</t>
-  </si>
-  <si>
-    <t>TDC</t>
-  </si>
-  <si>
-    <t>MDWT</t>
-  </si>
-  <si>
-    <t>APPF</t>
-  </si>
-  <si>
-    <t>EBIX</t>
-  </si>
-  <si>
-    <t>GRVY</t>
-  </si>
-  <si>
-    <t>PLAB</t>
-  </si>
-  <si>
-    <t>IBP</t>
-  </si>
-  <si>
-    <t>EXTR</t>
-  </si>
-  <si>
-    <t>CAAP</t>
-  </si>
-  <si>
-    <t>CRMT</t>
-  </si>
-  <si>
-    <t>ETHE</t>
-  </si>
-  <si>
-    <t>SMHI</t>
-  </si>
-  <si>
-    <t>AXR</t>
-  </si>
-  <si>
-    <t>U</t>
-  </si>
-  <si>
-    <t>TSQ</t>
-  </si>
-  <si>
-    <t>ADBE</t>
-  </si>
-  <si>
-    <t>CMT</t>
-  </si>
-  <si>
-    <t>GLBE</t>
-  </si>
-  <si>
-    <t>EXAS</t>
-  </si>
-  <si>
-    <t>GSHD</t>
-  </si>
-  <si>
-    <t>AZUL</t>
-  </si>
-  <si>
-    <t>KRUS</t>
-  </si>
-  <si>
-    <t>MRVL</t>
-  </si>
-  <si>
-    <t>TAYD</t>
-  </si>
-  <si>
-    <t>BELFB</t>
-  </si>
-  <si>
-    <t>TYRA</t>
-  </si>
-  <si>
-    <t>LZ</t>
-  </si>
-  <si>
-    <t>NWLI</t>
-  </si>
-  <si>
-    <t>AVDL</t>
-  </si>
-  <si>
-    <t>ALGT</t>
-  </si>
-  <si>
-    <t>POWL</t>
-  </si>
-  <si>
-    <t>AVGO</t>
-  </si>
-  <si>
-    <t>LTRPB</t>
-  </si>
-  <si>
-    <t>GOCO</t>
+    <t>DKNG</t>
+  </si>
+  <si>
+    <t>COIN</t>
+  </si>
+  <si>
+    <t>OSTK</t>
+  </si>
+  <si>
+    <t>FOR</t>
   </si>
   <si>
     <t>CPS</t>
   </si>
   <si>
-    <t>DICE</t>
-  </si>
-  <si>
-    <t>BLU</t>
-  </si>
-  <si>
-    <t>VIST</t>
-  </si>
-  <si>
-    <t>PRG</t>
-  </si>
-  <si>
-    <t>UFPT</t>
-  </si>
-  <si>
-    <t>TTD</t>
-  </si>
-  <si>
-    <t>GBX</t>
-  </si>
-  <si>
-    <t>ONON</t>
-  </si>
-  <si>
-    <t>TSLA</t>
-  </si>
-  <si>
-    <t>SHC</t>
-  </si>
-  <si>
-    <t>DOCN</t>
-  </si>
-  <si>
-    <t>IMRX</t>
-  </si>
-  <si>
-    <t>ABCM</t>
-  </si>
-  <si>
-    <t>RILY</t>
-  </si>
-  <si>
-    <t>DV</t>
-  </si>
-  <si>
-    <t>NGMS</t>
-  </si>
-  <si>
-    <t>ALPN</t>
-  </si>
-  <si>
-    <t>RCL</t>
-  </si>
-  <si>
-    <t>SNBR</t>
-  </si>
-  <si>
-    <t>FLNC</t>
-  </si>
-  <si>
-    <t>SPOT</t>
-  </si>
-  <si>
-    <t>CFLT</t>
-  </si>
-  <si>
-    <t>PLPC</t>
-  </si>
-  <si>
-    <t>ACAD</t>
-  </si>
-  <si>
-    <t>SAIA</t>
-  </si>
-  <si>
-    <t>STVN</t>
-  </si>
-  <si>
-    <t>RIVN</t>
-  </si>
-  <si>
-    <t>PCTTU</t>
-  </si>
-  <si>
-    <t>PCT</t>
-  </si>
-  <si>
-    <t>YPF</t>
-  </si>
-  <si>
-    <t>ACLS</t>
-  </si>
-  <si>
-    <t>ANF</t>
-  </si>
-  <si>
-    <t>VKTX</t>
-  </si>
-  <si>
-    <t>STRL</t>
-  </si>
-  <si>
-    <t>FCNCA</t>
-  </si>
-  <si>
-    <t>RDNT</t>
+    <t>MRNS</t>
   </si>
   <si>
     <t>LI</t>
   </si>
   <si>
+    <t>MSTR</t>
+  </si>
+  <si>
+    <t>CCL</t>
+  </si>
+  <si>
+    <t>WRLD</t>
+  </si>
+  <si>
+    <t>CMPR</t>
+  </si>
+  <si>
+    <t>CUK</t>
+  </si>
+  <si>
+    <t>EXPI</t>
+  </si>
+  <si>
+    <t>IOT</t>
+  </si>
+  <si>
+    <t>NVDA</t>
+  </si>
+  <si>
+    <t>CABA</t>
+  </si>
+  <si>
+    <t>MEOA</t>
+  </si>
+  <si>
+    <t>QS</t>
+  </si>
+  <si>
+    <t>ENVX</t>
+  </si>
+  <si>
+    <t>APP</t>
+  </si>
+  <si>
+    <t>SKYW</t>
+  </si>
+  <si>
+    <t>RXDX</t>
+  </si>
+  <si>
+    <t>DFH</t>
+  </si>
+  <si>
+    <t>MDB</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>CIR</t>
+  </si>
+  <si>
+    <t>AI</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>RXST</t>
+  </si>
+  <si>
+    <t>CBAY</t>
+  </si>
+  <si>
+    <t>OPRA</t>
+  </si>
+  <si>
+    <t>BZH</t>
+  </si>
+  <si>
+    <t>SOFI</t>
+  </si>
+  <si>
+    <t>ARLO</t>
+  </si>
+  <si>
+    <t>EVLO</t>
+  </si>
+  <si>
+    <t>SDGR</t>
+  </si>
+  <si>
+    <t>RCEL</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>RDFN</t>
+  </si>
+  <si>
+    <t>PLTR</t>
+  </si>
+  <si>
+    <t>MARA</t>
+  </si>
+  <si>
+    <t>WEAV</t>
+  </si>
+  <si>
+    <t>ROOT</t>
+  </si>
+  <si>
+    <t>MEOAU</t>
+  </si>
+  <si>
+    <t>AMSC</t>
+  </si>
+  <si>
+    <t>INOD</t>
+  </si>
+  <si>
+    <t>WW</t>
+  </si>
+  <si>
     <t>XPEV</t>
   </si>
   <si>
-    <t>MHO</t>
-  </si>
-  <si>
-    <t>GBTC</t>
-  </si>
-  <si>
-    <t>SG</t>
-  </si>
-  <si>
-    <t>TARS</t>
-  </si>
-  <si>
-    <t>ISEE</t>
-  </si>
-  <si>
-    <t>OSTK</t>
-  </si>
-  <si>
-    <t>BMA</t>
-  </si>
-  <si>
-    <t>HOV</t>
-  </si>
-  <si>
-    <t>COCO</t>
-  </si>
-  <si>
-    <t>TCMD</t>
-  </si>
-  <si>
-    <t>BMEA</t>
-  </si>
-  <si>
-    <t>BHVN</t>
-  </si>
-  <si>
-    <t>GRBK</t>
-  </si>
-  <si>
-    <t>EXPI</t>
-  </si>
-  <si>
-    <t>BLDR</t>
-  </si>
-  <si>
-    <t>FOR</t>
-  </si>
-  <si>
-    <t>CUBI</t>
-  </si>
-  <si>
-    <t>USAP</t>
-  </si>
-  <si>
-    <t>AEHR</t>
-  </si>
-  <si>
-    <t>BELFA</t>
-  </si>
-  <si>
-    <t>XP</t>
-  </si>
-  <si>
-    <t>CAMT</t>
-  </si>
-  <si>
-    <t>ARCT</t>
-  </si>
-  <si>
-    <t>IAS</t>
-  </si>
-  <si>
-    <t>XPO</t>
-  </si>
-  <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>COIN</t>
-  </si>
-  <si>
-    <t>ELF</t>
-  </si>
-  <si>
-    <t>QTRX</t>
-  </si>
-  <si>
-    <t>WRLD</t>
-  </si>
-  <si>
-    <t>VRT</t>
-  </si>
-  <si>
-    <t>VECT</t>
-  </si>
-  <si>
-    <t>GGAL</t>
-  </si>
-  <si>
-    <t>MOD</t>
-  </si>
-  <si>
-    <t>KDNY</t>
-  </si>
-  <si>
-    <t>DKNG</t>
-  </si>
-  <si>
-    <t>CCL</t>
-  </si>
-  <si>
-    <t>CUK</t>
-  </si>
-  <si>
-    <t>CMPR</t>
-  </si>
-  <si>
-    <t>APP</t>
-  </si>
-  <si>
-    <t>ODC</t>
-  </si>
-  <si>
-    <t>LMB</t>
-  </si>
-  <si>
-    <t>AMPH</t>
-  </si>
-  <si>
-    <t>ENVX</t>
-  </si>
-  <si>
-    <t>CBAY</t>
-  </si>
-  <si>
-    <t>ATRO</t>
-  </si>
-  <si>
-    <t>RXRX</t>
-  </si>
-  <si>
-    <t>BZH</t>
-  </si>
-  <si>
-    <t>IOT</t>
-  </si>
-  <si>
-    <t>RXST</t>
-  </si>
-  <si>
-    <t>MSTR</t>
-  </si>
-  <si>
-    <t>PLTR</t>
-  </si>
-  <si>
-    <t>MDB</t>
-  </si>
-  <si>
-    <t>MARA</t>
-  </si>
-  <si>
-    <t>SKYW</t>
+    <t>URGN</t>
+  </si>
+  <si>
+    <t>RIOT</t>
+  </si>
+  <si>
+    <t>CDLX</t>
+  </si>
+  <si>
+    <t>EH</t>
+  </si>
+  <si>
+    <t>SMCI</t>
   </si>
   <si>
     <t>RETA</t>
   </si>
   <si>
-    <t>RXDX</t>
-  </si>
-  <si>
-    <t>WEAV</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>RDFN</t>
-  </si>
-  <si>
-    <t>SDGR</t>
-  </si>
-  <si>
-    <t>RCEL</t>
-  </si>
-  <si>
-    <t>ARLO</t>
-  </si>
-  <si>
-    <t>CABA</t>
-  </si>
-  <si>
-    <t>NVDA</t>
-  </si>
-  <si>
-    <t>DFH</t>
-  </si>
-  <si>
-    <t>W</t>
-  </si>
-  <si>
-    <t>CIR</t>
-  </si>
-  <si>
-    <t>AI</t>
-  </si>
-  <si>
-    <t>EDN</t>
-  </si>
-  <si>
-    <t>EH</t>
-  </si>
-  <si>
-    <t>EVLO</t>
-  </si>
-  <si>
-    <t>INOD</t>
-  </si>
-  <si>
-    <t>ROOT</t>
+    <t>IMGN</t>
+  </si>
+  <si>
+    <t>EYPT</t>
+  </si>
+  <si>
+    <t>PHVS</t>
+  </si>
+  <si>
+    <t>BBIO</t>
   </si>
   <si>
     <t>IONQ</t>
   </si>
   <si>
-    <t>OPRA</t>
-  </si>
-  <si>
-    <t>RIOT</t>
-  </si>
-  <si>
-    <t>GGAAU</t>
-  </si>
-  <si>
-    <t>MEOA</t>
-  </si>
-  <si>
-    <t>EYPT</t>
+    <t>SGTX</t>
   </si>
   <si>
     <t>UPST</t>
   </si>
   <si>
-    <t>PHVS</t>
-  </si>
-  <si>
-    <t>SMCI</t>
-  </si>
-  <si>
-    <t>BBIO</t>
-  </si>
-  <si>
-    <t>MEOAU</t>
-  </si>
-  <si>
-    <t>IMGN</t>
-  </si>
-  <si>
-    <t>SGTX</t>
+    <t>AURC</t>
+  </si>
+  <si>
+    <t>AURCU</t>
   </si>
   <si>
     <t>CVNA</t>
@@ -1477,7 +1483,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B370"/>
+  <dimension ref="A1:B372"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1493,7 +1499,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1">
-        <v>128.8418385144505</v>
+        <v>132.4007905439622</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1501,7 +1507,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1">
-        <v>128.8556541746105</v>
+        <v>132.4804150761046</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1509,7 +1515,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1">
-        <v>128.9595671831721</v>
+        <v>132.5112663348856</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1517,7 +1523,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="1">
-        <v>129.0741997172067</v>
+        <v>132.5127920865168</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1525,7 +1531,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="1">
-        <v>129.1621229715601</v>
+        <v>132.5201029160819</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1533,7 +1539,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="1">
-        <v>129.1786661590297</v>
+        <v>132.5496053320778</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1541,7 +1547,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="1">
-        <v>129.1884133486842</v>
+        <v>132.5513518035199</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1549,7 +1555,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="1">
-        <v>129.2540680974793</v>
+        <v>132.5868141233705</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1557,7 +1563,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="1">
-        <v>129.2571143782511</v>
+        <v>132.6021110088814</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1565,7 +1571,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="1">
-        <v>129.3188096352597</v>
+        <v>132.6341144798291</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1573,7 +1579,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="1">
-        <v>129.3204917730164</v>
+        <v>132.6370402124867</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1581,7 +1587,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="1">
-        <v>129.3302272878408</v>
+        <v>132.6761322954118</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1589,7 +1595,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="1">
-        <v>129.3666034014301</v>
+        <v>132.7059363108922</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1597,7 +1603,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="1">
-        <v>129.487426634305</v>
+        <v>132.7579462424045</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1605,7 +1611,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="1">
-        <v>129.4893937245052</v>
+        <v>132.7802772224183</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1613,7 +1619,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="1">
-        <v>129.4925279782775</v>
+        <v>132.8072418058811</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1621,7 +1627,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="1">
-        <v>129.5557468372629</v>
+        <v>132.9888920113413</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1629,7 +1635,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="1">
-        <v>129.5722875188654</v>
+        <v>133.0103260834936</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1637,7 +1643,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="1">
-        <v>129.6257393373202</v>
+        <v>133.0190818791018</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1645,7 +1651,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="1">
-        <v>129.6553316219292</v>
+        <v>133.0395323920544</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1653,7 +1659,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="1">
-        <v>129.72982125931</v>
+        <v>133.0911338518626</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1661,7 +1667,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="1">
-        <v>129.7338095871469</v>
+        <v>133.1151961244593</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1669,7 +1675,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="1">
-        <v>129.7636734794255</v>
+        <v>133.2737579595212</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1677,7 +1683,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="1">
-        <v>129.7665234427931</v>
+        <v>133.3150128157422</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1685,7 +1691,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="1">
-        <v>129.8205806021168</v>
+        <v>133.3308046370113</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1693,7 +1699,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="1">
-        <v>129.9058089028698</v>
+        <v>133.5077832914707</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1701,7 +1707,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="1">
-        <v>129.9080589662269</v>
+        <v>133.5122565754114</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1709,7 +1715,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="1">
-        <v>129.9448220482373</v>
+        <v>133.5122787335413</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1717,7 +1723,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="1">
-        <v>130.013122092222</v>
+        <v>133.6748790423493</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1725,7 +1731,7 @@
         <v>31</v>
       </c>
       <c r="B31" s="1">
-        <v>130.0462272830487</v>
+        <v>133.6851306504516</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1733,7 +1739,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="1">
-        <v>130.1508189669505</v>
+        <v>133.7415564082201</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1741,7 +1747,7 @@
         <v>33</v>
       </c>
       <c r="B33" s="1">
-        <v>130.1701778527836</v>
+        <v>133.7703153172166</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1749,7 +1755,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="1">
-        <v>130.2012318739947</v>
+        <v>133.8220223489677</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1757,7 +1763,7 @@
         <v>35</v>
       </c>
       <c r="B35" s="1">
-        <v>130.2394848516819</v>
+        <v>133.8390295725521</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1765,7 +1771,7 @@
         <v>36</v>
       </c>
       <c r="B36" s="1">
-        <v>130.3166227565701</v>
+        <v>133.8649845864822</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1773,7 +1779,7 @@
         <v>37</v>
       </c>
       <c r="B37" s="1">
-        <v>130.3244016258064</v>
+        <v>133.8993498886863</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1781,7 +1787,7 @@
         <v>38</v>
       </c>
       <c r="B38" s="1">
-        <v>130.4018084857356</v>
+        <v>133.927745362198</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1789,7 +1795,7 @@
         <v>39</v>
       </c>
       <c r="B39" s="1">
-        <v>130.4499804997209</v>
+        <v>134.0278751657921</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1797,7 +1803,7 @@
         <v>40</v>
       </c>
       <c r="B40" s="1">
-        <v>130.4534305281069</v>
+        <v>134.0511420543813</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1805,7 +1811,7 @@
         <v>41</v>
       </c>
       <c r="B41" s="1">
-        <v>130.4761080022428</v>
+        <v>134.0927143052481</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -1813,7 +1819,7 @@
         <v>42</v>
       </c>
       <c r="B42" s="1">
-        <v>130.6119230774536</v>
+        <v>134.0992295488805</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -1821,7 +1827,7 @@
         <v>43</v>
       </c>
       <c r="B43" s="1">
-        <v>130.6507983271327</v>
+        <v>134.1570176188948</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1829,7 +1835,7 @@
         <v>44</v>
       </c>
       <c r="B44" s="1">
-        <v>130.6846452065481</v>
+        <v>134.2086963302984</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1837,7 +1843,7 @@
         <v>45</v>
       </c>
       <c r="B45" s="1">
-        <v>130.7137570071686</v>
+        <v>134.2858865551888</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1845,7 +1851,7 @@
         <v>46</v>
       </c>
       <c r="B46" s="1">
-        <v>130.7264746475709</v>
+        <v>134.3080848914423</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -1853,7 +1859,7 @@
         <v>47</v>
       </c>
       <c r="B47" s="1">
-        <v>130.7363037076441</v>
+        <v>134.314475745087</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -1861,7 +1867,7 @@
         <v>48</v>
       </c>
       <c r="B48" s="1">
-        <v>130.752981702612</v>
+        <v>134.3295306531838</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1869,7 +1875,7 @@
         <v>49</v>
       </c>
       <c r="B49" s="1">
-        <v>130.7554090838864</v>
+        <v>134.3643850699513</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1877,7 +1883,7 @@
         <v>50</v>
       </c>
       <c r="B50" s="1">
-        <v>130.797735246736</v>
+        <v>134.3824538807993</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1885,7 +1891,7 @@
         <v>51</v>
       </c>
       <c r="B51" s="1">
-        <v>130.8406668280275</v>
+        <v>134.3884700644366</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1893,7 +1899,7 @@
         <v>52</v>
       </c>
       <c r="B52" s="1">
-        <v>130.8922317118607</v>
+        <v>134.4071464186206</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1901,7 +1907,7 @@
         <v>53</v>
       </c>
       <c r="B53" s="1">
-        <v>130.9605400406355</v>
+        <v>134.454367680038</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1909,7 +1915,7 @@
         <v>54</v>
       </c>
       <c r="B54" s="1">
-        <v>131.0332404735889</v>
+        <v>134.6527947970509</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1917,7 +1923,7 @@
         <v>55</v>
       </c>
       <c r="B55" s="1">
-        <v>131.0511188431077</v>
+        <v>134.7217690934657</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1925,7 +1931,7 @@
         <v>56</v>
       </c>
       <c r="B56" s="1">
-        <v>131.0944142963648</v>
+        <v>134.7364636298082</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1933,7 +1939,7 @@
         <v>57</v>
       </c>
       <c r="B57" s="1">
-        <v>131.1129378658328</v>
+        <v>134.8953217040526</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1941,7 +1947,7 @@
         <v>58</v>
       </c>
       <c r="B58" s="1">
-        <v>131.1198384261066</v>
+        <v>134.9332486243562</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1949,7 +1955,7 @@
         <v>59</v>
       </c>
       <c r="B59" s="1">
-        <v>131.1528715465286</v>
+        <v>134.9343014815151</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1957,7 +1963,7 @@
         <v>60</v>
       </c>
       <c r="B60" s="1">
-        <v>131.1613884924556</v>
+        <v>134.9875048167602</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1965,7 +1971,7 @@
         <v>61</v>
       </c>
       <c r="B61" s="1">
-        <v>131.1761450682014</v>
+        <v>135.4186105577915</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1973,7 +1979,7 @@
         <v>62</v>
       </c>
       <c r="B62" s="1">
-        <v>131.2217491777038</v>
+        <v>135.437913776069</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1981,7 +1987,7 @@
         <v>63</v>
       </c>
       <c r="B63" s="1">
-        <v>131.2788015348657</v>
+        <v>135.4400902817853</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1989,7 +1995,7 @@
         <v>64</v>
       </c>
       <c r="B64" s="1">
-        <v>131.29059742464</v>
+        <v>135.4600862620373</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1997,7 +2003,7 @@
         <v>65</v>
       </c>
       <c r="B65" s="1">
-        <v>131.3489952740695</v>
+        <v>135.5158023774854</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -2005,7 +2011,7 @@
         <v>66</v>
       </c>
       <c r="B66" s="1">
-        <v>131.4177534453752</v>
+        <v>135.5970034853857</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -2013,7 +2019,7 @@
         <v>67</v>
       </c>
       <c r="B67" s="1">
-        <v>131.4738915251514</v>
+        <v>135.6100430517713</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -2021,7 +2027,7 @@
         <v>68</v>
       </c>
       <c r="B68" s="1">
-        <v>131.5117688873351</v>
+        <v>135.621238057134</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -2029,7 +2035,7 @@
         <v>69</v>
       </c>
       <c r="B69" s="1">
-        <v>131.5599533617691</v>
+        <v>135.6674834685106</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -2037,7 +2043,7 @@
         <v>70</v>
       </c>
       <c r="B70" s="1">
-        <v>131.5729226327164</v>
+        <v>135.6950767119968</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -2045,7 +2051,7 @@
         <v>71</v>
       </c>
       <c r="B71" s="1">
-        <v>131.6646478757366</v>
+        <v>135.8316055247269</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -2053,7 +2059,7 @@
         <v>72</v>
       </c>
       <c r="B72" s="1">
-        <v>131.6683093529969</v>
+        <v>135.9572991274033</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2061,7 +2067,7 @@
         <v>73</v>
       </c>
       <c r="B73" s="1">
-        <v>131.6921247062887</v>
+        <v>136.0003796518638</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -2069,7 +2075,7 @@
         <v>74</v>
       </c>
       <c r="B74" s="1">
-        <v>131.7129202798213</v>
+        <v>136.0409539148886</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -2077,7 +2083,7 @@
         <v>75</v>
       </c>
       <c r="B75" s="1">
-        <v>131.7506249114107</v>
+        <v>136.1365227108579</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -2085,7 +2091,7 @@
         <v>76</v>
       </c>
       <c r="B76" s="1">
-        <v>132.090161416676</v>
+        <v>136.2020114899823</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -2093,7 +2099,7 @@
         <v>77</v>
       </c>
       <c r="B77" s="1">
-        <v>132.1289174533914</v>
+        <v>136.2120059214713</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -2101,7 +2107,7 @@
         <v>78</v>
       </c>
       <c r="B78" s="1">
-        <v>132.1881413205918</v>
+        <v>136.2603888711199</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -2109,7 +2115,7 @@
         <v>79</v>
       </c>
       <c r="B79" s="1">
-        <v>132.2472489961463</v>
+        <v>136.2832721840746</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -2117,7 +2123,7 @@
         <v>80</v>
       </c>
       <c r="B80" s="1">
-        <v>132.2623030844752</v>
+        <v>136.4452698276311</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -2125,7 +2131,7 @@
         <v>81</v>
       </c>
       <c r="B81" s="1">
-        <v>132.2770881616839</v>
+        <v>136.5503867216219</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -2133,7 +2139,7 @@
         <v>82</v>
       </c>
       <c r="B82" s="1">
-        <v>132.344175140894</v>
+        <v>136.5836952936951</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -2141,7 +2147,7 @@
         <v>83</v>
       </c>
       <c r="B83" s="1">
-        <v>132.3587879234781</v>
+        <v>136.7061975357752</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -2149,7 +2155,7 @@
         <v>84</v>
       </c>
       <c r="B84" s="1">
-        <v>132.4402992601575</v>
+        <v>136.7497833782667</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -2157,7 +2163,7 @@
         <v>85</v>
       </c>
       <c r="B85" s="1">
-        <v>132.6424068405293</v>
+        <v>136.966968980622</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -2165,7 +2171,7 @@
         <v>86</v>
       </c>
       <c r="B86" s="1">
-        <v>132.7275798955153</v>
+        <v>136.9925352707035</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -2173,7 +2179,7 @@
         <v>87</v>
       </c>
       <c r="B87" s="1">
-        <v>132.79375217751</v>
+        <v>137.1737063670191</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -2181,7 +2187,7 @@
         <v>88</v>
       </c>
       <c r="B88" s="1">
-        <v>132.8583350676296</v>
+        <v>137.1758747856475</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -2189,7 +2195,7 @@
         <v>89</v>
       </c>
       <c r="B89" s="1">
-        <v>132.8633142148722</v>
+        <v>137.2528848106885</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -2197,7 +2203,7 @@
         <v>90</v>
       </c>
       <c r="B90" s="1">
-        <v>132.8916369482114</v>
+        <v>137.2578947401826</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -2205,7 +2211,7 @@
         <v>91</v>
       </c>
       <c r="B91" s="1">
-        <v>132.904225112107</v>
+        <v>137.3058302835671</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -2213,7 +2219,7 @@
         <v>92</v>
       </c>
       <c r="B92" s="1">
-        <v>133.0443574550879</v>
+        <v>137.3197207895626</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -2221,7 +2227,7 @@
         <v>93</v>
       </c>
       <c r="B93" s="1">
-        <v>133.0627705678469</v>
+        <v>137.3209600504246</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -2229,7 +2235,7 @@
         <v>94</v>
       </c>
       <c r="B94" s="1">
-        <v>133.0676272411874</v>
+        <v>137.3950090621339</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -2237,7 +2243,7 @@
         <v>95</v>
       </c>
       <c r="B95" s="1">
-        <v>133.0815307442033</v>
+        <v>137.4776868672812</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -2245,7 +2251,7 @@
         <v>96</v>
       </c>
       <c r="B96" s="1">
-        <v>133.0834432155956</v>
+        <v>137.6168911600767</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -2253,7 +2259,7 @@
         <v>97</v>
       </c>
       <c r="B97" s="1">
-        <v>133.0840597101596</v>
+        <v>137.6931366215514</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -2261,7 +2267,7 @@
         <v>98</v>
       </c>
       <c r="B98" s="1">
-        <v>133.1632653398787</v>
+        <v>137.7039096910782</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -2269,7 +2275,7 @@
         <v>99</v>
       </c>
       <c r="B99" s="1">
-        <v>133.1932124828586</v>
+        <v>137.8051790211989</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -2277,7 +2283,7 @@
         <v>100</v>
       </c>
       <c r="B100" s="1">
-        <v>133.2223612200225</v>
+        <v>137.8431035528049</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -2285,7 +2291,7 @@
         <v>101</v>
       </c>
       <c r="B101" s="1">
-        <v>133.2731592054614</v>
+        <v>137.852799556219</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -2293,7 +2299,7 @@
         <v>102</v>
       </c>
       <c r="B102" s="1">
-        <v>133.3192752461155</v>
+        <v>137.8622315151369</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -2301,7 +2307,7 @@
         <v>103</v>
       </c>
       <c r="B103" s="1">
-        <v>133.3684546803613</v>
+        <v>137.9516076787338</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -2309,7 +2315,7 @@
         <v>104</v>
       </c>
       <c r="B104" s="1">
-        <v>133.5371447841513</v>
+        <v>138.0086240615975</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -2317,7 +2323,7 @@
         <v>105</v>
       </c>
       <c r="B105" s="1">
-        <v>133.6051835902513</v>
+        <v>138.0469576251635</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -2325,7 +2331,7 @@
         <v>106</v>
       </c>
       <c r="B106" s="1">
-        <v>133.6164386524803</v>
+        <v>138.0836151683447</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -2333,7 +2339,7 @@
         <v>107</v>
       </c>
       <c r="B107" s="1">
-        <v>133.7015679893385</v>
+        <v>138.1336033461019</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -2341,7 +2347,7 @@
         <v>108</v>
       </c>
       <c r="B108" s="1">
-        <v>133.7351266929983</v>
+        <v>138.2251659760368</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -2349,7 +2355,7 @@
         <v>109</v>
       </c>
       <c r="B109" s="1">
-        <v>133.7534013755708</v>
+        <v>138.2292759605373</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -2357,7 +2363,7 @@
         <v>110</v>
       </c>
       <c r="B110" s="1">
-        <v>133.8914131423229</v>
+        <v>138.270652207015</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -2365,7 +2371,7 @@
         <v>111</v>
       </c>
       <c r="B111" s="1">
-        <v>133.8998698297357</v>
+        <v>138.4862618209644</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -2373,7 +2379,7 @@
         <v>112</v>
       </c>
       <c r="B112" s="1">
-        <v>133.9140724462457</v>
+        <v>138.5104684789908</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -2381,7 +2387,7 @@
         <v>113</v>
       </c>
       <c r="B113" s="1">
-        <v>133.9344621349694</v>
+        <v>138.5869484828926</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -2389,7 +2395,7 @@
         <v>114</v>
       </c>
       <c r="B114" s="1">
-        <v>134.0711538924853</v>
+        <v>138.6456162984568</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -2397,7 +2403,7 @@
         <v>115</v>
       </c>
       <c r="B115" s="1">
-        <v>134.2774978452899</v>
+        <v>138.6523379055089</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -2405,7 +2411,7 @@
         <v>116</v>
       </c>
       <c r="B116" s="1">
-        <v>134.2917374529565</v>
+        <v>138.9800622636457</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -2413,7 +2419,7 @@
         <v>117</v>
       </c>
       <c r="B117" s="1">
-        <v>134.5317276677093</v>
+        <v>138.9872154111048</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -2421,7 +2427,7 @@
         <v>118</v>
       </c>
       <c r="B118" s="1">
-        <v>134.5527021709759</v>
+        <v>139.1903097788406</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -2429,7 +2435,7 @@
         <v>119</v>
       </c>
       <c r="B119" s="1">
-        <v>134.6102728017987</v>
+        <v>139.2151448999379</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -2437,7 +2443,7 @@
         <v>120</v>
       </c>
       <c r="B120" s="1">
-        <v>134.6618931575434</v>
+        <v>139.3051283992682</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -2445,7 +2451,7 @@
         <v>121</v>
       </c>
       <c r="B121" s="1">
-        <v>134.6681814640669</v>
+        <v>139.3603578559304</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -2453,7 +2459,7 @@
         <v>122</v>
       </c>
       <c r="B122" s="1">
-        <v>134.6859473975873</v>
+        <v>139.4311498054925</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -2461,7 +2467,7 @@
         <v>123</v>
       </c>
       <c r="B123" s="1">
-        <v>134.7560234718916</v>
+        <v>139.4616192467998</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -2469,7 +2475,7 @@
         <v>124</v>
       </c>
       <c r="B124" s="1">
-        <v>134.8321626036516</v>
+        <v>139.5005397948665</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -2477,7 +2483,7 @@
         <v>125</v>
       </c>
       <c r="B125" s="1">
-        <v>134.9281150433661</v>
+        <v>139.6089159169267</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -2485,7 +2491,7 @@
         <v>126</v>
       </c>
       <c r="B126" s="1">
-        <v>134.992647692306</v>
+        <v>139.6360267235086</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -2493,7 +2499,7 @@
         <v>127</v>
       </c>
       <c r="B127" s="1">
-        <v>135.1280750654117</v>
+        <v>139.6547016794254</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -2501,7 +2507,7 @@
         <v>128</v>
       </c>
       <c r="B128" s="1">
-        <v>135.1839653936904</v>
+        <v>139.7036204714511</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -2509,7 +2515,7 @@
         <v>129</v>
       </c>
       <c r="B129" s="1">
-        <v>135.2015680536632</v>
+        <v>139.9255955039752</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -2517,7 +2523,7 @@
         <v>130</v>
       </c>
       <c r="B130" s="1">
-        <v>135.3487446386117</v>
+        <v>139.9336183503602</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -2525,7 +2531,7 @@
         <v>131</v>
       </c>
       <c r="B131" s="1">
-        <v>135.3603826579791</v>
+        <v>139.971794165633</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -2533,7 +2539,7 @@
         <v>132</v>
       </c>
       <c r="B132" s="1">
-        <v>135.6260725025899</v>
+        <v>139.9780317569823</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -2541,7 +2547,7 @@
         <v>133</v>
       </c>
       <c r="B133" s="1">
-        <v>135.8753332925177</v>
+        <v>140.0693153977036</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -2549,7 +2555,7 @@
         <v>134</v>
       </c>
       <c r="B134" s="1">
-        <v>136.0843606382982</v>
+        <v>140.2083779788335</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -2557,7 +2563,7 @@
         <v>135</v>
       </c>
       <c r="B135" s="1">
-        <v>136.153461452649</v>
+        <v>140.2491428624017</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -2565,7 +2571,7 @@
         <v>136</v>
       </c>
       <c r="B136" s="1">
-        <v>136.1568302880125</v>
+        <v>140.3218076484469</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -2573,7 +2579,7 @@
         <v>137</v>
       </c>
       <c r="B137" s="1">
-        <v>136.2511674197416</v>
+        <v>140.3778476354272</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -2581,7 +2587,7 @@
         <v>138</v>
       </c>
       <c r="B138" s="1">
-        <v>136.3692061226469</v>
+        <v>140.4100649758641</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -2589,7 +2595,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="1">
-        <v>136.4724314863476</v>
+        <v>140.4870794589808</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -2597,7 +2603,7 @@
         <v>140</v>
       </c>
       <c r="B140" s="1">
-        <v>136.5898630081201</v>
+        <v>140.6881026102848</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -2605,7 +2611,7 @@
         <v>141</v>
       </c>
       <c r="B141" s="1">
-        <v>136.6599260102346</v>
+        <v>140.8694707054412</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -2613,7 +2619,7 @@
         <v>142</v>
       </c>
       <c r="B142" s="1">
-        <v>136.9102226201362</v>
+        <v>140.8776195219346</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -2621,7 +2627,7 @@
         <v>143</v>
       </c>
       <c r="B143" s="1">
-        <v>136.937592057036</v>
+        <v>140.9861198298039</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -2629,7 +2635,7 @@
         <v>144</v>
       </c>
       <c r="B144" s="1">
-        <v>137.2029525483879</v>
+        <v>141.0169691289964</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -2637,7 +2643,7 @@
         <v>145</v>
       </c>
       <c r="B145" s="1">
-        <v>137.2720616111737</v>
+        <v>141.1628132987778</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -2645,7 +2651,7 @@
         <v>146</v>
       </c>
       <c r="B146" s="1">
-        <v>137.30659375389</v>
+        <v>141.2335407808444</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -2653,7 +2659,7 @@
         <v>147</v>
       </c>
       <c r="B147" s="1">
-        <v>137.3294162431843</v>
+        <v>141.3126199421443</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -2661,7 +2667,7 @@
         <v>148</v>
       </c>
       <c r="B148" s="1">
-        <v>137.4356364370926</v>
+        <v>141.3781568468242</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -2669,7 +2675,7 @@
         <v>149</v>
       </c>
       <c r="B149" s="1">
-        <v>137.5842499055375</v>
+        <v>141.3977580125558</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -2677,7 +2683,7 @@
         <v>150</v>
       </c>
       <c r="B150" s="1">
-        <v>137.6203336428015</v>
+        <v>141.4043040609131</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -2685,7 +2691,7 @@
         <v>151</v>
       </c>
       <c r="B151" s="1">
-        <v>137.70985573285</v>
+        <v>141.4911810273597</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -2693,7 +2699,7 @@
         <v>152</v>
       </c>
       <c r="B152" s="1">
-        <v>138.157100233013</v>
+        <v>141.5392021759902</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -2701,7 +2707,7 @@
         <v>153</v>
       </c>
       <c r="B153" s="1">
-        <v>138.2114519485719</v>
+        <v>141.6307902256906</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -2709,7 +2715,7 @@
         <v>154</v>
       </c>
       <c r="B154" s="1">
-        <v>138.2659150607776</v>
+        <v>141.8134417858823</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -2717,7 +2723,7 @@
         <v>155</v>
       </c>
       <c r="B155" s="1">
-        <v>138.3680107024486</v>
+        <v>141.8728480770349</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -2725,7 +2731,7 @@
         <v>156</v>
       </c>
       <c r="B156" s="1">
-        <v>138.3683271950471</v>
+        <v>142.116655594302</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -2733,7 +2739,7 @@
         <v>157</v>
       </c>
       <c r="B157" s="1">
-        <v>138.4165200910626</v>
+        <v>142.3481489406314</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -2741,7 +2747,7 @@
         <v>158</v>
       </c>
       <c r="B158" s="1">
-        <v>138.4806178251586</v>
+        <v>142.6893547982875</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -2749,7 +2755,7 @@
         <v>159</v>
       </c>
       <c r="B159" s="1">
-        <v>138.5245130158287</v>
+        <v>142.7290526873688</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -2757,7 +2763,7 @@
         <v>160</v>
       </c>
       <c r="B160" s="1">
-        <v>138.5869038382817</v>
+        <v>143.2401845482591</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -2765,7 +2771,7 @@
         <v>161</v>
       </c>
       <c r="B161" s="1">
-        <v>138.790548646384</v>
+        <v>143.3997481698588</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -2773,7 +2779,7 @@
         <v>162</v>
       </c>
       <c r="B162" s="1">
-        <v>138.8252676037534</v>
+        <v>143.438543036451</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -2781,7 +2787,7 @@
         <v>163</v>
       </c>
       <c r="B163" s="1">
-        <v>139.0306735924999</v>
+        <v>143.5475586451923</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -2789,7 +2795,7 @@
         <v>164</v>
       </c>
       <c r="B164" s="1">
-        <v>139.0757638213322</v>
+        <v>143.8026779054654</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -2797,7 +2803,7 @@
         <v>165</v>
       </c>
       <c r="B165" s="1">
-        <v>139.1008187274686</v>
+        <v>144.0716189625236</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -2805,7 +2811,7 @@
         <v>166</v>
       </c>
       <c r="B166" s="1">
-        <v>139.2108177691146</v>
+        <v>144.1319410014956</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -2813,7 +2819,7 @@
         <v>167</v>
       </c>
       <c r="B167" s="1">
-        <v>139.4100820864048</v>
+        <v>144.1963885214341</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -2821,7 +2827,7 @@
         <v>168</v>
       </c>
       <c r="B168" s="1">
-        <v>139.5383241409109</v>
+        <v>144.2791675123891</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -2829,7 +2835,7 @@
         <v>169</v>
       </c>
       <c r="B169" s="1">
-        <v>139.5528490673355</v>
+        <v>144.4718744849314</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -2837,7 +2843,7 @@
         <v>170</v>
       </c>
       <c r="B170" s="1">
-        <v>139.5773766729721</v>
+        <v>144.8184654798222</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -2845,7 +2851,7 @@
         <v>171</v>
       </c>
       <c r="B171" s="1">
-        <v>139.5849337419351</v>
+        <v>144.8630208083272</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -2853,7 +2859,7 @@
         <v>172</v>
       </c>
       <c r="B172" s="1">
-        <v>139.7209003481764</v>
+        <v>144.928615612203</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -2861,7 +2867,7 @@
         <v>173</v>
       </c>
       <c r="B173" s="1">
-        <v>139.8590903114757</v>
+        <v>145.0136218302808</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -2869,7 +2875,7 @@
         <v>174</v>
       </c>
       <c r="B174" s="1">
-        <v>139.9984411375982</v>
+        <v>145.1612748638886</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -2877,7 +2883,7 @@
         <v>175</v>
       </c>
       <c r="B175" s="1">
-        <v>140.002300868927</v>
+        <v>145.2084229647402</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -2885,7 +2891,7 @@
         <v>176</v>
       </c>
       <c r="B176" s="1">
-        <v>140.0336240038694</v>
+        <v>145.5658292896496</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -2893,7 +2899,7 @@
         <v>177</v>
       </c>
       <c r="B177" s="1">
-        <v>140.0374472226139</v>
+        <v>145.6228391540445</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -2901,7 +2907,7 @@
         <v>178</v>
       </c>
       <c r="B178" s="1">
-        <v>140.1458049237871</v>
+        <v>145.648767647391</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -2909,7 +2915,7 @@
         <v>179</v>
       </c>
       <c r="B179" s="1">
-        <v>140.1585614462658</v>
+        <v>145.7404666625909</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -2917,7 +2923,7 @@
         <v>180</v>
       </c>
       <c r="B180" s="1">
-        <v>140.1753285683016</v>
+        <v>145.8019098650194</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -2925,7 +2931,7 @@
         <v>181</v>
       </c>
       <c r="B181" s="1">
-        <v>140.1811070515768</v>
+        <v>145.8357115105397</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -2933,7 +2939,7 @@
         <v>182</v>
       </c>
       <c r="B182" s="1">
-        <v>140.2548441357495</v>
+        <v>145.8814235137661</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -2941,7 +2947,7 @@
         <v>183</v>
       </c>
       <c r="B183" s="1">
-        <v>140.2991611482426</v>
+        <v>145.9432272628523</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -2949,7 +2955,7 @@
         <v>184</v>
       </c>
       <c r="B184" s="1">
-        <v>140.3015975689732</v>
+        <v>146.0692318393389</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -2957,7 +2963,7 @@
         <v>185</v>
       </c>
       <c r="B185" s="1">
-        <v>140.7661214545707</v>
+        <v>146.0875810638839</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -2965,7 +2971,7 @@
         <v>186</v>
       </c>
       <c r="B186" s="1">
-        <v>141.0015768298448</v>
+        <v>146.2265941665691</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -2973,7 +2979,7 @@
         <v>187</v>
       </c>
       <c r="B187" s="1">
-        <v>141.2326048854281</v>
+        <v>146.2554998881015</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -2981,7 +2987,7 @@
         <v>188</v>
       </c>
       <c r="B188" s="1">
-        <v>141.2457605171266</v>
+        <v>146.3903220514274</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -2989,7 +2995,7 @@
         <v>189</v>
       </c>
       <c r="B189" s="1">
-        <v>141.255027362186</v>
+        <v>146.7646285964503</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -2997,7 +3003,7 @@
         <v>190</v>
       </c>
       <c r="B190" s="1">
-        <v>141.3590978575441</v>
+        <v>146.7747721284895</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -3005,7 +3011,7 @@
         <v>191</v>
       </c>
       <c r="B191" s="1">
-        <v>141.5275681285418</v>
+        <v>146.9294642710316</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -3013,7 +3019,7 @@
         <v>192</v>
       </c>
       <c r="B192" s="1">
-        <v>141.8633122806268</v>
+        <v>146.9563139258987</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -3021,7 +3027,7 @@
         <v>193</v>
       </c>
       <c r="B193" s="1">
-        <v>142.0374083714284</v>
+        <v>147.1853238240748</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -3029,7 +3035,7 @@
         <v>194</v>
       </c>
       <c r="B194" s="1">
-        <v>142.0566562986901</v>
+        <v>147.1931321770412</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -3037,7 +3043,7 @@
         <v>195</v>
       </c>
       <c r="B195" s="1">
-        <v>142.0699288390356</v>
+        <v>147.2081153468109</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -3045,7 +3051,7 @@
         <v>196</v>
       </c>
       <c r="B196" s="1">
-        <v>142.4801150665665</v>
+        <v>147.3970861802402</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -3053,7 +3059,7 @@
         <v>197</v>
       </c>
       <c r="B197" s="1">
-        <v>142.5277983261064</v>
+        <v>147.4134210541201</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -3061,7 +3067,7 @@
         <v>198</v>
       </c>
       <c r="B198" s="1">
-        <v>142.5791099732033</v>
+        <v>147.4288193241063</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -3069,7 +3075,7 @@
         <v>199</v>
       </c>
       <c r="B199" s="1">
-        <v>142.6575478978992</v>
+        <v>147.4672181018605</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -3077,7 +3083,7 @@
         <v>200</v>
       </c>
       <c r="B200" s="1">
-        <v>142.947661851444</v>
+        <v>147.5047598925026</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -3085,7 +3091,7 @@
         <v>201</v>
       </c>
       <c r="B201" s="1">
-        <v>142.9785131609205</v>
+        <v>147.6117736167616</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -3093,7 +3099,7 @@
         <v>202</v>
       </c>
       <c r="B202" s="1">
-        <v>142.9900420111261</v>
+        <v>147.9321920625801</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -3101,7 +3107,7 @@
         <v>203</v>
       </c>
       <c r="B203" s="1">
-        <v>143.1452118896332</v>
+        <v>148.1029962769371</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -3109,7 +3115,7 @@
         <v>204</v>
       </c>
       <c r="B204" s="1">
-        <v>143.3122389975256</v>
+        <v>148.2516380414317</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -3117,7 +3123,7 @@
         <v>205</v>
       </c>
       <c r="B205" s="1">
-        <v>143.3792457521962</v>
+        <v>148.2555243381455</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -3125,7 +3131,7 @@
         <v>206</v>
       </c>
       <c r="B206" s="1">
-        <v>143.5917415394537</v>
+        <v>148.3222102636411</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -3133,7 +3139,7 @@
         <v>207</v>
       </c>
       <c r="B207" s="1">
-        <v>143.6601432684386</v>
+        <v>148.9346750832101</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -3141,7 +3147,7 @@
         <v>208</v>
       </c>
       <c r="B208" s="1">
-        <v>144.026328370385</v>
+        <v>149.1243569126471</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -3149,7 +3155,7 @@
         <v>209</v>
       </c>
       <c r="B209" s="1">
-        <v>144.2857142866729</v>
+        <v>149.3132808730395</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -3157,7 +3163,7 @@
         <v>210</v>
       </c>
       <c r="B210" s="1">
-        <v>144.3100865234969</v>
+        <v>149.3396503066246</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -3165,7 +3171,7 @@
         <v>211</v>
       </c>
       <c r="B211" s="1">
-        <v>144.3139079130871</v>
+        <v>149.6276632524649</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -3173,7 +3179,7 @@
         <v>212</v>
       </c>
       <c r="B212" s="1">
-        <v>144.4026151359955</v>
+        <v>149.687513712443</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -3181,7 +3187,7 @@
         <v>213</v>
       </c>
       <c r="B213" s="1">
-        <v>144.5231043531464</v>
+        <v>149.75595124966</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -3189,7 +3195,7 @@
         <v>214</v>
       </c>
       <c r="B214" s="1">
-        <v>144.5719921245901</v>
+        <v>149.8612624272533</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -3197,7 +3203,7 @@
         <v>215</v>
       </c>
       <c r="B215" s="1">
-        <v>144.5745447768692</v>
+        <v>150.0990831131556</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -3205,7 +3211,7 @@
         <v>216</v>
       </c>
       <c r="B216" s="1">
-        <v>144.7086678215231</v>
+        <v>150.2456225828385</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -3213,7 +3219,7 @@
         <v>217</v>
       </c>
       <c r="B217" s="1">
-        <v>144.750001885976</v>
+        <v>150.2719732481746</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -3221,7 +3227,7 @@
         <v>218</v>
       </c>
       <c r="B218" s="1">
-        <v>145.107215349144</v>
+        <v>150.359176262351</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -3229,7 +3235,7 @@
         <v>219</v>
       </c>
       <c r="B219" s="1">
-        <v>145.1915621715714</v>
+        <v>150.422864469381</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -3237,7 +3243,7 @@
         <v>220</v>
       </c>
       <c r="B220" s="1">
-        <v>145.2130689022475</v>
+        <v>150.5563102517622</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -3245,7 +3251,7 @@
         <v>221</v>
       </c>
       <c r="B221" s="1">
-        <v>145.2663788448963</v>
+        <v>150.6082742092996</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -3253,7 +3259,7 @@
         <v>222</v>
       </c>
       <c r="B222" s="1">
-        <v>145.3845312890374</v>
+        <v>150.6272401455155</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -3261,7 +3267,7 @@
         <v>223</v>
       </c>
       <c r="B223" s="1">
-        <v>145.4580950517498</v>
+        <v>150.7781806268288</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -3269,7 +3275,7 @@
         <v>224</v>
       </c>
       <c r="B224" s="1">
-        <v>145.5427046338095</v>
+        <v>150.8371667060106</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -3277,7 +3283,7 @@
         <v>225</v>
       </c>
       <c r="B225" s="1">
-        <v>145.6317923598297</v>
+        <v>150.8460064799222</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -3285,7 +3291,7 @@
         <v>226</v>
       </c>
       <c r="B226" s="1">
-        <v>145.9730067349331</v>
+        <v>150.8586824366291</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -3293,7 +3299,7 @@
         <v>227</v>
       </c>
       <c r="B227" s="1">
-        <v>146.2684867575076</v>
+        <v>150.8952820334179</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -3301,7 +3307,7 @@
         <v>228</v>
       </c>
       <c r="B228" s="1">
-        <v>146.3141348464204</v>
+        <v>150.9402172629069</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -3309,7 +3315,7 @@
         <v>229</v>
       </c>
       <c r="B229" s="1">
-        <v>146.3394803260355</v>
+        <v>151.0780653096789</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -3317,7 +3323,7 @@
         <v>230</v>
       </c>
       <c r="B230" s="1">
-        <v>147.0418590179065</v>
+        <v>151.257829834366</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -3325,7 +3331,7 @@
         <v>231</v>
       </c>
       <c r="B231" s="1">
-        <v>147.315689092545</v>
+        <v>151.2972453723136</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -3333,7 +3339,7 @@
         <v>232</v>
       </c>
       <c r="B232" s="1">
-        <v>147.509124761938</v>
+        <v>151.3797681659705</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -3341,7 +3347,7 @@
         <v>233</v>
       </c>
       <c r="B233" s="1">
-        <v>147.7849905491536</v>
+        <v>151.4744876136699</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -3349,7 +3355,7 @@
         <v>234</v>
       </c>
       <c r="B234" s="1">
-        <v>147.8863702366639</v>
+        <v>151.954424252143</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -3357,7 +3363,7 @@
         <v>235</v>
       </c>
       <c r="B235" s="1">
-        <v>148.0600612074248</v>
+        <v>152.1607229792099</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -3365,7 +3371,7 @@
         <v>236</v>
       </c>
       <c r="B236" s="1">
-        <v>148.1575291827062</v>
+        <v>152.1845702477707</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -3373,7 +3379,7 @@
         <v>237</v>
       </c>
       <c r="B237" s="1">
-        <v>148.3581299354677</v>
+        <v>152.3112815127581</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -3381,7 +3387,7 @@
         <v>238</v>
       </c>
       <c r="B238" s="1">
-        <v>148.4027206241158</v>
+        <v>152.7682653624477</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -3389,7 +3395,7 @@
         <v>239</v>
       </c>
       <c r="B239" s="1">
-        <v>148.5288233549315</v>
+        <v>152.9919305626667</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -3397,7 +3403,7 @@
         <v>240</v>
       </c>
       <c r="B240" s="1">
-        <v>148.6293282844493</v>
+        <v>153.1142886250203</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -3405,7 +3411,7 @@
         <v>241</v>
       </c>
       <c r="B241" s="1">
-        <v>148.7276898000317</v>
+        <v>153.3422306711517</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -3413,7 +3419,7 @@
         <v>242</v>
       </c>
       <c r="B242" s="1">
-        <v>148.9975435545929</v>
+        <v>153.5256957681681</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -3421,7 +3427,7 @@
         <v>243</v>
       </c>
       <c r="B243" s="1">
-        <v>149.2551820554246</v>
+        <v>153.5821360250166</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -3429,7 +3435,7 @@
         <v>244</v>
       </c>
       <c r="B244" s="1">
-        <v>149.5480256104833</v>
+        <v>153.6176713393625</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -3437,7 +3443,7 @@
         <v>245</v>
       </c>
       <c r="B245" s="1">
-        <v>149.5525551561696</v>
+        <v>153.8479977014528</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -3445,7 +3451,7 @@
         <v>246</v>
       </c>
       <c r="B246" s="1">
-        <v>149.7412946608287</v>
+        <v>153.934715098498</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -3453,7 +3459,7 @@
         <v>247</v>
       </c>
       <c r="B247" s="1">
-        <v>149.7455280997524</v>
+        <v>154.1003051148066</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -3461,7 +3467,7 @@
         <v>248</v>
       </c>
       <c r="B248" s="1">
-        <v>149.9758647453591</v>
+        <v>154.2114616029173</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -3469,7 +3475,7 @@
         <v>249</v>
       </c>
       <c r="B249" s="1">
-        <v>150.163461834323</v>
+        <v>154.5868953062074</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -3477,7 +3483,7 @@
         <v>250</v>
       </c>
       <c r="B250" s="1">
-        <v>150.231407329553</v>
+        <v>154.7057237025718</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -3485,7 +3491,7 @@
         <v>251</v>
       </c>
       <c r="B251" s="1">
-        <v>150.2597636048207</v>
+        <v>154.8682781778302</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -3493,7 +3499,7 @@
         <v>252</v>
       </c>
       <c r="B252" s="1">
-        <v>150.492622845637</v>
+        <v>155.1074825633952</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -3501,7 +3507,7 @@
         <v>253</v>
       </c>
       <c r="B253" s="1">
-        <v>150.6169915384697</v>
+        <v>155.4577213152232</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -3509,7 +3515,7 @@
         <v>254</v>
       </c>
       <c r="B254" s="1">
-        <v>150.6253082630952</v>
+        <v>155.9803190100494</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -3517,7 +3523,7 @@
         <v>255</v>
       </c>
       <c r="B255" s="1">
-        <v>150.7752059259454</v>
+        <v>156.3581002418856</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -3525,7 +3531,7 @@
         <v>256</v>
       </c>
       <c r="B256" s="1">
-        <v>150.8002880020072</v>
+        <v>157.0273675620256</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -3533,7 +3539,7 @@
         <v>257</v>
       </c>
       <c r="B257" s="1">
-        <v>151.0958229307504</v>
+        <v>157.9940339343269</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -3541,7 +3547,7 @@
         <v>258</v>
       </c>
       <c r="B258" s="1">
-        <v>151.4720875157562</v>
+        <v>158.0649655318811</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -3549,7 +3555,7 @@
         <v>259</v>
       </c>
       <c r="B259" s="1">
-        <v>151.530272903834</v>
+        <v>159.0448620979279</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -3557,7 +3563,7 @@
         <v>260</v>
       </c>
       <c r="B260" s="1">
-        <v>151.8405378713438</v>
+        <v>159.0995762233708</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -3565,7 +3571,7 @@
         <v>261</v>
       </c>
       <c r="B261" s="1">
-        <v>152.0138559852837</v>
+        <v>159.1793745647682</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -3573,7 +3579,7 @@
         <v>262</v>
       </c>
       <c r="B262" s="1">
-        <v>152.4445239743982</v>
+        <v>159.5575279760833</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -3581,7 +3587,7 @@
         <v>263</v>
       </c>
       <c r="B263" s="1">
-        <v>152.9723042712538</v>
+        <v>159.5665212794964</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -3589,7 +3595,7 @@
         <v>264</v>
       </c>
       <c r="B264" s="1">
-        <v>153.6186168570916</v>
+        <v>160.034216100887</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -3597,7 +3603,7 @@
         <v>265</v>
       </c>
       <c r="B265" s="1">
-        <v>153.6723982007186</v>
+        <v>160.6646817246191</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -3605,7 +3611,7 @@
         <v>266</v>
       </c>
       <c r="B266" s="1">
-        <v>153.9990183026713</v>
+        <v>160.823003909658</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -3613,7 +3619,7 @@
         <v>267</v>
       </c>
       <c r="B267" s="1">
-        <v>154.3822503406911</v>
+        <v>160.8687788574994</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -3621,7 +3627,7 @@
         <v>268</v>
       </c>
       <c r="B268" s="1">
-        <v>154.4029761858587</v>
+        <v>161.4197255402331</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -3629,7 +3635,7 @@
         <v>269</v>
       </c>
       <c r="B269" s="1">
-        <v>154.6251071266665</v>
+        <v>161.7948314334095</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -3637,7 +3643,7 @@
         <v>270</v>
       </c>
       <c r="B270" s="1">
-        <v>154.8805995051191</v>
+        <v>161.9594467559942</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -3645,7 +3651,7 @@
         <v>271</v>
       </c>
       <c r="B271" s="1">
-        <v>154.8861261913671</v>
+        <v>162.3460234192603</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -3653,7 +3659,7 @@
         <v>272</v>
       </c>
       <c r="B272" s="1">
-        <v>155.8126763513131</v>
+        <v>162.7578677890454</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -3661,7 +3667,7 @@
         <v>273</v>
       </c>
       <c r="B273" s="1">
-        <v>155.9522572522366</v>
+        <v>162.8174828123756</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -3669,7 +3675,7 @@
         <v>274</v>
       </c>
       <c r="B274" s="1">
-        <v>156.057408752954</v>
+        <v>163.7756496144346</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -3677,7 +3683,7 @@
         <v>275</v>
       </c>
       <c r="B275" s="1">
-        <v>156.6337107524481</v>
+        <v>165.1325333752411</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -3685,7 +3691,7 @@
         <v>276</v>
       </c>
       <c r="B276" s="1">
-        <v>156.979236574529</v>
+        <v>165.4167186009292</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -3693,7 +3699,7 @@
         <v>277</v>
       </c>
       <c r="B277" s="1">
-        <v>157.2876128717563</v>
+        <v>165.8585123599655</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -3701,7 +3707,7 @@
         <v>278</v>
       </c>
       <c r="B278" s="1">
-        <v>157.5805582354955</v>
+        <v>166.1030706541295</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -3709,7 +3715,7 @@
         <v>279</v>
       </c>
       <c r="B279" s="1">
-        <v>158.5315628038649</v>
+        <v>166.5969842345849</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -3717,7 +3723,7 @@
         <v>280</v>
       </c>
       <c r="B280" s="1">
-        <v>158.7937128666052</v>
+        <v>166.6110400404456</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -3725,7 +3731,7 @@
         <v>281</v>
       </c>
       <c r="B281" s="1">
-        <v>159.1741132088299</v>
+        <v>166.7329893383465</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -3733,7 +3739,7 @@
         <v>282</v>
       </c>
       <c r="B282" s="1">
-        <v>159.228682454758</v>
+        <v>167.0989216880709</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -3741,7 +3747,7 @@
         <v>283</v>
       </c>
       <c r="B283" s="1">
-        <v>159.6691538481873</v>
+        <v>167.1796982115739</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -3749,7 +3755,7 @@
         <v>284</v>
       </c>
       <c r="B284" s="1">
-        <v>159.8052336803059</v>
+        <v>167.2979243932306</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -3757,7 +3763,7 @@
         <v>285</v>
       </c>
       <c r="B285" s="1">
-        <v>160.3185316215196</v>
+        <v>168.010011310707</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -3765,7 +3771,7 @@
         <v>286</v>
       </c>
       <c r="B286" s="1">
-        <v>160.6563359116057</v>
+        <v>168.2957192522639</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -3773,7 +3779,7 @@
         <v>287</v>
       </c>
       <c r="B287" s="1">
-        <v>160.6963734713058</v>
+        <v>168.407444260123</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -3781,7 +3787,7 @@
         <v>288</v>
       </c>
       <c r="B288" s="1">
-        <v>160.8439863953792</v>
+        <v>169.7756640412077</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -3789,7 +3795,7 @@
         <v>289</v>
       </c>
       <c r="B289" s="1">
-        <v>160.8922175724327</v>
+        <v>170.0038695596177</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -3797,7 +3803,7 @@
         <v>290</v>
       </c>
       <c r="B290" s="1">
-        <v>161.4757060938436</v>
+        <v>170.2688435410465</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -3805,7 +3811,7 @@
         <v>291</v>
       </c>
       <c r="B291" s="1">
-        <v>161.8455249057803</v>
+        <v>170.4929231573195</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -3813,7 +3819,7 @@
         <v>292</v>
       </c>
       <c r="B292" s="1">
-        <v>161.9213773783305</v>
+        <v>171.3302917528341</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -3821,7 +3827,7 @@
         <v>293</v>
       </c>
       <c r="B293" s="1">
-        <v>162.4919905167188</v>
+        <v>172.6200265477772</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -3829,7 +3835,7 @@
         <v>294</v>
       </c>
       <c r="B294" s="1">
-        <v>162.7442720400813</v>
+        <v>173.1221095008115</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -3837,7 +3843,7 @@
         <v>295</v>
       </c>
       <c r="B295" s="1">
-        <v>162.8974042011984</v>
+        <v>173.4727557173179</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -3845,7 +3851,7 @@
         <v>296</v>
       </c>
       <c r="B296" s="1">
-        <v>163.1674429312644</v>
+        <v>174.8383053458917</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -3853,7 +3859,7 @@
         <v>297</v>
       </c>
       <c r="B297" s="1">
-        <v>163.2103317871596</v>
+        <v>174.9158127296423</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -3861,7 +3867,7 @@
         <v>298</v>
       </c>
       <c r="B298" s="1">
-        <v>163.2518567240724</v>
+        <v>175.0301828025447</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -3869,7 +3875,7 @@
         <v>299</v>
       </c>
       <c r="B299" s="1">
-        <v>165.0838455007558</v>
+        <v>175.1066591801561</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -3877,7 +3883,7 @@
         <v>300</v>
       </c>
       <c r="B300" s="1">
-        <v>165.2986414332055</v>
+        <v>175.6126630958253</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -3885,7 +3891,7 @@
         <v>301</v>
       </c>
       <c r="B301" s="1">
-        <v>165.7174624479791</v>
+        <v>175.6689144221319</v>
       </c>
     </row>
     <row r="302" spans="1:2">
@@ -3893,7 +3899,7 @@
         <v>302</v>
       </c>
       <c r="B302" s="1">
-        <v>166.1765459885423</v>
+        <v>175.7078278556753</v>
       </c>
     </row>
     <row r="303" spans="1:2">
@@ -3901,7 +3907,7 @@
         <v>303</v>
       </c>
       <c r="B303" s="1">
-        <v>166.2453553767382</v>
+        <v>176.3206284344115</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -3909,7 +3915,7 @@
         <v>304</v>
       </c>
       <c r="B304" s="1">
-        <v>166.2590691865597</v>
+        <v>176.324642444911</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -3917,7 +3923,7 @@
         <v>305</v>
       </c>
       <c r="B305" s="1">
-        <v>167.1716717773506</v>
+        <v>176.5036739138644</v>
       </c>
     </row>
     <row r="306" spans="1:2">
@@ -3925,7 +3931,7 @@
         <v>306</v>
       </c>
       <c r="B306" s="1">
-        <v>168.0031309919731</v>
+        <v>176.5425608571317</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -3933,7 +3939,7 @@
         <v>307</v>
       </c>
       <c r="B307" s="1">
-        <v>168.0379970789592</v>
+        <v>178.0426149941399</v>
       </c>
     </row>
     <row r="308" spans="1:2">
@@ -3941,7 +3947,7 @@
         <v>308</v>
       </c>
       <c r="B308" s="1">
-        <v>168.4993846761335</v>
+        <v>178.3545691979927</v>
       </c>
     </row>
     <row r="309" spans="1:2">
@@ -3949,7 +3955,7 @@
         <v>309</v>
       </c>
       <c r="B309" s="1">
-        <v>168.7811235943186</v>
+        <v>178.5557426627231</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -3957,7 +3963,7 @@
         <v>310</v>
       </c>
       <c r="B310" s="1">
-        <v>169.7991514246532</v>
+        <v>180.6624112514824</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -3965,7 +3971,7 @@
         <v>311</v>
       </c>
       <c r="B311" s="1">
-        <v>169.9284707352504</v>
+        <v>180.6856718738921</v>
       </c>
     </row>
     <row r="312" spans="1:2">
@@ -3973,7 +3979,7 @@
         <v>312</v>
       </c>
       <c r="B312" s="1">
-        <v>169.9536084477205</v>
+        <v>181.1259662745777</v>
       </c>
     </row>
     <row r="313" spans="1:2">
@@ -3981,7 +3987,7 @@
         <v>313</v>
       </c>
       <c r="B313" s="1">
-        <v>170.1413980151002</v>
+        <v>181.6021907736554</v>
       </c>
     </row>
     <row r="314" spans="1:2">
@@ -3989,7 +3995,7 @@
         <v>314</v>
       </c>
       <c r="B314" s="1">
-        <v>170.9368387755291</v>
+        <v>181.6769978550583</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -3997,7 +4003,7 @@
         <v>315</v>
       </c>
       <c r="B315" s="1">
-        <v>171.4091125053183</v>
+        <v>182.205404663519</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -4005,7 +4011,7 @@
         <v>316</v>
       </c>
       <c r="B316" s="1">
-        <v>171.8799031805035</v>
+        <v>182.633519252463</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -4013,7 +4019,7 @@
         <v>317</v>
       </c>
       <c r="B317" s="1">
-        <v>173.0735070953451</v>
+        <v>184.8606026478251</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -4021,7 +4027,7 @@
         <v>318</v>
       </c>
       <c r="B318" s="1">
-        <v>173.5397684771616</v>
+        <v>186.0658006462933</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -4029,7 +4035,7 @@
         <v>319</v>
       </c>
       <c r="B319" s="1">
-        <v>174.270432253941</v>
+        <v>188.549891559784</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -4037,7 +4043,7 @@
         <v>320</v>
       </c>
       <c r="B320" s="1">
-        <v>174.312954340026</v>
+        <v>188.7717042022524</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -4045,7 +4051,7 @@
         <v>321</v>
       </c>
       <c r="B321" s="1">
-        <v>174.6701501176942</v>
+        <v>190.6099148388151</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -4053,7 +4059,7 @@
         <v>322</v>
       </c>
       <c r="B322" s="1">
-        <v>174.8399856620773</v>
+        <v>190.7511063866718</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -4061,7 +4067,7 @@
         <v>323</v>
       </c>
       <c r="B323" s="1">
-        <v>175.2058538885997</v>
+        <v>191.0112960968032</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -4069,7 +4075,7 @@
         <v>324</v>
       </c>
       <c r="B324" s="1">
-        <v>175.4941320170654</v>
+        <v>193.2932616709566</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -4077,7 +4083,7 @@
         <v>325</v>
       </c>
       <c r="B325" s="1">
-        <v>175.7294847983877</v>
+        <v>194.5488198867781</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -4085,7 +4091,7 @@
         <v>326</v>
       </c>
       <c r="B326" s="1">
-        <v>176.8898868988804</v>
+        <v>196.0600804044172</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -4093,7 +4099,7 @@
         <v>327</v>
       </c>
       <c r="B327" s="1">
-        <v>177.6907565266278</v>
+        <v>196.7962603205521</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -4101,7 +4107,7 @@
         <v>328</v>
       </c>
       <c r="B328" s="1">
-        <v>179.5037574449794</v>
+        <v>197.4831740843787</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -4109,7 +4115,7 @@
         <v>329</v>
       </c>
       <c r="B329" s="1">
-        <v>180.2701622626164</v>
+        <v>197.5589812359147</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -4117,7 +4123,7 @@
         <v>330</v>
       </c>
       <c r="B330" s="1">
-        <v>182.1254149464945</v>
+        <v>198.2365190893374</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -4125,7 +4131,7 @@
         <v>331</v>
       </c>
       <c r="B331" s="1">
-        <v>183.2210512348921</v>
+        <v>198.3807305691426</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -4133,7 +4139,7 @@
         <v>332</v>
       </c>
       <c r="B332" s="1">
-        <v>185.0259131984018</v>
+        <v>198.5881503821822</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -4141,7 +4147,7 @@
         <v>333</v>
       </c>
       <c r="B333" s="1">
-        <v>188.6272703691708</v>
+        <v>199.1323855022651</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -4149,7 +4155,7 @@
         <v>334</v>
       </c>
       <c r="B334" s="1">
-        <v>189.8403916355152</v>
+        <v>199.3021960308955</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -4157,7 +4163,7 @@
         <v>335</v>
       </c>
       <c r="B335" s="1">
-        <v>190.2180863895166</v>
+        <v>202.5312354104882</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -4165,7 +4171,7 @@
         <v>336</v>
       </c>
       <c r="B336" s="1">
-        <v>190.3591316243511</v>
+        <v>202.7191437974511</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -4173,7 +4179,7 @@
         <v>337</v>
       </c>
       <c r="B337" s="1">
-        <v>190.9046495749268</v>
+        <v>205.5526484116818</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -4181,7 +4187,7 @@
         <v>338</v>
       </c>
       <c r="B338" s="1">
-        <v>191.3358092495296</v>
+        <v>205.8239689198737</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -4189,7 +4195,7 @@
         <v>339</v>
       </c>
       <c r="B339" s="1">
-        <v>192.2526722383186</v>
+        <v>206.8883766387893</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -4197,7 +4203,7 @@
         <v>340</v>
       </c>
       <c r="B340" s="1">
-        <v>193.0051279855795</v>
+        <v>207.7204169707036</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -4205,7 +4211,7 @@
         <v>341</v>
       </c>
       <c r="B341" s="1">
-        <v>194.4275386577478</v>
+        <v>207.9131163077969</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -4213,7 +4219,7 @@
         <v>342</v>
       </c>
       <c r="B342" s="1">
-        <v>194.4608533668435</v>
+        <v>208.2792453119569</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -4221,7 +4227,7 @@
         <v>343</v>
       </c>
       <c r="B343" s="1">
-        <v>194.814206693846</v>
+        <v>209.3893274140154</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -4229,7 +4235,7 @@
         <v>344</v>
       </c>
       <c r="B344" s="1">
-        <v>195.5101448557973</v>
+        <v>213.6051067031337</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -4237,7 +4243,7 @@
         <v>345</v>
       </c>
       <c r="B345" s="1">
-        <v>195.8499428123625</v>
+        <v>215.0323626278594</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -4245,7 +4251,7 @@
         <v>346</v>
       </c>
       <c r="B346" s="1">
-        <v>195.920310549299</v>
+        <v>215.5973936421408</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -4253,7 +4259,7 @@
         <v>347</v>
       </c>
       <c r="B347" s="1">
-        <v>199.1697998367451</v>
+        <v>217.536662765915</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -4261,7 +4267,7 @@
         <v>348</v>
       </c>
       <c r="B348" s="1">
-        <v>201.3320814964501</v>
+        <v>217.781300803123</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -4269,7 +4275,7 @@
         <v>349</v>
       </c>
       <c r="B349" s="1">
-        <v>209.0816026061022</v>
+        <v>218.9711439338221</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -4277,7 +4283,7 @@
         <v>350</v>
       </c>
       <c r="B350" s="1">
-        <v>209.3396769346014</v>
+        <v>231.1795505529074</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -4285,7 +4291,7 @@
         <v>351</v>
       </c>
       <c r="B351" s="1">
-        <v>214.8798189099198</v>
+        <v>239.0767061813042</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -4293,7 +4299,7 @@
         <v>352</v>
       </c>
       <c r="B352" s="1">
-        <v>219.2488041077693</v>
+        <v>239.9444744359409</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -4301,7 +4307,7 @@
         <v>353</v>
       </c>
       <c r="B353" s="1">
-        <v>228.9059760541909</v>
+        <v>249.8422349733149</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -4309,7 +4315,7 @@
         <v>354</v>
       </c>
       <c r="B354" s="1">
-        <v>230.1177582584917</v>
+        <v>256.2407933537457</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -4317,7 +4323,7 @@
         <v>355</v>
       </c>
       <c r="B355" s="1">
-        <v>231.8242440066284</v>
+        <v>260.4092186618647</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -4325,7 +4331,7 @@
         <v>356</v>
       </c>
       <c r="B356" s="1">
-        <v>232.1218433792926</v>
+        <v>273.7172597567813</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -4333,7 +4339,7 @@
         <v>357</v>
       </c>
       <c r="B357" s="1">
-        <v>232.789031730069</v>
+        <v>275.2863998658778</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -4341,7 +4347,7 @@
         <v>358</v>
       </c>
       <c r="B358" s="1">
-        <v>246.5086808950119</v>
+        <v>280.4146651000763</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -4349,7 +4355,7 @@
         <v>359</v>
       </c>
       <c r="B359" s="1">
-        <v>260.7997735028497</v>
+        <v>283.3963057928091</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -4357,7 +4363,7 @@
         <v>360</v>
       </c>
       <c r="B360" s="1">
-        <v>270.1776239673481</v>
+        <v>293.2709590963472</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -4365,7 +4371,7 @@
         <v>361</v>
       </c>
       <c r="B361" s="1">
-        <v>271.9297759370343</v>
+        <v>301.5945710877178</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -4373,7 +4379,7 @@
         <v>362</v>
       </c>
       <c r="B362" s="1">
-        <v>280.5909856384841</v>
+        <v>303.6097144355306</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -4381,7 +4387,7 @@
         <v>363</v>
       </c>
       <c r="B363" s="1">
-        <v>290.5314514084259</v>
+        <v>305.8833824966043</v>
       </c>
     </row>
     <row r="364" spans="1:2">
@@ -4389,7 +4395,7 @@
         <v>364</v>
       </c>
       <c r="B364" s="1">
-        <v>296.7704629716832</v>
+        <v>318.0717481220635</v>
       </c>
     </row>
     <row r="365" spans="1:2">
@@ -4397,7 +4403,7 @@
         <v>365</v>
       </c>
       <c r="B365" s="1">
-        <v>299.2567598894694</v>
+        <v>339.618295640037</v>
       </c>
     </row>
     <row r="366" spans="1:2">
@@ -4405,7 +4411,7 @@
         <v>366</v>
       </c>
       <c r="B366" s="1">
-        <v>310.3700664470173</v>
+        <v>352.4751899923309</v>
       </c>
     </row>
     <row r="367" spans="1:2">
@@ -4413,7 +4419,7 @@
         <v>367</v>
       </c>
       <c r="B367" s="1">
-        <v>506.6364912782456</v>
+        <v>453.6179757064314</v>
       </c>
     </row>
     <row r="368" spans="1:2">
@@ -4421,7 +4427,7 @@
         <v>368</v>
       </c>
       <c r="B368" s="1">
-        <v>567.1717836405109</v>
+        <v>509.1957243873753</v>
       </c>
     </row>
     <row r="369" spans="1:2">
@@ -4429,7 +4435,7 @@
         <v>369</v>
       </c>
       <c r="B369" s="1">
-        <v>594.6581873627458</v>
+        <v>532.3798212526319</v>
       </c>
     </row>
     <row r="370" spans="1:2">
@@ -4437,7 +4443,23 @@
         <v>370</v>
       </c>
       <c r="B370" s="1">
-        <v>648.9755435686895</v>
+        <v>567.1717836405109</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2">
+      <c r="A371" t="s">
+        <v>371</v>
+      </c>
+      <c r="B371" s="1">
+        <v>581.5698777251038</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2">
+      <c r="A372" t="s">
+        <v>372</v>
+      </c>
+      <c r="B372" s="1">
+        <v>825.2939153992677</v>
       </c>
     </row>
   </sheetData>

--- a/Screener/data/rs_rating_top_30.xlsx
+++ b/Screener/data/rs_rating_top_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="367">
   <si>
     <t>Symbol</t>
   </si>
@@ -22,1081 +22,1066 @@
     <t>RS Rating</t>
   </si>
   <si>
+    <t>TPH</t>
+  </si>
+  <si>
+    <t>NEU</t>
+  </si>
+  <si>
+    <t>XPER</t>
+  </si>
+  <si>
+    <t>ESCA</t>
+  </si>
+  <si>
+    <t>DXPE</t>
+  </si>
+  <si>
+    <t>GHL</t>
+  </si>
+  <si>
+    <t>IGT</t>
+  </si>
+  <si>
     <t>VEL</t>
   </si>
   <si>
+    <t>IDCC</t>
+  </si>
+  <si>
+    <t>GE</t>
+  </si>
+  <si>
+    <t>CSTM</t>
+  </si>
+  <si>
+    <t>CRH</t>
+  </si>
+  <si>
+    <t>INMD</t>
+  </si>
+  <si>
+    <t>LAD</t>
+  </si>
+  <si>
+    <t>IIVI</t>
+  </si>
+  <si>
+    <t>DECK</t>
+  </si>
+  <si>
+    <t>BMEA</t>
+  </si>
+  <si>
+    <t>DUOL</t>
+  </si>
+  <si>
+    <t>URBN</t>
+  </si>
+  <si>
+    <t>SWI</t>
+  </si>
+  <si>
+    <t>GHRS</t>
+  </si>
+  <si>
+    <t>ATEC</t>
+  </si>
+  <si>
+    <t>GMS</t>
+  </si>
+  <si>
+    <t>BUR</t>
+  </si>
+  <si>
+    <t>PCTTU</t>
+  </si>
+  <si>
+    <t>FUTU</t>
+  </si>
+  <si>
+    <t>PATK</t>
+  </si>
+  <si>
+    <t>KRNT</t>
+  </si>
+  <si>
+    <t>CNX</t>
+  </si>
+  <si>
+    <t>APO</t>
+  </si>
+  <si>
+    <t>ON</t>
+  </si>
+  <si>
+    <t>AGRO</t>
+  </si>
+  <si>
+    <t>GHM</t>
+  </si>
+  <si>
+    <t>PCYO</t>
+  </si>
+  <si>
+    <t>CRC</t>
+  </si>
+  <si>
+    <t>NOG</t>
+  </si>
+  <si>
+    <t>JWN</t>
+  </si>
+  <si>
+    <t>ZG</t>
+  </si>
+  <si>
+    <t>MRVL</t>
+  </si>
+  <si>
+    <t>NEWT</t>
+  </si>
+  <si>
+    <t>TNET</t>
+  </si>
+  <si>
+    <t>FIX</t>
+  </si>
+  <si>
+    <t>FROG</t>
+  </si>
+  <si>
+    <t>TEX</t>
+  </si>
+  <si>
+    <t>ODFL</t>
+  </si>
+  <si>
+    <t>TMHC</t>
+  </si>
+  <si>
+    <t>RMBL</t>
+  </si>
+  <si>
+    <t>CSAN</t>
+  </si>
+  <si>
+    <t>Z</t>
+  </si>
+  <si>
+    <t>HLF</t>
+  </si>
+  <si>
+    <t>ATRC</t>
+  </si>
+  <si>
+    <t>AZUL</t>
+  </si>
+  <si>
+    <t>FDX</t>
+  </si>
+  <si>
+    <t>SMHI</t>
+  </si>
+  <si>
+    <t>VIPS</t>
+  </si>
+  <si>
+    <t>PH</t>
+  </si>
+  <si>
+    <t>PRIM</t>
+  </si>
+  <si>
+    <t>PAG</t>
+  </si>
+  <si>
+    <t>AEIS</t>
+  </si>
+  <si>
+    <t>MTW</t>
+  </si>
+  <si>
+    <t>ITRI</t>
+  </si>
+  <si>
+    <t>PRI</t>
+  </si>
+  <si>
+    <t>MSA</t>
+  </si>
+  <si>
+    <t>DDOG</t>
+  </si>
+  <si>
+    <t>MDC</t>
+  </si>
+  <si>
+    <t>TOL</t>
+  </si>
+  <si>
+    <t>PARR</t>
+  </si>
+  <si>
+    <t>VNO</t>
+  </si>
+  <si>
+    <t>SPNT</t>
+  </si>
+  <si>
+    <t>HAYW</t>
+  </si>
+  <si>
     <t>ARGX</t>
   </si>
   <si>
-    <t>GXO</t>
-  </si>
-  <si>
-    <t>QTWO</t>
-  </si>
-  <si>
-    <t>BELFB</t>
-  </si>
-  <si>
-    <t>CXM</t>
+    <t>NVT</t>
+  </si>
+  <si>
+    <t>SPNS</t>
+  </si>
+  <si>
+    <t>AXR</t>
+  </si>
+  <si>
+    <t>BMI</t>
+  </si>
+  <si>
+    <t>SLG</t>
+  </si>
+  <si>
+    <t>SWDAF</t>
+  </si>
+  <si>
+    <t>PNR</t>
+  </si>
+  <si>
+    <t>NEWR</t>
+  </si>
+  <si>
+    <t>TSQ</t>
+  </si>
+  <si>
+    <t>PKOH</t>
+  </si>
+  <si>
+    <t>HURN</t>
+  </si>
+  <si>
+    <t>AMWD</t>
+  </si>
+  <si>
+    <t>CVGI</t>
+  </si>
+  <si>
+    <t>CYD</t>
+  </si>
+  <si>
+    <t>APG</t>
+  </si>
+  <si>
+    <t>PETQ</t>
+  </si>
+  <si>
+    <t>USLM</t>
+  </si>
+  <si>
+    <t>IMVT</t>
+  </si>
+  <si>
+    <t>LRCX</t>
+  </si>
+  <si>
+    <t>ZWS</t>
+  </si>
+  <si>
+    <t>MGNI</t>
+  </si>
+  <si>
+    <t>ETD</t>
+  </si>
+  <si>
+    <t>WMS</t>
+  </si>
+  <si>
+    <t>TSLA</t>
+  </si>
+  <si>
+    <t>SIBN</t>
+  </si>
+  <si>
+    <t>AMNB</t>
+  </si>
+  <si>
+    <t>INBK</t>
+  </si>
+  <si>
+    <t>HSKA</t>
+  </si>
+  <si>
+    <t>JBL</t>
+  </si>
+  <si>
+    <t>COOP</t>
+  </si>
+  <si>
+    <t>YPF</t>
+  </si>
+  <si>
+    <t>WPRT</t>
+  </si>
+  <si>
+    <t>ZGN</t>
+  </si>
+  <si>
+    <t>BATRA</t>
+  </si>
+  <si>
+    <t>ACOR</t>
+  </si>
+  <si>
+    <t>FLNC</t>
+  </si>
+  <si>
+    <t>OTTR</t>
+  </si>
+  <si>
+    <t>ONTO</t>
+  </si>
+  <si>
+    <t>AUPH</t>
+  </si>
+  <si>
+    <t>FTDR</t>
+  </si>
+  <si>
+    <t>BVH</t>
+  </si>
+  <si>
+    <t>DIT</t>
+  </si>
+  <si>
+    <t>MTH</t>
+  </si>
+  <si>
+    <t>FMS</t>
+  </si>
+  <si>
+    <t>HROW</t>
+  </si>
+  <si>
+    <t>GOCO</t>
+  </si>
+  <si>
+    <t>ARCO</t>
   </si>
   <si>
     <t>NTES</t>
   </si>
   <si>
+    <t>CARR</t>
+  </si>
+  <si>
+    <t>AEL</t>
+  </si>
+  <si>
+    <t>NUVL</t>
+  </si>
+  <si>
+    <t>SHC</t>
+  </si>
+  <si>
+    <t>ANDE</t>
+  </si>
+  <si>
     <t>NE</t>
   </si>
   <si>
-    <t>ODFL</t>
-  </si>
-  <si>
-    <t>TNET</t>
-  </si>
-  <si>
-    <t>PBR</t>
-  </si>
-  <si>
-    <t>AMNB</t>
-  </si>
-  <si>
-    <t>PNR</t>
-  </si>
-  <si>
-    <t>FORM</t>
-  </si>
-  <si>
-    <t>CRH</t>
-  </si>
-  <si>
-    <t>GT</t>
+    <t>FTI</t>
+  </si>
+  <si>
+    <t>VECO</t>
+  </si>
+  <si>
+    <t>NRP</t>
+  </si>
+  <si>
+    <t>RVMD</t>
+  </si>
+  <si>
+    <t>KRUS</t>
+  </si>
+  <si>
+    <t>MOMO</t>
+  </si>
+  <si>
+    <t>KRYS</t>
+  </si>
+  <si>
+    <t>RCM</t>
+  </si>
+  <si>
+    <t>ASMIY</t>
+  </si>
+  <si>
+    <t>BLX</t>
+  </si>
+  <si>
+    <t>VICR</t>
+  </si>
+  <si>
+    <t>EME</t>
+  </si>
+  <si>
+    <t>KRT</t>
+  </si>
+  <si>
+    <t>HCCI</t>
+  </si>
+  <si>
+    <t>NATR</t>
+  </si>
+  <si>
+    <t>CFLT</t>
+  </si>
+  <si>
+    <t>CSWI</t>
+  </si>
+  <si>
+    <t>SPOK</t>
+  </si>
+  <si>
+    <t>EXAS</t>
+  </si>
+  <si>
+    <t>CORT</t>
+  </si>
+  <si>
+    <t>PLAB</t>
+  </si>
+  <si>
+    <t>LPG</t>
+  </si>
+  <si>
+    <t>ALGN</t>
+  </si>
+  <si>
+    <t>ADBE</t>
+  </si>
+  <si>
+    <t>CNM</t>
+  </si>
+  <si>
+    <t>AVGO</t>
+  </si>
+  <si>
+    <t>APPF</t>
+  </si>
+  <si>
+    <t>KBH</t>
+  </si>
+  <si>
+    <t>GTLS</t>
+  </si>
+  <si>
+    <t>GSHD</t>
+  </si>
+  <si>
+    <t>AZEK</t>
+  </si>
+  <si>
+    <t>FTAI</t>
+  </si>
+  <si>
+    <t>AROC</t>
+  </si>
+  <si>
+    <t>THO</t>
+  </si>
+  <si>
+    <t>IESC</t>
+  </si>
+  <si>
+    <t>DOCN</t>
+  </si>
+  <si>
+    <t>SBOW</t>
+  </si>
+  <si>
+    <t>EB</t>
+  </si>
+  <si>
+    <t>YELP</t>
+  </si>
+  <si>
+    <t>LOB</t>
+  </si>
+  <si>
+    <t>BRZE</t>
+  </si>
+  <si>
+    <t>CAAP</t>
+  </si>
+  <si>
+    <t>BMA</t>
+  </si>
+  <si>
+    <t>VIST</t>
+  </si>
+  <si>
+    <t>ROCK</t>
+  </si>
+  <si>
+    <t>NEX</t>
+  </si>
+  <si>
+    <t>ARCB</t>
+  </si>
+  <si>
+    <t>LEGN</t>
+  </si>
+  <si>
+    <t>TAYD</t>
+  </si>
+  <si>
+    <t>KNSA</t>
+  </si>
+  <si>
+    <t>PRO</t>
+  </si>
+  <si>
+    <t>FRSH</t>
+  </si>
+  <si>
+    <t>NYCB</t>
+  </si>
+  <si>
+    <t>TYRA</t>
+  </si>
+  <si>
+    <t>RDNT</t>
+  </si>
+  <si>
+    <t>UPWK</t>
+  </si>
+  <si>
+    <t>LII</t>
+  </si>
+  <si>
+    <t>ERO</t>
+  </si>
+  <si>
+    <t>BWMN</t>
+  </si>
+  <si>
+    <t>DASH</t>
+  </si>
+  <si>
+    <t>TDC</t>
+  </si>
+  <si>
+    <t>UBER</t>
+  </si>
+  <si>
+    <t>CLBR</t>
+  </si>
+  <si>
+    <t>SCX</t>
+  </si>
+  <si>
+    <t>BECN</t>
+  </si>
+  <si>
+    <t>ACAD</t>
+  </si>
+  <si>
+    <t>ARHS</t>
+  </si>
+  <si>
+    <t>SRDX</t>
+  </si>
+  <si>
+    <t>ETHE</t>
+  </si>
+  <si>
+    <t>ANF</t>
+  </si>
+  <si>
+    <t>TREX</t>
+  </si>
+  <si>
+    <t>VKTX</t>
+  </si>
+  <si>
+    <t>GKOS</t>
+  </si>
+  <si>
+    <t>RCMT</t>
+  </si>
+  <si>
+    <t>SSD</t>
+  </si>
+  <si>
+    <t>TTD</t>
+  </si>
+  <si>
+    <t>KALV</t>
+  </si>
+  <si>
+    <t>SGH</t>
+  </si>
+  <si>
+    <t>HELE</t>
+  </si>
+  <si>
+    <t>OC</t>
+  </si>
+  <si>
+    <t>AVDL</t>
+  </si>
+  <si>
+    <t>RILY</t>
+  </si>
+  <si>
+    <t>ACVA</t>
+  </si>
+  <si>
+    <t>IAS</t>
+  </si>
+  <si>
+    <t>IBP</t>
+  </si>
+  <si>
+    <t>MDWT</t>
+  </si>
+  <si>
+    <t>JOE</t>
+  </si>
+  <si>
+    <t>PHM</t>
+  </si>
+  <si>
+    <t>COCO</t>
+  </si>
+  <si>
+    <t>UFPT</t>
+  </si>
+  <si>
+    <t>BOOT</t>
+  </si>
+  <si>
+    <t>MLP</t>
+  </si>
+  <si>
+    <t>ONON</t>
+  </si>
+  <si>
+    <t>AEHR</t>
+  </si>
+  <si>
+    <t>GRBK</t>
   </si>
   <si>
     <t>IMTX</t>
   </si>
   <si>
-    <t>NRP</t>
-  </si>
-  <si>
-    <t>THC</t>
-  </si>
-  <si>
-    <t>NEWR</t>
-  </si>
-  <si>
-    <t>RKT</t>
-  </si>
-  <si>
-    <t>HZO</t>
-  </si>
-  <si>
-    <t>CARG</t>
-  </si>
-  <si>
-    <t>GRFS</t>
-  </si>
-  <si>
-    <t>MLNK</t>
-  </si>
-  <si>
-    <t>SPOT</t>
-  </si>
-  <si>
-    <t>TMHC</t>
-  </si>
-  <si>
-    <t>LAD</t>
-  </si>
-  <si>
-    <t>ITRI</t>
-  </si>
-  <si>
-    <t>TWST</t>
-  </si>
-  <si>
-    <t>BATRA</t>
-  </si>
-  <si>
-    <t>ZEUS</t>
-  </si>
-  <si>
-    <t>JBL</t>
-  </si>
-  <si>
-    <t>JHX</t>
-  </si>
-  <si>
-    <t>CSTM</t>
-  </si>
-  <si>
-    <t>AEL</t>
-  </si>
-  <si>
-    <t>ERII</t>
-  </si>
-  <si>
-    <t>MLCO</t>
-  </si>
-  <si>
-    <t>INTT</t>
-  </si>
-  <si>
-    <t>AGRO</t>
-  </si>
-  <si>
-    <t>CNM</t>
-  </si>
-  <si>
-    <t>IAC</t>
-  </si>
-  <si>
-    <t>ZUO</t>
-  </si>
-  <si>
-    <t>MRVL</t>
-  </si>
-  <si>
-    <t>APG</t>
-  </si>
-  <si>
-    <t>BOOT</t>
-  </si>
-  <si>
-    <t>ADDDF</t>
-  </si>
-  <si>
-    <t>ASMIY</t>
-  </si>
-  <si>
-    <t>ARHS</t>
-  </si>
-  <si>
-    <t>EME</t>
-  </si>
-  <si>
-    <t>IMVT</t>
-  </si>
-  <si>
-    <t>TPH</t>
-  </si>
-  <si>
-    <t>EVO</t>
-  </si>
-  <si>
-    <t>ATLC</t>
-  </si>
-  <si>
-    <t>AXR</t>
-  </si>
-  <si>
-    <t>ATEC</t>
-  </si>
-  <si>
-    <t>PATK</t>
-  </si>
-  <si>
-    <t>ABR</t>
-  </si>
-  <si>
-    <t>ANGN</t>
-  </si>
-  <si>
-    <t>IDCC</t>
-  </si>
-  <si>
-    <t>CSWI</t>
-  </si>
-  <si>
-    <t>BLX</t>
-  </si>
-  <si>
-    <t>PANW</t>
-  </si>
-  <si>
-    <t>TRDA</t>
-  </si>
-  <si>
-    <t>LPRO</t>
-  </si>
-  <si>
-    <t>INBK</t>
-  </si>
-  <si>
-    <t>BPMC</t>
-  </si>
-  <si>
-    <t>GOCO</t>
-  </si>
-  <si>
-    <t>VNO</t>
-  </si>
-  <si>
-    <t>TXG</t>
-  </si>
-  <si>
-    <t>KALV</t>
-  </si>
-  <si>
-    <t>HCCI</t>
-  </si>
-  <si>
-    <t>FUTU</t>
-  </si>
-  <si>
-    <t>CCJ</t>
-  </si>
-  <si>
-    <t>ARCB</t>
-  </si>
-  <si>
-    <t>AMWD</t>
-  </si>
-  <si>
-    <t>LRCX</t>
-  </si>
-  <si>
-    <t>OII</t>
-  </si>
-  <si>
-    <t>TMDX</t>
-  </si>
-  <si>
-    <t>AAN</t>
-  </si>
-  <si>
-    <t>ZGN</t>
-  </si>
-  <si>
-    <t>RRGB</t>
-  </si>
-  <si>
-    <t>IGT</t>
-  </si>
-  <si>
-    <t>NATR</t>
-  </si>
-  <si>
-    <t>PCOR</t>
-  </si>
-  <si>
-    <t>IESC</t>
-  </si>
-  <si>
-    <t>ETHE</t>
-  </si>
-  <si>
-    <t>BELFA</t>
-  </si>
-  <si>
-    <t>RCM</t>
-  </si>
-  <si>
-    <t>BYND</t>
-  </si>
-  <si>
-    <t>MTW</t>
-  </si>
-  <si>
-    <t>MDC</t>
-  </si>
-  <si>
-    <t>CARS</t>
-  </si>
-  <si>
-    <t>ZWS</t>
-  </si>
-  <si>
-    <t>TOL</t>
-  </si>
-  <si>
-    <t>FROG</t>
-  </si>
-  <si>
-    <t>CELH</t>
-  </si>
-  <si>
-    <t>DOMO</t>
-  </si>
-  <si>
-    <t>SHAK</t>
-  </si>
-  <si>
-    <t>HROW</t>
-  </si>
-  <si>
-    <t>MNDY</t>
-  </si>
-  <si>
-    <t>BUR</t>
-  </si>
-  <si>
-    <t>FMS</t>
-  </si>
-  <si>
-    <t>GNRC</t>
-  </si>
-  <si>
-    <t>FTI</t>
-  </si>
-  <si>
-    <t>CYD</t>
-  </si>
-  <si>
-    <t>CLBR</t>
-  </si>
-  <si>
-    <t>LEGN</t>
+    <t>JELD</t>
+  </si>
+  <si>
+    <t>GRVY</t>
+  </si>
+  <si>
+    <t>PLPC</t>
+  </si>
+  <si>
+    <t>GLBE</t>
+  </si>
+  <si>
+    <t>PHAT</t>
+  </si>
+  <si>
+    <t>LUNG</t>
+  </si>
+  <si>
+    <t>MATX</t>
+  </si>
+  <si>
+    <t>MRUS</t>
+  </si>
+  <si>
+    <t>GGAL</t>
+  </si>
+  <si>
+    <t>ABCM</t>
+  </si>
+  <si>
+    <t>CRMT</t>
+  </si>
+  <si>
+    <t>BLD</t>
+  </si>
+  <si>
+    <t>ENVX</t>
+  </si>
+  <si>
+    <t>MNSO</t>
+  </si>
+  <si>
+    <t>STVN</t>
+  </si>
+  <si>
+    <t>DMRC</t>
+  </si>
+  <si>
+    <t>BWMX</t>
+  </si>
+  <si>
+    <t>SG</t>
+  </si>
+  <si>
+    <t>ISEE</t>
   </si>
   <si>
     <t>EXTR</t>
   </si>
   <si>
-    <t>CRS</t>
-  </si>
-  <si>
-    <t>ONTO</t>
-  </si>
-  <si>
-    <t>AVDX</t>
-  </si>
-  <si>
-    <t>FIVN</t>
-  </si>
-  <si>
-    <t>CSAN</t>
+    <t>IMRX</t>
+  </si>
+  <si>
+    <t>RCL</t>
+  </si>
+  <si>
+    <t>PCT</t>
+  </si>
+  <si>
+    <t>FCAP</t>
+  </si>
+  <si>
+    <t>SDGR</t>
+  </si>
+  <si>
+    <t>WFRD</t>
+  </si>
+  <si>
+    <t>ARCT</t>
+  </si>
+  <si>
+    <t>ROKU</t>
+  </si>
+  <si>
+    <t>CVRX</t>
+  </si>
+  <si>
+    <t>BLU</t>
+  </si>
+  <si>
+    <t>CVLG</t>
+  </si>
+  <si>
+    <t>TCMD</t>
+  </si>
+  <si>
+    <t>VSTM</t>
   </si>
   <si>
     <t>RELY</t>
   </si>
   <si>
-    <t>CARR</t>
-  </si>
-  <si>
-    <t>ALGM</t>
-  </si>
-  <si>
-    <t>TREX</t>
-  </si>
-  <si>
-    <t>MOMO</t>
-  </si>
-  <si>
-    <t>ATI</t>
-  </si>
-  <si>
-    <t>LII</t>
-  </si>
-  <si>
-    <t>ON</t>
-  </si>
-  <si>
-    <t>PKOH</t>
-  </si>
-  <si>
-    <t>ARCO</t>
-  </si>
-  <si>
-    <t>AVGO</t>
-  </si>
-  <si>
-    <t>WPRT</t>
-  </si>
-  <si>
-    <t>BWMN</t>
-  </si>
-  <si>
-    <t>PLAB</t>
-  </si>
-  <si>
-    <t>FTAI</t>
-  </si>
-  <si>
-    <t>MLP</t>
-  </si>
-  <si>
-    <t>KRT</t>
-  </si>
-  <si>
-    <t>KRNT</t>
-  </si>
-  <si>
-    <t>TGTX</t>
-  </si>
-  <si>
-    <t>KBH</t>
-  </si>
-  <si>
-    <t>NEX</t>
-  </si>
-  <si>
-    <t>KNSA</t>
-  </si>
-  <si>
-    <t>AZEK</t>
-  </si>
-  <si>
-    <t>THO</t>
-  </si>
-  <si>
-    <t>SRDX</t>
-  </si>
-  <si>
-    <t>MTH</t>
-  </si>
-  <si>
-    <t>SBOW</t>
-  </si>
-  <si>
-    <t>CFLT</t>
-  </si>
-  <si>
-    <t>ALGT</t>
-  </si>
-  <si>
-    <t>SLG</t>
-  </si>
-  <si>
-    <t>CAAP</t>
-  </si>
-  <si>
-    <t>MATX</t>
-  </si>
-  <si>
-    <t>PETQ</t>
-  </si>
-  <si>
-    <t>BECN</t>
-  </si>
-  <si>
-    <t>NYCB</t>
-  </si>
-  <si>
-    <t>VIPS</t>
-  </si>
-  <si>
-    <t>SMHI</t>
-  </si>
-  <si>
-    <t>ACCD</t>
-  </si>
-  <si>
-    <t>MGNI</t>
-  </si>
-  <si>
-    <t>KRYS</t>
-  </si>
-  <si>
-    <t>HOOD</t>
-  </si>
-  <si>
-    <t>SIBN</t>
-  </si>
-  <si>
-    <t>APPF</t>
-  </si>
-  <si>
-    <t>TYRA</t>
-  </si>
-  <si>
-    <t>AZUL</t>
-  </si>
-  <si>
-    <t>MDWT</t>
-  </si>
-  <si>
-    <t>LPG</t>
-  </si>
-  <si>
-    <t>OC</t>
-  </si>
-  <si>
-    <t>SGH</t>
-  </si>
-  <si>
-    <t>ABNB</t>
-  </si>
-  <si>
-    <t>ETRN</t>
-  </si>
-  <si>
-    <t>RDNT</t>
+    <t>RH</t>
+  </si>
+  <si>
+    <t>MORF</t>
+  </si>
+  <si>
+    <t>RIVN</t>
+  </si>
+  <si>
+    <t>GBTC</t>
+  </si>
+  <si>
+    <t>CMT</t>
+  </si>
+  <si>
+    <t>MSTR</t>
+  </si>
+  <si>
+    <t>EBIX</t>
+  </si>
+  <si>
+    <t>FCNCA</t>
+  </si>
+  <si>
+    <t>GBX</t>
   </si>
   <si>
     <t>BCC</t>
   </si>
   <si>
-    <t>ANF</t>
-  </si>
-  <si>
-    <t>TSQ</t>
-  </si>
-  <si>
-    <t>ADBE</t>
-  </si>
-  <si>
-    <t>YPF</t>
-  </si>
-  <si>
-    <t>PRO</t>
-  </si>
-  <si>
-    <t>RCMT</t>
-  </si>
-  <si>
-    <t>HELE</t>
-  </si>
-  <si>
-    <t>STVN</t>
-  </si>
-  <si>
-    <t>GSHD</t>
-  </si>
-  <si>
-    <t>YELP</t>
-  </si>
-  <si>
-    <t>FWAC</t>
-  </si>
-  <si>
-    <t>DV</t>
-  </si>
-  <si>
-    <t>CVLG</t>
-  </si>
-  <si>
-    <t>DUOL</t>
-  </si>
-  <si>
-    <t>TDC</t>
-  </si>
-  <si>
-    <t>LMND</t>
-  </si>
-  <si>
-    <t>TARS</t>
-  </si>
-  <si>
-    <t>MORF</t>
-  </si>
-  <si>
-    <t>SHC</t>
-  </si>
-  <si>
-    <t>BLD</t>
-  </si>
-  <si>
-    <t>KRUS</t>
-  </si>
-  <si>
-    <t>AVDL</t>
-  </si>
-  <si>
-    <t>SHOP</t>
+    <t>ROIV</t>
+  </si>
+  <si>
+    <t>QTRX</t>
+  </si>
+  <si>
+    <t>EDU</t>
+  </si>
+  <si>
+    <t>RXRX</t>
+  </si>
+  <si>
+    <t>PRG</t>
+  </si>
+  <si>
+    <t>COIN</t>
+  </si>
+  <si>
+    <t>SAIA</t>
+  </si>
+  <si>
+    <t>ACLS</t>
+  </si>
+  <si>
+    <t>DICE</t>
+  </si>
+  <si>
+    <t>LZ</t>
+  </si>
+  <si>
+    <t>TDW</t>
+  </si>
+  <si>
+    <t>NOA</t>
+  </si>
+  <si>
+    <t>STRL</t>
+  </si>
+  <si>
+    <t>MHO</t>
+  </si>
+  <si>
+    <t>NWLI</t>
+  </si>
+  <si>
+    <t>FSLY</t>
+  </si>
+  <si>
+    <t>HOV</t>
+  </si>
+  <si>
+    <t>DKNG</t>
+  </si>
+  <si>
+    <t>NGMS</t>
+  </si>
+  <si>
+    <t>CCL</t>
+  </si>
+  <si>
+    <t>CUBI</t>
+  </si>
+  <si>
+    <t>EDN</t>
+  </si>
+  <si>
+    <t>CUK</t>
+  </si>
+  <si>
+    <t>XP</t>
+  </si>
+  <si>
+    <t>ATRO</t>
+  </si>
+  <si>
+    <t>WRLD</t>
+  </si>
+  <si>
+    <t>IOT</t>
+  </si>
+  <si>
+    <t>USAP</t>
+  </si>
+  <si>
+    <t>CPS</t>
+  </si>
+  <si>
+    <t>VECT</t>
+  </si>
+  <si>
+    <t>NIO</t>
+  </si>
+  <si>
+    <t>CABA</t>
+  </si>
+  <si>
+    <t>BLDR</t>
+  </si>
+  <si>
+    <t>CLS</t>
+  </si>
+  <si>
+    <t>ALPN</t>
+  </si>
+  <si>
+    <t>LMB</t>
+  </si>
+  <si>
+    <t>MDB</t>
+  </si>
+  <si>
+    <t>XPO</t>
+  </si>
+  <si>
+    <t>OSTK</t>
+  </si>
+  <si>
+    <t>MRNS</t>
+  </si>
+  <si>
+    <t>EXPI</t>
+  </si>
+  <si>
+    <t>LSEA</t>
+  </si>
+  <si>
+    <t>KDNY</t>
+  </si>
+  <si>
+    <t>ODC</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>AMPH</t>
+  </si>
+  <si>
+    <t>CAMT</t>
+  </si>
+  <si>
+    <t>DFH</t>
+  </si>
+  <si>
+    <t>ELF</t>
+  </si>
+  <si>
+    <t>NVDA</t>
+  </si>
+  <si>
+    <t>FRD</t>
+  </si>
+  <si>
+    <t>RCEL</t>
+  </si>
+  <si>
+    <t>APP</t>
+  </si>
+  <si>
+    <t>FOR</t>
+  </si>
+  <si>
+    <t>AI</t>
+  </si>
+  <si>
+    <t>RDFN</t>
+  </si>
+  <si>
+    <t>CMPR</t>
+  </si>
+  <si>
+    <t>SKYW</t>
+  </si>
+  <si>
+    <t>RXST</t>
+  </si>
+  <si>
+    <t>CBAY</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>BZH</t>
+  </si>
+  <si>
+    <t>MEOA</t>
+  </si>
+  <si>
+    <t>LI</t>
+  </si>
+  <si>
+    <t>CIR</t>
+  </si>
+  <si>
+    <t>OPRA</t>
+  </si>
+  <si>
+    <t>WEAV</t>
+  </si>
+  <si>
+    <t>PLTR</t>
   </si>
   <si>
     <t>POWL</t>
   </si>
   <si>
-    <t>LOB</t>
-  </si>
-  <si>
-    <t>TAYD</t>
-  </si>
-  <si>
-    <t>ALGN</t>
-  </si>
-  <si>
-    <t>SSD</t>
-  </si>
-  <si>
-    <t>MRUS</t>
-  </si>
-  <si>
-    <t>UFPT</t>
-  </si>
-  <si>
-    <t>GRVY</t>
-  </si>
-  <si>
-    <t>BVH</t>
-  </si>
-  <si>
-    <t>FCNCA</t>
-  </si>
-  <si>
-    <t>RH</t>
-  </si>
-  <si>
-    <t>VIST</t>
-  </si>
-  <si>
-    <t>DDOG</t>
-  </si>
-  <si>
-    <t>IBP</t>
-  </si>
-  <si>
-    <t>FSLY</t>
-  </si>
-  <si>
-    <t>FLNC</t>
-  </si>
-  <si>
-    <t>FCAP</t>
-  </si>
-  <si>
-    <t>CRMT</t>
-  </si>
-  <si>
-    <t>SPOK</t>
-  </si>
-  <si>
-    <t>ONON</t>
-  </si>
-  <si>
-    <t>JELD</t>
-  </si>
-  <si>
-    <t>DICE</t>
-  </si>
-  <si>
-    <t>NUVL</t>
-  </si>
-  <si>
-    <t>TSLA</t>
-  </si>
-  <si>
-    <t>ERO</t>
-  </si>
-  <si>
-    <t>AUPH</t>
-  </si>
-  <si>
-    <t>HUBS</t>
-  </si>
-  <si>
-    <t>BLU</t>
-  </si>
-  <si>
-    <t>ACAD</t>
-  </si>
-  <si>
-    <t>U</t>
-  </si>
-  <si>
-    <t>ABCM</t>
-  </si>
-  <si>
-    <t>JOE</t>
-  </si>
-  <si>
-    <t>DASH</t>
-  </si>
-  <si>
-    <t>BMEA</t>
-  </si>
-  <si>
-    <t>NCLH</t>
-  </si>
-  <si>
-    <t>ISEE</t>
-  </si>
-  <si>
-    <t>BMA</t>
-  </si>
-  <si>
-    <t>EB</t>
-  </si>
-  <si>
-    <t>AFRM</t>
-  </si>
-  <si>
-    <t>GKOS</t>
-  </si>
-  <si>
-    <t>PHM</t>
-  </si>
-  <si>
-    <t>GTLS</t>
-  </si>
-  <si>
-    <t>VKTX</t>
-  </si>
-  <si>
-    <t>BWMX</t>
-  </si>
-  <si>
-    <t>RILY</t>
-  </si>
-  <si>
-    <t>NWLI</t>
-  </si>
-  <si>
-    <t>ACVA</t>
-  </si>
-  <si>
-    <t>NOA</t>
-  </si>
-  <si>
-    <t>PLPC</t>
-  </si>
-  <si>
-    <t>GBX</t>
-  </si>
-  <si>
-    <t>CVRX</t>
-  </si>
-  <si>
-    <t>EXAS</t>
-  </si>
-  <si>
-    <t>BRZE</t>
-  </si>
-  <si>
-    <t>UBER</t>
-  </si>
-  <si>
-    <t>DOCN</t>
-  </si>
-  <si>
-    <t>TDW</t>
-  </si>
-  <si>
-    <t>WFRD</t>
-  </si>
-  <si>
-    <t>MNSO</t>
-  </si>
-  <si>
-    <t>STRL</t>
-  </si>
-  <si>
-    <t>ALPN</t>
-  </si>
-  <si>
-    <t>GBTC</t>
-  </si>
-  <si>
-    <t>COCO</t>
-  </si>
-  <si>
-    <t>MOD</t>
-  </si>
-  <si>
-    <t>EDU</t>
-  </si>
-  <si>
-    <t>GGAL</t>
-  </si>
-  <si>
-    <t>NGMS</t>
-  </si>
-  <si>
-    <t>VSTM</t>
-  </si>
-  <si>
-    <t>IMRX</t>
-  </si>
-  <si>
-    <t>ELF</t>
-  </si>
-  <si>
-    <t>SAIA</t>
-  </si>
-  <si>
-    <t>TTD</t>
-  </si>
-  <si>
-    <t>LUNG</t>
-  </si>
-  <si>
-    <t>CMT</t>
-  </si>
-  <si>
-    <t>PHAT</t>
-  </si>
-  <si>
-    <t>LZ</t>
-  </si>
-  <si>
-    <t>RCL</t>
-  </si>
-  <si>
-    <t>IAS</t>
-  </si>
-  <si>
-    <t>AEHR</t>
-  </si>
-  <si>
-    <t>ROIV</t>
-  </si>
-  <si>
-    <t>ATRO</t>
-  </si>
-  <si>
-    <t>TCMD</t>
+    <t>MARA</t>
+  </si>
+  <si>
+    <t>RXDX</t>
+  </si>
+  <si>
+    <t>INOD</t>
+  </si>
+  <si>
+    <t>ARLO</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>WW</t>
+  </si>
+  <si>
+    <t>ROOT</t>
   </si>
   <si>
     <t>VRT</t>
   </si>
   <si>
-    <t>VICR</t>
-  </si>
-  <si>
-    <t>GRBK</t>
-  </si>
-  <si>
-    <t>HOV</t>
-  </si>
-  <si>
-    <t>SG</t>
-  </si>
-  <si>
-    <t>GLBE</t>
-  </si>
-  <si>
-    <t>CUBI</t>
-  </si>
-  <si>
-    <t>VECT</t>
-  </si>
-  <si>
-    <t>RIVN</t>
-  </si>
-  <si>
-    <t>PCT</t>
-  </si>
-  <si>
-    <t>PRG</t>
-  </si>
-  <si>
-    <t>LTRPB</t>
-  </si>
-  <si>
-    <t>KDNY</t>
-  </si>
-  <si>
-    <t>XP</t>
-  </si>
-  <si>
-    <t>AMPH</t>
-  </si>
-  <si>
-    <t>MHO</t>
-  </si>
-  <si>
-    <t>BLDR</t>
-  </si>
-  <si>
-    <t>ACLS</t>
-  </si>
-  <si>
-    <t>ROKU</t>
-  </si>
-  <si>
-    <t>RXRX</t>
-  </si>
-  <si>
-    <t>NIO</t>
-  </si>
-  <si>
-    <t>NVTS</t>
-  </si>
-  <si>
-    <t>EBIX</t>
-  </si>
-  <si>
-    <t>LMB</t>
-  </si>
-  <si>
-    <t>QTRX</t>
-  </si>
-  <si>
-    <t>XPO</t>
-  </si>
-  <si>
-    <t>CAMT</t>
-  </si>
-  <si>
-    <t>ODC</t>
-  </si>
-  <si>
-    <t>USAP</t>
-  </si>
-  <si>
-    <t>EDN</t>
-  </si>
-  <si>
-    <t>CLS</t>
-  </si>
-  <si>
-    <t>ARCT</t>
-  </si>
-  <si>
-    <t>FRD</t>
-  </si>
-  <si>
-    <t>DKNG</t>
-  </si>
-  <si>
-    <t>COIN</t>
-  </si>
-  <si>
-    <t>OSTK</t>
-  </si>
-  <si>
-    <t>FOR</t>
-  </si>
-  <si>
-    <t>CPS</t>
-  </si>
-  <si>
-    <t>MRNS</t>
-  </si>
-  <si>
-    <t>LI</t>
-  </si>
-  <si>
-    <t>MSTR</t>
-  </si>
-  <si>
-    <t>CCL</t>
-  </si>
-  <si>
-    <t>WRLD</t>
-  </si>
-  <si>
-    <t>CMPR</t>
-  </si>
-  <si>
-    <t>CUK</t>
-  </si>
-  <si>
-    <t>EXPI</t>
-  </si>
-  <si>
-    <t>IOT</t>
-  </si>
-  <si>
-    <t>NVDA</t>
-  </si>
-  <si>
-    <t>CABA</t>
-  </si>
-  <si>
-    <t>MEOA</t>
-  </si>
-  <si>
-    <t>QS</t>
-  </si>
-  <si>
-    <t>ENVX</t>
-  </si>
-  <si>
-    <t>APP</t>
-  </si>
-  <si>
-    <t>SKYW</t>
-  </si>
-  <si>
-    <t>RXDX</t>
-  </si>
-  <si>
-    <t>DFH</t>
-  </si>
-  <si>
-    <t>MDB</t>
-  </si>
-  <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>CIR</t>
-  </si>
-  <si>
-    <t>AI</t>
-  </si>
-  <si>
-    <t>W</t>
-  </si>
-  <si>
-    <t>RXST</t>
-  </si>
-  <si>
-    <t>CBAY</t>
-  </si>
-  <si>
-    <t>OPRA</t>
-  </si>
-  <si>
-    <t>BZH</t>
-  </si>
-  <si>
-    <t>SOFI</t>
-  </si>
-  <si>
-    <t>ARLO</t>
+    <t>URGN</t>
+  </si>
+  <si>
+    <t>MEOAU</t>
+  </si>
+  <si>
+    <t>XPEV</t>
   </si>
   <si>
     <t>EVLO</t>
   </si>
   <si>
-    <t>SDGR</t>
-  </si>
-  <si>
-    <t>RCEL</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>RDFN</t>
-  </si>
-  <si>
-    <t>PLTR</t>
-  </si>
-  <si>
-    <t>MARA</t>
-  </si>
-  <si>
-    <t>WEAV</t>
-  </si>
-  <si>
-    <t>ROOT</t>
-  </si>
-  <si>
-    <t>MEOAU</t>
-  </si>
-  <si>
-    <t>AMSC</t>
-  </si>
-  <si>
-    <t>INOD</t>
-  </si>
-  <si>
-    <t>WW</t>
-  </si>
-  <si>
-    <t>XPEV</t>
-  </si>
-  <si>
-    <t>URGN</t>
-  </si>
-  <si>
     <t>RIOT</t>
   </si>
   <si>
+    <t>EH</t>
+  </si>
+  <si>
+    <t>IMGN</t>
+  </si>
+  <si>
+    <t>SMCI</t>
+  </si>
+  <si>
+    <t>RETA</t>
+  </si>
+  <si>
+    <t>BBIO</t>
+  </si>
+  <si>
     <t>CDLX</t>
   </si>
   <si>
-    <t>EH</t>
-  </si>
-  <si>
-    <t>SMCI</t>
-  </si>
-  <si>
-    <t>RETA</t>
-  </si>
-  <si>
-    <t>IMGN</t>
+    <t>IONQ</t>
   </si>
   <si>
     <t>EYPT</t>
@@ -1105,22 +1090,19 @@
     <t>PHVS</t>
   </si>
   <si>
-    <t>BBIO</t>
-  </si>
-  <si>
-    <t>IONQ</t>
+    <t>UPST</t>
+  </si>
+  <si>
+    <t>NERV</t>
   </si>
   <si>
     <t>SGTX</t>
   </si>
   <si>
-    <t>UPST</t>
+    <t>AURCU</t>
   </si>
   <si>
     <t>AURC</t>
-  </si>
-  <si>
-    <t>AURCU</t>
   </si>
   <si>
     <t>CVNA</t>
@@ -1483,7 +1465,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B372"/>
+  <dimension ref="A1:B366"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1499,7 +1481,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1">
-        <v>132.4007905439622</v>
+        <v>125.4154569860466</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1507,7 +1489,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1">
-        <v>132.4804150761046</v>
+        <v>125.4657774009173</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1515,7 +1497,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1">
-        <v>132.5112663348856</v>
+        <v>125.4699506555531</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1523,7 +1505,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="1">
-        <v>132.5127920865168</v>
+        <v>125.4731562073149</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1531,7 +1513,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="1">
-        <v>132.5201029160819</v>
+        <v>125.6951306276823</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1539,7 +1521,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="1">
-        <v>132.5496053320778</v>
+        <v>125.7573126181318</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1547,7 +1529,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="1">
-        <v>132.5513518035199</v>
+        <v>125.7623768225628</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1555,7 +1537,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="1">
-        <v>132.5868141233705</v>
+        <v>125.7674813525781</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1563,7 +1545,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="1">
-        <v>132.6021110088814</v>
+        <v>125.8103065931918</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1571,7 +1553,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="1">
-        <v>132.6341144798291</v>
+        <v>125.9707227683371</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1579,7 +1561,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="1">
-        <v>132.6370402124867</v>
+        <v>125.9887530401834</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1587,7 +1569,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="1">
-        <v>132.6761322954118</v>
+        <v>126.0024384509456</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1595,7 +1577,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="1">
-        <v>132.7059363108922</v>
+        <v>126.0036838243176</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1603,7 +1585,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="1">
-        <v>132.7579462424045</v>
+        <v>126.0097318327312</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1611,7 +1593,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="1">
-        <v>132.7802772224183</v>
+        <v>126.0343638742141</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1619,7 +1601,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="1">
-        <v>132.8072418058811</v>
+        <v>126.140502577076</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1627,7 +1609,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="1">
-        <v>132.9888920113413</v>
+        <v>126.1726950360488</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1635,7 +1617,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="1">
-        <v>133.0103260834936</v>
+        <v>126.2011857609074</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1643,7 +1625,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="1">
-        <v>133.0190818791018</v>
+        <v>126.2308646934236</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1651,7 +1633,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="1">
-        <v>133.0395323920544</v>
+        <v>126.2461864176311</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1659,7 +1641,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="1">
-        <v>133.0911338518626</v>
+        <v>126.2602539860691</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1667,7 +1649,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="1">
-        <v>133.1151961244593</v>
+        <v>126.3146395324592</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1675,7 +1657,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="1">
-        <v>133.2737579595212</v>
+        <v>126.3386576001221</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1683,7 +1665,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="1">
-        <v>133.3150128157422</v>
+        <v>126.3842058001431</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1691,7 +1673,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="1">
-        <v>133.3308046370113</v>
+        <v>126.4932365873209</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1699,7 +1681,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="1">
-        <v>133.5077832914707</v>
+        <v>126.5777271183209</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1707,7 +1689,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="1">
-        <v>133.5122565754114</v>
+        <v>126.6382005830039</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1715,7 +1697,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="1">
-        <v>133.5122787335413</v>
+        <v>126.7214873855165</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1723,7 +1705,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="1">
-        <v>133.6748790423493</v>
+        <v>126.7550295314504</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1731,7 +1713,7 @@
         <v>31</v>
       </c>
       <c r="B31" s="1">
-        <v>133.6851306504516</v>
+        <v>126.7716456050033</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1739,7 +1721,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="1">
-        <v>133.7415564082201</v>
+        <v>126.8170257536855</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1747,7 +1729,7 @@
         <v>33</v>
       </c>
       <c r="B33" s="1">
-        <v>133.7703153172166</v>
+        <v>126.8588001506004</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1755,7 +1737,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="1">
-        <v>133.8220223489677</v>
+        <v>126.8767456043908</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1763,7 +1745,7 @@
         <v>35</v>
       </c>
       <c r="B35" s="1">
-        <v>133.8390295725521</v>
+        <v>126.8777742662679</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1771,7 +1753,7 @@
         <v>36</v>
       </c>
       <c r="B36" s="1">
-        <v>133.8649845864822</v>
+        <v>126.9119845263428</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1779,7 +1761,7 @@
         <v>37</v>
       </c>
       <c r="B37" s="1">
-        <v>133.8993498886863</v>
+        <v>126.9222855493987</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1787,7 +1769,7 @@
         <v>38</v>
       </c>
       <c r="B38" s="1">
-        <v>133.927745362198</v>
+        <v>126.9612372181901</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1795,7 +1777,7 @@
         <v>39</v>
       </c>
       <c r="B39" s="1">
-        <v>134.0278751657921</v>
+        <v>126.992605114516</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1803,7 +1785,7 @@
         <v>40</v>
       </c>
       <c r="B40" s="1">
-        <v>134.0511420543813</v>
+        <v>127.0473652217298</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1811,7 +1793,7 @@
         <v>41</v>
       </c>
       <c r="B41" s="1">
-        <v>134.0927143052481</v>
+        <v>127.1311619578275</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -1819,7 +1801,7 @@
         <v>42</v>
       </c>
       <c r="B42" s="1">
-        <v>134.0992295488805</v>
+        <v>127.145499222131</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -1827,7 +1809,7 @@
         <v>43</v>
       </c>
       <c r="B43" s="1">
-        <v>134.1570176188948</v>
+        <v>127.2317493649838</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1835,7 +1817,7 @@
         <v>44</v>
       </c>
       <c r="B44" s="1">
-        <v>134.2086963302984</v>
+        <v>127.2820628086953</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1843,7 +1825,7 @@
         <v>45</v>
       </c>
       <c r="B45" s="1">
-        <v>134.2858865551888</v>
+        <v>127.3103653781682</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1851,7 +1833,7 @@
         <v>46</v>
       </c>
       <c r="B46" s="1">
-        <v>134.3080848914423</v>
+        <v>127.3644032535261</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -1859,7 +1841,7 @@
         <v>47</v>
       </c>
       <c r="B47" s="1">
-        <v>134.314475745087</v>
+        <v>127.3767151230392</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -1867,7 +1849,7 @@
         <v>48</v>
       </c>
       <c r="B48" s="1">
-        <v>134.3295306531838</v>
+        <v>127.4136491841599</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1875,7 +1857,7 @@
         <v>49</v>
       </c>
       <c r="B49" s="1">
-        <v>134.3643850699513</v>
+        <v>127.4969527508918</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1883,7 +1865,7 @@
         <v>50</v>
       </c>
       <c r="B50" s="1">
-        <v>134.3824538807993</v>
+        <v>127.502994653038</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1891,7 +1873,7 @@
         <v>51</v>
       </c>
       <c r="B51" s="1">
-        <v>134.3884700644366</v>
+        <v>127.535502412379</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1899,7 +1881,7 @@
         <v>52</v>
       </c>
       <c r="B52" s="1">
-        <v>134.4071464186206</v>
+        <v>127.5564645692201</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1907,7 +1889,7 @@
         <v>53</v>
       </c>
       <c r="B53" s="1">
-        <v>134.454367680038</v>
+        <v>127.6012255266318</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1915,7 +1897,7 @@
         <v>54</v>
       </c>
       <c r="B54" s="1">
-        <v>134.6527947970509</v>
+        <v>127.6254711441808</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1923,7 +1905,7 @@
         <v>55</v>
       </c>
       <c r="B55" s="1">
-        <v>134.7217690934657</v>
+        <v>127.6728845124347</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1931,7 +1913,7 @@
         <v>56</v>
       </c>
       <c r="B56" s="1">
-        <v>134.7364636298082</v>
+        <v>127.7057364483806</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1939,7 +1921,7 @@
         <v>57</v>
       </c>
       <c r="B57" s="1">
-        <v>134.8953217040526</v>
+        <v>127.7868839661596</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1947,7 +1929,7 @@
         <v>58</v>
       </c>
       <c r="B58" s="1">
-        <v>134.9332486243562</v>
+        <v>127.7902263354532</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1955,7 +1937,7 @@
         <v>59</v>
       </c>
       <c r="B59" s="1">
-        <v>134.9343014815151</v>
+        <v>127.8041030511158</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1963,7 +1945,7 @@
         <v>60</v>
       </c>
       <c r="B60" s="1">
-        <v>134.9875048167602</v>
+        <v>127.8818886223555</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1971,7 +1953,7 @@
         <v>61</v>
       </c>
       <c r="B61" s="1">
-        <v>135.4186105577915</v>
+        <v>127.8951703017764</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1979,7 +1961,7 @@
         <v>62</v>
       </c>
       <c r="B62" s="1">
-        <v>135.437913776069</v>
+        <v>127.9976450407955</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1987,7 +1969,7 @@
         <v>63</v>
       </c>
       <c r="B63" s="1">
-        <v>135.4400902817853</v>
+        <v>128.0999069860749</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1995,7 +1977,7 @@
         <v>64</v>
       </c>
       <c r="B64" s="1">
-        <v>135.4600862620373</v>
+        <v>128.3485026017449</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -2003,7 +1985,7 @@
         <v>65</v>
       </c>
       <c r="B65" s="1">
-        <v>135.5158023774854</v>
+        <v>128.3651514896611</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -2011,7 +1993,7 @@
         <v>66</v>
       </c>
       <c r="B66" s="1">
-        <v>135.5970034853857</v>
+        <v>128.5911648524974</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -2019,7 +2001,7 @@
         <v>67</v>
       </c>
       <c r="B67" s="1">
-        <v>135.6100430517713</v>
+        <v>128.7475335240506</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -2027,7 +2009,7 @@
         <v>68</v>
       </c>
       <c r="B68" s="1">
-        <v>135.621238057134</v>
+        <v>128.9200542805826</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -2035,7 +2017,7 @@
         <v>69</v>
       </c>
       <c r="B69" s="1">
-        <v>135.6674834685106</v>
+        <v>128.95561112324</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -2043,7 +2025,7 @@
         <v>70</v>
       </c>
       <c r="B70" s="1">
-        <v>135.6950767119968</v>
+        <v>129.1319410947947</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -2051,7 +2033,7 @@
         <v>71</v>
       </c>
       <c r="B71" s="1">
-        <v>135.8316055247269</v>
+        <v>129.138346324377</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -2059,7 +2041,7 @@
         <v>72</v>
       </c>
       <c r="B72" s="1">
-        <v>135.9572991274033</v>
+        <v>129.1447575418808</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2067,7 +2049,7 @@
         <v>73</v>
       </c>
       <c r="B73" s="1">
-        <v>136.0003796518638</v>
+        <v>129.1571037060192</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -2075,7 +2057,7 @@
         <v>74</v>
       </c>
       <c r="B74" s="1">
-        <v>136.0409539148886</v>
+        <v>129.1586443789338</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -2083,7 +2065,7 @@
         <v>75</v>
       </c>
       <c r="B75" s="1">
-        <v>136.1365227108579</v>
+        <v>129.2889071963513</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -2091,7 +2073,7 @@
         <v>76</v>
       </c>
       <c r="B76" s="1">
-        <v>136.2020114899823</v>
+        <v>129.3299901380308</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -2099,7 +2081,7 @@
         <v>77</v>
       </c>
       <c r="B77" s="1">
-        <v>136.2120059214713</v>
+        <v>129.3994700182373</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -2107,7 +2089,7 @@
         <v>78</v>
       </c>
       <c r="B78" s="1">
-        <v>136.2603888711199</v>
+        <v>129.4303284653222</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -2115,7 +2097,7 @@
         <v>79</v>
       </c>
       <c r="B79" s="1">
-        <v>136.2832721840746</v>
+        <v>129.5236368294642</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -2123,7 +2105,7 @@
         <v>80</v>
       </c>
       <c r="B80" s="1">
-        <v>136.4452698276311</v>
+        <v>129.5412432980482</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -2131,7 +2113,7 @@
         <v>81</v>
       </c>
       <c r="B81" s="1">
-        <v>136.5503867216219</v>
+        <v>129.7253918453006</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -2139,7 +2121,7 @@
         <v>82</v>
       </c>
       <c r="B82" s="1">
-        <v>136.5836952936951</v>
+        <v>129.7262873689581</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -2147,7 +2129,7 @@
         <v>83</v>
       </c>
       <c r="B83" s="1">
-        <v>136.7061975357752</v>
+        <v>129.7272213414045</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -2155,7 +2137,7 @@
         <v>84</v>
       </c>
       <c r="B84" s="1">
-        <v>136.7497833782667</v>
+        <v>129.8698644205666</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -2163,7 +2145,7 @@
         <v>85</v>
       </c>
       <c r="B85" s="1">
-        <v>136.966968980622</v>
+        <v>129.9755367236706</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -2171,7 +2153,7 @@
         <v>86</v>
       </c>
       <c r="B86" s="1">
-        <v>136.9925352707035</v>
+        <v>130.1084649858213</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -2179,7 +2161,7 @@
         <v>87</v>
       </c>
       <c r="B87" s="1">
-        <v>137.1737063670191</v>
+        <v>130.1711409472614</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -2187,7 +2169,7 @@
         <v>88</v>
       </c>
       <c r="B88" s="1">
-        <v>137.1758747856475</v>
+        <v>130.1807206687365</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -2195,7 +2177,7 @@
         <v>89</v>
       </c>
       <c r="B89" s="1">
-        <v>137.2528848106885</v>
+        <v>130.1824161149963</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -2203,7 +2185,7 @@
         <v>90</v>
       </c>
       <c r="B90" s="1">
-        <v>137.2578947401826</v>
+        <v>130.2502140495358</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -2211,7 +2193,7 @@
         <v>91</v>
       </c>
       <c r="B91" s="1">
-        <v>137.3058302835671</v>
+        <v>130.2812167710583</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -2219,7 +2201,7 @@
         <v>92</v>
       </c>
       <c r="B92" s="1">
-        <v>137.3197207895626</v>
+        <v>130.2939831637443</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -2227,7 +2209,7 @@
         <v>93</v>
       </c>
       <c r="B93" s="1">
-        <v>137.3209600504246</v>
+        <v>130.3849330816974</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -2235,7 +2217,7 @@
         <v>94</v>
       </c>
       <c r="B94" s="1">
-        <v>137.3950090621339</v>
+        <v>130.4855645348689</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -2243,7 +2225,7 @@
         <v>95</v>
       </c>
       <c r="B95" s="1">
-        <v>137.4776868672812</v>
+        <v>130.5284886310511</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -2251,7 +2233,7 @@
         <v>96</v>
       </c>
       <c r="B96" s="1">
-        <v>137.6168911600767</v>
+        <v>130.5337568068013</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -2259,7 +2241,7 @@
         <v>97</v>
       </c>
       <c r="B97" s="1">
-        <v>137.6931366215514</v>
+        <v>130.560314527763</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -2267,7 +2249,7 @@
         <v>98</v>
       </c>
       <c r="B98" s="1">
-        <v>137.7039096910782</v>
+        <v>130.629312989649</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -2275,7 +2257,7 @@
         <v>99</v>
       </c>
       <c r="B99" s="1">
-        <v>137.8051790211989</v>
+        <v>130.684717037975</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -2283,7 +2265,7 @@
         <v>100</v>
       </c>
       <c r="B100" s="1">
-        <v>137.8431035528049</v>
+        <v>130.7069823003743</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -2291,7 +2273,7 @@
         <v>101</v>
       </c>
       <c r="B101" s="1">
-        <v>137.852799556219</v>
+        <v>130.7831613826413</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -2299,7 +2281,7 @@
         <v>102</v>
       </c>
       <c r="B102" s="1">
-        <v>137.8622315151369</v>
+        <v>130.7909113705638</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -2307,7 +2289,7 @@
         <v>103</v>
       </c>
       <c r="B103" s="1">
-        <v>137.9516076787338</v>
+        <v>130.8084151370885</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -2315,7 +2297,7 @@
         <v>104</v>
       </c>
       <c r="B104" s="1">
-        <v>138.0086240615975</v>
+        <v>130.9545374221148</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -2323,7 +2305,7 @@
         <v>105</v>
       </c>
       <c r="B105" s="1">
-        <v>138.0469576251635</v>
+        <v>130.9738666142341</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -2331,7 +2313,7 @@
         <v>106</v>
       </c>
       <c r="B106" s="1">
-        <v>138.0836151683447</v>
+        <v>131.0673535767937</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -2339,7 +2321,7 @@
         <v>107</v>
       </c>
       <c r="B107" s="1">
-        <v>138.1336033461019</v>
+        <v>131.0941717948733</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -2347,7 +2329,7 @@
         <v>108</v>
       </c>
       <c r="B108" s="1">
-        <v>138.2251659760368</v>
+        <v>131.2024218480401</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -2355,7 +2337,7 @@
         <v>109</v>
       </c>
       <c r="B109" s="1">
-        <v>138.2292759605373</v>
+        <v>131.3265993505261</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -2363,7 +2345,7 @@
         <v>110</v>
       </c>
       <c r="B110" s="1">
-        <v>138.270652207015</v>
+        <v>131.5081729109738</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -2371,7 +2353,7 @@
         <v>111</v>
       </c>
       <c r="B111" s="1">
-        <v>138.4862618209644</v>
+        <v>131.5093489274657</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -2379,7 +2361,7 @@
         <v>112</v>
       </c>
       <c r="B112" s="1">
-        <v>138.5104684789908</v>
+        <v>131.5201898081596</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -2387,7 +2369,7 @@
         <v>113</v>
       </c>
       <c r="B113" s="1">
-        <v>138.5869484828926</v>
+        <v>131.7292080076733</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -2395,7 +2377,7 @@
         <v>114</v>
       </c>
       <c r="B114" s="1">
-        <v>138.6456162984568</v>
+        <v>131.7361136060909</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -2403,7 +2385,7 @@
         <v>115</v>
       </c>
       <c r="B115" s="1">
-        <v>138.6523379055089</v>
+        <v>131.755657470813</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -2411,7 +2393,7 @@
         <v>116</v>
       </c>
       <c r="B116" s="1">
-        <v>138.9800622636457</v>
+        <v>131.7682910342006</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -2419,7 +2401,7 @@
         <v>117</v>
       </c>
       <c r="B117" s="1">
-        <v>138.9872154111048</v>
+        <v>131.7861467476059</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -2427,7 +2409,7 @@
         <v>118</v>
       </c>
       <c r="B118" s="1">
-        <v>139.1903097788406</v>
+        <v>132.0044860904595</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -2435,7 +2417,7 @@
         <v>119</v>
       </c>
       <c r="B119" s="1">
-        <v>139.2151448999379</v>
+        <v>132.0441209219037</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -2443,7 +2425,7 @@
         <v>120</v>
       </c>
       <c r="B120" s="1">
-        <v>139.3051283992682</v>
+        <v>132.0532977514115</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -2451,7 +2433,7 @@
         <v>121</v>
       </c>
       <c r="B121" s="1">
-        <v>139.3603578559304</v>
+        <v>132.0594763273835</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -2459,7 +2441,7 @@
         <v>122</v>
       </c>
       <c r="B122" s="1">
-        <v>139.4311498054925</v>
+        <v>132.1821638423702</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -2467,7 +2449,7 @@
         <v>123</v>
       </c>
       <c r="B123" s="1">
-        <v>139.4616192467998</v>
+        <v>132.2661442102612</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -2475,7 +2457,7 @@
         <v>124</v>
       </c>
       <c r="B124" s="1">
-        <v>139.5005397948665</v>
+        <v>132.3341388144897</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -2483,7 +2465,7 @@
         <v>125</v>
       </c>
       <c r="B125" s="1">
-        <v>139.6089159169267</v>
+        <v>132.4357854744187</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -2491,7 +2473,7 @@
         <v>126</v>
       </c>
       <c r="B126" s="1">
-        <v>139.6360267235086</v>
+        <v>132.4579367657776</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -2499,7 +2481,7 @@
         <v>127</v>
       </c>
       <c r="B127" s="1">
-        <v>139.6547016794254</v>
+        <v>132.4668776999789</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -2507,7 +2489,7 @@
         <v>128</v>
       </c>
       <c r="B128" s="1">
-        <v>139.7036204714511</v>
+        <v>132.5919369229312</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -2515,7 +2497,7 @@
         <v>129</v>
       </c>
       <c r="B129" s="1">
-        <v>139.9255955039752</v>
+        <v>132.6677354440077</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -2523,7 +2505,7 @@
         <v>130</v>
       </c>
       <c r="B130" s="1">
-        <v>139.9336183503602</v>
+        <v>132.7042162885117</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -2531,7 +2513,7 @@
         <v>131</v>
       </c>
       <c r="B131" s="1">
-        <v>139.971794165633</v>
+        <v>132.8093797298177</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -2539,7 +2521,7 @@
         <v>132</v>
       </c>
       <c r="B132" s="1">
-        <v>139.9780317569823</v>
+        <v>132.8213546087935</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -2547,7 +2529,7 @@
         <v>133</v>
       </c>
       <c r="B133" s="1">
-        <v>140.0693153977036</v>
+        <v>132.8308174496671</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -2555,7 +2537,7 @@
         <v>134</v>
       </c>
       <c r="B134" s="1">
-        <v>140.2083779788335</v>
+        <v>132.8477524948536</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -2563,7 +2545,7 @@
         <v>135</v>
       </c>
       <c r="B135" s="1">
-        <v>140.2491428624017</v>
+        <v>132.8701798673598</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -2571,7 +2553,7 @@
         <v>136</v>
       </c>
       <c r="B136" s="1">
-        <v>140.3218076484469</v>
+        <v>132.9297330641278</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -2579,7 +2561,7 @@
         <v>137</v>
       </c>
       <c r="B137" s="1">
-        <v>140.3778476354272</v>
+        <v>132.9491945719062</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -2587,7 +2569,7 @@
         <v>138</v>
       </c>
       <c r="B138" s="1">
-        <v>140.4100649758641</v>
+        <v>133.1615765956707</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -2595,7 +2577,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="1">
-        <v>140.4870794589808</v>
+        <v>133.414500055388</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -2603,7 +2585,7 @@
         <v>140</v>
       </c>
       <c r="B140" s="1">
-        <v>140.6881026102848</v>
+        <v>133.4722920675918</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -2611,7 +2593,7 @@
         <v>141</v>
       </c>
       <c r="B141" s="1">
-        <v>140.8694707054412</v>
+        <v>133.4749801493575</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -2619,7 +2601,7 @@
         <v>142</v>
       </c>
       <c r="B142" s="1">
-        <v>140.8776195219346</v>
+        <v>133.7817021086419</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -2627,7 +2609,7 @@
         <v>143</v>
       </c>
       <c r="B143" s="1">
-        <v>140.9861198298039</v>
+        <v>133.8568270296104</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -2635,7 +2617,7 @@
         <v>144</v>
       </c>
       <c r="B144" s="1">
-        <v>141.0169691289964</v>
+        <v>133.9758668444756</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -2643,7 +2625,7 @@
         <v>145</v>
       </c>
       <c r="B145" s="1">
-        <v>141.1628132987778</v>
+        <v>133.9961530024761</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -2651,7 +2633,7 @@
         <v>146</v>
       </c>
       <c r="B146" s="1">
-        <v>141.2335407808444</v>
+        <v>134.0257928971722</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -2659,7 +2641,7 @@
         <v>147</v>
       </c>
       <c r="B147" s="1">
-        <v>141.3126199421443</v>
+        <v>134.2294440603854</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -2667,7 +2649,7 @@
         <v>148</v>
       </c>
       <c r="B148" s="1">
-        <v>141.3781568468242</v>
+        <v>134.2322376025219</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -2675,7 +2657,7 @@
         <v>149</v>
       </c>
       <c r="B149" s="1">
-        <v>141.3977580125558</v>
+        <v>134.4647603954529</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -2683,7 +2665,7 @@
         <v>150</v>
       </c>
       <c r="B150" s="1">
-        <v>141.4043040609131</v>
+        <v>134.5504957247051</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -2691,7 +2673,7 @@
         <v>151</v>
       </c>
       <c r="B151" s="1">
-        <v>141.4911810273597</v>
+        <v>134.6781611475295</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -2699,7 +2681,7 @@
         <v>152</v>
       </c>
       <c r="B152" s="1">
-        <v>141.5392021759902</v>
+        <v>134.6926311357979</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -2707,7 +2689,7 @@
         <v>153</v>
       </c>
       <c r="B153" s="1">
-        <v>141.6307902256906</v>
+        <v>134.7589092572078</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -2715,7 +2697,7 @@
         <v>154</v>
       </c>
       <c r="B154" s="1">
-        <v>141.8134417858823</v>
+        <v>134.7699533557918</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -2723,7 +2705,7 @@
         <v>155</v>
       </c>
       <c r="B155" s="1">
-        <v>141.8728480770349</v>
+        <v>134.8221144430859</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -2731,7 +2713,7 @@
         <v>156</v>
       </c>
       <c r="B156" s="1">
-        <v>142.116655594302</v>
+        <v>135.3283685542108</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -2739,7 +2721,7 @@
         <v>157</v>
       </c>
       <c r="B157" s="1">
-        <v>142.3481489406314</v>
+        <v>135.464526030828</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -2747,7 +2729,7 @@
         <v>158</v>
       </c>
       <c r="B158" s="1">
-        <v>142.6893547982875</v>
+        <v>135.4950686890014</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -2755,7 +2737,7 @@
         <v>159</v>
       </c>
       <c r="B159" s="1">
-        <v>142.7290526873688</v>
+        <v>135.538668227946</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -2763,7 +2745,7 @@
         <v>160</v>
       </c>
       <c r="B160" s="1">
-        <v>143.2401845482591</v>
+        <v>135.6252202007354</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -2771,7 +2753,7 @@
         <v>161</v>
       </c>
       <c r="B161" s="1">
-        <v>143.3997481698588</v>
+        <v>135.7257441496197</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -2779,7 +2761,7 @@
         <v>162</v>
       </c>
       <c r="B162" s="1">
-        <v>143.438543036451</v>
+        <v>135.7318313543984</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -2787,7 +2769,7 @@
         <v>163</v>
       </c>
       <c r="B163" s="1">
-        <v>143.5475586451923</v>
+        <v>135.8880801958747</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -2795,7 +2777,7 @@
         <v>164</v>
       </c>
       <c r="B164" s="1">
-        <v>143.8026779054654</v>
+        <v>135.9466714138315</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -2803,7 +2785,7 @@
         <v>165</v>
       </c>
       <c r="B165" s="1">
-        <v>144.0716189625236</v>
+        <v>135.9725468960019</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -2811,7 +2793,7 @@
         <v>166</v>
       </c>
       <c r="B166" s="1">
-        <v>144.1319410014956</v>
+        <v>135.9873616119455</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -2819,7 +2801,7 @@
         <v>167</v>
       </c>
       <c r="B167" s="1">
-        <v>144.1963885214341</v>
+        <v>136.1719380166885</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -2827,7 +2809,7 @@
         <v>168</v>
       </c>
       <c r="B168" s="1">
-        <v>144.2791675123891</v>
+        <v>136.3869199454992</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -2835,7 +2817,7 @@
         <v>169</v>
       </c>
       <c r="B169" s="1">
-        <v>144.4718744849314</v>
+        <v>136.4200880030203</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -2843,7 +2825,7 @@
         <v>170</v>
       </c>
       <c r="B170" s="1">
-        <v>144.8184654798222</v>
+        <v>136.434090002839</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -2851,7 +2833,7 @@
         <v>171</v>
       </c>
       <c r="B171" s="1">
-        <v>144.8630208083272</v>
+        <v>136.5959178159975</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -2859,7 +2841,7 @@
         <v>172</v>
       </c>
       <c r="B172" s="1">
-        <v>144.928615612203</v>
+        <v>136.596307475671</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -2867,7 +2849,7 @@
         <v>173</v>
       </c>
       <c r="B173" s="1">
-        <v>145.0136218302808</v>
+        <v>136.6228468789908</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -2875,7 +2857,7 @@
         <v>174</v>
       </c>
       <c r="B174" s="1">
-        <v>145.1612748638886</v>
+        <v>136.7515713199409</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -2883,7 +2865,7 @@
         <v>175</v>
       </c>
       <c r="B175" s="1">
-        <v>145.2084229647402</v>
+        <v>136.8314398908152</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -2891,7 +2873,7 @@
         <v>176</v>
       </c>
       <c r="B176" s="1">
-        <v>145.5658292896496</v>
+        <v>136.8582346097993</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -2899,7 +2881,7 @@
         <v>177</v>
       </c>
       <c r="B177" s="1">
-        <v>145.6228391540445</v>
+        <v>136.8838598273822</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -2907,7 +2889,7 @@
         <v>178</v>
       </c>
       <c r="B178" s="1">
-        <v>145.648767647391</v>
+        <v>136.885433412229</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -2915,7 +2897,7 @@
         <v>179</v>
       </c>
       <c r="B179" s="1">
-        <v>145.7404666625909</v>
+        <v>136.8856279875857</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -2923,7 +2905,7 @@
         <v>180</v>
       </c>
       <c r="B180" s="1">
-        <v>145.8019098650194</v>
+        <v>137.0488202883218</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -2931,7 +2913,7 @@
         <v>181</v>
       </c>
       <c r="B181" s="1">
-        <v>145.8357115105397</v>
+        <v>137.3209029552308</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -2939,7 +2921,7 @@
         <v>182</v>
       </c>
       <c r="B182" s="1">
-        <v>145.8814235137661</v>
+        <v>137.3630500203522</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -2947,7 +2929,7 @@
         <v>183</v>
       </c>
       <c r="B183" s="1">
-        <v>145.9432272628523</v>
+        <v>137.7453677797959</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -2955,7 +2937,7 @@
         <v>184</v>
       </c>
       <c r="B184" s="1">
-        <v>146.0692318393389</v>
+        <v>137.813333814353</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -2963,7 +2945,7 @@
         <v>185</v>
       </c>
       <c r="B185" s="1">
-        <v>146.0875810638839</v>
+        <v>137.9070412817209</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -2971,7 +2953,7 @@
         <v>186</v>
       </c>
       <c r="B186" s="1">
-        <v>146.2265941665691</v>
+        <v>138.0348139592548</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -2979,7 +2961,7 @@
         <v>187</v>
       </c>
       <c r="B187" s="1">
-        <v>146.2554998881015</v>
+        <v>138.0525312823246</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -2987,7 +2969,7 @@
         <v>188</v>
       </c>
       <c r="B188" s="1">
-        <v>146.3903220514274</v>
+        <v>138.1282983672957</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -2995,7 +2977,7 @@
         <v>189</v>
       </c>
       <c r="B189" s="1">
-        <v>146.7646285964503</v>
+        <v>138.2820215626973</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -3003,7 +2985,7 @@
         <v>190</v>
       </c>
       <c r="B190" s="1">
-        <v>146.7747721284895</v>
+        <v>138.6544467037946</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -3011,7 +2993,7 @@
         <v>191</v>
       </c>
       <c r="B191" s="1">
-        <v>146.9294642710316</v>
+        <v>138.9625394173734</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -3019,7 +3001,7 @@
         <v>192</v>
       </c>
       <c r="B192" s="1">
-        <v>146.9563139258987</v>
+        <v>138.9720525830414</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -3027,7 +3009,7 @@
         <v>193</v>
       </c>
       <c r="B193" s="1">
-        <v>147.1853238240748</v>
+        <v>138.9825892959376</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -3035,7 +3017,7 @@
         <v>194</v>
       </c>
       <c r="B194" s="1">
-        <v>147.1931321770412</v>
+        <v>139.0340946535466</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -3043,7 +3025,7 @@
         <v>195</v>
       </c>
       <c r="B195" s="1">
-        <v>147.2081153468109</v>
+        <v>139.1510664715894</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -3051,7 +3033,7 @@
         <v>196</v>
       </c>
       <c r="B196" s="1">
-        <v>147.3970861802402</v>
+        <v>139.2506167142048</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -3059,7 +3041,7 @@
         <v>197</v>
       </c>
       <c r="B197" s="1">
-        <v>147.4134210541201</v>
+        <v>139.4171510210183</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -3067,7 +3049,7 @@
         <v>198</v>
       </c>
       <c r="B198" s="1">
-        <v>147.4288193241063</v>
+        <v>139.5480593879044</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -3075,7 +3057,7 @@
         <v>199</v>
       </c>
       <c r="B199" s="1">
-        <v>147.4672181018605</v>
+        <v>139.8058017366882</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -3083,7 +3065,7 @@
         <v>200</v>
       </c>
       <c r="B200" s="1">
-        <v>147.5047598925026</v>
+        <v>139.8634922713013</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -3091,7 +3073,7 @@
         <v>201</v>
       </c>
       <c r="B201" s="1">
-        <v>147.6117736167616</v>
+        <v>139.9249117324219</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -3099,7 +3081,7 @@
         <v>202</v>
       </c>
       <c r="B202" s="1">
-        <v>147.9321920625801</v>
+        <v>140.0888905157719</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -3107,7 +3089,7 @@
         <v>203</v>
       </c>
       <c r="B203" s="1">
-        <v>148.1029962769371</v>
+        <v>140.1534844473142</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -3115,7 +3097,7 @@
         <v>204</v>
       </c>
       <c r="B204" s="1">
-        <v>148.2516380414317</v>
+        <v>140.1690805629563</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -3123,7 +3105,7 @@
         <v>205</v>
       </c>
       <c r="B205" s="1">
-        <v>148.2555243381455</v>
+        <v>140.3796241894688</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -3131,7 +3113,7 @@
         <v>206</v>
       </c>
       <c r="B206" s="1">
-        <v>148.3222102636411</v>
+        <v>140.6375885910446</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -3139,7 +3121,7 @@
         <v>207</v>
       </c>
       <c r="B207" s="1">
-        <v>148.9346750832101</v>
+        <v>140.8121580272143</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -3147,7 +3129,7 @@
         <v>208</v>
       </c>
       <c r="B208" s="1">
-        <v>149.1243569126471</v>
+        <v>140.9937023914265</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -3155,7 +3137,7 @@
         <v>209</v>
       </c>
       <c r="B209" s="1">
-        <v>149.3132808730395</v>
+        <v>141.0350031695498</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -3163,7 +3145,7 @@
         <v>210</v>
       </c>
       <c r="B210" s="1">
-        <v>149.3396503066246</v>
+        <v>141.1895073363439</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -3171,7 +3153,7 @@
         <v>211</v>
       </c>
       <c r="B211" s="1">
-        <v>149.6276632524649</v>
+        <v>141.2686675605021</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -3179,7 +3161,7 @@
         <v>212</v>
       </c>
       <c r="B212" s="1">
-        <v>149.687513712443</v>
+        <v>141.5185848332696</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -3187,7 +3169,7 @@
         <v>213</v>
       </c>
       <c r="B213" s="1">
-        <v>149.75595124966</v>
+        <v>141.5357284720218</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -3195,7 +3177,7 @@
         <v>214</v>
       </c>
       <c r="B214" s="1">
-        <v>149.8612624272533</v>
+        <v>141.5486644685861</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -3203,7 +3185,7 @@
         <v>215</v>
       </c>
       <c r="B215" s="1">
-        <v>150.0990831131556</v>
+        <v>141.5859178330701</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -3211,7 +3193,7 @@
         <v>216</v>
       </c>
       <c r="B216" s="1">
-        <v>150.2456225828385</v>
+        <v>141.8851819443104</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -3219,7 +3201,7 @@
         <v>217</v>
       </c>
       <c r="B217" s="1">
-        <v>150.2719732481746</v>
+        <v>142.1568172158429</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -3227,7 +3209,7 @@
         <v>218</v>
       </c>
       <c r="B218" s="1">
-        <v>150.359176262351</v>
+        <v>142.4210412244415</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -3235,7 +3217,7 @@
         <v>219</v>
       </c>
       <c r="B219" s="1">
-        <v>150.422864469381</v>
+        <v>142.7187957926884</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -3243,7 +3225,7 @@
         <v>220</v>
       </c>
       <c r="B220" s="1">
-        <v>150.5563102517622</v>
+        <v>142.7663481001454</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -3251,7 +3233,7 @@
         <v>221</v>
       </c>
       <c r="B221" s="1">
-        <v>150.6082742092996</v>
+        <v>142.9072352932486</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -3259,7 +3241,7 @@
         <v>222</v>
       </c>
       <c r="B222" s="1">
-        <v>150.6272401455155</v>
+        <v>143.1888770987958</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -3267,7 +3249,7 @@
         <v>223</v>
       </c>
       <c r="B223" s="1">
-        <v>150.7781806268288</v>
+        <v>143.4939481657526</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -3275,7 +3257,7 @@
         <v>224</v>
       </c>
       <c r="B224" s="1">
-        <v>150.8371667060106</v>
+        <v>143.5260322361981</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -3283,7 +3265,7 @@
         <v>225</v>
       </c>
       <c r="B225" s="1">
-        <v>150.8460064799222</v>
+        <v>143.8229075481551</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -3291,7 +3273,7 @@
         <v>226</v>
       </c>
       <c r="B226" s="1">
-        <v>150.8586824366291</v>
+        <v>143.8858896361583</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -3299,7 +3281,7 @@
         <v>227</v>
       </c>
       <c r="B227" s="1">
-        <v>150.8952820334179</v>
+        <v>144.0529902828545</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -3307,7 +3289,7 @@
         <v>228</v>
       </c>
       <c r="B228" s="1">
-        <v>150.9402172629069</v>
+        <v>144.2056488209747</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -3315,7 +3297,7 @@
         <v>229</v>
       </c>
       <c r="B229" s="1">
-        <v>151.0780653096789</v>
+        <v>144.2430152601437</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -3323,7 +3305,7 @@
         <v>230</v>
       </c>
       <c r="B230" s="1">
-        <v>151.257829834366</v>
+        <v>144.3385972360206</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -3331,7 +3313,7 @@
         <v>231</v>
       </c>
       <c r="B231" s="1">
-        <v>151.2972453723136</v>
+        <v>144.751293803373</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -3339,7 +3321,7 @@
         <v>232</v>
       </c>
       <c r="B232" s="1">
-        <v>151.3797681659705</v>
+        <v>144.8231704721786</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -3347,7 +3329,7 @@
         <v>233</v>
       </c>
       <c r="B233" s="1">
-        <v>151.4744876136699</v>
+        <v>145.2690585790599</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -3355,7 +3337,7 @@
         <v>234</v>
       </c>
       <c r="B234" s="1">
-        <v>151.954424252143</v>
+        <v>145.6329031426705</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -3363,7 +3345,7 @@
         <v>235</v>
       </c>
       <c r="B235" s="1">
-        <v>152.1607229792099</v>
+        <v>145.9161857418718</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -3371,7 +3353,7 @@
         <v>236</v>
       </c>
       <c r="B236" s="1">
-        <v>152.1845702477707</v>
+        <v>146.0724268561676</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -3379,7 +3361,7 @@
         <v>237</v>
       </c>
       <c r="B237" s="1">
-        <v>152.3112815127581</v>
+        <v>146.1653343675191</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -3387,7 +3369,7 @@
         <v>238</v>
       </c>
       <c r="B238" s="1">
-        <v>152.7682653624477</v>
+        <v>146.4440968464655</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -3395,7 +3377,7 @@
         <v>239</v>
       </c>
       <c r="B239" s="1">
-        <v>152.9919305626667</v>
+        <v>146.5474483703262</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -3403,7 +3385,7 @@
         <v>240</v>
       </c>
       <c r="B240" s="1">
-        <v>153.1142886250203</v>
+        <v>146.7146325217438</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -3411,7 +3393,7 @@
         <v>241</v>
       </c>
       <c r="B241" s="1">
-        <v>153.3422306711517</v>
+        <v>147.1948865735826</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -3419,7 +3401,7 @@
         <v>242</v>
       </c>
       <c r="B242" s="1">
-        <v>153.5256957681681</v>
+        <v>147.597006394801</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -3427,7 +3409,7 @@
         <v>243</v>
       </c>
       <c r="B243" s="1">
-        <v>153.5821360250166</v>
+        <v>147.7331095033362</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -3435,7 +3417,7 @@
         <v>244</v>
       </c>
       <c r="B244" s="1">
-        <v>153.6176713393625</v>
+        <v>147.9284171317249</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -3443,7 +3425,7 @@
         <v>245</v>
       </c>
       <c r="B245" s="1">
-        <v>153.8479977014528</v>
+        <v>148.2407555528505</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -3451,7 +3433,7 @@
         <v>246</v>
       </c>
       <c r="B246" s="1">
-        <v>153.934715098498</v>
+        <v>148.2980780329487</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -3459,7 +3441,7 @@
         <v>247</v>
       </c>
       <c r="B247" s="1">
-        <v>154.1003051148066</v>
+        <v>148.8564101774331</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -3467,7 +3449,7 @@
         <v>248</v>
       </c>
       <c r="B248" s="1">
-        <v>154.2114616029173</v>
+        <v>149.2301440582534</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -3475,7 +3457,7 @@
         <v>249</v>
       </c>
       <c r="B249" s="1">
-        <v>154.5868953062074</v>
+        <v>149.465687885177</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -3483,7 +3465,7 @@
         <v>250</v>
       </c>
       <c r="B250" s="1">
-        <v>154.7057237025718</v>
+        <v>149.5571508825638</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -3491,7 +3473,7 @@
         <v>251</v>
       </c>
       <c r="B251" s="1">
-        <v>154.8682781778302</v>
+        <v>149.6162110203929</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -3499,7 +3481,7 @@
         <v>252</v>
       </c>
       <c r="B252" s="1">
-        <v>155.1074825633952</v>
+        <v>150.0358578157643</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -3507,7 +3489,7 @@
         <v>253</v>
       </c>
       <c r="B253" s="1">
-        <v>155.4577213152232</v>
+        <v>150.2367368642802</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -3515,7 +3497,7 @@
         <v>254</v>
       </c>
       <c r="B254" s="1">
-        <v>155.9803190100494</v>
+        <v>150.3285260190029</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -3523,7 +3505,7 @@
         <v>255</v>
       </c>
       <c r="B255" s="1">
-        <v>156.3581002418856</v>
+        <v>150.5696263093544</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -3531,7 +3513,7 @@
         <v>256</v>
       </c>
       <c r="B256" s="1">
-        <v>157.0273675620256</v>
+        <v>150.6058172888888</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -3539,7 +3521,7 @@
         <v>257</v>
       </c>
       <c r="B257" s="1">
-        <v>157.9940339343269</v>
+        <v>150.7310739581264</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -3547,7 +3529,7 @@
         <v>258</v>
       </c>
       <c r="B258" s="1">
-        <v>158.0649655318811</v>
+        <v>150.8525009957056</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -3555,7 +3537,7 @@
         <v>259</v>
       </c>
       <c r="B259" s="1">
-        <v>159.0448620979279</v>
+        <v>150.8830205569993</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -3563,7 +3545,7 @@
         <v>260</v>
       </c>
       <c r="B260" s="1">
-        <v>159.0995762233708</v>
+        <v>151.0208724126259</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -3571,7 +3553,7 @@
         <v>261</v>
       </c>
       <c r="B261" s="1">
-        <v>159.1793745647682</v>
+        <v>151.0862881178963</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -3579,7 +3561,7 @@
         <v>262</v>
       </c>
       <c r="B262" s="1">
-        <v>159.5575279760833</v>
+        <v>151.1337517607917</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -3587,7 +3569,7 @@
         <v>263</v>
       </c>
       <c r="B263" s="1">
-        <v>159.5665212794964</v>
+        <v>151.5781281771919</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -3595,7 +3577,7 @@
         <v>264</v>
       </c>
       <c r="B264" s="1">
-        <v>160.034216100887</v>
+        <v>151.6060430031736</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -3603,7 +3585,7 @@
         <v>265</v>
       </c>
       <c r="B265" s="1">
-        <v>160.6646817246191</v>
+        <v>151.6573369003935</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -3611,7 +3593,7 @@
         <v>266</v>
       </c>
       <c r="B266" s="1">
-        <v>160.823003909658</v>
+        <v>152.0271840825212</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -3619,7 +3601,7 @@
         <v>267</v>
       </c>
       <c r="B267" s="1">
-        <v>160.8687788574994</v>
+        <v>152.4871659079732</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -3627,7 +3609,7 @@
         <v>268</v>
       </c>
       <c r="B268" s="1">
-        <v>161.4197255402331</v>
+        <v>152.6096346907263</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -3635,7 +3617,7 @@
         <v>269</v>
       </c>
       <c r="B269" s="1">
-        <v>161.7948314334095</v>
+        <v>152.6096435022669</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -3643,7 +3625,7 @@
         <v>270</v>
       </c>
       <c r="B270" s="1">
-        <v>161.9594467559942</v>
+        <v>152.7450755096108</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -3651,7 +3633,7 @@
         <v>271</v>
       </c>
       <c r="B271" s="1">
-        <v>162.3460234192603</v>
+        <v>153.6656852388908</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -3659,7 +3641,7 @@
         <v>272</v>
       </c>
       <c r="B272" s="1">
-        <v>162.7578677890454</v>
+        <v>153.9905579577738</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -3667,7 +3649,7 @@
         <v>273</v>
       </c>
       <c r="B273" s="1">
-        <v>162.8174828123756</v>
+        <v>154.0928205532058</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -3675,7 +3657,7 @@
         <v>274</v>
       </c>
       <c r="B274" s="1">
-        <v>163.7756496144346</v>
+        <v>154.9227533137995</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -3683,7 +3665,7 @@
         <v>275</v>
       </c>
       <c r="B275" s="1">
-        <v>165.1325333752411</v>
+        <v>154.9268505712554</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -3691,7 +3673,7 @@
         <v>276</v>
       </c>
       <c r="B276" s="1">
-        <v>165.4167186009292</v>
+        <v>155.390811396373</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -3699,7 +3681,7 @@
         <v>277</v>
       </c>
       <c r="B277" s="1">
-        <v>165.8585123599655</v>
+        <v>155.4102062062394</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -3707,7 +3689,7 @@
         <v>278</v>
       </c>
       <c r="B278" s="1">
-        <v>166.1030706541295</v>
+        <v>155.4554612036829</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -3715,7 +3697,7 @@
         <v>279</v>
       </c>
       <c r="B279" s="1">
-        <v>166.5969842345849</v>
+        <v>155.9099931669256</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -3723,7 +3705,7 @@
         <v>280</v>
       </c>
       <c r="B280" s="1">
-        <v>166.6110400404456</v>
+        <v>155.9731081513379</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -3731,7 +3713,7 @@
         <v>281</v>
       </c>
       <c r="B281" s="1">
-        <v>166.7329893383465</v>
+        <v>156.3053958897006</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -3739,7 +3721,7 @@
         <v>282</v>
       </c>
       <c r="B282" s="1">
-        <v>167.0989216880709</v>
+        <v>157.2924467518341</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -3747,7 +3729,7 @@
         <v>283</v>
       </c>
       <c r="B283" s="1">
-        <v>167.1796982115739</v>
+        <v>157.4436249270173</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -3755,7 +3737,7 @@
         <v>284</v>
       </c>
       <c r="B284" s="1">
-        <v>167.2979243932306</v>
+        <v>157.4729349764546</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -3763,7 +3745,7 @@
         <v>285</v>
       </c>
       <c r="B285" s="1">
-        <v>168.010011310707</v>
+        <v>158.8339247204097</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -3771,7 +3753,7 @@
         <v>286</v>
       </c>
       <c r="B286" s="1">
-        <v>168.2957192522639</v>
+        <v>159.0460194372707</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -3779,7 +3761,7 @@
         <v>287</v>
       </c>
       <c r="B287" s="1">
-        <v>168.407444260123</v>
+        <v>159.9517691395316</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -3787,7 +3769,7 @@
         <v>288</v>
       </c>
       <c r="B288" s="1">
-        <v>169.7756640412077</v>
+        <v>160.3784406642712</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -3795,7 +3777,7 @@
         <v>289</v>
       </c>
       <c r="B289" s="1">
-        <v>170.0038695596177</v>
+        <v>160.8449631147482</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -3803,7 +3785,7 @@
         <v>290</v>
       </c>
       <c r="B290" s="1">
-        <v>170.2688435410465</v>
+        <v>161.0354586674242</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -3811,7 +3793,7 @@
         <v>291</v>
       </c>
       <c r="B291" s="1">
-        <v>170.4929231573195</v>
+        <v>161.9483651575585</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -3819,7 +3801,7 @@
         <v>292</v>
       </c>
       <c r="B292" s="1">
-        <v>171.3302917528341</v>
+        <v>161.9997712311538</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -3827,7 +3809,7 @@
         <v>293</v>
       </c>
       <c r="B293" s="1">
-        <v>172.6200265477772</v>
+        <v>162.7609203119676</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -3835,7 +3817,7 @@
         <v>294</v>
       </c>
       <c r="B294" s="1">
-        <v>173.1221095008115</v>
+        <v>163.5334114711798</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -3843,7 +3825,7 @@
         <v>295</v>
       </c>
       <c r="B295" s="1">
-        <v>173.4727557173179</v>
+        <v>164.6965712489906</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -3851,7 +3833,7 @@
         <v>296</v>
       </c>
       <c r="B296" s="1">
-        <v>174.8383053458917</v>
+        <v>164.7722108957645</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -3859,7 +3841,7 @@
         <v>297</v>
       </c>
       <c r="B297" s="1">
-        <v>174.9158127296423</v>
+        <v>165.1976072777943</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -3867,7 +3849,7 @@
         <v>298</v>
       </c>
       <c r="B298" s="1">
-        <v>175.0301828025447</v>
+        <v>165.8408494809232</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -3875,7 +3857,7 @@
         <v>299</v>
       </c>
       <c r="B299" s="1">
-        <v>175.1066591801561</v>
+        <v>166.479777541394</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -3883,7 +3865,7 @@
         <v>300</v>
       </c>
       <c r="B300" s="1">
-        <v>175.6126630958253</v>
+        <v>166.6021824501797</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -3891,7 +3873,7 @@
         <v>301</v>
       </c>
       <c r="B301" s="1">
-        <v>175.6689144221319</v>
+        <v>167.1912282783538</v>
       </c>
     </row>
     <row r="302" spans="1:2">
@@ -3899,7 +3881,7 @@
         <v>302</v>
       </c>
       <c r="B302" s="1">
-        <v>175.7078278556753</v>
+        <v>167.5586637834012</v>
       </c>
     </row>
     <row r="303" spans="1:2">
@@ -3907,7 +3889,7 @@
         <v>303</v>
       </c>
       <c r="B303" s="1">
-        <v>176.3206284344115</v>
+        <v>167.6301381213031</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -3915,7 +3897,7 @@
         <v>304</v>
       </c>
       <c r="B304" s="1">
-        <v>176.324642444911</v>
+        <v>169.5139099417947</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -3923,7 +3905,7 @@
         <v>305</v>
       </c>
       <c r="B305" s="1">
-        <v>176.5036739138644</v>
+        <v>170.0442445275069</v>
       </c>
     </row>
     <row r="306" spans="1:2">
@@ -3931,7 +3913,7 @@
         <v>306</v>
       </c>
       <c r="B306" s="1">
-        <v>176.5425608571317</v>
+        <v>170.1018560654744</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -3939,7 +3921,7 @@
         <v>307</v>
       </c>
       <c r="B307" s="1">
-        <v>178.0426149941399</v>
+        <v>170.6719885575409</v>
       </c>
     </row>
     <row r="308" spans="1:2">
@@ -3947,7 +3929,7 @@
         <v>308</v>
       </c>
       <c r="B308" s="1">
-        <v>178.3545691979927</v>
+        <v>171.4649384613641</v>
       </c>
     </row>
     <row r="309" spans="1:2">
@@ -3955,7 +3937,7 @@
         <v>309</v>
       </c>
       <c r="B309" s="1">
-        <v>178.5557426627231</v>
+        <v>171.5032420851435</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -3963,7 +3945,7 @@
         <v>310</v>
       </c>
       <c r="B310" s="1">
-        <v>180.6624112514824</v>
+        <v>171.5903752973107</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -3971,7 +3953,7 @@
         <v>311</v>
       </c>
       <c r="B311" s="1">
-        <v>180.6856718738921</v>
+        <v>171.6050524420866</v>
       </c>
     </row>
     <row r="312" spans="1:2">
@@ -3979,7 +3961,7 @@
         <v>312</v>
       </c>
       <c r="B312" s="1">
-        <v>181.1259662745777</v>
+        <v>172.559088590271</v>
       </c>
     </row>
     <row r="313" spans="1:2">
@@ -3987,7 +3969,7 @@
         <v>313</v>
       </c>
       <c r="B313" s="1">
-        <v>181.6021907736554</v>
+        <v>173.7016879582047</v>
       </c>
     </row>
     <row r="314" spans="1:2">
@@ -3995,7 +3977,7 @@
         <v>314</v>
       </c>
       <c r="B314" s="1">
-        <v>181.6769978550583</v>
+        <v>174.4148937797347</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -4003,7 +3985,7 @@
         <v>315</v>
       </c>
       <c r="B315" s="1">
-        <v>182.205404663519</v>
+        <v>174.9091188014804</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -4011,7 +3993,7 @@
         <v>316</v>
       </c>
       <c r="B316" s="1">
-        <v>182.633519252463</v>
+        <v>175.1944072066</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -4019,7 +4001,7 @@
         <v>317</v>
       </c>
       <c r="B317" s="1">
-        <v>184.8606026478251</v>
+        <v>176.9755199510864</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -4027,7 +4009,7 @@
         <v>318</v>
       </c>
       <c r="B318" s="1">
-        <v>186.0658006462933</v>
+        <v>177.248396103968</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -4035,7 +4017,7 @@
         <v>319</v>
       </c>
       <c r="B319" s="1">
-        <v>188.549891559784</v>
+        <v>179.0386991967003</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -4043,7 +4025,7 @@
         <v>320</v>
       </c>
       <c r="B320" s="1">
-        <v>188.7717042022524</v>
+        <v>179.0411295801784</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -4051,7 +4033,7 @@
         <v>321</v>
       </c>
       <c r="B321" s="1">
-        <v>190.6099148388151</v>
+        <v>179.7520338011223</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -4059,7 +4041,7 @@
         <v>322</v>
       </c>
       <c r="B322" s="1">
-        <v>190.7511063866718</v>
+        <v>179.798481442359</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -4067,7 +4049,7 @@
         <v>323</v>
       </c>
       <c r="B323" s="1">
-        <v>191.0112960968032</v>
+        <v>181.2637849780702</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -4075,7 +4057,7 @@
         <v>324</v>
       </c>
       <c r="B324" s="1">
-        <v>193.2932616709566</v>
+        <v>183.7192630535317</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -4083,7 +4065,7 @@
         <v>325</v>
       </c>
       <c r="B325" s="1">
-        <v>194.5488198867781</v>
+        <v>185.008419431494</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -4091,7 +4073,7 @@
         <v>326</v>
       </c>
       <c r="B326" s="1">
-        <v>196.0600804044172</v>
+        <v>185.7454276117793</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -4099,7 +4081,7 @@
         <v>327</v>
       </c>
       <c r="B327" s="1">
-        <v>196.7962603205521</v>
+        <v>188.2343941346077</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -4107,7 +4089,7 @@
         <v>328</v>
       </c>
       <c r="B328" s="1">
-        <v>197.4831740843787</v>
+        <v>189.5076284625823</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -4115,7 +4097,7 @@
         <v>329</v>
       </c>
       <c r="B329" s="1">
-        <v>197.5589812359147</v>
+        <v>190.7845282479299</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -4123,7 +4105,7 @@
         <v>330</v>
       </c>
       <c r="B330" s="1">
-        <v>198.2365190893374</v>
+        <v>192.442073150157</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -4131,7 +4113,7 @@
         <v>331</v>
       </c>
       <c r="B331" s="1">
-        <v>198.3807305691426</v>
+        <v>193.7201056076209</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -4139,7 +4121,7 @@
         <v>332</v>
       </c>
       <c r="B332" s="1">
-        <v>198.5881503821822</v>
+        <v>193.9891333176583</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -4147,7 +4129,7 @@
         <v>333</v>
       </c>
       <c r="B333" s="1">
-        <v>199.1323855022651</v>
+        <v>195.1806682288841</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -4155,7 +4137,7 @@
         <v>334</v>
       </c>
       <c r="B334" s="1">
-        <v>199.3021960308955</v>
+        <v>196.7381423200804</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -4163,7 +4145,7 @@
         <v>335</v>
       </c>
       <c r="B335" s="1">
-        <v>202.5312354104882</v>
+        <v>197.1910409568794</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -4171,7 +4153,7 @@
         <v>336</v>
       </c>
       <c r="B336" s="1">
-        <v>202.7191437974511</v>
+        <v>198.6422184341107</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -4179,7 +4161,7 @@
         <v>337</v>
       </c>
       <c r="B337" s="1">
-        <v>205.5526484116818</v>
+        <v>201.2990990610614</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -4187,7 +4169,7 @@
         <v>338</v>
       </c>
       <c r="B338" s="1">
-        <v>205.8239689198737</v>
+        <v>201.7373700215835</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -4195,7 +4177,7 @@
         <v>339</v>
       </c>
       <c r="B339" s="1">
-        <v>206.8883766387893</v>
+        <v>202.1753323608125</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -4203,7 +4185,7 @@
         <v>340</v>
       </c>
       <c r="B340" s="1">
-        <v>207.7204169707036</v>
+        <v>207.1946966502958</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -4211,7 +4193,7 @@
         <v>341</v>
       </c>
       <c r="B341" s="1">
-        <v>207.9131163077969</v>
+        <v>208.0828064052492</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -4219,7 +4201,7 @@
         <v>342</v>
       </c>
       <c r="B342" s="1">
-        <v>208.2792453119569</v>
+        <v>209.4366295254397</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -4227,7 +4209,7 @@
         <v>343</v>
       </c>
       <c r="B343" s="1">
-        <v>209.3893274140154</v>
+        <v>214.6132208388158</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -4235,7 +4217,7 @@
         <v>344</v>
       </c>
       <c r="B344" s="1">
-        <v>213.6051067031337</v>
+        <v>217.7593115742441</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -4243,7 +4225,7 @@
         <v>345</v>
       </c>
       <c r="B345" s="1">
-        <v>215.0323626278594</v>
+        <v>218.9711439338221</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -4251,7 +4233,7 @@
         <v>346</v>
       </c>
       <c r="B346" s="1">
-        <v>215.5973936421408</v>
+        <v>220.0650723877261</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -4259,7 +4241,7 @@
         <v>347</v>
       </c>
       <c r="B347" s="1">
-        <v>217.536662765915</v>
+        <v>227.3078588762888</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -4267,7 +4249,7 @@
         <v>348</v>
       </c>
       <c r="B348" s="1">
-        <v>217.781300803123</v>
+        <v>234.0700258714982</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -4275,7 +4257,7 @@
         <v>349</v>
       </c>
       <c r="B349" s="1">
-        <v>218.9711439338221</v>
+        <v>243.9997269095433</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -4283,7 +4265,7 @@
         <v>350</v>
       </c>
       <c r="B350" s="1">
-        <v>231.1795505529074</v>
+        <v>265.4982901615595</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -4291,7 +4273,7 @@
         <v>351</v>
       </c>
       <c r="B351" s="1">
-        <v>239.0767061813042</v>
+        <v>272.1951199024072</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -4299,7 +4281,7 @@
         <v>352</v>
       </c>
       <c r="B352" s="1">
-        <v>239.9444744359409</v>
+        <v>276.9920398613946</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -4307,7 +4289,7 @@
         <v>353</v>
       </c>
       <c r="B353" s="1">
-        <v>249.8422349733149</v>
+        <v>277.8598794227735</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -4315,7 +4297,7 @@
         <v>354</v>
       </c>
       <c r="B354" s="1">
-        <v>256.2407933537457</v>
+        <v>281.4157485390699</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -4323,7 +4305,7 @@
         <v>355</v>
       </c>
       <c r="B355" s="1">
-        <v>260.4092186618647</v>
+        <v>293.3782449933111</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -4331,7 +4313,7 @@
         <v>356</v>
       </c>
       <c r="B356" s="1">
-        <v>273.7172597567813</v>
+        <v>297.2762736374641</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -4339,7 +4321,7 @@
         <v>357</v>
       </c>
       <c r="B357" s="1">
-        <v>275.2863998658778</v>
+        <v>306.7112959885945</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -4347,7 +4329,7 @@
         <v>358</v>
       </c>
       <c r="B358" s="1">
-        <v>280.4146651000763</v>
+        <v>326.9823344636471</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -4355,7 +4337,7 @@
         <v>359</v>
       </c>
       <c r="B359" s="1">
-        <v>283.3963057928091</v>
+        <v>334.7996909548909</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -4363,7 +4345,7 @@
         <v>360</v>
       </c>
       <c r="B360" s="1">
-        <v>293.2709590963472</v>
+        <v>357.7370107594063</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -4371,7 +4353,7 @@
         <v>361</v>
       </c>
       <c r="B361" s="1">
-        <v>301.5945710877178</v>
+        <v>397.6417205005864</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -4379,7 +4361,7 @@
         <v>362</v>
       </c>
       <c r="B362" s="1">
-        <v>303.6097144355306</v>
+        <v>428.7292142613572</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -4387,7 +4369,7 @@
         <v>363</v>
       </c>
       <c r="B363" s="1">
-        <v>305.8833824966043</v>
+        <v>497.2214425982315</v>
       </c>
     </row>
     <row r="364" spans="1:2">
@@ -4395,7 +4377,7 @@
         <v>364</v>
       </c>
       <c r="B364" s="1">
-        <v>318.0717481220635</v>
+        <v>566.6280911242668</v>
       </c>
     </row>
     <row r="365" spans="1:2">
@@ -4403,7 +4385,7 @@
         <v>365</v>
       </c>
       <c r="B365" s="1">
-        <v>339.618295640037</v>
+        <v>591.0866968817579</v>
       </c>
     </row>
     <row r="366" spans="1:2">
@@ -4411,55 +4393,7 @@
         <v>366</v>
       </c>
       <c r="B366" s="1">
-        <v>352.4751899923309</v>
-      </c>
-    </row>
-    <row r="367" spans="1:2">
-      <c r="A367" t="s">
-        <v>367</v>
-      </c>
-      <c r="B367" s="1">
-        <v>453.6179757064314</v>
-      </c>
-    </row>
-    <row r="368" spans="1:2">
-      <c r="A368" t="s">
-        <v>368</v>
-      </c>
-      <c r="B368" s="1">
-        <v>509.1957243873753</v>
-      </c>
-    </row>
-    <row r="369" spans="1:2">
-      <c r="A369" t="s">
-        <v>369</v>
-      </c>
-      <c r="B369" s="1">
-        <v>532.3798212526319</v>
-      </c>
-    </row>
-    <row r="370" spans="1:2">
-      <c r="A370" t="s">
-        <v>370</v>
-      </c>
-      <c r="B370" s="1">
-        <v>567.1717836405109</v>
-      </c>
-    </row>
-    <row r="371" spans="1:2">
-      <c r="A371" t="s">
-        <v>371</v>
-      </c>
-      <c r="B371" s="1">
-        <v>581.5698777251038</v>
-      </c>
-    </row>
-    <row r="372" spans="1:2">
-      <c r="A372" t="s">
-        <v>372</v>
-      </c>
-      <c r="B372" s="1">
-        <v>825.2939153992677</v>
+        <v>815.7666724015032</v>
       </c>
     </row>
   </sheetData>

--- a/Screener/data/rs_rating_top_30.xlsx
+++ b/Screener/data/rs_rating_top_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="363">
   <si>
     <t>Symbol</t>
   </si>
@@ -22,1090 +22,1078 @@
     <t>RS Rating</t>
   </si>
   <si>
+    <t>HSKA</t>
+  </si>
+  <si>
+    <t>GGAAU</t>
+  </si>
+  <si>
+    <t>MOMO</t>
+  </si>
+  <si>
+    <t>ALSN</t>
+  </si>
+  <si>
+    <t>NOG</t>
+  </si>
+  <si>
+    <t>ASTE</t>
+  </si>
+  <si>
+    <t>GLRE</t>
+  </si>
+  <si>
+    <t>TEX</t>
+  </si>
+  <si>
+    <t>TYRA</t>
+  </si>
+  <si>
+    <t>ON</t>
+  </si>
+  <si>
+    <t>XPRO</t>
+  </si>
+  <si>
+    <t>COOP</t>
+  </si>
+  <si>
+    <t>SHC</t>
+  </si>
+  <si>
+    <t>DECK</t>
+  </si>
+  <si>
+    <t>BVH</t>
+  </si>
+  <si>
+    <t>BATRA</t>
+  </si>
+  <si>
+    <t>URI</t>
+  </si>
+  <si>
+    <t>TBBK</t>
+  </si>
+  <si>
+    <t>VMW</t>
+  </si>
+  <si>
+    <t>URBN</t>
+  </si>
+  <si>
+    <t>BLBD</t>
+  </si>
+  <si>
+    <t>CRS</t>
+  </si>
+  <si>
+    <t>RCM</t>
+  </si>
+  <si>
+    <t>PRI</t>
+  </si>
+  <si>
+    <t>MSA</t>
+  </si>
+  <si>
+    <t>GAMB</t>
+  </si>
+  <si>
+    <t>BMI</t>
+  </si>
+  <si>
+    <t>CEIX</t>
+  </si>
+  <si>
+    <t>ARGX</t>
+  </si>
+  <si>
+    <t>DHI</t>
+  </si>
+  <si>
+    <t>MRVL</t>
+  </si>
+  <si>
+    <t>TNET</t>
+  </si>
+  <si>
+    <t>ODFL</t>
+  </si>
+  <si>
+    <t>HURN</t>
+  </si>
+  <si>
+    <t>ANIP</t>
+  </si>
+  <si>
+    <t>NEU</t>
+  </si>
+  <si>
+    <t>EXP</t>
+  </si>
+  <si>
+    <t>SUM</t>
+  </si>
+  <si>
+    <t>AMWD</t>
+  </si>
+  <si>
+    <t>BRZE</t>
+  </si>
+  <si>
+    <t>FLNC</t>
+  </si>
+  <si>
+    <t>LUNG</t>
+  </si>
+  <si>
+    <t>MMYT</t>
+  </si>
+  <si>
+    <t>KNSA</t>
+  </si>
+  <si>
+    <t>DXPE</t>
+  </si>
+  <si>
+    <t>FTDR</t>
+  </si>
+  <si>
+    <t>GTLS</t>
+  </si>
+  <si>
+    <t>DVA</t>
+  </si>
+  <si>
+    <t>ARCB</t>
+  </si>
+  <si>
+    <t>FSTR</t>
+  </si>
+  <si>
+    <t>AEL</t>
+  </si>
+  <si>
+    <t>FDX</t>
+  </si>
+  <si>
+    <t>EXAS</t>
+  </si>
+  <si>
+    <t>ACMR</t>
+  </si>
+  <si>
+    <t>LEU</t>
+  </si>
+  <si>
+    <t>IIVI</t>
+  </si>
+  <si>
+    <t>BKI</t>
+  </si>
+  <si>
+    <t>TMHC</t>
+  </si>
+  <si>
+    <t>COHR</t>
+  </si>
+  <si>
+    <t>GIC</t>
+  </si>
+  <si>
+    <t>SCX</t>
+  </si>
+  <si>
+    <t>RKT</t>
+  </si>
+  <si>
+    <t>NEX</t>
+  </si>
+  <si>
+    <t>PRIM</t>
+  </si>
+  <si>
+    <t>CNX</t>
+  </si>
+  <si>
+    <t>CELH</t>
+  </si>
+  <si>
+    <t>GE</t>
+  </si>
+  <si>
+    <t>PLUS</t>
+  </si>
+  <si>
+    <t>ETN</t>
+  </si>
+  <si>
+    <t>IMVT</t>
+  </si>
+  <si>
+    <t>ZWS</t>
+  </si>
+  <si>
+    <t>APG</t>
+  </si>
+  <si>
+    <t>GMS</t>
+  </si>
+  <si>
+    <t>NVT</t>
+  </si>
+  <si>
+    <t>CORT</t>
+  </si>
+  <si>
+    <t>VNO</t>
+  </si>
+  <si>
+    <t>ARHS</t>
+  </si>
+  <si>
+    <t>RRGB</t>
+  </si>
+  <si>
+    <t>RDNT</t>
+  </si>
+  <si>
+    <t>NEWR</t>
+  </si>
+  <si>
+    <t>PH</t>
+  </si>
+  <si>
+    <t>AGM</t>
+  </si>
+  <si>
+    <t>ZG</t>
+  </si>
+  <si>
+    <t>JELD</t>
+  </si>
+  <si>
+    <t>YPF</t>
+  </si>
+  <si>
+    <t>JBL</t>
+  </si>
+  <si>
+    <t>CARR</t>
+  </si>
+  <si>
+    <t>AMZN</t>
+  </si>
+  <si>
+    <t>INBK</t>
+  </si>
+  <si>
+    <t>LRCX</t>
+  </si>
+  <si>
+    <t>NVO</t>
+  </si>
+  <si>
+    <t>CFLT</t>
+  </si>
+  <si>
+    <t>GHRS</t>
+  </si>
+  <si>
+    <t>GPOR</t>
+  </si>
+  <si>
+    <t>RDFN</t>
+  </si>
+  <si>
     <t>TPH</t>
   </si>
   <si>
-    <t>NEU</t>
-  </si>
-  <si>
-    <t>XPER</t>
-  </si>
-  <si>
-    <t>ESCA</t>
-  </si>
-  <si>
-    <t>DXPE</t>
+    <t>Z</t>
   </si>
   <si>
     <t>GHL</t>
   </si>
   <si>
-    <t>IGT</t>
+    <t>AZUL</t>
+  </si>
+  <si>
+    <t>FMS</t>
+  </si>
+  <si>
+    <t>DELL</t>
+  </si>
+  <si>
+    <t>CRH</t>
+  </si>
+  <si>
+    <t>HAYW</t>
+  </si>
+  <si>
+    <t>DVAX</t>
+  </si>
+  <si>
+    <t>ANDE</t>
+  </si>
+  <si>
+    <t>FTI</t>
+  </si>
+  <si>
+    <t>PNR</t>
+  </si>
+  <si>
+    <t>BKNG</t>
+  </si>
+  <si>
+    <t>SPNT</t>
+  </si>
+  <si>
+    <t>SHAK</t>
+  </si>
+  <si>
+    <t>STCN</t>
+  </si>
+  <si>
+    <t>HCCI</t>
+  </si>
+  <si>
+    <t>LPG</t>
+  </si>
+  <si>
+    <t>ONTO</t>
+  </si>
+  <si>
+    <t>MNSO</t>
+  </si>
+  <si>
+    <t>FIX</t>
+  </si>
+  <si>
+    <t>MDC</t>
+  </si>
+  <si>
+    <t>ALGN</t>
+  </si>
+  <si>
+    <t>BOOT</t>
+  </si>
+  <si>
+    <t>TOL</t>
+  </si>
+  <si>
+    <t>PKOH</t>
+  </si>
+  <si>
+    <t>SMHI</t>
+  </si>
+  <si>
+    <t>TSQ</t>
+  </si>
+  <si>
+    <t>ACOR</t>
+  </si>
+  <si>
+    <t>AMNB</t>
+  </si>
+  <si>
+    <t>PVBC</t>
+  </si>
+  <si>
+    <t>NE</t>
+  </si>
+  <si>
+    <t>BECN</t>
+  </si>
+  <si>
+    <t>SXI</t>
+  </si>
+  <si>
+    <t>SWDAF</t>
+  </si>
+  <si>
+    <t>SPNS</t>
+  </si>
+  <si>
+    <t>CRC</t>
+  </si>
+  <si>
+    <t>GLBE</t>
+  </si>
+  <si>
+    <t>NYCB</t>
+  </si>
+  <si>
+    <t>SGH</t>
+  </si>
+  <si>
+    <t>ASUR</t>
+  </si>
+  <si>
+    <t>WST</t>
+  </si>
+  <si>
+    <t>PLAB</t>
+  </si>
+  <si>
+    <t>MTH</t>
+  </si>
+  <si>
+    <t>YELP</t>
+  </si>
+  <si>
+    <t>ERO</t>
+  </si>
+  <si>
+    <t>NATR</t>
+  </si>
+  <si>
+    <t>OTTR</t>
+  </si>
+  <si>
+    <t>ZGN</t>
+  </si>
+  <si>
+    <t>JHX</t>
+  </si>
+  <si>
+    <t>DASH</t>
+  </si>
+  <si>
+    <t>ARCO</t>
+  </si>
+  <si>
+    <t>CSWI</t>
+  </si>
+  <si>
+    <t>APPF</t>
+  </si>
+  <si>
+    <t>USLM</t>
+  </si>
+  <si>
+    <t>HELE</t>
+  </si>
+  <si>
+    <t>LTRPB</t>
+  </si>
+  <si>
+    <t>CRMT</t>
+  </si>
+  <si>
+    <t>ADBE</t>
+  </si>
+  <si>
+    <t>SATS</t>
+  </si>
+  <si>
+    <t>GSHD</t>
+  </si>
+  <si>
+    <t>ACVA</t>
+  </si>
+  <si>
+    <t>IMTX</t>
+  </si>
+  <si>
+    <t>DIT</t>
+  </si>
+  <si>
+    <t>VRTV</t>
+  </si>
+  <si>
+    <t>WLDN</t>
+  </si>
+  <si>
+    <t>CNM</t>
+  </si>
+  <si>
+    <t>AVDL</t>
+  </si>
+  <si>
+    <t>UBER</t>
+  </si>
+  <si>
+    <t>NUVL</t>
+  </si>
+  <si>
+    <t>LOB</t>
+  </si>
+  <si>
+    <t>ACAD</t>
+  </si>
+  <si>
+    <t>LLY</t>
+  </si>
+  <si>
+    <t>CYD</t>
+  </si>
+  <si>
+    <t>AVGO</t>
+  </si>
+  <si>
+    <t>UPWK</t>
+  </si>
+  <si>
+    <t>ASMIY</t>
+  </si>
+  <si>
+    <t>ATRO</t>
+  </si>
+  <si>
+    <t>ROCK</t>
+  </si>
+  <si>
+    <t>UFPT</t>
+  </si>
+  <si>
+    <t>KBH</t>
+  </si>
+  <si>
+    <t>AROC</t>
+  </si>
+  <si>
+    <t>RCMT</t>
+  </si>
+  <si>
+    <t>PRO</t>
+  </si>
+  <si>
+    <t>VECO</t>
+  </si>
+  <si>
+    <t>VIST</t>
+  </si>
+  <si>
+    <t>EME</t>
+  </si>
+  <si>
+    <t>SPOK</t>
+  </si>
+  <si>
+    <t>ANF</t>
+  </si>
+  <si>
+    <t>BMA</t>
+  </si>
+  <si>
+    <t>ROKU</t>
+  </si>
+  <si>
+    <t>PLPC</t>
+  </si>
+  <si>
+    <t>WMS</t>
+  </si>
+  <si>
+    <t>FRSH</t>
+  </si>
+  <si>
+    <t>BLX</t>
+  </si>
+  <si>
+    <t>KRT</t>
+  </si>
+  <si>
+    <t>CLBR</t>
+  </si>
+  <si>
+    <t>VSTM</t>
+  </si>
+  <si>
+    <t>KRUS</t>
+  </si>
+  <si>
+    <t>ACU</t>
+  </si>
+  <si>
+    <t>GKOS</t>
+  </si>
+  <si>
+    <t>LII</t>
+  </si>
+  <si>
+    <t>RXRX</t>
+  </si>
+  <si>
+    <t>EDU</t>
+  </si>
+  <si>
+    <t>ISEE</t>
+  </si>
+  <si>
+    <t>KTOS</t>
+  </si>
+  <si>
+    <t>SSD</t>
+  </si>
+  <si>
+    <t>VICR</t>
+  </si>
+  <si>
+    <t>PARR</t>
+  </si>
+  <si>
+    <t>GRVY</t>
+  </si>
+  <si>
+    <t>NRP</t>
+  </si>
+  <si>
+    <t>KALV</t>
   </si>
   <si>
     <t>VEL</t>
   </si>
   <si>
-    <t>IDCC</t>
-  </si>
-  <si>
-    <t>GE</t>
-  </si>
-  <si>
-    <t>CSTM</t>
-  </si>
-  <si>
-    <t>CRH</t>
-  </si>
-  <si>
-    <t>INMD</t>
-  </si>
-  <si>
-    <t>LAD</t>
-  </si>
-  <si>
-    <t>IIVI</t>
-  </si>
-  <si>
-    <t>DECK</t>
-  </si>
-  <si>
-    <t>BMEA</t>
-  </si>
-  <si>
-    <t>DUOL</t>
-  </si>
-  <si>
-    <t>URBN</t>
-  </si>
-  <si>
-    <t>SWI</t>
-  </si>
-  <si>
-    <t>GHRS</t>
-  </si>
-  <si>
-    <t>ATEC</t>
-  </si>
-  <si>
-    <t>GMS</t>
-  </si>
-  <si>
-    <t>BUR</t>
+    <t>PETQ</t>
+  </si>
+  <si>
+    <t>OC</t>
+  </si>
+  <si>
+    <t>EB</t>
+  </si>
+  <si>
+    <t>TREX</t>
   </si>
   <si>
     <t>PCTTU</t>
   </si>
   <si>
-    <t>FUTU</t>
-  </si>
-  <si>
-    <t>PATK</t>
-  </si>
-  <si>
-    <t>KRNT</t>
-  </si>
-  <si>
-    <t>CNX</t>
-  </si>
-  <si>
-    <t>APO</t>
-  </si>
-  <si>
-    <t>ON</t>
-  </si>
-  <si>
-    <t>AGRO</t>
+    <t>TTD</t>
+  </si>
+  <si>
+    <t>SOVO</t>
+  </si>
+  <si>
+    <t>MATX</t>
+  </si>
+  <si>
+    <t>MLP</t>
+  </si>
+  <si>
+    <t>CAAP</t>
+  </si>
+  <si>
+    <t>PCT</t>
+  </si>
+  <si>
+    <t>ONON</t>
+  </si>
+  <si>
+    <t>CVRX</t>
+  </si>
+  <si>
+    <t>IMRX</t>
+  </si>
+  <si>
+    <t>GGAL</t>
+  </si>
+  <si>
+    <t>VKTX</t>
+  </si>
+  <si>
+    <t>SDGR</t>
+  </si>
+  <si>
+    <t>ACLS</t>
+  </si>
+  <si>
+    <t>SG</t>
+  </si>
+  <si>
+    <t>PHAT</t>
+  </si>
+  <si>
+    <t>JOE</t>
+  </si>
+  <si>
+    <t>PHM</t>
+  </si>
+  <si>
+    <t>MDWT</t>
+  </si>
+  <si>
+    <t>IBP</t>
+  </si>
+  <si>
+    <t>SRDX</t>
+  </si>
+  <si>
+    <t>AEHR</t>
+  </si>
+  <si>
+    <t>SBOW</t>
   </si>
   <si>
     <t>GHM</t>
   </si>
   <si>
-    <t>PCYO</t>
-  </si>
-  <si>
-    <t>CRC</t>
-  </si>
-  <si>
-    <t>NOG</t>
-  </si>
-  <si>
-    <t>JWN</t>
-  </si>
-  <si>
-    <t>ZG</t>
-  </si>
-  <si>
-    <t>MRVL</t>
-  </si>
-  <si>
-    <t>NEWT</t>
-  </si>
-  <si>
-    <t>TNET</t>
-  </si>
-  <si>
-    <t>FIX</t>
-  </si>
-  <si>
-    <t>FROG</t>
-  </si>
-  <si>
-    <t>TEX</t>
-  </si>
-  <si>
-    <t>ODFL</t>
-  </si>
-  <si>
-    <t>TMHC</t>
-  </si>
-  <si>
-    <t>RMBL</t>
-  </si>
-  <si>
-    <t>CSAN</t>
-  </si>
-  <si>
-    <t>Z</t>
-  </si>
-  <si>
-    <t>HLF</t>
-  </si>
-  <si>
-    <t>ATRC</t>
-  </si>
-  <si>
-    <t>AZUL</t>
-  </si>
-  <si>
-    <t>FDX</t>
-  </si>
-  <si>
-    <t>SMHI</t>
-  </si>
-  <si>
-    <t>VIPS</t>
-  </si>
-  <si>
-    <t>PH</t>
-  </si>
-  <si>
-    <t>PRIM</t>
-  </si>
-  <si>
-    <t>PAG</t>
-  </si>
-  <si>
-    <t>AEIS</t>
-  </si>
-  <si>
-    <t>MTW</t>
-  </si>
-  <si>
-    <t>ITRI</t>
-  </si>
-  <si>
-    <t>PRI</t>
-  </si>
-  <si>
-    <t>MSA</t>
-  </si>
-  <si>
-    <t>DDOG</t>
-  </si>
-  <si>
-    <t>MDC</t>
-  </si>
-  <si>
-    <t>TOL</t>
-  </si>
-  <si>
-    <t>PARR</t>
-  </si>
-  <si>
-    <t>VNO</t>
-  </si>
-  <si>
-    <t>SPNT</t>
-  </si>
-  <si>
-    <t>HAYW</t>
-  </si>
-  <si>
-    <t>ARGX</t>
-  </si>
-  <si>
-    <t>NVT</t>
-  </si>
-  <si>
-    <t>SPNS</t>
-  </si>
-  <si>
-    <t>AXR</t>
-  </si>
-  <si>
-    <t>BMI</t>
-  </si>
-  <si>
-    <t>SLG</t>
-  </si>
-  <si>
-    <t>SWDAF</t>
-  </si>
-  <si>
-    <t>PNR</t>
-  </si>
-  <si>
-    <t>NEWR</t>
-  </si>
-  <si>
-    <t>TSQ</t>
-  </si>
-  <si>
-    <t>PKOH</t>
-  </si>
-  <si>
-    <t>HURN</t>
-  </si>
-  <si>
-    <t>AMWD</t>
-  </si>
-  <si>
-    <t>CVGI</t>
-  </si>
-  <si>
-    <t>CYD</t>
-  </si>
-  <si>
-    <t>APG</t>
-  </si>
-  <si>
-    <t>PETQ</t>
-  </si>
-  <si>
-    <t>USLM</t>
-  </si>
-  <si>
-    <t>IMVT</t>
-  </si>
-  <si>
-    <t>LRCX</t>
-  </si>
-  <si>
-    <t>ZWS</t>
-  </si>
-  <si>
-    <t>MGNI</t>
-  </si>
-  <si>
-    <t>ETD</t>
-  </si>
-  <si>
-    <t>WMS</t>
-  </si>
-  <si>
-    <t>TSLA</t>
-  </si>
-  <si>
-    <t>SIBN</t>
-  </si>
-  <si>
-    <t>AMNB</t>
-  </si>
-  <si>
-    <t>INBK</t>
-  </si>
-  <si>
-    <t>HSKA</t>
-  </si>
-  <si>
-    <t>JBL</t>
-  </si>
-  <si>
-    <t>COOP</t>
-  </si>
-  <si>
-    <t>YPF</t>
-  </si>
-  <si>
-    <t>WPRT</t>
-  </si>
-  <si>
-    <t>ZGN</t>
-  </si>
-  <si>
-    <t>BATRA</t>
-  </si>
-  <si>
-    <t>ACOR</t>
-  </si>
-  <si>
-    <t>FLNC</t>
-  </si>
-  <si>
-    <t>OTTR</t>
-  </si>
-  <si>
-    <t>ONTO</t>
-  </si>
-  <si>
-    <t>AUPH</t>
-  </si>
-  <si>
-    <t>FTDR</t>
-  </si>
-  <si>
-    <t>BVH</t>
-  </si>
-  <si>
-    <t>DIT</t>
-  </si>
-  <si>
-    <t>MTH</t>
-  </si>
-  <si>
-    <t>FMS</t>
-  </si>
-  <si>
-    <t>HROW</t>
-  </si>
-  <si>
-    <t>GOCO</t>
-  </si>
-  <si>
-    <t>ARCO</t>
-  </si>
-  <si>
-    <t>NTES</t>
-  </si>
-  <si>
-    <t>CARR</t>
-  </si>
-  <si>
-    <t>AEL</t>
-  </si>
-  <si>
-    <t>NUVL</t>
-  </si>
-  <si>
-    <t>SHC</t>
-  </si>
-  <si>
-    <t>ANDE</t>
-  </si>
-  <si>
-    <t>NE</t>
-  </si>
-  <si>
-    <t>FTI</t>
-  </si>
-  <si>
-    <t>VECO</t>
-  </si>
-  <si>
-    <t>NRP</t>
-  </si>
-  <si>
-    <t>RVMD</t>
-  </si>
-  <si>
-    <t>KRUS</t>
-  </si>
-  <si>
-    <t>MOMO</t>
-  </si>
-  <si>
-    <t>KRYS</t>
-  </si>
-  <si>
-    <t>RCM</t>
-  </si>
-  <si>
-    <t>ASMIY</t>
-  </si>
-  <si>
-    <t>BLX</t>
-  </si>
-  <si>
-    <t>VICR</t>
-  </si>
-  <si>
-    <t>EME</t>
-  </si>
-  <si>
-    <t>KRT</t>
-  </si>
-  <si>
-    <t>HCCI</t>
-  </si>
-  <si>
-    <t>NATR</t>
-  </si>
-  <si>
-    <t>CFLT</t>
-  </si>
-  <si>
-    <t>CSWI</t>
-  </si>
-  <si>
-    <t>SPOK</t>
-  </si>
-  <si>
-    <t>EXAS</t>
-  </si>
-  <si>
-    <t>CORT</t>
-  </si>
-  <si>
-    <t>PLAB</t>
-  </si>
-  <si>
-    <t>LPG</t>
-  </si>
-  <si>
-    <t>ALGN</t>
-  </si>
-  <si>
-    <t>ADBE</t>
-  </si>
-  <si>
-    <t>CNM</t>
-  </si>
-  <si>
-    <t>AVGO</t>
-  </si>
-  <si>
-    <t>APPF</t>
-  </si>
-  <si>
-    <t>KBH</t>
-  </si>
-  <si>
-    <t>GTLS</t>
-  </si>
-  <si>
-    <t>GSHD</t>
-  </si>
-  <si>
-    <t>AZEK</t>
+    <t>FCAP</t>
+  </si>
+  <si>
+    <t>EBIX</t>
+  </si>
+  <si>
+    <t>ETHE</t>
+  </si>
+  <si>
+    <t>RIVN</t>
+  </si>
+  <si>
+    <t>OSTK</t>
+  </si>
+  <si>
+    <t>PAY</t>
+  </si>
+  <si>
+    <t>RH</t>
   </si>
   <si>
     <t>FTAI</t>
   </si>
   <si>
-    <t>AROC</t>
-  </si>
-  <si>
-    <t>THO</t>
+    <t>ABCM</t>
+  </si>
+  <si>
+    <t>GBX</t>
+  </si>
+  <si>
+    <t>RCL</t>
+  </si>
+  <si>
+    <t>ROIV</t>
+  </si>
+  <si>
+    <t>MORF</t>
+  </si>
+  <si>
+    <t>CABA</t>
+  </si>
+  <si>
+    <t>MSTR</t>
+  </si>
+  <si>
+    <t>CVLG</t>
+  </si>
+  <si>
+    <t>NIO</t>
+  </si>
+  <si>
+    <t>IOT</t>
+  </si>
+  <si>
+    <t>COCO</t>
+  </si>
+  <si>
+    <t>ENVX</t>
+  </si>
+  <si>
+    <t>NOA</t>
+  </si>
+  <si>
+    <t>EDN</t>
+  </si>
+  <si>
+    <t>GRBK</t>
+  </si>
+  <si>
+    <t>WFRD</t>
+  </si>
+  <si>
+    <t>FCNCA</t>
+  </si>
+  <si>
+    <t>RILY</t>
+  </si>
+  <si>
+    <t>DMRC</t>
+  </si>
+  <si>
+    <t>EXTR</t>
+  </si>
+  <si>
+    <t>TDW</t>
+  </si>
+  <si>
+    <t>BLD</t>
+  </si>
+  <si>
+    <t>DICE</t>
+  </si>
+  <si>
+    <t>PRG</t>
+  </si>
+  <si>
+    <t>BLU</t>
+  </si>
+  <si>
+    <t>LZ</t>
+  </si>
+  <si>
+    <t>SAIA</t>
+  </si>
+  <si>
+    <t>CMT</t>
+  </si>
+  <si>
+    <t>RELY</t>
+  </si>
+  <si>
+    <t>BCC</t>
+  </si>
+  <si>
+    <t>NGMS</t>
   </si>
   <si>
     <t>IESC</t>
   </si>
   <si>
-    <t>DOCN</t>
-  </si>
-  <si>
-    <t>SBOW</t>
-  </si>
-  <si>
-    <t>EB</t>
-  </si>
-  <si>
-    <t>YELP</t>
-  </si>
-  <si>
-    <t>LOB</t>
-  </si>
-  <si>
-    <t>BRZE</t>
-  </si>
-  <si>
-    <t>CAAP</t>
-  </si>
-  <si>
-    <t>BMA</t>
-  </si>
-  <si>
-    <t>VIST</t>
-  </si>
-  <si>
-    <t>ROCK</t>
-  </si>
-  <si>
-    <t>NEX</t>
-  </si>
-  <si>
-    <t>ARCB</t>
-  </si>
-  <si>
-    <t>LEGN</t>
-  </si>
-  <si>
-    <t>TAYD</t>
-  </si>
-  <si>
-    <t>KNSA</t>
-  </si>
-  <si>
-    <t>PRO</t>
-  </si>
-  <si>
-    <t>FRSH</t>
-  </si>
-  <si>
-    <t>NYCB</t>
-  </si>
-  <si>
-    <t>TYRA</t>
-  </si>
-  <si>
-    <t>RDNT</t>
-  </si>
-  <si>
-    <t>UPWK</t>
-  </si>
-  <si>
-    <t>LII</t>
-  </si>
-  <si>
-    <t>ERO</t>
-  </si>
-  <si>
-    <t>BWMN</t>
-  </si>
-  <si>
-    <t>DASH</t>
-  </si>
-  <si>
-    <t>TDC</t>
-  </si>
-  <si>
-    <t>UBER</t>
-  </si>
-  <si>
-    <t>CLBR</t>
-  </si>
-  <si>
-    <t>SCX</t>
-  </si>
-  <si>
-    <t>BECN</t>
-  </si>
-  <si>
-    <t>ACAD</t>
-  </si>
-  <si>
-    <t>ARHS</t>
-  </si>
-  <si>
-    <t>SRDX</t>
-  </si>
-  <si>
-    <t>ETHE</t>
-  </si>
-  <si>
-    <t>ANF</t>
-  </si>
-  <si>
-    <t>TREX</t>
-  </si>
-  <si>
-    <t>VKTX</t>
-  </si>
-  <si>
-    <t>GKOS</t>
-  </si>
-  <si>
-    <t>RCMT</t>
-  </si>
-  <si>
-    <t>SSD</t>
-  </si>
-  <si>
-    <t>TTD</t>
-  </si>
-  <si>
-    <t>KALV</t>
-  </si>
-  <si>
-    <t>SGH</t>
-  </si>
-  <si>
-    <t>HELE</t>
-  </si>
-  <si>
-    <t>OC</t>
-  </si>
-  <si>
-    <t>AVDL</t>
-  </si>
-  <si>
-    <t>RILY</t>
-  </si>
-  <si>
-    <t>ACVA</t>
-  </si>
-  <si>
-    <t>IAS</t>
-  </si>
-  <si>
-    <t>IBP</t>
-  </si>
-  <si>
-    <t>MDWT</t>
-  </si>
-  <si>
-    <t>JOE</t>
-  </si>
-  <si>
-    <t>PHM</t>
-  </si>
-  <si>
-    <t>COCO</t>
-  </si>
-  <si>
-    <t>UFPT</t>
-  </si>
-  <si>
-    <t>BOOT</t>
-  </si>
-  <si>
-    <t>MLP</t>
-  </si>
-  <si>
-    <t>ONON</t>
-  </si>
-  <si>
-    <t>AEHR</t>
-  </si>
-  <si>
-    <t>GRBK</t>
-  </si>
-  <si>
-    <t>IMTX</t>
-  </si>
-  <si>
-    <t>JELD</t>
-  </si>
-  <si>
-    <t>GRVY</t>
-  </si>
-  <si>
-    <t>PLPC</t>
-  </si>
-  <si>
-    <t>GLBE</t>
-  </si>
-  <si>
-    <t>PHAT</t>
-  </si>
-  <si>
-    <t>LUNG</t>
-  </si>
-  <si>
-    <t>MATX</t>
-  </si>
-  <si>
-    <t>MRUS</t>
-  </si>
-  <si>
-    <t>GGAL</t>
-  </si>
-  <si>
-    <t>ABCM</t>
-  </si>
-  <si>
-    <t>CRMT</t>
-  </si>
-  <si>
-    <t>BLD</t>
-  </si>
-  <si>
-    <t>ENVX</t>
-  </si>
-  <si>
-    <t>MNSO</t>
+    <t>MDB</t>
+  </si>
+  <si>
+    <t>CUBI</t>
+  </si>
+  <si>
+    <t>NWLI</t>
+  </si>
+  <si>
+    <t>BWMX</t>
+  </si>
+  <si>
+    <t>GBTC</t>
+  </si>
+  <si>
+    <t>FSLY</t>
+  </si>
+  <si>
+    <t>CCL</t>
+  </si>
+  <si>
+    <t>XP</t>
+  </si>
+  <si>
+    <t>COIN</t>
+  </si>
+  <si>
+    <t>USAP</t>
   </si>
   <si>
     <t>STVN</t>
   </si>
   <si>
-    <t>DMRC</t>
-  </si>
-  <si>
-    <t>BWMX</t>
-  </si>
-  <si>
-    <t>SG</t>
-  </si>
-  <si>
-    <t>ISEE</t>
-  </si>
-  <si>
-    <t>EXTR</t>
-  </si>
-  <si>
-    <t>IMRX</t>
-  </si>
-  <si>
-    <t>RCL</t>
-  </si>
-  <si>
-    <t>PCT</t>
-  </si>
-  <si>
-    <t>FCAP</t>
-  </si>
-  <si>
-    <t>SDGR</t>
-  </si>
-  <si>
-    <t>WFRD</t>
-  </si>
-  <si>
-    <t>ARCT</t>
-  </si>
-  <si>
-    <t>ROKU</t>
-  </si>
-  <si>
-    <t>CVRX</t>
-  </si>
-  <si>
-    <t>BLU</t>
-  </si>
-  <si>
-    <t>CVLG</t>
-  </si>
-  <si>
-    <t>TCMD</t>
-  </si>
-  <si>
-    <t>VSTM</t>
-  </si>
-  <si>
-    <t>RELY</t>
-  </si>
-  <si>
-    <t>RH</t>
-  </si>
-  <si>
-    <t>MORF</t>
-  </si>
-  <si>
-    <t>RIVN</t>
-  </si>
-  <si>
-    <t>GBTC</t>
-  </si>
-  <si>
-    <t>CMT</t>
-  </si>
-  <si>
-    <t>MSTR</t>
-  </si>
-  <si>
-    <t>EBIX</t>
-  </si>
-  <si>
-    <t>FCNCA</t>
-  </si>
-  <si>
-    <t>GBX</t>
-  </si>
-  <si>
-    <t>BCC</t>
-  </si>
-  <si>
-    <t>ROIV</t>
-  </si>
-  <si>
     <t>QTRX</t>
   </si>
   <si>
-    <t>EDU</t>
-  </si>
-  <si>
-    <t>RXRX</t>
-  </si>
-  <si>
-    <t>PRG</t>
-  </si>
-  <si>
-    <t>COIN</t>
-  </si>
-  <si>
-    <t>SAIA</t>
-  </si>
-  <si>
-    <t>ACLS</t>
-  </si>
-  <si>
-    <t>DICE</t>
-  </si>
-  <si>
-    <t>LZ</t>
-  </si>
-  <si>
-    <t>TDW</t>
-  </si>
-  <si>
-    <t>NOA</t>
+    <t>VECT</t>
+  </si>
+  <si>
+    <t>LI</t>
+  </si>
+  <si>
+    <t>MHO</t>
+  </si>
+  <si>
+    <t>CUK</t>
+  </si>
+  <si>
+    <t>AI</t>
+  </si>
+  <si>
+    <t>HOV</t>
+  </si>
+  <si>
+    <t>WRLD</t>
+  </si>
+  <si>
+    <t>FRD</t>
+  </si>
+  <si>
+    <t>CIR</t>
+  </si>
+  <si>
+    <t>RCEL</t>
+  </si>
+  <si>
+    <t>DKNG</t>
+  </si>
+  <si>
+    <t>ALPN</t>
+  </si>
+  <si>
+    <t>LMB</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>EXPI</t>
+  </si>
+  <si>
+    <t>BLDR</t>
+  </si>
+  <si>
+    <t>CLS</t>
+  </si>
+  <si>
+    <t>KDNY</t>
+  </si>
+  <si>
+    <t>RXST</t>
+  </si>
+  <si>
+    <t>CAMT</t>
+  </si>
+  <si>
+    <t>ODC</t>
+  </si>
+  <si>
+    <t>PESI</t>
+  </si>
+  <si>
+    <t>CMPR</t>
+  </si>
+  <si>
+    <t>CPS</t>
+  </si>
+  <si>
+    <t>PLTR</t>
+  </si>
+  <si>
+    <t>LSEA</t>
+  </si>
+  <si>
+    <t>NVDA</t>
+  </si>
+  <si>
+    <t>ELF</t>
+  </si>
+  <si>
+    <t>AMPH</t>
+  </si>
+  <si>
+    <t>INOD</t>
+  </si>
+  <si>
+    <t>SKYW</t>
+  </si>
+  <si>
+    <t>TDS</t>
+  </si>
+  <si>
+    <t>XPO</t>
+  </si>
+  <si>
+    <t>APP</t>
+  </si>
+  <si>
+    <t>WEAV</t>
+  </si>
+  <si>
+    <t>FOR</t>
+  </si>
+  <si>
+    <t>MOD</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>CBAY</t>
+  </si>
+  <si>
+    <t>XPEV</t>
+  </si>
+  <si>
+    <t>TRHC</t>
+  </si>
+  <si>
+    <t>OPRA</t>
   </si>
   <si>
     <t>STRL</t>
   </si>
   <si>
-    <t>MHO</t>
-  </si>
-  <si>
-    <t>NWLI</t>
-  </si>
-  <si>
-    <t>FSLY</t>
-  </si>
-  <si>
-    <t>HOV</t>
-  </si>
-  <si>
-    <t>DKNG</t>
-  </si>
-  <si>
-    <t>NGMS</t>
-  </si>
-  <si>
-    <t>CCL</t>
-  </si>
-  <si>
-    <t>CUBI</t>
-  </si>
-  <si>
-    <t>EDN</t>
-  </si>
-  <si>
-    <t>CUK</t>
-  </si>
-  <si>
-    <t>XP</t>
-  </si>
-  <si>
-    <t>ATRO</t>
-  </si>
-  <si>
-    <t>WRLD</t>
-  </si>
-  <si>
-    <t>IOT</t>
-  </si>
-  <si>
-    <t>USAP</t>
-  </si>
-  <si>
-    <t>CPS</t>
-  </si>
-  <si>
-    <t>VECT</t>
-  </si>
-  <si>
-    <t>NIO</t>
-  </si>
-  <si>
-    <t>CABA</t>
-  </si>
-  <si>
-    <t>BLDR</t>
-  </si>
-  <si>
-    <t>CLS</t>
-  </si>
-  <si>
-    <t>ALPN</t>
-  </si>
-  <si>
-    <t>LMB</t>
-  </si>
-  <si>
-    <t>MDB</t>
-  </si>
-  <si>
-    <t>XPO</t>
-  </si>
-  <si>
-    <t>OSTK</t>
-  </si>
-  <si>
-    <t>MRNS</t>
-  </si>
-  <si>
-    <t>EXPI</t>
-  </si>
-  <si>
-    <t>LSEA</t>
-  </si>
-  <si>
-    <t>KDNY</t>
-  </si>
-  <si>
-    <t>ODC</t>
-  </si>
-  <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>AMPH</t>
-  </si>
-  <si>
-    <t>CAMT</t>
+    <t>BZH</t>
+  </si>
+  <si>
+    <t>MEOA</t>
+  </si>
+  <si>
+    <t>MARA</t>
+  </si>
+  <si>
+    <t>USM</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>ARLO</t>
+  </si>
+  <si>
+    <t>RXDX</t>
+  </si>
+  <si>
+    <t>URGN</t>
   </si>
   <si>
     <t>DFH</t>
   </si>
   <si>
-    <t>ELF</t>
-  </si>
-  <si>
-    <t>NVDA</t>
-  </si>
-  <si>
-    <t>FRD</t>
-  </si>
-  <si>
-    <t>RCEL</t>
-  </si>
-  <si>
-    <t>APP</t>
-  </si>
-  <si>
-    <t>FOR</t>
-  </si>
-  <si>
-    <t>AI</t>
-  </si>
-  <si>
-    <t>RDFN</t>
-  </si>
-  <si>
-    <t>CMPR</t>
-  </si>
-  <si>
-    <t>SKYW</t>
-  </si>
-  <si>
-    <t>RXST</t>
-  </si>
-  <si>
-    <t>CBAY</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>BZH</t>
-  </si>
-  <si>
-    <t>MEOA</t>
-  </si>
-  <si>
-    <t>LI</t>
-  </si>
-  <si>
-    <t>CIR</t>
-  </si>
-  <si>
-    <t>OPRA</t>
-  </si>
-  <si>
-    <t>WEAV</t>
-  </si>
-  <si>
-    <t>PLTR</t>
-  </si>
-  <si>
-    <t>POWL</t>
-  </si>
-  <si>
-    <t>MARA</t>
-  </si>
-  <si>
-    <t>RXDX</t>
-  </si>
-  <si>
-    <t>INOD</t>
-  </si>
-  <si>
-    <t>ARLO</t>
-  </si>
-  <si>
-    <t>W</t>
-  </si>
-  <si>
-    <t>WW</t>
-  </si>
-  <si>
-    <t>ROOT</t>
+    <t>MEOAU</t>
+  </si>
+  <si>
+    <t>RIOT</t>
+  </si>
+  <si>
+    <t>IMGN</t>
   </si>
   <si>
     <t>VRT</t>
   </si>
   <si>
-    <t>URGN</t>
-  </si>
-  <si>
-    <t>MEOAU</t>
-  </si>
-  <si>
-    <t>XPEV</t>
-  </si>
-  <si>
-    <t>EVLO</t>
-  </si>
-  <si>
-    <t>RIOT</t>
+    <t>IONQ</t>
+  </si>
+  <si>
+    <t>UPST</t>
   </si>
   <si>
     <t>EH</t>
   </si>
   <si>
-    <t>IMGN</t>
+    <t>BBIO</t>
+  </si>
+  <si>
+    <t>CDLX</t>
+  </si>
+  <si>
+    <t>RETA</t>
   </si>
   <si>
     <t>SMCI</t>
   </si>
   <si>
-    <t>RETA</t>
-  </si>
-  <si>
-    <t>BBIO</t>
-  </si>
-  <si>
-    <t>CDLX</t>
-  </si>
-  <si>
-    <t>IONQ</t>
-  </si>
-  <si>
     <t>EYPT</t>
   </si>
   <si>
     <t>PHVS</t>
   </si>
   <si>
-    <t>UPST</t>
-  </si>
-  <si>
-    <t>NERV</t>
+    <t>AURCU</t>
   </si>
   <si>
     <t>SGTX</t>
   </si>
   <si>
-    <t>AURCU</t>
+    <t>CVNA</t>
   </si>
   <si>
     <t>AURC</t>
   </si>
   <si>
-    <t>CVNA</t>
+    <t>AAOI</t>
   </si>
   <si>
     <t>EDTXU</t>
@@ -1465,7 +1453,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B366"/>
+  <dimension ref="A1:B362"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1481,7 +1469,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1">
-        <v>125.4154569860466</v>
+        <v>124.6092621817537</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1489,7 +1477,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1">
-        <v>125.4657774009173</v>
+        <v>124.6364682239148</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1497,7 +1485,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1">
-        <v>125.4699506555531</v>
+        <v>124.6757575560775</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1505,7 +1493,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="1">
-        <v>125.4731562073149</v>
+        <v>124.6837062415044</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1513,7 +1501,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="1">
-        <v>125.6951306276823</v>
+        <v>124.7390818158684</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1521,7 +1509,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="1">
-        <v>125.7573126181318</v>
+        <v>124.7630255049716</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1529,7 +1517,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="1">
-        <v>125.7623768225628</v>
+        <v>124.7880886181516</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1537,7 +1525,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="1">
-        <v>125.7674813525781</v>
+        <v>124.8280693271704</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1545,7 +1533,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="1">
-        <v>125.8103065931918</v>
+        <v>124.8369686859967</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1553,7 +1541,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="1">
-        <v>125.9707227683371</v>
+        <v>124.9432997325041</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1561,7 +1549,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="1">
-        <v>125.9887530401834</v>
+        <v>125.0558091173492</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1569,7 +1557,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="1">
-        <v>126.0024384509456</v>
+        <v>125.1606336601367</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1577,7 +1565,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="1">
-        <v>126.0036838243176</v>
+        <v>125.1816736423053</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1585,7 +1573,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="1">
-        <v>126.0097318327312</v>
+        <v>125.2537440814427</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1593,7 +1581,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="1">
-        <v>126.0343638742141</v>
+        <v>125.2755177788623</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1601,7 +1589,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="1">
-        <v>126.140502577076</v>
+        <v>125.2933726441961</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1609,7 +1597,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="1">
-        <v>126.1726950360488</v>
+        <v>125.3140746608057</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1617,7 +1605,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="1">
-        <v>126.2011857609074</v>
+        <v>125.3766515840249</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1625,7 +1613,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="1">
-        <v>126.2308646934236</v>
+        <v>125.4289676630226</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1633,7 +1621,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="1">
-        <v>126.2461864176311</v>
+        <v>125.4506226960056</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1641,7 +1629,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="1">
-        <v>126.2602539860691</v>
+        <v>125.4637703989916</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1649,7 +1637,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="1">
-        <v>126.3146395324592</v>
+        <v>125.4720128070037</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1657,7 +1645,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="1">
-        <v>126.3386576001221</v>
+        <v>125.4886856413621</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1665,7 +1653,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="1">
-        <v>126.3842058001431</v>
+        <v>125.5570666399557</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1673,7 +1661,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="1">
-        <v>126.4932365873209</v>
+        <v>125.5690747059299</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1681,7 +1669,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="1">
-        <v>126.5777271183209</v>
+        <v>125.8346589681354</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1689,7 +1677,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="1">
-        <v>126.6382005830039</v>
+        <v>125.9943609756212</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1697,7 +1685,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="1">
-        <v>126.7214873855165</v>
+        <v>126.004104572607</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1705,7 +1693,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="1">
-        <v>126.7550295314504</v>
+        <v>126.0959969014464</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1713,7 +1701,7 @@
         <v>31</v>
       </c>
       <c r="B31" s="1">
-        <v>126.7716456050033</v>
+        <v>126.1462210850073</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1721,7 +1709,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="1">
-        <v>126.8170257536855</v>
+        <v>126.1906243480294</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1729,7 +1717,7 @@
         <v>33</v>
       </c>
       <c r="B33" s="1">
-        <v>126.8588001506004</v>
+        <v>126.2051213363564</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1737,7 +1725,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="1">
-        <v>126.8767456043908</v>
+        <v>126.2409187568156</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1745,7 +1733,7 @@
         <v>35</v>
       </c>
       <c r="B35" s="1">
-        <v>126.8777742662679</v>
+        <v>126.2844173570107</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1753,7 +1741,7 @@
         <v>36</v>
       </c>
       <c r="B36" s="1">
-        <v>126.9119845263428</v>
+        <v>126.3427780197734</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1761,7 +1749,7 @@
         <v>37</v>
       </c>
       <c r="B37" s="1">
-        <v>126.9222855493987</v>
+        <v>126.4459007686974</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1769,7 +1757,7 @@
         <v>38</v>
       </c>
       <c r="B38" s="1">
-        <v>126.9612372181901</v>
+        <v>126.4652698265689</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1777,7 +1765,7 @@
         <v>39</v>
       </c>
       <c r="B39" s="1">
-        <v>126.992605114516</v>
+        <v>126.5707330014932</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1785,7 +1773,7 @@
         <v>40</v>
       </c>
       <c r="B40" s="1">
-        <v>127.0473652217298</v>
+        <v>126.6075083527369</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1793,7 +1781,7 @@
         <v>41</v>
       </c>
       <c r="B41" s="1">
-        <v>127.1311619578275</v>
+        <v>126.6221368823283</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -1801,7 +1789,7 @@
         <v>42</v>
       </c>
       <c r="B42" s="1">
-        <v>127.145499222131</v>
+        <v>126.6527518917484</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -1809,7 +1797,7 @@
         <v>43</v>
       </c>
       <c r="B43" s="1">
-        <v>127.2317493649838</v>
+        <v>126.6666884551212</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1817,7 +1805,7 @@
         <v>44</v>
       </c>
       <c r="B44" s="1">
-        <v>127.2820628086953</v>
+        <v>126.677098284089</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1825,7 +1813,7 @@
         <v>45</v>
       </c>
       <c r="B45" s="1">
-        <v>127.3103653781682</v>
+        <v>126.7452086618515</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1833,7 +1821,7 @@
         <v>46</v>
       </c>
       <c r="B46" s="1">
-        <v>127.3644032535261</v>
+        <v>126.7927421787385</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -1841,7 +1829,7 @@
         <v>47</v>
       </c>
       <c r="B47" s="1">
-        <v>127.3767151230392</v>
+        <v>126.8117681832398</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -1849,7 +1837,7 @@
         <v>48</v>
       </c>
       <c r="B48" s="1">
-        <v>127.4136491841599</v>
+        <v>126.870568083185</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1857,7 +1845,7 @@
         <v>49</v>
       </c>
       <c r="B49" s="1">
-        <v>127.4969527508918</v>
+        <v>126.9644429324393</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1865,7 +1853,7 @@
         <v>50</v>
       </c>
       <c r="B50" s="1">
-        <v>127.502994653038</v>
+        <v>126.9739429973167</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1873,7 +1861,7 @@
         <v>51</v>
       </c>
       <c r="B51" s="1">
-        <v>127.535502412379</v>
+        <v>127.0106911348959</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1881,7 +1869,7 @@
         <v>52</v>
       </c>
       <c r="B52" s="1">
-        <v>127.5564645692201</v>
+        <v>127.0379439859438</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1889,7 +1877,7 @@
         <v>53</v>
       </c>
       <c r="B53" s="1">
-        <v>127.6012255266318</v>
+        <v>127.0991331832926</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1897,7 +1885,7 @@
         <v>54</v>
       </c>
       <c r="B54" s="1">
-        <v>127.6254711441808</v>
+        <v>127.1542777805376</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1905,7 +1893,7 @@
         <v>55</v>
       </c>
       <c r="B55" s="1">
-        <v>127.6728845124347</v>
+        <v>127.2283553979041</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1913,7 +1901,7 @@
         <v>56</v>
       </c>
       <c r="B56" s="1">
-        <v>127.7057364483806</v>
+        <v>127.4333737509368</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1921,7 +1909,7 @@
         <v>57</v>
       </c>
       <c r="B57" s="1">
-        <v>127.7868839661596</v>
+        <v>127.521919185548</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1929,7 +1917,7 @@
         <v>58</v>
       </c>
       <c r="B58" s="1">
-        <v>127.7902263354532</v>
+        <v>127.5897680550657</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1937,7 +1925,7 @@
         <v>59</v>
       </c>
       <c r="B59" s="1">
-        <v>127.8041030511158</v>
+        <v>127.7669202303683</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1945,7 +1933,7 @@
         <v>60</v>
       </c>
       <c r="B60" s="1">
-        <v>127.8818886223555</v>
+        <v>127.8685407546635</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1953,7 +1941,7 @@
         <v>61</v>
       </c>
       <c r="B61" s="1">
-        <v>127.8951703017764</v>
+        <v>127.881380145986</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1961,7 +1949,7 @@
         <v>62</v>
       </c>
       <c r="B62" s="1">
-        <v>127.9976450407955</v>
+        <v>127.8829858410097</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1969,7 +1957,7 @@
         <v>63</v>
       </c>
       <c r="B63" s="1">
-        <v>128.0999069860749</v>
+        <v>128.142515597018</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1977,7 +1965,7 @@
         <v>64</v>
       </c>
       <c r="B64" s="1">
-        <v>128.3485026017449</v>
+        <v>128.2308683267096</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1985,7 +1973,7 @@
         <v>65</v>
       </c>
       <c r="B65" s="1">
-        <v>128.3651514896611</v>
+        <v>128.2699376687699</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -1993,7 +1981,7 @@
         <v>66</v>
       </c>
       <c r="B66" s="1">
-        <v>128.5911648524974</v>
+        <v>128.2765101072426</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -2001,7 +1989,7 @@
         <v>67</v>
       </c>
       <c r="B67" s="1">
-        <v>128.7475335240506</v>
+        <v>128.288971536425</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -2009,7 +1997,7 @@
         <v>68</v>
       </c>
       <c r="B68" s="1">
-        <v>128.9200542805826</v>
+        <v>128.3388398390167</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -2017,7 +2005,7 @@
         <v>69</v>
       </c>
       <c r="B69" s="1">
-        <v>128.95561112324</v>
+        <v>128.3729778949937</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -2025,7 +2013,7 @@
         <v>70</v>
       </c>
       <c r="B70" s="1">
-        <v>129.1319410947947</v>
+        <v>128.3989458739862</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -2033,7 +2021,7 @@
         <v>71</v>
       </c>
       <c r="B71" s="1">
-        <v>129.138346324377</v>
+        <v>128.4335270990193</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -2041,7 +2029,7 @@
         <v>72</v>
       </c>
       <c r="B72" s="1">
-        <v>129.1447575418808</v>
+        <v>128.451362135509</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2049,7 +2037,7 @@
         <v>73</v>
       </c>
       <c r="B73" s="1">
-        <v>129.1571037060192</v>
+        <v>128.4947166298838</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -2057,7 +2045,7 @@
         <v>74</v>
       </c>
       <c r="B74" s="1">
-        <v>129.1586443789338</v>
+        <v>128.5525964359129</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -2065,7 +2053,7 @@
         <v>75</v>
       </c>
       <c r="B75" s="1">
-        <v>129.2889071963513</v>
+        <v>128.5758769746884</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -2073,7 +2061,7 @@
         <v>76</v>
       </c>
       <c r="B76" s="1">
-        <v>129.3299901380308</v>
+        <v>128.5919157700761</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -2081,7 +2069,7 @@
         <v>77</v>
       </c>
       <c r="B77" s="1">
-        <v>129.3994700182373</v>
+        <v>128.6336232160199</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -2089,7 +2077,7 @@
         <v>78</v>
       </c>
       <c r="B78" s="1">
-        <v>129.4303284653222</v>
+        <v>128.669208395695</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -2097,7 +2085,7 @@
         <v>79</v>
       </c>
       <c r="B79" s="1">
-        <v>129.5236368294642</v>
+        <v>128.7264652008238</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -2105,7 +2093,7 @@
         <v>80</v>
       </c>
       <c r="B80" s="1">
-        <v>129.5412432980482</v>
+        <v>128.7499846069869</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -2113,7 +2101,7 @@
         <v>81</v>
       </c>
       <c r="B81" s="1">
-        <v>129.7253918453006</v>
+        <v>128.8055805616267</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -2121,7 +2109,7 @@
         <v>82</v>
       </c>
       <c r="B82" s="1">
-        <v>129.7262873689581</v>
+        <v>128.8851268634323</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -2129,7 +2117,7 @@
         <v>83</v>
       </c>
       <c r="B83" s="1">
-        <v>129.7272213414045</v>
+        <v>128.9268316039442</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -2137,7 +2125,7 @@
         <v>84</v>
       </c>
       <c r="B84" s="1">
-        <v>129.8698644205666</v>
+        <v>129.0420471825822</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -2145,7 +2133,7 @@
         <v>85</v>
       </c>
       <c r="B85" s="1">
-        <v>129.9755367236706</v>
+        <v>129.1294882308461</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -2153,7 +2141,7 @@
         <v>86</v>
       </c>
       <c r="B86" s="1">
-        <v>130.1084649858213</v>
+        <v>129.2843331183595</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -2161,7 +2149,7 @@
         <v>87</v>
       </c>
       <c r="B87" s="1">
-        <v>130.1711409472614</v>
+        <v>129.3410642721542</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -2169,7 +2157,7 @@
         <v>88</v>
       </c>
       <c r="B88" s="1">
-        <v>130.1807206687365</v>
+        <v>129.3462862966608</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -2177,7 +2165,7 @@
         <v>89</v>
       </c>
       <c r="B89" s="1">
-        <v>130.1824161149963</v>
+        <v>129.4651771430167</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -2185,7 +2173,7 @@
         <v>90</v>
       </c>
       <c r="B90" s="1">
-        <v>130.2502140495358</v>
+        <v>129.4683666802686</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -2193,7 +2181,7 @@
         <v>91</v>
       </c>
       <c r="B91" s="1">
-        <v>130.2812167710583</v>
+        <v>129.507961092539</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -2201,7 +2189,7 @@
         <v>92</v>
       </c>
       <c r="B92" s="1">
-        <v>130.2939831637443</v>
+        <v>129.5621745414584</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -2209,7 +2197,7 @@
         <v>93</v>
       </c>
       <c r="B93" s="1">
-        <v>130.3849330816974</v>
+        <v>129.6275805826434</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -2217,7 +2205,7 @@
         <v>94</v>
       </c>
       <c r="B94" s="1">
-        <v>130.4855645348689</v>
+        <v>129.6616889426944</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -2225,7 +2213,7 @@
         <v>95</v>
       </c>
       <c r="B95" s="1">
-        <v>130.5284886310511</v>
+        <v>129.7631057333545</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -2233,7 +2221,7 @@
         <v>96</v>
       </c>
       <c r="B96" s="1">
-        <v>130.5337568068013</v>
+        <v>129.8273525063746</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -2241,7 +2229,7 @@
         <v>97</v>
       </c>
       <c r="B97" s="1">
-        <v>130.560314527763</v>
+        <v>129.8881568220512</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -2249,7 +2237,7 @@
         <v>98</v>
       </c>
       <c r="B98" s="1">
-        <v>130.629312989649</v>
+        <v>129.9354384238604</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -2257,7 +2245,7 @@
         <v>99</v>
       </c>
       <c r="B99" s="1">
-        <v>130.684717037975</v>
+        <v>129.9627733927852</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -2265,7 +2253,7 @@
         <v>100</v>
       </c>
       <c r="B100" s="1">
-        <v>130.7069823003743</v>
+        <v>130.0974321077746</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -2273,7 +2261,7 @@
         <v>101</v>
       </c>
       <c r="B101" s="1">
-        <v>130.7831613826413</v>
+        <v>130.1233206528872</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -2281,7 +2269,7 @@
         <v>102</v>
       </c>
       <c r="B102" s="1">
-        <v>130.7909113705638</v>
+        <v>130.1933490976917</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -2289,7 +2277,7 @@
         <v>103</v>
       </c>
       <c r="B103" s="1">
-        <v>130.8084151370885</v>
+        <v>130.3101842471494</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -2297,7 +2285,7 @@
         <v>104</v>
       </c>
       <c r="B104" s="1">
-        <v>130.9545374221148</v>
+        <v>130.342784993163</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -2305,7 +2293,7 @@
         <v>105</v>
       </c>
       <c r="B105" s="1">
-        <v>130.9738666142341</v>
+        <v>130.4137425744988</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -2313,7 +2301,7 @@
         <v>106</v>
       </c>
       <c r="B106" s="1">
-        <v>131.0673535767937</v>
+        <v>130.6124345857269</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -2321,7 +2309,7 @@
         <v>107</v>
       </c>
       <c r="B107" s="1">
-        <v>131.0941717948733</v>
+        <v>130.7691305135755</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -2329,7 +2317,7 @@
         <v>108</v>
       </c>
       <c r="B108" s="1">
-        <v>131.2024218480401</v>
+        <v>130.8335549968744</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -2337,7 +2325,7 @@
         <v>109</v>
       </c>
       <c r="B109" s="1">
-        <v>131.3265993505261</v>
+        <v>130.875680939457</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -2345,7 +2333,7 @@
         <v>110</v>
       </c>
       <c r="B110" s="1">
-        <v>131.5081729109738</v>
+        <v>131.0707436564388</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -2353,7 +2341,7 @@
         <v>111</v>
       </c>
       <c r="B111" s="1">
-        <v>131.5093489274657</v>
+        <v>131.1799250904155</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -2361,7 +2349,7 @@
         <v>112</v>
       </c>
       <c r="B112" s="1">
-        <v>131.5201898081596</v>
+        <v>131.1855325380144</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -2369,7 +2357,7 @@
         <v>113</v>
       </c>
       <c r="B113" s="1">
-        <v>131.7292080076733</v>
+        <v>131.2752860153809</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -2377,7 +2365,7 @@
         <v>114</v>
       </c>
       <c r="B114" s="1">
-        <v>131.7361136060909</v>
+        <v>131.27547443351</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -2385,7 +2373,7 @@
         <v>115</v>
       </c>
       <c r="B115" s="1">
-        <v>131.755657470813</v>
+        <v>131.3232784295469</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -2393,7 +2381,7 @@
         <v>116</v>
       </c>
       <c r="B116" s="1">
-        <v>131.7682910342006</v>
+        <v>131.4445365887914</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -2401,7 +2389,7 @@
         <v>117</v>
       </c>
       <c r="B117" s="1">
-        <v>131.7861467476059</v>
+        <v>131.5613138856158</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -2409,7 +2397,7 @@
         <v>118</v>
       </c>
       <c r="B118" s="1">
-        <v>132.0044860904595</v>
+        <v>131.5834964933555</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -2417,7 +2405,7 @@
         <v>119</v>
       </c>
       <c r="B119" s="1">
-        <v>132.0441209219037</v>
+        <v>131.7033931159774</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -2425,7 +2413,7 @@
         <v>120</v>
       </c>
       <c r="B120" s="1">
-        <v>132.0532977514115</v>
+        <v>131.7180612933368</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -2433,7 +2421,7 @@
         <v>121</v>
       </c>
       <c r="B121" s="1">
-        <v>132.0594763273835</v>
+        <v>131.7932215214609</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -2441,7 +2429,7 @@
         <v>122</v>
       </c>
       <c r="B122" s="1">
-        <v>132.1821638423702</v>
+        <v>131.9533189204091</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -2449,7 +2437,7 @@
         <v>123</v>
       </c>
       <c r="B123" s="1">
-        <v>132.2661442102612</v>
+        <v>132.0693044367617</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -2457,7 +2445,7 @@
         <v>124</v>
       </c>
       <c r="B124" s="1">
-        <v>132.3341388144897</v>
+        <v>132.1141687369641</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -2465,7 +2453,7 @@
         <v>125</v>
       </c>
       <c r="B125" s="1">
-        <v>132.4357854744187</v>
+        <v>132.1478322464304</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -2473,7 +2461,7 @@
         <v>126</v>
       </c>
       <c r="B126" s="1">
-        <v>132.4579367657776</v>
+        <v>132.1875734457967</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -2481,7 +2469,7 @@
         <v>127</v>
       </c>
       <c r="B127" s="1">
-        <v>132.4668776999789</v>
+        <v>132.2482394053371</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -2489,7 +2477,7 @@
         <v>128</v>
       </c>
       <c r="B128" s="1">
-        <v>132.5919369229312</v>
+        <v>132.3638191578668</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -2497,7 +2485,7 @@
         <v>129</v>
       </c>
       <c r="B129" s="1">
-        <v>132.6677354440077</v>
+        <v>132.3943461258388</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -2505,7 +2493,7 @@
         <v>130</v>
       </c>
       <c r="B130" s="1">
-        <v>132.7042162885117</v>
+        <v>132.3995692309329</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -2513,7 +2501,7 @@
         <v>131</v>
       </c>
       <c r="B131" s="1">
-        <v>132.8093797298177</v>
+        <v>132.5299989750339</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -2521,7 +2509,7 @@
         <v>132</v>
       </c>
       <c r="B132" s="1">
-        <v>132.8213546087935</v>
+        <v>132.6933457540734</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -2529,7 +2517,7 @@
         <v>133</v>
       </c>
       <c r="B133" s="1">
-        <v>132.8308174496671</v>
+        <v>132.7293191241272</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -2537,7 +2525,7 @@
         <v>134</v>
       </c>
       <c r="B134" s="1">
-        <v>132.8477524948536</v>
+        <v>132.7596147138641</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -2545,7 +2533,7 @@
         <v>135</v>
       </c>
       <c r="B135" s="1">
-        <v>132.8701798673598</v>
+        <v>132.8223821631663</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -2553,7 +2541,7 @@
         <v>136</v>
       </c>
       <c r="B136" s="1">
-        <v>132.9297330641278</v>
+        <v>132.822400601878</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -2561,7 +2549,7 @@
         <v>137</v>
       </c>
       <c r="B137" s="1">
-        <v>132.9491945719062</v>
+        <v>132.9612543123872</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -2569,7 +2557,7 @@
         <v>138</v>
       </c>
       <c r="B138" s="1">
-        <v>133.1615765956707</v>
+        <v>132.9899978290975</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -2577,7 +2565,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="1">
-        <v>133.414500055388</v>
+        <v>133.163332540921</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -2585,7 +2573,7 @@
         <v>140</v>
       </c>
       <c r="B140" s="1">
-        <v>133.4722920675918</v>
+        <v>133.2237848789503</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -2593,7 +2581,7 @@
         <v>141</v>
       </c>
       <c r="B141" s="1">
-        <v>133.4749801493575</v>
+        <v>133.2855576135238</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -2601,7 +2589,7 @@
         <v>142</v>
       </c>
       <c r="B142" s="1">
-        <v>133.7817021086419</v>
+        <v>133.4591006854866</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -2609,7 +2597,7 @@
         <v>143</v>
       </c>
       <c r="B143" s="1">
-        <v>133.8568270296104</v>
+        <v>133.5120954155497</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -2617,7 +2605,7 @@
         <v>144</v>
       </c>
       <c r="B144" s="1">
-        <v>133.9758668444756</v>
+        <v>133.6113758689058</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -2625,7 +2613,7 @@
         <v>145</v>
       </c>
       <c r="B145" s="1">
-        <v>133.9961530024761</v>
+        <v>133.6994029608328</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -2633,7 +2621,7 @@
         <v>146</v>
       </c>
       <c r="B146" s="1">
-        <v>134.0257928971722</v>
+        <v>133.800221406801</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -2641,7 +2629,7 @@
         <v>147</v>
       </c>
       <c r="B147" s="1">
-        <v>134.2294440603854</v>
+        <v>133.8574325173187</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -2649,7 +2637,7 @@
         <v>148</v>
       </c>
       <c r="B148" s="1">
-        <v>134.2322376025219</v>
+        <v>133.9338733333196</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -2657,7 +2645,7 @@
         <v>149</v>
       </c>
       <c r="B149" s="1">
-        <v>134.4647603954529</v>
+        <v>133.9879567595489</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -2665,7 +2653,7 @@
         <v>150</v>
       </c>
       <c r="B150" s="1">
-        <v>134.5504957247051</v>
+        <v>133.9999349081887</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -2673,7 +2661,7 @@
         <v>151</v>
       </c>
       <c r="B151" s="1">
-        <v>134.6781611475295</v>
+        <v>134.042877100622</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -2681,7 +2669,7 @@
         <v>152</v>
       </c>
       <c r="B152" s="1">
-        <v>134.6926311357979</v>
+        <v>134.2146554817993</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -2689,7 +2677,7 @@
         <v>153</v>
       </c>
       <c r="B153" s="1">
-        <v>134.7589092572078</v>
+        <v>134.3023320306388</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -2697,7 +2685,7 @@
         <v>154</v>
       </c>
       <c r="B154" s="1">
-        <v>134.7699533557918</v>
+        <v>134.3026602916408</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -2705,7 +2693,7 @@
         <v>155</v>
       </c>
       <c r="B155" s="1">
-        <v>134.8221144430859</v>
+        <v>134.3412516983596</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -2713,7 +2701,7 @@
         <v>156</v>
       </c>
       <c r="B156" s="1">
-        <v>135.3283685542108</v>
+        <v>134.3603228290581</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -2721,7 +2709,7 @@
         <v>157</v>
       </c>
       <c r="B157" s="1">
-        <v>135.464526030828</v>
+        <v>134.3797692794508</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -2729,7 +2717,7 @@
         <v>158</v>
       </c>
       <c r="B158" s="1">
-        <v>135.4950686890014</v>
+        <v>134.4691012825402</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -2737,7 +2725,7 @@
         <v>159</v>
       </c>
       <c r="B159" s="1">
-        <v>135.538668227946</v>
+        <v>134.6133223660205</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -2745,7 +2733,7 @@
         <v>160</v>
       </c>
       <c r="B160" s="1">
-        <v>135.6252202007354</v>
+        <v>134.6736940728904</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -2753,7 +2741,7 @@
         <v>161</v>
       </c>
       <c r="B161" s="1">
-        <v>135.7257441496197</v>
+        <v>134.7087395738062</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -2761,7 +2749,7 @@
         <v>162</v>
       </c>
       <c r="B162" s="1">
-        <v>135.7318313543984</v>
+        <v>134.8863006308823</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -2769,7 +2757,7 @@
         <v>163</v>
       </c>
       <c r="B163" s="1">
-        <v>135.8880801958747</v>
+        <v>134.9736723172544</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -2777,7 +2765,7 @@
         <v>164</v>
       </c>
       <c r="B164" s="1">
-        <v>135.9466714138315</v>
+        <v>135.0285641576313</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -2785,7 +2773,7 @@
         <v>165</v>
       </c>
       <c r="B165" s="1">
-        <v>135.9725468960019</v>
+        <v>135.0302789479341</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -2793,7 +2781,7 @@
         <v>166</v>
       </c>
       <c r="B166" s="1">
-        <v>135.9873616119455</v>
+        <v>135.1312624139452</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -2801,7 +2789,7 @@
         <v>167</v>
       </c>
       <c r="B167" s="1">
-        <v>136.1719380166885</v>
+        <v>135.1453652600125</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -2809,7 +2797,7 @@
         <v>168</v>
       </c>
       <c r="B168" s="1">
-        <v>136.3869199454992</v>
+        <v>135.1590743095559</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -2817,7 +2805,7 @@
         <v>169</v>
       </c>
       <c r="B169" s="1">
-        <v>136.4200880030203</v>
+        <v>135.1759247283216</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -2825,7 +2813,7 @@
         <v>170</v>
       </c>
       <c r="B170" s="1">
-        <v>136.434090002839</v>
+        <v>135.3376298408638</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -2833,7 +2821,7 @@
         <v>171</v>
       </c>
       <c r="B171" s="1">
-        <v>136.5959178159975</v>
+        <v>135.4375103024965</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -2841,7 +2829,7 @@
         <v>172</v>
       </c>
       <c r="B172" s="1">
-        <v>136.596307475671</v>
+        <v>135.4430132261552</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -2849,7 +2837,7 @@
         <v>173</v>
       </c>
       <c r="B173" s="1">
-        <v>136.6228468789908</v>
+        <v>135.6868103432446</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -2857,7 +2845,7 @@
         <v>174</v>
       </c>
       <c r="B174" s="1">
-        <v>136.7515713199409</v>
+        <v>135.7314668681568</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -2865,7 +2853,7 @@
         <v>175</v>
       </c>
       <c r="B175" s="1">
-        <v>136.8314398908152</v>
+        <v>135.8829151491685</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -2873,7 +2861,7 @@
         <v>176</v>
       </c>
       <c r="B176" s="1">
-        <v>136.8582346097993</v>
+        <v>135.9062751264027</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -2881,7 +2869,7 @@
         <v>177</v>
       </c>
       <c r="B177" s="1">
-        <v>136.8838598273822</v>
+        <v>135.9624801810163</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -2889,7 +2877,7 @@
         <v>178</v>
       </c>
       <c r="B178" s="1">
-        <v>136.885433412229</v>
+        <v>136.0895029543066</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -2897,7 +2885,7 @@
         <v>179</v>
       </c>
       <c r="B179" s="1">
-        <v>136.8856279875857</v>
+        <v>136.5181403990751</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -2905,7 +2893,7 @@
         <v>180</v>
       </c>
       <c r="B180" s="1">
-        <v>137.0488202883218</v>
+        <v>136.6101633440267</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -2913,7 +2901,7 @@
         <v>181</v>
       </c>
       <c r="B181" s="1">
-        <v>137.3209029552308</v>
+        <v>136.9468915059881</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -2921,7 +2909,7 @@
         <v>182</v>
       </c>
       <c r="B182" s="1">
-        <v>137.3630500203522</v>
+        <v>136.9735154571766</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -2929,7 +2917,7 @@
         <v>183</v>
       </c>
       <c r="B183" s="1">
-        <v>137.7453677797959</v>
+        <v>136.9737893920463</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -2937,7 +2925,7 @@
         <v>184</v>
       </c>
       <c r="B184" s="1">
-        <v>137.813333814353</v>
+        <v>136.9946614876573</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -2945,7 +2933,7 @@
         <v>185</v>
       </c>
       <c r="B185" s="1">
-        <v>137.9070412817209</v>
+        <v>137.0380616475496</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -2953,7 +2941,7 @@
         <v>186</v>
       </c>
       <c r="B186" s="1">
-        <v>138.0348139592548</v>
+        <v>137.1032442136004</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -2961,7 +2949,7 @@
         <v>187</v>
       </c>
       <c r="B187" s="1">
-        <v>138.0525312823246</v>
+        <v>137.1075904824159</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -2969,7 +2957,7 @@
         <v>188</v>
       </c>
       <c r="B188" s="1">
-        <v>138.1282983672957</v>
+        <v>137.3117425144483</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -2977,7 +2965,7 @@
         <v>189</v>
       </c>
       <c r="B189" s="1">
-        <v>138.2820215626973</v>
+        <v>137.4790226257069</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -2985,7 +2973,7 @@
         <v>190</v>
       </c>
       <c r="B190" s="1">
-        <v>138.6544467037946</v>
+        <v>137.7536903813453</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -2993,7 +2981,7 @@
         <v>191</v>
       </c>
       <c r="B191" s="1">
-        <v>138.9625394173734</v>
+        <v>137.7573571985707</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -3001,7 +2989,7 @@
         <v>192</v>
       </c>
       <c r="B192" s="1">
-        <v>138.9720525830414</v>
+        <v>137.7807761233682</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -3009,7 +2997,7 @@
         <v>193</v>
       </c>
       <c r="B193" s="1">
-        <v>138.9825892959376</v>
+        <v>137.8945695997145</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -3017,7 +3005,7 @@
         <v>194</v>
       </c>
       <c r="B194" s="1">
-        <v>139.0340946535466</v>
+        <v>138.083385194311</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -3025,7 +3013,7 @@
         <v>195</v>
       </c>
       <c r="B195" s="1">
-        <v>139.1510664715894</v>
+        <v>138.1215490413345</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -3033,7 +3021,7 @@
         <v>196</v>
       </c>
       <c r="B196" s="1">
-        <v>139.2506167142048</v>
+        <v>138.1565900570076</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -3041,7 +3029,7 @@
         <v>197</v>
       </c>
       <c r="B197" s="1">
-        <v>139.4171510210183</v>
+        <v>138.1663907436597</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -3049,7 +3037,7 @@
         <v>198</v>
       </c>
       <c r="B198" s="1">
-        <v>139.5480593879044</v>
+        <v>138.2195730214023</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -3057,7 +3045,7 @@
         <v>199</v>
       </c>
       <c r="B199" s="1">
-        <v>139.8058017366882</v>
+        <v>138.3431263427562</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -3065,7 +3053,7 @@
         <v>200</v>
       </c>
       <c r="B200" s="1">
-        <v>139.8634922713013</v>
+        <v>138.7508859031284</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -3073,7 +3061,7 @@
         <v>201</v>
       </c>
       <c r="B201" s="1">
-        <v>139.9249117324219</v>
+        <v>138.9567113712588</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -3081,7 +3069,7 @@
         <v>202</v>
       </c>
       <c r="B202" s="1">
-        <v>140.0888905157719</v>
+        <v>139.0322403485192</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -3089,7 +3077,7 @@
         <v>203</v>
       </c>
       <c r="B203" s="1">
-        <v>140.1534844473142</v>
+        <v>139.0776434132237</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -3097,7 +3085,7 @@
         <v>204</v>
       </c>
       <c r="B204" s="1">
-        <v>140.1690805629563</v>
+        <v>139.290703861554</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -3105,7 +3093,7 @@
         <v>205</v>
       </c>
       <c r="B205" s="1">
-        <v>140.3796241894688</v>
+        <v>139.4357928260872</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -3113,7 +3101,7 @@
         <v>206</v>
       </c>
       <c r="B206" s="1">
-        <v>140.6375885910446</v>
+        <v>139.5999832901755</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -3121,7 +3109,7 @@
         <v>207</v>
       </c>
       <c r="B207" s="1">
-        <v>140.8121580272143</v>
+        <v>139.6330652887825</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -3129,7 +3117,7 @@
         <v>208</v>
       </c>
       <c r="B208" s="1">
-        <v>140.9937023914265</v>
+        <v>140.1438872465253</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -3137,7 +3125,7 @@
         <v>209</v>
       </c>
       <c r="B209" s="1">
-        <v>141.0350031695498</v>
+        <v>140.1501991024404</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -3145,7 +3133,7 @@
         <v>210</v>
       </c>
       <c r="B210" s="1">
-        <v>141.1895073363439</v>
+        <v>140.2541046669029</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -3153,7 +3141,7 @@
         <v>211</v>
       </c>
       <c r="B211" s="1">
-        <v>141.2686675605021</v>
+        <v>140.2716330985683</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -3161,7 +3149,7 @@
         <v>212</v>
       </c>
       <c r="B212" s="1">
-        <v>141.5185848332696</v>
+        <v>140.4953095267452</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -3169,7 +3157,7 @@
         <v>213</v>
       </c>
       <c r="B213" s="1">
-        <v>141.5357284720218</v>
+        <v>140.5604610951807</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -3177,7 +3165,7 @@
         <v>214</v>
       </c>
       <c r="B214" s="1">
-        <v>141.5486644685861</v>
+        <v>140.5986876354326</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -3185,7 +3173,7 @@
         <v>215</v>
       </c>
       <c r="B215" s="1">
-        <v>141.5859178330701</v>
+        <v>140.7465741597917</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -3193,7 +3181,7 @@
         <v>216</v>
       </c>
       <c r="B216" s="1">
-        <v>141.8851819443104</v>
+        <v>140.8003600350384</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -3201,7 +3189,7 @@
         <v>217</v>
       </c>
       <c r="B217" s="1">
-        <v>142.1568172158429</v>
+        <v>140.8872345808872</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -3209,7 +3197,7 @@
         <v>218</v>
       </c>
       <c r="B218" s="1">
-        <v>142.4210412244415</v>
+        <v>141.3213771186406</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -3217,7 +3205,7 @@
         <v>219</v>
       </c>
       <c r="B219" s="1">
-        <v>142.7187957926884</v>
+        <v>141.730202347404</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -3225,7 +3213,7 @@
         <v>220</v>
       </c>
       <c r="B220" s="1">
-        <v>142.7663481001454</v>
+        <v>141.8058654494284</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -3233,7 +3221,7 @@
         <v>221</v>
       </c>
       <c r="B221" s="1">
-        <v>142.9072352932486</v>
+        <v>142.0584172504361</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -3241,7 +3229,7 @@
         <v>222</v>
       </c>
       <c r="B222" s="1">
-        <v>143.1888770987958</v>
+        <v>142.5731372918068</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -3249,7 +3237,7 @@
         <v>223</v>
       </c>
       <c r="B223" s="1">
-        <v>143.4939481657526</v>
+        <v>142.7017178494285</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -3257,7 +3245,7 @@
         <v>224</v>
       </c>
       <c r="B224" s="1">
-        <v>143.5260322361981</v>
+        <v>143.0379114820345</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -3265,7 +3253,7 @@
         <v>225</v>
       </c>
       <c r="B225" s="1">
-        <v>143.8229075481551</v>
+        <v>143.3166267477089</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -3273,7 +3261,7 @@
         <v>226</v>
       </c>
       <c r="B226" s="1">
-        <v>143.8858896361583</v>
+        <v>143.7545884666683</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -3281,7 +3269,7 @@
         <v>227</v>
       </c>
       <c r="B227" s="1">
-        <v>144.0529902828545</v>
+        <v>144.7559778973308</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -3289,7 +3277,7 @@
         <v>228</v>
       </c>
       <c r="B228" s="1">
-        <v>144.2056488209747</v>
+        <v>144.9324935814104</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -3297,7 +3285,7 @@
         <v>229</v>
       </c>
       <c r="B229" s="1">
-        <v>144.2430152601437</v>
+        <v>145.1686529070574</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -3305,7 +3293,7 @@
         <v>230</v>
       </c>
       <c r="B230" s="1">
-        <v>144.3385972360206</v>
+        <v>145.2429256731017</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -3313,7 +3301,7 @@
         <v>231</v>
       </c>
       <c r="B231" s="1">
-        <v>144.751293803373</v>
+        <v>145.2601429697899</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -3321,7 +3309,7 @@
         <v>232</v>
       </c>
       <c r="B232" s="1">
-        <v>144.8231704721786</v>
+        <v>145.4857623455498</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -3329,7 +3317,7 @@
         <v>233</v>
       </c>
       <c r="B233" s="1">
-        <v>145.2690585790599</v>
+        <v>145.5180681203462</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -3337,7 +3325,7 @@
         <v>234</v>
       </c>
       <c r="B234" s="1">
-        <v>145.6329031426705</v>
+        <v>145.6656964022839</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -3345,7 +3333,7 @@
         <v>235</v>
       </c>
       <c r="B235" s="1">
-        <v>145.9161857418718</v>
+        <v>145.7507952465374</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -3353,7 +3341,7 @@
         <v>236</v>
       </c>
       <c r="B236" s="1">
-        <v>146.0724268561676</v>
+        <v>145.8893630710109</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -3361,7 +3349,7 @@
         <v>237</v>
       </c>
       <c r="B237" s="1">
-        <v>146.1653343675191</v>
+        <v>146.0287711614007</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -3369,7 +3357,7 @@
         <v>238</v>
       </c>
       <c r="B238" s="1">
-        <v>146.4440968464655</v>
+        <v>146.1919403026352</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -3377,7 +3365,7 @@
         <v>239</v>
       </c>
       <c r="B239" s="1">
-        <v>146.5474483703262</v>
+        <v>146.1938776544916</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -3385,7 +3373,7 @@
         <v>240</v>
       </c>
       <c r="B240" s="1">
-        <v>146.7146325217438</v>
+        <v>146.2916738409989</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -3393,7 +3381,7 @@
         <v>241</v>
       </c>
       <c r="B241" s="1">
-        <v>147.1948865735826</v>
+        <v>146.3285057612963</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -3401,7 +3389,7 @@
         <v>242</v>
       </c>
       <c r="B242" s="1">
-        <v>147.597006394801</v>
+        <v>146.7172062037879</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -3409,7 +3397,7 @@
         <v>243</v>
       </c>
       <c r="B243" s="1">
-        <v>147.7331095033362</v>
+        <v>146.7505821627256</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -3417,7 +3405,7 @@
         <v>244</v>
       </c>
       <c r="B244" s="1">
-        <v>147.9284171317249</v>
+        <v>146.7839310428782</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -3425,7 +3413,7 @@
         <v>245</v>
       </c>
       <c r="B245" s="1">
-        <v>148.2407555528505</v>
+        <v>147.6927667342856</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -3433,7 +3421,7 @@
         <v>246</v>
       </c>
       <c r="B246" s="1">
-        <v>148.2980780329487</v>
+        <v>147.7943906181666</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -3441,7 +3429,7 @@
         <v>247</v>
       </c>
       <c r="B247" s="1">
-        <v>148.8564101774331</v>
+        <v>147.8635980774913</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -3449,7 +3437,7 @@
         <v>248</v>
       </c>
       <c r="B248" s="1">
-        <v>149.2301440582534</v>
+        <v>147.885724236739</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -3457,7 +3445,7 @@
         <v>249</v>
       </c>
       <c r="B249" s="1">
-        <v>149.465687885177</v>
+        <v>147.9420622676186</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -3465,7 +3453,7 @@
         <v>250</v>
       </c>
       <c r="B250" s="1">
-        <v>149.5571508825638</v>
+        <v>148.2475073536607</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -3473,7 +3461,7 @@
         <v>251</v>
       </c>
       <c r="B251" s="1">
-        <v>149.6162110203929</v>
+        <v>148.377176889903</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -3481,7 +3469,7 @@
         <v>252</v>
       </c>
       <c r="B252" s="1">
-        <v>150.0358578157643</v>
+        <v>148.7527534757949</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -3489,7 +3477,7 @@
         <v>253</v>
       </c>
       <c r="B253" s="1">
-        <v>150.2367368642802</v>
+        <v>149.0024598560869</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -3497,7 +3485,7 @@
         <v>254</v>
       </c>
       <c r="B254" s="1">
-        <v>150.3285260190029</v>
+        <v>149.2069951034504</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -3505,7 +3493,7 @@
         <v>255</v>
       </c>
       <c r="B255" s="1">
-        <v>150.5696263093544</v>
+        <v>149.5618962850521</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -3513,7 +3501,7 @@
         <v>256</v>
       </c>
       <c r="B256" s="1">
-        <v>150.6058172888888</v>
+        <v>150.1304132260817</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -3521,7 +3509,7 @@
         <v>257</v>
       </c>
       <c r="B257" s="1">
-        <v>150.7310739581264</v>
+        <v>150.204002379743</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -3529,7 +3517,7 @@
         <v>258</v>
       </c>
       <c r="B258" s="1">
-        <v>150.8525009957056</v>
+        <v>150.5548768691871</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -3537,7 +3525,7 @@
         <v>259</v>
       </c>
       <c r="B259" s="1">
-        <v>150.8830205569993</v>
+        <v>150.821088140924</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -3545,7 +3533,7 @@
         <v>260</v>
       </c>
       <c r="B260" s="1">
-        <v>151.0208724126259</v>
+        <v>150.8248057013783</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -3553,7 +3541,7 @@
         <v>261</v>
       </c>
       <c r="B261" s="1">
-        <v>151.0862881178963</v>
+        <v>151.0845127302103</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -3561,7 +3549,7 @@
         <v>262</v>
       </c>
       <c r="B262" s="1">
-        <v>151.1337517607917</v>
+        <v>151.1021722780313</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -3569,7 +3557,7 @@
         <v>263</v>
       </c>
       <c r="B263" s="1">
-        <v>151.5781281771919</v>
+        <v>151.3209409014399</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -3577,7 +3565,7 @@
         <v>264</v>
       </c>
       <c r="B264" s="1">
-        <v>151.6060430031736</v>
+        <v>151.3819325360774</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -3585,7 +3573,7 @@
         <v>265</v>
       </c>
       <c r="B265" s="1">
-        <v>151.6573369003935</v>
+        <v>151.473785887918</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -3593,7 +3581,7 @@
         <v>266</v>
       </c>
       <c r="B266" s="1">
-        <v>152.0271840825212</v>
+        <v>151.573490671684</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -3601,7 +3589,7 @@
         <v>267</v>
       </c>
       <c r="B267" s="1">
-        <v>152.4871659079732</v>
+        <v>151.906527349188</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -3609,7 +3597,7 @@
         <v>268</v>
       </c>
       <c r="B268" s="1">
-        <v>152.6096346907263</v>
+        <v>152.0154751570682</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -3617,7 +3605,7 @@
         <v>269</v>
       </c>
       <c r="B269" s="1">
-        <v>152.6096435022669</v>
+        <v>152.6972789666754</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -3625,7 +3613,7 @@
         <v>270</v>
       </c>
       <c r="B270" s="1">
-        <v>152.7450755096108</v>
+        <v>152.7642005210558</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -3633,7 +3621,7 @@
         <v>271</v>
       </c>
       <c r="B271" s="1">
-        <v>153.6656852388908</v>
+        <v>153.134458094205</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -3641,7 +3629,7 @@
         <v>272</v>
       </c>
       <c r="B272" s="1">
-        <v>153.9905579577738</v>
+        <v>153.1918861074822</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -3649,7 +3637,7 @@
         <v>273</v>
       </c>
       <c r="B273" s="1">
-        <v>154.0928205532058</v>
+        <v>155.2122086317486</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -3657,7 +3645,7 @@
         <v>274</v>
       </c>
       <c r="B274" s="1">
-        <v>154.9227533137995</v>
+        <v>155.5237113430424</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -3665,7 +3653,7 @@
         <v>275</v>
       </c>
       <c r="B275" s="1">
-        <v>154.9268505712554</v>
+        <v>155.6875435756648</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -3673,7 +3661,7 @@
         <v>276</v>
       </c>
       <c r="B276" s="1">
-        <v>155.390811396373</v>
+        <v>155.7283212865877</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -3681,7 +3669,7 @@
         <v>277</v>
       </c>
       <c r="B277" s="1">
-        <v>155.4102062062394</v>
+        <v>155.8192730042092</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -3689,7 +3677,7 @@
         <v>278</v>
       </c>
       <c r="B278" s="1">
-        <v>155.4554612036829</v>
+        <v>155.8595579670367</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -3697,7 +3685,7 @@
         <v>279</v>
       </c>
       <c r="B279" s="1">
-        <v>155.9099931669256</v>
+        <v>156.5048758027658</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -3705,7 +3693,7 @@
         <v>280</v>
       </c>
       <c r="B280" s="1">
-        <v>155.9731081513379</v>
+        <v>157.4020910390263</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -3713,7 +3701,7 @@
         <v>281</v>
       </c>
       <c r="B281" s="1">
-        <v>156.3053958897006</v>
+        <v>157.953558265999</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -3721,7 +3709,7 @@
         <v>282</v>
       </c>
       <c r="B282" s="1">
-        <v>157.2924467518341</v>
+        <v>159.0839930024723</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -3729,7 +3717,7 @@
         <v>283</v>
       </c>
       <c r="B283" s="1">
-        <v>157.4436249270173</v>
+        <v>159.7695828310387</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -3737,7 +3725,7 @@
         <v>284</v>
       </c>
       <c r="B284" s="1">
-        <v>157.4729349764546</v>
+        <v>159.8105488416895</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -3745,7 +3733,7 @@
         <v>285</v>
       </c>
       <c r="B285" s="1">
-        <v>158.8339247204097</v>
+        <v>160.1524907371216</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -3753,7 +3741,7 @@
         <v>286</v>
       </c>
       <c r="B286" s="1">
-        <v>159.0460194372707</v>
+        <v>160.395851150393</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -3761,7 +3749,7 @@
         <v>287</v>
       </c>
       <c r="B287" s="1">
-        <v>159.9517691395316</v>
+        <v>161.0166450704968</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -3769,7 +3757,7 @@
         <v>288</v>
       </c>
       <c r="B288" s="1">
-        <v>160.3784406642712</v>
+        <v>161.1319262980886</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -3777,7 +3765,7 @@
         <v>289</v>
       </c>
       <c r="B289" s="1">
-        <v>160.8449631147482</v>
+        <v>161.3134022009235</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -3785,7 +3773,7 @@
         <v>290</v>
       </c>
       <c r="B290" s="1">
-        <v>161.0354586674242</v>
+        <v>161.4690441064647</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -3793,7 +3781,7 @@
         <v>291</v>
       </c>
       <c r="B291" s="1">
-        <v>161.9483651575585</v>
+        <v>161.59057559473</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -3801,7 +3789,7 @@
         <v>292</v>
       </c>
       <c r="B292" s="1">
-        <v>161.9997712311538</v>
+        <v>161.9399478198272</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -3809,7 +3797,7 @@
         <v>293</v>
       </c>
       <c r="B293" s="1">
-        <v>162.7609203119676</v>
+        <v>161.9418759836315</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -3817,7 +3805,7 @@
         <v>294</v>
       </c>
       <c r="B294" s="1">
-        <v>163.5334114711798</v>
+        <v>162.1854380739672</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -3825,7 +3813,7 @@
         <v>295</v>
       </c>
       <c r="B295" s="1">
-        <v>164.6965712489906</v>
+        <v>162.3282889397495</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -3833,7 +3821,7 @@
         <v>296</v>
       </c>
       <c r="B296" s="1">
-        <v>164.7722108957645</v>
+        <v>163.1569109840231</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -3841,7 +3829,7 @@
         <v>297</v>
       </c>
       <c r="B297" s="1">
-        <v>165.1976072777943</v>
+        <v>164.0312965110377</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -3849,7 +3837,7 @@
         <v>298</v>
       </c>
       <c r="B298" s="1">
-        <v>165.8408494809232</v>
+        <v>165.2668821978276</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -3857,7 +3845,7 @@
         <v>299</v>
       </c>
       <c r="B299" s="1">
-        <v>166.479777541394</v>
+        <v>165.6409274188778</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -3865,7 +3853,7 @@
         <v>300</v>
       </c>
       <c r="B300" s="1">
-        <v>166.6021824501797</v>
+        <v>165.8062056831798</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -3873,7 +3861,7 @@
         <v>301</v>
       </c>
       <c r="B301" s="1">
-        <v>167.1912282783538</v>
+        <v>166.9855904439393</v>
       </c>
     </row>
     <row r="302" spans="1:2">
@@ -3881,7 +3869,7 @@
         <v>302</v>
       </c>
       <c r="B302" s="1">
-        <v>167.5586637834012</v>
+        <v>167.6469494602538</v>
       </c>
     </row>
     <row r="303" spans="1:2">
@@ -3889,7 +3877,7 @@
         <v>303</v>
       </c>
       <c r="B303" s="1">
-        <v>167.6301381213031</v>
+        <v>168.5830618040611</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -3897,7 +3885,7 @@
         <v>304</v>
       </c>
       <c r="B304" s="1">
-        <v>169.5139099417947</v>
+        <v>168.8473280582695</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -3905,7 +3893,7 @@
         <v>305</v>
       </c>
       <c r="B305" s="1">
-        <v>170.0442445275069</v>
+        <v>169.569958645074</v>
       </c>
     </row>
     <row r="306" spans="1:2">
@@ -3913,7 +3901,7 @@
         <v>306</v>
       </c>
       <c r="B306" s="1">
-        <v>170.1018560654744</v>
+        <v>169.7751111731096</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -3921,7 +3909,7 @@
         <v>307</v>
       </c>
       <c r="B307" s="1">
-        <v>170.6719885575409</v>
+        <v>171.2303477982725</v>
       </c>
     </row>
     <row r="308" spans="1:2">
@@ -3929,7 +3917,7 @@
         <v>308</v>
       </c>
       <c r="B308" s="1">
-        <v>171.4649384613641</v>
+        <v>171.3610885443715</v>
       </c>
     </row>
     <row r="309" spans="1:2">
@@ -3937,7 +3925,7 @@
         <v>309</v>
       </c>
       <c r="B309" s="1">
-        <v>171.5032420851435</v>
+        <v>171.3834076715913</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -3945,7 +3933,7 @@
         <v>310</v>
       </c>
       <c r="B310" s="1">
-        <v>171.5903752973107</v>
+        <v>171.5069524555658</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -3953,7 +3941,7 @@
         <v>311</v>
       </c>
       <c r="B311" s="1">
-        <v>171.6050524420866</v>
+        <v>172.1930507445375</v>
       </c>
     </row>
     <row r="312" spans="1:2">
@@ -3961,7 +3949,7 @@
         <v>312</v>
       </c>
       <c r="B312" s="1">
-        <v>172.559088590271</v>
+        <v>173.4849246897927</v>
       </c>
     </row>
     <row r="313" spans="1:2">
@@ -3969,7 +3957,7 @@
         <v>313</v>
       </c>
       <c r="B313" s="1">
-        <v>173.7016879582047</v>
+        <v>173.6843377166255</v>
       </c>
     </row>
     <row r="314" spans="1:2">
@@ -3977,7 +3965,7 @@
         <v>314</v>
       </c>
       <c r="B314" s="1">
-        <v>174.4148937797347</v>
+        <v>176.106665002642</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -3985,7 +3973,7 @@
         <v>315</v>
       </c>
       <c r="B315" s="1">
-        <v>174.9091188014804</v>
+        <v>176.2191038326404</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -3993,7 +3981,7 @@
         <v>316</v>
       </c>
       <c r="B316" s="1">
-        <v>175.1944072066</v>
+        <v>176.3421800122788</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -4001,7 +3989,7 @@
         <v>317</v>
       </c>
       <c r="B317" s="1">
-        <v>176.9755199510864</v>
+        <v>176.3934583053485</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -4009,7 +3997,7 @@
         <v>318</v>
       </c>
       <c r="B318" s="1">
-        <v>177.248396103968</v>
+        <v>176.5697582215314</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -4017,7 +4005,7 @@
         <v>319</v>
       </c>
       <c r="B319" s="1">
-        <v>179.0386991967003</v>
+        <v>179.0540639253095</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -4025,7 +4013,7 @@
         <v>320</v>
       </c>
       <c r="B320" s="1">
-        <v>179.0411295801784</v>
+        <v>179.0828002320318</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -4033,7 +4021,7 @@
         <v>321</v>
       </c>
       <c r="B321" s="1">
-        <v>179.7520338011223</v>
+        <v>179.3955449688171</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -4041,7 +4029,7 @@
         <v>322</v>
       </c>
       <c r="B322" s="1">
-        <v>179.798481442359</v>
+        <v>179.9528708860766</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -4049,7 +4037,7 @@
         <v>323</v>
       </c>
       <c r="B323" s="1">
-        <v>181.2637849780702</v>
+        <v>180.7885437032916</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -4057,7 +4045,7 @@
         <v>324</v>
       </c>
       <c r="B324" s="1">
-        <v>183.7192630535317</v>
+        <v>181.769049592862</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -4065,7 +4053,7 @@
         <v>325</v>
       </c>
       <c r="B325" s="1">
-        <v>185.008419431494</v>
+        <v>181.8520538734474</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -4073,7 +4061,7 @@
         <v>326</v>
       </c>
       <c r="B326" s="1">
-        <v>185.7454276117793</v>
+        <v>182.7092600818787</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -4081,7 +4069,7 @@
         <v>327</v>
       </c>
       <c r="B327" s="1">
-        <v>188.2343941346077</v>
+        <v>183.0309939841841</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -4089,7 +4077,7 @@
         <v>328</v>
       </c>
       <c r="B328" s="1">
-        <v>189.5076284625823</v>
+        <v>183.7362501843911</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -4097,7 +4085,7 @@
         <v>329</v>
       </c>
       <c r="B329" s="1">
-        <v>190.7845282479299</v>
+        <v>184.6115878067162</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -4105,7 +4093,7 @@
         <v>330</v>
       </c>
       <c r="B330" s="1">
-        <v>192.442073150157</v>
+        <v>185.797028901293</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -4113,7 +4101,7 @@
         <v>331</v>
       </c>
       <c r="B331" s="1">
-        <v>193.7201056076209</v>
+        <v>187.2881717988011</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -4121,7 +4109,7 @@
         <v>332</v>
       </c>
       <c r="B332" s="1">
-        <v>193.9891333176583</v>
+        <v>187.2934803997703</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -4129,7 +4117,7 @@
         <v>333</v>
       </c>
       <c r="B333" s="1">
-        <v>195.1806682288841</v>
+        <v>188.685004672909</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -4137,7 +4125,7 @@
         <v>334</v>
       </c>
       <c r="B334" s="1">
-        <v>196.7381423200804</v>
+        <v>190.2960194510896</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -4145,7 +4133,7 @@
         <v>335</v>
       </c>
       <c r="B335" s="1">
-        <v>197.1910409568794</v>
+        <v>197.0451901302592</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -4153,7 +4141,7 @@
         <v>336</v>
       </c>
       <c r="B336" s="1">
-        <v>198.6422184341107</v>
+        <v>199.9816014755285</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -4161,7 +4149,7 @@
         <v>337</v>
       </c>
       <c r="B337" s="1">
-        <v>201.2990990610614</v>
+        <v>203.1962413713083</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -4169,7 +4157,7 @@
         <v>338</v>
       </c>
       <c r="B338" s="1">
-        <v>201.7373700215835</v>
+        <v>203.2694189808431</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -4177,7 +4165,7 @@
         <v>339</v>
       </c>
       <c r="B339" s="1">
-        <v>202.1753323608125</v>
+        <v>210.7611920516861</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -4185,7 +4173,7 @@
         <v>340</v>
       </c>
       <c r="B340" s="1">
-        <v>207.1946966502958</v>
+        <v>212.6533800649105</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -4193,7 +4181,7 @@
         <v>341</v>
       </c>
       <c r="B341" s="1">
-        <v>208.0828064052492</v>
+        <v>216.2559771279986</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -4201,7 +4189,7 @@
         <v>342</v>
       </c>
       <c r="B342" s="1">
-        <v>209.4366295254397</v>
+        <v>218.9711439338221</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -4209,7 +4197,7 @@
         <v>343</v>
       </c>
       <c r="B343" s="1">
-        <v>214.6132208388158</v>
+        <v>226.29352222788</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -4217,7 +4205,7 @@
         <v>344</v>
       </c>
       <c r="B344" s="1">
-        <v>217.7593115742441</v>
+        <v>226.718580420727</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -4225,7 +4213,7 @@
         <v>345</v>
       </c>
       <c r="B345" s="1">
-        <v>218.9711439338221</v>
+        <v>228.1172065735038</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -4233,7 +4221,7 @@
         <v>346</v>
       </c>
       <c r="B346" s="1">
-        <v>220.0650723877261</v>
+        <v>234.7552941379554</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -4241,7 +4229,7 @@
         <v>347</v>
       </c>
       <c r="B347" s="1">
-        <v>227.3078588762888</v>
+        <v>238.3157264530728</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -4249,7 +4237,7 @@
         <v>348</v>
       </c>
       <c r="B348" s="1">
-        <v>234.0700258714982</v>
+        <v>245.1883556724339</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -4257,7 +4245,7 @@
         <v>349</v>
       </c>
       <c r="B349" s="1">
-        <v>243.9997269095433</v>
+        <v>254.365041267413</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -4265,7 +4253,7 @@
         <v>350</v>
       </c>
       <c r="B350" s="1">
-        <v>265.4982901615595</v>
+        <v>263.5699503676062</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -4273,7 +4261,7 @@
         <v>351</v>
       </c>
       <c r="B351" s="1">
-        <v>272.1951199024072</v>
+        <v>263.7833350078593</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -4281,7 +4269,7 @@
         <v>352</v>
       </c>
       <c r="B352" s="1">
-        <v>276.9920398613946</v>
+        <v>286.4049839345308</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -4289,7 +4277,7 @@
         <v>353</v>
       </c>
       <c r="B353" s="1">
-        <v>277.8598794227735</v>
+        <v>289.9623432136356</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -4297,7 +4285,7 @@
         <v>354</v>
       </c>
       <c r="B354" s="1">
-        <v>281.4157485390699</v>
+        <v>338.2022991448598</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -4305,7 +4293,7 @@
         <v>355</v>
       </c>
       <c r="B355" s="1">
-        <v>293.3782449933111</v>
+        <v>370.5432729139933</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -4313,7 +4301,7 @@
         <v>356</v>
       </c>
       <c r="B356" s="1">
-        <v>297.2762736374641</v>
+        <v>386.8433205312426</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -4321,7 +4309,7 @@
         <v>357</v>
       </c>
       <c r="B357" s="1">
-        <v>306.7112959885945</v>
+        <v>395.9826511659476</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -4329,7 +4317,7 @@
         <v>358</v>
       </c>
       <c r="B358" s="1">
-        <v>326.9823344636471</v>
+        <v>414.7981944984094</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -4337,7 +4325,7 @@
         <v>359</v>
       </c>
       <c r="B359" s="1">
-        <v>334.7996909548909</v>
+        <v>499.3971298722361</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -4345,7 +4333,7 @@
         <v>360</v>
       </c>
       <c r="B360" s="1">
-        <v>357.7370107594063</v>
+        <v>554.9279657808423</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -4353,7 +4341,7 @@
         <v>361</v>
       </c>
       <c r="B361" s="1">
-        <v>397.6417205005864</v>
+        <v>586.0828333398433</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -4361,39 +4349,7 @@
         <v>362</v>
       </c>
       <c r="B362" s="1">
-        <v>428.7292142613572</v>
-      </c>
-    </row>
-    <row r="363" spans="1:2">
-      <c r="A363" t="s">
-        <v>363</v>
-      </c>
-      <c r="B363" s="1">
-        <v>497.2214425982315</v>
-      </c>
-    </row>
-    <row r="364" spans="1:2">
-      <c r="A364" t="s">
-        <v>364</v>
-      </c>
-      <c r="B364" s="1">
-        <v>566.6280911242668</v>
-      </c>
-    </row>
-    <row r="365" spans="1:2">
-      <c r="A365" t="s">
-        <v>365</v>
-      </c>
-      <c r="B365" s="1">
-        <v>591.0866968817579</v>
-      </c>
-    </row>
-    <row r="366" spans="1:2">
-      <c r="A366" t="s">
-        <v>366</v>
-      </c>
-      <c r="B366" s="1">
-        <v>815.7666724015032</v>
+        <v>827.7228735954943</v>
       </c>
     </row>
   </sheetData>

--- a/Screener/data/rs_rating_top_30.xlsx
+++ b/Screener/data/rs_rating_top_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="366">
   <si>
     <t>Symbol</t>
   </si>
@@ -22,1057 +22,1066 @@
     <t>RS Rating</t>
   </si>
   <si>
+    <t>NEOG</t>
+  </si>
+  <si>
+    <t>CVGI</t>
+  </si>
+  <si>
+    <t>RVMD</t>
+  </si>
+  <si>
+    <t>TNET</t>
+  </si>
+  <si>
+    <t>ARHS</t>
+  </si>
+  <si>
+    <t>HURN</t>
+  </si>
+  <si>
+    <t>GMS</t>
+  </si>
+  <si>
     <t>HSKA</t>
   </si>
   <si>
-    <t>GGAAU</t>
-  </si>
-  <si>
-    <t>MOMO</t>
+    <t>THC</t>
+  </si>
+  <si>
+    <t>GOCO</t>
   </si>
   <si>
     <t>ALSN</t>
   </si>
   <si>
+    <t>CCAP</t>
+  </si>
+  <si>
+    <t>DUOL</t>
+  </si>
+  <si>
+    <t>TWIN</t>
+  </si>
+  <si>
+    <t>MSA</t>
+  </si>
+  <si>
+    <t>CARR</t>
+  </si>
+  <si>
+    <t>MYRG</t>
+  </si>
+  <si>
+    <t>ALGN</t>
+  </si>
+  <si>
+    <t>PAG</t>
+  </si>
+  <si>
+    <t>RRC</t>
+  </si>
+  <si>
+    <t>TGH</t>
+  </si>
+  <si>
+    <t>PH</t>
+  </si>
+  <si>
+    <t>PWP</t>
+  </si>
+  <si>
+    <t>PRDO</t>
+  </si>
+  <si>
+    <t>RAMP</t>
+  </si>
+  <si>
+    <t>VST</t>
+  </si>
+  <si>
+    <t>AVGO</t>
+  </si>
+  <si>
+    <t>ZWS</t>
+  </si>
+  <si>
+    <t>HLNE</t>
+  </si>
+  <si>
+    <t>GSHD</t>
+  </si>
+  <si>
+    <t>DBRG</t>
+  </si>
+  <si>
+    <t>FDX</t>
+  </si>
+  <si>
+    <t>SGH</t>
+  </si>
+  <si>
+    <t>OII</t>
+  </si>
+  <si>
+    <t>BATRA</t>
+  </si>
+  <si>
+    <t>CRH</t>
+  </si>
+  <si>
+    <t>TMHC</t>
+  </si>
+  <si>
+    <t>DASH</t>
+  </si>
+  <si>
+    <t>PRI</t>
+  </si>
+  <si>
+    <t>MEDP</t>
+  </si>
+  <si>
+    <t>KALA</t>
+  </si>
+  <si>
+    <t>DVA</t>
+  </si>
+  <si>
+    <t>APPF</t>
+  </si>
+  <si>
+    <t>CLH</t>
+  </si>
+  <si>
+    <t>MTG</t>
+  </si>
+  <si>
+    <t>MPX</t>
+  </si>
+  <si>
+    <t>PLUS</t>
+  </si>
+  <si>
+    <t>APG</t>
+  </si>
+  <si>
+    <t>KD</t>
+  </si>
+  <si>
+    <t>ARCB</t>
+  </si>
+  <si>
+    <t>URI</t>
+  </si>
+  <si>
+    <t>COOP</t>
+  </si>
+  <si>
+    <t>VNO</t>
+  </si>
+  <si>
+    <t>RIVN</t>
+  </si>
+  <si>
+    <t>ESCA</t>
+  </si>
+  <si>
+    <t>UBER</t>
+  </si>
+  <si>
+    <t>MNSO</t>
+  </si>
+  <si>
+    <t>NMIH</t>
+  </si>
+  <si>
+    <t>PKOH</t>
+  </si>
+  <si>
+    <t>KRYS</t>
+  </si>
+  <si>
+    <t>CFLT</t>
+  </si>
+  <si>
+    <t>LEGN</t>
+  </si>
+  <si>
+    <t>XPRO</t>
+  </si>
+  <si>
+    <t>GTLS</t>
+  </si>
+  <si>
+    <t>IIVI</t>
+  </si>
+  <si>
+    <t>BMEA</t>
+  </si>
+  <si>
+    <t>CWCO</t>
+  </si>
+  <si>
+    <t>ARGX</t>
+  </si>
+  <si>
+    <t>ZNTL</t>
+  </si>
+  <si>
+    <t>RYTM</t>
+  </si>
+  <si>
+    <t>CCJ</t>
+  </si>
+  <si>
+    <t>ADBE</t>
+  </si>
+  <si>
+    <t>NEU</t>
+  </si>
+  <si>
+    <t>NEWR</t>
+  </si>
+  <si>
+    <t>GCBC</t>
+  </si>
+  <si>
+    <t>BKI</t>
+  </si>
+  <si>
+    <t>RDY</t>
+  </si>
+  <si>
+    <t>UFPT</t>
+  </si>
+  <si>
+    <t>ABR</t>
+  </si>
+  <si>
+    <t>LAUR</t>
+  </si>
+  <si>
+    <t>MDC</t>
+  </si>
+  <si>
+    <t>PBF</t>
+  </si>
+  <si>
+    <t>ACMR</t>
+  </si>
+  <si>
+    <t>PNR</t>
+  </si>
+  <si>
+    <t>HCCI</t>
+  </si>
+  <si>
+    <t>ETN</t>
+  </si>
+  <si>
+    <t>BMI</t>
+  </si>
+  <si>
+    <t>TPH</t>
+  </si>
+  <si>
+    <t>HUBS</t>
+  </si>
+  <si>
+    <t>SHAK</t>
+  </si>
+  <si>
+    <t>BVH</t>
+  </si>
+  <si>
+    <t>BOOT</t>
+  </si>
+  <si>
+    <t>AMWD</t>
+  </si>
+  <si>
+    <t>AMZN</t>
+  </si>
+  <si>
+    <t>TYRA</t>
+  </si>
+  <si>
+    <t>SPNT</t>
+  </si>
+  <si>
+    <t>CRMT</t>
+  </si>
+  <si>
+    <t>MPC</t>
+  </si>
+  <si>
+    <t>RKT</t>
+  </si>
+  <si>
+    <t>FMS</t>
+  </si>
+  <si>
+    <t>ACVA</t>
+  </si>
+  <si>
+    <t>BECN</t>
+  </si>
+  <si>
+    <t>JELD</t>
+  </si>
+  <si>
     <t>NOG</t>
   </si>
   <si>
-    <t>ASTE</t>
-  </si>
-  <si>
-    <t>GLRE</t>
-  </si>
-  <si>
-    <t>TEX</t>
-  </si>
-  <si>
-    <t>TYRA</t>
-  </si>
-  <si>
-    <t>ON</t>
-  </si>
-  <si>
-    <t>XPRO</t>
-  </si>
-  <si>
-    <t>COOP</t>
-  </si>
-  <si>
-    <t>SHC</t>
-  </si>
-  <si>
-    <t>DECK</t>
-  </si>
-  <si>
-    <t>BVH</t>
-  </si>
-  <si>
-    <t>BATRA</t>
-  </si>
-  <si>
-    <t>URI</t>
-  </si>
-  <si>
-    <t>TBBK</t>
-  </si>
-  <si>
-    <t>VMW</t>
-  </si>
-  <si>
-    <t>URBN</t>
-  </si>
-  <si>
-    <t>BLBD</t>
-  </si>
-  <si>
-    <t>CRS</t>
-  </si>
-  <si>
-    <t>RCM</t>
-  </si>
-  <si>
-    <t>PRI</t>
-  </si>
-  <si>
-    <t>MSA</t>
-  </si>
-  <si>
-    <t>GAMB</t>
-  </si>
-  <si>
-    <t>BMI</t>
+    <t>AEL</t>
+  </si>
+  <si>
+    <t>IMVT</t>
+  </si>
+  <si>
+    <t>ODFL</t>
+  </si>
+  <si>
+    <t>SM</t>
+  </si>
+  <si>
+    <t>DELL</t>
+  </si>
+  <si>
+    <t>MTH</t>
+  </si>
+  <si>
+    <t>OPAD</t>
+  </si>
+  <si>
+    <t>NUVL</t>
+  </si>
+  <si>
+    <t>SCPL</t>
+  </si>
+  <si>
+    <t>WST</t>
+  </si>
+  <si>
+    <t>SMHI</t>
+  </si>
+  <si>
+    <t>HAYW</t>
+  </si>
+  <si>
+    <t>ZG</t>
+  </si>
+  <si>
+    <t>LAD</t>
+  </si>
+  <si>
+    <t>CHX</t>
+  </si>
+  <si>
+    <t>KBH</t>
+  </si>
+  <si>
+    <t>BUR</t>
+  </si>
+  <si>
+    <t>RCMT</t>
+  </si>
+  <si>
+    <t>PRO</t>
+  </si>
+  <si>
+    <t>GE</t>
+  </si>
+  <si>
+    <t>FIX</t>
+  </si>
+  <si>
+    <t>ERO</t>
+  </si>
+  <si>
+    <t>Z</t>
+  </si>
+  <si>
+    <t>JHX</t>
+  </si>
+  <si>
+    <t>IOT</t>
+  </si>
+  <si>
+    <t>TOL</t>
+  </si>
+  <si>
+    <t>ASMIY</t>
+  </si>
+  <si>
+    <t>ANDE</t>
+  </si>
+  <si>
+    <t>NYCB</t>
+  </si>
+  <si>
+    <t>USLM</t>
+  </si>
+  <si>
+    <t>VRTV</t>
   </si>
   <si>
     <t>CEIX</t>
   </si>
   <si>
-    <t>ARGX</t>
-  </si>
-  <si>
-    <t>DHI</t>
-  </si>
-  <si>
-    <t>MRVL</t>
-  </si>
-  <si>
-    <t>TNET</t>
-  </si>
-  <si>
-    <t>ODFL</t>
-  </si>
-  <si>
-    <t>HURN</t>
+    <t>PRIM</t>
+  </si>
+  <si>
+    <t>SATS</t>
+  </si>
+  <si>
+    <t>BKNG</t>
+  </si>
+  <si>
+    <t>WLDN</t>
+  </si>
+  <si>
+    <t>AZUL</t>
+  </si>
+  <si>
+    <t>CVRX</t>
+  </si>
+  <si>
+    <t>CNX</t>
+  </si>
+  <si>
+    <t>COKE</t>
+  </si>
+  <si>
+    <t>SG</t>
+  </si>
+  <si>
+    <t>PAM</t>
+  </si>
+  <si>
+    <t>CORT</t>
+  </si>
+  <si>
+    <t>SWDAF</t>
+  </si>
+  <si>
+    <t>MLP</t>
+  </si>
+  <si>
+    <t>NEX</t>
+  </si>
+  <si>
+    <t>NRP</t>
+  </si>
+  <si>
+    <t>IMTX</t>
+  </si>
+  <si>
+    <t>OTTR</t>
+  </si>
+  <si>
+    <t>IDYA</t>
+  </si>
+  <si>
+    <t>AGM</t>
+  </si>
+  <si>
+    <t>LAW</t>
+  </si>
+  <si>
+    <t>YPF</t>
+  </si>
+  <si>
+    <t>CSWI</t>
+  </si>
+  <si>
+    <t>GIII</t>
+  </si>
+  <si>
+    <t>KTOS</t>
+  </si>
+  <si>
+    <t>YELP</t>
+  </si>
+  <si>
+    <t>SXI</t>
+  </si>
+  <si>
+    <t>NIO</t>
+  </si>
+  <si>
+    <t>ACLS</t>
+  </si>
+  <si>
+    <t>CNM</t>
+  </si>
+  <si>
+    <t>GHL</t>
+  </si>
+  <si>
+    <t>LOB</t>
+  </si>
+  <si>
+    <t>VEL</t>
+  </si>
+  <si>
+    <t>AMNB</t>
+  </si>
+  <si>
+    <t>ROCK</t>
+  </si>
+  <si>
+    <t>AEHR</t>
+  </si>
+  <si>
+    <t>ZGN</t>
+  </si>
+  <si>
+    <t>ENVX</t>
+  </si>
+  <si>
+    <t>EB</t>
+  </si>
+  <si>
+    <t>SPNS</t>
+  </si>
+  <si>
+    <t>ANF</t>
+  </si>
+  <si>
+    <t>ONON</t>
+  </si>
+  <si>
+    <t>BLX</t>
+  </si>
+  <si>
+    <t>MMYT</t>
+  </si>
+  <si>
+    <t>LLY</t>
+  </si>
+  <si>
+    <t>LII</t>
+  </si>
+  <si>
+    <t>ARCO</t>
+  </si>
+  <si>
+    <t>OC</t>
+  </si>
+  <si>
+    <t>KRUS</t>
+  </si>
+  <si>
+    <t>FCAP</t>
+  </si>
+  <si>
+    <t>CRC</t>
+  </si>
+  <si>
+    <t>VECO</t>
+  </si>
+  <si>
+    <t>GKOS</t>
+  </si>
+  <si>
+    <t>WMS</t>
+  </si>
+  <si>
+    <t>MORF</t>
+  </si>
+  <si>
+    <t>CLBR</t>
+  </si>
+  <si>
+    <t>GRVY</t>
+  </si>
+  <si>
+    <t>RH</t>
+  </si>
+  <si>
+    <t>AZEK</t>
+  </si>
+  <si>
+    <t>CAAP</t>
+  </si>
+  <si>
+    <t>EME</t>
+  </si>
+  <si>
+    <t>CYD</t>
+  </si>
+  <si>
+    <t>ACAD</t>
+  </si>
+  <si>
+    <t>GHM</t>
+  </si>
+  <si>
+    <t>AROC</t>
+  </si>
+  <si>
+    <t>MATX</t>
+  </si>
+  <si>
+    <t>FTI</t>
+  </si>
+  <si>
+    <t>SOVO</t>
+  </si>
+  <si>
+    <t>UPWK</t>
+  </si>
+  <si>
+    <t>AI</t>
+  </si>
+  <si>
+    <t>PLPC</t>
+  </si>
+  <si>
+    <t>SPOK</t>
+  </si>
+  <si>
+    <t>NE</t>
+  </si>
+  <si>
+    <t>PHM</t>
+  </si>
+  <si>
+    <t>COCO</t>
+  </si>
+  <si>
+    <t>SSD</t>
+  </si>
+  <si>
+    <t>STVN</t>
+  </si>
+  <si>
+    <t>PHAT</t>
+  </si>
+  <si>
+    <t>RCL</t>
+  </si>
+  <si>
+    <t>TREX</t>
+  </si>
+  <si>
+    <t>GBX</t>
+  </si>
+  <si>
+    <t>CTG</t>
+  </si>
+  <si>
+    <t>AVDL</t>
+  </si>
+  <si>
+    <t>KALV</t>
+  </si>
+  <si>
+    <t>IBP</t>
+  </si>
+  <si>
+    <t>FSTR</t>
+  </si>
+  <si>
+    <t>SDGR</t>
+  </si>
+  <si>
+    <t>LTRPB</t>
+  </si>
+  <si>
+    <t>VIST</t>
+  </si>
+  <si>
+    <t>CCL</t>
+  </si>
+  <si>
+    <t>GPOR</t>
+  </si>
+  <si>
+    <t>ISEE</t>
+  </si>
+  <si>
+    <t>EDU</t>
+  </si>
+  <si>
+    <t>PCTTU</t>
   </si>
   <si>
     <t>ANIP</t>
   </si>
   <si>
-    <t>NEU</t>
-  </si>
-  <si>
-    <t>EXP</t>
-  </si>
-  <si>
-    <t>SUM</t>
-  </si>
-  <si>
-    <t>AMWD</t>
-  </si>
-  <si>
-    <t>BRZE</t>
-  </si>
-  <si>
-    <t>FLNC</t>
-  </si>
-  <si>
-    <t>LUNG</t>
-  </si>
-  <si>
-    <t>MMYT</t>
-  </si>
-  <si>
-    <t>KNSA</t>
-  </si>
-  <si>
-    <t>DXPE</t>
-  </si>
-  <si>
-    <t>FTDR</t>
-  </si>
-  <si>
-    <t>GTLS</t>
-  </si>
-  <si>
-    <t>DVA</t>
-  </si>
-  <si>
-    <t>ARCB</t>
-  </si>
-  <si>
-    <t>FSTR</t>
-  </si>
-  <si>
-    <t>AEL</t>
-  </si>
-  <si>
-    <t>FDX</t>
-  </si>
-  <si>
-    <t>EXAS</t>
-  </si>
-  <si>
-    <t>ACMR</t>
-  </si>
-  <si>
-    <t>LEU</t>
-  </si>
-  <si>
-    <t>IIVI</t>
-  </si>
-  <si>
-    <t>BKI</t>
-  </si>
-  <si>
-    <t>TMHC</t>
-  </si>
-  <si>
-    <t>COHR</t>
-  </si>
-  <si>
-    <t>GIC</t>
-  </si>
-  <si>
-    <t>SCX</t>
-  </si>
-  <si>
-    <t>RKT</t>
-  </si>
-  <si>
-    <t>NEX</t>
-  </si>
-  <si>
-    <t>PRIM</t>
-  </si>
-  <si>
-    <t>CNX</t>
+    <t>SRDX</t>
+  </si>
+  <si>
+    <t>DMRC</t>
+  </si>
+  <si>
+    <t>ACOR</t>
+  </si>
+  <si>
+    <t>IMRX</t>
+  </si>
+  <si>
+    <t>CUK</t>
+  </si>
+  <si>
+    <t>BMA</t>
+  </si>
+  <si>
+    <t>BSAQ</t>
+  </si>
+  <si>
+    <t>FRSH</t>
+  </si>
+  <si>
+    <t>FTAI</t>
+  </si>
+  <si>
+    <t>COIN</t>
+  </si>
+  <si>
+    <t>HOV</t>
+  </si>
+  <si>
+    <t>RILY</t>
+  </si>
+  <si>
+    <t>AMPH</t>
+  </si>
+  <si>
+    <t>MDWT</t>
+  </si>
+  <si>
+    <t>GGAL</t>
+  </si>
+  <si>
+    <t>MSTR</t>
+  </si>
+  <si>
+    <t>GRBK</t>
+  </si>
+  <si>
+    <t>PRG</t>
+  </si>
+  <si>
+    <t>OSTK</t>
+  </si>
+  <si>
+    <t>CVLG</t>
+  </si>
+  <si>
+    <t>ROIV</t>
+  </si>
+  <si>
+    <t>CUBI</t>
+  </si>
+  <si>
+    <t>ABCM</t>
+  </si>
+  <si>
+    <t>KDNY</t>
+  </si>
+  <si>
+    <t>TISI</t>
+  </si>
+  <si>
+    <t>DICE</t>
+  </si>
+  <si>
+    <t>FSLY</t>
+  </si>
+  <si>
+    <t>JOE</t>
+  </si>
+  <si>
+    <t>UPST</t>
+  </si>
+  <si>
+    <t>EDN</t>
+  </si>
+  <si>
+    <t>ETHE</t>
+  </si>
+  <si>
+    <t>NGMS</t>
+  </si>
+  <si>
+    <t>BLD</t>
+  </si>
+  <si>
+    <t>EXPI</t>
+  </si>
+  <si>
+    <t>FCNCA</t>
+  </si>
+  <si>
+    <t>BLU</t>
+  </si>
+  <si>
+    <t>VKTX</t>
+  </si>
+  <si>
+    <t>BCC</t>
+  </si>
+  <si>
+    <t>MDB</t>
+  </si>
+  <si>
+    <t>KRT</t>
+  </si>
+  <si>
+    <t>NOA</t>
+  </si>
+  <si>
+    <t>NATR</t>
+  </si>
+  <si>
+    <t>ACU</t>
+  </si>
+  <si>
+    <t>TSAT</t>
+  </si>
+  <si>
+    <t>PARR</t>
+  </si>
+  <si>
+    <t>DKNG</t>
+  </si>
+  <si>
+    <t>XP</t>
+  </si>
+  <si>
+    <t>PETQ</t>
+  </si>
+  <si>
+    <t>WRLD</t>
+  </si>
+  <si>
+    <t>SBOW</t>
+  </si>
+  <si>
+    <t>EXTR</t>
+  </si>
+  <si>
+    <t>SAIA</t>
+  </si>
+  <si>
+    <t>PAY</t>
+  </si>
+  <si>
+    <t>TDW</t>
+  </si>
+  <si>
+    <t>CABA</t>
+  </si>
+  <si>
+    <t>USAP</t>
+  </si>
+  <si>
+    <t>PCT</t>
   </si>
   <si>
     <t>CELH</t>
   </si>
   <si>
-    <t>GE</t>
-  </si>
-  <si>
-    <t>PLUS</t>
-  </si>
-  <si>
-    <t>ETN</t>
-  </si>
-  <si>
-    <t>IMVT</t>
-  </si>
-  <si>
-    <t>ZWS</t>
-  </si>
-  <si>
-    <t>APG</t>
-  </si>
-  <si>
-    <t>GMS</t>
-  </si>
-  <si>
-    <t>NVT</t>
-  </si>
-  <si>
-    <t>CORT</t>
-  </si>
-  <si>
-    <t>VNO</t>
-  </si>
-  <si>
-    <t>ARHS</t>
-  </si>
-  <si>
-    <t>RRGB</t>
-  </si>
-  <si>
-    <t>RDNT</t>
-  </si>
-  <si>
-    <t>NEWR</t>
-  </si>
-  <si>
-    <t>PH</t>
-  </si>
-  <si>
-    <t>AGM</t>
-  </si>
-  <si>
-    <t>ZG</t>
-  </si>
-  <si>
-    <t>JELD</t>
-  </si>
-  <si>
-    <t>YPF</t>
-  </si>
-  <si>
-    <t>JBL</t>
-  </si>
-  <si>
-    <t>CARR</t>
-  </si>
-  <si>
-    <t>AMZN</t>
-  </si>
-  <si>
-    <t>INBK</t>
-  </si>
-  <si>
-    <t>LRCX</t>
-  </si>
-  <si>
-    <t>NVO</t>
-  </si>
-  <si>
-    <t>CFLT</t>
-  </si>
-  <si>
-    <t>GHRS</t>
-  </si>
-  <si>
-    <t>GPOR</t>
-  </si>
-  <si>
-    <t>RDFN</t>
-  </si>
-  <si>
-    <t>TPH</t>
-  </si>
-  <si>
-    <t>Z</t>
-  </si>
-  <si>
-    <t>GHL</t>
-  </si>
-  <si>
-    <t>AZUL</t>
-  </si>
-  <si>
-    <t>FMS</t>
-  </si>
-  <si>
-    <t>DELL</t>
-  </si>
-  <si>
-    <t>CRH</t>
-  </si>
-  <si>
-    <t>HAYW</t>
-  </si>
-  <si>
-    <t>DVAX</t>
-  </si>
-  <si>
-    <t>ANDE</t>
-  </si>
-  <si>
-    <t>FTI</t>
-  </si>
-  <si>
-    <t>PNR</t>
-  </si>
-  <si>
-    <t>BKNG</t>
-  </si>
-  <si>
-    <t>SPNT</t>
-  </si>
-  <si>
-    <t>SHAK</t>
-  </si>
-  <si>
-    <t>STCN</t>
-  </si>
-  <si>
-    <t>HCCI</t>
-  </si>
-  <si>
-    <t>LPG</t>
-  </si>
-  <si>
-    <t>ONTO</t>
-  </si>
-  <si>
-    <t>MNSO</t>
-  </si>
-  <si>
-    <t>FIX</t>
-  </si>
-  <si>
-    <t>MDC</t>
-  </si>
-  <si>
-    <t>ALGN</t>
-  </si>
-  <si>
-    <t>BOOT</t>
-  </si>
-  <si>
-    <t>TOL</t>
-  </si>
-  <si>
-    <t>PKOH</t>
-  </si>
-  <si>
-    <t>SMHI</t>
-  </si>
-  <si>
-    <t>TSQ</t>
-  </si>
-  <si>
-    <t>ACOR</t>
-  </si>
-  <si>
-    <t>AMNB</t>
-  </si>
-  <si>
-    <t>PVBC</t>
-  </si>
-  <si>
-    <t>NE</t>
-  </si>
-  <si>
-    <t>BECN</t>
-  </si>
-  <si>
-    <t>SXI</t>
-  </si>
-  <si>
-    <t>SWDAF</t>
-  </si>
-  <si>
-    <t>SPNS</t>
-  </si>
-  <si>
-    <t>CRC</t>
-  </si>
-  <si>
-    <t>GLBE</t>
-  </si>
-  <si>
-    <t>NYCB</t>
-  </si>
-  <si>
-    <t>SGH</t>
-  </si>
-  <si>
-    <t>ASUR</t>
-  </si>
-  <si>
-    <t>WST</t>
-  </si>
-  <si>
-    <t>PLAB</t>
-  </si>
-  <si>
-    <t>MTH</t>
-  </si>
-  <si>
-    <t>YELP</t>
-  </si>
-  <si>
-    <t>ERO</t>
-  </si>
-  <si>
-    <t>NATR</t>
-  </si>
-  <si>
-    <t>OTTR</t>
-  </si>
-  <si>
-    <t>ZGN</t>
-  </si>
-  <si>
-    <t>JHX</t>
-  </si>
-  <si>
-    <t>DASH</t>
-  </si>
-  <si>
-    <t>ARCO</t>
-  </si>
-  <si>
-    <t>CSWI</t>
-  </si>
-  <si>
-    <t>APPF</t>
-  </si>
-  <si>
-    <t>USLM</t>
-  </si>
-  <si>
-    <t>HELE</t>
-  </si>
-  <si>
-    <t>LTRPB</t>
-  </si>
-  <si>
-    <t>CRMT</t>
-  </si>
-  <si>
-    <t>ADBE</t>
-  </si>
-  <si>
-    <t>SATS</t>
-  </si>
-  <si>
-    <t>GSHD</t>
-  </si>
-  <si>
-    <t>ACVA</t>
-  </si>
-  <si>
-    <t>IMTX</t>
-  </si>
-  <si>
-    <t>DIT</t>
-  </si>
-  <si>
-    <t>VRTV</t>
-  </si>
-  <si>
-    <t>WLDN</t>
-  </si>
-  <si>
-    <t>CNM</t>
-  </si>
-  <si>
-    <t>AVDL</t>
-  </si>
-  <si>
-    <t>UBER</t>
-  </si>
-  <si>
-    <t>NUVL</t>
-  </si>
-  <si>
-    <t>LOB</t>
-  </si>
-  <si>
-    <t>ACAD</t>
-  </si>
-  <si>
-    <t>LLY</t>
-  </si>
-  <si>
-    <t>CYD</t>
-  </si>
-  <si>
-    <t>AVGO</t>
-  </si>
-  <si>
-    <t>UPWK</t>
-  </si>
-  <si>
-    <t>ASMIY</t>
-  </si>
-  <si>
-    <t>ATRO</t>
-  </si>
-  <si>
-    <t>ROCK</t>
-  </si>
-  <si>
-    <t>UFPT</t>
-  </si>
-  <si>
-    <t>KBH</t>
-  </si>
-  <si>
-    <t>AROC</t>
-  </si>
-  <si>
-    <t>RCMT</t>
-  </si>
-  <si>
-    <t>PRO</t>
-  </si>
-  <si>
-    <t>VECO</t>
-  </si>
-  <si>
-    <t>VIST</t>
-  </si>
-  <si>
-    <t>EME</t>
-  </si>
-  <si>
-    <t>SPOK</t>
-  </si>
-  <si>
-    <t>ANF</t>
-  </si>
-  <si>
-    <t>BMA</t>
-  </si>
-  <si>
-    <t>ROKU</t>
-  </si>
-  <si>
-    <t>PLPC</t>
-  </si>
-  <si>
-    <t>WMS</t>
-  </si>
-  <si>
-    <t>FRSH</t>
-  </si>
-  <si>
-    <t>BLX</t>
-  </si>
-  <si>
-    <t>KRT</t>
-  </si>
-  <si>
-    <t>CLBR</t>
-  </si>
-  <si>
-    <t>VSTM</t>
-  </si>
-  <si>
-    <t>KRUS</t>
-  </si>
-  <si>
-    <t>ACU</t>
-  </si>
-  <si>
-    <t>GKOS</t>
-  </si>
-  <si>
-    <t>LII</t>
-  </si>
-  <si>
-    <t>RXRX</t>
-  </si>
-  <si>
-    <t>EDU</t>
-  </si>
-  <si>
-    <t>ISEE</t>
-  </si>
-  <si>
-    <t>KTOS</t>
-  </si>
-  <si>
-    <t>SSD</t>
-  </si>
-  <si>
-    <t>VICR</t>
-  </si>
-  <si>
-    <t>PARR</t>
-  </si>
-  <si>
-    <t>GRVY</t>
-  </si>
-  <si>
-    <t>NRP</t>
-  </si>
-  <si>
-    <t>KALV</t>
-  </si>
-  <si>
-    <t>VEL</t>
-  </si>
-  <si>
-    <t>PETQ</t>
-  </si>
-  <si>
-    <t>OC</t>
-  </si>
-  <si>
-    <t>EB</t>
-  </si>
-  <si>
-    <t>TREX</t>
-  </si>
-  <si>
-    <t>PCTTU</t>
-  </si>
-  <si>
-    <t>TTD</t>
-  </si>
-  <si>
-    <t>SOVO</t>
-  </si>
-  <si>
-    <t>MATX</t>
-  </si>
-  <si>
-    <t>MLP</t>
-  </si>
-  <si>
-    <t>CAAP</t>
-  </si>
-  <si>
-    <t>PCT</t>
-  </si>
-  <si>
-    <t>ONON</t>
-  </si>
-  <si>
-    <t>CVRX</t>
-  </si>
-  <si>
-    <t>IMRX</t>
-  </si>
-  <si>
-    <t>GGAL</t>
-  </si>
-  <si>
-    <t>VKTX</t>
-  </si>
-  <si>
-    <t>SDGR</t>
-  </si>
-  <si>
-    <t>ACLS</t>
-  </si>
-  <si>
-    <t>SG</t>
-  </si>
-  <si>
-    <t>PHAT</t>
-  </si>
-  <si>
-    <t>JOE</t>
-  </si>
-  <si>
-    <t>PHM</t>
-  </si>
-  <si>
-    <t>MDWT</t>
-  </si>
-  <si>
-    <t>IBP</t>
-  </si>
-  <si>
-    <t>SRDX</t>
-  </si>
-  <si>
-    <t>AEHR</t>
-  </si>
-  <si>
-    <t>SBOW</t>
-  </si>
-  <si>
-    <t>GHM</t>
-  </si>
-  <si>
-    <t>FCAP</t>
-  </si>
-  <si>
-    <t>EBIX</t>
-  </si>
-  <si>
-    <t>ETHE</t>
-  </si>
-  <si>
-    <t>RIVN</t>
-  </si>
-  <si>
-    <t>OSTK</t>
-  </si>
-  <si>
-    <t>PAY</t>
-  </si>
-  <si>
-    <t>RH</t>
-  </si>
-  <si>
-    <t>FTAI</t>
-  </si>
-  <si>
-    <t>ABCM</t>
-  </si>
-  <si>
-    <t>GBX</t>
-  </si>
-  <si>
-    <t>RCL</t>
-  </si>
-  <si>
-    <t>ROIV</t>
-  </si>
-  <si>
-    <t>MORF</t>
-  </si>
-  <si>
-    <t>CABA</t>
-  </si>
-  <si>
-    <t>MSTR</t>
-  </si>
-  <si>
-    <t>CVLG</t>
-  </si>
-  <si>
-    <t>NIO</t>
-  </si>
-  <si>
-    <t>IOT</t>
-  </si>
-  <si>
-    <t>COCO</t>
-  </si>
-  <si>
-    <t>ENVX</t>
-  </si>
-  <si>
-    <t>NOA</t>
-  </si>
-  <si>
-    <t>EDN</t>
-  </si>
-  <si>
-    <t>GRBK</t>
+    <t>LI</t>
+  </si>
+  <si>
+    <t>ODC</t>
+  </si>
+  <si>
+    <t>QTRX</t>
+  </si>
+  <si>
+    <t>BWMX</t>
+  </si>
+  <si>
+    <t>PLTR</t>
+  </si>
+  <si>
+    <t>NWLI</t>
+  </si>
+  <si>
+    <t>XPEV</t>
   </si>
   <si>
     <t>WFRD</t>
   </si>
   <si>
-    <t>FCNCA</t>
-  </si>
-  <si>
-    <t>RILY</t>
-  </si>
-  <si>
-    <t>DMRC</t>
-  </si>
-  <si>
-    <t>EXTR</t>
-  </si>
-  <si>
-    <t>TDW</t>
-  </si>
-  <si>
-    <t>BLD</t>
-  </si>
-  <si>
-    <t>DICE</t>
-  </si>
-  <si>
-    <t>PRG</t>
-  </si>
-  <si>
-    <t>BLU</t>
-  </si>
-  <si>
-    <t>LZ</t>
-  </si>
-  <si>
-    <t>SAIA</t>
+    <t>ALPN</t>
+  </si>
+  <si>
+    <t>RXST</t>
+  </si>
+  <si>
+    <t>RELY</t>
+  </si>
+  <si>
+    <t>NVDA</t>
+  </si>
+  <si>
+    <t>MHO</t>
+  </si>
+  <si>
+    <t>VECT</t>
+  </si>
+  <si>
+    <t>IESC</t>
+  </si>
+  <si>
+    <t>GBTC</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>CAMT</t>
+  </si>
+  <si>
+    <t>RCEL</t>
   </si>
   <si>
     <t>CMT</t>
   </si>
   <si>
-    <t>RELY</t>
-  </si>
-  <si>
-    <t>BCC</t>
-  </si>
-  <si>
-    <t>NGMS</t>
-  </si>
-  <si>
-    <t>IESC</t>
-  </si>
-  <si>
-    <t>MDB</t>
-  </si>
-  <si>
-    <t>CUBI</t>
-  </si>
-  <si>
-    <t>NWLI</t>
-  </si>
-  <si>
-    <t>BWMX</t>
-  </si>
-  <si>
-    <t>GBTC</t>
-  </si>
-  <si>
-    <t>FSLY</t>
-  </si>
-  <si>
-    <t>CCL</t>
-  </si>
-  <si>
-    <t>XP</t>
-  </si>
-  <si>
-    <t>COIN</t>
-  </si>
-  <si>
-    <t>USAP</t>
-  </si>
-  <si>
-    <t>STVN</t>
-  </si>
-  <si>
-    <t>QTRX</t>
-  </si>
-  <si>
-    <t>VECT</t>
-  </si>
-  <si>
-    <t>LI</t>
-  </si>
-  <si>
-    <t>MHO</t>
-  </si>
-  <si>
-    <t>CUK</t>
-  </si>
-  <si>
-    <t>AI</t>
-  </si>
-  <si>
-    <t>HOV</t>
-  </si>
-  <si>
-    <t>WRLD</t>
+    <t>BLDR</t>
+  </si>
+  <si>
+    <t>CLS</t>
+  </si>
+  <si>
+    <t>CIR</t>
+  </si>
+  <si>
+    <t>CPS</t>
+  </si>
+  <si>
+    <t>TRHC</t>
+  </si>
+  <si>
+    <t>ELF</t>
+  </si>
+  <si>
+    <t>CMPR</t>
+  </si>
+  <si>
+    <t>OPRA</t>
+  </si>
+  <si>
+    <t>LSEA</t>
   </si>
   <si>
     <t>FRD</t>
   </si>
   <si>
-    <t>CIR</t>
-  </si>
-  <si>
-    <t>RCEL</t>
-  </si>
-  <si>
-    <t>DKNG</t>
-  </si>
-  <si>
-    <t>ALPN</t>
+    <t>PESI</t>
+  </si>
+  <si>
+    <t>SKYW</t>
+  </si>
+  <si>
+    <t>FOR</t>
+  </si>
+  <si>
+    <t>TDS</t>
+  </si>
+  <si>
+    <t>XPO</t>
+  </si>
+  <si>
+    <t>MOD</t>
+  </si>
+  <si>
+    <t>WEAV</t>
+  </si>
+  <si>
+    <t>CBAY</t>
+  </si>
+  <si>
+    <t>MARA</t>
+  </si>
+  <si>
+    <t>POWL</t>
+  </si>
+  <si>
+    <t>BZH</t>
+  </si>
+  <si>
+    <t>MEOA</t>
+  </si>
+  <si>
+    <t>EH</t>
+  </si>
+  <si>
+    <t>ARLO</t>
   </si>
   <si>
     <t>LMB</t>
   </si>
   <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>EXPI</t>
-  </si>
-  <si>
-    <t>BLDR</t>
-  </si>
-  <si>
-    <t>CLS</t>
-  </si>
-  <si>
-    <t>KDNY</t>
-  </si>
-  <si>
-    <t>RXST</t>
-  </si>
-  <si>
-    <t>CAMT</t>
-  </si>
-  <si>
-    <t>ODC</t>
-  </si>
-  <si>
-    <t>PESI</t>
-  </si>
-  <si>
-    <t>CMPR</t>
-  </si>
-  <si>
-    <t>CPS</t>
-  </si>
-  <si>
-    <t>PLTR</t>
-  </si>
-  <si>
-    <t>LSEA</t>
-  </si>
-  <si>
-    <t>NVDA</t>
-  </si>
-  <si>
-    <t>ELF</t>
-  </si>
-  <si>
-    <t>AMPH</t>
+    <t>RIOT</t>
+  </si>
+  <si>
+    <t>USM</t>
+  </si>
+  <si>
+    <t>DFH</t>
+  </si>
+  <si>
+    <t>STRL</t>
+  </si>
+  <si>
+    <t>SMCI</t>
+  </si>
+  <si>
+    <t>WW</t>
+  </si>
+  <si>
+    <t>VRT</t>
+  </si>
+  <si>
+    <t>CDLX</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>MEOAU</t>
+  </si>
+  <si>
+    <t>RXDX</t>
+  </si>
+  <si>
+    <t>IMGN</t>
   </si>
   <si>
     <t>INOD</t>
   </si>
   <si>
-    <t>SKYW</t>
-  </si>
-  <si>
-    <t>TDS</t>
-  </si>
-  <si>
-    <t>XPO</t>
+    <t>URGN</t>
+  </si>
+  <si>
+    <t>IONQ</t>
+  </si>
+  <si>
+    <t>OLMA</t>
   </si>
   <si>
     <t>APP</t>
   </si>
   <si>
-    <t>WEAV</t>
-  </si>
-  <si>
-    <t>FOR</t>
-  </si>
-  <si>
-    <t>MOD</t>
-  </si>
-  <si>
-    <t>W</t>
-  </si>
-  <si>
-    <t>CBAY</t>
-  </si>
-  <si>
-    <t>XPEV</t>
-  </si>
-  <si>
-    <t>TRHC</t>
-  </si>
-  <si>
-    <t>OPRA</t>
-  </si>
-  <si>
-    <t>STRL</t>
-  </si>
-  <si>
-    <t>BZH</t>
-  </si>
-  <si>
-    <t>MEOA</t>
-  </si>
-  <si>
-    <t>MARA</t>
-  </si>
-  <si>
-    <t>USM</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>ARLO</t>
-  </si>
-  <si>
-    <t>RXDX</t>
-  </si>
-  <si>
-    <t>URGN</t>
-  </si>
-  <si>
-    <t>DFH</t>
-  </si>
-  <si>
-    <t>MEOAU</t>
-  </si>
-  <si>
-    <t>RIOT</t>
-  </si>
-  <si>
-    <t>IMGN</t>
-  </si>
-  <si>
-    <t>VRT</t>
-  </si>
-  <si>
-    <t>IONQ</t>
-  </si>
-  <si>
-    <t>UPST</t>
-  </si>
-  <si>
-    <t>EH</t>
-  </si>
-  <si>
     <t>BBIO</t>
   </si>
   <si>
-    <t>CDLX</t>
-  </si>
-  <si>
     <t>RETA</t>
   </si>
   <si>
-    <t>SMCI</t>
+    <t>EVLO</t>
   </si>
   <si>
     <t>EYPT</t>
@@ -1081,16 +1090,16 @@
     <t>PHVS</t>
   </si>
   <si>
+    <t>CVNA</t>
+  </si>
+  <si>
+    <t>AURC</t>
+  </si>
+  <si>
     <t>AURCU</t>
   </si>
   <si>
     <t>SGTX</t>
-  </si>
-  <si>
-    <t>CVNA</t>
-  </si>
-  <si>
-    <t>AURC</t>
   </si>
   <si>
     <t>AAOI</t>
@@ -1453,7 +1462,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B362"/>
+  <dimension ref="A1:B365"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1469,7 +1478,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1">
-        <v>124.6092621817537</v>
+        <v>124.0829861665204</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1477,7 +1486,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1">
-        <v>124.6364682239148</v>
+        <v>124.1595479390792</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1485,7 +1494,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1">
-        <v>124.6757575560775</v>
+        <v>124.1975748164088</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1493,7 +1502,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="1">
-        <v>124.6837062415044</v>
+        <v>124.2317786739443</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1501,7 +1510,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="1">
-        <v>124.7390818158684</v>
+        <v>124.2702087461477</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1509,7 +1518,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="1">
-        <v>124.7630255049716</v>
+        <v>124.3521926897257</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1517,7 +1526,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="1">
-        <v>124.7880886181516</v>
+        <v>124.3665591213771</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1525,7 +1534,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="1">
-        <v>124.8280693271704</v>
+        <v>124.3845210398288</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1533,7 +1542,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="1">
-        <v>124.8369686859967</v>
+        <v>124.4381709994948</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1541,7 +1550,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="1">
-        <v>124.9432997325041</v>
+        <v>124.4563099539098</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1549,7 +1558,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="1">
-        <v>125.0558091173492</v>
+        <v>124.4859210501041</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1557,7 +1566,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="1">
-        <v>125.1606336601367</v>
+        <v>124.5617563603743</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1565,7 +1574,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="1">
-        <v>125.1816736423053</v>
+        <v>124.5630026585182</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1573,7 +1582,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="1">
-        <v>125.2537440814427</v>
+        <v>124.6336258018261</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1581,7 +1590,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="1">
-        <v>125.2755177788623</v>
+        <v>124.712692959347</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1589,7 +1598,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="1">
-        <v>125.2933726441961</v>
+        <v>124.7971295256411</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1597,7 +1606,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="1">
-        <v>125.3140746608057</v>
+        <v>124.8499225367773</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1605,7 +1614,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="1">
-        <v>125.3766515840249</v>
+        <v>124.8551353731227</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1613,7 +1622,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="1">
-        <v>125.4289676630226</v>
+        <v>124.9229016502065</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1621,7 +1630,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="1">
-        <v>125.4506226960056</v>
+        <v>125.0067893048456</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1629,7 +1638,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="1">
-        <v>125.4637703989916</v>
+        <v>125.1844118283891</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1637,7 +1646,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="1">
-        <v>125.4720128070037</v>
+        <v>125.2044676154203</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1645,7 +1654,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="1">
-        <v>125.4886856413621</v>
+        <v>125.2856369812978</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1653,7 +1662,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="1">
-        <v>125.5570666399557</v>
+        <v>125.350762371963</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1661,7 +1670,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="1">
-        <v>125.5690747059299</v>
+        <v>125.4535727314165</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1669,7 +1678,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="1">
-        <v>125.8346589681354</v>
+        <v>125.4540464617075</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1677,7 +1686,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="1">
-        <v>125.9943609756212</v>
+        <v>125.4783265747443</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1685,7 +1694,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="1">
-        <v>126.004104572607</v>
+        <v>125.4845877264405</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1693,7 +1702,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="1">
-        <v>126.0959969014464</v>
+        <v>125.4953791483459</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1701,7 +1710,7 @@
         <v>31</v>
       </c>
       <c r="B31" s="1">
-        <v>126.1462210850073</v>
+        <v>125.5590823510238</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1709,7 +1718,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="1">
-        <v>126.1906243480294</v>
+        <v>125.5941846125836</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1717,7 +1726,7 @@
         <v>33</v>
       </c>
       <c r="B33" s="1">
-        <v>126.2051213363564</v>
+        <v>125.6324980204941</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1725,7 +1734,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="1">
-        <v>126.2409187568156</v>
+        <v>125.642110911772</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1733,7 +1742,7 @@
         <v>35</v>
       </c>
       <c r="B35" s="1">
-        <v>126.2844173570107</v>
+        <v>125.6827913230994</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1741,7 +1750,7 @@
         <v>36</v>
       </c>
       <c r="B36" s="1">
-        <v>126.3427780197734</v>
+        <v>125.6907325020123</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1749,7 +1758,7 @@
         <v>37</v>
       </c>
       <c r="B37" s="1">
-        <v>126.4459007686974</v>
+        <v>125.7326378419124</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1757,7 +1766,7 @@
         <v>38</v>
       </c>
       <c r="B38" s="1">
-        <v>126.4652698265689</v>
+        <v>125.7526541370251</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1765,7 +1774,7 @@
         <v>39</v>
       </c>
       <c r="B39" s="1">
-        <v>126.5707330014932</v>
+        <v>125.7810106712664</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1773,7 +1782,7 @@
         <v>40</v>
       </c>
       <c r="B40" s="1">
-        <v>126.6075083527369</v>
+        <v>125.874354654279</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1781,7 +1790,7 @@
         <v>41</v>
       </c>
       <c r="B41" s="1">
-        <v>126.6221368823283</v>
+        <v>125.9646078006813</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -1789,7 +1798,7 @@
         <v>42</v>
       </c>
       <c r="B42" s="1">
-        <v>126.6527518917484</v>
+        <v>125.9938044978556</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -1797,7 +1806,7 @@
         <v>43</v>
       </c>
       <c r="B43" s="1">
-        <v>126.6666884551212</v>
+        <v>126.1581889062703</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1805,7 +1814,7 @@
         <v>44</v>
       </c>
       <c r="B44" s="1">
-        <v>126.677098284089</v>
+        <v>126.1709718332527</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1813,7 +1822,7 @@
         <v>45</v>
       </c>
       <c r="B45" s="1">
-        <v>126.7452086618515</v>
+        <v>126.2005892570191</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1821,7 +1830,7 @@
         <v>46</v>
       </c>
       <c r="B46" s="1">
-        <v>126.7927421787385</v>
+        <v>126.2370220154832</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -1829,7 +1838,7 @@
         <v>47</v>
       </c>
       <c r="B47" s="1">
-        <v>126.8117681832398</v>
+        <v>126.2479254993667</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -1837,7 +1846,7 @@
         <v>48</v>
       </c>
       <c r="B48" s="1">
-        <v>126.870568083185</v>
+        <v>126.2641889120621</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1845,7 +1854,7 @@
         <v>49</v>
       </c>
       <c r="B49" s="1">
-        <v>126.9644429324393</v>
+        <v>126.301647300819</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1853,7 +1862,7 @@
         <v>50</v>
       </c>
       <c r="B50" s="1">
-        <v>126.9739429973167</v>
+        <v>126.370572789885</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1861,7 +1870,7 @@
         <v>51</v>
       </c>
       <c r="B51" s="1">
-        <v>127.0106911348959</v>
+        <v>126.3763339426322</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1869,7 +1878,7 @@
         <v>52</v>
       </c>
       <c r="B52" s="1">
-        <v>127.0379439859438</v>
+        <v>126.5103662728782</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1877,7 +1886,7 @@
         <v>53</v>
       </c>
       <c r="B53" s="1">
-        <v>127.0991331832926</v>
+        <v>126.6382257651476</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1885,7 +1894,7 @@
         <v>54</v>
       </c>
       <c r="B54" s="1">
-        <v>127.1542777805376</v>
+        <v>126.6739160020548</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1893,7 +1902,7 @@
         <v>55</v>
       </c>
       <c r="B55" s="1">
-        <v>127.2283553979041</v>
+        <v>126.7017200156502</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1901,7 +1910,7 @@
         <v>56</v>
       </c>
       <c r="B56" s="1">
-        <v>127.4333737509368</v>
+        <v>126.7688996131203</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1909,7 +1918,7 @@
         <v>57</v>
       </c>
       <c r="B57" s="1">
-        <v>127.521919185548</v>
+        <v>126.7775816524545</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1917,7 +1926,7 @@
         <v>58</v>
       </c>
       <c r="B58" s="1">
-        <v>127.5897680550657</v>
+        <v>126.8491022670315</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1925,7 +1934,7 @@
         <v>59</v>
       </c>
       <c r="B59" s="1">
-        <v>127.7669202303683</v>
+        <v>126.8589835319579</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1933,7 +1942,7 @@
         <v>60</v>
       </c>
       <c r="B60" s="1">
-        <v>127.8685407546635</v>
+        <v>126.9190353818207</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1941,7 +1950,7 @@
         <v>61</v>
       </c>
       <c r="B61" s="1">
-        <v>127.881380145986</v>
+        <v>126.9494324233464</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1949,7 +1958,7 @@
         <v>62</v>
       </c>
       <c r="B62" s="1">
-        <v>127.8829858410097</v>
+        <v>126.950306998431</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1957,7 +1966,7 @@
         <v>63</v>
       </c>
       <c r="B63" s="1">
-        <v>128.142515597018</v>
+        <v>127.0549911254336</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1965,7 +1974,7 @@
         <v>64</v>
       </c>
       <c r="B64" s="1">
-        <v>128.2308683267096</v>
+        <v>127.0890561996871</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1973,7 +1982,7 @@
         <v>65</v>
       </c>
       <c r="B65" s="1">
-        <v>128.2699376687699</v>
+        <v>127.158166366983</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -1981,7 +1990,7 @@
         <v>66</v>
       </c>
       <c r="B66" s="1">
-        <v>128.2765101072426</v>
+        <v>127.2030946782174</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -1989,7 +1998,7 @@
         <v>67</v>
       </c>
       <c r="B67" s="1">
-        <v>128.288971536425</v>
+        <v>127.2470203176702</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -1997,7 +2006,7 @@
         <v>68</v>
       </c>
       <c r="B68" s="1">
-        <v>128.3388398390167</v>
+        <v>127.2798780358174</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -2005,7 +2014,7 @@
         <v>69</v>
       </c>
       <c r="B69" s="1">
-        <v>128.3729778949937</v>
+        <v>127.292972785944</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -2013,7 +2022,7 @@
         <v>70</v>
       </c>
       <c r="B70" s="1">
-        <v>128.3989458739862</v>
+        <v>127.3453866072637</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -2021,7 +2030,7 @@
         <v>71</v>
       </c>
       <c r="B71" s="1">
-        <v>128.4335270990193</v>
+        <v>127.3532730818984</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -2029,7 +2038,7 @@
         <v>72</v>
       </c>
       <c r="B72" s="1">
-        <v>128.451362135509</v>
+        <v>127.3725443809172</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2037,7 +2046,7 @@
         <v>73</v>
       </c>
       <c r="B73" s="1">
-        <v>128.4947166298838</v>
+        <v>127.4160823718624</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -2045,7 +2054,7 @@
         <v>74</v>
       </c>
       <c r="B74" s="1">
-        <v>128.5525964359129</v>
+        <v>127.5090896842275</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -2053,7 +2062,7 @@
         <v>75</v>
       </c>
       <c r="B75" s="1">
-        <v>128.5758769746884</v>
+        <v>127.5242743758276</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -2061,7 +2070,7 @@
         <v>76</v>
       </c>
       <c r="B76" s="1">
-        <v>128.5919157700761</v>
+        <v>127.5250226743852</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -2069,7 +2078,7 @@
         <v>77</v>
       </c>
       <c r="B77" s="1">
-        <v>128.6336232160199</v>
+        <v>127.6013465385664</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -2077,7 +2086,7 @@
         <v>78</v>
       </c>
       <c r="B78" s="1">
-        <v>128.669208395695</v>
+        <v>127.6061577399607</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -2085,7 +2094,7 @@
         <v>79</v>
       </c>
       <c r="B79" s="1">
-        <v>128.7264652008238</v>
+        <v>127.6337995583583</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -2093,7 +2102,7 @@
         <v>80</v>
       </c>
       <c r="B80" s="1">
-        <v>128.7499846069869</v>
+        <v>127.714381921303</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -2101,7 +2110,7 @@
         <v>81</v>
       </c>
       <c r="B81" s="1">
-        <v>128.8055805616267</v>
+        <v>127.7181725128841</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -2109,7 +2118,7 @@
         <v>82</v>
       </c>
       <c r="B82" s="1">
-        <v>128.8851268634323</v>
+        <v>127.7241253795214</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -2117,7 +2126,7 @@
         <v>83</v>
       </c>
       <c r="B83" s="1">
-        <v>128.9268316039442</v>
+        <v>127.7482211011853</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -2125,7 +2134,7 @@
         <v>84</v>
       </c>
       <c r="B84" s="1">
-        <v>129.0420471825822</v>
+        <v>127.7490447114442</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -2133,7 +2142,7 @@
         <v>85</v>
       </c>
       <c r="B85" s="1">
-        <v>129.1294882308461</v>
+        <v>127.7870506305755</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -2141,7 +2150,7 @@
         <v>86</v>
       </c>
       <c r="B86" s="1">
-        <v>129.2843331183595</v>
+        <v>127.9371654894457</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -2149,7 +2158,7 @@
         <v>87</v>
       </c>
       <c r="B87" s="1">
-        <v>129.3410642721542</v>
+        <v>127.9521132948472</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -2157,7 +2166,7 @@
         <v>88</v>
       </c>
       <c r="B88" s="1">
-        <v>129.3462862966608</v>
+        <v>127.9868531020263</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -2165,7 +2174,7 @@
         <v>89</v>
       </c>
       <c r="B89" s="1">
-        <v>129.4651771430167</v>
+        <v>128.0822809429671</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -2173,7 +2182,7 @@
         <v>90</v>
       </c>
       <c r="B90" s="1">
-        <v>129.4683666802686</v>
+        <v>128.2296991823873</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -2181,7 +2190,7 @@
         <v>91</v>
       </c>
       <c r="B91" s="1">
-        <v>129.507961092539</v>
+        <v>128.2520753974548</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -2189,7 +2198,7 @@
         <v>92</v>
       </c>
       <c r="B92" s="1">
-        <v>129.5621745414584</v>
+        <v>128.2657078335446</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -2197,7 +2206,7 @@
         <v>93</v>
       </c>
       <c r="B93" s="1">
-        <v>129.6275805826434</v>
+        <v>128.3078500791912</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -2205,7 +2214,7 @@
         <v>94</v>
       </c>
       <c r="B94" s="1">
-        <v>129.6616889426944</v>
+        <v>128.3350598374419</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -2213,7 +2222,7 @@
         <v>95</v>
       </c>
       <c r="B95" s="1">
-        <v>129.7631057333545</v>
+        <v>128.3437101427465</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -2221,7 +2230,7 @@
         <v>96</v>
       </c>
       <c r="B96" s="1">
-        <v>129.8273525063746</v>
+        <v>128.3786167231696</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -2229,7 +2238,7 @@
         <v>97</v>
       </c>
       <c r="B97" s="1">
-        <v>129.8881568220512</v>
+        <v>128.4484646102484</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -2237,7 +2246,7 @@
         <v>98</v>
       </c>
       <c r="B98" s="1">
-        <v>129.9354384238604</v>
+        <v>128.4716447515167</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -2245,7 +2254,7 @@
         <v>99</v>
       </c>
       <c r="B99" s="1">
-        <v>129.9627733927852</v>
+        <v>128.488916358998</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -2253,7 +2262,7 @@
         <v>100</v>
       </c>
       <c r="B100" s="1">
-        <v>130.0974321077746</v>
+        <v>128.5983462380588</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -2261,7 +2270,7 @@
         <v>101</v>
       </c>
       <c r="B101" s="1">
-        <v>130.1233206528872</v>
+        <v>128.6498927541182</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -2269,7 +2278,7 @@
         <v>102</v>
       </c>
       <c r="B102" s="1">
-        <v>130.1933490976917</v>
+        <v>128.6514535378718</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -2277,7 +2286,7 @@
         <v>103</v>
       </c>
       <c r="B103" s="1">
-        <v>130.3101842471494</v>
+        <v>128.6541892318087</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -2285,7 +2294,7 @@
         <v>104</v>
       </c>
       <c r="B104" s="1">
-        <v>130.342784993163</v>
+        <v>128.6664031263227</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -2293,7 +2302,7 @@
         <v>105</v>
       </c>
       <c r="B105" s="1">
-        <v>130.4137425744988</v>
+        <v>128.7547156560537</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -2301,7 +2310,7 @@
         <v>106</v>
       </c>
       <c r="B106" s="1">
-        <v>130.6124345857269</v>
+        <v>128.7887322138049</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -2309,7 +2318,7 @@
         <v>107</v>
       </c>
       <c r="B107" s="1">
-        <v>130.7691305135755</v>
+        <v>128.792245654413</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -2317,7 +2326,7 @@
         <v>108</v>
       </c>
       <c r="B108" s="1">
-        <v>130.8335549968744</v>
+        <v>128.7950124664951</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -2325,7 +2334,7 @@
         <v>109</v>
       </c>
       <c r="B109" s="1">
-        <v>130.875680939457</v>
+        <v>128.8083977525122</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -2333,7 +2342,7 @@
         <v>110</v>
       </c>
       <c r="B110" s="1">
-        <v>131.0707436564388</v>
+        <v>128.8848941264693</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -2341,7 +2350,7 @@
         <v>111</v>
       </c>
       <c r="B111" s="1">
-        <v>131.1799250904155</v>
+        <v>128.9038489400424</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -2349,7 +2358,7 @@
         <v>112</v>
       </c>
       <c r="B112" s="1">
-        <v>131.1855325380144</v>
+        <v>128.9436889143977</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -2357,7 +2366,7 @@
         <v>113</v>
       </c>
       <c r="B113" s="1">
-        <v>131.2752860153809</v>
+        <v>129.0491367977121</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -2365,7 +2374,7 @@
         <v>114</v>
       </c>
       <c r="B114" s="1">
-        <v>131.27547443351</v>
+        <v>129.073264833155</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -2373,7 +2382,7 @@
         <v>115</v>
       </c>
       <c r="B115" s="1">
-        <v>131.3232784295469</v>
+        <v>129.1618824936386</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -2381,7 +2390,7 @@
         <v>116</v>
       </c>
       <c r="B116" s="1">
-        <v>131.4445365887914</v>
+        <v>129.4114387837731</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -2389,7 +2398,7 @@
         <v>117</v>
       </c>
       <c r="B117" s="1">
-        <v>131.5613138856158</v>
+        <v>129.4476894243408</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -2397,7 +2406,7 @@
         <v>118</v>
       </c>
       <c r="B118" s="1">
-        <v>131.5834964933555</v>
+        <v>129.6265754118318</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -2405,7 +2414,7 @@
         <v>119</v>
       </c>
       <c r="B119" s="1">
-        <v>131.7033931159774</v>
+        <v>129.7403585985813</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -2413,7 +2422,7 @@
         <v>120</v>
       </c>
       <c r="B120" s="1">
-        <v>131.7180612933368</v>
+        <v>129.7620497359756</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -2421,7 +2430,7 @@
         <v>121</v>
       </c>
       <c r="B121" s="1">
-        <v>131.7932215214609</v>
+        <v>129.8489324369625</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -2429,7 +2438,7 @@
         <v>122</v>
       </c>
       <c r="B122" s="1">
-        <v>131.9533189204091</v>
+        <v>129.8806525371881</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -2437,7 +2446,7 @@
         <v>123</v>
       </c>
       <c r="B123" s="1">
-        <v>132.0693044367617</v>
+        <v>129.9063174807688</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -2445,7 +2454,7 @@
         <v>124</v>
       </c>
       <c r="B124" s="1">
-        <v>132.1141687369641</v>
+        <v>129.9541797958996</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -2453,7 +2462,7 @@
         <v>125</v>
       </c>
       <c r="B125" s="1">
-        <v>132.1478322464304</v>
+        <v>129.9545375235461</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -2461,7 +2470,7 @@
         <v>126</v>
       </c>
       <c r="B126" s="1">
-        <v>132.1875734457967</v>
+        <v>129.9957102297416</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -2469,7 +2478,7 @@
         <v>127</v>
       </c>
       <c r="B127" s="1">
-        <v>132.2482394053371</v>
+        <v>130.1172516637907</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -2477,7 +2486,7 @@
         <v>128</v>
       </c>
       <c r="B128" s="1">
-        <v>132.3638191578668</v>
+        <v>130.2034523106618</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -2485,7 +2494,7 @@
         <v>129</v>
       </c>
       <c r="B129" s="1">
-        <v>132.3943461258388</v>
+        <v>130.3164965704787</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -2493,7 +2502,7 @@
         <v>130</v>
       </c>
       <c r="B130" s="1">
-        <v>132.3995692309329</v>
+        <v>130.3744516074356</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -2501,7 +2510,7 @@
         <v>131</v>
       </c>
       <c r="B131" s="1">
-        <v>132.5299989750339</v>
+        <v>130.4338572917512</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -2509,7 +2518,7 @@
         <v>132</v>
       </c>
       <c r="B132" s="1">
-        <v>132.6933457540734</v>
+        <v>130.4695579265789</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -2517,7 +2526,7 @@
         <v>133</v>
       </c>
       <c r="B133" s="1">
-        <v>132.7293191241272</v>
+        <v>130.4894921862387</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -2525,7 +2534,7 @@
         <v>134</v>
       </c>
       <c r="B134" s="1">
-        <v>132.7596147138641</v>
+        <v>130.749804244786</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -2533,7 +2542,7 @@
         <v>135</v>
       </c>
       <c r="B135" s="1">
-        <v>132.8223821631663</v>
+        <v>130.7776758712376</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -2541,7 +2550,7 @@
         <v>136</v>
       </c>
       <c r="B136" s="1">
-        <v>132.822400601878</v>
+        <v>130.983447158802</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -2549,7 +2558,7 @@
         <v>137</v>
       </c>
       <c r="B137" s="1">
-        <v>132.9612543123872</v>
+        <v>131.1534537183965</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -2557,7 +2566,7 @@
         <v>138</v>
       </c>
       <c r="B138" s="1">
-        <v>132.9899978290975</v>
+        <v>131.2173168007979</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -2565,7 +2574,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="1">
-        <v>133.163332540921</v>
+        <v>131.2829909345503</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -2573,7 +2582,7 @@
         <v>140</v>
       </c>
       <c r="B140" s="1">
-        <v>133.2237848789503</v>
+        <v>131.2948143616237</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -2581,7 +2590,7 @@
         <v>141</v>
       </c>
       <c r="B141" s="1">
-        <v>133.2855576135238</v>
+        <v>131.3124626174712</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -2589,7 +2598,7 @@
         <v>142</v>
       </c>
       <c r="B142" s="1">
-        <v>133.4591006854866</v>
+        <v>131.3299020366235</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -2597,7 +2606,7 @@
         <v>143</v>
       </c>
       <c r="B143" s="1">
-        <v>133.5120954155497</v>
+        <v>131.4099235311241</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -2605,7 +2614,7 @@
         <v>144</v>
       </c>
       <c r="B144" s="1">
-        <v>133.6113758689058</v>
+        <v>131.6761108931362</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -2613,7 +2622,7 @@
         <v>145</v>
       </c>
       <c r="B145" s="1">
-        <v>133.6994029608328</v>
+        <v>131.6788382836702</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -2621,7 +2630,7 @@
         <v>146</v>
       </c>
       <c r="B146" s="1">
-        <v>133.800221406801</v>
+        <v>131.7990897615463</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -2629,7 +2638,7 @@
         <v>147</v>
       </c>
       <c r="B147" s="1">
-        <v>133.8574325173187</v>
+        <v>132.0871347428294</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -2637,7 +2646,7 @@
         <v>148</v>
       </c>
       <c r="B148" s="1">
-        <v>133.9338733333196</v>
+        <v>132.2493096746987</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -2645,7 +2654,7 @@
         <v>149</v>
       </c>
       <c r="B149" s="1">
-        <v>133.9879567595489</v>
+        <v>132.3262448199615</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -2653,7 +2662,7 @@
         <v>150</v>
       </c>
       <c r="B150" s="1">
-        <v>133.9999349081887</v>
+        <v>132.4006207353256</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -2661,7 +2670,7 @@
         <v>151</v>
       </c>
       <c r="B151" s="1">
-        <v>134.042877100622</v>
+        <v>132.4744343528598</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -2669,7 +2678,7 @@
         <v>152</v>
       </c>
       <c r="B152" s="1">
-        <v>134.2146554817993</v>
+        <v>132.5296305483573</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -2677,7 +2686,7 @@
         <v>153</v>
       </c>
       <c r="B153" s="1">
-        <v>134.3023320306388</v>
+        <v>132.5816998118583</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -2685,7 +2694,7 @@
         <v>154</v>
       </c>
       <c r="B154" s="1">
-        <v>134.3026602916408</v>
+        <v>132.6044502577217</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -2693,7 +2702,7 @@
         <v>155</v>
       </c>
       <c r="B155" s="1">
-        <v>134.3412516983596</v>
+        <v>132.729673947039</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -2701,7 +2710,7 @@
         <v>156</v>
       </c>
       <c r="B156" s="1">
-        <v>134.3603228290581</v>
+        <v>132.990643481224</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -2709,7 +2718,7 @@
         <v>157</v>
       </c>
       <c r="B157" s="1">
-        <v>134.3797692794508</v>
+        <v>132.9935805121691</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -2717,7 +2726,7 @@
         <v>158</v>
       </c>
       <c r="B158" s="1">
-        <v>134.4691012825402</v>
+        <v>133.0172424412924</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -2725,7 +2734,7 @@
         <v>159</v>
       </c>
       <c r="B159" s="1">
-        <v>134.6133223660205</v>
+        <v>133.0470173664501</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -2733,7 +2742,7 @@
         <v>160</v>
       </c>
       <c r="B160" s="1">
-        <v>134.6736940728904</v>
+        <v>133.1506551233277</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -2741,7 +2750,7 @@
         <v>161</v>
       </c>
       <c r="B161" s="1">
-        <v>134.7087395738062</v>
+        <v>133.3039710378434</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -2749,7 +2758,7 @@
         <v>162</v>
       </c>
       <c r="B162" s="1">
-        <v>134.8863006308823</v>
+        <v>133.4452361814381</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -2757,7 +2766,7 @@
         <v>163</v>
       </c>
       <c r="B163" s="1">
-        <v>134.9736723172544</v>
+        <v>133.4731296530535</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -2765,7 +2774,7 @@
         <v>164</v>
       </c>
       <c r="B164" s="1">
-        <v>135.0285641576313</v>
+        <v>133.6978635452127</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -2773,7 +2782,7 @@
         <v>165</v>
       </c>
       <c r="B165" s="1">
-        <v>135.0302789479341</v>
+        <v>133.7586008602386</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -2781,7 +2790,7 @@
         <v>166</v>
       </c>
       <c r="B166" s="1">
-        <v>135.1312624139452</v>
+        <v>133.8076164573903</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -2789,7 +2798,7 @@
         <v>167</v>
       </c>
       <c r="B167" s="1">
-        <v>135.1453652600125</v>
+        <v>133.8647387858678</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -2797,7 +2806,7 @@
         <v>168</v>
       </c>
       <c r="B168" s="1">
-        <v>135.1590743095559</v>
+        <v>133.920092084682</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -2805,7 +2814,7 @@
         <v>169</v>
       </c>
       <c r="B169" s="1">
-        <v>135.1759247283216</v>
+        <v>133.9811738087282</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -2813,7 +2822,7 @@
         <v>170</v>
       </c>
       <c r="B170" s="1">
-        <v>135.3376298408638</v>
+        <v>134.2428215933341</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -2821,7 +2830,7 @@
         <v>171</v>
       </c>
       <c r="B171" s="1">
-        <v>135.4375103024965</v>
+        <v>134.3070564124008</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -2829,7 +2838,7 @@
         <v>172</v>
       </c>
       <c r="B172" s="1">
-        <v>135.4430132261552</v>
+        <v>134.4818075635634</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -2837,7 +2846,7 @@
         <v>173</v>
       </c>
       <c r="B173" s="1">
-        <v>135.6868103432446</v>
+        <v>134.5764056541234</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -2845,7 +2854,7 @@
         <v>174</v>
       </c>
       <c r="B174" s="1">
-        <v>135.7314668681568</v>
+        <v>134.7504436190654</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -2853,7 +2862,7 @@
         <v>175</v>
       </c>
       <c r="B175" s="1">
-        <v>135.8829151491685</v>
+        <v>134.801458522311</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -2861,7 +2870,7 @@
         <v>176</v>
       </c>
       <c r="B176" s="1">
-        <v>135.9062751264027</v>
+        <v>135.0721648454088</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -2869,7 +2878,7 @@
         <v>177</v>
       </c>
       <c r="B177" s="1">
-        <v>135.9624801810163</v>
+        <v>135.1331679148208</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -2877,7 +2886,7 @@
         <v>178</v>
       </c>
       <c r="B178" s="1">
-        <v>136.0895029543066</v>
+        <v>135.3086143984004</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -2885,7 +2894,7 @@
         <v>179</v>
       </c>
       <c r="B179" s="1">
-        <v>136.5181403990751</v>
+        <v>135.5425556788738</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -2893,7 +2902,7 @@
         <v>180</v>
       </c>
       <c r="B180" s="1">
-        <v>136.6101633440267</v>
+        <v>135.9971298595455</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -2901,7 +2910,7 @@
         <v>181</v>
       </c>
       <c r="B181" s="1">
-        <v>136.9468915059881</v>
+        <v>136.1431177762248</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -2909,7 +2918,7 @@
         <v>182</v>
       </c>
       <c r="B182" s="1">
-        <v>136.9735154571766</v>
+        <v>136.147424272235</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -2917,7 +2926,7 @@
         <v>183</v>
       </c>
       <c r="B183" s="1">
-        <v>136.9737893920463</v>
+        <v>136.4277168988233</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -2925,7 +2934,7 @@
         <v>184</v>
       </c>
       <c r="B184" s="1">
-        <v>136.9946614876573</v>
+        <v>136.4639098814952</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -2933,7 +2942,7 @@
         <v>185</v>
       </c>
       <c r="B185" s="1">
-        <v>137.0380616475496</v>
+        <v>136.7076488483891</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -2941,7 +2950,7 @@
         <v>186</v>
       </c>
       <c r="B186" s="1">
-        <v>137.1032442136004</v>
+        <v>136.8985158914812</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -2949,7 +2958,7 @@
         <v>187</v>
       </c>
       <c r="B187" s="1">
-        <v>137.1075904824159</v>
+        <v>137.0682141423244</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -2957,7 +2966,7 @@
         <v>188</v>
       </c>
       <c r="B188" s="1">
-        <v>137.3117425144483</v>
+        <v>137.1427239176866</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -2965,7 +2974,7 @@
         <v>189</v>
       </c>
       <c r="B189" s="1">
-        <v>137.4790226257069</v>
+        <v>137.2527013094927</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -2973,7 +2982,7 @@
         <v>190</v>
       </c>
       <c r="B190" s="1">
-        <v>137.7536903813453</v>
+        <v>137.2828303925376</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -2981,7 +2990,7 @@
         <v>191</v>
       </c>
       <c r="B191" s="1">
-        <v>137.7573571985707</v>
+        <v>137.2969793999234</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -2989,7 +2998,7 @@
         <v>192</v>
       </c>
       <c r="B192" s="1">
-        <v>137.7807761233682</v>
+        <v>137.4754157399989</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -2997,7 +3006,7 @@
         <v>193</v>
       </c>
       <c r="B193" s="1">
-        <v>137.8945695997145</v>
+        <v>137.5315678733478</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -3005,7 +3014,7 @@
         <v>194</v>
       </c>
       <c r="B194" s="1">
-        <v>138.083385194311</v>
+        <v>137.8405324119095</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -3013,7 +3022,7 @@
         <v>195</v>
       </c>
       <c r="B195" s="1">
-        <v>138.1215490413345</v>
+        <v>138.204827195071</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -3021,7 +3030,7 @@
         <v>196</v>
       </c>
       <c r="B196" s="1">
-        <v>138.1565900570076</v>
+        <v>138.3613170519559</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -3029,7 +3038,7 @@
         <v>197</v>
       </c>
       <c r="B197" s="1">
-        <v>138.1663907436597</v>
+        <v>138.4076502903102</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -3037,7 +3046,7 @@
         <v>198</v>
       </c>
       <c r="B198" s="1">
-        <v>138.2195730214023</v>
+        <v>138.6918380727558</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -3045,7 +3054,7 @@
         <v>199</v>
       </c>
       <c r="B199" s="1">
-        <v>138.3431263427562</v>
+        <v>138.7342561425032</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -3053,7 +3062,7 @@
         <v>200</v>
       </c>
       <c r="B200" s="1">
-        <v>138.7508859031284</v>
+        <v>138.9542539506856</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -3061,7 +3070,7 @@
         <v>201</v>
       </c>
       <c r="B201" s="1">
-        <v>138.9567113712588</v>
+        <v>139.1489512786926</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -3069,7 +3078,7 @@
         <v>202</v>
       </c>
       <c r="B202" s="1">
-        <v>139.0322403485192</v>
+        <v>139.2210030572633</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -3077,7 +3086,7 @@
         <v>203</v>
       </c>
       <c r="B203" s="1">
-        <v>139.0776434132237</v>
+        <v>139.5499225744606</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -3085,7 +3094,7 @@
         <v>204</v>
       </c>
       <c r="B204" s="1">
-        <v>139.290703861554</v>
+        <v>139.7904698268517</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -3093,7 +3102,7 @@
         <v>205</v>
       </c>
       <c r="B205" s="1">
-        <v>139.4357928260872</v>
+        <v>139.9521185156612</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -3101,7 +3110,7 @@
         <v>206</v>
       </c>
       <c r="B206" s="1">
-        <v>139.5999832901755</v>
+        <v>139.9642299978598</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -3109,7 +3118,7 @@
         <v>207</v>
       </c>
       <c r="B207" s="1">
-        <v>139.6330652887825</v>
+        <v>140.2217651657554</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -3117,7 +3126,7 @@
         <v>208</v>
       </c>
       <c r="B208" s="1">
-        <v>140.1438872465253</v>
+        <v>140.4219181576626</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -3125,7 +3134,7 @@
         <v>209</v>
       </c>
       <c r="B209" s="1">
-        <v>140.1501991024404</v>
+        <v>140.4228397423457</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -3133,7 +3142,7 @@
         <v>210</v>
       </c>
       <c r="B210" s="1">
-        <v>140.2541046669029</v>
+        <v>140.4674616564985</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -3141,7 +3150,7 @@
         <v>211</v>
       </c>
       <c r="B211" s="1">
-        <v>140.2716330985683</v>
+        <v>140.7117271776148</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -3149,7 +3158,7 @@
         <v>212</v>
       </c>
       <c r="B212" s="1">
-        <v>140.4953095267452</v>
+        <v>141.0186030021931</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -3157,7 +3166,7 @@
         <v>213</v>
       </c>
       <c r="B213" s="1">
-        <v>140.5604610951807</v>
+        <v>141.1130969592363</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -3165,7 +3174,7 @@
         <v>214</v>
       </c>
       <c r="B214" s="1">
-        <v>140.5986876354326</v>
+        <v>141.1971700309032</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -3173,7 +3182,7 @@
         <v>215</v>
       </c>
       <c r="B215" s="1">
-        <v>140.7465741597917</v>
+        <v>141.3124687109154</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -3181,7 +3190,7 @@
         <v>216</v>
       </c>
       <c r="B216" s="1">
-        <v>140.8003600350384</v>
+        <v>141.4141881633905</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -3189,7 +3198,7 @@
         <v>217</v>
       </c>
       <c r="B217" s="1">
-        <v>140.8872345808872</v>
+        <v>141.6157307948109</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -3197,7 +3206,7 @@
         <v>218</v>
       </c>
       <c r="B218" s="1">
-        <v>141.3213771186406</v>
+        <v>141.8537647013028</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -3205,7 +3214,7 @@
         <v>219</v>
       </c>
       <c r="B219" s="1">
-        <v>141.730202347404</v>
+        <v>141.8700676581266</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -3213,7 +3222,7 @@
         <v>220</v>
       </c>
       <c r="B220" s="1">
-        <v>141.8058654494284</v>
+        <v>142.0138557966405</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -3221,7 +3230,7 @@
         <v>221</v>
       </c>
       <c r="B221" s="1">
-        <v>142.0584172504361</v>
+        <v>142.0864517220795</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -3229,7 +3238,7 @@
         <v>222</v>
       </c>
       <c r="B222" s="1">
-        <v>142.5731372918068</v>
+        <v>142.1218788833395</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -3237,7 +3246,7 @@
         <v>223</v>
       </c>
       <c r="B223" s="1">
-        <v>142.7017178494285</v>
+        <v>142.3017944340626</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -3245,7 +3254,7 @@
         <v>224</v>
       </c>
       <c r="B224" s="1">
-        <v>143.0379114820345</v>
+        <v>142.3028017682485</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -3253,7 +3262,7 @@
         <v>225</v>
       </c>
       <c r="B225" s="1">
-        <v>143.3166267477089</v>
+        <v>142.3700664691631</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -3261,7 +3270,7 @@
         <v>226</v>
       </c>
       <c r="B226" s="1">
-        <v>143.7545884666683</v>
+        <v>142.6271851689096</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -3269,7 +3278,7 @@
         <v>227</v>
       </c>
       <c r="B227" s="1">
-        <v>144.7559778973308</v>
+        <v>142.7074627034073</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -3277,7 +3286,7 @@
         <v>228</v>
       </c>
       <c r="B228" s="1">
-        <v>144.9324935814104</v>
+        <v>142.9177169598384</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -3285,7 +3294,7 @@
         <v>229</v>
       </c>
       <c r="B229" s="1">
-        <v>145.1686529070574</v>
+        <v>143.4162025847165</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -3293,7 +3302,7 @@
         <v>230</v>
       </c>
       <c r="B230" s="1">
-        <v>145.2429256731017</v>
+        <v>143.7563156599863</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -3301,7 +3310,7 @@
         <v>231</v>
       </c>
       <c r="B231" s="1">
-        <v>145.2601429697899</v>
+        <v>143.7874838261025</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -3309,7 +3318,7 @@
         <v>232</v>
       </c>
       <c r="B232" s="1">
-        <v>145.4857623455498</v>
+        <v>143.9313233484539</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -3317,7 +3326,7 @@
         <v>233</v>
       </c>
       <c r="B233" s="1">
-        <v>145.5180681203462</v>
+        <v>143.9386954747752</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -3325,7 +3334,7 @@
         <v>234</v>
       </c>
       <c r="B234" s="1">
-        <v>145.6656964022839</v>
+        <v>144.0150197118303</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -3333,7 +3342,7 @@
         <v>235</v>
       </c>
       <c r="B235" s="1">
-        <v>145.7507952465374</v>
+        <v>144.1104673369159</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -3341,7 +3350,7 @@
         <v>236</v>
       </c>
       <c r="B236" s="1">
-        <v>145.8893630710109</v>
+        <v>144.2364733919311</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -3349,7 +3358,7 @@
         <v>237</v>
       </c>
       <c r="B237" s="1">
-        <v>146.0287711614007</v>
+        <v>145.0753221655055</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -3357,7 +3366,7 @@
         <v>238</v>
       </c>
       <c r="B238" s="1">
-        <v>146.1919403026352</v>
+        <v>145.2886458421303</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -3365,7 +3374,7 @@
         <v>239</v>
       </c>
       <c r="B239" s="1">
-        <v>146.1938776544916</v>
+        <v>145.3003503096471</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -3373,7 +3382,7 @@
         <v>240</v>
       </c>
       <c r="B240" s="1">
-        <v>146.2916738409989</v>
+        <v>145.4208761694426</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -3381,7 +3390,7 @@
         <v>241</v>
       </c>
       <c r="B241" s="1">
-        <v>146.3285057612963</v>
+        <v>145.5335703874646</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -3389,7 +3398,7 @@
         <v>242</v>
       </c>
       <c r="B242" s="1">
-        <v>146.7172062037879</v>
+        <v>145.5602060985507</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -3397,7 +3406,7 @@
         <v>243</v>
       </c>
       <c r="B243" s="1">
-        <v>146.7505821627256</v>
+        <v>145.6509150730755</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -3405,7 +3414,7 @@
         <v>244</v>
       </c>
       <c r="B244" s="1">
-        <v>146.7839310428782</v>
+        <v>145.7341966036603</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -3413,7 +3422,7 @@
         <v>245</v>
       </c>
       <c r="B245" s="1">
-        <v>147.6927667342856</v>
+        <v>146.2745292418855</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -3421,7 +3430,7 @@
         <v>246</v>
       </c>
       <c r="B246" s="1">
-        <v>147.7943906181666</v>
+        <v>146.3484271556072</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -3429,7 +3438,7 @@
         <v>247</v>
       </c>
       <c r="B247" s="1">
-        <v>147.8635980774913</v>
+        <v>146.4625996965309</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -3437,7 +3446,7 @@
         <v>248</v>
       </c>
       <c r="B248" s="1">
-        <v>147.885724236739</v>
+        <v>146.7132691819577</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -3445,7 +3454,7 @@
         <v>249</v>
       </c>
       <c r="B249" s="1">
-        <v>147.9420622676186</v>
+        <v>147.1953432862092</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -3453,7 +3462,7 @@
         <v>250</v>
       </c>
       <c r="B250" s="1">
-        <v>148.2475073536607</v>
+        <v>147.3498599813152</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -3461,7 +3470,7 @@
         <v>251</v>
       </c>
       <c r="B251" s="1">
-        <v>148.377176889903</v>
+        <v>147.6810226490112</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -3469,7 +3478,7 @@
         <v>252</v>
       </c>
       <c r="B252" s="1">
-        <v>148.7527534757949</v>
+        <v>148.1367650581797</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -3477,7 +3486,7 @@
         <v>253</v>
       </c>
       <c r="B253" s="1">
-        <v>149.0024598560869</v>
+        <v>148.378278901612</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -3485,7 +3494,7 @@
         <v>254</v>
       </c>
       <c r="B254" s="1">
-        <v>149.2069951034504</v>
+        <v>148.6746919920275</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -3493,7 +3502,7 @@
         <v>255</v>
       </c>
       <c r="B255" s="1">
-        <v>149.5618962850521</v>
+        <v>148.8898279476895</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -3501,7 +3510,7 @@
         <v>256</v>
       </c>
       <c r="B256" s="1">
-        <v>150.1304132260817</v>
+        <v>149.0198758319567</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -3509,7 +3518,7 @@
         <v>257</v>
       </c>
       <c r="B257" s="1">
-        <v>150.204002379743</v>
+        <v>149.1204312994956</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -3517,7 +3526,7 @@
         <v>258</v>
       </c>
       <c r="B258" s="1">
-        <v>150.5548768691871</v>
+        <v>149.1495617249296</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -3525,7 +3534,7 @@
         <v>259</v>
       </c>
       <c r="B259" s="1">
-        <v>150.821088140924</v>
+        <v>149.2274859982583</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -3533,7 +3542,7 @@
         <v>260</v>
       </c>
       <c r="B260" s="1">
-        <v>150.8248057013783</v>
+        <v>149.265569538992</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -3541,7 +3550,7 @@
         <v>261</v>
       </c>
       <c r="B261" s="1">
-        <v>151.0845127302103</v>
+        <v>149.3630610031549</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -3549,7 +3558,7 @@
         <v>262</v>
       </c>
       <c r="B262" s="1">
-        <v>151.1021722780313</v>
+        <v>149.5005924538437</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -3557,7 +3566,7 @@
         <v>263</v>
       </c>
       <c r="B263" s="1">
-        <v>151.3209409014399</v>
+        <v>149.9886608150451</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -3565,7 +3574,7 @@
         <v>264</v>
       </c>
       <c r="B264" s="1">
-        <v>151.3819325360774</v>
+        <v>150.121320521442</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -3573,7 +3582,7 @@
         <v>265</v>
       </c>
       <c r="B265" s="1">
-        <v>151.473785887918</v>
+        <v>150.5017364316517</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -3581,7 +3590,7 @@
         <v>266</v>
       </c>
       <c r="B266" s="1">
-        <v>151.573490671684</v>
+        <v>150.557000656446</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -3589,7 +3598,7 @@
         <v>267</v>
       </c>
       <c r="B267" s="1">
-        <v>151.906527349188</v>
+        <v>150.6358975752698</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -3597,7 +3606,7 @@
         <v>268</v>
       </c>
       <c r="B268" s="1">
-        <v>152.0154751570682</v>
+        <v>150.935765854733</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -3605,7 +3614,7 @@
         <v>269</v>
       </c>
       <c r="B269" s="1">
-        <v>152.6972789666754</v>
+        <v>150.9652225945763</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -3613,7 +3622,7 @@
         <v>270</v>
       </c>
       <c r="B270" s="1">
-        <v>152.7642005210558</v>
+        <v>151.093474626043</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -3621,7 +3630,7 @@
         <v>271</v>
       </c>
       <c r="B271" s="1">
-        <v>153.134458094205</v>
+        <v>151.2203655790371</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -3629,7 +3638,7 @@
         <v>272</v>
       </c>
       <c r="B272" s="1">
-        <v>153.1918861074822</v>
+        <v>151.9778954695466</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -3637,7 +3646,7 @@
         <v>273</v>
       </c>
       <c r="B273" s="1">
-        <v>155.2122086317486</v>
+        <v>152.0353602246721</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -3645,7 +3654,7 @@
         <v>274</v>
       </c>
       <c r="B274" s="1">
-        <v>155.5237113430424</v>
+        <v>152.0384165611634</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -3653,7 +3662,7 @@
         <v>275</v>
       </c>
       <c r="B275" s="1">
-        <v>155.6875435756648</v>
+        <v>152.0761251676269</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -3661,7 +3670,7 @@
         <v>276</v>
       </c>
       <c r="B276" s="1">
-        <v>155.7283212865877</v>
+        <v>152.3855231195887</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -3669,7 +3678,7 @@
         <v>277</v>
       </c>
       <c r="B277" s="1">
-        <v>155.8192730042092</v>
+        <v>152.5388909543182</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -3677,7 +3686,7 @@
         <v>278</v>
       </c>
       <c r="B278" s="1">
-        <v>155.8595579670367</v>
+        <v>152.8399818630474</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -3685,7 +3694,7 @@
         <v>279</v>
       </c>
       <c r="B279" s="1">
-        <v>156.5048758027658</v>
+        <v>153.0833996554127</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -3693,7 +3702,7 @@
         <v>280</v>
       </c>
       <c r="B280" s="1">
-        <v>157.4020910390263</v>
+        <v>153.1896292117925</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -3701,7 +3710,7 @@
         <v>281</v>
       </c>
       <c r="B281" s="1">
-        <v>157.953558265999</v>
+        <v>153.1907853051449</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -3709,7 +3718,7 @@
         <v>282</v>
       </c>
       <c r="B282" s="1">
-        <v>159.0839930024723</v>
+        <v>153.2729392427558</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -3717,7 +3726,7 @@
         <v>283</v>
       </c>
       <c r="B283" s="1">
-        <v>159.7695828310387</v>
+        <v>153.3900893469971</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -3725,7 +3734,7 @@
         <v>284</v>
       </c>
       <c r="B284" s="1">
-        <v>159.8105488416895</v>
+        <v>153.9534793149107</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -3733,7 +3742,7 @@
         <v>285</v>
       </c>
       <c r="B285" s="1">
-        <v>160.1524907371216</v>
+        <v>154.0893150303502</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -3741,7 +3750,7 @@
         <v>286</v>
       </c>
       <c r="B286" s="1">
-        <v>160.395851150393</v>
+        <v>154.4791600997551</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -3749,7 +3758,7 @@
         <v>287</v>
       </c>
       <c r="B287" s="1">
-        <v>161.0166450704968</v>
+        <v>154.5234311738164</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -3757,7 +3766,7 @@
         <v>288</v>
       </c>
       <c r="B288" s="1">
-        <v>161.1319262980886</v>
+        <v>154.8394154220977</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -3765,7 +3774,7 @@
         <v>289</v>
       </c>
       <c r="B289" s="1">
-        <v>161.3134022009235</v>
+        <v>154.9093034705795</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -3773,7 +3782,7 @@
         <v>290</v>
       </c>
       <c r="B290" s="1">
-        <v>161.4690441064647</v>
+        <v>155.1789599824439</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -3781,7 +3790,7 @@
         <v>291</v>
       </c>
       <c r="B291" s="1">
-        <v>161.59057559473</v>
+        <v>155.5216340497774</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -3789,7 +3798,7 @@
         <v>292</v>
       </c>
       <c r="B292" s="1">
-        <v>161.9399478198272</v>
+        <v>155.9511070710915</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -3797,7 +3806,7 @@
         <v>293</v>
       </c>
       <c r="B293" s="1">
-        <v>161.9418759836315</v>
+        <v>155.953914392323</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -3805,7 +3814,7 @@
         <v>294</v>
       </c>
       <c r="B294" s="1">
-        <v>162.1854380739672</v>
+        <v>156.0737209289954</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -3813,7 +3822,7 @@
         <v>295</v>
       </c>
       <c r="B295" s="1">
-        <v>162.3282889397495</v>
+        <v>156.7883754504644</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -3821,7 +3830,7 @@
         <v>296</v>
       </c>
       <c r="B296" s="1">
-        <v>163.1569109840231</v>
+        <v>157.5882032314923</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -3829,7 +3838,7 @@
         <v>297</v>
       </c>
       <c r="B297" s="1">
-        <v>164.0312965110377</v>
+        <v>157.6979241085656</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -3837,7 +3846,7 @@
         <v>298</v>
       </c>
       <c r="B298" s="1">
-        <v>165.2668821978276</v>
+        <v>157.746982584233</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -3845,7 +3854,7 @@
         <v>299</v>
       </c>
       <c r="B299" s="1">
-        <v>165.6409274188778</v>
+        <v>158.4782812422286</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -3853,7 +3862,7 @@
         <v>300</v>
       </c>
       <c r="B300" s="1">
-        <v>165.8062056831798</v>
+        <v>158.6524613545851</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -3861,7 +3870,7 @@
         <v>301</v>
       </c>
       <c r="B301" s="1">
-        <v>166.9855904439393</v>
+        <v>158.957195248279</v>
       </c>
     </row>
     <row r="302" spans="1:2">
@@ -3869,7 +3878,7 @@
         <v>302</v>
       </c>
       <c r="B302" s="1">
-        <v>167.6469494602538</v>
+        <v>159.4495990989138</v>
       </c>
     </row>
     <row r="303" spans="1:2">
@@ -3877,7 +3886,7 @@
         <v>303</v>
       </c>
       <c r="B303" s="1">
-        <v>168.5830618040611</v>
+        <v>159.9634167640314</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -3885,7 +3894,7 @@
         <v>304</v>
       </c>
       <c r="B304" s="1">
-        <v>168.8473280582695</v>
+        <v>161.271886214352</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -3893,7 +3902,7 @@
         <v>305</v>
       </c>
       <c r="B305" s="1">
-        <v>169.569958645074</v>
+        <v>161.7244857802673</v>
       </c>
     </row>
     <row r="306" spans="1:2">
@@ -3901,7 +3910,7 @@
         <v>306</v>
       </c>
       <c r="B306" s="1">
-        <v>169.7751111731096</v>
+        <v>162.0177366423817</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -3909,7 +3918,7 @@
         <v>307</v>
       </c>
       <c r="B307" s="1">
-        <v>171.2303477982725</v>
+        <v>162.983220167706</v>
       </c>
     </row>
     <row r="308" spans="1:2">
@@ -3917,7 +3926,7 @@
         <v>308</v>
       </c>
       <c r="B308" s="1">
-        <v>171.3610885443715</v>
+        <v>163.7094643231712</v>
       </c>
     </row>
     <row r="309" spans="1:2">
@@ -3925,7 +3934,7 @@
         <v>309</v>
       </c>
       <c r="B309" s="1">
-        <v>171.3834076715913</v>
+        <v>163.8084277208574</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -3933,7 +3942,7 @@
         <v>310</v>
       </c>
       <c r="B310" s="1">
-        <v>171.5069524555658</v>
+        <v>164.7327318809673</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -3941,7 +3950,7 @@
         <v>311</v>
       </c>
       <c r="B311" s="1">
-        <v>172.1930507445375</v>
+        <v>165.5071257169221</v>
       </c>
     </row>
     <row r="312" spans="1:2">
@@ -3949,7 +3958,7 @@
         <v>312</v>
       </c>
       <c r="B312" s="1">
-        <v>173.4849246897927</v>
+        <v>165.6083176441935</v>
       </c>
     </row>
     <row r="313" spans="1:2">
@@ -3957,7 +3966,7 @@
         <v>313</v>
       </c>
       <c r="B313" s="1">
-        <v>173.6843377166255</v>
+        <v>167.2049992555237</v>
       </c>
     </row>
     <row r="314" spans="1:2">
@@ -3965,7 +3974,7 @@
         <v>314</v>
       </c>
       <c r="B314" s="1">
-        <v>176.106665002642</v>
+        <v>168.4929689948519</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -3973,7 +3982,7 @@
         <v>315</v>
       </c>
       <c r="B315" s="1">
-        <v>176.2191038326404</v>
+        <v>169.3487770323608</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -3981,7 +3990,7 @@
         <v>316</v>
       </c>
       <c r="B316" s="1">
-        <v>176.3421800122788</v>
+        <v>169.4788705640971</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -3989,7 +3998,7 @@
         <v>317</v>
       </c>
       <c r="B317" s="1">
-        <v>176.3934583053485</v>
+        <v>170.3714337103268</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -3997,7 +4006,7 @@
         <v>318</v>
       </c>
       <c r="B318" s="1">
-        <v>176.5697582215314</v>
+        <v>171.6247865032925</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -4005,7 +4014,7 @@
         <v>319</v>
       </c>
       <c r="B319" s="1">
-        <v>179.0540639253095</v>
+        <v>172.0937866526471</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -4013,7 +4022,7 @@
         <v>320</v>
       </c>
       <c r="B320" s="1">
-        <v>179.0828002320318</v>
+        <v>172.1902516245763</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -4021,7 +4030,7 @@
         <v>321</v>
       </c>
       <c r="B321" s="1">
-        <v>179.3955449688171</v>
+        <v>172.4399357066671</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -4029,7 +4038,7 @@
         <v>322</v>
       </c>
       <c r="B322" s="1">
-        <v>179.9528708860766</v>
+        <v>175.7298073953244</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -4037,7 +4046,7 @@
         <v>323</v>
       </c>
       <c r="B323" s="1">
-        <v>180.7885437032916</v>
+        <v>180.0827365568298</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -4045,7 +4054,7 @@
         <v>324</v>
       </c>
       <c r="B324" s="1">
-        <v>181.769049592862</v>
+        <v>181.797196523146</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -4053,7 +4062,7 @@
         <v>325</v>
       </c>
       <c r="B325" s="1">
-        <v>181.8520538734474</v>
+        <v>182.7114409443364</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -4061,7 +4070,7 @@
         <v>326</v>
       </c>
       <c r="B326" s="1">
-        <v>182.7092600818787</v>
+        <v>185.1023422931817</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -4069,7 +4078,7 @@
         <v>327</v>
       </c>
       <c r="B327" s="1">
-        <v>183.0309939841841</v>
+        <v>186.3378649961078</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -4077,7 +4086,7 @@
         <v>328</v>
       </c>
       <c r="B328" s="1">
-        <v>183.7362501843911</v>
+        <v>186.5350455563866</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -4085,7 +4094,7 @@
         <v>329</v>
       </c>
       <c r="B329" s="1">
-        <v>184.6115878067162</v>
+        <v>187.0004646974953</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -4093,7 +4102,7 @@
         <v>330</v>
       </c>
       <c r="B330" s="1">
-        <v>185.797028901293</v>
+        <v>187.424600436858</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -4101,7 +4110,7 @@
         <v>331</v>
       </c>
       <c r="B331" s="1">
-        <v>187.2881717988011</v>
+        <v>188.1464529940239</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -4109,7 +4118,7 @@
         <v>332</v>
       </c>
       <c r="B332" s="1">
-        <v>187.2934803997703</v>
+        <v>189.8005032163167</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -4117,7 +4126,7 @@
         <v>333</v>
       </c>
       <c r="B333" s="1">
-        <v>188.685004672909</v>
+        <v>193.4035075032654</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -4125,7 +4134,7 @@
         <v>334</v>
       </c>
       <c r="B334" s="1">
-        <v>190.2960194510896</v>
+        <v>193.7459530378031</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -4133,7 +4142,7 @@
         <v>335</v>
       </c>
       <c r="B335" s="1">
-        <v>197.0451901302592</v>
+        <v>198.4079176638729</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -4141,7 +4150,7 @@
         <v>336</v>
       </c>
       <c r="B336" s="1">
-        <v>199.9816014755285</v>
+        <v>199.2459657552803</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -4149,7 +4158,7 @@
         <v>337</v>
       </c>
       <c r="B337" s="1">
-        <v>203.1962413713083</v>
+        <v>201.9134151446149</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -4157,7 +4166,7 @@
         <v>338</v>
       </c>
       <c r="B338" s="1">
-        <v>203.2694189808431</v>
+        <v>202.1041236781414</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -4165,7 +4174,7 @@
         <v>339</v>
       </c>
       <c r="B339" s="1">
-        <v>210.7611920516861</v>
+        <v>202.1545778035803</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -4173,7 +4182,7 @@
         <v>340</v>
       </c>
       <c r="B340" s="1">
-        <v>212.6533800649105</v>
+        <v>209.3392467587773</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -4181,7 +4190,7 @@
         <v>341</v>
       </c>
       <c r="B341" s="1">
-        <v>216.2559771279986</v>
+        <v>210.78363520465</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -4189,7 +4198,7 @@
         <v>342</v>
       </c>
       <c r="B342" s="1">
-        <v>218.9711439338221</v>
+        <v>210.7993659480594</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -4197,7 +4206,7 @@
         <v>343</v>
       </c>
       <c r="B343" s="1">
-        <v>226.29352222788</v>
+        <v>213.4429273079405</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -4205,7 +4214,7 @@
         <v>344</v>
       </c>
       <c r="B344" s="1">
-        <v>226.718580420727</v>
+        <v>217.0080003718516</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -4213,7 +4222,7 @@
         <v>345</v>
       </c>
       <c r="B345" s="1">
-        <v>228.1172065735038</v>
+        <v>218.3231152978015</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -4221,7 +4230,7 @@
         <v>346</v>
       </c>
       <c r="B346" s="1">
-        <v>234.7552941379554</v>
+        <v>218.5788222250409</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -4229,7 +4238,7 @@
         <v>347</v>
       </c>
       <c r="B347" s="1">
-        <v>238.3157264530728</v>
+        <v>220.677249406837</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -4237,7 +4246,7 @@
         <v>348</v>
       </c>
       <c r="B348" s="1">
-        <v>245.1883556724339</v>
+        <v>220.9878353105352</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -4245,7 +4254,7 @@
         <v>349</v>
       </c>
       <c r="B349" s="1">
-        <v>254.365041267413</v>
+        <v>222.3549735307382</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -4253,7 +4262,7 @@
         <v>350</v>
       </c>
       <c r="B350" s="1">
-        <v>263.5699503676062</v>
+        <v>231.1366346494183</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -4261,7 +4270,7 @@
         <v>351</v>
       </c>
       <c r="B351" s="1">
-        <v>263.7833350078593</v>
+        <v>233.2057634101486</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -4269,7 +4278,7 @@
         <v>352</v>
       </c>
       <c r="B352" s="1">
-        <v>286.4049839345308</v>
+        <v>240.9037995370595</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -4277,7 +4286,7 @@
         <v>353</v>
       </c>
       <c r="B353" s="1">
-        <v>289.9623432136356</v>
+        <v>241.9801397446898</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -4285,7 +4294,7 @@
         <v>354</v>
       </c>
       <c r="B354" s="1">
-        <v>338.2022991448598</v>
+        <v>255.1950520930116</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -4293,7 +4302,7 @@
         <v>355</v>
       </c>
       <c r="B355" s="1">
-        <v>370.5432729139933</v>
+        <v>274.3894448654654</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -4301,7 +4310,7 @@
         <v>356</v>
       </c>
       <c r="B356" s="1">
-        <v>386.8433205312426</v>
+        <v>322.7169382634154</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -4309,7 +4318,7 @@
         <v>357</v>
       </c>
       <c r="B357" s="1">
-        <v>395.9826511659476</v>
+        <v>336.5309966365377</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -4317,7 +4326,7 @@
         <v>358</v>
       </c>
       <c r="B358" s="1">
-        <v>414.7981944984094</v>
+        <v>342.6013602293594</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -4325,7 +4334,7 @@
         <v>359</v>
       </c>
       <c r="B359" s="1">
-        <v>499.3971298722361</v>
+        <v>351.853047395245</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -4333,7 +4342,7 @@
         <v>360</v>
       </c>
       <c r="B360" s="1">
-        <v>554.9279657808423</v>
+        <v>371.1404354059238</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -4341,7 +4350,7 @@
         <v>361</v>
       </c>
       <c r="B361" s="1">
-        <v>586.0828333398433</v>
+        <v>392.6150703737437</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -4349,7 +4358,31 @@
         <v>362</v>
       </c>
       <c r="B362" s="1">
-        <v>827.7228735954943</v>
+        <v>463.9789720453022</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2">
+      <c r="A363" t="s">
+        <v>363</v>
+      </c>
+      <c r="B363" s="1">
+        <v>555.4575109929298</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2">
+      <c r="A364" t="s">
+        <v>364</v>
+      </c>
+      <c r="B364" s="1">
+        <v>584.1406074220556</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2">
+      <c r="A365" t="s">
+        <v>365</v>
+      </c>
+      <c r="B365" s="1">
+        <v>780.6369087437845</v>
       </c>
     </row>
   </sheetData>

--- a/Screener/data/rs_rating_top_30.xlsx
+++ b/Screener/data/rs_rating_top_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="699">
   <si>
     <t>Symbol</t>
   </si>
@@ -22,1096 +22,2095 @@
     <t>RS Rating</t>
   </si>
   <si>
+    <t>NPO</t>
+  </si>
+  <si>
+    <t>NWSA</t>
+  </si>
+  <si>
+    <t>CSAN</t>
+  </si>
+  <si>
+    <t>GWRE</t>
+  </si>
+  <si>
+    <t>INTU</t>
+  </si>
+  <si>
+    <t>ENLC</t>
+  </si>
+  <si>
+    <t>UBA</t>
+  </si>
+  <si>
+    <t>ALC</t>
+  </si>
+  <si>
+    <t>AR</t>
+  </si>
+  <si>
+    <t>ESQ</t>
+  </si>
+  <si>
+    <t>WMB</t>
+  </si>
+  <si>
+    <t>MTACU</t>
+  </si>
+  <si>
+    <t>SWI</t>
+  </si>
+  <si>
+    <t>KE</t>
+  </si>
+  <si>
+    <t>ALRM</t>
+  </si>
+  <si>
+    <t>EVTC</t>
+  </si>
+  <si>
+    <t>OMAB</t>
+  </si>
+  <si>
+    <t>DBX</t>
+  </si>
+  <si>
+    <t>BFST</t>
+  </si>
+  <si>
+    <t>SBS</t>
+  </si>
+  <si>
+    <t>VMC</t>
+  </si>
+  <si>
+    <t>STE</t>
+  </si>
+  <si>
+    <t>ABST</t>
+  </si>
+  <si>
+    <t>PBR</t>
+  </si>
+  <si>
+    <t>HEAR</t>
+  </si>
+  <si>
+    <t>MSM</t>
+  </si>
+  <si>
+    <t>SHW</t>
+  </si>
+  <si>
+    <t>BWXT</t>
+  </si>
+  <si>
+    <t>MCK</t>
+  </si>
+  <si>
+    <t>VSH</t>
+  </si>
+  <si>
+    <t>GFF</t>
+  </si>
+  <si>
+    <t>HWM</t>
+  </si>
+  <si>
+    <t>HY</t>
+  </si>
+  <si>
+    <t>RUSHB</t>
+  </si>
+  <si>
+    <t>PMGMU</t>
+  </si>
+  <si>
+    <t>CEN</t>
+  </si>
+  <si>
+    <t>WTM</t>
+  </si>
+  <si>
+    <t>BLMN</t>
+  </si>
+  <si>
+    <t>BBW</t>
+  </si>
+  <si>
+    <t>TIPT</t>
+  </si>
+  <si>
+    <t>SLG</t>
+  </si>
+  <si>
+    <t>MTSI</t>
+  </si>
+  <si>
+    <t>CMC</t>
+  </si>
+  <si>
+    <t>DHI</t>
+  </si>
+  <si>
+    <t>RUSHA</t>
+  </si>
+  <si>
+    <t>ZNTL</t>
+  </si>
+  <si>
+    <t>NWS</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>AIZ</t>
+  </si>
+  <si>
+    <t>PPC</t>
+  </si>
+  <si>
+    <t>GGAAU</t>
+  </si>
+  <si>
+    <t>TBBK</t>
+  </si>
+  <si>
+    <t>APOG</t>
+  </si>
+  <si>
+    <t>KTB</t>
+  </si>
+  <si>
+    <t>ML</t>
+  </si>
+  <si>
+    <t>SNPS</t>
+  </si>
+  <si>
+    <t>ETD</t>
+  </si>
+  <si>
+    <t>DXPE</t>
+  </si>
+  <si>
+    <t>INFU</t>
+  </si>
+  <si>
+    <t>DDOG</t>
+  </si>
+  <si>
+    <t>BIGC</t>
+  </si>
+  <si>
+    <t>DOOR</t>
+  </si>
+  <si>
+    <t>XPEL</t>
+  </si>
+  <si>
+    <t>CMRE</t>
+  </si>
+  <si>
+    <t>MATW</t>
+  </si>
+  <si>
+    <t>URI</t>
+  </si>
+  <si>
+    <t>CPNG</t>
+  </si>
+  <si>
+    <t>MUSA</t>
+  </si>
+  <si>
+    <t>DKS</t>
+  </si>
+  <si>
+    <t>MDGL</t>
+  </si>
+  <si>
+    <t>RCLFU</t>
+  </si>
+  <si>
+    <t>MLM</t>
+  </si>
+  <si>
+    <t>THC</t>
+  </si>
+  <si>
+    <t>PGTI</t>
+  </si>
+  <si>
+    <t>TNC</t>
+  </si>
+  <si>
+    <t>TJX</t>
+  </si>
+  <si>
+    <t>LZB</t>
+  </si>
+  <si>
+    <t>INSM</t>
+  </si>
+  <si>
+    <t>WHD</t>
+  </si>
+  <si>
+    <t>IDCC</t>
+  </si>
+  <si>
+    <t>PATK</t>
+  </si>
+  <si>
+    <t>ON</t>
+  </si>
+  <si>
+    <t>GYRO</t>
+  </si>
+  <si>
+    <t>GMS</t>
+  </si>
+  <si>
+    <t>FLYW</t>
+  </si>
+  <si>
+    <t>CR</t>
+  </si>
+  <si>
+    <t>MUR</t>
+  </si>
+  <si>
+    <t>TCBX</t>
+  </si>
+  <si>
+    <t>PCYO</t>
+  </si>
+  <si>
+    <t>ICFI</t>
+  </si>
+  <si>
+    <t>TRU</t>
+  </si>
+  <si>
+    <t>ERII</t>
+  </si>
+  <si>
+    <t>NYT</t>
+  </si>
+  <si>
+    <t>DPZ</t>
+  </si>
+  <si>
+    <t>BLKB</t>
+  </si>
+  <si>
+    <t>JBI</t>
+  </si>
+  <si>
+    <t>ETNB</t>
+  </si>
+  <si>
+    <t>NOV</t>
+  </si>
+  <si>
+    <t>SFL</t>
+  </si>
+  <si>
+    <t>HMC</t>
+  </si>
+  <si>
+    <t>NATI</t>
+  </si>
+  <si>
+    <t>TPX</t>
+  </si>
+  <si>
+    <t>IMAX</t>
+  </si>
+  <si>
+    <t>FINW</t>
+  </si>
+  <si>
+    <t>GO</t>
+  </si>
+  <si>
+    <t>STER</t>
+  </si>
+  <si>
+    <t>AMEH</t>
+  </si>
+  <si>
+    <t>EHC</t>
+  </si>
+  <si>
+    <t>CDRE</t>
+  </si>
+  <si>
+    <t>DUOL</t>
+  </si>
+  <si>
+    <t>ENTG</t>
+  </si>
+  <si>
+    <t>TRIN</t>
+  </si>
+  <si>
+    <t>SLB</t>
+  </si>
+  <si>
+    <t>HQY</t>
+  </si>
+  <si>
+    <t>ARCE</t>
+  </si>
+  <si>
+    <t>KEX</t>
+  </si>
+  <si>
+    <t>PSX</t>
+  </si>
+  <si>
+    <t>KOP</t>
+  </si>
+  <si>
+    <t>RNGR</t>
+  </si>
+  <si>
+    <t>VRRM</t>
+  </si>
+  <si>
+    <t>CAL</t>
+  </si>
+  <si>
+    <t>OLED</t>
+  </si>
+  <si>
+    <t>LBRT</t>
+  </si>
+  <si>
+    <t>BELFB</t>
+  </si>
+  <si>
+    <t>HNI</t>
+  </si>
+  <si>
+    <t>SQSP</t>
+  </si>
+  <si>
+    <t>RYTM</t>
+  </si>
+  <si>
+    <t>TDG</t>
+  </si>
+  <si>
+    <t>KSS</t>
+  </si>
+  <si>
+    <t>BWMN</t>
+  </si>
+  <si>
+    <t>NOW</t>
+  </si>
+  <si>
+    <t>HAL</t>
+  </si>
+  <si>
+    <t>STN</t>
+  </si>
+  <si>
+    <t>HUBB</t>
+  </si>
+  <si>
+    <t>WDAY</t>
+  </si>
+  <si>
+    <t>MTH</t>
+  </si>
+  <si>
+    <t>NECB</t>
+  </si>
+  <si>
+    <t>DLX</t>
+  </si>
+  <si>
+    <t>TPL</t>
+  </si>
+  <si>
+    <t>DAC</t>
+  </si>
+  <si>
+    <t>AKAM</t>
+  </si>
+  <si>
+    <t>BVH</t>
+  </si>
+  <si>
+    <t>ATVI</t>
+  </si>
+  <si>
+    <t>ATRO</t>
+  </si>
+  <si>
+    <t>SGEN</t>
+  </si>
+  <si>
+    <t>SHAK</t>
+  </si>
+  <si>
+    <t>WLK</t>
+  </si>
+  <si>
+    <t>QTWO</t>
+  </si>
+  <si>
+    <t>ZEUS</t>
+  </si>
+  <si>
+    <t>AM</t>
+  </si>
+  <si>
+    <t>DIT</t>
+  </si>
+  <si>
+    <t>DLR</t>
+  </si>
+  <si>
+    <t>RACE</t>
+  </si>
+  <si>
+    <t>TTWO</t>
+  </si>
+  <si>
+    <t>BHWB</t>
+  </si>
+  <si>
+    <t>AIR</t>
+  </si>
+  <si>
+    <t>SUM</t>
+  </si>
+  <si>
+    <t>UFPI</t>
+  </si>
+  <si>
+    <t>AEIS</t>
+  </si>
+  <si>
+    <t>PBAM</t>
+  </si>
+  <si>
+    <t>LOGI</t>
+  </si>
+  <si>
+    <t>MTAL</t>
+  </si>
+  <si>
+    <t>FWRG</t>
+  </si>
+  <si>
+    <t>PTGX</t>
+  </si>
+  <si>
+    <t>PCAR</t>
+  </si>
+  <si>
+    <t>VNT</t>
+  </si>
+  <si>
+    <t>MTDR</t>
+  </si>
+  <si>
+    <t>PMGM</t>
+  </si>
+  <si>
+    <t>OSIS</t>
+  </si>
+  <si>
+    <t>STEP</t>
+  </si>
+  <si>
+    <t>REX</t>
+  </si>
+  <si>
+    <t>TRGP</t>
+  </si>
+  <si>
+    <t>GCBC</t>
+  </si>
+  <si>
+    <t>CPRT</t>
+  </si>
+  <si>
+    <t>MEDP</t>
+  </si>
+  <si>
+    <t>CRWD</t>
+  </si>
+  <si>
+    <t>CAT</t>
+  </si>
+  <si>
+    <t>HCI</t>
+  </si>
+  <si>
+    <t>CRM</t>
+  </si>
+  <si>
+    <t>BATRA</t>
+  </si>
+  <si>
+    <t>OSK</t>
+  </si>
+  <si>
+    <t>UNM</t>
+  </si>
+  <si>
+    <t>RCM</t>
+  </si>
+  <si>
+    <t>EXP</t>
+  </si>
+  <si>
+    <t>QCRH</t>
+  </si>
+  <si>
+    <t>LZRFY</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>MGPI</t>
+  </si>
+  <si>
+    <t>GH</t>
+  </si>
+  <si>
+    <t>VRNS</t>
+  </si>
+  <si>
+    <t>RPM</t>
+  </si>
+  <si>
+    <t>GRC</t>
+  </si>
+  <si>
+    <t>TGH</t>
+  </si>
+  <si>
+    <t>UBS</t>
+  </si>
+  <si>
+    <t>UFPT</t>
+  </si>
+  <si>
+    <t>TNP</t>
+  </si>
+  <si>
+    <t>GNTX</t>
+  </si>
+  <si>
+    <t>GRFS</t>
+  </si>
+  <si>
+    <t>MAR</t>
+  </si>
+  <si>
+    <t>TNK</t>
+  </si>
+  <si>
+    <t>PLAB</t>
+  </si>
+  <si>
+    <t>OPCH</t>
+  </si>
+  <si>
+    <t>HLF</t>
+  </si>
+  <si>
+    <t>BFAM</t>
+  </si>
+  <si>
+    <t>FRO</t>
+  </si>
+  <si>
+    <t>NTES</t>
+  </si>
+  <si>
+    <t>IBKR</t>
+  </si>
+  <si>
+    <t>INSW</t>
+  </si>
+  <si>
+    <t>ARNC</t>
+  </si>
+  <si>
+    <t>RKT</t>
+  </si>
+  <si>
+    <t>ROAD</t>
+  </si>
+  <si>
+    <t>APA</t>
+  </si>
+  <si>
+    <t>CSWC</t>
+  </si>
+  <si>
+    <t>OFG</t>
+  </si>
+  <si>
+    <t>TPH</t>
+  </si>
+  <si>
+    <t>GPI</t>
+  </si>
+  <si>
+    <t>AMD</t>
+  </si>
+  <si>
+    <t>JBL</t>
+  </si>
+  <si>
+    <t>GOLF</t>
+  </si>
+  <si>
+    <t>ENVX</t>
+  </si>
+  <si>
+    <t>TMST</t>
+  </si>
+  <si>
+    <t>ACT</t>
+  </si>
+  <si>
+    <t>GXO</t>
+  </si>
+  <si>
+    <t>FTDR</t>
+  </si>
+  <si>
+    <t>SPB</t>
+  </si>
+  <si>
+    <t>SKT</t>
+  </si>
+  <si>
+    <t>DBRG</t>
+  </si>
+  <si>
+    <t>QLYS</t>
+  </si>
+  <si>
+    <t>ALGN</t>
+  </si>
+  <si>
+    <t>SRV</t>
+  </si>
+  <si>
+    <t>AZTA</t>
+  </si>
+  <si>
+    <t>PLUS</t>
+  </si>
+  <si>
+    <t>NHC</t>
+  </si>
+  <si>
+    <t>TMHC</t>
+  </si>
+  <si>
+    <t>ERO</t>
+  </si>
+  <si>
+    <t>FMS</t>
+  </si>
+  <si>
+    <t>KD</t>
+  </si>
+  <si>
+    <t>BKR</t>
+  </si>
+  <si>
+    <t>PH</t>
+  </si>
+  <si>
+    <t>RS</t>
+  </si>
+  <si>
+    <t>ARES</t>
+  </si>
+  <si>
+    <t>BRO</t>
+  </si>
+  <si>
+    <t>TARO</t>
+  </si>
+  <si>
+    <t>SWBI</t>
+  </si>
+  <si>
+    <t>SHEN</t>
+  </si>
+  <si>
+    <t>RDN</t>
+  </si>
+  <si>
+    <t>PWP</t>
+  </si>
+  <si>
+    <t>TRNS</t>
+  </si>
+  <si>
+    <t>VRSK</t>
+  </si>
+  <si>
+    <t>NSIT</t>
+  </si>
+  <si>
+    <t>DCBO</t>
+  </si>
+  <si>
+    <t>STRT</t>
+  </si>
+  <si>
+    <t>SMHI</t>
+  </si>
+  <si>
+    <t>APO</t>
+  </si>
+  <si>
+    <t>UBP</t>
+  </si>
+  <si>
+    <t>CARR</t>
+  </si>
+  <si>
+    <t>TFII</t>
+  </si>
+  <si>
+    <t>KNSL</t>
+  </si>
+  <si>
+    <t>PRI</t>
+  </si>
+  <si>
+    <t>CNXN</t>
+  </si>
+  <si>
+    <t>MDC</t>
+  </si>
+  <si>
+    <t>ATI</t>
+  </si>
+  <si>
+    <t>LZ</t>
+  </si>
+  <si>
+    <t>RILY</t>
+  </si>
+  <si>
+    <t>HTGC</t>
+  </si>
+  <si>
+    <t>BECN</t>
+  </si>
+  <si>
+    <t>WINA</t>
+  </si>
+  <si>
+    <t>KLAC</t>
+  </si>
+  <si>
+    <t>VAL</t>
+  </si>
+  <si>
+    <t>CRH</t>
+  </si>
+  <si>
+    <t>NTRA</t>
+  </si>
+  <si>
+    <t>OVV</t>
+  </si>
+  <si>
+    <t>ESNT</t>
+  </si>
+  <si>
+    <t>CSTM</t>
+  </si>
+  <si>
+    <t>XM</t>
+  </si>
+  <si>
+    <t>FLT</t>
+  </si>
+  <si>
+    <t>CW</t>
+  </si>
+  <si>
+    <t>AXR</t>
+  </si>
+  <si>
+    <t>CHTR</t>
+  </si>
+  <si>
+    <t>ORCL</t>
+  </si>
+  <si>
+    <t>PSTG</t>
+  </si>
+  <si>
+    <t>IMVT</t>
+  </si>
+  <si>
+    <t>CMCSA</t>
+  </si>
+  <si>
+    <t>AN</t>
+  </si>
+  <si>
+    <t>NVT</t>
+  </si>
+  <si>
+    <t>PAGP</t>
+  </si>
+  <si>
+    <t>VVI</t>
+  </si>
+  <si>
+    <t>GLRE</t>
+  </si>
+  <si>
+    <t>DASH</t>
+  </si>
+  <si>
+    <t>EXEL</t>
+  </si>
+  <si>
+    <t>GPN</t>
+  </si>
+  <si>
+    <t>DVA</t>
+  </si>
+  <si>
+    <t>MTG</t>
+  </si>
+  <si>
+    <t>YETI</t>
+  </si>
+  <si>
+    <t>OBT</t>
+  </si>
+  <si>
+    <t>MAT</t>
+  </si>
+  <si>
+    <t>PAR</t>
+  </si>
+  <si>
+    <t>BG</t>
+  </si>
+  <si>
+    <t>PAG</t>
+  </si>
+  <si>
+    <t>CPRI</t>
+  </si>
+  <si>
+    <t>AMWD</t>
+  </si>
+  <si>
+    <t>SFM</t>
+  </si>
+  <si>
+    <t>KBH</t>
+  </si>
+  <si>
+    <t>MVBF</t>
+  </si>
+  <si>
+    <t>WDFC</t>
+  </si>
+  <si>
+    <t>CCF</t>
+  </si>
+  <si>
+    <t>GOGN</t>
+  </si>
+  <si>
+    <t>FICO</t>
+  </si>
+  <si>
+    <t>AZZ</t>
+  </si>
+  <si>
+    <t>GIII</t>
+  </si>
+  <si>
+    <t>BR</t>
+  </si>
+  <si>
+    <t>VNO</t>
+  </si>
+  <si>
+    <t>ACEL</t>
+  </si>
+  <si>
+    <t>ONON</t>
+  </si>
+  <si>
+    <t>RRC</t>
+  </si>
+  <si>
+    <t>MMP</t>
+  </si>
+  <si>
+    <t>AMR</t>
+  </si>
+  <si>
+    <t>HOFT</t>
+  </si>
+  <si>
+    <t>NUVL</t>
+  </si>
+  <si>
+    <t>BRZE</t>
+  </si>
+  <si>
+    <t>SGH</t>
+  </si>
+  <si>
+    <t>LAD</t>
+  </si>
+  <si>
+    <t>SHC</t>
+  </si>
+  <si>
+    <t>TOL</t>
+  </si>
+  <si>
+    <t>MANH</t>
+  </si>
+  <si>
+    <t>CVI</t>
+  </si>
+  <si>
+    <t>LEGN</t>
+  </si>
+  <si>
+    <t>VERX</t>
+  </si>
+  <si>
+    <t>CXM</t>
+  </si>
+  <si>
+    <t>PAA</t>
+  </si>
+  <si>
+    <t>MPX</t>
+  </si>
+  <si>
+    <t>ZWS</t>
+  </si>
+  <si>
+    <t>PSN</t>
+  </si>
+  <si>
+    <t>KNSA</t>
+  </si>
+  <si>
+    <t>WWD</t>
+  </si>
+  <si>
+    <t>ACA</t>
+  </si>
+  <si>
+    <t>TW</t>
+  </si>
+  <si>
+    <t>CRS</t>
+  </si>
+  <si>
+    <t>OSTK</t>
+  </si>
+  <si>
+    <t>ASTE</t>
+  </si>
+  <si>
+    <t>PDCO</t>
+  </si>
+  <si>
+    <t>PUMP</t>
+  </si>
+  <si>
+    <t>HLNE</t>
+  </si>
+  <si>
+    <t>TTD</t>
+  </si>
+  <si>
+    <t>THO</t>
+  </si>
+  <si>
+    <t>CSPI</t>
+  </si>
+  <si>
+    <t>GSHD</t>
+  </si>
+  <si>
+    <t>USLM</t>
+  </si>
+  <si>
+    <t>EVI</t>
+  </si>
+  <si>
+    <t>RVMD</t>
+  </si>
+  <si>
+    <t>GOOG</t>
+  </si>
+  <si>
+    <t>PBF</t>
+  </si>
+  <si>
+    <t>GOOGL</t>
+  </si>
+  <si>
+    <t>AEO</t>
+  </si>
+  <si>
+    <t>OII</t>
+  </si>
+  <si>
+    <t>ACMR</t>
+  </si>
+  <si>
+    <t>GGAL</t>
+  </si>
+  <si>
+    <t>ESCA</t>
+  </si>
+  <si>
+    <t>NMIH</t>
+  </si>
+  <si>
+    <t>OTTR</t>
+  </si>
+  <si>
+    <t>NCR</t>
+  </si>
+  <si>
+    <t>RDNT</t>
+  </si>
+  <si>
+    <t>HEP</t>
+  </si>
+  <si>
+    <t>CRVL</t>
+  </si>
+  <si>
+    <t>MRVL</t>
+  </si>
+  <si>
+    <t>PNR</t>
+  </si>
+  <si>
+    <t>ERIE</t>
+  </si>
+  <si>
+    <t>MSTR</t>
+  </si>
+  <si>
+    <t>MSA</t>
+  </si>
+  <si>
+    <t>COKE</t>
+  </si>
+  <si>
+    <t>SPOK</t>
+  </si>
+  <si>
+    <t>PWR</t>
+  </si>
+  <si>
+    <t>GTLS</t>
+  </si>
+  <si>
+    <t>BCSF</t>
+  </si>
+  <si>
+    <t>PDS</t>
+  </si>
+  <si>
+    <t>FDX</t>
+  </si>
+  <si>
+    <t>SDGR</t>
+  </si>
+  <si>
     <t>NEOG</t>
   </si>
   <si>
-    <t>CVGI</t>
-  </si>
-  <si>
-    <t>RVMD</t>
+    <t>GBLI</t>
+  </si>
+  <si>
+    <t>CRMT</t>
+  </si>
+  <si>
+    <t>GLBE</t>
+  </si>
+  <si>
+    <t>MPC</t>
+  </si>
+  <si>
+    <t>WOR</t>
+  </si>
+  <si>
+    <t>URBN</t>
+  </si>
+  <si>
+    <t>EXAS</t>
+  </si>
+  <si>
+    <t>CHX</t>
+  </si>
+  <si>
+    <t>MLR</t>
+  </si>
+  <si>
+    <t>AMAT</t>
+  </si>
+  <si>
+    <t>NEX</t>
+  </si>
+  <si>
+    <t>NVO</t>
+  </si>
+  <si>
+    <t>FMX</t>
+  </si>
+  <si>
+    <t>CLH</t>
+  </si>
+  <si>
+    <t>STRS</t>
+  </si>
+  <si>
+    <t>ETN</t>
+  </si>
+  <si>
+    <t>PANW</t>
+  </si>
+  <si>
+    <t>DELL</t>
+  </si>
+  <si>
+    <t>NEWR</t>
+  </si>
+  <si>
+    <t>BUR</t>
+  </si>
+  <si>
+    <t>PRDO</t>
+  </si>
+  <si>
+    <t>LOB</t>
+  </si>
+  <si>
+    <t>SOI</t>
+  </si>
+  <si>
+    <t>ARCB</t>
+  </si>
+  <si>
+    <t>NVMI</t>
+  </si>
+  <si>
+    <t>GIC</t>
+  </si>
+  <si>
+    <t>ODFL</t>
+  </si>
+  <si>
+    <t>RH</t>
+  </si>
+  <si>
+    <t>NOG</t>
+  </si>
+  <si>
+    <t>APG</t>
+  </si>
+  <si>
+    <t>CNK</t>
+  </si>
+  <si>
+    <t>CIVI</t>
+  </si>
+  <si>
+    <t>HURN</t>
+  </si>
+  <si>
+    <t>BMI</t>
+  </si>
+  <si>
+    <t>NYCB</t>
+  </si>
+  <si>
+    <t>JHX</t>
+  </si>
+  <si>
+    <t>ADDYY</t>
+  </si>
+  <si>
+    <t>IRMD</t>
+  </si>
+  <si>
+    <t>LTRPB</t>
+  </si>
+  <si>
+    <t>GRVY</t>
+  </si>
+  <si>
+    <t>TREX</t>
+  </si>
+  <si>
+    <t>MYRG</t>
+  </si>
+  <si>
+    <t>BRBR</t>
+  </si>
+  <si>
+    <t>RDY</t>
+  </si>
+  <si>
+    <t>ABR</t>
+  </si>
+  <si>
+    <t>BKNG</t>
+  </si>
+  <si>
+    <t>VST</t>
+  </si>
+  <si>
+    <t>HNRG</t>
+  </si>
+  <si>
+    <t>ACU</t>
+  </si>
+  <si>
+    <t>DECK</t>
+  </si>
+  <si>
+    <t>HUBS</t>
+  </si>
+  <si>
+    <t>DVAX</t>
+  </si>
+  <si>
+    <t>WWE</t>
+  </si>
+  <si>
+    <t>ALSN</t>
+  </si>
+  <si>
+    <t>HAYW</t>
+  </si>
+  <si>
+    <t>BOOT</t>
+  </si>
+  <si>
+    <t>ACVA</t>
+  </si>
+  <si>
+    <t>RAMP</t>
+  </si>
+  <si>
+    <t>AZEK</t>
+  </si>
+  <si>
+    <t>COOP</t>
+  </si>
+  <si>
+    <t>RIVN</t>
+  </si>
+  <si>
+    <t>WST</t>
+  </si>
+  <si>
+    <t>ANET</t>
+  </si>
+  <si>
+    <t>LII</t>
+  </si>
+  <si>
+    <t>LRCX</t>
+  </si>
+  <si>
+    <t>EQT</t>
+  </si>
+  <si>
+    <t>VEL</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>FRPT</t>
+  </si>
+  <si>
+    <t>BKI</t>
+  </si>
+  <si>
+    <t>PAM</t>
+  </si>
+  <si>
+    <t>AMZN</t>
+  </si>
+  <si>
+    <t>YPF</t>
+  </si>
+  <si>
+    <t>HELE</t>
   </si>
   <si>
     <t>TNET</t>
   </si>
   <si>
-    <t>ARHS</t>
-  </si>
-  <si>
-    <t>HURN</t>
-  </si>
-  <si>
-    <t>GMS</t>
-  </si>
-  <si>
-    <t>HSKA</t>
-  </si>
-  <si>
-    <t>THC</t>
-  </si>
-  <si>
-    <t>GOCO</t>
-  </si>
-  <si>
-    <t>ALSN</t>
-  </si>
-  <si>
-    <t>CCAP</t>
-  </si>
-  <si>
-    <t>DUOL</t>
+    <t>PRO</t>
+  </si>
+  <si>
+    <t>IBP</t>
+  </si>
+  <si>
+    <t>TYRA</t>
+  </si>
+  <si>
+    <t>CYD</t>
+  </si>
+  <si>
+    <t>IGIC</t>
+  </si>
+  <si>
+    <t>LEU</t>
+  </si>
+  <si>
+    <t>OC</t>
+  </si>
+  <si>
+    <t>VMW</t>
+  </si>
+  <si>
+    <t>ZGN</t>
+  </si>
+  <si>
+    <t>LYTS</t>
+  </si>
+  <si>
+    <t>KRUS</t>
+  </si>
+  <si>
+    <t>CNM</t>
+  </si>
+  <si>
+    <t>ANDE</t>
+  </si>
+  <si>
+    <t>TAYD</t>
+  </si>
+  <si>
+    <t>ROIV</t>
+  </si>
+  <si>
+    <t>PHG</t>
+  </si>
+  <si>
+    <t>EXPI</t>
+  </si>
+  <si>
+    <t>EB</t>
+  </si>
+  <si>
+    <t>FCAP</t>
+  </si>
+  <si>
+    <t>PKOH</t>
+  </si>
+  <si>
+    <t>BLBD</t>
+  </si>
+  <si>
+    <t>COUR</t>
+  </si>
+  <si>
+    <t>BLX</t>
+  </si>
+  <si>
+    <t>AMNB</t>
+  </si>
+  <si>
+    <t>AGM</t>
+  </si>
+  <si>
+    <t>YELP</t>
+  </si>
+  <si>
+    <t>AEHR</t>
+  </si>
+  <si>
+    <t>ITRN</t>
+  </si>
+  <si>
+    <t>HCCI</t>
+  </si>
+  <si>
+    <t>ESEA</t>
+  </si>
+  <si>
+    <t>ADDDF</t>
+  </si>
+  <si>
+    <t>FRHC</t>
+  </si>
+  <si>
+    <t>KTOS</t>
+  </si>
+  <si>
+    <t>SXI</t>
+  </si>
+  <si>
+    <t>GE</t>
+  </si>
+  <si>
+    <t>AGRO</t>
+  </si>
+  <si>
+    <t>ROKU</t>
+  </si>
+  <si>
+    <t>LAUR</t>
+  </si>
+  <si>
+    <t>NGVC</t>
+  </si>
+  <si>
+    <t>AEL</t>
+  </si>
+  <si>
+    <t>AVGO</t>
+  </si>
+  <si>
+    <t>NEU</t>
+  </si>
+  <si>
+    <t>STVN</t>
+  </si>
+  <si>
+    <t>OLLI</t>
+  </si>
+  <si>
+    <t>ASMIY</t>
+  </si>
+  <si>
+    <t>MORF</t>
+  </si>
+  <si>
+    <t>CSWI</t>
+  </si>
+  <si>
+    <t>VICR</t>
+  </si>
+  <si>
+    <t>PHM</t>
+  </si>
+  <si>
+    <t>BLU</t>
+  </si>
+  <si>
+    <t>GRBK</t>
+  </si>
+  <si>
+    <t>ADBE</t>
+  </si>
+  <si>
+    <t>WMS</t>
+  </si>
+  <si>
+    <t>ONTO</t>
   </si>
   <si>
     <t>TWIN</t>
   </si>
   <si>
-    <t>MSA</t>
-  </si>
-  <si>
-    <t>CARR</t>
-  </si>
-  <si>
-    <t>MYRG</t>
-  </si>
-  <si>
-    <t>ALGN</t>
-  </si>
-  <si>
-    <t>PAG</t>
-  </si>
-  <si>
-    <t>RRC</t>
-  </si>
-  <si>
-    <t>TGH</t>
-  </si>
-  <si>
-    <t>PH</t>
-  </si>
-  <si>
-    <t>PWP</t>
-  </si>
-  <si>
-    <t>PRDO</t>
-  </si>
-  <si>
-    <t>RAMP</t>
-  </si>
-  <si>
-    <t>VST</t>
-  </si>
-  <si>
-    <t>AVGO</t>
-  </si>
-  <si>
-    <t>ZWS</t>
-  </si>
-  <si>
-    <t>HLNE</t>
-  </si>
-  <si>
-    <t>GSHD</t>
-  </si>
-  <si>
-    <t>DBRG</t>
-  </si>
-  <si>
-    <t>FDX</t>
-  </si>
-  <si>
-    <t>SGH</t>
-  </si>
-  <si>
-    <t>OII</t>
-  </si>
-  <si>
-    <t>BATRA</t>
-  </si>
-  <si>
-    <t>CRH</t>
-  </si>
-  <si>
-    <t>TMHC</t>
-  </si>
-  <si>
-    <t>DASH</t>
-  </si>
-  <si>
-    <t>PRI</t>
-  </si>
-  <si>
-    <t>MEDP</t>
+    <t>SPNS</t>
+  </si>
+  <si>
+    <t>ABCM</t>
+  </si>
+  <si>
+    <t>UBER</t>
+  </si>
+  <si>
+    <t>ETHE</t>
+  </si>
+  <si>
+    <t>FIX</t>
+  </si>
+  <si>
+    <t>CVRX</t>
+  </si>
+  <si>
+    <t>AVDL</t>
+  </si>
+  <si>
+    <t>LQDT</t>
+  </si>
+  <si>
+    <t>SCPL</t>
+  </si>
+  <si>
+    <t>SCU</t>
+  </si>
+  <si>
+    <t>SPNT</t>
+  </si>
+  <si>
+    <t>MATX</t>
+  </si>
+  <si>
+    <t>HWKN</t>
+  </si>
+  <si>
+    <t>CCJ</t>
+  </si>
+  <si>
+    <t>ARGX</t>
+  </si>
+  <si>
+    <t>HOV</t>
+  </si>
+  <si>
+    <t>CEIX</t>
+  </si>
+  <si>
+    <t>VIST</t>
+  </si>
+  <si>
+    <t>FEDU</t>
+  </si>
+  <si>
+    <t>NE</t>
+  </si>
+  <si>
+    <t>IMTX</t>
+  </si>
+  <si>
+    <t>RCMT</t>
+  </si>
+  <si>
+    <t>CRC</t>
+  </si>
+  <si>
+    <t>XPRO</t>
+  </si>
+  <si>
+    <t>VRTV</t>
+  </si>
+  <si>
+    <t>FRSH</t>
+  </si>
+  <si>
+    <t>GHL</t>
+  </si>
+  <si>
+    <t>ROCK</t>
+  </si>
+  <si>
+    <t>SSD</t>
+  </si>
+  <si>
+    <t>DICE</t>
+  </si>
+  <si>
+    <t>VECO</t>
+  </si>
+  <si>
+    <t>FLXS</t>
+  </si>
+  <si>
+    <t>AI</t>
+  </si>
+  <si>
+    <t>EXTR</t>
+  </si>
+  <si>
+    <t>FTI</t>
+  </si>
+  <si>
+    <t>ACOR</t>
+  </si>
+  <si>
+    <t>BOOM</t>
+  </si>
+  <si>
+    <t>CCL</t>
+  </si>
+  <si>
+    <t>CIX</t>
+  </si>
+  <si>
+    <t>CUBI</t>
+  </si>
+  <si>
+    <t>AMPH</t>
+  </si>
+  <si>
+    <t>APPF</t>
+  </si>
+  <si>
+    <t>CUK</t>
+  </si>
+  <si>
+    <t>RCL</t>
+  </si>
+  <si>
+    <t>SRDX</t>
+  </si>
+  <si>
+    <t>GBX</t>
+  </si>
+  <si>
+    <t>PRIM</t>
+  </si>
+  <si>
+    <t>UPWK</t>
+  </si>
+  <si>
+    <t>GBTC</t>
+  </si>
+  <si>
+    <t>CNX</t>
+  </si>
+  <si>
+    <t>WLDN</t>
+  </si>
+  <si>
+    <t>AROC</t>
+  </si>
+  <si>
+    <t>ACLS</t>
+  </si>
+  <si>
+    <t>SM</t>
+  </si>
+  <si>
+    <t>EME</t>
+  </si>
+  <si>
+    <t>MNSO</t>
+  </si>
+  <si>
+    <t>BLD</t>
+  </si>
+  <si>
+    <t>NRP</t>
+  </si>
+  <si>
+    <t>PLPC</t>
+  </si>
+  <si>
+    <t>GKOS</t>
+  </si>
+  <si>
+    <t>FSLY</t>
+  </si>
+  <si>
+    <t>MDB</t>
+  </si>
+  <si>
+    <t>EDN</t>
+  </si>
+  <si>
+    <t>KRYS</t>
+  </si>
+  <si>
+    <t>GPOR</t>
   </si>
   <si>
     <t>KALA</t>
   </si>
   <si>
-    <t>DVA</t>
-  </si>
-  <si>
-    <t>APPF</t>
-  </si>
-  <si>
-    <t>CLH</t>
-  </si>
-  <si>
-    <t>MTG</t>
-  </si>
-  <si>
-    <t>MPX</t>
-  </si>
-  <si>
-    <t>PLUS</t>
-  </si>
-  <si>
-    <t>APG</t>
-  </si>
-  <si>
-    <t>KD</t>
-  </si>
-  <si>
-    <t>ARCB</t>
-  </si>
-  <si>
-    <t>URI</t>
-  </si>
-  <si>
-    <t>COOP</t>
-  </si>
-  <si>
-    <t>VNO</t>
-  </si>
-  <si>
-    <t>RIVN</t>
-  </si>
-  <si>
-    <t>ESCA</t>
-  </si>
-  <si>
-    <t>UBER</t>
-  </si>
-  <si>
-    <t>MNSO</t>
-  </si>
-  <si>
-    <t>NMIH</t>
-  </si>
-  <si>
-    <t>PKOH</t>
-  </si>
-  <si>
-    <t>KRYS</t>
-  </si>
-  <si>
-    <t>CFLT</t>
-  </si>
-  <si>
-    <t>LEGN</t>
-  </si>
-  <si>
-    <t>XPRO</t>
-  </si>
-  <si>
-    <t>GTLS</t>
-  </si>
-  <si>
-    <t>IIVI</t>
-  </si>
-  <si>
-    <t>BMEA</t>
+    <t>ARCT</t>
+  </si>
+  <si>
+    <t>JOE</t>
+  </si>
+  <si>
+    <t>ANIP</t>
+  </si>
+  <si>
+    <t>PRG</t>
+  </si>
+  <si>
+    <t>MARA</t>
+  </si>
+  <si>
+    <t>FRD</t>
+  </si>
+  <si>
+    <t>CLBR</t>
+  </si>
+  <si>
+    <t>ESTE</t>
+  </si>
+  <si>
+    <t>DLO</t>
+  </si>
+  <si>
+    <t>MMYT</t>
   </si>
   <si>
     <t>CWCO</t>
   </si>
   <si>
-    <t>ARGX</t>
-  </si>
-  <si>
-    <t>ZNTL</t>
-  </si>
-  <si>
-    <t>RYTM</t>
-  </si>
-  <si>
-    <t>CCJ</t>
-  </si>
-  <si>
-    <t>ADBE</t>
-  </si>
-  <si>
-    <t>NEU</t>
-  </si>
-  <si>
-    <t>NEWR</t>
-  </si>
-  <si>
-    <t>GCBC</t>
-  </si>
-  <si>
-    <t>BKI</t>
-  </si>
-  <si>
-    <t>RDY</t>
-  </si>
-  <si>
-    <t>UFPT</t>
-  </si>
-  <si>
-    <t>ABR</t>
-  </si>
-  <si>
-    <t>LAUR</t>
-  </si>
-  <si>
-    <t>MDC</t>
-  </si>
-  <si>
-    <t>PBF</t>
-  </si>
-  <si>
-    <t>ACMR</t>
-  </si>
-  <si>
-    <t>PNR</t>
-  </si>
-  <si>
-    <t>HCCI</t>
-  </si>
-  <si>
-    <t>ETN</t>
-  </si>
-  <si>
-    <t>BMI</t>
-  </si>
-  <si>
-    <t>TPH</t>
-  </si>
-  <si>
-    <t>HUBS</t>
-  </si>
-  <si>
-    <t>SHAK</t>
-  </si>
-  <si>
-    <t>BVH</t>
-  </si>
-  <si>
-    <t>BOOT</t>
-  </si>
-  <si>
-    <t>AMWD</t>
-  </si>
-  <si>
-    <t>AMZN</t>
-  </si>
-  <si>
-    <t>TYRA</t>
-  </si>
-  <si>
-    <t>SPNT</t>
-  </si>
-  <si>
-    <t>CRMT</t>
-  </si>
-  <si>
-    <t>MPC</t>
-  </si>
-  <si>
-    <t>RKT</t>
-  </si>
-  <si>
-    <t>FMS</t>
-  </si>
-  <si>
-    <t>ACVA</t>
-  </si>
-  <si>
-    <t>BECN</t>
-  </si>
-  <si>
-    <t>JELD</t>
-  </si>
-  <si>
-    <t>NOG</t>
-  </si>
-  <si>
-    <t>AEL</t>
-  </si>
-  <si>
-    <t>IMVT</t>
-  </si>
-  <si>
-    <t>ODFL</t>
-  </si>
-  <si>
-    <t>SM</t>
-  </si>
-  <si>
-    <t>DELL</t>
-  </si>
-  <si>
-    <t>MTH</t>
-  </si>
-  <si>
-    <t>OPAD</t>
-  </si>
-  <si>
-    <t>NUVL</t>
-  </si>
-  <si>
-    <t>SCPL</t>
-  </si>
-  <si>
-    <t>WST</t>
-  </si>
-  <si>
-    <t>SMHI</t>
-  </si>
-  <si>
-    <t>HAYW</t>
-  </si>
-  <si>
-    <t>ZG</t>
-  </si>
-  <si>
-    <t>LAD</t>
-  </si>
-  <si>
-    <t>CHX</t>
-  </si>
-  <si>
-    <t>KBH</t>
-  </si>
-  <si>
-    <t>BUR</t>
-  </si>
-  <si>
-    <t>RCMT</t>
-  </si>
-  <si>
-    <t>PRO</t>
-  </si>
-  <si>
-    <t>GE</t>
-  </si>
-  <si>
-    <t>FIX</t>
-  </si>
-  <si>
-    <t>ERO</t>
-  </si>
-  <si>
-    <t>Z</t>
-  </si>
-  <si>
-    <t>JHX</t>
-  </si>
-  <si>
-    <t>IOT</t>
-  </si>
-  <si>
-    <t>TOL</t>
-  </si>
-  <si>
-    <t>ASMIY</t>
-  </si>
-  <si>
-    <t>ANDE</t>
-  </si>
-  <si>
-    <t>NYCB</t>
-  </si>
-  <si>
-    <t>USLM</t>
-  </si>
-  <si>
-    <t>VRTV</t>
-  </si>
-  <si>
-    <t>CEIX</t>
-  </si>
-  <si>
-    <t>PRIM</t>
-  </si>
-  <si>
-    <t>SATS</t>
-  </si>
-  <si>
-    <t>BKNG</t>
-  </si>
-  <si>
-    <t>WLDN</t>
-  </si>
-  <si>
-    <t>AZUL</t>
-  </si>
-  <si>
-    <t>CVRX</t>
-  </si>
-  <si>
-    <t>CNX</t>
-  </si>
-  <si>
-    <t>COKE</t>
+    <t>COIN</t>
+  </si>
+  <si>
+    <t>MRAM</t>
+  </si>
+  <si>
+    <t>FTAI</t>
+  </si>
+  <si>
+    <t>RCEL</t>
+  </si>
+  <si>
+    <t>WRLD</t>
+  </si>
+  <si>
+    <t>PLTR</t>
+  </si>
+  <si>
+    <t>EDU</t>
+  </si>
+  <si>
+    <t>KALV</t>
+  </si>
+  <si>
+    <t>COCO</t>
+  </si>
+  <si>
+    <t>PAY</t>
+  </si>
+  <si>
+    <t>SOVO</t>
+  </si>
+  <si>
+    <t>CORT</t>
+  </si>
+  <si>
+    <t>LLY</t>
+  </si>
+  <si>
+    <t>BLDR</t>
+  </si>
+  <si>
+    <t>MLP</t>
+  </si>
+  <si>
+    <t>IDYA</t>
+  </si>
+  <si>
+    <t>NOA</t>
+  </si>
+  <si>
+    <t>DMRC</t>
+  </si>
+  <si>
+    <t>CAAP</t>
+  </si>
+  <si>
+    <t>BCC</t>
+  </si>
+  <si>
+    <t>PHAT</t>
+  </si>
+  <si>
+    <t>ANF</t>
+  </si>
+  <si>
+    <t>ISEE</t>
+  </si>
+  <si>
+    <t>SWDAF</t>
+  </si>
+  <si>
+    <t>DKNG</t>
+  </si>
+  <si>
+    <t>RIOT</t>
+  </si>
+  <si>
+    <t>PCTTU</t>
+  </si>
+  <si>
+    <t>FCNCA</t>
   </si>
   <si>
     <t>SG</t>
   </si>
   <si>
-    <t>PAM</t>
-  </si>
-  <si>
-    <t>CORT</t>
-  </si>
-  <si>
-    <t>SWDAF</t>
-  </si>
-  <si>
-    <t>MLP</t>
-  </si>
-  <si>
-    <t>NEX</t>
-  </si>
-  <si>
-    <t>NRP</t>
-  </si>
-  <si>
-    <t>IMTX</t>
-  </si>
-  <si>
-    <t>OTTR</t>
-  </si>
-  <si>
-    <t>IDYA</t>
-  </si>
-  <si>
-    <t>AGM</t>
-  </si>
-  <si>
-    <t>LAW</t>
-  </si>
-  <si>
-    <t>YPF</t>
-  </si>
-  <si>
-    <t>CSWI</t>
-  </si>
-  <si>
-    <t>GIII</t>
-  </si>
-  <si>
-    <t>KTOS</t>
-  </si>
-  <si>
-    <t>YELP</t>
-  </si>
-  <si>
-    <t>SXI</t>
-  </si>
-  <si>
-    <t>NIO</t>
-  </si>
-  <si>
-    <t>ACLS</t>
-  </si>
-  <si>
-    <t>CNM</t>
-  </si>
-  <si>
-    <t>GHL</t>
-  </si>
-  <si>
-    <t>LOB</t>
-  </si>
-  <si>
-    <t>VEL</t>
-  </si>
-  <si>
-    <t>AMNB</t>
-  </si>
-  <si>
-    <t>ROCK</t>
-  </si>
-  <si>
-    <t>AEHR</t>
-  </si>
-  <si>
-    <t>ZGN</t>
-  </si>
-  <si>
-    <t>ENVX</t>
-  </si>
-  <si>
-    <t>EB</t>
-  </si>
-  <si>
-    <t>SPNS</t>
-  </si>
-  <si>
-    <t>ANF</t>
-  </si>
-  <si>
-    <t>ONON</t>
-  </si>
-  <si>
-    <t>BLX</t>
-  </si>
-  <si>
-    <t>MMYT</t>
-  </si>
-  <si>
-    <t>LLY</t>
-  </si>
-  <si>
-    <t>LII</t>
-  </si>
-  <si>
-    <t>ARCO</t>
-  </si>
-  <si>
-    <t>OC</t>
-  </si>
-  <si>
-    <t>KRUS</t>
-  </si>
-  <si>
-    <t>FCAP</t>
-  </si>
-  <si>
-    <t>CRC</t>
-  </si>
-  <si>
-    <t>VECO</t>
-  </si>
-  <si>
-    <t>GKOS</t>
-  </si>
-  <si>
-    <t>WMS</t>
-  </si>
-  <si>
-    <t>MORF</t>
-  </si>
-  <si>
-    <t>CLBR</t>
-  </si>
-  <si>
-    <t>GRVY</t>
-  </si>
-  <si>
-    <t>RH</t>
-  </si>
-  <si>
-    <t>AZEK</t>
-  </si>
-  <si>
-    <t>CAAP</t>
-  </si>
-  <si>
-    <t>EME</t>
-  </si>
-  <si>
-    <t>CYD</t>
+    <t>GAMB</t>
+  </si>
+  <si>
+    <t>BWMX</t>
+  </si>
+  <si>
+    <t>TDW</t>
+  </si>
+  <si>
+    <t>VKTX</t>
+  </si>
+  <si>
+    <t>XP</t>
+  </si>
+  <si>
+    <t>ELF</t>
+  </si>
+  <si>
+    <t>PARR</t>
+  </si>
+  <si>
+    <t>KDNY</t>
+  </si>
+  <si>
+    <t>SAIA</t>
+  </si>
+  <si>
+    <t>NWLI</t>
+  </si>
+  <si>
+    <t>WFRD</t>
+  </si>
+  <si>
+    <t>OPRA</t>
+  </si>
+  <si>
+    <t>LI</t>
+  </si>
+  <si>
+    <t>MHO</t>
+  </si>
+  <si>
+    <t>EH</t>
+  </si>
+  <si>
+    <t>LSEA</t>
+  </si>
+  <si>
+    <t>USAP</t>
+  </si>
+  <si>
+    <t>W</t>
   </si>
   <si>
     <t>ACAD</t>
   </si>
   <si>
-    <t>GHM</t>
-  </si>
-  <si>
-    <t>AROC</t>
-  </si>
-  <si>
-    <t>MATX</t>
-  </si>
-  <si>
-    <t>FTI</t>
-  </si>
-  <si>
-    <t>SOVO</t>
-  </si>
-  <si>
-    <t>UPWK</t>
-  </si>
-  <si>
-    <t>AI</t>
-  </si>
-  <si>
-    <t>PLPC</t>
-  </si>
-  <si>
-    <t>SPOK</t>
-  </si>
-  <si>
-    <t>NE</t>
-  </si>
-  <si>
-    <t>PHM</t>
-  </si>
-  <si>
-    <t>COCO</t>
-  </si>
-  <si>
-    <t>SSD</t>
-  </si>
-  <si>
-    <t>STVN</t>
-  </si>
-  <si>
-    <t>PHAT</t>
-  </si>
-  <si>
-    <t>RCL</t>
-  </si>
-  <si>
-    <t>TREX</t>
-  </si>
-  <si>
-    <t>GBX</t>
-  </si>
-  <si>
-    <t>CTG</t>
-  </si>
-  <si>
-    <t>AVDL</t>
-  </si>
-  <si>
-    <t>KALV</t>
-  </si>
-  <si>
-    <t>IBP</t>
+    <t>MDWT</t>
+  </si>
+  <si>
+    <t>QTRX</t>
+  </si>
+  <si>
+    <t>NGMS</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>CLS</t>
+  </si>
+  <si>
+    <t>CMPR</t>
+  </si>
+  <si>
+    <t>XPEV</t>
+  </si>
+  <si>
+    <t>ODC</t>
+  </si>
+  <si>
+    <t>NATR</t>
+  </si>
+  <si>
+    <t>CABA</t>
+  </si>
+  <si>
+    <t>ALPN</t>
+  </si>
+  <si>
+    <t>CELH</t>
+  </si>
+  <si>
+    <t>SKYW</t>
+  </si>
+  <si>
+    <t>VSTM</t>
+  </si>
+  <si>
+    <t>SBOW</t>
+  </si>
+  <si>
+    <t>BZH</t>
+  </si>
+  <si>
+    <t>KRT</t>
+  </si>
+  <si>
+    <t>UPST</t>
+  </si>
+  <si>
+    <t>VECT</t>
+  </si>
+  <si>
+    <t>PETQ</t>
+  </si>
+  <si>
+    <t>IESC</t>
+  </si>
+  <si>
+    <t>RELY</t>
+  </si>
+  <si>
+    <t>FOR</t>
+  </si>
+  <si>
+    <t>POWL</t>
   </si>
   <si>
     <t>FSTR</t>
   </si>
   <si>
-    <t>SDGR</t>
-  </si>
-  <si>
-    <t>LTRPB</t>
-  </si>
-  <si>
-    <t>VIST</t>
-  </si>
-  <si>
-    <t>CCL</t>
-  </si>
-  <si>
-    <t>GPOR</t>
-  </si>
-  <si>
-    <t>ISEE</t>
-  </si>
-  <si>
-    <t>EDU</t>
-  </si>
-  <si>
-    <t>PCTTU</t>
-  </si>
-  <si>
-    <t>ANIP</t>
-  </si>
-  <si>
-    <t>SRDX</t>
-  </si>
-  <si>
-    <t>DMRC</t>
-  </si>
-  <si>
-    <t>ACOR</t>
-  </si>
-  <si>
-    <t>IMRX</t>
-  </si>
-  <si>
-    <t>CUK</t>
-  </si>
-  <si>
-    <t>BMA</t>
-  </si>
-  <si>
-    <t>BSAQ</t>
-  </si>
-  <si>
-    <t>FRSH</t>
-  </si>
-  <si>
-    <t>FTAI</t>
-  </si>
-  <si>
-    <t>COIN</t>
-  </si>
-  <si>
-    <t>HOV</t>
-  </si>
-  <si>
-    <t>RILY</t>
-  </si>
-  <si>
-    <t>AMPH</t>
-  </si>
-  <si>
-    <t>MDWT</t>
-  </si>
-  <si>
-    <t>GGAL</t>
-  </si>
-  <si>
-    <t>MSTR</t>
-  </si>
-  <si>
-    <t>GRBK</t>
-  </si>
-  <si>
-    <t>PRG</t>
-  </si>
-  <si>
-    <t>OSTK</t>
-  </si>
-  <si>
-    <t>CVLG</t>
-  </si>
-  <si>
-    <t>ROIV</t>
-  </si>
-  <si>
-    <t>CUBI</t>
-  </si>
-  <si>
-    <t>ABCM</t>
-  </si>
-  <si>
-    <t>KDNY</t>
-  </si>
-  <si>
-    <t>TISI</t>
-  </si>
-  <si>
-    <t>DICE</t>
-  </si>
-  <si>
-    <t>FSLY</t>
-  </si>
-  <si>
-    <t>JOE</t>
-  </si>
-  <si>
-    <t>UPST</t>
-  </si>
-  <si>
-    <t>EDN</t>
-  </si>
-  <si>
-    <t>ETHE</t>
-  </si>
-  <si>
-    <t>NGMS</t>
-  </si>
-  <si>
-    <t>BLD</t>
-  </si>
-  <si>
-    <t>EXPI</t>
-  </si>
-  <si>
-    <t>FCNCA</t>
-  </si>
-  <si>
-    <t>BLU</t>
-  </si>
-  <si>
-    <t>VKTX</t>
-  </si>
-  <si>
-    <t>BCC</t>
-  </si>
-  <si>
-    <t>MDB</t>
-  </si>
-  <si>
-    <t>KRT</t>
-  </si>
-  <si>
-    <t>NOA</t>
-  </si>
-  <si>
-    <t>NATR</t>
-  </si>
-  <si>
-    <t>ACU</t>
+    <t>RXST</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>NVDA</t>
+  </si>
+  <si>
+    <t>XPO</t>
+  </si>
+  <si>
+    <t>CMT</t>
+  </si>
+  <si>
+    <t>MOD</t>
+  </si>
+  <si>
+    <t>CBAY</t>
+  </si>
+  <si>
+    <t>TRHC</t>
+  </si>
+  <si>
+    <t>DFH</t>
+  </si>
+  <si>
+    <t>WEAV</t>
+  </si>
+  <si>
+    <t>CAMT</t>
+  </si>
+  <si>
+    <t>WW</t>
+  </si>
+  <si>
+    <t>MEOA</t>
+  </si>
+  <si>
+    <t>STRL</t>
+  </si>
+  <si>
+    <t>TDS</t>
+  </si>
+  <si>
+    <t>SMCI</t>
+  </si>
+  <si>
+    <t>CDLX</t>
+  </si>
+  <si>
+    <t>URGN</t>
+  </si>
+  <si>
+    <t>GRPN</t>
+  </si>
+  <si>
+    <t>PHVS</t>
+  </si>
+  <si>
+    <t>USM</t>
+  </si>
+  <si>
+    <t>VRT</t>
+  </si>
+  <si>
+    <t>LMB</t>
+  </si>
+  <si>
+    <t>AURC</t>
+  </si>
+  <si>
+    <t>BBIO</t>
+  </si>
+  <si>
+    <t>MEOAU</t>
+  </si>
+  <si>
+    <t>INOD</t>
   </si>
   <si>
     <t>TSAT</t>
   </si>
   <si>
-    <t>PARR</t>
-  </si>
-  <si>
-    <t>DKNG</t>
-  </si>
-  <si>
-    <t>XP</t>
-  </si>
-  <si>
-    <t>PETQ</t>
-  </si>
-  <si>
-    <t>WRLD</t>
-  </si>
-  <si>
-    <t>SBOW</t>
-  </si>
-  <si>
-    <t>EXTR</t>
-  </si>
-  <si>
-    <t>SAIA</t>
-  </si>
-  <si>
-    <t>PAY</t>
-  </si>
-  <si>
-    <t>TDW</t>
-  </si>
-  <si>
-    <t>CABA</t>
-  </si>
-  <si>
-    <t>USAP</t>
-  </si>
-  <si>
-    <t>PCT</t>
-  </si>
-  <si>
-    <t>CELH</t>
-  </si>
-  <si>
-    <t>LI</t>
-  </si>
-  <si>
-    <t>ODC</t>
-  </si>
-  <si>
-    <t>QTRX</t>
-  </si>
-  <si>
-    <t>BWMX</t>
-  </si>
-  <si>
-    <t>PLTR</t>
-  </si>
-  <si>
-    <t>NWLI</t>
-  </si>
-  <si>
-    <t>XPEV</t>
-  </si>
-  <si>
-    <t>WFRD</t>
-  </si>
-  <si>
-    <t>ALPN</t>
-  </si>
-  <si>
-    <t>RXST</t>
-  </si>
-  <si>
-    <t>RELY</t>
-  </si>
-  <si>
-    <t>NVDA</t>
-  </si>
-  <si>
-    <t>MHO</t>
-  </si>
-  <si>
-    <t>VECT</t>
-  </si>
-  <si>
-    <t>IESC</t>
-  </si>
-  <si>
-    <t>GBTC</t>
-  </si>
-  <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>W</t>
-  </si>
-  <si>
-    <t>CAMT</t>
-  </si>
-  <si>
-    <t>RCEL</t>
-  </si>
-  <si>
-    <t>CMT</t>
-  </si>
-  <si>
-    <t>BLDR</t>
-  </si>
-  <si>
-    <t>CLS</t>
-  </si>
-  <si>
-    <t>CIR</t>
-  </si>
-  <si>
-    <t>CPS</t>
-  </si>
-  <si>
-    <t>TRHC</t>
-  </si>
-  <si>
-    <t>ELF</t>
-  </si>
-  <si>
-    <t>CMPR</t>
-  </si>
-  <si>
-    <t>OPRA</t>
-  </si>
-  <si>
-    <t>LSEA</t>
-  </si>
-  <si>
-    <t>FRD</t>
-  </si>
-  <si>
-    <t>PESI</t>
-  </si>
-  <si>
-    <t>SKYW</t>
-  </si>
-  <si>
-    <t>FOR</t>
-  </si>
-  <si>
-    <t>TDS</t>
-  </si>
-  <si>
-    <t>XPO</t>
-  </si>
-  <si>
-    <t>MOD</t>
-  </si>
-  <si>
-    <t>WEAV</t>
-  </si>
-  <si>
-    <t>CBAY</t>
-  </si>
-  <si>
-    <t>MARA</t>
-  </si>
-  <si>
-    <t>POWL</t>
-  </si>
-  <si>
-    <t>BZH</t>
-  </si>
-  <si>
-    <t>MEOA</t>
-  </si>
-  <si>
-    <t>EH</t>
-  </si>
-  <si>
-    <t>ARLO</t>
-  </si>
-  <si>
-    <t>LMB</t>
-  </si>
-  <si>
-    <t>RIOT</t>
-  </si>
-  <si>
-    <t>USM</t>
-  </si>
-  <si>
-    <t>DFH</t>
-  </si>
-  <si>
-    <t>STRL</t>
-  </si>
-  <si>
-    <t>SMCI</t>
-  </si>
-  <si>
-    <t>WW</t>
-  </si>
-  <si>
-    <t>VRT</t>
-  </si>
-  <si>
-    <t>CDLX</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>MEOAU</t>
-  </si>
-  <si>
-    <t>RXDX</t>
+    <t>AURCU</t>
+  </si>
+  <si>
+    <t>IONQ</t>
+  </si>
+  <si>
+    <t>APP</t>
   </si>
   <si>
     <t>IMGN</t>
   </si>
   <si>
-    <t>INOD</t>
-  </si>
-  <si>
-    <t>URGN</t>
-  </si>
-  <si>
-    <t>IONQ</t>
-  </si>
-  <si>
-    <t>OLMA</t>
-  </si>
-  <si>
-    <t>APP</t>
-  </si>
-  <si>
-    <t>BBIO</t>
-  </si>
-  <si>
     <t>RETA</t>
   </si>
   <si>
-    <t>EVLO</t>
-  </si>
-  <si>
     <t>EYPT</t>
   </si>
   <si>
-    <t>PHVS</t>
+    <t>SGTX</t>
   </si>
   <si>
     <t>CVNA</t>
   </si>
   <si>
-    <t>AURC</t>
-  </si>
-  <si>
-    <t>AURCU</t>
-  </si>
-  <si>
-    <t>SGTX</t>
+    <t>EDTXU</t>
+  </si>
+  <si>
+    <t>EDTX</t>
   </si>
   <si>
     <t>AAOI</t>
-  </si>
-  <si>
-    <t>EDTXU</t>
-  </si>
-  <si>
-    <t>EDTX</t>
-  </si>
-  <si>
-    <t>AMAM</t>
   </si>
 </sst>
 </file>
@@ -1462,7 +2461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B365"/>
+  <dimension ref="A1:B698"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1478,7 +2477,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1">
-        <v>124.0829861665204</v>
+        <v>110.8647912736285</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1486,7 +2485,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1">
-        <v>124.1595479390792</v>
+        <v>110.8901917715365</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1494,7 +2493,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1">
-        <v>124.1975748164088</v>
+        <v>110.8922377971169</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1502,7 +2501,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="1">
-        <v>124.2317786739443</v>
+        <v>110.9118329544624</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1510,7 +2509,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="1">
-        <v>124.2702087461477</v>
+        <v>110.9125038170068</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1518,7 +2517,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="1">
-        <v>124.3521926897257</v>
+        <v>110.9229990682797</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1526,7 +2525,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="1">
-        <v>124.3665591213771</v>
+        <v>110.930744438892</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1534,7 +2533,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="1">
-        <v>124.3845210398288</v>
+        <v>110.9546202374334</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1542,7 +2541,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="1">
-        <v>124.4381709994948</v>
+        <v>110.971568548441</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1550,7 +2549,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="1">
-        <v>124.4563099539098</v>
+        <v>110.9837017901691</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1558,7 +2557,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="1">
-        <v>124.4859210501041</v>
+        <v>111.0056721204515</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1566,7 +2565,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="1">
-        <v>124.5617563603743</v>
+        <v>111.0489830958142</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1574,7 +2573,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="1">
-        <v>124.5630026585182</v>
+        <v>111.0697613542611</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1582,7 +2581,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="1">
-        <v>124.6336258018261</v>
+        <v>111.0730399792104</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1590,7 +2589,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="1">
-        <v>124.712692959347</v>
+        <v>111.1300263116886</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1598,7 +2597,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="1">
-        <v>124.7971295256411</v>
+        <v>111.1371530379617</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1606,7 +2605,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="1">
-        <v>124.8499225367773</v>
+        <v>111.1377506473336</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1614,7 +2613,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="1">
-        <v>124.8551353731227</v>
+        <v>111.1634860821335</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1622,7 +2621,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="1">
-        <v>124.9229016502065</v>
+        <v>111.1719650950922</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1630,7 +2629,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="1">
-        <v>125.0067893048456</v>
+        <v>111.1731255767884</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1638,7 +2637,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="1">
-        <v>125.1844118283891</v>
+        <v>111.1857740297151</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1646,7 +2645,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="1">
-        <v>125.2044676154203</v>
+        <v>111.2055385825037</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1654,7 +2653,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="1">
-        <v>125.2856369812978</v>
+        <v>111.2159990526238</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1662,7 +2661,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="1">
-        <v>125.350762371963</v>
+        <v>111.2235887094137</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1670,7 +2669,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="1">
-        <v>125.4535727314165</v>
+        <v>111.2351062958504</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1678,7 +2677,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="1">
-        <v>125.4540464617075</v>
+        <v>111.2474165457382</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1686,7 +2685,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="1">
-        <v>125.4783265747443</v>
+        <v>111.2525676187947</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1694,7 +2693,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="1">
-        <v>125.4845877264405</v>
+        <v>111.3489964150798</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1702,7 +2701,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="1">
-        <v>125.4953791483459</v>
+        <v>111.3855282747894</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1710,7 +2709,7 @@
         <v>31</v>
       </c>
       <c r="B31" s="1">
-        <v>125.5590823510238</v>
+        <v>111.3877721444288</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1718,7 +2717,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="1">
-        <v>125.5941846125836</v>
+        <v>111.4311062305727</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1726,7 +2725,7 @@
         <v>33</v>
       </c>
       <c r="B33" s="1">
-        <v>125.6324980204941</v>
+        <v>111.4754677632055</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1734,7 +2733,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="1">
-        <v>125.642110911772</v>
+        <v>111.515843541231</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1742,7 +2741,7 @@
         <v>35</v>
       </c>
       <c r="B35" s="1">
-        <v>125.6827913230994</v>
+        <v>111.5171277515678</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1750,7 +2749,7 @@
         <v>36</v>
       </c>
       <c r="B36" s="1">
-        <v>125.6907325020123</v>
+        <v>111.540340632579</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1758,7 +2757,7 @@
         <v>37</v>
       </c>
       <c r="B37" s="1">
-        <v>125.7326378419124</v>
+        <v>111.5610450843848</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1766,7 +2765,7 @@
         <v>38</v>
       </c>
       <c r="B38" s="1">
-        <v>125.7526541370251</v>
+        <v>111.5848936020303</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1774,7 +2773,7 @@
         <v>39</v>
       </c>
       <c r="B39" s="1">
-        <v>125.7810106712664</v>
+        <v>111.63384268333</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1782,7 +2781,7 @@
         <v>40</v>
       </c>
       <c r="B40" s="1">
-        <v>125.874354654279</v>
+        <v>111.6694913251985</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1790,7 +2789,7 @@
         <v>41</v>
       </c>
       <c r="B41" s="1">
-        <v>125.9646078006813</v>
+        <v>111.6855897241987</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -1798,7 +2797,7 @@
         <v>42</v>
       </c>
       <c r="B42" s="1">
-        <v>125.9938044978556</v>
+        <v>111.6862636299955</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -1806,7 +2805,7 @@
         <v>43</v>
       </c>
       <c r="B43" s="1">
-        <v>126.1581889062703</v>
+        <v>111.7431412390116</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1814,7 +2813,7 @@
         <v>44</v>
       </c>
       <c r="B44" s="1">
-        <v>126.1709718332527</v>
+        <v>111.7488768018433</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1822,7 +2821,7 @@
         <v>45</v>
       </c>
       <c r="B45" s="1">
-        <v>126.2005892570191</v>
+        <v>111.8350881990507</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1830,7 +2829,7 @@
         <v>46</v>
       </c>
       <c r="B46" s="1">
-        <v>126.2370220154832</v>
+        <v>111.859244573806</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -1838,7 +2837,7 @@
         <v>47</v>
       </c>
       <c r="B47" s="1">
-        <v>126.2479254993667</v>
+        <v>111.8795217089708</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -1846,7 +2845,7 @@
         <v>48</v>
       </c>
       <c r="B48" s="1">
-        <v>126.2641889120621</v>
+        <v>111.9146296290772</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1854,7 +2853,7 @@
         <v>49</v>
       </c>
       <c r="B49" s="1">
-        <v>126.301647300819</v>
+        <v>111.9376289062551</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1862,7 +2861,7 @@
         <v>50</v>
       </c>
       <c r="B50" s="1">
-        <v>126.370572789885</v>
+        <v>111.95021984191</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1870,7 +2869,7 @@
         <v>51</v>
       </c>
       <c r="B51" s="1">
-        <v>126.3763339426322</v>
+        <v>111.954652340026</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1878,7 +2877,7 @@
         <v>52</v>
       </c>
       <c r="B52" s="1">
-        <v>126.5103662728782</v>
+        <v>111.9553798328644</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1886,7 +2885,7 @@
         <v>53</v>
       </c>
       <c r="B53" s="1">
-        <v>126.6382257651476</v>
+        <v>112.0339452229842</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1894,7 +2893,7 @@
         <v>54</v>
       </c>
       <c r="B54" s="1">
-        <v>126.6739160020548</v>
+        <v>112.0386091089752</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1902,7 +2901,7 @@
         <v>55</v>
       </c>
       <c r="B55" s="1">
-        <v>126.7017200156502</v>
+        <v>112.0641895911811</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1910,7 +2909,7 @@
         <v>56</v>
       </c>
       <c r="B56" s="1">
-        <v>126.7688996131203</v>
+        <v>112.0649336025015</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1918,7 +2917,7 @@
         <v>57</v>
       </c>
       <c r="B57" s="1">
-        <v>126.7775816524545</v>
+        <v>112.0721255542242</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1926,7 +2925,7 @@
         <v>58</v>
       </c>
       <c r="B58" s="1">
-        <v>126.8491022670315</v>
+        <v>112.1001914626676</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1934,7 +2933,7 @@
         <v>59</v>
       </c>
       <c r="B59" s="1">
-        <v>126.8589835319579</v>
+        <v>112.1059004712754</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1942,7 +2941,7 @@
         <v>60</v>
       </c>
       <c r="B60" s="1">
-        <v>126.9190353818207</v>
+        <v>112.127359078842</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1950,7 +2949,7 @@
         <v>61</v>
       </c>
       <c r="B61" s="1">
-        <v>126.9494324233464</v>
+        <v>112.1444682208722</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1958,7 +2957,7 @@
         <v>62</v>
       </c>
       <c r="B62" s="1">
-        <v>126.950306998431</v>
+        <v>112.1554987572934</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1966,7 +2965,7 @@
         <v>63</v>
       </c>
       <c r="B63" s="1">
-        <v>127.0549911254336</v>
+        <v>112.1618408622081</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1974,7 +2973,7 @@
         <v>64</v>
       </c>
       <c r="B64" s="1">
-        <v>127.0890561996871</v>
+        <v>112.2246827199497</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1982,7 +2981,7 @@
         <v>65</v>
       </c>
       <c r="B65" s="1">
-        <v>127.158166366983</v>
+        <v>112.2382864112019</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -1990,7 +2989,7 @@
         <v>66</v>
       </c>
       <c r="B66" s="1">
-        <v>127.2030946782174</v>
+        <v>112.2457351734439</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -1998,7 +2997,7 @@
         <v>67</v>
       </c>
       <c r="B67" s="1">
-        <v>127.2470203176702</v>
+        <v>112.3109619552524</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -2006,7 +3005,7 @@
         <v>68</v>
       </c>
       <c r="B68" s="1">
-        <v>127.2798780358174</v>
+        <v>112.3120676979905</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -2014,7 +3013,7 @@
         <v>69</v>
       </c>
       <c r="B69" s="1">
-        <v>127.292972785944</v>
+        <v>112.3174388300888</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -2022,7 +3021,7 @@
         <v>70</v>
       </c>
       <c r="B70" s="1">
-        <v>127.3453866072637</v>
+        <v>112.3384978635287</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -2030,7 +3029,7 @@
         <v>71</v>
       </c>
       <c r="B71" s="1">
-        <v>127.3532730818984</v>
+        <v>112.3932997259265</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -2038,7 +3037,7 @@
         <v>72</v>
       </c>
       <c r="B72" s="1">
-        <v>127.3725443809172</v>
+        <v>112.4369163137601</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2046,7 +3045,7 @@
         <v>73</v>
       </c>
       <c r="B73" s="1">
-        <v>127.4160823718624</v>
+        <v>112.4457105943059</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -2054,7 +3053,7 @@
         <v>74</v>
       </c>
       <c r="B74" s="1">
-        <v>127.5090896842275</v>
+        <v>112.4602446973828</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -2062,7 +3061,7 @@
         <v>75</v>
       </c>
       <c r="B75" s="1">
-        <v>127.5242743758276</v>
+        <v>112.4636465433874</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -2070,7 +3069,7 @@
         <v>76</v>
       </c>
       <c r="B76" s="1">
-        <v>127.5250226743852</v>
+        <v>112.4866945545343</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -2078,7 +3077,7 @@
         <v>77</v>
       </c>
       <c r="B77" s="1">
-        <v>127.6013465385664</v>
+        <v>112.4909267939348</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -2086,7 +3085,7 @@
         <v>78</v>
       </c>
       <c r="B78" s="1">
-        <v>127.6061577399607</v>
+        <v>112.4951666545483</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -2094,7 +3093,7 @@
         <v>79</v>
       </c>
       <c r="B79" s="1">
-        <v>127.6337995583583</v>
+        <v>112.5002626312391</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -2102,7 +3101,7 @@
         <v>80</v>
       </c>
       <c r="B80" s="1">
-        <v>127.714381921303</v>
+        <v>112.5069609432311</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -2110,7 +3109,7 @@
         <v>81</v>
       </c>
       <c r="B81" s="1">
-        <v>127.7181725128841</v>
+        <v>112.5171339613725</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -2118,7 +3117,7 @@
         <v>82</v>
       </c>
       <c r="B82" s="1">
-        <v>127.7241253795214</v>
+        <v>112.5239012550908</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -2126,7 +3125,7 @@
         <v>83</v>
       </c>
       <c r="B83" s="1">
-        <v>127.7482211011853</v>
+        <v>112.5392399181627</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -2134,7 +3133,7 @@
         <v>84</v>
       </c>
       <c r="B84" s="1">
-        <v>127.7490447114442</v>
+        <v>112.5484740083833</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -2142,7 +3141,7 @@
         <v>85</v>
       </c>
       <c r="B85" s="1">
-        <v>127.7870506305755</v>
+        <v>112.5489894267813</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -2150,7 +3149,7 @@
         <v>86</v>
       </c>
       <c r="B86" s="1">
-        <v>127.9371654894457</v>
+        <v>112.5510011980902</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -2158,7 +3157,7 @@
         <v>87</v>
       </c>
       <c r="B87" s="1">
-        <v>127.9521132948472</v>
+        <v>112.5584186439458</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -2166,7 +3165,7 @@
         <v>88</v>
       </c>
       <c r="B88" s="1">
-        <v>127.9868531020263</v>
+        <v>112.5955337718902</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -2174,7 +3173,7 @@
         <v>89</v>
       </c>
       <c r="B89" s="1">
-        <v>128.0822809429671</v>
+        <v>112.624171757551</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -2182,7 +3181,7 @@
         <v>90</v>
       </c>
       <c r="B90" s="1">
-        <v>128.2296991823873</v>
+        <v>112.6319673457117</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -2190,7 +3189,7 @@
         <v>91</v>
       </c>
       <c r="B91" s="1">
-        <v>128.2520753974548</v>
+        <v>112.677682276161</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -2198,7 +3197,7 @@
         <v>92</v>
       </c>
       <c r="B92" s="1">
-        <v>128.2657078335446</v>
+        <v>112.6894275041773</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -2206,7 +3205,7 @@
         <v>93</v>
       </c>
       <c r="B93" s="1">
-        <v>128.3078500791912</v>
+        <v>112.6895428738074</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -2214,7 +3213,7 @@
         <v>94</v>
       </c>
       <c r="B94" s="1">
-        <v>128.3350598374419</v>
+        <v>112.7118764830948</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -2222,7 +3221,7 @@
         <v>95</v>
       </c>
       <c r="B95" s="1">
-        <v>128.3437101427465</v>
+        <v>112.7864427294929</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -2230,7 +3229,7 @@
         <v>96</v>
       </c>
       <c r="B96" s="1">
-        <v>128.3786167231696</v>
+        <v>112.8031657851604</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -2238,7 +3237,7 @@
         <v>97</v>
       </c>
       <c r="B97" s="1">
-        <v>128.4484646102484</v>
+        <v>112.8588662096013</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -2246,7 +3245,7 @@
         <v>98</v>
       </c>
       <c r="B98" s="1">
-        <v>128.4716447515167</v>
+        <v>112.8628950088184</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -2254,7 +3253,7 @@
         <v>99</v>
       </c>
       <c r="B99" s="1">
-        <v>128.488916358998</v>
+        <v>112.8835904876899</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -2262,7 +3261,7 @@
         <v>100</v>
       </c>
       <c r="B100" s="1">
-        <v>128.5983462380588</v>
+        <v>112.933352221355</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -2270,7 +3269,7 @@
         <v>101</v>
       </c>
       <c r="B101" s="1">
-        <v>128.6498927541182</v>
+        <v>113.041457937758</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -2278,7 +3277,7 @@
         <v>102</v>
       </c>
       <c r="B102" s="1">
-        <v>128.6514535378718</v>
+        <v>113.0747620992742</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -2286,7 +3285,7 @@
         <v>103</v>
       </c>
       <c r="B103" s="1">
-        <v>128.6541892318087</v>
+        <v>113.102343826024</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -2294,7 +3293,7 @@
         <v>104</v>
       </c>
       <c r="B104" s="1">
-        <v>128.6664031263227</v>
+        <v>113.1072096083887</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -2302,7 +3301,7 @@
         <v>105</v>
       </c>
       <c r="B105" s="1">
-        <v>128.7547156560537</v>
+        <v>113.1159589228084</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -2310,7 +3309,7 @@
         <v>106</v>
       </c>
       <c r="B106" s="1">
-        <v>128.7887322138049</v>
+        <v>113.1481733289554</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -2318,7 +3317,7 @@
         <v>107</v>
       </c>
       <c r="B107" s="1">
-        <v>128.792245654413</v>
+        <v>113.1641838522858</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -2326,7 +3325,7 @@
         <v>108</v>
       </c>
       <c r="B108" s="1">
-        <v>128.7950124664951</v>
+        <v>113.2323735459246</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -2334,7 +3333,7 @@
         <v>109</v>
       </c>
       <c r="B109" s="1">
-        <v>128.8083977525122</v>
+        <v>113.2530267266307</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -2342,7 +3341,7 @@
         <v>110</v>
       </c>
       <c r="B110" s="1">
-        <v>128.8848941264693</v>
+        <v>113.2686138808616</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -2350,7 +3349,7 @@
         <v>111</v>
       </c>
       <c r="B111" s="1">
-        <v>128.9038489400424</v>
+        <v>113.2754131365293</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -2358,7 +3357,7 @@
         <v>112</v>
       </c>
       <c r="B112" s="1">
-        <v>128.9436889143977</v>
+        <v>113.2882090832779</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -2366,7 +3365,7 @@
         <v>113</v>
       </c>
       <c r="B113" s="1">
-        <v>129.0491367977121</v>
+        <v>113.3024375526175</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -2374,7 +3373,7 @@
         <v>114</v>
       </c>
       <c r="B114" s="1">
-        <v>129.073264833155</v>
+        <v>113.3581453438479</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -2382,7 +3381,7 @@
         <v>115</v>
       </c>
       <c r="B115" s="1">
-        <v>129.1618824936386</v>
+        <v>113.3592977068726</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -2390,7 +3389,7 @@
         <v>116</v>
       </c>
       <c r="B116" s="1">
-        <v>129.4114387837731</v>
+        <v>113.3792194063035</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -2398,7 +3397,7 @@
         <v>117</v>
       </c>
       <c r="B117" s="1">
-        <v>129.4476894243408</v>
+        <v>113.4017594843759</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -2406,7 +3405,7 @@
         <v>118</v>
       </c>
       <c r="B118" s="1">
-        <v>129.6265754118318</v>
+        <v>113.4132983457293</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -2414,7 +3413,7 @@
         <v>119</v>
       </c>
       <c r="B119" s="1">
-        <v>129.7403585985813</v>
+        <v>113.4326882077768</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -2422,7 +3421,7 @@
         <v>120</v>
       </c>
       <c r="B120" s="1">
-        <v>129.7620497359756</v>
+        <v>113.4687950651167</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -2430,7 +3429,7 @@
         <v>121</v>
       </c>
       <c r="B121" s="1">
-        <v>129.8489324369625</v>
+        <v>113.4794473195246</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -2438,7 +3437,7 @@
         <v>122</v>
       </c>
       <c r="B122" s="1">
-        <v>129.8806525371881</v>
+        <v>113.4979323640599</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -2446,7 +3445,7 @@
         <v>123</v>
       </c>
       <c r="B123" s="1">
-        <v>129.9063174807688</v>
+        <v>113.5039042677739</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -2454,7 +3453,7 @@
         <v>124</v>
       </c>
       <c r="B124" s="1">
-        <v>129.9541797958996</v>
+        <v>113.5171358533814</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -2462,7 +3461,7 @@
         <v>125</v>
       </c>
       <c r="B125" s="1">
-        <v>129.9545375235461</v>
+        <v>113.5676941750637</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -2470,7 +3469,7 @@
         <v>126</v>
       </c>
       <c r="B126" s="1">
-        <v>129.9957102297416</v>
+        <v>113.582549838585</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -2478,7 +3477,7 @@
         <v>127</v>
       </c>
       <c r="B127" s="1">
-        <v>130.1172516637907</v>
+        <v>113.5840916161213</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -2486,7 +3485,7 @@
         <v>128</v>
       </c>
       <c r="B128" s="1">
-        <v>130.2034523106618</v>
+        <v>113.6027614745096</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -2494,7 +3493,7 @@
         <v>129</v>
       </c>
       <c r="B129" s="1">
-        <v>130.3164965704787</v>
+        <v>113.6170184007267</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -2502,7 +3501,7 @@
         <v>130</v>
       </c>
       <c r="B130" s="1">
-        <v>130.3744516074356</v>
+        <v>113.6530235324607</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -2510,7 +3509,7 @@
         <v>131</v>
       </c>
       <c r="B131" s="1">
-        <v>130.4338572917512</v>
+        <v>113.6648351483097</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -2518,7 +3517,7 @@
         <v>132</v>
       </c>
       <c r="B132" s="1">
-        <v>130.4695579265789</v>
+        <v>113.6689548039554</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -2526,7 +3525,7 @@
         <v>133</v>
       </c>
       <c r="B133" s="1">
-        <v>130.4894921862387</v>
+        <v>113.6793207299069</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -2534,7 +3533,7 @@
         <v>134</v>
       </c>
       <c r="B134" s="1">
-        <v>130.749804244786</v>
+        <v>113.6804914558656</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -2542,7 +3541,7 @@
         <v>135</v>
       </c>
       <c r="B135" s="1">
-        <v>130.7776758712376</v>
+        <v>113.6902246266808</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -2550,7 +3549,7 @@
         <v>136</v>
       </c>
       <c r="B136" s="1">
-        <v>130.983447158802</v>
+        <v>113.7103099036666</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -2558,7 +3557,7 @@
         <v>137</v>
       </c>
       <c r="B137" s="1">
-        <v>131.1534537183965</v>
+        <v>113.7287500574251</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -2566,7 +3565,7 @@
         <v>138</v>
       </c>
       <c r="B138" s="1">
-        <v>131.2173168007979</v>
+        <v>113.7780813773275</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -2574,7 +3573,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="1">
-        <v>131.2829909345503</v>
+        <v>113.7914711215384</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -2582,7 +3581,7 @@
         <v>140</v>
       </c>
       <c r="B140" s="1">
-        <v>131.2948143616237</v>
+        <v>113.8339444085862</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -2590,7 +3589,7 @@
         <v>141</v>
       </c>
       <c r="B141" s="1">
-        <v>131.3124626174712</v>
+        <v>113.882148949995</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -2598,7 +3597,7 @@
         <v>142</v>
       </c>
       <c r="B142" s="1">
-        <v>131.3299020366235</v>
+        <v>113.8948345777003</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -2606,7 +3605,7 @@
         <v>143</v>
       </c>
       <c r="B143" s="1">
-        <v>131.4099235311241</v>
+        <v>113.9659166957802</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -2614,7 +3613,7 @@
         <v>144</v>
       </c>
       <c r="B144" s="1">
-        <v>131.6761108931362</v>
+        <v>114.016320637967</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -2622,7 +3621,7 @@
         <v>145</v>
       </c>
       <c r="B145" s="1">
-        <v>131.6788382836702</v>
+        <v>114.0398279084865</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -2630,7 +3629,7 @@
         <v>146</v>
       </c>
       <c r="B146" s="1">
-        <v>131.7990897615463</v>
+        <v>114.0471316159944</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -2638,7 +3637,7 @@
         <v>147</v>
       </c>
       <c r="B147" s="1">
-        <v>132.0871347428294</v>
+        <v>114.0482836380509</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -2646,7 +3645,7 @@
         <v>148</v>
       </c>
       <c r="B148" s="1">
-        <v>132.2493096746987</v>
+        <v>114.0522451310311</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -2654,7 +3653,7 @@
         <v>149</v>
       </c>
       <c r="B149" s="1">
-        <v>132.3262448199615</v>
+        <v>114.0648747603351</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -2662,7 +3661,7 @@
         <v>150</v>
       </c>
       <c r="B150" s="1">
-        <v>132.4006207353256</v>
+        <v>114.083288196853</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -2670,7 +3669,7 @@
         <v>151</v>
       </c>
       <c r="B151" s="1">
-        <v>132.4744343528598</v>
+        <v>114.1223784295987</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -2678,7 +3677,7 @@
         <v>152</v>
       </c>
       <c r="B152" s="1">
-        <v>132.5296305483573</v>
+        <v>114.1307652224007</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -2686,7 +3685,7 @@
         <v>153</v>
       </c>
       <c r="B153" s="1">
-        <v>132.5816998118583</v>
+        <v>114.1364766778258</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -2694,7 +3693,7 @@
         <v>154</v>
       </c>
       <c r="B154" s="1">
-        <v>132.6044502577217</v>
+        <v>114.1562424319056</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -2702,7 +3701,7 @@
         <v>155</v>
       </c>
       <c r="B155" s="1">
-        <v>132.729673947039</v>
+        <v>114.2047200001222</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -2710,7 +3709,7 @@
         <v>156</v>
       </c>
       <c r="B156" s="1">
-        <v>132.990643481224</v>
+        <v>114.2232121310074</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -2718,7 +3717,7 @@
         <v>157</v>
       </c>
       <c r="B157" s="1">
-        <v>132.9935805121691</v>
+        <v>114.2377333609813</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -2726,7 +3725,7 @@
         <v>158</v>
       </c>
       <c r="B158" s="1">
-        <v>133.0172424412924</v>
+        <v>114.2782407278108</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -2734,7 +3733,7 @@
         <v>159</v>
       </c>
       <c r="B159" s="1">
-        <v>133.0470173664501</v>
+        <v>114.3098290287035</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -2742,7 +3741,7 @@
         <v>160</v>
       </c>
       <c r="B160" s="1">
-        <v>133.1506551233277</v>
+        <v>114.3296763590119</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -2750,7 +3749,7 @@
         <v>161</v>
       </c>
       <c r="B161" s="1">
-        <v>133.3039710378434</v>
+        <v>114.3940820788603</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -2758,7 +3757,7 @@
         <v>162</v>
       </c>
       <c r="B162" s="1">
-        <v>133.4452361814381</v>
+        <v>114.4366017181397</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -2766,7 +3765,7 @@
         <v>163</v>
       </c>
       <c r="B163" s="1">
-        <v>133.4731296530535</v>
+        <v>114.5051208199172</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -2774,7 +3773,7 @@
         <v>164</v>
       </c>
       <c r="B164" s="1">
-        <v>133.6978635452127</v>
+        <v>114.5433186155488</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -2782,7 +3781,7 @@
         <v>165</v>
       </c>
       <c r="B165" s="1">
-        <v>133.7586008602386</v>
+        <v>114.5490577795923</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -2790,7 +3789,7 @@
         <v>166</v>
       </c>
       <c r="B166" s="1">
-        <v>133.8076164573903</v>
+        <v>114.5820968799014</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -2798,7 +3797,7 @@
         <v>167</v>
       </c>
       <c r="B167" s="1">
-        <v>133.8647387858678</v>
+        <v>114.5887529544187</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -2806,7 +3805,7 @@
         <v>168</v>
       </c>
       <c r="B168" s="1">
-        <v>133.920092084682</v>
+        <v>114.63584468682</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -2814,7 +3813,7 @@
         <v>169</v>
       </c>
       <c r="B169" s="1">
-        <v>133.9811738087282</v>
+        <v>114.6359140064786</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -2822,7 +3821,7 @@
         <v>170</v>
       </c>
       <c r="B170" s="1">
-        <v>134.2428215933341</v>
+        <v>114.7022962568226</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -2830,7 +3829,7 @@
         <v>171</v>
       </c>
       <c r="B171" s="1">
-        <v>134.3070564124008</v>
+        <v>114.7276836252478</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -2838,7 +3837,7 @@
         <v>172</v>
       </c>
       <c r="B172" s="1">
-        <v>134.4818075635634</v>
+        <v>114.7450598961282</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -2846,7 +3845,7 @@
         <v>173</v>
       </c>
       <c r="B173" s="1">
-        <v>134.5764056541234</v>
+        <v>114.7936216938911</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -2854,7 +3853,7 @@
         <v>174</v>
       </c>
       <c r="B174" s="1">
-        <v>134.7504436190654</v>
+        <v>114.8395222453272</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -2862,7 +3861,7 @@
         <v>175</v>
       </c>
       <c r="B175" s="1">
-        <v>134.801458522311</v>
+        <v>114.8847107691254</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -2870,7 +3869,7 @@
         <v>176</v>
       </c>
       <c r="B176" s="1">
-        <v>135.0721648454088</v>
+        <v>114.9114745846652</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -2878,7 +3877,7 @@
         <v>177</v>
       </c>
       <c r="B177" s="1">
-        <v>135.1331679148208</v>
+        <v>114.9518619166073</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -2886,7 +3885,7 @@
         <v>178</v>
       </c>
       <c r="B178" s="1">
-        <v>135.3086143984004</v>
+        <v>114.9525512150111</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -2894,7 +3893,7 @@
         <v>179</v>
       </c>
       <c r="B179" s="1">
-        <v>135.5425556788738</v>
+        <v>115.0149211128021</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -2902,7 +3901,7 @@
         <v>180</v>
       </c>
       <c r="B180" s="1">
-        <v>135.9971298595455</v>
+        <v>115.0205488527057</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -2910,7 +3909,7 @@
         <v>181</v>
       </c>
       <c r="B181" s="1">
-        <v>136.1431177762248</v>
+        <v>115.0609035683646</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -2918,7 +3917,7 @@
         <v>182</v>
       </c>
       <c r="B182" s="1">
-        <v>136.147424272235</v>
+        <v>115.0626420800751</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -2926,7 +3925,7 @@
         <v>183</v>
       </c>
       <c r="B183" s="1">
-        <v>136.4277168988233</v>
+        <v>115.0636771877305</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -2934,7 +3933,7 @@
         <v>184</v>
       </c>
       <c r="B184" s="1">
-        <v>136.4639098814952</v>
+        <v>115.0772435045716</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -2942,7 +3941,7 @@
         <v>185</v>
       </c>
       <c r="B185" s="1">
-        <v>136.7076488483891</v>
+        <v>115.0786860693424</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -2950,7 +3949,7 @@
         <v>186</v>
       </c>
       <c r="B186" s="1">
-        <v>136.8985158914812</v>
+        <v>115.0796016860821</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -2958,7 +3957,7 @@
         <v>187</v>
       </c>
       <c r="B187" s="1">
-        <v>137.0682141423244</v>
+        <v>115.0846738160146</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -2966,7 +3965,7 @@
         <v>188</v>
       </c>
       <c r="B188" s="1">
-        <v>137.1427239176866</v>
+        <v>115.1340049188879</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -2974,7 +3973,7 @@
         <v>189</v>
       </c>
       <c r="B189" s="1">
-        <v>137.2527013094927</v>
+        <v>115.2018304440228</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -2982,7 +3981,7 @@
         <v>190</v>
       </c>
       <c r="B190" s="1">
-        <v>137.2828303925376</v>
+        <v>115.2140079508356</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -2990,7 +3989,7 @@
         <v>191</v>
       </c>
       <c r="B191" s="1">
-        <v>137.2969793999234</v>
+        <v>115.269227645817</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -2998,7 +3997,7 @@
         <v>192</v>
       </c>
       <c r="B192" s="1">
-        <v>137.4754157399989</v>
+        <v>115.3127958747807</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -3006,7 +4005,7 @@
         <v>193</v>
       </c>
       <c r="B193" s="1">
-        <v>137.5315678733478</v>
+        <v>115.355001023091</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -3014,7 +4013,7 @@
         <v>194</v>
       </c>
       <c r="B194" s="1">
-        <v>137.8405324119095</v>
+        <v>115.3659147444239</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -3022,7 +4021,7 @@
         <v>195</v>
       </c>
       <c r="B195" s="1">
-        <v>138.204827195071</v>
+        <v>115.4308777430539</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -3030,7 +4029,7 @@
         <v>196</v>
       </c>
       <c r="B196" s="1">
-        <v>138.3613170519559</v>
+        <v>115.4479451045624</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -3038,7 +4037,7 @@
         <v>197</v>
       </c>
       <c r="B197" s="1">
-        <v>138.4076502903102</v>
+        <v>115.4635811481295</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -3046,7 +4045,7 @@
         <v>198</v>
       </c>
       <c r="B198" s="1">
-        <v>138.6918380727558</v>
+        <v>115.5142621691569</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -3054,7 +4053,7 @@
         <v>199</v>
       </c>
       <c r="B199" s="1">
-        <v>138.7342561425032</v>
+        <v>115.517467575567</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -3062,7 +4061,7 @@
         <v>200</v>
       </c>
       <c r="B200" s="1">
-        <v>138.9542539506856</v>
+        <v>115.5445651962146</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -3070,7 +4069,7 @@
         <v>201</v>
       </c>
       <c r="B201" s="1">
-        <v>139.1489512786926</v>
+        <v>115.5530643837317</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -3078,7 +4077,7 @@
         <v>202</v>
       </c>
       <c r="B202" s="1">
-        <v>139.2210030572633</v>
+        <v>115.6058967933578</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -3086,7 +4085,7 @@
         <v>203</v>
       </c>
       <c r="B203" s="1">
-        <v>139.5499225744606</v>
+        <v>115.6450611208302</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -3094,7 +4093,7 @@
         <v>204</v>
       </c>
       <c r="B204" s="1">
-        <v>139.7904698268517</v>
+        <v>115.6615773664466</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -3102,7 +4101,7 @@
         <v>205</v>
       </c>
       <c r="B205" s="1">
-        <v>139.9521185156612</v>
+        <v>115.6828107218037</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -3110,7 +4109,7 @@
         <v>206</v>
       </c>
       <c r="B206" s="1">
-        <v>139.9642299978598</v>
+        <v>115.6862892954402</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -3118,7 +4117,7 @@
         <v>207</v>
       </c>
       <c r="B207" s="1">
-        <v>140.2217651657554</v>
+        <v>115.6932303046975</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -3126,7 +4125,7 @@
         <v>208</v>
       </c>
       <c r="B208" s="1">
-        <v>140.4219181576626</v>
+        <v>115.6936330646188</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -3134,7 +4133,7 @@
         <v>209</v>
       </c>
       <c r="B209" s="1">
-        <v>140.4228397423457</v>
+        <v>115.7010892949569</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -3142,7 +4141,7 @@
         <v>210</v>
       </c>
       <c r="B210" s="1">
-        <v>140.4674616564985</v>
+        <v>115.7134732684824</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -3150,7 +4149,7 @@
         <v>211</v>
       </c>
       <c r="B211" s="1">
-        <v>140.7117271776148</v>
+        <v>115.7394072260758</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -3158,7 +4157,7 @@
         <v>212</v>
       </c>
       <c r="B212" s="1">
-        <v>141.0186030021931</v>
+        <v>115.7523241630014</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -3166,7 +4165,7 @@
         <v>213</v>
       </c>
       <c r="B213" s="1">
-        <v>141.1130969592363</v>
+        <v>115.7934281563089</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -3174,7 +4173,7 @@
         <v>214</v>
       </c>
       <c r="B214" s="1">
-        <v>141.1971700309032</v>
+        <v>115.8099346686525</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -3182,7 +4181,7 @@
         <v>215</v>
       </c>
       <c r="B215" s="1">
-        <v>141.3124687109154</v>
+        <v>115.8329297792183</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -3190,7 +4189,7 @@
         <v>216</v>
       </c>
       <c r="B216" s="1">
-        <v>141.4141881633905</v>
+        <v>115.8635894949314</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -3198,7 +4197,7 @@
         <v>217</v>
       </c>
       <c r="B217" s="1">
-        <v>141.6157307948109</v>
+        <v>115.8736807126701</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -3206,7 +4205,7 @@
         <v>218</v>
       </c>
       <c r="B218" s="1">
-        <v>141.8537647013028</v>
+        <v>115.8957399570128</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -3214,7 +4213,7 @@
         <v>219</v>
       </c>
       <c r="B219" s="1">
-        <v>141.8700676581266</v>
+        <v>115.9315399930317</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -3222,7 +4221,7 @@
         <v>220</v>
       </c>
       <c r="B220" s="1">
-        <v>142.0138557966405</v>
+        <v>115.9590478837542</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -3230,7 +4229,7 @@
         <v>221</v>
       </c>
       <c r="B221" s="1">
-        <v>142.0864517220795</v>
+        <v>115.963100289782</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -3238,7 +4237,7 @@
         <v>222</v>
       </c>
       <c r="B222" s="1">
-        <v>142.1218788833395</v>
+        <v>115.9950235603115</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -3246,7 +4245,7 @@
         <v>223</v>
       </c>
       <c r="B223" s="1">
-        <v>142.3017944340626</v>
+        <v>116.0357511009081</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -3254,7 +4253,7 @@
         <v>224</v>
       </c>
       <c r="B224" s="1">
-        <v>142.3028017682485</v>
+        <v>116.100489054935</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -3262,7 +4261,7 @@
         <v>225</v>
       </c>
       <c r="B225" s="1">
-        <v>142.3700664691631</v>
+        <v>116.1024352596279</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -3270,7 +4269,7 @@
         <v>226</v>
       </c>
       <c r="B226" s="1">
-        <v>142.6271851689096</v>
+        <v>116.1029699699378</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -3278,7 +4277,7 @@
         <v>227</v>
       </c>
       <c r="B227" s="1">
-        <v>142.7074627034073</v>
+        <v>116.1360227059373</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -3286,7 +4285,7 @@
         <v>228</v>
       </c>
       <c r="B228" s="1">
-        <v>142.9177169598384</v>
+        <v>116.1507501996863</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -3294,7 +4293,7 @@
         <v>229</v>
       </c>
       <c r="B229" s="1">
-        <v>143.4162025847165</v>
+        <v>116.1721813914905</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -3302,7 +4301,7 @@
         <v>230</v>
       </c>
       <c r="B230" s="1">
-        <v>143.7563156599863</v>
+        <v>116.2049547073389</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -3310,7 +4309,7 @@
         <v>231</v>
       </c>
       <c r="B231" s="1">
-        <v>143.7874838261025</v>
+        <v>116.2554165667749</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -3318,7 +4317,7 @@
         <v>232</v>
       </c>
       <c r="B232" s="1">
-        <v>143.9313233484539</v>
+        <v>116.2712293800288</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -3326,7 +4325,7 @@
         <v>233</v>
       </c>
       <c r="B233" s="1">
-        <v>143.9386954747752</v>
+        <v>116.2791485266362</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -3334,7 +4333,7 @@
         <v>234</v>
       </c>
       <c r="B234" s="1">
-        <v>144.0150197118303</v>
+        <v>116.2817661089989</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -3342,7 +4341,7 @@
         <v>235</v>
       </c>
       <c r="B235" s="1">
-        <v>144.1104673369159</v>
+        <v>116.2940428956452</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -3350,7 +4349,7 @@
         <v>236</v>
       </c>
       <c r="B236" s="1">
-        <v>144.2364733919311</v>
+        <v>116.3106178360152</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -3358,7 +4357,7 @@
         <v>237</v>
       </c>
       <c r="B237" s="1">
-        <v>145.0753221655055</v>
+        <v>116.3207061397035</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -3366,7 +4365,7 @@
         <v>238</v>
       </c>
       <c r="B238" s="1">
-        <v>145.2886458421303</v>
+        <v>116.3429095729792</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -3374,7 +4373,7 @@
         <v>239</v>
       </c>
       <c r="B239" s="1">
-        <v>145.3003503096471</v>
+        <v>116.3631223774945</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -3382,7 +4381,7 @@
         <v>240</v>
       </c>
       <c r="B240" s="1">
-        <v>145.4208761694426</v>
+        <v>116.4492331877463</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -3390,7 +4389,7 @@
         <v>241</v>
       </c>
       <c r="B241" s="1">
-        <v>145.5335703874646</v>
+        <v>116.4519905116477</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -3398,7 +4397,7 @@
         <v>242</v>
       </c>
       <c r="B242" s="1">
-        <v>145.5602060985507</v>
+        <v>116.4639974722631</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -3406,7 +4405,7 @@
         <v>243</v>
       </c>
       <c r="B243" s="1">
-        <v>145.6509150730755</v>
+        <v>116.4713707695876</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -3414,7 +4413,7 @@
         <v>244</v>
       </c>
       <c r="B244" s="1">
-        <v>145.7341966036603</v>
+        <v>116.5025886510251</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -3422,7 +4421,7 @@
         <v>245</v>
       </c>
       <c r="B245" s="1">
-        <v>146.2745292418855</v>
+        <v>116.5036622628921</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -3430,7 +4429,7 @@
         <v>246</v>
       </c>
       <c r="B246" s="1">
-        <v>146.3484271556072</v>
+        <v>116.5348271838349</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -3438,7 +4437,7 @@
         <v>247</v>
       </c>
       <c r="B247" s="1">
-        <v>146.4625996965309</v>
+        <v>116.564525179259</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -3446,7 +4445,7 @@
         <v>248</v>
       </c>
       <c r="B248" s="1">
-        <v>146.7132691819577</v>
+        <v>116.5978222447868</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -3454,7 +4453,7 @@
         <v>249</v>
       </c>
       <c r="B249" s="1">
-        <v>147.1953432862092</v>
+        <v>116.5990025908338</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -3462,7 +4461,7 @@
         <v>250</v>
       </c>
       <c r="B250" s="1">
-        <v>147.3498599813152</v>
+        <v>116.6453631904678</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -3470,7 +4469,7 @@
         <v>251</v>
       </c>
       <c r="B251" s="1">
-        <v>147.6810226490112</v>
+        <v>116.6488196484038</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -3478,7 +4477,7 @@
         <v>252</v>
       </c>
       <c r="B252" s="1">
-        <v>148.1367650581797</v>
+        <v>116.6777486605849</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -3486,7 +4485,7 @@
         <v>253</v>
       </c>
       <c r="B253" s="1">
-        <v>148.378278901612</v>
+        <v>116.7091541620856</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -3494,7 +4493,7 @@
         <v>254</v>
       </c>
       <c r="B254" s="1">
-        <v>148.6746919920275</v>
+        <v>116.7099428283593</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -3502,7 +4501,7 @@
         <v>255</v>
       </c>
       <c r="B255" s="1">
-        <v>148.8898279476895</v>
+        <v>116.7285773028293</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -3510,7 +4509,7 @@
         <v>256</v>
       </c>
       <c r="B256" s="1">
-        <v>149.0198758319567</v>
+        <v>116.7646871464885</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -3518,7 +4517,7 @@
         <v>257</v>
       </c>
       <c r="B257" s="1">
-        <v>149.1204312994956</v>
+        <v>116.8316840881842</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -3526,7 +4525,7 @@
         <v>258</v>
       </c>
       <c r="B258" s="1">
-        <v>149.1495617249296</v>
+        <v>116.8590560326206</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -3534,7 +4533,7 @@
         <v>259</v>
       </c>
       <c r="B259" s="1">
-        <v>149.2274859982583</v>
+        <v>116.865858850697</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -3542,7 +4541,7 @@
         <v>260</v>
       </c>
       <c r="B260" s="1">
-        <v>149.265569538992</v>
+        <v>116.94558503514</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -3550,7 +4549,7 @@
         <v>261</v>
       </c>
       <c r="B261" s="1">
-        <v>149.3630610031549</v>
+        <v>116.9548592003947</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -3558,7 +4557,7 @@
         <v>262</v>
       </c>
       <c r="B262" s="1">
-        <v>149.5005924538437</v>
+        <v>116.9953508079986</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -3566,7 +4565,7 @@
         <v>263</v>
       </c>
       <c r="B263" s="1">
-        <v>149.9886608150451</v>
+        <v>117.0077135142714</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -3574,7 +4573,7 @@
         <v>264</v>
       </c>
       <c r="B264" s="1">
-        <v>150.121320521442</v>
+        <v>117.0114021150171</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -3582,7 +4581,7 @@
         <v>265</v>
       </c>
       <c r="B265" s="1">
-        <v>150.5017364316517</v>
+        <v>117.0154110821537</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -3590,7 +4589,7 @@
         <v>266</v>
       </c>
       <c r="B266" s="1">
-        <v>150.557000656446</v>
+        <v>117.0456664574378</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -3598,7 +4597,7 @@
         <v>267</v>
       </c>
       <c r="B267" s="1">
-        <v>150.6358975752698</v>
+        <v>117.0671706455902</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -3606,7 +4605,7 @@
         <v>268</v>
       </c>
       <c r="B268" s="1">
-        <v>150.935765854733</v>
+        <v>117.0744135368296</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -3614,7 +4613,7 @@
         <v>269</v>
       </c>
       <c r="B269" s="1">
-        <v>150.9652225945763</v>
+        <v>117.0872497029365</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -3622,7 +4621,7 @@
         <v>270</v>
       </c>
       <c r="B270" s="1">
-        <v>151.093474626043</v>
+        <v>117.2146820675713</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -3630,7 +4629,7 @@
         <v>271</v>
       </c>
       <c r="B271" s="1">
-        <v>151.2203655790371</v>
+        <v>117.2201303063032</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -3638,7 +4637,7 @@
         <v>272</v>
       </c>
       <c r="B272" s="1">
-        <v>151.9778954695466</v>
+        <v>117.2242445204989</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -3646,7 +4645,7 @@
         <v>273</v>
       </c>
       <c r="B273" s="1">
-        <v>152.0353602246721</v>
+        <v>117.2642467611347</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -3654,7 +4653,7 @@
         <v>274</v>
       </c>
       <c r="B274" s="1">
-        <v>152.0384165611634</v>
+        <v>117.3284031893641</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -3662,7 +4661,7 @@
         <v>275</v>
       </c>
       <c r="B275" s="1">
-        <v>152.0761251676269</v>
+        <v>117.3456947006276</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -3670,7 +4669,7 @@
         <v>276</v>
       </c>
       <c r="B276" s="1">
-        <v>152.3855231195887</v>
+        <v>117.3692003463086</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -3678,7 +4677,7 @@
         <v>277</v>
       </c>
       <c r="B277" s="1">
-        <v>152.5388909543182</v>
+        <v>117.3707336082891</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -3686,7 +4685,7 @@
         <v>278</v>
       </c>
       <c r="B278" s="1">
-        <v>152.8399818630474</v>
+        <v>117.3931172181952</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -3694,7 +4693,7 @@
         <v>279</v>
       </c>
       <c r="B279" s="1">
-        <v>153.0833996554127</v>
+        <v>117.4647318177871</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -3702,7 +4701,7 @@
         <v>280</v>
       </c>
       <c r="B280" s="1">
-        <v>153.1896292117925</v>
+        <v>117.4977419621957</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -3710,7 +4709,7 @@
         <v>281</v>
       </c>
       <c r="B281" s="1">
-        <v>153.1907853051449</v>
+        <v>117.5033612248346</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -3718,7 +4717,7 @@
         <v>282</v>
       </c>
       <c r="B282" s="1">
-        <v>153.2729392427558</v>
+        <v>117.5397676034224</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -3726,7 +4725,7 @@
         <v>283</v>
       </c>
       <c r="B283" s="1">
-        <v>153.3900893469971</v>
+        <v>117.5570551691597</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -3734,7 +4733,7 @@
         <v>284</v>
       </c>
       <c r="B284" s="1">
-        <v>153.9534793149107</v>
+        <v>117.5711910082227</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -3742,7 +4741,7 @@
         <v>285</v>
       </c>
       <c r="B285" s="1">
-        <v>154.0893150303502</v>
+        <v>117.5962584574623</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -3750,7 +4749,7 @@
         <v>286</v>
       </c>
       <c r="B286" s="1">
-        <v>154.4791600997551</v>
+        <v>117.613883807638</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -3758,7 +4757,7 @@
         <v>287</v>
       </c>
       <c r="B287" s="1">
-        <v>154.5234311738164</v>
+        <v>117.6500676235055</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -3766,7 +4765,7 @@
         <v>288</v>
       </c>
       <c r="B288" s="1">
-        <v>154.8394154220977</v>
+        <v>117.6504743564992</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -3774,7 +4773,7 @@
         <v>289</v>
       </c>
       <c r="B289" s="1">
-        <v>154.9093034705795</v>
+        <v>117.6846822235248</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -3782,7 +4781,7 @@
         <v>290</v>
       </c>
       <c r="B290" s="1">
-        <v>155.1789599824439</v>
+        <v>117.6988550348087</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -3790,7 +4789,7 @@
         <v>291</v>
       </c>
       <c r="B291" s="1">
-        <v>155.5216340497774</v>
+        <v>117.7308637618376</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -3798,7 +4797,7 @@
         <v>292</v>
       </c>
       <c r="B292" s="1">
-        <v>155.9511070710915</v>
+        <v>117.7634446841664</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -3806,7 +4805,7 @@
         <v>293</v>
       </c>
       <c r="B293" s="1">
-        <v>155.953914392323</v>
+        <v>117.7706478892038</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -3814,7 +4813,7 @@
         <v>294</v>
       </c>
       <c r="B294" s="1">
-        <v>156.0737209289954</v>
+        <v>117.7840211537754</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -3822,7 +4821,7 @@
         <v>295</v>
       </c>
       <c r="B295" s="1">
-        <v>156.7883754504644</v>
+        <v>117.7976517763748</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -3830,7 +4829,7 @@
         <v>296</v>
       </c>
       <c r="B296" s="1">
-        <v>157.5882032314923</v>
+        <v>117.8836037717644</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -3838,7 +4837,7 @@
         <v>297</v>
       </c>
       <c r="B297" s="1">
-        <v>157.6979241085656</v>
+        <v>117.9097603732758</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -3846,7 +4845,7 @@
         <v>298</v>
       </c>
       <c r="B298" s="1">
-        <v>157.746982584233</v>
+        <v>117.9605012122933</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -3854,7 +4853,7 @@
         <v>299</v>
       </c>
       <c r="B299" s="1">
-        <v>158.4782812422286</v>
+        <v>117.966998183845</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -3862,7 +4861,7 @@
         <v>300</v>
       </c>
       <c r="B300" s="1">
-        <v>158.6524613545851</v>
+        <v>117.9849896870622</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -3870,7 +4869,7 @@
         <v>301</v>
       </c>
       <c r="B301" s="1">
-        <v>158.957195248279</v>
+        <v>118.0021126134324</v>
       </c>
     </row>
     <row r="302" spans="1:2">
@@ -3878,7 +4877,7 @@
         <v>302</v>
       </c>
       <c r="B302" s="1">
-        <v>159.4495990989138</v>
+        <v>118.0332387104532</v>
       </c>
     </row>
     <row r="303" spans="1:2">
@@ -3886,7 +4885,7 @@
         <v>303</v>
       </c>
       <c r="B303" s="1">
-        <v>159.9634167640314</v>
+        <v>118.062093385185</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -3894,7 +4893,7 @@
         <v>304</v>
       </c>
       <c r="B304" s="1">
-        <v>161.271886214352</v>
+        <v>118.0711744485461</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -3902,7 +4901,7 @@
         <v>305</v>
       </c>
       <c r="B305" s="1">
-        <v>161.7244857802673</v>
+        <v>118.0733790044283</v>
       </c>
     </row>
     <row r="306" spans="1:2">
@@ -3910,7 +4909,7 @@
         <v>306</v>
       </c>
       <c r="B306" s="1">
-        <v>162.0177366423817</v>
+        <v>118.0876511068666</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -3918,7 +4917,7 @@
         <v>307</v>
       </c>
       <c r="B307" s="1">
-        <v>162.983220167706</v>
+        <v>118.1867379074273</v>
       </c>
     </row>
     <row r="308" spans="1:2">
@@ -3926,7 +4925,7 @@
         <v>308</v>
       </c>
       <c r="B308" s="1">
-        <v>163.7094643231712</v>
+        <v>118.186928905023</v>
       </c>
     </row>
     <row r="309" spans="1:2">
@@ -3934,7 +4933,7 @@
         <v>309</v>
       </c>
       <c r="B309" s="1">
-        <v>163.8084277208574</v>
+        <v>118.2201321704121</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -3942,7 +4941,7 @@
         <v>310</v>
       </c>
       <c r="B310" s="1">
-        <v>164.7327318809673</v>
+        <v>118.3141280846783</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -3950,7 +4949,7 @@
         <v>311</v>
       </c>
       <c r="B311" s="1">
-        <v>165.5071257169221</v>
+        <v>118.3400787144913</v>
       </c>
     </row>
     <row r="312" spans="1:2">
@@ -3958,7 +4957,7 @@
         <v>312</v>
       </c>
       <c r="B312" s="1">
-        <v>165.6083176441935</v>
+        <v>118.3534022565145</v>
       </c>
     </row>
     <row r="313" spans="1:2">
@@ -3966,7 +4965,7 @@
         <v>313</v>
       </c>
       <c r="B313" s="1">
-        <v>167.2049992555237</v>
+        <v>118.3682873474836</v>
       </c>
     </row>
     <row r="314" spans="1:2">
@@ -3974,7 +4973,7 @@
         <v>314</v>
       </c>
       <c r="B314" s="1">
-        <v>168.4929689948519</v>
+        <v>118.402755938659</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -3982,7 +4981,7 @@
         <v>315</v>
       </c>
       <c r="B315" s="1">
-        <v>169.3487770323608</v>
+        <v>118.4417349954097</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -3990,7 +4989,7 @@
         <v>316</v>
       </c>
       <c r="B316" s="1">
-        <v>169.4788705640971</v>
+        <v>118.4451707052528</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -3998,7 +4997,7 @@
         <v>317</v>
       </c>
       <c r="B317" s="1">
-        <v>170.3714337103268</v>
+        <v>118.4576279930599</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -4006,7 +5005,7 @@
         <v>318</v>
       </c>
       <c r="B318" s="1">
-        <v>171.6247865032925</v>
+        <v>118.5067489573166</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -4014,7 +5013,7 @@
         <v>319</v>
       </c>
       <c r="B319" s="1">
-        <v>172.0937866526471</v>
+        <v>118.5156836583018</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -4022,7 +5021,7 @@
         <v>320</v>
       </c>
       <c r="B320" s="1">
-        <v>172.1902516245763</v>
+        <v>118.5284053951491</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -4030,7 +5029,7 @@
         <v>321</v>
       </c>
       <c r="B321" s="1">
-        <v>172.4399357066671</v>
+        <v>118.545356253334</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -4038,7 +5037,7 @@
         <v>322</v>
       </c>
       <c r="B322" s="1">
-        <v>175.7298073953244</v>
+        <v>118.6408995050248</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -4046,7 +5045,7 @@
         <v>323</v>
       </c>
       <c r="B323" s="1">
-        <v>180.0827365568298</v>
+        <v>118.7284008865864</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -4054,7 +5053,7 @@
         <v>324</v>
       </c>
       <c r="B324" s="1">
-        <v>181.797196523146</v>
+        <v>118.8896079053186</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -4062,7 +5061,7 @@
         <v>325</v>
       </c>
       <c r="B325" s="1">
-        <v>182.7114409443364</v>
+        <v>118.9191510389957</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -4070,7 +5069,7 @@
         <v>326</v>
       </c>
       <c r="B326" s="1">
-        <v>185.1023422931817</v>
+        <v>118.9205287927692</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -4078,7 +5077,7 @@
         <v>327</v>
       </c>
       <c r="B327" s="1">
-        <v>186.3378649961078</v>
+        <v>118.9911222976591</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -4086,7 +5085,7 @@
         <v>328</v>
       </c>
       <c r="B328" s="1">
-        <v>186.5350455563866</v>
+        <v>119.1016902688193</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -4094,7 +5093,7 @@
         <v>329</v>
       </c>
       <c r="B329" s="1">
-        <v>187.0004646974953</v>
+        <v>119.158000402998</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -4102,7 +5101,7 @@
         <v>330</v>
       </c>
       <c r="B330" s="1">
-        <v>187.424600436858</v>
+        <v>119.1592238636045</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -4110,7 +5109,7 @@
         <v>331</v>
       </c>
       <c r="B331" s="1">
-        <v>188.1464529940239</v>
+        <v>119.2025204237945</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -4118,7 +5117,7 @@
         <v>332</v>
       </c>
       <c r="B332" s="1">
-        <v>189.8005032163167</v>
+        <v>119.2189257504577</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -4126,7 +5125,7 @@
         <v>333</v>
       </c>
       <c r="B333" s="1">
-        <v>193.4035075032654</v>
+        <v>119.2626293869509</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -4134,7 +5133,7 @@
         <v>334</v>
       </c>
       <c r="B334" s="1">
-        <v>193.7459530378031</v>
+        <v>119.2809633789582</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -4142,7 +5141,7 @@
         <v>335</v>
       </c>
       <c r="B335" s="1">
-        <v>198.4079176638729</v>
+        <v>119.3186710442844</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -4150,7 +5149,7 @@
         <v>336</v>
       </c>
       <c r="B336" s="1">
-        <v>199.2459657552803</v>
+        <v>119.362713705729</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -4158,7 +5157,7 @@
         <v>337</v>
       </c>
       <c r="B337" s="1">
-        <v>201.9134151446149</v>
+        <v>119.4676707606156</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -4166,7 +5165,7 @@
         <v>338</v>
       </c>
       <c r="B338" s="1">
-        <v>202.1041236781414</v>
+        <v>119.5330154877332</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -4174,7 +5173,7 @@
         <v>339</v>
       </c>
       <c r="B339" s="1">
-        <v>202.1545778035803</v>
+        <v>119.7311926070115</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -4182,7 +5181,7 @@
         <v>340</v>
       </c>
       <c r="B340" s="1">
-        <v>209.3392467587773</v>
+        <v>119.7504024728128</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -4190,7 +5189,7 @@
         <v>341</v>
       </c>
       <c r="B341" s="1">
-        <v>210.78363520465</v>
+        <v>119.7591818796765</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -4198,7 +5197,7 @@
         <v>342</v>
       </c>
       <c r="B342" s="1">
-        <v>210.7993659480594</v>
+        <v>119.8158624160783</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -4206,7 +5205,7 @@
         <v>343</v>
       </c>
       <c r="B343" s="1">
-        <v>213.4429273079405</v>
+        <v>119.8291333895149</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -4214,7 +5213,7 @@
         <v>344</v>
       </c>
       <c r="B344" s="1">
-        <v>217.0080003718516</v>
+        <v>119.9505124360234</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -4222,7 +5221,7 @@
         <v>345</v>
       </c>
       <c r="B345" s="1">
-        <v>218.3231152978015</v>
+        <v>119.9988628443847</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -4230,7 +5229,7 @@
         <v>346</v>
       </c>
       <c r="B346" s="1">
-        <v>218.5788222250409</v>
+        <v>120.0058867698036</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -4238,7 +5237,7 @@
         <v>347</v>
       </c>
       <c r="B347" s="1">
-        <v>220.677249406837</v>
+        <v>120.0449194225551</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -4246,7 +5245,7 @@
         <v>348</v>
       </c>
       <c r="B348" s="1">
-        <v>220.9878353105352</v>
+        <v>120.1226387704862</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -4254,7 +5253,7 @@
         <v>349</v>
       </c>
       <c r="B349" s="1">
-        <v>222.3549735307382</v>
+        <v>120.1736089649266</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -4262,7 +5261,7 @@
         <v>350</v>
       </c>
       <c r="B350" s="1">
-        <v>231.1366346494183</v>
+        <v>120.1765416181346</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -4270,7 +5269,7 @@
         <v>351</v>
       </c>
       <c r="B351" s="1">
-        <v>233.2057634101486</v>
+        <v>120.2173606811577</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -4278,7 +5277,7 @@
         <v>352</v>
       </c>
       <c r="B352" s="1">
-        <v>240.9037995370595</v>
+        <v>120.2306526520568</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -4286,7 +5285,7 @@
         <v>353</v>
       </c>
       <c r="B353" s="1">
-        <v>241.9801397446898</v>
+        <v>120.2396645325777</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -4294,7 +5293,7 @@
         <v>354</v>
       </c>
       <c r="B354" s="1">
-        <v>255.1950520930116</v>
+        <v>120.2446735690673</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -4302,7 +5301,7 @@
         <v>355</v>
       </c>
       <c r="B355" s="1">
-        <v>274.3894448654654</v>
+        <v>120.2766450974419</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -4310,7 +5309,7 @@
         <v>356</v>
       </c>
       <c r="B356" s="1">
-        <v>322.7169382634154</v>
+        <v>120.3653902318826</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -4318,7 +5317,7 @@
         <v>357</v>
       </c>
       <c r="B357" s="1">
-        <v>336.5309966365377</v>
+        <v>120.3718642953306</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -4326,7 +5325,7 @@
         <v>358</v>
       </c>
       <c r="B358" s="1">
-        <v>342.6013602293594</v>
+        <v>120.3801375065622</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -4334,7 +5333,7 @@
         <v>359</v>
       </c>
       <c r="B359" s="1">
-        <v>351.853047395245</v>
+        <v>120.4008868860399</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -4342,7 +5341,7 @@
         <v>360</v>
       </c>
       <c r="B360" s="1">
-        <v>371.1404354059238</v>
+        <v>120.5144155321002</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -4350,7 +5349,7 @@
         <v>361</v>
       </c>
       <c r="B361" s="1">
-        <v>392.6150703737437</v>
+        <v>120.7230965113951</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -4358,7 +5357,7 @@
         <v>362</v>
       </c>
       <c r="B362" s="1">
-        <v>463.9789720453022</v>
+        <v>120.7830465501431</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -4366,7 +5365,7 @@
         <v>363</v>
       </c>
       <c r="B363" s="1">
-        <v>555.4575109929298</v>
+        <v>120.8080637530113</v>
       </c>
     </row>
     <row r="364" spans="1:2">
@@ -4374,7 +5373,7 @@
         <v>364</v>
       </c>
       <c r="B364" s="1">
-        <v>584.1406074220556</v>
+        <v>120.8574010136578</v>
       </c>
     </row>
     <row r="365" spans="1:2">
@@ -4382,7 +5381,2671 @@
         <v>365</v>
       </c>
       <c r="B365" s="1">
-        <v>780.6369087437845</v>
+        <v>120.8859355540577</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2">
+      <c r="A366" t="s">
+        <v>366</v>
+      </c>
+      <c r="B366" s="1">
+        <v>120.9219453870675</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2">
+      <c r="A367" t="s">
+        <v>367</v>
+      </c>
+      <c r="B367" s="1">
+        <v>121.0062555833693</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2">
+      <c r="A368" t="s">
+        <v>368</v>
+      </c>
+      <c r="B368" s="1">
+        <v>121.0291612184205</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2">
+      <c r="A369" t="s">
+        <v>369</v>
+      </c>
+      <c r="B369" s="1">
+        <v>121.0694316583474</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2">
+      <c r="A370" t="s">
+        <v>370</v>
+      </c>
+      <c r="B370" s="1">
+        <v>121.1628689270335</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2">
+      <c r="A371" t="s">
+        <v>371</v>
+      </c>
+      <c r="B371" s="1">
+        <v>121.1861746419489</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2">
+      <c r="A372" t="s">
+        <v>372</v>
+      </c>
+      <c r="B372" s="1">
+        <v>121.1962094394326</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2">
+      <c r="A373" t="s">
+        <v>373</v>
+      </c>
+      <c r="B373" s="1">
+        <v>121.1963541098772</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2">
+      <c r="A374" t="s">
+        <v>374</v>
+      </c>
+      <c r="B374" s="1">
+        <v>121.3165976896054</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2">
+      <c r="A375" t="s">
+        <v>375</v>
+      </c>
+      <c r="B375" s="1">
+        <v>121.344304065057</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2">
+      <c r="A376" t="s">
+        <v>376</v>
+      </c>
+      <c r="B376" s="1">
+        <v>121.3477086103811</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2">
+      <c r="A377" t="s">
+        <v>377</v>
+      </c>
+      <c r="B377" s="1">
+        <v>121.4034035359424</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2">
+      <c r="A378" t="s">
+        <v>378</v>
+      </c>
+      <c r="B378" s="1">
+        <v>121.4778194105959</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2">
+      <c r="A379" t="s">
+        <v>379</v>
+      </c>
+      <c r="B379" s="1">
+        <v>121.4897626159857</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2">
+      <c r="A380" t="s">
+        <v>380</v>
+      </c>
+      <c r="B380" s="1">
+        <v>121.5203168575304</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2">
+      <c r="A381" t="s">
+        <v>381</v>
+      </c>
+      <c r="B381" s="1">
+        <v>121.532812089473</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2">
+      <c r="A382" t="s">
+        <v>382</v>
+      </c>
+      <c r="B382" s="1">
+        <v>121.5347912055628</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2">
+      <c r="A383" t="s">
+        <v>383</v>
+      </c>
+      <c r="B383" s="1">
+        <v>121.5625219798987</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2">
+      <c r="A384" t="s">
+        <v>384</v>
+      </c>
+      <c r="B384" s="1">
+        <v>121.5815979644305</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2">
+      <c r="A385" t="s">
+        <v>385</v>
+      </c>
+      <c r="B385" s="1">
+        <v>121.5825541871181</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2">
+      <c r="A386" t="s">
+        <v>386</v>
+      </c>
+      <c r="B386" s="1">
+        <v>121.5838560267638</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2">
+      <c r="A387" t="s">
+        <v>387</v>
+      </c>
+      <c r="B387" s="1">
+        <v>121.6535278130965</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2">
+      <c r="A388" t="s">
+        <v>388</v>
+      </c>
+      <c r="B388" s="1">
+        <v>121.7052632689697</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2">
+      <c r="A389" t="s">
+        <v>389</v>
+      </c>
+      <c r="B389" s="1">
+        <v>121.7423774680662</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2">
+      <c r="A390" t="s">
+        <v>390</v>
+      </c>
+      <c r="B390" s="1">
+        <v>121.8636656704172</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2">
+      <c r="A391" t="s">
+        <v>391</v>
+      </c>
+      <c r="B391" s="1">
+        <v>121.8718360235135</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2">
+      <c r="A392" t="s">
+        <v>392</v>
+      </c>
+      <c r="B392" s="1">
+        <v>122.0070512101737</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2">
+      <c r="A393" t="s">
+        <v>393</v>
+      </c>
+      <c r="B393" s="1">
+        <v>122.0809046427897</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2">
+      <c r="A394" t="s">
+        <v>394</v>
+      </c>
+      <c r="B394" s="1">
+        <v>122.095223885909</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2">
+      <c r="A395" t="s">
+        <v>395</v>
+      </c>
+      <c r="B395" s="1">
+        <v>122.1023879976139</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2">
+      <c r="A396" t="s">
+        <v>396</v>
+      </c>
+      <c r="B396" s="1">
+        <v>122.2182882230829</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2">
+      <c r="A397" t="s">
+        <v>397</v>
+      </c>
+      <c r="B397" s="1">
+        <v>122.2989965321824</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2">
+      <c r="A398" t="s">
+        <v>398</v>
+      </c>
+      <c r="B398" s="1">
+        <v>122.3223995875286</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2">
+      <c r="A399" t="s">
+        <v>399</v>
+      </c>
+      <c r="B399" s="1">
+        <v>122.3372908988925</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2">
+      <c r="A400" t="s">
+        <v>400</v>
+      </c>
+      <c r="B400" s="1">
+        <v>122.3906126505646</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2">
+      <c r="A401" t="s">
+        <v>401</v>
+      </c>
+      <c r="B401" s="1">
+        <v>122.4351025069768</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2">
+      <c r="A402" t="s">
+        <v>402</v>
+      </c>
+      <c r="B402" s="1">
+        <v>122.4515750704276</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2">
+      <c r="A403" t="s">
+        <v>403</v>
+      </c>
+      <c r="B403" s="1">
+        <v>122.5205920212276</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2">
+      <c r="A404" t="s">
+        <v>404</v>
+      </c>
+      <c r="B404" s="1">
+        <v>122.6290816731153</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2">
+      <c r="A405" t="s">
+        <v>405</v>
+      </c>
+      <c r="B405" s="1">
+        <v>122.6522939412293</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2">
+      <c r="A406" t="s">
+        <v>406</v>
+      </c>
+      <c r="B406" s="1">
+        <v>122.7110564756402</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2">
+      <c r="A407" t="s">
+        <v>407</v>
+      </c>
+      <c r="B407" s="1">
+        <v>122.8413433957595</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2">
+      <c r="A408" t="s">
+        <v>408</v>
+      </c>
+      <c r="B408" s="1">
+        <v>122.8487896702169</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2">
+      <c r="A409" t="s">
+        <v>409</v>
+      </c>
+      <c r="B409" s="1">
+        <v>122.8732279937168</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2">
+      <c r="A410" t="s">
+        <v>410</v>
+      </c>
+      <c r="B410" s="1">
+        <v>122.9019764865729</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2">
+      <c r="A411" t="s">
+        <v>411</v>
+      </c>
+      <c r="B411" s="1">
+        <v>122.9220066433827</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2">
+      <c r="A412" t="s">
+        <v>412</v>
+      </c>
+      <c r="B412" s="1">
+        <v>123.114743882014</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2">
+      <c r="A413" t="s">
+        <v>413</v>
+      </c>
+      <c r="B413" s="1">
+        <v>123.1408839568825</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2">
+      <c r="A414" t="s">
+        <v>414</v>
+      </c>
+      <c r="B414" s="1">
+        <v>123.1803006419766</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2">
+      <c r="A415" t="s">
+        <v>415</v>
+      </c>
+      <c r="B415" s="1">
+        <v>123.2115856089457</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2">
+      <c r="A416" t="s">
+        <v>416</v>
+      </c>
+      <c r="B416" s="1">
+        <v>123.2294412423071</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2">
+      <c r="A417" t="s">
+        <v>417</v>
+      </c>
+      <c r="B417" s="1">
+        <v>123.3070287918925</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2">
+      <c r="A418" t="s">
+        <v>418</v>
+      </c>
+      <c r="B418" s="1">
+        <v>123.3161985822766</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2">
+      <c r="A419" t="s">
+        <v>419</v>
+      </c>
+      <c r="B419" s="1">
+        <v>123.3409516592568</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2">
+      <c r="A420" t="s">
+        <v>420</v>
+      </c>
+      <c r="B420" s="1">
+        <v>123.3762609542272</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2">
+      <c r="A421" t="s">
+        <v>421</v>
+      </c>
+      <c r="B421" s="1">
+        <v>123.420710320796</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2">
+      <c r="A422" t="s">
+        <v>422</v>
+      </c>
+      <c r="B422" s="1">
+        <v>123.4277833718676</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2">
+      <c r="A423" t="s">
+        <v>423</v>
+      </c>
+      <c r="B423" s="1">
+        <v>123.4311380773394</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2">
+      <c r="A424" t="s">
+        <v>424</v>
+      </c>
+      <c r="B424" s="1">
+        <v>123.4399765096335</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2">
+      <c r="A425" t="s">
+        <v>425</v>
+      </c>
+      <c r="B425" s="1">
+        <v>123.4456319038048</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2">
+      <c r="A426" t="s">
+        <v>426</v>
+      </c>
+      <c r="B426" s="1">
+        <v>123.51601358472</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2">
+      <c r="A427" t="s">
+        <v>427</v>
+      </c>
+      <c r="B427" s="1">
+        <v>123.5250973819992</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2">
+      <c r="A428" t="s">
+        <v>428</v>
+      </c>
+      <c r="B428" s="1">
+        <v>123.5267924922484</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2">
+      <c r="A429" t="s">
+        <v>429</v>
+      </c>
+      <c r="B429" s="1">
+        <v>123.5384005897132</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2">
+      <c r="A430" t="s">
+        <v>430</v>
+      </c>
+      <c r="B430" s="1">
+        <v>123.5412492139322</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2">
+      <c r="A431" t="s">
+        <v>431</v>
+      </c>
+      <c r="B431" s="1">
+        <v>123.5580743178528</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2">
+      <c r="A432" t="s">
+        <v>432</v>
+      </c>
+      <c r="B432" s="1">
+        <v>123.6379186140544</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2">
+      <c r="A433" t="s">
+        <v>433</v>
+      </c>
+      <c r="B433" s="1">
+        <v>123.697015347881</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2">
+      <c r="A434" t="s">
+        <v>434</v>
+      </c>
+      <c r="B434" s="1">
+        <v>123.81821702582</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2">
+      <c r="A435" t="s">
+        <v>435</v>
+      </c>
+      <c r="B435" s="1">
+        <v>123.8260083492633</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2">
+      <c r="A436" t="s">
+        <v>436</v>
+      </c>
+      <c r="B436" s="1">
+        <v>123.8434905102079</v>
+      </c>
+    </row>
+    <row r="437" spans="1:2">
+      <c r="A437" t="s">
+        <v>437</v>
+      </c>
+      <c r="B437" s="1">
+        <v>123.9437050003249</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2">
+      <c r="A438" t="s">
+        <v>438</v>
+      </c>
+      <c r="B438" s="1">
+        <v>124.1215811521256</v>
+      </c>
+    </row>
+    <row r="439" spans="1:2">
+      <c r="A439" t="s">
+        <v>439</v>
+      </c>
+      <c r="B439" s="1">
+        <v>124.1524852589919</v>
+      </c>
+    </row>
+    <row r="440" spans="1:2">
+      <c r="A440" t="s">
+        <v>440</v>
+      </c>
+      <c r="B440" s="1">
+        <v>124.208487961111</v>
+      </c>
+    </row>
+    <row r="441" spans="1:2">
+      <c r="A441" t="s">
+        <v>441</v>
+      </c>
+      <c r="B441" s="1">
+        <v>124.2227849517624</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2">
+      <c r="A442" t="s">
+        <v>442</v>
+      </c>
+      <c r="B442" s="1">
+        <v>124.38796792896</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2">
+      <c r="A443" t="s">
+        <v>443</v>
+      </c>
+      <c r="B443" s="1">
+        <v>124.4058861986366</v>
+      </c>
+    </row>
+    <row r="444" spans="1:2">
+      <c r="A444" t="s">
+        <v>444</v>
+      </c>
+      <c r="B444" s="1">
+        <v>124.6504775113191</v>
+      </c>
+    </row>
+    <row r="445" spans="1:2">
+      <c r="A445" t="s">
+        <v>445</v>
+      </c>
+      <c r="B445" s="1">
+        <v>124.8259021311593</v>
+      </c>
+    </row>
+    <row r="446" spans="1:2">
+      <c r="A446" t="s">
+        <v>446</v>
+      </c>
+      <c r="B446" s="1">
+        <v>124.8681684992617</v>
+      </c>
+    </row>
+    <row r="447" spans="1:2">
+      <c r="A447" t="s">
+        <v>447</v>
+      </c>
+      <c r="B447" s="1">
+        <v>125.0150267295282</v>
+      </c>
+    </row>
+    <row r="448" spans="1:2">
+      <c r="A448" t="s">
+        <v>448</v>
+      </c>
+      <c r="B448" s="1">
+        <v>125.0620754250666</v>
+      </c>
+    </row>
+    <row r="449" spans="1:2">
+      <c r="A449" t="s">
+        <v>449</v>
+      </c>
+      <c r="B449" s="1">
+        <v>125.0711970599482</v>
+      </c>
+    </row>
+    <row r="450" spans="1:2">
+      <c r="A450" t="s">
+        <v>450</v>
+      </c>
+      <c r="B450" s="1">
+        <v>125.1347118185246</v>
+      </c>
+    </row>
+    <row r="451" spans="1:2">
+      <c r="A451" t="s">
+        <v>451</v>
+      </c>
+      <c r="B451" s="1">
+        <v>125.3009333862144</v>
+      </c>
+    </row>
+    <row r="452" spans="1:2">
+      <c r="A452" t="s">
+        <v>452</v>
+      </c>
+      <c r="B452" s="1">
+        <v>125.3529799360454</v>
+      </c>
+    </row>
+    <row r="453" spans="1:2">
+      <c r="A453" t="s">
+        <v>453</v>
+      </c>
+      <c r="B453" s="1">
+        <v>125.384078354756</v>
+      </c>
+    </row>
+    <row r="454" spans="1:2">
+      <c r="A454" t="s">
+        <v>454</v>
+      </c>
+      <c r="B454" s="1">
+        <v>125.3949571161905</v>
+      </c>
+    </row>
+    <row r="455" spans="1:2">
+      <c r="A455" t="s">
+        <v>455</v>
+      </c>
+      <c r="B455" s="1">
+        <v>125.4493404623136</v>
+      </c>
+    </row>
+    <row r="456" spans="1:2">
+      <c r="A456" t="s">
+        <v>456</v>
+      </c>
+      <c r="B456" s="1">
+        <v>125.556987610018</v>
+      </c>
+    </row>
+    <row r="457" spans="1:2">
+      <c r="A457" t="s">
+        <v>457</v>
+      </c>
+      <c r="B457" s="1">
+        <v>125.584443423033</v>
+      </c>
+    </row>
+    <row r="458" spans="1:2">
+      <c r="A458" t="s">
+        <v>458</v>
+      </c>
+      <c r="B458" s="1">
+        <v>125.5906165351075</v>
+      </c>
+    </row>
+    <row r="459" spans="1:2">
+      <c r="A459" t="s">
+        <v>459</v>
+      </c>
+      <c r="B459" s="1">
+        <v>125.5918082629295</v>
+      </c>
+    </row>
+    <row r="460" spans="1:2">
+      <c r="A460" t="s">
+        <v>460</v>
+      </c>
+      <c r="B460" s="1">
+        <v>125.6718558982489</v>
+      </c>
+    </row>
+    <row r="461" spans="1:2">
+      <c r="A461" t="s">
+        <v>461</v>
+      </c>
+      <c r="B461" s="1">
+        <v>125.7000027296969</v>
+      </c>
+    </row>
+    <row r="462" spans="1:2">
+      <c r="A462" t="s">
+        <v>462</v>
+      </c>
+      <c r="B462" s="1">
+        <v>125.7009974135933</v>
+      </c>
+    </row>
+    <row r="463" spans="1:2">
+      <c r="A463" t="s">
+        <v>463</v>
+      </c>
+      <c r="B463" s="1">
+        <v>125.7059875172118</v>
+      </c>
+    </row>
+    <row r="464" spans="1:2">
+      <c r="A464" t="s">
+        <v>464</v>
+      </c>
+      <c r="B464" s="1">
+        <v>125.7657724814948</v>
+      </c>
+    </row>
+    <row r="465" spans="1:2">
+      <c r="A465" t="s">
+        <v>465</v>
+      </c>
+      <c r="B465" s="1">
+        <v>125.7809928606386</v>
+      </c>
+    </row>
+    <row r="466" spans="1:2">
+      <c r="A466" t="s">
+        <v>466</v>
+      </c>
+      <c r="B466" s="1">
+        <v>126.0291628117029</v>
+      </c>
+    </row>
+    <row r="467" spans="1:2">
+      <c r="A467" t="s">
+        <v>467</v>
+      </c>
+      <c r="B467" s="1">
+        <v>126.0311331602815</v>
+      </c>
+    </row>
+    <row r="468" spans="1:2">
+      <c r="A468" t="s">
+        <v>468</v>
+      </c>
+      <c r="B468" s="1">
+        <v>126.0648096559013</v>
+      </c>
+    </row>
+    <row r="469" spans="1:2">
+      <c r="A469" t="s">
+        <v>469</v>
+      </c>
+      <c r="B469" s="1">
+        <v>126.0672480666567</v>
+      </c>
+    </row>
+    <row r="470" spans="1:2">
+      <c r="A470" t="s">
+        <v>470</v>
+      </c>
+      <c r="B470" s="1">
+        <v>126.0695090562286</v>
+      </c>
+    </row>
+    <row r="471" spans="1:2">
+      <c r="A471" t="s">
+        <v>471</v>
+      </c>
+      <c r="B471" s="1">
+        <v>126.2241049953675</v>
+      </c>
+    </row>
+    <row r="472" spans="1:2">
+      <c r="A472" t="s">
+        <v>472</v>
+      </c>
+      <c r="B472" s="1">
+        <v>126.2529543750576</v>
+      </c>
+    </row>
+    <row r="473" spans="1:2">
+      <c r="A473" t="s">
+        <v>473</v>
+      </c>
+      <c r="B473" s="1">
+        <v>126.2732106555858</v>
+      </c>
+    </row>
+    <row r="474" spans="1:2">
+      <c r="A474" t="s">
+        <v>474</v>
+      </c>
+      <c r="B474" s="1">
+        <v>126.2970657133525</v>
+      </c>
+    </row>
+    <row r="475" spans="1:2">
+      <c r="A475" t="s">
+        <v>475</v>
+      </c>
+      <c r="B475" s="1">
+        <v>126.4664380018667</v>
+      </c>
+    </row>
+    <row r="476" spans="1:2">
+      <c r="A476" t="s">
+        <v>476</v>
+      </c>
+      <c r="B476" s="1">
+        <v>126.486946505697</v>
+      </c>
+    </row>
+    <row r="477" spans="1:2">
+      <c r="A477" t="s">
+        <v>477</v>
+      </c>
+      <c r="B477" s="1">
+        <v>126.4931872900777</v>
+      </c>
+    </row>
+    <row r="478" spans="1:2">
+      <c r="A478" t="s">
+        <v>478</v>
+      </c>
+      <c r="B478" s="1">
+        <v>126.519239383953</v>
+      </c>
+    </row>
+    <row r="479" spans="1:2">
+      <c r="A479" t="s">
+        <v>479</v>
+      </c>
+      <c r="B479" s="1">
+        <v>126.6358065017426</v>
+      </c>
+    </row>
+    <row r="480" spans="1:2">
+      <c r="A480" t="s">
+        <v>480</v>
+      </c>
+      <c r="B480" s="1">
+        <v>126.6604639433654</v>
+      </c>
+    </row>
+    <row r="481" spans="1:2">
+      <c r="A481" t="s">
+        <v>481</v>
+      </c>
+      <c r="B481" s="1">
+        <v>126.7416446758697</v>
+      </c>
+    </row>
+    <row r="482" spans="1:2">
+      <c r="A482" t="s">
+        <v>482</v>
+      </c>
+      <c r="B482" s="1">
+        <v>126.8577129665163</v>
+      </c>
+    </row>
+    <row r="483" spans="1:2">
+      <c r="A483" t="s">
+        <v>483</v>
+      </c>
+      <c r="B483" s="1">
+        <v>127.0173399767462</v>
+      </c>
+    </row>
+    <row r="484" spans="1:2">
+      <c r="A484" t="s">
+        <v>484</v>
+      </c>
+      <c r="B484" s="1">
+        <v>127.0532379499545</v>
+      </c>
+    </row>
+    <row r="485" spans="1:2">
+      <c r="A485" t="s">
+        <v>485</v>
+      </c>
+      <c r="B485" s="1">
+        <v>127.1127038812048</v>
+      </c>
+    </row>
+    <row r="486" spans="1:2">
+      <c r="A486" t="s">
+        <v>486</v>
+      </c>
+      <c r="B486" s="1">
+        <v>127.167937512669</v>
+      </c>
+    </row>
+    <row r="487" spans="1:2">
+      <c r="A487" t="s">
+        <v>487</v>
+      </c>
+      <c r="B487" s="1">
+        <v>127.1954348380616</v>
+      </c>
+    </row>
+    <row r="488" spans="1:2">
+      <c r="A488" t="s">
+        <v>488</v>
+      </c>
+      <c r="B488" s="1">
+        <v>127.2508796955543</v>
+      </c>
+    </row>
+    <row r="489" spans="1:2">
+      <c r="A489" t="s">
+        <v>489</v>
+      </c>
+      <c r="B489" s="1">
+        <v>127.2745294940574</v>
+      </c>
+    </row>
+    <row r="490" spans="1:2">
+      <c r="A490" t="s">
+        <v>490</v>
+      </c>
+      <c r="B490" s="1">
+        <v>127.3965049204594</v>
+      </c>
+    </row>
+    <row r="491" spans="1:2">
+      <c r="A491" t="s">
+        <v>491</v>
+      </c>
+      <c r="B491" s="1">
+        <v>127.5181431004925</v>
+      </c>
+    </row>
+    <row r="492" spans="1:2">
+      <c r="A492" t="s">
+        <v>492</v>
+      </c>
+      <c r="B492" s="1">
+        <v>127.5280351133209</v>
+      </c>
+    </row>
+    <row r="493" spans="1:2">
+      <c r="A493" t="s">
+        <v>493</v>
+      </c>
+      <c r="B493" s="1">
+        <v>127.5361489046046</v>
+      </c>
+    </row>
+    <row r="494" spans="1:2">
+      <c r="A494" t="s">
+        <v>494</v>
+      </c>
+      <c r="B494" s="1">
+        <v>127.558938187346</v>
+      </c>
+    </row>
+    <row r="495" spans="1:2">
+      <c r="A495" t="s">
+        <v>495</v>
+      </c>
+      <c r="B495" s="1">
+        <v>127.6144875116743</v>
+      </c>
+    </row>
+    <row r="496" spans="1:2">
+      <c r="A496" t="s">
+        <v>496</v>
+      </c>
+      <c r="B496" s="1">
+        <v>127.7318940370957</v>
+      </c>
+    </row>
+    <row r="497" spans="1:2">
+      <c r="A497" t="s">
+        <v>497</v>
+      </c>
+      <c r="B497" s="1">
+        <v>127.8013864682144</v>
+      </c>
+    </row>
+    <row r="498" spans="1:2">
+      <c r="A498" t="s">
+        <v>498</v>
+      </c>
+      <c r="B498" s="1">
+        <v>127.9636854046595</v>
+      </c>
+    </row>
+    <row r="499" spans="1:2">
+      <c r="A499" t="s">
+        <v>499</v>
+      </c>
+      <c r="B499" s="1">
+        <v>128.0442821451672</v>
+      </c>
+    </row>
+    <row r="500" spans="1:2">
+      <c r="A500" t="s">
+        <v>500</v>
+      </c>
+      <c r="B500" s="1">
+        <v>128.0606959332799</v>
+      </c>
+    </row>
+    <row r="501" spans="1:2">
+      <c r="A501" t="s">
+        <v>501</v>
+      </c>
+      <c r="B501" s="1">
+        <v>128.0621452797156</v>
+      </c>
+    </row>
+    <row r="502" spans="1:2">
+      <c r="A502" t="s">
+        <v>502</v>
+      </c>
+      <c r="B502" s="1">
+        <v>128.1182759372876</v>
+      </c>
+    </row>
+    <row r="503" spans="1:2">
+      <c r="A503" t="s">
+        <v>503</v>
+      </c>
+      <c r="B503" s="1">
+        <v>128.2139614929803</v>
+      </c>
+    </row>
+    <row r="504" spans="1:2">
+      <c r="A504" t="s">
+        <v>504</v>
+      </c>
+      <c r="B504" s="1">
+        <v>128.3030746041347</v>
+      </c>
+    </row>
+    <row r="505" spans="1:2">
+      <c r="A505" t="s">
+        <v>505</v>
+      </c>
+      <c r="B505" s="1">
+        <v>128.3243933503749</v>
+      </c>
+    </row>
+    <row r="506" spans="1:2">
+      <c r="A506" t="s">
+        <v>506</v>
+      </c>
+      <c r="B506" s="1">
+        <v>128.3616354288569</v>
+      </c>
+    </row>
+    <row r="507" spans="1:2">
+      <c r="A507" t="s">
+        <v>507</v>
+      </c>
+      <c r="B507" s="1">
+        <v>128.4290354031858</v>
+      </c>
+    </row>
+    <row r="508" spans="1:2">
+      <c r="A508" t="s">
+        <v>508</v>
+      </c>
+      <c r="B508" s="1">
+        <v>128.4483654654748</v>
+      </c>
+    </row>
+    <row r="509" spans="1:2">
+      <c r="A509" t="s">
+        <v>509</v>
+      </c>
+      <c r="B509" s="1">
+        <v>128.6199041443911</v>
+      </c>
+    </row>
+    <row r="510" spans="1:2">
+      <c r="A510" t="s">
+        <v>510</v>
+      </c>
+      <c r="B510" s="1">
+        <v>128.712741779611</v>
+      </c>
+    </row>
+    <row r="511" spans="1:2">
+      <c r="A511" t="s">
+        <v>511</v>
+      </c>
+      <c r="B511" s="1">
+        <v>128.7960306892861</v>
+      </c>
+    </row>
+    <row r="512" spans="1:2">
+      <c r="A512" t="s">
+        <v>512</v>
+      </c>
+      <c r="B512" s="1">
+        <v>128.8846516145133</v>
+      </c>
+    </row>
+    <row r="513" spans="1:2">
+      <c r="A513" t="s">
+        <v>513</v>
+      </c>
+      <c r="B513" s="1">
+        <v>128.9603119008748</v>
+      </c>
+    </row>
+    <row r="514" spans="1:2">
+      <c r="A514" t="s">
+        <v>514</v>
+      </c>
+      <c r="B514" s="1">
+        <v>129.0501498357382</v>
+      </c>
+    </row>
+    <row r="515" spans="1:2">
+      <c r="A515" t="s">
+        <v>515</v>
+      </c>
+      <c r="B515" s="1">
+        <v>129.1200490970912</v>
+      </c>
+    </row>
+    <row r="516" spans="1:2">
+      <c r="A516" t="s">
+        <v>516</v>
+      </c>
+      <c r="B516" s="1">
+        <v>129.3019187840006</v>
+      </c>
+    </row>
+    <row r="517" spans="1:2">
+      <c r="A517" t="s">
+        <v>517</v>
+      </c>
+      <c r="B517" s="1">
+        <v>129.4409220610737</v>
+      </c>
+    </row>
+    <row r="518" spans="1:2">
+      <c r="A518" t="s">
+        <v>518</v>
+      </c>
+      <c r="B518" s="1">
+        <v>129.4964603825232</v>
+      </c>
+    </row>
+    <row r="519" spans="1:2">
+      <c r="A519" t="s">
+        <v>519</v>
+      </c>
+      <c r="B519" s="1">
+        <v>129.5412430271703</v>
+      </c>
+    </row>
+    <row r="520" spans="1:2">
+      <c r="A520" t="s">
+        <v>520</v>
+      </c>
+      <c r="B520" s="1">
+        <v>130.0407161858954</v>
+      </c>
+    </row>
+    <row r="521" spans="1:2">
+      <c r="A521" t="s">
+        <v>521</v>
+      </c>
+      <c r="B521" s="1">
+        <v>130.0665596057445</v>
+      </c>
+    </row>
+    <row r="522" spans="1:2">
+      <c r="A522" t="s">
+        <v>522</v>
+      </c>
+      <c r="B522" s="1">
+        <v>130.1077495161769</v>
+      </c>
+    </row>
+    <row r="523" spans="1:2">
+      <c r="A523" t="s">
+        <v>523</v>
+      </c>
+      <c r="B523" s="1">
+        <v>130.121532716593</v>
+      </c>
+    </row>
+    <row r="524" spans="1:2">
+      <c r="A524" t="s">
+        <v>524</v>
+      </c>
+      <c r="B524" s="1">
+        <v>130.1394284013839</v>
+      </c>
+    </row>
+    <row r="525" spans="1:2">
+      <c r="A525" t="s">
+        <v>525</v>
+      </c>
+      <c r="B525" s="1">
+        <v>130.4536632947536</v>
+      </c>
+    </row>
+    <row r="526" spans="1:2">
+      <c r="A526" t="s">
+        <v>526</v>
+      </c>
+      <c r="B526" s="1">
+        <v>130.5851753932231</v>
+      </c>
+    </row>
+    <row r="527" spans="1:2">
+      <c r="A527" t="s">
+        <v>527</v>
+      </c>
+      <c r="B527" s="1">
+        <v>130.7549727236556</v>
+      </c>
+    </row>
+    <row r="528" spans="1:2">
+      <c r="A528" t="s">
+        <v>528</v>
+      </c>
+      <c r="B528" s="1">
+        <v>131.1708086767566</v>
+      </c>
+    </row>
+    <row r="529" spans="1:2">
+      <c r="A529" t="s">
+        <v>529</v>
+      </c>
+      <c r="B529" s="1">
+        <v>131.2493979631263</v>
+      </c>
+    </row>
+    <row r="530" spans="1:2">
+      <c r="A530" t="s">
+        <v>530</v>
+      </c>
+      <c r="B530" s="1">
+        <v>131.272908043034</v>
+      </c>
+    </row>
+    <row r="531" spans="1:2">
+      <c r="A531" t="s">
+        <v>531</v>
+      </c>
+      <c r="B531" s="1">
+        <v>131.466809286564</v>
+      </c>
+    </row>
+    <row r="532" spans="1:2">
+      <c r="A532" t="s">
+        <v>532</v>
+      </c>
+      <c r="B532" s="1">
+        <v>131.5347822079805</v>
+      </c>
+    </row>
+    <row r="533" spans="1:2">
+      <c r="A533" t="s">
+        <v>533</v>
+      </c>
+      <c r="B533" s="1">
+        <v>131.5403079572679</v>
+      </c>
+    </row>
+    <row r="534" spans="1:2">
+      <c r="A534" t="s">
+        <v>534</v>
+      </c>
+      <c r="B534" s="1">
+        <v>131.6714862370827</v>
+      </c>
+    </row>
+    <row r="535" spans="1:2">
+      <c r="A535" t="s">
+        <v>535</v>
+      </c>
+      <c r="B535" s="1">
+        <v>131.8154009097049</v>
+      </c>
+    </row>
+    <row r="536" spans="1:2">
+      <c r="A536" t="s">
+        <v>536</v>
+      </c>
+      <c r="B536" s="1">
+        <v>132.1078146657173</v>
+      </c>
+    </row>
+    <row r="537" spans="1:2">
+      <c r="A537" t="s">
+        <v>537</v>
+      </c>
+      <c r="B537" s="1">
+        <v>132.1440072510177</v>
+      </c>
+    </row>
+    <row r="538" spans="1:2">
+      <c r="A538" t="s">
+        <v>538</v>
+      </c>
+      <c r="B538" s="1">
+        <v>132.3543730000327</v>
+      </c>
+    </row>
+    <row r="539" spans="1:2">
+      <c r="A539" t="s">
+        <v>539</v>
+      </c>
+      <c r="B539" s="1">
+        <v>132.5418863478653</v>
+      </c>
+    </row>
+    <row r="540" spans="1:2">
+      <c r="A540" t="s">
+        <v>540</v>
+      </c>
+      <c r="B540" s="1">
+        <v>132.6742521943811</v>
+      </c>
+    </row>
+    <row r="541" spans="1:2">
+      <c r="A541" t="s">
+        <v>541</v>
+      </c>
+      <c r="B541" s="1">
+        <v>132.7205270505035</v>
+      </c>
+    </row>
+    <row r="542" spans="1:2">
+      <c r="A542" t="s">
+        <v>542</v>
+      </c>
+      <c r="B542" s="1">
+        <v>132.7412609730069</v>
+      </c>
+    </row>
+    <row r="543" spans="1:2">
+      <c r="A543" t="s">
+        <v>543</v>
+      </c>
+      <c r="B543" s="1">
+        <v>132.8628872352002</v>
+      </c>
+    </row>
+    <row r="544" spans="1:2">
+      <c r="A544" t="s">
+        <v>544</v>
+      </c>
+      <c r="B544" s="1">
+        <v>132.9637063947944</v>
+      </c>
+    </row>
+    <row r="545" spans="1:2">
+      <c r="A545" t="s">
+        <v>545</v>
+      </c>
+      <c r="B545" s="1">
+        <v>133.0916080022783</v>
+      </c>
+    </row>
+    <row r="546" spans="1:2">
+      <c r="A546" t="s">
+        <v>546</v>
+      </c>
+      <c r="B546" s="1">
+        <v>133.1440161899042</v>
+      </c>
+    </row>
+    <row r="547" spans="1:2">
+      <c r="A547" t="s">
+        <v>547</v>
+      </c>
+      <c r="B547" s="1">
+        <v>133.1644680579921</v>
+      </c>
+    </row>
+    <row r="548" spans="1:2">
+      <c r="A548" t="s">
+        <v>548</v>
+      </c>
+      <c r="B548" s="1">
+        <v>133.2576264796828</v>
+      </c>
+    </row>
+    <row r="549" spans="1:2">
+      <c r="A549" t="s">
+        <v>549</v>
+      </c>
+      <c r="B549" s="1">
+        <v>133.3285877111944</v>
+      </c>
+    </row>
+    <row r="550" spans="1:2">
+      <c r="A550" t="s">
+        <v>550</v>
+      </c>
+      <c r="B550" s="1">
+        <v>133.5947422615553</v>
+      </c>
+    </row>
+    <row r="551" spans="1:2">
+      <c r="A551" t="s">
+        <v>551</v>
+      </c>
+      <c r="B551" s="1">
+        <v>133.5998703053228</v>
+      </c>
+    </row>
+    <row r="552" spans="1:2">
+      <c r="A552" t="s">
+        <v>552</v>
+      </c>
+      <c r="B552" s="1">
+        <v>133.8245673464926</v>
+      </c>
+    </row>
+    <row r="553" spans="1:2">
+      <c r="A553" t="s">
+        <v>553</v>
+      </c>
+      <c r="B553" s="1">
+        <v>133.8590783664626</v>
+      </c>
+    </row>
+    <row r="554" spans="1:2">
+      <c r="A554" t="s">
+        <v>554</v>
+      </c>
+      <c r="B554" s="1">
+        <v>133.9270330331991</v>
+      </c>
+    </row>
+    <row r="555" spans="1:2">
+      <c r="A555" t="s">
+        <v>555</v>
+      </c>
+      <c r="B555" s="1">
+        <v>133.9414369908549</v>
+      </c>
+    </row>
+    <row r="556" spans="1:2">
+      <c r="A556" t="s">
+        <v>556</v>
+      </c>
+      <c r="B556" s="1">
+        <v>134.1212142308035</v>
+      </c>
+    </row>
+    <row r="557" spans="1:2">
+      <c r="A557" t="s">
+        <v>557</v>
+      </c>
+      <c r="B557" s="1">
+        <v>134.1425681894286</v>
+      </c>
+    </row>
+    <row r="558" spans="1:2">
+      <c r="A558" t="s">
+        <v>558</v>
+      </c>
+      <c r="B558" s="1">
+        <v>134.1796772167984</v>
+      </c>
+    </row>
+    <row r="559" spans="1:2">
+      <c r="A559" t="s">
+        <v>559</v>
+      </c>
+      <c r="B559" s="1">
+        <v>134.1808421953878</v>
+      </c>
+    </row>
+    <row r="560" spans="1:2">
+      <c r="A560" t="s">
+        <v>560</v>
+      </c>
+      <c r="B560" s="1">
+        <v>134.2069595774925</v>
+      </c>
+    </row>
+    <row r="561" spans="1:2">
+      <c r="A561" t="s">
+        <v>561</v>
+      </c>
+      <c r="B561" s="1">
+        <v>134.2667584314629</v>
+      </c>
+    </row>
+    <row r="562" spans="1:2">
+      <c r="A562" t="s">
+        <v>562</v>
+      </c>
+      <c r="B562" s="1">
+        <v>134.31874931275</v>
+      </c>
+    </row>
+    <row r="563" spans="1:2">
+      <c r="A563" t="s">
+        <v>563</v>
+      </c>
+      <c r="B563" s="1">
+        <v>134.5536614808695</v>
+      </c>
+    </row>
+    <row r="564" spans="1:2">
+      <c r="A564" t="s">
+        <v>564</v>
+      </c>
+      <c r="B564" s="1">
+        <v>134.6457206818532</v>
+      </c>
+    </row>
+    <row r="565" spans="1:2">
+      <c r="A565" t="s">
+        <v>565</v>
+      </c>
+      <c r="B565" s="1">
+        <v>134.6704249627749</v>
+      </c>
+    </row>
+    <row r="566" spans="1:2">
+      <c r="A566" t="s">
+        <v>566</v>
+      </c>
+      <c r="B566" s="1">
+        <v>134.7023553146224</v>
+      </c>
+    </row>
+    <row r="567" spans="1:2">
+      <c r="A567" t="s">
+        <v>567</v>
+      </c>
+      <c r="B567" s="1">
+        <v>134.7325385859609</v>
+      </c>
+    </row>
+    <row r="568" spans="1:2">
+      <c r="A568" t="s">
+        <v>568</v>
+      </c>
+      <c r="B568" s="1">
+        <v>134.7991367591694</v>
+      </c>
+    </row>
+    <row r="569" spans="1:2">
+      <c r="A569" t="s">
+        <v>569</v>
+      </c>
+      <c r="B569" s="1">
+        <v>134.9331059325363</v>
+      </c>
+    </row>
+    <row r="570" spans="1:2">
+      <c r="A570" t="s">
+        <v>570</v>
+      </c>
+      <c r="B570" s="1">
+        <v>134.9732629631344</v>
+      </c>
+    </row>
+    <row r="571" spans="1:2">
+      <c r="A571" t="s">
+        <v>571</v>
+      </c>
+      <c r="B571" s="1">
+        <v>135.1020270518096</v>
+      </c>
+    </row>
+    <row r="572" spans="1:2">
+      <c r="A572" t="s">
+        <v>572</v>
+      </c>
+      <c r="B572" s="1">
+        <v>135.3528302797602</v>
+      </c>
+    </row>
+    <row r="573" spans="1:2">
+      <c r="A573" t="s">
+        <v>573</v>
+      </c>
+      <c r="B573" s="1">
+        <v>135.9527463454412</v>
+      </c>
+    </row>
+    <row r="574" spans="1:2">
+      <c r="A574" t="s">
+        <v>574</v>
+      </c>
+      <c r="B574" s="1">
+        <v>136.0445890187315</v>
+      </c>
+    </row>
+    <row r="575" spans="1:2">
+      <c r="A575" t="s">
+        <v>575</v>
+      </c>
+      <c r="B575" s="1">
+        <v>136.1555101338938</v>
+      </c>
+    </row>
+    <row r="576" spans="1:2">
+      <c r="A576" t="s">
+        <v>576</v>
+      </c>
+      <c r="B576" s="1">
+        <v>136.2345466167971</v>
+      </c>
+    </row>
+    <row r="577" spans="1:2">
+      <c r="A577" t="s">
+        <v>577</v>
+      </c>
+      <c r="B577" s="1">
+        <v>136.3886779352026</v>
+      </c>
+    </row>
+    <row r="578" spans="1:2">
+      <c r="A578" t="s">
+        <v>578</v>
+      </c>
+      <c r="B578" s="1">
+        <v>136.4430570707169</v>
+      </c>
+    </row>
+    <row r="579" spans="1:2">
+      <c r="A579" t="s">
+        <v>579</v>
+      </c>
+      <c r="B579" s="1">
+        <v>136.7128339270303</v>
+      </c>
+    </row>
+    <row r="580" spans="1:2">
+      <c r="A580" t="s">
+        <v>580</v>
+      </c>
+      <c r="B580" s="1">
+        <v>136.9463445125564</v>
+      </c>
+    </row>
+    <row r="581" spans="1:2">
+      <c r="A581" t="s">
+        <v>581</v>
+      </c>
+      <c r="B581" s="1">
+        <v>137.4553053037776</v>
+      </c>
+    </row>
+    <row r="582" spans="1:2">
+      <c r="A582" t="s">
+        <v>582</v>
+      </c>
+      <c r="B582" s="1">
+        <v>137.4718137984415</v>
+      </c>
+    </row>
+    <row r="583" spans="1:2">
+      <c r="A583" t="s">
+        <v>583</v>
+      </c>
+      <c r="B583" s="1">
+        <v>137.8726480063285</v>
+      </c>
+    </row>
+    <row r="584" spans="1:2">
+      <c r="A584" t="s">
+        <v>584</v>
+      </c>
+      <c r="B584" s="1">
+        <v>137.9477348770077</v>
+      </c>
+    </row>
+    <row r="585" spans="1:2">
+      <c r="A585" t="s">
+        <v>585</v>
+      </c>
+      <c r="B585" s="1">
+        <v>138.3145183725813</v>
+      </c>
+    </row>
+    <row r="586" spans="1:2">
+      <c r="A586" t="s">
+        <v>586</v>
+      </c>
+      <c r="B586" s="1">
+        <v>138.9459937432437</v>
+      </c>
+    </row>
+    <row r="587" spans="1:2">
+      <c r="A587" t="s">
+        <v>587</v>
+      </c>
+      <c r="B587" s="1">
+        <v>139.5496864800168</v>
+      </c>
+    </row>
+    <row r="588" spans="1:2">
+      <c r="A588" t="s">
+        <v>588</v>
+      </c>
+      <c r="B588" s="1">
+        <v>139.6930889680834</v>
+      </c>
+    </row>
+    <row r="589" spans="1:2">
+      <c r="A589" t="s">
+        <v>589</v>
+      </c>
+      <c r="B589" s="1">
+        <v>139.7752726566263</v>
+      </c>
+    </row>
+    <row r="590" spans="1:2">
+      <c r="A590" t="s">
+        <v>590</v>
+      </c>
+      <c r="B590" s="1">
+        <v>139.9999496932189</v>
+      </c>
+    </row>
+    <row r="591" spans="1:2">
+      <c r="A591" t="s">
+        <v>591</v>
+      </c>
+      <c r="B591" s="1">
+        <v>140.0041509047234</v>
+      </c>
+    </row>
+    <row r="592" spans="1:2">
+      <c r="A592" t="s">
+        <v>592</v>
+      </c>
+      <c r="B592" s="1">
+        <v>140.0709245680816</v>
+      </c>
+    </row>
+    <row r="593" spans="1:2">
+      <c r="A593" t="s">
+        <v>593</v>
+      </c>
+      <c r="B593" s="1">
+        <v>140.2036456144506</v>
+      </c>
+    </row>
+    <row r="594" spans="1:2">
+      <c r="A594" t="s">
+        <v>594</v>
+      </c>
+      <c r="B594" s="1">
+        <v>140.2538390648787</v>
+      </c>
+    </row>
+    <row r="595" spans="1:2">
+      <c r="A595" t="s">
+        <v>595</v>
+      </c>
+      <c r="B595" s="1">
+        <v>140.2782226810197</v>
+      </c>
+    </row>
+    <row r="596" spans="1:2">
+      <c r="A596" t="s">
+        <v>596</v>
+      </c>
+      <c r="B596" s="1">
+        <v>140.4159725212541</v>
+      </c>
+    </row>
+    <row r="597" spans="1:2">
+      <c r="A597" t="s">
+        <v>597</v>
+      </c>
+      <c r="B597" s="1">
+        <v>140.4643962816835</v>
+      </c>
+    </row>
+    <row r="598" spans="1:2">
+      <c r="A598" t="s">
+        <v>598</v>
+      </c>
+      <c r="B598" s="1">
+        <v>140.592185067955</v>
+      </c>
+    </row>
+    <row r="599" spans="1:2">
+      <c r="A599" t="s">
+        <v>599</v>
+      </c>
+      <c r="B599" s="1">
+        <v>140.7466300050617</v>
+      </c>
+    </row>
+    <row r="600" spans="1:2">
+      <c r="A600" t="s">
+        <v>600</v>
+      </c>
+      <c r="B600" s="1">
+        <v>141.0165768038667</v>
+      </c>
+    </row>
+    <row r="601" spans="1:2">
+      <c r="A601" t="s">
+        <v>601</v>
+      </c>
+      <c r="B601" s="1">
+        <v>141.392152286811</v>
+      </c>
+    </row>
+    <row r="602" spans="1:2">
+      <c r="A602" t="s">
+        <v>602</v>
+      </c>
+      <c r="B602" s="1">
+        <v>141.5328297646311</v>
+      </c>
+    </row>
+    <row r="603" spans="1:2">
+      <c r="A603" t="s">
+        <v>603</v>
+      </c>
+      <c r="B603" s="1">
+        <v>141.8940692655496</v>
+      </c>
+    </row>
+    <row r="604" spans="1:2">
+      <c r="A604" t="s">
+        <v>604</v>
+      </c>
+      <c r="B604" s="1">
+        <v>141.9271465430416</v>
+      </c>
+    </row>
+    <row r="605" spans="1:2">
+      <c r="A605" t="s">
+        <v>605</v>
+      </c>
+      <c r="B605" s="1">
+        <v>142.1670343254481</v>
+      </c>
+    </row>
+    <row r="606" spans="1:2">
+      <c r="A606" t="s">
+        <v>606</v>
+      </c>
+      <c r="B606" s="1">
+        <v>142.2485708839017</v>
+      </c>
+    </row>
+    <row r="607" spans="1:2">
+      <c r="A607" t="s">
+        <v>607</v>
+      </c>
+      <c r="B607" s="1">
+        <v>142.3486795991252</v>
+      </c>
+    </row>
+    <row r="608" spans="1:2">
+      <c r="A608" t="s">
+        <v>608</v>
+      </c>
+      <c r="B608" s="1">
+        <v>142.3749006274235</v>
+      </c>
+    </row>
+    <row r="609" spans="1:2">
+      <c r="A609" t="s">
+        <v>609</v>
+      </c>
+      <c r="B609" s="1">
+        <v>142.4392814870751</v>
+      </c>
+    </row>
+    <row r="610" spans="1:2">
+      <c r="A610" t="s">
+        <v>610</v>
+      </c>
+      <c r="B610" s="1">
+        <v>142.4688420704403</v>
+      </c>
+    </row>
+    <row r="611" spans="1:2">
+      <c r="A611" t="s">
+        <v>611</v>
+      </c>
+      <c r="B611" s="1">
+        <v>142.6935157137953</v>
+      </c>
+    </row>
+    <row r="612" spans="1:2">
+      <c r="A612" t="s">
+        <v>612</v>
+      </c>
+      <c r="B612" s="1">
+        <v>143.2066468338436</v>
+      </c>
+    </row>
+    <row r="613" spans="1:2">
+      <c r="A613" t="s">
+        <v>613</v>
+      </c>
+      <c r="B613" s="1">
+        <v>143.3525272626623</v>
+      </c>
+    </row>
+    <row r="614" spans="1:2">
+      <c r="A614" t="s">
+        <v>614</v>
+      </c>
+      <c r="B614" s="1">
+        <v>143.3628671098525</v>
+      </c>
+    </row>
+    <row r="615" spans="1:2">
+      <c r="A615" t="s">
+        <v>615</v>
+      </c>
+      <c r="B615" s="1">
+        <v>144.0646230055881</v>
+      </c>
+    </row>
+    <row r="616" spans="1:2">
+      <c r="A616" t="s">
+        <v>616</v>
+      </c>
+      <c r="B616" s="1">
+        <v>144.3316032000219</v>
+      </c>
+    </row>
+    <row r="617" spans="1:2">
+      <c r="A617" t="s">
+        <v>617</v>
+      </c>
+      <c r="B617" s="1">
+        <v>144.4085992144063</v>
+      </c>
+    </row>
+    <row r="618" spans="1:2">
+      <c r="A618" t="s">
+        <v>618</v>
+      </c>
+      <c r="B618" s="1">
+        <v>144.4735852388145</v>
+      </c>
+    </row>
+    <row r="619" spans="1:2">
+      <c r="A619" t="s">
+        <v>619</v>
+      </c>
+      <c r="B619" s="1">
+        <v>144.5731915437257</v>
+      </c>
+    </row>
+    <row r="620" spans="1:2">
+      <c r="A620" t="s">
+        <v>620</v>
+      </c>
+      <c r="B620" s="1">
+        <v>144.5932947045835</v>
+      </c>
+    </row>
+    <row r="621" spans="1:2">
+      <c r="A621" t="s">
+        <v>621</v>
+      </c>
+      <c r="B621" s="1">
+        <v>145.4482799773905</v>
+      </c>
+    </row>
+    <row r="622" spans="1:2">
+      <c r="A622" t="s">
+        <v>622</v>
+      </c>
+      <c r="B622" s="1">
+        <v>145.4718496636519</v>
+      </c>
+    </row>
+    <row r="623" spans="1:2">
+      <c r="A623" t="s">
+        <v>623</v>
+      </c>
+      <c r="B623" s="1">
+        <v>145.8992073836287</v>
+      </c>
+    </row>
+    <row r="624" spans="1:2">
+      <c r="A624" t="s">
+        <v>624</v>
+      </c>
+      <c r="B624" s="1">
+        <v>147.0316778629383</v>
+      </c>
+    </row>
+    <row r="625" spans="1:2">
+      <c r="A625" t="s">
+        <v>625</v>
+      </c>
+      <c r="B625" s="1">
+        <v>147.5661775284088</v>
+      </c>
+    </row>
+    <row r="626" spans="1:2">
+      <c r="A626" t="s">
+        <v>626</v>
+      </c>
+      <c r="B626" s="1">
+        <v>148.0722618243338</v>
+      </c>
+    </row>
+    <row r="627" spans="1:2">
+      <c r="A627" t="s">
+        <v>627</v>
+      </c>
+      <c r="B627" s="1">
+        <v>148.385979657926</v>
+      </c>
+    </row>
+    <row r="628" spans="1:2">
+      <c r="A628" t="s">
+        <v>628</v>
+      </c>
+      <c r="B628" s="1">
+        <v>148.5922307123358</v>
+      </c>
+    </row>
+    <row r="629" spans="1:2">
+      <c r="A629" t="s">
+        <v>629</v>
+      </c>
+      <c r="B629" s="1">
+        <v>148.6254192838488</v>
+      </c>
+    </row>
+    <row r="630" spans="1:2">
+      <c r="A630" t="s">
+        <v>630</v>
+      </c>
+      <c r="B630" s="1">
+        <v>149.426064850939</v>
+      </c>
+    </row>
+    <row r="631" spans="1:2">
+      <c r="A631" t="s">
+        <v>631</v>
+      </c>
+      <c r="B631" s="1">
+        <v>149.8204529062646</v>
+      </c>
+    </row>
+    <row r="632" spans="1:2">
+      <c r="A632" t="s">
+        <v>632</v>
+      </c>
+      <c r="B632" s="1">
+        <v>151.2069892826078</v>
+      </c>
+    </row>
+    <row r="633" spans="1:2">
+      <c r="A633" t="s">
+        <v>633</v>
+      </c>
+      <c r="B633" s="1">
+        <v>151.4637385304516</v>
+      </c>
+    </row>
+    <row r="634" spans="1:2">
+      <c r="A634" t="s">
+        <v>634</v>
+      </c>
+      <c r="B634" s="1">
+        <v>151.7029070397099</v>
+      </c>
+    </row>
+    <row r="635" spans="1:2">
+      <c r="A635" t="s">
+        <v>635</v>
+      </c>
+      <c r="B635" s="1">
+        <v>152.1039890158609</v>
+      </c>
+    </row>
+    <row r="636" spans="1:2">
+      <c r="A636" t="s">
+        <v>636</v>
+      </c>
+      <c r="B636" s="1">
+        <v>152.9227086147487</v>
+      </c>
+    </row>
+    <row r="637" spans="1:2">
+      <c r="A637" t="s">
+        <v>637</v>
+      </c>
+      <c r="B637" s="1">
+        <v>152.9449047587219</v>
+      </c>
+    </row>
+    <row r="638" spans="1:2">
+      <c r="A638" t="s">
+        <v>638</v>
+      </c>
+      <c r="B638" s="1">
+        <v>153.2271102181106</v>
+      </c>
+    </row>
+    <row r="639" spans="1:2">
+      <c r="A639" t="s">
+        <v>639</v>
+      </c>
+      <c r="B639" s="1">
+        <v>155.8247019474702</v>
+      </c>
+    </row>
+    <row r="640" spans="1:2">
+      <c r="A640" t="s">
+        <v>640</v>
+      </c>
+      <c r="B640" s="1">
+        <v>155.9872787173383</v>
+      </c>
+    </row>
+    <row r="641" spans="1:2">
+      <c r="A641" t="s">
+        <v>641</v>
+      </c>
+      <c r="B641" s="1">
+        <v>156.2169116405286</v>
+      </c>
+    </row>
+    <row r="642" spans="1:2">
+      <c r="A642" t="s">
+        <v>642</v>
+      </c>
+      <c r="B642" s="1">
+        <v>157.03521518298</v>
+      </c>
+    </row>
+    <row r="643" spans="1:2">
+      <c r="A643" t="s">
+        <v>643</v>
+      </c>
+      <c r="B643" s="1">
+        <v>157.130523264099</v>
+      </c>
+    </row>
+    <row r="644" spans="1:2">
+      <c r="A644" t="s">
+        <v>644</v>
+      </c>
+      <c r="B644" s="1">
+        <v>157.8167276970302</v>
+      </c>
+    </row>
+    <row r="645" spans="1:2">
+      <c r="A645" t="s">
+        <v>645</v>
+      </c>
+      <c r="B645" s="1">
+        <v>158.1339704926759</v>
+      </c>
+    </row>
+    <row r="646" spans="1:2">
+      <c r="A646" t="s">
+        <v>646</v>
+      </c>
+      <c r="B646" s="1">
+        <v>158.320494792574</v>
+      </c>
+    </row>
+    <row r="647" spans="1:2">
+      <c r="A647" t="s">
+        <v>647</v>
+      </c>
+      <c r="B647" s="1">
+        <v>158.3949102892771</v>
+      </c>
+    </row>
+    <row r="648" spans="1:2">
+      <c r="A648" t="s">
+        <v>648</v>
+      </c>
+      <c r="B648" s="1">
+        <v>159.2150296405023</v>
+      </c>
+    </row>
+    <row r="649" spans="1:2">
+      <c r="A649" t="s">
+        <v>649</v>
+      </c>
+      <c r="B649" s="1">
+        <v>160.0098328927405</v>
+      </c>
+    </row>
+    <row r="650" spans="1:2">
+      <c r="A650" t="s">
+        <v>650</v>
+      </c>
+      <c r="B650" s="1">
+        <v>160.6309974554449</v>
+      </c>
+    </row>
+    <row r="651" spans="1:2">
+      <c r="A651" t="s">
+        <v>651</v>
+      </c>
+      <c r="B651" s="1">
+        <v>160.9595584063483</v>
+      </c>
+    </row>
+    <row r="652" spans="1:2">
+      <c r="A652" t="s">
+        <v>652</v>
+      </c>
+      <c r="B652" s="1">
+        <v>161.1868856801391</v>
+      </c>
+    </row>
+    <row r="653" spans="1:2">
+      <c r="A653" t="s">
+        <v>653</v>
+      </c>
+      <c r="B653" s="1">
+        <v>161.2115145535739</v>
+      </c>
+    </row>
+    <row r="654" spans="1:2">
+      <c r="A654" t="s">
+        <v>654</v>
+      </c>
+      <c r="B654" s="1">
+        <v>162.5933273713696</v>
+      </c>
+    </row>
+    <row r="655" spans="1:2">
+      <c r="A655" t="s">
+        <v>655</v>
+      </c>
+      <c r="B655" s="1">
+        <v>165.2175858088021</v>
+      </c>
+    </row>
+    <row r="656" spans="1:2">
+      <c r="A656" t="s">
+        <v>656</v>
+      </c>
+      <c r="B656" s="1">
+        <v>165.3794567953473</v>
+      </c>
+    </row>
+    <row r="657" spans="1:2">
+      <c r="A657" t="s">
+        <v>657</v>
+      </c>
+      <c r="B657" s="1">
+        <v>165.5514880923389</v>
+      </c>
+    </row>
+    <row r="658" spans="1:2">
+      <c r="A658" t="s">
+        <v>658</v>
+      </c>
+      <c r="B658" s="1">
+        <v>166.2129986863655</v>
+      </c>
+    </row>
+    <row r="659" spans="1:2">
+      <c r="A659" t="s">
+        <v>659</v>
+      </c>
+      <c r="B659" s="1">
+        <v>166.5487292585726</v>
+      </c>
+    </row>
+    <row r="660" spans="1:2">
+      <c r="A660" t="s">
+        <v>660</v>
+      </c>
+      <c r="B660" s="1">
+        <v>167.5388901987798</v>
+      </c>
+    </row>
+    <row r="661" spans="1:2">
+      <c r="A661" t="s">
+        <v>661</v>
+      </c>
+      <c r="B661" s="1">
+        <v>168.6227099306648</v>
+      </c>
+    </row>
+    <row r="662" spans="1:2">
+      <c r="A662" t="s">
+        <v>662</v>
+      </c>
+      <c r="B662" s="1">
+        <v>169.7061213448532</v>
+      </c>
+    </row>
+    <row r="663" spans="1:2">
+      <c r="A663" t="s">
+        <v>663</v>
+      </c>
+      <c r="B663" s="1">
+        <v>170.4415198032617</v>
+      </c>
+    </row>
+    <row r="664" spans="1:2">
+      <c r="A664" t="s">
+        <v>664</v>
+      </c>
+      <c r="B664" s="1">
+        <v>172.4695353784916</v>
+      </c>
+    </row>
+    <row r="665" spans="1:2">
+      <c r="A665" t="s">
+        <v>665</v>
+      </c>
+      <c r="B665" s="1">
+        <v>173.9472977699687</v>
+      </c>
+    </row>
+    <row r="666" spans="1:2">
+      <c r="A666" t="s">
+        <v>666</v>
+      </c>
+      <c r="B666" s="1">
+        <v>175.6200992306331</v>
+      </c>
+    </row>
+    <row r="667" spans="1:2">
+      <c r="A667" t="s">
+        <v>667</v>
+      </c>
+      <c r="B667" s="1">
+        <v>176.419965470953</v>
+      </c>
+    </row>
+    <row r="668" spans="1:2">
+      <c r="A668" t="s">
+        <v>668</v>
+      </c>
+      <c r="B668" s="1">
+        <v>176.7539276439751</v>
+      </c>
+    </row>
+    <row r="669" spans="1:2">
+      <c r="A669" t="s">
+        <v>669</v>
+      </c>
+      <c r="B669" s="1">
+        <v>176.8031086457219</v>
+      </c>
+    </row>
+    <row r="670" spans="1:2">
+      <c r="A670" t="s">
+        <v>670</v>
+      </c>
+      <c r="B670" s="1">
+        <v>177.3282883207904</v>
+      </c>
+    </row>
+    <row r="671" spans="1:2">
+      <c r="A671" t="s">
+        <v>671</v>
+      </c>
+      <c r="B671" s="1">
+        <v>182.065899631175</v>
+      </c>
+    </row>
+    <row r="672" spans="1:2">
+      <c r="A672" t="s">
+        <v>672</v>
+      </c>
+      <c r="B672" s="1">
+        <v>189.6790043573956</v>
+      </c>
+    </row>
+    <row r="673" spans="1:2">
+      <c r="A673" t="s">
+        <v>673</v>
+      </c>
+      <c r="B673" s="1">
+        <v>191.1436662222693</v>
+      </c>
+    </row>
+    <row r="674" spans="1:2">
+      <c r="A674" t="s">
+        <v>674</v>
+      </c>
+      <c r="B674" s="1">
+        <v>193.73519033948</v>
+      </c>
+    </row>
+    <row r="675" spans="1:2">
+      <c r="A675" t="s">
+        <v>675</v>
+      </c>
+      <c r="B675" s="1">
+        <v>199.5799420029931</v>
+      </c>
+    </row>
+    <row r="676" spans="1:2">
+      <c r="A676" t="s">
+        <v>676</v>
+      </c>
+      <c r="B676" s="1">
+        <v>202.3870172316073</v>
+      </c>
+    </row>
+    <row r="677" spans="1:2">
+      <c r="A677" t="s">
+        <v>677</v>
+      </c>
+      <c r="B677" s="1">
+        <v>205.9679660503097</v>
+      </c>
+    </row>
+    <row r="678" spans="1:2">
+      <c r="A678" t="s">
+        <v>678</v>
+      </c>
+      <c r="B678" s="1">
+        <v>206.3896359096363</v>
+      </c>
+    </row>
+    <row r="679" spans="1:2">
+      <c r="A679" t="s">
+        <v>679</v>
+      </c>
+      <c r="B679" s="1">
+        <v>207.7500518109333</v>
+      </c>
+    </row>
+    <row r="680" spans="1:2">
+      <c r="A680" t="s">
+        <v>680</v>
+      </c>
+      <c r="B680" s="1">
+        <v>211.3539276813083</v>
+      </c>
+    </row>
+    <row r="681" spans="1:2">
+      <c r="A681" t="s">
+        <v>681</v>
+      </c>
+      <c r="B681" s="1">
+        <v>211.5409806952388</v>
+      </c>
+    </row>
+    <row r="682" spans="1:2">
+      <c r="A682" t="s">
+        <v>682</v>
+      </c>
+      <c r="B682" s="1">
+        <v>214.210627151177</v>
+      </c>
+    </row>
+    <row r="683" spans="1:2">
+      <c r="A683" t="s">
+        <v>683</v>
+      </c>
+      <c r="B683" s="1">
+        <v>214.2266075160047</v>
+      </c>
+    </row>
+    <row r="684" spans="1:2">
+      <c r="A684" t="s">
+        <v>684</v>
+      </c>
+      <c r="B684" s="1">
+        <v>215.8741177938066</v>
+      </c>
+    </row>
+    <row r="685" spans="1:2">
+      <c r="A685" t="s">
+        <v>685</v>
+      </c>
+      <c r="B685" s="1">
+        <v>217.7491204103518</v>
+      </c>
+    </row>
+    <row r="686" spans="1:2">
+      <c r="A686" t="s">
+        <v>686</v>
+      </c>
+      <c r="B686" s="1">
+        <v>218.2263955132005</v>
+      </c>
+    </row>
+    <row r="687" spans="1:2">
+      <c r="A687" t="s">
+        <v>687</v>
+      </c>
+      <c r="B687" s="1">
+        <v>219.3852508624493</v>
+      </c>
+    </row>
+    <row r="688" spans="1:2">
+      <c r="A688" t="s">
+        <v>688</v>
+      </c>
+      <c r="B688" s="1">
+        <v>219.6643827635574</v>
+      </c>
+    </row>
+    <row r="689" spans="1:2">
+      <c r="A689" t="s">
+        <v>689</v>
+      </c>
+      <c r="B689" s="1">
+        <v>231.572235419191</v>
+      </c>
+    </row>
+    <row r="690" spans="1:2">
+      <c r="A690" t="s">
+        <v>690</v>
+      </c>
+      <c r="B690" s="1">
+        <v>235.9113867713231</v>
+      </c>
+    </row>
+    <row r="691" spans="1:2">
+      <c r="A691" t="s">
+        <v>691</v>
+      </c>
+      <c r="B691" s="1">
+        <v>247.8508571072771</v>
+      </c>
+    </row>
+    <row r="692" spans="1:2">
+      <c r="A692" t="s">
+        <v>692</v>
+      </c>
+      <c r="B692" s="1">
+        <v>280.4690408004643</v>
+      </c>
+    </row>
+    <row r="693" spans="1:2">
+      <c r="A693" t="s">
+        <v>693</v>
+      </c>
+      <c r="B693" s="1">
+        <v>335.914401328226</v>
+      </c>
+    </row>
+    <row r="694" spans="1:2">
+      <c r="A694" t="s">
+        <v>694</v>
+      </c>
+      <c r="B694" s="1">
+        <v>398.352263803539</v>
+      </c>
+    </row>
+    <row r="695" spans="1:2">
+      <c r="A695" t="s">
+        <v>695</v>
+      </c>
+      <c r="B695" s="1">
+        <v>402.5877908268833</v>
+      </c>
+    </row>
+    <row r="696" spans="1:2">
+      <c r="A696" t="s">
+        <v>696</v>
+      </c>
+      <c r="B696" s="1">
+        <v>435.9782420844183</v>
+      </c>
+    </row>
+    <row r="697" spans="1:2">
+      <c r="A697" t="s">
+        <v>697</v>
+      </c>
+      <c r="B697" s="1">
+        <v>465.6310313212279</v>
+      </c>
+    </row>
+    <row r="698" spans="1:2">
+      <c r="A698" t="s">
+        <v>698</v>
+      </c>
+      <c r="B698" s="1">
+        <v>517.8022810720011</v>
       </c>
     </row>
   </sheetData>

--- a/Screener/data/rs_rating_top_30.xlsx
+++ b/Screener/data/rs_rating_top_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="699">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="584">
   <si>
     <t>Symbol</t>
   </si>
@@ -22,2092 +22,1747 @@
     <t>RS Rating</t>
   </si>
   <si>
-    <t>NPO</t>
+    <t>CFNB</t>
+  </si>
+  <si>
+    <t>MRTX</t>
+  </si>
+  <si>
+    <t>CRVL</t>
+  </si>
+  <si>
+    <t>LOPE</t>
+  </si>
+  <si>
+    <t>PAA</t>
+  </si>
+  <si>
+    <t>GOOGL</t>
+  </si>
+  <si>
+    <t>EMYB</t>
+  </si>
+  <si>
+    <t>FTV</t>
+  </si>
+  <si>
+    <t>ATEX</t>
+  </si>
+  <si>
+    <t>JAZZ</t>
+  </si>
+  <si>
+    <t>EHC</t>
+  </si>
+  <si>
+    <t>GOOG</t>
+  </si>
+  <si>
+    <t>BKE</t>
+  </si>
+  <si>
+    <t>RBB</t>
+  </si>
+  <si>
+    <t>SPB</t>
+  </si>
+  <si>
+    <t>FXNC</t>
+  </si>
+  <si>
+    <t>SCCO</t>
+  </si>
+  <si>
+    <t>CSCO</t>
+  </si>
+  <si>
+    <t>DHACU</t>
+  </si>
+  <si>
+    <t>NXGN</t>
+  </si>
+  <si>
+    <t>CLH</t>
+  </si>
+  <si>
+    <t>MORN</t>
+  </si>
+  <si>
+    <t>TNK</t>
+  </si>
+  <si>
+    <t>TWST</t>
+  </si>
+  <si>
+    <t>FFIC</t>
+  </si>
+  <si>
+    <t>REVG</t>
+  </si>
+  <si>
+    <t>CTSH</t>
+  </si>
+  <si>
+    <t>MEDP</t>
+  </si>
+  <si>
+    <t>FLT</t>
+  </si>
+  <si>
+    <t>JHX</t>
+  </si>
+  <si>
+    <t>PNR</t>
+  </si>
+  <si>
+    <t>GBDC</t>
+  </si>
+  <si>
+    <t>ICFI</t>
+  </si>
+  <si>
+    <t>ATI</t>
+  </si>
+  <si>
+    <t>BWXT</t>
+  </si>
+  <si>
+    <t>CMUV</t>
+  </si>
+  <si>
+    <t>HES</t>
+  </si>
+  <si>
+    <t>CCAP</t>
+  </si>
+  <si>
+    <t>UBAB</t>
+  </si>
+  <si>
+    <t>PWR</t>
+  </si>
+  <si>
+    <t>CAL</t>
+  </si>
+  <si>
+    <t>ANAB</t>
+  </si>
+  <si>
+    <t>NWPX</t>
+  </si>
+  <si>
+    <t>UNP</t>
+  </si>
+  <si>
+    <t>PH</t>
+  </si>
+  <si>
+    <t>CBOE</t>
+  </si>
+  <si>
+    <t>TJX</t>
+  </si>
+  <si>
+    <t>ACAD</t>
+  </si>
+  <si>
+    <t>FBP</t>
+  </si>
+  <si>
+    <t>PFX</t>
+  </si>
+  <si>
+    <t>MATX</t>
+  </si>
+  <si>
+    <t>INTU</t>
+  </si>
+  <si>
+    <t>AIZ</t>
+  </si>
+  <si>
+    <t>BROS</t>
+  </si>
+  <si>
+    <t>COLL</t>
+  </si>
+  <si>
+    <t>NTNX</t>
+  </si>
+  <si>
+    <t>DEI</t>
+  </si>
+  <si>
+    <t>IR</t>
+  </si>
+  <si>
+    <t>CEN</t>
+  </si>
+  <si>
+    <t>SPFI</t>
+  </si>
+  <si>
+    <t>NTIC</t>
+  </si>
+  <si>
+    <t>BBSI</t>
+  </si>
+  <si>
+    <t>FRSB</t>
+  </si>
+  <si>
+    <t>USLM</t>
+  </si>
+  <si>
+    <t>CFST</t>
+  </si>
+  <si>
+    <t>BA</t>
+  </si>
+  <si>
+    <t>VIST</t>
+  </si>
+  <si>
+    <t>CME</t>
+  </si>
+  <si>
+    <t>IHG</t>
+  </si>
+  <si>
+    <t>PBF</t>
+  </si>
+  <si>
+    <t>RXST</t>
+  </si>
+  <si>
+    <t>CIGI</t>
+  </si>
+  <si>
+    <t>FARO</t>
+  </si>
+  <si>
+    <t>CRMT</t>
+  </si>
+  <si>
+    <t>CVE</t>
+  </si>
+  <si>
+    <t>ABCM</t>
+  </si>
+  <si>
+    <t>NFE</t>
+  </si>
+  <si>
+    <t>CADE</t>
+  </si>
+  <si>
+    <t>VLO</t>
+  </si>
+  <si>
+    <t>BKU</t>
+  </si>
+  <si>
+    <t>MET</t>
+  </si>
+  <si>
+    <t>ALSN</t>
+  </si>
+  <si>
+    <t>ITT</t>
+  </si>
+  <si>
+    <t>VET</t>
+  </si>
+  <si>
+    <t>STX</t>
+  </si>
+  <si>
+    <t>BHWB</t>
+  </si>
+  <si>
+    <t>TT</t>
+  </si>
+  <si>
+    <t>AIT</t>
+  </si>
+  <si>
+    <t>CSWC</t>
   </si>
   <si>
     <t>NWSA</t>
   </si>
   <si>
-    <t>CSAN</t>
-  </si>
-  <si>
-    <t>GWRE</t>
-  </si>
-  <si>
-    <t>INTU</t>
+    <t>FANG</t>
+  </si>
+  <si>
+    <t>CMCSA</t>
+  </si>
+  <si>
+    <t>TSBK</t>
+  </si>
+  <si>
+    <t>DCPH</t>
+  </si>
+  <si>
+    <t>LSCC</t>
+  </si>
+  <si>
+    <t>GNE</t>
+  </si>
+  <si>
+    <t>TFSL</t>
+  </si>
+  <si>
+    <t>WDFC</t>
+  </si>
+  <si>
+    <t>TARO</t>
+  </si>
+  <si>
+    <t>MANU</t>
+  </si>
+  <si>
+    <t>FMX</t>
+  </si>
+  <si>
+    <t>CTRA</t>
+  </si>
+  <si>
+    <t>RCMT</t>
+  </si>
+  <si>
+    <t>HOLI</t>
+  </si>
+  <si>
+    <t>IMTX</t>
+  </si>
+  <si>
+    <t>LDOS</t>
+  </si>
+  <si>
+    <t>PWSC</t>
+  </si>
+  <si>
+    <t>CFBK</t>
+  </si>
+  <si>
+    <t>ARVN</t>
+  </si>
+  <si>
+    <t>COIN</t>
+  </si>
+  <si>
+    <t>BSRR</t>
+  </si>
+  <si>
+    <t>WMB</t>
+  </si>
+  <si>
+    <t>VERX</t>
+  </si>
+  <si>
+    <t>WWD</t>
+  </si>
+  <si>
+    <t>DELL</t>
+  </si>
+  <si>
+    <t>NEU</t>
+  </si>
+  <si>
+    <t>NVMI</t>
+  </si>
+  <si>
+    <t>PPC</t>
+  </si>
+  <si>
+    <t>PAHC</t>
+  </si>
+  <si>
+    <t>ERF</t>
+  </si>
+  <si>
+    <t>ARBV</t>
+  </si>
+  <si>
+    <t>WWE</t>
+  </si>
+  <si>
+    <t>RCL</t>
+  </si>
+  <si>
+    <t>ARCE</t>
+  </si>
+  <si>
+    <t>BCML</t>
+  </si>
+  <si>
+    <t>ARCB</t>
+  </si>
+  <si>
+    <t>URI</t>
+  </si>
+  <si>
+    <t>EOG</t>
+  </si>
+  <si>
+    <t>ICLR</t>
+  </si>
+  <si>
+    <t>IMO</t>
+  </si>
+  <si>
+    <t>ABCB</t>
+  </si>
+  <si>
+    <t>SAL</t>
+  </si>
+  <si>
+    <t>SNEX</t>
+  </si>
+  <si>
+    <t>SMCI</t>
+  </si>
+  <si>
+    <t>FFNW</t>
+  </si>
+  <si>
+    <t>FWRG</t>
+  </si>
+  <si>
+    <t>LNG</t>
+  </si>
+  <si>
+    <t>AVID</t>
+  </si>
+  <si>
+    <t>ZION</t>
+  </si>
+  <si>
+    <t>TCBI</t>
+  </si>
+  <si>
+    <t>BLX</t>
+  </si>
+  <si>
+    <t>TCPC</t>
+  </si>
+  <si>
+    <t>PXD</t>
+  </si>
+  <si>
+    <t>SMMF</t>
+  </si>
+  <si>
+    <t>BRZE</t>
+  </si>
+  <si>
+    <t>MRCY</t>
+  </si>
+  <si>
+    <t>BY</t>
+  </si>
+  <si>
+    <t>PRMW</t>
+  </si>
+  <si>
+    <t>NWS</t>
+  </si>
+  <si>
+    <t>TRMD</t>
+  </si>
+  <si>
+    <t>HP</t>
+  </si>
+  <si>
+    <t>LAD</t>
+  </si>
+  <si>
+    <t>LIVN</t>
+  </si>
+  <si>
+    <t>EMR</t>
+  </si>
+  <si>
+    <t>EXEL</t>
+  </si>
+  <si>
+    <t>DGICB</t>
+  </si>
+  <si>
+    <t>MLR</t>
+  </si>
+  <si>
+    <t>NBIX</t>
+  </si>
+  <si>
+    <t>PRGO</t>
+  </si>
+  <si>
+    <t>JXN</t>
+  </si>
+  <si>
+    <t>QTRX</t>
+  </si>
+  <si>
+    <t>SU</t>
+  </si>
+  <si>
+    <t>FETM</t>
+  </si>
+  <si>
+    <t>GNTX</t>
+  </si>
+  <si>
+    <t>ARCT</t>
+  </si>
+  <si>
+    <t>DAWN</t>
+  </si>
+  <si>
+    <t>VRE</t>
+  </si>
+  <si>
+    <t>VABK</t>
+  </si>
+  <si>
+    <t>EVBN</t>
+  </si>
+  <si>
+    <t>LBRDK</t>
+  </si>
+  <si>
+    <t>DDS</t>
+  </si>
+  <si>
+    <t>STRT</t>
+  </si>
+  <si>
+    <t>CCB</t>
+  </si>
+  <si>
+    <t>ADBE</t>
+  </si>
+  <si>
+    <t>CPRX</t>
+  </si>
+  <si>
+    <t>WOR</t>
+  </si>
+  <si>
+    <t>AIR</t>
+  </si>
+  <si>
+    <t>PX</t>
+  </si>
+  <si>
+    <t>FNF</t>
+  </si>
+  <si>
+    <t>MBIN</t>
+  </si>
+  <si>
+    <t>FRHC</t>
+  </si>
+  <si>
+    <t>GPOR</t>
+  </si>
+  <si>
+    <t>ADP</t>
+  </si>
+  <si>
+    <t>NYT</t>
+  </si>
+  <si>
+    <t>ZWS</t>
+  </si>
+  <si>
+    <t>HTHT</t>
+  </si>
+  <si>
+    <t>IMAX</t>
+  </si>
+  <si>
+    <t>INSM</t>
+  </si>
+  <si>
+    <t>TRGP</t>
+  </si>
+  <si>
+    <t>KTOS</t>
+  </si>
+  <si>
+    <t>NVDA</t>
+  </si>
+  <si>
+    <t>PFBC</t>
+  </si>
+  <si>
+    <t>STER</t>
+  </si>
+  <si>
+    <t>UFPI</t>
+  </si>
+  <si>
+    <t>PDCO</t>
+  </si>
+  <si>
+    <t>GH</t>
+  </si>
+  <si>
+    <t>AKAM</t>
+  </si>
+  <si>
+    <t>ORRF</t>
+  </si>
+  <si>
+    <t>TS</t>
+  </si>
+  <si>
+    <t>MAT</t>
+  </si>
+  <si>
+    <t>SRV</t>
+  </si>
+  <si>
+    <t>PNFP</t>
+  </si>
+  <si>
+    <t>WMS</t>
+  </si>
+  <si>
+    <t>PSTG</t>
+  </si>
+  <si>
+    <t>LBRDA</t>
+  </si>
+  <si>
+    <t>BKR</t>
+  </si>
+  <si>
+    <t>PFC</t>
+  </si>
+  <si>
+    <t>KNSA</t>
+  </si>
+  <si>
+    <t>ROST</t>
+  </si>
+  <si>
+    <t>GOLF</t>
+  </si>
+  <si>
+    <t>CSTL</t>
+  </si>
+  <si>
+    <t>XPEL</t>
+  </si>
+  <si>
+    <t>MAR</t>
+  </si>
+  <si>
+    <t>MBWM</t>
+  </si>
+  <si>
+    <t>BRBR</t>
+  </si>
+  <si>
+    <t>ACT</t>
+  </si>
+  <si>
+    <t>APO</t>
+  </si>
+  <si>
+    <t>CVI</t>
+  </si>
+  <si>
+    <t>IBP</t>
+  </si>
+  <si>
+    <t>CDW</t>
+  </si>
+  <si>
+    <t>DPZ</t>
+  </si>
+  <si>
+    <t>VALU</t>
+  </si>
+  <si>
+    <t>KOP</t>
+  </si>
+  <si>
+    <t>COOP</t>
+  </si>
+  <si>
+    <t>MLP</t>
+  </si>
+  <si>
+    <t>VVI</t>
+  </si>
+  <si>
+    <t>REGN</t>
+  </si>
+  <si>
+    <t>ALKT</t>
+  </si>
+  <si>
+    <t>GBLI</t>
+  </si>
+  <si>
+    <t>ALRM</t>
+  </si>
+  <si>
+    <t>AR</t>
+  </si>
+  <si>
+    <t>APPF</t>
+  </si>
+  <si>
+    <t>NECB</t>
+  </si>
+  <si>
+    <t>SSD</t>
+  </si>
+  <si>
+    <t>NARI</t>
+  </si>
+  <si>
+    <t>VMW</t>
+  </si>
+  <si>
+    <t>HALO</t>
+  </si>
+  <si>
+    <t>CRS</t>
+  </si>
+  <si>
+    <t>VAL</t>
+  </si>
+  <si>
+    <t>BG</t>
+  </si>
+  <si>
+    <t>CENTA</t>
+  </si>
+  <si>
+    <t>VECO</t>
+  </si>
+  <si>
+    <t>VEL</t>
+  </si>
+  <si>
+    <t>SKYW</t>
+  </si>
+  <si>
+    <t>BR</t>
+  </si>
+  <si>
+    <t>BKNG</t>
+  </si>
+  <si>
+    <t>CDRE</t>
+  </si>
+  <si>
+    <t>TNET</t>
+  </si>
+  <si>
+    <t>SXI</t>
+  </si>
+  <si>
+    <t>OC</t>
+  </si>
+  <si>
+    <t>ETN</t>
+  </si>
+  <si>
+    <t>TH</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>ALGN</t>
+  </si>
+  <si>
+    <t>MSA</t>
+  </si>
+  <si>
+    <t>TCOM</t>
+  </si>
+  <si>
+    <t>DMRC</t>
+  </si>
+  <si>
+    <t>AMGN</t>
+  </si>
+  <si>
+    <t>HQY</t>
+  </si>
+  <si>
+    <t>SAH</t>
+  </si>
+  <si>
+    <t>OPCH</t>
+  </si>
+  <si>
+    <t>FIX</t>
+  </si>
+  <si>
+    <t>FUTU</t>
+  </si>
+  <si>
+    <t>ROAD</t>
+  </si>
+  <si>
+    <t>IPI</t>
+  </si>
+  <si>
+    <t>NHC</t>
+  </si>
+  <si>
+    <t>MTCH</t>
+  </si>
+  <si>
+    <t>MHO</t>
+  </si>
+  <si>
+    <t>CCL</t>
+  </si>
+  <si>
+    <t>INFA</t>
+  </si>
+  <si>
+    <t>ZGN</t>
+  </si>
+  <si>
+    <t>PSX</t>
+  </si>
+  <si>
+    <t>TEAM</t>
+  </si>
+  <si>
+    <t>NTRA</t>
+  </si>
+  <si>
+    <t>BWMX</t>
+  </si>
+  <si>
+    <t>ETD</t>
+  </si>
+  <si>
+    <t>RNGR</t>
+  </si>
+  <si>
+    <t>GKOS</t>
+  </si>
+  <si>
+    <t>TFII</t>
+  </si>
+  <si>
+    <t>WSM</t>
+  </si>
+  <si>
+    <t>ESCA</t>
+  </si>
+  <si>
+    <t>IBKR</t>
+  </si>
+  <si>
+    <t>FLR</t>
+  </si>
+  <si>
+    <t>TCBX</t>
+  </si>
+  <si>
+    <t>MUR</t>
+  </si>
+  <si>
+    <t>CMPR</t>
+  </si>
+  <si>
+    <t>CNOB</t>
+  </si>
+  <si>
+    <t>PTEN</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>NREF</t>
+  </si>
+  <si>
+    <t>ARGX</t>
+  </si>
+  <si>
+    <t>ANDE</t>
+  </si>
+  <si>
+    <t>HNI</t>
+  </si>
+  <si>
+    <t>LQDT</t>
+  </si>
+  <si>
+    <t>WIX</t>
+  </si>
+  <si>
+    <t>KTB</t>
+  </si>
+  <si>
+    <t>DICE</t>
+  </si>
+  <si>
+    <t>FC</t>
+  </si>
+  <si>
+    <t>SITM</t>
+  </si>
+  <si>
+    <t>CUBI</t>
+  </si>
+  <si>
+    <t>BCSF</t>
+  </si>
+  <si>
+    <t>TIPT</t>
+  </si>
+  <si>
+    <t>YELP</t>
+  </si>
+  <si>
+    <t>APOG</t>
+  </si>
+  <si>
+    <t>ANET</t>
+  </si>
+  <si>
+    <t>RCEL</t>
+  </si>
+  <si>
+    <t>CPNG</t>
+  </si>
+  <si>
+    <t>CAR</t>
+  </si>
+  <si>
+    <t>CAT</t>
+  </si>
+  <si>
+    <t>BOOT</t>
+  </si>
+  <si>
+    <t>NEOG</t>
+  </si>
+  <si>
+    <t>AFBI</t>
+  </si>
+  <si>
+    <t>OII</t>
+  </si>
+  <si>
+    <t>QLYS</t>
+  </si>
+  <si>
+    <t>FLXS</t>
+  </si>
+  <si>
+    <t>STRS</t>
+  </si>
+  <si>
+    <t>PAM</t>
+  </si>
+  <si>
+    <t>SAM</t>
+  </si>
+  <si>
+    <t>AEL</t>
+  </si>
+  <si>
+    <t>GRC</t>
+  </si>
+  <si>
+    <t>CUK</t>
+  </si>
+  <si>
+    <t>CLW</t>
+  </si>
+  <si>
+    <t>AGM</t>
+  </si>
+  <si>
+    <t>HLF</t>
+  </si>
+  <si>
+    <t>AURCU</t>
+  </si>
+  <si>
+    <t>HAL</t>
+  </si>
+  <si>
+    <t>MLKN</t>
+  </si>
+  <si>
+    <t>TXT</t>
+  </si>
+  <si>
+    <t>FSFG</t>
+  </si>
+  <si>
+    <t>DLR</t>
+  </si>
+  <si>
+    <t>MGPI</t>
+  </si>
+  <si>
+    <t>DRQ</t>
+  </si>
+  <si>
+    <t>CSWI</t>
+  </si>
+  <si>
+    <t>CARR</t>
+  </si>
+  <si>
+    <t>ELF</t>
+  </si>
+  <si>
+    <t>BNTX</t>
+  </si>
+  <si>
+    <t>CENT</t>
+  </si>
+  <si>
+    <t>BXP</t>
+  </si>
+  <si>
+    <t>PLUS</t>
+  </si>
+  <si>
+    <t>SLB</t>
+  </si>
+  <si>
+    <t>KRC</t>
+  </si>
+  <si>
+    <t>FTI</t>
+  </si>
+  <si>
+    <t>DCOM</t>
+  </si>
+  <si>
+    <t>STNG</t>
+  </si>
+  <si>
+    <t>TREX</t>
+  </si>
+  <si>
+    <t>SPOK</t>
+  </si>
+  <si>
+    <t>VST</t>
+  </si>
+  <si>
+    <t>CSPI</t>
+  </si>
+  <si>
+    <t>CPS</t>
+  </si>
+  <si>
+    <t>NEWT</t>
+  </si>
+  <si>
+    <t>RCUS</t>
+  </si>
+  <si>
+    <t>EVI</t>
+  </si>
+  <si>
+    <t>LBRT</t>
+  </si>
+  <si>
+    <t>RPM</t>
+  </si>
+  <si>
+    <t>FORG</t>
+  </si>
+  <si>
+    <t>AZPN</t>
+  </si>
+  <si>
+    <t>SCPL</t>
+  </si>
+  <si>
+    <t>CHTR</t>
   </si>
   <si>
     <t>ENLC</t>
   </si>
   <si>
-    <t>UBA</t>
-  </si>
-  <si>
-    <t>ALC</t>
-  </si>
-  <si>
-    <t>AR</t>
-  </si>
-  <si>
-    <t>ESQ</t>
-  </si>
-  <si>
-    <t>WMB</t>
-  </si>
-  <si>
-    <t>MTACU</t>
-  </si>
-  <si>
-    <t>SWI</t>
-  </si>
-  <si>
-    <t>KE</t>
-  </si>
-  <si>
-    <t>ALRM</t>
-  </si>
-  <si>
-    <t>EVTC</t>
-  </si>
-  <si>
-    <t>OMAB</t>
-  </si>
-  <si>
-    <t>DBX</t>
+    <t>ARCH</t>
+  </si>
+  <si>
+    <t>PBNK</t>
+  </si>
+  <si>
+    <t>CNXN</t>
+  </si>
+  <si>
+    <t>RH</t>
+  </si>
+  <si>
+    <t>LAUR</t>
+  </si>
+  <si>
+    <t>FRPT</t>
+  </si>
+  <si>
+    <t>DBRG</t>
+  </si>
+  <si>
+    <t>NE</t>
+  </si>
+  <si>
+    <t>SPNS</t>
+  </si>
+  <si>
+    <t>ATSG</t>
+  </si>
+  <si>
+    <t>HURN</t>
+  </si>
+  <si>
+    <t>VRNS</t>
+  </si>
+  <si>
+    <t>MVBF</t>
+  </si>
+  <si>
+    <t>LI</t>
+  </si>
+  <si>
+    <t>HEP</t>
+  </si>
+  <si>
+    <t>BOH</t>
+  </si>
+  <si>
+    <t>CW</t>
+  </si>
+  <si>
+    <t>CIVI</t>
+  </si>
+  <si>
+    <t>DVAX</t>
+  </si>
+  <si>
+    <t>TRNS</t>
+  </si>
+  <si>
+    <t>CVLG</t>
+  </si>
+  <si>
+    <t>AMEH</t>
+  </si>
+  <si>
+    <t>LII</t>
+  </si>
+  <si>
+    <t>BBW</t>
+  </si>
+  <si>
+    <t>AZEK</t>
+  </si>
+  <si>
+    <t>RIVN</t>
+  </si>
+  <si>
+    <t>NWLI</t>
+  </si>
+  <si>
+    <t>HCCI</t>
+  </si>
+  <si>
+    <t>HAYW</t>
+  </si>
+  <si>
+    <t>MCB</t>
+  </si>
+  <si>
+    <t>ACU</t>
+  </si>
+  <si>
+    <t>ODFL</t>
+  </si>
+  <si>
+    <t>TNP</t>
+  </si>
+  <si>
+    <t>NVO</t>
+  </si>
+  <si>
+    <t>AZZ</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>HOFT</t>
+  </si>
+  <si>
+    <t>CHX</t>
+  </si>
+  <si>
+    <t>INOD</t>
+  </si>
+  <si>
+    <t>SHEN</t>
+  </si>
+  <si>
+    <t>OLLI</t>
+  </si>
+  <si>
+    <t>SRI</t>
+  </si>
+  <si>
+    <t>CCJ</t>
+  </si>
+  <si>
+    <t>NCR</t>
+  </si>
+  <si>
+    <t>SFBS</t>
+  </si>
+  <si>
+    <t>NOG</t>
+  </si>
+  <si>
+    <t>RAMP</t>
+  </si>
+  <si>
+    <t>KSS</t>
+  </si>
+  <si>
+    <t>ALPN</t>
+  </si>
+  <si>
+    <t>UBS</t>
+  </si>
+  <si>
+    <t>MTDR</t>
+  </si>
+  <si>
+    <t>BLD</t>
+  </si>
+  <si>
+    <t>HLNE</t>
+  </si>
+  <si>
+    <t>PRIM</t>
+  </si>
+  <si>
+    <t>DOMO</t>
+  </si>
+  <si>
+    <t>DLX</t>
+  </si>
+  <si>
+    <t>TALO</t>
+  </si>
+  <si>
+    <t>QCRH</t>
+  </si>
+  <si>
+    <t>GPN</t>
+  </si>
+  <si>
+    <t>SOVO</t>
+  </si>
+  <si>
+    <t>FRO</t>
+  </si>
+  <si>
+    <t>CVRX</t>
+  </si>
+  <si>
+    <t>RDY</t>
+  </si>
+  <si>
+    <t>EURN</t>
+  </si>
+  <si>
+    <t>WMG</t>
+  </si>
+  <si>
+    <t>ASMIY</t>
+  </si>
+  <si>
+    <t>APA</t>
+  </si>
+  <si>
+    <t>PESI</t>
+  </si>
+  <si>
+    <t>PHAT</t>
+  </si>
+  <si>
+    <t>CAAP</t>
+  </si>
+  <si>
+    <t>VICR</t>
+  </si>
+  <si>
+    <t>ITRN</t>
+  </si>
+  <si>
+    <t>FRD</t>
+  </si>
+  <si>
+    <t>GTLS</t>
+  </si>
+  <si>
+    <t>XP</t>
+  </si>
+  <si>
+    <t>PRO</t>
+  </si>
+  <si>
+    <t>GIC</t>
+  </si>
+  <si>
+    <t>OSK</t>
+  </si>
+  <si>
+    <t>TW</t>
+  </si>
+  <si>
+    <t>PRA</t>
+  </si>
+  <si>
+    <t>INSW</t>
+  </si>
+  <si>
+    <t>NEWR</t>
+  </si>
+  <si>
+    <t>BKI</t>
+  </si>
+  <si>
+    <t>PLCE</t>
+  </si>
+  <si>
+    <t>CABA</t>
+  </si>
+  <si>
+    <t>FTAI</t>
+  </si>
+  <si>
+    <t>PSFE</t>
+  </si>
+  <si>
+    <t>STEP</t>
+  </si>
+  <si>
+    <t>EME</t>
+  </si>
+  <si>
+    <t>SG</t>
+  </si>
+  <si>
+    <t>ASTE</t>
+  </si>
+  <si>
+    <t>MPC</t>
+  </si>
+  <si>
+    <t>PSN</t>
+  </si>
+  <si>
+    <t>AMNB</t>
+  </si>
+  <si>
+    <t>SENEB</t>
+  </si>
+  <si>
+    <t>HWKN</t>
+  </si>
+  <si>
+    <t>CVBF</t>
+  </si>
+  <si>
+    <t>BZH</t>
+  </si>
+  <si>
+    <t>AURC</t>
+  </si>
+  <si>
+    <t>ROCK</t>
+  </si>
+  <si>
+    <t>ACOR</t>
+  </si>
+  <si>
+    <t>RVMD</t>
+  </si>
+  <si>
+    <t>EXTR</t>
+  </si>
+  <si>
+    <t>CALB</t>
+  </si>
+  <si>
+    <t>SENEA</t>
+  </si>
+  <si>
+    <t>TDW</t>
+  </si>
+  <si>
+    <t>PAR</t>
+  </si>
+  <si>
+    <t>CRC</t>
+  </si>
+  <si>
+    <t>CWCO</t>
+  </si>
+  <si>
+    <t>TRDA</t>
+  </si>
+  <si>
+    <t>XPRO</t>
+  </si>
+  <si>
+    <t>NRP</t>
+  </si>
+  <si>
+    <t>YETI</t>
+  </si>
+  <si>
+    <t>WAL</t>
+  </si>
+  <si>
+    <t>WHD</t>
+  </si>
+  <si>
+    <t>NOV</t>
+  </si>
+  <si>
+    <t>LLY</t>
+  </si>
+  <si>
+    <t>INBK</t>
+  </si>
+  <si>
+    <t>JOE</t>
+  </si>
+  <si>
+    <t>HRB</t>
+  </si>
+  <si>
+    <t>OVV</t>
+  </si>
+  <si>
+    <t>DFH</t>
+  </si>
+  <si>
+    <t>FOR</t>
+  </si>
+  <si>
+    <t>IDYA</t>
+  </si>
+  <si>
+    <t>KD</t>
+  </si>
+  <si>
+    <t>KDNY</t>
+  </si>
+  <si>
+    <t>SLG</t>
+  </si>
+  <si>
+    <t>AROC</t>
+  </si>
+  <si>
+    <t>AZTA</t>
+  </si>
+  <si>
+    <t>XPO</t>
+  </si>
+  <si>
+    <t>WFRD</t>
+  </si>
+  <si>
+    <t>ESEA</t>
+  </si>
+  <si>
+    <t>GCO</t>
+  </si>
+  <si>
+    <t>SAIA</t>
+  </si>
+  <si>
+    <t>GBX</t>
+  </si>
+  <si>
+    <t>MTSI</t>
+  </si>
+  <si>
+    <t>ANIP</t>
+  </si>
+  <si>
+    <t>TRUP</t>
+  </si>
+  <si>
+    <t>AMR</t>
+  </si>
+  <si>
+    <t>LEAT</t>
+  </si>
+  <si>
+    <t>BCC</t>
+  </si>
+  <si>
+    <t>ROKU</t>
+  </si>
+  <si>
+    <t>NATR</t>
+  </si>
+  <si>
+    <t>CNX</t>
+  </si>
+  <si>
+    <t>GHM</t>
+  </si>
+  <si>
+    <t>DCBO</t>
   </si>
   <si>
     <t>BFST</t>
   </si>
   <si>
-    <t>SBS</t>
-  </si>
-  <si>
-    <t>VMC</t>
-  </si>
-  <si>
-    <t>STE</t>
-  </si>
-  <si>
-    <t>ABST</t>
-  </si>
-  <si>
-    <t>PBR</t>
-  </si>
-  <si>
-    <t>HEAR</t>
-  </si>
-  <si>
-    <t>MSM</t>
-  </si>
-  <si>
-    <t>SHW</t>
-  </si>
-  <si>
-    <t>BWXT</t>
-  </si>
-  <si>
-    <t>MCK</t>
-  </si>
-  <si>
-    <t>VSH</t>
-  </si>
-  <si>
-    <t>GFF</t>
-  </si>
-  <si>
-    <t>HWM</t>
-  </si>
-  <si>
-    <t>HY</t>
-  </si>
-  <si>
-    <t>RUSHB</t>
-  </si>
-  <si>
-    <t>PMGMU</t>
-  </si>
-  <si>
-    <t>CEN</t>
-  </si>
-  <si>
-    <t>WTM</t>
-  </si>
-  <si>
-    <t>BLMN</t>
-  </si>
-  <si>
-    <t>BBW</t>
-  </si>
-  <si>
-    <t>TIPT</t>
-  </si>
-  <si>
-    <t>SLG</t>
-  </si>
-  <si>
-    <t>MTSI</t>
-  </si>
-  <si>
-    <t>CMC</t>
-  </si>
-  <si>
-    <t>DHI</t>
-  </si>
-  <si>
-    <t>RUSHA</t>
-  </si>
-  <si>
-    <t>ZNTL</t>
-  </si>
-  <si>
-    <t>NWS</t>
-  </si>
-  <si>
-    <t>R</t>
-  </si>
-  <si>
-    <t>AIZ</t>
-  </si>
-  <si>
-    <t>PPC</t>
-  </si>
-  <si>
-    <t>GGAAU</t>
-  </si>
-  <si>
-    <t>TBBK</t>
-  </si>
-  <si>
-    <t>APOG</t>
-  </si>
-  <si>
-    <t>KTB</t>
+    <t>NOA</t>
+  </si>
+  <si>
+    <t>CELH</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>LYTS</t>
+  </si>
+  <si>
+    <t>LOB</t>
+  </si>
+  <si>
+    <t>OBT</t>
+  </si>
+  <si>
+    <t>PRDO</t>
+  </si>
+  <si>
+    <t>TWIN</t>
+  </si>
+  <si>
+    <t>CIR</t>
+  </si>
+  <si>
+    <t>PDS</t>
+  </si>
+  <si>
+    <t>EDU</t>
+  </si>
+  <si>
+    <t>SM</t>
+  </si>
+  <si>
+    <t>FRSH</t>
+  </si>
+  <si>
+    <t>CEIX</t>
+  </si>
+  <si>
+    <t>COUR</t>
+  </si>
+  <si>
+    <t>FSLY</t>
+  </si>
+  <si>
+    <t>CMT</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>WLDN</t>
+  </si>
+  <si>
+    <t>ODC</t>
+  </si>
+  <si>
+    <t>ERIE</t>
+  </si>
+  <si>
+    <t>VNO</t>
+  </si>
+  <si>
+    <t>FN</t>
+  </si>
+  <si>
+    <t>AEO</t>
+  </si>
+  <si>
+    <t>EH</t>
+  </si>
+  <si>
+    <t>FSTR</t>
+  </si>
+  <si>
+    <t>GAMB</t>
+  </si>
+  <si>
+    <t>POWL</t>
+  </si>
+  <si>
+    <t>MNSO</t>
+  </si>
+  <si>
+    <t>TPL</t>
+  </si>
+  <si>
+    <t>IESC</t>
+  </si>
+  <si>
+    <t>RELY</t>
+  </si>
+  <si>
+    <t>CORT</t>
+  </si>
+  <si>
+    <t>KRT</t>
+  </si>
+  <si>
+    <t>IONQ</t>
+  </si>
+  <si>
+    <t>PAY</t>
+  </si>
+  <si>
+    <t>LEU</t>
+  </si>
+  <si>
+    <t>ACMR</t>
+  </si>
+  <si>
+    <t>VRTV</t>
+  </si>
+  <si>
+    <t>ESTE</t>
+  </si>
+  <si>
+    <t>MMYT</t>
+  </si>
+  <si>
+    <t>BOOM</t>
+  </si>
+  <si>
+    <t>PARR</t>
+  </si>
+  <si>
+    <t>PETQ</t>
+  </si>
+  <si>
+    <t>CPRI</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>CTRN</t>
+  </si>
+  <si>
+    <t>ANF</t>
+  </si>
+  <si>
+    <t>DLO</t>
+  </si>
+  <si>
+    <t>MOD</t>
+  </si>
+  <si>
+    <t>XPEV</t>
+  </si>
+  <si>
+    <t>RYTM</t>
+  </si>
+  <si>
+    <t>CBAY</t>
+  </si>
+  <si>
+    <t>SBOW</t>
+  </si>
+  <si>
+    <t>SRDX</t>
+  </si>
+  <si>
+    <t>CAMT</t>
+  </si>
+  <si>
+    <t>STRL</t>
+  </si>
+  <si>
+    <t>CLS</t>
+  </si>
+  <si>
+    <t>BBIO</t>
+  </si>
+  <si>
+    <t>PHVS</t>
+  </si>
+  <si>
+    <t>LMB</t>
+  </si>
+  <si>
+    <t>VRT</t>
+  </si>
+  <si>
+    <t>APP</t>
   </si>
   <si>
     <t>ML</t>
   </si>
   <si>
-    <t>SNPS</t>
-  </si>
-  <si>
-    <t>ETD</t>
-  </si>
-  <si>
-    <t>DXPE</t>
-  </si>
-  <si>
-    <t>INFU</t>
-  </si>
-  <si>
-    <t>DDOG</t>
-  </si>
-  <si>
-    <t>BIGC</t>
-  </si>
-  <si>
-    <t>DOOR</t>
-  </si>
-  <si>
-    <t>XPEL</t>
-  </si>
-  <si>
-    <t>CMRE</t>
-  </si>
-  <si>
-    <t>MATW</t>
-  </si>
-  <si>
-    <t>URI</t>
-  </si>
-  <si>
-    <t>CPNG</t>
-  </si>
-  <si>
-    <t>MUSA</t>
-  </si>
-  <si>
-    <t>DKS</t>
-  </si>
-  <si>
-    <t>MDGL</t>
-  </si>
-  <si>
-    <t>RCLFU</t>
-  </si>
-  <si>
-    <t>MLM</t>
-  </si>
-  <si>
-    <t>THC</t>
-  </si>
-  <si>
-    <t>PGTI</t>
-  </si>
-  <si>
-    <t>TNC</t>
-  </si>
-  <si>
-    <t>TJX</t>
-  </si>
-  <si>
-    <t>LZB</t>
-  </si>
-  <si>
-    <t>INSM</t>
-  </si>
-  <si>
-    <t>WHD</t>
-  </si>
-  <si>
-    <t>IDCC</t>
-  </si>
-  <si>
-    <t>PATK</t>
-  </si>
-  <si>
-    <t>ON</t>
-  </si>
-  <si>
-    <t>GYRO</t>
-  </si>
-  <si>
-    <t>GMS</t>
-  </si>
-  <si>
-    <t>FLYW</t>
-  </si>
-  <si>
-    <t>CR</t>
-  </si>
-  <si>
-    <t>MUR</t>
-  </si>
-  <si>
-    <t>TCBX</t>
-  </si>
-  <si>
-    <t>PCYO</t>
-  </si>
-  <si>
-    <t>ICFI</t>
-  </si>
-  <si>
-    <t>TRU</t>
-  </si>
-  <si>
-    <t>ERII</t>
-  </si>
-  <si>
-    <t>NYT</t>
-  </si>
-  <si>
-    <t>DPZ</t>
-  </si>
-  <si>
-    <t>BLKB</t>
-  </si>
-  <si>
-    <t>JBI</t>
-  </si>
-  <si>
-    <t>ETNB</t>
-  </si>
-  <si>
-    <t>NOV</t>
-  </si>
-  <si>
-    <t>SFL</t>
-  </si>
-  <si>
-    <t>HMC</t>
-  </si>
-  <si>
-    <t>NATI</t>
-  </si>
-  <si>
-    <t>TPX</t>
-  </si>
-  <si>
-    <t>IMAX</t>
-  </si>
-  <si>
-    <t>FINW</t>
-  </si>
-  <si>
-    <t>GO</t>
-  </si>
-  <si>
-    <t>STER</t>
-  </si>
-  <si>
-    <t>AMEH</t>
-  </si>
-  <si>
-    <t>EHC</t>
-  </si>
-  <si>
-    <t>CDRE</t>
-  </si>
-  <si>
-    <t>DUOL</t>
-  </si>
-  <si>
-    <t>ENTG</t>
-  </si>
-  <si>
-    <t>TRIN</t>
-  </si>
-  <si>
-    <t>SLB</t>
-  </si>
-  <si>
-    <t>HQY</t>
-  </si>
-  <si>
-    <t>ARCE</t>
-  </si>
-  <si>
-    <t>KEX</t>
-  </si>
-  <si>
-    <t>PSX</t>
-  </si>
-  <si>
-    <t>KOP</t>
-  </si>
-  <si>
-    <t>RNGR</t>
-  </si>
-  <si>
-    <t>VRRM</t>
-  </si>
-  <si>
-    <t>CAL</t>
-  </si>
-  <si>
-    <t>OLED</t>
-  </si>
-  <si>
-    <t>LBRT</t>
-  </si>
-  <si>
-    <t>BELFB</t>
-  </si>
-  <si>
-    <t>HNI</t>
-  </si>
-  <si>
-    <t>SQSP</t>
-  </si>
-  <si>
-    <t>RYTM</t>
-  </si>
-  <si>
-    <t>TDG</t>
-  </si>
-  <si>
-    <t>KSS</t>
-  </si>
-  <si>
-    <t>BWMN</t>
-  </si>
-  <si>
-    <t>NOW</t>
-  </si>
-  <si>
-    <t>HAL</t>
-  </si>
-  <si>
-    <t>STN</t>
-  </si>
-  <si>
-    <t>HUBB</t>
-  </si>
-  <si>
-    <t>WDAY</t>
-  </si>
-  <si>
-    <t>MTH</t>
-  </si>
-  <si>
-    <t>NECB</t>
-  </si>
-  <si>
-    <t>DLX</t>
-  </si>
-  <si>
-    <t>TPL</t>
-  </si>
-  <si>
-    <t>DAC</t>
-  </si>
-  <si>
-    <t>AKAM</t>
-  </si>
-  <si>
-    <t>BVH</t>
-  </si>
-  <si>
-    <t>ATVI</t>
-  </si>
-  <si>
-    <t>ATRO</t>
-  </si>
-  <si>
-    <t>SGEN</t>
-  </si>
-  <si>
-    <t>SHAK</t>
-  </si>
-  <si>
-    <t>WLK</t>
-  </si>
-  <si>
-    <t>QTWO</t>
-  </si>
-  <si>
-    <t>ZEUS</t>
-  </si>
-  <si>
-    <t>AM</t>
-  </si>
-  <si>
-    <t>DIT</t>
-  </si>
-  <si>
-    <t>DLR</t>
-  </si>
-  <si>
-    <t>RACE</t>
-  </si>
-  <si>
-    <t>TTWO</t>
-  </si>
-  <si>
-    <t>BHWB</t>
-  </si>
-  <si>
-    <t>AIR</t>
-  </si>
-  <si>
-    <t>SUM</t>
-  </si>
-  <si>
-    <t>UFPI</t>
-  </si>
-  <si>
-    <t>AEIS</t>
-  </si>
-  <si>
-    <t>PBAM</t>
-  </si>
-  <si>
-    <t>LOGI</t>
-  </si>
-  <si>
-    <t>MTAL</t>
-  </si>
-  <si>
-    <t>FWRG</t>
-  </si>
-  <si>
-    <t>PTGX</t>
-  </si>
-  <si>
-    <t>PCAR</t>
-  </si>
-  <si>
-    <t>VNT</t>
-  </si>
-  <si>
-    <t>MTDR</t>
-  </si>
-  <si>
-    <t>PMGM</t>
-  </si>
-  <si>
-    <t>OSIS</t>
-  </si>
-  <si>
-    <t>STEP</t>
-  </si>
-  <si>
-    <t>REX</t>
-  </si>
-  <si>
-    <t>TRGP</t>
-  </si>
-  <si>
-    <t>GCBC</t>
-  </si>
-  <si>
-    <t>CPRT</t>
-  </si>
-  <si>
-    <t>MEDP</t>
-  </si>
-  <si>
-    <t>CRWD</t>
-  </si>
-  <si>
-    <t>CAT</t>
-  </si>
-  <si>
-    <t>HCI</t>
-  </si>
-  <si>
-    <t>CRM</t>
-  </si>
-  <si>
-    <t>BATRA</t>
-  </si>
-  <si>
-    <t>OSK</t>
-  </si>
-  <si>
-    <t>UNM</t>
-  </si>
-  <si>
-    <t>RCM</t>
-  </si>
-  <si>
-    <t>EXP</t>
-  </si>
-  <si>
-    <t>QCRH</t>
-  </si>
-  <si>
-    <t>LZRFY</t>
-  </si>
-  <si>
-    <t>J</t>
-  </si>
-  <si>
-    <t>MGPI</t>
-  </si>
-  <si>
-    <t>GH</t>
-  </si>
-  <si>
-    <t>VRNS</t>
-  </si>
-  <si>
-    <t>RPM</t>
-  </si>
-  <si>
-    <t>GRC</t>
-  </si>
-  <si>
-    <t>TGH</t>
-  </si>
-  <si>
-    <t>UBS</t>
-  </si>
-  <si>
-    <t>UFPT</t>
-  </si>
-  <si>
-    <t>TNP</t>
-  </si>
-  <si>
-    <t>GNTX</t>
-  </si>
-  <si>
-    <t>GRFS</t>
-  </si>
-  <si>
-    <t>MAR</t>
-  </si>
-  <si>
-    <t>TNK</t>
-  </si>
-  <si>
-    <t>PLAB</t>
-  </si>
-  <si>
-    <t>OPCH</t>
-  </si>
-  <si>
-    <t>HLF</t>
-  </si>
-  <si>
-    <t>BFAM</t>
-  </si>
-  <si>
-    <t>FRO</t>
-  </si>
-  <si>
-    <t>NTES</t>
-  </si>
-  <si>
-    <t>IBKR</t>
-  </si>
-  <si>
-    <t>INSW</t>
-  </si>
-  <si>
-    <t>ARNC</t>
-  </si>
-  <si>
-    <t>RKT</t>
-  </si>
-  <si>
-    <t>ROAD</t>
-  </si>
-  <si>
-    <t>APA</t>
-  </si>
-  <si>
-    <t>CSWC</t>
-  </si>
-  <si>
-    <t>OFG</t>
-  </si>
-  <si>
-    <t>TPH</t>
-  </si>
-  <si>
-    <t>GPI</t>
-  </si>
-  <si>
-    <t>AMD</t>
-  </si>
-  <si>
-    <t>JBL</t>
-  </si>
-  <si>
-    <t>GOLF</t>
-  </si>
-  <si>
-    <t>ENVX</t>
-  </si>
-  <si>
-    <t>TMST</t>
-  </si>
-  <si>
-    <t>ACT</t>
-  </si>
-  <si>
-    <t>GXO</t>
-  </si>
-  <si>
-    <t>FTDR</t>
-  </si>
-  <si>
-    <t>SPB</t>
-  </si>
-  <si>
-    <t>SKT</t>
-  </si>
-  <si>
-    <t>DBRG</t>
-  </si>
-  <si>
-    <t>QLYS</t>
-  </si>
-  <si>
-    <t>ALGN</t>
-  </si>
-  <si>
-    <t>SRV</t>
-  </si>
-  <si>
-    <t>AZTA</t>
-  </si>
-  <si>
-    <t>PLUS</t>
-  </si>
-  <si>
-    <t>NHC</t>
-  </si>
-  <si>
-    <t>TMHC</t>
-  </si>
-  <si>
-    <t>ERO</t>
-  </si>
-  <si>
-    <t>FMS</t>
-  </si>
-  <si>
-    <t>KD</t>
-  </si>
-  <si>
-    <t>BKR</t>
-  </si>
-  <si>
-    <t>PH</t>
-  </si>
-  <si>
-    <t>RS</t>
-  </si>
-  <si>
-    <t>ARES</t>
-  </si>
-  <si>
-    <t>BRO</t>
-  </si>
-  <si>
-    <t>TARO</t>
-  </si>
-  <si>
-    <t>SWBI</t>
-  </si>
-  <si>
-    <t>SHEN</t>
-  </si>
-  <si>
-    <t>RDN</t>
-  </si>
-  <si>
-    <t>PWP</t>
-  </si>
-  <si>
-    <t>TRNS</t>
-  </si>
-  <si>
-    <t>VRSK</t>
-  </si>
-  <si>
-    <t>NSIT</t>
-  </si>
-  <si>
-    <t>DCBO</t>
-  </si>
-  <si>
-    <t>STRT</t>
-  </si>
-  <si>
-    <t>SMHI</t>
-  </si>
-  <si>
-    <t>APO</t>
-  </si>
-  <si>
-    <t>UBP</t>
-  </si>
-  <si>
-    <t>CARR</t>
-  </si>
-  <si>
-    <t>TFII</t>
-  </si>
-  <si>
-    <t>KNSL</t>
-  </si>
-  <si>
-    <t>PRI</t>
-  </si>
-  <si>
-    <t>CNXN</t>
-  </si>
-  <si>
-    <t>MDC</t>
-  </si>
-  <si>
-    <t>ATI</t>
-  </si>
-  <si>
-    <t>LZ</t>
-  </si>
-  <si>
-    <t>RILY</t>
-  </si>
-  <si>
-    <t>HTGC</t>
-  </si>
-  <si>
-    <t>BECN</t>
-  </si>
-  <si>
-    <t>WINA</t>
-  </si>
-  <si>
-    <t>KLAC</t>
-  </si>
-  <si>
-    <t>VAL</t>
-  </si>
-  <si>
-    <t>CRH</t>
-  </si>
-  <si>
-    <t>NTRA</t>
-  </si>
-  <si>
-    <t>OVV</t>
-  </si>
-  <si>
-    <t>ESNT</t>
-  </si>
-  <si>
-    <t>CSTM</t>
-  </si>
-  <si>
-    <t>XM</t>
-  </si>
-  <si>
-    <t>FLT</t>
-  </si>
-  <si>
-    <t>CW</t>
-  </si>
-  <si>
-    <t>AXR</t>
-  </si>
-  <si>
-    <t>CHTR</t>
-  </si>
-  <si>
-    <t>ORCL</t>
-  </si>
-  <si>
-    <t>PSTG</t>
-  </si>
-  <si>
-    <t>IMVT</t>
-  </si>
-  <si>
-    <t>CMCSA</t>
-  </si>
-  <si>
-    <t>AN</t>
-  </si>
-  <si>
-    <t>NVT</t>
-  </si>
-  <si>
-    <t>PAGP</t>
-  </si>
-  <si>
-    <t>VVI</t>
-  </si>
-  <si>
-    <t>GLRE</t>
-  </si>
-  <si>
-    <t>DASH</t>
-  </si>
-  <si>
-    <t>EXEL</t>
-  </si>
-  <si>
-    <t>GPN</t>
-  </si>
-  <si>
-    <t>DVA</t>
-  </si>
-  <si>
-    <t>MTG</t>
-  </si>
-  <si>
-    <t>YETI</t>
-  </si>
-  <si>
-    <t>OBT</t>
-  </si>
-  <si>
-    <t>MAT</t>
-  </si>
-  <si>
-    <t>PAR</t>
-  </si>
-  <si>
-    <t>BG</t>
-  </si>
-  <si>
-    <t>PAG</t>
-  </si>
-  <si>
-    <t>CPRI</t>
-  </si>
-  <si>
-    <t>AMWD</t>
-  </si>
-  <si>
-    <t>SFM</t>
-  </si>
-  <si>
-    <t>KBH</t>
-  </si>
-  <si>
-    <t>MVBF</t>
-  </si>
-  <si>
-    <t>WDFC</t>
-  </si>
-  <si>
-    <t>CCF</t>
-  </si>
-  <si>
-    <t>GOGN</t>
-  </si>
-  <si>
-    <t>FICO</t>
-  </si>
-  <si>
-    <t>AZZ</t>
-  </si>
-  <si>
-    <t>GIII</t>
-  </si>
-  <si>
-    <t>BR</t>
-  </si>
-  <si>
-    <t>VNO</t>
-  </si>
-  <si>
-    <t>ACEL</t>
-  </si>
-  <si>
-    <t>ONON</t>
-  </si>
-  <si>
-    <t>RRC</t>
-  </si>
-  <si>
-    <t>MMP</t>
-  </si>
-  <si>
-    <t>AMR</t>
-  </si>
-  <si>
-    <t>HOFT</t>
-  </si>
-  <si>
-    <t>NUVL</t>
-  </si>
-  <si>
-    <t>BRZE</t>
-  </si>
-  <si>
-    <t>SGH</t>
-  </si>
-  <si>
-    <t>LAD</t>
-  </si>
-  <si>
-    <t>SHC</t>
-  </si>
-  <si>
-    <t>TOL</t>
-  </si>
-  <si>
-    <t>MANH</t>
-  </si>
-  <si>
-    <t>CVI</t>
-  </si>
-  <si>
-    <t>LEGN</t>
-  </si>
-  <si>
-    <t>VERX</t>
-  </si>
-  <si>
-    <t>CXM</t>
-  </si>
-  <si>
-    <t>PAA</t>
-  </si>
-  <si>
-    <t>MPX</t>
-  </si>
-  <si>
-    <t>ZWS</t>
-  </si>
-  <si>
-    <t>PSN</t>
-  </si>
-  <si>
-    <t>KNSA</t>
-  </si>
-  <si>
-    <t>WWD</t>
-  </si>
-  <si>
-    <t>ACA</t>
-  </si>
-  <si>
-    <t>TW</t>
-  </si>
-  <si>
-    <t>CRS</t>
-  </si>
-  <si>
-    <t>OSTK</t>
-  </si>
-  <si>
-    <t>ASTE</t>
-  </si>
-  <si>
-    <t>PDCO</t>
-  </si>
-  <si>
-    <t>PUMP</t>
-  </si>
-  <si>
-    <t>HLNE</t>
-  </si>
-  <si>
-    <t>TTD</t>
-  </si>
-  <si>
-    <t>THO</t>
-  </si>
-  <si>
-    <t>CSPI</t>
-  </si>
-  <si>
-    <t>GSHD</t>
-  </si>
-  <si>
-    <t>USLM</t>
-  </si>
-  <si>
-    <t>EVI</t>
-  </si>
-  <si>
-    <t>RVMD</t>
-  </si>
-  <si>
-    <t>GOOG</t>
-  </si>
-  <si>
-    <t>PBF</t>
-  </si>
-  <si>
-    <t>GOOGL</t>
-  </si>
-  <si>
-    <t>AEO</t>
-  </si>
-  <si>
-    <t>OII</t>
-  </si>
-  <si>
-    <t>ACMR</t>
-  </si>
-  <si>
-    <t>GGAL</t>
-  </si>
-  <si>
-    <t>ESCA</t>
-  </si>
-  <si>
-    <t>NMIH</t>
-  </si>
-  <si>
-    <t>OTTR</t>
-  </si>
-  <si>
-    <t>NCR</t>
-  </si>
-  <si>
-    <t>RDNT</t>
-  </si>
-  <si>
-    <t>HEP</t>
-  </si>
-  <si>
-    <t>CRVL</t>
-  </si>
-  <si>
-    <t>MRVL</t>
-  </si>
-  <si>
-    <t>PNR</t>
-  </si>
-  <si>
-    <t>ERIE</t>
-  </si>
-  <si>
-    <t>MSTR</t>
-  </si>
-  <si>
-    <t>MSA</t>
-  </si>
-  <si>
-    <t>COKE</t>
-  </si>
-  <si>
-    <t>SPOK</t>
-  </si>
-  <si>
-    <t>PWR</t>
-  </si>
-  <si>
-    <t>GTLS</t>
-  </si>
-  <si>
-    <t>BCSF</t>
-  </si>
-  <si>
-    <t>PDS</t>
-  </si>
-  <si>
-    <t>FDX</t>
-  </si>
-  <si>
-    <t>SDGR</t>
-  </si>
-  <si>
-    <t>NEOG</t>
-  </si>
-  <si>
-    <t>GBLI</t>
-  </si>
-  <si>
-    <t>CRMT</t>
-  </si>
-  <si>
-    <t>GLBE</t>
-  </si>
-  <si>
-    <t>MPC</t>
-  </si>
-  <si>
-    <t>WOR</t>
-  </si>
-  <si>
-    <t>URBN</t>
-  </si>
-  <si>
-    <t>EXAS</t>
-  </si>
-  <si>
-    <t>CHX</t>
-  </si>
-  <si>
-    <t>MLR</t>
-  </si>
-  <si>
-    <t>AMAT</t>
-  </si>
-  <si>
-    <t>NEX</t>
-  </si>
-  <si>
-    <t>NVO</t>
-  </si>
-  <si>
-    <t>FMX</t>
-  </si>
-  <si>
-    <t>CLH</t>
-  </si>
-  <si>
-    <t>STRS</t>
-  </si>
-  <si>
-    <t>ETN</t>
-  </si>
-  <si>
-    <t>PANW</t>
-  </si>
-  <si>
-    <t>DELL</t>
-  </si>
-  <si>
-    <t>NEWR</t>
-  </si>
-  <si>
-    <t>BUR</t>
-  </si>
-  <si>
-    <t>PRDO</t>
-  </si>
-  <si>
-    <t>LOB</t>
-  </si>
-  <si>
-    <t>SOI</t>
-  </si>
-  <si>
-    <t>ARCB</t>
-  </si>
-  <si>
-    <t>NVMI</t>
-  </si>
-  <si>
-    <t>GIC</t>
-  </si>
-  <si>
-    <t>ODFL</t>
-  </si>
-  <si>
-    <t>RH</t>
-  </si>
-  <si>
-    <t>NOG</t>
-  </si>
-  <si>
-    <t>APG</t>
-  </si>
-  <si>
-    <t>CNK</t>
-  </si>
-  <si>
-    <t>CIVI</t>
-  </si>
-  <si>
-    <t>HURN</t>
-  </si>
-  <si>
-    <t>BMI</t>
-  </si>
-  <si>
-    <t>NYCB</t>
-  </si>
-  <si>
-    <t>JHX</t>
-  </si>
-  <si>
-    <t>ADDYY</t>
-  </si>
-  <si>
-    <t>IRMD</t>
-  </si>
-  <si>
-    <t>LTRPB</t>
-  </si>
-  <si>
-    <t>GRVY</t>
-  </si>
-  <si>
-    <t>TREX</t>
-  </si>
-  <si>
-    <t>MYRG</t>
-  </si>
-  <si>
-    <t>BRBR</t>
-  </si>
-  <si>
-    <t>RDY</t>
-  </si>
-  <si>
-    <t>ABR</t>
-  </si>
-  <si>
-    <t>BKNG</t>
-  </si>
-  <si>
-    <t>VST</t>
-  </si>
-  <si>
-    <t>HNRG</t>
-  </si>
-  <si>
-    <t>ACU</t>
-  </si>
-  <si>
-    <t>DECK</t>
-  </si>
-  <si>
-    <t>HUBS</t>
-  </si>
-  <si>
-    <t>DVAX</t>
-  </si>
-  <si>
-    <t>WWE</t>
-  </si>
-  <si>
-    <t>ALSN</t>
-  </si>
-  <si>
-    <t>HAYW</t>
-  </si>
-  <si>
-    <t>BOOT</t>
-  </si>
-  <si>
-    <t>ACVA</t>
-  </si>
-  <si>
-    <t>RAMP</t>
-  </si>
-  <si>
-    <t>AZEK</t>
-  </si>
-  <si>
-    <t>COOP</t>
-  </si>
-  <si>
-    <t>RIVN</t>
-  </si>
-  <si>
-    <t>WST</t>
-  </si>
-  <si>
-    <t>ANET</t>
-  </si>
-  <si>
-    <t>LII</t>
-  </si>
-  <si>
-    <t>LRCX</t>
-  </si>
-  <si>
-    <t>EQT</t>
-  </si>
-  <si>
-    <t>VEL</t>
-  </si>
-  <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>FRPT</t>
-  </si>
-  <si>
-    <t>BKI</t>
-  </si>
-  <si>
-    <t>PAM</t>
-  </si>
-  <si>
-    <t>AMZN</t>
-  </si>
-  <si>
-    <t>YPF</t>
-  </si>
-  <si>
-    <t>HELE</t>
-  </si>
-  <si>
-    <t>TNET</t>
-  </si>
-  <si>
-    <t>PRO</t>
-  </si>
-  <si>
-    <t>IBP</t>
-  </si>
-  <si>
-    <t>TYRA</t>
-  </si>
-  <si>
-    <t>CYD</t>
-  </si>
-  <si>
-    <t>IGIC</t>
-  </si>
-  <si>
-    <t>LEU</t>
-  </si>
-  <si>
-    <t>OC</t>
-  </si>
-  <si>
-    <t>VMW</t>
-  </si>
-  <si>
-    <t>ZGN</t>
-  </si>
-  <si>
-    <t>LYTS</t>
-  </si>
-  <si>
-    <t>KRUS</t>
-  </si>
-  <si>
-    <t>CNM</t>
-  </si>
-  <si>
-    <t>ANDE</t>
-  </si>
-  <si>
-    <t>TAYD</t>
-  </si>
-  <si>
-    <t>ROIV</t>
-  </si>
-  <si>
-    <t>PHG</t>
-  </si>
-  <si>
-    <t>EXPI</t>
-  </si>
-  <si>
-    <t>EB</t>
-  </si>
-  <si>
-    <t>FCAP</t>
-  </si>
-  <si>
-    <t>PKOH</t>
-  </si>
-  <si>
-    <t>BLBD</t>
-  </si>
-  <si>
-    <t>COUR</t>
-  </si>
-  <si>
-    <t>BLX</t>
-  </si>
-  <si>
-    <t>AMNB</t>
-  </si>
-  <si>
-    <t>AGM</t>
-  </si>
-  <si>
-    <t>YELP</t>
-  </si>
-  <si>
-    <t>AEHR</t>
-  </si>
-  <si>
-    <t>ITRN</t>
-  </si>
-  <si>
-    <t>HCCI</t>
-  </si>
-  <si>
-    <t>ESEA</t>
-  </si>
-  <si>
-    <t>ADDDF</t>
-  </si>
-  <si>
-    <t>FRHC</t>
-  </si>
-  <si>
-    <t>KTOS</t>
-  </si>
-  <si>
-    <t>SXI</t>
-  </si>
-  <si>
-    <t>GE</t>
-  </si>
-  <si>
-    <t>AGRO</t>
-  </si>
-  <si>
-    <t>ROKU</t>
-  </si>
-  <si>
-    <t>LAUR</t>
-  </si>
-  <si>
-    <t>NGVC</t>
-  </si>
-  <si>
-    <t>AEL</t>
-  </si>
-  <si>
-    <t>AVGO</t>
-  </si>
-  <si>
-    <t>NEU</t>
-  </si>
-  <si>
-    <t>STVN</t>
-  </si>
-  <si>
-    <t>OLLI</t>
-  </si>
-  <si>
-    <t>ASMIY</t>
-  </si>
-  <si>
-    <t>MORF</t>
-  </si>
-  <si>
-    <t>CSWI</t>
-  </si>
-  <si>
-    <t>VICR</t>
-  </si>
-  <si>
-    <t>PHM</t>
-  </si>
-  <si>
-    <t>BLU</t>
-  </si>
-  <si>
-    <t>GRBK</t>
-  </si>
-  <si>
-    <t>ADBE</t>
-  </si>
-  <si>
-    <t>WMS</t>
-  </si>
-  <si>
-    <t>ONTO</t>
-  </si>
-  <si>
-    <t>TWIN</t>
-  </si>
-  <si>
-    <t>SPNS</t>
-  </si>
-  <si>
-    <t>ABCM</t>
-  </si>
-  <si>
-    <t>UBER</t>
-  </si>
-  <si>
-    <t>ETHE</t>
-  </si>
-  <si>
-    <t>FIX</t>
-  </si>
-  <si>
-    <t>CVRX</t>
-  </si>
-  <si>
-    <t>AVDL</t>
-  </si>
-  <si>
-    <t>LQDT</t>
-  </si>
-  <si>
-    <t>SCPL</t>
-  </si>
-  <si>
-    <t>SCU</t>
-  </si>
-  <si>
-    <t>SPNT</t>
-  </si>
-  <si>
-    <t>MATX</t>
-  </si>
-  <si>
-    <t>HWKN</t>
-  </si>
-  <si>
-    <t>CCJ</t>
-  </si>
-  <si>
-    <t>ARGX</t>
-  </si>
-  <si>
-    <t>HOV</t>
-  </si>
-  <si>
-    <t>CEIX</t>
-  </si>
-  <si>
-    <t>VIST</t>
-  </si>
-  <si>
-    <t>FEDU</t>
-  </si>
-  <si>
-    <t>NE</t>
-  </si>
-  <si>
-    <t>IMTX</t>
-  </si>
-  <si>
-    <t>RCMT</t>
-  </si>
-  <si>
-    <t>CRC</t>
-  </si>
-  <si>
-    <t>XPRO</t>
-  </si>
-  <si>
-    <t>VRTV</t>
-  </si>
-  <si>
-    <t>FRSH</t>
-  </si>
-  <si>
-    <t>GHL</t>
-  </si>
-  <si>
-    <t>ROCK</t>
-  </si>
-  <si>
-    <t>SSD</t>
-  </si>
-  <si>
-    <t>DICE</t>
-  </si>
-  <si>
-    <t>VECO</t>
-  </si>
-  <si>
-    <t>FLXS</t>
-  </si>
-  <si>
-    <t>AI</t>
-  </si>
-  <si>
-    <t>EXTR</t>
-  </si>
-  <si>
-    <t>FTI</t>
-  </si>
-  <si>
-    <t>ACOR</t>
-  </si>
-  <si>
-    <t>BOOM</t>
-  </si>
-  <si>
-    <t>CCL</t>
-  </si>
-  <si>
-    <t>CIX</t>
-  </si>
-  <si>
-    <t>CUBI</t>
-  </si>
-  <si>
-    <t>AMPH</t>
-  </si>
-  <si>
-    <t>APPF</t>
-  </si>
-  <si>
-    <t>CUK</t>
-  </si>
-  <si>
-    <t>RCL</t>
-  </si>
-  <si>
-    <t>SRDX</t>
-  </si>
-  <si>
-    <t>GBX</t>
-  </si>
-  <si>
-    <t>PRIM</t>
+    <t>RETA</t>
   </si>
   <si>
     <t>UPWK</t>
   </si>
   <si>
-    <t>GBTC</t>
-  </si>
-  <si>
-    <t>CNX</t>
-  </si>
-  <si>
-    <t>WLDN</t>
-  </si>
-  <si>
-    <t>AROC</t>
-  </si>
-  <si>
-    <t>ACLS</t>
-  </si>
-  <si>
-    <t>SM</t>
-  </si>
-  <si>
-    <t>EME</t>
-  </si>
-  <si>
-    <t>MNSO</t>
-  </si>
-  <si>
-    <t>BLD</t>
-  </si>
-  <si>
-    <t>NRP</t>
-  </si>
-  <si>
-    <t>PLPC</t>
-  </si>
-  <si>
-    <t>GKOS</t>
-  </si>
-  <si>
-    <t>FSLY</t>
-  </si>
-  <si>
-    <t>MDB</t>
-  </si>
-  <si>
-    <t>EDN</t>
-  </si>
-  <si>
-    <t>KRYS</t>
-  </si>
-  <si>
-    <t>GPOR</t>
-  </si>
-  <si>
-    <t>KALA</t>
-  </si>
-  <si>
-    <t>ARCT</t>
-  </si>
-  <si>
-    <t>JOE</t>
-  </si>
-  <si>
-    <t>ANIP</t>
-  </si>
-  <si>
-    <t>PRG</t>
-  </si>
-  <si>
-    <t>MARA</t>
-  </si>
-  <si>
-    <t>FRD</t>
-  </si>
-  <si>
-    <t>CLBR</t>
-  </si>
-  <si>
-    <t>ESTE</t>
-  </si>
-  <si>
-    <t>DLO</t>
-  </si>
-  <si>
-    <t>MMYT</t>
-  </si>
-  <si>
-    <t>CWCO</t>
-  </si>
-  <si>
-    <t>COIN</t>
-  </si>
-  <si>
-    <t>MRAM</t>
-  </si>
-  <si>
-    <t>FTAI</t>
-  </si>
-  <si>
-    <t>RCEL</t>
-  </si>
-  <si>
-    <t>WRLD</t>
-  </si>
-  <si>
-    <t>PLTR</t>
-  </si>
-  <si>
-    <t>EDU</t>
-  </si>
-  <si>
-    <t>KALV</t>
-  </si>
-  <si>
-    <t>COCO</t>
-  </si>
-  <si>
-    <t>PAY</t>
-  </si>
-  <si>
-    <t>SOVO</t>
-  </si>
-  <si>
-    <t>CORT</t>
-  </si>
-  <si>
-    <t>LLY</t>
-  </si>
-  <si>
-    <t>BLDR</t>
-  </si>
-  <si>
-    <t>MLP</t>
-  </si>
-  <si>
-    <t>IDYA</t>
-  </si>
-  <si>
-    <t>NOA</t>
-  </si>
-  <si>
-    <t>DMRC</t>
-  </si>
-  <si>
-    <t>CAAP</t>
-  </si>
-  <si>
-    <t>BCC</t>
-  </si>
-  <si>
-    <t>PHAT</t>
-  </si>
-  <si>
-    <t>ANF</t>
-  </si>
-  <si>
-    <t>ISEE</t>
-  </si>
-  <si>
-    <t>SWDAF</t>
-  </si>
-  <si>
-    <t>DKNG</t>
-  </si>
-  <si>
-    <t>RIOT</t>
-  </si>
-  <si>
-    <t>PCTTU</t>
-  </si>
-  <si>
-    <t>FCNCA</t>
-  </si>
-  <si>
-    <t>SG</t>
-  </si>
-  <si>
-    <t>GAMB</t>
-  </si>
-  <si>
-    <t>BWMX</t>
-  </si>
-  <si>
-    <t>TDW</t>
-  </si>
-  <si>
-    <t>VKTX</t>
-  </si>
-  <si>
-    <t>XP</t>
-  </si>
-  <si>
-    <t>ELF</t>
-  </si>
-  <si>
-    <t>PARR</t>
-  </si>
-  <si>
-    <t>KDNY</t>
-  </si>
-  <si>
-    <t>SAIA</t>
-  </si>
-  <si>
-    <t>NWLI</t>
-  </si>
-  <si>
-    <t>WFRD</t>
-  </si>
-  <si>
-    <t>OPRA</t>
-  </si>
-  <si>
-    <t>LI</t>
-  </si>
-  <si>
-    <t>MHO</t>
-  </si>
-  <si>
-    <t>EH</t>
-  </si>
-  <si>
-    <t>LSEA</t>
-  </si>
-  <si>
-    <t>USAP</t>
-  </si>
-  <si>
-    <t>W</t>
-  </si>
-  <si>
-    <t>ACAD</t>
-  </si>
-  <si>
-    <t>MDWT</t>
-  </si>
-  <si>
-    <t>QTRX</t>
-  </si>
-  <si>
-    <t>NGMS</t>
-  </si>
-  <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>CLS</t>
-  </si>
-  <si>
-    <t>CMPR</t>
-  </si>
-  <si>
-    <t>XPEV</t>
-  </si>
-  <si>
-    <t>ODC</t>
-  </si>
-  <si>
-    <t>NATR</t>
-  </si>
-  <si>
-    <t>CABA</t>
-  </si>
-  <si>
-    <t>ALPN</t>
-  </si>
-  <si>
-    <t>CELH</t>
-  </si>
-  <si>
-    <t>SKYW</t>
-  </si>
-  <si>
-    <t>VSTM</t>
-  </si>
-  <si>
-    <t>SBOW</t>
-  </si>
-  <si>
-    <t>BZH</t>
-  </si>
-  <si>
-    <t>KRT</t>
-  </si>
-  <si>
-    <t>UPST</t>
-  </si>
-  <si>
-    <t>VECT</t>
-  </si>
-  <si>
-    <t>PETQ</t>
-  </si>
-  <si>
-    <t>IESC</t>
-  </si>
-  <si>
-    <t>RELY</t>
-  </si>
-  <si>
-    <t>FOR</t>
-  </si>
-  <si>
-    <t>POWL</t>
-  </si>
-  <si>
-    <t>FSTR</t>
-  </si>
-  <si>
-    <t>RXST</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>NVDA</t>
-  </si>
-  <si>
-    <t>XPO</t>
-  </si>
-  <si>
-    <t>CMT</t>
-  </si>
-  <si>
-    <t>MOD</t>
-  </si>
-  <si>
-    <t>CBAY</t>
-  </si>
-  <si>
-    <t>TRHC</t>
-  </si>
-  <si>
-    <t>DFH</t>
-  </si>
-  <si>
-    <t>WEAV</t>
-  </si>
-  <si>
-    <t>CAMT</t>
-  </si>
-  <si>
-    <t>WW</t>
-  </si>
-  <si>
-    <t>MEOA</t>
-  </si>
-  <si>
-    <t>STRL</t>
+    <t>CVNA</t>
+  </si>
+  <si>
+    <t>URGN</t>
+  </si>
+  <si>
+    <t>CDLX</t>
   </si>
   <si>
     <t>TDS</t>
   </si>
   <si>
-    <t>SMCI</t>
-  </si>
-  <si>
-    <t>CDLX</t>
-  </si>
-  <si>
-    <t>URGN</t>
-  </si>
-  <si>
-    <t>GRPN</t>
-  </si>
-  <si>
-    <t>PHVS</t>
-  </si>
-  <si>
     <t>USM</t>
   </si>
   <si>
-    <t>VRT</t>
-  </si>
-  <si>
-    <t>LMB</t>
-  </si>
-  <si>
-    <t>AURC</t>
-  </si>
-  <si>
-    <t>BBIO</t>
-  </si>
-  <si>
-    <t>MEOAU</t>
-  </si>
-  <si>
-    <t>INOD</t>
-  </si>
-  <si>
     <t>TSAT</t>
   </si>
   <si>
-    <t>AURCU</t>
-  </si>
-  <si>
-    <t>IONQ</t>
-  </si>
-  <si>
-    <t>APP</t>
-  </si>
-  <si>
-    <t>IMGN</t>
-  </si>
-  <si>
-    <t>RETA</t>
-  </si>
-  <si>
-    <t>EYPT</t>
+    <t>EDTXU</t>
+  </si>
+  <si>
+    <t>EDTX</t>
   </si>
   <si>
     <t>SGTX</t>
-  </si>
-  <si>
-    <t>CVNA</t>
-  </si>
-  <si>
-    <t>EDTXU</t>
-  </si>
-  <si>
-    <t>EDTX</t>
   </si>
   <si>
     <t>AAOI</t>
@@ -2461,7 +2116,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B698"/>
+  <dimension ref="A1:B583"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -2477,7 +2132,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1">
-        <v>110.8647912736285</v>
+        <v>108.6541878233259</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2485,7 +2140,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1">
-        <v>110.8901917715365</v>
+        <v>108.664767588674</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -2493,7 +2148,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1">
-        <v>110.8922377971169</v>
+        <v>108.6868041007391</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -2501,7 +2156,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="1">
-        <v>110.9118329544624</v>
+        <v>108.6945180944333</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -2509,7 +2164,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="1">
-        <v>110.9125038170068</v>
+        <v>108.726678229737</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -2517,7 +2172,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="1">
-        <v>110.9229990682797</v>
+        <v>108.7503505518207</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -2525,7 +2180,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="1">
-        <v>110.930744438892</v>
+        <v>108.7606066510682</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -2533,7 +2188,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="1">
-        <v>110.9546202374334</v>
+        <v>108.7671326109623</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -2541,7 +2196,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="1">
-        <v>110.971568548441</v>
+        <v>108.7756675799262</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -2549,7 +2204,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="1">
-        <v>110.9837017901691</v>
+        <v>108.7795913724433</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -2557,7 +2212,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="1">
-        <v>111.0056721204515</v>
+        <v>108.7813951800798</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -2565,7 +2220,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="1">
-        <v>111.0489830958142</v>
+        <v>108.8121919101746</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -2573,7 +2228,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="1">
-        <v>111.0697613542611</v>
+        <v>108.813754923784</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -2581,7 +2236,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="1">
-        <v>111.0730399792104</v>
+        <v>108.8433576971025</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -2589,7 +2244,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="1">
-        <v>111.1300263116886</v>
+        <v>108.8611846989841</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -2597,7 +2252,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="1">
-        <v>111.1371530379617</v>
+        <v>108.8964157710821</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -2605,7 +2260,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="1">
-        <v>111.1377506473336</v>
+        <v>108.9034874594899</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -2613,7 +2268,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="1">
-        <v>111.1634860821335</v>
+        <v>108.9059507828491</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -2621,7 +2276,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="1">
-        <v>111.1719650950922</v>
+        <v>108.9072120510168</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -2629,7 +2284,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="1">
-        <v>111.1731255767884</v>
+        <v>108.9158486310906</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -2637,7 +2292,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="1">
-        <v>111.1857740297151</v>
+        <v>108.9195377743651</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -2645,7 +2300,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="1">
-        <v>111.2055385825037</v>
+        <v>108.9200837240218</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -2653,7 +2308,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="1">
-        <v>111.2159990526238</v>
+        <v>108.9429593599016</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -2661,7 +2316,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="1">
-        <v>111.2235887094137</v>
+        <v>108.9672061586851</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -2669,7 +2324,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="1">
-        <v>111.2351062958504</v>
+        <v>108.9893510264152</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -2677,7 +2332,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="1">
-        <v>111.2474165457382</v>
+        <v>108.9969136743706</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -2685,7 +2340,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="1">
-        <v>111.2525676187947</v>
+        <v>109.0036834597021</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -2693,7 +2348,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="1">
-        <v>111.3489964150798</v>
+        <v>109.0337869704832</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -2701,7 +2356,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="1">
-        <v>111.3855282747894</v>
+        <v>109.0354976155129</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -2709,7 +2364,7 @@
         <v>31</v>
       </c>
       <c r="B31" s="1">
-        <v>111.3877721444288</v>
+        <v>109.0387751151719</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -2717,7 +2372,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="1">
-        <v>111.4311062305727</v>
+        <v>109.0406669765156</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -2725,7 +2380,7 @@
         <v>33</v>
       </c>
       <c r="B33" s="1">
-        <v>111.4754677632055</v>
+        <v>109.0591176349555</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -2733,7 +2388,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="1">
-        <v>111.515843541231</v>
+        <v>109.0871581650757</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -2741,7 +2396,7 @@
         <v>35</v>
       </c>
       <c r="B35" s="1">
-        <v>111.5171277515678</v>
+        <v>109.1308276812391</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -2749,7 +2404,7 @@
         <v>36</v>
       </c>
       <c r="B36" s="1">
-        <v>111.540340632579</v>
+        <v>109.1541448199019</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -2757,7 +2412,7 @@
         <v>37</v>
       </c>
       <c r="B37" s="1">
-        <v>111.5610450843848</v>
+        <v>109.1951223584257</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -2765,7 +2420,7 @@
         <v>38</v>
       </c>
       <c r="B38" s="1">
-        <v>111.5848936020303</v>
+        <v>109.2139498499748</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -2773,7 +2428,7 @@
         <v>39</v>
       </c>
       <c r="B39" s="1">
-        <v>111.63384268333</v>
+        <v>109.2226617368752</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -2781,7 +2436,7 @@
         <v>40</v>
       </c>
       <c r="B40" s="1">
-        <v>111.6694913251985</v>
+        <v>109.2529216372053</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2789,7 +2444,7 @@
         <v>41</v>
       </c>
       <c r="B41" s="1">
-        <v>111.6855897241987</v>
+        <v>109.2537433142523</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2797,7 +2452,7 @@
         <v>42</v>
       </c>
       <c r="B42" s="1">
-        <v>111.6862636299955</v>
+        <v>109.2852718161785</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2805,7 +2460,7 @@
         <v>43</v>
       </c>
       <c r="B43" s="1">
-        <v>111.7431412390116</v>
+        <v>109.3033831865531</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2813,7 +2468,7 @@
         <v>44</v>
       </c>
       <c r="B44" s="1">
-        <v>111.7488768018433</v>
+        <v>109.3191734953404</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2821,7 +2476,7 @@
         <v>45</v>
       </c>
       <c r="B45" s="1">
-        <v>111.8350881990507</v>
+        <v>109.3204910636044</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2829,7 +2484,7 @@
         <v>46</v>
       </c>
       <c r="B46" s="1">
-        <v>111.859244573806</v>
+        <v>109.3234688964561</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2837,7 +2492,7 @@
         <v>47</v>
       </c>
       <c r="B47" s="1">
-        <v>111.8795217089708</v>
+        <v>109.3359959115181</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2845,7 +2500,7 @@
         <v>48</v>
       </c>
       <c r="B48" s="1">
-        <v>111.9146296290772</v>
+        <v>109.3632982346311</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -2853,7 +2508,7 @@
         <v>49</v>
       </c>
       <c r="B49" s="1">
-        <v>111.9376289062551</v>
+        <v>109.3858801531355</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -2861,7 +2516,7 @@
         <v>50</v>
       </c>
       <c r="B50" s="1">
-        <v>111.95021984191</v>
+        <v>109.3911761986673</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -2869,7 +2524,7 @@
         <v>51</v>
       </c>
       <c r="B51" s="1">
-        <v>111.954652340026</v>
+        <v>109.3963997415775</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -2877,7 +2532,7 @@
         <v>52</v>
       </c>
       <c r="B52" s="1">
-        <v>111.9553798328644</v>
+        <v>109.4045928182428</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -2885,7 +2540,7 @@
         <v>53</v>
       </c>
       <c r="B53" s="1">
-        <v>112.0339452229842</v>
+        <v>109.4112288002551</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -2893,7 +2548,7 @@
         <v>54</v>
       </c>
       <c r="B54" s="1">
-        <v>112.0386091089752</v>
+        <v>109.4480760081051</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -2901,7 +2556,7 @@
         <v>55</v>
       </c>
       <c r="B55" s="1">
-        <v>112.0641895911811</v>
+        <v>109.4518397838625</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -2909,7 +2564,7 @@
         <v>56</v>
       </c>
       <c r="B56" s="1">
-        <v>112.0649336025015</v>
+        <v>109.4801060784987</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -2917,7 +2572,7 @@
         <v>57</v>
       </c>
       <c r="B57" s="1">
-        <v>112.0721255542242</v>
+        <v>109.4935347518899</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -2925,7 +2580,7 @@
         <v>58</v>
       </c>
       <c r="B58" s="1">
-        <v>112.1001914626676</v>
+        <v>109.5080104967122</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -2933,7 +2588,7 @@
         <v>59</v>
       </c>
       <c r="B59" s="1">
-        <v>112.1059004712754</v>
+        <v>109.5096027024098</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -2941,7 +2596,7 @@
         <v>60</v>
       </c>
       <c r="B60" s="1">
-        <v>112.127359078842</v>
+        <v>109.532353190997</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -2949,7 +2604,7 @@
         <v>61</v>
       </c>
       <c r="B61" s="1">
-        <v>112.1444682208722</v>
+        <v>109.623310666245</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -2957,7 +2612,7 @@
         <v>62</v>
       </c>
       <c r="B62" s="1">
-        <v>112.1554987572934</v>
+        <v>109.6367468406861</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -2965,7 +2620,7 @@
         <v>63</v>
       </c>
       <c r="B63" s="1">
-        <v>112.1618408622081</v>
+        <v>109.6536589400593</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -2973,7 +2628,7 @@
         <v>64</v>
       </c>
       <c r="B64" s="1">
-        <v>112.2246827199497</v>
+        <v>109.7108023920208</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -2981,7 +2636,7 @@
         <v>65</v>
       </c>
       <c r="B65" s="1">
-        <v>112.2382864112019</v>
+        <v>109.7158188763976</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -2989,7 +2644,7 @@
         <v>66</v>
       </c>
       <c r="B66" s="1">
-        <v>112.2457351734439</v>
+        <v>109.7189358830763</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -2997,7 +2652,7 @@
         <v>67</v>
       </c>
       <c r="B67" s="1">
-        <v>112.3109619552524</v>
+        <v>109.733431878471</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -3005,7 +2660,7 @@
         <v>68</v>
       </c>
       <c r="B68" s="1">
-        <v>112.3120676979905</v>
+        <v>109.7374209284333</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -3013,7 +2668,7 @@
         <v>69</v>
       </c>
       <c r="B69" s="1">
-        <v>112.3174388300888</v>
+        <v>109.7484349390835</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -3021,7 +2676,7 @@
         <v>70</v>
       </c>
       <c r="B70" s="1">
-        <v>112.3384978635287</v>
+        <v>109.7558410579739</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -3029,7 +2684,7 @@
         <v>71</v>
       </c>
       <c r="B71" s="1">
-        <v>112.3932997259265</v>
+        <v>109.7681123561073</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -3037,7 +2692,7 @@
         <v>72</v>
       </c>
       <c r="B72" s="1">
-        <v>112.4369163137601</v>
+        <v>109.7874773321726</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -3045,7 +2700,7 @@
         <v>73</v>
       </c>
       <c r="B73" s="1">
-        <v>112.4457105943059</v>
+        <v>109.8041022575253</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -3053,7 +2708,7 @@
         <v>74</v>
       </c>
       <c r="B74" s="1">
-        <v>112.4602446973828</v>
+        <v>109.8341930830541</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -3061,7 +2716,7 @@
         <v>75</v>
       </c>
       <c r="B75" s="1">
-        <v>112.4636465433874</v>
+        <v>109.8423217114095</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -3069,7 +2724,7 @@
         <v>76</v>
       </c>
       <c r="B76" s="1">
-        <v>112.4866945545343</v>
+        <v>109.8535548141814</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -3077,7 +2732,7 @@
         <v>77</v>
       </c>
       <c r="B77" s="1">
-        <v>112.4909267939348</v>
+        <v>109.8797978251421</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -3085,7 +2740,7 @@
         <v>78</v>
       </c>
       <c r="B78" s="1">
-        <v>112.4951666545483</v>
+        <v>109.9380133828587</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -3093,7 +2748,7 @@
         <v>79</v>
       </c>
       <c r="B79" s="1">
-        <v>112.5002626312391</v>
+        <v>109.9639638830205</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -3101,7 +2756,7 @@
         <v>80</v>
       </c>
       <c r="B80" s="1">
-        <v>112.5069609432311</v>
+        <v>109.9989392389046</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -3109,7 +2764,7 @@
         <v>81</v>
       </c>
       <c r="B81" s="1">
-        <v>112.5171339613725</v>
+        <v>110.0007919524907</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -3117,7 +2772,7 @@
         <v>82</v>
       </c>
       <c r="B82" s="1">
-        <v>112.5239012550908</v>
+        <v>110.0069241070703</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -3125,7 +2780,7 @@
         <v>83</v>
       </c>
       <c r="B83" s="1">
-        <v>112.5392399181627</v>
+        <v>110.0305264976416</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -3133,7 +2788,7 @@
         <v>84</v>
       </c>
       <c r="B84" s="1">
-        <v>112.5484740083833</v>
+        <v>110.0362533824624</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -3141,7 +2796,7 @@
         <v>85</v>
       </c>
       <c r="B85" s="1">
-        <v>112.5489894267813</v>
+        <v>110.0612418687082</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -3149,7 +2804,7 @@
         <v>86</v>
       </c>
       <c r="B86" s="1">
-        <v>112.5510011980902</v>
+        <v>110.0829488032846</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -3157,7 +2812,7 @@
         <v>87</v>
       </c>
       <c r="B87" s="1">
-        <v>112.5584186439458</v>
+        <v>110.0842363453334</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -3165,7 +2820,7 @@
         <v>88</v>
       </c>
       <c r="B88" s="1">
-        <v>112.5955337718902</v>
+        <v>110.0919921337981</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -3173,7 +2828,7 @@
         <v>89</v>
       </c>
       <c r="B89" s="1">
-        <v>112.624171757551</v>
+        <v>110.0919954251345</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -3181,7 +2836,7 @@
         <v>90</v>
       </c>
       <c r="B90" s="1">
-        <v>112.6319673457117</v>
+        <v>110.1015921808671</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -3189,7 +2844,7 @@
         <v>91</v>
       </c>
       <c r="B91" s="1">
-        <v>112.677682276161</v>
+        <v>110.1035574547346</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -3197,7 +2852,7 @@
         <v>92</v>
       </c>
       <c r="B92" s="1">
-        <v>112.6894275041773</v>
+        <v>110.1151998287071</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -3205,7 +2860,7 @@
         <v>93</v>
       </c>
       <c r="B93" s="1">
-        <v>112.6895428738074</v>
+        <v>110.1637121491319</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -3213,7 +2868,7 @@
         <v>94</v>
       </c>
       <c r="B94" s="1">
-        <v>112.7118764830948</v>
+        <v>110.1824578886186</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -3221,7 +2876,7 @@
         <v>95</v>
       </c>
       <c r="B95" s="1">
-        <v>112.7864427294929</v>
+        <v>110.1931153290264</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -3229,7 +2884,7 @@
         <v>96</v>
       </c>
       <c r="B96" s="1">
-        <v>112.8031657851604</v>
+        <v>110.1931827285504</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -3237,7 +2892,7 @@
         <v>97</v>
       </c>
       <c r="B97" s="1">
-        <v>112.8588662096013</v>
+        <v>110.1974248099182</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -3245,7 +2900,7 @@
         <v>98</v>
       </c>
       <c r="B98" s="1">
-        <v>112.8628950088184</v>
+        <v>110.1995993745136</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -3253,7 +2908,7 @@
         <v>99</v>
       </c>
       <c r="B99" s="1">
-        <v>112.8835904876899</v>
+        <v>110.2138492008338</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -3261,7 +2916,7 @@
         <v>100</v>
       </c>
       <c r="B100" s="1">
-        <v>112.933352221355</v>
+        <v>110.2315692615862</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -3269,7 +2924,7 @@
         <v>101</v>
       </c>
       <c r="B101" s="1">
-        <v>113.041457937758</v>
+        <v>110.2751401572244</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -3277,7 +2932,7 @@
         <v>102</v>
       </c>
       <c r="B102" s="1">
-        <v>113.0747620992742</v>
+        <v>110.283681163536</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -3285,7 +2940,7 @@
         <v>103</v>
       </c>
       <c r="B103" s="1">
-        <v>113.102343826024</v>
+        <v>110.2956826060586</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -3293,7 +2948,7 @@
         <v>104</v>
       </c>
       <c r="B104" s="1">
-        <v>113.1072096083887</v>
+        <v>110.3438377655099</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -3301,7 +2956,7 @@
         <v>105</v>
       </c>
       <c r="B105" s="1">
-        <v>113.1159589228084</v>
+        <v>110.361347258184</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -3309,7 +2964,7 @@
         <v>106</v>
       </c>
       <c r="B106" s="1">
-        <v>113.1481733289554</v>
+        <v>110.3732883240173</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -3317,7 +2972,7 @@
         <v>107</v>
       </c>
       <c r="B107" s="1">
-        <v>113.1641838522858</v>
+        <v>110.4392155247892</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -3325,7 +2980,7 @@
         <v>108</v>
       </c>
       <c r="B108" s="1">
-        <v>113.2323735459246</v>
+        <v>110.4669042286584</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -3333,7 +2988,7 @@
         <v>109</v>
       </c>
       <c r="B109" s="1">
-        <v>113.2530267266307</v>
+        <v>110.4721625528352</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -3341,7 +2996,7 @@
         <v>110</v>
       </c>
       <c r="B110" s="1">
-        <v>113.2686138808616</v>
+        <v>110.4903398788568</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -3349,7 +3004,7 @@
         <v>111</v>
       </c>
       <c r="B111" s="1">
-        <v>113.2754131365293</v>
+        <v>110.5172608330772</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -3357,7 +3012,7 @@
         <v>112</v>
       </c>
       <c r="B112" s="1">
-        <v>113.2882090832779</v>
+        <v>110.5252620604669</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -3365,7 +3020,7 @@
         <v>113</v>
       </c>
       <c r="B113" s="1">
-        <v>113.3024375526175</v>
+        <v>110.5612450842393</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -3373,7 +3028,7 @@
         <v>114</v>
       </c>
       <c r="B114" s="1">
-        <v>113.3581453438479</v>
+        <v>110.5739463043869</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -3381,7 +3036,7 @@
         <v>115</v>
       </c>
       <c r="B115" s="1">
-        <v>113.3592977068726</v>
+        <v>110.6446821338508</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -3389,7 +3044,7 @@
         <v>116</v>
       </c>
       <c r="B116" s="1">
-        <v>113.3792194063035</v>
+        <v>110.651694263882</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -3397,7 +3052,7 @@
         <v>117</v>
       </c>
       <c r="B117" s="1">
-        <v>113.4017594843759</v>
+        <v>110.6819757110929</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -3405,7 +3060,7 @@
         <v>118</v>
       </c>
       <c r="B118" s="1">
-        <v>113.4132983457293</v>
+        <v>110.6989003896083</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -3413,7 +3068,7 @@
         <v>119</v>
       </c>
       <c r="B119" s="1">
-        <v>113.4326882077768</v>
+        <v>110.7077368723163</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -3421,7 +3076,7 @@
         <v>120</v>
       </c>
       <c r="B120" s="1">
-        <v>113.4687950651167</v>
+        <v>110.709574178167</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -3429,7 +3084,7 @@
         <v>121</v>
       </c>
       <c r="B121" s="1">
-        <v>113.4794473195246</v>
+        <v>110.7786222227785</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -3437,7 +3092,7 @@
         <v>122</v>
       </c>
       <c r="B122" s="1">
-        <v>113.4979323640599</v>
+        <v>110.7787941462775</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -3445,7 +3100,7 @@
         <v>123</v>
       </c>
       <c r="B123" s="1">
-        <v>113.5039042677739</v>
+        <v>110.7870513065502</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -3453,7 +3108,7 @@
         <v>124</v>
       </c>
       <c r="B124" s="1">
-        <v>113.5171358533814</v>
+        <v>110.7958620176886</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -3461,7 +3116,7 @@
         <v>125</v>
       </c>
       <c r="B125" s="1">
-        <v>113.5676941750637</v>
+        <v>110.8163512830035</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -3469,7 +3124,7 @@
         <v>126</v>
       </c>
       <c r="B126" s="1">
-        <v>113.582549838585</v>
+        <v>110.8470684195164</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -3477,7 +3132,7 @@
         <v>127</v>
       </c>
       <c r="B127" s="1">
-        <v>113.5840916161213</v>
+        <v>110.8480556768133</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -3485,7 +3140,7 @@
         <v>128</v>
       </c>
       <c r="B128" s="1">
-        <v>113.6027614745096</v>
+        <v>110.8490115704361</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -3493,7 +3148,7 @@
         <v>129</v>
       </c>
       <c r="B129" s="1">
-        <v>113.6170184007267</v>
+        <v>110.8628814110862</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -3501,7 +3156,7 @@
         <v>130</v>
       </c>
       <c r="B130" s="1">
-        <v>113.6530235324607</v>
+        <v>110.8726469464798</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -3509,7 +3164,7 @@
         <v>131</v>
       </c>
       <c r="B131" s="1">
-        <v>113.6648351483097</v>
+        <v>110.9163444416006</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -3517,7 +3172,7 @@
         <v>132</v>
       </c>
       <c r="B132" s="1">
-        <v>113.6689548039554</v>
+        <v>110.9302227585751</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -3525,7 +3180,7 @@
         <v>133</v>
       </c>
       <c r="B133" s="1">
-        <v>113.6793207299069</v>
+        <v>110.9731120101126</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -3533,7 +3188,7 @@
         <v>134</v>
       </c>
       <c r="B134" s="1">
-        <v>113.6804914558656</v>
+        <v>111.0183512527371</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -3541,7 +3196,7 @@
         <v>135</v>
       </c>
       <c r="B135" s="1">
-        <v>113.6902246266808</v>
+        <v>111.0208985248642</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -3549,7 +3204,7 @@
         <v>136</v>
       </c>
       <c r="B136" s="1">
-        <v>113.7103099036666</v>
+        <v>111.0381702619269</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -3557,7 +3212,7 @@
         <v>137</v>
       </c>
       <c r="B137" s="1">
-        <v>113.7287500574251</v>
+        <v>111.1006087660603</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -3565,7 +3220,7 @@
         <v>138</v>
       </c>
       <c r="B138" s="1">
-        <v>113.7780813773275</v>
+        <v>111.1299918670148</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -3573,7 +3228,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="1">
-        <v>113.7914711215384</v>
+        <v>111.1300592596378</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -3581,7 +3236,7 @@
         <v>140</v>
       </c>
       <c r="B140" s="1">
-        <v>113.8339444085862</v>
+        <v>111.2004573613926</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -3589,7 +3244,7 @@
         <v>141</v>
       </c>
       <c r="B141" s="1">
-        <v>113.882148949995</v>
+        <v>111.2191497627486</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -3597,7 +3252,7 @@
         <v>142</v>
       </c>
       <c r="B142" s="1">
-        <v>113.8948345777003</v>
+        <v>111.2278183218817</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -3605,7 +3260,7 @@
         <v>143</v>
       </c>
       <c r="B143" s="1">
-        <v>113.9659166957802</v>
+        <v>111.2763132591377</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -3613,7 +3268,7 @@
         <v>144</v>
       </c>
       <c r="B144" s="1">
-        <v>114.016320637967</v>
+        <v>111.2906595427569</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -3621,7 +3276,7 @@
         <v>145</v>
       </c>
       <c r="B145" s="1">
-        <v>114.0398279084865</v>
+        <v>111.3261715141003</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -3629,7 +3284,7 @@
         <v>146</v>
       </c>
       <c r="B146" s="1">
-        <v>114.0471316159944</v>
+        <v>111.3307983913146</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -3637,7 +3292,7 @@
         <v>147</v>
       </c>
       <c r="B147" s="1">
-        <v>114.0482836380509</v>
+        <v>111.3451847448531</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -3645,7 +3300,7 @@
         <v>148</v>
       </c>
       <c r="B148" s="1">
-        <v>114.0522451310311</v>
+        <v>111.3538163878421</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -3653,7 +3308,7 @@
         <v>149</v>
       </c>
       <c r="B149" s="1">
-        <v>114.0648747603351</v>
+        <v>111.4090401097603</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -3661,7 +3316,7 @@
         <v>150</v>
       </c>
       <c r="B150" s="1">
-        <v>114.083288196853</v>
+        <v>111.4311785446576</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -3669,7 +3324,7 @@
         <v>151</v>
       </c>
       <c r="B151" s="1">
-        <v>114.1223784295987</v>
+        <v>111.4347538265135</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -3677,7 +3332,7 @@
         <v>152</v>
       </c>
       <c r="B152" s="1">
-        <v>114.1307652224007</v>
+        <v>111.4834688505973</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -3685,7 +3340,7 @@
         <v>153</v>
       </c>
       <c r="B153" s="1">
-        <v>114.1364766778258</v>
+        <v>111.5224098402282</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -3693,7 +3348,7 @@
         <v>154</v>
       </c>
       <c r="B154" s="1">
-        <v>114.1562424319056</v>
+        <v>111.5299227889456</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -3701,7 +3356,7 @@
         <v>155</v>
       </c>
       <c r="B155" s="1">
-        <v>114.2047200001222</v>
+        <v>111.6357436095442</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -3709,7 +3364,7 @@
         <v>156</v>
       </c>
       <c r="B156" s="1">
-        <v>114.2232121310074</v>
+        <v>111.6451202037525</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -3717,7 +3372,7 @@
         <v>157</v>
       </c>
       <c r="B157" s="1">
-        <v>114.2377333609813</v>
+        <v>111.6453169679832</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -3725,7 +3380,7 @@
         <v>158</v>
       </c>
       <c r="B158" s="1">
-        <v>114.2782407278108</v>
+        <v>111.6654419730041</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -3733,7 +3388,7 @@
         <v>159</v>
       </c>
       <c r="B159" s="1">
-        <v>114.3098290287035</v>
+        <v>111.6665838908569</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -3741,7 +3396,7 @@
         <v>160</v>
       </c>
       <c r="B160" s="1">
-        <v>114.3296763590119</v>
+        <v>111.677833687265</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -3749,7 +3404,7 @@
         <v>161</v>
       </c>
       <c r="B161" s="1">
-        <v>114.3940820788603</v>
+        <v>111.7007675885576</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -3757,7 +3412,7 @@
         <v>162</v>
       </c>
       <c r="B162" s="1">
-        <v>114.4366017181397</v>
+        <v>111.7251640155633</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -3765,7 +3420,7 @@
         <v>163</v>
       </c>
       <c r="B163" s="1">
-        <v>114.5051208199172</v>
+        <v>111.7481306295452</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -3773,7 +3428,7 @@
         <v>164</v>
       </c>
       <c r="B164" s="1">
-        <v>114.5433186155488</v>
+        <v>111.7514807869026</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -3781,7 +3436,7 @@
         <v>165</v>
       </c>
       <c r="B165" s="1">
-        <v>114.5490577795923</v>
+        <v>111.7722392394721</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -3789,7 +3444,7 @@
         <v>166</v>
       </c>
       <c r="B166" s="1">
-        <v>114.5820968799014</v>
+        <v>111.7992388138016</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -3797,7 +3452,7 @@
         <v>167</v>
       </c>
       <c r="B167" s="1">
-        <v>114.5887529544187</v>
+        <v>111.8173339167051</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -3805,7 +3460,7 @@
         <v>168</v>
       </c>
       <c r="B168" s="1">
-        <v>114.63584468682</v>
+        <v>111.8594464410554</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -3813,7 +3468,7 @@
         <v>169</v>
       </c>
       <c r="B169" s="1">
-        <v>114.6359140064786</v>
+        <v>111.8621902098471</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -3821,7 +3476,7 @@
         <v>170</v>
       </c>
       <c r="B170" s="1">
-        <v>114.7022962568226</v>
+        <v>111.8649356369658</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -3829,7 +3484,7 @@
         <v>171</v>
       </c>
       <c r="B171" s="1">
-        <v>114.7276836252478</v>
+        <v>111.9045681639048</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -3837,7 +3492,7 @@
         <v>172</v>
       </c>
       <c r="B172" s="1">
-        <v>114.7450598961282</v>
+        <v>111.9054493972529</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -3845,7 +3500,7 @@
         <v>173</v>
       </c>
       <c r="B173" s="1">
-        <v>114.7936216938911</v>
+        <v>111.9082874074293</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -3853,7 +3508,7 @@
         <v>174</v>
       </c>
       <c r="B174" s="1">
-        <v>114.8395222453272</v>
+        <v>111.9121725809974</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -3861,7 +3516,7 @@
         <v>175</v>
       </c>
       <c r="B175" s="1">
-        <v>114.8847107691254</v>
+        <v>111.9407073096489</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -3869,7 +3524,7 @@
         <v>176</v>
       </c>
       <c r="B176" s="1">
-        <v>114.9114745846652</v>
+        <v>111.9481611153545</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -3877,7 +3532,7 @@
         <v>177</v>
       </c>
       <c r="B177" s="1">
-        <v>114.9518619166073</v>
+        <v>111.9520343361331</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -3885,7 +3540,7 @@
         <v>178</v>
       </c>
       <c r="B178" s="1">
-        <v>114.9525512150111</v>
+        <v>111.9691590125399</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -3893,7 +3548,7 @@
         <v>179</v>
       </c>
       <c r="B179" s="1">
-        <v>115.0149211128021</v>
+        <v>111.9718046154938</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -3901,7 +3556,7 @@
         <v>180</v>
       </c>
       <c r="B180" s="1">
-        <v>115.0205488527057</v>
+        <v>111.9780023377533</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -3909,7 +3564,7 @@
         <v>181</v>
       </c>
       <c r="B181" s="1">
-        <v>115.0609035683646</v>
+        <v>111.9906775817554</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -3917,7 +3572,7 @@
         <v>182</v>
       </c>
       <c r="B182" s="1">
-        <v>115.0626420800751</v>
+        <v>112.069824793466</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -3925,7 +3580,7 @@
         <v>183</v>
       </c>
       <c r="B183" s="1">
-        <v>115.0636771877305</v>
+        <v>112.0746921395195</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -3933,7 +3588,7 @@
         <v>184</v>
       </c>
       <c r="B184" s="1">
-        <v>115.0772435045716</v>
+        <v>112.0882389931314</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -3941,7 +3596,7 @@
         <v>185</v>
       </c>
       <c r="B185" s="1">
-        <v>115.0786860693424</v>
+        <v>112.1079572242092</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -3949,7 +3604,7 @@
         <v>186</v>
       </c>
       <c r="B186" s="1">
-        <v>115.0796016860821</v>
+        <v>112.1590832967887</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -3957,7 +3612,7 @@
         <v>187</v>
       </c>
       <c r="B187" s="1">
-        <v>115.0846738160146</v>
+        <v>112.1802968606833</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -3965,7 +3620,7 @@
         <v>188</v>
       </c>
       <c r="B188" s="1">
-        <v>115.1340049188879</v>
+        <v>112.227735926473</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -3973,7 +3628,7 @@
         <v>189</v>
       </c>
       <c r="B189" s="1">
-        <v>115.2018304440228</v>
+        <v>112.2528499077744</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -3981,7 +3636,7 @@
         <v>190</v>
       </c>
       <c r="B190" s="1">
-        <v>115.2140079508356</v>
+        <v>112.2957715387944</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -3989,7 +3644,7 @@
         <v>191</v>
       </c>
       <c r="B191" s="1">
-        <v>115.269227645817</v>
+        <v>112.3198559618261</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -3997,7 +3652,7 @@
         <v>192</v>
       </c>
       <c r="B192" s="1">
-        <v>115.3127958747807</v>
+        <v>112.3390354981857</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -4005,7 +3660,7 @@
         <v>193</v>
       </c>
       <c r="B193" s="1">
-        <v>115.355001023091</v>
+        <v>112.3494425634043</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -4013,7 +3668,7 @@
         <v>194</v>
       </c>
       <c r="B194" s="1">
-        <v>115.3659147444239</v>
+        <v>112.3819844229076</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -4021,7 +3676,7 @@
         <v>195</v>
       </c>
       <c r="B195" s="1">
-        <v>115.4308777430539</v>
+        <v>112.4008488610883</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -4029,7 +3684,7 @@
         <v>196</v>
       </c>
       <c r="B196" s="1">
-        <v>115.4479451045624</v>
+        <v>112.4580362540257</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -4037,7 +3692,7 @@
         <v>197</v>
       </c>
       <c r="B197" s="1">
-        <v>115.4635811481295</v>
+        <v>112.4682675083315</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -4045,7 +3700,7 @@
         <v>198</v>
       </c>
       <c r="B198" s="1">
-        <v>115.5142621691569</v>
+        <v>112.4686369397608</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -4053,7 +3708,7 @@
         <v>199</v>
       </c>
       <c r="B199" s="1">
-        <v>115.517467575567</v>
+        <v>112.4734112149274</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -4061,7 +3716,7 @@
         <v>200</v>
       </c>
       <c r="B200" s="1">
-        <v>115.5445651962146</v>
+        <v>112.5051929042053</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -4069,7 +3724,7 @@
         <v>201</v>
       </c>
       <c r="B201" s="1">
-        <v>115.5530643837317</v>
+        <v>112.5068020696144</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -4077,7 +3732,7 @@
         <v>202</v>
       </c>
       <c r="B202" s="1">
-        <v>115.6058967933578</v>
+        <v>112.5660440153347</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -4085,7 +3740,7 @@
         <v>203</v>
       </c>
       <c r="B203" s="1">
-        <v>115.6450611208302</v>
+        <v>112.5732898130175</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -4093,7 +3748,7 @@
         <v>204</v>
       </c>
       <c r="B204" s="1">
-        <v>115.6615773664466</v>
+        <v>112.6295974995</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -4101,7 +3756,7 @@
         <v>205</v>
       </c>
       <c r="B205" s="1">
-        <v>115.6828107218037</v>
+        <v>112.6392065598057</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -4109,7 +3764,7 @@
         <v>206</v>
       </c>
       <c r="B206" s="1">
-        <v>115.6862892954402</v>
+        <v>112.6542017582276</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -4117,7 +3772,7 @@
         <v>207</v>
       </c>
       <c r="B207" s="1">
-        <v>115.6932303046975</v>
+        <v>112.6737397148334</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -4125,7 +3780,7 @@
         <v>208</v>
       </c>
       <c r="B208" s="1">
-        <v>115.6936330646188</v>
+        <v>112.6751029490665</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -4133,7 +3788,7 @@
         <v>209</v>
       </c>
       <c r="B209" s="1">
-        <v>115.7010892949569</v>
+        <v>112.6782759354937</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -4141,7 +3796,7 @@
         <v>210</v>
       </c>
       <c r="B210" s="1">
-        <v>115.7134732684824</v>
+        <v>112.6814745447344</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -4149,7 +3804,7 @@
         <v>211</v>
       </c>
       <c r="B211" s="1">
-        <v>115.7394072260758</v>
+        <v>112.7034978502298</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -4157,7 +3812,7 @@
         <v>212</v>
       </c>
       <c r="B212" s="1">
-        <v>115.7523241630014</v>
+        <v>112.7321892144345</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -4165,7 +3820,7 @@
         <v>213</v>
       </c>
       <c r="B213" s="1">
-        <v>115.7934281563089</v>
+        <v>112.7653547304883</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -4173,7 +3828,7 @@
         <v>214</v>
       </c>
       <c r="B214" s="1">
-        <v>115.8099346686525</v>
+        <v>112.7806677357717</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -4181,7 +3836,7 @@
         <v>215</v>
       </c>
       <c r="B215" s="1">
-        <v>115.8329297792183</v>
+        <v>112.784723501314</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -4189,7 +3844,7 @@
         <v>216</v>
       </c>
       <c r="B216" s="1">
-        <v>115.8635894949314</v>
+        <v>112.7980709520567</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -4197,7 +3852,7 @@
         <v>217</v>
       </c>
       <c r="B217" s="1">
-        <v>115.8736807126701</v>
+        <v>112.8303691640817</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -4205,7 +3860,7 @@
         <v>218</v>
       </c>
       <c r="B218" s="1">
-        <v>115.8957399570128</v>
+        <v>112.8494968393406</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -4213,7 +3868,7 @@
         <v>219</v>
       </c>
       <c r="B219" s="1">
-        <v>115.9315399930317</v>
+        <v>112.8869611278936</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -4221,7 +3876,7 @@
         <v>220</v>
       </c>
       <c r="B220" s="1">
-        <v>115.9590478837542</v>
+        <v>112.9013485889429</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -4229,7 +3884,7 @@
         <v>221</v>
       </c>
       <c r="B221" s="1">
-        <v>115.963100289782</v>
+        <v>112.9133845217914</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -4237,7 +3892,7 @@
         <v>222</v>
       </c>
       <c r="B222" s="1">
-        <v>115.9950235603115</v>
+        <v>112.9400548612031</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -4245,7 +3900,7 @@
         <v>223</v>
       </c>
       <c r="B223" s="1">
-        <v>116.0357511009081</v>
+        <v>112.9472333045595</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -4253,7 +3908,7 @@
         <v>224</v>
       </c>
       <c r="B224" s="1">
-        <v>116.100489054935</v>
+        <v>112.957357175609</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -4261,7 +3916,7 @@
         <v>225</v>
       </c>
       <c r="B225" s="1">
-        <v>116.1024352596279</v>
+        <v>112.9732975200876</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -4269,7 +3924,7 @@
         <v>226</v>
       </c>
       <c r="B226" s="1">
-        <v>116.1029699699378</v>
+        <v>112.9936931111751</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -4277,7 +3932,7 @@
         <v>227</v>
       </c>
       <c r="B227" s="1">
-        <v>116.1360227059373</v>
+        <v>112.995256082783</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -4285,7 +3940,7 @@
         <v>228</v>
       </c>
       <c r="B228" s="1">
-        <v>116.1507501996863</v>
+        <v>113.0273590248876</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -4293,7 +3948,7 @@
         <v>229</v>
       </c>
       <c r="B229" s="1">
-        <v>116.1721813914905</v>
+        <v>113.0692856940382</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -4301,7 +3956,7 @@
         <v>230</v>
       </c>
       <c r="B230" s="1">
-        <v>116.2049547073389</v>
+        <v>113.1198047633826</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -4309,7 +3964,7 @@
         <v>231</v>
       </c>
       <c r="B231" s="1">
-        <v>116.2554165667749</v>
+        <v>113.1261475051322</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -4317,7 +3972,7 @@
         <v>232</v>
       </c>
       <c r="B232" s="1">
-        <v>116.2712293800288</v>
+        <v>113.1596231424052</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -4325,7 +3980,7 @@
         <v>233</v>
       </c>
       <c r="B233" s="1">
-        <v>116.2791485266362</v>
+        <v>113.1691047701156</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -4333,7 +3988,7 @@
         <v>234</v>
       </c>
       <c r="B234" s="1">
-        <v>116.2817661089989</v>
+        <v>113.1939466142302</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -4341,7 +3996,7 @@
         <v>235</v>
       </c>
       <c r="B235" s="1">
-        <v>116.2940428956452</v>
+        <v>113.2057892887621</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -4349,7 +4004,7 @@
         <v>236</v>
       </c>
       <c r="B236" s="1">
-        <v>116.3106178360152</v>
+        <v>113.2434269675169</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -4357,7 +4012,7 @@
         <v>237</v>
       </c>
       <c r="B237" s="1">
-        <v>116.3207061397035</v>
+        <v>113.2494553871121</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -4365,7 +4020,7 @@
         <v>238</v>
       </c>
       <c r="B238" s="1">
-        <v>116.3429095729792</v>
+        <v>113.2523349726654</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -4373,7 +4028,7 @@
         <v>239</v>
       </c>
       <c r="B239" s="1">
-        <v>116.3631223774945</v>
+        <v>113.321780991502</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -4381,7 +4036,7 @@
         <v>240</v>
       </c>
       <c r="B240" s="1">
-        <v>116.4492331877463</v>
+        <v>113.3661740329412</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -4389,7 +4044,7 @@
         <v>241</v>
       </c>
       <c r="B241" s="1">
-        <v>116.4519905116477</v>
+        <v>113.4095399441479</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -4397,7 +4052,7 @@
         <v>242</v>
       </c>
       <c r="B242" s="1">
-        <v>116.4639974722631</v>
+        <v>113.4495262783349</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -4405,7 +4060,7 @@
         <v>243</v>
       </c>
       <c r="B243" s="1">
-        <v>116.4713707695876</v>
+        <v>113.4800005255514</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -4413,7 +4068,7 @@
         <v>244</v>
       </c>
       <c r="B244" s="1">
-        <v>116.5025886510251</v>
+        <v>113.4864316222028</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -4421,7 +4076,7 @@
         <v>245</v>
       </c>
       <c r="B245" s="1">
-        <v>116.5036622628921</v>
+        <v>113.4883206476719</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -4429,7 +4084,7 @@
         <v>246</v>
       </c>
       <c r="B246" s="1">
-        <v>116.5348271838349</v>
+        <v>113.5106374423223</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -4437,7 +4092,7 @@
         <v>247</v>
       </c>
       <c r="B247" s="1">
-        <v>116.564525179259</v>
+        <v>113.5346776113842</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -4445,7 +4100,7 @@
         <v>248</v>
       </c>
       <c r="B248" s="1">
-        <v>116.5978222447868</v>
+        <v>113.5548298117168</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -4453,7 +4108,7 @@
         <v>249</v>
       </c>
       <c r="B249" s="1">
-        <v>116.5990025908338</v>
+        <v>113.5570216478002</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -4461,7 +4116,7 @@
         <v>250</v>
       </c>
       <c r="B250" s="1">
-        <v>116.6453631904678</v>
+        <v>113.5698285443022</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -4469,7 +4124,7 @@
         <v>251</v>
       </c>
       <c r="B251" s="1">
-        <v>116.6488196484038</v>
+        <v>113.602030682785</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -4477,7 +4132,7 @@
         <v>252</v>
       </c>
       <c r="B252" s="1">
-        <v>116.6777486605849</v>
+        <v>113.6051795385633</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -4485,7 +4140,7 @@
         <v>253</v>
       </c>
       <c r="B253" s="1">
-        <v>116.7091541620856</v>
+        <v>113.6055297356287</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -4493,7 +4148,7 @@
         <v>254</v>
       </c>
       <c r="B254" s="1">
-        <v>116.7099428283593</v>
+        <v>113.6083975420092</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -4501,7 +4156,7 @@
         <v>255</v>
       </c>
       <c r="B255" s="1">
-        <v>116.7285773028293</v>
+        <v>113.6169302498038</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -4509,7 +4164,7 @@
         <v>256</v>
       </c>
       <c r="B256" s="1">
-        <v>116.7646871464885</v>
+        <v>113.6644901681912</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -4517,7 +4172,7 @@
         <v>257</v>
       </c>
       <c r="B257" s="1">
-        <v>116.8316840881842</v>
+        <v>113.6695363421643</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -4525,7 +4180,7 @@
         <v>258</v>
       </c>
       <c r="B258" s="1">
-        <v>116.8590560326206</v>
+        <v>113.6901676957353</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -4533,7 +4188,7 @@
         <v>259</v>
       </c>
       <c r="B259" s="1">
-        <v>116.865858850697</v>
+        <v>113.6953411059119</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -4541,7 +4196,7 @@
         <v>260</v>
       </c>
       <c r="B260" s="1">
-        <v>116.94558503514</v>
+        <v>113.6967821272123</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -4549,7 +4204,7 @@
         <v>261</v>
       </c>
       <c r="B261" s="1">
-        <v>116.9548592003947</v>
+        <v>113.6990857975118</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -4557,7 +4212,7 @@
         <v>262</v>
       </c>
       <c r="B262" s="1">
-        <v>116.9953508079986</v>
+        <v>113.7232878159068</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -4565,7 +4220,7 @@
         <v>263</v>
       </c>
       <c r="B263" s="1">
-        <v>117.0077135142714</v>
+        <v>113.7286116868798</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -4573,7 +4228,7 @@
         <v>264</v>
       </c>
       <c r="B264" s="1">
-        <v>117.0114021150171</v>
+        <v>113.7873413500043</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -4581,7 +4236,7 @@
         <v>265</v>
       </c>
       <c r="B265" s="1">
-        <v>117.0154110821537</v>
+        <v>113.7920671271025</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -4589,7 +4244,7 @@
         <v>266</v>
       </c>
       <c r="B266" s="1">
-        <v>117.0456664574378</v>
+        <v>113.7964481200459</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -4597,7 +4252,7 @@
         <v>267</v>
       </c>
       <c r="B267" s="1">
-        <v>117.0671706455902</v>
+        <v>113.8073260438493</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -4605,7 +4260,7 @@
         <v>268</v>
       </c>
       <c r="B268" s="1">
-        <v>117.0744135368296</v>
+        <v>113.849793348492</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -4613,7 +4268,7 @@
         <v>269</v>
       </c>
       <c r="B269" s="1">
-        <v>117.0872497029365</v>
+        <v>113.8538222857482</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -4621,7 +4276,7 @@
         <v>270</v>
       </c>
       <c r="B270" s="1">
-        <v>117.2146820675713</v>
+        <v>113.8577782549808</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -4629,7 +4284,7 @@
         <v>271</v>
       </c>
       <c r="B271" s="1">
-        <v>117.2201303063032</v>
+        <v>113.891445380596</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -4637,7 +4292,7 @@
         <v>272</v>
       </c>
       <c r="B272" s="1">
-        <v>117.2242445204989</v>
+        <v>113.9410080910135</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -4645,7 +4300,7 @@
         <v>273</v>
       </c>
       <c r="B273" s="1">
-        <v>117.2642467611347</v>
+        <v>113.9723817647356</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -4653,7 +4308,7 @@
         <v>274</v>
       </c>
       <c r="B274" s="1">
-        <v>117.3284031893641</v>
+        <v>113.9777178796051</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -4661,7 +4316,7 @@
         <v>275</v>
       </c>
       <c r="B275" s="1">
-        <v>117.3456947006276</v>
+        <v>113.9825109767834</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -4669,7 +4324,7 @@
         <v>276</v>
       </c>
       <c r="B276" s="1">
-        <v>117.3692003463086</v>
+        <v>113.9868423449374</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -4677,7 +4332,7 @@
         <v>277</v>
       </c>
       <c r="B277" s="1">
-        <v>117.3707336082891</v>
+        <v>114.0806323016397</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -4685,7 +4340,7 @@
         <v>278</v>
       </c>
       <c r="B278" s="1">
-        <v>117.3931172181952</v>
+        <v>114.1047046962834</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -4693,7 +4348,7 @@
         <v>279</v>
       </c>
       <c r="B279" s="1">
-        <v>117.4647318177871</v>
+        <v>114.1071518051587</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -4701,7 +4356,7 @@
         <v>280</v>
       </c>
       <c r="B280" s="1">
-        <v>117.4977419621957</v>
+        <v>114.1194156759649</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -4709,7 +4364,7 @@
         <v>281</v>
       </c>
       <c r="B281" s="1">
-        <v>117.5033612248346</v>
+        <v>114.1563817395504</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -4717,7 +4372,7 @@
         <v>282</v>
       </c>
       <c r="B282" s="1">
-        <v>117.5397676034224</v>
+        <v>114.2872316556573</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -4725,7 +4380,7 @@
         <v>283</v>
       </c>
       <c r="B283" s="1">
-        <v>117.5570551691597</v>
+        <v>114.2898120166434</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -4733,7 +4388,7 @@
         <v>284</v>
       </c>
       <c r="B284" s="1">
-        <v>117.5711910082227</v>
+        <v>114.3166186505254</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -4741,7 +4396,7 @@
         <v>285</v>
       </c>
       <c r="B285" s="1">
-        <v>117.5962584574623</v>
+        <v>114.3244740798967</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -4749,7 +4404,7 @@
         <v>286</v>
       </c>
       <c r="B286" s="1">
-        <v>117.613883807638</v>
+        <v>114.360009878749</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -4757,7 +4412,7 @@
         <v>287</v>
       </c>
       <c r="B287" s="1">
-        <v>117.6500676235055</v>
+        <v>114.4020731894207</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -4765,7 +4420,7 @@
         <v>288</v>
       </c>
       <c r="B288" s="1">
-        <v>117.6504743564992</v>
+        <v>114.4065932954779</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -4773,7 +4428,7 @@
         <v>289</v>
       </c>
       <c r="B289" s="1">
-        <v>117.6846822235248</v>
+        <v>114.4528141319316</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -4781,7 +4436,7 @@
         <v>290</v>
       </c>
       <c r="B290" s="1">
-        <v>117.6988550348087</v>
+        <v>114.4604015436887</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -4789,7 +4444,7 @@
         <v>291</v>
       </c>
       <c r="B291" s="1">
-        <v>117.7308637618376</v>
+        <v>114.4907167381965</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -4797,7 +4452,7 @@
         <v>292</v>
       </c>
       <c r="B292" s="1">
-        <v>117.7634446841664</v>
+        <v>114.5015419446152</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -4805,7 +4460,7 @@
         <v>293</v>
       </c>
       <c r="B293" s="1">
-        <v>117.7706478892038</v>
+        <v>114.5051753380617</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -4813,7 +4468,7 @@
         <v>294</v>
       </c>
       <c r="B294" s="1">
-        <v>117.7840211537754</v>
+        <v>114.5550147565222</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -4821,7 +4476,7 @@
         <v>295</v>
       </c>
       <c r="B295" s="1">
-        <v>117.7976517763748</v>
+        <v>114.5782283900252</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -4829,7 +4484,7 @@
         <v>296</v>
       </c>
       <c r="B296" s="1">
-        <v>117.8836037717644</v>
+        <v>114.578766643326</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -4837,7 +4492,7 @@
         <v>297</v>
       </c>
       <c r="B297" s="1">
-        <v>117.9097603732758</v>
+        <v>114.5857660078372</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -4845,7 +4500,7 @@
         <v>298</v>
       </c>
       <c r="B298" s="1">
-        <v>117.9605012122933</v>
+        <v>114.6170498917687</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -4853,7 +4508,7 @@
         <v>299</v>
       </c>
       <c r="B299" s="1">
-        <v>117.966998183845</v>
+        <v>114.7271675512593</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -4861,7 +4516,7 @@
         <v>300</v>
       </c>
       <c r="B300" s="1">
-        <v>117.9849896870622</v>
+        <v>114.7394752279948</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -4869,7 +4524,7 @@
         <v>301</v>
       </c>
       <c r="B301" s="1">
-        <v>118.0021126134324</v>
+        <v>114.7446438684924</v>
       </c>
     </row>
     <row r="302" spans="1:2">
@@ -4877,7 +4532,7 @@
         <v>302</v>
       </c>
       <c r="B302" s="1">
-        <v>118.0332387104532</v>
+        <v>114.7607668558996</v>
       </c>
     </row>
     <row r="303" spans="1:2">
@@ -4885,7 +4540,7 @@
         <v>303</v>
       </c>
       <c r="B303" s="1">
-        <v>118.062093385185</v>
+        <v>114.7622921935814</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -4893,7 +4548,7 @@
         <v>304</v>
       </c>
       <c r="B304" s="1">
-        <v>118.0711744485461</v>
+        <v>114.8030878457459</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -4901,7 +4556,7 @@
         <v>305</v>
       </c>
       <c r="B305" s="1">
-        <v>118.0733790044283</v>
+        <v>114.8033355833749</v>
       </c>
     </row>
     <row r="306" spans="1:2">
@@ -4909,7 +4564,7 @@
         <v>306</v>
       </c>
       <c r="B306" s="1">
-        <v>118.0876511068666</v>
+        <v>114.8066842331193</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -4917,7 +4572,7 @@
         <v>307</v>
       </c>
       <c r="B307" s="1">
-        <v>118.1867379074273</v>
+        <v>114.830654267211</v>
       </c>
     </row>
     <row r="308" spans="1:2">
@@ -4925,7 +4580,7 @@
         <v>308</v>
       </c>
       <c r="B308" s="1">
-        <v>118.186928905023</v>
+        <v>114.8639652312031</v>
       </c>
     </row>
     <row r="309" spans="1:2">
@@ -4933,7 +4588,7 @@
         <v>309</v>
       </c>
       <c r="B309" s="1">
-        <v>118.2201321704121</v>
+        <v>114.8706712209531</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -4941,7 +4596,7 @@
         <v>310</v>
       </c>
       <c r="B310" s="1">
-        <v>118.3141280846783</v>
+        <v>114.9152823307876</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -4949,7 +4604,7 @@
         <v>311</v>
       </c>
       <c r="B311" s="1">
-        <v>118.3400787144913</v>
+        <v>114.9334221102505</v>
       </c>
     </row>
     <row r="312" spans="1:2">
@@ -4957,7 +4612,7 @@
         <v>312</v>
       </c>
       <c r="B312" s="1">
-        <v>118.3534022565145</v>
+        <v>114.9720511419248</v>
       </c>
     </row>
     <row r="313" spans="1:2">
@@ -4965,7 +4620,7 @@
         <v>313</v>
       </c>
       <c r="B313" s="1">
-        <v>118.3682873474836</v>
+        <v>114.9738609925148</v>
       </c>
     </row>
     <row r="314" spans="1:2">
@@ -4973,7 +4628,7 @@
         <v>314</v>
       </c>
       <c r="B314" s="1">
-        <v>118.402755938659</v>
+        <v>114.9781001522203</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -4981,7 +4636,7 @@
         <v>315</v>
       </c>
       <c r="B315" s="1">
-        <v>118.4417349954097</v>
+        <v>114.9951122315015</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -4989,7 +4644,7 @@
         <v>316</v>
       </c>
       <c r="B316" s="1">
-        <v>118.4451707052528</v>
+        <v>115.0182895917852</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -4997,7 +4652,7 @@
         <v>317</v>
       </c>
       <c r="B317" s="1">
-        <v>118.4576279930599</v>
+        <v>115.029870380782</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -5005,7 +4660,7 @@
         <v>318</v>
       </c>
       <c r="B318" s="1">
-        <v>118.5067489573166</v>
+        <v>115.1160442432117</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -5013,7 +4668,7 @@
         <v>319</v>
       </c>
       <c r="B319" s="1">
-        <v>118.5156836583018</v>
+        <v>115.1291430247202</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -5021,7 +4676,7 @@
         <v>320</v>
       </c>
       <c r="B320" s="1">
-        <v>118.5284053951491</v>
+        <v>115.1719834693274</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -5029,7 +4684,7 @@
         <v>321</v>
       </c>
       <c r="B321" s="1">
-        <v>118.545356253334</v>
+        <v>115.2510875252513</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -5037,7 +4692,7 @@
         <v>322</v>
       </c>
       <c r="B322" s="1">
-        <v>118.6408995050248</v>
+        <v>115.2623012209937</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -5045,7 +4700,7 @@
         <v>323</v>
       </c>
       <c r="B323" s="1">
-        <v>118.7284008865864</v>
+        <v>115.283789098831</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -5053,7 +4708,7 @@
         <v>324</v>
       </c>
       <c r="B324" s="1">
-        <v>118.8896079053186</v>
+        <v>115.3772164742344</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -5061,7 +4716,7 @@
         <v>325</v>
       </c>
       <c r="B325" s="1">
-        <v>118.9191510389957</v>
+        <v>115.3781455330018</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -5069,7 +4724,7 @@
         <v>326</v>
       </c>
       <c r="B326" s="1">
-        <v>118.9205287927692</v>
+        <v>115.4061251544942</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -5077,7 +4732,7 @@
         <v>327</v>
       </c>
       <c r="B327" s="1">
-        <v>118.9911222976591</v>
+        <v>115.4541623796154</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -5085,7 +4740,7 @@
         <v>328</v>
       </c>
       <c r="B328" s="1">
-        <v>119.1016902688193</v>
+        <v>115.4602011232378</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -5093,7 +4748,7 @@
         <v>329</v>
       </c>
       <c r="B329" s="1">
-        <v>119.158000402998</v>
+        <v>115.4884569531589</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -5101,7 +4756,7 @@
         <v>330</v>
       </c>
       <c r="B330" s="1">
-        <v>119.1592238636045</v>
+        <v>115.4974191549499</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -5109,7 +4764,7 @@
         <v>331</v>
       </c>
       <c r="B331" s="1">
-        <v>119.2025204237945</v>
+        <v>115.5077993200326</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -5117,7 +4772,7 @@
         <v>332</v>
       </c>
       <c r="B332" s="1">
-        <v>119.2189257504577</v>
+        <v>115.5092854085449</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -5125,7 +4780,7 @@
         <v>333</v>
       </c>
       <c r="B333" s="1">
-        <v>119.2626293869509</v>
+        <v>115.5111578100216</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -5133,7 +4788,7 @@
         <v>334</v>
       </c>
       <c r="B334" s="1">
-        <v>119.2809633789582</v>
+        <v>115.5638970538736</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -5141,7 +4796,7 @@
         <v>335</v>
       </c>
       <c r="B335" s="1">
-        <v>119.3186710442844</v>
+        <v>115.5718796654211</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -5149,7 +4804,7 @@
         <v>336</v>
       </c>
       <c r="B336" s="1">
-        <v>119.362713705729</v>
+        <v>115.6027938233997</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -5157,7 +4812,7 @@
         <v>337</v>
       </c>
       <c r="B337" s="1">
-        <v>119.4676707606156</v>
+        <v>115.6028290205163</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -5165,7 +4820,7 @@
         <v>338</v>
       </c>
       <c r="B338" s="1">
-        <v>119.5330154877332</v>
+        <v>115.6333819268054</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -5173,7 +4828,7 @@
         <v>339</v>
       </c>
       <c r="B339" s="1">
-        <v>119.7311926070115</v>
+        <v>115.6498094841783</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -5181,7 +4836,7 @@
         <v>340</v>
       </c>
       <c r="B340" s="1">
-        <v>119.7504024728128</v>
+        <v>115.7043368066782</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -5189,7 +4844,7 @@
         <v>341</v>
       </c>
       <c r="B341" s="1">
-        <v>119.7591818796765</v>
+        <v>115.7216090201991</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -5197,7 +4852,7 @@
         <v>342</v>
       </c>
       <c r="B342" s="1">
-        <v>119.8158624160783</v>
+        <v>115.8265822740889</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -5205,7 +4860,7 @@
         <v>343</v>
       </c>
       <c r="B343" s="1">
-        <v>119.8291333895149</v>
+        <v>115.829917451294</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -5213,7 +4868,7 @@
         <v>344</v>
       </c>
       <c r="B344" s="1">
-        <v>119.9505124360234</v>
+        <v>115.845339150896</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -5221,7 +4876,7 @@
         <v>345</v>
       </c>
       <c r="B345" s="1">
-        <v>119.9988628443847</v>
+        <v>115.8740542089406</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -5229,7 +4884,7 @@
         <v>346</v>
       </c>
       <c r="B346" s="1">
-        <v>120.0058867698036</v>
+        <v>115.9144886810343</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -5237,7 +4892,7 @@
         <v>347</v>
       </c>
       <c r="B347" s="1">
-        <v>120.0449194225551</v>
+        <v>115.9301086701104</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -5245,7 +4900,7 @@
         <v>348</v>
       </c>
       <c r="B348" s="1">
-        <v>120.1226387704862</v>
+        <v>115.9320673319638</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -5253,7 +4908,7 @@
         <v>349</v>
       </c>
       <c r="B349" s="1">
-        <v>120.1736089649266</v>
+        <v>115.937681532248</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -5261,7 +4916,7 @@
         <v>350</v>
       </c>
       <c r="B350" s="1">
-        <v>120.1765416181346</v>
+        <v>115.9902527637389</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -5269,7 +4924,7 @@
         <v>351</v>
       </c>
       <c r="B351" s="1">
-        <v>120.2173606811577</v>
+        <v>116.010271207563</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -5277,7 +4932,7 @@
         <v>352</v>
       </c>
       <c r="B352" s="1">
-        <v>120.2306526520568</v>
+        <v>116.0292105640367</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -5285,7 +4940,7 @@
         <v>353</v>
       </c>
       <c r="B353" s="1">
-        <v>120.2396645325777</v>
+        <v>116.0410838505859</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -5293,7 +4948,7 @@
         <v>354</v>
       </c>
       <c r="B354" s="1">
-        <v>120.2446735690673</v>
+        <v>116.0524290095144</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -5301,7 +4956,7 @@
         <v>355</v>
       </c>
       <c r="B355" s="1">
-        <v>120.2766450974419</v>
+        <v>116.088737347627</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -5309,7 +4964,7 @@
         <v>356</v>
       </c>
       <c r="B356" s="1">
-        <v>120.3653902318826</v>
+        <v>116.2645310456672</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -5317,7 +4972,7 @@
         <v>357</v>
       </c>
       <c r="B357" s="1">
-        <v>120.3718642953306</v>
+        <v>116.2731443768865</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -5325,7 +4980,7 @@
         <v>358</v>
       </c>
       <c r="B358" s="1">
-        <v>120.3801375065622</v>
+        <v>116.2957740988703</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -5333,7 +4988,7 @@
         <v>359</v>
       </c>
       <c r="B359" s="1">
-        <v>120.4008868860399</v>
+        <v>116.3682240589537</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -5341,7 +4996,7 @@
         <v>360</v>
       </c>
       <c r="B360" s="1">
-        <v>120.5144155321002</v>
+        <v>116.3749427588767</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -5349,7 +5004,7 @@
         <v>361</v>
       </c>
       <c r="B361" s="1">
-        <v>120.7230965113951</v>
+        <v>116.3848393543873</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -5357,7 +5012,7 @@
         <v>362</v>
       </c>
       <c r="B362" s="1">
-        <v>120.7830465501431</v>
+        <v>116.4244740252939</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -5365,7 +5020,7 @@
         <v>363</v>
       </c>
       <c r="B363" s="1">
-        <v>120.8080637530113</v>
+        <v>116.4800639813238</v>
       </c>
     </row>
     <row r="364" spans="1:2">
@@ -5373,7 +5028,7 @@
         <v>364</v>
       </c>
       <c r="B364" s="1">
-        <v>120.8574010136578</v>
+        <v>116.4991425494964</v>
       </c>
     </row>
     <row r="365" spans="1:2">
@@ -5381,7 +5036,7 @@
         <v>365</v>
       </c>
       <c r="B365" s="1">
-        <v>120.8859355540577</v>
+        <v>116.4992092849209</v>
       </c>
     </row>
     <row r="366" spans="1:2">
@@ -5389,7 +5044,7 @@
         <v>366</v>
       </c>
       <c r="B366" s="1">
-        <v>120.9219453870675</v>
+        <v>116.5999449714447</v>
       </c>
     </row>
     <row r="367" spans="1:2">
@@ -5397,7 +5052,7 @@
         <v>367</v>
       </c>
       <c r="B367" s="1">
-        <v>121.0062555833693</v>
+        <v>116.6271738760636</v>
       </c>
     </row>
     <row r="368" spans="1:2">
@@ -5405,7 +5060,7 @@
         <v>368</v>
       </c>
       <c r="B368" s="1">
-        <v>121.0291612184205</v>
+        <v>116.7004096602823</v>
       </c>
     </row>
     <row r="369" spans="1:2">
@@ -5413,7 +5068,7 @@
         <v>369</v>
       </c>
       <c r="B369" s="1">
-        <v>121.0694316583474</v>
+        <v>116.7964998762489</v>
       </c>
     </row>
     <row r="370" spans="1:2">
@@ -5421,7 +5076,7 @@
         <v>370</v>
       </c>
       <c r="B370" s="1">
-        <v>121.1628689270335</v>
+        <v>116.8773223809925</v>
       </c>
     </row>
     <row r="371" spans="1:2">
@@ -5429,7 +5084,7 @@
         <v>371</v>
       </c>
       <c r="B371" s="1">
-        <v>121.1861746419489</v>
+        <v>116.9128007420371</v>
       </c>
     </row>
     <row r="372" spans="1:2">
@@ -5437,7 +5092,7 @@
         <v>372</v>
       </c>
       <c r="B372" s="1">
-        <v>121.1962094394326</v>
+        <v>116.9934341144478</v>
       </c>
     </row>
     <row r="373" spans="1:2">
@@ -5445,7 +5100,7 @@
         <v>373</v>
       </c>
       <c r="B373" s="1">
-        <v>121.1963541098772</v>
+        <v>116.9948092231751</v>
       </c>
     </row>
     <row r="374" spans="1:2">
@@ -5453,7 +5108,7 @@
         <v>374</v>
       </c>
       <c r="B374" s="1">
-        <v>121.3165976896054</v>
+        <v>116.9975564459318</v>
       </c>
     </row>
     <row r="375" spans="1:2">
@@ -5461,7 +5116,7 @@
         <v>375</v>
       </c>
       <c r="B375" s="1">
-        <v>121.344304065057</v>
+        <v>117.0228895669501</v>
       </c>
     </row>
     <row r="376" spans="1:2">
@@ -5469,7 +5124,7 @@
         <v>376</v>
       </c>
       <c r="B376" s="1">
-        <v>121.3477086103811</v>
+        <v>117.0879180329212</v>
       </c>
     </row>
     <row r="377" spans="1:2">
@@ -5477,7 +5132,7 @@
         <v>377</v>
       </c>
       <c r="B377" s="1">
-        <v>121.4034035359424</v>
+        <v>117.1109998694368</v>
       </c>
     </row>
     <row r="378" spans="1:2">
@@ -5485,7 +5140,7 @@
         <v>378</v>
       </c>
       <c r="B378" s="1">
-        <v>121.4778194105959</v>
+        <v>117.1305494743791</v>
       </c>
     </row>
     <row r="379" spans="1:2">
@@ -5493,7 +5148,7 @@
         <v>379</v>
       </c>
       <c r="B379" s="1">
-        <v>121.4897626159857</v>
+        <v>117.1836386310932</v>
       </c>
     </row>
     <row r="380" spans="1:2">
@@ -5501,7 +5156,7 @@
         <v>380</v>
       </c>
       <c r="B380" s="1">
-        <v>121.5203168575304</v>
+        <v>117.227920080178</v>
       </c>
     </row>
     <row r="381" spans="1:2">
@@ -5509,7 +5164,7 @@
         <v>381</v>
       </c>
       <c r="B381" s="1">
-        <v>121.532812089473</v>
+        <v>117.2690581788951</v>
       </c>
     </row>
     <row r="382" spans="1:2">
@@ -5517,7 +5172,7 @@
         <v>382</v>
       </c>
       <c r="B382" s="1">
-        <v>121.5347912055628</v>
+        <v>117.5031202789068</v>
       </c>
     </row>
     <row r="383" spans="1:2">
@@ -5525,7 +5180,7 @@
         <v>383</v>
       </c>
       <c r="B383" s="1">
-        <v>121.5625219798987</v>
+        <v>117.5089484306562</v>
       </c>
     </row>
     <row r="384" spans="1:2">
@@ -5533,7 +5188,7 @@
         <v>384</v>
       </c>
       <c r="B384" s="1">
-        <v>121.5815979644305</v>
+        <v>117.603320318912</v>
       </c>
     </row>
     <row r="385" spans="1:2">
@@ -5541,7 +5196,7 @@
         <v>385</v>
       </c>
       <c r="B385" s="1">
-        <v>121.5825541871181</v>
+        <v>117.6491846810969</v>
       </c>
     </row>
     <row r="386" spans="1:2">
@@ -5549,7 +5204,7 @@
         <v>386</v>
       </c>
       <c r="B386" s="1">
-        <v>121.5838560267638</v>
+        <v>117.6507347180145</v>
       </c>
     </row>
     <row r="387" spans="1:2">
@@ -5557,7 +5212,7 @@
         <v>387</v>
       </c>
       <c r="B387" s="1">
-        <v>121.6535278130965</v>
+        <v>117.6666880307988</v>
       </c>
     </row>
     <row r="388" spans="1:2">
@@ -5565,7 +5220,7 @@
         <v>388</v>
       </c>
       <c r="B388" s="1">
-        <v>121.7052632689697</v>
+        <v>117.7692584816623</v>
       </c>
     </row>
     <row r="389" spans="1:2">
@@ -5573,7 +5228,7 @@
         <v>389</v>
       </c>
       <c r="B389" s="1">
-        <v>121.7423774680662</v>
+        <v>117.7781201362049</v>
       </c>
     </row>
     <row r="390" spans="1:2">
@@ -5581,7 +5236,7 @@
         <v>390</v>
       </c>
       <c r="B390" s="1">
-        <v>121.8636656704172</v>
+        <v>117.8378071403499</v>
       </c>
     </row>
     <row r="391" spans="1:2">
@@ -5589,7 +5244,7 @@
         <v>391</v>
       </c>
       <c r="B391" s="1">
-        <v>121.8718360235135</v>
+        <v>117.9086296003225</v>
       </c>
     </row>
     <row r="392" spans="1:2">
@@ -5597,7 +5252,7 @@
         <v>392</v>
       </c>
       <c r="B392" s="1">
-        <v>122.0070512101737</v>
+        <v>117.949498628659</v>
       </c>
     </row>
     <row r="393" spans="1:2">
@@ -5605,7 +5260,7 @@
         <v>393</v>
       </c>
       <c r="B393" s="1">
-        <v>122.0809046427897</v>
+        <v>118.0446931849822</v>
       </c>
     </row>
     <row r="394" spans="1:2">
@@ -5613,7 +5268,7 @@
         <v>394</v>
       </c>
       <c r="B394" s="1">
-        <v>122.095223885909</v>
+        <v>118.0795202186806</v>
       </c>
     </row>
     <row r="395" spans="1:2">
@@ -5621,7 +5276,7 @@
         <v>395</v>
       </c>
       <c r="B395" s="1">
-        <v>122.1023879976139</v>
+        <v>118.1186607382177</v>
       </c>
     </row>
     <row r="396" spans="1:2">
@@ -5629,7 +5284,7 @@
         <v>396</v>
       </c>
       <c r="B396" s="1">
-        <v>122.2182882230829</v>
+        <v>118.1566117140939</v>
       </c>
     </row>
     <row r="397" spans="1:2">
@@ -5637,7 +5292,7 @@
         <v>397</v>
       </c>
       <c r="B397" s="1">
-        <v>122.2989965321824</v>
+        <v>118.2014260646295</v>
       </c>
     </row>
     <row r="398" spans="1:2">
@@ -5645,7 +5300,7 @@
         <v>398</v>
       </c>
       <c r="B398" s="1">
-        <v>122.3223995875286</v>
+        <v>118.2143320331007</v>
       </c>
     </row>
     <row r="399" spans="1:2">
@@ -5653,7 +5308,7 @@
         <v>399</v>
       </c>
       <c r="B399" s="1">
-        <v>122.3372908988925</v>
+        <v>118.3543473227393</v>
       </c>
     </row>
     <row r="400" spans="1:2">
@@ -5661,7 +5316,7 @@
         <v>400</v>
       </c>
       <c r="B400" s="1">
-        <v>122.3906126505646</v>
+        <v>118.3744149403439</v>
       </c>
     </row>
     <row r="401" spans="1:2">
@@ -5669,7 +5324,7 @@
         <v>401</v>
       </c>
       <c r="B401" s="1">
-        <v>122.4351025069768</v>
+        <v>118.3814121274494</v>
       </c>
     </row>
     <row r="402" spans="1:2">
@@ -5677,7 +5332,7 @@
         <v>402</v>
       </c>
       <c r="B402" s="1">
-        <v>122.4515750704276</v>
+        <v>118.4060257802477</v>
       </c>
     </row>
     <row r="403" spans="1:2">
@@ -5685,7 +5340,7 @@
         <v>403</v>
       </c>
       <c r="B403" s="1">
-        <v>122.5205920212276</v>
+        <v>118.4113406216315</v>
       </c>
     </row>
     <row r="404" spans="1:2">
@@ -5693,7 +5348,7 @@
         <v>404</v>
       </c>
       <c r="B404" s="1">
-        <v>122.6290816731153</v>
+        <v>118.5006237871265</v>
       </c>
     </row>
     <row r="405" spans="1:2">
@@ -5701,7 +5356,7 @@
         <v>405</v>
       </c>
       <c r="B405" s="1">
-        <v>122.6522939412293</v>
+        <v>118.5928081497532</v>
       </c>
     </row>
     <row r="406" spans="1:2">
@@ -5709,7 +5364,7 @@
         <v>406</v>
       </c>
       <c r="B406" s="1">
-        <v>122.7110564756402</v>
+        <v>118.6027371379308</v>
       </c>
     </row>
     <row r="407" spans="1:2">
@@ -5717,7 +5372,7 @@
         <v>407</v>
       </c>
       <c r="B407" s="1">
-        <v>122.8413433957595</v>
+        <v>118.6847165924409</v>
       </c>
     </row>
     <row r="408" spans="1:2">
@@ -5725,7 +5380,7 @@
         <v>408</v>
       </c>
       <c r="B408" s="1">
-        <v>122.8487896702169</v>
+        <v>118.7040145312785</v>
       </c>
     </row>
     <row r="409" spans="1:2">
@@ -5733,7 +5388,7 @@
         <v>409</v>
       </c>
       <c r="B409" s="1">
-        <v>122.8732279937168</v>
+        <v>118.8475888972588</v>
       </c>
     </row>
     <row r="410" spans="1:2">
@@ -5741,7 +5396,7 @@
         <v>410</v>
       </c>
       <c r="B410" s="1">
-        <v>122.9019764865729</v>
+        <v>118.8651255641355</v>
       </c>
     </row>
     <row r="411" spans="1:2">
@@ -5749,7 +5404,7 @@
         <v>411</v>
       </c>
       <c r="B411" s="1">
-        <v>122.9220066433827</v>
+        <v>118.8874586324447</v>
       </c>
     </row>
     <row r="412" spans="1:2">
@@ -5757,7 +5412,7 @@
         <v>412</v>
       </c>
       <c r="B412" s="1">
-        <v>123.114743882014</v>
+        <v>118.911334607628</v>
       </c>
     </row>
     <row r="413" spans="1:2">
@@ -5765,7 +5420,7 @@
         <v>413</v>
       </c>
       <c r="B413" s="1">
-        <v>123.1408839568825</v>
+        <v>118.9122088333161</v>
       </c>
     </row>
     <row r="414" spans="1:2">
@@ -5773,7 +5428,7 @@
         <v>414</v>
       </c>
       <c r="B414" s="1">
-        <v>123.1803006419766</v>
+        <v>118.9502244537876</v>
       </c>
     </row>
     <row r="415" spans="1:2">
@@ -5781,7 +5436,7 @@
         <v>415</v>
       </c>
       <c r="B415" s="1">
-        <v>123.2115856089457</v>
+        <v>119.0120162725098</v>
       </c>
     </row>
     <row r="416" spans="1:2">
@@ -5789,7 +5444,7 @@
         <v>416</v>
       </c>
       <c r="B416" s="1">
-        <v>123.2294412423071</v>
+        <v>119.051930589079</v>
       </c>
     </row>
     <row r="417" spans="1:2">
@@ -5797,7 +5452,7 @@
         <v>417</v>
       </c>
       <c r="B417" s="1">
-        <v>123.3070287918925</v>
+        <v>119.2395992182971</v>
       </c>
     </row>
     <row r="418" spans="1:2">
@@ -5805,7 +5460,7 @@
         <v>418</v>
       </c>
       <c r="B418" s="1">
-        <v>123.3161985822766</v>
+        <v>119.3689727245629</v>
       </c>
     </row>
     <row r="419" spans="1:2">
@@ -5813,7 +5468,7 @@
         <v>419</v>
       </c>
       <c r="B419" s="1">
-        <v>123.3409516592568</v>
+        <v>119.5050727245786</v>
       </c>
     </row>
     <row r="420" spans="1:2">
@@ -5821,7 +5476,7 @@
         <v>420</v>
       </c>
       <c r="B420" s="1">
-        <v>123.3762609542272</v>
+        <v>119.5816341242625</v>
       </c>
     </row>
     <row r="421" spans="1:2">
@@ -5829,7 +5484,7 @@
         <v>421</v>
       </c>
       <c r="B421" s="1">
-        <v>123.420710320796</v>
+        <v>119.6384820083467</v>
       </c>
     </row>
     <row r="422" spans="1:2">
@@ -5837,7 +5492,7 @@
         <v>422</v>
       </c>
       <c r="B422" s="1">
-        <v>123.4277833718676</v>
+        <v>119.7100940064157</v>
       </c>
     </row>
     <row r="423" spans="1:2">
@@ -5845,7 +5500,7 @@
         <v>423</v>
       </c>
       <c r="B423" s="1">
-        <v>123.4311380773394</v>
+        <v>119.7523530332266</v>
       </c>
     </row>
     <row r="424" spans="1:2">
@@ -5853,7 +5508,7 @@
         <v>424</v>
       </c>
       <c r="B424" s="1">
-        <v>123.4399765096335</v>
+        <v>119.7824064441706</v>
       </c>
     </row>
     <row r="425" spans="1:2">
@@ -5861,7 +5516,7 @@
         <v>425</v>
       </c>
       <c r="B425" s="1">
-        <v>123.4456319038048</v>
+        <v>119.8065325987272</v>
       </c>
     </row>
     <row r="426" spans="1:2">
@@ -5869,7 +5524,7 @@
         <v>426</v>
       </c>
       <c r="B426" s="1">
-        <v>123.51601358472</v>
+        <v>119.8258826737704</v>
       </c>
     </row>
     <row r="427" spans="1:2">
@@ -5877,7 +5532,7 @@
         <v>427</v>
       </c>
       <c r="B427" s="1">
-        <v>123.5250973819992</v>
+        <v>119.8380254115107</v>
       </c>
     </row>
     <row r="428" spans="1:2">
@@ -5885,7 +5540,7 @@
         <v>428</v>
       </c>
       <c r="B428" s="1">
-        <v>123.5267924922484</v>
+        <v>120.0532545090909</v>
       </c>
     </row>
     <row r="429" spans="1:2">
@@ -5893,7 +5548,7 @@
         <v>429</v>
       </c>
       <c r="B429" s="1">
-        <v>123.5384005897132</v>
+        <v>120.0928434829588</v>
       </c>
     </row>
     <row r="430" spans="1:2">
@@ -5901,7 +5556,7 @@
         <v>430</v>
       </c>
       <c r="B430" s="1">
-        <v>123.5412492139322</v>
+        <v>120.2328854892706</v>
       </c>
     </row>
     <row r="431" spans="1:2">
@@ -5909,7 +5564,7 @@
         <v>431</v>
       </c>
       <c r="B431" s="1">
-        <v>123.5580743178528</v>
+        <v>120.2745953240478</v>
       </c>
     </row>
     <row r="432" spans="1:2">
@@ -5917,7 +5572,7 @@
         <v>432</v>
       </c>
       <c r="B432" s="1">
-        <v>123.6379186140544</v>
+        <v>120.3470390348873</v>
       </c>
     </row>
     <row r="433" spans="1:2">
@@ -5925,7 +5580,7 @@
         <v>433</v>
       </c>
       <c r="B433" s="1">
-        <v>123.697015347881</v>
+        <v>120.3905271166615</v>
       </c>
     </row>
     <row r="434" spans="1:2">
@@ -5933,7 +5588,7 @@
         <v>434</v>
       </c>
       <c r="B434" s="1">
-        <v>123.81821702582</v>
+        <v>120.4402075325492</v>
       </c>
     </row>
     <row r="435" spans="1:2">
@@ -5941,7 +5596,7 @@
         <v>435</v>
       </c>
       <c r="B435" s="1">
-        <v>123.8260083492633</v>
+        <v>120.4427663010336</v>
       </c>
     </row>
     <row r="436" spans="1:2">
@@ -5949,7 +5604,7 @@
         <v>436</v>
       </c>
       <c r="B436" s="1">
-        <v>123.8434905102079</v>
+        <v>120.4618532780922</v>
       </c>
     </row>
     <row r="437" spans="1:2">
@@ -5957,7 +5612,7 @@
         <v>437</v>
       </c>
       <c r="B437" s="1">
-        <v>123.9437050003249</v>
+        <v>120.52138453317</v>
       </c>
     </row>
     <row r="438" spans="1:2">
@@ -5965,7 +5620,7 @@
         <v>438</v>
       </c>
       <c r="B438" s="1">
-        <v>124.1215811521256</v>
+        <v>120.5583675495176</v>
       </c>
     </row>
     <row r="439" spans="1:2">
@@ -5973,7 +5628,7 @@
         <v>439</v>
       </c>
       <c r="B439" s="1">
-        <v>124.1524852589919</v>
+        <v>120.5708617062005</v>
       </c>
     </row>
     <row r="440" spans="1:2">
@@ -5981,7 +5636,7 @@
         <v>440</v>
       </c>
       <c r="B440" s="1">
-        <v>124.208487961111</v>
+        <v>120.6588458783167</v>
       </c>
     </row>
     <row r="441" spans="1:2">
@@ -5989,7 +5644,7 @@
         <v>441</v>
       </c>
       <c r="B441" s="1">
-        <v>124.2227849517624</v>
+        <v>120.7199769179737</v>
       </c>
     </row>
     <row r="442" spans="1:2">
@@ -5997,7 +5652,7 @@
         <v>442</v>
       </c>
       <c r="B442" s="1">
-        <v>124.38796792896</v>
+        <v>120.7918003457622</v>
       </c>
     </row>
     <row r="443" spans="1:2">
@@ -6005,7 +5660,7 @@
         <v>443</v>
       </c>
       <c r="B443" s="1">
-        <v>124.4058861986366</v>
+        <v>121.0391568352772</v>
       </c>
     </row>
     <row r="444" spans="1:2">
@@ -6013,7 +5668,7 @@
         <v>444</v>
       </c>
       <c r="B444" s="1">
-        <v>124.6504775113191</v>
+        <v>121.4050517606745</v>
       </c>
     </row>
     <row r="445" spans="1:2">
@@ -6021,7 +5676,7 @@
         <v>445</v>
       </c>
       <c r="B445" s="1">
-        <v>124.8259021311593</v>
+        <v>121.491921563381</v>
       </c>
     </row>
     <row r="446" spans="1:2">
@@ -6029,7 +5684,7 @@
         <v>446</v>
       </c>
       <c r="B446" s="1">
-        <v>124.8681684992617</v>
+        <v>121.5758717440222</v>
       </c>
     </row>
     <row r="447" spans="1:2">
@@ -6037,7 +5692,7 @@
         <v>447</v>
       </c>
       <c r="B447" s="1">
-        <v>125.0150267295282</v>
+        <v>121.6183818685245</v>
       </c>
     </row>
     <row r="448" spans="1:2">
@@ -6045,7 +5700,7 @@
         <v>448</v>
       </c>
       <c r="B448" s="1">
-        <v>125.0620754250666</v>
+        <v>121.6204437379186</v>
       </c>
     </row>
     <row r="449" spans="1:2">
@@ -6053,7 +5708,7 @@
         <v>449</v>
       </c>
       <c r="B449" s="1">
-        <v>125.0711970599482</v>
+        <v>121.6721571617931</v>
       </c>
     </row>
     <row r="450" spans="1:2">
@@ -6061,7 +5716,7 @@
         <v>450</v>
       </c>
       <c r="B450" s="1">
-        <v>125.1347118185246</v>
+        <v>121.7386660345313</v>
       </c>
     </row>
     <row r="451" spans="1:2">
@@ -6069,7 +5724,7 @@
         <v>451</v>
       </c>
       <c r="B451" s="1">
-        <v>125.3009333862144</v>
+        <v>122.0214444842703</v>
       </c>
     </row>
     <row r="452" spans="1:2">
@@ -6077,7 +5732,7 @@
         <v>452</v>
       </c>
       <c r="B452" s="1">
-        <v>125.3529799360454</v>
+        <v>122.0662677526282</v>
       </c>
     </row>
     <row r="453" spans="1:2">
@@ -6085,7 +5740,7 @@
         <v>453</v>
       </c>
       <c r="B453" s="1">
-        <v>125.384078354756</v>
+        <v>122.1588812415722</v>
       </c>
     </row>
     <row r="454" spans="1:2">
@@ -6093,7 +5748,7 @@
         <v>454</v>
       </c>
       <c r="B454" s="1">
-        <v>125.3949571161905</v>
+        <v>122.2400466012957</v>
       </c>
     </row>
     <row r="455" spans="1:2">
@@ -6101,7 +5756,7 @@
         <v>455</v>
       </c>
       <c r="B455" s="1">
-        <v>125.4493404623136</v>
+        <v>122.2756813163186</v>
       </c>
     </row>
     <row r="456" spans="1:2">
@@ -6109,7 +5764,7 @@
         <v>456</v>
       </c>
       <c r="B456" s="1">
-        <v>125.556987610018</v>
+        <v>122.2939117360794</v>
       </c>
     </row>
     <row r="457" spans="1:2">
@@ -6117,7 +5772,7 @@
         <v>457</v>
       </c>
       <c r="B457" s="1">
-        <v>125.584443423033</v>
+        <v>122.3788144975987</v>
       </c>
     </row>
     <row r="458" spans="1:2">
@@ -6125,7 +5780,7 @@
         <v>458</v>
       </c>
       <c r="B458" s="1">
-        <v>125.5906165351075</v>
+        <v>122.5125488365846</v>
       </c>
     </row>
     <row r="459" spans="1:2">
@@ -6133,7 +5788,7 @@
         <v>459</v>
       </c>
       <c r="B459" s="1">
-        <v>125.5918082629295</v>
+        <v>122.5686836365075</v>
       </c>
     </row>
     <row r="460" spans="1:2">
@@ -6141,7 +5796,7 @@
         <v>460</v>
       </c>
       <c r="B460" s="1">
-        <v>125.6718558982489</v>
+        <v>122.6425595654766</v>
       </c>
     </row>
     <row r="461" spans="1:2">
@@ -6149,7 +5804,7 @@
         <v>461</v>
       </c>
       <c r="B461" s="1">
-        <v>125.7000027296969</v>
+        <v>122.7261139965673</v>
       </c>
     </row>
     <row r="462" spans="1:2">
@@ -6157,7 +5812,7 @@
         <v>462</v>
       </c>
       <c r="B462" s="1">
-        <v>125.7009974135933</v>
+        <v>122.767877137324</v>
       </c>
     </row>
     <row r="463" spans="1:2">
@@ -6165,7 +5820,7 @@
         <v>463</v>
       </c>
       <c r="B463" s="1">
-        <v>125.7059875172118</v>
+        <v>122.8005153745452</v>
       </c>
     </row>
     <row r="464" spans="1:2">
@@ -6173,7 +5828,7 @@
         <v>464</v>
       </c>
       <c r="B464" s="1">
-        <v>125.7657724814948</v>
+        <v>122.8632614207925</v>
       </c>
     </row>
     <row r="465" spans="1:2">
@@ -6181,7 +5836,7 @@
         <v>465</v>
       </c>
       <c r="B465" s="1">
-        <v>125.7809928606386</v>
+        <v>122.8913524250442</v>
       </c>
     </row>
     <row r="466" spans="1:2">
@@ -6189,7 +5844,7 @@
         <v>466</v>
       </c>
       <c r="B466" s="1">
-        <v>126.0291628117029</v>
+        <v>122.9846416183081</v>
       </c>
     </row>
     <row r="467" spans="1:2">
@@ -6197,7 +5852,7 @@
         <v>467</v>
       </c>
       <c r="B467" s="1">
-        <v>126.0311331602815</v>
+        <v>123.0907875084756</v>
       </c>
     </row>
     <row r="468" spans="1:2">
@@ -6205,7 +5860,7 @@
         <v>468</v>
       </c>
       <c r="B468" s="1">
-        <v>126.0648096559013</v>
+        <v>123.2384337356775</v>
       </c>
     </row>
     <row r="469" spans="1:2">
@@ -6213,7 +5868,7 @@
         <v>469</v>
       </c>
       <c r="B469" s="1">
-        <v>126.0672480666567</v>
+        <v>123.2432342387912</v>
       </c>
     </row>
     <row r="470" spans="1:2">
@@ -6221,7 +5876,7 @@
         <v>470</v>
       </c>
       <c r="B470" s="1">
-        <v>126.0695090562286</v>
+        <v>123.3023791117422</v>
       </c>
     </row>
     <row r="471" spans="1:2">
@@ -6229,7 +5884,7 @@
         <v>471</v>
       </c>
       <c r="B471" s="1">
-        <v>126.2241049953675</v>
+        <v>123.3933159242183</v>
       </c>
     </row>
     <row r="472" spans="1:2">
@@ -6237,7 +5892,7 @@
         <v>472</v>
       </c>
       <c r="B472" s="1">
-        <v>126.2529543750576</v>
+        <v>123.4403554316374</v>
       </c>
     </row>
     <row r="473" spans="1:2">
@@ -6245,7 +5900,7 @@
         <v>473</v>
       </c>
       <c r="B473" s="1">
-        <v>126.2732106555858</v>
+        <v>123.4773562131466</v>
       </c>
     </row>
     <row r="474" spans="1:2">
@@ -6253,7 +5908,7 @@
         <v>474</v>
       </c>
       <c r="B474" s="1">
-        <v>126.2970657133525</v>
+        <v>123.6151470456042</v>
       </c>
     </row>
     <row r="475" spans="1:2">
@@ -6261,7 +5916,7 @@
         <v>475</v>
       </c>
       <c r="B475" s="1">
-        <v>126.4664380018667</v>
+        <v>123.6780967432296</v>
       </c>
     </row>
     <row r="476" spans="1:2">
@@ -6269,7 +5924,7 @@
         <v>476</v>
       </c>
       <c r="B476" s="1">
-        <v>126.486946505697</v>
+        <v>123.9254955958413</v>
       </c>
     </row>
     <row r="477" spans="1:2">
@@ -6277,7 +5932,7 @@
         <v>477</v>
       </c>
       <c r="B477" s="1">
-        <v>126.4931872900777</v>
+        <v>124.0309835777498</v>
       </c>
     </row>
     <row r="478" spans="1:2">
@@ -6285,7 +5940,7 @@
         <v>478</v>
       </c>
       <c r="B478" s="1">
-        <v>126.519239383953</v>
+        <v>124.1678320326571</v>
       </c>
     </row>
     <row r="479" spans="1:2">
@@ -6293,7 +5948,7 @@
         <v>479</v>
       </c>
       <c r="B479" s="1">
-        <v>126.6358065017426</v>
+        <v>124.1830862164171</v>
       </c>
     </row>
     <row r="480" spans="1:2">
@@ -6301,7 +5956,7 @@
         <v>480</v>
       </c>
       <c r="B480" s="1">
-        <v>126.6604639433654</v>
+        <v>124.2757389277149</v>
       </c>
     </row>
     <row r="481" spans="1:2">
@@ -6309,7 +5964,7 @@
         <v>481</v>
       </c>
       <c r="B481" s="1">
-        <v>126.7416446758697</v>
+        <v>124.380918102284</v>
       </c>
     </row>
     <row r="482" spans="1:2">
@@ -6317,7 +5972,7 @@
         <v>482</v>
       </c>
       <c r="B482" s="1">
-        <v>126.8577129665163</v>
+        <v>124.3815163367396</v>
       </c>
     </row>
     <row r="483" spans="1:2">
@@ -6325,7 +5980,7 @@
         <v>483</v>
       </c>
       <c r="B483" s="1">
-        <v>127.0173399767462</v>
+        <v>124.7026795301294</v>
       </c>
     </row>
     <row r="484" spans="1:2">
@@ -6333,7 +5988,7 @@
         <v>484</v>
       </c>
       <c r="B484" s="1">
-        <v>127.0532379499545</v>
+        <v>124.8255894775848</v>
       </c>
     </row>
     <row r="485" spans="1:2">
@@ -6341,7 +5996,7 @@
         <v>485</v>
       </c>
       <c r="B485" s="1">
-        <v>127.1127038812048</v>
+        <v>124.8305019491684</v>
       </c>
     </row>
     <row r="486" spans="1:2">
@@ -6349,7 +6004,7 @@
         <v>486</v>
       </c>
       <c r="B486" s="1">
-        <v>127.167937512669</v>
+        <v>124.8446720167587</v>
       </c>
     </row>
     <row r="487" spans="1:2">
@@ -6357,7 +6012,7 @@
         <v>487</v>
       </c>
       <c r="B487" s="1">
-        <v>127.1954348380616</v>
+        <v>125.0722353485012</v>
       </c>
     </row>
     <row r="488" spans="1:2">
@@ -6365,7 +6020,7 @@
         <v>488</v>
       </c>
       <c r="B488" s="1">
-        <v>127.2508796955543</v>
+        <v>125.0853668547446</v>
       </c>
     </row>
     <row r="489" spans="1:2">
@@ -6373,7 +6028,7 @@
         <v>489</v>
       </c>
       <c r="B489" s="1">
-        <v>127.2745294940574</v>
+        <v>125.130114440068</v>
       </c>
     </row>
     <row r="490" spans="1:2">
@@ -6381,7 +6036,7 @@
         <v>490</v>
       </c>
       <c r="B490" s="1">
-        <v>127.3965049204594</v>
+        <v>125.1766527855865</v>
       </c>
     </row>
     <row r="491" spans="1:2">
@@ -6389,7 +6044,7 @@
         <v>491</v>
       </c>
       <c r="B491" s="1">
-        <v>127.5181431004925</v>
+        <v>125.4042423570102</v>
       </c>
     </row>
     <row r="492" spans="1:2">
@@ -6397,7 +6052,7 @@
         <v>492</v>
       </c>
       <c r="B492" s="1">
-        <v>127.5280351133209</v>
+        <v>125.4112620905138</v>
       </c>
     </row>
     <row r="493" spans="1:2">
@@ -6405,7 +6060,7 @@
         <v>493</v>
       </c>
       <c r="B493" s="1">
-        <v>127.5361489046046</v>
+        <v>125.6057423862624</v>
       </c>
     </row>
     <row r="494" spans="1:2">
@@ -6413,7 +6068,7 @@
         <v>494</v>
       </c>
       <c r="B494" s="1">
-        <v>127.558938187346</v>
+        <v>125.7045193016981</v>
       </c>
     </row>
     <row r="495" spans="1:2">
@@ -6421,7 +6076,7 @@
         <v>495</v>
       </c>
       <c r="B495" s="1">
-        <v>127.6144875116743</v>
+        <v>125.7310539936156</v>
       </c>
     </row>
     <row r="496" spans="1:2">
@@ -6429,7 +6084,7 @@
         <v>496</v>
       </c>
       <c r="B496" s="1">
-        <v>127.7318940370957</v>
+        <v>125.7958372055574</v>
       </c>
     </row>
     <row r="497" spans="1:2">
@@ -6437,7 +6092,7 @@
         <v>497</v>
       </c>
       <c r="B497" s="1">
-        <v>127.8013864682144</v>
+        <v>125.8411763674321</v>
       </c>
     </row>
     <row r="498" spans="1:2">
@@ -6445,7 +6100,7 @@
         <v>498</v>
       </c>
       <c r="B498" s="1">
-        <v>127.9636854046595</v>
+        <v>125.8970597752992</v>
       </c>
     </row>
     <row r="499" spans="1:2">
@@ -6453,7 +6108,7 @@
         <v>499</v>
       </c>
       <c r="B499" s="1">
-        <v>128.0442821451672</v>
+        <v>126.0981719924856</v>
       </c>
     </row>
     <row r="500" spans="1:2">
@@ -6461,7 +6116,7 @@
         <v>500</v>
       </c>
       <c r="B500" s="1">
-        <v>128.0606959332799</v>
+        <v>126.3679871185055</v>
       </c>
     </row>
     <row r="501" spans="1:2">
@@ -6469,7 +6124,7 @@
         <v>501</v>
       </c>
       <c r="B501" s="1">
-        <v>128.0621452797156</v>
+        <v>126.7724306046017</v>
       </c>
     </row>
     <row r="502" spans="1:2">
@@ -6477,7 +6132,7 @@
         <v>502</v>
       </c>
       <c r="B502" s="1">
-        <v>128.1182759372876</v>
+        <v>126.8316230404087</v>
       </c>
     </row>
     <row r="503" spans="1:2">
@@ -6485,7 +6140,7 @@
         <v>503</v>
       </c>
       <c r="B503" s="1">
-        <v>128.2139614929803</v>
+        <v>127.7046497215018</v>
       </c>
     </row>
     <row r="504" spans="1:2">
@@ -6493,7 +6148,7 @@
         <v>504</v>
       </c>
       <c r="B504" s="1">
-        <v>128.3030746041347</v>
+        <v>127.9425197087221</v>
       </c>
     </row>
     <row r="505" spans="1:2">
@@ -6501,7 +6156,7 @@
         <v>505</v>
       </c>
       <c r="B505" s="1">
-        <v>128.3243933503749</v>
+        <v>128.099279228371</v>
       </c>
     </row>
     <row r="506" spans="1:2">
@@ -6509,7 +6164,7 @@
         <v>506</v>
       </c>
       <c r="B506" s="1">
-        <v>128.3616354288569</v>
+        <v>128.3130465552071</v>
       </c>
     </row>
     <row r="507" spans="1:2">
@@ -6517,7 +6172,7 @@
         <v>507</v>
       </c>
       <c r="B507" s="1">
-        <v>128.4290354031858</v>
+        <v>128.343588251484</v>
       </c>
     </row>
     <row r="508" spans="1:2">
@@ -6525,7 +6180,7 @@
         <v>508</v>
       </c>
       <c r="B508" s="1">
-        <v>128.4483654654748</v>
+        <v>128.7185407755414</v>
       </c>
     </row>
     <row r="509" spans="1:2">
@@ -6533,7 +6188,7 @@
         <v>509</v>
       </c>
       <c r="B509" s="1">
-        <v>128.6199041443911</v>
+        <v>128.759598226899</v>
       </c>
     </row>
     <row r="510" spans="1:2">
@@ -6541,7 +6196,7 @@
         <v>510</v>
       </c>
       <c r="B510" s="1">
-        <v>128.712741779611</v>
+        <v>128.7700575712931</v>
       </c>
     </row>
     <row r="511" spans="1:2">
@@ -6549,7 +6204,7 @@
         <v>511</v>
       </c>
       <c r="B511" s="1">
-        <v>128.7960306892861</v>
+        <v>128.8220281510526</v>
       </c>
     </row>
     <row r="512" spans="1:2">
@@ -6557,7 +6212,7 @@
         <v>512</v>
       </c>
       <c r="B512" s="1">
-        <v>128.8846516145133</v>
+        <v>129.3590255271221</v>
       </c>
     </row>
     <row r="513" spans="1:2">
@@ -6565,7 +6220,7 @@
         <v>513</v>
       </c>
       <c r="B513" s="1">
-        <v>128.9603119008748</v>
+        <v>129.6566506043779</v>
       </c>
     </row>
     <row r="514" spans="1:2">
@@ -6573,7 +6228,7 @@
         <v>514</v>
       </c>
       <c r="B514" s="1">
-        <v>129.0501498357382</v>
+        <v>129.7668675135713</v>
       </c>
     </row>
     <row r="515" spans="1:2">
@@ -6581,7 +6236,7 @@
         <v>515</v>
       </c>
       <c r="B515" s="1">
-        <v>129.1200490970912</v>
+        <v>130.0149776274214</v>
       </c>
     </row>
     <row r="516" spans="1:2">
@@ -6589,7 +6244,7 @@
         <v>516</v>
       </c>
       <c r="B516" s="1">
-        <v>129.3019187840006</v>
+        <v>130.3801278945924</v>
       </c>
     </row>
     <row r="517" spans="1:2">
@@ -6597,7 +6252,7 @@
         <v>517</v>
       </c>
       <c r="B517" s="1">
-        <v>129.4409220610737</v>
+        <v>130.4031560459095</v>
       </c>
     </row>
     <row r="518" spans="1:2">
@@ -6605,7 +6260,7 @@
         <v>518</v>
       </c>
       <c r="B518" s="1">
-        <v>129.4964603825232</v>
+        <v>130.4649817096896</v>
       </c>
     </row>
     <row r="519" spans="1:2">
@@ -6613,7 +6268,7 @@
         <v>519</v>
       </c>
       <c r="B519" s="1">
-        <v>129.5412430271703</v>
+        <v>130.6839483030402</v>
       </c>
     </row>
     <row r="520" spans="1:2">
@@ -6621,7 +6276,7 @@
         <v>520</v>
       </c>
       <c r="B520" s="1">
-        <v>130.0407161858954</v>
+        <v>130.7378099512932</v>
       </c>
     </row>
     <row r="521" spans="1:2">
@@ -6629,7 +6284,7 @@
         <v>521</v>
       </c>
       <c r="B521" s="1">
-        <v>130.0665596057445</v>
+        <v>130.7791240391813</v>
       </c>
     </row>
     <row r="522" spans="1:2">
@@ -6637,7 +6292,7 @@
         <v>522</v>
       </c>
       <c r="B522" s="1">
-        <v>130.1077495161769</v>
+        <v>130.9009048361881</v>
       </c>
     </row>
     <row r="523" spans="1:2">
@@ -6645,7 +6300,7 @@
         <v>523</v>
       </c>
       <c r="B523" s="1">
-        <v>130.121532716593</v>
+        <v>131.3455438382084</v>
       </c>
     </row>
     <row r="524" spans="1:2">
@@ -6653,7 +6308,7 @@
         <v>524</v>
       </c>
       <c r="B524" s="1">
-        <v>130.1394284013839</v>
+        <v>131.5298010001613</v>
       </c>
     </row>
     <row r="525" spans="1:2">
@@ -6661,7 +6316,7 @@
         <v>525</v>
       </c>
       <c r="B525" s="1">
-        <v>130.4536632947536</v>
+        <v>131.7392716765293</v>
       </c>
     </row>
     <row r="526" spans="1:2">
@@ -6669,7 +6324,7 @@
         <v>526</v>
       </c>
       <c r="B526" s="1">
-        <v>130.5851753932231</v>
+        <v>131.8333354078148</v>
       </c>
     </row>
     <row r="527" spans="1:2">
@@ -6677,7 +6332,7 @@
         <v>527</v>
       </c>
       <c r="B527" s="1">
-        <v>130.7549727236556</v>
+        <v>131.8594774018143</v>
       </c>
     </row>
     <row r="528" spans="1:2">
@@ -6685,7 +6340,7 @@
         <v>528</v>
       </c>
       <c r="B528" s="1">
-        <v>131.1708086767566</v>
+        <v>132.0761585792649</v>
       </c>
     </row>
     <row r="529" spans="1:2">
@@ -6693,7 +6348,7 @@
         <v>529</v>
       </c>
       <c r="B529" s="1">
-        <v>131.2493979631263</v>
+        <v>132.363279899657</v>
       </c>
     </row>
     <row r="530" spans="1:2">
@@ -6701,7 +6356,7 @@
         <v>530</v>
       </c>
       <c r="B530" s="1">
-        <v>131.272908043034</v>
+        <v>132.3918549050302</v>
       </c>
     </row>
     <row r="531" spans="1:2">
@@ -6709,7 +6364,7 @@
         <v>531</v>
       </c>
       <c r="B531" s="1">
-        <v>131.466809286564</v>
+        <v>132.913318189739</v>
       </c>
     </row>
     <row r="532" spans="1:2">
@@ -6717,7 +6372,7 @@
         <v>532</v>
       </c>
       <c r="B532" s="1">
-        <v>131.5347822079805</v>
+        <v>133.3945733635198</v>
       </c>
     </row>
     <row r="533" spans="1:2">
@@ -6725,7 +6380,7 @@
         <v>533</v>
       </c>
       <c r="B533" s="1">
-        <v>131.5403079572679</v>
+        <v>134.7534928629026</v>
       </c>
     </row>
     <row r="534" spans="1:2">
@@ -6733,7 +6388,7 @@
         <v>534</v>
       </c>
       <c r="B534" s="1">
-        <v>131.6714862370827</v>
+        <v>134.9620783687639</v>
       </c>
     </row>
     <row r="535" spans="1:2">
@@ -6741,7 +6396,7 @@
         <v>535</v>
       </c>
       <c r="B535" s="1">
-        <v>131.8154009097049</v>
+        <v>135.1110639089383</v>
       </c>
     </row>
     <row r="536" spans="1:2">
@@ -6749,7 +6404,7 @@
         <v>536</v>
       </c>
       <c r="B536" s="1">
-        <v>132.1078146657173</v>
+        <v>135.5793354647257</v>
       </c>
     </row>
     <row r="537" spans="1:2">
@@ -6757,7 +6412,7 @@
         <v>537</v>
       </c>
       <c r="B537" s="1">
-        <v>132.1440072510177</v>
+        <v>135.8069273097774</v>
       </c>
     </row>
     <row r="538" spans="1:2">
@@ -6765,7 +6420,7 @@
         <v>538</v>
       </c>
       <c r="B538" s="1">
-        <v>132.3543730000327</v>
+        <v>135.8101216079676</v>
       </c>
     </row>
     <row r="539" spans="1:2">
@@ -6773,7 +6428,7 @@
         <v>539</v>
       </c>
       <c r="B539" s="1">
-        <v>132.5418863478653</v>
+        <v>135.9573515974866</v>
       </c>
     </row>
     <row r="540" spans="1:2">
@@ -6781,7 +6436,7 @@
         <v>540</v>
       </c>
       <c r="B540" s="1">
-        <v>132.6742521943811</v>
+        <v>136.2084141459405</v>
       </c>
     </row>
     <row r="541" spans="1:2">
@@ -6789,7 +6444,7 @@
         <v>541</v>
       </c>
       <c r="B541" s="1">
-        <v>132.7205270505035</v>
+        <v>136.8703800717454</v>
       </c>
     </row>
     <row r="542" spans="1:2">
@@ -6797,7 +6452,7 @@
         <v>542</v>
       </c>
       <c r="B542" s="1">
-        <v>132.7412609730069</v>
+        <v>137.3697676371432</v>
       </c>
     </row>
     <row r="543" spans="1:2">
@@ -6805,7 +6460,7 @@
         <v>543</v>
       </c>
       <c r="B543" s="1">
-        <v>132.8628872352002</v>
+        <v>137.437170506547</v>
       </c>
     </row>
     <row r="544" spans="1:2">
@@ -6813,7 +6468,7 @@
         <v>544</v>
       </c>
       <c r="B544" s="1">
-        <v>132.9637063947944</v>
+        <v>137.891232981536</v>
       </c>
     </row>
     <row r="545" spans="1:2">
@@ -6821,7 +6476,7 @@
         <v>545</v>
       </c>
       <c r="B545" s="1">
-        <v>133.0916080022783</v>
+        <v>138.3320957158581</v>
       </c>
     </row>
     <row r="546" spans="1:2">
@@ -6829,7 +6484,7 @@
         <v>546</v>
       </c>
       <c r="B546" s="1">
-        <v>133.1440161899042</v>
+        <v>138.3438330488742</v>
       </c>
     </row>
     <row r="547" spans="1:2">
@@ -6837,7 +6492,7 @@
         <v>547</v>
       </c>
       <c r="B547" s="1">
-        <v>133.1644680579921</v>
+        <v>138.3761703217812</v>
       </c>
     </row>
     <row r="548" spans="1:2">
@@ -6845,7 +6500,7 @@
         <v>548</v>
       </c>
       <c r="B548" s="1">
-        <v>133.2576264796828</v>
+        <v>139.2781771713223</v>
       </c>
     </row>
     <row r="549" spans="1:2">
@@ -6853,7 +6508,7 @@
         <v>549</v>
       </c>
       <c r="B549" s="1">
-        <v>133.3285877111944</v>
+        <v>139.4772994551172</v>
       </c>
     </row>
     <row r="550" spans="1:2">
@@ -6861,7 +6516,7 @@
         <v>550</v>
       </c>
       <c r="B550" s="1">
-        <v>133.5947422615553</v>
+        <v>139.954136623105</v>
       </c>
     </row>
     <row r="551" spans="1:2">
@@ -6869,7 +6524,7 @@
         <v>551</v>
       </c>
       <c r="B551" s="1">
-        <v>133.5998703053228</v>
+        <v>140.1677560714863</v>
       </c>
     </row>
     <row r="552" spans="1:2">
@@ -6877,7 +6532,7 @@
         <v>552</v>
       </c>
       <c r="B552" s="1">
-        <v>133.8245673464926</v>
+        <v>140.2294729300898</v>
       </c>
     </row>
     <row r="553" spans="1:2">
@@ -6885,7 +6540,7 @@
         <v>553</v>
       </c>
       <c r="B553" s="1">
-        <v>133.8590783664626</v>
+        <v>144.9926954073103</v>
       </c>
     </row>
     <row r="554" spans="1:2">
@@ -6893,7 +6548,7 @@
         <v>554</v>
       </c>
       <c r="B554" s="1">
-        <v>133.9270330331991</v>
+        <v>145.8912729429784</v>
       </c>
     </row>
     <row r="555" spans="1:2">
@@ -6901,7 +6556,7 @@
         <v>555</v>
       </c>
       <c r="B555" s="1">
-        <v>133.9414369908549</v>
+        <v>145.9459645032262</v>
       </c>
     </row>
     <row r="556" spans="1:2">
@@ -6909,7 +6564,7 @@
         <v>556</v>
       </c>
       <c r="B556" s="1">
-        <v>134.1212142308035</v>
+        <v>146.2189748711134</v>
       </c>
     </row>
     <row r="557" spans="1:2">
@@ -6917,7 +6572,7 @@
         <v>557</v>
       </c>
       <c r="B557" s="1">
-        <v>134.1425681894286</v>
+        <v>146.399127290552</v>
       </c>
     </row>
     <row r="558" spans="1:2">
@@ -6925,7 +6580,7 @@
         <v>558</v>
       </c>
       <c r="B558" s="1">
-        <v>134.1796772167984</v>
+        <v>148.000272162274</v>
       </c>
     </row>
     <row r="559" spans="1:2">
@@ -6933,7 +6588,7 @@
         <v>559</v>
       </c>
       <c r="B559" s="1">
-        <v>134.1808421953878</v>
+        <v>149.0310476877417</v>
       </c>
     </row>
     <row r="560" spans="1:2">
@@ -6941,7 +6596,7 @@
         <v>560</v>
       </c>
       <c r="B560" s="1">
-        <v>134.2069595774925</v>
+        <v>149.5294966341174</v>
       </c>
     </row>
     <row r="561" spans="1:2">
@@ -6949,7 +6604,7 @@
         <v>561</v>
       </c>
       <c r="B561" s="1">
-        <v>134.2667584314629</v>
+        <v>150.3936550073457</v>
       </c>
     </row>
     <row r="562" spans="1:2">
@@ -6957,7 +6612,7 @@
         <v>562</v>
       </c>
       <c r="B562" s="1">
-        <v>134.31874931275</v>
+        <v>150.5504240591883</v>
       </c>
     </row>
     <row r="563" spans="1:2">
@@ -6965,7 +6620,7 @@
         <v>563</v>
       </c>
       <c r="B563" s="1">
-        <v>134.5536614808695</v>
+        <v>151.481013481751</v>
       </c>
     </row>
     <row r="564" spans="1:2">
@@ -6973,7 +6628,7 @@
         <v>564</v>
       </c>
       <c r="B564" s="1">
-        <v>134.6457206818532</v>
+        <v>151.6057646606955</v>
       </c>
     </row>
     <row r="565" spans="1:2">
@@ -6981,7 +6636,7 @@
         <v>565</v>
       </c>
       <c r="B565" s="1">
-        <v>134.6704249627749</v>
+        <v>152.0632627065476</v>
       </c>
     </row>
     <row r="566" spans="1:2">
@@ -6989,7 +6644,7 @@
         <v>566</v>
       </c>
       <c r="B566" s="1">
-        <v>134.7023553146224</v>
+        <v>152.8614573303545</v>
       </c>
     </row>
     <row r="567" spans="1:2">
@@ -6997,7 +6652,7 @@
         <v>567</v>
       </c>
       <c r="B567" s="1">
-        <v>134.7325385859609</v>
+        <v>153.3346434060217</v>
       </c>
     </row>
     <row r="568" spans="1:2">
@@ -7005,7 +6660,7 @@
         <v>568</v>
       </c>
       <c r="B568" s="1">
-        <v>134.7991367591694</v>
+        <v>153.3434867939234</v>
       </c>
     </row>
     <row r="569" spans="1:2">
@@ -7013,7 +6668,7 @@
         <v>569</v>
       </c>
       <c r="B569" s="1">
-        <v>134.9331059325363</v>
+        <v>154.7844086420247</v>
       </c>
     </row>
     <row r="570" spans="1:2">
@@ -7021,7 +6676,7 @@
         <v>570</v>
       </c>
       <c r="B570" s="1">
-        <v>134.9732629631344</v>
+        <v>156.0684119020499</v>
       </c>
     </row>
     <row r="571" spans="1:2">
@@ -7029,7 +6684,7 @@
         <v>571</v>
       </c>
       <c r="B571" s="1">
-        <v>135.1020270518096</v>
+        <v>165.5079969080281</v>
       </c>
     </row>
     <row r="572" spans="1:2">
@@ -7037,7 +6692,7 @@
         <v>572</v>
       </c>
       <c r="B572" s="1">
-        <v>135.3528302797602</v>
+        <v>174.9022355460879</v>
       </c>
     </row>
     <row r="573" spans="1:2">
@@ -7045,7 +6700,7 @@
         <v>573</v>
       </c>
       <c r="B573" s="1">
-        <v>135.9527463454412</v>
+        <v>175.3267122993277</v>
       </c>
     </row>
     <row r="574" spans="1:2">
@@ -7053,7 +6708,7 @@
         <v>574</v>
       </c>
       <c r="B574" s="1">
-        <v>136.0445890187315</v>
+        <v>197.2475447703386</v>
       </c>
     </row>
     <row r="575" spans="1:2">
@@ -7061,7 +6716,7 @@
         <v>575</v>
       </c>
       <c r="B575" s="1">
-        <v>136.1555101338938</v>
+        <v>204.0499953535999</v>
       </c>
     </row>
     <row r="576" spans="1:2">
@@ -7069,7 +6724,7 @@
         <v>576</v>
       </c>
       <c r="B576" s="1">
-        <v>136.2345466167971</v>
+        <v>212.760834693395</v>
       </c>
     </row>
     <row r="577" spans="1:2">
@@ -7077,7 +6732,7 @@
         <v>577</v>
       </c>
       <c r="B577" s="1">
-        <v>136.3886779352026</v>
+        <v>235.5773022844236</v>
       </c>
     </row>
     <row r="578" spans="1:2">
@@ -7085,7 +6740,7 @@
         <v>578</v>
       </c>
       <c r="B578" s="1">
-        <v>136.4430570707169</v>
+        <v>237.074063963061</v>
       </c>
     </row>
     <row r="579" spans="1:2">
@@ -7093,7 +6748,7 @@
         <v>579</v>
       </c>
       <c r="B579" s="1">
-        <v>136.7128339270303</v>
+        <v>256.8062287893329</v>
       </c>
     </row>
     <row r="580" spans="1:2">
@@ -7101,7 +6756,7 @@
         <v>580</v>
       </c>
       <c r="B580" s="1">
-        <v>136.9463445125564</v>
+        <v>300.7783434469101</v>
       </c>
     </row>
     <row r="581" spans="1:2">
@@ -7109,7 +6764,7 @@
         <v>581</v>
       </c>
       <c r="B581" s="1">
-        <v>137.4553053037776</v>
+        <v>328.5715905595619</v>
       </c>
     </row>
     <row r="582" spans="1:2">
@@ -7117,7 +6772,7 @@
         <v>582</v>
       </c>
       <c r="B582" s="1">
-        <v>137.4718137984415</v>
+        <v>350.8551599095337</v>
       </c>
     </row>
     <row r="583" spans="1:2">
@@ -7125,927 +6780,7 @@
         <v>583</v>
       </c>
       <c r="B583" s="1">
-        <v>137.8726480063285</v>
-      </c>
-    </row>
-    <row r="584" spans="1:2">
-      <c r="A584" t="s">
-        <v>584</v>
-      </c>
-      <c r="B584" s="1">
-        <v>137.9477348770077</v>
-      </c>
-    </row>
-    <row r="585" spans="1:2">
-      <c r="A585" t="s">
-        <v>585</v>
-      </c>
-      <c r="B585" s="1">
-        <v>138.3145183725813</v>
-      </c>
-    </row>
-    <row r="586" spans="1:2">
-      <c r="A586" t="s">
-        <v>586</v>
-      </c>
-      <c r="B586" s="1">
-        <v>138.9459937432437</v>
-      </c>
-    </row>
-    <row r="587" spans="1:2">
-      <c r="A587" t="s">
-        <v>587</v>
-      </c>
-      <c r="B587" s="1">
-        <v>139.5496864800168</v>
-      </c>
-    </row>
-    <row r="588" spans="1:2">
-      <c r="A588" t="s">
-        <v>588</v>
-      </c>
-      <c r="B588" s="1">
-        <v>139.6930889680834</v>
-      </c>
-    </row>
-    <row r="589" spans="1:2">
-      <c r="A589" t="s">
-        <v>589</v>
-      </c>
-      <c r="B589" s="1">
-        <v>139.7752726566263</v>
-      </c>
-    </row>
-    <row r="590" spans="1:2">
-      <c r="A590" t="s">
-        <v>590</v>
-      </c>
-      <c r="B590" s="1">
-        <v>139.9999496932189</v>
-      </c>
-    </row>
-    <row r="591" spans="1:2">
-      <c r="A591" t="s">
-        <v>591</v>
-      </c>
-      <c r="B591" s="1">
-        <v>140.0041509047234</v>
-      </c>
-    </row>
-    <row r="592" spans="1:2">
-      <c r="A592" t="s">
-        <v>592</v>
-      </c>
-      <c r="B592" s="1">
-        <v>140.0709245680816</v>
-      </c>
-    </row>
-    <row r="593" spans="1:2">
-      <c r="A593" t="s">
-        <v>593</v>
-      </c>
-      <c r="B593" s="1">
-        <v>140.2036456144506</v>
-      </c>
-    </row>
-    <row r="594" spans="1:2">
-      <c r="A594" t="s">
-        <v>594</v>
-      </c>
-      <c r="B594" s="1">
-        <v>140.2538390648787</v>
-      </c>
-    </row>
-    <row r="595" spans="1:2">
-      <c r="A595" t="s">
-        <v>595</v>
-      </c>
-      <c r="B595" s="1">
-        <v>140.2782226810197</v>
-      </c>
-    </row>
-    <row r="596" spans="1:2">
-      <c r="A596" t="s">
-        <v>596</v>
-      </c>
-      <c r="B596" s="1">
-        <v>140.4159725212541</v>
-      </c>
-    </row>
-    <row r="597" spans="1:2">
-      <c r="A597" t="s">
-        <v>597</v>
-      </c>
-      <c r="B597" s="1">
-        <v>140.4643962816835</v>
-      </c>
-    </row>
-    <row r="598" spans="1:2">
-      <c r="A598" t="s">
-        <v>598</v>
-      </c>
-      <c r="B598" s="1">
-        <v>140.592185067955</v>
-      </c>
-    </row>
-    <row r="599" spans="1:2">
-      <c r="A599" t="s">
-        <v>599</v>
-      </c>
-      <c r="B599" s="1">
-        <v>140.7466300050617</v>
-      </c>
-    </row>
-    <row r="600" spans="1:2">
-      <c r="A600" t="s">
-        <v>600</v>
-      </c>
-      <c r="B600" s="1">
-        <v>141.0165768038667</v>
-      </c>
-    </row>
-    <row r="601" spans="1:2">
-      <c r="A601" t="s">
-        <v>601</v>
-      </c>
-      <c r="B601" s="1">
-        <v>141.392152286811</v>
-      </c>
-    </row>
-    <row r="602" spans="1:2">
-      <c r="A602" t="s">
-        <v>602</v>
-      </c>
-      <c r="B602" s="1">
-        <v>141.5328297646311</v>
-      </c>
-    </row>
-    <row r="603" spans="1:2">
-      <c r="A603" t="s">
-        <v>603</v>
-      </c>
-      <c r="B603" s="1">
-        <v>141.8940692655496</v>
-      </c>
-    </row>
-    <row r="604" spans="1:2">
-      <c r="A604" t="s">
-        <v>604</v>
-      </c>
-      <c r="B604" s="1">
-        <v>141.9271465430416</v>
-      </c>
-    </row>
-    <row r="605" spans="1:2">
-      <c r="A605" t="s">
-        <v>605</v>
-      </c>
-      <c r="B605" s="1">
-        <v>142.1670343254481</v>
-      </c>
-    </row>
-    <row r="606" spans="1:2">
-      <c r="A606" t="s">
-        <v>606</v>
-      </c>
-      <c r="B606" s="1">
-        <v>142.2485708839017</v>
-      </c>
-    </row>
-    <row r="607" spans="1:2">
-      <c r="A607" t="s">
-        <v>607</v>
-      </c>
-      <c r="B607" s="1">
-        <v>142.3486795991252</v>
-      </c>
-    </row>
-    <row r="608" spans="1:2">
-      <c r="A608" t="s">
-        <v>608</v>
-      </c>
-      <c r="B608" s="1">
-        <v>142.3749006274235</v>
-      </c>
-    </row>
-    <row r="609" spans="1:2">
-      <c r="A609" t="s">
-        <v>609</v>
-      </c>
-      <c r="B609" s="1">
-        <v>142.4392814870751</v>
-      </c>
-    </row>
-    <row r="610" spans="1:2">
-      <c r="A610" t="s">
-        <v>610</v>
-      </c>
-      <c r="B610" s="1">
-        <v>142.4688420704403</v>
-      </c>
-    </row>
-    <row r="611" spans="1:2">
-      <c r="A611" t="s">
-        <v>611</v>
-      </c>
-      <c r="B611" s="1">
-        <v>142.6935157137953</v>
-      </c>
-    </row>
-    <row r="612" spans="1:2">
-      <c r="A612" t="s">
-        <v>612</v>
-      </c>
-      <c r="B612" s="1">
-        <v>143.2066468338436</v>
-      </c>
-    </row>
-    <row r="613" spans="1:2">
-      <c r="A613" t="s">
-        <v>613</v>
-      </c>
-      <c r="B613" s="1">
-        <v>143.3525272626623</v>
-      </c>
-    </row>
-    <row r="614" spans="1:2">
-      <c r="A614" t="s">
-        <v>614</v>
-      </c>
-      <c r="B614" s="1">
-        <v>143.3628671098525</v>
-      </c>
-    </row>
-    <row r="615" spans="1:2">
-      <c r="A615" t="s">
-        <v>615</v>
-      </c>
-      <c r="B615" s="1">
-        <v>144.0646230055881</v>
-      </c>
-    </row>
-    <row r="616" spans="1:2">
-      <c r="A616" t="s">
-        <v>616</v>
-      </c>
-      <c r="B616" s="1">
-        <v>144.3316032000219</v>
-      </c>
-    </row>
-    <row r="617" spans="1:2">
-      <c r="A617" t="s">
-        <v>617</v>
-      </c>
-      <c r="B617" s="1">
-        <v>144.4085992144063</v>
-      </c>
-    </row>
-    <row r="618" spans="1:2">
-      <c r="A618" t="s">
-        <v>618</v>
-      </c>
-      <c r="B618" s="1">
-        <v>144.4735852388145</v>
-      </c>
-    </row>
-    <row r="619" spans="1:2">
-      <c r="A619" t="s">
-        <v>619</v>
-      </c>
-      <c r="B619" s="1">
-        <v>144.5731915437257</v>
-      </c>
-    </row>
-    <row r="620" spans="1:2">
-      <c r="A620" t="s">
-        <v>620</v>
-      </c>
-      <c r="B620" s="1">
-        <v>144.5932947045835</v>
-      </c>
-    </row>
-    <row r="621" spans="1:2">
-      <c r="A621" t="s">
-        <v>621</v>
-      </c>
-      <c r="B621" s="1">
-        <v>145.4482799773905</v>
-      </c>
-    </row>
-    <row r="622" spans="1:2">
-      <c r="A622" t="s">
-        <v>622</v>
-      </c>
-      <c r="B622" s="1">
-        <v>145.4718496636519</v>
-      </c>
-    </row>
-    <row r="623" spans="1:2">
-      <c r="A623" t="s">
-        <v>623</v>
-      </c>
-      <c r="B623" s="1">
-        <v>145.8992073836287</v>
-      </c>
-    </row>
-    <row r="624" spans="1:2">
-      <c r="A624" t="s">
-        <v>624</v>
-      </c>
-      <c r="B624" s="1">
-        <v>147.0316778629383</v>
-      </c>
-    </row>
-    <row r="625" spans="1:2">
-      <c r="A625" t="s">
-        <v>625</v>
-      </c>
-      <c r="B625" s="1">
-        <v>147.5661775284088</v>
-      </c>
-    </row>
-    <row r="626" spans="1:2">
-      <c r="A626" t="s">
-        <v>626</v>
-      </c>
-      <c r="B626" s="1">
-        <v>148.0722618243338</v>
-      </c>
-    </row>
-    <row r="627" spans="1:2">
-      <c r="A627" t="s">
-        <v>627</v>
-      </c>
-      <c r="B627" s="1">
-        <v>148.385979657926</v>
-      </c>
-    </row>
-    <row r="628" spans="1:2">
-      <c r="A628" t="s">
-        <v>628</v>
-      </c>
-      <c r="B628" s="1">
-        <v>148.5922307123358</v>
-      </c>
-    </row>
-    <row r="629" spans="1:2">
-      <c r="A629" t="s">
-        <v>629</v>
-      </c>
-      <c r="B629" s="1">
-        <v>148.6254192838488</v>
-      </c>
-    </row>
-    <row r="630" spans="1:2">
-      <c r="A630" t="s">
-        <v>630</v>
-      </c>
-      <c r="B630" s="1">
-        <v>149.426064850939</v>
-      </c>
-    </row>
-    <row r="631" spans="1:2">
-      <c r="A631" t="s">
-        <v>631</v>
-      </c>
-      <c r="B631" s="1">
-        <v>149.8204529062646</v>
-      </c>
-    </row>
-    <row r="632" spans="1:2">
-      <c r="A632" t="s">
-        <v>632</v>
-      </c>
-      <c r="B632" s="1">
-        <v>151.2069892826078</v>
-      </c>
-    </row>
-    <row r="633" spans="1:2">
-      <c r="A633" t="s">
-        <v>633</v>
-      </c>
-      <c r="B633" s="1">
-        <v>151.4637385304516</v>
-      </c>
-    </row>
-    <row r="634" spans="1:2">
-      <c r="A634" t="s">
-        <v>634</v>
-      </c>
-      <c r="B634" s="1">
-        <v>151.7029070397099</v>
-      </c>
-    </row>
-    <row r="635" spans="1:2">
-      <c r="A635" t="s">
-        <v>635</v>
-      </c>
-      <c r="B635" s="1">
-        <v>152.1039890158609</v>
-      </c>
-    </row>
-    <row r="636" spans="1:2">
-      <c r="A636" t="s">
-        <v>636</v>
-      </c>
-      <c r="B636" s="1">
-        <v>152.9227086147487</v>
-      </c>
-    </row>
-    <row r="637" spans="1:2">
-      <c r="A637" t="s">
-        <v>637</v>
-      </c>
-      <c r="B637" s="1">
-        <v>152.9449047587219</v>
-      </c>
-    </row>
-    <row r="638" spans="1:2">
-      <c r="A638" t="s">
-        <v>638</v>
-      </c>
-      <c r="B638" s="1">
-        <v>153.2271102181106</v>
-      </c>
-    </row>
-    <row r="639" spans="1:2">
-      <c r="A639" t="s">
-        <v>639</v>
-      </c>
-      <c r="B639" s="1">
-        <v>155.8247019474702</v>
-      </c>
-    </row>
-    <row r="640" spans="1:2">
-      <c r="A640" t="s">
-        <v>640</v>
-      </c>
-      <c r="B640" s="1">
-        <v>155.9872787173383</v>
-      </c>
-    </row>
-    <row r="641" spans="1:2">
-      <c r="A641" t="s">
-        <v>641</v>
-      </c>
-      <c r="B641" s="1">
-        <v>156.2169116405286</v>
-      </c>
-    </row>
-    <row r="642" spans="1:2">
-      <c r="A642" t="s">
-        <v>642</v>
-      </c>
-      <c r="B642" s="1">
-        <v>157.03521518298</v>
-      </c>
-    </row>
-    <row r="643" spans="1:2">
-      <c r="A643" t="s">
-        <v>643</v>
-      </c>
-      <c r="B643" s="1">
-        <v>157.130523264099</v>
-      </c>
-    </row>
-    <row r="644" spans="1:2">
-      <c r="A644" t="s">
-        <v>644</v>
-      </c>
-      <c r="B644" s="1">
-        <v>157.8167276970302</v>
-      </c>
-    </row>
-    <row r="645" spans="1:2">
-      <c r="A645" t="s">
-        <v>645</v>
-      </c>
-      <c r="B645" s="1">
-        <v>158.1339704926759</v>
-      </c>
-    </row>
-    <row r="646" spans="1:2">
-      <c r="A646" t="s">
-        <v>646</v>
-      </c>
-      <c r="B646" s="1">
-        <v>158.320494792574</v>
-      </c>
-    </row>
-    <row r="647" spans="1:2">
-      <c r="A647" t="s">
-        <v>647</v>
-      </c>
-      <c r="B647" s="1">
-        <v>158.3949102892771</v>
-      </c>
-    </row>
-    <row r="648" spans="1:2">
-      <c r="A648" t="s">
-        <v>648</v>
-      </c>
-      <c r="B648" s="1">
-        <v>159.2150296405023</v>
-      </c>
-    </row>
-    <row r="649" spans="1:2">
-      <c r="A649" t="s">
-        <v>649</v>
-      </c>
-      <c r="B649" s="1">
-        <v>160.0098328927405</v>
-      </c>
-    </row>
-    <row r="650" spans="1:2">
-      <c r="A650" t="s">
-        <v>650</v>
-      </c>
-      <c r="B650" s="1">
-        <v>160.6309974554449</v>
-      </c>
-    </row>
-    <row r="651" spans="1:2">
-      <c r="A651" t="s">
-        <v>651</v>
-      </c>
-      <c r="B651" s="1">
-        <v>160.9595584063483</v>
-      </c>
-    </row>
-    <row r="652" spans="1:2">
-      <c r="A652" t="s">
-        <v>652</v>
-      </c>
-      <c r="B652" s="1">
-        <v>161.1868856801391</v>
-      </c>
-    </row>
-    <row r="653" spans="1:2">
-      <c r="A653" t="s">
-        <v>653</v>
-      </c>
-      <c r="B653" s="1">
-        <v>161.2115145535739</v>
-      </c>
-    </row>
-    <row r="654" spans="1:2">
-      <c r="A654" t="s">
-        <v>654</v>
-      </c>
-      <c r="B654" s="1">
-        <v>162.5933273713696</v>
-      </c>
-    </row>
-    <row r="655" spans="1:2">
-      <c r="A655" t="s">
-        <v>655</v>
-      </c>
-      <c r="B655" s="1">
-        <v>165.2175858088021</v>
-      </c>
-    </row>
-    <row r="656" spans="1:2">
-      <c r="A656" t="s">
-        <v>656</v>
-      </c>
-      <c r="B656" s="1">
-        <v>165.3794567953473</v>
-      </c>
-    </row>
-    <row r="657" spans="1:2">
-      <c r="A657" t="s">
-        <v>657</v>
-      </c>
-      <c r="B657" s="1">
-        <v>165.5514880923389</v>
-      </c>
-    </row>
-    <row r="658" spans="1:2">
-      <c r="A658" t="s">
-        <v>658</v>
-      </c>
-      <c r="B658" s="1">
-        <v>166.2129986863655</v>
-      </c>
-    </row>
-    <row r="659" spans="1:2">
-      <c r="A659" t="s">
-        <v>659</v>
-      </c>
-      <c r="B659" s="1">
-        <v>166.5487292585726</v>
-      </c>
-    </row>
-    <row r="660" spans="1:2">
-      <c r="A660" t="s">
-        <v>660</v>
-      </c>
-      <c r="B660" s="1">
-        <v>167.5388901987798</v>
-      </c>
-    </row>
-    <row r="661" spans="1:2">
-      <c r="A661" t="s">
-        <v>661</v>
-      </c>
-      <c r="B661" s="1">
-        <v>168.6227099306648</v>
-      </c>
-    </row>
-    <row r="662" spans="1:2">
-      <c r="A662" t="s">
-        <v>662</v>
-      </c>
-      <c r="B662" s="1">
-        <v>169.7061213448532</v>
-      </c>
-    </row>
-    <row r="663" spans="1:2">
-      <c r="A663" t="s">
-        <v>663</v>
-      </c>
-      <c r="B663" s="1">
-        <v>170.4415198032617</v>
-      </c>
-    </row>
-    <row r="664" spans="1:2">
-      <c r="A664" t="s">
-        <v>664</v>
-      </c>
-      <c r="B664" s="1">
-        <v>172.4695353784916</v>
-      </c>
-    </row>
-    <row r="665" spans="1:2">
-      <c r="A665" t="s">
-        <v>665</v>
-      </c>
-      <c r="B665" s="1">
-        <v>173.9472977699687</v>
-      </c>
-    </row>
-    <row r="666" spans="1:2">
-      <c r="A666" t="s">
-        <v>666</v>
-      </c>
-      <c r="B666" s="1">
-        <v>175.6200992306331</v>
-      </c>
-    </row>
-    <row r="667" spans="1:2">
-      <c r="A667" t="s">
-        <v>667</v>
-      </c>
-      <c r="B667" s="1">
-        <v>176.419965470953</v>
-      </c>
-    </row>
-    <row r="668" spans="1:2">
-      <c r="A668" t="s">
-        <v>668</v>
-      </c>
-      <c r="B668" s="1">
-        <v>176.7539276439751</v>
-      </c>
-    </row>
-    <row r="669" spans="1:2">
-      <c r="A669" t="s">
-        <v>669</v>
-      </c>
-      <c r="B669" s="1">
-        <v>176.8031086457219</v>
-      </c>
-    </row>
-    <row r="670" spans="1:2">
-      <c r="A670" t="s">
-        <v>670</v>
-      </c>
-      <c r="B670" s="1">
-        <v>177.3282883207904</v>
-      </c>
-    </row>
-    <row r="671" spans="1:2">
-      <c r="A671" t="s">
-        <v>671</v>
-      </c>
-      <c r="B671" s="1">
-        <v>182.065899631175</v>
-      </c>
-    </row>
-    <row r="672" spans="1:2">
-      <c r="A672" t="s">
-        <v>672</v>
-      </c>
-      <c r="B672" s="1">
-        <v>189.6790043573956</v>
-      </c>
-    </row>
-    <row r="673" spans="1:2">
-      <c r="A673" t="s">
-        <v>673</v>
-      </c>
-      <c r="B673" s="1">
-        <v>191.1436662222693</v>
-      </c>
-    </row>
-    <row r="674" spans="1:2">
-      <c r="A674" t="s">
-        <v>674</v>
-      </c>
-      <c r="B674" s="1">
-        <v>193.73519033948</v>
-      </c>
-    </row>
-    <row r="675" spans="1:2">
-      <c r="A675" t="s">
-        <v>675</v>
-      </c>
-      <c r="B675" s="1">
-        <v>199.5799420029931</v>
-      </c>
-    </row>
-    <row r="676" spans="1:2">
-      <c r="A676" t="s">
-        <v>676</v>
-      </c>
-      <c r="B676" s="1">
-        <v>202.3870172316073</v>
-      </c>
-    </row>
-    <row r="677" spans="1:2">
-      <c r="A677" t="s">
-        <v>677</v>
-      </c>
-      <c r="B677" s="1">
-        <v>205.9679660503097</v>
-      </c>
-    </row>
-    <row r="678" spans="1:2">
-      <c r="A678" t="s">
-        <v>678</v>
-      </c>
-      <c r="B678" s="1">
-        <v>206.3896359096363</v>
-      </c>
-    </row>
-    <row r="679" spans="1:2">
-      <c r="A679" t="s">
-        <v>679</v>
-      </c>
-      <c r="B679" s="1">
-        <v>207.7500518109333</v>
-      </c>
-    </row>
-    <row r="680" spans="1:2">
-      <c r="A680" t="s">
-        <v>680</v>
-      </c>
-      <c r="B680" s="1">
-        <v>211.3539276813083</v>
-      </c>
-    </row>
-    <row r="681" spans="1:2">
-      <c r="A681" t="s">
-        <v>681</v>
-      </c>
-      <c r="B681" s="1">
-        <v>211.5409806952388</v>
-      </c>
-    </row>
-    <row r="682" spans="1:2">
-      <c r="A682" t="s">
-        <v>682</v>
-      </c>
-      <c r="B682" s="1">
-        <v>214.210627151177</v>
-      </c>
-    </row>
-    <row r="683" spans="1:2">
-      <c r="A683" t="s">
-        <v>683</v>
-      </c>
-      <c r="B683" s="1">
-        <v>214.2266075160047</v>
-      </c>
-    </row>
-    <row r="684" spans="1:2">
-      <c r="A684" t="s">
-        <v>684</v>
-      </c>
-      <c r="B684" s="1">
-        <v>215.8741177938066</v>
-      </c>
-    </row>
-    <row r="685" spans="1:2">
-      <c r="A685" t="s">
-        <v>685</v>
-      </c>
-      <c r="B685" s="1">
-        <v>217.7491204103518</v>
-      </c>
-    </row>
-    <row r="686" spans="1:2">
-      <c r="A686" t="s">
-        <v>686</v>
-      </c>
-      <c r="B686" s="1">
-        <v>218.2263955132005</v>
-      </c>
-    </row>
-    <row r="687" spans="1:2">
-      <c r="A687" t="s">
-        <v>687</v>
-      </c>
-      <c r="B687" s="1">
-        <v>219.3852508624493</v>
-      </c>
-    </row>
-    <row r="688" spans="1:2">
-      <c r="A688" t="s">
-        <v>688</v>
-      </c>
-      <c r="B688" s="1">
-        <v>219.6643827635574</v>
-      </c>
-    </row>
-    <row r="689" spans="1:2">
-      <c r="A689" t="s">
-        <v>689</v>
-      </c>
-      <c r="B689" s="1">
-        <v>231.572235419191</v>
-      </c>
-    </row>
-    <row r="690" spans="1:2">
-      <c r="A690" t="s">
-        <v>690</v>
-      </c>
-      <c r="B690" s="1">
-        <v>235.9113867713231</v>
-      </c>
-    </row>
-    <row r="691" spans="1:2">
-      <c r="A691" t="s">
-        <v>691</v>
-      </c>
-      <c r="B691" s="1">
-        <v>247.8508571072771</v>
-      </c>
-    </row>
-    <row r="692" spans="1:2">
-      <c r="A692" t="s">
-        <v>692</v>
-      </c>
-      <c r="B692" s="1">
-        <v>280.4690408004643</v>
-      </c>
-    </row>
-    <row r="693" spans="1:2">
-      <c r="A693" t="s">
-        <v>693</v>
-      </c>
-      <c r="B693" s="1">
-        <v>335.914401328226</v>
-      </c>
-    </row>
-    <row r="694" spans="1:2">
-      <c r="A694" t="s">
-        <v>694</v>
-      </c>
-      <c r="B694" s="1">
-        <v>398.352263803539</v>
-      </c>
-    </row>
-    <row r="695" spans="1:2">
-      <c r="A695" t="s">
-        <v>695</v>
-      </c>
-      <c r="B695" s="1">
-        <v>402.5877908268833</v>
-      </c>
-    </row>
-    <row r="696" spans="1:2">
-      <c r="A696" t="s">
-        <v>696</v>
-      </c>
-      <c r="B696" s="1">
-        <v>435.9782420844183</v>
-      </c>
-    </row>
-    <row r="697" spans="1:2">
-      <c r="A697" t="s">
-        <v>697</v>
-      </c>
-      <c r="B697" s="1">
-        <v>465.6310313212279</v>
-      </c>
-    </row>
-    <row r="698" spans="1:2">
-      <c r="A698" t="s">
-        <v>698</v>
-      </c>
-      <c r="B698" s="1">
-        <v>517.8022810720011</v>
+        <v>413.6960672253205</v>
       </c>
     </row>
   </sheetData>

--- a/Screener/data/rs_rating_top_30.xlsx
+++ b/Screener/data/rs_rating_top_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="584">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="582">
   <si>
     <t>Symbol</t>
   </si>
@@ -22,1750 +22,1744 @@
     <t>RS Rating</t>
   </si>
   <si>
-    <t>CFNB</t>
+    <t>APLS</t>
+  </si>
+  <si>
+    <t>VIR</t>
+  </si>
+  <si>
+    <t>DRVN</t>
+  </si>
+  <si>
+    <t>KDSKF</t>
+  </si>
+  <si>
+    <t>PI</t>
+  </si>
+  <si>
+    <t>ZI</t>
+  </si>
+  <si>
+    <t>NVCR</t>
+  </si>
+  <si>
+    <t>DXC</t>
+  </si>
+  <si>
+    <t>CYRX</t>
+  </si>
+  <si>
+    <t>VSAT</t>
+  </si>
+  <si>
+    <t>PRFT</t>
+  </si>
+  <si>
+    <t>SAGE</t>
+  </si>
+  <si>
+    <t>BMEA</t>
+  </si>
+  <si>
+    <t>IMXI</t>
+  </si>
+  <si>
+    <t>CTGO</t>
+  </si>
+  <si>
+    <t>RGC</t>
+  </si>
+  <si>
+    <t>SHYF</t>
+  </si>
+  <si>
+    <t>SEDG</t>
+  </si>
+  <si>
+    <t>CERE</t>
+  </si>
+  <si>
+    <t>EEFT</t>
+  </si>
+  <si>
+    <t>XMTR</t>
+  </si>
+  <si>
+    <t>MXL</t>
+  </si>
+  <si>
+    <t>VKTX</t>
+  </si>
+  <si>
+    <t>SDGR</t>
+  </si>
+  <si>
+    <t>ONEW</t>
+  </si>
+  <si>
+    <t>SILC</t>
+  </si>
+  <si>
+    <t>INBX</t>
+  </si>
+  <si>
+    <t>SPR</t>
+  </si>
+  <si>
+    <t>MASI</t>
+  </si>
+  <si>
+    <t>SILK</t>
+  </si>
+  <si>
+    <t>PEN</t>
+  </si>
+  <si>
+    <t>BHVN</t>
+  </si>
+  <si>
+    <t>OFED</t>
+  </si>
+  <si>
+    <t>NVRO</t>
+  </si>
+  <si>
+    <t>ENPH</t>
+  </si>
+  <si>
+    <t>IRBT</t>
+  </si>
+  <si>
+    <t>MODV</t>
+  </si>
+  <si>
+    <t>PTGX</t>
+  </si>
+  <si>
+    <t>RYI</t>
+  </si>
+  <si>
+    <t>GNRC</t>
   </si>
   <si>
     <t>MRTX</t>
   </si>
   <si>
-    <t>CRVL</t>
-  </si>
-  <si>
-    <t>LOPE</t>
-  </si>
-  <si>
-    <t>PAA</t>
-  </si>
-  <si>
-    <t>GOOGL</t>
-  </si>
-  <si>
-    <t>EMYB</t>
-  </si>
-  <si>
-    <t>FTV</t>
+    <t>IPGP</t>
+  </si>
+  <si>
+    <t>VRDN</t>
+  </si>
+  <si>
+    <t>CCRN</t>
+  </si>
+  <si>
+    <t>DKL</t>
+  </si>
+  <si>
+    <t>IRDM</t>
+  </si>
+  <si>
+    <t>OPRA</t>
+  </si>
+  <si>
+    <t>NSP</t>
+  </si>
+  <si>
+    <t>BPMC</t>
+  </si>
+  <si>
+    <t>LTHM</t>
+  </si>
+  <si>
+    <t>LNTH</t>
+  </si>
+  <si>
+    <t>INTA</t>
+  </si>
+  <si>
+    <t>BEAM</t>
+  </si>
+  <si>
+    <t>MDGL</t>
+  </si>
+  <si>
+    <t>RDWR</t>
+  </si>
+  <si>
+    <t>LTH</t>
+  </si>
+  <si>
+    <t>NXRT</t>
+  </si>
+  <si>
+    <t>ETNB</t>
+  </si>
+  <si>
+    <t>RCKT</t>
+  </si>
+  <si>
+    <t>SSTK</t>
+  </si>
+  <si>
+    <t>NEP</t>
+  </si>
+  <si>
+    <t>MLNK</t>
+  </si>
+  <si>
+    <t>ALB</t>
+  </si>
+  <si>
+    <t>CNMD</t>
+  </si>
+  <si>
+    <t>KRTX</t>
+  </si>
+  <si>
+    <t>NTRA</t>
+  </si>
+  <si>
+    <t>CRNC</t>
+  </si>
+  <si>
+    <t>MAXN</t>
+  </si>
+  <si>
+    <t>ZBRA</t>
+  </si>
+  <si>
+    <t>AMOT</t>
+  </si>
+  <si>
+    <t>ANIK</t>
+  </si>
+  <si>
+    <t>KPLT</t>
+  </si>
+  <si>
+    <t>AU</t>
+  </si>
+  <si>
+    <t>NOVA</t>
+  </si>
+  <si>
+    <t>OM</t>
+  </si>
+  <si>
+    <t>IPG</t>
+  </si>
+  <si>
+    <t>CALX</t>
+  </si>
+  <si>
+    <t>AYX</t>
+  </si>
+  <si>
+    <t>PLL</t>
+  </si>
+  <si>
+    <t>TMCI</t>
+  </si>
+  <si>
+    <t>EFX</t>
+  </si>
+  <si>
+    <t>CWEN</t>
+  </si>
+  <si>
+    <t>WING</t>
+  </si>
+  <si>
+    <t>EYE</t>
+  </si>
+  <si>
+    <t>DV</t>
+  </si>
+  <si>
+    <t>RBLX</t>
+  </si>
+  <si>
+    <t>FNA</t>
+  </si>
+  <si>
+    <t>MEG</t>
+  </si>
+  <si>
+    <t>DQ</t>
+  </si>
+  <si>
+    <t>NUS</t>
+  </si>
+  <si>
+    <t>SWAV</t>
+  </si>
+  <si>
+    <t>TBI</t>
+  </si>
+  <si>
+    <t>TGS</t>
+  </si>
+  <si>
+    <t>MMSI</t>
+  </si>
+  <si>
+    <t>EW</t>
+  </si>
+  <si>
+    <t>NVEC</t>
+  </si>
+  <si>
+    <t>BELFB</t>
+  </si>
+  <si>
+    <t>LMAT</t>
+  </si>
+  <si>
+    <t>SIBN</t>
+  </si>
+  <si>
+    <t>CHWY</t>
+  </si>
+  <si>
+    <t>CWCO</t>
+  </si>
+  <si>
+    <t>CHEF</t>
+  </si>
+  <si>
+    <t>TCX</t>
+  </si>
+  <si>
+    <t>SGRY</t>
+  </si>
+  <si>
+    <t>OMC</t>
+  </si>
+  <si>
+    <t>VEON</t>
+  </si>
+  <si>
+    <t>ARRY</t>
+  </si>
+  <si>
+    <t>VAC</t>
+  </si>
+  <si>
+    <t>YZCAY</t>
+  </si>
+  <si>
+    <t>RTX</t>
+  </si>
+  <si>
+    <t>OMCL</t>
+  </si>
+  <si>
+    <t>INTT</t>
+  </si>
+  <si>
+    <t>HTZ</t>
+  </si>
+  <si>
+    <t>GME</t>
+  </si>
+  <si>
+    <t>SXT</t>
+  </si>
+  <si>
+    <t>SMG</t>
+  </si>
+  <si>
+    <t>DFS</t>
+  </si>
+  <si>
+    <t>NTLA</t>
+  </si>
+  <si>
+    <t>BELFA</t>
+  </si>
+  <si>
+    <t>IMGN</t>
+  </si>
+  <si>
+    <t>OFLX</t>
+  </si>
+  <si>
+    <t>JKS</t>
+  </si>
+  <si>
+    <t>ZBH</t>
+  </si>
+  <si>
+    <t>MRNA</t>
+  </si>
+  <si>
+    <t>WCC</t>
+  </si>
+  <si>
+    <t>BEPC</t>
+  </si>
+  <si>
+    <t>STAA</t>
+  </si>
+  <si>
+    <t>PTLO</t>
+  </si>
+  <si>
+    <t>RARE</t>
+  </si>
+  <si>
+    <t>HCBC</t>
+  </si>
+  <si>
+    <t>TCMD</t>
+  </si>
+  <si>
+    <t>LITE</t>
+  </si>
+  <si>
+    <t>RGNX</t>
+  </si>
+  <si>
+    <t>REPL</t>
+  </si>
+  <si>
+    <t>ETSY</t>
+  </si>
+  <si>
+    <t>KIDS</t>
+  </si>
+  <si>
+    <t>AXON</t>
+  </si>
+  <si>
+    <t>RMBS</t>
+  </si>
+  <si>
+    <t>EL</t>
+  </si>
+  <si>
+    <t>PHR</t>
+  </si>
+  <si>
+    <t>AIRT</t>
+  </si>
+  <si>
+    <t>VMI</t>
+  </si>
+  <si>
+    <t>AXTA</t>
+  </si>
+  <si>
+    <t>MANU</t>
+  </si>
+  <si>
+    <t>MYGN</t>
+  </si>
+  <si>
+    <t>LUV</t>
+  </si>
+  <si>
+    <t>EXPE</t>
+  </si>
+  <si>
+    <t>SAVE</t>
+  </si>
+  <si>
+    <t>FDMT</t>
+  </si>
+  <si>
+    <t>ALKS</t>
+  </si>
+  <si>
+    <t>TTGT</t>
+  </si>
+  <si>
+    <t>AKRO</t>
+  </si>
+  <si>
+    <t>GFL</t>
+  </si>
+  <si>
+    <t>ALK</t>
+  </si>
+  <si>
+    <t>DY</t>
+  </si>
+  <si>
+    <t>XOMA</t>
+  </si>
+  <si>
+    <t>RVNC</t>
+  </si>
+  <si>
+    <t>CCOI</t>
+  </si>
+  <si>
+    <t>DNLI</t>
+  </si>
+  <si>
+    <t>SAVA</t>
+  </si>
+  <si>
+    <t>NCLH</t>
+  </si>
+  <si>
+    <t>UHS</t>
+  </si>
+  <si>
+    <t>VCEL</t>
+  </si>
+  <si>
+    <t>CYTK</t>
+  </si>
+  <si>
+    <t>MNRO</t>
+  </si>
+  <si>
+    <t>TOST</t>
+  </si>
+  <si>
+    <t>PRLB</t>
+  </si>
+  <si>
+    <t>AMG</t>
+  </si>
+  <si>
+    <t>CSIQ</t>
+  </si>
+  <si>
+    <t>LFUS</t>
+  </si>
+  <si>
+    <t>XPOF</t>
+  </si>
+  <si>
+    <t>MTR</t>
+  </si>
+  <si>
+    <t>COHR</t>
+  </si>
+  <si>
+    <t>PAYC</t>
+  </si>
+  <si>
+    <t>CHDN</t>
+  </si>
+  <si>
+    <t>BIP</t>
+  </si>
+  <si>
+    <t>ARVN</t>
+  </si>
+  <si>
+    <t>BEP</t>
+  </si>
+  <si>
+    <t>CWH</t>
+  </si>
+  <si>
+    <t>TU</t>
+  </si>
+  <si>
+    <t>BRKR</t>
+  </si>
+  <si>
+    <t>CRSP</t>
+  </si>
+  <si>
+    <t>AMX</t>
+  </si>
+  <si>
+    <t>SANM</t>
+  </si>
+  <si>
+    <t>GFI</t>
+  </si>
+  <si>
+    <t>OLK</t>
+  </si>
+  <si>
+    <t>EDVMF</t>
+  </si>
+  <si>
+    <t>CROX</t>
+  </si>
+  <si>
+    <t>INSP</t>
+  </si>
+  <si>
+    <t>SLAB</t>
+  </si>
+  <si>
+    <t>ARW</t>
+  </si>
+  <si>
+    <t>SPOT</t>
+  </si>
+  <si>
+    <t>ORA</t>
+  </si>
+  <si>
+    <t>DAVA</t>
+  </si>
+  <si>
+    <t>CRTO</t>
+  </si>
+  <si>
+    <t>MTRN</t>
+  </si>
+  <si>
+    <t>TGLS</t>
+  </si>
+  <si>
+    <t>HXL</t>
+  </si>
+  <si>
+    <t>SRPT</t>
+  </si>
+  <si>
+    <t>IMOS</t>
+  </si>
+  <si>
+    <t>LW</t>
+  </si>
+  <si>
+    <t>JNPR</t>
+  </si>
+  <si>
+    <t>TYRA</t>
+  </si>
+  <si>
+    <t>RCUS</t>
+  </si>
+  <si>
+    <t>INSE</t>
+  </si>
+  <si>
+    <t>SHOP</t>
+  </si>
+  <si>
+    <t>WSC</t>
+  </si>
+  <si>
+    <t>SPSC</t>
+  </si>
+  <si>
+    <t>FMC</t>
+  </si>
+  <si>
+    <t>ESMT</t>
+  </si>
+  <si>
+    <t>DT</t>
+  </si>
+  <si>
+    <t>ENTA</t>
+  </si>
+  <si>
+    <t>BIPC</t>
+  </si>
+  <si>
+    <t>PMT</t>
+  </si>
+  <si>
+    <t>DGII</t>
+  </si>
+  <si>
+    <t>ANVS</t>
+  </si>
+  <si>
+    <t>TLK</t>
+  </si>
+  <si>
+    <t>MSGE</t>
+  </si>
+  <si>
+    <t>VALN</t>
+  </si>
+  <si>
+    <t>TRP</t>
+  </si>
+  <si>
+    <t>AVDL</t>
+  </si>
+  <si>
+    <t>ALGT</t>
+  </si>
+  <si>
+    <t>MIRM</t>
+  </si>
+  <si>
+    <t>SRCL</t>
+  </si>
+  <si>
+    <t>PLNT</t>
+  </si>
+  <si>
+    <t>EXPO</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>LGND</t>
+  </si>
+  <si>
+    <t>CGNX</t>
+  </si>
+  <si>
+    <t>HKHHF</t>
+  </si>
+  <si>
+    <t>EXLS</t>
+  </si>
+  <si>
+    <t>TSM</t>
   </si>
   <si>
     <t>ATEX</t>
   </si>
   <si>
-    <t>JAZZ</t>
-  </si>
-  <si>
-    <t>EHC</t>
-  </si>
-  <si>
-    <t>GOOG</t>
-  </si>
-  <si>
-    <t>BKE</t>
-  </si>
-  <si>
-    <t>RBB</t>
-  </si>
-  <si>
-    <t>SPB</t>
-  </si>
-  <si>
-    <t>FXNC</t>
-  </si>
-  <si>
-    <t>SCCO</t>
-  </si>
-  <si>
-    <t>CSCO</t>
-  </si>
-  <si>
-    <t>DHACU</t>
-  </si>
-  <si>
-    <t>NXGN</t>
-  </si>
-  <si>
-    <t>CLH</t>
-  </si>
-  <si>
-    <t>MORN</t>
-  </si>
-  <si>
-    <t>TNK</t>
-  </si>
-  <si>
-    <t>TWST</t>
-  </si>
-  <si>
-    <t>FFIC</t>
-  </si>
-  <si>
-    <t>REVG</t>
-  </si>
-  <si>
-    <t>CTSH</t>
-  </si>
-  <si>
-    <t>MEDP</t>
-  </si>
-  <si>
-    <t>FLT</t>
-  </si>
-  <si>
-    <t>JHX</t>
-  </si>
-  <si>
-    <t>PNR</t>
-  </si>
-  <si>
-    <t>GBDC</t>
-  </si>
-  <si>
-    <t>ICFI</t>
-  </si>
-  <si>
-    <t>ATI</t>
-  </si>
-  <si>
-    <t>BWXT</t>
-  </si>
-  <si>
-    <t>CMUV</t>
-  </si>
-  <si>
-    <t>HES</t>
-  </si>
-  <si>
-    <t>CCAP</t>
-  </si>
-  <si>
-    <t>UBAB</t>
-  </si>
-  <si>
-    <t>PWR</t>
-  </si>
-  <si>
-    <t>CAL</t>
+    <t>IRT</t>
+  </si>
+  <si>
+    <t>SNN</t>
+  </si>
+  <si>
+    <t>CCRD</t>
+  </si>
+  <si>
+    <t>ANSS</t>
+  </si>
+  <si>
+    <t>NCSM</t>
+  </si>
+  <si>
+    <t>IDT</t>
+  </si>
+  <si>
+    <t>NEM</t>
+  </si>
+  <si>
+    <t>FSUMF</t>
+  </si>
+  <si>
+    <t>MSB</t>
+  </si>
+  <si>
+    <t>GTY</t>
+  </si>
+  <si>
+    <t>HRMY</t>
+  </si>
+  <si>
+    <t>ESTC</t>
+  </si>
+  <si>
+    <t>CCI</t>
+  </si>
+  <si>
+    <t>PEGA</t>
+  </si>
+  <si>
+    <t>JBT</t>
+  </si>
+  <si>
+    <t>EXAS</t>
+  </si>
+  <si>
+    <t>SNOW</t>
+  </si>
+  <si>
+    <t>SMLR</t>
+  </si>
+  <si>
+    <t>IDYA</t>
+  </si>
+  <si>
+    <t>ITCI</t>
+  </si>
+  <si>
+    <t>WEYS</t>
+  </si>
+  <si>
+    <t>ST</t>
+  </si>
+  <si>
+    <t>HI</t>
+  </si>
+  <si>
+    <t>GTLB</t>
+  </si>
+  <si>
+    <t>THC</t>
+  </si>
+  <si>
+    <t>DOX</t>
+  </si>
+  <si>
+    <t>AAL</t>
+  </si>
+  <si>
+    <t>LAC</t>
+  </si>
+  <si>
+    <t>PYPL</t>
+  </si>
+  <si>
+    <t>ARMK</t>
+  </si>
+  <si>
+    <t>SSYS</t>
+  </si>
+  <si>
+    <t>PNTG</t>
+  </si>
+  <si>
+    <t>BDC</t>
+  </si>
+  <si>
+    <t>ISRG</t>
+  </si>
+  <si>
+    <t>AMBA</t>
+  </si>
+  <si>
+    <t>BSIG</t>
+  </si>
+  <si>
+    <t>JCI</t>
+  </si>
+  <si>
+    <t>GGG</t>
+  </si>
+  <si>
+    <t>TKR</t>
+  </si>
+  <si>
+    <t>CLDX</t>
+  </si>
+  <si>
+    <t>FBTT</t>
+  </si>
+  <si>
+    <t>PGTI</t>
+  </si>
+  <si>
+    <t>ROK</t>
+  </si>
+  <si>
+    <t>SIX</t>
+  </si>
+  <si>
+    <t>CCSI</t>
+  </si>
+  <si>
+    <t>PODD</t>
+  </si>
+  <si>
+    <t>ERII</t>
+  </si>
+  <si>
+    <t>KD</t>
+  </si>
+  <si>
+    <t>QEPC</t>
+  </si>
+  <si>
+    <t>GLOB</t>
+  </si>
+  <si>
+    <t>HQI</t>
+  </si>
+  <si>
+    <t>PRAA</t>
+  </si>
+  <si>
+    <t>LMND</t>
+  </si>
+  <si>
+    <t>SYK</t>
+  </si>
+  <si>
+    <t>AAUKF</t>
+  </si>
+  <si>
+    <t>UFCS</t>
+  </si>
+  <si>
+    <t>MMS</t>
+  </si>
+  <si>
+    <t>JBSS</t>
+  </si>
+  <si>
+    <t>LPX</t>
+  </si>
+  <si>
+    <t>IFNNY</t>
+  </si>
+  <si>
+    <t>DXCM</t>
+  </si>
+  <si>
+    <t>HUBS</t>
+  </si>
+  <si>
+    <t>GGAL</t>
+  </si>
+  <si>
+    <t>TARO</t>
+  </si>
+  <si>
+    <t>BLBD</t>
+  </si>
+  <si>
+    <t>SQM</t>
+  </si>
+  <si>
+    <t>FWONB</t>
+  </si>
+  <si>
+    <t>BCE</t>
+  </si>
+  <si>
+    <t>DCPH</t>
+  </si>
+  <si>
+    <t>KN</t>
+  </si>
+  <si>
+    <t>ALLE</t>
+  </si>
+  <si>
+    <t>VNT</t>
+  </si>
+  <si>
+    <t>DUOL</t>
+  </si>
+  <si>
+    <t>ARWR</t>
+  </si>
+  <si>
+    <t>QTRX</t>
+  </si>
+  <si>
+    <t>AGR</t>
+  </si>
+  <si>
+    <t>ICUI</t>
+  </si>
+  <si>
+    <t>HASI</t>
+  </si>
+  <si>
+    <t>NTCT</t>
+  </si>
+  <si>
+    <t>BCYC</t>
+  </si>
+  <si>
+    <t>NEO</t>
+  </si>
+  <si>
+    <t>WFG</t>
+  </si>
+  <si>
+    <t>CCD</t>
+  </si>
+  <si>
+    <t>PATH</t>
+  </si>
+  <si>
+    <t>FSUGY</t>
+  </si>
+  <si>
+    <t>MP</t>
+  </si>
+  <si>
+    <t>HSY</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>KAR</t>
+  </si>
+  <si>
+    <t>PFE</t>
+  </si>
+  <si>
+    <t>SWTX</t>
+  </si>
+  <si>
+    <t>CSGP</t>
+  </si>
+  <si>
+    <t>FN</t>
+  </si>
+  <si>
+    <t>WHR</t>
+  </si>
+  <si>
+    <t>SGML</t>
+  </si>
+  <si>
+    <t>PAM</t>
+  </si>
+  <si>
+    <t>BXC</t>
+  </si>
+  <si>
+    <t>KAMN</t>
+  </si>
+  <si>
+    <t>WIRE</t>
+  </si>
+  <si>
+    <t>HON</t>
+  </si>
+  <si>
+    <t>CMG</t>
+  </si>
+  <si>
+    <t>IDCC</t>
+  </si>
+  <si>
+    <t>MLI</t>
+  </si>
+  <si>
+    <t>RYAAY</t>
+  </si>
+  <si>
+    <t>NGG</t>
+  </si>
+  <si>
+    <t>HCA</t>
+  </si>
+  <si>
+    <t>TREE</t>
+  </si>
+  <si>
+    <t>SIM</t>
+  </si>
+  <si>
+    <t>MEI</t>
+  </si>
+  <si>
+    <t>TWNK</t>
+  </si>
+  <si>
+    <t>TWLO</t>
+  </si>
+  <si>
+    <t>SLGN</t>
+  </si>
+  <si>
+    <t>UGI</t>
+  </si>
+  <si>
+    <t>FMAO</t>
+  </si>
+  <si>
+    <t>CPK</t>
+  </si>
+  <si>
+    <t>UVE</t>
+  </si>
+  <si>
+    <t>TDY</t>
+  </si>
+  <si>
+    <t>LAMR</t>
+  </si>
+  <si>
+    <t>FTS</t>
+  </si>
+  <si>
+    <t>MODN</t>
+  </si>
+  <si>
+    <t>UDR</t>
+  </si>
+  <si>
+    <t>NLCP</t>
+  </si>
+  <si>
+    <t>VCYT</t>
+  </si>
+  <si>
+    <t>FHI</t>
+  </si>
+  <si>
+    <t>VZ</t>
+  </si>
+  <si>
+    <t>CNNE</t>
+  </si>
+  <si>
+    <t>WSBF</t>
+  </si>
+  <si>
+    <t>CWST</t>
+  </si>
+  <si>
+    <t>ACDVF</t>
+  </si>
+  <si>
+    <t>GT</t>
+  </si>
+  <si>
+    <t>QNTO</t>
+  </si>
+  <si>
+    <t>ZNTL</t>
+  </si>
+  <si>
+    <t>GFS</t>
+  </si>
+  <si>
+    <t>ULTA</t>
+  </si>
+  <si>
+    <t>FMBL</t>
+  </si>
+  <si>
+    <t>CXM</t>
+  </si>
+  <si>
+    <t>AVNW</t>
+  </si>
+  <si>
+    <t>BIIB</t>
+  </si>
+  <si>
+    <t>CNXC</t>
+  </si>
+  <si>
+    <t>BLMN</t>
+  </si>
+  <si>
+    <t>BMA</t>
+  </si>
+  <si>
+    <t>MAA</t>
+  </si>
+  <si>
+    <t>NNN</t>
+  </si>
+  <si>
+    <t>ARTNA</t>
+  </si>
+  <si>
+    <t>AVT</t>
+  </si>
+  <si>
+    <t>TRDA</t>
+  </si>
+  <si>
+    <t>NODK</t>
+  </si>
+  <si>
+    <t>HUBB</t>
+  </si>
+  <si>
+    <t>RDIB</t>
+  </si>
+  <si>
+    <t>EPR</t>
+  </si>
+  <si>
+    <t>ACVA</t>
+  </si>
+  <si>
+    <t>STER</t>
+  </si>
+  <si>
+    <t>HAIN</t>
+  </si>
+  <si>
+    <t>CARG</t>
+  </si>
+  <si>
+    <t>ASAN</t>
+  </si>
+  <si>
+    <t>NJR</t>
+  </si>
+  <si>
+    <t>ILMN</t>
+  </si>
+  <si>
+    <t>MTN</t>
+  </si>
+  <si>
+    <t>WNC</t>
+  </si>
+  <si>
+    <t>AVNS</t>
+  </si>
+  <si>
+    <t>ASR</t>
+  </si>
+  <si>
+    <t>SAFE</t>
+  </si>
+  <si>
+    <t>GPK</t>
+  </si>
+  <si>
+    <t>UI</t>
+  </si>
+  <si>
+    <t>ALNY</t>
+  </si>
+  <si>
+    <t>ASML</t>
+  </si>
+  <si>
+    <t>PUK</t>
+  </si>
+  <si>
+    <t>XNCR</t>
+  </si>
+  <si>
+    <t>APPN</t>
+  </si>
+  <si>
+    <t>FELE</t>
+  </si>
+  <si>
+    <t>NGLOY</t>
+  </si>
+  <si>
+    <t>AI</t>
+  </si>
+  <si>
+    <t>GRBK</t>
+  </si>
+  <si>
+    <t>NWE</t>
+  </si>
+  <si>
+    <t>IONS</t>
+  </si>
+  <si>
+    <t>MYE</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>SSNC</t>
+  </si>
+  <si>
+    <t>ITOS</t>
+  </si>
+  <si>
+    <t>VRNA</t>
+  </si>
+  <si>
+    <t>EXR</t>
+  </si>
+  <si>
+    <t>FE</t>
+  </si>
+  <si>
+    <t>XENE</t>
+  </si>
+  <si>
+    <t>NOBH</t>
+  </si>
+  <si>
+    <t>AXSM</t>
+  </si>
+  <si>
+    <t>AIRC</t>
+  </si>
+  <si>
+    <t>OR</t>
+  </si>
+  <si>
+    <t>FBRT</t>
+  </si>
+  <si>
+    <t>TRIP</t>
+  </si>
+  <si>
+    <t>CHT</t>
+  </si>
+  <si>
+    <t>KBR</t>
+  </si>
+  <si>
+    <t>TNL</t>
+  </si>
+  <si>
+    <t>NEE</t>
+  </si>
+  <si>
+    <t>FLMMF</t>
+  </si>
+  <si>
+    <t>GPC</t>
+  </si>
+  <si>
+    <t>HOLX</t>
+  </si>
+  <si>
+    <t>AXR</t>
+  </si>
+  <si>
+    <t>MNDY</t>
+  </si>
+  <si>
+    <t>LHX</t>
+  </si>
+  <si>
+    <t>MVO</t>
+  </si>
+  <si>
+    <t>BMBL</t>
+  </si>
+  <si>
+    <t>FCN</t>
+  </si>
+  <si>
+    <t>ABG</t>
+  </si>
+  <si>
+    <t>HEINY</t>
+  </si>
+  <si>
+    <t>EA</t>
+  </si>
+  <si>
+    <t>TYL</t>
+  </si>
+  <si>
+    <t>VERV</t>
+  </si>
+  <si>
+    <t>EQC</t>
+  </si>
+  <si>
+    <t>UGIC</t>
+  </si>
+  <si>
+    <t>RCI</t>
+  </si>
+  <si>
+    <t>GH</t>
+  </si>
+  <si>
+    <t>ALTR</t>
+  </si>
+  <si>
+    <t>SMLP</t>
+  </si>
+  <si>
+    <t>CIEN</t>
+  </si>
+  <si>
+    <t>ADSK</t>
+  </si>
+  <si>
+    <t>CLFD</t>
+  </si>
+  <si>
+    <t>MCFT</t>
+  </si>
+  <si>
+    <t>MKTX</t>
+  </si>
+  <si>
+    <t>SENEB</t>
+  </si>
+  <si>
+    <t>HKHHY</t>
+  </si>
+  <si>
+    <t>HY</t>
+  </si>
+  <si>
+    <t>TCI</t>
+  </si>
+  <si>
+    <t>TSLA</t>
+  </si>
+  <si>
+    <t>KMB</t>
+  </si>
+  <si>
+    <t>AGI</t>
+  </si>
+  <si>
+    <t>SNCY</t>
+  </si>
+  <si>
+    <t>HTH</t>
+  </si>
+  <si>
+    <t>HSON</t>
+  </si>
+  <si>
+    <t>YPF</t>
+  </si>
+  <si>
+    <t>KOF</t>
+  </si>
+  <si>
+    <t>LZRFY</t>
+  </si>
+  <si>
+    <t>GIL</t>
+  </si>
+  <si>
+    <t>DIS</t>
+  </si>
+  <si>
+    <t>QDEL</t>
+  </si>
+  <si>
+    <t>TPH</t>
+  </si>
+  <si>
+    <t>ATLC</t>
+  </si>
+  <si>
+    <t>OFIX</t>
+  </si>
+  <si>
+    <t>VEEV</t>
+  </si>
+  <si>
+    <t>UTL</t>
+  </si>
+  <si>
+    <t>AGIO</t>
+  </si>
+  <si>
+    <t>GM</t>
+  </si>
+  <si>
+    <t>AVTE</t>
+  </si>
+  <si>
+    <t>VRSN</t>
+  </si>
+  <si>
+    <t>MHGU</t>
+  </si>
+  <si>
+    <t>GOOS</t>
+  </si>
+  <si>
+    <t>SLM</t>
+  </si>
+  <si>
+    <t>ES</t>
+  </si>
+  <si>
+    <t>TH</t>
+  </si>
+  <si>
+    <t>COCO</t>
+  </si>
+  <si>
+    <t>CUBE</t>
+  </si>
+  <si>
+    <t>SWKH</t>
+  </si>
+  <si>
+    <t>SBAC</t>
+  </si>
+  <si>
+    <t>GLW</t>
+  </si>
+  <si>
+    <t>AMLX</t>
+  </si>
+  <si>
+    <t>BWA</t>
+  </si>
+  <si>
+    <t>DSGX</t>
+  </si>
+  <si>
+    <t>KRP</t>
+  </si>
+  <si>
+    <t>YORW</t>
+  </si>
+  <si>
+    <t>HGV</t>
+  </si>
+  <si>
+    <t>GIB</t>
+  </si>
+  <si>
+    <t>CACC</t>
+  </si>
+  <si>
+    <t>NSIT</t>
+  </si>
+  <si>
+    <t>MNAT</t>
+  </si>
+  <si>
+    <t>AMN</t>
+  </si>
+  <si>
+    <t>LYV</t>
+  </si>
+  <si>
+    <t>NUVA</t>
+  </si>
+  <si>
+    <t>CMCO</t>
+  </si>
+  <si>
+    <t>JHG</t>
+  </si>
+  <si>
+    <t>CASS</t>
+  </si>
+  <si>
+    <t>SBS</t>
+  </si>
+  <si>
+    <t>MTW</t>
+  </si>
+  <si>
+    <t>AON</t>
+  </si>
+  <si>
+    <t>ISBA</t>
+  </si>
+  <si>
+    <t>AEP</t>
+  </si>
+  <si>
+    <t>AEM</t>
+  </si>
+  <si>
+    <t>IBEX</t>
+  </si>
+  <si>
+    <t>BMY</t>
+  </si>
+  <si>
+    <t>KMT</t>
+  </si>
+  <si>
+    <t>PNW</t>
+  </si>
+  <si>
+    <t>BSX</t>
+  </si>
+  <si>
+    <t>IVZ</t>
+  </si>
+  <si>
+    <t>ROG</t>
+  </si>
+  <si>
+    <t>TROX</t>
+  </si>
+  <si>
+    <t>MKSI</t>
+  </si>
+  <si>
+    <t>TARS</t>
+  </si>
+  <si>
+    <t>TRS</t>
+  </si>
+  <si>
+    <t>CPT</t>
+  </si>
+  <si>
+    <t>EBAY</t>
+  </si>
+  <si>
+    <t>SAP</t>
+  </si>
+  <si>
+    <t>PPG</t>
+  </si>
+  <si>
+    <t>OLP</t>
+  </si>
+  <si>
+    <t>OPY</t>
+  </si>
+  <si>
+    <t>ENTG</t>
+  </si>
+  <si>
+    <t>SR</t>
+  </si>
+  <si>
+    <t>TAK</t>
+  </si>
+  <si>
+    <t>BBN</t>
+  </si>
+  <si>
+    <t>PENN</t>
+  </si>
+  <si>
+    <t>NC</t>
+  </si>
+  <si>
+    <t>ALOT</t>
+  </si>
+  <si>
+    <t>TSEM</t>
+  </si>
+  <si>
+    <t>SITE</t>
+  </si>
+  <si>
+    <t>ATUSF</t>
+  </si>
+  <si>
+    <t>MDT</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>QSR</t>
+  </si>
+  <si>
+    <t>RICK</t>
+  </si>
+  <si>
+    <t>BKH</t>
+  </si>
+  <si>
+    <t>RGLD</t>
+  </si>
+  <si>
+    <t>JRVR</t>
+  </si>
+  <si>
+    <t>GATX</t>
+  </si>
+  <si>
+    <t>CRL</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>AVA</t>
+  </si>
+  <si>
+    <t>TFX</t>
+  </si>
+  <si>
+    <t>HSTM</t>
+  </si>
+  <si>
+    <t>FR</t>
+  </si>
+  <si>
+    <t>KEYS</t>
+  </si>
+  <si>
+    <t>AVB</t>
+  </si>
+  <si>
+    <t>GIS</t>
+  </si>
+  <si>
+    <t>THRY</t>
+  </si>
+  <si>
+    <t>MGIC</t>
+  </si>
+  <si>
+    <t>GWW</t>
+  </si>
+  <si>
+    <t>NSA</t>
+  </si>
+  <si>
+    <t>MPX</t>
+  </si>
+  <si>
+    <t>SSL</t>
   </si>
   <si>
     <t>ANAB</t>
   </si>
   <si>
-    <t>NWPX</t>
-  </si>
-  <si>
-    <t>UNP</t>
-  </si>
-  <si>
-    <t>PH</t>
-  </si>
-  <si>
-    <t>CBOE</t>
-  </si>
-  <si>
-    <t>TJX</t>
-  </si>
-  <si>
-    <t>ACAD</t>
-  </si>
-  <si>
-    <t>FBP</t>
-  </si>
-  <si>
-    <t>PFX</t>
-  </si>
-  <si>
-    <t>MATX</t>
-  </si>
-  <si>
-    <t>INTU</t>
-  </si>
-  <si>
-    <t>AIZ</t>
-  </si>
-  <si>
-    <t>BROS</t>
-  </si>
-  <si>
-    <t>COLL</t>
-  </si>
-  <si>
-    <t>NTNX</t>
-  </si>
-  <si>
-    <t>DEI</t>
-  </si>
-  <si>
-    <t>IR</t>
-  </si>
-  <si>
-    <t>CEN</t>
-  </si>
-  <si>
-    <t>SPFI</t>
-  </si>
-  <si>
-    <t>NTIC</t>
-  </si>
-  <si>
-    <t>BBSI</t>
-  </si>
-  <si>
-    <t>FRSB</t>
-  </si>
-  <si>
-    <t>USLM</t>
-  </si>
-  <si>
-    <t>CFST</t>
-  </si>
-  <si>
-    <t>BA</t>
-  </si>
-  <si>
-    <t>VIST</t>
-  </si>
-  <si>
-    <t>CME</t>
-  </si>
-  <si>
-    <t>IHG</t>
-  </si>
-  <si>
-    <t>PBF</t>
-  </si>
-  <si>
-    <t>RXST</t>
-  </si>
-  <si>
-    <t>CIGI</t>
-  </si>
-  <si>
-    <t>FARO</t>
-  </si>
-  <si>
-    <t>CRMT</t>
-  </si>
-  <si>
-    <t>CVE</t>
-  </si>
-  <si>
-    <t>ABCM</t>
-  </si>
-  <si>
-    <t>NFE</t>
-  </si>
-  <si>
-    <t>CADE</t>
-  </si>
-  <si>
-    <t>VLO</t>
-  </si>
-  <si>
-    <t>BKU</t>
-  </si>
-  <si>
-    <t>MET</t>
-  </si>
-  <si>
-    <t>ALSN</t>
-  </si>
-  <si>
-    <t>ITT</t>
-  </si>
-  <si>
-    <t>VET</t>
-  </si>
-  <si>
-    <t>STX</t>
-  </si>
-  <si>
-    <t>BHWB</t>
-  </si>
-  <si>
-    <t>TT</t>
-  </si>
-  <si>
-    <t>AIT</t>
-  </si>
-  <si>
-    <t>CSWC</t>
-  </si>
-  <si>
-    <t>NWSA</t>
-  </si>
-  <si>
-    <t>FANG</t>
-  </si>
-  <si>
-    <t>CMCSA</t>
-  </si>
-  <si>
-    <t>TSBK</t>
-  </si>
-  <si>
-    <t>DCPH</t>
-  </si>
-  <si>
-    <t>LSCC</t>
-  </si>
-  <si>
-    <t>GNE</t>
-  </si>
-  <si>
-    <t>TFSL</t>
-  </si>
-  <si>
-    <t>WDFC</t>
-  </si>
-  <si>
-    <t>TARO</t>
-  </si>
-  <si>
-    <t>MANU</t>
-  </si>
-  <si>
-    <t>FMX</t>
-  </si>
-  <si>
-    <t>CTRA</t>
-  </si>
-  <si>
-    <t>RCMT</t>
-  </si>
-  <si>
-    <t>HOLI</t>
-  </si>
-  <si>
-    <t>IMTX</t>
-  </si>
-  <si>
-    <t>LDOS</t>
-  </si>
-  <si>
-    <t>PWSC</t>
-  </si>
-  <si>
-    <t>CFBK</t>
-  </si>
-  <si>
-    <t>ARVN</t>
-  </si>
-  <si>
-    <t>COIN</t>
-  </si>
-  <si>
-    <t>BSRR</t>
-  </si>
-  <si>
-    <t>WMB</t>
-  </si>
-  <si>
-    <t>VERX</t>
-  </si>
-  <si>
-    <t>WWD</t>
-  </si>
-  <si>
-    <t>DELL</t>
-  </si>
-  <si>
-    <t>NEU</t>
-  </si>
-  <si>
-    <t>NVMI</t>
-  </si>
-  <si>
-    <t>PPC</t>
-  </si>
-  <si>
-    <t>PAHC</t>
-  </si>
-  <si>
-    <t>ERF</t>
-  </si>
-  <si>
-    <t>ARBV</t>
-  </si>
-  <si>
-    <t>WWE</t>
-  </si>
-  <si>
-    <t>RCL</t>
-  </si>
-  <si>
-    <t>ARCE</t>
-  </si>
-  <si>
-    <t>BCML</t>
-  </si>
-  <si>
-    <t>ARCB</t>
-  </si>
-  <si>
-    <t>URI</t>
-  </si>
-  <si>
-    <t>EOG</t>
-  </si>
-  <si>
-    <t>ICLR</t>
-  </si>
-  <si>
-    <t>IMO</t>
-  </si>
-  <si>
-    <t>ABCB</t>
-  </si>
-  <si>
-    <t>SAL</t>
-  </si>
-  <si>
-    <t>SNEX</t>
-  </si>
-  <si>
-    <t>SMCI</t>
-  </si>
-  <si>
-    <t>FFNW</t>
-  </si>
-  <si>
-    <t>FWRG</t>
-  </si>
-  <si>
-    <t>LNG</t>
-  </si>
-  <si>
-    <t>AVID</t>
-  </si>
-  <si>
-    <t>ZION</t>
-  </si>
-  <si>
-    <t>TCBI</t>
-  </si>
-  <si>
-    <t>BLX</t>
-  </si>
-  <si>
-    <t>TCPC</t>
-  </si>
-  <si>
-    <t>PXD</t>
-  </si>
-  <si>
-    <t>SMMF</t>
-  </si>
-  <si>
-    <t>BRZE</t>
-  </si>
-  <si>
-    <t>MRCY</t>
-  </si>
-  <si>
-    <t>BY</t>
-  </si>
-  <si>
-    <t>PRMW</t>
-  </si>
-  <si>
-    <t>NWS</t>
-  </si>
-  <si>
-    <t>TRMD</t>
-  </si>
-  <si>
-    <t>HP</t>
-  </si>
-  <si>
-    <t>LAD</t>
-  </si>
-  <si>
-    <t>LIVN</t>
-  </si>
-  <si>
-    <t>EMR</t>
-  </si>
-  <si>
-    <t>EXEL</t>
-  </si>
-  <si>
-    <t>DGICB</t>
-  </si>
-  <si>
-    <t>MLR</t>
-  </si>
-  <si>
-    <t>NBIX</t>
-  </si>
-  <si>
-    <t>PRGO</t>
-  </si>
-  <si>
-    <t>JXN</t>
-  </si>
-  <si>
-    <t>QTRX</t>
-  </si>
-  <si>
-    <t>SU</t>
-  </si>
-  <si>
-    <t>FETM</t>
-  </si>
-  <si>
-    <t>GNTX</t>
-  </si>
-  <si>
-    <t>ARCT</t>
-  </si>
-  <si>
-    <t>DAWN</t>
-  </si>
-  <si>
-    <t>VRE</t>
-  </si>
-  <si>
-    <t>VABK</t>
-  </si>
-  <si>
-    <t>EVBN</t>
-  </si>
-  <si>
-    <t>LBRDK</t>
-  </si>
-  <si>
-    <t>DDS</t>
-  </si>
-  <si>
-    <t>STRT</t>
-  </si>
-  <si>
-    <t>CCB</t>
-  </si>
-  <si>
-    <t>ADBE</t>
-  </si>
-  <si>
-    <t>CPRX</t>
-  </si>
-  <si>
-    <t>WOR</t>
-  </si>
-  <si>
-    <t>AIR</t>
-  </si>
-  <si>
-    <t>PX</t>
-  </si>
-  <si>
-    <t>FNF</t>
-  </si>
-  <si>
-    <t>MBIN</t>
-  </si>
-  <si>
-    <t>FRHC</t>
-  </si>
-  <si>
-    <t>GPOR</t>
-  </si>
-  <si>
-    <t>ADP</t>
-  </si>
-  <si>
-    <t>NYT</t>
-  </si>
-  <si>
-    <t>ZWS</t>
-  </si>
-  <si>
-    <t>HTHT</t>
-  </si>
-  <si>
-    <t>IMAX</t>
-  </si>
-  <si>
-    <t>INSM</t>
-  </si>
-  <si>
-    <t>TRGP</t>
-  </si>
-  <si>
-    <t>KTOS</t>
-  </si>
-  <si>
-    <t>NVDA</t>
-  </si>
-  <si>
-    <t>PFBC</t>
-  </si>
-  <si>
-    <t>STER</t>
-  </si>
-  <si>
-    <t>UFPI</t>
-  </si>
-  <si>
-    <t>PDCO</t>
-  </si>
-  <si>
-    <t>GH</t>
-  </si>
-  <si>
-    <t>AKAM</t>
-  </si>
-  <si>
-    <t>ORRF</t>
-  </si>
-  <si>
-    <t>TS</t>
-  </si>
-  <si>
-    <t>MAT</t>
-  </si>
-  <si>
-    <t>SRV</t>
-  </si>
-  <si>
-    <t>PNFP</t>
-  </si>
-  <si>
-    <t>WMS</t>
-  </si>
-  <si>
-    <t>PSTG</t>
-  </si>
-  <si>
-    <t>LBRDA</t>
-  </si>
-  <si>
-    <t>BKR</t>
-  </si>
-  <si>
-    <t>PFC</t>
-  </si>
-  <si>
-    <t>KNSA</t>
-  </si>
-  <si>
-    <t>ROST</t>
-  </si>
-  <si>
-    <t>GOLF</t>
-  </si>
-  <si>
-    <t>CSTL</t>
-  </si>
-  <si>
-    <t>XPEL</t>
-  </si>
-  <si>
-    <t>MAR</t>
-  </si>
-  <si>
-    <t>MBWM</t>
-  </si>
-  <si>
-    <t>BRBR</t>
-  </si>
-  <si>
-    <t>ACT</t>
-  </si>
-  <si>
-    <t>APO</t>
-  </si>
-  <si>
-    <t>CVI</t>
-  </si>
-  <si>
-    <t>IBP</t>
-  </si>
-  <si>
-    <t>CDW</t>
-  </si>
-  <si>
-    <t>DPZ</t>
-  </si>
-  <si>
-    <t>VALU</t>
-  </si>
-  <si>
-    <t>KOP</t>
-  </si>
-  <si>
-    <t>COOP</t>
-  </si>
-  <si>
-    <t>MLP</t>
-  </si>
-  <si>
-    <t>VVI</t>
-  </si>
-  <si>
-    <t>REGN</t>
-  </si>
-  <si>
-    <t>ALKT</t>
-  </si>
-  <si>
-    <t>GBLI</t>
-  </si>
-  <si>
-    <t>ALRM</t>
-  </si>
-  <si>
-    <t>AR</t>
-  </si>
-  <si>
-    <t>APPF</t>
-  </si>
-  <si>
-    <t>NECB</t>
-  </si>
-  <si>
-    <t>SSD</t>
-  </si>
-  <si>
-    <t>NARI</t>
-  </si>
-  <si>
-    <t>VMW</t>
-  </si>
-  <si>
-    <t>HALO</t>
-  </si>
-  <si>
-    <t>CRS</t>
-  </si>
-  <si>
-    <t>VAL</t>
-  </si>
-  <si>
-    <t>BG</t>
-  </si>
-  <si>
-    <t>CENTA</t>
-  </si>
-  <si>
-    <t>VECO</t>
-  </si>
-  <si>
-    <t>VEL</t>
-  </si>
-  <si>
-    <t>SKYW</t>
-  </si>
-  <si>
-    <t>BR</t>
-  </si>
-  <si>
-    <t>BKNG</t>
-  </si>
-  <si>
-    <t>CDRE</t>
-  </si>
-  <si>
-    <t>TNET</t>
-  </si>
-  <si>
-    <t>SXI</t>
-  </si>
-  <si>
-    <t>OC</t>
-  </si>
-  <si>
-    <t>ETN</t>
-  </si>
-  <si>
-    <t>TH</t>
-  </si>
-  <si>
-    <t>R</t>
-  </si>
-  <si>
-    <t>ALGN</t>
-  </si>
-  <si>
-    <t>MSA</t>
-  </si>
-  <si>
-    <t>TCOM</t>
-  </si>
-  <si>
-    <t>DMRC</t>
-  </si>
-  <si>
-    <t>AMGN</t>
-  </si>
-  <si>
-    <t>HQY</t>
-  </si>
-  <si>
-    <t>SAH</t>
-  </si>
-  <si>
-    <t>OPCH</t>
-  </si>
-  <si>
-    <t>FIX</t>
-  </si>
-  <si>
-    <t>FUTU</t>
-  </si>
-  <si>
-    <t>ROAD</t>
-  </si>
-  <si>
-    <t>IPI</t>
-  </si>
-  <si>
-    <t>NHC</t>
-  </si>
-  <si>
-    <t>MTCH</t>
-  </si>
-  <si>
-    <t>MHO</t>
-  </si>
-  <si>
-    <t>CCL</t>
-  </si>
-  <si>
-    <t>INFA</t>
-  </si>
-  <si>
-    <t>ZGN</t>
-  </si>
-  <si>
-    <t>PSX</t>
-  </si>
-  <si>
-    <t>TEAM</t>
-  </si>
-  <si>
-    <t>NTRA</t>
-  </si>
-  <si>
-    <t>BWMX</t>
-  </si>
-  <si>
-    <t>ETD</t>
-  </si>
-  <si>
-    <t>RNGR</t>
-  </si>
-  <si>
-    <t>GKOS</t>
-  </si>
-  <si>
-    <t>TFII</t>
-  </si>
-  <si>
-    <t>WSM</t>
-  </si>
-  <si>
-    <t>ESCA</t>
-  </si>
-  <si>
-    <t>IBKR</t>
-  </si>
-  <si>
-    <t>FLR</t>
-  </si>
-  <si>
-    <t>TCBX</t>
-  </si>
-  <si>
-    <t>MUR</t>
-  </si>
-  <si>
-    <t>CMPR</t>
-  </si>
-  <si>
-    <t>CNOB</t>
-  </si>
-  <si>
-    <t>PTEN</t>
-  </si>
-  <si>
-    <t>J</t>
-  </si>
-  <si>
-    <t>NREF</t>
-  </si>
-  <si>
-    <t>ARGX</t>
-  </si>
-  <si>
-    <t>ANDE</t>
-  </si>
-  <si>
-    <t>HNI</t>
-  </si>
-  <si>
-    <t>LQDT</t>
-  </si>
-  <si>
-    <t>WIX</t>
-  </si>
-  <si>
-    <t>KTB</t>
-  </si>
-  <si>
-    <t>DICE</t>
-  </si>
-  <si>
-    <t>FC</t>
-  </si>
-  <si>
-    <t>SITM</t>
-  </si>
-  <si>
-    <t>CUBI</t>
-  </si>
-  <si>
-    <t>BCSF</t>
-  </si>
-  <si>
-    <t>TIPT</t>
-  </si>
-  <si>
-    <t>YELP</t>
-  </si>
-  <si>
-    <t>APOG</t>
-  </si>
-  <si>
-    <t>ANET</t>
-  </si>
-  <si>
-    <t>RCEL</t>
-  </si>
-  <si>
-    <t>CPNG</t>
-  </si>
-  <si>
-    <t>CAR</t>
-  </si>
-  <si>
-    <t>CAT</t>
-  </si>
-  <si>
-    <t>BOOT</t>
-  </si>
-  <si>
-    <t>NEOG</t>
-  </si>
-  <si>
-    <t>AFBI</t>
-  </si>
-  <si>
-    <t>OII</t>
-  </si>
-  <si>
-    <t>QLYS</t>
-  </si>
-  <si>
-    <t>FLXS</t>
-  </si>
-  <si>
-    <t>STRS</t>
-  </si>
-  <si>
-    <t>PAM</t>
-  </si>
-  <si>
-    <t>SAM</t>
-  </si>
-  <si>
-    <t>AEL</t>
-  </si>
-  <si>
-    <t>GRC</t>
-  </si>
-  <si>
-    <t>CUK</t>
-  </si>
-  <si>
-    <t>CLW</t>
-  </si>
-  <si>
-    <t>AGM</t>
-  </si>
-  <si>
-    <t>HLF</t>
-  </si>
-  <si>
-    <t>AURCU</t>
-  </si>
-  <si>
-    <t>HAL</t>
-  </si>
-  <si>
-    <t>MLKN</t>
-  </si>
-  <si>
-    <t>TXT</t>
-  </si>
-  <si>
-    <t>FSFG</t>
-  </si>
-  <si>
-    <t>DLR</t>
-  </si>
-  <si>
-    <t>MGPI</t>
-  </si>
-  <si>
-    <t>DRQ</t>
-  </si>
-  <si>
-    <t>CSWI</t>
-  </si>
-  <si>
-    <t>CARR</t>
-  </si>
-  <si>
-    <t>ELF</t>
-  </si>
-  <si>
-    <t>BNTX</t>
-  </si>
-  <si>
-    <t>CENT</t>
-  </si>
-  <si>
-    <t>BXP</t>
-  </si>
-  <si>
-    <t>PLUS</t>
-  </si>
-  <si>
-    <t>SLB</t>
-  </si>
-  <si>
-    <t>KRC</t>
-  </si>
-  <si>
-    <t>FTI</t>
-  </si>
-  <si>
-    <t>DCOM</t>
-  </si>
-  <si>
-    <t>STNG</t>
-  </si>
-  <si>
-    <t>TREX</t>
-  </si>
-  <si>
-    <t>SPOK</t>
-  </si>
-  <si>
-    <t>VST</t>
-  </si>
-  <si>
-    <t>CSPI</t>
-  </si>
-  <si>
-    <t>CPS</t>
-  </si>
-  <si>
-    <t>NEWT</t>
-  </si>
-  <si>
-    <t>RCUS</t>
-  </si>
-  <si>
-    <t>EVI</t>
-  </si>
-  <si>
-    <t>LBRT</t>
-  </si>
-  <si>
-    <t>RPM</t>
-  </si>
-  <si>
-    <t>FORG</t>
-  </si>
-  <si>
-    <t>AZPN</t>
-  </si>
-  <si>
-    <t>SCPL</t>
-  </si>
-  <si>
-    <t>CHTR</t>
-  </si>
-  <si>
-    <t>ENLC</t>
-  </si>
-  <si>
-    <t>ARCH</t>
-  </si>
-  <si>
-    <t>PBNK</t>
-  </si>
-  <si>
-    <t>CNXN</t>
-  </si>
-  <si>
-    <t>RH</t>
-  </si>
-  <si>
-    <t>LAUR</t>
-  </si>
-  <si>
-    <t>FRPT</t>
-  </si>
-  <si>
-    <t>DBRG</t>
-  </si>
-  <si>
-    <t>NE</t>
-  </si>
-  <si>
-    <t>SPNS</t>
-  </si>
-  <si>
-    <t>ATSG</t>
-  </si>
-  <si>
-    <t>HURN</t>
-  </si>
-  <si>
-    <t>VRNS</t>
-  </si>
-  <si>
-    <t>MVBF</t>
-  </si>
-  <si>
-    <t>LI</t>
-  </si>
-  <si>
-    <t>HEP</t>
-  </si>
-  <si>
-    <t>BOH</t>
-  </si>
-  <si>
-    <t>CW</t>
-  </si>
-  <si>
-    <t>CIVI</t>
-  </si>
-  <si>
-    <t>DVAX</t>
-  </si>
-  <si>
-    <t>TRNS</t>
-  </si>
-  <si>
-    <t>CVLG</t>
-  </si>
-  <si>
-    <t>AMEH</t>
-  </si>
-  <si>
-    <t>LII</t>
-  </si>
-  <si>
-    <t>BBW</t>
-  </si>
-  <si>
-    <t>AZEK</t>
-  </si>
-  <si>
-    <t>RIVN</t>
-  </si>
-  <si>
-    <t>NWLI</t>
-  </si>
-  <si>
-    <t>HCCI</t>
-  </si>
-  <si>
-    <t>HAYW</t>
-  </si>
-  <si>
-    <t>MCB</t>
-  </si>
-  <si>
-    <t>ACU</t>
-  </si>
-  <si>
-    <t>ODFL</t>
-  </si>
-  <si>
-    <t>TNP</t>
-  </si>
-  <si>
-    <t>NVO</t>
-  </si>
-  <si>
-    <t>AZZ</t>
-  </si>
-  <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>HOFT</t>
-  </si>
-  <si>
-    <t>CHX</t>
-  </si>
-  <si>
-    <t>INOD</t>
-  </si>
-  <si>
-    <t>SHEN</t>
-  </si>
-  <si>
-    <t>OLLI</t>
-  </si>
-  <si>
-    <t>SRI</t>
-  </si>
-  <si>
-    <t>CCJ</t>
-  </si>
-  <si>
-    <t>NCR</t>
-  </si>
-  <si>
-    <t>SFBS</t>
-  </si>
-  <si>
-    <t>NOG</t>
-  </si>
-  <si>
-    <t>RAMP</t>
-  </si>
-  <si>
-    <t>KSS</t>
-  </si>
-  <si>
-    <t>ALPN</t>
-  </si>
-  <si>
-    <t>UBS</t>
-  </si>
-  <si>
-    <t>MTDR</t>
-  </si>
-  <si>
-    <t>BLD</t>
-  </si>
-  <si>
-    <t>HLNE</t>
-  </si>
-  <si>
-    <t>PRIM</t>
-  </si>
-  <si>
-    <t>DOMO</t>
-  </si>
-  <si>
-    <t>DLX</t>
-  </si>
-  <si>
-    <t>TALO</t>
-  </si>
-  <si>
-    <t>QCRH</t>
-  </si>
-  <si>
-    <t>GPN</t>
-  </si>
-  <si>
-    <t>SOVO</t>
-  </si>
-  <si>
-    <t>FRO</t>
-  </si>
-  <si>
-    <t>CVRX</t>
-  </si>
-  <si>
-    <t>RDY</t>
-  </si>
-  <si>
-    <t>EURN</t>
-  </si>
-  <si>
-    <t>WMG</t>
-  </si>
-  <si>
-    <t>ASMIY</t>
-  </si>
-  <si>
-    <t>APA</t>
-  </si>
-  <si>
-    <t>PESI</t>
-  </si>
-  <si>
-    <t>PHAT</t>
-  </si>
-  <si>
-    <t>CAAP</t>
-  </si>
-  <si>
-    <t>VICR</t>
-  </si>
-  <si>
-    <t>ITRN</t>
-  </si>
-  <si>
-    <t>FRD</t>
-  </si>
-  <si>
-    <t>GTLS</t>
-  </si>
-  <si>
-    <t>XP</t>
-  </si>
-  <si>
-    <t>PRO</t>
-  </si>
-  <si>
-    <t>GIC</t>
-  </si>
-  <si>
-    <t>OSK</t>
-  </si>
-  <si>
-    <t>TW</t>
-  </si>
-  <si>
-    <t>PRA</t>
-  </si>
-  <si>
-    <t>INSW</t>
-  </si>
-  <si>
-    <t>NEWR</t>
-  </si>
-  <si>
-    <t>BKI</t>
-  </si>
-  <si>
-    <t>PLCE</t>
-  </si>
-  <si>
-    <t>CABA</t>
-  </si>
-  <si>
-    <t>FTAI</t>
-  </si>
-  <si>
-    <t>PSFE</t>
-  </si>
-  <si>
-    <t>STEP</t>
-  </si>
-  <si>
-    <t>EME</t>
-  </si>
-  <si>
-    <t>SG</t>
-  </si>
-  <si>
-    <t>ASTE</t>
-  </si>
-  <si>
-    <t>MPC</t>
-  </si>
-  <si>
-    <t>PSN</t>
-  </si>
-  <si>
-    <t>AMNB</t>
-  </si>
-  <si>
-    <t>SENEB</t>
-  </si>
-  <si>
-    <t>HWKN</t>
-  </si>
-  <si>
-    <t>CVBF</t>
-  </si>
-  <si>
-    <t>BZH</t>
-  </si>
-  <si>
-    <t>AURC</t>
-  </si>
-  <si>
-    <t>ROCK</t>
-  </si>
-  <si>
-    <t>ACOR</t>
-  </si>
-  <si>
-    <t>RVMD</t>
-  </si>
-  <si>
-    <t>EXTR</t>
-  </si>
-  <si>
-    <t>CALB</t>
-  </si>
-  <si>
-    <t>SENEA</t>
-  </si>
-  <si>
-    <t>TDW</t>
-  </si>
-  <si>
-    <t>PAR</t>
-  </si>
-  <si>
-    <t>CRC</t>
-  </si>
-  <si>
-    <t>CWCO</t>
-  </si>
-  <si>
-    <t>TRDA</t>
-  </si>
-  <si>
-    <t>XPRO</t>
-  </si>
-  <si>
-    <t>NRP</t>
-  </si>
-  <si>
-    <t>YETI</t>
-  </si>
-  <si>
-    <t>WAL</t>
-  </si>
-  <si>
-    <t>WHD</t>
-  </si>
-  <si>
-    <t>NOV</t>
-  </si>
-  <si>
-    <t>LLY</t>
-  </si>
-  <si>
-    <t>INBK</t>
-  </si>
-  <si>
-    <t>JOE</t>
-  </si>
-  <si>
-    <t>HRB</t>
-  </si>
-  <si>
-    <t>OVV</t>
+    <t>ROL</t>
   </si>
   <si>
     <t>DFH</t>
   </si>
   <si>
-    <t>FOR</t>
-  </si>
-  <si>
-    <t>IDYA</t>
-  </si>
-  <si>
-    <t>KD</t>
-  </si>
-  <si>
-    <t>KDNY</t>
-  </si>
-  <si>
-    <t>SLG</t>
-  </si>
-  <si>
-    <t>AROC</t>
-  </si>
-  <si>
-    <t>AZTA</t>
-  </si>
-  <si>
-    <t>XPO</t>
-  </si>
-  <si>
-    <t>WFRD</t>
-  </si>
-  <si>
-    <t>ESEA</t>
-  </si>
-  <si>
-    <t>GCO</t>
-  </si>
-  <si>
-    <t>SAIA</t>
-  </si>
-  <si>
-    <t>GBX</t>
-  </si>
-  <si>
-    <t>MTSI</t>
-  </si>
-  <si>
-    <t>ANIP</t>
-  </si>
-  <si>
-    <t>TRUP</t>
-  </si>
-  <si>
-    <t>AMR</t>
-  </si>
-  <si>
-    <t>LEAT</t>
-  </si>
-  <si>
-    <t>BCC</t>
-  </si>
-  <si>
-    <t>ROKU</t>
-  </si>
-  <si>
-    <t>NATR</t>
-  </si>
-  <si>
-    <t>CNX</t>
-  </si>
-  <si>
-    <t>GHM</t>
-  </si>
-  <si>
-    <t>DCBO</t>
-  </si>
-  <si>
-    <t>BFST</t>
-  </si>
-  <si>
-    <t>NOA</t>
-  </si>
-  <si>
-    <t>CELH</t>
-  </si>
-  <si>
-    <t>W</t>
-  </si>
-  <si>
-    <t>LYTS</t>
-  </si>
-  <si>
-    <t>LOB</t>
-  </si>
-  <si>
-    <t>OBT</t>
-  </si>
-  <si>
-    <t>PRDO</t>
-  </si>
-  <si>
-    <t>TWIN</t>
-  </si>
-  <si>
-    <t>CIR</t>
-  </si>
-  <si>
-    <t>PDS</t>
-  </si>
-  <si>
-    <t>EDU</t>
-  </si>
-  <si>
-    <t>SM</t>
-  </si>
-  <si>
-    <t>FRSH</t>
-  </si>
-  <si>
-    <t>CEIX</t>
-  </si>
-  <si>
-    <t>COUR</t>
-  </si>
-  <si>
-    <t>FSLY</t>
-  </si>
-  <si>
-    <t>CMT</t>
-  </si>
-  <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>WLDN</t>
-  </si>
-  <si>
-    <t>ODC</t>
-  </si>
-  <si>
-    <t>ERIE</t>
-  </si>
-  <si>
-    <t>VNO</t>
-  </si>
-  <si>
-    <t>FN</t>
-  </si>
-  <si>
-    <t>AEO</t>
-  </si>
-  <si>
-    <t>EH</t>
-  </si>
-  <si>
-    <t>FSTR</t>
-  </si>
-  <si>
-    <t>GAMB</t>
-  </si>
-  <si>
-    <t>POWL</t>
-  </si>
-  <si>
-    <t>MNSO</t>
-  </si>
-  <si>
-    <t>TPL</t>
-  </si>
-  <si>
-    <t>IESC</t>
-  </si>
-  <si>
-    <t>RELY</t>
-  </si>
-  <si>
-    <t>CORT</t>
-  </si>
-  <si>
-    <t>KRT</t>
-  </si>
-  <si>
-    <t>IONQ</t>
-  </si>
-  <si>
-    <t>PAY</t>
-  </si>
-  <si>
-    <t>LEU</t>
-  </si>
-  <si>
-    <t>ACMR</t>
-  </si>
-  <si>
-    <t>VRTV</t>
-  </si>
-  <si>
-    <t>ESTE</t>
-  </si>
-  <si>
-    <t>MMYT</t>
-  </si>
-  <si>
-    <t>BOOM</t>
-  </si>
-  <si>
-    <t>PARR</t>
-  </si>
-  <si>
-    <t>PETQ</t>
-  </si>
-  <si>
-    <t>CPRI</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>CTRN</t>
-  </si>
-  <si>
-    <t>ANF</t>
-  </si>
-  <si>
-    <t>DLO</t>
-  </si>
-  <si>
-    <t>MOD</t>
-  </si>
-  <si>
-    <t>XPEV</t>
-  </si>
-  <si>
-    <t>RYTM</t>
-  </si>
-  <si>
-    <t>CBAY</t>
-  </si>
-  <si>
-    <t>SBOW</t>
-  </si>
-  <si>
-    <t>SRDX</t>
-  </si>
-  <si>
-    <t>CAMT</t>
-  </si>
-  <si>
-    <t>STRL</t>
-  </si>
-  <si>
-    <t>CLS</t>
-  </si>
-  <si>
-    <t>BBIO</t>
-  </si>
-  <si>
-    <t>PHVS</t>
-  </si>
-  <si>
-    <t>LMB</t>
-  </si>
-  <si>
-    <t>VRT</t>
-  </si>
-  <si>
-    <t>APP</t>
-  </si>
-  <si>
-    <t>ML</t>
-  </si>
-  <si>
-    <t>RETA</t>
-  </si>
-  <si>
-    <t>UPWK</t>
-  </si>
-  <si>
-    <t>CVNA</t>
-  </si>
-  <si>
-    <t>URGN</t>
-  </si>
-  <si>
-    <t>CDLX</t>
-  </si>
-  <si>
-    <t>TDS</t>
-  </si>
-  <si>
-    <t>USM</t>
-  </si>
-  <si>
-    <t>TSAT</t>
-  </si>
-  <si>
-    <t>EDTXU</t>
-  </si>
-  <si>
-    <t>EDTX</t>
-  </si>
-  <si>
-    <t>SGTX</t>
-  </si>
-  <si>
-    <t>AAOI</t>
+    <t>OZ</t>
+  </si>
+  <si>
+    <t>TIGO</t>
+  </si>
+  <si>
+    <t>FSS</t>
+  </si>
+  <si>
+    <t>SONY</t>
+  </si>
+  <si>
+    <t>BBU</t>
+  </si>
+  <si>
+    <t>KRNT</t>
+  </si>
+  <si>
+    <t>PRTC</t>
+  </si>
+  <si>
+    <t>CRNX</t>
+  </si>
+  <si>
+    <t>TR</t>
+  </si>
+  <si>
+    <t>MBUU</t>
+  </si>
+  <si>
+    <t>CHE</t>
+  </si>
+  <si>
+    <t>ARL</t>
+  </si>
+  <si>
+    <t>RHP</t>
+  </si>
+  <si>
+    <t>SPGI</t>
+  </si>
+  <si>
+    <t>IOT</t>
+  </si>
+  <si>
+    <t>BRT</t>
+  </si>
+  <si>
+    <t>TTEC</t>
+  </si>
+  <si>
+    <t>BE</t>
+  </si>
+  <si>
+    <t>VSH</t>
   </si>
 </sst>
 </file>
@@ -2116,7 +2110,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B583"/>
+  <dimension ref="A1:B581"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -2132,7 +2126,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1">
-        <v>108.6541878233259</v>
+        <v>36.44613518155683</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2140,7 +2134,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1">
-        <v>108.664767588674</v>
+        <v>34.65366820381705</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -2148,7 +2142,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1">
-        <v>108.6868041007391</v>
+        <v>34.53594956320657</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -2156,7 +2150,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="1">
-        <v>108.6945180944333</v>
+        <v>34.40191926610895</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -2164,7 +2158,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="1">
-        <v>108.726678229737</v>
+        <v>34.22697703780153</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -2172,7 +2166,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="1">
-        <v>108.7503505518207</v>
+        <v>34.20083531614338</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -2180,7 +2174,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="1">
-        <v>108.7606066510682</v>
+        <v>34.19444631520608</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -2188,7 +2182,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="1">
-        <v>108.7671326109623</v>
+        <v>34.19302837326239</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -2196,7 +2190,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="1">
-        <v>108.7756675799262</v>
+        <v>34.18349713479175</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -2204,7 +2198,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="1">
-        <v>108.7795913724433</v>
+        <v>34.17526705785681</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -2212,7 +2206,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="1">
-        <v>108.7813951800798</v>
+        <v>34.16357773169764</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -2220,7 +2214,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="1">
-        <v>108.8121919101746</v>
+        <v>34.15854572420383</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -2228,7 +2222,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="1">
-        <v>108.813754923784</v>
+        <v>34.15395625090404</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -2236,7 +2230,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="1">
-        <v>108.8433576971025</v>
+        <v>34.1532215967606</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -2244,7 +2238,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="1">
-        <v>108.8611846989841</v>
+        <v>34.14777388895773</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -2252,7 +2246,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="1">
-        <v>108.8964157710821</v>
+        <v>34.13748943874684</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -2260,7 +2254,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="1">
-        <v>108.9034874594899</v>
+        <v>34.09276107938651</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -2268,7 +2262,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="1">
-        <v>108.9059507828491</v>
+        <v>34.09204805524081</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -2276,7 +2270,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="1">
-        <v>108.9072120510168</v>
+        <v>34.03726263558264</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -2284,7 +2278,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="1">
-        <v>108.9158486310906</v>
+        <v>34.02600209163256</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -2292,7 +2286,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="1">
-        <v>108.9195377743651</v>
+        <v>34.01592244372451</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -2300,7 +2294,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="1">
-        <v>108.9200837240218</v>
+        <v>34.00782856685324</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -2308,7 +2302,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="1">
-        <v>108.9429593599016</v>
+        <v>34.00612922333337</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -2316,7 +2310,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="1">
-        <v>108.9672061586851</v>
+        <v>34.00408546130149</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -2324,7 +2318,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="1">
-        <v>108.9893510264152</v>
+        <v>33.99325229098142</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -2332,7 +2326,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="1">
-        <v>108.9969136743706</v>
+        <v>33.98291775587756</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -2340,7 +2334,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="1">
-        <v>109.0036834597021</v>
+        <v>33.96387337211537</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -2348,7 +2342,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="1">
-        <v>109.0337869704832</v>
+        <v>33.9471158304777</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -2356,7 +2350,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="1">
-        <v>109.0354976155129</v>
+        <v>33.93792880867697</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -2364,7 +2358,7 @@
         <v>31</v>
       </c>
       <c r="B31" s="1">
-        <v>109.0387751151719</v>
+        <v>33.92111273863861</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -2372,7 +2366,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="1">
-        <v>109.0406669765156</v>
+        <v>33.90831272690734</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -2380,7 +2374,7 @@
         <v>33</v>
       </c>
       <c r="B33" s="1">
-        <v>109.0591176349555</v>
+        <v>33.89113197543339</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -2388,7 +2382,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="1">
-        <v>109.0871581650757</v>
+        <v>33.87726089505646</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -2396,7 +2390,7 @@
         <v>35</v>
       </c>
       <c r="B35" s="1">
-        <v>109.1308276812391</v>
+        <v>33.87713448841662</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -2404,7 +2398,7 @@
         <v>36</v>
       </c>
       <c r="B36" s="1">
-        <v>109.1541448199019</v>
+        <v>33.87007743688464</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -2412,7 +2406,7 @@
         <v>37</v>
       </c>
       <c r="B37" s="1">
-        <v>109.1951223584257</v>
+        <v>33.85835352697505</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -2420,7 +2414,7 @@
         <v>38</v>
       </c>
       <c r="B38" s="1">
-        <v>109.2139498499748</v>
+        <v>33.85582121681148</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -2428,7 +2422,7 @@
         <v>39</v>
       </c>
       <c r="B39" s="1">
-        <v>109.2226617368752</v>
+        <v>33.85127117727878</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -2436,7 +2430,7 @@
         <v>40</v>
       </c>
       <c r="B40" s="1">
-        <v>109.2529216372053</v>
+        <v>33.85044099866683</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2444,7 +2438,7 @@
         <v>41</v>
       </c>
       <c r="B41" s="1">
-        <v>109.2537433142523</v>
+        <v>33.84102682593059</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2452,7 +2446,7 @@
         <v>42</v>
       </c>
       <c r="B42" s="1">
-        <v>109.2852718161785</v>
+        <v>33.83282961401182</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2460,7 +2454,7 @@
         <v>43</v>
       </c>
       <c r="B43" s="1">
-        <v>109.3033831865531</v>
+        <v>33.82715692467102</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2468,7 +2462,7 @@
         <v>44</v>
       </c>
       <c r="B44" s="1">
-        <v>109.3191734953404</v>
+        <v>33.81193301855625</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2476,7 +2470,7 @@
         <v>45</v>
       </c>
       <c r="B45" s="1">
-        <v>109.3204910636044</v>
+        <v>33.80708485304547</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2484,7 +2478,7 @@
         <v>46</v>
       </c>
       <c r="B46" s="1">
-        <v>109.3234688964561</v>
+        <v>33.78926133197449</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2492,7 +2486,7 @@
         <v>47</v>
       </c>
       <c r="B47" s="1">
-        <v>109.3359959115181</v>
+        <v>33.78664749819835</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2500,7 +2494,7 @@
         <v>48</v>
       </c>
       <c r="B48" s="1">
-        <v>109.3632982346311</v>
+        <v>33.78531336965244</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -2508,7 +2502,7 @@
         <v>49</v>
       </c>
       <c r="B49" s="1">
-        <v>109.3858801531355</v>
+        <v>33.78464525191141</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -2516,7 +2510,7 @@
         <v>50</v>
       </c>
       <c r="B50" s="1">
-        <v>109.3911761986673</v>
+        <v>33.77527199223735</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -2524,7 +2518,7 @@
         <v>51</v>
       </c>
       <c r="B51" s="1">
-        <v>109.3963997415775</v>
+        <v>33.76596044811614</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -2532,7 +2526,7 @@
         <v>52</v>
       </c>
       <c r="B52" s="1">
-        <v>109.4045928182428</v>
+        <v>33.7629498880229</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -2540,7 +2534,7 @@
         <v>53</v>
       </c>
       <c r="B53" s="1">
-        <v>109.4112288002551</v>
+        <v>33.76136885662964</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -2548,7 +2542,7 @@
         <v>54</v>
       </c>
       <c r="B54" s="1">
-        <v>109.4480760081051</v>
+        <v>33.75603913622456</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -2556,7 +2550,7 @@
         <v>55</v>
       </c>
       <c r="B55" s="1">
-        <v>109.4518397838625</v>
+        <v>33.75384644721159</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -2564,7 +2558,7 @@
         <v>56</v>
       </c>
       <c r="B56" s="1">
-        <v>109.4801060784987</v>
+        <v>33.75328143133117</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -2572,7 +2566,7 @@
         <v>57</v>
       </c>
       <c r="B57" s="1">
-        <v>109.4935347518899</v>
+        <v>33.74944051251085</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -2580,7 +2574,7 @@
         <v>58</v>
       </c>
       <c r="B58" s="1">
-        <v>109.5080104967122</v>
+        <v>33.74662692684737</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -2588,7 +2582,7 @@
         <v>59</v>
       </c>
       <c r="B59" s="1">
-        <v>109.5096027024098</v>
+        <v>33.74415975580974</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -2596,7 +2590,7 @@
         <v>60</v>
       </c>
       <c r="B60" s="1">
-        <v>109.532353190997</v>
+        <v>33.74099758660204</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -2604,7 +2598,7 @@
         <v>61</v>
       </c>
       <c r="B61" s="1">
-        <v>109.623310666245</v>
+        <v>33.74030888701294</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -2612,7 +2606,7 @@
         <v>62</v>
       </c>
       <c r="B62" s="1">
-        <v>109.6367468406861</v>
+        <v>33.73849459639311</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -2620,7 +2614,7 @@
         <v>63</v>
       </c>
       <c r="B63" s="1">
-        <v>109.6536589400593</v>
+        <v>33.73531844084999</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -2628,7 +2622,7 @@
         <v>64</v>
       </c>
       <c r="B64" s="1">
-        <v>109.7108023920208</v>
+        <v>33.73504928801169</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -2636,7 +2630,7 @@
         <v>65</v>
       </c>
       <c r="B65" s="1">
-        <v>109.7158188763976</v>
+        <v>33.73348217555029</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -2644,7 +2638,7 @@
         <v>66</v>
       </c>
       <c r="B66" s="1">
-        <v>109.7189358830763</v>
+        <v>33.73160629297406</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -2652,7 +2646,7 @@
         <v>67</v>
       </c>
       <c r="B67" s="1">
-        <v>109.733431878471</v>
+        <v>33.7285658879643</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -2660,7 +2654,7 @@
         <v>68</v>
       </c>
       <c r="B68" s="1">
-        <v>109.7374209284333</v>
+        <v>33.72570464002096</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -2668,7 +2662,7 @@
         <v>69</v>
       </c>
       <c r="B69" s="1">
-        <v>109.7484349390835</v>
+        <v>33.7196564180519</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -2676,7 +2670,7 @@
         <v>70</v>
       </c>
       <c r="B70" s="1">
-        <v>109.7558410579739</v>
+        <v>33.71884419243967</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -2684,7 +2678,7 @@
         <v>71</v>
       </c>
       <c r="B71" s="1">
-        <v>109.7681123561073</v>
+        <v>33.71281320532133</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -2692,7 +2686,7 @@
         <v>72</v>
       </c>
       <c r="B72" s="1">
-        <v>109.7874773321726</v>
+        <v>33.71106498428377</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2700,7 +2694,7 @@
         <v>73</v>
       </c>
       <c r="B73" s="1">
-        <v>109.8041022575253</v>
+        <v>33.7072516195818</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -2708,7 +2702,7 @@
         <v>74</v>
       </c>
       <c r="B74" s="1">
-        <v>109.8341930830541</v>
+        <v>33.70700363594543</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -2716,7 +2710,7 @@
         <v>75</v>
       </c>
       <c r="B75" s="1">
-        <v>109.8423217114095</v>
+        <v>33.70654984594174</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -2724,7 +2718,7 @@
         <v>76</v>
       </c>
       <c r="B76" s="1">
-        <v>109.8535548141814</v>
+        <v>33.70485298471279</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -2732,7 +2726,7 @@
         <v>77</v>
       </c>
       <c r="B77" s="1">
-        <v>109.8797978251421</v>
+        <v>33.70454859471369</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -2740,7 +2734,7 @@
         <v>78</v>
       </c>
       <c r="B78" s="1">
-        <v>109.9380133828587</v>
+        <v>33.70217961706629</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -2748,7 +2742,7 @@
         <v>79</v>
       </c>
       <c r="B79" s="1">
-        <v>109.9639638830205</v>
+        <v>33.69700546006359</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -2756,7 +2750,7 @@
         <v>80</v>
       </c>
       <c r="B80" s="1">
-        <v>109.9989392389046</v>
+        <v>33.69002627256219</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -2764,7 +2758,7 @@
         <v>81</v>
       </c>
       <c r="B81" s="1">
-        <v>110.0007919524907</v>
+        <v>33.68982649196746</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -2772,7 +2766,7 @@
         <v>82</v>
       </c>
       <c r="B82" s="1">
-        <v>110.0069241070703</v>
+        <v>33.68214219295197</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -2780,7 +2774,7 @@
         <v>83</v>
       </c>
       <c r="B83" s="1">
-        <v>110.0305264976416</v>
+        <v>33.68202660444511</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -2788,7 +2782,7 @@
         <v>84</v>
       </c>
       <c r="B84" s="1">
-        <v>110.0362533824624</v>
+        <v>33.67782978760407</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -2796,7 +2790,7 @@
         <v>85</v>
       </c>
       <c r="B85" s="1">
-        <v>110.0612418687082</v>
+        <v>33.67528878159981</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -2804,7 +2798,7 @@
         <v>86</v>
       </c>
       <c r="B86" s="1">
-        <v>110.0829488032846</v>
+        <v>33.67445641304788</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -2812,7 +2806,7 @@
         <v>87</v>
       </c>
       <c r="B87" s="1">
-        <v>110.0842363453334</v>
+        <v>33.67358478818616</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -2820,7 +2814,7 @@
         <v>88</v>
       </c>
       <c r="B88" s="1">
-        <v>110.0919921337981</v>
+        <v>33.67344169813305</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -2828,7 +2822,7 @@
         <v>89</v>
       </c>
       <c r="B89" s="1">
-        <v>110.0919954251345</v>
+        <v>33.66647855099281</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -2836,7 +2830,7 @@
         <v>90</v>
       </c>
       <c r="B90" s="1">
-        <v>110.1015921808671</v>
+        <v>33.66638374201854</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -2844,7 +2838,7 @@
         <v>91</v>
       </c>
       <c r="B91" s="1">
-        <v>110.1035574547346</v>
+        <v>33.66608650825937</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -2852,7 +2846,7 @@
         <v>92</v>
       </c>
       <c r="B92" s="1">
-        <v>110.1151998287071</v>
+        <v>33.66503002228749</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -2860,7 +2854,7 @@
         <v>93</v>
       </c>
       <c r="B93" s="1">
-        <v>110.1637121491319</v>
+        <v>33.66463012932737</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -2868,7 +2862,7 @@
         <v>94</v>
       </c>
       <c r="B94" s="1">
-        <v>110.1824578886186</v>
+        <v>33.6645295984429</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -2876,7 +2870,7 @@
         <v>95</v>
       </c>
       <c r="B95" s="1">
-        <v>110.1931153290264</v>
+        <v>33.66404599456532</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -2884,7 +2878,7 @@
         <v>96</v>
       </c>
       <c r="B96" s="1">
-        <v>110.1931827285504</v>
+        <v>33.66339579898486</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -2892,7 +2886,7 @@
         <v>97</v>
       </c>
       <c r="B97" s="1">
-        <v>110.1974248099182</v>
+        <v>33.66285634824642</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -2900,7 +2894,7 @@
         <v>98</v>
       </c>
       <c r="B98" s="1">
-        <v>110.1995993745136</v>
+        <v>33.66261583929639</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -2908,7 +2902,7 @@
         <v>99</v>
       </c>
       <c r="B99" s="1">
-        <v>110.2138492008338</v>
+        <v>33.66254964891767</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -2916,7 +2910,7 @@
         <v>100</v>
       </c>
       <c r="B100" s="1">
-        <v>110.2315692615862</v>
+        <v>33.66245281501764</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -2924,7 +2918,7 @@
         <v>101</v>
       </c>
       <c r="B101" s="1">
-        <v>110.2751401572244</v>
+        <v>33.66113563766851</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -2932,7 +2926,7 @@
         <v>102</v>
       </c>
       <c r="B102" s="1">
-        <v>110.283681163536</v>
+        <v>33.661086439395</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -2940,7 +2934,7 @@
         <v>103</v>
       </c>
       <c r="B103" s="1">
-        <v>110.2956826060586</v>
+        <v>33.65933597533992</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -2948,7 +2942,7 @@
         <v>104</v>
       </c>
       <c r="B104" s="1">
-        <v>110.3438377655099</v>
+        <v>33.6586381217352</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -2956,7 +2950,7 @@
         <v>105</v>
       </c>
       <c r="B105" s="1">
-        <v>110.361347258184</v>
+        <v>33.65656721148788</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -2964,7 +2958,7 @@
         <v>106</v>
       </c>
       <c r="B106" s="1">
-        <v>110.3732883240173</v>
+        <v>33.65585142315204</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -2972,7 +2966,7 @@
         <v>107</v>
       </c>
       <c r="B107" s="1">
-        <v>110.4392155247892</v>
+        <v>33.65320363990656</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -2980,7 +2974,7 @@
         <v>108</v>
       </c>
       <c r="B108" s="1">
-        <v>110.4669042286584</v>
+        <v>33.64996524387514</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -2988,7 +2982,7 @@
         <v>109</v>
       </c>
       <c r="B109" s="1">
-        <v>110.4721625528352</v>
+        <v>33.64864366849973</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -2996,7 +2990,7 @@
         <v>110</v>
       </c>
       <c r="B110" s="1">
-        <v>110.4903398788568</v>
+        <v>33.64853280976268</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -3004,7 +2998,7 @@
         <v>111</v>
       </c>
       <c r="B111" s="1">
-        <v>110.5172608330772</v>
+        <v>33.64811462524366</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -3012,7 +3006,7 @@
         <v>112</v>
       </c>
       <c r="B112" s="1">
-        <v>110.5252620604669</v>
+        <v>33.64773130718596</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -3020,7 +3014,7 @@
         <v>113</v>
       </c>
       <c r="B113" s="1">
-        <v>110.5612450842393</v>
+        <v>33.646002595559</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -3028,7 +3022,7 @@
         <v>114</v>
       </c>
       <c r="B114" s="1">
-        <v>110.5739463043869</v>
+        <v>33.64477377701716</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -3036,7 +3030,7 @@
         <v>115</v>
       </c>
       <c r="B115" s="1">
-        <v>110.6446821338508</v>
+        <v>33.64375265619612</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -3044,7 +3038,7 @@
         <v>116</v>
       </c>
       <c r="B116" s="1">
-        <v>110.651694263882</v>
+        <v>33.6420079667265</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -3052,7 +3046,7 @@
         <v>117</v>
       </c>
       <c r="B117" s="1">
-        <v>110.6819757110929</v>
+        <v>33.63809165128612</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -3060,7 +3054,7 @@
         <v>118</v>
       </c>
       <c r="B118" s="1">
-        <v>110.6989003896083</v>
+        <v>33.63738639254859</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -3068,7 +3062,7 @@
         <v>119</v>
       </c>
       <c r="B119" s="1">
-        <v>110.7077368723163</v>
+        <v>33.63609727702814</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -3076,7 +3070,7 @@
         <v>120</v>
       </c>
       <c r="B120" s="1">
-        <v>110.709574178167</v>
+        <v>33.63358295894011</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -3084,7 +3078,7 @@
         <v>121</v>
       </c>
       <c r="B121" s="1">
-        <v>110.7786222227785</v>
+        <v>33.6308166376149</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -3092,7 +3086,7 @@
         <v>122</v>
       </c>
       <c r="B122" s="1">
-        <v>110.7787941462775</v>
+        <v>33.63035028567044</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -3100,7 +3094,7 @@
         <v>123</v>
       </c>
       <c r="B123" s="1">
-        <v>110.7870513065502</v>
+        <v>33.62672165200224</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -3108,7 +3102,7 @@
         <v>124</v>
       </c>
       <c r="B124" s="1">
-        <v>110.7958620176886</v>
+        <v>33.62658145683927</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -3116,7 +3110,7 @@
         <v>125</v>
       </c>
       <c r="B125" s="1">
-        <v>110.8163512830035</v>
+        <v>33.6255196369098</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -3124,7 +3118,7 @@
         <v>126</v>
       </c>
       <c r="B126" s="1">
-        <v>110.8470684195164</v>
+        <v>33.62162913083299</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -3132,7 +3126,7 @@
         <v>127</v>
       </c>
       <c r="B127" s="1">
-        <v>110.8480556768133</v>
+        <v>33.62144645805729</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -3140,7 +3134,7 @@
         <v>128</v>
       </c>
       <c r="B128" s="1">
-        <v>110.8490115704361</v>
+        <v>33.62113446293507</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -3148,7 +3142,7 @@
         <v>129</v>
       </c>
       <c r="B129" s="1">
-        <v>110.8628814110862</v>
+        <v>33.61886864832594</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -3156,7 +3150,7 @@
         <v>130</v>
       </c>
       <c r="B130" s="1">
-        <v>110.8726469464798</v>
+        <v>33.61851827248075</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -3164,7 +3158,7 @@
         <v>131</v>
       </c>
       <c r="B131" s="1">
-        <v>110.9163444416006</v>
+        <v>33.61708154762857</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -3172,7 +3166,7 @@
         <v>132</v>
       </c>
       <c r="B132" s="1">
-        <v>110.9302227585751</v>
+        <v>33.61634295068241</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -3180,7 +3174,7 @@
         <v>133</v>
       </c>
       <c r="B133" s="1">
-        <v>110.9731120101126</v>
+        <v>33.61563974818901</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -3188,7 +3182,7 @@
         <v>134</v>
       </c>
       <c r="B134" s="1">
-        <v>111.0183512527371</v>
+        <v>33.61380907991782</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -3196,7 +3190,7 @@
         <v>135</v>
       </c>
       <c r="B135" s="1">
-        <v>111.0208985248642</v>
+        <v>33.61352272120368</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -3204,7 +3198,7 @@
         <v>136</v>
       </c>
       <c r="B136" s="1">
-        <v>111.0381702619269</v>
+        <v>33.61236007014958</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -3212,7 +3206,7 @@
         <v>137</v>
       </c>
       <c r="B137" s="1">
-        <v>111.1006087660603</v>
+        <v>33.61232321095412</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -3220,7 +3214,7 @@
         <v>138</v>
       </c>
       <c r="B138" s="1">
-        <v>111.1299918670148</v>
+        <v>33.61141495886937</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -3228,7 +3222,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="1">
-        <v>111.1300592596378</v>
+        <v>33.61096086443218</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -3236,7 +3230,7 @@
         <v>140</v>
       </c>
       <c r="B140" s="1">
-        <v>111.2004573613926</v>
+        <v>33.61089010465346</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -3244,7 +3238,7 @@
         <v>141</v>
       </c>
       <c r="B141" s="1">
-        <v>111.2191497627486</v>
+        <v>33.61064561036468</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -3252,7 +3246,7 @@
         <v>142</v>
       </c>
       <c r="B142" s="1">
-        <v>111.2278183218817</v>
+        <v>33.61000272799174</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -3260,7 +3254,7 @@
         <v>143</v>
       </c>
       <c r="B143" s="1">
-        <v>111.2763132591377</v>
+        <v>33.60818111921201</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -3268,7 +3262,7 @@
         <v>144</v>
       </c>
       <c r="B144" s="1">
-        <v>111.2906595427569</v>
+        <v>33.60752632823576</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -3276,7 +3270,7 @@
         <v>145</v>
       </c>
       <c r="B145" s="1">
-        <v>111.3261715141003</v>
+        <v>33.60742780942049</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -3284,7 +3278,7 @@
         <v>146</v>
       </c>
       <c r="B146" s="1">
-        <v>111.3307983913146</v>
+        <v>33.60708405453028</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -3292,7 +3286,7 @@
         <v>147</v>
       </c>
       <c r="B147" s="1">
-        <v>111.3451847448531</v>
+        <v>33.60656495348044</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -3300,7 +3294,7 @@
         <v>148</v>
       </c>
       <c r="B148" s="1">
-        <v>111.3538163878421</v>
+        <v>33.60600797249231</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -3308,7 +3302,7 @@
         <v>149</v>
       </c>
       <c r="B149" s="1">
-        <v>111.4090401097603</v>
+        <v>33.60541047088312</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -3316,7 +3310,7 @@
         <v>150</v>
       </c>
       <c r="B150" s="1">
-        <v>111.4311785446576</v>
+        <v>33.60505346855464</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -3324,7 +3318,7 @@
         <v>151</v>
       </c>
       <c r="B151" s="1">
-        <v>111.4347538265135</v>
+        <v>33.60461873573311</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -3332,7 +3326,7 @@
         <v>152</v>
       </c>
       <c r="B152" s="1">
-        <v>111.4834688505973</v>
+        <v>33.60267748004217</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -3340,7 +3334,7 @@
         <v>153</v>
       </c>
       <c r="B153" s="1">
-        <v>111.5224098402282</v>
+        <v>33.60182600168687</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -3348,7 +3342,7 @@
         <v>154</v>
       </c>
       <c r="B154" s="1">
-        <v>111.5299227889456</v>
+        <v>33.59914241770848</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -3356,7 +3350,7 @@
         <v>155</v>
       </c>
       <c r="B155" s="1">
-        <v>111.6357436095442</v>
+        <v>33.59517240976987</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -3364,7 +3358,7 @@
         <v>156</v>
       </c>
       <c r="B156" s="1">
-        <v>111.6451202037525</v>
+        <v>33.59387982282053</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -3372,7 +3366,7 @@
         <v>157</v>
       </c>
       <c r="B157" s="1">
-        <v>111.6453169679832</v>
+        <v>33.59328609313215</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -3380,7 +3374,7 @@
         <v>158</v>
       </c>
       <c r="B158" s="1">
-        <v>111.6654419730041</v>
+        <v>33.59244201854055</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -3388,7 +3382,7 @@
         <v>159</v>
       </c>
       <c r="B159" s="1">
-        <v>111.6665838908569</v>
+        <v>33.59181542477126</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -3396,7 +3390,7 @@
         <v>160</v>
       </c>
       <c r="B160" s="1">
-        <v>111.677833687265</v>
+        <v>33.59140092943387</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -3404,7 +3398,7 @@
         <v>161</v>
       </c>
       <c r="B161" s="1">
-        <v>111.7007675885576</v>
+        <v>33.59131631875091</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -3412,7 +3406,7 @@
         <v>162</v>
       </c>
       <c r="B162" s="1">
-        <v>111.7251640155633</v>
+        <v>33.58915202658722</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -3420,7 +3414,7 @@
         <v>163</v>
       </c>
       <c r="B163" s="1">
-        <v>111.7481306295452</v>
+        <v>33.58897382859155</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -3428,7 +3422,7 @@
         <v>164</v>
       </c>
       <c r="B164" s="1">
-        <v>111.7514807869026</v>
+        <v>33.58797710733226</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -3436,7 +3430,7 @@
         <v>165</v>
       </c>
       <c r="B165" s="1">
-        <v>111.7722392394721</v>
+        <v>33.58780086724585</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -3444,7 +3438,7 @@
         <v>166</v>
       </c>
       <c r="B166" s="1">
-        <v>111.7992388138016</v>
+        <v>33.58569003075665</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -3452,7 +3446,7 @@
         <v>167</v>
       </c>
       <c r="B167" s="1">
-        <v>111.8173339167051</v>
+        <v>33.58467547204801</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -3460,7 +3454,7 @@
         <v>168</v>
       </c>
       <c r="B168" s="1">
-        <v>111.8594464410554</v>
+        <v>33.58457652931642</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -3468,7 +3462,7 @@
         <v>169</v>
       </c>
       <c r="B169" s="1">
-        <v>111.8621902098471</v>
+        <v>33.58440100833992</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -3476,7 +3470,7 @@
         <v>170</v>
       </c>
       <c r="B170" s="1">
-        <v>111.8649356369658</v>
+        <v>33.584299577335</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -3484,7 +3478,7 @@
         <v>171</v>
       </c>
       <c r="B171" s="1">
-        <v>111.9045681639048</v>
+        <v>33.58427085588485</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -3492,7 +3486,7 @@
         <v>172</v>
       </c>
       <c r="B172" s="1">
-        <v>111.9054493972529</v>
+        <v>33.58317659616827</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -3500,7 +3494,7 @@
         <v>173</v>
       </c>
       <c r="B173" s="1">
-        <v>111.9082874074293</v>
+        <v>33.58276605318171</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -3508,7 +3502,7 @@
         <v>174</v>
       </c>
       <c r="B174" s="1">
-        <v>111.9121725809974</v>
+        <v>33.58259801762527</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -3516,7 +3510,7 @@
         <v>175</v>
       </c>
       <c r="B175" s="1">
-        <v>111.9407073096489</v>
+        <v>33.5817053945409</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -3524,7 +3518,7 @@
         <v>176</v>
       </c>
       <c r="B176" s="1">
-        <v>111.9481611153545</v>
+        <v>33.58099838132468</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -3532,7 +3526,7 @@
         <v>177</v>
       </c>
       <c r="B177" s="1">
-        <v>111.9520343361331</v>
+        <v>33.58064973738191</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -3540,7 +3534,7 @@
         <v>178</v>
       </c>
       <c r="B178" s="1">
-        <v>111.9691590125399</v>
+        <v>33.5774441455762</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -3548,7 +3542,7 @@
         <v>179</v>
       </c>
       <c r="B179" s="1">
-        <v>111.9718046154938</v>
+        <v>33.57735568854005</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -3556,7 +3550,7 @@
         <v>180</v>
       </c>
       <c r="B180" s="1">
-        <v>111.9780023377533</v>
+        <v>33.57707238027583</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -3564,7 +3558,7 @@
         <v>181</v>
       </c>
       <c r="B181" s="1">
-        <v>111.9906775817554</v>
+        <v>33.57680362891305</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -3572,7 +3566,7 @@
         <v>182</v>
       </c>
       <c r="B182" s="1">
-        <v>112.069824793466</v>
+        <v>33.57669642967971</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -3580,7 +3574,7 @@
         <v>183</v>
       </c>
       <c r="B183" s="1">
-        <v>112.0746921395195</v>
+        <v>33.57657211251372</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -3588,7 +3582,7 @@
         <v>184</v>
       </c>
       <c r="B184" s="1">
-        <v>112.0882389931314</v>
+        <v>33.57403993809609</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -3596,7 +3590,7 @@
         <v>185</v>
       </c>
       <c r="B185" s="1">
-        <v>112.1079572242092</v>
+        <v>33.57297971620446</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -3604,7 +3598,7 @@
         <v>186</v>
       </c>
       <c r="B186" s="1">
-        <v>112.1590832967887</v>
+        <v>33.57273961485839</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -3612,7 +3606,7 @@
         <v>187</v>
       </c>
       <c r="B187" s="1">
-        <v>112.1802968606833</v>
+        <v>33.57219262073743</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -3620,7 +3614,7 @@
         <v>188</v>
       </c>
       <c r="B188" s="1">
-        <v>112.227735926473</v>
+        <v>33.5712875939003</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -3628,7 +3622,7 @@
         <v>189</v>
       </c>
       <c r="B189" s="1">
-        <v>112.2528499077744</v>
+        <v>33.57109754413467</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -3636,7 +3630,7 @@
         <v>190</v>
       </c>
       <c r="B190" s="1">
-        <v>112.2957715387944</v>
+        <v>33.56914510937698</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -3644,7 +3638,7 @@
         <v>191</v>
       </c>
       <c r="B191" s="1">
-        <v>112.3198559618261</v>
+        <v>33.56838146369305</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -3652,7 +3646,7 @@
         <v>192</v>
       </c>
       <c r="B192" s="1">
-        <v>112.3390354981857</v>
+        <v>33.56769150954084</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -3660,7 +3654,7 @@
         <v>193</v>
       </c>
       <c r="B193" s="1">
-        <v>112.3494425634043</v>
+        <v>33.56577569177654</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -3668,7 +3662,7 @@
         <v>194</v>
       </c>
       <c r="B194" s="1">
-        <v>112.3819844229076</v>
+        <v>33.56565682084993</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -3676,7 +3670,7 @@
         <v>195</v>
       </c>
       <c r="B195" s="1">
-        <v>112.4008488610883</v>
+        <v>33.56554559828594</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -3684,7 +3678,7 @@
         <v>196</v>
       </c>
       <c r="B196" s="1">
-        <v>112.4580362540257</v>
+        <v>33.56526044415597</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -3692,7 +3686,7 @@
         <v>197</v>
       </c>
       <c r="B197" s="1">
-        <v>112.4682675083315</v>
+        <v>33.56324935914405</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -3700,7 +3694,7 @@
         <v>198</v>
       </c>
       <c r="B198" s="1">
-        <v>112.4686369397608</v>
+        <v>33.56196100328156</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -3708,7 +3702,7 @@
         <v>199</v>
       </c>
       <c r="B199" s="1">
-        <v>112.4734112149274</v>
+        <v>33.55979608422593</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -3716,7 +3710,7 @@
         <v>200</v>
       </c>
       <c r="B200" s="1">
-        <v>112.5051929042053</v>
+        <v>33.55739637332457</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -3724,7 +3718,7 @@
         <v>201</v>
       </c>
       <c r="B201" s="1">
-        <v>112.5068020696144</v>
+        <v>33.55733987172364</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -3732,7 +3726,7 @@
         <v>202</v>
       </c>
       <c r="B202" s="1">
-        <v>112.5660440153347</v>
+        <v>33.55676861158825</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -3740,7 +3734,7 @@
         <v>203</v>
       </c>
       <c r="B203" s="1">
-        <v>112.5732898130175</v>
+        <v>33.55643444653035</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -3748,7 +3742,7 @@
         <v>204</v>
       </c>
       <c r="B204" s="1">
-        <v>112.6295974995</v>
+        <v>33.55617556363828</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -3756,7 +3750,7 @@
         <v>205</v>
       </c>
       <c r="B205" s="1">
-        <v>112.6392065598057</v>
+        <v>33.55538762196388</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -3764,7 +3758,7 @@
         <v>206</v>
       </c>
       <c r="B206" s="1">
-        <v>112.6542017582276</v>
+        <v>33.55400475907953</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -3772,7 +3766,7 @@
         <v>207</v>
       </c>
       <c r="B207" s="1">
-        <v>112.6737397148334</v>
+        <v>33.55350003539543</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -3780,7 +3774,7 @@
         <v>208</v>
       </c>
       <c r="B208" s="1">
-        <v>112.6751029490665</v>
+        <v>33.55211263413402</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -3788,7 +3782,7 @@
         <v>209</v>
       </c>
       <c r="B209" s="1">
-        <v>112.6782759354937</v>
+        <v>33.55088780718492</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -3796,7 +3790,7 @@
         <v>210</v>
       </c>
       <c r="B210" s="1">
-        <v>112.6814745447344</v>
+        <v>33.54944617098973</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -3804,7 +3798,7 @@
         <v>211</v>
       </c>
       <c r="B211" s="1">
-        <v>112.7034978502298</v>
+        <v>33.54826310823798</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -3812,7 +3806,7 @@
         <v>212</v>
       </c>
       <c r="B212" s="1">
-        <v>112.7321892144345</v>
+        <v>33.54816864209702</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -3820,7 +3814,7 @@
         <v>213</v>
       </c>
       <c r="B213" s="1">
-        <v>112.7653547304883</v>
+        <v>33.54677377523422</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -3828,7 +3822,7 @@
         <v>214</v>
       </c>
       <c r="B214" s="1">
-        <v>112.7806677357717</v>
+        <v>33.54672818342289</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -3836,7 +3830,7 @@
         <v>215</v>
       </c>
       <c r="B215" s="1">
-        <v>112.784723501314</v>
+        <v>33.54624841171944</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -3844,7 +3838,7 @@
         <v>216</v>
       </c>
       <c r="B216" s="1">
-        <v>112.7980709520567</v>
+        <v>33.54612352744698</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -3852,7 +3846,7 @@
         <v>217</v>
       </c>
       <c r="B217" s="1">
-        <v>112.8303691640817</v>
+        <v>33.54455808267972</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -3860,7 +3854,7 @@
         <v>218</v>
       </c>
       <c r="B218" s="1">
-        <v>112.8494968393406</v>
+        <v>33.54305618496925</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -3868,7 +3862,7 @@
         <v>219</v>
       </c>
       <c r="B219" s="1">
-        <v>112.8869611278936</v>
+        <v>33.54297750272539</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -3876,7 +3870,7 @@
         <v>220</v>
       </c>
       <c r="B220" s="1">
-        <v>112.9013485889429</v>
+        <v>33.54260053304136</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -3884,7 +3878,7 @@
         <v>221</v>
       </c>
       <c r="B221" s="1">
-        <v>112.9133845217914</v>
+        <v>33.54246101521937</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -3892,7 +3886,7 @@
         <v>222</v>
       </c>
       <c r="B222" s="1">
-        <v>112.9400548612031</v>
+        <v>33.54167246593043</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -3900,7 +3894,7 @@
         <v>223</v>
       </c>
       <c r="B223" s="1">
-        <v>112.9472333045595</v>
+        <v>33.54118271524746</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -3908,7 +3902,7 @@
         <v>224</v>
       </c>
       <c r="B224" s="1">
-        <v>112.957357175609</v>
+        <v>33.54078993903427</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -3916,7 +3910,7 @@
         <v>225</v>
       </c>
       <c r="B225" s="1">
-        <v>112.9732975200876</v>
+        <v>33.54074567257591</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -3924,7 +3918,7 @@
         <v>226</v>
       </c>
       <c r="B226" s="1">
-        <v>112.9936931111751</v>
+        <v>33.54057214803066</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -3932,7 +3926,7 @@
         <v>227</v>
       </c>
       <c r="B227" s="1">
-        <v>112.995256082783</v>
+        <v>33.54044026892929</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -3940,7 +3934,7 @@
         <v>228</v>
       </c>
       <c r="B228" s="1">
-        <v>113.0273590248876</v>
+        <v>33.54009774936439</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -3948,7 +3942,7 @@
         <v>229</v>
       </c>
       <c r="B229" s="1">
-        <v>113.0692856940382</v>
+        <v>33.53996017525156</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -3956,7 +3950,7 @@
         <v>230</v>
       </c>
       <c r="B230" s="1">
-        <v>113.1198047633826</v>
+        <v>33.53974412448621</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -3964,7 +3958,7 @@
         <v>231</v>
       </c>
       <c r="B231" s="1">
-        <v>113.1261475051322</v>
+        <v>33.53747696475274</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -3972,7 +3966,7 @@
         <v>232</v>
       </c>
       <c r="B232" s="1">
-        <v>113.1596231424052</v>
+        <v>33.53676176616997</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -3980,7 +3974,7 @@
         <v>233</v>
       </c>
       <c r="B233" s="1">
-        <v>113.1691047701156</v>
+        <v>33.53657670138312</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -3988,7 +3982,7 @@
         <v>234</v>
       </c>
       <c r="B234" s="1">
-        <v>113.1939466142302</v>
+        <v>33.53596066840399</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -3996,7 +3990,7 @@
         <v>235</v>
       </c>
       <c r="B235" s="1">
-        <v>113.2057892887621</v>
+        <v>33.53585567632238</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -4004,7 +3998,7 @@
         <v>236</v>
       </c>
       <c r="B236" s="1">
-        <v>113.2434269675169</v>
+        <v>33.53580519904816</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -4012,7 +4006,7 @@
         <v>237</v>
       </c>
       <c r="B237" s="1">
-        <v>113.2494553871121</v>
+        <v>33.53543247752344</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -4020,7 +4014,7 @@
         <v>238</v>
       </c>
       <c r="B238" s="1">
-        <v>113.2523349726654</v>
+        <v>33.53500615817512</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -4028,7 +4022,7 @@
         <v>239</v>
       </c>
       <c r="B239" s="1">
-        <v>113.321780991502</v>
+        <v>33.53314938504023</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -4036,7 +4030,7 @@
         <v>240</v>
       </c>
       <c r="B240" s="1">
-        <v>113.3661740329412</v>
+        <v>33.53179905047373</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -4044,7 +4038,7 @@
         <v>241</v>
       </c>
       <c r="B241" s="1">
-        <v>113.4095399441479</v>
+        <v>33.53010687927653</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -4052,7 +4046,7 @@
         <v>242</v>
       </c>
       <c r="B242" s="1">
-        <v>113.4495262783349</v>
+        <v>33.52974548526097</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -4060,7 +4054,7 @@
         <v>243</v>
       </c>
       <c r="B243" s="1">
-        <v>113.4800005255514</v>
+        <v>33.52972796557045</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -4068,7 +4062,7 @@
         <v>244</v>
       </c>
       <c r="B244" s="1">
-        <v>113.4864316222028</v>
+        <v>33.52946152609403</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -4076,7 +4070,7 @@
         <v>245</v>
       </c>
       <c r="B245" s="1">
-        <v>113.4883206476719</v>
+        <v>33.52888850155016</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -4084,7 +4078,7 @@
         <v>246</v>
       </c>
       <c r="B246" s="1">
-        <v>113.5106374423223</v>
+        <v>33.52859851422897</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -4092,7 +4086,7 @@
         <v>247</v>
       </c>
       <c r="B247" s="1">
-        <v>113.5346776113842</v>
+        <v>33.5282370866283</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -4100,7 +4094,7 @@
         <v>248</v>
       </c>
       <c r="B248" s="1">
-        <v>113.5548298117168</v>
+        <v>33.52744895919876</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -4108,7 +4102,7 @@
         <v>249</v>
       </c>
       <c r="B249" s="1">
-        <v>113.5570216478002</v>
+        <v>33.52711758675506</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -4116,7 +4110,7 @@
         <v>250</v>
       </c>
       <c r="B250" s="1">
-        <v>113.5698285443022</v>
+        <v>33.52659515393254</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -4124,7 +4118,7 @@
         <v>251</v>
       </c>
       <c r="B251" s="1">
-        <v>113.602030682785</v>
+        <v>33.52604679065968</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -4132,7 +4126,7 @@
         <v>252</v>
       </c>
       <c r="B252" s="1">
-        <v>113.6051795385633</v>
+        <v>33.5257108697046</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -4140,7 +4134,7 @@
         <v>253</v>
       </c>
       <c r="B253" s="1">
-        <v>113.6055297356287</v>
+        <v>33.52485335906608</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -4148,7 +4142,7 @@
         <v>254</v>
       </c>
       <c r="B254" s="1">
-        <v>113.6083975420092</v>
+        <v>33.52472920443488</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -4156,7 +4150,7 @@
         <v>255</v>
       </c>
       <c r="B255" s="1">
-        <v>113.6169302498038</v>
+        <v>33.52451328177003</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -4164,7 +4158,7 @@
         <v>256</v>
       </c>
       <c r="B256" s="1">
-        <v>113.6644901681912</v>
+        <v>33.52417611510023</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -4172,7 +4166,7 @@
         <v>257</v>
       </c>
       <c r="B257" s="1">
-        <v>113.6695363421643</v>
+        <v>33.52322647642823</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -4180,7 +4174,7 @@
         <v>258</v>
       </c>
       <c r="B258" s="1">
-        <v>113.6901676957353</v>
+        <v>33.52265461912715</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -4188,7 +4182,7 @@
         <v>259</v>
       </c>
       <c r="B259" s="1">
-        <v>113.6953411059119</v>
+        <v>33.52200170592638</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -4196,7 +4190,7 @@
         <v>260</v>
       </c>
       <c r="B260" s="1">
-        <v>113.6967821272123</v>
+        <v>33.52152535494837</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -4204,7 +4198,7 @@
         <v>261</v>
       </c>
       <c r="B261" s="1">
-        <v>113.6990857975118</v>
+        <v>33.52150572005971</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -4212,7 +4206,7 @@
         <v>262</v>
       </c>
       <c r="B262" s="1">
-        <v>113.7232878159068</v>
+        <v>33.5206564091875</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -4220,7 +4214,7 @@
         <v>263</v>
       </c>
       <c r="B263" s="1">
-        <v>113.7286116868798</v>
+        <v>33.52010526568967</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -4228,7 +4222,7 @@
         <v>264</v>
       </c>
       <c r="B264" s="1">
-        <v>113.7873413500043</v>
+        <v>33.51947172842235</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -4236,7 +4230,7 @@
         <v>265</v>
       </c>
       <c r="B265" s="1">
-        <v>113.7920671271025</v>
+        <v>33.5193372273214</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -4244,7 +4238,7 @@
         <v>266</v>
       </c>
       <c r="B266" s="1">
-        <v>113.7964481200459</v>
+        <v>33.51809691468788</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -4252,7 +4246,7 @@
         <v>267</v>
       </c>
       <c r="B267" s="1">
-        <v>113.8073260438493</v>
+        <v>33.51506102259103</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -4260,7 +4254,7 @@
         <v>268</v>
       </c>
       <c r="B268" s="1">
-        <v>113.849793348492</v>
+        <v>33.5148712734746</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -4268,7 +4262,7 @@
         <v>269</v>
       </c>
       <c r="B269" s="1">
-        <v>113.8538222857482</v>
+        <v>33.51383573310397</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -4276,7 +4270,7 @@
         <v>270</v>
       </c>
       <c r="B270" s="1">
-        <v>113.8577782549808</v>
+        <v>33.51375258340561</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -4284,7 +4278,7 @@
         <v>271</v>
       </c>
       <c r="B271" s="1">
-        <v>113.891445380596</v>
+        <v>33.51365843675482</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -4292,7 +4286,7 @@
         <v>272</v>
       </c>
       <c r="B272" s="1">
-        <v>113.9410080910135</v>
+        <v>33.51356179861448</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -4300,7 +4294,7 @@
         <v>273</v>
       </c>
       <c r="B273" s="1">
-        <v>113.9723817647356</v>
+        <v>33.51321583396935</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -4308,7 +4302,7 @@
         <v>274</v>
       </c>
       <c r="B274" s="1">
-        <v>113.9777178796051</v>
+        <v>33.51275272107269</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -4316,7 +4310,7 @@
         <v>275</v>
       </c>
       <c r="B275" s="1">
-        <v>113.9825109767834</v>
+        <v>33.51252278492969</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -4324,7 +4318,7 @@
         <v>276</v>
       </c>
       <c r="B276" s="1">
-        <v>113.9868423449374</v>
+        <v>33.5124331423858</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -4332,7 +4326,7 @@
         <v>277</v>
       </c>
       <c r="B277" s="1">
-        <v>114.0806323016397</v>
+        <v>33.51214508590646</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -4340,7 +4334,7 @@
         <v>278</v>
       </c>
       <c r="B278" s="1">
-        <v>114.1047046962834</v>
+        <v>33.51208850265445</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -4348,7 +4342,7 @@
         <v>279</v>
       </c>
       <c r="B279" s="1">
-        <v>114.1071518051587</v>
+        <v>33.511781105214</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -4356,7 +4350,7 @@
         <v>280</v>
       </c>
       <c r="B280" s="1">
-        <v>114.1194156759649</v>
+        <v>33.51116767886082</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -4364,7 +4358,7 @@
         <v>281</v>
       </c>
       <c r="B281" s="1">
-        <v>114.1563817395504</v>
+        <v>33.51093989216193</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -4372,7 +4366,7 @@
         <v>282</v>
       </c>
       <c r="B282" s="1">
-        <v>114.2872316556573</v>
+        <v>33.51016810318954</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -4380,7 +4374,7 @@
         <v>283</v>
       </c>
       <c r="B283" s="1">
-        <v>114.2898120166434</v>
+        <v>33.51014040561623</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -4388,7 +4382,7 @@
         <v>284</v>
       </c>
       <c r="B284" s="1">
-        <v>114.3166186505254</v>
+        <v>33.50946498338728</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -4396,7 +4390,7 @@
         <v>285</v>
       </c>
       <c r="B285" s="1">
-        <v>114.3244740798967</v>
+        <v>33.50907558729255</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -4404,7 +4398,7 @@
         <v>286</v>
       </c>
       <c r="B286" s="1">
-        <v>114.360009878749</v>
+        <v>33.5085243791204</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -4412,7 +4406,7 @@
         <v>287</v>
       </c>
       <c r="B287" s="1">
-        <v>114.4020731894207</v>
+        <v>33.5084391669539</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -4420,7 +4414,7 @@
         <v>288</v>
       </c>
       <c r="B288" s="1">
-        <v>114.4065932954779</v>
+        <v>33.50836973517723</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -4428,7 +4422,7 @@
         <v>289</v>
       </c>
       <c r="B289" s="1">
-        <v>114.4528141319316</v>
+        <v>33.50821793131691</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -4436,7 +4430,7 @@
         <v>290</v>
       </c>
       <c r="B290" s="1">
-        <v>114.4604015436887</v>
+        <v>33.50780364171419</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -4444,7 +4438,7 @@
         <v>291</v>
       </c>
       <c r="B291" s="1">
-        <v>114.4907167381965</v>
+        <v>33.50662978925057</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -4452,7 +4446,7 @@
         <v>292</v>
       </c>
       <c r="B292" s="1">
-        <v>114.5015419446152</v>
+        <v>33.50657695820964</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -4460,7 +4454,7 @@
         <v>293</v>
       </c>
       <c r="B293" s="1">
-        <v>114.5051753380617</v>
+        <v>33.50654233507819</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -4468,7 +4462,7 @@
         <v>294</v>
       </c>
       <c r="B294" s="1">
-        <v>114.5550147565222</v>
+        <v>33.50625982874203</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -4476,7 +4470,7 @@
         <v>295</v>
       </c>
       <c r="B295" s="1">
-        <v>114.5782283900252</v>
+        <v>33.50577558267416</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -4484,7 +4478,7 @@
         <v>296</v>
       </c>
       <c r="B296" s="1">
-        <v>114.578766643326</v>
+        <v>33.5055498205697</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -4492,7 +4486,7 @@
         <v>297</v>
       </c>
       <c r="B297" s="1">
-        <v>114.5857660078372</v>
+        <v>33.50482699065955</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -4500,7 +4494,7 @@
         <v>298</v>
       </c>
       <c r="B298" s="1">
-        <v>114.6170498917687</v>
+        <v>33.50444142929251</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -4508,7 +4502,7 @@
         <v>299</v>
       </c>
       <c r="B299" s="1">
-        <v>114.7271675512593</v>
+        <v>33.50442146571053</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -4516,7 +4510,7 @@
         <v>300</v>
       </c>
       <c r="B300" s="1">
-        <v>114.7394752279948</v>
+        <v>33.50408706151101</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -4524,7 +4518,7 @@
         <v>301</v>
       </c>
       <c r="B301" s="1">
-        <v>114.7446438684924</v>
+        <v>33.5035316021444</v>
       </c>
     </row>
     <row r="302" spans="1:2">
@@ -4532,7 +4526,7 @@
         <v>302</v>
       </c>
       <c r="B302" s="1">
-        <v>114.7607668558996</v>
+        <v>33.50302970815921</v>
       </c>
     </row>
     <row r="303" spans="1:2">
@@ -4540,7 +4534,7 @@
         <v>303</v>
       </c>
       <c r="B303" s="1">
-        <v>114.7622921935814</v>
+        <v>33.50239523682603</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -4548,7 +4542,7 @@
         <v>304</v>
       </c>
       <c r="B304" s="1">
-        <v>114.8030878457459</v>
+        <v>33.50201947985732</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -4556,7 +4550,7 @@
         <v>305</v>
       </c>
       <c r="B305" s="1">
-        <v>114.8033355833749</v>
+        <v>33.50143288014112</v>
       </c>
     </row>
     <row r="306" spans="1:2">
@@ -4564,7 +4558,7 @@
         <v>306</v>
       </c>
       <c r="B306" s="1">
-        <v>114.8066842331193</v>
+        <v>33.50098237592076</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -4572,7 +4566,7 @@
         <v>307</v>
       </c>
       <c r="B307" s="1">
-        <v>114.830654267211</v>
+        <v>33.50096049653843</v>
       </c>
     </row>
     <row r="308" spans="1:2">
@@ -4580,7 +4574,7 @@
         <v>308</v>
       </c>
       <c r="B308" s="1">
-        <v>114.8639652312031</v>
+        <v>33.50093392556688</v>
       </c>
     </row>
     <row r="309" spans="1:2">
@@ -4588,7 +4582,7 @@
         <v>309</v>
       </c>
       <c r="B309" s="1">
-        <v>114.8706712209531</v>
+        <v>33.50077351625767</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -4596,7 +4590,7 @@
         <v>310</v>
       </c>
       <c r="B310" s="1">
-        <v>114.9152823307876</v>
+        <v>33.49985170670804</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -4604,7 +4598,7 @@
         <v>311</v>
       </c>
       <c r="B311" s="1">
-        <v>114.9334221102505</v>
+        <v>33.49940900663834</v>
       </c>
     </row>
     <row r="312" spans="1:2">
@@ -4612,7 +4606,7 @@
         <v>312</v>
       </c>
       <c r="B312" s="1">
-        <v>114.9720511419248</v>
+        <v>33.49936767124986</v>
       </c>
     </row>
     <row r="313" spans="1:2">
@@ -4620,7 +4614,7 @@
         <v>313</v>
       </c>
       <c r="B313" s="1">
-        <v>114.9738609925148</v>
+        <v>33.49872894047522</v>
       </c>
     </row>
     <row r="314" spans="1:2">
@@ -4628,7 +4622,7 @@
         <v>314</v>
       </c>
       <c r="B314" s="1">
-        <v>114.9781001522203</v>
+        <v>33.4978077356559</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -4636,7 +4630,7 @@
         <v>315</v>
       </c>
       <c r="B315" s="1">
-        <v>114.9951122315015</v>
+        <v>33.49770821376183</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -4644,7 +4638,7 @@
         <v>316</v>
       </c>
       <c r="B316" s="1">
-        <v>115.0182895917852</v>
+        <v>33.49730423924287</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -4652,7 +4646,7 @@
         <v>317</v>
       </c>
       <c r="B317" s="1">
-        <v>115.029870380782</v>
+        <v>33.49721204795014</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -4660,7 +4654,7 @@
         <v>318</v>
       </c>
       <c r="B318" s="1">
-        <v>115.1160442432117</v>
+        <v>33.49689627066589</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -4668,7 +4662,7 @@
         <v>319</v>
       </c>
       <c r="B319" s="1">
-        <v>115.1291430247202</v>
+        <v>33.49596137807174</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -4676,7 +4670,7 @@
         <v>320</v>
       </c>
       <c r="B320" s="1">
-        <v>115.1719834693274</v>
+        <v>33.49495361521441</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -4684,7 +4678,7 @@
         <v>321</v>
       </c>
       <c r="B321" s="1">
-        <v>115.2510875252513</v>
+        <v>33.49487372323811</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -4692,7 +4686,7 @@
         <v>322</v>
       </c>
       <c r="B322" s="1">
-        <v>115.2623012209937</v>
+        <v>33.49467909772622</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -4700,7 +4694,7 @@
         <v>323</v>
       </c>
       <c r="B323" s="1">
-        <v>115.283789098831</v>
+        <v>33.49418341204928</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -4708,7 +4702,7 @@
         <v>324</v>
       </c>
       <c r="B324" s="1">
-        <v>115.3772164742344</v>
+        <v>33.49385009389905</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -4716,7 +4710,7 @@
         <v>325</v>
       </c>
       <c r="B325" s="1">
-        <v>115.3781455330018</v>
+        <v>33.49357695443575</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -4724,7 +4718,7 @@
         <v>326</v>
       </c>
       <c r="B326" s="1">
-        <v>115.4061251544942</v>
+        <v>33.49347688048373</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -4732,7 +4726,7 @@
         <v>327</v>
       </c>
       <c r="B327" s="1">
-        <v>115.4541623796154</v>
+        <v>33.49332976752008</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -4740,7 +4734,7 @@
         <v>328</v>
       </c>
       <c r="B328" s="1">
-        <v>115.4602011232378</v>
+        <v>33.49330846573928</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -4748,7 +4742,7 @@
         <v>329</v>
       </c>
       <c r="B329" s="1">
-        <v>115.4884569531589</v>
+        <v>33.49317431303796</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -4756,7 +4750,7 @@
         <v>330</v>
       </c>
       <c r="B330" s="1">
-        <v>115.4974191549499</v>
+        <v>33.49311873509397</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -4764,7 +4758,7 @@
         <v>331</v>
       </c>
       <c r="B331" s="1">
-        <v>115.5077993200326</v>
+        <v>33.49282994668457</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -4772,7 +4766,7 @@
         <v>332</v>
       </c>
       <c r="B332" s="1">
-        <v>115.5092854085449</v>
+        <v>33.4927945505274</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -4780,7 +4774,7 @@
         <v>333</v>
       </c>
       <c r="B333" s="1">
-        <v>115.5111578100216</v>
+        <v>33.49222668865924</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -4788,7 +4782,7 @@
         <v>334</v>
       </c>
       <c r="B334" s="1">
-        <v>115.5638970538736</v>
+        <v>33.49128116593879</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -4796,7 +4790,7 @@
         <v>335</v>
       </c>
       <c r="B335" s="1">
-        <v>115.5718796654211</v>
+        <v>33.49117720419001</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -4804,7 +4798,7 @@
         <v>336</v>
       </c>
       <c r="B336" s="1">
-        <v>115.6027938233997</v>
+        <v>33.48971390875361</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -4812,7 +4806,7 @@
         <v>337</v>
       </c>
       <c r="B337" s="1">
-        <v>115.6028290205163</v>
+        <v>33.48959287054194</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -4820,7 +4814,7 @@
         <v>338</v>
       </c>
       <c r="B338" s="1">
-        <v>115.6333819268054</v>
+        <v>33.48930408902422</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -4828,7 +4822,7 @@
         <v>339</v>
       </c>
       <c r="B339" s="1">
-        <v>115.6498094841783</v>
+        <v>33.48925932266464</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -4836,7 +4830,7 @@
         <v>340</v>
       </c>
       <c r="B340" s="1">
-        <v>115.7043368066782</v>
+        <v>33.48912064212513</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -4844,7 +4838,7 @@
         <v>341</v>
       </c>
       <c r="B341" s="1">
-        <v>115.7216090201991</v>
+        <v>33.48897917003244</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -4852,7 +4846,7 @@
         <v>342</v>
       </c>
       <c r="B342" s="1">
-        <v>115.8265822740889</v>
+        <v>33.4886492459645</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -4860,7 +4854,7 @@
         <v>343</v>
       </c>
       <c r="B343" s="1">
-        <v>115.829917451294</v>
+        <v>33.48842290684116</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -4868,7 +4862,7 @@
         <v>344</v>
       </c>
       <c r="B344" s="1">
-        <v>115.845339150896</v>
+        <v>33.48837310494597</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -4876,7 +4870,7 @@
         <v>345</v>
       </c>
       <c r="B345" s="1">
-        <v>115.8740542089406</v>
+        <v>33.48771724696126</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -4884,7 +4878,7 @@
         <v>346</v>
       </c>
       <c r="B346" s="1">
-        <v>115.9144886810343</v>
+        <v>33.48720102903969</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -4892,7 +4886,7 @@
         <v>347</v>
       </c>
       <c r="B347" s="1">
-        <v>115.9301086701104</v>
+        <v>33.48660806844057</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -4900,7 +4894,7 @@
         <v>348</v>
       </c>
       <c r="B348" s="1">
-        <v>115.9320673319638</v>
+        <v>33.48655061430094</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -4908,7 +4902,7 @@
         <v>349</v>
       </c>
       <c r="B349" s="1">
-        <v>115.937681532248</v>
+        <v>33.48616592561335</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -4916,7 +4910,7 @@
         <v>350</v>
       </c>
       <c r="B350" s="1">
-        <v>115.9902527637389</v>
+        <v>33.48572579255978</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -4924,7 +4918,7 @@
         <v>351</v>
       </c>
       <c r="B351" s="1">
-        <v>116.010271207563</v>
+        <v>33.4856624663627</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -4932,7 +4926,7 @@
         <v>352</v>
       </c>
       <c r="B352" s="1">
-        <v>116.0292105640367</v>
+        <v>33.48565403502429</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -4940,7 +4934,7 @@
         <v>353</v>
       </c>
       <c r="B353" s="1">
-        <v>116.0410838505859</v>
+        <v>33.48553730880447</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -4948,7 +4942,7 @@
         <v>354</v>
       </c>
       <c r="B354" s="1">
-        <v>116.0524290095144</v>
+        <v>33.4854304019517</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -4956,7 +4950,7 @@
         <v>355</v>
       </c>
       <c r="B355" s="1">
-        <v>116.088737347627</v>
+        <v>33.48386423115799</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -4964,7 +4958,7 @@
         <v>356</v>
       </c>
       <c r="B356" s="1">
-        <v>116.2645310456672</v>
+        <v>33.48320652348238</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -4972,7 +4966,7 @@
         <v>357</v>
       </c>
       <c r="B357" s="1">
-        <v>116.2731443768865</v>
+        <v>33.4830826502377</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -4980,7 +4974,7 @@
         <v>358</v>
       </c>
       <c r="B358" s="1">
-        <v>116.2957740988703</v>
+        <v>33.48268462037871</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -4988,7 +4982,7 @@
         <v>359</v>
       </c>
       <c r="B359" s="1">
-        <v>116.3682240589537</v>
+        <v>33.48241466677776</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -4996,7 +4990,7 @@
         <v>360</v>
       </c>
       <c r="B360" s="1">
-        <v>116.3749427588767</v>
+        <v>33.48126252422995</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -5004,7 +4998,7 @@
         <v>361</v>
       </c>
       <c r="B361" s="1">
-        <v>116.3848393543873</v>
+        <v>33.4805277164328</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -5012,7 +5006,7 @@
         <v>362</v>
       </c>
       <c r="B362" s="1">
-        <v>116.4244740252939</v>
+        <v>33.4804302064359</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -5020,7 +5014,7 @@
         <v>363</v>
       </c>
       <c r="B363" s="1">
-        <v>116.4800639813238</v>
+        <v>33.48028538504956</v>
       </c>
     </row>
     <row r="364" spans="1:2">
@@ -5028,7 +5022,7 @@
         <v>364</v>
       </c>
       <c r="B364" s="1">
-        <v>116.4991425494964</v>
+        <v>33.47947837543899</v>
       </c>
     </row>
     <row r="365" spans="1:2">
@@ -5036,7 +5030,7 @@
         <v>365</v>
       </c>
       <c r="B365" s="1">
-        <v>116.4992092849209</v>
+        <v>33.47912530127956</v>
       </c>
     </row>
     <row r="366" spans="1:2">
@@ -5044,7 +5038,7 @@
         <v>366</v>
       </c>
       <c r="B366" s="1">
-        <v>116.5999449714447</v>
+        <v>33.4789931073711</v>
       </c>
     </row>
     <row r="367" spans="1:2">
@@ -5052,7 +5046,7 @@
         <v>367</v>
       </c>
       <c r="B367" s="1">
-        <v>116.6271738760636</v>
+        <v>33.47857949727192</v>
       </c>
     </row>
     <row r="368" spans="1:2">
@@ -5060,7 +5054,7 @@
         <v>368</v>
       </c>
       <c r="B368" s="1">
-        <v>116.7004096602823</v>
+        <v>33.47846846356942</v>
       </c>
     </row>
     <row r="369" spans="1:2">
@@ -5068,7 +5062,7 @@
         <v>369</v>
       </c>
       <c r="B369" s="1">
-        <v>116.7964998762489</v>
+        <v>33.47834210449975</v>
       </c>
     </row>
     <row r="370" spans="1:2">
@@ -5076,7 +5070,7 @@
         <v>370</v>
       </c>
       <c r="B370" s="1">
-        <v>116.8773223809925</v>
+        <v>33.4780466727107</v>
       </c>
     </row>
     <row r="371" spans="1:2">
@@ -5084,7 +5078,7 @@
         <v>371</v>
       </c>
       <c r="B371" s="1">
-        <v>116.9128007420371</v>
+        <v>33.47756482888224</v>
       </c>
     </row>
     <row r="372" spans="1:2">
@@ -5092,7 +5086,7 @@
         <v>372</v>
       </c>
       <c r="B372" s="1">
-        <v>116.9934341144478</v>
+        <v>33.47727748616663</v>
       </c>
     </row>
     <row r="373" spans="1:2">
@@ -5100,7 +5094,7 @@
         <v>373</v>
       </c>
       <c r="B373" s="1">
-        <v>116.9948092231751</v>
+        <v>33.47720182921725</v>
       </c>
     </row>
     <row r="374" spans="1:2">
@@ -5108,7 +5102,7 @@
         <v>374</v>
       </c>
       <c r="B374" s="1">
-        <v>116.9975564459318</v>
+        <v>33.47701982023085</v>
       </c>
     </row>
     <row r="375" spans="1:2">
@@ -5116,7 +5110,7 @@
         <v>375</v>
       </c>
       <c r="B375" s="1">
-        <v>117.0228895669501</v>
+        <v>33.47652203894435</v>
       </c>
     </row>
     <row r="376" spans="1:2">
@@ -5124,7 +5118,7 @@
         <v>376</v>
       </c>
       <c r="B376" s="1">
-        <v>117.0879180329212</v>
+        <v>33.47631279887372</v>
       </c>
     </row>
     <row r="377" spans="1:2">
@@ -5132,7 +5126,7 @@
         <v>377</v>
       </c>
       <c r="B377" s="1">
-        <v>117.1109998694368</v>
+        <v>33.47626929994744</v>
       </c>
     </row>
     <row r="378" spans="1:2">
@@ -5140,7 +5134,7 @@
         <v>378</v>
       </c>
       <c r="B378" s="1">
-        <v>117.1305494743791</v>
+        <v>33.47611767373223</v>
       </c>
     </row>
     <row r="379" spans="1:2">
@@ -5148,7 +5142,7 @@
         <v>379</v>
       </c>
       <c r="B379" s="1">
-        <v>117.1836386310932</v>
+        <v>33.47481385214371</v>
       </c>
     </row>
     <row r="380" spans="1:2">
@@ -5156,7 +5150,7 @@
         <v>380</v>
       </c>
       <c r="B380" s="1">
-        <v>117.227920080178</v>
+        <v>33.47414312020024</v>
       </c>
     </row>
     <row r="381" spans="1:2">
@@ -5164,7 +5158,7 @@
         <v>381</v>
       </c>
       <c r="B381" s="1">
-        <v>117.2690581788951</v>
+        <v>33.47400998742099</v>
       </c>
     </row>
     <row r="382" spans="1:2">
@@ -5172,7 +5166,7 @@
         <v>382</v>
       </c>
       <c r="B382" s="1">
-        <v>117.5031202789068</v>
+        <v>33.47285546253314</v>
       </c>
     </row>
     <row r="383" spans="1:2">
@@ -5180,7 +5174,7 @@
         <v>383</v>
       </c>
       <c r="B383" s="1">
-        <v>117.5089484306562</v>
+        <v>33.47230716506757</v>
       </c>
     </row>
     <row r="384" spans="1:2">
@@ -5188,7 +5182,7 @@
         <v>384</v>
       </c>
       <c r="B384" s="1">
-        <v>117.603320318912</v>
+        <v>33.47226547558101</v>
       </c>
     </row>
     <row r="385" spans="1:2">
@@ -5196,7 +5190,7 @@
         <v>385</v>
       </c>
       <c r="B385" s="1">
-        <v>117.6491846810969</v>
+        <v>33.47223406731987</v>
       </c>
     </row>
     <row r="386" spans="1:2">
@@ -5204,7 +5198,7 @@
         <v>386</v>
       </c>
       <c r="B386" s="1">
-        <v>117.6507347180145</v>
+        <v>33.47221445133869</v>
       </c>
     </row>
     <row r="387" spans="1:2">
@@ -5212,7 +5206,7 @@
         <v>387</v>
       </c>
       <c r="B387" s="1">
-        <v>117.6666880307988</v>
+        <v>33.47206009087559</v>
       </c>
     </row>
     <row r="388" spans="1:2">
@@ -5220,7 +5214,7 @@
         <v>388</v>
       </c>
       <c r="B388" s="1">
-        <v>117.7692584816623</v>
+        <v>33.47033884239301</v>
       </c>
     </row>
     <row r="389" spans="1:2">
@@ -5228,7 +5222,7 @@
         <v>389</v>
       </c>
       <c r="B389" s="1">
-        <v>117.7781201362049</v>
+        <v>33.47021368034338</v>
       </c>
     </row>
     <row r="390" spans="1:2">
@@ -5236,7 +5230,7 @@
         <v>390</v>
       </c>
       <c r="B390" s="1">
-        <v>117.8378071403499</v>
+        <v>33.47016517125193</v>
       </c>
     </row>
     <row r="391" spans="1:2">
@@ -5244,7 +5238,7 @@
         <v>391</v>
       </c>
       <c r="B391" s="1">
-        <v>117.9086296003225</v>
+        <v>33.46921249852326</v>
       </c>
     </row>
     <row r="392" spans="1:2">
@@ -5252,7 +5246,7 @@
         <v>392</v>
       </c>
       <c r="B392" s="1">
-        <v>117.949498628659</v>
+        <v>33.4687474100061</v>
       </c>
     </row>
     <row r="393" spans="1:2">
@@ -5260,7 +5254,7 @@
         <v>393</v>
       </c>
       <c r="B393" s="1">
-        <v>118.0446931849822</v>
+        <v>33.46865067428394</v>
       </c>
     </row>
     <row r="394" spans="1:2">
@@ -5268,7 +5262,7 @@
         <v>394</v>
       </c>
       <c r="B394" s="1">
-        <v>118.0795202186806</v>
+        <v>33.46845926282078</v>
       </c>
     </row>
     <row r="395" spans="1:2">
@@ -5276,7 +5270,7 @@
         <v>395</v>
       </c>
       <c r="B395" s="1">
-        <v>118.1186607382177</v>
+        <v>33.46804554988747</v>
       </c>
     </row>
     <row r="396" spans="1:2">
@@ -5284,7 +5278,7 @@
         <v>396</v>
       </c>
       <c r="B396" s="1">
-        <v>118.1566117140939</v>
+        <v>33.46750124961946</v>
       </c>
     </row>
     <row r="397" spans="1:2">
@@ -5292,7 +5286,7 @@
         <v>397</v>
       </c>
       <c r="B397" s="1">
-        <v>118.2014260646295</v>
+        <v>33.4673551135716</v>
       </c>
     </row>
     <row r="398" spans="1:2">
@@ -5300,7 +5294,7 @@
         <v>398</v>
       </c>
       <c r="B398" s="1">
-        <v>118.2143320331007</v>
+        <v>33.46733024849576</v>
       </c>
     </row>
     <row r="399" spans="1:2">
@@ -5308,7 +5302,7 @@
         <v>399</v>
       </c>
       <c r="B399" s="1">
-        <v>118.3543473227393</v>
+        <v>33.46679135514981</v>
       </c>
     </row>
     <row r="400" spans="1:2">
@@ -5316,7 +5310,7 @@
         <v>400</v>
       </c>
       <c r="B400" s="1">
-        <v>118.3744149403439</v>
+        <v>33.46642731593055</v>
       </c>
     </row>
     <row r="401" spans="1:2">
@@ -5324,7 +5318,7 @@
         <v>401</v>
       </c>
       <c r="B401" s="1">
-        <v>118.3814121274494</v>
+        <v>33.4662531089506</v>
       </c>
     </row>
     <row r="402" spans="1:2">
@@ -5332,7 +5326,7 @@
         <v>402</v>
       </c>
       <c r="B402" s="1">
-        <v>118.4060257802477</v>
+        <v>33.46624370860762</v>
       </c>
     </row>
     <row r="403" spans="1:2">
@@ -5340,7 +5334,7 @@
         <v>403</v>
       </c>
       <c r="B403" s="1">
-        <v>118.4113406216315</v>
+        <v>33.46579905918608</v>
       </c>
     </row>
     <row r="404" spans="1:2">
@@ -5348,7 +5342,7 @@
         <v>404</v>
       </c>
       <c r="B404" s="1">
-        <v>118.5006237871265</v>
+        <v>33.46557035555384</v>
       </c>
     </row>
     <row r="405" spans="1:2">
@@ -5356,7 +5350,7 @@
         <v>405</v>
       </c>
       <c r="B405" s="1">
-        <v>118.5928081497532</v>
+        <v>33.46515827740832</v>
       </c>
     </row>
     <row r="406" spans="1:2">
@@ -5364,7 +5358,7 @@
         <v>406</v>
       </c>
       <c r="B406" s="1">
-        <v>118.6027371379308</v>
+        <v>33.46488548559476</v>
       </c>
     </row>
     <row r="407" spans="1:2">
@@ -5372,7 +5366,7 @@
         <v>407</v>
       </c>
       <c r="B407" s="1">
-        <v>118.6847165924409</v>
+        <v>33.46478945991747</v>
       </c>
     </row>
     <row r="408" spans="1:2">
@@ -5380,7 +5374,7 @@
         <v>408</v>
       </c>
       <c r="B408" s="1">
-        <v>118.7040145312785</v>
+        <v>33.46409597934149</v>
       </c>
     </row>
     <row r="409" spans="1:2">
@@ -5388,7 +5382,7 @@
         <v>409</v>
       </c>
       <c r="B409" s="1">
-        <v>118.8475888972588</v>
+        <v>33.46390196374067</v>
       </c>
     </row>
     <row r="410" spans="1:2">
@@ -5396,7 +5390,7 @@
         <v>410</v>
       </c>
       <c r="B410" s="1">
-        <v>118.8651255641355</v>
+        <v>33.46386399535209</v>
       </c>
     </row>
     <row r="411" spans="1:2">
@@ -5404,7 +5398,7 @@
         <v>411</v>
       </c>
       <c r="B411" s="1">
-        <v>118.8874586324447</v>
+        <v>33.46384682974804</v>
       </c>
     </row>
     <row r="412" spans="1:2">
@@ -5412,7 +5406,7 @@
         <v>412</v>
       </c>
       <c r="B412" s="1">
-        <v>118.911334607628</v>
+        <v>33.46371042304229</v>
       </c>
     </row>
     <row r="413" spans="1:2">
@@ -5420,7 +5414,7 @@
         <v>413</v>
       </c>
       <c r="B413" s="1">
-        <v>118.9122088333161</v>
+        <v>33.46362601783841</v>
       </c>
     </row>
     <row r="414" spans="1:2">
@@ -5428,7 +5422,7 @@
         <v>414</v>
       </c>
       <c r="B414" s="1">
-        <v>118.9502244537876</v>
+        <v>33.46348268198954</v>
       </c>
     </row>
     <row r="415" spans="1:2">
@@ -5436,7 +5430,7 @@
         <v>415</v>
       </c>
       <c r="B415" s="1">
-        <v>119.0120162725098</v>
+        <v>33.46271342619517</v>
       </c>
     </row>
     <row r="416" spans="1:2">
@@ -5444,7 +5438,7 @@
         <v>416</v>
       </c>
       <c r="B416" s="1">
-        <v>119.051930589079</v>
+        <v>33.46230723242094</v>
       </c>
     </row>
     <row r="417" spans="1:2">
@@ -5452,7 +5446,7 @@
         <v>417</v>
       </c>
       <c r="B417" s="1">
-        <v>119.2395992182971</v>
+        <v>33.46209452766762</v>
       </c>
     </row>
     <row r="418" spans="1:2">
@@ -5460,7 +5454,7 @@
         <v>418</v>
       </c>
       <c r="B418" s="1">
-        <v>119.3689727245629</v>
+        <v>33.46184098098448</v>
       </c>
     </row>
     <row r="419" spans="1:2">
@@ -5468,7 +5462,7 @@
         <v>419</v>
       </c>
       <c r="B419" s="1">
-        <v>119.5050727245786</v>
+        <v>33.46170403733719</v>
       </c>
     </row>
     <row r="420" spans="1:2">
@@ -5476,7 +5470,7 @@
         <v>420</v>
       </c>
       <c r="B420" s="1">
-        <v>119.5816341242625</v>
+        <v>33.4611177588494</v>
       </c>
     </row>
     <row r="421" spans="1:2">
@@ -5484,7 +5478,7 @@
         <v>421</v>
       </c>
       <c r="B421" s="1">
-        <v>119.6384820083467</v>
+        <v>33.4604395144052</v>
       </c>
     </row>
     <row r="422" spans="1:2">
@@ -5492,7 +5486,7 @@
         <v>422</v>
       </c>
       <c r="B422" s="1">
-        <v>119.7100940064157</v>
+        <v>33.46039719042043</v>
       </c>
     </row>
     <row r="423" spans="1:2">
@@ -5500,7 +5494,7 @@
         <v>423</v>
       </c>
       <c r="B423" s="1">
-        <v>119.7523530332266</v>
+        <v>33.45965933306147</v>
       </c>
     </row>
     <row r="424" spans="1:2">
@@ -5508,7 +5502,7 @@
         <v>424</v>
       </c>
       <c r="B424" s="1">
-        <v>119.7824064441706</v>
+        <v>33.45928134527193</v>
       </c>
     </row>
     <row r="425" spans="1:2">
@@ -5516,7 +5510,7 @@
         <v>425</v>
       </c>
       <c r="B425" s="1">
-        <v>119.8065325987272</v>
+        <v>33.45816210963472</v>
       </c>
     </row>
     <row r="426" spans="1:2">
@@ -5524,7 +5518,7 @@
         <v>426</v>
       </c>
       <c r="B426" s="1">
-        <v>119.8258826737704</v>
+        <v>33.45808617493937</v>
       </c>
     </row>
     <row r="427" spans="1:2">
@@ -5532,7 +5526,7 @@
         <v>427</v>
       </c>
       <c r="B427" s="1">
-        <v>119.8380254115107</v>
+        <v>33.4580561323577</v>
       </c>
     </row>
     <row r="428" spans="1:2">
@@ -5540,7 +5534,7 @@
         <v>428</v>
       </c>
       <c r="B428" s="1">
-        <v>120.0532545090909</v>
+        <v>33.45745581022231</v>
       </c>
     </row>
     <row r="429" spans="1:2">
@@ -5548,7 +5542,7 @@
         <v>429</v>
       </c>
       <c r="B429" s="1">
-        <v>120.0928434829588</v>
+        <v>33.45693639024253</v>
       </c>
     </row>
     <row r="430" spans="1:2">
@@ -5556,7 +5550,7 @@
         <v>430</v>
       </c>
       <c r="B430" s="1">
-        <v>120.2328854892706</v>
+        <v>33.45662261808949</v>
       </c>
     </row>
     <row r="431" spans="1:2">
@@ -5564,7 +5558,7 @@
         <v>431</v>
       </c>
       <c r="B431" s="1">
-        <v>120.2745953240478</v>
+        <v>33.45656244286562</v>
       </c>
     </row>
     <row r="432" spans="1:2">
@@ -5572,7 +5566,7 @@
         <v>432</v>
       </c>
       <c r="B432" s="1">
-        <v>120.3470390348873</v>
+        <v>33.45637200188909</v>
       </c>
     </row>
     <row r="433" spans="1:2">
@@ -5580,7 +5574,7 @@
         <v>433</v>
       </c>
       <c r="B433" s="1">
-        <v>120.3905271166615</v>
+        <v>33.45629994561346</v>
       </c>
     </row>
     <row r="434" spans="1:2">
@@ -5588,7 +5582,7 @@
         <v>434</v>
       </c>
       <c r="B434" s="1">
-        <v>120.4402075325492</v>
+        <v>33.45629919435431</v>
       </c>
     </row>
     <row r="435" spans="1:2">
@@ -5596,7 +5590,7 @@
         <v>435</v>
       </c>
       <c r="B435" s="1">
-        <v>120.4427663010336</v>
+        <v>33.45628897618948</v>
       </c>
     </row>
     <row r="436" spans="1:2">
@@ -5604,7 +5598,7 @@
         <v>436</v>
       </c>
       <c r="B436" s="1">
-        <v>120.4618532780922</v>
+        <v>33.45627602637884</v>
       </c>
     </row>
     <row r="437" spans="1:2">
@@ -5612,7 +5606,7 @@
         <v>437</v>
       </c>
       <c r="B437" s="1">
-        <v>120.52138453317</v>
+        <v>33.45627436842241</v>
       </c>
     </row>
     <row r="438" spans="1:2">
@@ -5620,7 +5614,7 @@
         <v>438</v>
       </c>
       <c r="B438" s="1">
-        <v>120.5583675495176</v>
+        <v>33.45605196481408</v>
       </c>
     </row>
     <row r="439" spans="1:2">
@@ -5628,7 +5622,7 @@
         <v>439</v>
       </c>
       <c r="B439" s="1">
-        <v>120.5708617062005</v>
+        <v>33.45582250722723</v>
       </c>
     </row>
     <row r="440" spans="1:2">
@@ -5636,7 +5630,7 @@
         <v>440</v>
       </c>
       <c r="B440" s="1">
-        <v>120.6588458783167</v>
+        <v>33.45578609689374</v>
       </c>
     </row>
     <row r="441" spans="1:2">
@@ -5644,7 +5638,7 @@
         <v>441</v>
       </c>
       <c r="B441" s="1">
-        <v>120.7199769179737</v>
+        <v>33.45452539859841</v>
       </c>
     </row>
     <row r="442" spans="1:2">
@@ -5652,7 +5646,7 @@
         <v>442</v>
       </c>
       <c r="B442" s="1">
-        <v>120.7918003457622</v>
+        <v>33.45442090920653</v>
       </c>
     </row>
     <row r="443" spans="1:2">
@@ -5660,7 +5654,7 @@
         <v>443</v>
       </c>
       <c r="B443" s="1">
-        <v>121.0391568352772</v>
+        <v>33.45398484168761</v>
       </c>
     </row>
     <row r="444" spans="1:2">
@@ -5668,7 +5662,7 @@
         <v>444</v>
       </c>
       <c r="B444" s="1">
-        <v>121.4050517606745</v>
+        <v>33.45389334360502</v>
       </c>
     </row>
     <row r="445" spans="1:2">
@@ -5676,7 +5670,7 @@
         <v>445</v>
       </c>
       <c r="B445" s="1">
-        <v>121.491921563381</v>
+        <v>33.45326019105751</v>
       </c>
     </row>
     <row r="446" spans="1:2">
@@ -5684,7 +5678,7 @@
         <v>446</v>
       </c>
       <c r="B446" s="1">
-        <v>121.5758717440222</v>
+        <v>33.45277421571337</v>
       </c>
     </row>
     <row r="447" spans="1:2">
@@ -5692,7 +5686,7 @@
         <v>447</v>
       </c>
       <c r="B447" s="1">
-        <v>121.6183818685245</v>
+        <v>33.45260372506853</v>
       </c>
     </row>
     <row r="448" spans="1:2">
@@ -5700,7 +5694,7 @@
         <v>448</v>
       </c>
       <c r="B448" s="1">
-        <v>121.6204437379186</v>
+        <v>33.45211374733393</v>
       </c>
     </row>
     <row r="449" spans="1:2">
@@ -5708,7 +5702,7 @@
         <v>449</v>
       </c>
       <c r="B449" s="1">
-        <v>121.6721571617931</v>
+        <v>33.45206394386697</v>
       </c>
     </row>
     <row r="450" spans="1:2">
@@ -5716,7 +5710,7 @@
         <v>450</v>
       </c>
       <c r="B450" s="1">
-        <v>121.7386660345313</v>
+        <v>33.45126341728317</v>
       </c>
     </row>
     <row r="451" spans="1:2">
@@ -5724,7 +5718,7 @@
         <v>451</v>
       </c>
       <c r="B451" s="1">
-        <v>122.0214444842703</v>
+        <v>33.45124015101256</v>
       </c>
     </row>
     <row r="452" spans="1:2">
@@ -5732,7 +5726,7 @@
         <v>452</v>
       </c>
       <c r="B452" s="1">
-        <v>122.0662677526282</v>
+        <v>33.45096577682036</v>
       </c>
     </row>
     <row r="453" spans="1:2">
@@ -5740,7 +5734,7 @@
         <v>453</v>
       </c>
       <c r="B453" s="1">
-        <v>122.1588812415722</v>
+        <v>33.45087212375289</v>
       </c>
     </row>
     <row r="454" spans="1:2">
@@ -5748,7 +5742,7 @@
         <v>454</v>
       </c>
       <c r="B454" s="1">
-        <v>122.2400466012957</v>
+        <v>33.45059813901428</v>
       </c>
     </row>
     <row r="455" spans="1:2">
@@ -5756,7 +5750,7 @@
         <v>455</v>
       </c>
       <c r="B455" s="1">
-        <v>122.2756813163186</v>
+        <v>33.45056252751274</v>
       </c>
     </row>
     <row r="456" spans="1:2">
@@ -5764,7 +5758,7 @@
         <v>456</v>
       </c>
       <c r="B456" s="1">
-        <v>122.2939117360794</v>
+        <v>33.45053636990627</v>
       </c>
     </row>
     <row r="457" spans="1:2">
@@ -5772,7 +5766,7 @@
         <v>457</v>
       </c>
       <c r="B457" s="1">
-        <v>122.3788144975987</v>
+        <v>33.45031153138483</v>
       </c>
     </row>
     <row r="458" spans="1:2">
@@ -5780,7 +5774,7 @@
         <v>458</v>
       </c>
       <c r="B458" s="1">
-        <v>122.5125488365846</v>
+        <v>33.4497418099857</v>
       </c>
     </row>
     <row r="459" spans="1:2">
@@ -5788,7 +5782,7 @@
         <v>459</v>
       </c>
       <c r="B459" s="1">
-        <v>122.5686836365075</v>
+        <v>33.44942323150682</v>
       </c>
     </row>
     <row r="460" spans="1:2">
@@ -5796,7 +5790,7 @@
         <v>460</v>
       </c>
       <c r="B460" s="1">
-        <v>122.6425595654766</v>
+        <v>33.4489897214881</v>
       </c>
     </row>
     <row r="461" spans="1:2">
@@ -5804,7 +5798,7 @@
         <v>461</v>
       </c>
       <c r="B461" s="1">
-        <v>122.7261139965673</v>
+        <v>33.44882695617908</v>
       </c>
     </row>
     <row r="462" spans="1:2">
@@ -5812,7 +5806,7 @@
         <v>462</v>
       </c>
       <c r="B462" s="1">
-        <v>122.767877137324</v>
+        <v>33.44871484785744</v>
       </c>
     </row>
     <row r="463" spans="1:2">
@@ -5820,7 +5814,7 @@
         <v>463</v>
       </c>
       <c r="B463" s="1">
-        <v>122.8005153745452</v>
+        <v>33.44834392319669</v>
       </c>
     </row>
     <row r="464" spans="1:2">
@@ -5828,7 +5822,7 @@
         <v>464</v>
       </c>
       <c r="B464" s="1">
-        <v>122.8632614207925</v>
+        <v>33.44773966440634</v>
       </c>
     </row>
     <row r="465" spans="1:2">
@@ -5836,7 +5830,7 @@
         <v>465</v>
       </c>
       <c r="B465" s="1">
-        <v>122.8913524250442</v>
+        <v>33.44741823151674</v>
       </c>
     </row>
     <row r="466" spans="1:2">
@@ -5844,7 +5838,7 @@
         <v>466</v>
       </c>
       <c r="B466" s="1">
-        <v>122.9846416183081</v>
+        <v>33.44734911908416</v>
       </c>
     </row>
     <row r="467" spans="1:2">
@@ -5852,7 +5846,7 @@
         <v>467</v>
       </c>
       <c r="B467" s="1">
-        <v>123.0907875084756</v>
+        <v>33.44727362037243</v>
       </c>
     </row>
     <row r="468" spans="1:2">
@@ -5860,7 +5854,7 @@
         <v>468</v>
       </c>
       <c r="B468" s="1">
-        <v>123.2384337356775</v>
+        <v>33.44650583271457</v>
       </c>
     </row>
     <row r="469" spans="1:2">
@@ -5868,7 +5862,7 @@
         <v>469</v>
       </c>
       <c r="B469" s="1">
-        <v>123.2432342387912</v>
+        <v>33.44644501348676</v>
       </c>
     </row>
     <row r="470" spans="1:2">
@@ -5876,7 +5870,7 @@
         <v>470</v>
       </c>
       <c r="B470" s="1">
-        <v>123.3023791117422</v>
+        <v>33.44635280999093</v>
       </c>
     </row>
     <row r="471" spans="1:2">
@@ -5884,7 +5878,7 @@
         <v>471</v>
       </c>
       <c r="B471" s="1">
-        <v>123.3933159242183</v>
+        <v>33.44586422782043</v>
       </c>
     </row>
     <row r="472" spans="1:2">
@@ -5892,7 +5886,7 @@
         <v>472</v>
       </c>
       <c r="B472" s="1">
-        <v>123.4403554316374</v>
+        <v>33.44570048699427</v>
       </c>
     </row>
     <row r="473" spans="1:2">
@@ -5900,7 +5894,7 @@
         <v>473</v>
       </c>
       <c r="B473" s="1">
-        <v>123.4773562131466</v>
+        <v>33.4451667254373</v>
       </c>
     </row>
     <row r="474" spans="1:2">
@@ -5908,7 +5902,7 @@
         <v>474</v>
       </c>
       <c r="B474" s="1">
-        <v>123.6151470456042</v>
+        <v>33.44492259000022</v>
       </c>
     </row>
     <row r="475" spans="1:2">
@@ -5916,7 +5910,7 @@
         <v>475</v>
       </c>
       <c r="B475" s="1">
-        <v>123.6780967432296</v>
+        <v>33.44481080723207</v>
       </c>
     </row>
     <row r="476" spans="1:2">
@@ -5924,7 +5918,7 @@
         <v>476</v>
       </c>
       <c r="B476" s="1">
-        <v>123.9254955958413</v>
+        <v>33.44453795893945</v>
       </c>
     </row>
     <row r="477" spans="1:2">
@@ -5932,7 +5926,7 @@
         <v>477</v>
       </c>
       <c r="B477" s="1">
-        <v>124.0309835777498</v>
+        <v>33.44452571698763</v>
       </c>
     </row>
     <row r="478" spans="1:2">
@@ -5940,7 +5934,7 @@
         <v>478</v>
       </c>
       <c r="B478" s="1">
-        <v>124.1678320326571</v>
+        <v>33.4440344403444</v>
       </c>
     </row>
     <row r="479" spans="1:2">
@@ -5948,7 +5942,7 @@
         <v>479</v>
       </c>
       <c r="B479" s="1">
-        <v>124.1830862164171</v>
+        <v>33.44377698086988</v>
       </c>
     </row>
     <row r="480" spans="1:2">
@@ -5956,7 +5950,7 @@
         <v>480</v>
       </c>
       <c r="B480" s="1">
-        <v>124.2757389277149</v>
+        <v>33.44357215398968</v>
       </c>
     </row>
     <row r="481" spans="1:2">
@@ -5964,7 +5958,7 @@
         <v>481</v>
       </c>
       <c r="B481" s="1">
-        <v>124.380918102284</v>
+        <v>33.44239955934569</v>
       </c>
     </row>
     <row r="482" spans="1:2">
@@ -5972,7 +5966,7 @@
         <v>482</v>
       </c>
       <c r="B482" s="1">
-        <v>124.3815163367396</v>
+        <v>33.44193610167959</v>
       </c>
     </row>
     <row r="483" spans="1:2">
@@ -5980,7 +5974,7 @@
         <v>483</v>
       </c>
       <c r="B483" s="1">
-        <v>124.7026795301294</v>
+        <v>33.44181710531121</v>
       </c>
     </row>
     <row r="484" spans="1:2">
@@ -5988,7 +5982,7 @@
         <v>484</v>
       </c>
       <c r="B484" s="1">
-        <v>124.8255894775848</v>
+        <v>33.44165131212536</v>
       </c>
     </row>
     <row r="485" spans="1:2">
@@ -5996,7 +5990,7 @@
         <v>485</v>
       </c>
       <c r="B485" s="1">
-        <v>124.8305019491684</v>
+        <v>33.44163131056737</v>
       </c>
     </row>
     <row r="486" spans="1:2">
@@ -6004,7 +5998,7 @@
         <v>486</v>
       </c>
       <c r="B486" s="1">
-        <v>124.8446720167587</v>
+        <v>33.4413533983887</v>
       </c>
     </row>
     <row r="487" spans="1:2">
@@ -6012,7 +6006,7 @@
         <v>487</v>
       </c>
       <c r="B487" s="1">
-        <v>125.0722353485012</v>
+        <v>33.44123998957851</v>
       </c>
     </row>
     <row r="488" spans="1:2">
@@ -6020,7 +6014,7 @@
         <v>488</v>
       </c>
       <c r="B488" s="1">
-        <v>125.0853668547446</v>
+        <v>33.44110357558579</v>
       </c>
     </row>
     <row r="489" spans="1:2">
@@ -6028,7 +6022,7 @@
         <v>489</v>
       </c>
       <c r="B489" s="1">
-        <v>125.130114440068</v>
+        <v>33.44110166880617</v>
       </c>
     </row>
     <row r="490" spans="1:2">
@@ -6036,7 +6030,7 @@
         <v>490</v>
       </c>
       <c r="B490" s="1">
-        <v>125.1766527855865</v>
+        <v>33.44098368512871</v>
       </c>
     </row>
     <row r="491" spans="1:2">
@@ -6044,7 +6038,7 @@
         <v>491</v>
       </c>
       <c r="B491" s="1">
-        <v>125.4042423570102</v>
+        <v>33.44040417939213</v>
       </c>
     </row>
     <row r="492" spans="1:2">
@@ -6052,7 +6046,7 @@
         <v>492</v>
       </c>
       <c r="B492" s="1">
-        <v>125.4112620905138</v>
+        <v>33.44027692487887</v>
       </c>
     </row>
     <row r="493" spans="1:2">
@@ -6060,7 +6054,7 @@
         <v>493</v>
       </c>
       <c r="B493" s="1">
-        <v>125.6057423862624</v>
+        <v>33.4402662605024</v>
       </c>
     </row>
     <row r="494" spans="1:2">
@@ -6068,7 +6062,7 @@
         <v>494</v>
       </c>
       <c r="B494" s="1">
-        <v>125.7045193016981</v>
+        <v>33.44019940167696</v>
       </c>
     </row>
     <row r="495" spans="1:2">
@@ -6076,7 +6070,7 @@
         <v>495</v>
       </c>
       <c r="B495" s="1">
-        <v>125.7310539936156</v>
+        <v>33.43994279866465</v>
       </c>
     </row>
     <row r="496" spans="1:2">
@@ -6084,7 +6078,7 @@
         <v>496</v>
       </c>
       <c r="B496" s="1">
-        <v>125.7958372055574</v>
+        <v>33.43982071615302</v>
       </c>
     </row>
     <row r="497" spans="1:2">
@@ -6092,7 +6086,7 @@
         <v>497</v>
       </c>
       <c r="B497" s="1">
-        <v>125.8411763674321</v>
+        <v>33.43929399950996</v>
       </c>
     </row>
     <row r="498" spans="1:2">
@@ -6100,7 +6094,7 @@
         <v>498</v>
       </c>
       <c r="B498" s="1">
-        <v>125.8970597752992</v>
+        <v>33.43926073989009</v>
       </c>
     </row>
     <row r="499" spans="1:2">
@@ -6108,7 +6102,7 @@
         <v>499</v>
       </c>
       <c r="B499" s="1">
-        <v>126.0981719924856</v>
+        <v>33.43909446060663</v>
       </c>
     </row>
     <row r="500" spans="1:2">
@@ -6116,7 +6110,7 @@
         <v>500</v>
       </c>
       <c r="B500" s="1">
-        <v>126.3679871185055</v>
+        <v>33.43881655258223</v>
       </c>
     </row>
     <row r="501" spans="1:2">
@@ -6124,7 +6118,7 @@
         <v>501</v>
       </c>
       <c r="B501" s="1">
-        <v>126.7724306046017</v>
+        <v>33.43864520617436</v>
       </c>
     </row>
     <row r="502" spans="1:2">
@@ -6132,7 +6126,7 @@
         <v>502</v>
       </c>
       <c r="B502" s="1">
-        <v>126.8316230404087</v>
+        <v>33.43823671277589</v>
       </c>
     </row>
     <row r="503" spans="1:2">
@@ -6140,7 +6134,7 @@
         <v>503</v>
       </c>
       <c r="B503" s="1">
-        <v>127.7046497215018</v>
+        <v>33.43804750130648</v>
       </c>
     </row>
     <row r="504" spans="1:2">
@@ -6148,7 +6142,7 @@
         <v>504</v>
       </c>
       <c r="B504" s="1">
-        <v>127.9425197087221</v>
+        <v>33.43722846694256</v>
       </c>
     </row>
     <row r="505" spans="1:2">
@@ -6156,7 +6150,7 @@
         <v>505</v>
       </c>
       <c r="B505" s="1">
-        <v>128.099279228371</v>
+        <v>33.43719927902172</v>
       </c>
     </row>
     <row r="506" spans="1:2">
@@ -6164,7 +6158,7 @@
         <v>506</v>
       </c>
       <c r="B506" s="1">
-        <v>128.3130465552071</v>
+        <v>33.43698364457971</v>
       </c>
     </row>
     <row r="507" spans="1:2">
@@ -6172,7 +6166,7 @@
         <v>507</v>
       </c>
       <c r="B507" s="1">
-        <v>128.343588251484</v>
+        <v>33.43693242451377</v>
       </c>
     </row>
     <row r="508" spans="1:2">
@@ -6180,7 +6174,7 @@
         <v>508</v>
       </c>
       <c r="B508" s="1">
-        <v>128.7185407755414</v>
+        <v>33.43683014000708</v>
       </c>
     </row>
     <row r="509" spans="1:2">
@@ -6188,7 +6182,7 @@
         <v>509</v>
       </c>
       <c r="B509" s="1">
-        <v>128.759598226899</v>
+        <v>33.43641727006803</v>
       </c>
     </row>
     <row r="510" spans="1:2">
@@ -6196,7 +6190,7 @@
         <v>510</v>
       </c>
       <c r="B510" s="1">
-        <v>128.7700575712931</v>
+        <v>33.43641307717014</v>
       </c>
     </row>
     <row r="511" spans="1:2">
@@ -6204,7 +6198,7 @@
         <v>511</v>
       </c>
       <c r="B511" s="1">
-        <v>128.8220281510526</v>
+        <v>33.43589898695337</v>
       </c>
     </row>
     <row r="512" spans="1:2">
@@ -6212,7 +6206,7 @@
         <v>512</v>
       </c>
       <c r="B512" s="1">
-        <v>129.3590255271221</v>
+        <v>33.43531250938636</v>
       </c>
     </row>
     <row r="513" spans="1:2">
@@ -6220,7 +6214,7 @@
         <v>513</v>
       </c>
       <c r="B513" s="1">
-        <v>129.6566506043779</v>
+        <v>33.43498142712208</v>
       </c>
     </row>
     <row r="514" spans="1:2">
@@ -6228,7 +6222,7 @@
         <v>514</v>
       </c>
       <c r="B514" s="1">
-        <v>129.7668675135713</v>
+        <v>33.43476580031274</v>
       </c>
     </row>
     <row r="515" spans="1:2">
@@ -6236,7 +6230,7 @@
         <v>515</v>
       </c>
       <c r="B515" s="1">
-        <v>130.0149776274214</v>
+        <v>33.43460640367353</v>
       </c>
     </row>
     <row r="516" spans="1:2">
@@ -6244,7 +6238,7 @@
         <v>516</v>
       </c>
       <c r="B516" s="1">
-        <v>130.3801278945924</v>
+        <v>33.43460107902755</v>
       </c>
     </row>
     <row r="517" spans="1:2">
@@ -6252,7 +6246,7 @@
         <v>517</v>
       </c>
       <c r="B517" s="1">
-        <v>130.4031560459095</v>
+        <v>33.43445132868265</v>
       </c>
     </row>
     <row r="518" spans="1:2">
@@ -6260,7 +6254,7 @@
         <v>518</v>
       </c>
       <c r="B518" s="1">
-        <v>130.4649817096896</v>
+        <v>33.43443718976762</v>
       </c>
     </row>
     <row r="519" spans="1:2">
@@ -6268,7 +6262,7 @@
         <v>519</v>
       </c>
       <c r="B519" s="1">
-        <v>130.6839483030402</v>
+        <v>33.43391558985112</v>
       </c>
     </row>
     <row r="520" spans="1:2">
@@ -6276,7 +6270,7 @@
         <v>520</v>
       </c>
       <c r="B520" s="1">
-        <v>130.7378099512932</v>
+        <v>33.43384938394491</v>
       </c>
     </row>
     <row r="521" spans="1:2">
@@ -6284,7 +6278,7 @@
         <v>521</v>
       </c>
       <c r="B521" s="1">
-        <v>130.7791240391813</v>
+        <v>33.43383174112847</v>
       </c>
     </row>
     <row r="522" spans="1:2">
@@ -6292,7 +6286,7 @@
         <v>522</v>
       </c>
       <c r="B522" s="1">
-        <v>130.9009048361881</v>
+        <v>33.43378607082433</v>
       </c>
     </row>
     <row r="523" spans="1:2">
@@ -6300,7 +6294,7 @@
         <v>523</v>
       </c>
       <c r="B523" s="1">
-        <v>131.3455438382084</v>
+        <v>33.43362122545026</v>
       </c>
     </row>
     <row r="524" spans="1:2">
@@ -6308,7 +6302,7 @@
         <v>524</v>
       </c>
       <c r="B524" s="1">
-        <v>131.5298010001613</v>
+        <v>33.43346234885209</v>
       </c>
     </row>
     <row r="525" spans="1:2">
@@ -6316,7 +6310,7 @@
         <v>525</v>
       </c>
       <c r="B525" s="1">
-        <v>131.7392716765293</v>
+        <v>33.43318069927589</v>
       </c>
     </row>
     <row r="526" spans="1:2">
@@ -6324,7 +6318,7 @@
         <v>526</v>
       </c>
       <c r="B526" s="1">
-        <v>131.8333354078148</v>
+        <v>33.43288280099128</v>
       </c>
     </row>
     <row r="527" spans="1:2">
@@ -6332,7 +6326,7 @@
         <v>527</v>
       </c>
       <c r="B527" s="1">
-        <v>131.8594774018143</v>
+        <v>33.4327298776052</v>
       </c>
     </row>
     <row r="528" spans="1:2">
@@ -6340,7 +6334,7 @@
         <v>528</v>
       </c>
       <c r="B528" s="1">
-        <v>132.0761585792649</v>
+        <v>33.43244144860932</v>
       </c>
     </row>
     <row r="529" spans="1:2">
@@ -6348,7 +6342,7 @@
         <v>529</v>
       </c>
       <c r="B529" s="1">
-        <v>132.363279899657</v>
+        <v>33.43235851455147</v>
       </c>
     </row>
     <row r="530" spans="1:2">
@@ -6356,7 +6350,7 @@
         <v>530</v>
       </c>
       <c r="B530" s="1">
-        <v>132.3918549050302</v>
+        <v>33.43226807524141</v>
       </c>
     </row>
     <row r="531" spans="1:2">
@@ -6364,7 +6358,7 @@
         <v>531</v>
       </c>
       <c r="B531" s="1">
-        <v>132.913318189739</v>
+        <v>33.43201907675337</v>
       </c>
     </row>
     <row r="532" spans="1:2">
@@ -6372,7 +6366,7 @@
         <v>532</v>
       </c>
       <c r="B532" s="1">
-        <v>133.3945733635198</v>
+        <v>33.43194841555246</v>
       </c>
     </row>
     <row r="533" spans="1:2">
@@ -6380,7 +6374,7 @@
         <v>533</v>
       </c>
       <c r="B533" s="1">
-        <v>134.7534928629026</v>
+        <v>33.43180531876926</v>
       </c>
     </row>
     <row r="534" spans="1:2">
@@ -6388,7 +6382,7 @@
         <v>534</v>
       </c>
       <c r="B534" s="1">
-        <v>134.9620783687639</v>
+        <v>33.43172516019835</v>
       </c>
     </row>
     <row r="535" spans="1:2">
@@ -6396,7 +6390,7 @@
         <v>535</v>
       </c>
       <c r="B535" s="1">
-        <v>135.1110639089383</v>
+        <v>33.43147991531752</v>
       </c>
     </row>
     <row r="536" spans="1:2">
@@ -6404,7 +6398,7 @@
         <v>536</v>
       </c>
       <c r="B536" s="1">
-        <v>135.5793354647257</v>
+        <v>33.43119163936947</v>
       </c>
     </row>
     <row r="537" spans="1:2">
@@ -6412,7 +6406,7 @@
         <v>537</v>
       </c>
       <c r="B537" s="1">
-        <v>135.8069273097774</v>
+        <v>33.43077378644661</v>
       </c>
     </row>
     <row r="538" spans="1:2">
@@ -6420,7 +6414,7 @@
         <v>538</v>
       </c>
       <c r="B538" s="1">
-        <v>135.8101216079676</v>
+        <v>33.43054076206211</v>
       </c>
     </row>
     <row r="539" spans="1:2">
@@ -6428,7 +6422,7 @@
         <v>539</v>
       </c>
       <c r="B539" s="1">
-        <v>135.9573515974866</v>
+        <v>33.43046415653582</v>
       </c>
     </row>
     <row r="540" spans="1:2">
@@ -6436,7 +6430,7 @@
         <v>540</v>
       </c>
       <c r="B540" s="1">
-        <v>136.2084141459405</v>
+        <v>33.43037933227902</v>
       </c>
     </row>
     <row r="541" spans="1:2">
@@ -6444,7 +6438,7 @@
         <v>541</v>
       </c>
       <c r="B541" s="1">
-        <v>136.8703800717454</v>
+        <v>33.43009082722605</v>
       </c>
     </row>
     <row r="542" spans="1:2">
@@ -6452,7 +6446,7 @@
         <v>542</v>
       </c>
       <c r="B542" s="1">
-        <v>137.3697676371432</v>
+        <v>33.42953617447929</v>
       </c>
     </row>
     <row r="543" spans="1:2">
@@ -6460,7 +6454,7 @@
         <v>543</v>
       </c>
       <c r="B543" s="1">
-        <v>137.437170506547</v>
+        <v>33.42914257993684</v>
       </c>
     </row>
     <row r="544" spans="1:2">
@@ -6468,7 +6462,7 @@
         <v>544</v>
       </c>
       <c r="B544" s="1">
-        <v>137.891232981536</v>
+        <v>33.42871296433835</v>
       </c>
     </row>
     <row r="545" spans="1:2">
@@ -6476,7 +6470,7 @@
         <v>545</v>
       </c>
       <c r="B545" s="1">
-        <v>138.3320957158581</v>
+        <v>33.42814102534907</v>
       </c>
     </row>
     <row r="546" spans="1:2">
@@ -6484,7 +6478,7 @@
         <v>546</v>
       </c>
       <c r="B546" s="1">
-        <v>138.3438330488742</v>
+        <v>33.42784033389722</v>
       </c>
     </row>
     <row r="547" spans="1:2">
@@ -6492,7 +6486,7 @@
         <v>547</v>
       </c>
       <c r="B547" s="1">
-        <v>138.3761703217812</v>
+        <v>33.42766144905583</v>
       </c>
     </row>
     <row r="548" spans="1:2">
@@ -6500,7 +6494,7 @@
         <v>548</v>
       </c>
       <c r="B548" s="1">
-        <v>139.2781771713223</v>
+        <v>33.42756170409078</v>
       </c>
     </row>
     <row r="549" spans="1:2">
@@ -6508,7 +6502,7 @@
         <v>549</v>
       </c>
       <c r="B549" s="1">
-        <v>139.4772994551172</v>
+        <v>33.42705816111207</v>
       </c>
     </row>
     <row r="550" spans="1:2">
@@ -6516,7 +6510,7 @@
         <v>550</v>
       </c>
       <c r="B550" s="1">
-        <v>139.954136623105</v>
+        <v>33.42678284656984</v>
       </c>
     </row>
     <row r="551" spans="1:2">
@@ -6524,7 +6518,7 @@
         <v>551</v>
       </c>
       <c r="B551" s="1">
-        <v>140.1677560714863</v>
+        <v>33.42671096144898</v>
       </c>
     </row>
     <row r="552" spans="1:2">
@@ -6532,7 +6526,7 @@
         <v>552</v>
       </c>
       <c r="B552" s="1">
-        <v>140.2294729300898</v>
+        <v>33.42664886091029</v>
       </c>
     </row>
     <row r="553" spans="1:2">
@@ -6540,7 +6534,7 @@
         <v>553</v>
       </c>
       <c r="B553" s="1">
-        <v>144.9926954073103</v>
+        <v>33.42657037513349</v>
       </c>
     </row>
     <row r="554" spans="1:2">
@@ -6548,7 +6542,7 @@
         <v>554</v>
       </c>
       <c r="B554" s="1">
-        <v>145.8912729429784</v>
+        <v>33.42638665004073</v>
       </c>
     </row>
     <row r="555" spans="1:2">
@@ -6556,7 +6550,7 @@
         <v>555</v>
       </c>
       <c r="B555" s="1">
-        <v>145.9459645032262</v>
+        <v>33.4263706312558</v>
       </c>
     </row>
     <row r="556" spans="1:2">
@@ -6564,7 +6558,7 @@
         <v>556</v>
       </c>
       <c r="B556" s="1">
-        <v>146.2189748711134</v>
+        <v>33.42546290367241</v>
       </c>
     </row>
     <row r="557" spans="1:2">
@@ -6572,7 +6566,7 @@
         <v>557</v>
       </c>
       <c r="B557" s="1">
-        <v>146.399127290552</v>
+        <v>33.4244838355808</v>
       </c>
     </row>
     <row r="558" spans="1:2">
@@ -6580,7 +6574,7 @@
         <v>558</v>
       </c>
       <c r="B558" s="1">
-        <v>148.000272162274</v>
+        <v>33.42424842958649</v>
       </c>
     </row>
     <row r="559" spans="1:2">
@@ -6588,7 +6582,7 @@
         <v>559</v>
       </c>
       <c r="B559" s="1">
-        <v>149.0310476877417</v>
+        <v>33.42409272385215</v>
       </c>
     </row>
     <row r="560" spans="1:2">
@@ -6596,7 +6590,7 @@
         <v>560</v>
       </c>
       <c r="B560" s="1">
-        <v>149.5294966341174</v>
+        <v>33.42349865978355</v>
       </c>
     </row>
     <row r="561" spans="1:2">
@@ -6604,7 +6598,7 @@
         <v>561</v>
       </c>
       <c r="B561" s="1">
-        <v>150.3936550073457</v>
+        <v>33.42339191783386</v>
       </c>
     </row>
     <row r="562" spans="1:2">
@@ -6612,7 +6606,7 @@
         <v>562</v>
       </c>
       <c r="B562" s="1">
-        <v>150.5504240591883</v>
+        <v>33.42319142586498</v>
       </c>
     </row>
     <row r="563" spans="1:2">
@@ -6620,7 +6614,7 @@
         <v>563</v>
       </c>
       <c r="B563" s="1">
-        <v>151.481013481751</v>
+        <v>33.42311612282665</v>
       </c>
     </row>
     <row r="564" spans="1:2">
@@ -6628,7 +6622,7 @@
         <v>564</v>
       </c>
       <c r="B564" s="1">
-        <v>151.6057646606955</v>
+        <v>33.42305628857152</v>
       </c>
     </row>
     <row r="565" spans="1:2">
@@ -6636,7 +6630,7 @@
         <v>565</v>
       </c>
       <c r="B565" s="1">
-        <v>152.0632627065476</v>
+        <v>33.42296585951996</v>
       </c>
     </row>
     <row r="566" spans="1:2">
@@ -6644,7 +6638,7 @@
         <v>566</v>
       </c>
       <c r="B566" s="1">
-        <v>152.8614573303545</v>
+        <v>33.42286148363105</v>
       </c>
     </row>
     <row r="567" spans="1:2">
@@ -6652,7 +6646,7 @@
         <v>567</v>
       </c>
       <c r="B567" s="1">
-        <v>153.3346434060217</v>
+        <v>33.42282627281778</v>
       </c>
     </row>
     <row r="568" spans="1:2">
@@ -6660,7 +6654,7 @@
         <v>568</v>
       </c>
       <c r="B568" s="1">
-        <v>153.3434867939234</v>
+        <v>33.42221769654681</v>
       </c>
     </row>
     <row r="569" spans="1:2">
@@ -6668,7 +6662,7 @@
         <v>569</v>
       </c>
       <c r="B569" s="1">
-        <v>154.7844086420247</v>
+        <v>33.42204527139312</v>
       </c>
     </row>
     <row r="570" spans="1:2">
@@ -6676,7 +6670,7 @@
         <v>570</v>
       </c>
       <c r="B570" s="1">
-        <v>156.0684119020499</v>
+        <v>33.42184124678826</v>
       </c>
     </row>
     <row r="571" spans="1:2">
@@ -6684,7 +6678,7 @@
         <v>571</v>
       </c>
       <c r="B571" s="1">
-        <v>165.5079969080281</v>
+        <v>33.42169654580277</v>
       </c>
     </row>
     <row r="572" spans="1:2">
@@ -6692,7 +6686,7 @@
         <v>572</v>
       </c>
       <c r="B572" s="1">
-        <v>174.9022355460879</v>
+        <v>33.42146877830172</v>
       </c>
     </row>
     <row r="573" spans="1:2">
@@ -6700,7 +6694,7 @@
         <v>573</v>
       </c>
       <c r="B573" s="1">
-        <v>175.3267122993277</v>
+        <v>33.42141153223691</v>
       </c>
     </row>
     <row r="574" spans="1:2">
@@ -6708,7 +6702,7 @@
         <v>574</v>
       </c>
       <c r="B574" s="1">
-        <v>197.2475447703386</v>
+        <v>33.42133786442258</v>
       </c>
     </row>
     <row r="575" spans="1:2">
@@ -6716,7 +6710,7 @@
         <v>575</v>
       </c>
       <c r="B575" s="1">
-        <v>204.0499953535999</v>
+        <v>33.42122608859736</v>
       </c>
     </row>
     <row r="576" spans="1:2">
@@ -6724,7 +6718,7 @@
         <v>576</v>
       </c>
       <c r="B576" s="1">
-        <v>212.760834693395</v>
+        <v>33.4210272535982</v>
       </c>
     </row>
     <row r="577" spans="1:2">
@@ -6732,7 +6726,7 @@
         <v>577</v>
       </c>
       <c r="B577" s="1">
-        <v>235.5773022844236</v>
+        <v>33.4206423923605</v>
       </c>
     </row>
     <row r="578" spans="1:2">
@@ -6740,7 +6734,7 @@
         <v>578</v>
       </c>
       <c r="B578" s="1">
-        <v>237.074063963061</v>
+        <v>33.42056655100343</v>
       </c>
     </row>
     <row r="579" spans="1:2">
@@ -6748,7 +6742,7 @@
         <v>579</v>
       </c>
       <c r="B579" s="1">
-        <v>256.8062287893329</v>
+        <v>33.41985402707143</v>
       </c>
     </row>
     <row r="580" spans="1:2">
@@ -6756,7 +6750,7 @@
         <v>580</v>
       </c>
       <c r="B580" s="1">
-        <v>300.7783434469101</v>
+        <v>33.41970438779525</v>
       </c>
     </row>
     <row r="581" spans="1:2">
@@ -6764,23 +6758,7 @@
         <v>581</v>
       </c>
       <c r="B581" s="1">
-        <v>328.5715905595619</v>
-      </c>
-    </row>
-    <row r="582" spans="1:2">
-      <c r="A582" t="s">
-        <v>582</v>
-      </c>
-      <c r="B582" s="1">
-        <v>350.8551599095337</v>
-      </c>
-    </row>
-    <row r="583" spans="1:2">
-      <c r="A583" t="s">
-        <v>583</v>
-      </c>
-      <c r="B583" s="1">
-        <v>413.6960672253205</v>
+        <v>33.41886860744412</v>
       </c>
     </row>
   </sheetData>

--- a/Screener/data/rs_rating_top_30.xlsx
+++ b/Screener/data/rs_rating_top_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="582">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="581">
   <si>
     <t>Symbol</t>
   </si>
@@ -22,1744 +22,1741 @@
     <t>RS Rating</t>
   </si>
   <si>
-    <t>APLS</t>
-  </si>
-  <si>
-    <t>VIR</t>
-  </si>
-  <si>
-    <t>DRVN</t>
-  </si>
-  <si>
-    <t>KDSKF</t>
-  </si>
-  <si>
-    <t>PI</t>
-  </si>
-  <si>
-    <t>ZI</t>
-  </si>
-  <si>
-    <t>NVCR</t>
-  </si>
-  <si>
-    <t>DXC</t>
-  </si>
-  <si>
-    <t>CYRX</t>
-  </si>
-  <si>
-    <t>VSAT</t>
-  </si>
-  <si>
-    <t>PRFT</t>
-  </si>
-  <si>
-    <t>SAGE</t>
-  </si>
-  <si>
-    <t>BMEA</t>
-  </si>
-  <si>
-    <t>IMXI</t>
-  </si>
-  <si>
-    <t>CTGO</t>
-  </si>
-  <si>
-    <t>RGC</t>
-  </si>
-  <si>
-    <t>SHYF</t>
-  </si>
-  <si>
-    <t>SEDG</t>
-  </si>
-  <si>
-    <t>CERE</t>
-  </si>
-  <si>
-    <t>EEFT</t>
-  </si>
-  <si>
-    <t>XMTR</t>
-  </si>
-  <si>
-    <t>MXL</t>
-  </si>
-  <si>
-    <t>VKTX</t>
-  </si>
-  <si>
-    <t>SDGR</t>
-  </si>
-  <si>
-    <t>ONEW</t>
-  </si>
-  <si>
-    <t>SILC</t>
-  </si>
-  <si>
-    <t>INBX</t>
-  </si>
-  <si>
-    <t>SPR</t>
-  </si>
-  <si>
-    <t>MASI</t>
-  </si>
-  <si>
-    <t>SILK</t>
-  </si>
-  <si>
-    <t>PEN</t>
-  </si>
-  <si>
-    <t>BHVN</t>
-  </si>
-  <si>
-    <t>OFED</t>
-  </si>
-  <si>
-    <t>NVRO</t>
-  </si>
-  <si>
-    <t>ENPH</t>
-  </si>
-  <si>
-    <t>IRBT</t>
-  </si>
-  <si>
-    <t>MODV</t>
-  </si>
-  <si>
-    <t>PTGX</t>
-  </si>
-  <si>
-    <t>RYI</t>
-  </si>
-  <si>
-    <t>GNRC</t>
+    <t>EDTX</t>
+  </si>
+  <si>
+    <t>USM</t>
+  </si>
+  <si>
+    <t>EDTXU</t>
+  </si>
+  <si>
+    <t>TDS</t>
+  </si>
+  <si>
+    <t>TSAT</t>
+  </si>
+  <si>
+    <t>SGTX</t>
+  </si>
+  <si>
+    <t>AAOI</t>
+  </si>
+  <si>
+    <t>GRPN</t>
+  </si>
+  <si>
+    <t>CDLX</t>
+  </si>
+  <si>
+    <t>URGN</t>
+  </si>
+  <si>
+    <t>CPRI</t>
+  </si>
+  <si>
+    <t>APP</t>
+  </si>
+  <si>
+    <t>LMB</t>
+  </si>
+  <si>
+    <t>RETA</t>
+  </si>
+  <si>
+    <t>CAMT</t>
+  </si>
+  <si>
+    <t>ML</t>
+  </si>
+  <si>
+    <t>DLO</t>
+  </si>
+  <si>
+    <t>ANF</t>
+  </si>
+  <si>
+    <t>STRL</t>
+  </si>
+  <si>
+    <t>BBIO</t>
+  </si>
+  <si>
+    <t>BOOM</t>
+  </si>
+  <si>
+    <t>SBOW</t>
+  </si>
+  <si>
+    <t>UPWK</t>
+  </si>
+  <si>
+    <t>PARR</t>
+  </si>
+  <si>
+    <t>FSTR</t>
+  </si>
+  <si>
+    <t>IESC</t>
+  </si>
+  <si>
+    <t>CBAY</t>
+  </si>
+  <si>
+    <t>TPL</t>
+  </si>
+  <si>
+    <t>PETQ</t>
+  </si>
+  <si>
+    <t>SENEA</t>
+  </si>
+  <si>
+    <t>CLS</t>
+  </si>
+  <si>
+    <t>CTRN</t>
+  </si>
+  <si>
+    <t>VRTV</t>
+  </si>
+  <si>
+    <t>LEU</t>
+  </si>
+  <si>
+    <t>SENEB</t>
+  </si>
+  <si>
+    <t>LEAT</t>
+  </si>
+  <si>
+    <t>ESTE</t>
+  </si>
+  <si>
+    <t>PAY</t>
+  </si>
+  <si>
+    <t>PHVS</t>
+  </si>
+  <si>
+    <t>VRT</t>
+  </si>
+  <si>
+    <t>KRT</t>
+  </si>
+  <si>
+    <t>RYTM</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>ACMR</t>
+  </si>
+  <si>
+    <t>MMYT</t>
+  </si>
+  <si>
+    <t>FN</t>
+  </si>
+  <si>
+    <t>WLDN</t>
+  </si>
+  <si>
+    <t>GAMB</t>
+  </si>
+  <si>
+    <t>CORT</t>
+  </si>
+  <si>
+    <t>LYTS</t>
+  </si>
+  <si>
+    <t>MNSO</t>
+  </si>
+  <si>
+    <t>KD</t>
+  </si>
+  <si>
+    <t>SOVO</t>
+  </si>
+  <si>
+    <t>MOD</t>
+  </si>
+  <si>
+    <t>AEO</t>
+  </si>
+  <si>
+    <t>CELH</t>
+  </si>
+  <si>
+    <t>ERIE</t>
+  </si>
+  <si>
+    <t>IDYA</t>
+  </si>
+  <si>
+    <t>OBT</t>
+  </si>
+  <si>
+    <t>LLY</t>
+  </si>
+  <si>
+    <t>PRDO</t>
+  </si>
+  <si>
+    <t>CMT</t>
+  </si>
+  <si>
+    <t>RELY</t>
+  </si>
+  <si>
+    <t>ANIP</t>
+  </si>
+  <si>
+    <t>CWCO</t>
+  </si>
+  <si>
+    <t>GHM</t>
+  </si>
+  <si>
+    <t>CEIX</t>
+  </si>
+  <si>
+    <t>SM</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>NATR</t>
+  </si>
+  <si>
+    <t>SRDX</t>
+  </si>
+  <si>
+    <t>DCBO</t>
+  </si>
+  <si>
+    <t>ARGX</t>
+  </si>
+  <si>
+    <t>TWIN</t>
+  </si>
+  <si>
+    <t>RNGR</t>
+  </si>
+  <si>
+    <t>CSPI</t>
+  </si>
+  <si>
+    <t>HWKN</t>
+  </si>
+  <si>
+    <t>POWL</t>
+  </si>
+  <si>
+    <t>HRB</t>
+  </si>
+  <si>
+    <t>UBS</t>
+  </si>
+  <si>
+    <t>AMR</t>
+  </si>
+  <si>
+    <t>BKI</t>
+  </si>
+  <si>
+    <t>NVO</t>
+  </si>
+  <si>
+    <t>SHEN</t>
+  </si>
+  <si>
+    <t>NRP</t>
+  </si>
+  <si>
+    <t>PDS</t>
+  </si>
+  <si>
+    <t>VNO</t>
+  </si>
+  <si>
+    <t>TH</t>
+  </si>
+  <si>
+    <t>BBW</t>
+  </si>
+  <si>
+    <t>ACU</t>
+  </si>
+  <si>
+    <t>MPC</t>
+  </si>
+  <si>
+    <t>MTSI</t>
+  </si>
+  <si>
+    <t>XPRO</t>
+  </si>
+  <si>
+    <t>STER</t>
+  </si>
+  <si>
+    <t>ITRN</t>
+  </si>
+  <si>
+    <t>YETI</t>
+  </si>
+  <si>
+    <t>WFRD</t>
+  </si>
+  <si>
+    <t>EDU</t>
+  </si>
+  <si>
+    <t>TW</t>
+  </si>
+  <si>
+    <t>PAR</t>
+  </si>
+  <si>
+    <t>FORG</t>
+  </si>
+  <si>
+    <t>ESEA</t>
+  </si>
+  <si>
+    <t>AZTA</t>
+  </si>
+  <si>
+    <t>XPO</t>
+  </si>
+  <si>
+    <t>AURC</t>
+  </si>
+  <si>
+    <t>FOR</t>
+  </si>
+  <si>
+    <t>BFST</t>
+  </si>
+  <si>
+    <t>NTRA</t>
+  </si>
+  <si>
+    <t>FRHC</t>
+  </si>
+  <si>
+    <t>SCPL</t>
+  </si>
+  <si>
+    <t>WMPN</t>
+  </si>
+  <si>
+    <t>WAL</t>
+  </si>
+  <si>
+    <t>CALB</t>
+  </si>
+  <si>
+    <t>NHC</t>
+  </si>
+  <si>
+    <t>COUR</t>
+  </si>
+  <si>
+    <t>CNX</t>
+  </si>
+  <si>
+    <t>TRNS</t>
+  </si>
+  <si>
+    <t>QCRH</t>
+  </si>
+  <si>
+    <t>HEP</t>
+  </si>
+  <si>
+    <t>AMNB</t>
+  </si>
+  <si>
+    <t>OSIS</t>
+  </si>
+  <si>
+    <t>NEWR</t>
+  </si>
+  <si>
+    <t>AROC</t>
+  </si>
+  <si>
+    <t>CRC</t>
+  </si>
+  <si>
+    <t>LAUR</t>
+  </si>
+  <si>
+    <t>NOA</t>
+  </si>
+  <si>
+    <t>SAIA</t>
+  </si>
+  <si>
+    <t>RCUS</t>
+  </si>
+  <si>
+    <t>INSW</t>
+  </si>
+  <si>
+    <t>CSTL</t>
+  </si>
+  <si>
+    <t>NCR</t>
+  </si>
+  <si>
+    <t>VERX</t>
+  </si>
+  <si>
+    <t>SFBS</t>
+  </si>
+  <si>
+    <t>AMGN</t>
+  </si>
+  <si>
+    <t>CIVI</t>
+  </si>
+  <si>
+    <t>GES</t>
+  </si>
+  <si>
+    <t>WMG</t>
+  </si>
+  <si>
+    <t>JOE</t>
+  </si>
+  <si>
+    <t>BWMX</t>
+  </si>
+  <si>
+    <t>EME</t>
+  </si>
+  <si>
+    <t>SLG</t>
+  </si>
+  <si>
+    <t>FLXS</t>
+  </si>
+  <si>
+    <t>VST</t>
+  </si>
+  <si>
+    <t>APA</t>
+  </si>
+  <si>
+    <t>GIC</t>
+  </si>
+  <si>
+    <t>RVMD</t>
+  </si>
+  <si>
+    <t>CAAP</t>
+  </si>
+  <si>
+    <t>PSN</t>
+  </si>
+  <si>
+    <t>FTAI</t>
+  </si>
+  <si>
+    <t>STEP</t>
+  </si>
+  <si>
+    <t>INOD</t>
+  </si>
+  <si>
+    <t>AZZ</t>
+  </si>
+  <si>
+    <t>AFBI</t>
+  </si>
+  <si>
+    <t>OVV</t>
+  </si>
+  <si>
+    <t>MTDR</t>
+  </si>
+  <si>
+    <t>FRO</t>
+  </si>
+  <si>
+    <t>CDRE</t>
+  </si>
+  <si>
+    <t>NOV</t>
+  </si>
+  <si>
+    <t>RAMP</t>
+  </si>
+  <si>
+    <t>FSLY</t>
+  </si>
+  <si>
+    <t>BCC</t>
+  </si>
+  <si>
+    <t>BRBR</t>
+  </si>
+  <si>
+    <t>PRMW</t>
+  </si>
+  <si>
+    <t>ARRY</t>
+  </si>
+  <si>
+    <t>TALO</t>
+  </si>
+  <si>
+    <t>BR</t>
+  </si>
+  <si>
+    <t>DVAX</t>
+  </si>
+  <si>
+    <t>PBNK</t>
+  </si>
+  <si>
+    <t>INBK</t>
+  </si>
+  <si>
+    <t>HURN</t>
+  </si>
+  <si>
+    <t>PRA</t>
+  </si>
+  <si>
+    <t>VALU</t>
+  </si>
+  <si>
+    <t>DLR</t>
+  </si>
+  <si>
+    <t>GNE</t>
+  </si>
+  <si>
+    <t>ROCK</t>
+  </si>
+  <si>
+    <t>AKAM</t>
+  </si>
+  <si>
+    <t>PAM</t>
+  </si>
+  <si>
+    <t>FRSH</t>
+  </si>
+  <si>
+    <t>HALO</t>
+  </si>
+  <si>
+    <t>CABA</t>
+  </si>
+  <si>
+    <t>ENLC</t>
+  </si>
+  <si>
+    <t>CCOI</t>
+  </si>
+  <si>
+    <t>QLYS</t>
+  </si>
+  <si>
+    <t>COSO</t>
+  </si>
+  <si>
+    <t>AMEH</t>
+  </si>
+  <si>
+    <t>ODFL</t>
+  </si>
+  <si>
+    <t>ACAD</t>
+  </si>
+  <si>
+    <t>RDY</t>
+  </si>
+  <si>
+    <t>TDW</t>
+  </si>
+  <si>
+    <t>FSFG</t>
+  </si>
+  <si>
+    <t>SXI</t>
+  </si>
+  <si>
+    <t>LOB</t>
+  </si>
+  <si>
+    <t>FETM</t>
+  </si>
+  <si>
+    <t>ASTE</t>
+  </si>
+  <si>
+    <t>AURCU</t>
+  </si>
+  <si>
+    <t>PBF</t>
+  </si>
+  <si>
+    <t>EXEL</t>
+  </si>
+  <si>
+    <t>VICR</t>
+  </si>
+  <si>
+    <t>BOH</t>
+  </si>
+  <si>
+    <t>CCJ</t>
+  </si>
+  <si>
+    <t>VLO</t>
+  </si>
+  <si>
+    <t>TFII</t>
+  </si>
+  <si>
+    <t>CFBK</t>
+  </si>
+  <si>
+    <t>MNMB</t>
+  </si>
+  <si>
+    <t>XPEV</t>
+  </si>
+  <si>
+    <t>BNTX</t>
+  </si>
+  <si>
+    <t>AGM</t>
+  </si>
+  <si>
+    <t>EVI</t>
+  </si>
+  <si>
+    <t>PSX</t>
+  </si>
+  <si>
+    <t>WHD</t>
+  </si>
+  <si>
+    <t>REGN</t>
+  </si>
+  <si>
+    <t>EURN</t>
+  </si>
+  <si>
+    <t>ODC</t>
+  </si>
+  <si>
+    <t>BKNG</t>
+  </si>
+  <si>
+    <t>IPI</t>
+  </si>
+  <si>
+    <t>ARCE</t>
+  </si>
+  <si>
+    <t>OPCH</t>
+  </si>
+  <si>
+    <t>SU</t>
+  </si>
+  <si>
+    <t>FFNW</t>
+  </si>
+  <si>
+    <t>PRIM</t>
+  </si>
+  <si>
+    <t>CNXN</t>
+  </si>
+  <si>
+    <t>HNI</t>
+  </si>
+  <si>
+    <t>RPD</t>
+  </si>
+  <si>
+    <t>TIPT</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>GPN</t>
+  </si>
+  <si>
+    <t>BCSF</t>
+  </si>
+  <si>
+    <t>PLUS</t>
+  </si>
+  <si>
+    <t>STNG</t>
+  </si>
+  <si>
+    <t>SMMF</t>
+  </si>
+  <si>
+    <t>MOH</t>
+  </si>
+  <si>
+    <t>SAL</t>
+  </si>
+  <si>
+    <t>ICFI</t>
+  </si>
+  <si>
+    <t>IONQ</t>
+  </si>
+  <si>
+    <t>ALRM</t>
+  </si>
+  <si>
+    <t>CVBF</t>
+  </si>
+  <si>
+    <t>TRUP</t>
+  </si>
+  <si>
+    <t>MUR</t>
+  </si>
+  <si>
+    <t>FNF</t>
+  </si>
+  <si>
+    <t>AEL</t>
+  </si>
+  <si>
+    <t>ESCA</t>
+  </si>
+  <si>
+    <t>IMO</t>
+  </si>
+  <si>
+    <t>SAM</t>
+  </si>
+  <si>
+    <t>DCOM</t>
+  </si>
+  <si>
+    <t>TRGP</t>
+  </si>
+  <si>
+    <t>JAZZ</t>
+  </si>
+  <si>
+    <t>BG</t>
+  </si>
+  <si>
+    <t>HCCI</t>
+  </si>
+  <si>
+    <t>CVLG</t>
+  </si>
+  <si>
+    <t>CHTR</t>
+  </si>
+  <si>
+    <t>CHX</t>
+  </si>
+  <si>
+    <t>TRDA</t>
+  </si>
+  <si>
+    <t>PRGO</t>
+  </si>
+  <si>
+    <t>DFH</t>
+  </si>
+  <si>
+    <t>HOFT</t>
+  </si>
+  <si>
+    <t>NWLI</t>
+  </si>
+  <si>
+    <t>MGRC</t>
+  </si>
+  <si>
+    <t>TNP</t>
+  </si>
+  <si>
+    <t>NXGN</t>
+  </si>
+  <si>
+    <t>DELL</t>
+  </si>
+  <si>
+    <t>AIT</t>
+  </si>
+  <si>
+    <t>ERF</t>
+  </si>
+  <si>
+    <t>CFNB</t>
+  </si>
+  <si>
+    <t>FRPT</t>
+  </si>
+  <si>
+    <t>MLR</t>
+  </si>
+  <si>
+    <t>KNSA</t>
+  </si>
+  <si>
+    <t>DAWN</t>
+  </si>
+  <si>
+    <t>AZEK</t>
+  </si>
+  <si>
+    <t>CW</t>
+  </si>
+  <si>
+    <t>ARCH</t>
+  </si>
+  <si>
+    <t>ARBV</t>
+  </si>
+  <si>
+    <t>CIBH</t>
+  </si>
+  <si>
+    <t>WWE</t>
+  </si>
+  <si>
+    <t>KTB</t>
+  </si>
+  <si>
+    <t>SPB</t>
+  </si>
+  <si>
+    <t>MLKN</t>
+  </si>
+  <si>
+    <t>SMLR</t>
+  </si>
+  <si>
+    <t>PDCO</t>
+  </si>
+  <si>
+    <t>BBSI</t>
+  </si>
+  <si>
+    <t>HOLI</t>
+  </si>
+  <si>
+    <t>CBOE</t>
+  </si>
+  <si>
+    <t>ANET</t>
+  </si>
+  <si>
+    <t>COCO</t>
+  </si>
+  <si>
+    <t>GBDC</t>
+  </si>
+  <si>
+    <t>NTIC</t>
+  </si>
+  <si>
+    <t>BHWB</t>
+  </si>
+  <si>
+    <t>NARI</t>
+  </si>
+  <si>
+    <t>DOMO</t>
+  </si>
+  <si>
+    <t>ATEX</t>
+  </si>
+  <si>
+    <t>FLR</t>
+  </si>
+  <si>
+    <t>PPC</t>
+  </si>
+  <si>
+    <t>STRT</t>
+  </si>
+  <si>
+    <t>NOG</t>
+  </si>
+  <si>
+    <t>PBAM</t>
+  </si>
+  <si>
+    <t>ETN</t>
+  </si>
+  <si>
+    <t>GPOR</t>
+  </si>
+  <si>
+    <t>ADP</t>
+  </si>
+  <si>
+    <t>NBIX</t>
+  </si>
+  <si>
+    <t>YELP</t>
+  </si>
+  <si>
+    <t>KTOS</t>
+  </si>
+  <si>
+    <t>SPOK</t>
+  </si>
+  <si>
+    <t>STRA</t>
+  </si>
+  <si>
+    <t>CLW</t>
+  </si>
+  <si>
+    <t>JXN</t>
+  </si>
+  <si>
+    <t>ACT</t>
+  </si>
+  <si>
+    <t>VRNS</t>
+  </si>
+  <si>
+    <t>ROST</t>
+  </si>
+  <si>
+    <t>PXD</t>
+  </si>
+  <si>
+    <t>FANG</t>
+  </si>
+  <si>
+    <t>DBRG</t>
+  </si>
+  <si>
+    <t>ARLP</t>
+  </si>
+  <si>
+    <t>SCSC</t>
+  </si>
+  <si>
+    <t>ATGE</t>
+  </si>
+  <si>
+    <t>TNET</t>
+  </si>
+  <si>
+    <t>SPLK</t>
+  </si>
+  <si>
+    <t>LOPE</t>
+  </si>
+  <si>
+    <t>LRN</t>
+  </si>
+  <si>
+    <t>ORRF</t>
+  </si>
+  <si>
+    <t>MBWM</t>
+  </si>
+  <si>
+    <t>TRMD</t>
+  </si>
+  <si>
+    <t>PSFE</t>
+  </si>
+  <si>
+    <t>FRD</t>
+  </si>
+  <si>
+    <t>NE</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>NREF</t>
+  </si>
+  <si>
+    <t>CFST</t>
+  </si>
+  <si>
+    <t>FWRG</t>
+  </si>
+  <si>
+    <t>AVTR</t>
+  </si>
+  <si>
+    <t>AR</t>
+  </si>
+  <si>
+    <t>SBS</t>
+  </si>
+  <si>
+    <t>ZION</t>
+  </si>
+  <si>
+    <t>LOGI</t>
+  </si>
+  <si>
+    <t>FIX</t>
+  </si>
+  <si>
+    <t>SPNS</t>
+  </si>
+  <si>
+    <t>DGICB</t>
+  </si>
+  <si>
+    <t>IBKR</t>
+  </si>
+  <si>
+    <t>OII</t>
+  </si>
+  <si>
+    <t>SIM</t>
+  </si>
+  <si>
+    <t>VAL</t>
+  </si>
+  <si>
+    <t>AE</t>
+  </si>
+  <si>
+    <t>NVDA</t>
+  </si>
+  <si>
+    <t>OLLI</t>
+  </si>
+  <si>
+    <t>DRQ</t>
+  </si>
+  <si>
+    <t>SSD</t>
+  </si>
+  <si>
+    <t>CDW</t>
+  </si>
+  <si>
+    <t>RPM</t>
+  </si>
+  <si>
+    <t>MANU</t>
+  </si>
+  <si>
+    <t>CSWI</t>
+  </si>
+  <si>
+    <t>NYT</t>
+  </si>
+  <si>
+    <t>JILL</t>
+  </si>
+  <si>
+    <t>SBFG</t>
+  </si>
+  <si>
+    <t>PHAR</t>
+  </si>
+  <si>
+    <t>PAA</t>
+  </si>
+  <si>
+    <t>HLNE</t>
+  </si>
+  <si>
+    <t>XP</t>
+  </si>
+  <si>
+    <t>SFM</t>
+  </si>
+  <si>
+    <t>VECO</t>
+  </si>
+  <si>
+    <t>IRTC</t>
+  </si>
+  <si>
+    <t>ATSG</t>
+  </si>
+  <si>
+    <t>MUSA</t>
+  </si>
+  <si>
+    <t>VMW</t>
+  </si>
+  <si>
+    <t>TS</t>
+  </si>
+  <si>
+    <t>HCM</t>
+  </si>
+  <si>
+    <t>EVBN</t>
+  </si>
+  <si>
+    <t>CVNA</t>
+  </si>
+  <si>
+    <t>DHACU</t>
+  </si>
+  <si>
+    <t>OSK</t>
+  </si>
+  <si>
+    <t>ALPN</t>
+  </si>
+  <si>
+    <t>SPFI</t>
+  </si>
+  <si>
+    <t>CSCO</t>
+  </si>
+  <si>
+    <t>NSIT</t>
+  </si>
+  <si>
+    <t>BXP</t>
+  </si>
+  <si>
+    <t>PAGP</t>
+  </si>
+  <si>
+    <t>INFY</t>
+  </si>
+  <si>
+    <t>DCPH</t>
+  </si>
+  <si>
+    <t>KT</t>
+  </si>
+  <si>
+    <t>CENT</t>
+  </si>
+  <si>
+    <t>TEAM</t>
+  </si>
+  <si>
+    <t>CPRX</t>
+  </si>
+  <si>
+    <t>ANDE</t>
+  </si>
+  <si>
+    <t>CSWC</t>
+  </si>
+  <si>
+    <t>KRC</t>
+  </si>
+  <si>
+    <t>MGPI</t>
+  </si>
+  <si>
+    <t>ATR</t>
+  </si>
+  <si>
+    <t>SRV</t>
+  </si>
+  <si>
+    <t>APOG</t>
+  </si>
+  <si>
+    <t>FRSB</t>
+  </si>
+  <si>
+    <t>AIR</t>
+  </si>
+  <si>
+    <t>NECB</t>
+  </si>
+  <si>
+    <t>PX</t>
+  </si>
+  <si>
+    <t>CIGI</t>
+  </si>
+  <si>
+    <t>HUM</t>
+  </si>
+  <si>
+    <t>CRVL</t>
+  </si>
+  <si>
+    <t>CCB</t>
+  </si>
+  <si>
+    <t>MPV</t>
+  </si>
+  <si>
+    <t>LBRT</t>
+  </si>
+  <si>
+    <t>TCOM</t>
+  </si>
+  <si>
+    <t>MLAB</t>
+  </si>
+  <si>
+    <t>GBLI</t>
+  </si>
+  <si>
+    <t>WAYN</t>
+  </si>
+  <si>
+    <t>MAT</t>
+  </si>
+  <si>
+    <t>LBRDA</t>
+  </si>
+  <si>
+    <t>NEU</t>
+  </si>
+  <si>
+    <t>SAH</t>
+  </si>
+  <si>
+    <t>TXT</t>
+  </si>
+  <si>
+    <t>BSFO</t>
+  </si>
+  <si>
+    <t>WSM</t>
+  </si>
+  <si>
+    <t>COLL</t>
+  </si>
+  <si>
+    <t>NWS</t>
+  </si>
+  <si>
+    <t>MDRX</t>
+  </si>
+  <si>
+    <t>VVI</t>
+  </si>
+  <si>
+    <t>GCO</t>
+  </si>
+  <si>
+    <t>BSRR</t>
+  </si>
+  <si>
+    <t>CTRA</t>
+  </si>
+  <si>
+    <t>BDX</t>
+  </si>
+  <si>
+    <t>CRAI</t>
+  </si>
+  <si>
+    <t>EMYB</t>
+  </si>
+  <si>
+    <t>BKR</t>
+  </si>
+  <si>
+    <t>LBRDK</t>
+  </si>
+  <si>
+    <t>MVBF</t>
+  </si>
+  <si>
+    <t>SFST</t>
+  </si>
+  <si>
+    <t>TTE</t>
+  </si>
+  <si>
+    <t>LDOS</t>
+  </si>
+  <si>
+    <t>CMUV</t>
+  </si>
+  <si>
+    <t>BLMN</t>
+  </si>
+  <si>
+    <t>SCHL</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>AZPN</t>
+  </si>
+  <si>
+    <t>NGVC</t>
+  </si>
+  <si>
+    <t>WOR</t>
+  </si>
+  <si>
+    <t>PHAT</t>
+  </si>
+  <si>
+    <t>HLF</t>
+  </si>
+  <si>
+    <t>CMCSA</t>
+  </si>
+  <si>
+    <t>ZGN</t>
+  </si>
+  <si>
+    <t>FTI</t>
+  </si>
+  <si>
+    <t>BCML</t>
+  </si>
+  <si>
+    <t>HES</t>
+  </si>
+  <si>
+    <t>CME</t>
+  </si>
+  <si>
+    <t>UNF</t>
+  </si>
+  <si>
+    <t>WTM</t>
+  </si>
+  <si>
+    <t>BRO</t>
+  </si>
+  <si>
+    <t>FLT</t>
+  </si>
+  <si>
+    <t>PRO</t>
+  </si>
+  <si>
+    <t>AIZ</t>
+  </si>
+  <si>
+    <t>SFBC</t>
+  </si>
+  <si>
+    <t>AVNW</t>
+  </si>
+  <si>
+    <t>BMI</t>
+  </si>
+  <si>
+    <t>FDS</t>
+  </si>
+  <si>
+    <t>BY</t>
+  </si>
+  <si>
+    <t>MAR</t>
+  </si>
+  <si>
+    <t>LPLA</t>
+  </si>
+  <si>
+    <t>SLB</t>
+  </si>
+  <si>
+    <t>ARL</t>
+  </si>
+  <si>
+    <t>SVBT</t>
+  </si>
+  <si>
+    <t>BLX</t>
+  </si>
+  <si>
+    <t>DWACU</t>
+  </si>
+  <si>
+    <t>HZNP</t>
+  </si>
+  <si>
+    <t>ISTR</t>
+  </si>
+  <si>
+    <t>HAL</t>
+  </si>
+  <si>
+    <t>COP</t>
+  </si>
+  <si>
+    <t>CVRX</t>
+  </si>
+  <si>
+    <t>EIC</t>
+  </si>
+  <si>
+    <t>WIX</t>
+  </si>
+  <si>
+    <t>WST</t>
+  </si>
+  <si>
+    <t>NVMI</t>
+  </si>
+  <si>
+    <t>OLED</t>
+  </si>
+  <si>
+    <t>TJX</t>
+  </si>
+  <si>
+    <t>CLMT</t>
+  </si>
+  <si>
+    <t>TCBX</t>
+  </si>
+  <si>
+    <t>CNQ</t>
+  </si>
+  <si>
+    <t>JLL</t>
+  </si>
+  <si>
+    <t>GBX</t>
+  </si>
+  <si>
+    <t>NWSA</t>
+  </si>
+  <si>
+    <t>CAE</t>
+  </si>
+  <si>
+    <t>AIF</t>
+  </si>
+  <si>
+    <t>FMX</t>
+  </si>
+  <si>
+    <t>NDP</t>
+  </si>
+  <si>
+    <t>COOP</t>
+  </si>
+  <si>
+    <t>MSCI</t>
+  </si>
+  <si>
+    <t>BWXT</t>
+  </si>
+  <si>
+    <t>ABM</t>
+  </si>
+  <si>
+    <t>VABK</t>
+  </si>
+  <si>
+    <t>QTRX</t>
+  </si>
+  <si>
+    <t>BLD</t>
+  </si>
+  <si>
+    <t>MHO</t>
+  </si>
+  <si>
+    <t>IHG</t>
+  </si>
+  <si>
+    <t>ASND</t>
+  </si>
+  <si>
+    <t>TCBI</t>
+  </si>
+  <si>
+    <t>FNWB</t>
+  </si>
+  <si>
+    <t>CHH</t>
+  </si>
+  <si>
+    <t>CENTA</t>
+  </si>
+  <si>
+    <t>EDR</t>
+  </si>
+  <si>
+    <t>JDVB</t>
+  </si>
+  <si>
+    <t>GOOG</t>
+  </si>
+  <si>
+    <t>JHX</t>
+  </si>
+  <si>
+    <t>KCLI</t>
+  </si>
+  <si>
+    <t>GOOGL</t>
+  </si>
+  <si>
+    <t>LII</t>
+  </si>
+  <si>
+    <t>MET</t>
+  </si>
+  <si>
+    <t>ESNT</t>
+  </si>
+  <si>
+    <t>BCO</t>
+  </si>
+  <si>
+    <t>SWTX</t>
+  </si>
+  <si>
+    <t>TCPC</t>
+  </si>
+  <si>
+    <t>DK</t>
+  </si>
+  <si>
+    <t>ROAD</t>
+  </si>
+  <si>
+    <t>KB</t>
+  </si>
+  <si>
+    <t>TSBK</t>
+  </si>
+  <si>
+    <t>ODP</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>BMRN</t>
+  </si>
+  <si>
+    <t>AUBN</t>
+  </si>
+  <si>
+    <t>UFPI</t>
+  </si>
+  <si>
+    <t>FUNC</t>
+  </si>
+  <si>
+    <t>MAYS</t>
+  </si>
+  <si>
+    <t>ABBV</t>
+  </si>
+  <si>
+    <t>ARCB</t>
+  </si>
+  <si>
+    <t>NTNX</t>
+  </si>
+  <si>
+    <t>INSM</t>
+  </si>
+  <si>
+    <t>ATVI</t>
+  </si>
+  <si>
+    <t>BRP</t>
+  </si>
+  <si>
+    <t>NOMD</t>
+  </si>
+  <si>
+    <t>PFGC</t>
+  </si>
+  <si>
+    <t>VRE</t>
   </si>
   <si>
     <t>MRTX</t>
   </si>
   <si>
-    <t>IPGP</t>
-  </si>
-  <si>
-    <t>VRDN</t>
-  </si>
-  <si>
-    <t>CCRN</t>
-  </si>
-  <si>
-    <t>DKL</t>
-  </si>
-  <si>
-    <t>IRDM</t>
-  </si>
-  <si>
-    <t>OPRA</t>
-  </si>
-  <si>
-    <t>NSP</t>
-  </si>
-  <si>
-    <t>BPMC</t>
-  </si>
-  <si>
-    <t>LTHM</t>
-  </si>
-  <si>
-    <t>LNTH</t>
-  </si>
-  <si>
-    <t>INTA</t>
-  </si>
-  <si>
-    <t>BEAM</t>
-  </si>
-  <si>
-    <t>MDGL</t>
-  </si>
-  <si>
-    <t>RDWR</t>
-  </si>
-  <si>
-    <t>LTH</t>
-  </si>
-  <si>
-    <t>NXRT</t>
-  </si>
-  <si>
-    <t>ETNB</t>
-  </si>
-  <si>
-    <t>RCKT</t>
-  </si>
-  <si>
-    <t>SSTK</t>
-  </si>
-  <si>
-    <t>NEP</t>
-  </si>
-  <si>
-    <t>MLNK</t>
-  </si>
-  <si>
-    <t>ALB</t>
-  </si>
-  <si>
-    <t>CNMD</t>
-  </si>
-  <si>
-    <t>KRTX</t>
-  </si>
-  <si>
-    <t>NTRA</t>
-  </si>
-  <si>
-    <t>CRNC</t>
-  </si>
-  <si>
-    <t>MAXN</t>
-  </si>
-  <si>
-    <t>ZBRA</t>
-  </si>
-  <si>
-    <t>AMOT</t>
-  </si>
-  <si>
-    <t>ANIK</t>
-  </si>
-  <si>
-    <t>KPLT</t>
-  </si>
-  <si>
-    <t>AU</t>
-  </si>
-  <si>
-    <t>NOVA</t>
-  </si>
-  <si>
-    <t>OM</t>
-  </si>
-  <si>
-    <t>IPG</t>
-  </si>
-  <si>
-    <t>CALX</t>
-  </si>
-  <si>
-    <t>AYX</t>
-  </si>
-  <si>
-    <t>PLL</t>
-  </si>
-  <si>
-    <t>TMCI</t>
-  </si>
-  <si>
-    <t>EFX</t>
-  </si>
-  <si>
-    <t>CWEN</t>
-  </si>
-  <si>
-    <t>WING</t>
-  </si>
-  <si>
-    <t>EYE</t>
-  </si>
-  <si>
-    <t>DV</t>
-  </si>
-  <si>
-    <t>RBLX</t>
-  </si>
-  <si>
-    <t>FNA</t>
-  </si>
-  <si>
-    <t>MEG</t>
-  </si>
-  <si>
-    <t>DQ</t>
-  </si>
-  <si>
-    <t>NUS</t>
-  </si>
-  <si>
-    <t>SWAV</t>
-  </si>
-  <si>
-    <t>TBI</t>
-  </si>
-  <si>
-    <t>TGS</t>
-  </si>
-  <si>
-    <t>MMSI</t>
-  </si>
-  <si>
-    <t>EW</t>
-  </si>
-  <si>
-    <t>NVEC</t>
-  </si>
-  <si>
-    <t>BELFB</t>
-  </si>
-  <si>
-    <t>LMAT</t>
-  </si>
-  <si>
-    <t>SIBN</t>
-  </si>
-  <si>
-    <t>CHWY</t>
-  </si>
-  <si>
-    <t>CWCO</t>
-  </si>
-  <si>
-    <t>CHEF</t>
-  </si>
-  <si>
-    <t>TCX</t>
-  </si>
-  <si>
-    <t>SGRY</t>
-  </si>
-  <si>
-    <t>OMC</t>
-  </si>
-  <si>
-    <t>VEON</t>
-  </si>
-  <si>
-    <t>ARRY</t>
-  </si>
-  <si>
-    <t>VAC</t>
-  </si>
-  <si>
-    <t>YZCAY</t>
-  </si>
-  <si>
-    <t>RTX</t>
-  </si>
-  <si>
-    <t>OMCL</t>
-  </si>
-  <si>
-    <t>INTT</t>
-  </si>
-  <si>
-    <t>HTZ</t>
-  </si>
-  <si>
-    <t>GME</t>
-  </si>
-  <si>
-    <t>SXT</t>
-  </si>
-  <si>
-    <t>SMG</t>
-  </si>
-  <si>
-    <t>DFS</t>
-  </si>
-  <si>
-    <t>NTLA</t>
-  </si>
-  <si>
-    <t>BELFA</t>
-  </si>
-  <si>
-    <t>IMGN</t>
-  </si>
-  <si>
-    <t>OFLX</t>
-  </si>
-  <si>
-    <t>JKS</t>
-  </si>
-  <si>
-    <t>ZBH</t>
-  </si>
-  <si>
-    <t>MRNA</t>
-  </si>
-  <si>
-    <t>WCC</t>
-  </si>
-  <si>
-    <t>BEPC</t>
-  </si>
-  <si>
-    <t>STAA</t>
-  </si>
-  <si>
-    <t>PTLO</t>
-  </si>
-  <si>
-    <t>RARE</t>
-  </si>
-  <si>
-    <t>HCBC</t>
-  </si>
-  <si>
-    <t>TCMD</t>
-  </si>
-  <si>
-    <t>LITE</t>
-  </si>
-  <si>
-    <t>RGNX</t>
-  </si>
-  <si>
-    <t>REPL</t>
-  </si>
-  <si>
-    <t>ETSY</t>
-  </si>
-  <si>
-    <t>KIDS</t>
-  </si>
-  <si>
-    <t>AXON</t>
-  </si>
-  <si>
-    <t>RMBS</t>
-  </si>
-  <si>
-    <t>EL</t>
-  </si>
-  <si>
-    <t>PHR</t>
-  </si>
-  <si>
-    <t>AIRT</t>
-  </si>
-  <si>
-    <t>VMI</t>
-  </si>
-  <si>
-    <t>AXTA</t>
-  </si>
-  <si>
-    <t>MANU</t>
-  </si>
-  <si>
-    <t>MYGN</t>
-  </si>
-  <si>
-    <t>LUV</t>
-  </si>
-  <si>
-    <t>EXPE</t>
-  </si>
-  <si>
-    <t>SAVE</t>
-  </si>
-  <si>
-    <t>FDMT</t>
-  </si>
-  <si>
-    <t>ALKS</t>
-  </si>
-  <si>
-    <t>TTGT</t>
-  </si>
-  <si>
-    <t>AKRO</t>
-  </si>
-  <si>
-    <t>GFL</t>
-  </si>
-  <si>
-    <t>ALK</t>
-  </si>
-  <si>
-    <t>DY</t>
-  </si>
-  <si>
-    <t>XOMA</t>
-  </si>
-  <si>
-    <t>RVNC</t>
-  </si>
-  <si>
-    <t>CCOI</t>
-  </si>
-  <si>
-    <t>DNLI</t>
-  </si>
-  <si>
-    <t>SAVA</t>
-  </si>
-  <si>
-    <t>NCLH</t>
-  </si>
-  <si>
-    <t>UHS</t>
-  </si>
-  <si>
-    <t>VCEL</t>
-  </si>
-  <si>
-    <t>CYTK</t>
-  </si>
-  <si>
-    <t>MNRO</t>
-  </si>
-  <si>
-    <t>TOST</t>
-  </si>
-  <si>
-    <t>PRLB</t>
-  </si>
-  <si>
-    <t>AMG</t>
-  </si>
-  <si>
-    <t>CSIQ</t>
-  </si>
-  <si>
-    <t>LFUS</t>
-  </si>
-  <si>
-    <t>XPOF</t>
-  </si>
-  <si>
-    <t>MTR</t>
-  </si>
-  <si>
-    <t>COHR</t>
-  </si>
-  <si>
-    <t>PAYC</t>
-  </si>
-  <si>
-    <t>CHDN</t>
-  </si>
-  <si>
-    <t>BIP</t>
-  </si>
-  <si>
-    <t>ARVN</t>
-  </si>
-  <si>
-    <t>BEP</t>
-  </si>
-  <si>
-    <t>CWH</t>
-  </si>
-  <si>
-    <t>TU</t>
-  </si>
-  <si>
-    <t>BRKR</t>
-  </si>
-  <si>
-    <t>CRSP</t>
-  </si>
-  <si>
-    <t>AMX</t>
-  </si>
-  <si>
-    <t>SANM</t>
-  </si>
-  <si>
-    <t>GFI</t>
-  </si>
-  <si>
-    <t>OLK</t>
-  </si>
-  <si>
-    <t>EDVMF</t>
-  </si>
-  <si>
-    <t>CROX</t>
-  </si>
-  <si>
-    <t>INSP</t>
-  </si>
-  <si>
-    <t>SLAB</t>
-  </si>
-  <si>
-    <t>ARW</t>
-  </si>
-  <si>
-    <t>SPOT</t>
-  </si>
-  <si>
-    <t>ORA</t>
-  </si>
-  <si>
-    <t>DAVA</t>
-  </si>
-  <si>
-    <t>CRTO</t>
-  </si>
-  <si>
-    <t>MTRN</t>
-  </si>
-  <si>
-    <t>TGLS</t>
-  </si>
-  <si>
-    <t>HXL</t>
-  </si>
-  <si>
-    <t>SRPT</t>
-  </si>
-  <si>
-    <t>IMOS</t>
-  </si>
-  <si>
-    <t>LW</t>
-  </si>
-  <si>
-    <t>JNPR</t>
-  </si>
-  <si>
-    <t>TYRA</t>
-  </si>
-  <si>
-    <t>RCUS</t>
-  </si>
-  <si>
-    <t>INSE</t>
-  </si>
-  <si>
-    <t>SHOP</t>
-  </si>
-  <si>
-    <t>WSC</t>
-  </si>
-  <si>
-    <t>SPSC</t>
-  </si>
-  <si>
-    <t>FMC</t>
-  </si>
-  <si>
-    <t>ESMT</t>
-  </si>
-  <si>
-    <t>DT</t>
-  </si>
-  <si>
-    <t>ENTA</t>
-  </si>
-  <si>
-    <t>BIPC</t>
-  </si>
-  <si>
-    <t>PMT</t>
-  </si>
-  <si>
-    <t>DGII</t>
-  </si>
-  <si>
-    <t>ANVS</t>
-  </si>
-  <si>
-    <t>TLK</t>
-  </si>
-  <si>
-    <t>MSGE</t>
-  </si>
-  <si>
-    <t>VALN</t>
-  </si>
-  <si>
-    <t>TRP</t>
-  </si>
-  <si>
-    <t>AVDL</t>
-  </si>
-  <si>
-    <t>ALGT</t>
-  </si>
-  <si>
-    <t>MIRM</t>
-  </si>
-  <si>
-    <t>SRCL</t>
-  </si>
-  <si>
-    <t>PLNT</t>
-  </si>
-  <si>
-    <t>EXPO</t>
-  </si>
-  <si>
-    <t>T</t>
-  </si>
-  <si>
-    <t>LGND</t>
-  </si>
-  <si>
-    <t>CGNX</t>
-  </si>
-  <si>
-    <t>HKHHF</t>
-  </si>
-  <si>
-    <t>EXLS</t>
-  </si>
-  <si>
-    <t>TSM</t>
-  </si>
-  <si>
-    <t>ATEX</t>
-  </si>
-  <si>
-    <t>IRT</t>
-  </si>
-  <si>
-    <t>SNN</t>
-  </si>
-  <si>
-    <t>CCRD</t>
-  </si>
-  <si>
-    <t>ANSS</t>
-  </si>
-  <si>
-    <t>NCSM</t>
-  </si>
-  <si>
-    <t>IDT</t>
-  </si>
-  <si>
-    <t>NEM</t>
-  </si>
-  <si>
-    <t>FSUMF</t>
-  </si>
-  <si>
-    <t>MSB</t>
-  </si>
-  <si>
-    <t>GTY</t>
-  </si>
-  <si>
-    <t>HRMY</t>
-  </si>
-  <si>
-    <t>ESTC</t>
-  </si>
-  <si>
-    <t>CCI</t>
-  </si>
-  <si>
-    <t>PEGA</t>
-  </si>
-  <si>
-    <t>JBT</t>
-  </si>
-  <si>
-    <t>EXAS</t>
-  </si>
-  <si>
-    <t>SNOW</t>
-  </si>
-  <si>
-    <t>SMLR</t>
-  </si>
-  <si>
-    <t>IDYA</t>
-  </si>
-  <si>
-    <t>ITCI</t>
-  </si>
-  <si>
-    <t>WEYS</t>
-  </si>
-  <si>
-    <t>ST</t>
-  </si>
-  <si>
-    <t>HI</t>
-  </si>
-  <si>
-    <t>GTLB</t>
-  </si>
-  <si>
-    <t>THC</t>
-  </si>
-  <si>
-    <t>DOX</t>
-  </si>
-  <si>
-    <t>AAL</t>
-  </si>
-  <si>
-    <t>LAC</t>
-  </si>
-  <si>
-    <t>PYPL</t>
-  </si>
-  <si>
-    <t>ARMK</t>
-  </si>
-  <si>
-    <t>SSYS</t>
-  </si>
-  <si>
-    <t>PNTG</t>
-  </si>
-  <si>
-    <t>BDC</t>
-  </si>
-  <si>
-    <t>ISRG</t>
-  </si>
-  <si>
-    <t>AMBA</t>
-  </si>
-  <si>
-    <t>BSIG</t>
-  </si>
-  <si>
-    <t>JCI</t>
-  </si>
-  <si>
-    <t>GGG</t>
-  </si>
-  <si>
-    <t>TKR</t>
-  </si>
-  <si>
-    <t>CLDX</t>
-  </si>
-  <si>
-    <t>FBTT</t>
-  </si>
-  <si>
-    <t>PGTI</t>
-  </si>
-  <si>
-    <t>ROK</t>
-  </si>
-  <si>
-    <t>SIX</t>
-  </si>
-  <si>
-    <t>CCSI</t>
-  </si>
-  <si>
-    <t>PODD</t>
-  </si>
-  <si>
-    <t>ERII</t>
-  </si>
-  <si>
-    <t>KD</t>
-  </si>
-  <si>
-    <t>QEPC</t>
-  </si>
-  <si>
-    <t>GLOB</t>
-  </si>
-  <si>
-    <t>HQI</t>
-  </si>
-  <si>
-    <t>PRAA</t>
-  </si>
-  <si>
-    <t>LMND</t>
-  </si>
-  <si>
-    <t>SYK</t>
-  </si>
-  <si>
-    <t>AAUKF</t>
-  </si>
-  <si>
-    <t>UFCS</t>
-  </si>
-  <si>
-    <t>MMS</t>
-  </si>
-  <si>
-    <t>JBSS</t>
-  </si>
-  <si>
-    <t>LPX</t>
-  </si>
-  <si>
-    <t>IFNNY</t>
-  </si>
-  <si>
-    <t>DXCM</t>
-  </si>
-  <si>
-    <t>HUBS</t>
-  </si>
-  <si>
-    <t>GGAL</t>
-  </si>
-  <si>
-    <t>TARO</t>
-  </si>
-  <si>
-    <t>BLBD</t>
-  </si>
-  <si>
-    <t>SQM</t>
-  </si>
-  <si>
-    <t>FWONB</t>
-  </si>
-  <si>
-    <t>BCE</t>
-  </si>
-  <si>
-    <t>DCPH</t>
-  </si>
-  <si>
-    <t>KN</t>
-  </si>
-  <si>
-    <t>ALLE</t>
-  </si>
-  <si>
-    <t>VNT</t>
-  </si>
-  <si>
-    <t>DUOL</t>
-  </si>
-  <si>
-    <t>ARWR</t>
-  </si>
-  <si>
-    <t>QTRX</t>
-  </si>
-  <si>
-    <t>AGR</t>
-  </si>
-  <si>
-    <t>ICUI</t>
-  </si>
-  <si>
-    <t>HASI</t>
-  </si>
-  <si>
-    <t>NTCT</t>
-  </si>
-  <si>
-    <t>BCYC</t>
-  </si>
-  <si>
-    <t>NEO</t>
-  </si>
-  <si>
-    <t>WFG</t>
-  </si>
-  <si>
-    <t>CCD</t>
-  </si>
-  <si>
-    <t>PATH</t>
-  </si>
-  <si>
-    <t>FSUGY</t>
-  </si>
-  <si>
-    <t>MP</t>
-  </si>
-  <si>
-    <t>HSY</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>KAR</t>
-  </si>
-  <si>
-    <t>PFE</t>
-  </si>
-  <si>
-    <t>SWTX</t>
-  </si>
-  <si>
-    <t>CSGP</t>
-  </si>
-  <si>
-    <t>FN</t>
-  </si>
-  <si>
-    <t>WHR</t>
-  </si>
-  <si>
-    <t>SGML</t>
-  </si>
-  <si>
-    <t>PAM</t>
-  </si>
-  <si>
-    <t>BXC</t>
-  </si>
-  <si>
-    <t>KAMN</t>
-  </si>
-  <si>
-    <t>WIRE</t>
-  </si>
-  <si>
-    <t>HON</t>
-  </si>
-  <si>
-    <t>CMG</t>
-  </si>
-  <si>
-    <t>IDCC</t>
-  </si>
-  <si>
-    <t>MLI</t>
-  </si>
-  <si>
-    <t>RYAAY</t>
-  </si>
-  <si>
-    <t>NGG</t>
-  </si>
-  <si>
-    <t>HCA</t>
-  </si>
-  <si>
-    <t>TREE</t>
-  </si>
-  <si>
-    <t>SIM</t>
-  </si>
-  <si>
-    <t>MEI</t>
-  </si>
-  <si>
-    <t>TWNK</t>
-  </si>
-  <si>
-    <t>TWLO</t>
-  </si>
-  <si>
-    <t>SLGN</t>
-  </si>
-  <si>
-    <t>UGI</t>
-  </si>
-  <si>
-    <t>FMAO</t>
-  </si>
-  <si>
-    <t>CPK</t>
-  </si>
-  <si>
-    <t>UVE</t>
-  </si>
-  <si>
-    <t>TDY</t>
-  </si>
-  <si>
-    <t>LAMR</t>
-  </si>
-  <si>
-    <t>FTS</t>
-  </si>
-  <si>
-    <t>MODN</t>
-  </si>
-  <si>
-    <t>UDR</t>
-  </si>
-  <si>
-    <t>NLCP</t>
-  </si>
-  <si>
-    <t>VCYT</t>
-  </si>
-  <si>
-    <t>FHI</t>
-  </si>
-  <si>
-    <t>VZ</t>
-  </si>
-  <si>
-    <t>CNNE</t>
-  </si>
-  <si>
-    <t>WSBF</t>
-  </si>
-  <si>
-    <t>CWST</t>
-  </si>
-  <si>
-    <t>ACDVF</t>
-  </si>
-  <si>
-    <t>GT</t>
-  </si>
-  <si>
-    <t>QNTO</t>
-  </si>
-  <si>
-    <t>ZNTL</t>
-  </si>
-  <si>
-    <t>GFS</t>
-  </si>
-  <si>
-    <t>ULTA</t>
-  </si>
-  <si>
-    <t>FMBL</t>
-  </si>
-  <si>
-    <t>CXM</t>
-  </si>
-  <si>
-    <t>AVNW</t>
-  </si>
-  <si>
-    <t>BIIB</t>
-  </si>
-  <si>
-    <t>CNXC</t>
-  </si>
-  <si>
-    <t>BLMN</t>
-  </si>
-  <si>
-    <t>BMA</t>
-  </si>
-  <si>
-    <t>MAA</t>
-  </si>
-  <si>
-    <t>NNN</t>
-  </si>
-  <si>
-    <t>ARTNA</t>
-  </si>
-  <si>
-    <t>AVT</t>
-  </si>
-  <si>
-    <t>TRDA</t>
-  </si>
-  <si>
-    <t>NODK</t>
-  </si>
-  <si>
-    <t>HUBB</t>
-  </si>
-  <si>
-    <t>RDIB</t>
-  </si>
-  <si>
-    <t>EPR</t>
-  </si>
-  <si>
-    <t>ACVA</t>
-  </si>
-  <si>
-    <t>STER</t>
-  </si>
-  <si>
-    <t>HAIN</t>
-  </si>
-  <si>
-    <t>CARG</t>
-  </si>
-  <si>
-    <t>ASAN</t>
-  </si>
-  <si>
-    <t>NJR</t>
-  </si>
-  <si>
-    <t>ILMN</t>
-  </si>
-  <si>
-    <t>MTN</t>
-  </si>
-  <si>
-    <t>WNC</t>
-  </si>
-  <si>
-    <t>AVNS</t>
-  </si>
-  <si>
-    <t>ASR</t>
-  </si>
-  <si>
-    <t>SAFE</t>
-  </si>
-  <si>
-    <t>GPK</t>
-  </si>
-  <si>
-    <t>UI</t>
-  </si>
-  <si>
-    <t>ALNY</t>
-  </si>
-  <si>
-    <t>ASML</t>
-  </si>
-  <si>
-    <t>PUK</t>
-  </si>
-  <si>
-    <t>XNCR</t>
-  </si>
-  <si>
-    <t>APPN</t>
-  </si>
-  <si>
-    <t>FELE</t>
-  </si>
-  <si>
-    <t>NGLOY</t>
-  </si>
-  <si>
-    <t>AI</t>
-  </si>
-  <si>
-    <t>GRBK</t>
-  </si>
-  <si>
-    <t>NWE</t>
-  </si>
-  <si>
-    <t>IONS</t>
-  </si>
-  <si>
-    <t>MYE</t>
-  </si>
-  <si>
-    <t>G</t>
-  </si>
-  <si>
-    <t>SSNC</t>
-  </si>
-  <si>
-    <t>ITOS</t>
-  </si>
-  <si>
-    <t>VRNA</t>
-  </si>
-  <si>
-    <t>EXR</t>
-  </si>
-  <si>
-    <t>FE</t>
-  </si>
-  <si>
-    <t>XENE</t>
-  </si>
-  <si>
-    <t>NOBH</t>
-  </si>
-  <si>
-    <t>AXSM</t>
-  </si>
-  <si>
-    <t>AIRC</t>
-  </si>
-  <si>
-    <t>OR</t>
-  </si>
-  <si>
-    <t>FBRT</t>
-  </si>
-  <si>
-    <t>TRIP</t>
-  </si>
-  <si>
-    <t>CHT</t>
-  </si>
-  <si>
-    <t>KBR</t>
-  </si>
-  <si>
-    <t>TNL</t>
-  </si>
-  <si>
-    <t>NEE</t>
-  </si>
-  <si>
-    <t>FLMMF</t>
-  </si>
-  <si>
-    <t>GPC</t>
-  </si>
-  <si>
-    <t>HOLX</t>
-  </si>
-  <si>
-    <t>AXR</t>
-  </si>
-  <si>
-    <t>MNDY</t>
-  </si>
-  <si>
-    <t>LHX</t>
-  </si>
-  <si>
-    <t>MVO</t>
-  </si>
-  <si>
-    <t>BMBL</t>
-  </si>
-  <si>
-    <t>FCN</t>
-  </si>
-  <si>
-    <t>ABG</t>
-  </si>
-  <si>
-    <t>HEINY</t>
-  </si>
-  <si>
-    <t>EA</t>
-  </si>
-  <si>
-    <t>TYL</t>
-  </si>
-  <si>
-    <t>VERV</t>
-  </si>
-  <si>
-    <t>EQC</t>
-  </si>
-  <si>
-    <t>UGIC</t>
-  </si>
-  <si>
-    <t>RCI</t>
-  </si>
-  <si>
-    <t>GH</t>
-  </si>
-  <si>
-    <t>ALTR</t>
-  </si>
-  <si>
-    <t>SMLP</t>
-  </si>
-  <si>
-    <t>CIEN</t>
-  </si>
-  <si>
-    <t>ADSK</t>
-  </si>
-  <si>
-    <t>CLFD</t>
-  </si>
-  <si>
-    <t>MCFT</t>
-  </si>
-  <si>
-    <t>MKTX</t>
-  </si>
-  <si>
-    <t>SENEB</t>
-  </si>
-  <si>
-    <t>HKHHY</t>
-  </si>
-  <si>
-    <t>HY</t>
-  </si>
-  <si>
-    <t>TCI</t>
-  </si>
-  <si>
-    <t>TSLA</t>
-  </si>
-  <si>
-    <t>KMB</t>
-  </si>
-  <si>
-    <t>AGI</t>
-  </si>
-  <si>
-    <t>SNCY</t>
-  </si>
-  <si>
-    <t>HTH</t>
-  </si>
-  <si>
-    <t>HSON</t>
-  </si>
-  <si>
-    <t>YPF</t>
-  </si>
-  <si>
-    <t>KOF</t>
-  </si>
-  <si>
-    <t>LZRFY</t>
-  </si>
-  <si>
-    <t>GIL</t>
-  </si>
-  <si>
-    <t>DIS</t>
-  </si>
-  <si>
-    <t>QDEL</t>
-  </si>
-  <si>
-    <t>TPH</t>
-  </si>
-  <si>
-    <t>ATLC</t>
-  </si>
-  <si>
-    <t>OFIX</t>
-  </si>
-  <si>
-    <t>VEEV</t>
-  </si>
-  <si>
-    <t>UTL</t>
-  </si>
-  <si>
-    <t>AGIO</t>
-  </si>
-  <si>
-    <t>GM</t>
-  </si>
-  <si>
-    <t>AVTE</t>
-  </si>
-  <si>
-    <t>VRSN</t>
-  </si>
-  <si>
-    <t>MHGU</t>
-  </si>
-  <si>
-    <t>GOOS</t>
-  </si>
-  <si>
-    <t>SLM</t>
-  </si>
-  <si>
-    <t>ES</t>
-  </si>
-  <si>
-    <t>TH</t>
-  </si>
-  <si>
-    <t>COCO</t>
-  </si>
-  <si>
-    <t>CUBE</t>
-  </si>
-  <si>
-    <t>SWKH</t>
-  </si>
-  <si>
-    <t>SBAC</t>
-  </si>
-  <si>
-    <t>GLW</t>
-  </si>
-  <si>
-    <t>AMLX</t>
-  </si>
-  <si>
-    <t>BWA</t>
-  </si>
-  <si>
-    <t>DSGX</t>
-  </si>
-  <si>
-    <t>KRP</t>
-  </si>
-  <si>
-    <t>YORW</t>
-  </si>
-  <si>
-    <t>HGV</t>
-  </si>
-  <si>
-    <t>GIB</t>
-  </si>
-  <si>
-    <t>CACC</t>
-  </si>
-  <si>
-    <t>NSIT</t>
-  </si>
-  <si>
-    <t>MNAT</t>
-  </si>
-  <si>
-    <t>AMN</t>
-  </si>
-  <si>
-    <t>LYV</t>
-  </si>
-  <si>
-    <t>NUVA</t>
-  </si>
-  <si>
-    <t>CMCO</t>
-  </si>
-  <si>
-    <t>JHG</t>
-  </si>
-  <si>
-    <t>CASS</t>
-  </si>
-  <si>
-    <t>SBS</t>
-  </si>
-  <si>
-    <t>MTW</t>
-  </si>
-  <si>
-    <t>AON</t>
-  </si>
-  <si>
-    <t>ISBA</t>
-  </si>
-  <si>
-    <t>AEP</t>
-  </si>
-  <si>
-    <t>AEM</t>
-  </si>
-  <si>
-    <t>IBEX</t>
-  </si>
-  <si>
-    <t>BMY</t>
-  </si>
-  <si>
-    <t>KMT</t>
-  </si>
-  <si>
-    <t>PNW</t>
-  </si>
-  <si>
-    <t>BSX</t>
-  </si>
-  <si>
-    <t>IVZ</t>
-  </si>
-  <si>
-    <t>ROG</t>
-  </si>
-  <si>
-    <t>TROX</t>
-  </si>
-  <si>
-    <t>MKSI</t>
-  </si>
-  <si>
-    <t>TARS</t>
-  </si>
-  <si>
-    <t>TRS</t>
-  </si>
-  <si>
-    <t>CPT</t>
-  </si>
-  <si>
-    <t>EBAY</t>
-  </si>
-  <si>
-    <t>SAP</t>
-  </si>
-  <si>
-    <t>PPG</t>
-  </si>
-  <si>
-    <t>OLP</t>
-  </si>
-  <si>
-    <t>OPY</t>
-  </si>
-  <si>
-    <t>ENTG</t>
-  </si>
-  <si>
-    <t>SR</t>
-  </si>
-  <si>
-    <t>TAK</t>
-  </si>
-  <si>
-    <t>BBN</t>
-  </si>
-  <si>
-    <t>PENN</t>
-  </si>
-  <si>
-    <t>NC</t>
-  </si>
-  <si>
-    <t>ALOT</t>
-  </si>
-  <si>
-    <t>TSEM</t>
-  </si>
-  <si>
-    <t>SITE</t>
-  </si>
-  <si>
-    <t>ATUSF</t>
-  </si>
-  <si>
-    <t>MDT</t>
-  </si>
-  <si>
-    <t>IT</t>
-  </si>
-  <si>
-    <t>QSR</t>
-  </si>
-  <si>
-    <t>RICK</t>
-  </si>
-  <si>
-    <t>BKH</t>
-  </si>
-  <si>
-    <t>RGLD</t>
-  </si>
-  <si>
-    <t>JRVR</t>
-  </si>
-  <si>
-    <t>GATX</t>
-  </si>
-  <si>
-    <t>CRL</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>AVA</t>
-  </si>
-  <si>
-    <t>TFX</t>
-  </si>
-  <si>
-    <t>HSTM</t>
-  </si>
-  <si>
-    <t>FR</t>
-  </si>
-  <si>
-    <t>KEYS</t>
-  </si>
-  <si>
-    <t>AVB</t>
-  </si>
-  <si>
-    <t>GIS</t>
-  </si>
-  <si>
-    <t>THRY</t>
-  </si>
-  <si>
-    <t>MGIC</t>
-  </si>
-  <si>
-    <t>GWW</t>
-  </si>
-  <si>
-    <t>NSA</t>
-  </si>
-  <si>
-    <t>MPX</t>
-  </si>
-  <si>
-    <t>SSL</t>
-  </si>
-  <si>
-    <t>ANAB</t>
-  </si>
-  <si>
-    <t>ROL</t>
-  </si>
-  <si>
-    <t>DFH</t>
+    <t>MKL</t>
+  </si>
+  <si>
+    <t>ICLR</t>
+  </si>
+  <si>
+    <t>CIR</t>
+  </si>
+  <si>
+    <t>HAYW</t>
   </si>
   <si>
     <t>OZ</t>
   </si>
   <si>
-    <t>TIGO</t>
-  </si>
-  <si>
-    <t>FSS</t>
-  </si>
-  <si>
-    <t>SONY</t>
-  </si>
-  <si>
-    <t>BBU</t>
-  </si>
-  <si>
-    <t>KRNT</t>
-  </si>
-  <si>
-    <t>PRTC</t>
-  </si>
-  <si>
-    <t>CRNX</t>
-  </si>
-  <si>
-    <t>TR</t>
-  </si>
-  <si>
-    <t>MBUU</t>
-  </si>
-  <si>
-    <t>CHE</t>
-  </si>
-  <si>
-    <t>ARL</t>
-  </si>
-  <si>
-    <t>RHP</t>
-  </si>
-  <si>
-    <t>SPGI</t>
-  </si>
-  <si>
-    <t>IOT</t>
-  </si>
-  <si>
-    <t>BRT</t>
-  </si>
-  <si>
-    <t>TTEC</t>
-  </si>
-  <si>
-    <t>BE</t>
-  </si>
-  <si>
-    <t>VSH</t>
+    <t>CVE</t>
+  </si>
+  <si>
+    <t>USLM</t>
+  </si>
+  <si>
+    <t>ESE</t>
+  </si>
+  <si>
+    <t>INTU</t>
+  </si>
+  <si>
+    <t>ASGN</t>
+  </si>
+  <si>
+    <t>LYB</t>
+  </si>
+  <si>
+    <t>MTG</t>
+  </si>
+  <si>
+    <t>IMAX</t>
+  </si>
+  <si>
+    <t>WLK</t>
+  </si>
+  <si>
+    <t>DLX</t>
+  </si>
+  <si>
+    <t>RYAN</t>
+  </si>
+  <si>
+    <t>WMB</t>
+  </si>
+  <si>
+    <t>MSA</t>
+  </si>
+  <si>
+    <t>CWAN</t>
+  </si>
+  <si>
+    <t>EMR</t>
+  </si>
+  <si>
+    <t>FXNC</t>
+  </si>
+  <si>
+    <t>MEDP</t>
+  </si>
+  <si>
+    <t>NDAQ</t>
+  </si>
+  <si>
+    <t>CPNG</t>
+  </si>
+  <si>
+    <t>KEX</t>
+  </si>
+  <si>
+    <t>SBSI</t>
+  </si>
+  <si>
+    <t>COKE</t>
+  </si>
+  <si>
+    <t>TWI</t>
+  </si>
+  <si>
+    <t>PHG</t>
+  </si>
+  <si>
+    <t>RBB</t>
+  </si>
+  <si>
+    <t>ALKT</t>
+  </si>
+  <si>
+    <t>MRCY</t>
+  </si>
+  <si>
+    <t>DJCO</t>
+  </si>
+  <si>
+    <t>ZTS</t>
+  </si>
+  <si>
+    <t>BGR</t>
+  </si>
+  <si>
+    <t>FUTU</t>
+  </si>
+  <si>
+    <t>MRO</t>
+  </si>
+  <si>
+    <t>NMIH</t>
+  </si>
+  <si>
+    <t>POST</t>
+  </si>
+  <si>
+    <t>ABR</t>
+  </si>
+  <si>
+    <t>GOLF</t>
+  </si>
+  <si>
+    <t>HFBL</t>
+  </si>
+  <si>
+    <t>RCMT</t>
+  </si>
+  <si>
+    <t>AFT</t>
+  </si>
+  <si>
+    <t>RWCB</t>
+  </si>
+  <si>
+    <t>MATX</t>
+  </si>
+  <si>
+    <t>MBNKP</t>
+  </si>
+  <si>
+    <t>MORN</t>
+  </si>
+  <si>
+    <t>IRM</t>
+  </si>
+  <si>
+    <t>IBM</t>
+  </si>
+  <si>
+    <t>PAAS</t>
+  </si>
+  <si>
+    <t>VBFC</t>
+  </si>
+  <si>
+    <t>MMP</t>
+  </si>
+  <si>
+    <t>UNP</t>
+  </si>
+  <si>
+    <t>PBR</t>
   </si>
 </sst>
 </file>
@@ -2110,7 +2107,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B581"/>
+  <dimension ref="A1:B580"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -2126,7 +2123,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1">
-        <v>36.44613518155683</v>
+        <v>255.4372032446254</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2134,7 +2131,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1">
-        <v>34.65366820381705</v>
+        <v>232.4896500897095</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -2142,7 +2139,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1">
-        <v>34.53594956320657</v>
+        <v>232.3910325827611</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -2150,7 +2147,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="1">
-        <v>34.40191926610895</v>
+        <v>226.3082618298068</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -2158,7 +2155,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="1">
-        <v>34.22697703780153</v>
+        <v>224.5077213802019</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -2166,7 +2163,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="1">
-        <v>34.20083531614338</v>
+        <v>213.7220272426785</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -2174,7 +2171,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="1">
-        <v>34.19444631520608</v>
+        <v>211.1201615895684</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -2182,7 +2179,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="1">
-        <v>34.19302837326239</v>
+        <v>202.6105737137543</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -2190,7 +2187,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="1">
-        <v>34.18349713479175</v>
+        <v>147.165390851998</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -2198,7 +2195,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="1">
-        <v>34.17526705785681</v>
+        <v>147.1153539266195</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -2206,7 +2203,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="1">
-        <v>34.16357773169764</v>
+        <v>144.2753746360162</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -2214,7 +2211,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="1">
-        <v>34.15854572420383</v>
+        <v>143.0865258569359</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -2222,7 +2219,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="1">
-        <v>34.15395625090404</v>
+        <v>142.1745394788033</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -2230,7 +2227,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="1">
-        <v>34.1532215967606</v>
+        <v>141.1562140807508</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -2238,7 +2235,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="1">
-        <v>34.14777388895773</v>
+        <v>138.4981942286498</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -2246,7 +2243,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="1">
-        <v>34.13748943874684</v>
+        <v>138.1921725621646</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -2254,7 +2251,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="1">
-        <v>34.09276107938651</v>
+        <v>138.0232238069118</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -2262,7 +2259,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="1">
-        <v>34.09204805524081</v>
+        <v>136.4092185411029</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -2270,7 +2267,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="1">
-        <v>34.03726263558264</v>
+        <v>135.4455427563442</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -2278,7 +2275,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="1">
-        <v>34.02600209163256</v>
+        <v>132.6537522564329</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -2286,7 +2283,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="1">
-        <v>34.01592244372451</v>
+        <v>132.548235908364</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -2294,7 +2291,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="1">
-        <v>34.00782856685324</v>
+        <v>132.1817001546993</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -2302,7 +2299,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="1">
-        <v>34.00612922333337</v>
+        <v>131.9854412950382</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -2310,7 +2307,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="1">
-        <v>34.00408546130149</v>
+        <v>131.0192561741487</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -2318,7 +2315,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="1">
-        <v>33.99325229098142</v>
+        <v>129.5433546121298</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -2326,7 +2323,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="1">
-        <v>33.98291775587756</v>
+        <v>129.4456489327364</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -2334,7 +2331,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="1">
-        <v>33.96387337211537</v>
+        <v>129.1620129457897</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -2342,7 +2339,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="1">
-        <v>33.9471158304777</v>
+        <v>129.141139817589</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -2350,7 +2347,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="1">
-        <v>33.93792880867697</v>
+        <v>129.0874166038521</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -2358,7 +2355,7 @@
         <v>31</v>
       </c>
       <c r="B31" s="1">
-        <v>33.92111273863861</v>
+        <v>128.8815036092661</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -2366,7 +2363,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="1">
-        <v>33.90831272690734</v>
+        <v>128.4327115465275</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -2374,7 +2371,7 @@
         <v>33</v>
       </c>
       <c r="B33" s="1">
-        <v>33.89113197543339</v>
+        <v>128.0723165624481</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -2382,7 +2379,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="1">
-        <v>33.87726089505646</v>
+        <v>127.8963435051743</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -2390,7 +2387,7 @@
         <v>35</v>
       </c>
       <c r="B35" s="1">
-        <v>33.87713448841662</v>
+        <v>127.5129674502357</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -2398,7 +2395,7 @@
         <v>36</v>
       </c>
       <c r="B36" s="1">
-        <v>33.87007743688464</v>
+        <v>127.4026456394295</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -2406,7 +2403,7 @@
         <v>37</v>
       </c>
       <c r="B37" s="1">
-        <v>33.85835352697505</v>
+        <v>126.9752163851319</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -2414,7 +2411,7 @@
         <v>38</v>
       </c>
       <c r="B38" s="1">
-        <v>33.85582121681148</v>
+        <v>126.7620063771785</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -2422,7 +2419,7 @@
         <v>39</v>
       </c>
       <c r="B39" s="1">
-        <v>33.85127117727878</v>
+        <v>126.7493286985751</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -2430,7 +2427,7 @@
         <v>40</v>
       </c>
       <c r="B40" s="1">
-        <v>33.85044099866683</v>
+        <v>126.3810078765538</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2438,7 +2435,7 @@
         <v>41</v>
       </c>
       <c r="B41" s="1">
-        <v>33.84102682593059</v>
+        <v>126.3638131611164</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2446,7 +2443,7 @@
         <v>42</v>
       </c>
       <c r="B42" s="1">
-        <v>33.83282961401182</v>
+        <v>126.011879087461</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2454,7 +2451,7 @@
         <v>43</v>
       </c>
       <c r="B43" s="1">
-        <v>33.82715692467102</v>
+        <v>125.8295255371107</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2462,7 +2459,7 @@
         <v>44</v>
       </c>
       <c r="B44" s="1">
-        <v>33.81193301855625</v>
+        <v>125.5661066265212</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2470,7 +2467,7 @@
         <v>45</v>
       </c>
       <c r="B45" s="1">
-        <v>33.80708485304547</v>
+        <v>125.5339484033279</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2478,7 +2475,7 @@
         <v>46</v>
       </c>
       <c r="B46" s="1">
-        <v>33.78926133197449</v>
+        <v>125.1492600262316</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2486,7 +2483,7 @@
         <v>47</v>
       </c>
       <c r="B47" s="1">
-        <v>33.78664749819835</v>
+        <v>125.1311198986199</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2494,7 +2491,7 @@
         <v>48</v>
       </c>
       <c r="B48" s="1">
-        <v>33.78531336965244</v>
+        <v>125.0684651811989</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -2502,7 +2499,7 @@
         <v>49</v>
       </c>
       <c r="B49" s="1">
-        <v>33.78464525191141</v>
+        <v>124.6544005897391</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -2510,7 +2507,7 @@
         <v>50</v>
       </c>
       <c r="B50" s="1">
-        <v>33.77527199223735</v>
+        <v>124.2670048723938</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -2518,7 +2515,7 @@
         <v>51</v>
       </c>
       <c r="B51" s="1">
-        <v>33.76596044811614</v>
+        <v>124.044294945157</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -2526,7 +2523,7 @@
         <v>52</v>
       </c>
       <c r="B52" s="1">
-        <v>33.7629498880229</v>
+        <v>123.6942698124326</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -2534,7 +2531,7 @@
         <v>53</v>
       </c>
       <c r="B53" s="1">
-        <v>33.76136885662964</v>
+        <v>123.5120576911184</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -2542,7 +2539,7 @@
         <v>54</v>
       </c>
       <c r="B54" s="1">
-        <v>33.75603913622456</v>
+        <v>123.305205781116</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -2550,7 +2547,7 @@
         <v>55</v>
       </c>
       <c r="B55" s="1">
-        <v>33.75384644721159</v>
+        <v>122.9398176389222</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -2558,7 +2555,7 @@
         <v>56</v>
       </c>
       <c r="B56" s="1">
-        <v>33.75328143133117</v>
+        <v>122.9006133177667</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -2566,7 +2563,7 @@
         <v>57</v>
       </c>
       <c r="B57" s="1">
-        <v>33.74944051251085</v>
+        <v>122.8163278130604</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -2574,7 +2571,7 @@
         <v>58</v>
       </c>
       <c r="B58" s="1">
-        <v>33.74662692684737</v>
+        <v>122.7564711903479</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -2582,7 +2579,7 @@
         <v>59</v>
       </c>
       <c r="B59" s="1">
-        <v>33.74415975580974</v>
+        <v>122.6336917575704</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -2590,7 +2587,7 @@
         <v>60</v>
       </c>
       <c r="B60" s="1">
-        <v>33.74099758660204</v>
+        <v>122.4942653908328</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -2598,7 +2595,7 @@
         <v>61</v>
       </c>
       <c r="B61" s="1">
-        <v>33.74030888701294</v>
+        <v>122.4906672805949</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -2606,7 +2603,7 @@
         <v>62</v>
       </c>
       <c r="B62" s="1">
-        <v>33.73849459639311</v>
+        <v>122.4393207762098</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -2614,7 +2611,7 @@
         <v>63</v>
       </c>
       <c r="B63" s="1">
-        <v>33.73531844084999</v>
+        <v>122.3481417194698</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -2622,7 +2619,7 @@
         <v>64</v>
       </c>
       <c r="B64" s="1">
-        <v>33.73504928801169</v>
+        <v>121.8718733020944</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -2630,7 +2627,7 @@
         <v>65</v>
       </c>
       <c r="B65" s="1">
-        <v>33.73348217555029</v>
+        <v>121.8230558423345</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -2638,7 +2635,7 @@
         <v>66</v>
       </c>
       <c r="B66" s="1">
-        <v>33.73160629297406</v>
+        <v>121.7609192433521</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -2646,7 +2643,7 @@
         <v>67</v>
       </c>
       <c r="B67" s="1">
-        <v>33.7285658879643</v>
+        <v>121.7327628950884</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -2654,7 +2651,7 @@
         <v>68</v>
       </c>
       <c r="B68" s="1">
-        <v>33.72570464002096</v>
+        <v>121.5419348678818</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -2662,7 +2659,7 @@
         <v>69</v>
       </c>
       <c r="B69" s="1">
-        <v>33.7196564180519</v>
+        <v>121.2808306037658</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -2670,7 +2667,7 @@
         <v>70</v>
       </c>
       <c r="B70" s="1">
-        <v>33.71884419243967</v>
+        <v>121.0610917081422</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -2678,7 +2675,7 @@
         <v>71</v>
       </c>
       <c r="B71" s="1">
-        <v>33.71281320532133</v>
+        <v>120.7597462922815</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -2686,7 +2683,7 @@
         <v>72</v>
       </c>
       <c r="B72" s="1">
-        <v>33.71106498428377</v>
+        <v>120.552630287258</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2694,7 +2691,7 @@
         <v>73</v>
       </c>
       <c r="B73" s="1">
-        <v>33.7072516195818</v>
+        <v>120.3114074927041</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -2702,7 +2699,7 @@
         <v>74</v>
       </c>
       <c r="B74" s="1">
-        <v>33.70700363594543</v>
+        <v>120.2356704812904</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -2710,7 +2707,7 @@
         <v>75</v>
       </c>
       <c r="B75" s="1">
-        <v>33.70654984594174</v>
+        <v>119.5815394660856</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -2718,7 +2715,7 @@
         <v>76</v>
       </c>
       <c r="B76" s="1">
-        <v>33.70485298471279</v>
+        <v>119.285866093714</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -2726,7 +2723,7 @@
         <v>77</v>
       </c>
       <c r="B77" s="1">
-        <v>33.70454859471369</v>
+        <v>119.2306700745033</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -2734,7 +2731,7 @@
         <v>78</v>
       </c>
       <c r="B78" s="1">
-        <v>33.70217961706629</v>
+        <v>119.2062053629531</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -2742,7 +2739,7 @@
         <v>79</v>
       </c>
       <c r="B79" s="1">
-        <v>33.69700546006359</v>
+        <v>118.8218259408394</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -2750,7 +2747,7 @@
         <v>80</v>
       </c>
       <c r="B80" s="1">
-        <v>33.69002627256219</v>
+        <v>118.7689401328494</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -2758,7 +2755,7 @@
         <v>81</v>
       </c>
       <c r="B81" s="1">
-        <v>33.68982649196746</v>
+        <v>118.0729584666918</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -2766,7 +2763,7 @@
         <v>82</v>
       </c>
       <c r="B82" s="1">
-        <v>33.68214219295197</v>
+        <v>117.9723674874725</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -2774,7 +2771,7 @@
         <v>83</v>
       </c>
       <c r="B83" s="1">
-        <v>33.68202660444511</v>
+        <v>117.7905544865506</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -2782,7 +2779,7 @@
         <v>84</v>
       </c>
       <c r="B84" s="1">
-        <v>33.67782978760407</v>
+        <v>117.3903407418821</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -2790,7 +2787,7 @@
         <v>85</v>
       </c>
       <c r="B85" s="1">
-        <v>33.67528878159981</v>
+        <v>117.3584182606637</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -2798,7 +2795,7 @@
         <v>86</v>
       </c>
       <c r="B86" s="1">
-        <v>33.67445641304788</v>
+        <v>117.3279755064616</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -2806,7 +2803,7 @@
         <v>87</v>
       </c>
       <c r="B87" s="1">
-        <v>33.67358478818616</v>
+        <v>117.3253261454229</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -2814,7 +2811,7 @@
         <v>88</v>
       </c>
       <c r="B88" s="1">
-        <v>33.67344169813305</v>
+        <v>117.2150530209044</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -2822,7 +2819,7 @@
         <v>89</v>
       </c>
       <c r="B89" s="1">
-        <v>33.66647855099281</v>
+        <v>117.0924984280799</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -2830,7 +2827,7 @@
         <v>90</v>
       </c>
       <c r="B90" s="1">
-        <v>33.66638374201854</v>
+        <v>116.9722664971391</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -2838,7 +2835,7 @@
         <v>91</v>
       </c>
       <c r="B91" s="1">
-        <v>33.66608650825937</v>
+        <v>116.9355305410038</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -2846,7 +2843,7 @@
         <v>92</v>
       </c>
       <c r="B92" s="1">
-        <v>33.66503002228749</v>
+        <v>116.910858301572</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -2854,7 +2851,7 @@
         <v>93</v>
       </c>
       <c r="B93" s="1">
-        <v>33.66463012932737</v>
+        <v>116.8847486666178</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -2862,7 +2859,7 @@
         <v>94</v>
       </c>
       <c r="B94" s="1">
-        <v>33.6645295984429</v>
+        <v>116.8767327531502</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -2870,7 +2867,7 @@
         <v>95</v>
       </c>
       <c r="B95" s="1">
-        <v>33.66404599456532</v>
+        <v>116.8640953915592</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -2878,7 +2875,7 @@
         <v>96</v>
       </c>
       <c r="B96" s="1">
-        <v>33.66339579898486</v>
+        <v>116.6077253944437</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -2886,7 +2883,7 @@
         <v>97</v>
       </c>
       <c r="B97" s="1">
-        <v>33.66285634824642</v>
+        <v>116.5655827549685</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -2894,7 +2891,7 @@
         <v>98</v>
       </c>
       <c r="B98" s="1">
-        <v>33.66261583929639</v>
+        <v>116.5486099173818</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -2902,7 +2899,7 @@
         <v>99</v>
       </c>
       <c r="B99" s="1">
-        <v>33.66254964891767</v>
+        <v>116.4558732807591</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -2910,7 +2907,7 @@
         <v>100</v>
       </c>
       <c r="B100" s="1">
-        <v>33.66245281501764</v>
+        <v>116.4343472947386</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -2918,7 +2915,7 @@
         <v>101</v>
       </c>
       <c r="B101" s="1">
-        <v>33.66113563766851</v>
+        <v>116.3425188466369</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -2926,7 +2923,7 @@
         <v>102</v>
       </c>
       <c r="B102" s="1">
-        <v>33.661086439395</v>
+        <v>116.2467158021782</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -2934,7 +2931,7 @@
         <v>103</v>
       </c>
       <c r="B103" s="1">
-        <v>33.65933597533992</v>
+        <v>116.1785984254573</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -2942,7 +2939,7 @@
         <v>104</v>
       </c>
       <c r="B104" s="1">
-        <v>33.6586381217352</v>
+        <v>116.1655759558836</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -2950,7 +2947,7 @@
         <v>105</v>
       </c>
       <c r="B105" s="1">
-        <v>33.65656721148788</v>
+        <v>116.1551532574323</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -2958,7 +2955,7 @@
         <v>106</v>
       </c>
       <c r="B106" s="1">
-        <v>33.65585142315204</v>
+        <v>116.0901735353001</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -2966,7 +2963,7 @@
         <v>107</v>
       </c>
       <c r="B107" s="1">
-        <v>33.65320363990656</v>
+        <v>115.6351988252011</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -2974,7 +2971,7 @@
         <v>108</v>
       </c>
       <c r="B108" s="1">
-        <v>33.64996524387514</v>
+        <v>115.6060182563145</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -2982,7 +2979,7 @@
         <v>109</v>
       </c>
       <c r="B109" s="1">
-        <v>33.64864366849973</v>
+        <v>115.576054729594</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -2990,7 +2987,7 @@
         <v>110</v>
       </c>
       <c r="B110" s="1">
-        <v>33.64853280976268</v>
+        <v>115.5107720195065</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -2998,7 +2995,7 @@
         <v>111</v>
       </c>
       <c r="B111" s="1">
-        <v>33.64811462524366</v>
+        <v>115.314608805732</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -3006,7 +3003,7 @@
         <v>112</v>
       </c>
       <c r="B112" s="1">
-        <v>33.64773130718596</v>
+        <v>115.1788038304336</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -3014,7 +3011,7 @@
         <v>113</v>
       </c>
       <c r="B113" s="1">
-        <v>33.646002595559</v>
+        <v>115.1772910593903</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -3022,7 +3019,7 @@
         <v>114</v>
       </c>
       <c r="B114" s="1">
-        <v>33.64477377701716</v>
+        <v>115.1180554931809</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -3030,7 +3027,7 @@
         <v>115</v>
       </c>
       <c r="B115" s="1">
-        <v>33.64375265619612</v>
+        <v>115.0190667962254</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -3038,7 +3035,7 @@
         <v>116</v>
       </c>
       <c r="B116" s="1">
-        <v>33.6420079667265</v>
+        <v>115.0099063465901</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -3046,7 +3043,7 @@
         <v>117</v>
       </c>
       <c r="B117" s="1">
-        <v>33.63809165128612</v>
+        <v>114.7630721750088</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -3054,7 +3051,7 @@
         <v>118</v>
       </c>
       <c r="B118" s="1">
-        <v>33.63738639254859</v>
+        <v>114.7350764453523</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -3062,7 +3059,7 @@
         <v>119</v>
       </c>
       <c r="B119" s="1">
-        <v>33.63609727702814</v>
+        <v>114.3850502065295</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -3070,7 +3067,7 @@
         <v>120</v>
       </c>
       <c r="B120" s="1">
-        <v>33.63358295894011</v>
+        <v>114.3663998433953</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -3078,7 +3075,7 @@
         <v>121</v>
       </c>
       <c r="B121" s="1">
-        <v>33.6308166376149</v>
+        <v>114.3380049710739</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -3086,7 +3083,7 @@
         <v>122</v>
       </c>
       <c r="B122" s="1">
-        <v>33.63035028567044</v>
+        <v>114.3282886117716</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -3094,7 +3091,7 @@
         <v>123</v>
       </c>
       <c r="B123" s="1">
-        <v>33.62672165200224</v>
+        <v>114.3039519961244</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -3102,7 +3099,7 @@
         <v>124</v>
       </c>
       <c r="B124" s="1">
-        <v>33.62658145683927</v>
+        <v>114.2988185278907</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -3110,7 +3107,7 @@
         <v>125</v>
       </c>
       <c r="B125" s="1">
-        <v>33.6255196369098</v>
+        <v>114.2379077028294</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -3118,7 +3115,7 @@
         <v>126</v>
       </c>
       <c r="B126" s="1">
-        <v>33.62162913083299</v>
+        <v>114.2003721341588</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -3126,7 +3123,7 @@
         <v>127</v>
       </c>
       <c r="B127" s="1">
-        <v>33.62144645805729</v>
+        <v>113.9873077720361</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -3134,7 +3131,7 @@
         <v>128</v>
       </c>
       <c r="B128" s="1">
-        <v>33.62113446293507</v>
+        <v>113.8476688478566</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -3142,7 +3139,7 @@
         <v>129</v>
       </c>
       <c r="B129" s="1">
-        <v>33.61886864832594</v>
+        <v>113.6713753513925</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -3150,7 +3147,7 @@
         <v>130</v>
       </c>
       <c r="B130" s="1">
-        <v>33.61851827248075</v>
+        <v>113.5442591419512</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -3158,7 +3155,7 @@
         <v>131</v>
       </c>
       <c r="B131" s="1">
-        <v>33.61708154762857</v>
+        <v>113.5394687706013</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -3166,7 +3163,7 @@
         <v>132</v>
       </c>
       <c r="B132" s="1">
-        <v>33.61634295068241</v>
+        <v>113.444959149351</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -3174,7 +3171,7 @@
         <v>133</v>
       </c>
       <c r="B133" s="1">
-        <v>33.61563974818901</v>
+        <v>113.3261892777696</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -3182,7 +3179,7 @@
         <v>134</v>
       </c>
       <c r="B134" s="1">
-        <v>33.61380907991782</v>
+        <v>113.2782569688219</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -3190,7 +3187,7 @@
         <v>135</v>
       </c>
       <c r="B135" s="1">
-        <v>33.61352272120368</v>
+        <v>113.1954609303813</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -3198,7 +3195,7 @@
         <v>136</v>
       </c>
       <c r="B136" s="1">
-        <v>33.61236007014958</v>
+        <v>113.0710929096851</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -3206,7 +3203,7 @@
         <v>137</v>
       </c>
       <c r="B137" s="1">
-        <v>33.61232321095412</v>
+        <v>113.0344959431441</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -3214,7 +3211,7 @@
         <v>138</v>
       </c>
       <c r="B138" s="1">
-        <v>33.61141495886937</v>
+        <v>113.0343027668676</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -3222,7 +3219,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="1">
-        <v>33.61096086443218</v>
+        <v>112.9487253196114</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -3230,7 +3227,7 @@
         <v>140</v>
       </c>
       <c r="B140" s="1">
-        <v>33.61089010465346</v>
+        <v>112.875204830793</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -3238,7 +3235,7 @@
         <v>141</v>
       </c>
       <c r="B141" s="1">
-        <v>33.61064561036468</v>
+        <v>112.777743452436</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -3246,7 +3243,7 @@
         <v>142</v>
       </c>
       <c r="B142" s="1">
-        <v>33.61000272799174</v>
+        <v>112.732569915804</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -3254,7 +3251,7 @@
         <v>143</v>
       </c>
       <c r="B143" s="1">
-        <v>33.60818111921201</v>
+        <v>112.676492099097</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -3262,7 +3259,7 @@
         <v>144</v>
       </c>
       <c r="B144" s="1">
-        <v>33.60752632823576</v>
+        <v>112.6622580188997</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -3270,7 +3267,7 @@
         <v>145</v>
       </c>
       <c r="B145" s="1">
-        <v>33.60742780942049</v>
+        <v>112.6139383219039</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -3278,7 +3275,7 @@
         <v>146</v>
       </c>
       <c r="B146" s="1">
-        <v>33.60708405453028</v>
+        <v>112.5859223308479</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -3286,7 +3283,7 @@
         <v>147</v>
       </c>
       <c r="B147" s="1">
-        <v>33.60656495348044</v>
+        <v>112.5193923590384</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -3294,7 +3291,7 @@
         <v>148</v>
       </c>
       <c r="B148" s="1">
-        <v>33.60600797249231</v>
+        <v>112.519055341014</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -3302,7 +3299,7 @@
         <v>149</v>
       </c>
       <c r="B149" s="1">
-        <v>33.60541047088312</v>
+        <v>112.4533496475858</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -3310,7 +3307,7 @@
         <v>150</v>
       </c>
       <c r="B150" s="1">
-        <v>33.60505346855464</v>
+        <v>112.3906411292103</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -3318,7 +3315,7 @@
         <v>151</v>
       </c>
       <c r="B151" s="1">
-        <v>33.60461873573311</v>
+        <v>112.3269794636288</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -3326,7 +3323,7 @@
         <v>152</v>
       </c>
       <c r="B152" s="1">
-        <v>33.60267748004217</v>
+        <v>112.2457426124794</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -3334,7 +3331,7 @@
         <v>153</v>
       </c>
       <c r="B153" s="1">
-        <v>33.60182600168687</v>
+        <v>112.1977264910452</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -3342,7 +3339,7 @@
         <v>154</v>
       </c>
       <c r="B154" s="1">
-        <v>33.59914241770848</v>
+        <v>112.143019162249</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -3350,7 +3347,7 @@
         <v>155</v>
       </c>
       <c r="B155" s="1">
-        <v>33.59517240976987</v>
+        <v>112.1060325684553</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -3358,7 +3355,7 @@
         <v>156</v>
       </c>
       <c r="B156" s="1">
-        <v>33.59387982282053</v>
+        <v>112.0679333299758</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -3366,7 +3363,7 @@
         <v>157</v>
       </c>
       <c r="B157" s="1">
-        <v>33.59328609313215</v>
+        <v>112.0531450319764</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -3374,7 +3371,7 @@
         <v>158</v>
       </c>
       <c r="B158" s="1">
-        <v>33.59244201854055</v>
+        <v>112.0521413242142</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -3382,7 +3379,7 @@
         <v>159</v>
       </c>
       <c r="B159" s="1">
-        <v>33.59181542477126</v>
+        <v>112.0193667459477</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -3390,7 +3387,7 @@
         <v>160</v>
       </c>
       <c r="B160" s="1">
-        <v>33.59140092943387</v>
+        <v>111.97473540536</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -3398,7 +3395,7 @@
         <v>161</v>
       </c>
       <c r="B161" s="1">
-        <v>33.59131631875091</v>
+        <v>111.9320026442953</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -3406,7 +3403,7 @@
         <v>162</v>
       </c>
       <c r="B162" s="1">
-        <v>33.58915202658722</v>
+        <v>111.8558510564928</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -3414,7 +3411,7 @@
         <v>163</v>
       </c>
       <c r="B163" s="1">
-        <v>33.58897382859155</v>
+        <v>111.7263230745141</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -3422,7 +3419,7 @@
         <v>164</v>
       </c>
       <c r="B164" s="1">
-        <v>33.58797710733226</v>
+        <v>111.6854930250687</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -3430,7 +3427,7 @@
         <v>165</v>
       </c>
       <c r="B165" s="1">
-        <v>33.58780086724585</v>
+        <v>111.5934363100019</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -3438,7 +3435,7 @@
         <v>166</v>
       </c>
       <c r="B166" s="1">
-        <v>33.58569003075665</v>
+        <v>111.586901276318</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -3446,7 +3443,7 @@
         <v>167</v>
       </c>
       <c r="B167" s="1">
-        <v>33.58467547204801</v>
+        <v>111.3789935550132</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -3454,7 +3451,7 @@
         <v>168</v>
       </c>
       <c r="B168" s="1">
-        <v>33.58457652931642</v>
+        <v>111.3611380750681</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -3462,7 +3459,7 @@
         <v>169</v>
       </c>
       <c r="B169" s="1">
-        <v>33.58440100833992</v>
+        <v>111.346665802587</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -3470,7 +3467,7 @@
         <v>170</v>
       </c>
       <c r="B170" s="1">
-        <v>33.584299577335</v>
+        <v>111.3465180961861</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -3478,7 +3475,7 @@
         <v>171</v>
       </c>
       <c r="B171" s="1">
-        <v>33.58427085588485</v>
+        <v>111.3179205735857</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -3486,7 +3483,7 @@
         <v>172</v>
       </c>
       <c r="B172" s="1">
-        <v>33.58317659616827</v>
+        <v>111.1408915639471</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -3494,7 +3491,7 @@
         <v>173</v>
       </c>
       <c r="B173" s="1">
-        <v>33.58276605318171</v>
+        <v>111.1250751402151</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -3502,7 +3499,7 @@
         <v>174</v>
       </c>
       <c r="B174" s="1">
-        <v>33.58259801762527</v>
+        <v>111.1135796284285</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -3510,7 +3507,7 @@
         <v>175</v>
       </c>
       <c r="B175" s="1">
-        <v>33.5817053945409</v>
+        <v>111.0300982250302</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -3518,7 +3515,7 @@
         <v>176</v>
       </c>
       <c r="B176" s="1">
-        <v>33.58099838132468</v>
+        <v>111.0018227932589</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -3526,7 +3523,7 @@
         <v>177</v>
       </c>
       <c r="B177" s="1">
-        <v>33.58064973738191</v>
+        <v>110.9721957249015</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -3534,7 +3531,7 @@
         <v>178</v>
       </c>
       <c r="B178" s="1">
-        <v>33.5774441455762</v>
+        <v>110.9255160975927</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -3542,7 +3539,7 @@
         <v>179</v>
       </c>
       <c r="B179" s="1">
-        <v>33.57735568854005</v>
+        <v>110.8947851278548</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -3550,7 +3547,7 @@
         <v>180</v>
       </c>
       <c r="B180" s="1">
-        <v>33.57707238027583</v>
+        <v>110.8627599558183</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -3558,7 +3555,7 @@
         <v>181</v>
       </c>
       <c r="B181" s="1">
-        <v>33.57680362891305</v>
+        <v>110.8397862587471</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -3566,7 +3563,7 @@
         <v>182</v>
       </c>
       <c r="B182" s="1">
-        <v>33.57669642967971</v>
+        <v>110.6376258760223</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -3574,7 +3571,7 @@
         <v>183</v>
       </c>
       <c r="B183" s="1">
-        <v>33.57657211251372</v>
+        <v>110.5931391804349</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -3582,7 +3579,7 @@
         <v>184</v>
       </c>
       <c r="B184" s="1">
-        <v>33.57403993809609</v>
+        <v>110.5926902412967</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -3590,7 +3587,7 @@
         <v>185</v>
       </c>
       <c r="B185" s="1">
-        <v>33.57297971620446</v>
+        <v>110.4926250165401</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -3598,7 +3595,7 @@
         <v>186</v>
       </c>
       <c r="B186" s="1">
-        <v>33.57273961485839</v>
+        <v>110.4775706912209</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -3606,7 +3603,7 @@
         <v>187</v>
       </c>
       <c r="B187" s="1">
-        <v>33.57219262073743</v>
+        <v>110.4523000389414</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -3614,7 +3611,7 @@
         <v>188</v>
       </c>
       <c r="B188" s="1">
-        <v>33.5712875939003</v>
+        <v>110.4495929853834</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -3622,7 +3619,7 @@
         <v>189</v>
       </c>
       <c r="B189" s="1">
-        <v>33.57109754413467</v>
+        <v>110.4124233963192</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -3630,7 +3627,7 @@
         <v>190</v>
       </c>
       <c r="B190" s="1">
-        <v>33.56914510937698</v>
+        <v>110.3627484688429</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -3638,7 +3635,7 @@
         <v>191</v>
       </c>
       <c r="B191" s="1">
-        <v>33.56838146369305</v>
+        <v>110.1906094399694</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -3646,7 +3643,7 @@
         <v>192</v>
       </c>
       <c r="B192" s="1">
-        <v>33.56769150954084</v>
+        <v>110.1764303331871</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -3654,7 +3651,7 @@
         <v>193</v>
       </c>
       <c r="B193" s="1">
-        <v>33.56577569177654</v>
+        <v>110.1594648158969</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -3662,7 +3659,7 @@
         <v>194</v>
       </c>
       <c r="B194" s="1">
-        <v>33.56565682084993</v>
+        <v>110.1584634376858</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -3670,7 +3667,7 @@
         <v>195</v>
       </c>
       <c r="B195" s="1">
-        <v>33.56554559828594</v>
+        <v>110.1444241443542</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -3678,7 +3675,7 @@
         <v>196</v>
       </c>
       <c r="B196" s="1">
-        <v>33.56526044415597</v>
+        <v>110.1381430034398</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -3686,7 +3683,7 @@
         <v>197</v>
       </c>
       <c r="B197" s="1">
-        <v>33.56324935914405</v>
+        <v>110.1128008794736</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -3694,7 +3691,7 @@
         <v>198</v>
       </c>
       <c r="B198" s="1">
-        <v>33.56196100328156</v>
+        <v>110.0445216743583</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -3702,7 +3699,7 @@
         <v>199</v>
       </c>
       <c r="B199" s="1">
-        <v>33.55979608422593</v>
+        <v>110.0391324843375</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -3710,7 +3707,7 @@
         <v>200</v>
       </c>
       <c r="B200" s="1">
-        <v>33.55739637332457</v>
+        <v>110.0239433535197</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -3718,7 +3715,7 @@
         <v>201</v>
       </c>
       <c r="B201" s="1">
-        <v>33.55733987172364</v>
+        <v>110.0163037460615</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -3726,7 +3723,7 @@
         <v>202</v>
       </c>
       <c r="B202" s="1">
-        <v>33.55676861158825</v>
+        <v>109.9915391939989</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -3734,7 +3731,7 @@
         <v>203</v>
       </c>
       <c r="B203" s="1">
-        <v>33.55643444653035</v>
+        <v>109.9697141025042</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -3742,7 +3739,7 @@
         <v>204</v>
       </c>
       <c r="B204" s="1">
-        <v>33.55617556363828</v>
+        <v>109.967194782257</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -3750,7 +3747,7 @@
         <v>205</v>
       </c>
       <c r="B205" s="1">
-        <v>33.55538762196388</v>
+        <v>109.9403150138444</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -3758,7 +3755,7 @@
         <v>206</v>
       </c>
       <c r="B206" s="1">
-        <v>33.55400475907953</v>
+        <v>109.9110726192919</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -3766,7 +3763,7 @@
         <v>207</v>
       </c>
       <c r="B207" s="1">
-        <v>33.55350003539543</v>
+        <v>109.9026845797132</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -3774,7 +3771,7 @@
         <v>208</v>
       </c>
       <c r="B208" s="1">
-        <v>33.55211263413402</v>
+        <v>109.8901340334126</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -3782,7 +3779,7 @@
         <v>209</v>
       </c>
       <c r="B209" s="1">
-        <v>33.55088780718492</v>
+        <v>109.8810554098349</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -3790,7 +3787,7 @@
         <v>210</v>
       </c>
       <c r="B210" s="1">
-        <v>33.54944617098973</v>
+        <v>109.8548517053724</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -3798,7 +3795,7 @@
         <v>211</v>
       </c>
       <c r="B211" s="1">
-        <v>33.54826310823798</v>
+        <v>109.804341750345</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -3806,7 +3803,7 @@
         <v>212</v>
       </c>
       <c r="B212" s="1">
-        <v>33.54816864209702</v>
+        <v>109.7286000394487</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -3814,7 +3811,7 @@
         <v>213</v>
       </c>
       <c r="B213" s="1">
-        <v>33.54677377523422</v>
+        <v>109.7245499338698</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -3822,7 +3819,7 @@
         <v>214</v>
       </c>
       <c r="B214" s="1">
-        <v>33.54672818342289</v>
+        <v>109.6881323067637</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -3830,7 +3827,7 @@
         <v>215</v>
       </c>
       <c r="B215" s="1">
-        <v>33.54624841171944</v>
+        <v>109.6207351585819</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -3838,7 +3835,7 @@
         <v>216</v>
       </c>
       <c r="B216" s="1">
-        <v>33.54612352744698</v>
+        <v>109.5941582932509</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -3846,7 +3843,7 @@
         <v>217</v>
       </c>
       <c r="B217" s="1">
-        <v>33.54455808267972</v>
+        <v>109.5007134731656</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -3854,7 +3851,7 @@
         <v>218</v>
       </c>
       <c r="B218" s="1">
-        <v>33.54305618496925</v>
+        <v>109.4254309043247</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -3862,7 +3859,7 @@
         <v>219</v>
       </c>
       <c r="B219" s="1">
-        <v>33.54297750272539</v>
+        <v>109.4225873637941</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -3870,7 +3867,7 @@
         <v>220</v>
       </c>
       <c r="B220" s="1">
-        <v>33.54260053304136</v>
+        <v>109.4163176758458</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -3878,7 +3875,7 @@
         <v>221</v>
       </c>
       <c r="B221" s="1">
-        <v>33.54246101521937</v>
+        <v>109.4152720123788</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -3886,7 +3883,7 @@
         <v>222</v>
       </c>
       <c r="B222" s="1">
-        <v>33.54167246593043</v>
+        <v>109.3925371786257</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -3894,7 +3891,7 @@
         <v>223</v>
       </c>
       <c r="B223" s="1">
-        <v>33.54118271524746</v>
+        <v>109.371664564078</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -3902,7 +3899,7 @@
         <v>224</v>
       </c>
       <c r="B224" s="1">
-        <v>33.54078993903427</v>
+        <v>109.3612138285899</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -3910,7 +3907,7 @@
         <v>225</v>
       </c>
       <c r="B225" s="1">
-        <v>33.54074567257591</v>
+        <v>109.3494463391298</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -3918,7 +3915,7 @@
         <v>226</v>
       </c>
       <c r="B226" s="1">
-        <v>33.54057214803066</v>
+        <v>109.3230179954365</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -3926,7 +3923,7 @@
         <v>227</v>
       </c>
       <c r="B227" s="1">
-        <v>33.54044026892929</v>
+        <v>109.2593863164856</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -3934,7 +3931,7 @@
         <v>228</v>
       </c>
       <c r="B228" s="1">
-        <v>33.54009774936439</v>
+        <v>109.2452862513797</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -3942,7 +3939,7 @@
         <v>229</v>
       </c>
       <c r="B229" s="1">
-        <v>33.53996017525156</v>
+        <v>109.2445275324623</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -3950,7 +3947,7 @@
         <v>230</v>
       </c>
       <c r="B230" s="1">
-        <v>33.53974412448621</v>
+        <v>109.105188905917</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -3958,7 +3955,7 @@
         <v>231</v>
       </c>
       <c r="B231" s="1">
-        <v>33.53747696475274</v>
+        <v>109.0685859482133</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -3966,7 +3963,7 @@
         <v>232</v>
       </c>
       <c r="B232" s="1">
-        <v>33.53676176616997</v>
+        <v>109.0397996585525</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -3974,7 +3971,7 @@
         <v>233</v>
       </c>
       <c r="B233" s="1">
-        <v>33.53657670138312</v>
+        <v>109.0355320777742</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -3982,7 +3979,7 @@
         <v>234</v>
       </c>
       <c r="B234" s="1">
-        <v>33.53596066840399</v>
+        <v>108.9457248271857</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -3990,7 +3987,7 @@
         <v>235</v>
       </c>
       <c r="B235" s="1">
-        <v>33.53585567632238</v>
+        <v>108.8805804136121</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -3998,7 +3995,7 @@
         <v>236</v>
       </c>
       <c r="B236" s="1">
-        <v>33.53580519904816</v>
+        <v>108.8238365230966</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -4006,7 +4003,7 @@
         <v>237</v>
       </c>
       <c r="B237" s="1">
-        <v>33.53543247752344</v>
+        <v>108.8213031074816</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -4014,7 +4011,7 @@
         <v>238</v>
       </c>
       <c r="B238" s="1">
-        <v>33.53500615817512</v>
+        <v>108.8016402726917</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -4022,7 +4019,7 @@
         <v>239</v>
       </c>
       <c r="B239" s="1">
-        <v>33.53314938504023</v>
+        <v>108.7694143728578</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -4030,7 +4027,7 @@
         <v>240</v>
       </c>
       <c r="B240" s="1">
-        <v>33.53179905047373</v>
+        <v>108.7539489383964</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -4038,7 +4035,7 @@
         <v>241</v>
       </c>
       <c r="B241" s="1">
-        <v>33.53010687927653</v>
+        <v>108.7500257791994</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -4046,7 +4043,7 @@
         <v>242</v>
       </c>
       <c r="B242" s="1">
-        <v>33.52974548526097</v>
+        <v>108.7442613708145</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -4054,7 +4051,7 @@
         <v>243</v>
       </c>
       <c r="B243" s="1">
-        <v>33.52972796557045</v>
+        <v>108.7135833644987</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -4062,7 +4059,7 @@
         <v>244</v>
       </c>
       <c r="B244" s="1">
-        <v>33.52946152609403</v>
+        <v>108.6453062728561</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -4070,7 +4067,7 @@
         <v>245</v>
       </c>
       <c r="B245" s="1">
-        <v>33.52888850155016</v>
+        <v>108.6118421114181</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -4078,7 +4075,7 @@
         <v>246</v>
       </c>
       <c r="B246" s="1">
-        <v>33.52859851422897</v>
+        <v>108.6006414279477</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -4086,7 +4083,7 @@
         <v>247</v>
       </c>
       <c r="B247" s="1">
-        <v>33.5282370866283</v>
+        <v>108.583356850018</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -4094,7 +4091,7 @@
         <v>248</v>
       </c>
       <c r="B248" s="1">
-        <v>33.52744895919876</v>
+        <v>108.5631053071633</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -4102,7 +4099,7 @@
         <v>249</v>
       </c>
       <c r="B249" s="1">
-        <v>33.52711758675506</v>
+        <v>108.5280400573414</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -4110,7 +4107,7 @@
         <v>250</v>
       </c>
       <c r="B250" s="1">
-        <v>33.52659515393254</v>
+        <v>108.5197181049477</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -4118,7 +4115,7 @@
         <v>251</v>
       </c>
       <c r="B251" s="1">
-        <v>33.52604679065968</v>
+        <v>108.5172210362064</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -4126,7 +4123,7 @@
         <v>252</v>
       </c>
       <c r="B252" s="1">
-        <v>33.5257108697046</v>
+        <v>108.5040302130104</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -4134,7 +4131,7 @@
         <v>253</v>
       </c>
       <c r="B253" s="1">
-        <v>33.52485335906608</v>
+        <v>108.4879460127584</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -4142,7 +4139,7 @@
         <v>254</v>
       </c>
       <c r="B254" s="1">
-        <v>33.52472920443488</v>
+        <v>108.4695722595417</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -4150,7 +4147,7 @@
         <v>255</v>
       </c>
       <c r="B255" s="1">
-        <v>33.52451328177003</v>
+        <v>108.4453449889561</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -4158,7 +4155,7 @@
         <v>256</v>
       </c>
       <c r="B256" s="1">
-        <v>33.52417611510023</v>
+        <v>108.4355010131187</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -4166,7 +4163,7 @@
         <v>257</v>
       </c>
       <c r="B257" s="1">
-        <v>33.52322647642823</v>
+        <v>108.4293548260467</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -4174,7 +4171,7 @@
         <v>258</v>
       </c>
       <c r="B258" s="1">
-        <v>33.52265461912715</v>
+        <v>108.3485124227473</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -4182,7 +4179,7 @@
         <v>259</v>
       </c>
       <c r="B259" s="1">
-        <v>33.52200170592638</v>
+        <v>108.3380400620968</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -4190,7 +4187,7 @@
         <v>260</v>
       </c>
       <c r="B260" s="1">
-        <v>33.52152535494837</v>
+        <v>108.307919256461</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -4198,7 +4195,7 @@
         <v>261</v>
       </c>
       <c r="B261" s="1">
-        <v>33.52150572005971</v>
+        <v>108.2868993667295</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -4206,7 +4203,7 @@
         <v>262</v>
       </c>
       <c r="B262" s="1">
-        <v>33.5206564091875</v>
+        <v>108.2751547855899</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -4214,7 +4211,7 @@
         <v>263</v>
       </c>
       <c r="B263" s="1">
-        <v>33.52010526568967</v>
+        <v>108.263532480959</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -4222,7 +4219,7 @@
         <v>264</v>
       </c>
       <c r="B264" s="1">
-        <v>33.51947172842235</v>
+        <v>108.2552624496726</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -4230,7 +4227,7 @@
         <v>265</v>
       </c>
       <c r="B265" s="1">
-        <v>33.5193372273214</v>
+        <v>108.2308490732492</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -4238,7 +4235,7 @@
         <v>266</v>
       </c>
       <c r="B266" s="1">
-        <v>33.51809691468788</v>
+        <v>108.195477738056</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -4246,7 +4243,7 @@
         <v>267</v>
       </c>
       <c r="B267" s="1">
-        <v>33.51506102259103</v>
+        <v>108.1896190489633</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -4254,7 +4251,7 @@
         <v>268</v>
       </c>
       <c r="B268" s="1">
-        <v>33.5148712734746</v>
+        <v>108.1847804637386</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -4262,7 +4259,7 @@
         <v>269</v>
       </c>
       <c r="B269" s="1">
-        <v>33.51383573310397</v>
+        <v>108.1791792827654</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -4270,7 +4267,7 @@
         <v>270</v>
       </c>
       <c r="B270" s="1">
-        <v>33.51375258340561</v>
+        <v>108.1008672269782</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -4278,7 +4275,7 @@
         <v>271</v>
       </c>
       <c r="B271" s="1">
-        <v>33.51365843675482</v>
+        <v>108.0976919606198</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -4286,7 +4283,7 @@
         <v>272</v>
       </c>
       <c r="B272" s="1">
-        <v>33.51356179861448</v>
+        <v>108.0681333659302</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -4294,7 +4291,7 @@
         <v>273</v>
       </c>
       <c r="B273" s="1">
-        <v>33.51321583396935</v>
+        <v>108.0449810572618</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -4302,7 +4299,7 @@
         <v>274</v>
       </c>
       <c r="B274" s="1">
-        <v>33.51275272107269</v>
+        <v>108.0135970624105</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -4310,7 +4307,7 @@
         <v>275</v>
       </c>
       <c r="B275" s="1">
-        <v>33.51252278492969</v>
+        <v>108.0071656987081</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -4318,7 +4315,7 @@
         <v>276</v>
       </c>
       <c r="B276" s="1">
-        <v>33.5124331423858</v>
+        <v>107.9974877146484</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -4326,7 +4323,7 @@
         <v>277</v>
       </c>
       <c r="B277" s="1">
-        <v>33.51214508590646</v>
+        <v>107.9940175457025</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -4334,7 +4331,7 @@
         <v>278</v>
       </c>
       <c r="B278" s="1">
-        <v>33.51208850265445</v>
+        <v>107.9847164427934</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -4342,7 +4339,7 @@
         <v>279</v>
       </c>
       <c r="B279" s="1">
-        <v>33.511781105214</v>
+        <v>107.9526742912932</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -4350,7 +4347,7 @@
         <v>280</v>
       </c>
       <c r="B280" s="1">
-        <v>33.51116767886082</v>
+        <v>107.8877584436412</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -4358,7 +4355,7 @@
         <v>281</v>
       </c>
       <c r="B281" s="1">
-        <v>33.51093989216193</v>
+        <v>107.8873831019104</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -4366,7 +4363,7 @@
         <v>282</v>
       </c>
       <c r="B282" s="1">
-        <v>33.51016810318954</v>
+        <v>107.8873643560209</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -4374,7 +4371,7 @@
         <v>283</v>
       </c>
       <c r="B283" s="1">
-        <v>33.51014040561623</v>
+        <v>107.8866266839896</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -4382,7 +4379,7 @@
         <v>284</v>
       </c>
       <c r="B284" s="1">
-        <v>33.50946498338728</v>
+        <v>107.8754235247931</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -4390,7 +4387,7 @@
         <v>285</v>
       </c>
       <c r="B285" s="1">
-        <v>33.50907558729255</v>
+        <v>107.8421986733093</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -4398,7 +4395,7 @@
         <v>286</v>
       </c>
       <c r="B286" s="1">
-        <v>33.5085243791204</v>
+        <v>107.833969257543</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -4406,7 +4403,7 @@
         <v>287</v>
       </c>
       <c r="B287" s="1">
-        <v>33.5084391669539</v>
+        <v>107.742335949786</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -4414,7 +4411,7 @@
         <v>288</v>
       </c>
       <c r="B288" s="1">
-        <v>33.50836973517723</v>
+        <v>107.7154784503519</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -4422,7 +4419,7 @@
         <v>289</v>
       </c>
       <c r="B289" s="1">
-        <v>33.50821793131691</v>
+        <v>107.7138964151287</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -4430,7 +4427,7 @@
         <v>290</v>
       </c>
       <c r="B290" s="1">
-        <v>33.50780364171419</v>
+        <v>107.7014781807888</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -4438,7 +4435,7 @@
         <v>291</v>
       </c>
       <c r="B291" s="1">
-        <v>33.50662978925057</v>
+        <v>107.6915539604903</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -4446,7 +4443,7 @@
         <v>292</v>
       </c>
       <c r="B292" s="1">
-        <v>33.50657695820964</v>
+        <v>107.6899914690012</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -4454,7 +4451,7 @@
         <v>293</v>
       </c>
       <c r="B293" s="1">
-        <v>33.50654233507819</v>
+        <v>107.6638863167691</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -4462,7 +4459,7 @@
         <v>294</v>
       </c>
       <c r="B294" s="1">
-        <v>33.50625982874203</v>
+        <v>107.6620628159967</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -4470,7 +4467,7 @@
         <v>295</v>
       </c>
       <c r="B295" s="1">
-        <v>33.50577558267416</v>
+        <v>107.6618283298141</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -4478,7 +4475,7 @@
         <v>296</v>
       </c>
       <c r="B296" s="1">
-        <v>33.5055498205697</v>
+        <v>107.6442843714625</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -4486,7 +4483,7 @@
         <v>297</v>
       </c>
       <c r="B297" s="1">
-        <v>33.50482699065955</v>
+        <v>107.6225026410125</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -4494,7 +4491,7 @@
         <v>298</v>
       </c>
       <c r="B298" s="1">
-        <v>33.50444142929251</v>
+        <v>107.6188080514157</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -4502,7 +4499,7 @@
         <v>299</v>
       </c>
       <c r="B299" s="1">
-        <v>33.50442146571053</v>
+        <v>107.6177857591665</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -4510,7 +4507,7 @@
         <v>300</v>
       </c>
       <c r="B300" s="1">
-        <v>33.50408706151101</v>
+        <v>107.5891737574686</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -4518,7 +4515,7 @@
         <v>301</v>
       </c>
       <c r="B301" s="1">
-        <v>33.5035316021444</v>
+        <v>107.5886522526593</v>
       </c>
     </row>
     <row r="302" spans="1:2">
@@ -4526,7 +4523,7 @@
         <v>302</v>
       </c>
       <c r="B302" s="1">
-        <v>33.50302970815921</v>
+        <v>107.5837295932754</v>
       </c>
     </row>
     <row r="303" spans="1:2">
@@ -4534,7 +4531,7 @@
         <v>303</v>
       </c>
       <c r="B303" s="1">
-        <v>33.50239523682603</v>
+        <v>107.5277221786158</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -4542,7 +4539,7 @@
         <v>304</v>
       </c>
       <c r="B304" s="1">
-        <v>33.50201947985732</v>
+        <v>107.4946858977501</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -4550,7 +4547,7 @@
         <v>305</v>
       </c>
       <c r="B305" s="1">
-        <v>33.50143288014112</v>
+        <v>107.4917818034271</v>
       </c>
     </row>
     <row r="306" spans="1:2">
@@ -4558,7 +4555,7 @@
         <v>306</v>
       </c>
       <c r="B306" s="1">
-        <v>33.50098237592076</v>
+        <v>107.4843324345364</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -4566,7 +4563,7 @@
         <v>307</v>
       </c>
       <c r="B307" s="1">
-        <v>33.50096049653843</v>
+        <v>107.46973639812</v>
       </c>
     </row>
     <row r="308" spans="1:2">
@@ -4574,7 +4571,7 @@
         <v>308</v>
       </c>
       <c r="B308" s="1">
-        <v>33.50093392556688</v>
+        <v>107.4403433076816</v>
       </c>
     </row>
     <row r="309" spans="1:2">
@@ -4582,7 +4579,7 @@
         <v>309</v>
       </c>
       <c r="B309" s="1">
-        <v>33.50077351625767</v>
+        <v>107.4282262655243</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -4590,7 +4587,7 @@
         <v>310</v>
       </c>
       <c r="B310" s="1">
-        <v>33.49985170670804</v>
+        <v>107.4121037911361</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -4598,7 +4595,7 @@
         <v>311</v>
       </c>
       <c r="B311" s="1">
-        <v>33.49940900663834</v>
+        <v>107.4052464759697</v>
       </c>
     </row>
     <row r="312" spans="1:2">
@@ -4606,7 +4603,7 @@
         <v>312</v>
       </c>
       <c r="B312" s="1">
-        <v>33.49936767124986</v>
+        <v>107.3957115794868</v>
       </c>
     </row>
     <row r="313" spans="1:2">
@@ -4614,7 +4611,7 @@
         <v>313</v>
       </c>
       <c r="B313" s="1">
-        <v>33.49872894047522</v>
+        <v>107.3521280326701</v>
       </c>
     </row>
     <row r="314" spans="1:2">
@@ -4622,7 +4619,7 @@
         <v>314</v>
       </c>
       <c r="B314" s="1">
-        <v>33.4978077356559</v>
+        <v>107.3361948581132</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -4630,7 +4627,7 @@
         <v>315</v>
       </c>
       <c r="B315" s="1">
-        <v>33.49770821376183</v>
+        <v>107.3106870293134</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -4638,7 +4635,7 @@
         <v>316</v>
       </c>
       <c r="B316" s="1">
-        <v>33.49730423924287</v>
+        <v>107.3078292683225</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -4646,7 +4643,7 @@
         <v>317</v>
       </c>
       <c r="B317" s="1">
-        <v>33.49721204795014</v>
+        <v>107.2970227881309</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -4654,7 +4651,7 @@
         <v>318</v>
       </c>
       <c r="B318" s="1">
-        <v>33.49689627066589</v>
+        <v>107.2921744975198</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -4662,7 +4659,7 @@
         <v>319</v>
       </c>
       <c r="B319" s="1">
-        <v>33.49596137807174</v>
+        <v>107.2727279353326</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -4670,7 +4667,7 @@
         <v>320</v>
       </c>
       <c r="B320" s="1">
-        <v>33.49495361521441</v>
+        <v>107.2645113551407</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -4678,7 +4675,7 @@
         <v>321</v>
       </c>
       <c r="B321" s="1">
-        <v>33.49487372323811</v>
+        <v>107.2638749470507</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -4686,7 +4683,7 @@
         <v>322</v>
       </c>
       <c r="B322" s="1">
-        <v>33.49467909772622</v>
+        <v>107.2121730670316</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -4694,7 +4691,7 @@
         <v>323</v>
       </c>
       <c r="B323" s="1">
-        <v>33.49418341204928</v>
+        <v>107.2097102106367</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -4702,7 +4699,7 @@
         <v>324</v>
       </c>
       <c r="B324" s="1">
-        <v>33.49385009389905</v>
+        <v>107.1776592051601</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -4710,7 +4707,7 @@
         <v>325</v>
       </c>
       <c r="B325" s="1">
-        <v>33.49357695443575</v>
+        <v>107.174362194882</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -4718,7 +4715,7 @@
         <v>326</v>
       </c>
       <c r="B326" s="1">
-        <v>33.49347688048373</v>
+        <v>107.157017510286</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -4726,7 +4723,7 @@
         <v>327</v>
       </c>
       <c r="B327" s="1">
-        <v>33.49332976752008</v>
+        <v>107.156444133081</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -4734,7 +4731,7 @@
         <v>328</v>
       </c>
       <c r="B328" s="1">
-        <v>33.49330846573928</v>
+        <v>107.1305780736901</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -4742,7 +4739,7 @@
         <v>329</v>
       </c>
       <c r="B329" s="1">
-        <v>33.49317431303796</v>
+        <v>107.122830153029</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -4750,7 +4747,7 @@
         <v>330</v>
       </c>
       <c r="B330" s="1">
-        <v>33.49311873509397</v>
+        <v>107.0862998626522</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -4758,7 +4755,7 @@
         <v>331</v>
       </c>
       <c r="B331" s="1">
-        <v>33.49282994668457</v>
+        <v>107.0609401701599</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -4766,7 +4763,7 @@
         <v>332</v>
       </c>
       <c r="B332" s="1">
-        <v>33.4927945505274</v>
+        <v>107.04698036168</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -4774,7 +4771,7 @@
         <v>333</v>
       </c>
       <c r="B333" s="1">
-        <v>33.49222668865924</v>
+        <v>107.0092206545987</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -4782,7 +4779,7 @@
         <v>334</v>
       </c>
       <c r="B334" s="1">
-        <v>33.49128116593879</v>
+        <v>107.0059397640808</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -4790,7 +4787,7 @@
         <v>335</v>
       </c>
       <c r="B335" s="1">
-        <v>33.49117720419001</v>
+        <v>106.9995709084778</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -4798,7 +4795,7 @@
         <v>336</v>
       </c>
       <c r="B336" s="1">
-        <v>33.48971390875361</v>
+        <v>106.9859357966642</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -4806,7 +4803,7 @@
         <v>337</v>
       </c>
       <c r="B337" s="1">
-        <v>33.48959287054194</v>
+        <v>106.9844110734444</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -4814,7 +4811,7 @@
         <v>338</v>
       </c>
       <c r="B338" s="1">
-        <v>33.48930408902422</v>
+        <v>106.9744675100796</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -4822,7 +4819,7 @@
         <v>339</v>
       </c>
       <c r="B339" s="1">
-        <v>33.48925932266464</v>
+        <v>106.9568496702838</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -4830,7 +4827,7 @@
         <v>340</v>
       </c>
       <c r="B340" s="1">
-        <v>33.48912064212513</v>
+        <v>106.9327690335236</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -4838,7 +4835,7 @@
         <v>341</v>
       </c>
       <c r="B341" s="1">
-        <v>33.48897917003244</v>
+        <v>106.9259691788386</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -4846,7 +4843,7 @@
         <v>342</v>
       </c>
       <c r="B342" s="1">
-        <v>33.4886492459645</v>
+        <v>106.9053240006801</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -4854,7 +4851,7 @@
         <v>343</v>
       </c>
       <c r="B343" s="1">
-        <v>33.48842290684116</v>
+        <v>106.8686562838427</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -4862,7 +4859,7 @@
         <v>344</v>
       </c>
       <c r="B344" s="1">
-        <v>33.48837310494597</v>
+        <v>106.8646880610034</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -4870,7 +4867,7 @@
         <v>345</v>
       </c>
       <c r="B345" s="1">
-        <v>33.48771724696126</v>
+        <v>106.8499951028302</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -4878,7 +4875,7 @@
         <v>346</v>
       </c>
       <c r="B346" s="1">
-        <v>33.48720102903969</v>
+        <v>106.8295121422154</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -4886,7 +4883,7 @@
         <v>347</v>
       </c>
       <c r="B347" s="1">
-        <v>33.48660806844057</v>
+        <v>106.8016424413377</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -4894,7 +4891,7 @@
         <v>348</v>
       </c>
       <c r="B348" s="1">
-        <v>33.48655061430094</v>
+        <v>106.7748386718829</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -4902,7 +4899,7 @@
         <v>349</v>
       </c>
       <c r="B349" s="1">
-        <v>33.48616592561335</v>
+        <v>106.7720110633728</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -4910,7 +4907,7 @@
         <v>350</v>
       </c>
       <c r="B350" s="1">
-        <v>33.48572579255978</v>
+        <v>106.7413965088057</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -4918,7 +4915,7 @@
         <v>351</v>
       </c>
       <c r="B351" s="1">
-        <v>33.4856624663627</v>
+        <v>106.7387455472268</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -4926,7 +4923,7 @@
         <v>352</v>
       </c>
       <c r="B352" s="1">
-        <v>33.48565403502429</v>
+        <v>106.7261574437181</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -4934,7 +4931,7 @@
         <v>353</v>
       </c>
       <c r="B353" s="1">
-        <v>33.48553730880447</v>
+        <v>106.722867873317</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -4942,7 +4939,7 @@
         <v>354</v>
       </c>
       <c r="B354" s="1">
-        <v>33.4854304019517</v>
+        <v>106.7110437439044</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -4950,7 +4947,7 @@
         <v>355</v>
       </c>
       <c r="B355" s="1">
-        <v>33.48386423115799</v>
+        <v>106.6425521377843</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -4958,7 +4955,7 @@
         <v>356</v>
       </c>
       <c r="B356" s="1">
-        <v>33.48320652348238</v>
+        <v>106.6312649919673</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -4966,7 +4963,7 @@
         <v>357</v>
       </c>
       <c r="B357" s="1">
-        <v>33.4830826502377</v>
+        <v>106.619699106584</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -4974,7 +4971,7 @@
         <v>358</v>
       </c>
       <c r="B358" s="1">
-        <v>33.48268462037871</v>
+        <v>106.5675470663586</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -4982,7 +4979,7 @@
         <v>359</v>
       </c>
       <c r="B359" s="1">
-        <v>33.48241466677776</v>
+        <v>106.5581910876991</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -4990,7 +4987,7 @@
         <v>360</v>
       </c>
       <c r="B360" s="1">
-        <v>33.48126252422995</v>
+        <v>106.5244797672222</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -4998,7 +4995,7 @@
         <v>361</v>
       </c>
       <c r="B361" s="1">
-        <v>33.4805277164328</v>
+        <v>106.5101975939811</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -5006,7 +5003,7 @@
         <v>362</v>
       </c>
       <c r="B362" s="1">
-        <v>33.4804302064359</v>
+        <v>106.5018111581585</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -5014,7 +5011,7 @@
         <v>363</v>
       </c>
       <c r="B363" s="1">
-        <v>33.48028538504956</v>
+        <v>106.4991323124589</v>
       </c>
     </row>
     <row r="364" spans="1:2">
@@ -5022,7 +5019,7 @@
         <v>364</v>
       </c>
       <c r="B364" s="1">
-        <v>33.47947837543899</v>
+        <v>106.4976492378107</v>
       </c>
     </row>
     <row r="365" spans="1:2">
@@ -5030,7 +5027,7 @@
         <v>365</v>
       </c>
       <c r="B365" s="1">
-        <v>33.47912530127956</v>
+        <v>106.4843417498122</v>
       </c>
     </row>
     <row r="366" spans="1:2">
@@ -5038,7 +5035,7 @@
         <v>366</v>
       </c>
       <c r="B366" s="1">
-        <v>33.4789931073711</v>
+        <v>106.4555014588435</v>
       </c>
     </row>
     <row r="367" spans="1:2">
@@ -5046,7 +5043,7 @@
         <v>367</v>
       </c>
       <c r="B367" s="1">
-        <v>33.47857949727192</v>
+        <v>106.4407695078929</v>
       </c>
     </row>
     <row r="368" spans="1:2">
@@ -5054,7 +5051,7 @@
         <v>368</v>
       </c>
       <c r="B368" s="1">
-        <v>33.47846846356942</v>
+        <v>106.4158314376268</v>
       </c>
     </row>
     <row r="369" spans="1:2">
@@ -5062,7 +5059,7 @@
         <v>369</v>
       </c>
       <c r="B369" s="1">
-        <v>33.47834210449975</v>
+        <v>106.4048853962495</v>
       </c>
     </row>
     <row r="370" spans="1:2">
@@ -5070,7 +5067,7 @@
         <v>370</v>
       </c>
       <c r="B370" s="1">
-        <v>33.4780466727107</v>
+        <v>106.3817427130815</v>
       </c>
     </row>
     <row r="371" spans="1:2">
@@ -5078,7 +5075,7 @@
         <v>371</v>
       </c>
       <c r="B371" s="1">
-        <v>33.47756482888224</v>
+        <v>106.3809607643407</v>
       </c>
     </row>
     <row r="372" spans="1:2">
@@ -5086,7 +5083,7 @@
         <v>372</v>
       </c>
       <c r="B372" s="1">
-        <v>33.47727748616663</v>
+        <v>106.3582058094647</v>
       </c>
     </row>
     <row r="373" spans="1:2">
@@ -5094,7 +5091,7 @@
         <v>373</v>
       </c>
       <c r="B373" s="1">
-        <v>33.47720182921725</v>
+        <v>106.3484509014427</v>
       </c>
     </row>
     <row r="374" spans="1:2">
@@ -5102,7 +5099,7 @@
         <v>374</v>
       </c>
       <c r="B374" s="1">
-        <v>33.47701982023085</v>
+        <v>106.3419733116478</v>
       </c>
     </row>
     <row r="375" spans="1:2">
@@ -5110,7 +5107,7 @@
         <v>375</v>
       </c>
       <c r="B375" s="1">
-        <v>33.47652203894435</v>
+        <v>106.3390128579726</v>
       </c>
     </row>
     <row r="376" spans="1:2">
@@ -5118,7 +5115,7 @@
         <v>376</v>
       </c>
       <c r="B376" s="1">
-        <v>33.47631279887372</v>
+        <v>106.3324972784344</v>
       </c>
     </row>
     <row r="377" spans="1:2">
@@ -5126,7 +5123,7 @@
         <v>377</v>
       </c>
       <c r="B377" s="1">
-        <v>33.47626929994744</v>
+        <v>106.3162129751284</v>
       </c>
     </row>
     <row r="378" spans="1:2">
@@ -5134,7 +5131,7 @@
         <v>378</v>
       </c>
       <c r="B378" s="1">
-        <v>33.47611767373223</v>
+        <v>106.2873414784253</v>
       </c>
     </row>
     <row r="379" spans="1:2">
@@ -5142,7 +5139,7 @@
         <v>379</v>
       </c>
       <c r="B379" s="1">
-        <v>33.47481385214371</v>
+        <v>106.2706435331995</v>
       </c>
     </row>
     <row r="380" spans="1:2">
@@ -5150,7 +5147,7 @@
         <v>380</v>
       </c>
       <c r="B380" s="1">
-        <v>33.47414312020024</v>
+        <v>106.2704787918382</v>
       </c>
     </row>
     <row r="381" spans="1:2">
@@ -5158,7 +5155,7 @@
         <v>381</v>
       </c>
       <c r="B381" s="1">
-        <v>33.47400998742099</v>
+        <v>106.2698047812122</v>
       </c>
     </row>
     <row r="382" spans="1:2">
@@ -5166,7 +5163,7 @@
         <v>382</v>
       </c>
       <c r="B382" s="1">
-        <v>33.47285546253314</v>
+        <v>106.236636832187</v>
       </c>
     </row>
     <row r="383" spans="1:2">
@@ -5174,7 +5171,7 @@
         <v>383</v>
       </c>
       <c r="B383" s="1">
-        <v>33.47230716506757</v>
+        <v>106.2097944613101</v>
       </c>
     </row>
     <row r="384" spans="1:2">
@@ -5182,7 +5179,7 @@
         <v>384</v>
       </c>
       <c r="B384" s="1">
-        <v>33.47226547558101</v>
+        <v>106.2030206093237</v>
       </c>
     </row>
     <row r="385" spans="1:2">
@@ -5190,7 +5187,7 @@
         <v>385</v>
       </c>
       <c r="B385" s="1">
-        <v>33.47223406731987</v>
+        <v>106.196301800066</v>
       </c>
     </row>
     <row r="386" spans="1:2">
@@ -5198,7 +5195,7 @@
         <v>386</v>
       </c>
       <c r="B386" s="1">
-        <v>33.47221445133869</v>
+        <v>106.1854980709998</v>
       </c>
     </row>
     <row r="387" spans="1:2">
@@ -5206,7 +5203,7 @@
         <v>387</v>
       </c>
       <c r="B387" s="1">
-        <v>33.47206009087559</v>
+        <v>106.173755909117</v>
       </c>
     </row>
     <row r="388" spans="1:2">
@@ -5214,7 +5211,7 @@
         <v>388</v>
       </c>
       <c r="B388" s="1">
-        <v>33.47033884239301</v>
+        <v>106.1669557002319</v>
       </c>
     </row>
     <row r="389" spans="1:2">
@@ -5222,7 +5219,7 @@
         <v>389</v>
       </c>
       <c r="B389" s="1">
-        <v>33.47021368034338</v>
+        <v>106.1409083159317</v>
       </c>
     </row>
     <row r="390" spans="1:2">
@@ -5230,7 +5227,7 @@
         <v>390</v>
       </c>
       <c r="B390" s="1">
-        <v>33.47016517125193</v>
+        <v>106.1314013944217</v>
       </c>
     </row>
     <row r="391" spans="1:2">
@@ -5238,7 +5235,7 @@
         <v>391</v>
       </c>
       <c r="B391" s="1">
-        <v>33.46921249852326</v>
+        <v>106.1310333394876</v>
       </c>
     </row>
     <row r="392" spans="1:2">
@@ -5246,7 +5243,7 @@
         <v>392</v>
       </c>
       <c r="B392" s="1">
-        <v>33.4687474100061</v>
+        <v>106.1091239133034</v>
       </c>
     </row>
     <row r="393" spans="1:2">
@@ -5254,7 +5251,7 @@
         <v>393</v>
       </c>
       <c r="B393" s="1">
-        <v>33.46865067428394</v>
+        <v>106.1027567037186</v>
       </c>
     </row>
     <row r="394" spans="1:2">
@@ -5262,7 +5259,7 @@
         <v>394</v>
       </c>
       <c r="B394" s="1">
-        <v>33.46845926282078</v>
+        <v>106.0890515990323</v>
       </c>
     </row>
     <row r="395" spans="1:2">
@@ -5270,7 +5267,7 @@
         <v>395</v>
       </c>
       <c r="B395" s="1">
-        <v>33.46804554988747</v>
+        <v>106.0651543539861</v>
       </c>
     </row>
     <row r="396" spans="1:2">
@@ -5278,7 +5275,7 @@
         <v>396</v>
       </c>
       <c r="B396" s="1">
-        <v>33.46750124961946</v>
+        <v>106.0533138097109</v>
       </c>
     </row>
     <row r="397" spans="1:2">
@@ -5286,7 +5283,7 @@
         <v>397</v>
       </c>
       <c r="B397" s="1">
-        <v>33.4673551135716</v>
+        <v>106.0513248040899</v>
       </c>
     </row>
     <row r="398" spans="1:2">
@@ -5294,7 +5291,7 @@
         <v>398</v>
       </c>
       <c r="B398" s="1">
-        <v>33.46733024849576</v>
+        <v>106.0480512226022</v>
       </c>
     </row>
     <row r="399" spans="1:2">
@@ -5302,7 +5299,7 @@
         <v>399</v>
       </c>
       <c r="B399" s="1">
-        <v>33.46679135514981</v>
+        <v>106.0187871460006</v>
       </c>
     </row>
     <row r="400" spans="1:2">
@@ -5310,7 +5307,7 @@
         <v>400</v>
       </c>
       <c r="B400" s="1">
-        <v>33.46642731593055</v>
+        <v>105.9912985539242</v>
       </c>
     </row>
     <row r="401" spans="1:2">
@@ -5318,7 +5315,7 @@
         <v>401</v>
       </c>
       <c r="B401" s="1">
-        <v>33.4662531089506</v>
+        <v>105.9316123283701</v>
       </c>
     </row>
     <row r="402" spans="1:2">
@@ -5326,7 +5323,7 @@
         <v>402</v>
       </c>
       <c r="B402" s="1">
-        <v>33.46624370860762</v>
+        <v>105.9286679459907</v>
       </c>
     </row>
     <row r="403" spans="1:2">
@@ -5334,7 +5331,7 @@
         <v>403</v>
       </c>
       <c r="B403" s="1">
-        <v>33.46579905918608</v>
+        <v>105.9251616291667</v>
       </c>
     </row>
     <row r="404" spans="1:2">
@@ -5342,7 +5339,7 @@
         <v>404</v>
       </c>
       <c r="B404" s="1">
-        <v>33.46557035555384</v>
+        <v>105.9101642722887</v>
       </c>
     </row>
     <row r="405" spans="1:2">
@@ -5350,7 +5347,7 @@
         <v>405</v>
       </c>
       <c r="B405" s="1">
-        <v>33.46515827740832</v>
+        <v>105.865968376186</v>
       </c>
     </row>
     <row r="406" spans="1:2">
@@ -5358,7 +5355,7 @@
         <v>406</v>
       </c>
       <c r="B406" s="1">
-        <v>33.46488548559476</v>
+        <v>105.839064241855</v>
       </c>
     </row>
     <row r="407" spans="1:2">
@@ -5366,7 +5363,7 @@
         <v>407</v>
       </c>
       <c r="B407" s="1">
-        <v>33.46478945991747</v>
+        <v>105.830136130912</v>
       </c>
     </row>
     <row r="408" spans="1:2">
@@ -5374,7 +5371,7 @@
         <v>408</v>
       </c>
       <c r="B408" s="1">
-        <v>33.46409597934149</v>
+        <v>105.8113367781082</v>
       </c>
     </row>
     <row r="409" spans="1:2">
@@ -5382,7 +5379,7 @@
         <v>409</v>
       </c>
       <c r="B409" s="1">
-        <v>33.46390196374067</v>
+        <v>105.8077544527077</v>
       </c>
     </row>
     <row r="410" spans="1:2">
@@ -5390,7 +5387,7 @@
         <v>410</v>
       </c>
       <c r="B410" s="1">
-        <v>33.46386399535209</v>
+        <v>105.8062087332248</v>
       </c>
     </row>
     <row r="411" spans="1:2">
@@ -5398,7 +5395,7 @@
         <v>411</v>
       </c>
       <c r="B411" s="1">
-        <v>33.46384682974804</v>
+        <v>105.8012257935768</v>
       </c>
     </row>
     <row r="412" spans="1:2">
@@ -5406,7 +5403,7 @@
         <v>412</v>
       </c>
       <c r="B412" s="1">
-        <v>33.46371042304229</v>
+        <v>105.7934121252259</v>
       </c>
     </row>
     <row r="413" spans="1:2">
@@ -5414,7 +5411,7 @@
         <v>413</v>
       </c>
       <c r="B413" s="1">
-        <v>33.46362601783841</v>
+        <v>105.7691454336142</v>
       </c>
     </row>
     <row r="414" spans="1:2">
@@ -5422,7 +5419,7 @@
         <v>414</v>
       </c>
       <c r="B414" s="1">
-        <v>33.46348268198954</v>
+        <v>105.7690637093579</v>
       </c>
     </row>
     <row r="415" spans="1:2">
@@ -5430,7 +5427,7 @@
         <v>415</v>
       </c>
       <c r="B415" s="1">
-        <v>33.46271342619517</v>
+        <v>105.7642546526346</v>
       </c>
     </row>
     <row r="416" spans="1:2">
@@ -5438,7 +5435,7 @@
         <v>416</v>
       </c>
       <c r="B416" s="1">
-        <v>33.46230723242094</v>
+        <v>105.7641433702202</v>
       </c>
     </row>
     <row r="417" spans="1:2">
@@ -5446,7 +5443,7 @@
         <v>417</v>
       </c>
       <c r="B417" s="1">
-        <v>33.46209452766762</v>
+        <v>105.7528516468853</v>
       </c>
     </row>
     <row r="418" spans="1:2">
@@ -5454,7 +5451,7 @@
         <v>418</v>
       </c>
       <c r="B418" s="1">
-        <v>33.46184098098448</v>
+        <v>105.7253771669574</v>
       </c>
     </row>
     <row r="419" spans="1:2">
@@ -5462,7 +5459,7 @@
         <v>419</v>
       </c>
       <c r="B419" s="1">
-        <v>33.46170403733719</v>
+        <v>105.6833470828783</v>
       </c>
     </row>
     <row r="420" spans="1:2">
@@ -5470,7 +5467,7 @@
         <v>420</v>
       </c>
       <c r="B420" s="1">
-        <v>33.4611177588494</v>
+        <v>105.6738340462075</v>
       </c>
     </row>
     <row r="421" spans="1:2">
@@ -5478,7 +5475,7 @@
         <v>421</v>
       </c>
       <c r="B421" s="1">
-        <v>33.4604395144052</v>
+        <v>105.6320609090326</v>
       </c>
     </row>
     <row r="422" spans="1:2">
@@ -5486,7 +5483,7 @@
         <v>422</v>
       </c>
       <c r="B422" s="1">
-        <v>33.46039719042043</v>
+        <v>105.6300270460606</v>
       </c>
     </row>
     <row r="423" spans="1:2">
@@ -5494,7 +5491,7 @@
         <v>423</v>
       </c>
       <c r="B423" s="1">
-        <v>33.45965933306147</v>
+        <v>105.6142628094166</v>
       </c>
     </row>
     <row r="424" spans="1:2">
@@ -5502,7 +5499,7 @@
         <v>424</v>
       </c>
       <c r="B424" s="1">
-        <v>33.45928134527193</v>
+        <v>105.5925817345525</v>
       </c>
     </row>
     <row r="425" spans="1:2">
@@ -5510,7 +5507,7 @@
         <v>425</v>
       </c>
       <c r="B425" s="1">
-        <v>33.45816210963472</v>
+        <v>105.590896732892</v>
       </c>
     </row>
     <row r="426" spans="1:2">
@@ -5518,7 +5515,7 @@
         <v>426</v>
       </c>
       <c r="B426" s="1">
-        <v>33.45808617493937</v>
+        <v>105.5597458206934</v>
       </c>
     </row>
     <row r="427" spans="1:2">
@@ -5526,7 +5523,7 @@
         <v>427</v>
       </c>
       <c r="B427" s="1">
-        <v>33.4580561323577</v>
+        <v>105.5501452699919</v>
       </c>
     </row>
     <row r="428" spans="1:2">
@@ -5534,7 +5531,7 @@
         <v>428</v>
       </c>
       <c r="B428" s="1">
-        <v>33.45745581022231</v>
+        <v>105.5433583484362</v>
       </c>
     </row>
     <row r="429" spans="1:2">
@@ -5542,7 +5539,7 @@
         <v>429</v>
       </c>
       <c r="B429" s="1">
-        <v>33.45693639024253</v>
+        <v>105.5391966347814</v>
       </c>
     </row>
     <row r="430" spans="1:2">
@@ -5550,7 +5547,7 @@
         <v>430</v>
       </c>
       <c r="B430" s="1">
-        <v>33.45662261808949</v>
+        <v>105.5387883204472</v>
       </c>
     </row>
     <row r="431" spans="1:2">
@@ -5558,7 +5555,7 @@
         <v>431</v>
       </c>
       <c r="B431" s="1">
-        <v>33.45656244286562</v>
+        <v>105.5356675067985</v>
       </c>
     </row>
     <row r="432" spans="1:2">
@@ -5566,7 +5563,7 @@
         <v>432</v>
       </c>
       <c r="B432" s="1">
-        <v>33.45637200188909</v>
+        <v>105.5269522740494</v>
       </c>
     </row>
     <row r="433" spans="1:2">
@@ -5574,7 +5571,7 @@
         <v>433</v>
       </c>
       <c r="B433" s="1">
-        <v>33.45629994561346</v>
+        <v>105.5156212657483</v>
       </c>
     </row>
     <row r="434" spans="1:2">
@@ -5582,7 +5579,7 @@
         <v>434</v>
       </c>
       <c r="B434" s="1">
-        <v>33.45629919435431</v>
+        <v>105.5124577817305</v>
       </c>
     </row>
     <row r="435" spans="1:2">
@@ -5590,7 +5587,7 @@
         <v>435</v>
       </c>
       <c r="B435" s="1">
-        <v>33.45628897618948</v>
+        <v>105.5049401655169</v>
       </c>
     </row>
     <row r="436" spans="1:2">
@@ -5598,7 +5595,7 @@
         <v>436</v>
       </c>
       <c r="B436" s="1">
-        <v>33.45627602637884</v>
+        <v>105.4846625138025</v>
       </c>
     </row>
     <row r="437" spans="1:2">
@@ -5606,7 +5603,7 @@
         <v>437</v>
       </c>
       <c r="B437" s="1">
-        <v>33.45627436842241</v>
+        <v>105.474750790334</v>
       </c>
     </row>
     <row r="438" spans="1:2">
@@ -5614,7 +5611,7 @@
         <v>438</v>
       </c>
       <c r="B438" s="1">
-        <v>33.45605196481408</v>
+        <v>105.4503996394532</v>
       </c>
     </row>
     <row r="439" spans="1:2">
@@ -5622,7 +5619,7 @@
         <v>439</v>
       </c>
       <c r="B439" s="1">
-        <v>33.45582250722723</v>
+        <v>105.4329235796929</v>
       </c>
     </row>
     <row r="440" spans="1:2">
@@ -5630,7 +5627,7 @@
         <v>440</v>
       </c>
       <c r="B440" s="1">
-        <v>33.45578609689374</v>
+        <v>105.4253569561411</v>
       </c>
     </row>
     <row r="441" spans="1:2">
@@ -5638,7 +5635,7 @@
         <v>441</v>
       </c>
       <c r="B441" s="1">
-        <v>33.45452539859841</v>
+        <v>105.3817782762477</v>
       </c>
     </row>
     <row r="442" spans="1:2">
@@ -5646,7 +5643,7 @@
         <v>442</v>
       </c>
       <c r="B442" s="1">
-        <v>33.45442090920653</v>
+        <v>105.3807756364774</v>
       </c>
     </row>
     <row r="443" spans="1:2">
@@ -5654,7 +5651,7 @@
         <v>443</v>
       </c>
       <c r="B443" s="1">
-        <v>33.45398484168761</v>
+        <v>105.3355464761853</v>
       </c>
     </row>
     <row r="444" spans="1:2">
@@ -5662,7 +5659,7 @@
         <v>444</v>
       </c>
       <c r="B444" s="1">
-        <v>33.45389334360502</v>
+        <v>105.3263801789621</v>
       </c>
     </row>
     <row r="445" spans="1:2">
@@ -5670,7 +5667,7 @@
         <v>445</v>
       </c>
       <c r="B445" s="1">
-        <v>33.45326019105751</v>
+        <v>105.3260596216083</v>
       </c>
     </row>
     <row r="446" spans="1:2">
@@ -5678,7 +5675,7 @@
         <v>446</v>
       </c>
       <c r="B446" s="1">
-        <v>33.45277421571337</v>
+        <v>105.316717281498</v>
       </c>
     </row>
     <row r="447" spans="1:2">
@@ -5686,7 +5683,7 @@
         <v>447</v>
       </c>
       <c r="B447" s="1">
-        <v>33.45260372506853</v>
+        <v>105.3142264135533</v>
       </c>
     </row>
     <row r="448" spans="1:2">
@@ -5694,7 +5691,7 @@
         <v>448</v>
       </c>
       <c r="B448" s="1">
-        <v>33.45211374733393</v>
+        <v>105.3127864920982</v>
       </c>
     </row>
     <row r="449" spans="1:2">
@@ -5702,7 +5699,7 @@
         <v>449</v>
       </c>
       <c r="B449" s="1">
-        <v>33.45206394386697</v>
+        <v>105.2964935201929</v>
       </c>
     </row>
     <row r="450" spans="1:2">
@@ -5710,7 +5707,7 @@
         <v>450</v>
       </c>
       <c r="B450" s="1">
-        <v>33.45126341728317</v>
+        <v>105.2964609695569</v>
       </c>
     </row>
     <row r="451" spans="1:2">
@@ -5718,7 +5715,7 @@
         <v>451</v>
       </c>
       <c r="B451" s="1">
-        <v>33.45124015101256</v>
+        <v>105.2915371468971</v>
       </c>
     </row>
     <row r="452" spans="1:2">
@@ -5726,7 +5723,7 @@
         <v>452</v>
       </c>
       <c r="B452" s="1">
-        <v>33.45096577682036</v>
+        <v>105.2914569081252</v>
       </c>
     </row>
     <row r="453" spans="1:2">
@@ -5734,7 +5731,7 @@
         <v>453</v>
       </c>
       <c r="B453" s="1">
-        <v>33.45087212375289</v>
+        <v>105.2867653013711</v>
       </c>
     </row>
     <row r="454" spans="1:2">
@@ -5742,7 +5739,7 @@
         <v>454</v>
       </c>
       <c r="B454" s="1">
-        <v>33.45059813901428</v>
+        <v>105.269708664249</v>
       </c>
     </row>
     <row r="455" spans="1:2">
@@ -5750,7 +5747,7 @@
         <v>455</v>
       </c>
       <c r="B455" s="1">
-        <v>33.45056252751274</v>
+        <v>105.2640469378262</v>
       </c>
     </row>
     <row r="456" spans="1:2">
@@ -5758,7 +5755,7 @@
         <v>456</v>
       </c>
       <c r="B456" s="1">
-        <v>33.45053636990627</v>
+        <v>105.2596440240733</v>
       </c>
     </row>
     <row r="457" spans="1:2">
@@ -5766,7 +5763,7 @@
         <v>457</v>
       </c>
       <c r="B457" s="1">
-        <v>33.45031153138483</v>
+        <v>105.2538571513283</v>
       </c>
     </row>
     <row r="458" spans="1:2">
@@ -5774,7 +5771,7 @@
         <v>458</v>
       </c>
       <c r="B458" s="1">
-        <v>33.4497418099857</v>
+        <v>105.249754546407</v>
       </c>
     </row>
     <row r="459" spans="1:2">
@@ -5782,7 +5779,7 @@
         <v>459</v>
       </c>
       <c r="B459" s="1">
-        <v>33.44942323150682</v>
+        <v>105.2368477979764</v>
       </c>
     </row>
     <row r="460" spans="1:2">
@@ -5790,7 +5787,7 @@
         <v>460</v>
       </c>
       <c r="B460" s="1">
-        <v>33.4489897214881</v>
+        <v>105.2340327439779</v>
       </c>
     </row>
     <row r="461" spans="1:2">
@@ -5798,7 +5795,7 @@
         <v>461</v>
       </c>
       <c r="B461" s="1">
-        <v>33.44882695617908</v>
+        <v>105.1954139445809</v>
       </c>
     </row>
     <row r="462" spans="1:2">
@@ -5806,7 +5803,7 @@
         <v>462</v>
       </c>
       <c r="B462" s="1">
-        <v>33.44871484785744</v>
+        <v>105.1846871563601</v>
       </c>
     </row>
     <row r="463" spans="1:2">
@@ -5814,7 +5811,7 @@
         <v>463</v>
       </c>
       <c r="B463" s="1">
-        <v>33.44834392319669</v>
+        <v>105.153757045428</v>
       </c>
     </row>
     <row r="464" spans="1:2">
@@ -5822,7 +5819,7 @@
         <v>464</v>
       </c>
       <c r="B464" s="1">
-        <v>33.44773966440634</v>
+        <v>105.1355117495712</v>
       </c>
     </row>
     <row r="465" spans="1:2">
@@ -5830,7 +5827,7 @@
         <v>465</v>
       </c>
       <c r="B465" s="1">
-        <v>33.44741823151674</v>
+        <v>105.1201583447916</v>
       </c>
     </row>
     <row r="466" spans="1:2">
@@ -5838,7 +5835,7 @@
         <v>466</v>
       </c>
       <c r="B466" s="1">
-        <v>33.44734911908416</v>
+        <v>105.1188300795607</v>
       </c>
     </row>
     <row r="467" spans="1:2">
@@ -5846,7 +5843,7 @@
         <v>467</v>
       </c>
       <c r="B467" s="1">
-        <v>33.44727362037243</v>
+        <v>105.1080544329615</v>
       </c>
     </row>
     <row r="468" spans="1:2">
@@ -5854,7 +5851,7 @@
         <v>468</v>
       </c>
       <c r="B468" s="1">
-        <v>33.44650583271457</v>
+        <v>105.0972919185189</v>
       </c>
     </row>
     <row r="469" spans="1:2">
@@ -5862,7 +5859,7 @@
         <v>469</v>
       </c>
       <c r="B469" s="1">
-        <v>33.44644501348676</v>
+        <v>105.0932838041471</v>
       </c>
     </row>
     <row r="470" spans="1:2">
@@ -5870,7 +5867,7 @@
         <v>470</v>
       </c>
       <c r="B470" s="1">
-        <v>33.44635280999093</v>
+        <v>105.0697217721997</v>
       </c>
     </row>
     <row r="471" spans="1:2">
@@ -5878,7 +5875,7 @@
         <v>471</v>
       </c>
       <c r="B471" s="1">
-        <v>33.44586422782043</v>
+        <v>105.0577261019518</v>
       </c>
     </row>
     <row r="472" spans="1:2">
@@ -5886,7 +5883,7 @@
         <v>472</v>
       </c>
       <c r="B472" s="1">
-        <v>33.44570048699427</v>
+        <v>105.0537433431772</v>
       </c>
     </row>
     <row r="473" spans="1:2">
@@ -5894,7 +5891,7 @@
         <v>473</v>
       </c>
       <c r="B473" s="1">
-        <v>33.4451667254373</v>
+        <v>105.0402749845284</v>
       </c>
     </row>
     <row r="474" spans="1:2">
@@ -5902,7 +5899,7 @@
         <v>474</v>
       </c>
       <c r="B474" s="1">
-        <v>33.44492259000022</v>
+        <v>105.0374816235702</v>
       </c>
     </row>
     <row r="475" spans="1:2">
@@ -5910,7 +5907,7 @@
         <v>475</v>
       </c>
       <c r="B475" s="1">
-        <v>33.44481080723207</v>
+        <v>105.0371368667724</v>
       </c>
     </row>
     <row r="476" spans="1:2">
@@ -5918,7 +5915,7 @@
         <v>476</v>
       </c>
       <c r="B476" s="1">
-        <v>33.44453795893945</v>
+        <v>105.0285641264457</v>
       </c>
     </row>
     <row r="477" spans="1:2">
@@ -5926,7 +5923,7 @@
         <v>477</v>
       </c>
       <c r="B477" s="1">
-        <v>33.44452571698763</v>
+        <v>105.0226492214299</v>
       </c>
     </row>
     <row r="478" spans="1:2">
@@ -5934,7 +5931,7 @@
         <v>478</v>
       </c>
       <c r="B478" s="1">
-        <v>33.4440344403444</v>
+        <v>105.0169911734385</v>
       </c>
     </row>
     <row r="479" spans="1:2">
@@ -5942,7 +5939,7 @@
         <v>479</v>
       </c>
       <c r="B479" s="1">
-        <v>33.44377698086988</v>
+        <v>104.9983361047902</v>
       </c>
     </row>
     <row r="480" spans="1:2">
@@ -5950,7 +5947,7 @@
         <v>480</v>
       </c>
       <c r="B480" s="1">
-        <v>33.44357215398968</v>
+        <v>104.9749752944884</v>
       </c>
     </row>
     <row r="481" spans="1:2">
@@ -5958,7 +5955,7 @@
         <v>481</v>
       </c>
       <c r="B481" s="1">
-        <v>33.44239955934569</v>
+        <v>104.9689306974707</v>
       </c>
     </row>
     <row r="482" spans="1:2">
@@ -5966,7 +5963,7 @@
         <v>482</v>
       </c>
       <c r="B482" s="1">
-        <v>33.44193610167959</v>
+        <v>104.9682156581442</v>
       </c>
     </row>
     <row r="483" spans="1:2">
@@ -5974,7 +5971,7 @@
         <v>483</v>
       </c>
       <c r="B483" s="1">
-        <v>33.44181710531121</v>
+        <v>104.9641484064791</v>
       </c>
     </row>
     <row r="484" spans="1:2">
@@ -5982,7 +5979,7 @@
         <v>484</v>
       </c>
       <c r="B484" s="1">
-        <v>33.44165131212536</v>
+        <v>104.9534343260471</v>
       </c>
     </row>
     <row r="485" spans="1:2">
@@ -5990,7 +5987,7 @@
         <v>485</v>
       </c>
       <c r="B485" s="1">
-        <v>33.44163131056737</v>
+        <v>104.9363804970694</v>
       </c>
     </row>
     <row r="486" spans="1:2">
@@ -5998,7 +5995,7 @@
         <v>486</v>
       </c>
       <c r="B486" s="1">
-        <v>33.4413533983887</v>
+        <v>104.9358479984597</v>
       </c>
     </row>
     <row r="487" spans="1:2">
@@ -6006,7 +6003,7 @@
         <v>487</v>
       </c>
       <c r="B487" s="1">
-        <v>33.44123998957851</v>
+        <v>104.9145990447985</v>
       </c>
     </row>
     <row r="488" spans="1:2">
@@ -6014,7 +6011,7 @@
         <v>488</v>
       </c>
       <c r="B488" s="1">
-        <v>33.44110357558579</v>
+        <v>104.9032015618063</v>
       </c>
     </row>
     <row r="489" spans="1:2">
@@ -6022,7 +6019,7 @@
         <v>489</v>
       </c>
       <c r="B489" s="1">
-        <v>33.44110166880617</v>
+        <v>104.8876313994029</v>
       </c>
     </row>
     <row r="490" spans="1:2">
@@ -6030,7 +6027,7 @@
         <v>490</v>
       </c>
       <c r="B490" s="1">
-        <v>33.44098368512871</v>
+        <v>104.8827254535633</v>
       </c>
     </row>
     <row r="491" spans="1:2">
@@ -6038,7 +6035,7 @@
         <v>491</v>
       </c>
       <c r="B491" s="1">
-        <v>33.44040417939213</v>
+        <v>104.8787987073611</v>
       </c>
     </row>
     <row r="492" spans="1:2">
@@ -6046,7 +6043,7 @@
         <v>492</v>
       </c>
       <c r="B492" s="1">
-        <v>33.44027692487887</v>
+        <v>104.8776592748335</v>
       </c>
     </row>
     <row r="493" spans="1:2">
@@ -6054,7 +6051,7 @@
         <v>493</v>
       </c>
       <c r="B493" s="1">
-        <v>33.4402662605024</v>
+        <v>104.8641370378659</v>
       </c>
     </row>
     <row r="494" spans="1:2">
@@ -6062,7 +6059,7 @@
         <v>494</v>
       </c>
       <c r="B494" s="1">
-        <v>33.44019940167696</v>
+        <v>104.824823661886</v>
       </c>
     </row>
     <row r="495" spans="1:2">
@@ -6070,7 +6067,7 @@
         <v>495</v>
       </c>
       <c r="B495" s="1">
-        <v>33.43994279866465</v>
+        <v>104.8125569841868</v>
       </c>
     </row>
     <row r="496" spans="1:2">
@@ -6078,7 +6075,7 @@
         <v>496</v>
       </c>
       <c r="B496" s="1">
-        <v>33.43982071615302</v>
+        <v>104.8021554198291</v>
       </c>
     </row>
     <row r="497" spans="1:2">
@@ -6086,7 +6083,7 @@
         <v>497</v>
       </c>
       <c r="B497" s="1">
-        <v>33.43929399950996</v>
+        <v>104.7940804662536</v>
       </c>
     </row>
     <row r="498" spans="1:2">
@@ -6094,7 +6091,7 @@
         <v>498</v>
       </c>
       <c r="B498" s="1">
-        <v>33.43926073989009</v>
+        <v>104.7790180415666</v>
       </c>
     </row>
     <row r="499" spans="1:2">
@@ -6102,7 +6099,7 @@
         <v>499</v>
       </c>
       <c r="B499" s="1">
-        <v>33.43909446060663</v>
+        <v>104.76324824368</v>
       </c>
     </row>
     <row r="500" spans="1:2">
@@ -6110,7 +6107,7 @@
         <v>500</v>
       </c>
       <c r="B500" s="1">
-        <v>33.43881655258223</v>
+        <v>104.7540336455053</v>
       </c>
     </row>
     <row r="501" spans="1:2">
@@ -6118,7 +6115,7 @@
         <v>501</v>
       </c>
       <c r="B501" s="1">
-        <v>33.43864520617436</v>
+        <v>104.7227794095532</v>
       </c>
     </row>
     <row r="502" spans="1:2">
@@ -6126,7 +6123,7 @@
         <v>502</v>
       </c>
       <c r="B502" s="1">
-        <v>33.43823671277589</v>
+        <v>104.7144707645015</v>
       </c>
     </row>
     <row r="503" spans="1:2">
@@ -6134,7 +6131,7 @@
         <v>503</v>
       </c>
       <c r="B503" s="1">
-        <v>33.43804750130648</v>
+        <v>104.7105927984157</v>
       </c>
     </row>
     <row r="504" spans="1:2">
@@ -6142,7 +6139,7 @@
         <v>504</v>
       </c>
       <c r="B504" s="1">
-        <v>33.43722846694256</v>
+        <v>104.7012798177472</v>
       </c>
     </row>
     <row r="505" spans="1:2">
@@ -6150,7 +6147,7 @@
         <v>505</v>
       </c>
       <c r="B505" s="1">
-        <v>33.43719927902172</v>
+        <v>104.6677199945701</v>
       </c>
     </row>
     <row r="506" spans="1:2">
@@ -6158,7 +6155,7 @@
         <v>506</v>
       </c>
       <c r="B506" s="1">
-        <v>33.43698364457971</v>
+        <v>104.6647527521165</v>
       </c>
     </row>
     <row r="507" spans="1:2">
@@ -6166,7 +6163,7 @@
         <v>507</v>
       </c>
       <c r="B507" s="1">
-        <v>33.43693242451377</v>
+        <v>104.6105907564984</v>
       </c>
     </row>
     <row r="508" spans="1:2">
@@ -6174,7 +6171,7 @@
         <v>508</v>
       </c>
       <c r="B508" s="1">
-        <v>33.43683014000708</v>
+        <v>104.6078701905604</v>
       </c>
     </row>
     <row r="509" spans="1:2">
@@ -6182,7 +6179,7 @@
         <v>509</v>
       </c>
       <c r="B509" s="1">
-        <v>33.43641727006803</v>
+        <v>104.6029773116609</v>
       </c>
     </row>
     <row r="510" spans="1:2">
@@ -6190,7 +6187,7 @@
         <v>510</v>
       </c>
       <c r="B510" s="1">
-        <v>33.43641307717014</v>
+        <v>104.6019201800173</v>
       </c>
     </row>
     <row r="511" spans="1:2">
@@ -6198,7 +6195,7 @@
         <v>511</v>
       </c>
       <c r="B511" s="1">
-        <v>33.43589898695337</v>
+        <v>104.5899628472441</v>
       </c>
     </row>
     <row r="512" spans="1:2">
@@ -6206,7 +6203,7 @@
         <v>512</v>
       </c>
       <c r="B512" s="1">
-        <v>33.43531250938636</v>
+        <v>104.585397094434</v>
       </c>
     </row>
     <row r="513" spans="1:2">
@@ -6214,7 +6211,7 @@
         <v>513</v>
       </c>
       <c r="B513" s="1">
-        <v>33.43498142712208</v>
+        <v>104.5833041116294</v>
       </c>
     </row>
     <row r="514" spans="1:2">
@@ -6222,7 +6219,7 @@
         <v>514</v>
       </c>
       <c r="B514" s="1">
-        <v>33.43476580031274</v>
+        <v>104.5788526104039</v>
       </c>
     </row>
     <row r="515" spans="1:2">
@@ -6230,7 +6227,7 @@
         <v>515</v>
       </c>
       <c r="B515" s="1">
-        <v>33.43460640367353</v>
+        <v>104.5740334147221</v>
       </c>
     </row>
     <row r="516" spans="1:2">
@@ -6238,7 +6235,7 @@
         <v>516</v>
       </c>
       <c r="B516" s="1">
-        <v>33.43460107902755</v>
+        <v>104.5726792610435</v>
       </c>
     </row>
     <row r="517" spans="1:2">
@@ -6246,7 +6243,7 @@
         <v>517</v>
       </c>
       <c r="B517" s="1">
-        <v>33.43445132868265</v>
+        <v>104.5689609783173</v>
       </c>
     </row>
     <row r="518" spans="1:2">
@@ -6254,7 +6251,7 @@
         <v>518</v>
       </c>
       <c r="B518" s="1">
-        <v>33.43443718976762</v>
+        <v>104.5532716952552</v>
       </c>
     </row>
     <row r="519" spans="1:2">
@@ -6262,7 +6259,7 @@
         <v>519</v>
       </c>
       <c r="B519" s="1">
-        <v>33.43391558985112</v>
+        <v>104.5488146529737</v>
       </c>
     </row>
     <row r="520" spans="1:2">
@@ -6270,7 +6267,7 @@
         <v>520</v>
       </c>
       <c r="B520" s="1">
-        <v>33.43384938394491</v>
+        <v>104.5297710479697</v>
       </c>
     </row>
     <row r="521" spans="1:2">
@@ -6278,7 +6275,7 @@
         <v>521</v>
       </c>
       <c r="B521" s="1">
-        <v>33.43383174112847</v>
+        <v>104.5276214320399</v>
       </c>
     </row>
     <row r="522" spans="1:2">
@@ -6286,7 +6283,7 @@
         <v>522</v>
       </c>
       <c r="B522" s="1">
-        <v>33.43378607082433</v>
+        <v>104.5212869185219</v>
       </c>
     </row>
     <row r="523" spans="1:2">
@@ -6294,7 +6291,7 @@
         <v>523</v>
       </c>
       <c r="B523" s="1">
-        <v>33.43362122545026</v>
+        <v>104.5212119210419</v>
       </c>
     </row>
     <row r="524" spans="1:2">
@@ -6302,7 +6299,7 @@
         <v>524</v>
       </c>
       <c r="B524" s="1">
-        <v>33.43346234885209</v>
+        <v>104.5134124012375</v>
       </c>
     </row>
     <row r="525" spans="1:2">
@@ -6310,7 +6307,7 @@
         <v>525</v>
       </c>
       <c r="B525" s="1">
-        <v>33.43318069927589</v>
+        <v>104.4824037553939</v>
       </c>
     </row>
     <row r="526" spans="1:2">
@@ -6318,7 +6315,7 @@
         <v>526</v>
       </c>
       <c r="B526" s="1">
-        <v>33.43288280099128</v>
+        <v>104.4721302335236</v>
       </c>
     </row>
     <row r="527" spans="1:2">
@@ -6326,7 +6323,7 @@
         <v>527</v>
       </c>
       <c r="B527" s="1">
-        <v>33.4327298776052</v>
+        <v>104.4692056608185</v>
       </c>
     </row>
     <row r="528" spans="1:2">
@@ -6334,7 +6331,7 @@
         <v>528</v>
       </c>
       <c r="B528" s="1">
-        <v>33.43244144860932</v>
+        <v>104.452407617793</v>
       </c>
     </row>
     <row r="529" spans="1:2">
@@ -6342,7 +6339,7 @@
         <v>529</v>
       </c>
       <c r="B529" s="1">
-        <v>33.43235851455147</v>
+        <v>104.4477874183478</v>
       </c>
     </row>
     <row r="530" spans="1:2">
@@ -6350,7 +6347,7 @@
         <v>530</v>
       </c>
       <c r="B530" s="1">
-        <v>33.43226807524141</v>
+        <v>104.4259659851831</v>
       </c>
     </row>
     <row r="531" spans="1:2">
@@ -6358,7 +6355,7 @@
         <v>531</v>
       </c>
       <c r="B531" s="1">
-        <v>33.43201907675337</v>
+        <v>104.3991760439085</v>
       </c>
     </row>
     <row r="532" spans="1:2">
@@ -6366,7 +6363,7 @@
         <v>532</v>
       </c>
       <c r="B532" s="1">
-        <v>33.43194841555246</v>
+        <v>104.3671669632064</v>
       </c>
     </row>
     <row r="533" spans="1:2">
@@ -6374,7 +6371,7 @@
         <v>533</v>
       </c>
       <c r="B533" s="1">
-        <v>33.43180531876926</v>
+        <v>104.3625564994703</v>
       </c>
     </row>
     <row r="534" spans="1:2">
@@ -6382,7 +6379,7 @@
         <v>534</v>
       </c>
       <c r="B534" s="1">
-        <v>33.43172516019835</v>
+        <v>104.3438028323874</v>
       </c>
     </row>
     <row r="535" spans="1:2">
@@ -6390,7 +6387,7 @@
         <v>535</v>
       </c>
       <c r="B535" s="1">
-        <v>33.43147991531752</v>
+        <v>104.3260812741813</v>
       </c>
     </row>
     <row r="536" spans="1:2">
@@ -6398,7 +6395,7 @@
         <v>536</v>
       </c>
       <c r="B536" s="1">
-        <v>33.43119163936947</v>
+        <v>104.325574406182</v>
       </c>
     </row>
     <row r="537" spans="1:2">
@@ -6406,7 +6403,7 @@
         <v>537</v>
       </c>
       <c r="B537" s="1">
-        <v>33.43077378644661</v>
+        <v>104.2855710858858</v>
       </c>
     </row>
     <row r="538" spans="1:2">
@@ -6414,7 +6411,7 @@
         <v>538</v>
       </c>
       <c r="B538" s="1">
-        <v>33.43054076206211</v>
+        <v>104.2836718536628</v>
       </c>
     </row>
     <row r="539" spans="1:2">
@@ -6422,7 +6419,7 @@
         <v>539</v>
       </c>
       <c r="B539" s="1">
-        <v>33.43046415653582</v>
+        <v>104.2689329825687</v>
       </c>
     </row>
     <row r="540" spans="1:2">
@@ -6430,7 +6427,7 @@
         <v>540</v>
       </c>
       <c r="B540" s="1">
-        <v>33.43037933227902</v>
+        <v>104.2622397188512</v>
       </c>
     </row>
     <row r="541" spans="1:2">
@@ -6438,7 +6435,7 @@
         <v>541</v>
       </c>
       <c r="B541" s="1">
-        <v>33.43009082722605</v>
+        <v>104.2592688209265</v>
       </c>
     </row>
     <row r="542" spans="1:2">
@@ -6446,7 +6443,7 @@
         <v>542</v>
       </c>
       <c r="B542" s="1">
-        <v>33.42953617447929</v>
+        <v>104.2524720047183</v>
       </c>
     </row>
     <row r="543" spans="1:2">
@@ -6454,7 +6451,7 @@
         <v>543</v>
       </c>
       <c r="B543" s="1">
-        <v>33.42914257993684</v>
+        <v>104.2423252263393</v>
       </c>
     </row>
     <row r="544" spans="1:2">
@@ -6462,7 +6459,7 @@
         <v>544</v>
       </c>
       <c r="B544" s="1">
-        <v>33.42871296433835</v>
+        <v>104.2423080802134</v>
       </c>
     </row>
     <row r="545" spans="1:2">
@@ -6470,7 +6467,7 @@
         <v>545</v>
       </c>
       <c r="B545" s="1">
-        <v>33.42814102534907</v>
+        <v>104.2246981705942</v>
       </c>
     </row>
     <row r="546" spans="1:2">
@@ -6478,7 +6475,7 @@
         <v>546</v>
       </c>
       <c r="B546" s="1">
-        <v>33.42784033389722</v>
+        <v>104.2234440216869</v>
       </c>
     </row>
     <row r="547" spans="1:2">
@@ -6486,7 +6483,7 @@
         <v>547</v>
       </c>
       <c r="B547" s="1">
-        <v>33.42766144905583</v>
+        <v>104.2214179717905</v>
       </c>
     </row>
     <row r="548" spans="1:2">
@@ -6494,7 +6491,7 @@
         <v>548</v>
       </c>
       <c r="B548" s="1">
-        <v>33.42756170409078</v>
+        <v>104.2002655514064</v>
       </c>
     </row>
     <row r="549" spans="1:2">
@@ -6502,7 +6499,7 @@
         <v>549</v>
       </c>
       <c r="B549" s="1">
-        <v>33.42705816111207</v>
+        <v>104.1793347949875</v>
       </c>
     </row>
     <row r="550" spans="1:2">
@@ -6510,7 +6507,7 @@
         <v>550</v>
       </c>
       <c r="B550" s="1">
-        <v>33.42678284656984</v>
+        <v>104.1528677209773</v>
       </c>
     </row>
     <row r="551" spans="1:2">
@@ -6518,7 +6515,7 @@
         <v>551</v>
       </c>
       <c r="B551" s="1">
-        <v>33.42671096144898</v>
+        <v>104.1445565557657</v>
       </c>
     </row>
     <row r="552" spans="1:2">
@@ -6526,7 +6523,7 @@
         <v>552</v>
       </c>
       <c r="B552" s="1">
-        <v>33.42664886091029</v>
+        <v>104.1421732062791</v>
       </c>
     </row>
     <row r="553" spans="1:2">
@@ -6534,7 +6531,7 @@
         <v>553</v>
       </c>
       <c r="B553" s="1">
-        <v>33.42657037513349</v>
+        <v>104.1395030582384</v>
       </c>
     </row>
     <row r="554" spans="1:2">
@@ -6542,7 +6539,7 @@
         <v>554</v>
       </c>
       <c r="B554" s="1">
-        <v>33.42638665004073</v>
+        <v>104.1253516766168</v>
       </c>
     </row>
     <row r="555" spans="1:2">
@@ -6550,7 +6547,7 @@
         <v>555</v>
       </c>
       <c r="B555" s="1">
-        <v>33.4263706312558</v>
+        <v>104.1247545601137</v>
       </c>
     </row>
     <row r="556" spans="1:2">
@@ -6558,7 +6555,7 @@
         <v>556</v>
       </c>
       <c r="B556" s="1">
-        <v>33.42546290367241</v>
+        <v>104.1211538199461</v>
       </c>
     </row>
     <row r="557" spans="1:2">
@@ -6566,7 +6563,7 @@
         <v>557</v>
       </c>
       <c r="B557" s="1">
-        <v>33.4244838355808</v>
+        <v>104.1164208348171</v>
       </c>
     </row>
     <row r="558" spans="1:2">
@@ -6574,7 +6571,7 @@
         <v>558</v>
       </c>
       <c r="B558" s="1">
-        <v>33.42424842958649</v>
+        <v>104.0919780259055</v>
       </c>
     </row>
     <row r="559" spans="1:2">
@@ -6582,7 +6579,7 @@
         <v>559</v>
       </c>
       <c r="B559" s="1">
-        <v>33.42409272385215</v>
+        <v>104.0903699561253</v>
       </c>
     </row>
     <row r="560" spans="1:2">
@@ -6590,7 +6587,7 @@
         <v>560</v>
       </c>
       <c r="B560" s="1">
-        <v>33.42349865978355</v>
+        <v>104.069585179571</v>
       </c>
     </row>
     <row r="561" spans="1:2">
@@ -6598,7 +6595,7 @@
         <v>561</v>
       </c>
       <c r="B561" s="1">
-        <v>33.42339191783386</v>
+        <v>104.0324901232109</v>
       </c>
     </row>
     <row r="562" spans="1:2">
@@ -6606,7 +6603,7 @@
         <v>562</v>
       </c>
       <c r="B562" s="1">
-        <v>33.42319142586498</v>
+        <v>104.0295253215012</v>
       </c>
     </row>
     <row r="563" spans="1:2">
@@ -6614,7 +6611,7 @@
         <v>563</v>
       </c>
       <c r="B563" s="1">
-        <v>33.42311612282665</v>
+        <v>104.0109540297533</v>
       </c>
     </row>
     <row r="564" spans="1:2">
@@ -6622,7 +6619,7 @@
         <v>564</v>
       </c>
       <c r="B564" s="1">
-        <v>33.42305628857152</v>
+        <v>104.0056765299979</v>
       </c>
     </row>
     <row r="565" spans="1:2">
@@ -6630,7 +6627,7 @@
         <v>565</v>
       </c>
       <c r="B565" s="1">
-        <v>33.42296585951996</v>
+        <v>103.9906091120605</v>
       </c>
     </row>
     <row r="566" spans="1:2">
@@ -6638,7 +6635,7 @@
         <v>566</v>
       </c>
       <c r="B566" s="1">
-        <v>33.42286148363105</v>
+        <v>103.9694122601321</v>
       </c>
     </row>
     <row r="567" spans="1:2">
@@ -6646,7 +6643,7 @@
         <v>567</v>
       </c>
       <c r="B567" s="1">
-        <v>33.42282627281778</v>
+        <v>103.9584158826622</v>
       </c>
     </row>
     <row r="568" spans="1:2">
@@ -6654,7 +6651,7 @@
         <v>568</v>
       </c>
       <c r="B568" s="1">
-        <v>33.42221769654681</v>
+        <v>103.9530684995897</v>
       </c>
     </row>
     <row r="569" spans="1:2">
@@ -6662,7 +6659,7 @@
         <v>569</v>
       </c>
       <c r="B569" s="1">
-        <v>33.42204527139312</v>
+        <v>103.9518237598984</v>
       </c>
     </row>
     <row r="570" spans="1:2">
@@ -6670,7 +6667,7 @@
         <v>570</v>
       </c>
       <c r="B570" s="1">
-        <v>33.42184124678826</v>
+        <v>103.9297470794348</v>
       </c>
     </row>
     <row r="571" spans="1:2">
@@ -6678,7 +6675,7 @@
         <v>571</v>
       </c>
       <c r="B571" s="1">
-        <v>33.42169654580277</v>
+        <v>103.9252773627429</v>
       </c>
     </row>
     <row r="572" spans="1:2">
@@ -6686,7 +6683,7 @@
         <v>572</v>
       </c>
       <c r="B572" s="1">
-        <v>33.42146877830172</v>
+        <v>103.8849970395448</v>
       </c>
     </row>
     <row r="573" spans="1:2">
@@ -6694,7 +6691,7 @@
         <v>573</v>
       </c>
       <c r="B573" s="1">
-        <v>33.42141153223691</v>
+        <v>103.8786584810623</v>
       </c>
     </row>
     <row r="574" spans="1:2">
@@ -6702,7 +6699,7 @@
         <v>574</v>
       </c>
       <c r="B574" s="1">
-        <v>33.42133786442258</v>
+        <v>103.8503344101329</v>
       </c>
     </row>
     <row r="575" spans="1:2">
@@ -6710,7 +6707,7 @@
         <v>575</v>
       </c>
       <c r="B575" s="1">
-        <v>33.42122608859736</v>
+        <v>103.8442376617699</v>
       </c>
     </row>
     <row r="576" spans="1:2">
@@ -6718,7 +6715,7 @@
         <v>576</v>
       </c>
       <c r="B576" s="1">
-        <v>33.4210272535982</v>
+        <v>103.8319716327929</v>
       </c>
     </row>
     <row r="577" spans="1:2">
@@ -6726,7 +6723,7 @@
         <v>577</v>
       </c>
       <c r="B577" s="1">
-        <v>33.4206423923605</v>
+        <v>103.8246007506221</v>
       </c>
     </row>
     <row r="578" spans="1:2">
@@ -6734,7 +6731,7 @@
         <v>578</v>
       </c>
       <c r="B578" s="1">
-        <v>33.42056655100343</v>
+        <v>103.8212301082223</v>
       </c>
     </row>
     <row r="579" spans="1:2">
@@ -6742,7 +6739,7 @@
         <v>579</v>
       </c>
       <c r="B579" s="1">
-        <v>33.41985402707143</v>
+        <v>103.8198198116002</v>
       </c>
     </row>
     <row r="580" spans="1:2">
@@ -6750,15 +6747,7 @@
         <v>580</v>
       </c>
       <c r="B580" s="1">
-        <v>33.41970438779525</v>
-      </c>
-    </row>
-    <row r="581" spans="1:2">
-      <c r="A581" t="s">
-        <v>581</v>
-      </c>
-      <c r="B581" s="1">
-        <v>33.41886860744412</v>
+        <v>103.7993642657749</v>
       </c>
     </row>
   </sheetData>

--- a/Screener/data/rs_rating_top_30.xlsx
+++ b/Screener/data/rs_rating_top_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="582">
   <si>
     <t>Symbol</t>
   </si>
@@ -22,1741 +22,1744 @@
     <t>RS Rating</t>
   </si>
   <si>
+    <t>SGTX</t>
+  </si>
+  <si>
+    <t>GRPN</t>
+  </si>
+  <si>
+    <t>TSAT</t>
+  </si>
+  <si>
+    <t>USM</t>
+  </si>
+  <si>
+    <t>TDS</t>
+  </si>
+  <si>
+    <t>AAOI</t>
+  </si>
+  <si>
     <t>EDTX</t>
   </si>
   <si>
-    <t>USM</t>
-  </si>
-  <si>
     <t>EDTXU</t>
   </si>
   <si>
-    <t>TDS</t>
-  </si>
-  <si>
-    <t>TSAT</t>
-  </si>
-  <si>
-    <t>SGTX</t>
-  </si>
-  <si>
-    <t>AAOI</t>
-  </si>
-  <si>
-    <t>GRPN</t>
+    <t>ML</t>
+  </si>
+  <si>
+    <t>DLO</t>
+  </si>
+  <si>
+    <t>URGN</t>
+  </si>
+  <si>
+    <t>CPRI</t>
+  </si>
+  <si>
+    <t>APP</t>
+  </si>
+  <si>
+    <t>BBIO</t>
   </si>
   <si>
     <t>CDLX</t>
   </si>
   <si>
-    <t>URGN</t>
-  </si>
-  <si>
-    <t>CPRI</t>
-  </si>
-  <si>
-    <t>APP</t>
+    <t>RETA</t>
+  </si>
+  <si>
+    <t>STRL</t>
+  </si>
+  <si>
+    <t>ANF</t>
+  </si>
+  <si>
+    <t>VRT</t>
+  </si>
+  <si>
+    <t>RYTM</t>
+  </si>
+  <si>
+    <t>SBOW</t>
+  </si>
+  <si>
+    <t>CAMT</t>
+  </si>
+  <si>
+    <t>PARR</t>
+  </si>
+  <si>
+    <t>BOOM</t>
+  </si>
+  <si>
+    <t>UPWK</t>
   </si>
   <si>
     <t>LMB</t>
   </si>
   <si>
-    <t>RETA</t>
-  </si>
-  <si>
-    <t>CAMT</t>
-  </si>
-  <si>
-    <t>ML</t>
-  </si>
-  <si>
-    <t>DLO</t>
-  </si>
-  <si>
-    <t>ANF</t>
-  </si>
-  <si>
-    <t>STRL</t>
-  </si>
-  <si>
-    <t>BBIO</t>
-  </si>
-  <si>
-    <t>BOOM</t>
-  </si>
-  <si>
-    <t>SBOW</t>
-  </si>
-  <si>
-    <t>UPWK</t>
-  </si>
-  <si>
-    <t>PARR</t>
+    <t>PHVS</t>
   </si>
   <si>
     <t>FSTR</t>
   </si>
   <si>
+    <t>CWCO</t>
+  </si>
+  <si>
+    <t>ESTE</t>
+  </si>
+  <si>
+    <t>SENEA</t>
+  </si>
+  <si>
+    <t>GAMB</t>
+  </si>
+  <si>
+    <t>TPL</t>
+  </si>
+  <si>
+    <t>CELH</t>
+  </si>
+  <si>
+    <t>PETQ</t>
+  </si>
+  <si>
+    <t>VRTV</t>
+  </si>
+  <si>
+    <t>LEAT</t>
+  </si>
+  <si>
+    <t>MMYT</t>
+  </si>
+  <si>
+    <t>SENEB</t>
+  </si>
+  <si>
+    <t>PAY</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>XPEV</t>
+  </si>
+  <si>
+    <t>CORT</t>
+  </si>
+  <si>
+    <t>CLS</t>
+  </si>
+  <si>
+    <t>CTRN</t>
+  </si>
+  <si>
+    <t>KRT</t>
+  </si>
+  <si>
+    <t>LLY</t>
+  </si>
+  <si>
+    <t>LYTS</t>
+  </si>
+  <si>
+    <t>CKX</t>
+  </si>
+  <si>
+    <t>CBAY</t>
+  </si>
+  <si>
+    <t>SOVO</t>
+  </si>
+  <si>
+    <t>ACMR</t>
+  </si>
+  <si>
+    <t>ERIE</t>
+  </si>
+  <si>
+    <t>IDYA</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>RELY</t>
+  </si>
+  <si>
+    <t>NATR</t>
+  </si>
+  <si>
+    <t>ANIP</t>
+  </si>
+  <si>
     <t>IESC</t>
   </si>
   <si>
-    <t>CBAY</t>
-  </si>
-  <si>
-    <t>TPL</t>
-  </si>
-  <si>
-    <t>PETQ</t>
-  </si>
-  <si>
-    <t>SENEA</t>
-  </si>
-  <si>
-    <t>CLS</t>
-  </si>
-  <si>
-    <t>CTRN</t>
-  </si>
-  <si>
-    <t>VRTV</t>
+    <t>CEIX</t>
+  </si>
+  <si>
+    <t>KD</t>
+  </si>
+  <si>
+    <t>ESEA</t>
+  </si>
+  <si>
+    <t>FN</t>
+  </si>
+  <si>
+    <t>GHM</t>
+  </si>
+  <si>
+    <t>POWL</t>
+  </si>
+  <si>
+    <t>AEO</t>
+  </si>
+  <si>
+    <t>HWKN</t>
+  </si>
+  <si>
+    <t>MNSO</t>
+  </si>
+  <si>
+    <t>ARGX</t>
+  </si>
+  <si>
+    <t>MOD</t>
+  </si>
+  <si>
+    <t>CVNA</t>
+  </si>
+  <si>
+    <t>OBT</t>
+  </si>
+  <si>
+    <t>CMT</t>
+  </si>
+  <si>
+    <t>HRB</t>
+  </si>
+  <si>
+    <t>SM</t>
+  </si>
+  <si>
+    <t>DCBO</t>
   </si>
   <si>
     <t>LEU</t>
   </si>
   <si>
-    <t>SENEB</t>
-  </si>
-  <si>
-    <t>LEAT</t>
-  </si>
-  <si>
-    <t>ESTE</t>
-  </si>
-  <si>
-    <t>PAY</t>
-  </si>
-  <si>
-    <t>PHVS</t>
-  </si>
-  <si>
-    <t>VRT</t>
-  </si>
-  <si>
-    <t>KRT</t>
-  </si>
-  <si>
-    <t>RYTM</t>
-  </si>
-  <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>ACMR</t>
-  </si>
-  <si>
-    <t>MMYT</t>
-  </si>
-  <si>
-    <t>FN</t>
+    <t>PRDO</t>
+  </si>
+  <si>
+    <t>AZTA</t>
+  </si>
+  <si>
+    <t>FSLY</t>
+  </si>
+  <si>
+    <t>SRDX</t>
+  </si>
+  <si>
+    <t>STER</t>
+  </si>
+  <si>
+    <t>COUR</t>
+  </si>
+  <si>
+    <t>RVMD</t>
+  </si>
+  <si>
+    <t>ITRN</t>
+  </si>
+  <si>
+    <t>TWIN</t>
+  </si>
+  <si>
+    <t>NVO</t>
+  </si>
+  <si>
+    <t>FRHC</t>
+  </si>
+  <si>
+    <t>MTSI</t>
+  </si>
+  <si>
+    <t>RNGR</t>
+  </si>
+  <si>
+    <t>TH</t>
+  </si>
+  <si>
+    <t>CSTL</t>
+  </si>
+  <si>
+    <t>YETI</t>
+  </si>
+  <si>
+    <t>BKI</t>
+  </si>
+  <si>
+    <t>WMPN</t>
+  </si>
+  <si>
+    <t>AMR</t>
+  </si>
+  <si>
+    <t>UBS</t>
+  </si>
+  <si>
+    <t>EDU</t>
+  </si>
+  <si>
+    <t>MPC</t>
+  </si>
+  <si>
+    <t>BBW</t>
+  </si>
+  <si>
+    <t>AURC</t>
+  </si>
+  <si>
+    <t>VNO</t>
+  </si>
+  <si>
+    <t>BFST</t>
+  </si>
+  <si>
+    <t>CNX</t>
+  </si>
+  <si>
+    <t>TW</t>
+  </si>
+  <si>
+    <t>FORG</t>
+  </si>
+  <si>
+    <t>SCPL</t>
+  </si>
+  <si>
+    <t>PDS</t>
   </si>
   <si>
     <t>WLDN</t>
   </si>
   <si>
-    <t>GAMB</t>
-  </si>
-  <si>
-    <t>CORT</t>
-  </si>
-  <si>
-    <t>LYTS</t>
-  </si>
-  <si>
-    <t>MNSO</t>
-  </si>
-  <si>
-    <t>KD</t>
-  </si>
-  <si>
-    <t>SOVO</t>
-  </si>
-  <si>
-    <t>MOD</t>
-  </si>
-  <si>
-    <t>AEO</t>
-  </si>
-  <si>
-    <t>CELH</t>
-  </si>
-  <si>
-    <t>ERIE</t>
-  </si>
-  <si>
-    <t>IDYA</t>
-  </si>
-  <si>
-    <t>OBT</t>
-  </si>
-  <si>
-    <t>LLY</t>
-  </si>
-  <si>
-    <t>PRDO</t>
-  </si>
-  <si>
-    <t>CMT</t>
-  </si>
-  <si>
-    <t>RELY</t>
-  </si>
-  <si>
-    <t>ANIP</t>
-  </si>
-  <si>
-    <t>CWCO</t>
-  </si>
-  <si>
-    <t>GHM</t>
-  </si>
-  <si>
-    <t>CEIX</t>
-  </si>
-  <si>
-    <t>SM</t>
-  </si>
-  <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>NATR</t>
-  </si>
-  <si>
-    <t>SRDX</t>
-  </si>
-  <si>
-    <t>DCBO</t>
-  </si>
-  <si>
-    <t>ARGX</t>
-  </si>
-  <si>
-    <t>TWIN</t>
-  </si>
-  <si>
-    <t>RNGR</t>
+    <t>FRSH</t>
+  </si>
+  <si>
+    <t>XPRO</t>
+  </si>
+  <si>
+    <t>WFRD</t>
+  </si>
+  <si>
+    <t>ARRY</t>
+  </si>
+  <si>
+    <t>HEP</t>
+  </si>
+  <si>
+    <t>VERX</t>
+  </si>
+  <si>
+    <t>CRC</t>
+  </si>
+  <si>
+    <t>TRNS</t>
+  </si>
+  <si>
+    <t>REX</t>
+  </si>
+  <si>
+    <t>ACU</t>
+  </si>
+  <si>
+    <t>QCRH</t>
+  </si>
+  <si>
+    <t>PAR</t>
+  </si>
+  <si>
+    <t>CALB</t>
+  </si>
+  <si>
+    <t>TRUP</t>
+  </si>
+  <si>
+    <t>INOD</t>
+  </si>
+  <si>
+    <t>NEWR</t>
+  </si>
+  <si>
+    <t>SMMF</t>
   </si>
   <si>
     <t>CSPI</t>
   </si>
   <si>
-    <t>HWKN</t>
-  </si>
-  <si>
-    <t>POWL</t>
-  </si>
-  <si>
-    <t>HRB</t>
-  </si>
-  <si>
-    <t>UBS</t>
-  </si>
-  <si>
-    <t>AMR</t>
-  </si>
-  <si>
-    <t>BKI</t>
-  </si>
-  <si>
-    <t>NVO</t>
+    <t>WAL</t>
+  </si>
+  <si>
+    <t>NOA</t>
+  </si>
+  <si>
+    <t>AROC</t>
+  </si>
+  <si>
+    <t>FETM</t>
+  </si>
+  <si>
+    <t>FRO</t>
+  </si>
+  <si>
+    <t>AMNB</t>
   </si>
   <si>
     <t>SHEN</t>
   </si>
   <si>
+    <t>RCUS</t>
+  </si>
+  <si>
+    <t>NHC</t>
+  </si>
+  <si>
+    <t>SFBS</t>
+  </si>
+  <si>
+    <t>EME</t>
+  </si>
+  <si>
+    <t>PBF</t>
+  </si>
+  <si>
+    <t>CDRE</t>
+  </si>
+  <si>
+    <t>BRBR</t>
+  </si>
+  <si>
+    <t>FOR</t>
+  </si>
+  <si>
+    <t>AKAM</t>
+  </si>
+  <si>
+    <t>XPO</t>
+  </si>
+  <si>
+    <t>TALO</t>
+  </si>
+  <si>
+    <t>QLYS</t>
+  </si>
+  <si>
+    <t>VRNS</t>
+  </si>
+  <si>
+    <t>BWMX</t>
+  </si>
+  <si>
+    <t>WMG</t>
+  </si>
+  <si>
+    <t>CIVI</t>
+  </si>
+  <si>
+    <t>PSN</t>
+  </si>
+  <si>
+    <t>VLO</t>
+  </si>
+  <si>
+    <t>CLW</t>
+  </si>
+  <si>
+    <t>CABA</t>
+  </si>
+  <si>
+    <t>FLXS</t>
+  </si>
+  <si>
+    <t>GIC</t>
+  </si>
+  <si>
+    <t>PRA</t>
+  </si>
+  <si>
+    <t>SLG</t>
+  </si>
+  <si>
+    <t>EXEL</t>
+  </si>
+  <si>
+    <t>OVV</t>
+  </si>
+  <si>
     <t>NRP</t>
   </si>
   <si>
-    <t>PDS</t>
-  </si>
-  <si>
-    <t>VNO</t>
-  </si>
-  <si>
-    <t>TH</t>
-  </si>
-  <si>
-    <t>BBW</t>
-  </si>
-  <si>
-    <t>ACU</t>
-  </si>
-  <si>
-    <t>MPC</t>
-  </si>
-  <si>
-    <t>MTSI</t>
-  </si>
-  <si>
-    <t>XPRO</t>
-  </si>
-  <si>
-    <t>STER</t>
-  </si>
-  <si>
-    <t>ITRN</t>
-  </si>
-  <si>
-    <t>YETI</t>
-  </si>
-  <si>
-    <t>WFRD</t>
-  </si>
-  <si>
-    <t>EDU</t>
-  </si>
-  <si>
-    <t>TW</t>
-  </si>
-  <si>
-    <t>PAR</t>
-  </si>
-  <si>
-    <t>FORG</t>
-  </si>
-  <si>
-    <t>ESEA</t>
-  </si>
-  <si>
-    <t>AZTA</t>
-  </si>
-  <si>
-    <t>XPO</t>
-  </si>
-  <si>
-    <t>AURC</t>
-  </si>
-  <si>
-    <t>FOR</t>
-  </si>
-  <si>
-    <t>BFST</t>
+    <t>GNE</t>
+  </si>
+  <si>
+    <t>CCJ</t>
+  </si>
+  <si>
+    <t>VST</t>
+  </si>
+  <si>
+    <t>AFBI</t>
+  </si>
+  <si>
+    <t>APA</t>
+  </si>
+  <si>
+    <t>JOE</t>
+  </si>
+  <si>
+    <t>IONQ</t>
+  </si>
+  <si>
+    <t>PRMW</t>
+  </si>
+  <si>
+    <t>OSIS</t>
+  </si>
+  <si>
+    <t>ENLC</t>
+  </si>
+  <si>
+    <t>BR</t>
+  </si>
+  <si>
+    <t>ALRM</t>
   </si>
   <si>
     <t>NTRA</t>
   </si>
   <si>
-    <t>FRHC</t>
-  </si>
-  <si>
-    <t>SCPL</t>
-  </si>
-  <si>
-    <t>WMPN</t>
-  </si>
-  <si>
-    <t>WAL</t>
-  </si>
-  <si>
-    <t>CALB</t>
-  </si>
-  <si>
-    <t>NHC</t>
-  </si>
-  <si>
-    <t>COUR</t>
-  </si>
-  <si>
-    <t>CNX</t>
-  </si>
-  <si>
-    <t>TRNS</t>
-  </si>
-  <si>
-    <t>QCRH</t>
-  </si>
-  <si>
-    <t>HEP</t>
-  </si>
-  <si>
-    <t>AMNB</t>
-  </si>
-  <si>
-    <t>OSIS</t>
-  </si>
-  <si>
-    <t>NEWR</t>
-  </si>
-  <si>
-    <t>AROC</t>
-  </si>
-  <si>
-    <t>CRC</t>
+    <t>NCR</t>
+  </si>
+  <si>
+    <t>AURCU</t>
+  </si>
+  <si>
+    <t>NWLI</t>
+  </si>
+  <si>
+    <t>AZZ</t>
+  </si>
+  <si>
+    <t>HURN</t>
+  </si>
+  <si>
+    <t>HIBB</t>
+  </si>
+  <si>
+    <t>PSX</t>
+  </si>
+  <si>
+    <t>CPTP</t>
+  </si>
+  <si>
+    <t>MTDR</t>
+  </si>
+  <si>
+    <t>SAIA</t>
+  </si>
+  <si>
+    <t>RPD</t>
+  </si>
+  <si>
+    <t>ACAD</t>
+  </si>
+  <si>
+    <t>CFBK</t>
+  </si>
+  <si>
+    <t>PBNK</t>
+  </si>
+  <si>
+    <t>INSW</t>
+  </si>
+  <si>
+    <t>CCOI</t>
+  </si>
+  <si>
+    <t>AMGN</t>
+  </si>
+  <si>
+    <t>NOV</t>
+  </si>
+  <si>
+    <t>OPCH</t>
+  </si>
+  <si>
+    <t>SPLK</t>
+  </si>
+  <si>
+    <t>DWAC</t>
+  </si>
+  <si>
+    <t>ODC</t>
+  </si>
+  <si>
+    <t>ROCK</t>
+  </si>
+  <si>
+    <t>COSO</t>
+  </si>
+  <si>
+    <t>CHTR</t>
+  </si>
+  <si>
+    <t>HAS</t>
+  </si>
+  <si>
+    <t>PRIM</t>
+  </si>
+  <si>
+    <t>TWNK</t>
+  </si>
+  <si>
+    <t>PLUS</t>
+  </si>
+  <si>
+    <t>ODFL</t>
+  </si>
+  <si>
+    <t>DLR</t>
+  </si>
+  <si>
+    <t>ARLP</t>
   </si>
   <si>
     <t>LAUR</t>
   </si>
   <si>
-    <t>NOA</t>
-  </si>
-  <si>
-    <t>SAIA</t>
-  </si>
-  <si>
-    <t>RCUS</t>
-  </si>
-  <si>
-    <t>INSW</t>
-  </si>
-  <si>
-    <t>CSTL</t>
-  </si>
-  <si>
-    <t>NCR</t>
-  </si>
-  <si>
-    <t>VERX</t>
-  </si>
-  <si>
-    <t>SFBS</t>
-  </si>
-  <si>
-    <t>AMGN</t>
-  </si>
-  <si>
-    <t>CIVI</t>
+    <t>RAMP</t>
+  </si>
+  <si>
+    <t>FTAI</t>
+  </si>
+  <si>
+    <t>SMLR</t>
+  </si>
+  <si>
+    <t>AMEH</t>
+  </si>
+  <si>
+    <t>ARCE</t>
+  </si>
+  <si>
+    <t>BCSF</t>
+  </si>
+  <si>
+    <t>STEP</t>
+  </si>
+  <si>
+    <t>EURN</t>
+  </si>
+  <si>
+    <t>JAZZ</t>
+  </si>
+  <si>
+    <t>REGN</t>
   </si>
   <si>
     <t>GES</t>
   </si>
   <si>
-    <t>WMG</t>
-  </si>
-  <si>
-    <t>JOE</t>
-  </si>
-  <si>
-    <t>BWMX</t>
-  </si>
-  <si>
-    <t>EME</t>
-  </si>
-  <si>
-    <t>SLG</t>
-  </si>
-  <si>
-    <t>FLXS</t>
-  </si>
-  <si>
-    <t>VST</t>
-  </si>
-  <si>
-    <t>APA</t>
-  </si>
-  <si>
-    <t>GIC</t>
-  </si>
-  <si>
-    <t>RVMD</t>
+    <t>DAWN</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>MRTX</t>
+  </si>
+  <si>
+    <t>DGICB</t>
+  </si>
+  <si>
+    <t>INBK</t>
+  </si>
+  <si>
+    <t>BG</t>
+  </si>
+  <si>
+    <t>TFII</t>
+  </si>
+  <si>
+    <t>NARI</t>
+  </si>
+  <si>
+    <t>LIVE</t>
+  </si>
+  <si>
+    <t>HNI</t>
+  </si>
+  <si>
+    <t>MAT</t>
+  </si>
+  <si>
+    <t>MLR</t>
+  </si>
+  <si>
+    <t>LOB</t>
+  </si>
+  <si>
+    <t>HOFT</t>
+  </si>
+  <si>
+    <t>SU</t>
+  </si>
+  <si>
+    <t>AIT</t>
+  </si>
+  <si>
+    <t>BNTX</t>
+  </si>
+  <si>
+    <t>ASTE</t>
+  </si>
+  <si>
+    <t>RDY</t>
+  </si>
+  <si>
+    <t>WHD</t>
+  </si>
+  <si>
+    <t>FSFG</t>
+  </si>
+  <si>
+    <t>BCC</t>
+  </si>
+  <si>
+    <t>HOLI</t>
+  </si>
+  <si>
+    <t>NXGN</t>
+  </si>
+  <si>
+    <t>MLAB</t>
+  </si>
+  <si>
+    <t>NOG</t>
+  </si>
+  <si>
+    <t>ADP</t>
+  </si>
+  <si>
+    <t>ETN</t>
+  </si>
+  <si>
+    <t>WIX</t>
   </si>
   <si>
     <t>CAAP</t>
   </si>
   <si>
-    <t>PSN</t>
-  </si>
-  <si>
-    <t>FTAI</t>
-  </si>
-  <si>
-    <t>STEP</t>
-  </si>
-  <si>
-    <t>INOD</t>
-  </si>
-  <si>
-    <t>AZZ</t>
-  </si>
-  <si>
-    <t>AFBI</t>
-  </si>
-  <si>
-    <t>OVV</t>
-  </si>
-  <si>
-    <t>MTDR</t>
-  </si>
-  <si>
-    <t>FRO</t>
-  </si>
-  <si>
-    <t>CDRE</t>
-  </si>
-  <si>
-    <t>NOV</t>
-  </si>
-  <si>
-    <t>RAMP</t>
-  </si>
-  <si>
-    <t>FSLY</t>
-  </si>
-  <si>
-    <t>BCC</t>
-  </si>
-  <si>
-    <t>BRBR</t>
-  </si>
-  <si>
-    <t>PRMW</t>
-  </si>
-  <si>
-    <t>ARRY</t>
-  </si>
-  <si>
-    <t>TALO</t>
-  </si>
-  <si>
-    <t>BR</t>
+    <t>SBFG</t>
+  </si>
+  <si>
+    <t>MOH</t>
+  </si>
+  <si>
+    <t>TIPT</t>
+  </si>
+  <si>
+    <t>ATR</t>
+  </si>
+  <si>
+    <t>AGM</t>
+  </si>
+  <si>
+    <t>VALU</t>
+  </si>
+  <si>
+    <t>GPN</t>
+  </si>
+  <si>
+    <t>HCCI</t>
+  </si>
+  <si>
+    <t>CVBF</t>
+  </si>
+  <si>
+    <t>AEL</t>
+  </si>
+  <si>
+    <t>SAM</t>
+  </si>
+  <si>
+    <t>INTU</t>
+  </si>
+  <si>
+    <t>IBKR</t>
+  </si>
+  <si>
+    <t>ATEX</t>
+  </si>
+  <si>
+    <t>NBIX</t>
+  </si>
+  <si>
+    <t>SAL</t>
+  </si>
+  <si>
+    <t>STRA</t>
+  </si>
+  <si>
+    <t>SPOK</t>
+  </si>
+  <si>
+    <t>AZPN</t>
+  </si>
+  <si>
+    <t>LOGI</t>
+  </si>
+  <si>
+    <t>MUR</t>
+  </si>
+  <si>
+    <t>FWRG</t>
+  </si>
+  <si>
+    <t>CDW</t>
+  </si>
+  <si>
+    <t>HALO</t>
+  </si>
+  <si>
+    <t>FRPT</t>
+  </si>
+  <si>
+    <t>MNMB</t>
+  </si>
+  <si>
+    <t>WWE</t>
+  </si>
+  <si>
+    <t>ANET</t>
+  </si>
+  <si>
+    <t>PAM</t>
+  </si>
+  <si>
+    <t>FFNW</t>
+  </si>
+  <si>
+    <t>SFM</t>
+  </si>
+  <si>
+    <t>PBAM</t>
+  </si>
+  <si>
+    <t>AR</t>
+  </si>
+  <si>
+    <t>PSFE</t>
+  </si>
+  <si>
+    <t>CNXN</t>
+  </si>
+  <si>
+    <t>MGRC</t>
+  </si>
+  <si>
+    <t>PRGO</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>KNSA</t>
+  </si>
+  <si>
+    <t>ESCA</t>
+  </si>
+  <si>
+    <t>STNG</t>
+  </si>
+  <si>
+    <t>MLKN</t>
+  </si>
+  <si>
+    <t>CHX</t>
+  </si>
+  <si>
+    <t>DBRG</t>
+  </si>
+  <si>
+    <t>TRGP</t>
+  </si>
+  <si>
+    <t>CRVL</t>
+  </si>
+  <si>
+    <t>EVI</t>
+  </si>
+  <si>
+    <t>ARBV</t>
+  </si>
+  <si>
+    <t>MEDP</t>
+  </si>
+  <si>
+    <t>SIM</t>
+  </si>
+  <si>
+    <t>CW</t>
+  </si>
+  <si>
+    <t>SXI</t>
+  </si>
+  <si>
+    <t>ERF</t>
+  </si>
+  <si>
+    <t>IMO</t>
+  </si>
+  <si>
+    <t>LBRDA</t>
+  </si>
+  <si>
+    <t>NECB</t>
+  </si>
+  <si>
+    <t>CSWI</t>
+  </si>
+  <si>
+    <t>TNET</t>
+  </si>
+  <si>
+    <t>BBSI</t>
+  </si>
+  <si>
+    <t>WOR</t>
+  </si>
+  <si>
+    <t>AFRM</t>
+  </si>
+  <si>
+    <t>CFNB</t>
+  </si>
+  <si>
+    <t>WSM</t>
+  </si>
+  <si>
+    <t>CSCO</t>
+  </si>
+  <si>
+    <t>ROST</t>
+  </si>
+  <si>
+    <t>FANG</t>
+  </si>
+  <si>
+    <t>VAL</t>
+  </si>
+  <si>
+    <t>VMW</t>
+  </si>
+  <si>
+    <t>ARVN</t>
+  </si>
+  <si>
+    <t>CFST</t>
+  </si>
+  <si>
+    <t>NE</t>
+  </si>
+  <si>
+    <t>JILL</t>
+  </si>
+  <si>
+    <t>TNP</t>
+  </si>
+  <si>
+    <t>GBDC</t>
+  </si>
+  <si>
+    <t>VICR</t>
+  </si>
+  <si>
+    <t>ACT</t>
+  </si>
+  <si>
+    <t>ARCT</t>
+  </si>
+  <si>
+    <t>LRN</t>
+  </si>
+  <si>
+    <t>HCM</t>
+  </si>
+  <si>
+    <t>ALPN</t>
+  </si>
+  <si>
+    <t>ATGE</t>
+  </si>
+  <si>
+    <t>RPM</t>
+  </si>
+  <si>
+    <t>LBRDK</t>
+  </si>
+  <si>
+    <t>TDW</t>
+  </si>
+  <si>
+    <t>DK</t>
+  </si>
+  <si>
+    <t>FUTU</t>
+  </si>
+  <si>
+    <t>CBOE</t>
+  </si>
+  <si>
+    <t>JXN</t>
+  </si>
+  <si>
+    <t>MUSA</t>
+  </si>
+  <si>
+    <t>PXD</t>
+  </si>
+  <si>
+    <t>CENT</t>
+  </si>
+  <si>
+    <t>PGR</t>
+  </si>
+  <si>
+    <t>CPRX</t>
+  </si>
+  <si>
+    <t>MANU</t>
+  </si>
+  <si>
+    <t>COCO</t>
+  </si>
+  <si>
+    <t>FIX</t>
+  </si>
+  <si>
+    <t>BHWB</t>
+  </si>
+  <si>
+    <t>ASND</t>
+  </si>
+  <si>
+    <t>SRV</t>
+  </si>
+  <si>
+    <t>ORRF</t>
+  </si>
+  <si>
+    <t>DRQ</t>
+  </si>
+  <si>
+    <t>RYAN</t>
+  </si>
+  <si>
+    <t>NYT</t>
+  </si>
+  <si>
+    <t>BRO</t>
+  </si>
+  <si>
+    <t>OLN</t>
+  </si>
+  <si>
+    <t>AUBN</t>
+  </si>
+  <si>
+    <t>STRT</t>
+  </si>
+  <si>
+    <t>OSK</t>
+  </si>
+  <si>
+    <t>AE</t>
+  </si>
+  <si>
+    <t>SPB</t>
+  </si>
+  <si>
+    <t>AZEK</t>
+  </si>
+  <si>
+    <t>FTI</t>
+  </si>
+  <si>
+    <t>SCSC</t>
+  </si>
+  <si>
+    <t>R</t>
   </si>
   <si>
     <t>DVAX</t>
   </si>
   <si>
-    <t>PBNK</t>
-  </si>
-  <si>
-    <t>INBK</t>
-  </si>
-  <si>
-    <t>HURN</t>
-  </si>
-  <si>
-    <t>PRA</t>
-  </si>
-  <si>
-    <t>VALU</t>
-  </si>
-  <si>
-    <t>DLR</t>
-  </si>
-  <si>
-    <t>GNE</t>
-  </si>
-  <si>
-    <t>ROCK</t>
-  </si>
-  <si>
-    <t>AKAM</t>
-  </si>
-  <si>
-    <t>PAM</t>
-  </si>
-  <si>
-    <t>FRSH</t>
-  </si>
-  <si>
-    <t>HALO</t>
-  </si>
-  <si>
-    <t>CABA</t>
-  </si>
-  <si>
-    <t>ENLC</t>
-  </si>
-  <si>
-    <t>CCOI</t>
-  </si>
-  <si>
-    <t>QLYS</t>
-  </si>
-  <si>
-    <t>COSO</t>
-  </si>
-  <si>
-    <t>AMEH</t>
-  </si>
-  <si>
-    <t>ODFL</t>
-  </si>
-  <si>
-    <t>ACAD</t>
-  </si>
-  <si>
-    <t>RDY</t>
-  </si>
-  <si>
-    <t>TDW</t>
-  </si>
-  <si>
-    <t>FSFG</t>
-  </si>
-  <si>
-    <t>SXI</t>
-  </si>
-  <si>
-    <t>LOB</t>
-  </si>
-  <si>
-    <t>FETM</t>
-  </si>
-  <si>
-    <t>ASTE</t>
-  </si>
-  <si>
-    <t>AURCU</t>
-  </si>
-  <si>
-    <t>PBF</t>
-  </si>
-  <si>
-    <t>EXEL</t>
-  </si>
-  <si>
-    <t>VICR</t>
+    <t>CVRX</t>
+  </si>
+  <si>
+    <t>ICFI</t>
+  </si>
+  <si>
+    <t>CME</t>
+  </si>
+  <si>
+    <t>FMX</t>
+  </si>
+  <si>
+    <t>TRMD</t>
+  </si>
+  <si>
+    <t>SCHL</t>
+  </si>
+  <si>
+    <t>FLT</t>
+  </si>
+  <si>
+    <t>BKNG</t>
+  </si>
+  <si>
+    <t>AVTR</t>
+  </si>
+  <si>
+    <t>CIGI</t>
+  </si>
+  <si>
+    <t>DHACU</t>
+  </si>
+  <si>
+    <t>KTB</t>
+  </si>
+  <si>
+    <t>EVBN</t>
+  </si>
+  <si>
+    <t>ZGN</t>
+  </si>
+  <si>
+    <t>HQY</t>
+  </si>
+  <si>
+    <t>BSRR</t>
+  </si>
+  <si>
+    <t>VECO</t>
+  </si>
+  <si>
+    <t>FNF</t>
+  </si>
+  <si>
+    <t>SSD</t>
+  </si>
+  <si>
+    <t>BDX</t>
+  </si>
+  <si>
+    <t>COP</t>
+  </si>
+  <si>
+    <t>YELP</t>
+  </si>
+  <si>
+    <t>KT</t>
+  </si>
+  <si>
+    <t>MBWM</t>
+  </si>
+  <si>
+    <t>LQDT</t>
+  </si>
+  <si>
+    <t>UNF</t>
+  </si>
+  <si>
+    <t>SRPT</t>
+  </si>
+  <si>
+    <t>DELL</t>
+  </si>
+  <si>
+    <t>CMCSA</t>
+  </si>
+  <si>
+    <t>SPFI</t>
+  </si>
+  <si>
+    <t>FRSB</t>
+  </si>
+  <si>
+    <t>GPOR</t>
+  </si>
+  <si>
+    <t>EMR</t>
+  </si>
+  <si>
+    <t>APOG</t>
+  </si>
+  <si>
+    <t>AVNW</t>
+  </si>
+  <si>
+    <t>CLMT</t>
+  </si>
+  <si>
+    <t>SBS</t>
+  </si>
+  <si>
+    <t>ODP</t>
+  </si>
+  <si>
+    <t>SPNS</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>CSWC</t>
+  </si>
+  <si>
+    <t>TJX</t>
+  </si>
+  <si>
+    <t>MGPI</t>
+  </si>
+  <si>
+    <t>CENTA</t>
+  </si>
+  <si>
+    <t>SAH</t>
+  </si>
+  <si>
+    <t>WDAY</t>
   </si>
   <si>
     <t>BOH</t>
   </si>
   <si>
-    <t>CCJ</t>
-  </si>
-  <si>
-    <t>VLO</t>
-  </si>
-  <si>
-    <t>TFII</t>
-  </si>
-  <si>
-    <t>CFBK</t>
-  </si>
-  <si>
-    <t>MNMB</t>
-  </si>
-  <si>
-    <t>XPEV</t>
-  </si>
-  <si>
-    <t>BNTX</t>
-  </si>
-  <si>
-    <t>AGM</t>
-  </si>
-  <si>
-    <t>EVI</t>
-  </si>
-  <si>
-    <t>PSX</t>
-  </si>
-  <si>
-    <t>WHD</t>
-  </si>
-  <si>
-    <t>REGN</t>
-  </si>
-  <si>
-    <t>EURN</t>
-  </si>
-  <si>
-    <t>ODC</t>
-  </si>
-  <si>
-    <t>BKNG</t>
+    <t>CEN</t>
+  </si>
+  <si>
+    <t>CHKP</t>
+  </si>
+  <si>
+    <t>BMI</t>
+  </si>
+  <si>
+    <t>TRDA</t>
+  </si>
+  <si>
+    <t>IHG</t>
+  </si>
+  <si>
+    <t>HLNE</t>
+  </si>
+  <si>
+    <t>CTRA</t>
+  </si>
+  <si>
+    <t>BUR</t>
   </si>
   <si>
     <t>IPI</t>
   </si>
   <si>
-    <t>ARCE</t>
-  </si>
-  <si>
-    <t>OPCH</t>
-  </si>
-  <si>
-    <t>SU</t>
-  </si>
-  <si>
-    <t>FFNW</t>
-  </si>
-  <si>
-    <t>PRIM</t>
-  </si>
-  <si>
-    <t>CNXN</t>
-  </si>
-  <si>
-    <t>HNI</t>
-  </si>
-  <si>
-    <t>RPD</t>
-  </si>
-  <si>
-    <t>TIPT</t>
-  </si>
-  <si>
-    <t>J</t>
-  </si>
-  <si>
-    <t>GPN</t>
-  </si>
-  <si>
-    <t>BCSF</t>
-  </si>
-  <si>
-    <t>PLUS</t>
-  </si>
-  <si>
-    <t>STNG</t>
-  </si>
-  <si>
-    <t>SMMF</t>
-  </si>
-  <si>
-    <t>MOH</t>
-  </si>
-  <si>
-    <t>SAL</t>
-  </si>
-  <si>
-    <t>ICFI</t>
-  </si>
-  <si>
-    <t>IONQ</t>
-  </si>
-  <si>
-    <t>ALRM</t>
-  </si>
-  <si>
-    <t>CVBF</t>
-  </si>
-  <si>
-    <t>TRUP</t>
-  </si>
-  <si>
-    <t>MUR</t>
-  </si>
-  <si>
-    <t>FNF</t>
-  </si>
-  <si>
-    <t>AEL</t>
-  </si>
-  <si>
-    <t>ESCA</t>
-  </si>
-  <si>
-    <t>IMO</t>
-  </si>
-  <si>
-    <t>SAM</t>
+    <t>INFY</t>
+  </si>
+  <si>
+    <t>VRE</t>
+  </si>
+  <si>
+    <t>PAGP</t>
+  </si>
+  <si>
+    <t>IEX</t>
+  </si>
+  <si>
+    <t>WLK</t>
+  </si>
+  <si>
+    <t>WTM</t>
+  </si>
+  <si>
+    <t>WAYN</t>
+  </si>
+  <si>
+    <t>HES</t>
+  </si>
+  <si>
+    <t>BCO</t>
+  </si>
+  <si>
+    <t>JHX</t>
+  </si>
+  <si>
+    <t>ARCH</t>
+  </si>
+  <si>
+    <t>MSA</t>
+  </si>
+  <si>
+    <t>ANDE</t>
+  </si>
+  <si>
+    <t>LPLA</t>
+  </si>
+  <si>
+    <t>SFBC</t>
+  </si>
+  <si>
+    <t>NEU</t>
+  </si>
+  <si>
+    <t>QTRX</t>
+  </si>
+  <si>
+    <t>MRCY</t>
+  </si>
+  <si>
+    <t>IBM</t>
+  </si>
+  <si>
+    <t>CQP</t>
   </si>
   <si>
     <t>DCOM</t>
   </si>
   <si>
-    <t>TRGP</t>
-  </si>
-  <si>
-    <t>JAZZ</t>
-  </si>
-  <si>
-    <t>BG</t>
-  </si>
-  <si>
-    <t>HCCI</t>
+    <t>ANAB</t>
+  </si>
+  <si>
+    <t>CWAN</t>
+  </si>
+  <si>
+    <t>ATVI</t>
+  </si>
+  <si>
+    <t>NWS</t>
+  </si>
+  <si>
+    <t>ARL</t>
+  </si>
+  <si>
+    <t>LII</t>
   </si>
   <si>
     <t>CVLG</t>
   </si>
   <si>
-    <t>CHTR</t>
-  </si>
-  <si>
-    <t>CHX</t>
-  </si>
-  <si>
-    <t>TRDA</t>
-  </si>
-  <si>
-    <t>PRGO</t>
-  </si>
-  <si>
-    <t>DFH</t>
-  </si>
-  <si>
-    <t>HOFT</t>
-  </si>
-  <si>
-    <t>NWLI</t>
-  </si>
-  <si>
-    <t>MGRC</t>
-  </si>
-  <si>
-    <t>TNP</t>
-  </si>
-  <si>
-    <t>NXGN</t>
-  </si>
-  <si>
-    <t>DELL</t>
-  </si>
-  <si>
-    <t>AIT</t>
-  </si>
-  <si>
-    <t>ERF</t>
-  </si>
-  <si>
-    <t>CFNB</t>
-  </si>
-  <si>
-    <t>FRPT</t>
-  </si>
-  <si>
-    <t>MLR</t>
-  </si>
-  <si>
-    <t>KNSA</t>
-  </si>
-  <si>
-    <t>DAWN</t>
-  </si>
-  <si>
-    <t>AZEK</t>
-  </si>
-  <si>
-    <t>CW</t>
-  </si>
-  <si>
-    <t>ARCH</t>
-  </si>
-  <si>
-    <t>ARBV</t>
+    <t>LOPE</t>
+  </si>
+  <si>
+    <t>ZTS</t>
+  </si>
+  <si>
+    <t>PAA</t>
+  </si>
+  <si>
+    <t>ASGN</t>
+  </si>
+  <si>
+    <t>BKR</t>
+  </si>
+  <si>
+    <t>SVBT</t>
+  </si>
+  <si>
+    <t>MET</t>
+  </si>
+  <si>
+    <t>CAT</t>
+  </si>
+  <si>
+    <t>CAE</t>
+  </si>
+  <si>
+    <t>HFBL</t>
+  </si>
+  <si>
+    <t>AJG</t>
   </si>
   <si>
     <t>CIBH</t>
   </si>
   <si>
-    <t>WWE</t>
-  </si>
-  <si>
-    <t>KTB</t>
-  </si>
-  <si>
-    <t>SPB</t>
-  </si>
-  <si>
-    <t>MLKN</t>
-  </si>
-  <si>
-    <t>SMLR</t>
-  </si>
-  <si>
-    <t>PDCO</t>
-  </si>
-  <si>
-    <t>BBSI</t>
-  </si>
-  <si>
-    <t>HOLI</t>
-  </si>
-  <si>
-    <t>CBOE</t>
-  </si>
-  <si>
-    <t>ANET</t>
-  </si>
-  <si>
-    <t>COCO</t>
-  </si>
-  <si>
-    <t>GBDC</t>
-  </si>
-  <si>
-    <t>NTIC</t>
-  </si>
-  <si>
-    <t>BHWB</t>
-  </si>
-  <si>
-    <t>NARI</t>
-  </si>
-  <si>
-    <t>DOMO</t>
-  </si>
-  <si>
-    <t>ATEX</t>
+    <t>ABBV</t>
+  </si>
+  <si>
+    <t>HUM</t>
+  </si>
+  <si>
+    <t>OLLI</t>
+  </si>
+  <si>
+    <t>ICLR</t>
+  </si>
+  <si>
+    <t>MDRX</t>
+  </si>
+  <si>
+    <t>TCBI</t>
+  </si>
+  <si>
+    <t>SWTX</t>
+  </si>
+  <si>
+    <t>BROS</t>
+  </si>
+  <si>
+    <t>TCBX</t>
+  </si>
+  <si>
+    <t>ABM</t>
+  </si>
+  <si>
+    <t>AIF</t>
+  </si>
+  <si>
+    <t>KEX</t>
+  </si>
+  <si>
+    <t>CVE</t>
+  </si>
+  <si>
+    <t>NSIT</t>
+  </si>
+  <si>
+    <t>NVMI</t>
+  </si>
+  <si>
+    <t>HZNP</t>
+  </si>
+  <si>
+    <t>ABCM</t>
+  </si>
+  <si>
+    <t>LBRT</t>
+  </si>
+  <si>
+    <t>ALOT</t>
+  </si>
+  <si>
+    <t>CMUV</t>
+  </si>
+  <si>
+    <t>CPNG</t>
+  </si>
+  <si>
+    <t>BSFO</t>
+  </si>
+  <si>
+    <t>OZ</t>
+  </si>
+  <si>
+    <t>MORN</t>
+  </si>
+  <si>
+    <t>TXT</t>
+  </si>
+  <si>
+    <t>VABK</t>
+  </si>
+  <si>
+    <t>NDAQ</t>
+  </si>
+  <si>
+    <t>CALM</t>
+  </si>
+  <si>
+    <t>NREF</t>
+  </si>
+  <si>
+    <t>JDVB</t>
+  </si>
+  <si>
+    <t>PRO</t>
+  </si>
+  <si>
+    <t>WST</t>
+  </si>
+  <si>
+    <t>GKOS</t>
+  </si>
+  <si>
+    <t>ESE</t>
+  </si>
+  <si>
+    <t>MTG</t>
+  </si>
+  <si>
+    <t>MSCI</t>
+  </si>
+  <si>
+    <t>ENSG</t>
+  </si>
+  <si>
+    <t>HAL</t>
+  </si>
+  <si>
+    <t>BLX</t>
+  </si>
+  <si>
+    <t>MAR</t>
+  </si>
+  <si>
+    <t>AXON</t>
+  </si>
+  <si>
+    <t>COKE</t>
+  </si>
+  <si>
+    <t>SFST</t>
+  </si>
+  <si>
+    <t>LDOS</t>
+  </si>
+  <si>
+    <t>COLL</t>
+  </si>
+  <si>
+    <t>TEAM</t>
+  </si>
+  <si>
+    <t>MYFW</t>
+  </si>
+  <si>
+    <t>EOG</t>
+  </si>
+  <si>
+    <t>DCPH</t>
+  </si>
+  <si>
+    <t>DIT</t>
+  </si>
+  <si>
+    <t>ZION</t>
+  </si>
+  <si>
+    <t>NWSA</t>
+  </si>
+  <si>
+    <t>CNQ</t>
+  </si>
+  <si>
+    <t>CCB</t>
+  </si>
+  <si>
+    <t>MKL</t>
   </si>
   <si>
     <t>FLR</t>
   </si>
   <si>
+    <t>FNWB</t>
+  </si>
+  <si>
+    <t>TTE</t>
+  </si>
+  <si>
+    <t>MATX</t>
+  </si>
+  <si>
+    <t>RMR</t>
+  </si>
+  <si>
+    <t>OII</t>
+  </si>
+  <si>
+    <t>EIC</t>
+  </si>
+  <si>
+    <t>AXNX</t>
+  </si>
+  <si>
+    <t>CIR</t>
+  </si>
+  <si>
+    <t>KNSL</t>
+  </si>
+  <si>
+    <t>BGR</t>
+  </si>
+  <si>
+    <t>DHR</t>
+  </si>
+  <si>
+    <t>WMB</t>
+  </si>
+  <si>
+    <t>HAYW</t>
+  </si>
+  <si>
+    <t>KCLI</t>
+  </si>
+  <si>
+    <t>IR</t>
+  </si>
+  <si>
+    <t>GOOG</t>
+  </si>
+  <si>
+    <t>DDS</t>
+  </si>
+  <si>
+    <t>NOMD</t>
+  </si>
+  <si>
+    <t>FICO</t>
+  </si>
+  <si>
+    <t>MMC</t>
+  </si>
+  <si>
+    <t>RGEN</t>
+  </si>
+  <si>
+    <t>GLOB</t>
+  </si>
+  <si>
+    <t>PHG</t>
+  </si>
+  <si>
+    <t>HLF</t>
+  </si>
+  <si>
+    <t>DJCO</t>
+  </si>
+  <si>
+    <t>PWR</t>
+  </si>
+  <si>
+    <t>TS</t>
+  </si>
+  <si>
     <t>PPC</t>
   </si>
   <si>
-    <t>STRT</t>
-  </si>
-  <si>
-    <t>NOG</t>
-  </si>
-  <si>
-    <t>PBAM</t>
-  </si>
-  <si>
-    <t>ETN</t>
-  </si>
-  <si>
-    <t>GPOR</t>
-  </si>
-  <si>
-    <t>ADP</t>
-  </si>
-  <si>
-    <t>NBIX</t>
-  </si>
-  <si>
-    <t>YELP</t>
-  </si>
-  <si>
-    <t>KTOS</t>
-  </si>
-  <si>
-    <t>SPOK</t>
-  </si>
-  <si>
-    <t>STRA</t>
-  </si>
-  <si>
-    <t>CLW</t>
-  </si>
-  <si>
-    <t>JXN</t>
-  </si>
-  <si>
-    <t>ACT</t>
-  </si>
-  <si>
-    <t>VRNS</t>
-  </si>
-  <si>
-    <t>ROST</t>
-  </si>
-  <si>
-    <t>PXD</t>
-  </si>
-  <si>
-    <t>FANG</t>
-  </si>
-  <si>
-    <t>DBRG</t>
-  </si>
-  <si>
-    <t>ARLP</t>
-  </si>
-  <si>
-    <t>SCSC</t>
-  </si>
-  <si>
-    <t>ATGE</t>
-  </si>
-  <si>
-    <t>TNET</t>
-  </si>
-  <si>
-    <t>SPLK</t>
-  </si>
-  <si>
-    <t>LOPE</t>
-  </si>
-  <si>
-    <t>LRN</t>
-  </si>
-  <si>
-    <t>ORRF</t>
-  </si>
-  <si>
-    <t>MBWM</t>
-  </si>
-  <si>
-    <t>TRMD</t>
-  </si>
-  <si>
-    <t>PSFE</t>
-  </si>
-  <si>
-    <t>FRD</t>
-  </si>
-  <si>
-    <t>NE</t>
-  </si>
-  <si>
-    <t>R</t>
-  </si>
-  <si>
-    <t>NREF</t>
-  </si>
-  <si>
-    <t>CFST</t>
-  </si>
-  <si>
-    <t>FWRG</t>
-  </si>
-  <si>
-    <t>AVTR</t>
-  </si>
-  <si>
-    <t>AR</t>
-  </si>
-  <si>
-    <t>SBS</t>
-  </si>
-  <si>
-    <t>ZION</t>
-  </si>
-  <si>
-    <t>LOGI</t>
-  </si>
-  <si>
-    <t>FIX</t>
-  </si>
-  <si>
-    <t>SPNS</t>
-  </si>
-  <si>
-    <t>DGICB</t>
-  </si>
-  <si>
-    <t>IBKR</t>
-  </si>
-  <si>
-    <t>OII</t>
-  </si>
-  <si>
-    <t>SIM</t>
-  </si>
-  <si>
-    <t>VAL</t>
-  </si>
-  <si>
-    <t>AE</t>
-  </si>
-  <si>
-    <t>NVDA</t>
-  </si>
-  <si>
-    <t>OLLI</t>
-  </si>
-  <si>
-    <t>DRQ</t>
-  </si>
-  <si>
-    <t>SSD</t>
-  </si>
-  <si>
-    <t>CDW</t>
-  </si>
-  <si>
-    <t>RPM</t>
-  </si>
-  <si>
-    <t>MANU</t>
-  </si>
-  <si>
-    <t>CSWI</t>
-  </si>
-  <si>
-    <t>NYT</t>
-  </si>
-  <si>
-    <t>JILL</t>
-  </si>
-  <si>
-    <t>SBFG</t>
-  </si>
-  <si>
-    <t>PHAR</t>
-  </si>
-  <si>
-    <t>PAA</t>
-  </si>
-  <si>
-    <t>HLNE</t>
-  </si>
-  <si>
-    <t>XP</t>
-  </si>
-  <si>
-    <t>SFM</t>
-  </si>
-  <si>
-    <t>VECO</t>
-  </si>
-  <si>
-    <t>IRTC</t>
-  </si>
-  <si>
-    <t>ATSG</t>
-  </si>
-  <si>
-    <t>MUSA</t>
-  </si>
-  <si>
-    <t>VMW</t>
-  </si>
-  <si>
-    <t>TS</t>
-  </si>
-  <si>
-    <t>HCM</t>
-  </si>
-  <si>
-    <t>EVBN</t>
-  </si>
-  <si>
-    <t>CVNA</t>
-  </si>
-  <si>
-    <t>DHACU</t>
-  </si>
-  <si>
-    <t>OSK</t>
-  </si>
-  <si>
-    <t>ALPN</t>
-  </si>
-  <si>
-    <t>SPFI</t>
-  </si>
-  <si>
-    <t>CSCO</t>
-  </si>
-  <si>
-    <t>NSIT</t>
-  </si>
-  <si>
-    <t>BXP</t>
-  </si>
-  <si>
-    <t>PAGP</t>
-  </si>
-  <si>
-    <t>INFY</t>
-  </si>
-  <si>
-    <t>DCPH</t>
-  </si>
-  <si>
-    <t>KT</t>
-  </si>
-  <si>
-    <t>CENT</t>
-  </si>
-  <si>
-    <t>TEAM</t>
-  </si>
-  <si>
-    <t>CPRX</t>
-  </si>
-  <si>
-    <t>ANDE</t>
-  </si>
-  <si>
-    <t>CSWC</t>
+    <t>IRM</t>
+  </si>
+  <si>
+    <t>BMRN</t>
+  </si>
+  <si>
+    <t>PRGS</t>
+  </si>
+  <si>
+    <t>ORI</t>
+  </si>
+  <si>
+    <t>POST</t>
+  </si>
+  <si>
+    <t>UNP</t>
+  </si>
+  <si>
+    <t>ROP</t>
+  </si>
+  <si>
+    <t>LIVN</t>
   </si>
   <si>
     <t>KRC</t>
   </si>
   <si>
-    <t>MGPI</t>
-  </si>
-  <si>
-    <t>ATR</t>
-  </si>
-  <si>
-    <t>SRV</t>
-  </si>
-  <si>
-    <t>APOG</t>
-  </si>
-  <si>
-    <t>FRSB</t>
-  </si>
-  <si>
-    <t>AIR</t>
-  </si>
-  <si>
-    <t>NECB</t>
-  </si>
-  <si>
-    <t>PX</t>
-  </si>
-  <si>
-    <t>CIGI</t>
-  </si>
-  <si>
-    <t>HUM</t>
-  </si>
-  <si>
-    <t>CRVL</t>
-  </si>
-  <si>
-    <t>CCB</t>
-  </si>
-  <si>
-    <t>MPV</t>
-  </si>
-  <si>
-    <t>LBRT</t>
-  </si>
-  <si>
-    <t>TCOM</t>
-  </si>
-  <si>
-    <t>MLAB</t>
-  </si>
-  <si>
-    <t>GBLI</t>
-  </si>
-  <si>
-    <t>WAYN</t>
-  </si>
-  <si>
-    <t>MAT</t>
-  </si>
-  <si>
-    <t>LBRDA</t>
-  </si>
-  <si>
-    <t>NEU</t>
-  </si>
-  <si>
-    <t>SAH</t>
-  </si>
-  <si>
-    <t>TXT</t>
-  </si>
-  <si>
-    <t>BSFO</t>
-  </si>
-  <si>
-    <t>WSM</t>
-  </si>
-  <si>
-    <t>COLL</t>
-  </si>
-  <si>
-    <t>NWS</t>
-  </si>
-  <si>
-    <t>MDRX</t>
-  </si>
-  <si>
-    <t>VVI</t>
-  </si>
-  <si>
-    <t>GCO</t>
-  </si>
-  <si>
-    <t>BSRR</t>
-  </si>
-  <si>
-    <t>CTRA</t>
-  </si>
-  <si>
-    <t>BDX</t>
-  </si>
-  <si>
-    <t>CRAI</t>
-  </si>
-  <si>
-    <t>EMYB</t>
-  </si>
-  <si>
-    <t>BKR</t>
-  </si>
-  <si>
-    <t>LBRDK</t>
-  </si>
-  <si>
-    <t>MVBF</t>
-  </si>
-  <si>
-    <t>SFST</t>
-  </si>
-  <si>
-    <t>TTE</t>
-  </si>
-  <si>
-    <t>LDOS</t>
-  </si>
-  <si>
-    <t>CMUV</t>
-  </si>
-  <si>
-    <t>BLMN</t>
-  </si>
-  <si>
-    <t>SCHL</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>AZPN</t>
-  </si>
-  <si>
-    <t>NGVC</t>
-  </si>
-  <si>
-    <t>WOR</t>
-  </si>
-  <si>
-    <t>PHAT</t>
-  </si>
-  <si>
-    <t>HLF</t>
-  </si>
-  <si>
-    <t>CMCSA</t>
-  </si>
-  <si>
-    <t>ZGN</t>
-  </si>
-  <si>
-    <t>FTI</t>
+    <t>GOOGL</t>
+  </si>
+  <si>
+    <t>SLB</t>
+  </si>
+  <si>
+    <t>CRS</t>
+  </si>
+  <si>
+    <t>KB</t>
+  </si>
+  <si>
+    <t>AFL</t>
+  </si>
+  <si>
+    <t>MMP</t>
+  </si>
+  <si>
+    <t>PFX</t>
+  </si>
+  <si>
+    <t>NMIH</t>
+  </si>
+  <si>
+    <t>VRSK</t>
+  </si>
+  <si>
+    <t>APPF</t>
+  </si>
+  <si>
+    <t>ALKT</t>
+  </si>
+  <si>
+    <t>AVT</t>
+  </si>
+  <si>
+    <t>NDP</t>
+  </si>
+  <si>
+    <t>EQT</t>
+  </si>
+  <si>
+    <t>LYB</t>
+  </si>
+  <si>
+    <t>WWD</t>
+  </si>
+  <si>
+    <t>USLM</t>
+  </si>
+  <si>
+    <t>CCAP</t>
+  </si>
+  <si>
+    <t>GBX</t>
+  </si>
+  <si>
+    <t>PKG</t>
+  </si>
+  <si>
+    <t>ESNT</t>
   </si>
   <si>
     <t>BCML</t>
   </si>
   <si>
-    <t>HES</t>
-  </si>
-  <si>
-    <t>CME</t>
-  </si>
-  <si>
-    <t>UNF</t>
-  </si>
-  <si>
-    <t>WTM</t>
-  </si>
-  <si>
-    <t>BRO</t>
-  </si>
-  <si>
-    <t>FLT</t>
-  </si>
-  <si>
-    <t>PRO</t>
-  </si>
-  <si>
-    <t>AIZ</t>
-  </si>
-  <si>
-    <t>SFBC</t>
-  </si>
-  <si>
-    <t>AVNW</t>
-  </si>
-  <si>
-    <t>BMI</t>
-  </si>
-  <si>
-    <t>FDS</t>
+    <t>BRP</t>
+  </si>
+  <si>
+    <t>ADSK</t>
   </si>
   <si>
     <t>BY</t>
   </si>
   <si>
-    <t>MAR</t>
-  </si>
-  <si>
-    <t>LPLA</t>
-  </si>
-  <si>
-    <t>SLB</t>
-  </si>
-  <si>
-    <t>ARL</t>
-  </si>
-  <si>
-    <t>SVBT</t>
-  </si>
-  <si>
-    <t>BLX</t>
-  </si>
-  <si>
-    <t>DWACU</t>
-  </si>
-  <si>
-    <t>HZNP</t>
-  </si>
-  <si>
-    <t>ISTR</t>
-  </si>
-  <si>
-    <t>HAL</t>
-  </si>
-  <si>
-    <t>COP</t>
-  </si>
-  <si>
-    <t>CVRX</t>
-  </si>
-  <si>
-    <t>EIC</t>
-  </si>
-  <si>
-    <t>WIX</t>
-  </si>
-  <si>
-    <t>WST</t>
-  </si>
-  <si>
-    <t>NVMI</t>
-  </si>
-  <si>
-    <t>OLED</t>
-  </si>
-  <si>
-    <t>TJX</t>
-  </si>
-  <si>
-    <t>CLMT</t>
-  </si>
-  <si>
-    <t>TCBX</t>
-  </si>
-  <si>
-    <t>CNQ</t>
-  </si>
-  <si>
-    <t>JLL</t>
-  </si>
-  <si>
-    <t>GBX</t>
-  </si>
-  <si>
-    <t>NWSA</t>
-  </si>
-  <si>
-    <t>CAE</t>
-  </si>
-  <si>
-    <t>AIF</t>
-  </si>
-  <si>
-    <t>FMX</t>
-  </si>
-  <si>
-    <t>NDP</t>
-  </si>
-  <si>
-    <t>COOP</t>
-  </si>
-  <si>
-    <t>MSCI</t>
-  </si>
-  <si>
-    <t>BWXT</t>
-  </si>
-  <si>
-    <t>ABM</t>
-  </si>
-  <si>
-    <t>VABK</t>
-  </si>
-  <si>
-    <t>QTRX</t>
-  </si>
-  <si>
-    <t>BLD</t>
-  </si>
-  <si>
-    <t>MHO</t>
-  </si>
-  <si>
-    <t>IHG</t>
-  </si>
-  <si>
-    <t>ASND</t>
-  </si>
-  <si>
-    <t>TCBI</t>
-  </si>
-  <si>
-    <t>FNWB</t>
-  </si>
-  <si>
-    <t>CHH</t>
-  </si>
-  <si>
-    <t>CENTA</t>
-  </si>
-  <si>
-    <t>EDR</t>
-  </si>
-  <si>
-    <t>JDVB</t>
-  </si>
-  <si>
-    <t>GOOG</t>
-  </si>
-  <si>
-    <t>JHX</t>
-  </si>
-  <si>
-    <t>KCLI</t>
-  </si>
-  <si>
-    <t>GOOGL</t>
-  </si>
-  <si>
-    <t>LII</t>
-  </si>
-  <si>
-    <t>MET</t>
-  </si>
-  <si>
-    <t>ESNT</t>
-  </si>
-  <si>
-    <t>BCO</t>
-  </si>
-  <si>
-    <t>SWTX</t>
-  </si>
-  <si>
-    <t>TCPC</t>
-  </si>
-  <si>
-    <t>DK</t>
-  </si>
-  <si>
-    <t>ROAD</t>
-  </si>
-  <si>
-    <t>KB</t>
-  </si>
-  <si>
-    <t>TSBK</t>
-  </si>
-  <si>
-    <t>ODP</t>
-  </si>
-  <si>
-    <t>S</t>
-  </si>
-  <si>
-    <t>BMRN</t>
-  </si>
-  <si>
-    <t>AUBN</t>
-  </si>
-  <si>
-    <t>UFPI</t>
-  </si>
-  <si>
-    <t>FUNC</t>
-  </si>
-  <si>
-    <t>MAYS</t>
-  </si>
-  <si>
-    <t>ABBV</t>
-  </si>
-  <si>
-    <t>ARCB</t>
-  </si>
-  <si>
-    <t>NTNX</t>
-  </si>
-  <si>
-    <t>INSM</t>
-  </si>
-  <si>
-    <t>ATVI</t>
-  </si>
-  <si>
-    <t>BRP</t>
-  </si>
-  <si>
-    <t>NOMD</t>
-  </si>
-  <si>
-    <t>PFGC</t>
-  </si>
-  <si>
-    <t>VRE</t>
-  </si>
-  <si>
-    <t>MRTX</t>
-  </si>
-  <si>
-    <t>MKL</t>
-  </si>
-  <si>
-    <t>ICLR</t>
-  </si>
-  <si>
-    <t>CIR</t>
-  </si>
-  <si>
-    <t>HAYW</t>
-  </si>
-  <si>
-    <t>OZ</t>
-  </si>
-  <si>
-    <t>CVE</t>
-  </si>
-  <si>
-    <t>USLM</t>
-  </si>
-  <si>
-    <t>ESE</t>
-  </si>
-  <si>
-    <t>INTU</t>
-  </si>
-  <si>
-    <t>ASGN</t>
-  </si>
-  <si>
-    <t>LYB</t>
-  </si>
-  <si>
-    <t>MTG</t>
-  </si>
-  <si>
-    <t>IMAX</t>
-  </si>
-  <si>
-    <t>WLK</t>
+    <t>FC</t>
   </si>
   <si>
     <t>DLX</t>
   </si>
   <si>
-    <t>RYAN</t>
-  </si>
-  <si>
-    <t>WMB</t>
-  </si>
-  <si>
-    <t>MSA</t>
-  </si>
-  <si>
-    <t>CWAN</t>
-  </si>
-  <si>
-    <t>EMR</t>
-  </si>
-  <si>
-    <t>FXNC</t>
-  </si>
-  <si>
-    <t>MEDP</t>
-  </si>
-  <si>
-    <t>NDAQ</t>
-  </si>
-  <si>
-    <t>CPNG</t>
-  </si>
-  <si>
-    <t>KEX</t>
-  </si>
-  <si>
-    <t>SBSI</t>
-  </si>
-  <si>
-    <t>COKE</t>
-  </si>
-  <si>
-    <t>TWI</t>
-  </si>
-  <si>
-    <t>PHG</t>
-  </si>
-  <si>
-    <t>RBB</t>
-  </si>
-  <si>
-    <t>ALKT</t>
-  </si>
-  <si>
-    <t>MRCY</t>
-  </si>
-  <si>
-    <t>DJCO</t>
-  </si>
-  <si>
-    <t>ZTS</t>
-  </si>
-  <si>
-    <t>BGR</t>
-  </si>
-  <si>
-    <t>FUTU</t>
-  </si>
-  <si>
-    <t>MRO</t>
-  </si>
-  <si>
-    <t>NMIH</t>
-  </si>
-  <si>
-    <t>POST</t>
-  </si>
-  <si>
-    <t>ABR</t>
-  </si>
-  <si>
-    <t>GOLF</t>
-  </si>
-  <si>
-    <t>HFBL</t>
-  </si>
-  <si>
-    <t>RCMT</t>
-  </si>
-  <si>
-    <t>AFT</t>
-  </si>
-  <si>
-    <t>RWCB</t>
-  </si>
-  <si>
-    <t>MATX</t>
-  </si>
-  <si>
-    <t>MBNKP</t>
-  </si>
-  <si>
-    <t>MORN</t>
-  </si>
-  <si>
-    <t>IRM</t>
-  </si>
-  <si>
-    <t>IBM</t>
-  </si>
-  <si>
-    <t>PAAS</t>
-  </si>
-  <si>
-    <t>VBFC</t>
-  </si>
-  <si>
-    <t>MMP</t>
-  </si>
-  <si>
-    <t>UNP</t>
-  </si>
-  <si>
-    <t>PBR</t>
+    <t>CARR</t>
   </si>
 </sst>
 </file>
@@ -2107,7 +2110,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B580"/>
+  <dimension ref="A1:B581"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -2123,7 +2126,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1">
-        <v>255.4372032446254</v>
+        <v>219.0146525595992</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2131,7 +2134,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1">
-        <v>232.4896500897095</v>
+        <v>203.2707508414633</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -2139,7 +2142,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1">
-        <v>232.3910325827611</v>
+        <v>201.2673746405262</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -2147,7 +2150,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="1">
-        <v>226.3082618298068</v>
+        <v>188.9810262021249</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -2155,7 +2158,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="1">
-        <v>224.5077213802019</v>
+        <v>183.938775388255</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -2163,7 +2166,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="1">
-        <v>213.7220272426785</v>
+        <v>177.3161072003477</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -2171,7 +2174,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="1">
-        <v>211.1201615895684</v>
+        <v>166.1942227145018</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -2179,7 +2182,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="1">
-        <v>202.6105737137543</v>
+        <v>162.0072083063262</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -2187,7 +2190,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="1">
-        <v>147.165390851998</v>
+        <v>148.8972553094104</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -2195,7 +2198,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="1">
-        <v>147.1153539266195</v>
+        <v>146.0360074018575</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -2203,7 +2206,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="1">
-        <v>144.2753746360162</v>
+        <v>145.5564356669597</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -2211,7 +2214,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="1">
-        <v>143.0865258569359</v>
+        <v>144.894081686944</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -2219,7 +2222,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="1">
-        <v>142.1745394788033</v>
+        <v>142.9430124510256</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -2227,7 +2230,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="1">
-        <v>141.1562140807508</v>
+        <v>142.5870868783586</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -2235,7 +2238,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="1">
-        <v>138.4981942286498</v>
+        <v>141.2375283016572</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -2243,7 +2246,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="1">
-        <v>138.1921725621646</v>
+        <v>140.6431414386608</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -2251,7 +2254,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="1">
-        <v>138.0232238069118</v>
+        <v>137.2499371051156</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -2259,7 +2262,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="1">
-        <v>136.4092185411029</v>
+        <v>136.2098925982619</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -2267,7 +2270,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="1">
-        <v>135.4455427563442</v>
+        <v>133.4187855009851</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -2275,7 +2278,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="1">
-        <v>132.6537522564329</v>
+        <v>132.5098562994093</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -2283,7 +2286,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="1">
-        <v>132.548235908364</v>
+        <v>131.8350641447302</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -2291,7 +2294,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="1">
-        <v>132.1817001546993</v>
+        <v>130.9180650891898</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -2299,7 +2302,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="1">
-        <v>131.9854412950382</v>
+        <v>130.1000623834383</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -2307,7 +2310,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="1">
-        <v>131.0192561741487</v>
+        <v>130.0312523966905</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -2315,7 +2318,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="1">
-        <v>129.5433546121298</v>
+        <v>129.5242121171748</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -2323,7 +2326,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="1">
-        <v>129.4456489327364</v>
+        <v>129.4476623073011</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -2331,7 +2334,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="1">
-        <v>129.1620129457897</v>
+        <v>128.473157542667</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -2339,7 +2342,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="1">
-        <v>129.141139817589</v>
+        <v>128.4594081144422</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -2347,7 +2350,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="1">
-        <v>129.0874166038521</v>
+        <v>127.9324918125657</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -2355,7 +2358,7 @@
         <v>31</v>
       </c>
       <c r="B31" s="1">
-        <v>128.8815036092661</v>
+        <v>127.5379253406824</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -2363,7 +2366,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="1">
-        <v>128.4327115465275</v>
+        <v>127.4567429321819</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -2371,7 +2374,7 @@
         <v>33</v>
       </c>
       <c r="B33" s="1">
-        <v>128.0723165624481</v>
+        <v>127.328858515854</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -2379,7 +2382,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="1">
-        <v>127.8963435051743</v>
+        <v>127.0444061480664</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -2387,7 +2390,7 @@
         <v>35</v>
       </c>
       <c r="B35" s="1">
-        <v>127.5129674502357</v>
+        <v>126.6266223029726</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -2395,7 +2398,7 @@
         <v>36</v>
       </c>
       <c r="B36" s="1">
-        <v>127.4026456394295</v>
+        <v>126.5252459553168</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -2403,7 +2406,7 @@
         <v>37</v>
       </c>
       <c r="B37" s="1">
-        <v>126.9752163851319</v>
+        <v>126.4894942687355</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -2411,7 +2414,7 @@
         <v>38</v>
       </c>
       <c r="B38" s="1">
-        <v>126.7620063771785</v>
+        <v>126.2187409508146</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -2419,7 +2422,7 @@
         <v>39</v>
       </c>
       <c r="B39" s="1">
-        <v>126.7493286985751</v>
+        <v>125.9729094535065</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -2427,7 +2430,7 @@
         <v>40</v>
       </c>
       <c r="B40" s="1">
-        <v>126.3810078765538</v>
+        <v>125.8964088864917</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2435,7 +2438,7 @@
         <v>41</v>
       </c>
       <c r="B41" s="1">
-        <v>126.3638131611164</v>
+        <v>125.7077952216301</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2443,7 +2446,7 @@
         <v>42</v>
       </c>
       <c r="B42" s="1">
-        <v>126.011879087461</v>
+        <v>125.4218906332117</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2451,7 +2454,7 @@
         <v>43</v>
       </c>
       <c r="B43" s="1">
-        <v>125.8295255371107</v>
+        <v>125.2055683260689</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2459,7 +2462,7 @@
         <v>44</v>
       </c>
       <c r="B44" s="1">
-        <v>125.5661066265212</v>
+        <v>125.1567679041667</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2467,7 +2470,7 @@
         <v>45</v>
       </c>
       <c r="B45" s="1">
-        <v>125.5339484033279</v>
+        <v>125.0322897325251</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2475,7 +2478,7 @@
         <v>46</v>
       </c>
       <c r="B46" s="1">
-        <v>125.1492600262316</v>
+        <v>124.9070721946984</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2483,7 +2486,7 @@
         <v>47</v>
       </c>
       <c r="B47" s="1">
-        <v>125.1311198986199</v>
+        <v>124.2119250579804</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2491,7 +2494,7 @@
         <v>48</v>
       </c>
       <c r="B48" s="1">
-        <v>125.0684651811989</v>
+        <v>124.1438498444847</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -2499,7 +2502,7 @@
         <v>49</v>
       </c>
       <c r="B49" s="1">
-        <v>124.6544005897391</v>
+        <v>123.9031766363712</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -2507,7 +2510,7 @@
         <v>50</v>
       </c>
       <c r="B50" s="1">
-        <v>124.2670048723938</v>
+        <v>123.719817674583</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -2515,7 +2518,7 @@
         <v>51</v>
       </c>
       <c r="B51" s="1">
-        <v>124.044294945157</v>
+        <v>123.3210973926122</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -2523,7 +2526,7 @@
         <v>52</v>
       </c>
       <c r="B52" s="1">
-        <v>123.6942698124326</v>
+        <v>122.7851242853271</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -2531,7 +2534,7 @@
         <v>53</v>
       </c>
       <c r="B53" s="1">
-        <v>123.5120576911184</v>
+        <v>122.4596161775353</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -2539,7 +2542,7 @@
         <v>54</v>
       </c>
       <c r="B54" s="1">
-        <v>123.305205781116</v>
+        <v>122.3790535951929</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -2547,7 +2550,7 @@
         <v>55</v>
       </c>
       <c r="B55" s="1">
-        <v>122.9398176389222</v>
+        <v>122.3607070091389</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -2555,7 +2558,7 @@
         <v>56</v>
       </c>
       <c r="B56" s="1">
-        <v>122.9006133177667</v>
+        <v>122.340274274262</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -2563,7 +2566,7 @@
         <v>57</v>
       </c>
       <c r="B57" s="1">
-        <v>122.8163278130604</v>
+        <v>122.3318397068268</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -2571,7 +2574,7 @@
         <v>58</v>
       </c>
       <c r="B58" s="1">
-        <v>122.7564711903479</v>
+        <v>122.205204643065</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -2579,7 +2582,7 @@
         <v>59</v>
       </c>
       <c r="B59" s="1">
-        <v>122.6336917575704</v>
+        <v>122.0669915425226</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -2587,7 +2590,7 @@
         <v>60</v>
       </c>
       <c r="B60" s="1">
-        <v>122.4942653908328</v>
+        <v>122.0659140100165</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -2595,7 +2598,7 @@
         <v>61</v>
       </c>
       <c r="B61" s="1">
-        <v>122.4906672805949</v>
+        <v>121.9385123040289</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -2603,7 +2606,7 @@
         <v>62</v>
       </c>
       <c r="B62" s="1">
-        <v>122.4393207762098</v>
+        <v>121.4801081787665</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -2611,7 +2614,7 @@
         <v>63</v>
       </c>
       <c r="B63" s="1">
-        <v>122.3481417194698</v>
+        <v>121.29291976968</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -2619,7 +2622,7 @@
         <v>64</v>
       </c>
       <c r="B64" s="1">
-        <v>121.8718733020944</v>
+        <v>121.1981854430993</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -2627,7 +2630,7 @@
         <v>65</v>
       </c>
       <c r="B65" s="1">
-        <v>121.8230558423345</v>
+        <v>121.1347772187355</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -2635,7 +2638,7 @@
         <v>66</v>
       </c>
       <c r="B66" s="1">
-        <v>121.7609192433521</v>
+        <v>120.9729547954448</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -2643,7 +2646,7 @@
         <v>67</v>
       </c>
       <c r="B67" s="1">
-        <v>121.7327628950884</v>
+        <v>120.8270223518791</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -2651,7 +2654,7 @@
         <v>68</v>
       </c>
       <c r="B68" s="1">
-        <v>121.5419348678818</v>
+        <v>120.7976940363907</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -2659,7 +2662,7 @@
         <v>69</v>
       </c>
       <c r="B69" s="1">
-        <v>121.2808306037658</v>
+        <v>120.6721964372143</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -2667,7 +2670,7 @@
         <v>70</v>
       </c>
       <c r="B70" s="1">
-        <v>121.0610917081422</v>
+        <v>120.5410831793632</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -2675,7 +2678,7 @@
         <v>71</v>
       </c>
       <c r="B71" s="1">
-        <v>120.7597462922815</v>
+        <v>120.4369664139478</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -2683,7 +2686,7 @@
         <v>72</v>
       </c>
       <c r="B72" s="1">
-        <v>120.552630287258</v>
+        <v>120.2079303996222</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2691,7 +2694,7 @@
         <v>73</v>
       </c>
       <c r="B73" s="1">
-        <v>120.3114074927041</v>
+        <v>120.0431006331739</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -2699,7 +2702,7 @@
         <v>74</v>
       </c>
       <c r="B74" s="1">
-        <v>120.2356704812904</v>
+        <v>119.7387642713009</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -2707,7 +2710,7 @@
         <v>75</v>
       </c>
       <c r="B75" s="1">
-        <v>119.5815394660856</v>
+        <v>119.6094336419654</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -2715,7 +2718,7 @@
         <v>76</v>
       </c>
       <c r="B76" s="1">
-        <v>119.285866093714</v>
+        <v>119.5923334727337</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -2723,7 +2726,7 @@
         <v>77</v>
       </c>
       <c r="B77" s="1">
-        <v>119.2306700745033</v>
+        <v>119.4202396677459</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -2731,7 +2734,7 @@
         <v>78</v>
       </c>
       <c r="B78" s="1">
-        <v>119.2062053629531</v>
+        <v>119.2571607492088</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -2739,7 +2742,7 @@
         <v>79</v>
       </c>
       <c r="B79" s="1">
-        <v>118.8218259408394</v>
+        <v>119.1802733008268</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -2747,7 +2750,7 @@
         <v>80</v>
       </c>
       <c r="B80" s="1">
-        <v>118.7689401328494</v>
+        <v>119.013706188467</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -2755,7 +2758,7 @@
         <v>81</v>
       </c>
       <c r="B81" s="1">
-        <v>118.0729584666918</v>
+        <v>118.9900257350446</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -2763,7 +2766,7 @@
         <v>82</v>
       </c>
       <c r="B82" s="1">
-        <v>117.9723674874725</v>
+        <v>118.9066204950056</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -2771,7 +2774,7 @@
         <v>83</v>
       </c>
       <c r="B83" s="1">
-        <v>117.7905544865506</v>
+        <v>118.6263961203748</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -2779,7 +2782,7 @@
         <v>84</v>
       </c>
       <c r="B84" s="1">
-        <v>117.3903407418821</v>
+        <v>118.5350404722387</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -2787,7 +2790,7 @@
         <v>85</v>
       </c>
       <c r="B85" s="1">
-        <v>117.3584182606637</v>
+        <v>118.5128992343909</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -2795,7 +2798,7 @@
         <v>86</v>
       </c>
       <c r="B86" s="1">
-        <v>117.3279755064616</v>
+        <v>118.4249350858761</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -2803,7 +2806,7 @@
         <v>87</v>
       </c>
       <c r="B87" s="1">
-        <v>117.3253261454229</v>
+        <v>118.2512474133199</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -2811,7 +2814,7 @@
         <v>88</v>
       </c>
       <c r="B88" s="1">
-        <v>117.2150530209044</v>
+        <v>118.1082688702354</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -2819,7 +2822,7 @@
         <v>89</v>
       </c>
       <c r="B89" s="1">
-        <v>117.0924984280799</v>
+        <v>117.9911335375456</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -2827,7 +2830,7 @@
         <v>90</v>
       </c>
       <c r="B90" s="1">
-        <v>116.9722664971391</v>
+        <v>117.8956153028092</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -2835,7 +2838,7 @@
         <v>91</v>
       </c>
       <c r="B91" s="1">
-        <v>116.9355305410038</v>
+        <v>117.8253528140544</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -2843,7 +2846,7 @@
         <v>92</v>
       </c>
       <c r="B92" s="1">
-        <v>116.910858301572</v>
+        <v>117.7583595986391</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -2851,7 +2854,7 @@
         <v>93</v>
       </c>
       <c r="B93" s="1">
-        <v>116.8847486666178</v>
+        <v>117.6743981349413</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -2859,7 +2862,7 @@
         <v>94</v>
       </c>
       <c r="B94" s="1">
-        <v>116.8767327531502</v>
+        <v>117.3828200245722</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -2867,7 +2870,7 @@
         <v>95</v>
       </c>
       <c r="B95" s="1">
-        <v>116.8640953915592</v>
+        <v>117.2213952523693</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -2875,7 +2878,7 @@
         <v>96</v>
       </c>
       <c r="B96" s="1">
-        <v>116.6077253944437</v>
+        <v>116.8644173751075</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -2883,7 +2886,7 @@
         <v>97</v>
       </c>
       <c r="B97" s="1">
-        <v>116.5655827549685</v>
+        <v>116.6579581983106</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -2891,7 +2894,7 @@
         <v>98</v>
       </c>
       <c r="B98" s="1">
-        <v>116.5486099173818</v>
+        <v>116.5958140320984</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -2899,7 +2902,7 @@
         <v>99</v>
       </c>
       <c r="B99" s="1">
-        <v>116.4558732807591</v>
+        <v>116.5523726411095</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -2907,7 +2910,7 @@
         <v>100</v>
       </c>
       <c r="B100" s="1">
-        <v>116.4343472947386</v>
+        <v>116.3335417119557</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -2915,7 +2918,7 @@
         <v>101</v>
       </c>
       <c r="B101" s="1">
-        <v>116.3425188466369</v>
+        <v>116.3070009547909</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -2923,7 +2926,7 @@
         <v>102</v>
       </c>
       <c r="B102" s="1">
-        <v>116.2467158021782</v>
+        <v>116.2655019901721</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -2931,7 +2934,7 @@
         <v>103</v>
       </c>
       <c r="B103" s="1">
-        <v>116.1785984254573</v>
+        <v>116.0916455398064</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -2939,7 +2942,7 @@
         <v>104</v>
       </c>
       <c r="B104" s="1">
-        <v>116.1655759558836</v>
+        <v>116.0706025433135</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -2947,7 +2950,7 @@
         <v>105</v>
       </c>
       <c r="B105" s="1">
-        <v>116.1551532574323</v>
+        <v>115.9581817584721</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -2955,7 +2958,7 @@
         <v>106</v>
       </c>
       <c r="B106" s="1">
-        <v>116.0901735353001</v>
+        <v>115.8163137819314</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -2963,7 +2966,7 @@
         <v>107</v>
       </c>
       <c r="B107" s="1">
-        <v>115.6351988252011</v>
+        <v>115.4942744750824</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -2971,7 +2974,7 @@
         <v>108</v>
       </c>
       <c r="B108" s="1">
-        <v>115.6060182563145</v>
+        <v>115.4696259105589</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -2979,7 +2982,7 @@
         <v>109</v>
       </c>
       <c r="B109" s="1">
-        <v>115.576054729594</v>
+        <v>115.4590887578645</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -2987,7 +2990,7 @@
         <v>110</v>
       </c>
       <c r="B110" s="1">
-        <v>115.5107720195065</v>
+        <v>115.4494595279505</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -2995,7 +2998,7 @@
         <v>111</v>
       </c>
       <c r="B111" s="1">
-        <v>115.314608805732</v>
+        <v>115.2912926721716</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -3003,7 +3006,7 @@
         <v>112</v>
       </c>
       <c r="B112" s="1">
-        <v>115.1788038304336</v>
+        <v>115.2347640531353</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -3011,7 +3014,7 @@
         <v>113</v>
       </c>
       <c r="B113" s="1">
-        <v>115.1772910593903</v>
+        <v>115.2204496513761</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -3019,7 +3022,7 @@
         <v>114</v>
       </c>
       <c r="B114" s="1">
-        <v>115.1180554931809</v>
+        <v>114.9718950952141</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -3027,7 +3030,7 @@
         <v>115</v>
       </c>
       <c r="B115" s="1">
-        <v>115.0190667962254</v>
+        <v>114.9310516008276</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -3035,7 +3038,7 @@
         <v>116</v>
       </c>
       <c r="B116" s="1">
-        <v>115.0099063465901</v>
+        <v>114.9130041816834</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -3043,7 +3046,7 @@
         <v>117</v>
       </c>
       <c r="B117" s="1">
-        <v>114.7630721750088</v>
+        <v>114.8691515835428</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -3051,7 +3054,7 @@
         <v>118</v>
       </c>
       <c r="B118" s="1">
-        <v>114.7350764453523</v>
+        <v>114.4949161916172</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -3059,7 +3062,7 @@
         <v>119</v>
       </c>
       <c r="B119" s="1">
-        <v>114.3850502065295</v>
+        <v>114.3142989662003</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -3067,7 +3070,7 @@
         <v>120</v>
       </c>
       <c r="B120" s="1">
-        <v>114.3663998433953</v>
+        <v>114.285608855192</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -3075,7 +3078,7 @@
         <v>121</v>
       </c>
       <c r="B121" s="1">
-        <v>114.3380049710739</v>
+        <v>114.0608358274658</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -3083,7 +3086,7 @@
         <v>122</v>
       </c>
       <c r="B122" s="1">
-        <v>114.3282886117716</v>
+        <v>113.831057370203</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -3091,7 +3094,7 @@
         <v>123</v>
       </c>
       <c r="B123" s="1">
-        <v>114.3039519961244</v>
+        <v>113.8172071634526</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -3099,7 +3102,7 @@
         <v>124</v>
       </c>
       <c r="B124" s="1">
-        <v>114.2988185278907</v>
+        <v>113.8038206030284</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -3107,7 +3110,7 @@
         <v>125</v>
       </c>
       <c r="B125" s="1">
-        <v>114.2379077028294</v>
+        <v>113.7931364625282</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -3115,7 +3118,7 @@
         <v>126</v>
       </c>
       <c r="B126" s="1">
-        <v>114.2003721341588</v>
+        <v>113.7468908729729</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -3123,7 +3126,7 @@
         <v>127</v>
       </c>
       <c r="B127" s="1">
-        <v>113.9873077720361</v>
+        <v>113.7267701408259</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -3131,7 +3134,7 @@
         <v>128</v>
       </c>
       <c r="B128" s="1">
-        <v>113.8476688478566</v>
+        <v>113.7075426404624</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -3139,7 +3142,7 @@
         <v>129</v>
       </c>
       <c r="B129" s="1">
-        <v>113.6713753513925</v>
+        <v>113.7036740070213</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -3147,7 +3150,7 @@
         <v>130</v>
       </c>
       <c r="B130" s="1">
-        <v>113.5442591419512</v>
+        <v>113.7026453265042</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -3155,7 +3158,7 @@
         <v>131</v>
       </c>
       <c r="B131" s="1">
-        <v>113.5394687706013</v>
+        <v>113.7001004007721</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -3163,7 +3166,7 @@
         <v>132</v>
       </c>
       <c r="B132" s="1">
-        <v>113.444959149351</v>
+        <v>113.6635092763502</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -3171,7 +3174,7 @@
         <v>133</v>
       </c>
       <c r="B133" s="1">
-        <v>113.3261892777696</v>
+        <v>113.6026539593181</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -3179,7 +3182,7 @@
         <v>134</v>
       </c>
       <c r="B134" s="1">
-        <v>113.2782569688219</v>
+        <v>113.4466058190664</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -3187,7 +3190,7 @@
         <v>135</v>
       </c>
       <c r="B135" s="1">
-        <v>113.1954609303813</v>
+        <v>113.2388877846508</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -3195,7 +3198,7 @@
         <v>136</v>
       </c>
       <c r="B136" s="1">
-        <v>113.0710929096851</v>
+        <v>113.2270191815026</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -3203,7 +3206,7 @@
         <v>137</v>
       </c>
       <c r="B137" s="1">
-        <v>113.0344959431441</v>
+        <v>113.103752794043</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -3211,7 +3214,7 @@
         <v>138</v>
       </c>
       <c r="B138" s="1">
-        <v>113.0343027668676</v>
+        <v>113.0541759470215</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -3219,7 +3222,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="1">
-        <v>112.9487253196114</v>
+        <v>112.9111770278752</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -3227,7 +3230,7 @@
         <v>140</v>
       </c>
       <c r="B140" s="1">
-        <v>112.875204830793</v>
+        <v>112.8860620489545</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -3235,7 +3238,7 @@
         <v>141</v>
       </c>
       <c r="B141" s="1">
-        <v>112.777743452436</v>
+        <v>112.8716136407553</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -3243,7 +3246,7 @@
         <v>142</v>
       </c>
       <c r="B142" s="1">
-        <v>112.732569915804</v>
+        <v>112.644978902065</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -3251,7 +3254,7 @@
         <v>143</v>
       </c>
       <c r="B143" s="1">
-        <v>112.676492099097</v>
+        <v>112.5879638026102</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -3259,7 +3262,7 @@
         <v>144</v>
       </c>
       <c r="B144" s="1">
-        <v>112.6622580188997</v>
+        <v>112.5817623300718</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -3267,7 +3270,7 @@
         <v>145</v>
       </c>
       <c r="B145" s="1">
-        <v>112.6139383219039</v>
+        <v>112.5520476866857</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -3275,7 +3278,7 @@
         <v>146</v>
       </c>
       <c r="B146" s="1">
-        <v>112.5859223308479</v>
+        <v>112.5445592345309</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -3283,7 +3286,7 @@
         <v>147</v>
       </c>
       <c r="B147" s="1">
-        <v>112.5193923590384</v>
+        <v>112.5286823007308</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -3291,7 +3294,7 @@
         <v>148</v>
       </c>
       <c r="B148" s="1">
-        <v>112.519055341014</v>
+        <v>112.4492102085143</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -3299,7 +3302,7 @@
         <v>149</v>
       </c>
       <c r="B149" s="1">
-        <v>112.4533496475858</v>
+        <v>112.3896849400066</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -3307,7 +3310,7 @@
         <v>150</v>
       </c>
       <c r="B150" s="1">
-        <v>112.3906411292103</v>
+        <v>112.3676880723026</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -3315,7 +3318,7 @@
         <v>151</v>
       </c>
       <c r="B151" s="1">
-        <v>112.3269794636288</v>
+        <v>112.3422208148995</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -3323,7 +3326,7 @@
         <v>152</v>
       </c>
       <c r="B152" s="1">
-        <v>112.2457426124794</v>
+        <v>112.3320594721739</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -3331,7 +3334,7 @@
         <v>153</v>
       </c>
       <c r="B153" s="1">
-        <v>112.1977264910452</v>
+        <v>112.3160646090602</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -3339,7 +3342,7 @@
         <v>154</v>
       </c>
       <c r="B154" s="1">
-        <v>112.143019162249</v>
+        <v>112.3062202171229</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -3347,7 +3350,7 @@
         <v>155</v>
       </c>
       <c r="B155" s="1">
-        <v>112.1060325684553</v>
+        <v>112.2818607803228</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -3355,7 +3358,7 @@
         <v>156</v>
       </c>
       <c r="B156" s="1">
-        <v>112.0679333299758</v>
+        <v>112.279392925968</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -3363,7 +3366,7 @@
         <v>157</v>
       </c>
       <c r="B157" s="1">
-        <v>112.0531450319764</v>
+        <v>112.2622577931475</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -3371,7 +3374,7 @@
         <v>158</v>
       </c>
       <c r="B158" s="1">
-        <v>112.0521413242142</v>
+        <v>112.2593542968149</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -3379,7 +3382,7 @@
         <v>159</v>
       </c>
       <c r="B159" s="1">
-        <v>112.0193667459477</v>
+        <v>112.2025437375524</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -3387,7 +3390,7 @@
         <v>160</v>
       </c>
       <c r="B160" s="1">
-        <v>111.97473540536</v>
+        <v>112.1899866135254</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -3395,7 +3398,7 @@
         <v>161</v>
       </c>
       <c r="B161" s="1">
-        <v>111.9320026442953</v>
+        <v>112.1859600745779</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -3403,7 +3406,7 @@
         <v>162</v>
       </c>
       <c r="B162" s="1">
-        <v>111.8558510564928</v>
+        <v>112.0488723009267</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -3411,7 +3414,7 @@
         <v>163</v>
       </c>
       <c r="B163" s="1">
-        <v>111.7263230745141</v>
+        <v>112.0186089093079</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -3419,7 +3422,7 @@
         <v>164</v>
       </c>
       <c r="B164" s="1">
-        <v>111.6854930250687</v>
+        <v>111.9998866953433</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -3427,7 +3430,7 @@
         <v>165</v>
       </c>
       <c r="B165" s="1">
-        <v>111.5934363100019</v>
+        <v>111.9728949805858</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -3435,7 +3438,7 @@
         <v>166</v>
       </c>
       <c r="B166" s="1">
-        <v>111.586901276318</v>
+        <v>111.9713369850722</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -3443,7 +3446,7 @@
         <v>167</v>
       </c>
       <c r="B167" s="1">
-        <v>111.3789935550132</v>
+        <v>111.970652301605</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -3451,7 +3454,7 @@
         <v>168</v>
       </c>
       <c r="B168" s="1">
-        <v>111.3611380750681</v>
+        <v>111.9139780391905</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -3459,7 +3462,7 @@
         <v>169</v>
       </c>
       <c r="B169" s="1">
-        <v>111.346665802587</v>
+        <v>111.9124044358927</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -3467,7 +3470,7 @@
         <v>170</v>
       </c>
       <c r="B170" s="1">
-        <v>111.3465180961861</v>
+        <v>111.8858373107637</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -3475,7 +3478,7 @@
         <v>171</v>
       </c>
       <c r="B171" s="1">
-        <v>111.3179205735857</v>
+        <v>111.8452446788656</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -3483,7 +3486,7 @@
         <v>172</v>
       </c>
       <c r="B172" s="1">
-        <v>111.1408915639471</v>
+        <v>111.8201540852349</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -3491,7 +3494,7 @@
         <v>173</v>
       </c>
       <c r="B173" s="1">
-        <v>111.1250751402151</v>
+        <v>111.6618405202762</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -3499,7 +3502,7 @@
         <v>174</v>
       </c>
       <c r="B174" s="1">
-        <v>111.1135796284285</v>
+        <v>111.6232484015288</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -3507,7 +3510,7 @@
         <v>175</v>
       </c>
       <c r="B175" s="1">
-        <v>111.0300982250302</v>
+        <v>111.5553168717073</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -3515,7 +3518,7 @@
         <v>176</v>
       </c>
       <c r="B176" s="1">
-        <v>111.0018227932589</v>
+        <v>111.5113409311862</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -3523,7 +3526,7 @@
         <v>177</v>
       </c>
       <c r="B177" s="1">
-        <v>110.9721957249015</v>
+        <v>111.4229939103859</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -3531,7 +3534,7 @@
         <v>178</v>
       </c>
       <c r="B178" s="1">
-        <v>110.9255160975927</v>
+        <v>111.3634655671088</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -3539,7 +3542,7 @@
         <v>179</v>
       </c>
       <c r="B179" s="1">
-        <v>110.8947851278548</v>
+        <v>111.3430448957096</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -3547,7 +3550,7 @@
         <v>180</v>
       </c>
       <c r="B180" s="1">
-        <v>110.8627599558183</v>
+        <v>111.3082580030947</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -3555,7 +3558,7 @@
         <v>181</v>
       </c>
       <c r="B181" s="1">
-        <v>110.8397862587471</v>
+        <v>111.1967396612225</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -3563,7 +3566,7 @@
         <v>182</v>
       </c>
       <c r="B182" s="1">
-        <v>110.6376258760223</v>
+        <v>111.1707034797413</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -3571,7 +3574,7 @@
         <v>183</v>
       </c>
       <c r="B183" s="1">
-        <v>110.5931391804349</v>
+        <v>111.1570298283221</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -3579,7 +3582,7 @@
         <v>184</v>
       </c>
       <c r="B184" s="1">
-        <v>110.5926902412967</v>
+        <v>111.1330455017879</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -3587,7 +3590,7 @@
         <v>185</v>
       </c>
       <c r="B185" s="1">
-        <v>110.4926250165401</v>
+        <v>111.1316562301778</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -3595,7 +3598,7 @@
         <v>186</v>
       </c>
       <c r="B186" s="1">
-        <v>110.4775706912209</v>
+        <v>111.0641327107731</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -3603,7 +3606,7 @@
         <v>187</v>
       </c>
       <c r="B187" s="1">
-        <v>110.4523000389414</v>
+        <v>110.9465457400038</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -3611,7 +3614,7 @@
         <v>188</v>
       </c>
       <c r="B188" s="1">
-        <v>110.4495929853834</v>
+        <v>110.8872393364481</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -3619,7 +3622,7 @@
         <v>189</v>
       </c>
       <c r="B189" s="1">
-        <v>110.4124233963192</v>
+        <v>110.8508778249388</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -3627,7 +3630,7 @@
         <v>190</v>
       </c>
       <c r="B190" s="1">
-        <v>110.3627484688429</v>
+        <v>110.7993082919147</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -3635,7 +3638,7 @@
         <v>191</v>
       </c>
       <c r="B191" s="1">
-        <v>110.1906094399694</v>
+        <v>110.7275401195776</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -3643,7 +3646,7 @@
         <v>192</v>
       </c>
       <c r="B192" s="1">
-        <v>110.1764303331871</v>
+        <v>110.7050941391466</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -3651,7 +3654,7 @@
         <v>193</v>
       </c>
       <c r="B193" s="1">
-        <v>110.1594648158969</v>
+        <v>110.6626855694578</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -3659,7 +3662,7 @@
         <v>194</v>
       </c>
       <c r="B194" s="1">
-        <v>110.1584634376858</v>
+        <v>110.6213439659858</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -3667,7 +3670,7 @@
         <v>195</v>
       </c>
       <c r="B195" s="1">
-        <v>110.1444241443542</v>
+        <v>110.5697002752201</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -3675,7 +3678,7 @@
         <v>196</v>
       </c>
       <c r="B196" s="1">
-        <v>110.1381430034398</v>
+        <v>110.5226185973664</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -3683,7 +3686,7 @@
         <v>197</v>
       </c>
       <c r="B197" s="1">
-        <v>110.1128008794736</v>
+        <v>110.5136354905902</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -3691,7 +3694,7 @@
         <v>198</v>
       </c>
       <c r="B198" s="1">
-        <v>110.0445216743583</v>
+        <v>110.4873049283363</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -3699,7 +3702,7 @@
         <v>199</v>
       </c>
       <c r="B199" s="1">
-        <v>110.0391324843375</v>
+        <v>110.4698102643475</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -3707,7 +3710,7 @@
         <v>200</v>
       </c>
       <c r="B200" s="1">
-        <v>110.0239433535197</v>
+        <v>110.4242439187477</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -3715,7 +3718,7 @@
         <v>201</v>
       </c>
       <c r="B201" s="1">
-        <v>110.0163037460615</v>
+        <v>110.4230070519585</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -3723,7 +3726,7 @@
         <v>202</v>
       </c>
       <c r="B202" s="1">
-        <v>109.9915391939989</v>
+        <v>110.3874180910558</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -3731,7 +3734,7 @@
         <v>203</v>
       </c>
       <c r="B203" s="1">
-        <v>109.9697141025042</v>
+        <v>110.314337459962</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -3739,7 +3742,7 @@
         <v>204</v>
       </c>
       <c r="B204" s="1">
-        <v>109.967194782257</v>
+        <v>110.2902402885026</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -3747,7 +3750,7 @@
         <v>205</v>
       </c>
       <c r="B205" s="1">
-        <v>109.9403150138444</v>
+        <v>110.2767222326485</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -3755,7 +3758,7 @@
         <v>206</v>
       </c>
       <c r="B206" s="1">
-        <v>109.9110726192919</v>
+        <v>110.1533553561363</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -3763,7 +3766,7 @@
         <v>207</v>
       </c>
       <c r="B207" s="1">
-        <v>109.9026845797132</v>
+        <v>110.1145559739885</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -3771,7 +3774,7 @@
         <v>208</v>
       </c>
       <c r="B208" s="1">
-        <v>109.8901340334126</v>
+        <v>110.1094893434654</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -3779,7 +3782,7 @@
         <v>209</v>
       </c>
       <c r="B209" s="1">
-        <v>109.8810554098349</v>
+        <v>110.0969790346836</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -3787,7 +3790,7 @@
         <v>210</v>
       </c>
       <c r="B210" s="1">
-        <v>109.8548517053724</v>
+        <v>110.0953736829356</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -3795,7 +3798,7 @@
         <v>211</v>
       </c>
       <c r="B211" s="1">
-        <v>109.804341750345</v>
+        <v>110.0652206504124</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -3803,7 +3806,7 @@
         <v>212</v>
       </c>
       <c r="B212" s="1">
-        <v>109.7286000394487</v>
+        <v>110.0372744335073</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -3811,7 +3814,7 @@
         <v>213</v>
       </c>
       <c r="B213" s="1">
-        <v>109.7245499338698</v>
+        <v>110.0348978706136</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -3819,7 +3822,7 @@
         <v>214</v>
       </c>
       <c r="B214" s="1">
-        <v>109.6881323067637</v>
+        <v>109.962444968561</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -3827,7 +3830,7 @@
         <v>215</v>
       </c>
       <c r="B215" s="1">
-        <v>109.6207351585819</v>
+        <v>109.9020161027792</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -3835,7 +3838,7 @@
         <v>216</v>
       </c>
       <c r="B216" s="1">
-        <v>109.5941582932509</v>
+        <v>109.894291329282</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -3843,7 +3846,7 @@
         <v>217</v>
       </c>
       <c r="B217" s="1">
-        <v>109.5007134731656</v>
+        <v>109.8798817533126</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -3851,7 +3854,7 @@
         <v>218</v>
       </c>
       <c r="B218" s="1">
-        <v>109.4254309043247</v>
+        <v>109.8732862075393</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -3859,7 +3862,7 @@
         <v>219</v>
       </c>
       <c r="B219" s="1">
-        <v>109.4225873637941</v>
+        <v>109.8702156402811</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -3867,7 +3870,7 @@
         <v>220</v>
       </c>
       <c r="B220" s="1">
-        <v>109.4163176758458</v>
+        <v>109.8150053059505</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -3875,7 +3878,7 @@
         <v>221</v>
       </c>
       <c r="B221" s="1">
-        <v>109.4152720123788</v>
+        <v>109.7971731771916</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -3883,7 +3886,7 @@
         <v>222</v>
       </c>
       <c r="B222" s="1">
-        <v>109.3925371786257</v>
+        <v>109.7833270615447</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -3891,7 +3894,7 @@
         <v>223</v>
       </c>
       <c r="B223" s="1">
-        <v>109.371664564078</v>
+        <v>109.7729752088032</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -3899,7 +3902,7 @@
         <v>224</v>
       </c>
       <c r="B224" s="1">
-        <v>109.3612138285899</v>
+        <v>109.7663043847657</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -3907,7 +3910,7 @@
         <v>225</v>
       </c>
       <c r="B225" s="1">
-        <v>109.3494463391298</v>
+        <v>109.7559438000149</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -3915,7 +3918,7 @@
         <v>226</v>
       </c>
       <c r="B226" s="1">
-        <v>109.3230179954365</v>
+        <v>109.7480334309206</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -3923,7 +3926,7 @@
         <v>227</v>
       </c>
       <c r="B227" s="1">
-        <v>109.2593863164856</v>
+        <v>109.722945760057</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -3931,7 +3934,7 @@
         <v>228</v>
       </c>
       <c r="B228" s="1">
-        <v>109.2452862513797</v>
+        <v>109.6008093520778</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -3939,7 +3942,7 @@
         <v>229</v>
       </c>
       <c r="B229" s="1">
-        <v>109.2445275324623</v>
+        <v>109.5279458729495</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -3947,7 +3950,7 @@
         <v>230</v>
       </c>
       <c r="B230" s="1">
-        <v>109.105188905917</v>
+        <v>109.5113189550956</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -3955,7 +3958,7 @@
         <v>231</v>
       </c>
       <c r="B231" s="1">
-        <v>109.0685859482133</v>
+        <v>109.5016311897018</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -3963,7 +3966,7 @@
         <v>232</v>
       </c>
       <c r="B232" s="1">
-        <v>109.0397996585525</v>
+        <v>109.4319783867734</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -3971,7 +3974,7 @@
         <v>233</v>
       </c>
       <c r="B233" s="1">
-        <v>109.0355320777742</v>
+        <v>109.3182578909494</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -3979,7 +3982,7 @@
         <v>234</v>
       </c>
       <c r="B234" s="1">
-        <v>108.9457248271857</v>
+        <v>109.3173496528161</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -3987,7 +3990,7 @@
         <v>235</v>
       </c>
       <c r="B235" s="1">
-        <v>108.8805804136121</v>
+        <v>109.2482587440566</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -3995,7 +3998,7 @@
         <v>236</v>
       </c>
       <c r="B236" s="1">
-        <v>108.8238365230966</v>
+        <v>109.2336536352719</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -4003,7 +4006,7 @@
         <v>237</v>
       </c>
       <c r="B237" s="1">
-        <v>108.8213031074816</v>
+        <v>109.1962562921665</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -4011,7 +4014,7 @@
         <v>238</v>
       </c>
       <c r="B238" s="1">
-        <v>108.8016402726917</v>
+        <v>109.1859917971266</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -4019,7 +4022,7 @@
         <v>239</v>
       </c>
       <c r="B239" s="1">
-        <v>108.7694143728578</v>
+        <v>109.1782324923318</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -4027,7 +4030,7 @@
         <v>240</v>
       </c>
       <c r="B240" s="1">
-        <v>108.7539489383964</v>
+        <v>109.1534852126299</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -4035,7 +4038,7 @@
         <v>241</v>
       </c>
       <c r="B241" s="1">
-        <v>108.7500257791994</v>
+        <v>109.1167140690912</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -4043,7 +4046,7 @@
         <v>242</v>
       </c>
       <c r="B242" s="1">
-        <v>108.7442613708145</v>
+        <v>109.1128599096522</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -4051,7 +4054,7 @@
         <v>243</v>
       </c>
       <c r="B243" s="1">
-        <v>108.7135833644987</v>
+        <v>109.0581053239039</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -4059,7 +4062,7 @@
         <v>244</v>
       </c>
       <c r="B244" s="1">
-        <v>108.6453062728561</v>
+        <v>109.0422118079366</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -4067,7 +4070,7 @@
         <v>245</v>
       </c>
       <c r="B245" s="1">
-        <v>108.6118421114181</v>
+        <v>109.0312659189606</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -4075,7 +4078,7 @@
         <v>246</v>
       </c>
       <c r="B246" s="1">
-        <v>108.6006414279477</v>
+        <v>109.024907084727</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -4083,7 +4086,7 @@
         <v>247</v>
       </c>
       <c r="B247" s="1">
-        <v>108.583356850018</v>
+        <v>108.9951924974343</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -4091,7 +4094,7 @@
         <v>248</v>
       </c>
       <c r="B248" s="1">
-        <v>108.5631053071633</v>
+        <v>108.9892401312785</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -4099,7 +4102,7 @@
         <v>249</v>
       </c>
       <c r="B249" s="1">
-        <v>108.5280400573414</v>
+        <v>108.984297943012</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -4107,7 +4110,7 @@
         <v>250</v>
       </c>
       <c r="B250" s="1">
-        <v>108.5197181049477</v>
+        <v>108.9837677715467</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -4115,7 +4118,7 @@
         <v>251</v>
       </c>
       <c r="B251" s="1">
-        <v>108.5172210362064</v>
+        <v>108.9568148521436</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -4123,7 +4126,7 @@
         <v>252</v>
       </c>
       <c r="B252" s="1">
-        <v>108.5040302130104</v>
+        <v>108.9193016798436</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -4131,7 +4134,7 @@
         <v>253</v>
       </c>
       <c r="B253" s="1">
-        <v>108.4879460127584</v>
+        <v>108.8894749449555</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -4139,7 +4142,7 @@
         <v>254</v>
       </c>
       <c r="B254" s="1">
-        <v>108.4695722595417</v>
+        <v>108.8789972291625</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -4147,7 +4150,7 @@
         <v>255</v>
       </c>
       <c r="B255" s="1">
-        <v>108.4453449889561</v>
+        <v>108.8660832450047</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -4155,7 +4158,7 @@
         <v>256</v>
       </c>
       <c r="B256" s="1">
-        <v>108.4355010131187</v>
+        <v>108.8361199961236</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -4163,7 +4166,7 @@
         <v>257</v>
       </c>
       <c r="B257" s="1">
-        <v>108.4293548260467</v>
+        <v>108.8161121070671</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -4171,7 +4174,7 @@
         <v>258</v>
       </c>
       <c r="B258" s="1">
-        <v>108.3485124227473</v>
+        <v>108.7810959110729</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -4179,7 +4182,7 @@
         <v>259</v>
       </c>
       <c r="B259" s="1">
-        <v>108.3380400620968</v>
+        <v>108.7695679875082</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -4187,7 +4190,7 @@
         <v>260</v>
       </c>
       <c r="B260" s="1">
-        <v>108.307919256461</v>
+        <v>108.7110836527499</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -4195,7 +4198,7 @@
         <v>261</v>
       </c>
       <c r="B261" s="1">
-        <v>108.2868993667295</v>
+        <v>108.6885931042359</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -4203,7 +4206,7 @@
         <v>262</v>
       </c>
       <c r="B262" s="1">
-        <v>108.2751547855899</v>
+        <v>108.6796533887317</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -4211,7 +4214,7 @@
         <v>263</v>
       </c>
       <c r="B263" s="1">
-        <v>108.263532480959</v>
+        <v>108.6360239234998</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -4219,7 +4222,7 @@
         <v>264</v>
       </c>
       <c r="B264" s="1">
-        <v>108.2552624496726</v>
+        <v>108.6183928134003</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -4227,7 +4230,7 @@
         <v>265</v>
       </c>
       <c r="B265" s="1">
-        <v>108.2308490732492</v>
+        <v>108.5725565745078</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -4235,7 +4238,7 @@
         <v>266</v>
       </c>
       <c r="B266" s="1">
-        <v>108.195477738056</v>
+        <v>108.5643118176507</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -4243,7 +4246,7 @@
         <v>267</v>
       </c>
       <c r="B267" s="1">
-        <v>108.1896190489633</v>
+        <v>108.5311215220115</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -4251,7 +4254,7 @@
         <v>268</v>
       </c>
       <c r="B268" s="1">
-        <v>108.1847804637386</v>
+        <v>108.5260196443022</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -4259,7 +4262,7 @@
         <v>269</v>
       </c>
       <c r="B269" s="1">
-        <v>108.1791792827654</v>
+        <v>108.4594247414904</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -4267,7 +4270,7 @@
         <v>270</v>
       </c>
       <c r="B270" s="1">
-        <v>108.1008672269782</v>
+        <v>108.4488134397407</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -4275,7 +4278,7 @@
         <v>271</v>
       </c>
       <c r="B271" s="1">
-        <v>108.0976919606198</v>
+        <v>108.4270174577566</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -4283,7 +4286,7 @@
         <v>272</v>
       </c>
       <c r="B272" s="1">
-        <v>108.0681333659302</v>
+        <v>108.3923076262029</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -4291,7 +4294,7 @@
         <v>273</v>
       </c>
       <c r="B273" s="1">
-        <v>108.0449810572618</v>
+        <v>108.3834838339867</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -4299,7 +4302,7 @@
         <v>274</v>
       </c>
       <c r="B274" s="1">
-        <v>108.0135970624105</v>
+        <v>108.3697487817445</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -4307,7 +4310,7 @@
         <v>275</v>
       </c>
       <c r="B275" s="1">
-        <v>108.0071656987081</v>
+        <v>108.3458043246911</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -4315,7 +4318,7 @@
         <v>276</v>
       </c>
       <c r="B276" s="1">
-        <v>107.9974877146484</v>
+        <v>108.3437633551084</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -4323,7 +4326,7 @@
         <v>277</v>
       </c>
       <c r="B277" s="1">
-        <v>107.9940175457025</v>
+        <v>108.2956493558162</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -4331,7 +4334,7 @@
         <v>278</v>
       </c>
       <c r="B278" s="1">
-        <v>107.9847164427934</v>
+        <v>108.2853403187922</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -4339,7 +4342,7 @@
         <v>279</v>
       </c>
       <c r="B279" s="1">
-        <v>107.9526742912932</v>
+        <v>108.2276921997821</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -4347,7 +4350,7 @@
         <v>280</v>
       </c>
       <c r="B280" s="1">
-        <v>107.8877584436412</v>
+        <v>108.2164341710734</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -4355,7 +4358,7 @@
         <v>281</v>
       </c>
       <c r="B281" s="1">
-        <v>107.8873831019104</v>
+        <v>108.1673462445674</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -4363,7 +4366,7 @@
         <v>282</v>
       </c>
       <c r="B282" s="1">
-        <v>107.8873643560209</v>
+        <v>108.166434663536</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -4371,7 +4374,7 @@
         <v>283</v>
       </c>
       <c r="B283" s="1">
-        <v>107.8866266839896</v>
+        <v>108.1520515884639</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -4379,7 +4382,7 @@
         <v>284</v>
       </c>
       <c r="B284" s="1">
-        <v>107.8754235247931</v>
+        <v>108.151496950175</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -4387,7 +4390,7 @@
         <v>285</v>
       </c>
       <c r="B285" s="1">
-        <v>107.8421986733093</v>
+        <v>108.1464089660046</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -4395,7 +4398,7 @@
         <v>286</v>
       </c>
       <c r="B286" s="1">
-        <v>107.833969257543</v>
+        <v>108.1016672711797</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -4403,7 +4406,7 @@
         <v>287</v>
       </c>
       <c r="B287" s="1">
-        <v>107.742335949786</v>
+        <v>108.0948679428786</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -4411,7 +4414,7 @@
         <v>288</v>
       </c>
       <c r="B288" s="1">
-        <v>107.7154784503519</v>
+        <v>108.0916916360467</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -4419,7 +4422,7 @@
         <v>289</v>
       </c>
       <c r="B289" s="1">
-        <v>107.7138964151287</v>
+        <v>108.0906929366951</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -4427,7 +4430,7 @@
         <v>290</v>
       </c>
       <c r="B290" s="1">
-        <v>107.7014781807888</v>
+        <v>108.08314253728</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -4435,7 +4438,7 @@
         <v>291</v>
       </c>
       <c r="B291" s="1">
-        <v>107.6915539604903</v>
+        <v>108.0760765950416</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -4443,7 +4446,7 @@
         <v>292</v>
       </c>
       <c r="B292" s="1">
-        <v>107.6899914690012</v>
+        <v>108.0655941729099</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -4451,7 +4454,7 @@
         <v>293</v>
       </c>
       <c r="B293" s="1">
-        <v>107.6638863167691</v>
+        <v>108.0622123875131</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -4459,7 +4462,7 @@
         <v>294</v>
       </c>
       <c r="B294" s="1">
-        <v>107.6620628159967</v>
+        <v>108.0465636317181</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -4467,7 +4470,7 @@
         <v>295</v>
       </c>
       <c r="B295" s="1">
-        <v>107.6618283298141</v>
+        <v>108.003662837364</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -4475,7 +4478,7 @@
         <v>296</v>
       </c>
       <c r="B296" s="1">
-        <v>107.6442843714625</v>
+        <v>108.002386312841</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -4483,7 +4486,7 @@
         <v>297</v>
       </c>
       <c r="B297" s="1">
-        <v>107.6225026410125</v>
+        <v>107.9538240210518</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -4491,7 +4494,7 @@
         <v>298</v>
       </c>
       <c r="B298" s="1">
-        <v>107.6188080514157</v>
+        <v>107.945458626981</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -4499,7 +4502,7 @@
         <v>299</v>
       </c>
       <c r="B299" s="1">
-        <v>107.6177857591665</v>
+        <v>107.9395554530802</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -4507,7 +4510,7 @@
         <v>300</v>
       </c>
       <c r="B300" s="1">
-        <v>107.5891737574686</v>
+        <v>107.9130329777617</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -4515,7 +4518,7 @@
         <v>301</v>
       </c>
       <c r="B301" s="1">
-        <v>107.5886522526593</v>
+        <v>107.9105849722599</v>
       </c>
     </row>
     <row r="302" spans="1:2">
@@ -4523,7 +4526,7 @@
         <v>302</v>
       </c>
       <c r="B302" s="1">
-        <v>107.5837295932754</v>
+        <v>107.8139259843787</v>
       </c>
     </row>
     <row r="303" spans="1:2">
@@ -4531,7 +4534,7 @@
         <v>303</v>
       </c>
       <c r="B303" s="1">
-        <v>107.5277221786158</v>
+        <v>107.8078303889354</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -4539,7 +4542,7 @@
         <v>304</v>
       </c>
       <c r="B304" s="1">
-        <v>107.4946858977501</v>
+        <v>107.7559884002194</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -4547,7 +4550,7 @@
         <v>305</v>
       </c>
       <c r="B305" s="1">
-        <v>107.4917818034271</v>
+        <v>107.7279908685672</v>
       </c>
     </row>
     <row r="306" spans="1:2">
@@ -4555,7 +4558,7 @@
         <v>306</v>
       </c>
       <c r="B306" s="1">
-        <v>107.4843324345364</v>
+        <v>107.6933068619881</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -4563,7 +4566,7 @@
         <v>307</v>
       </c>
       <c r="B307" s="1">
-        <v>107.46973639812</v>
+        <v>107.6798833030373</v>
       </c>
     </row>
     <row r="308" spans="1:2">
@@ -4571,7 +4574,7 @@
         <v>308</v>
       </c>
       <c r="B308" s="1">
-        <v>107.4403433076816</v>
+        <v>107.6756876174751</v>
       </c>
     </row>
     <row r="309" spans="1:2">
@@ -4579,7 +4582,7 @@
         <v>309</v>
       </c>
       <c r="B309" s="1">
-        <v>107.4282262655243</v>
+        <v>107.6628035813256</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -4587,7 +4590,7 @@
         <v>310</v>
       </c>
       <c r="B310" s="1">
-        <v>107.4121037911361</v>
+        <v>107.6530972909622</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -4595,7 +4598,7 @@
         <v>311</v>
       </c>
       <c r="B311" s="1">
-        <v>107.4052464759697</v>
+        <v>107.6436530229184</v>
       </c>
     </row>
     <row r="312" spans="1:2">
@@ -4603,7 +4606,7 @@
         <v>312</v>
       </c>
       <c r="B312" s="1">
-        <v>107.3957115794868</v>
+        <v>107.6263986978364</v>
       </c>
     </row>
     <row r="313" spans="1:2">
@@ -4611,7 +4614,7 @@
         <v>313</v>
       </c>
       <c r="B313" s="1">
-        <v>107.3521280326701</v>
+        <v>107.6223413119346</v>
       </c>
     </row>
     <row r="314" spans="1:2">
@@ -4619,7 +4622,7 @@
         <v>314</v>
       </c>
       <c r="B314" s="1">
-        <v>107.3361948581132</v>
+        <v>107.5907889638281</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -4627,7 +4630,7 @@
         <v>315</v>
       </c>
       <c r="B315" s="1">
-        <v>107.3106870293134</v>
+        <v>107.5872816180018</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -4635,7 +4638,7 @@
         <v>316</v>
       </c>
       <c r="B316" s="1">
-        <v>107.3078292683225</v>
+        <v>107.5648664925108</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -4643,7 +4646,7 @@
         <v>317</v>
       </c>
       <c r="B317" s="1">
-        <v>107.2970227881309</v>
+        <v>107.5148926780217</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -4651,7 +4654,7 @@
         <v>318</v>
       </c>
       <c r="B318" s="1">
-        <v>107.2921744975198</v>
+        <v>107.4797625149438</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -4659,7 +4662,7 @@
         <v>319</v>
       </c>
       <c r="B319" s="1">
-        <v>107.2727279353326</v>
+        <v>107.4618472909325</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -4667,7 +4670,7 @@
         <v>320</v>
       </c>
       <c r="B320" s="1">
-        <v>107.2645113551407</v>
+        <v>107.4496395367866</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -4675,7 +4678,7 @@
         <v>321</v>
       </c>
       <c r="B321" s="1">
-        <v>107.2638749470507</v>
+        <v>107.4451640360849</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -4683,7 +4686,7 @@
         <v>322</v>
       </c>
       <c r="B322" s="1">
-        <v>107.2121730670316</v>
+        <v>107.4418598881684</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -4691,7 +4694,7 @@
         <v>323</v>
       </c>
       <c r="B323" s="1">
-        <v>107.2097102106367</v>
+        <v>107.384456201249</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -4699,7 +4702,7 @@
         <v>324</v>
       </c>
       <c r="B324" s="1">
-        <v>107.1776592051601</v>
+        <v>107.3806410866355</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -4707,7 +4710,7 @@
         <v>325</v>
       </c>
       <c r="B325" s="1">
-        <v>107.174362194882</v>
+        <v>107.3747889509628</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -4715,7 +4718,7 @@
         <v>326</v>
       </c>
       <c r="B326" s="1">
-        <v>107.157017510286</v>
+        <v>107.3746434072834</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -4723,7 +4726,7 @@
         <v>327</v>
       </c>
       <c r="B327" s="1">
-        <v>107.156444133081</v>
+        <v>107.3660385466621</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -4731,7 +4734,7 @@
         <v>328</v>
       </c>
       <c r="B328" s="1">
-        <v>107.1305780736901</v>
+        <v>107.3575398996683</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -4739,7 +4742,7 @@
         <v>329</v>
       </c>
       <c r="B329" s="1">
-        <v>107.122830153029</v>
+        <v>107.3429081681908</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -4747,7 +4750,7 @@
         <v>330</v>
       </c>
       <c r="B330" s="1">
-        <v>107.0862998626522</v>
+        <v>107.3281372868132</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -4755,7 +4758,7 @@
         <v>331</v>
       </c>
       <c r="B331" s="1">
-        <v>107.0609401701599</v>
+        <v>107.2662809710205</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -4763,7 +4766,7 @@
         <v>332</v>
       </c>
       <c r="B332" s="1">
-        <v>107.04698036168</v>
+        <v>107.2256942982979</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -4771,7 +4774,7 @@
         <v>333</v>
       </c>
       <c r="B333" s="1">
-        <v>107.0092206545987</v>
+        <v>107.2012296744143</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -4779,7 +4782,7 @@
         <v>334</v>
       </c>
       <c r="B334" s="1">
-        <v>107.0059397640808</v>
+        <v>107.109666896585</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -4787,7 +4790,7 @@
         <v>335</v>
       </c>
       <c r="B335" s="1">
-        <v>106.9995709084778</v>
+        <v>107.0915465224824</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -4795,7 +4798,7 @@
         <v>336</v>
       </c>
       <c r="B336" s="1">
-        <v>106.9859357966642</v>
+        <v>107.0858910111489</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -4803,7 +4806,7 @@
         <v>337</v>
       </c>
       <c r="B337" s="1">
-        <v>106.9844110734444</v>
+        <v>107.0841235192</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -4811,7 +4814,7 @@
         <v>338</v>
       </c>
       <c r="B338" s="1">
-        <v>106.9744675100796</v>
+        <v>107.0563343095028</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -4819,7 +4822,7 @@
         <v>339</v>
       </c>
       <c r="B339" s="1">
-        <v>106.9568496702838</v>
+        <v>107.0451752608331</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -4827,7 +4830,7 @@
         <v>340</v>
       </c>
       <c r="B340" s="1">
-        <v>106.9327690335236</v>
+        <v>107.026217134934</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -4835,7 +4838,7 @@
         <v>341</v>
       </c>
       <c r="B341" s="1">
-        <v>106.9259691788386</v>
+        <v>107.0164801716641</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -4843,7 +4846,7 @@
         <v>342</v>
       </c>
       <c r="B342" s="1">
-        <v>106.9053240006801</v>
+        <v>107.0120781374529</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -4851,7 +4854,7 @@
         <v>343</v>
       </c>
       <c r="B343" s="1">
-        <v>106.8686562838427</v>
+        <v>107.0111371229488</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -4859,7 +4862,7 @@
         <v>344</v>
       </c>
       <c r="B344" s="1">
-        <v>106.8646880610034</v>
+        <v>106.966866315193</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -4867,7 +4870,7 @@
         <v>345</v>
       </c>
       <c r="B345" s="1">
-        <v>106.8499951028302</v>
+        <v>106.9463437667861</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -4875,7 +4878,7 @@
         <v>346</v>
       </c>
       <c r="B346" s="1">
-        <v>106.8295121422154</v>
+        <v>106.9173028811712</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -4883,7 +4886,7 @@
         <v>347</v>
       </c>
       <c r="B347" s="1">
-        <v>106.8016424413377</v>
+        <v>106.8588926487439</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -4891,7 +4894,7 @@
         <v>348</v>
       </c>
       <c r="B348" s="1">
-        <v>106.7748386718829</v>
+        <v>106.833727801759</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -4899,7 +4902,7 @@
         <v>349</v>
       </c>
       <c r="B349" s="1">
-        <v>106.7720110633728</v>
+        <v>106.8220255582123</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -4907,7 +4910,7 @@
         <v>350</v>
       </c>
       <c r="B350" s="1">
-        <v>106.7413965088057</v>
+        <v>106.7949266581302</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -4915,7 +4918,7 @@
         <v>351</v>
       </c>
       <c r="B351" s="1">
-        <v>106.7387455472268</v>
+        <v>106.7939741659042</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -4923,7 +4926,7 @@
         <v>352</v>
       </c>
       <c r="B352" s="1">
-        <v>106.7261574437181</v>
+        <v>106.7701065500572</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -4931,7 +4934,7 @@
         <v>353</v>
       </c>
       <c r="B353" s="1">
-        <v>106.722867873317</v>
+        <v>106.7552900479144</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -4939,7 +4942,7 @@
         <v>354</v>
       </c>
       <c r="B354" s="1">
-        <v>106.7110437439044</v>
+        <v>106.7423378050291</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -4947,7 +4950,7 @@
         <v>355</v>
       </c>
       <c r="B355" s="1">
-        <v>106.6425521377843</v>
+        <v>106.7404843361148</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -4955,7 +4958,7 @@
         <v>356</v>
       </c>
       <c r="B356" s="1">
-        <v>106.6312649919673</v>
+        <v>106.7193112211685</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -4963,7 +4966,7 @@
         <v>357</v>
       </c>
       <c r="B357" s="1">
-        <v>106.619699106584</v>
+        <v>106.6779945669984</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -4971,7 +4974,7 @@
         <v>358</v>
       </c>
       <c r="B358" s="1">
-        <v>106.5675470663586</v>
+        <v>106.6477354117203</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -4979,7 +4982,7 @@
         <v>359</v>
       </c>
       <c r="B359" s="1">
-        <v>106.5581910876991</v>
+        <v>106.645192739169</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -4987,7 +4990,7 @@
         <v>360</v>
       </c>
       <c r="B360" s="1">
-        <v>106.5244797672222</v>
+        <v>106.6155044781671</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -4995,7 +4998,7 @@
         <v>361</v>
       </c>
       <c r="B361" s="1">
-        <v>106.5101975939811</v>
+        <v>106.5943136133497</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -5003,7 +5006,7 @@
         <v>362</v>
       </c>
       <c r="B362" s="1">
-        <v>106.5018111581585</v>
+        <v>106.5729312499874</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -5011,7 +5014,7 @@
         <v>363</v>
       </c>
       <c r="B363" s="1">
-        <v>106.4991323124589</v>
+        <v>106.5449403961863</v>
       </c>
     </row>
     <row r="364" spans="1:2">
@@ -5019,7 +5022,7 @@
         <v>364</v>
       </c>
       <c r="B364" s="1">
-        <v>106.4976492378107</v>
+        <v>106.5350203184401</v>
       </c>
     </row>
     <row r="365" spans="1:2">
@@ -5027,7 +5030,7 @@
         <v>365</v>
       </c>
       <c r="B365" s="1">
-        <v>106.4843417498122</v>
+        <v>106.5306968144827</v>
       </c>
     </row>
     <row r="366" spans="1:2">
@@ -5035,7 +5038,7 @@
         <v>366</v>
       </c>
       <c r="B366" s="1">
-        <v>106.4555014588435</v>
+        <v>106.4870965502756</v>
       </c>
     </row>
     <row r="367" spans="1:2">
@@ -5043,7 +5046,7 @@
         <v>367</v>
       </c>
       <c r="B367" s="1">
-        <v>106.4407695078929</v>
+        <v>106.4854830497579</v>
       </c>
     </row>
     <row r="368" spans="1:2">
@@ -5051,7 +5054,7 @@
         <v>368</v>
       </c>
       <c r="B368" s="1">
-        <v>106.4158314376268</v>
+        <v>106.4807264380406</v>
       </c>
     </row>
     <row r="369" spans="1:2">
@@ -5059,7 +5062,7 @@
         <v>369</v>
       </c>
       <c r="B369" s="1">
-        <v>106.4048853962495</v>
+        <v>106.4796472676229</v>
       </c>
     </row>
     <row r="370" spans="1:2">
@@ -5067,7 +5070,7 @@
         <v>370</v>
       </c>
       <c r="B370" s="1">
-        <v>106.3817427130815</v>
+        <v>106.4742824754439</v>
       </c>
     </row>
     <row r="371" spans="1:2">
@@ -5075,7 +5078,7 @@
         <v>371</v>
       </c>
       <c r="B371" s="1">
-        <v>106.3809607643407</v>
+        <v>106.4651067065302</v>
       </c>
     </row>
     <row r="372" spans="1:2">
@@ -5083,7 +5086,7 @@
         <v>372</v>
       </c>
       <c r="B372" s="1">
-        <v>106.3582058094647</v>
+        <v>106.455839056173</v>
       </c>
     </row>
     <row r="373" spans="1:2">
@@ -5091,7 +5094,7 @@
         <v>373</v>
       </c>
       <c r="B373" s="1">
-        <v>106.3484509014427</v>
+        <v>106.4519037067508</v>
       </c>
     </row>
     <row r="374" spans="1:2">
@@ -5099,7 +5102,7 @@
         <v>374</v>
       </c>
       <c r="B374" s="1">
-        <v>106.3419733116478</v>
+        <v>106.4484454960322</v>
       </c>
     </row>
     <row r="375" spans="1:2">
@@ -5107,7 +5110,7 @@
         <v>375</v>
       </c>
       <c r="B375" s="1">
-        <v>106.3390128579726</v>
+        <v>106.4407695078929</v>
       </c>
     </row>
     <row r="376" spans="1:2">
@@ -5115,7 +5118,7 @@
         <v>376</v>
       </c>
       <c r="B376" s="1">
-        <v>106.3324972784344</v>
+        <v>106.429227806932</v>
       </c>
     </row>
     <row r="377" spans="1:2">
@@ -5123,7 +5126,7 @@
         <v>377</v>
       </c>
       <c r="B377" s="1">
-        <v>106.3162129751284</v>
+        <v>106.4270800571772</v>
       </c>
     </row>
     <row r="378" spans="1:2">
@@ -5131,7 +5134,7 @@
         <v>378</v>
       </c>
       <c r="B378" s="1">
-        <v>106.2873414784253</v>
+        <v>106.3875990083122</v>
       </c>
     </row>
     <row r="379" spans="1:2">
@@ -5139,7 +5142,7 @@
         <v>379</v>
       </c>
       <c r="B379" s="1">
-        <v>106.2706435331995</v>
+        <v>106.3717848158085</v>
       </c>
     </row>
     <row r="380" spans="1:2">
@@ -5147,7 +5150,7 @@
         <v>380</v>
       </c>
       <c r="B380" s="1">
-        <v>106.2704787918382</v>
+        <v>106.352957438737</v>
       </c>
     </row>
     <row r="381" spans="1:2">
@@ -5155,7 +5158,7 @@
         <v>381</v>
       </c>
       <c r="B381" s="1">
-        <v>106.2698047812122</v>
+        <v>106.3485833470954</v>
       </c>
     </row>
     <row r="382" spans="1:2">
@@ -5163,7 +5166,7 @@
         <v>382</v>
       </c>
       <c r="B382" s="1">
-        <v>106.236636832187</v>
+        <v>106.3322154413341</v>
       </c>
     </row>
     <row r="383" spans="1:2">
@@ -5171,7 +5174,7 @@
         <v>383</v>
       </c>
       <c r="B383" s="1">
-        <v>106.2097944613101</v>
+        <v>106.3289114895426</v>
       </c>
     </row>
     <row r="384" spans="1:2">
@@ -5179,7 +5182,7 @@
         <v>384</v>
       </c>
       <c r="B384" s="1">
-        <v>106.2030206093237</v>
+        <v>106.323615806129</v>
       </c>
     </row>
     <row r="385" spans="1:2">
@@ -5187,7 +5190,7 @@
         <v>385</v>
       </c>
       <c r="B385" s="1">
-        <v>106.196301800066</v>
+        <v>106.3173335759833</v>
       </c>
     </row>
     <row r="386" spans="1:2">
@@ -5195,7 +5198,7 @@
         <v>386</v>
       </c>
       <c r="B386" s="1">
-        <v>106.1854980709998</v>
+        <v>106.3155182937835</v>
       </c>
     </row>
     <row r="387" spans="1:2">
@@ -5203,7 +5206,7 @@
         <v>387</v>
       </c>
       <c r="B387" s="1">
-        <v>106.173755909117</v>
+        <v>106.297821290336</v>
       </c>
     </row>
     <row r="388" spans="1:2">
@@ -5211,7 +5214,7 @@
         <v>388</v>
       </c>
       <c r="B388" s="1">
-        <v>106.1669557002319</v>
+        <v>106.2776212839907</v>
       </c>
     </row>
     <row r="389" spans="1:2">
@@ -5219,7 +5222,7 @@
         <v>389</v>
       </c>
       <c r="B389" s="1">
-        <v>106.1409083159317</v>
+        <v>106.2747428401356</v>
       </c>
     </row>
     <row r="390" spans="1:2">
@@ -5227,7 +5230,7 @@
         <v>390</v>
       </c>
       <c r="B390" s="1">
-        <v>106.1314013944217</v>
+        <v>106.253675472367</v>
       </c>
     </row>
     <row r="391" spans="1:2">
@@ -5235,7 +5238,7 @@
         <v>391</v>
       </c>
       <c r="B391" s="1">
-        <v>106.1310333394876</v>
+        <v>106.2421522580198</v>
       </c>
     </row>
     <row r="392" spans="1:2">
@@ -5243,7 +5246,7 @@
         <v>392</v>
       </c>
       <c r="B392" s="1">
-        <v>106.1091239133034</v>
+        <v>106.2243114667919</v>
       </c>
     </row>
     <row r="393" spans="1:2">
@@ -5251,7 +5254,7 @@
         <v>393</v>
       </c>
       <c r="B393" s="1">
-        <v>106.1027567037186</v>
+        <v>106.1952019026901</v>
       </c>
     </row>
     <row r="394" spans="1:2">
@@ -5259,7 +5262,7 @@
         <v>394</v>
       </c>
       <c r="B394" s="1">
-        <v>106.0890515990323</v>
+        <v>106.1762441472701</v>
       </c>
     </row>
     <row r="395" spans="1:2">
@@ -5267,7 +5270,7 @@
         <v>395</v>
       </c>
       <c r="B395" s="1">
-        <v>106.0651543539861</v>
+        <v>106.1669557002319</v>
       </c>
     </row>
     <row r="396" spans="1:2">
@@ -5275,7 +5278,7 @@
         <v>396</v>
       </c>
       <c r="B396" s="1">
-        <v>106.0533138097109</v>
+        <v>106.1099372882424</v>
       </c>
     </row>
     <row r="397" spans="1:2">
@@ -5283,7 +5286,7 @@
         <v>397</v>
       </c>
       <c r="B397" s="1">
-        <v>106.0513248040899</v>
+        <v>106.099415227014</v>
       </c>
     </row>
     <row r="398" spans="1:2">
@@ -5291,7 +5294,7 @@
         <v>398</v>
       </c>
       <c r="B398" s="1">
-        <v>106.0480512226022</v>
+        <v>106.0877809526078</v>
       </c>
     </row>
     <row r="399" spans="1:2">
@@ -5299,7 +5302,7 @@
         <v>399</v>
       </c>
       <c r="B399" s="1">
-        <v>106.0187871460006</v>
+        <v>106.0703311833729</v>
       </c>
     </row>
     <row r="400" spans="1:2">
@@ -5307,7 +5310,7 @@
         <v>400</v>
       </c>
       <c r="B400" s="1">
-        <v>105.9912985539242</v>
+        <v>106.0246724607433</v>
       </c>
     </row>
     <row r="401" spans="1:2">
@@ -5315,7 +5318,7 @@
         <v>401</v>
       </c>
       <c r="B401" s="1">
-        <v>105.9316123283701</v>
+        <v>106.0232973193135</v>
       </c>
     </row>
     <row r="402" spans="1:2">
@@ -5323,7 +5326,7 @@
         <v>402</v>
       </c>
       <c r="B402" s="1">
-        <v>105.9286679459907</v>
+        <v>106.0211794003444</v>
       </c>
     </row>
     <row r="403" spans="1:2">
@@ -5331,7 +5334,7 @@
         <v>403</v>
       </c>
       <c r="B403" s="1">
-        <v>105.9251616291667</v>
+        <v>105.9893041604697</v>
       </c>
     </row>
     <row r="404" spans="1:2">
@@ -5339,7 +5342,7 @@
         <v>404</v>
       </c>
       <c r="B404" s="1">
-        <v>105.9101642722887</v>
+        <v>105.9633146989555</v>
       </c>
     </row>
     <row r="405" spans="1:2">
@@ -5347,7 +5350,7 @@
         <v>405</v>
       </c>
       <c r="B405" s="1">
-        <v>105.865968376186</v>
+        <v>105.9297337399377</v>
       </c>
     </row>
     <row r="406" spans="1:2">
@@ -5355,7 +5358,7 @@
         <v>406</v>
       </c>
       <c r="B406" s="1">
-        <v>105.839064241855</v>
+        <v>105.8970866037624</v>
       </c>
     </row>
     <row r="407" spans="1:2">
@@ -5363,7 +5366,7 @@
         <v>407</v>
       </c>
       <c r="B407" s="1">
-        <v>105.830136130912</v>
+        <v>105.8950658315015</v>
       </c>
     </row>
     <row r="408" spans="1:2">
@@ -5371,7 +5374,7 @@
         <v>408</v>
       </c>
       <c r="B408" s="1">
-        <v>105.8113367781082</v>
+        <v>105.8944097173882</v>
       </c>
     </row>
     <row r="409" spans="1:2">
@@ -5379,7 +5382,7 @@
         <v>409</v>
       </c>
       <c r="B409" s="1">
-        <v>105.8077544527077</v>
+        <v>105.8932357532183</v>
       </c>
     </row>
     <row r="410" spans="1:2">
@@ -5387,7 +5390,7 @@
         <v>410</v>
       </c>
       <c r="B410" s="1">
-        <v>105.8062087332248</v>
+        <v>105.8762019963215</v>
       </c>
     </row>
     <row r="411" spans="1:2">
@@ -5395,7 +5398,7 @@
         <v>411</v>
       </c>
       <c r="B411" s="1">
-        <v>105.8012257935768</v>
+        <v>105.8640960051514</v>
       </c>
     </row>
     <row r="412" spans="1:2">
@@ -5403,7 +5406,7 @@
         <v>412</v>
       </c>
       <c r="B412" s="1">
-        <v>105.7934121252259</v>
+        <v>105.8638133996012</v>
       </c>
     </row>
     <row r="413" spans="1:2">
@@ -5411,7 +5414,7 @@
         <v>413</v>
       </c>
       <c r="B413" s="1">
-        <v>105.7691454336142</v>
+        <v>105.8574761653746</v>
       </c>
     </row>
     <row r="414" spans="1:2">
@@ -5419,7 +5422,7 @@
         <v>414</v>
       </c>
       <c r="B414" s="1">
-        <v>105.7690637093579</v>
+        <v>105.8484374176865</v>
       </c>
     </row>
     <row r="415" spans="1:2">
@@ -5427,7 +5430,7 @@
         <v>415</v>
       </c>
       <c r="B415" s="1">
-        <v>105.7642546526346</v>
+        <v>105.8333668321061</v>
       </c>
     </row>
     <row r="416" spans="1:2">
@@ -5435,7 +5438,7 @@
         <v>416</v>
       </c>
       <c r="B416" s="1">
-        <v>105.7641433702202</v>
+        <v>105.8054750881072</v>
       </c>
     </row>
     <row r="417" spans="1:2">
@@ -5443,7 +5446,7 @@
         <v>417</v>
       </c>
       <c r="B417" s="1">
-        <v>105.7528516468853</v>
+        <v>105.7960084175067</v>
       </c>
     </row>
     <row r="418" spans="1:2">
@@ -5451,7 +5454,7 @@
         <v>418</v>
       </c>
       <c r="B418" s="1">
-        <v>105.7253771669574</v>
+        <v>105.7884055373517</v>
       </c>
     </row>
     <row r="419" spans="1:2">
@@ -5459,7 +5462,7 @@
         <v>419</v>
       </c>
       <c r="B419" s="1">
-        <v>105.6833470828783</v>
+        <v>105.7627920778724</v>
       </c>
     </row>
     <row r="420" spans="1:2">
@@ -5467,7 +5470,7 @@
         <v>420</v>
       </c>
       <c r="B420" s="1">
-        <v>105.6738340462075</v>
+        <v>105.7567532819876</v>
       </c>
     </row>
     <row r="421" spans="1:2">
@@ -5475,7 +5478,7 @@
         <v>421</v>
       </c>
       <c r="B421" s="1">
-        <v>105.6320609090326</v>
+        <v>105.7402877722121</v>
       </c>
     </row>
     <row r="422" spans="1:2">
@@ -5483,7 +5486,7 @@
         <v>422</v>
       </c>
       <c r="B422" s="1">
-        <v>105.6300270460606</v>
+        <v>105.7297117816681</v>
       </c>
     </row>
     <row r="423" spans="1:2">
@@ -5491,7 +5494,7 @@
         <v>423</v>
       </c>
       <c r="B423" s="1">
-        <v>105.6142628094166</v>
+        <v>105.7221503787879</v>
       </c>
     </row>
     <row r="424" spans="1:2">
@@ -5499,7 +5502,7 @@
         <v>424</v>
       </c>
       <c r="B424" s="1">
-        <v>105.5925817345525</v>
+        <v>105.6845736658943</v>
       </c>
     </row>
     <row r="425" spans="1:2">
@@ -5507,7 +5510,7 @@
         <v>425</v>
       </c>
       <c r="B425" s="1">
-        <v>105.590896732892</v>
+        <v>105.6829838898915</v>
       </c>
     </row>
     <row r="426" spans="1:2">
@@ -5515,7 +5518,7 @@
         <v>426</v>
       </c>
       <c r="B426" s="1">
-        <v>105.5597458206934</v>
+        <v>105.6777951531306</v>
       </c>
     </row>
     <row r="427" spans="1:2">
@@ -5523,7 +5526,7 @@
         <v>427</v>
       </c>
       <c r="B427" s="1">
-        <v>105.5501452699919</v>
+        <v>105.6733446943171</v>
       </c>
     </row>
     <row r="428" spans="1:2">
@@ -5531,7 +5534,7 @@
         <v>428</v>
       </c>
       <c r="B428" s="1">
-        <v>105.5433583484362</v>
+        <v>105.6712901138323</v>
       </c>
     </row>
     <row r="429" spans="1:2">
@@ -5539,7 +5542,7 @@
         <v>429</v>
       </c>
       <c r="B429" s="1">
-        <v>105.5391966347814</v>
+        <v>105.6542628807561</v>
       </c>
     </row>
     <row r="430" spans="1:2">
@@ -5547,7 +5550,7 @@
         <v>430</v>
       </c>
       <c r="B430" s="1">
-        <v>105.5387883204472</v>
+        <v>105.6062125833429</v>
       </c>
     </row>
     <row r="431" spans="1:2">
@@ -5555,7 +5558,7 @@
         <v>431</v>
       </c>
       <c r="B431" s="1">
-        <v>105.5356675067985</v>
+        <v>105.5989084897128</v>
       </c>
     </row>
     <row r="432" spans="1:2">
@@ -5563,7 +5566,7 @@
         <v>432</v>
       </c>
       <c r="B432" s="1">
-        <v>105.5269522740494</v>
+        <v>105.5556677619487</v>
       </c>
     </row>
     <row r="433" spans="1:2">
@@ -5571,7 +5574,7 @@
         <v>433</v>
       </c>
       <c r="B433" s="1">
-        <v>105.5156212657483</v>
+        <v>105.5536755626248</v>
       </c>
     </row>
     <row r="434" spans="1:2">
@@ -5579,7 +5582,7 @@
         <v>434</v>
       </c>
       <c r="B434" s="1">
-        <v>105.5124577817305</v>
+        <v>105.5422086563192</v>
       </c>
     </row>
     <row r="435" spans="1:2">
@@ -5587,7 +5590,7 @@
         <v>435</v>
       </c>
       <c r="B435" s="1">
-        <v>105.5049401655169</v>
+        <v>105.5342315815447</v>
       </c>
     </row>
     <row r="436" spans="1:2">
@@ -5595,7 +5598,7 @@
         <v>436</v>
       </c>
       <c r="B436" s="1">
-        <v>105.4846625138025</v>
+        <v>105.5221511916573</v>
       </c>
     </row>
     <row r="437" spans="1:2">
@@ -5603,7 +5606,7 @@
         <v>437</v>
       </c>
       <c r="B437" s="1">
-        <v>105.474750790334</v>
+        <v>105.5116940970566</v>
       </c>
     </row>
     <row r="438" spans="1:2">
@@ -5611,7 +5614,7 @@
         <v>438</v>
       </c>
       <c r="B438" s="1">
-        <v>105.4503996394532</v>
+        <v>105.4919953968144</v>
       </c>
     </row>
     <row r="439" spans="1:2">
@@ -5619,7 +5622,7 @@
         <v>439</v>
       </c>
       <c r="B439" s="1">
-        <v>105.4329235796929</v>
+        <v>105.4848077746656</v>
       </c>
     </row>
     <row r="440" spans="1:2">
@@ -5627,7 +5630,7 @@
         <v>440</v>
       </c>
       <c r="B440" s="1">
-        <v>105.4253569561411</v>
+        <v>105.4672456146157</v>
       </c>
     </row>
     <row r="441" spans="1:2">
@@ -5635,7 +5638,7 @@
         <v>441</v>
       </c>
       <c r="B441" s="1">
-        <v>105.3817782762477</v>
+        <v>105.4664792002312</v>
       </c>
     </row>
     <row r="442" spans="1:2">
@@ -5643,7 +5646,7 @@
         <v>442</v>
       </c>
       <c r="B442" s="1">
-        <v>105.3807756364774</v>
+        <v>105.4296165260314</v>
       </c>
     </row>
     <row r="443" spans="1:2">
@@ -5651,7 +5654,7 @@
         <v>443</v>
       </c>
       <c r="B443" s="1">
-        <v>105.3355464761853</v>
+        <v>105.4248876190444</v>
       </c>
     </row>
     <row r="444" spans="1:2">
@@ -5659,7 +5662,7 @@
         <v>444</v>
       </c>
       <c r="B444" s="1">
-        <v>105.3263801789621</v>
+        <v>105.4163504027706</v>
       </c>
     </row>
     <row r="445" spans="1:2">
@@ -5667,7 +5670,7 @@
         <v>445</v>
       </c>
       <c r="B445" s="1">
-        <v>105.3260596216083</v>
+        <v>105.3980524208967</v>
       </c>
     </row>
     <row r="446" spans="1:2">
@@ -5675,7 +5678,7 @@
         <v>446</v>
       </c>
       <c r="B446" s="1">
-        <v>105.316717281498</v>
+        <v>105.3966732047052</v>
       </c>
     </row>
     <row r="447" spans="1:2">
@@ -5683,7 +5686,7 @@
         <v>447</v>
       </c>
       <c r="B447" s="1">
-        <v>105.3142264135533</v>
+        <v>105.3886985443242</v>
       </c>
     </row>
     <row r="448" spans="1:2">
@@ -5691,7 +5694,7 @@
         <v>448</v>
       </c>
       <c r="B448" s="1">
-        <v>105.3127864920982</v>
+        <v>105.3572990890851</v>
       </c>
     </row>
     <row r="449" spans="1:2">
@@ -5699,7 +5702,7 @@
         <v>449</v>
       </c>
       <c r="B449" s="1">
-        <v>105.2964935201929</v>
+        <v>105.3045244690618</v>
       </c>
     </row>
     <row r="450" spans="1:2">
@@ -5707,7 +5710,7 @@
         <v>450</v>
       </c>
       <c r="B450" s="1">
-        <v>105.2964609695569</v>
+        <v>105.2970810887428</v>
       </c>
     </row>
     <row r="451" spans="1:2">
@@ -5715,7 +5718,7 @@
         <v>451</v>
       </c>
       <c r="B451" s="1">
-        <v>105.2915371468971</v>
+        <v>105.2969815651035</v>
       </c>
     </row>
     <row r="452" spans="1:2">
@@ -5723,7 +5726,7 @@
         <v>452</v>
       </c>
       <c r="B452" s="1">
-        <v>105.2914569081252</v>
+        <v>105.29380321222</v>
       </c>
     </row>
     <row r="453" spans="1:2">
@@ -5731,7 +5734,7 @@
         <v>453</v>
       </c>
       <c r="B453" s="1">
-        <v>105.2867653013711</v>
+        <v>105.2890409871318</v>
       </c>
     </row>
     <row r="454" spans="1:2">
@@ -5739,7 +5742,7 @@
         <v>454</v>
       </c>
       <c r="B454" s="1">
-        <v>105.269708664249</v>
+        <v>105.2640469378262</v>
       </c>
     </row>
     <row r="455" spans="1:2">
@@ -5747,7 +5750,7 @@
         <v>455</v>
       </c>
       <c r="B455" s="1">
-        <v>105.2640469378262</v>
+        <v>105.2601874347467</v>
       </c>
     </row>
     <row r="456" spans="1:2">
@@ -5755,7 +5758,7 @@
         <v>456</v>
       </c>
       <c r="B456" s="1">
-        <v>105.2596440240733</v>
+        <v>105.257866834156</v>
       </c>
     </row>
     <row r="457" spans="1:2">
@@ -5763,7 +5766,7 @@
         <v>457</v>
       </c>
       <c r="B457" s="1">
-        <v>105.2538571513283</v>
+        <v>105.2514376976126</v>
       </c>
     </row>
     <row r="458" spans="1:2">
@@ -5771,7 +5774,7 @@
         <v>458</v>
       </c>
       <c r="B458" s="1">
-        <v>105.249754546407</v>
+        <v>105.239844003637</v>
       </c>
     </row>
     <row r="459" spans="1:2">
@@ -5779,7 +5782,7 @@
         <v>459</v>
       </c>
       <c r="B459" s="1">
-        <v>105.2368477979764</v>
+        <v>105.222781743713</v>
       </c>
     </row>
     <row r="460" spans="1:2">
@@ -5787,7 +5790,7 @@
         <v>460</v>
       </c>
       <c r="B460" s="1">
-        <v>105.2340327439779</v>
+        <v>105.1776312637328</v>
       </c>
     </row>
     <row r="461" spans="1:2">
@@ -5795,7 +5798,7 @@
         <v>461</v>
       </c>
       <c r="B461" s="1">
-        <v>105.1954139445809</v>
+        <v>105.1714739746549</v>
       </c>
     </row>
     <row r="462" spans="1:2">
@@ -5803,7 +5806,7 @@
         <v>462</v>
       </c>
       <c r="B462" s="1">
-        <v>105.1846871563601</v>
+        <v>105.1612346313485</v>
       </c>
     </row>
     <row r="463" spans="1:2">
@@ -5811,7 +5814,7 @@
         <v>463</v>
       </c>
       <c r="B463" s="1">
-        <v>105.153757045428</v>
+        <v>105.156730376304</v>
       </c>
     </row>
     <row r="464" spans="1:2">
@@ -5819,7 +5822,7 @@
         <v>464</v>
       </c>
       <c r="B464" s="1">
-        <v>105.1355117495712</v>
+        <v>105.1554977896376</v>
       </c>
     </row>
     <row r="465" spans="1:2">
@@ -5827,7 +5830,7 @@
         <v>465</v>
       </c>
       <c r="B465" s="1">
-        <v>105.1201583447916</v>
+        <v>105.1480828919585</v>
       </c>
     </row>
     <row r="466" spans="1:2">
@@ -5835,7 +5838,7 @@
         <v>466</v>
       </c>
       <c r="B466" s="1">
-        <v>105.1188300795607</v>
+        <v>105.14343613701</v>
       </c>
     </row>
     <row r="467" spans="1:2">
@@ -5843,7 +5846,7 @@
         <v>467</v>
       </c>
       <c r="B467" s="1">
-        <v>105.1080544329615</v>
+        <v>105.1234723973482</v>
       </c>
     </row>
     <row r="468" spans="1:2">
@@ -5851,7 +5854,7 @@
         <v>468</v>
       </c>
       <c r="B468" s="1">
-        <v>105.0972919185189</v>
+        <v>105.0924379719654</v>
       </c>
     </row>
     <row r="469" spans="1:2">
@@ -5859,7 +5862,7 @@
         <v>469</v>
       </c>
       <c r="B469" s="1">
-        <v>105.0932838041471</v>
+        <v>105.0805664086608</v>
       </c>
     </row>
     <row r="470" spans="1:2">
@@ -5867,7 +5870,7 @@
         <v>470</v>
       </c>
       <c r="B470" s="1">
-        <v>105.0697217721997</v>
+        <v>105.0625030920476</v>
       </c>
     </row>
     <row r="471" spans="1:2">
@@ -5875,7 +5878,7 @@
         <v>471</v>
       </c>
       <c r="B471" s="1">
-        <v>105.0577261019518</v>
+        <v>105.0570849238609</v>
       </c>
     </row>
     <row r="472" spans="1:2">
@@ -5883,7 +5886,7 @@
         <v>472</v>
       </c>
       <c r="B472" s="1">
-        <v>105.0537433431772</v>
+        <v>105.0513601334753</v>
       </c>
     </row>
     <row r="473" spans="1:2">
@@ -5891,7 +5894,7 @@
         <v>473</v>
       </c>
       <c r="B473" s="1">
-        <v>105.0402749845284</v>
+        <v>105.0211185930062</v>
       </c>
     </row>
     <row r="474" spans="1:2">
@@ -5899,7 +5902,7 @@
         <v>474</v>
       </c>
       <c r="B474" s="1">
-        <v>105.0374816235702</v>
+        <v>105.0149410711593</v>
       </c>
     </row>
     <row r="475" spans="1:2">
@@ -5907,7 +5910,7 @@
         <v>475</v>
       </c>
       <c r="B475" s="1">
-        <v>105.0371368667724</v>
+        <v>105.0130553372464</v>
       </c>
     </row>
     <row r="476" spans="1:2">
@@ -5915,7 +5918,7 @@
         <v>476</v>
       </c>
       <c r="B476" s="1">
-        <v>105.0285641264457</v>
+        <v>104.9688608650702</v>
       </c>
     </row>
     <row r="477" spans="1:2">
@@ -5923,7 +5926,7 @@
         <v>477</v>
       </c>
       <c r="B477" s="1">
-        <v>105.0226492214299</v>
+        <v>104.9671958917019</v>
       </c>
     </row>
     <row r="478" spans="1:2">
@@ -5931,7 +5934,7 @@
         <v>478</v>
       </c>
       <c r="B478" s="1">
-        <v>105.0169911734385</v>
+        <v>104.9670775141016</v>
       </c>
     </row>
     <row r="479" spans="1:2">
@@ -5939,7 +5942,7 @@
         <v>479</v>
       </c>
       <c r="B479" s="1">
-        <v>104.9983361047902</v>
+        <v>104.9494440595956</v>
       </c>
     </row>
     <row r="480" spans="1:2">
@@ -5947,7 +5950,7 @@
         <v>480</v>
       </c>
       <c r="B480" s="1">
-        <v>104.9749752944884</v>
+        <v>104.948362804871</v>
       </c>
     </row>
     <row r="481" spans="1:2">
@@ -5955,7 +5958,7 @@
         <v>481</v>
       </c>
       <c r="B481" s="1">
-        <v>104.9689306974707</v>
+        <v>104.9405332243194</v>
       </c>
     </row>
     <row r="482" spans="1:2">
@@ -5963,7 +5966,7 @@
         <v>482</v>
       </c>
       <c r="B482" s="1">
-        <v>104.9682156581442</v>
+        <v>104.928500154273</v>
       </c>
     </row>
     <row r="483" spans="1:2">
@@ -5971,7 +5974,7 @@
         <v>483</v>
       </c>
       <c r="B483" s="1">
-        <v>104.9641484064791</v>
+        <v>104.9156951298375</v>
       </c>
     </row>
     <row r="484" spans="1:2">
@@ -5979,7 +5982,7 @@
         <v>484</v>
       </c>
       <c r="B484" s="1">
-        <v>104.9534343260471</v>
+        <v>104.9134823126955</v>
       </c>
     </row>
     <row r="485" spans="1:2">
@@ -5987,7 +5990,7 @@
         <v>485</v>
       </c>
       <c r="B485" s="1">
-        <v>104.9363804970694</v>
+        <v>104.9061023184472</v>
       </c>
     </row>
     <row r="486" spans="1:2">
@@ -5995,7 +5998,7 @@
         <v>486</v>
       </c>
       <c r="B486" s="1">
-        <v>104.9358479984597</v>
+        <v>104.9010789714852</v>
       </c>
     </row>
     <row r="487" spans="1:2">
@@ -6003,7 +6006,7 @@
         <v>487</v>
       </c>
       <c r="B487" s="1">
-        <v>104.9145990447985</v>
+        <v>104.8553612348782</v>
       </c>
     </row>
     <row r="488" spans="1:2">
@@ -6011,7 +6014,7 @@
         <v>488</v>
       </c>
       <c r="B488" s="1">
-        <v>104.9032015618063</v>
+        <v>104.8401422837286</v>
       </c>
     </row>
     <row r="489" spans="1:2">
@@ -6019,7 +6022,7 @@
         <v>489</v>
       </c>
       <c r="B489" s="1">
-        <v>104.8876313994029</v>
+        <v>104.8345010629741</v>
       </c>
     </row>
     <row r="490" spans="1:2">
@@ -6027,7 +6030,7 @@
         <v>490</v>
       </c>
       <c r="B490" s="1">
-        <v>104.8827254535633</v>
+        <v>104.824823661886</v>
       </c>
     </row>
     <row r="491" spans="1:2">
@@ -6035,7 +6038,7 @@
         <v>491</v>
       </c>
       <c r="B491" s="1">
-        <v>104.8787987073611</v>
+        <v>104.8118126855896</v>
       </c>
     </row>
     <row r="492" spans="1:2">
@@ -6043,7 +6046,7 @@
         <v>492</v>
       </c>
       <c r="B492" s="1">
-        <v>104.8776592748335</v>
+        <v>104.7966932175376</v>
       </c>
     </row>
     <row r="493" spans="1:2">
@@ -6051,7 +6054,7 @@
         <v>493</v>
       </c>
       <c r="B493" s="1">
-        <v>104.8641370378659</v>
+        <v>104.7935145667512</v>
       </c>
     </row>
     <row r="494" spans="1:2">
@@ -6059,7 +6062,7 @@
         <v>494</v>
       </c>
       <c r="B494" s="1">
-        <v>104.824823661886</v>
+        <v>104.7793411004945</v>
       </c>
     </row>
     <row r="495" spans="1:2">
@@ -6067,7 +6070,7 @@
         <v>495</v>
       </c>
       <c r="B495" s="1">
-        <v>104.8125569841868</v>
+        <v>104.7662088506687</v>
       </c>
     </row>
     <row r="496" spans="1:2">
@@ -6075,7 +6078,7 @@
         <v>496</v>
       </c>
       <c r="B496" s="1">
-        <v>104.8021554198291</v>
+        <v>104.7626533235989</v>
       </c>
     </row>
     <row r="497" spans="1:2">
@@ -6083,7 +6086,7 @@
         <v>497</v>
       </c>
       <c r="B497" s="1">
-        <v>104.7940804662536</v>
+        <v>104.7594579914139</v>
       </c>
     </row>
     <row r="498" spans="1:2">
@@ -6091,7 +6094,7 @@
         <v>498</v>
       </c>
       <c r="B498" s="1">
-        <v>104.7790180415666</v>
+        <v>104.7572195976193</v>
       </c>
     </row>
     <row r="499" spans="1:2">
@@ -6099,7 +6102,7 @@
         <v>499</v>
       </c>
       <c r="B499" s="1">
-        <v>104.76324824368</v>
+        <v>104.7378559552381</v>
       </c>
     </row>
     <row r="500" spans="1:2">
@@ -6107,7 +6110,7 @@
         <v>500</v>
       </c>
       <c r="B500" s="1">
-        <v>104.7540336455053</v>
+        <v>104.7052393020686</v>
       </c>
     </row>
     <row r="501" spans="1:2">
@@ -6115,7 +6118,7 @@
         <v>501</v>
       </c>
       <c r="B501" s="1">
-        <v>104.7227794095532</v>
+        <v>104.7013454523631</v>
       </c>
     </row>
     <row r="502" spans="1:2">
@@ -6123,7 +6126,7 @@
         <v>502</v>
       </c>
       <c r="B502" s="1">
-        <v>104.7144707645015</v>
+        <v>104.6803527444824</v>
       </c>
     </row>
     <row r="503" spans="1:2">
@@ -6131,7 +6134,7 @@
         <v>503</v>
       </c>
       <c r="B503" s="1">
-        <v>104.7105927984157</v>
+        <v>104.6779892608353</v>
       </c>
     </row>
     <row r="504" spans="1:2">
@@ -6139,7 +6142,7 @@
         <v>504</v>
       </c>
       <c r="B504" s="1">
-        <v>104.7012798177472</v>
+        <v>104.6700295397288</v>
       </c>
     </row>
     <row r="505" spans="1:2">
@@ -6147,7 +6150,7 @@
         <v>505</v>
       </c>
       <c r="B505" s="1">
-        <v>104.6677199945701</v>
+        <v>104.669537571727</v>
       </c>
     </row>
     <row r="506" spans="1:2">
@@ -6155,7 +6158,7 @@
         <v>506</v>
       </c>
       <c r="B506" s="1">
-        <v>104.6647527521165</v>
+        <v>104.6622282906328</v>
       </c>
     </row>
     <row r="507" spans="1:2">
@@ -6163,7 +6166,7 @@
         <v>507</v>
       </c>
       <c r="B507" s="1">
-        <v>104.6105907564984</v>
+        <v>104.6522176576728</v>
       </c>
     </row>
     <row r="508" spans="1:2">
@@ -6171,7 +6174,7 @@
         <v>508</v>
       </c>
       <c r="B508" s="1">
-        <v>104.6078701905604</v>
+        <v>104.6518642905216</v>
       </c>
     </row>
     <row r="509" spans="1:2">
@@ -6179,7 +6182,7 @@
         <v>509</v>
       </c>
       <c r="B509" s="1">
-        <v>104.6029773116609</v>
+        <v>104.639036494021</v>
       </c>
     </row>
     <row r="510" spans="1:2">
@@ -6187,7 +6190,7 @@
         <v>510</v>
       </c>
       <c r="B510" s="1">
-        <v>104.6019201800173</v>
+        <v>104.6360195163014</v>
       </c>
     </row>
     <row r="511" spans="1:2">
@@ -6195,7 +6198,7 @@
         <v>511</v>
       </c>
       <c r="B511" s="1">
-        <v>104.5899628472441</v>
+        <v>104.6322624206827</v>
       </c>
     </row>
     <row r="512" spans="1:2">
@@ -6203,7 +6206,7 @@
         <v>512</v>
       </c>
       <c r="B512" s="1">
-        <v>104.585397094434</v>
+        <v>104.6239308605246</v>
       </c>
     </row>
     <row r="513" spans="1:2">
@@ -6211,7 +6214,7 @@
         <v>513</v>
       </c>
       <c r="B513" s="1">
-        <v>104.5833041116294</v>
+        <v>104.614136529115</v>
       </c>
     </row>
     <row r="514" spans="1:2">
@@ -6219,7 +6222,7 @@
         <v>514</v>
       </c>
       <c r="B514" s="1">
-        <v>104.5788526104039</v>
+        <v>104.6049400651373</v>
       </c>
     </row>
     <row r="515" spans="1:2">
@@ -6227,7 +6230,7 @@
         <v>515</v>
       </c>
       <c r="B515" s="1">
-        <v>104.5740334147221</v>
+        <v>104.6027291174481</v>
       </c>
     </row>
     <row r="516" spans="1:2">
@@ -6235,7 +6238,7 @@
         <v>516</v>
       </c>
       <c r="B516" s="1">
-        <v>104.5726792610435</v>
+        <v>104.5930657403868</v>
       </c>
     </row>
     <row r="517" spans="1:2">
@@ -6243,7 +6246,7 @@
         <v>517</v>
       </c>
       <c r="B517" s="1">
-        <v>104.5689609783173</v>
+        <v>104.5744175473796</v>
       </c>
     </row>
     <row r="518" spans="1:2">
@@ -6251,7 +6254,7 @@
         <v>518</v>
       </c>
       <c r="B518" s="1">
-        <v>104.5532716952552</v>
+        <v>104.5453515813785</v>
       </c>
     </row>
     <row r="519" spans="1:2">
@@ -6259,7 +6262,7 @@
         <v>519</v>
       </c>
       <c r="B519" s="1">
-        <v>104.5488146529737</v>
+        <v>104.5350127274745</v>
       </c>
     </row>
     <row r="520" spans="1:2">
@@ -6267,7 +6270,7 @@
         <v>520</v>
       </c>
       <c r="B520" s="1">
-        <v>104.5297710479697</v>
+        <v>104.5135528266781</v>
       </c>
     </row>
     <row r="521" spans="1:2">
@@ -6275,7 +6278,7 @@
         <v>521</v>
       </c>
       <c r="B521" s="1">
-        <v>104.5276214320399</v>
+        <v>104.5039554119663</v>
       </c>
     </row>
     <row r="522" spans="1:2">
@@ -6283,7 +6286,7 @@
         <v>522</v>
       </c>
       <c r="B522" s="1">
-        <v>104.5212869185219</v>
+        <v>104.4995094747041</v>
       </c>
     </row>
     <row r="523" spans="1:2">
@@ -6291,7 +6294,7 @@
         <v>523</v>
       </c>
       <c r="B523" s="1">
-        <v>104.5212119210419</v>
+        <v>104.4961778069713</v>
       </c>
     </row>
     <row r="524" spans="1:2">
@@ -6299,7 +6302,7 @@
         <v>524</v>
       </c>
       <c r="B524" s="1">
-        <v>104.5134124012375</v>
+        <v>104.4957746108724</v>
       </c>
     </row>
     <row r="525" spans="1:2">
@@ -6307,7 +6310,7 @@
         <v>525</v>
       </c>
       <c r="B525" s="1">
-        <v>104.4824037553939</v>
+        <v>104.483762725143</v>
       </c>
     </row>
     <row r="526" spans="1:2">
@@ -6315,7 +6318,7 @@
         <v>526</v>
       </c>
       <c r="B526" s="1">
-        <v>104.4721302335236</v>
+        <v>104.4815042117634</v>
       </c>
     </row>
     <row r="527" spans="1:2">
@@ -6323,7 +6326,7 @@
         <v>527</v>
       </c>
       <c r="B527" s="1">
-        <v>104.4692056608185</v>
+        <v>104.4718453018802</v>
       </c>
     </row>
     <row r="528" spans="1:2">
@@ -6331,7 +6334,7 @@
         <v>528</v>
       </c>
       <c r="B528" s="1">
-        <v>104.452407617793</v>
+        <v>104.4674661166485</v>
       </c>
     </row>
     <row r="529" spans="1:2">
@@ -6339,7 +6342,7 @@
         <v>529</v>
       </c>
       <c r="B529" s="1">
-        <v>104.4477874183478</v>
+        <v>104.4667038754363</v>
       </c>
     </row>
     <row r="530" spans="1:2">
@@ -6347,7 +6350,7 @@
         <v>530</v>
       </c>
       <c r="B530" s="1">
-        <v>104.4259659851831</v>
+        <v>104.463065995931</v>
       </c>
     </row>
     <row r="531" spans="1:2">
@@ -6355,7 +6358,7 @@
         <v>531</v>
       </c>
       <c r="B531" s="1">
-        <v>104.3991760439085</v>
+        <v>104.4198642445151</v>
       </c>
     </row>
     <row r="532" spans="1:2">
@@ -6363,7 +6366,7 @@
         <v>532</v>
       </c>
       <c r="B532" s="1">
-        <v>104.3671669632064</v>
+        <v>104.4103742518681</v>
       </c>
     </row>
     <row r="533" spans="1:2">
@@ -6371,7 +6374,7 @@
         <v>533</v>
       </c>
       <c r="B533" s="1">
-        <v>104.3625564994703</v>
+        <v>104.4031571249002</v>
       </c>
     </row>
     <row r="534" spans="1:2">
@@ -6379,7 +6382,7 @@
         <v>534</v>
       </c>
       <c r="B534" s="1">
-        <v>104.3438028323874</v>
+        <v>104.3690918679949</v>
       </c>
     </row>
     <row r="535" spans="1:2">
@@ -6387,7 +6390,7 @@
         <v>535</v>
       </c>
       <c r="B535" s="1">
-        <v>104.3260812741813</v>
+        <v>104.3671341434208</v>
       </c>
     </row>
     <row r="536" spans="1:2">
@@ -6395,7 +6398,7 @@
         <v>536</v>
       </c>
       <c r="B536" s="1">
-        <v>104.325574406182</v>
+        <v>104.3624312061473</v>
       </c>
     </row>
     <row r="537" spans="1:2">
@@ -6403,7 +6406,7 @@
         <v>537</v>
       </c>
       <c r="B537" s="1">
-        <v>104.2855710858858</v>
+        <v>104.3583213258246</v>
       </c>
     </row>
     <row r="538" spans="1:2">
@@ -6411,7 +6414,7 @@
         <v>538</v>
       </c>
       <c r="B538" s="1">
-        <v>104.2836718536628</v>
+        <v>104.3559359575493</v>
       </c>
     </row>
     <row r="539" spans="1:2">
@@ -6419,7 +6422,7 @@
         <v>539</v>
       </c>
       <c r="B539" s="1">
-        <v>104.2689329825687</v>
+        <v>104.3558723563555</v>
       </c>
     </row>
     <row r="540" spans="1:2">
@@ -6427,7 +6430,7 @@
         <v>540</v>
       </c>
       <c r="B540" s="1">
-        <v>104.2622397188512</v>
+        <v>104.3516867653726</v>
       </c>
     </row>
     <row r="541" spans="1:2">
@@ -6435,7 +6438,7 @@
         <v>541</v>
       </c>
       <c r="B541" s="1">
-        <v>104.2592688209265</v>
+        <v>104.3160733584435</v>
       </c>
     </row>
     <row r="542" spans="1:2">
@@ -6443,7 +6446,7 @@
         <v>542</v>
       </c>
       <c r="B542" s="1">
-        <v>104.2524720047183</v>
+        <v>104.3072604572066</v>
       </c>
     </row>
     <row r="543" spans="1:2">
@@ -6451,7 +6454,7 @@
         <v>543</v>
       </c>
       <c r="B543" s="1">
-        <v>104.2423252263393</v>
+        <v>104.3009394091758</v>
       </c>
     </row>
     <row r="544" spans="1:2">
@@ -6459,7 +6462,7 @@
         <v>544</v>
       </c>
       <c r="B544" s="1">
-        <v>104.2423080802134</v>
+        <v>104.2739430788124</v>
       </c>
     </row>
     <row r="545" spans="1:2">
@@ -6467,7 +6470,7 @@
         <v>545</v>
       </c>
       <c r="B545" s="1">
-        <v>104.2246981705942</v>
+        <v>104.2447598089996</v>
       </c>
     </row>
     <row r="546" spans="1:2">
@@ -6475,7 +6478,7 @@
         <v>546</v>
       </c>
       <c r="B546" s="1">
-        <v>104.2234440216869</v>
+        <v>104.2389102289108</v>
       </c>
     </row>
     <row r="547" spans="1:2">
@@ -6483,7 +6486,7 @@
         <v>547</v>
       </c>
       <c r="B547" s="1">
-        <v>104.2214179717905</v>
+        <v>104.2384002029113</v>
       </c>
     </row>
     <row r="548" spans="1:2">
@@ -6491,7 +6494,7 @@
         <v>548</v>
       </c>
       <c r="B548" s="1">
-        <v>104.2002655514064</v>
+        <v>104.2377905291185</v>
       </c>
     </row>
     <row r="549" spans="1:2">
@@ -6499,7 +6502,7 @@
         <v>549</v>
       </c>
       <c r="B549" s="1">
-        <v>104.1793347949875</v>
+        <v>104.2013384220123</v>
       </c>
     </row>
     <row r="550" spans="1:2">
@@ -6507,7 +6510,7 @@
         <v>550</v>
       </c>
       <c r="B550" s="1">
-        <v>104.1528677209773</v>
+        <v>104.1958727588215</v>
       </c>
     </row>
     <row r="551" spans="1:2">
@@ -6515,7 +6518,7 @@
         <v>551</v>
       </c>
       <c r="B551" s="1">
-        <v>104.1445565557657</v>
+        <v>104.1911294883595</v>
       </c>
     </row>
     <row r="552" spans="1:2">
@@ -6523,7 +6526,7 @@
         <v>552</v>
       </c>
       <c r="B552" s="1">
-        <v>104.1421732062791</v>
+        <v>104.1815956648813</v>
       </c>
     </row>
     <row r="553" spans="1:2">
@@ -6531,7 +6534,7 @@
         <v>553</v>
       </c>
       <c r="B553" s="1">
-        <v>104.1395030582384</v>
+        <v>104.1614956108233</v>
       </c>
     </row>
     <row r="554" spans="1:2">
@@ -6539,7 +6542,7 @@
         <v>554</v>
       </c>
       <c r="B554" s="1">
-        <v>104.1253516766168</v>
+        <v>104.1608445990104</v>
       </c>
     </row>
     <row r="555" spans="1:2">
@@ -6547,7 +6550,7 @@
         <v>555</v>
       </c>
       <c r="B555" s="1">
-        <v>104.1247545601137</v>
+        <v>104.1240006181064</v>
       </c>
     </row>
     <row r="556" spans="1:2">
@@ -6555,7 +6558,7 @@
         <v>556</v>
       </c>
       <c r="B556" s="1">
-        <v>104.1211538199461</v>
+        <v>104.0714319581381</v>
       </c>
     </row>
     <row r="557" spans="1:2">
@@ -6563,7 +6566,7 @@
         <v>557</v>
       </c>
       <c r="B557" s="1">
-        <v>104.1164208348171</v>
+        <v>104.0636775445271</v>
       </c>
     </row>
     <row r="558" spans="1:2">
@@ -6571,7 +6574,7 @@
         <v>558</v>
       </c>
       <c r="B558" s="1">
-        <v>104.0919780259055</v>
+        <v>104.0632905302229</v>
       </c>
     </row>
     <row r="559" spans="1:2">
@@ -6579,7 +6582,7 @@
         <v>559</v>
       </c>
       <c r="B559" s="1">
-        <v>104.0903699561253</v>
+        <v>104.0312384630354</v>
       </c>
     </row>
     <row r="560" spans="1:2">
@@ -6587,7 +6590,7 @@
         <v>560</v>
       </c>
       <c r="B560" s="1">
-        <v>104.069585179571</v>
+        <v>104.025033014224</v>
       </c>
     </row>
     <row r="561" spans="1:2">
@@ -6595,7 +6598,7 @@
         <v>561</v>
       </c>
       <c r="B561" s="1">
-        <v>104.0324901232109</v>
+        <v>104.0200841382119</v>
       </c>
     </row>
     <row r="562" spans="1:2">
@@ -6603,7 +6606,7 @@
         <v>562</v>
       </c>
       <c r="B562" s="1">
-        <v>104.0295253215012</v>
+        <v>104.0119001216308</v>
       </c>
     </row>
     <row r="563" spans="1:2">
@@ -6611,7 +6614,7 @@
         <v>563</v>
       </c>
       <c r="B563" s="1">
-        <v>104.0109540297533</v>
+        <v>103.9696707324137</v>
       </c>
     </row>
     <row r="564" spans="1:2">
@@ -6619,7 +6622,7 @@
         <v>564</v>
       </c>
       <c r="B564" s="1">
-        <v>104.0056765299979</v>
+        <v>103.9489312775706</v>
       </c>
     </row>
     <row r="565" spans="1:2">
@@ -6627,7 +6630,7 @@
         <v>565</v>
       </c>
       <c r="B565" s="1">
-        <v>103.9906091120605</v>
+        <v>103.9471283379342</v>
       </c>
     </row>
     <row r="566" spans="1:2">
@@ -6635,7 +6638,7 @@
         <v>566</v>
       </c>
       <c r="B566" s="1">
-        <v>103.9694122601321</v>
+        <v>103.9373629541842</v>
       </c>
     </row>
     <row r="567" spans="1:2">
@@ -6643,7 +6646,7 @@
         <v>567</v>
       </c>
       <c r="B567" s="1">
-        <v>103.9584158826622</v>
+        <v>103.9360731652704</v>
       </c>
     </row>
     <row r="568" spans="1:2">
@@ -6651,7 +6654,7 @@
         <v>568</v>
       </c>
       <c r="B568" s="1">
-        <v>103.9530684995897</v>
+        <v>103.9354084379036</v>
       </c>
     </row>
     <row r="569" spans="1:2">
@@ -6659,7 +6662,7 @@
         <v>569</v>
       </c>
       <c r="B569" s="1">
-        <v>103.9518237598984</v>
+        <v>103.9318387458498</v>
       </c>
     </row>
     <row r="570" spans="1:2">
@@ -6667,7 +6670,7 @@
         <v>570</v>
       </c>
       <c r="B570" s="1">
-        <v>103.9297470794348</v>
+        <v>103.9277282547408</v>
       </c>
     </row>
     <row r="571" spans="1:2">
@@ -6675,7 +6678,7 @@
         <v>571</v>
       </c>
       <c r="B571" s="1">
-        <v>103.9252773627429</v>
+        <v>103.918950199007</v>
       </c>
     </row>
     <row r="572" spans="1:2">
@@ -6683,7 +6686,7 @@
         <v>572</v>
       </c>
       <c r="B572" s="1">
-        <v>103.8849970395448</v>
+        <v>103.9176428858484</v>
       </c>
     </row>
     <row r="573" spans="1:2">
@@ -6691,7 +6694,7 @@
         <v>573</v>
       </c>
       <c r="B573" s="1">
-        <v>103.8786584810623</v>
+        <v>103.9170873172406</v>
       </c>
     </row>
     <row r="574" spans="1:2">
@@ -6699,7 +6702,7 @@
         <v>574</v>
       </c>
       <c r="B574" s="1">
-        <v>103.8503344101329</v>
+        <v>103.913560632745</v>
       </c>
     </row>
     <row r="575" spans="1:2">
@@ -6707,7 +6710,7 @@
         <v>575</v>
       </c>
       <c r="B575" s="1">
-        <v>103.8442376617699</v>
+        <v>103.9125296635075</v>
       </c>
     </row>
     <row r="576" spans="1:2">
@@ -6715,7 +6718,7 @@
         <v>576</v>
       </c>
       <c r="B576" s="1">
-        <v>103.8319716327929</v>
+        <v>103.909775183052</v>
       </c>
     </row>
     <row r="577" spans="1:2">
@@ -6723,7 +6726,7 @@
         <v>577</v>
       </c>
       <c r="B577" s="1">
-        <v>103.8246007506221</v>
+        <v>103.9001450510405</v>
       </c>
     </row>
     <row r="578" spans="1:2">
@@ -6731,7 +6734,7 @@
         <v>578</v>
       </c>
       <c r="B578" s="1">
-        <v>103.8212301082223</v>
+        <v>103.8928121697638</v>
       </c>
     </row>
     <row r="579" spans="1:2">
@@ -6739,7 +6742,7 @@
         <v>579</v>
       </c>
       <c r="B579" s="1">
-        <v>103.8198198116002</v>
+        <v>103.8888268236873</v>
       </c>
     </row>
     <row r="580" spans="1:2">
@@ -6747,7 +6750,15 @@
         <v>580</v>
       </c>
       <c r="B580" s="1">
-        <v>103.7993642657749</v>
+        <v>103.8626379123043</v>
+      </c>
+    </row>
+    <row r="581" spans="1:2">
+      <c r="A581" t="s">
+        <v>581</v>
+      </c>
+      <c r="B581" s="1">
+        <v>103.8600633129654</v>
       </c>
     </row>
   </sheetData>

--- a/Screener/data/rs_rating_top_30.xlsx
+++ b/Screener/data/rs_rating_top_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Symbol</t>
   </si>
@@ -22,58 +22,22 @@
     <t>RS Rating</t>
   </si>
   <si>
-    <t>APP</t>
-  </si>
-  <si>
-    <t>ANET</t>
-  </si>
-  <si>
-    <t>AFRM</t>
-  </si>
-  <si>
-    <t>APA</t>
-  </si>
-  <si>
-    <t>ADBE</t>
-  </si>
-  <si>
-    <t>APO</t>
-  </si>
-  <si>
-    <t>ARGX</t>
-  </si>
-  <si>
-    <t>AMGN</t>
-  </si>
-  <si>
-    <t>AKAM</t>
-  </si>
-  <si>
-    <t>AZPN</t>
-  </si>
-  <si>
-    <t>ADP</t>
-  </si>
-  <si>
-    <t>ASMIY</t>
-  </si>
-  <si>
-    <t>ARES</t>
+    <t>AMZN</t>
+  </si>
+  <si>
+    <t>AAPL</t>
   </si>
   <si>
     <t>AVGO</t>
   </si>
   <si>
-    <t>ALGN</t>
-  </si>
-  <si>
-    <t>AFL</t>
-  </si>
-  <si>
-    <t>ATVI</t>
-  </si>
-  <si>
-    <t>AJG</t>
+    <t>ASML</t>
+  </si>
+  <si>
+    <t>ABBV</t>
+  </si>
+  <si>
+    <t>AMD</t>
   </si>
 </sst>
 </file>
@@ -424,7 +388,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -440,7 +404,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1">
-        <v>150.8512952401765</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -448,7 +412,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1">
-        <v>124.1263072933768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -456,7 +420,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1">
-        <v>122.325245875333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -464,7 +428,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="1">
-        <v>121.8412905014272</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -472,7 +436,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="1">
-        <v>118.3685001295362</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -480,103 +444,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="1">
-        <v>116.7350798754637</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="1">
-        <v>116.5695812947397</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="1">
-        <v>115.0471809462143</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="1">
-        <v>114.9153765429072</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="1">
-        <v>114.523897198331</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="1">
-        <v>111.8508714806012</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="1">
-        <v>111.6787707662816</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="1">
-        <v>111.0327169716226</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="1">
-        <v>110.5282896522894</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" s="1">
-        <v>110.091270552602</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" s="1">
-        <v>109.2618252208588</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" s="1">
-        <v>109.1901466705209</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" s="1">
-        <v>109.1851859876058</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Screener/data/rs_rating_top_30.xlsx
+++ b/Screener/data/rs_rating_top_30.xlsx
@@ -22,22 +22,22 @@
     <t>RS Rating</t>
   </si>
   <si>
-    <t>AMZN</t>
-  </si>
-  <si>
-    <t>AAPL</t>
+    <t>ADBE</t>
+  </si>
+  <si>
+    <t>AMGN</t>
+  </si>
+  <si>
+    <t>ADP</t>
+  </si>
+  <si>
+    <t>ADDDF</t>
+  </si>
+  <si>
+    <t>ADSK</t>
   </si>
   <si>
     <t>AVGO</t>
-  </si>
-  <si>
-    <t>ASML</t>
-  </si>
-  <si>
-    <t>ABBV</t>
-  </si>
-  <si>
-    <t>AMD</t>
   </si>
 </sst>
 </file>
@@ -404,7 +404,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1">
-        <v>0</v>
+        <v>115.4508138824493</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -412,7 +412,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1">
-        <v>0</v>
+        <v>115.2827890783211</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -420,7 +420,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1">
-        <v>0</v>
+        <v>113.0456350186045</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -428,7 +428,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="1">
-        <v>0</v>
+        <v>108.9135369415349</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -436,7 +436,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="1">
-        <v>0</v>
+        <v>107.8636925285734</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -444,7 +444,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="1">
-        <v>0</v>
+        <v>107.6387464561719</v>
       </c>
     </row>
   </sheetData>

--- a/Screener/data/rs_rating_top_30.xlsx
+++ b/Screener/data/rs_rating_top_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Symbol</t>
   </si>
@@ -22,22 +22,49 @@
     <t>RS Rating</t>
   </si>
   <si>
+    <t>APP</t>
+  </si>
+  <si>
+    <t>AFRM</t>
+  </si>
+  <si>
+    <t>ANET</t>
+  </si>
+  <si>
+    <t>ARGX</t>
+  </si>
+  <si>
+    <t>APO</t>
+  </si>
+  <si>
     <t>ADBE</t>
   </si>
   <si>
     <t>AMGN</t>
   </si>
   <si>
+    <t>AKAM</t>
+  </si>
+  <si>
     <t>ADP</t>
   </si>
   <si>
-    <t>ADDDF</t>
-  </si>
-  <si>
-    <t>ADSK</t>
-  </si>
-  <si>
-    <t>AVGO</t>
+    <t>ALGN</t>
+  </si>
+  <si>
+    <t>ASMIY</t>
+  </si>
+  <si>
+    <t>AJG</t>
+  </si>
+  <si>
+    <t>ATVI</t>
+  </si>
+  <si>
+    <t>AVTR</t>
+  </si>
+  <si>
+    <t>AFL</t>
   </si>
 </sst>
 </file>
@@ -388,7 +415,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -404,7 +431,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1">
-        <v>115.4508138824493</v>
+        <v>158.5165923821816</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -412,7 +439,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1">
-        <v>115.2827890783211</v>
+        <v>123.9674258761739</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -420,7 +447,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1">
-        <v>113.0456350186045</v>
+        <v>120.2036448358768</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -428,7 +455,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="1">
-        <v>108.9135369415349</v>
+        <v>116.8165831194336</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -436,7 +463,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="1">
-        <v>107.8636925285734</v>
+        <v>116.0053880386057</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -444,7 +471,79 @@
         <v>7</v>
       </c>
       <c r="B7" s="1">
-        <v>107.6387464561719</v>
+        <v>115.5843379752632</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1">
+        <v>115.5157285613406</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="1">
+        <v>114.7923154557496</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="1">
+        <v>113.2722392686485</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="1">
+        <v>111.221667566574</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="1">
+        <v>110.135244194136</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="1">
+        <v>109.8073800614181</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="1">
+        <v>109.6120061433241</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="1">
+        <v>109.4401331598144</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="1">
+        <v>109.3504917974402</v>
       </c>
     </row>
   </sheetData>

--- a/Screener/data/rs_rating_top_30.xlsx
+++ b/Screener/data/rs_rating_top_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="588">
   <si>
     <t>Symbol</t>
   </si>
@@ -22,49 +22,1762 @@
     <t>RS Rating</t>
   </si>
   <si>
+    <t>EDTX</t>
+  </si>
+  <si>
+    <t>EDTXU</t>
+  </si>
+  <si>
+    <t>AAOI</t>
+  </si>
+  <si>
+    <t>TDS</t>
+  </si>
+  <si>
+    <t>USM</t>
+  </si>
+  <si>
+    <t>SGTX</t>
+  </si>
+  <si>
+    <t>CDLX</t>
+  </si>
+  <si>
+    <t>TSAT</t>
+  </si>
+  <si>
+    <t>ADTX</t>
+  </si>
+  <si>
+    <t>UPTDU</t>
+  </si>
+  <si>
+    <t>CVNA</t>
+  </si>
+  <si>
+    <t>UPTD</t>
+  </si>
+  <si>
+    <t>ML</t>
+  </si>
+  <si>
+    <t>DLO</t>
+  </si>
+  <si>
+    <t>CAMT</t>
+  </si>
+  <si>
+    <t>PHVS</t>
+  </si>
+  <si>
     <t>APP</t>
   </si>
   <si>
+    <t>BBIO</t>
+  </si>
+  <si>
+    <t>VRT</t>
+  </si>
+  <si>
+    <t>ACMR</t>
+  </si>
+  <si>
+    <t>ANF</t>
+  </si>
+  <si>
+    <t>LEU</t>
+  </si>
+  <si>
+    <t>STRL</t>
+  </si>
+  <si>
+    <t>LMB</t>
+  </si>
+  <si>
+    <t>XPEV</t>
+  </si>
+  <si>
+    <t>PAY</t>
+  </si>
+  <si>
+    <t>CLS</t>
+  </si>
+  <si>
+    <t>ESTE</t>
+  </si>
+  <si>
+    <t>CPRI</t>
+  </si>
+  <si>
+    <t>RYTM</t>
+  </si>
+  <si>
+    <t>MNSO</t>
+  </si>
+  <si>
+    <t>KRT</t>
+  </si>
+  <si>
+    <t>RETA</t>
+  </si>
+  <si>
+    <t>UPWK</t>
+  </si>
+  <si>
+    <t>URGN</t>
+  </si>
+  <si>
+    <t>SBOW</t>
+  </si>
+  <si>
+    <t>MNBP</t>
+  </si>
+  <si>
+    <t>BOOM</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>MOD</t>
+  </si>
+  <si>
+    <t>AEO</t>
+  </si>
+  <si>
+    <t>CEIX</t>
+  </si>
+  <si>
+    <t>FUTU</t>
+  </si>
+  <si>
+    <t>IESC</t>
+  </si>
+  <si>
+    <t>GCO</t>
+  </si>
+  <si>
+    <t>GENTF</t>
+  </si>
+  <si>
+    <t>CELH</t>
+  </si>
+  <si>
+    <t>SRDX</t>
+  </si>
+  <si>
+    <t>PRDO</t>
+  </si>
+  <si>
+    <t>BWMX</t>
+  </si>
+  <si>
+    <t>AMR</t>
+  </si>
+  <si>
+    <t>FSLY</t>
+  </si>
+  <si>
+    <t>PDD</t>
+  </si>
+  <si>
+    <t>VNO</t>
+  </si>
+  <si>
+    <t>VIEW</t>
+  </si>
+  <si>
+    <t>NTRA</t>
+  </si>
+  <si>
+    <t>VRTV</t>
+  </si>
+  <si>
+    <t>SM</t>
+  </si>
+  <si>
     <t>AFRM</t>
   </si>
   <si>
+    <t>DFH</t>
+  </si>
+  <si>
+    <t>WHD</t>
+  </si>
+  <si>
+    <t>MMYT</t>
+  </si>
+  <si>
+    <t>PARR</t>
+  </si>
+  <si>
+    <t>DELL</t>
+  </si>
+  <si>
+    <t>TPL</t>
+  </si>
+  <si>
+    <t>HOV</t>
+  </si>
+  <si>
+    <t>KD</t>
+  </si>
+  <si>
+    <t>SLG</t>
+  </si>
+  <si>
+    <t>CWCO</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>IDYA</t>
+  </si>
+  <si>
+    <t>ESEA</t>
+  </si>
+  <si>
+    <t>FN</t>
+  </si>
+  <si>
+    <t>CAL</t>
+  </si>
+  <si>
+    <t>WFRD</t>
+  </si>
+  <si>
+    <t>XPO</t>
+  </si>
+  <si>
+    <t>WLDN</t>
+  </si>
+  <si>
+    <t>PDS</t>
+  </si>
+  <si>
+    <t>EDU</t>
+  </si>
+  <si>
+    <t>YETI</t>
+  </si>
+  <si>
+    <t>HWKN</t>
+  </si>
+  <si>
+    <t>PAR</t>
+  </si>
+  <si>
+    <t>SENEB</t>
+  </si>
+  <si>
+    <t>ODC</t>
+  </si>
+  <si>
+    <t>EH</t>
+  </si>
+  <si>
+    <t>PETQ</t>
+  </si>
+  <si>
+    <t>CBAY</t>
+  </si>
+  <si>
+    <t>CORT</t>
+  </si>
+  <si>
+    <t>PSFE</t>
+  </si>
+  <si>
+    <t>OII</t>
+  </si>
+  <si>
+    <t>GAMB</t>
+  </si>
+  <si>
+    <t>LYTS</t>
+  </si>
+  <si>
+    <t>UBS</t>
+  </si>
+  <si>
+    <t>CTRN</t>
+  </si>
+  <si>
+    <t>NATR</t>
+  </si>
+  <si>
+    <t>NOV</t>
+  </si>
+  <si>
+    <t>CSPI</t>
+  </si>
+  <si>
+    <t>ANIP</t>
+  </si>
+  <si>
+    <t>IOT</t>
+  </si>
+  <si>
+    <t>RELY</t>
+  </si>
+  <si>
+    <t>OBT</t>
+  </si>
+  <si>
+    <t>GTLS</t>
+  </si>
+  <si>
+    <t>TWST</t>
+  </si>
+  <si>
+    <t>IPI</t>
+  </si>
+  <si>
+    <t>CRC</t>
+  </si>
+  <si>
+    <t>KDNY</t>
+  </si>
+  <si>
+    <t>POWL</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>CIR</t>
+  </si>
+  <si>
+    <t>JXN</t>
+  </si>
+  <si>
+    <t>FSTR</t>
+  </si>
+  <si>
+    <t>CMT</t>
+  </si>
+  <si>
+    <t>QTRX</t>
+  </si>
+  <si>
+    <t>SENEA</t>
+  </si>
+  <si>
+    <t>MTDR</t>
+  </si>
+  <si>
+    <t>WAL</t>
+  </si>
+  <si>
+    <t>SAIA</t>
+  </si>
+  <si>
+    <t>APA</t>
+  </si>
+  <si>
+    <t>GHM</t>
+  </si>
+  <si>
+    <t>IONQ</t>
+  </si>
+  <si>
+    <t>STEP</t>
+  </si>
+  <si>
+    <t>CNX</t>
+  </si>
+  <si>
+    <t>RVMD</t>
+  </si>
+  <si>
+    <t>AZEK</t>
+  </si>
+  <si>
+    <t>COUR</t>
+  </si>
+  <si>
+    <t>LLY</t>
+  </si>
+  <si>
+    <t>ELAN</t>
+  </si>
+  <si>
+    <t>BMA</t>
+  </si>
+  <si>
+    <t>DICE</t>
+  </si>
+  <si>
+    <t>NRP</t>
+  </si>
+  <si>
+    <t>AZTA</t>
+  </si>
+  <si>
+    <t>TDW</t>
+  </si>
+  <si>
+    <t>SMHI</t>
+  </si>
+  <si>
+    <t>HRB</t>
+  </si>
+  <si>
+    <t>BFST</t>
+  </si>
+  <si>
+    <t>MTSI</t>
+  </si>
+  <si>
+    <t>FRHC</t>
+  </si>
+  <si>
+    <t>AEHR</t>
+  </si>
+  <si>
+    <t>XPRO</t>
+  </si>
+  <si>
+    <t>PLCE</t>
+  </si>
+  <si>
+    <t>BOH</t>
+  </si>
+  <si>
+    <t>CVBF</t>
+  </si>
+  <si>
+    <t>BCC</t>
+  </si>
+  <si>
+    <t>CKX</t>
+  </si>
+  <si>
+    <t>INBK</t>
+  </si>
+  <si>
+    <t>ROCK</t>
+  </si>
+  <si>
+    <t>WMG</t>
+  </si>
+  <si>
+    <t>BBW</t>
+  </si>
+  <si>
+    <t>PESI</t>
+  </si>
+  <si>
+    <t>LBRDB</t>
+  </si>
+  <si>
+    <t>AMNB</t>
+  </si>
+  <si>
+    <t>GIC</t>
+  </si>
+  <si>
+    <t>SFBS</t>
+  </si>
+  <si>
+    <t>PRA</t>
+  </si>
+  <si>
+    <t>FTI</t>
+  </si>
+  <si>
+    <t>ARRY</t>
+  </si>
+  <si>
+    <t>ERIE</t>
+  </si>
+  <si>
+    <t>OVV</t>
+  </si>
+  <si>
+    <t>HDSN</t>
+  </si>
+  <si>
+    <t>GES</t>
+  </si>
+  <si>
+    <t>FTAI</t>
+  </si>
+  <si>
+    <t>CVI</t>
+  </si>
+  <si>
+    <t>NOG</t>
+  </si>
+  <si>
+    <t>TALO</t>
+  </si>
+  <si>
+    <t>MPC</t>
+  </si>
+  <si>
+    <t>FLR</t>
+  </si>
+  <si>
+    <t>HOFT</t>
+  </si>
+  <si>
+    <t>ASTE</t>
+  </si>
+  <si>
+    <t>NE</t>
+  </si>
+  <si>
+    <t>AROC</t>
+  </si>
+  <si>
+    <t>ARCH</t>
+  </si>
+  <si>
+    <t>GGAL</t>
+  </si>
+  <si>
+    <t>NBR</t>
+  </si>
+  <si>
+    <t>VST</t>
+  </si>
+  <si>
+    <t>FRSH</t>
+  </si>
+  <si>
+    <t>AURC</t>
+  </si>
+  <si>
+    <t>ARGX</t>
+  </si>
+  <si>
+    <t>MLKN</t>
+  </si>
+  <si>
+    <t>TRUP</t>
+  </si>
+  <si>
+    <t>TWIN</t>
+  </si>
+  <si>
+    <t>CRS</t>
+  </si>
+  <si>
+    <t>HNI</t>
+  </si>
+  <si>
+    <t>CHX</t>
+  </si>
+  <si>
+    <t>PLUS</t>
+  </si>
+  <si>
+    <t>GPOR</t>
+  </si>
+  <si>
+    <t>IIPR</t>
+  </si>
+  <si>
+    <t>ITRN</t>
+  </si>
+  <si>
+    <t>CIVI</t>
+  </si>
+  <si>
+    <t>CCJ</t>
+  </si>
+  <si>
+    <t>OSK</t>
+  </si>
+  <si>
+    <t>KRC</t>
+  </si>
+  <si>
+    <t>VET</t>
+  </si>
+  <si>
+    <t>LYFT</t>
+  </si>
+  <si>
+    <t>PTEN</t>
+  </si>
+  <si>
+    <t>QCRH</t>
+  </si>
+  <si>
+    <t>MHO</t>
+  </si>
+  <si>
+    <t>BKI</t>
+  </si>
+  <si>
+    <t>DBRG</t>
+  </si>
+  <si>
+    <t>EVI</t>
+  </si>
+  <si>
+    <t>GPN</t>
+  </si>
+  <si>
+    <t>SLB</t>
+  </si>
+  <si>
+    <t>HEP</t>
+  </si>
+  <si>
+    <t>NTNX</t>
+  </si>
+  <si>
+    <t>MUR</t>
+  </si>
+  <si>
+    <t>INTU</t>
+  </si>
+  <si>
+    <t>TIPT</t>
+  </si>
+  <si>
+    <t>HIBB</t>
+  </si>
+  <si>
+    <t>PBF</t>
+  </si>
+  <si>
+    <t>DWAC</t>
+  </si>
+  <si>
+    <t>EME</t>
+  </si>
+  <si>
+    <t>AZZ</t>
+  </si>
+  <si>
+    <t>TH</t>
+  </si>
+  <si>
+    <t>ODFL</t>
+  </si>
+  <si>
+    <t>FOR</t>
+  </si>
+  <si>
+    <t>CPE</t>
+  </si>
+  <si>
+    <t>SSD</t>
+  </si>
+  <si>
+    <t>PRIM</t>
+  </si>
+  <si>
+    <t>NXGN</t>
+  </si>
+  <si>
+    <t>NVO</t>
+  </si>
+  <si>
+    <t>URI</t>
+  </si>
+  <si>
+    <t>ONTO</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>BLD</t>
+  </si>
+  <si>
+    <t>SOVO</t>
+  </si>
+  <si>
+    <t>ZION</t>
+  </si>
+  <si>
+    <t>RH</t>
+  </si>
+  <si>
+    <t>BRZE</t>
+  </si>
+  <si>
+    <t>SPLK</t>
+  </si>
+  <si>
+    <t>DLX</t>
+  </si>
+  <si>
+    <t>AR</t>
+  </si>
+  <si>
+    <t>WMPN</t>
+  </si>
+  <si>
+    <t>TEAM</t>
+  </si>
+  <si>
+    <t>QLYS</t>
+  </si>
+  <si>
+    <t>PSX</t>
+  </si>
+  <si>
+    <t>BCSF</t>
+  </si>
+  <si>
+    <t>APPF</t>
+  </si>
+  <si>
+    <t>TW</t>
+  </si>
+  <si>
+    <t>JOE</t>
+  </si>
+  <si>
+    <t>OLLI</t>
+  </si>
+  <si>
+    <t>ARVN</t>
+  </si>
+  <si>
+    <t>RIVN</t>
+  </si>
+  <si>
+    <t>SKYW</t>
+  </si>
+  <si>
+    <t>ETN</t>
+  </si>
+  <si>
+    <t>LBRT</t>
+  </si>
+  <si>
+    <t>ADBE</t>
+  </si>
+  <si>
+    <t>BR</t>
+  </si>
+  <si>
+    <t>NFE</t>
+  </si>
+  <si>
+    <t>DCOM</t>
+  </si>
+  <si>
+    <t>LII</t>
+  </si>
+  <si>
+    <t>CTLT</t>
+  </si>
+  <si>
+    <t>ENLC</t>
+  </si>
+  <si>
+    <t>NX</t>
+  </si>
+  <si>
+    <t>SU</t>
+  </si>
+  <si>
+    <t>FETM</t>
+  </si>
+  <si>
+    <t>CUBI</t>
+  </si>
+  <si>
+    <t>XP</t>
+  </si>
+  <si>
+    <t>ZEUS</t>
+  </si>
+  <si>
+    <t>KOP</t>
+  </si>
+  <si>
+    <t>RAMP</t>
+  </si>
+  <si>
+    <t>CLMT</t>
+  </si>
+  <si>
+    <t>DCBO</t>
+  </si>
+  <si>
+    <t>CDRE</t>
+  </si>
+  <si>
+    <t>SHEN</t>
+  </si>
+  <si>
+    <t>DWACU</t>
+  </si>
+  <si>
+    <t>BKU</t>
+  </si>
+  <si>
+    <t>IMO</t>
+  </si>
+  <si>
+    <t>BEKE</t>
+  </si>
+  <si>
+    <t>HAL</t>
+  </si>
+  <si>
+    <t>CAT</t>
+  </si>
+  <si>
+    <t>NCR</t>
+  </si>
+  <si>
+    <t>TWI</t>
+  </si>
+  <si>
+    <t>LEAT</t>
+  </si>
+  <si>
+    <t>BKR</t>
+  </si>
+  <si>
+    <t>NOA</t>
+  </si>
+  <si>
+    <t>CARR</t>
+  </si>
+  <si>
+    <t>CCOI</t>
+  </si>
+  <si>
+    <t>ELF</t>
+  </si>
+  <si>
+    <t>HPK</t>
+  </si>
+  <si>
+    <t>DLR</t>
+  </si>
+  <si>
+    <t>TROX</t>
+  </si>
+  <si>
+    <t>FLXS</t>
+  </si>
+  <si>
+    <t>UFPI</t>
+  </si>
+  <si>
+    <t>SMMF</t>
+  </si>
+  <si>
+    <t>CRK</t>
+  </si>
+  <si>
     <t>ANET</t>
   </si>
   <si>
-    <t>ARGX</t>
+    <t>BRP</t>
+  </si>
+  <si>
+    <t>HLNE</t>
+  </si>
+  <si>
+    <t>HAYW</t>
+  </si>
+  <si>
+    <t>OC</t>
+  </si>
+  <si>
+    <t>CNOB</t>
+  </si>
+  <si>
+    <t>VEEV</t>
+  </si>
+  <si>
+    <t>TREX</t>
+  </si>
+  <si>
+    <t>TCBI</t>
+  </si>
+  <si>
+    <t>JHX</t>
+  </si>
+  <si>
+    <t>ROKU</t>
+  </si>
+  <si>
+    <t>RILY</t>
+  </si>
+  <si>
+    <t>MBWM</t>
+  </si>
+  <si>
+    <t>YY</t>
+  </si>
+  <si>
+    <t>TFII</t>
+  </si>
+  <si>
+    <t>WOR</t>
+  </si>
+  <si>
+    <t>TPX</t>
+  </si>
+  <si>
+    <t>WMS</t>
+  </si>
+  <si>
+    <t>RBB</t>
+  </si>
+  <si>
+    <t>DRQ</t>
+  </si>
+  <si>
+    <t>RNGR</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>NVDA</t>
+  </si>
+  <si>
+    <t>PSN</t>
+  </si>
+  <si>
+    <t>MEDP</t>
+  </si>
+  <si>
+    <t>ERF</t>
+  </si>
+  <si>
+    <t>KTOS</t>
+  </si>
+  <si>
+    <t>ALRM</t>
+  </si>
+  <si>
+    <t>PBR</t>
+  </si>
+  <si>
+    <t>HCM</t>
+  </si>
+  <si>
+    <t>FORG</t>
+  </si>
+  <si>
+    <t>JILL</t>
+  </si>
+  <si>
+    <t>CW</t>
+  </si>
+  <si>
+    <t>LOB</t>
+  </si>
+  <si>
+    <t>AFYA</t>
+  </si>
+  <si>
+    <t>PRMW</t>
+  </si>
+  <si>
+    <t>STER</t>
+  </si>
+  <si>
+    <t>YELP</t>
+  </si>
+  <si>
+    <t>GBX</t>
+  </si>
+  <si>
+    <t>HAS</t>
+  </si>
+  <si>
+    <t>BHWB</t>
+  </si>
+  <si>
+    <t>SG</t>
+  </si>
+  <si>
+    <t>VRNS</t>
+  </si>
+  <si>
+    <t>TRGP</t>
+  </si>
+  <si>
+    <t>STX</t>
+  </si>
+  <si>
+    <t>SKY</t>
+  </si>
+  <si>
+    <t>PNFP</t>
+  </si>
+  <si>
+    <t>TWNK</t>
+  </si>
+  <si>
+    <t>ATSG</t>
+  </si>
+  <si>
+    <t>BXP</t>
+  </si>
+  <si>
+    <t>TRNS</t>
+  </si>
+  <si>
+    <t>DVAX</t>
+  </si>
+  <si>
+    <t>VAL</t>
+  </si>
+  <si>
+    <t>CALB</t>
+  </si>
+  <si>
+    <t>SCPL</t>
+  </si>
+  <si>
+    <t>FNF</t>
+  </si>
+  <si>
+    <t>CLW</t>
+  </si>
+  <si>
+    <t>GSHD</t>
+  </si>
+  <si>
+    <t>AVNW</t>
+  </si>
+  <si>
+    <t>APOG</t>
+  </si>
+  <si>
+    <t>IMVT</t>
+  </si>
+  <si>
+    <t>CAAP</t>
+  </si>
+  <si>
+    <t>CVE</t>
+  </si>
+  <si>
+    <t>AURCU</t>
+  </si>
+  <si>
+    <t>BKNG</t>
+  </si>
+  <si>
+    <t>MAT</t>
+  </si>
+  <si>
+    <t>KNSL</t>
+  </si>
+  <si>
+    <t>NEWR</t>
+  </si>
+  <si>
+    <t>FRO</t>
+  </si>
+  <si>
+    <t>GRC</t>
+  </si>
+  <si>
+    <t>SWTX</t>
+  </si>
+  <si>
+    <t>AXON</t>
+  </si>
+  <si>
+    <t>NYT</t>
+  </si>
+  <si>
+    <t>ITT</t>
+  </si>
+  <si>
+    <t>CDW</t>
+  </si>
+  <si>
+    <t>COP</t>
+  </si>
+  <si>
+    <t>NEWT</t>
+  </si>
+  <si>
+    <t>HCCI</t>
+  </si>
+  <si>
+    <t>GFF</t>
+  </si>
+  <si>
+    <t>HALO</t>
+  </si>
+  <si>
+    <t>EVR</t>
+  </si>
+  <si>
+    <t>MLR</t>
+  </si>
+  <si>
+    <t>LI</t>
+  </si>
+  <si>
+    <t>PAM</t>
+  </si>
+  <si>
+    <t>SPOK</t>
+  </si>
+  <si>
+    <t>NBIX</t>
+  </si>
+  <si>
+    <t>SAH</t>
+  </si>
+  <si>
+    <t>CABA</t>
+  </si>
+  <si>
+    <t>NVT</t>
+  </si>
+  <si>
+    <t>VIST</t>
+  </si>
+  <si>
+    <t>AIT</t>
+  </si>
+  <si>
+    <t>AGM</t>
+  </si>
+  <si>
+    <t>AMWD</t>
+  </si>
+  <si>
+    <t>OLED</t>
+  </si>
+  <si>
+    <t>EXEL</t>
+  </si>
+  <si>
+    <t>MSA</t>
+  </si>
+  <si>
+    <t>SRV</t>
+  </si>
+  <si>
+    <t>HZNP</t>
+  </si>
+  <si>
+    <t>WIX</t>
+  </si>
+  <si>
+    <t>TNET</t>
+  </si>
+  <si>
+    <t>VLO</t>
+  </si>
+  <si>
+    <t>AMEH</t>
+  </si>
+  <si>
+    <t>TRDA</t>
+  </si>
+  <si>
+    <t>VVI</t>
+  </si>
+  <si>
+    <t>AMGN</t>
+  </si>
+  <si>
+    <t>MRO</t>
+  </si>
+  <si>
+    <t>CNQ</t>
+  </si>
+  <si>
+    <t>DPZ</t>
+  </si>
+  <si>
+    <t>ZGN</t>
+  </si>
+  <si>
+    <t>CCB</t>
+  </si>
+  <si>
+    <t>PFC</t>
+  </si>
+  <si>
+    <t>KNSA</t>
+  </si>
+  <si>
+    <t>PBNK</t>
+  </si>
+  <si>
+    <t>CZR</t>
+  </si>
+  <si>
+    <t>CRMT</t>
+  </si>
+  <si>
+    <t>OFIX</t>
+  </si>
+  <si>
+    <t>AKAM</t>
+  </si>
+  <si>
+    <t>EQNR</t>
+  </si>
+  <si>
+    <t>CIGI</t>
+  </si>
+  <si>
+    <t>BNTX</t>
+  </si>
+  <si>
+    <t>CQP</t>
+  </si>
+  <si>
+    <t>JLL</t>
+  </si>
+  <si>
+    <t>NTIC</t>
+  </si>
+  <si>
+    <t>NEOG</t>
+  </si>
+  <si>
+    <t>IIIN</t>
+  </si>
+  <si>
+    <t>ALKT</t>
+  </si>
+  <si>
+    <t>FANG</t>
+  </si>
+  <si>
+    <t>ALPN</t>
+  </si>
+  <si>
+    <t>BRBR</t>
+  </si>
+  <si>
+    <t>WDC</t>
+  </si>
+  <si>
+    <t>PFBC</t>
+  </si>
+  <si>
+    <t>KE</t>
+  </si>
+  <si>
+    <t>FIX</t>
+  </si>
+  <si>
+    <t>LAD</t>
+  </si>
+  <si>
+    <t>PEBK</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>VHNAU</t>
+  </si>
+  <si>
+    <t>NSIT</t>
+  </si>
+  <si>
+    <t>SCSC</t>
+  </si>
+  <si>
+    <t>BG</t>
+  </si>
+  <si>
+    <t>STRT</t>
+  </si>
+  <si>
+    <t>ATR</t>
+  </si>
+  <si>
+    <t>HP</t>
+  </si>
+  <si>
+    <t>SPNS</t>
+  </si>
+  <si>
+    <t>EQT</t>
+  </si>
+  <si>
+    <t>WSM</t>
+  </si>
+  <si>
+    <t>LAUR</t>
+  </si>
+  <si>
+    <t>FSFG</t>
+  </si>
+  <si>
+    <t>MTCH</t>
+  </si>
+  <si>
+    <t>MET</t>
+  </si>
+  <si>
+    <t>ATGE</t>
+  </si>
+  <si>
+    <t>TCOM</t>
+  </si>
+  <si>
+    <t>CVRX</t>
+  </si>
+  <si>
+    <t>CADE</t>
+  </si>
+  <si>
+    <t>ALGN</t>
+  </si>
+  <si>
+    <t>ABCB</t>
+  </si>
+  <si>
+    <t>LRN</t>
+  </si>
+  <si>
+    <t>FRPT</t>
+  </si>
+  <si>
+    <t>CMC</t>
   </si>
   <si>
     <t>APO</t>
   </si>
   <si>
-    <t>ADBE</t>
-  </si>
-  <si>
-    <t>AMGN</t>
-  </si>
-  <si>
-    <t>AKAM</t>
+    <t>PXD</t>
+  </si>
+  <si>
+    <t>FFNW</t>
+  </si>
+  <si>
+    <t>KSS</t>
+  </si>
+  <si>
+    <t>VECO</t>
   </si>
   <si>
     <t>ADP</t>
   </si>
   <si>
-    <t>ALGN</t>
-  </si>
-  <si>
-    <t>ASMIY</t>
-  </si>
-  <si>
-    <t>AJG</t>
-  </si>
-  <si>
-    <t>ATVI</t>
-  </si>
-  <si>
-    <t>AVTR</t>
-  </si>
-  <si>
-    <t>AFL</t>
+    <t>CPTP</t>
+  </si>
+  <si>
+    <t>GLOB</t>
+  </si>
+  <si>
+    <t>SPFI</t>
+  </si>
+  <si>
+    <t>CHTR</t>
+  </si>
+  <si>
+    <t>RYAN</t>
+  </si>
+  <si>
+    <t>ROAD</t>
+  </si>
+  <si>
+    <t>CSWI</t>
+  </si>
+  <si>
+    <t>MELI</t>
+  </si>
+  <si>
+    <t>ESCA</t>
+  </si>
+  <si>
+    <t>HES</t>
+  </si>
+  <si>
+    <t>FUNC</t>
+  </si>
+  <si>
+    <t>EBC</t>
+  </si>
+  <si>
+    <t>WST</t>
+  </si>
+  <si>
+    <t>OKTA</t>
+  </si>
+  <si>
+    <t>CNXN</t>
+  </si>
+  <si>
+    <t>JBL</t>
+  </si>
+  <si>
+    <t>RPD</t>
+  </si>
+  <si>
+    <t>NCNO</t>
+  </si>
+  <si>
+    <t>MANU</t>
+  </si>
+  <si>
+    <t>ATI</t>
+  </si>
+  <si>
+    <t>PNR</t>
+  </si>
+  <si>
+    <t>AMPL</t>
+  </si>
+  <si>
+    <t>SIG</t>
+  </si>
+  <si>
+    <t>ABR</t>
+  </si>
+  <si>
+    <t>IBP</t>
+  </si>
+  <si>
+    <t>ICFI</t>
+  </si>
+  <si>
+    <t>CPNG</t>
+  </si>
+  <si>
+    <t>PH</t>
+  </si>
+  <si>
+    <t>OSIS</t>
+  </si>
+  <si>
+    <t>JAZZ</t>
+  </si>
+  <si>
+    <t>EMR</t>
+  </si>
+  <si>
+    <t>TJX</t>
+  </si>
+  <si>
+    <t>NLCP</t>
+  </si>
+  <si>
+    <t>TXT</t>
+  </si>
+  <si>
+    <t>ARCE</t>
+  </si>
+  <si>
+    <t>CIEN</t>
+  </si>
+  <si>
+    <t>ESTC</t>
+  </si>
+  <si>
+    <t>FLT</t>
+  </si>
+  <si>
+    <t>CXM</t>
+  </si>
+  <si>
+    <t>INDB</t>
+  </si>
+  <si>
+    <t>BY</t>
+  </si>
+  <si>
+    <t>ALSN</t>
+  </si>
+  <si>
+    <t>HURN</t>
+  </si>
+  <si>
+    <t>CTRA</t>
+  </si>
+  <si>
+    <t>WINA</t>
+  </si>
+  <si>
+    <t>CSCO</t>
+  </si>
+  <si>
+    <t>QTWO</t>
+  </si>
+  <si>
+    <t>VSEC</t>
+  </si>
+  <si>
+    <t>REVG</t>
+  </si>
+  <si>
+    <t>ANDE</t>
+  </si>
+  <si>
+    <t>CSWC</t>
+  </si>
+  <si>
+    <t>NWPX</t>
+  </si>
+  <si>
+    <t>FBP</t>
+  </si>
+  <si>
+    <t>CMPR</t>
+  </si>
+  <si>
+    <t>GBLI</t>
+  </si>
+  <si>
+    <t>TOL</t>
+  </si>
+  <si>
+    <t>BLDR</t>
+  </si>
+  <si>
+    <t>NREF</t>
+  </si>
+  <si>
+    <t>VEL</t>
+  </si>
+  <si>
+    <t>REX</t>
+  </si>
+  <si>
+    <t>ZWS</t>
+  </si>
+  <si>
+    <t>OFG</t>
+  </si>
+  <si>
+    <t>HCC</t>
+  </si>
+  <si>
+    <t>HLI</t>
+  </si>
+  <si>
+    <t>FLIC</t>
+  </si>
+  <si>
+    <t>AKRO</t>
+  </si>
+  <si>
+    <t>ATKR</t>
+  </si>
+  <si>
+    <t>RCMT</t>
+  </si>
+  <si>
+    <t>GOLF</t>
+  </si>
+  <si>
+    <t>MCB</t>
+  </si>
+  <si>
+    <t>VICR</t>
+  </si>
+  <si>
+    <t>TS</t>
+  </si>
+  <si>
+    <t>TCPC</t>
+  </si>
+  <si>
+    <t>BLMN</t>
+  </si>
+  <si>
+    <t>CE</t>
+  </si>
+  <si>
+    <t>ZTS</t>
+  </si>
+  <si>
+    <t>VERX</t>
+  </si>
+  <si>
+    <t>CHK</t>
+  </si>
+  <si>
+    <t>NEU</t>
+  </si>
+  <si>
+    <t>USAC</t>
+  </si>
+  <si>
+    <t>AEL</t>
+  </si>
+  <si>
+    <t>IRM</t>
+  </si>
+  <si>
+    <t>ASGN</t>
+  </si>
+  <si>
+    <t>MORN</t>
+  </si>
+  <si>
+    <t>CF</t>
+  </si>
+  <si>
+    <t>REPYY</t>
+  </si>
+  <si>
+    <t>HOLI</t>
+  </si>
+  <si>
+    <t>GKOS</t>
+  </si>
+  <si>
+    <t>LDOS</t>
+  </si>
+  <si>
+    <t>NDP</t>
+  </si>
+  <si>
+    <t>BMI</t>
+  </si>
+  <si>
+    <t>RRC</t>
+  </si>
+  <si>
+    <t>HAFC</t>
+  </si>
+  <si>
+    <t>WLK</t>
+  </si>
+  <si>
+    <t>SITE</t>
+  </si>
+  <si>
+    <t>NHC</t>
+  </si>
+  <si>
+    <t>PSTG</t>
+  </si>
+  <si>
+    <t>LOPE</t>
+  </si>
+  <si>
+    <t>REGN</t>
+  </si>
+  <si>
+    <t>PAA</t>
+  </si>
+  <si>
+    <t>TEX</t>
+  </si>
+  <si>
+    <t>ROST</t>
+  </si>
+  <si>
+    <t>GHLD</t>
+  </si>
+  <si>
+    <t>NWLI</t>
+  </si>
+  <si>
+    <t>VMW</t>
+  </si>
+  <si>
+    <t>NPO</t>
+  </si>
+  <si>
+    <t>NWS</t>
+  </si>
+  <si>
+    <t>SF</t>
+  </si>
+  <si>
+    <t>WDAY</t>
+  </si>
+  <si>
+    <t>UBP</t>
+  </si>
+  <si>
+    <t>LAZ</t>
+  </si>
+  <si>
+    <t>NVMI</t>
+  </si>
+  <si>
+    <t>GRVY</t>
+  </si>
+  <si>
+    <t>PIPR</t>
+  </si>
+  <si>
+    <t>SFST</t>
+  </si>
+  <si>
+    <t>IBTX</t>
+  </si>
+  <si>
+    <t>MAR</t>
+  </si>
+  <si>
+    <t>KKR</t>
+  </si>
+  <si>
+    <t>SPB</t>
+  </si>
+  <si>
+    <t>INSW</t>
+  </si>
+  <si>
+    <t>AXSM</t>
+  </si>
+  <si>
+    <t>DKNG</t>
+  </si>
+  <si>
+    <t>PAGP</t>
+  </si>
+  <si>
+    <t>CFBK</t>
+  </si>
+  <si>
+    <t>WWD</t>
+  </si>
+  <si>
+    <t>HPE</t>
+  </si>
+  <si>
+    <t>STRS</t>
+  </si>
+  <si>
+    <t>DDS</t>
+  </si>
+  <si>
+    <t>LYB</t>
+  </si>
+  <si>
+    <t>SBFG</t>
+  </si>
+  <si>
+    <t>PATK</t>
+  </si>
+  <si>
+    <t>BWXT</t>
+  </si>
+  <si>
+    <t>CNS</t>
+  </si>
+  <si>
+    <t>SCCO</t>
+  </si>
+  <si>
+    <t>ICLR</t>
+  </si>
+  <si>
+    <t>VFC</t>
+  </si>
+  <si>
+    <t>EURN</t>
   </si>
 </sst>
 </file>
@@ -415,7 +2128,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B587"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -431,7 +2144,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1">
-        <v>158.5165923821816</v>
+        <v>367.365189127595</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -439,7 +2152,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1">
-        <v>123.9674258761739</v>
+        <v>350.0340710060489</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -447,7 +2160,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1">
-        <v>120.2036448358768</v>
+        <v>341.8876227007241</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -455,7 +2168,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="1">
-        <v>116.8165831194336</v>
+        <v>281.9982377747722</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -463,7 +2176,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="1">
-        <v>116.0053880386057</v>
+        <v>278.3347514987391</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -471,7 +2184,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="1">
-        <v>115.5843379752632</v>
+        <v>269.0856612119244</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -479,7 +2192,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="1">
-        <v>115.5157285613406</v>
+        <v>232.1111246910582</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -487,7 +2200,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="1">
-        <v>114.7923154557496</v>
+        <v>229.3056354874691</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -495,7 +2208,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="1">
-        <v>113.2722392686485</v>
+        <v>224.4946559530995</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -503,7 +2216,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="1">
-        <v>111.221667566574</v>
+        <v>217.7896475721439</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -511,7 +2224,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="1">
-        <v>110.135244194136</v>
+        <v>216.4746473738084</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -519,7 +2232,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="1">
-        <v>109.8073800614181</v>
+        <v>212.1284761913011</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -527,7 +2240,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="1">
-        <v>109.6120061433241</v>
+        <v>180.9346638752744</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -535,7 +2248,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="1">
-        <v>109.4401331598144</v>
+        <v>169.8495911945186</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -543,7 +2256,4575 @@
         <v>16</v>
       </c>
       <c r="B16" s="1">
-        <v>109.3504917974402</v>
+        <v>165.893637541049</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="1">
+        <v>165.6254054028396</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="1">
+        <v>158.2716696196807</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="1">
+        <v>157.8478878611776</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="1">
+        <v>156.2942661247725</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="1">
+        <v>153.5582675059871</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="1">
+        <v>152.4339128984715</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="1">
+        <v>151.2519178835652</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="1">
+        <v>151.2280504733532</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="1">
+        <v>151.216447233269</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" s="1">
+        <v>149.6820914079164</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" s="1">
+        <v>148.6519279352862</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" s="1">
+        <v>148.4868335887433</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29" s="1">
+        <v>147.863406136705</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30" s="1">
+        <v>147.8050288287885</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31" s="1">
+        <v>147.7533404110362</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32" s="1">
+        <v>146.3594336714994</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33" s="1">
+        <v>146.2610271569462</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>34</v>
+      </c>
+      <c r="B34" s="1">
+        <v>146.2477111771201</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>35</v>
+      </c>
+      <c r="B35" s="1">
+        <v>145.5016863974711</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>36</v>
+      </c>
+      <c r="B36" s="1">
+        <v>145.3517446689975</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="1">
+        <v>144.1438398038153</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="1">
+        <v>143.6799140950631</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="1">
+        <v>142.7892212824563</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="1">
+        <v>142.3611793459206</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="1">
+        <v>141.5229973515477</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" s="1">
+        <v>141.414517585197</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" t="s">
+        <v>43</v>
+      </c>
+      <c r="B43" s="1">
+        <v>141.2041648549374</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" t="s">
+        <v>44</v>
+      </c>
+      <c r="B44" s="1">
+        <v>141.1577525895082</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" t="s">
+        <v>45</v>
+      </c>
+      <c r="B45" s="1">
+        <v>140.7682618360872</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" t="s">
+        <v>46</v>
+      </c>
+      <c r="B46" s="1">
+        <v>140.5052586684555</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" t="s">
+        <v>47</v>
+      </c>
+      <c r="B47" s="1">
+        <v>140.3688242188591</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" t="s">
+        <v>48</v>
+      </c>
+      <c r="B48" s="1">
+        <v>139.9040723880485</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" t="s">
+        <v>49</v>
+      </c>
+      <c r="B49" s="1">
+        <v>138.7236716690947</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" t="s">
+        <v>50</v>
+      </c>
+      <c r="B50" s="1">
+        <v>138.1938042121476</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" t="s">
+        <v>51</v>
+      </c>
+      <c r="B51" s="1">
+        <v>137.6919955565027</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" t="s">
+        <v>52</v>
+      </c>
+      <c r="B52" s="1">
+        <v>137.6161578341367</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" t="s">
+        <v>53</v>
+      </c>
+      <c r="B53" s="1">
+        <v>137.5964350349556</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" t="s">
+        <v>54</v>
+      </c>
+      <c r="B54" s="1">
+        <v>137.4266775413192</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" t="s">
+        <v>55</v>
+      </c>
+      <c r="B55" s="1">
+        <v>137.2468539544757</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" t="s">
+        <v>56</v>
+      </c>
+      <c r="B56" s="1">
+        <v>136.2565295561244</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" t="s">
+        <v>57</v>
+      </c>
+      <c r="B57" s="1">
+        <v>135.9091675644856</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" t="s">
+        <v>58</v>
+      </c>
+      <c r="B58" s="1">
+        <v>135.708294938195</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" t="s">
+        <v>59</v>
+      </c>
+      <c r="B59" s="1">
+        <v>135.6341139122364</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" t="s">
+        <v>60</v>
+      </c>
+      <c r="B60" s="1">
+        <v>134.923162845435</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" t="s">
+        <v>61</v>
+      </c>
+      <c r="B61" s="1">
+        <v>134.9224817494981</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" t="s">
+        <v>62</v>
+      </c>
+      <c r="B62" s="1">
+        <v>134.8222439040043</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" t="s">
+        <v>63</v>
+      </c>
+      <c r="B63" s="1">
+        <v>134.8209953642474</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" t="s">
+        <v>64</v>
+      </c>
+      <c r="B64" s="1">
+        <v>134.7029720623959</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" t="s">
+        <v>65</v>
+      </c>
+      <c r="B65" s="1">
+        <v>134.6647276734397</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" t="s">
+        <v>66</v>
+      </c>
+      <c r="B66" s="1">
+        <v>134.0457650766354</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" t="s">
+        <v>67</v>
+      </c>
+      <c r="B67" s="1">
+        <v>133.7777466083522</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" t="s">
+        <v>68</v>
+      </c>
+      <c r="B68" s="1">
+        <v>133.661336542394</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" t="s">
+        <v>69</v>
+      </c>
+      <c r="B69" s="1">
+        <v>133.5750233627743</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" t="s">
+        <v>70</v>
+      </c>
+      <c r="B70" s="1">
+        <v>133.4729998160718</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" t="s">
+        <v>71</v>
+      </c>
+      <c r="B71" s="1">
+        <v>132.9176474337629</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" t="s">
+        <v>72</v>
+      </c>
+      <c r="B72" s="1">
+        <v>132.8527369998306</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" t="s">
+        <v>73</v>
+      </c>
+      <c r="B73" s="1">
+        <v>132.7768379220713</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" t="s">
+        <v>74</v>
+      </c>
+      <c r="B74" s="1">
+        <v>132.6371590601599</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" t="s">
+        <v>75</v>
+      </c>
+      <c r="B75" s="1">
+        <v>132.0743204969195</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" t="s">
+        <v>76</v>
+      </c>
+      <c r="B76" s="1">
+        <v>131.5279893439846</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" t="s">
+        <v>77</v>
+      </c>
+      <c r="B77" s="1">
+        <v>131.5024906438925</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" t="s">
+        <v>78</v>
+      </c>
+      <c r="B78" s="1">
+        <v>131.363400383611</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" t="s">
+        <v>79</v>
+      </c>
+      <c r="B79" s="1">
+        <v>131.3479331523545</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" t="s">
+        <v>80</v>
+      </c>
+      <c r="B80" s="1">
+        <v>131.2446031928867</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" t="s">
+        <v>81</v>
+      </c>
+      <c r="B81" s="1">
+        <v>130.8148007927623</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" t="s">
+        <v>82</v>
+      </c>
+      <c r="B82" s="1">
+        <v>130.7295189823975</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" t="s">
+        <v>83</v>
+      </c>
+      <c r="B83" s="1">
+        <v>130.6671392307618</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" t="s">
+        <v>84</v>
+      </c>
+      <c r="B84" s="1">
+        <v>130.2605944349812</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" t="s">
+        <v>85</v>
+      </c>
+      <c r="B85" s="1">
+        <v>130.0405810679477</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" t="s">
+        <v>86</v>
+      </c>
+      <c r="B86" s="1">
+        <v>130.033824091785</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" t="s">
+        <v>87</v>
+      </c>
+      <c r="B87" s="1">
+        <v>130.0037772771292</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88" t="s">
+        <v>88</v>
+      </c>
+      <c r="B88" s="1">
+        <v>129.5837880651845</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" t="s">
+        <v>89</v>
+      </c>
+      <c r="B89" s="1">
+        <v>129.5666680134296</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90" t="s">
+        <v>90</v>
+      </c>
+      <c r="B90" s="1">
+        <v>129.4427305635469</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91" t="s">
+        <v>91</v>
+      </c>
+      <c r="B91" s="1">
+        <v>129.3100396723562</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92" t="s">
+        <v>92</v>
+      </c>
+      <c r="B92" s="1">
+        <v>129.2571142878984</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" t="s">
+        <v>93</v>
+      </c>
+      <c r="B93" s="1">
+        <v>129.2066536885204</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" t="s">
+        <v>94</v>
+      </c>
+      <c r="B94" s="1">
+        <v>129.032909483407</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" t="s">
+        <v>95</v>
+      </c>
+      <c r="B95" s="1">
+        <v>129.0133920079554</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" t="s">
+        <v>96</v>
+      </c>
+      <c r="B96" s="1">
+        <v>128.7632057633027</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" t="s">
+        <v>97</v>
+      </c>
+      <c r="B97" s="1">
+        <v>128.6856382568543</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" t="s">
+        <v>98</v>
+      </c>
+      <c r="B98" s="1">
+        <v>128.406150717161</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" t="s">
+        <v>99</v>
+      </c>
+      <c r="B99" s="1">
+        <v>128.2898609918281</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" t="s">
+        <v>100</v>
+      </c>
+      <c r="B100" s="1">
+        <v>128.2121808954344</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" t="s">
+        <v>101</v>
+      </c>
+      <c r="B101" s="1">
+        <v>128.2064210271663</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" t="s">
+        <v>102</v>
+      </c>
+      <c r="B102" s="1">
+        <v>128.1785188283537</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" t="s">
+        <v>103</v>
+      </c>
+      <c r="B103" s="1">
+        <v>128.0456747602422</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" t="s">
+        <v>104</v>
+      </c>
+      <c r="B104" s="1">
+        <v>127.8531620145949</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" t="s">
+        <v>105</v>
+      </c>
+      <c r="B105" s="1">
+        <v>127.6916827965863</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" t="s">
+        <v>106</v>
+      </c>
+      <c r="B106" s="1">
+        <v>127.4356076082371</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" t="s">
+        <v>107</v>
+      </c>
+      <c r="B107" s="1">
+        <v>127.3983371195367</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" t="s">
+        <v>108</v>
+      </c>
+      <c r="B108" s="1">
+        <v>127.2324382390233</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" t="s">
+        <v>109</v>
+      </c>
+      <c r="B109" s="1">
+        <v>127.1985120234847</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" t="s">
+        <v>110</v>
+      </c>
+      <c r="B110" s="1">
+        <v>127.1004573738192</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" t="s">
+        <v>111</v>
+      </c>
+      <c r="B111" s="1">
+        <v>126.985876548102</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" t="s">
+        <v>112</v>
+      </c>
+      <c r="B112" s="1">
+        <v>126.8126702840656</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" t="s">
+        <v>113</v>
+      </c>
+      <c r="B113" s="1">
+        <v>126.7506147376815</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" t="s">
+        <v>114</v>
+      </c>
+      <c r="B114" s="1">
+        <v>126.4365163530184</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" t="s">
+        <v>115</v>
+      </c>
+      <c r="B115" s="1">
+        <v>126.4094617770374</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" t="s">
+        <v>116</v>
+      </c>
+      <c r="B116" s="1">
+        <v>126.3374451950819</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" t="s">
+        <v>117</v>
+      </c>
+      <c r="B117" s="1">
+        <v>126.2679433413379</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" t="s">
+        <v>118</v>
+      </c>
+      <c r="B118" s="1">
+        <v>126.173736662738</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" t="s">
+        <v>119</v>
+      </c>
+      <c r="B119" s="1">
+        <v>126.0895369497327</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" t="s">
+        <v>120</v>
+      </c>
+      <c r="B120" s="1">
+        <v>126.0333016365484</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" t="s">
+        <v>121</v>
+      </c>
+      <c r="B121" s="1">
+        <v>125.8892274563426</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122" t="s">
+        <v>122</v>
+      </c>
+      <c r="B122" s="1">
+        <v>125.5863169866949</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" t="s">
+        <v>123</v>
+      </c>
+      <c r="B123" s="1">
+        <v>125.5312013648904</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124" t="s">
+        <v>124</v>
+      </c>
+      <c r="B124" s="1">
+        <v>125.332925221772</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125" t="s">
+        <v>125</v>
+      </c>
+      <c r="B125" s="1">
+        <v>125.1609277827849</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126" t="s">
+        <v>126</v>
+      </c>
+      <c r="B126" s="1">
+        <v>125.0462148447059</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127" t="s">
+        <v>127</v>
+      </c>
+      <c r="B127" s="1">
+        <v>125.0193762936817</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" t="s">
+        <v>128</v>
+      </c>
+      <c r="B128" s="1">
+        <v>124.9889929642181</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" t="s">
+        <v>129</v>
+      </c>
+      <c r="B129" s="1">
+        <v>124.8927017652516</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130" t="s">
+        <v>130</v>
+      </c>
+      <c r="B130" s="1">
+        <v>124.8637330331905</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" t="s">
+        <v>131</v>
+      </c>
+      <c r="B131" s="1">
+        <v>124.7726592660137</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" t="s">
+        <v>132</v>
+      </c>
+      <c r="B132" s="1">
+        <v>124.7464514213292</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133" t="s">
+        <v>133</v>
+      </c>
+      <c r="B133" s="1">
+        <v>124.6587897203242</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" t="s">
+        <v>134</v>
+      </c>
+      <c r="B134" s="1">
+        <v>124.6195427512572</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" t="s">
+        <v>135</v>
+      </c>
+      <c r="B135" s="1">
+        <v>124.5322927556025</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136" t="s">
+        <v>136</v>
+      </c>
+      <c r="B136" s="1">
+        <v>124.4386611660897</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137" t="s">
+        <v>137</v>
+      </c>
+      <c r="B137" s="1">
+        <v>124.4317701969513</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138" t="s">
+        <v>138</v>
+      </c>
+      <c r="B138" s="1">
+        <v>124.2641166795534</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139" t="s">
+        <v>139</v>
+      </c>
+      <c r="B139" s="1">
+        <v>124.1850491159853</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" t="s">
+        <v>140</v>
+      </c>
+      <c r="B140" s="1">
+        <v>124.0504263919983</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" t="s">
+        <v>141</v>
+      </c>
+      <c r="B141" s="1">
+        <v>124.0438977590193</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142" t="s">
+        <v>142</v>
+      </c>
+      <c r="B142" s="1">
+        <v>123.8657637971622</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143" t="s">
+        <v>143</v>
+      </c>
+      <c r="B143" s="1">
+        <v>123.8106313031927</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144" t="s">
+        <v>144</v>
+      </c>
+      <c r="B144" s="1">
+        <v>123.7486524590439</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" t="s">
+        <v>145</v>
+      </c>
+      <c r="B145" s="1">
+        <v>123.7058570200789</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146" t="s">
+        <v>146</v>
+      </c>
+      <c r="B146" s="1">
+        <v>123.5423512594482</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" t="s">
+        <v>147</v>
+      </c>
+      <c r="B147" s="1">
+        <v>123.4081148941395</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" t="s">
+        <v>148</v>
+      </c>
+      <c r="B148" s="1">
+        <v>123.3742631579212</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" t="s">
+        <v>149</v>
+      </c>
+      <c r="B149" s="1">
+        <v>123.2843931743379</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" t="s">
+        <v>150</v>
+      </c>
+      <c r="B150" s="1">
+        <v>123.2174161086014</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" t="s">
+        <v>151</v>
+      </c>
+      <c r="B151" s="1">
+        <v>123.1959709835127</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" t="s">
+        <v>152</v>
+      </c>
+      <c r="B152" s="1">
+        <v>123.0638916518348</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" t="s">
+        <v>153</v>
+      </c>
+      <c r="B153" s="1">
+        <v>123.0465017009082</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" t="s">
+        <v>154</v>
+      </c>
+      <c r="B154" s="1">
+        <v>122.9648207610722</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" t="s">
+        <v>155</v>
+      </c>
+      <c r="B155" s="1">
+        <v>122.837436758697</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" t="s">
+        <v>156</v>
+      </c>
+      <c r="B156" s="1">
+        <v>122.7723346629056</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" t="s">
+        <v>157</v>
+      </c>
+      <c r="B157" s="1">
+        <v>122.7405259057571</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158" t="s">
+        <v>158</v>
+      </c>
+      <c r="B158" s="1">
+        <v>122.6976085779776</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159" t="s">
+        <v>159</v>
+      </c>
+      <c r="B159" s="1">
+        <v>122.6925101913907</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160" t="s">
+        <v>160</v>
+      </c>
+      <c r="B160" s="1">
+        <v>122.6794025343286</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" t="s">
+        <v>161</v>
+      </c>
+      <c r="B161" s="1">
+        <v>122.6669422581622</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" t="s">
+        <v>162</v>
+      </c>
+      <c r="B162" s="1">
+        <v>122.6352002910656</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163" t="s">
+        <v>163</v>
+      </c>
+      <c r="B163" s="1">
+        <v>122.5645534028136</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" t="s">
+        <v>164</v>
+      </c>
+      <c r="B164" s="1">
+        <v>122.5007832214279</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165" t="s">
+        <v>165</v>
+      </c>
+      <c r="B165" s="1">
+        <v>122.4881458287939</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166" t="s">
+        <v>166</v>
+      </c>
+      <c r="B166" s="1">
+        <v>122.4707961866203</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167" t="s">
+        <v>167</v>
+      </c>
+      <c r="B167" s="1">
+        <v>122.4104087785523</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168" t="s">
+        <v>168</v>
+      </c>
+      <c r="B168" s="1">
+        <v>122.3751230667579</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169" t="s">
+        <v>169</v>
+      </c>
+      <c r="B169" s="1">
+        <v>122.3749542160245</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170" t="s">
+        <v>170</v>
+      </c>
+      <c r="B170" s="1">
+        <v>122.3646873901205</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171" t="s">
+        <v>171</v>
+      </c>
+      <c r="B171" s="1">
+        <v>122.3625055507816</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172" t="s">
+        <v>172</v>
+      </c>
+      <c r="B172" s="1">
+        <v>122.3332484035391</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173" t="s">
+        <v>173</v>
+      </c>
+      <c r="B173" s="1">
+        <v>122.3293545123131</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174" t="s">
+        <v>174</v>
+      </c>
+      <c r="B174" s="1">
+        <v>122.2879690757544</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175" t="s">
+        <v>175</v>
+      </c>
+      <c r="B175" s="1">
+        <v>122.1798265065437</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176" t="s">
+        <v>176</v>
+      </c>
+      <c r="B176" s="1">
+        <v>122.1602474375711</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177" t="s">
+        <v>177</v>
+      </c>
+      <c r="B177" s="1">
+        <v>121.9957582280899</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178" t="s">
+        <v>178</v>
+      </c>
+      <c r="B178" s="1">
+        <v>121.905323164701</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179" t="s">
+        <v>179</v>
+      </c>
+      <c r="B179" s="1">
+        <v>121.7883288830511</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
+      <c r="A180" t="s">
+        <v>180</v>
+      </c>
+      <c r="B180" s="1">
+        <v>121.7751601394658</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
+      <c r="A181" t="s">
+        <v>181</v>
+      </c>
+      <c r="B181" s="1">
+        <v>121.7189798364885</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
+      <c r="A182" t="s">
+        <v>182</v>
+      </c>
+      <c r="B182" s="1">
+        <v>121.6291743829991</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
+      <c r="A183" t="s">
+        <v>183</v>
+      </c>
+      <c r="B183" s="1">
+        <v>121.5498197485869</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
+      <c r="A184" t="s">
+        <v>184</v>
+      </c>
+      <c r="B184" s="1">
+        <v>121.4696861130258</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
+      <c r="A185" t="s">
+        <v>185</v>
+      </c>
+      <c r="B185" s="1">
+        <v>121.4510582343672</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
+      <c r="A186" t="s">
+        <v>186</v>
+      </c>
+      <c r="B186" s="1">
+        <v>121.3823181131021</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
+      <c r="A187" t="s">
+        <v>187</v>
+      </c>
+      <c r="B187" s="1">
+        <v>121.3408389133216</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188" t="s">
+        <v>188</v>
+      </c>
+      <c r="B188" s="1">
+        <v>121.1877249308588</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
+      <c r="A189" t="s">
+        <v>189</v>
+      </c>
+      <c r="B189" s="1">
+        <v>121.008309152316</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
+      <c r="A190" t="s">
+        <v>190</v>
+      </c>
+      <c r="B190" s="1">
+        <v>121.0047664874766</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
+      <c r="A191" t="s">
+        <v>191</v>
+      </c>
+      <c r="B191" s="1">
+        <v>120.9896702141069</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
+      <c r="A192" t="s">
+        <v>192</v>
+      </c>
+      <c r="B192" s="1">
+        <v>120.8618380809304</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
+      <c r="A193" t="s">
+        <v>193</v>
+      </c>
+      <c r="B193" s="1">
+        <v>120.643971220224</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2">
+      <c r="A194" t="s">
+        <v>194</v>
+      </c>
+      <c r="B194" s="1">
+        <v>120.435449966005</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2">
+      <c r="A195" t="s">
+        <v>195</v>
+      </c>
+      <c r="B195" s="1">
+        <v>120.3882329248872</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2">
+      <c r="A196" t="s">
+        <v>196</v>
+      </c>
+      <c r="B196" s="1">
+        <v>120.3695544835843</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2">
+      <c r="A197" t="s">
+        <v>197</v>
+      </c>
+      <c r="B197" s="1">
+        <v>120.3685133900473</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2">
+      <c r="A198" t="s">
+        <v>198</v>
+      </c>
+      <c r="B198" s="1">
+        <v>120.3493494130659</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2">
+      <c r="A199" t="s">
+        <v>199</v>
+      </c>
+      <c r="B199" s="1">
+        <v>120.3384928381095</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2">
+      <c r="A200" t="s">
+        <v>200</v>
+      </c>
+      <c r="B200" s="1">
+        <v>120.3373865913415</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2">
+      <c r="A201" t="s">
+        <v>201</v>
+      </c>
+      <c r="B201" s="1">
+        <v>120.3100240308019</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2">
+      <c r="A202" t="s">
+        <v>202</v>
+      </c>
+      <c r="B202" s="1">
+        <v>120.2745108561388</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2">
+      <c r="A203" t="s">
+        <v>203</v>
+      </c>
+      <c r="B203" s="1">
+        <v>120.2640426845117</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2">
+      <c r="A204" t="s">
+        <v>204</v>
+      </c>
+      <c r="B204" s="1">
+        <v>120.2605435008535</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2">
+      <c r="A205" t="s">
+        <v>205</v>
+      </c>
+      <c r="B205" s="1">
+        <v>120.2526852711057</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2">
+      <c r="A206" t="s">
+        <v>206</v>
+      </c>
+      <c r="B206" s="1">
+        <v>120.2186211903905</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2">
+      <c r="A207" t="s">
+        <v>207</v>
+      </c>
+      <c r="B207" s="1">
+        <v>120.1565316734505</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2">
+      <c r="A208" t="s">
+        <v>208</v>
+      </c>
+      <c r="B208" s="1">
+        <v>120.1490715176269</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2">
+      <c r="A209" t="s">
+        <v>209</v>
+      </c>
+      <c r="B209" s="1">
+        <v>120.0916146162473</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2">
+      <c r="A210" t="s">
+        <v>210</v>
+      </c>
+      <c r="B210" s="1">
+        <v>120.0240229256152</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2">
+      <c r="A211" t="s">
+        <v>211</v>
+      </c>
+      <c r="B211" s="1">
+        <v>119.9977801440651</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2">
+      <c r="A212" t="s">
+        <v>212</v>
+      </c>
+      <c r="B212" s="1">
+        <v>119.9928676709577</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2">
+      <c r="A213" t="s">
+        <v>213</v>
+      </c>
+      <c r="B213" s="1">
+        <v>119.9685370982104</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2">
+      <c r="A214" t="s">
+        <v>214</v>
+      </c>
+      <c r="B214" s="1">
+        <v>119.9313359841115</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2">
+      <c r="A215" t="s">
+        <v>215</v>
+      </c>
+      <c r="B215" s="1">
+        <v>119.9012665412881</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2">
+      <c r="A216" t="s">
+        <v>216</v>
+      </c>
+      <c r="B216" s="1">
+        <v>119.8763471795926</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2">
+      <c r="A217" t="s">
+        <v>217</v>
+      </c>
+      <c r="B217" s="1">
+        <v>119.8222693468075</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2">
+      <c r="A218" t="s">
+        <v>218</v>
+      </c>
+      <c r="B218" s="1">
+        <v>119.7536921220655</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2">
+      <c r="A219" t="s">
+        <v>219</v>
+      </c>
+      <c r="B219" s="1">
+        <v>119.6718655748274</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2">
+      <c r="A220" t="s">
+        <v>220</v>
+      </c>
+      <c r="B220" s="1">
+        <v>119.6586098908239</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2">
+      <c r="A221" t="s">
+        <v>221</v>
+      </c>
+      <c r="B221" s="1">
+        <v>119.6044701418876</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2">
+      <c r="A222" t="s">
+        <v>222</v>
+      </c>
+      <c r="B222" s="1">
+        <v>119.4928547295332</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2">
+      <c r="A223" t="s">
+        <v>223</v>
+      </c>
+      <c r="B223" s="1">
+        <v>119.4713022427287</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2">
+      <c r="A224" t="s">
+        <v>224</v>
+      </c>
+      <c r="B224" s="1">
+        <v>119.3870872101094</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2">
+      <c r="A225" t="s">
+        <v>225</v>
+      </c>
+      <c r="B225" s="1">
+        <v>119.2782332371309</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2">
+      <c r="A226" t="s">
+        <v>226</v>
+      </c>
+      <c r="B226" s="1">
+        <v>119.2383418487252</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2">
+      <c r="A227" t="s">
+        <v>227</v>
+      </c>
+      <c r="B227" s="1">
+        <v>119.2267736841242</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2">
+      <c r="A228" t="s">
+        <v>228</v>
+      </c>
+      <c r="B228" s="1">
+        <v>119.1602800750887</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2">
+      <c r="A229" t="s">
+        <v>229</v>
+      </c>
+      <c r="B229" s="1">
+        <v>119.0988998710212</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2">
+      <c r="A230" t="s">
+        <v>230</v>
+      </c>
+      <c r="B230" s="1">
+        <v>119.0336299063324</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2">
+      <c r="A231" t="s">
+        <v>231</v>
+      </c>
+      <c r="B231" s="1">
+        <v>118.9286611999692</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2">
+      <c r="A232" t="s">
+        <v>232</v>
+      </c>
+      <c r="B232" s="1">
+        <v>118.8574642875544</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2">
+      <c r="A233" t="s">
+        <v>233</v>
+      </c>
+      <c r="B233" s="1">
+        <v>118.7294780529284</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2">
+      <c r="A234" t="s">
+        <v>234</v>
+      </c>
+      <c r="B234" s="1">
+        <v>118.7116549987861</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2">
+      <c r="A235" t="s">
+        <v>235</v>
+      </c>
+      <c r="B235" s="1">
+        <v>118.6650922277848</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2">
+      <c r="A236" t="s">
+        <v>236</v>
+      </c>
+      <c r="B236" s="1">
+        <v>118.6194543334791</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2">
+      <c r="A237" t="s">
+        <v>237</v>
+      </c>
+      <c r="B237" s="1">
+        <v>118.5185972011887</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2">
+      <c r="A238" t="s">
+        <v>238</v>
+      </c>
+      <c r="B238" s="1">
+        <v>118.5062675489194</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2">
+      <c r="A239" t="s">
+        <v>239</v>
+      </c>
+      <c r="B239" s="1">
+        <v>118.471727942547</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2">
+      <c r="A240" t="s">
+        <v>240</v>
+      </c>
+      <c r="B240" s="1">
+        <v>118.4473235130647</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2">
+      <c r="A241" t="s">
+        <v>241</v>
+      </c>
+      <c r="B241" s="1">
+        <v>118.4187044492172</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2">
+      <c r="A242" t="s">
+        <v>242</v>
+      </c>
+      <c r="B242" s="1">
+        <v>118.4109808928197</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2">
+      <c r="A243" t="s">
+        <v>243</v>
+      </c>
+      <c r="B243" s="1">
+        <v>118.336975582168</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2">
+      <c r="A244" t="s">
+        <v>244</v>
+      </c>
+      <c r="B244" s="1">
+        <v>118.3148450230387</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2">
+      <c r="A245" t="s">
+        <v>245</v>
+      </c>
+      <c r="B245" s="1">
+        <v>118.2836626612427</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2">
+      <c r="A246" t="s">
+        <v>246</v>
+      </c>
+      <c r="B246" s="1">
+        <v>118.277576141401</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2">
+      <c r="A247" t="s">
+        <v>247</v>
+      </c>
+      <c r="B247" s="1">
+        <v>118.1961820525824</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2">
+      <c r="A248" t="s">
+        <v>248</v>
+      </c>
+      <c r="B248" s="1">
+        <v>118.1703137788589</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2">
+      <c r="A249" t="s">
+        <v>249</v>
+      </c>
+      <c r="B249" s="1">
+        <v>118.1544722429556</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2">
+      <c r="A250" t="s">
+        <v>250</v>
+      </c>
+      <c r="B250" s="1">
+        <v>118.1377849326235</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2">
+      <c r="A251" t="s">
+        <v>251</v>
+      </c>
+      <c r="B251" s="1">
+        <v>118.0402594775313</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2">
+      <c r="A252" t="s">
+        <v>252</v>
+      </c>
+      <c r="B252" s="1">
+        <v>118.0272086560831</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2">
+      <c r="A253" t="s">
+        <v>253</v>
+      </c>
+      <c r="B253" s="1">
+        <v>118.005893643287</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2">
+      <c r="A254" t="s">
+        <v>254</v>
+      </c>
+      <c r="B254" s="1">
+        <v>117.9852417999835</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2">
+      <c r="A255" t="s">
+        <v>255</v>
+      </c>
+      <c r="B255" s="1">
+        <v>117.9643783027335</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2">
+      <c r="A256" t="s">
+        <v>256</v>
+      </c>
+      <c r="B256" s="1">
+        <v>117.9027912167108</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2">
+      <c r="A257" t="s">
+        <v>257</v>
+      </c>
+      <c r="B257" s="1">
+        <v>117.8733865917665</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2">
+      <c r="A258" t="s">
+        <v>258</v>
+      </c>
+      <c r="B258" s="1">
+        <v>117.8631427938996</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2">
+      <c r="A259" t="s">
+        <v>259</v>
+      </c>
+      <c r="B259" s="1">
+        <v>117.8300645646352</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2">
+      <c r="A260" t="s">
+        <v>260</v>
+      </c>
+      <c r="B260" s="1">
+        <v>117.7593741758366</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2">
+      <c r="A261" t="s">
+        <v>261</v>
+      </c>
+      <c r="B261" s="1">
+        <v>117.7524559017542</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2">
+      <c r="A262" t="s">
+        <v>262</v>
+      </c>
+      <c r="B262" s="1">
+        <v>117.6961243521119</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2">
+      <c r="A263" t="s">
+        <v>263</v>
+      </c>
+      <c r="B263" s="1">
+        <v>117.6707026933316</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2">
+      <c r="A264" t="s">
+        <v>264</v>
+      </c>
+      <c r="B264" s="1">
+        <v>117.6355321472581</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2">
+      <c r="A265" t="s">
+        <v>265</v>
+      </c>
+      <c r="B265" s="1">
+        <v>117.6226741312743</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2">
+      <c r="A266" t="s">
+        <v>266</v>
+      </c>
+      <c r="B266" s="1">
+        <v>117.6075033409853</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2">
+      <c r="A267" t="s">
+        <v>267</v>
+      </c>
+      <c r="B267" s="1">
+        <v>117.598799610966</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2">
+      <c r="A268" t="s">
+        <v>268</v>
+      </c>
+      <c r="B268" s="1">
+        <v>117.5711200601933</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2">
+      <c r="A269" t="s">
+        <v>269</v>
+      </c>
+      <c r="B269" s="1">
+        <v>117.5348912454271</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2">
+      <c r="A270" t="s">
+        <v>270</v>
+      </c>
+      <c r="B270" s="1">
+        <v>117.5191824512938</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2">
+      <c r="A271" t="s">
+        <v>271</v>
+      </c>
+      <c r="B271" s="1">
+        <v>117.4925877701445</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2">
+      <c r="A272" t="s">
+        <v>272</v>
+      </c>
+      <c r="B272" s="1">
+        <v>117.4865144918828</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2">
+      <c r="A273" t="s">
+        <v>273</v>
+      </c>
+      <c r="B273" s="1">
+        <v>117.4492994203681</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2">
+      <c r="A274" t="s">
+        <v>274</v>
+      </c>
+      <c r="B274" s="1">
+        <v>117.4337446362687</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2">
+      <c r="A275" t="s">
+        <v>275</v>
+      </c>
+      <c r="B275" s="1">
+        <v>117.4174792500405</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2">
+      <c r="A276" t="s">
+        <v>276</v>
+      </c>
+      <c r="B276" s="1">
+        <v>117.288509107901</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2">
+      <c r="A277" t="s">
+        <v>277</v>
+      </c>
+      <c r="B277" s="1">
+        <v>117.2865342531691</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2">
+      <c r="A278" t="s">
+        <v>278</v>
+      </c>
+      <c r="B278" s="1">
+        <v>117.2736297783211</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2">
+      <c r="A279" t="s">
+        <v>279</v>
+      </c>
+      <c r="B279" s="1">
+        <v>117.2681884439967</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2">
+      <c r="A280" t="s">
+        <v>280</v>
+      </c>
+      <c r="B280" s="1">
+        <v>117.25787183182</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2">
+      <c r="A281" t="s">
+        <v>281</v>
+      </c>
+      <c r="B281" s="1">
+        <v>117.2536709758113</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2">
+      <c r="A282" t="s">
+        <v>282</v>
+      </c>
+      <c r="B282" s="1">
+        <v>117.1867799720908</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2">
+      <c r="A283" t="s">
+        <v>283</v>
+      </c>
+      <c r="B283" s="1">
+        <v>117.1784698968149</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2">
+      <c r="A284" t="s">
+        <v>284</v>
+      </c>
+      <c r="B284" s="1">
+        <v>117.0992421491662</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2">
+      <c r="A285" t="s">
+        <v>285</v>
+      </c>
+      <c r="B285" s="1">
+        <v>117.0400744034751</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2">
+      <c r="A286" t="s">
+        <v>286</v>
+      </c>
+      <c r="B286" s="1">
+        <v>117.0331529126549</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2">
+      <c r="A287" t="s">
+        <v>287</v>
+      </c>
+      <c r="B287" s="1">
+        <v>117.0328298125633</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2">
+      <c r="A288" t="s">
+        <v>288</v>
+      </c>
+      <c r="B288" s="1">
+        <v>117.0153215634094</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2">
+      <c r="A289" t="s">
+        <v>289</v>
+      </c>
+      <c r="B289" s="1">
+        <v>117.0073665088496</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2">
+      <c r="A290" t="s">
+        <v>290</v>
+      </c>
+      <c r="B290" s="1">
+        <v>117.0048362188108</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2">
+      <c r="A291" t="s">
+        <v>291</v>
+      </c>
+      <c r="B291" s="1">
+        <v>116.9495401710114</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2">
+      <c r="A292" t="s">
+        <v>292</v>
+      </c>
+      <c r="B292" s="1">
+        <v>116.8116136601508</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2">
+      <c r="A293" t="s">
+        <v>293</v>
+      </c>
+      <c r="B293" s="1">
+        <v>116.7988165487802</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2">
+      <c r="A294" t="s">
+        <v>294</v>
+      </c>
+      <c r="B294" s="1">
+        <v>116.6757169941372</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2">
+      <c r="A295" t="s">
+        <v>295</v>
+      </c>
+      <c r="B295" s="1">
+        <v>116.5933162781765</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2">
+      <c r="A296" t="s">
+        <v>296</v>
+      </c>
+      <c r="B296" s="1">
+        <v>116.5924932858657</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2">
+      <c r="A297" t="s">
+        <v>297</v>
+      </c>
+      <c r="B297" s="1">
+        <v>116.5738642845721</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2">
+      <c r="A298" t="s">
+        <v>298</v>
+      </c>
+      <c r="B298" s="1">
+        <v>116.5439195930108</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2">
+      <c r="A299" t="s">
+        <v>299</v>
+      </c>
+      <c r="B299" s="1">
+        <v>116.511590943913</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2">
+      <c r="A300" t="s">
+        <v>300</v>
+      </c>
+      <c r="B300" s="1">
+        <v>116.4769034851241</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2">
+      <c r="A301" t="s">
+        <v>301</v>
+      </c>
+      <c r="B301" s="1">
+        <v>116.4746066958744</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2">
+      <c r="A302" t="s">
+        <v>302</v>
+      </c>
+      <c r="B302" s="1">
+        <v>116.4542594480357</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2">
+      <c r="A303" t="s">
+        <v>303</v>
+      </c>
+      <c r="B303" s="1">
+        <v>116.4454871364777</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2">
+      <c r="A304" t="s">
+        <v>304</v>
+      </c>
+      <c r="B304" s="1">
+        <v>116.4245517242312</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2">
+      <c r="A305" t="s">
+        <v>305</v>
+      </c>
+      <c r="B305" s="1">
+        <v>116.4165237175696</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2">
+      <c r="A306" t="s">
+        <v>306</v>
+      </c>
+      <c r="B306" s="1">
+        <v>116.3912257732237</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2">
+      <c r="A307" t="s">
+        <v>307</v>
+      </c>
+      <c r="B307" s="1">
+        <v>116.3886222876035</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2">
+      <c r="A308" t="s">
+        <v>308</v>
+      </c>
+      <c r="B308" s="1">
+        <v>116.3693774519284</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2">
+      <c r="A309" t="s">
+        <v>309</v>
+      </c>
+      <c r="B309" s="1">
+        <v>116.3647686115201</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2">
+      <c r="A310" t="s">
+        <v>310</v>
+      </c>
+      <c r="B310" s="1">
+        <v>116.3647527767874</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2">
+      <c r="A311" t="s">
+        <v>311</v>
+      </c>
+      <c r="B311" s="1">
+        <v>116.3431058011608</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2">
+      <c r="A312" t="s">
+        <v>312</v>
+      </c>
+      <c r="B312" s="1">
+        <v>116.310780960434</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2">
+      <c r="A313" t="s">
+        <v>313</v>
+      </c>
+      <c r="B313" s="1">
+        <v>116.2992564404179</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2">
+      <c r="A314" t="s">
+        <v>314</v>
+      </c>
+      <c r="B314" s="1">
+        <v>116.2750377510557</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2">
+      <c r="A315" t="s">
+        <v>315</v>
+      </c>
+      <c r="B315" s="1">
+        <v>116.2741934198886</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2">
+      <c r="A316" t="s">
+        <v>316</v>
+      </c>
+      <c r="B316" s="1">
+        <v>116.2605385334144</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2">
+      <c r="A317" t="s">
+        <v>317</v>
+      </c>
+      <c r="B317" s="1">
+        <v>116.2268005133823</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2">
+      <c r="A318" t="s">
+        <v>318</v>
+      </c>
+      <c r="B318" s="1">
+        <v>116.2121541975533</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2">
+      <c r="A319" t="s">
+        <v>319</v>
+      </c>
+      <c r="B319" s="1">
+        <v>116.1566942381423</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2">
+      <c r="A320" t="s">
+        <v>320</v>
+      </c>
+      <c r="B320" s="1">
+        <v>116.1234239537334</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2">
+      <c r="A321" t="s">
+        <v>321</v>
+      </c>
+      <c r="B321" s="1">
+        <v>116.0863017640522</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2">
+      <c r="A322" t="s">
+        <v>322</v>
+      </c>
+      <c r="B322" s="1">
+        <v>116.064485437522</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2">
+      <c r="A323" t="s">
+        <v>323</v>
+      </c>
+      <c r="B323" s="1">
+        <v>116.0536691214113</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2">
+      <c r="A324" t="s">
+        <v>324</v>
+      </c>
+      <c r="B324" s="1">
+        <v>116.0270618051872</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2">
+      <c r="A325" t="s">
+        <v>325</v>
+      </c>
+      <c r="B325" s="1">
+        <v>116.0257302432735</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2">
+      <c r="A326" t="s">
+        <v>326</v>
+      </c>
+      <c r="B326" s="1">
+        <v>115.9829945754496</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2">
+      <c r="A327" t="s">
+        <v>327</v>
+      </c>
+      <c r="B327" s="1">
+        <v>115.9799778672907</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2">
+      <c r="A328" t="s">
+        <v>328</v>
+      </c>
+      <c r="B328" s="1">
+        <v>115.9742635580621</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2">
+      <c r="A329" t="s">
+        <v>329</v>
+      </c>
+      <c r="B329" s="1">
+        <v>115.9366396933145</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2">
+      <c r="A330" t="s">
+        <v>330</v>
+      </c>
+      <c r="B330" s="1">
+        <v>115.9268081560374</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2">
+      <c r="A331" t="s">
+        <v>331</v>
+      </c>
+      <c r="B331" s="1">
+        <v>115.899793485406</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2">
+      <c r="A332" t="s">
+        <v>332</v>
+      </c>
+      <c r="B332" s="1">
+        <v>115.8919818365401</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2">
+      <c r="A333" t="s">
+        <v>333</v>
+      </c>
+      <c r="B333" s="1">
+        <v>115.8154043423834</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2">
+      <c r="A334" t="s">
+        <v>334</v>
+      </c>
+      <c r="B334" s="1">
+        <v>115.8109764972475</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2">
+      <c r="A335" t="s">
+        <v>335</v>
+      </c>
+      <c r="B335" s="1">
+        <v>115.8023675086408</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2">
+      <c r="A336" t="s">
+        <v>336</v>
+      </c>
+      <c r="B336" s="1">
+        <v>115.7912257506566</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2">
+      <c r="A337" t="s">
+        <v>337</v>
+      </c>
+      <c r="B337" s="1">
+        <v>115.729582886662</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2">
+      <c r="A338" t="s">
+        <v>338</v>
+      </c>
+      <c r="B338" s="1">
+        <v>115.7278961334804</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2">
+      <c r="A339" t="s">
+        <v>339</v>
+      </c>
+      <c r="B339" s="1">
+        <v>115.684378083185</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2">
+      <c r="A340" t="s">
+        <v>340</v>
+      </c>
+      <c r="B340" s="1">
+        <v>115.6716788739994</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2">
+      <c r="A341" t="s">
+        <v>341</v>
+      </c>
+      <c r="B341" s="1">
+        <v>115.6372181286432</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2">
+      <c r="A342" t="s">
+        <v>342</v>
+      </c>
+      <c r="B342" s="1">
+        <v>115.6357996275238</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2">
+      <c r="A343" t="s">
+        <v>343</v>
+      </c>
+      <c r="B343" s="1">
+        <v>115.6129790736528</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2">
+      <c r="A344" t="s">
+        <v>344</v>
+      </c>
+      <c r="B344" s="1">
+        <v>115.6113095594524</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2">
+      <c r="A345" t="s">
+        <v>345</v>
+      </c>
+      <c r="B345" s="1">
+        <v>115.5888648314188</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2">
+      <c r="A346" t="s">
+        <v>346</v>
+      </c>
+      <c r="B346" s="1">
+        <v>115.5550352520424</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2">
+      <c r="A347" t="s">
+        <v>347</v>
+      </c>
+      <c r="B347" s="1">
+        <v>115.5280994413831</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2">
+      <c r="A348" t="s">
+        <v>348</v>
+      </c>
+      <c r="B348" s="1">
+        <v>115.5210501673947</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2">
+      <c r="A349" t="s">
+        <v>349</v>
+      </c>
+      <c r="B349" s="1">
+        <v>115.5003801093591</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2">
+      <c r="A350" t="s">
+        <v>350</v>
+      </c>
+      <c r="B350" s="1">
+        <v>115.4665201295584</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2">
+      <c r="A351" t="s">
+        <v>351</v>
+      </c>
+      <c r="B351" s="1">
+        <v>115.4250451934093</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2">
+      <c r="A352" t="s">
+        <v>352</v>
+      </c>
+      <c r="B352" s="1">
+        <v>115.4153233904614</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2">
+      <c r="A353" t="s">
+        <v>353</v>
+      </c>
+      <c r="B353" s="1">
+        <v>115.3998101822904</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2">
+      <c r="A354" t="s">
+        <v>354</v>
+      </c>
+      <c r="B354" s="1">
+        <v>115.3851862437931</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2">
+      <c r="A355" t="s">
+        <v>355</v>
+      </c>
+      <c r="B355" s="1">
+        <v>115.3631416617868</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2">
+      <c r="A356" t="s">
+        <v>356</v>
+      </c>
+      <c r="B356" s="1">
+        <v>115.3587316413947</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2">
+      <c r="A357" t="s">
+        <v>357</v>
+      </c>
+      <c r="B357" s="1">
+        <v>115.3525981039435</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2">
+      <c r="A358" t="s">
+        <v>358</v>
+      </c>
+      <c r="B358" s="1">
+        <v>115.3081852139851</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2">
+      <c r="A359" t="s">
+        <v>359</v>
+      </c>
+      <c r="B359" s="1">
+        <v>115.2794261145728</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2">
+      <c r="A360" t="s">
+        <v>360</v>
+      </c>
+      <c r="B360" s="1">
+        <v>115.2773652471783</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2">
+      <c r="A361" t="s">
+        <v>361</v>
+      </c>
+      <c r="B361" s="1">
+        <v>115.2636180149678</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2">
+      <c r="A362" t="s">
+        <v>362</v>
+      </c>
+      <c r="B362" s="1">
+        <v>115.2538928913416</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2">
+      <c r="A363" t="s">
+        <v>363</v>
+      </c>
+      <c r="B363" s="1">
+        <v>115.1903761933153</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2">
+      <c r="A364" t="s">
+        <v>364</v>
+      </c>
+      <c r="B364" s="1">
+        <v>115.1696839244146</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2">
+      <c r="A365" t="s">
+        <v>365</v>
+      </c>
+      <c r="B365" s="1">
+        <v>115.1274428452386</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2">
+      <c r="A366" t="s">
+        <v>366</v>
+      </c>
+      <c r="B366" s="1">
+        <v>115.1221143390295</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2">
+      <c r="A367" t="s">
+        <v>367</v>
+      </c>
+      <c r="B367" s="1">
+        <v>115.0977036481678</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2">
+      <c r="A368" t="s">
+        <v>368</v>
+      </c>
+      <c r="B368" s="1">
+        <v>115.079370153855</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2">
+      <c r="A369" t="s">
+        <v>369</v>
+      </c>
+      <c r="B369" s="1">
+        <v>115.0639465926794</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2">
+      <c r="A370" t="s">
+        <v>370</v>
+      </c>
+      <c r="B370" s="1">
+        <v>115.0637869299111</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2">
+      <c r="A371" t="s">
+        <v>371</v>
+      </c>
+      <c r="B371" s="1">
+        <v>115.0408035656555</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2">
+      <c r="A372" t="s">
+        <v>372</v>
+      </c>
+      <c r="B372" s="1">
+        <v>115.0402222808909</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2">
+      <c r="A373" t="s">
+        <v>373</v>
+      </c>
+      <c r="B373" s="1">
+        <v>115.0163544358535</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2">
+      <c r="A374" t="s">
+        <v>374</v>
+      </c>
+      <c r="B374" s="1">
+        <v>115.0064649477844</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2">
+      <c r="A375" t="s">
+        <v>375</v>
+      </c>
+      <c r="B375" s="1">
+        <v>114.9764016377146</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2">
+      <c r="A376" t="s">
+        <v>376</v>
+      </c>
+      <c r="B376" s="1">
+        <v>114.9571788090878</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2">
+      <c r="A377" t="s">
+        <v>377</v>
+      </c>
+      <c r="B377" s="1">
+        <v>114.9423250127247</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2">
+      <c r="A378" t="s">
+        <v>378</v>
+      </c>
+      <c r="B378" s="1">
+        <v>114.9272316375727</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2">
+      <c r="A379" t="s">
+        <v>379</v>
+      </c>
+      <c r="B379" s="1">
+        <v>114.9176529871134</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2">
+      <c r="A380" t="s">
+        <v>380</v>
+      </c>
+      <c r="B380" s="1">
+        <v>114.8601100230053</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2">
+      <c r="A381" t="s">
+        <v>381</v>
+      </c>
+      <c r="B381" s="1">
+        <v>114.8253947608493</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2">
+      <c r="A382" t="s">
+        <v>382</v>
+      </c>
+      <c r="B382" s="1">
+        <v>114.7432750225324</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2">
+      <c r="A383" t="s">
+        <v>383</v>
+      </c>
+      <c r="B383" s="1">
+        <v>114.7313601677314</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2">
+      <c r="A384" t="s">
+        <v>384</v>
+      </c>
+      <c r="B384" s="1">
+        <v>114.7149191505637</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2">
+      <c r="A385" t="s">
+        <v>385</v>
+      </c>
+      <c r="B385" s="1">
+        <v>114.7087121075753</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2">
+      <c r="A386" t="s">
+        <v>386</v>
+      </c>
+      <c r="B386" s="1">
+        <v>114.6770005910024</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2">
+      <c r="A387" t="s">
+        <v>387</v>
+      </c>
+      <c r="B387" s="1">
+        <v>114.6297653762043</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2">
+      <c r="A388" t="s">
+        <v>388</v>
+      </c>
+      <c r="B388" s="1">
+        <v>114.5972058077659</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2">
+      <c r="A389" t="s">
+        <v>389</v>
+      </c>
+      <c r="B389" s="1">
+        <v>114.5857754313303</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2">
+      <c r="A390" t="s">
+        <v>390</v>
+      </c>
+      <c r="B390" s="1">
+        <v>114.5597511901854</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2">
+      <c r="A391" t="s">
+        <v>391</v>
+      </c>
+      <c r="B391" s="1">
+        <v>114.5588641484246</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2">
+      <c r="A392" t="s">
+        <v>392</v>
+      </c>
+      <c r="B392" s="1">
+        <v>114.517912181153</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2">
+      <c r="A393" t="s">
+        <v>393</v>
+      </c>
+      <c r="B393" s="1">
+        <v>114.482830604689</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2">
+      <c r="A394" t="s">
+        <v>394</v>
+      </c>
+      <c r="B394" s="1">
+        <v>114.4644116400549</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2">
+      <c r="A395" t="s">
+        <v>395</v>
+      </c>
+      <c r="B395" s="1">
+        <v>114.4565939691257</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2">
+      <c r="A396" t="s">
+        <v>396</v>
+      </c>
+      <c r="B396" s="1">
+        <v>114.4427984334927</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2">
+      <c r="A397" t="s">
+        <v>397</v>
+      </c>
+      <c r="B397" s="1">
+        <v>114.3949854515352</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2">
+      <c r="A398" t="s">
+        <v>398</v>
+      </c>
+      <c r="B398" s="1">
+        <v>114.3888748811229</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2">
+      <c r="A399" t="s">
+        <v>399</v>
+      </c>
+      <c r="B399" s="1">
+        <v>114.3815528132307</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2">
+      <c r="A400" t="s">
+        <v>400</v>
+      </c>
+      <c r="B400" s="1">
+        <v>114.3756109003018</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2">
+      <c r="A401" t="s">
+        <v>401</v>
+      </c>
+      <c r="B401" s="1">
+        <v>114.3574320555643</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2">
+      <c r="A402" t="s">
+        <v>402</v>
+      </c>
+      <c r="B402" s="1">
+        <v>114.3564374712188</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2">
+      <c r="A403" t="s">
+        <v>403</v>
+      </c>
+      <c r="B403" s="1">
+        <v>114.3141929954747</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2">
+      <c r="A404" t="s">
+        <v>404</v>
+      </c>
+      <c r="B404" s="1">
+        <v>114.3040014365724</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2">
+      <c r="A405" t="s">
+        <v>405</v>
+      </c>
+      <c r="B405" s="1">
+        <v>114.2985190877281</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2">
+      <c r="A406" t="s">
+        <v>406</v>
+      </c>
+      <c r="B406" s="1">
+        <v>114.2657118378897</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2">
+      <c r="A407" t="s">
+        <v>407</v>
+      </c>
+      <c r="B407" s="1">
+        <v>114.2543180731323</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2">
+      <c r="A408" t="s">
+        <v>408</v>
+      </c>
+      <c r="B408" s="1">
+        <v>114.104583901422</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2">
+      <c r="A409" t="s">
+        <v>409</v>
+      </c>
+      <c r="B409" s="1">
+        <v>114.1035981217257</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2">
+      <c r="A410" t="s">
+        <v>410</v>
+      </c>
+      <c r="B410" s="1">
+        <v>114.0994714581257</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2">
+      <c r="A411" t="s">
+        <v>411</v>
+      </c>
+      <c r="B411" s="1">
+        <v>113.9989110009225</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2">
+      <c r="A412" t="s">
+        <v>412</v>
+      </c>
+      <c r="B412" s="1">
+        <v>113.9803143474116</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2">
+      <c r="A413" t="s">
+        <v>413</v>
+      </c>
+      <c r="B413" s="1">
+        <v>113.957388697597</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2">
+      <c r="A414" t="s">
+        <v>414</v>
+      </c>
+      <c r="B414" s="1">
+        <v>113.9249755349999</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2">
+      <c r="A415" t="s">
+        <v>415</v>
+      </c>
+      <c r="B415" s="1">
+        <v>113.9005311461096</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2">
+      <c r="A416" t="s">
+        <v>416</v>
+      </c>
+      <c r="B416" s="1">
+        <v>113.8842515408951</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2">
+      <c r="A417" t="s">
+        <v>417</v>
+      </c>
+      <c r="B417" s="1">
+        <v>113.8591780298825</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2">
+      <c r="A418" t="s">
+        <v>418</v>
+      </c>
+      <c r="B418" s="1">
+        <v>113.8389167067161</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2">
+      <c r="A419" t="s">
+        <v>419</v>
+      </c>
+      <c r="B419" s="1">
+        <v>113.8269434446479</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2">
+      <c r="A420" t="s">
+        <v>420</v>
+      </c>
+      <c r="B420" s="1">
+        <v>113.7680631008233</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2">
+      <c r="A421" t="s">
+        <v>421</v>
+      </c>
+      <c r="B421" s="1">
+        <v>113.7233926848544</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2">
+      <c r="A422" t="s">
+        <v>422</v>
+      </c>
+      <c r="B422" s="1">
+        <v>113.7123024576222</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2">
+      <c r="A423" t="s">
+        <v>423</v>
+      </c>
+      <c r="B423" s="1">
+        <v>113.7078981686206</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2">
+      <c r="A424" t="s">
+        <v>424</v>
+      </c>
+      <c r="B424" s="1">
+        <v>113.7000092587665</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2">
+      <c r="A425" t="s">
+        <v>425</v>
+      </c>
+      <c r="B425" s="1">
+        <v>113.6743383101207</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2">
+      <c r="A426" t="s">
+        <v>426</v>
+      </c>
+      <c r="B426" s="1">
+        <v>113.6028206946431</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2">
+      <c r="A427" t="s">
+        <v>427</v>
+      </c>
+      <c r="B427" s="1">
+        <v>113.5953034503218</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2">
+      <c r="A428" t="s">
+        <v>428</v>
+      </c>
+      <c r="B428" s="1">
+        <v>113.5836059180706</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2">
+      <c r="A429" t="s">
+        <v>429</v>
+      </c>
+      <c r="B429" s="1">
+        <v>113.5664541178336</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2">
+      <c r="A430" t="s">
+        <v>430</v>
+      </c>
+      <c r="B430" s="1">
+        <v>113.555086567314</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2">
+      <c r="A431" t="s">
+        <v>431</v>
+      </c>
+      <c r="B431" s="1">
+        <v>113.5360148789063</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2">
+      <c r="A432" t="s">
+        <v>432</v>
+      </c>
+      <c r="B432" s="1">
+        <v>113.5245088394541</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2">
+      <c r="A433" t="s">
+        <v>433</v>
+      </c>
+      <c r="B433" s="1">
+        <v>113.5205033235612</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2">
+      <c r="A434" t="s">
+        <v>434</v>
+      </c>
+      <c r="B434" s="1">
+        <v>113.517107509522</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2">
+      <c r="A435" t="s">
+        <v>435</v>
+      </c>
+      <c r="B435" s="1">
+        <v>113.4612356483266</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2">
+      <c r="A436" t="s">
+        <v>436</v>
+      </c>
+      <c r="B436" s="1">
+        <v>113.4156210683079</v>
+      </c>
+    </row>
+    <row r="437" spans="1:2">
+      <c r="A437" t="s">
+        <v>437</v>
+      </c>
+      <c r="B437" s="1">
+        <v>113.4089094099393</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2">
+      <c r="A438" t="s">
+        <v>438</v>
+      </c>
+      <c r="B438" s="1">
+        <v>113.4081453695192</v>
+      </c>
+    </row>
+    <row r="439" spans="1:2">
+      <c r="A439" t="s">
+        <v>439</v>
+      </c>
+      <c r="B439" s="1">
+        <v>113.375991445644</v>
+      </c>
+    </row>
+    <row r="440" spans="1:2">
+      <c r="A440" t="s">
+        <v>440</v>
+      </c>
+      <c r="B440" s="1">
+        <v>113.3744686091094</v>
+      </c>
+    </row>
+    <row r="441" spans="1:2">
+      <c r="A441" t="s">
+        <v>441</v>
+      </c>
+      <c r="B441" s="1">
+        <v>113.3484311955397</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2">
+      <c r="A442" t="s">
+        <v>442</v>
+      </c>
+      <c r="B442" s="1">
+        <v>113.3300754726304</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2">
+      <c r="A443" t="s">
+        <v>443</v>
+      </c>
+      <c r="B443" s="1">
+        <v>113.3190319966095</v>
+      </c>
+    </row>
+    <row r="444" spans="1:2">
+      <c r="A444" t="s">
+        <v>444</v>
+      </c>
+      <c r="B444" s="1">
+        <v>113.3106512740437</v>
+      </c>
+    </row>
+    <row r="445" spans="1:2">
+      <c r="A445" t="s">
+        <v>445</v>
+      </c>
+      <c r="B445" s="1">
+        <v>113.2829856832555</v>
+      </c>
+    </row>
+    <row r="446" spans="1:2">
+      <c r="A446" t="s">
+        <v>446</v>
+      </c>
+      <c r="B446" s="1">
+        <v>113.2806950489124</v>
+      </c>
+    </row>
+    <row r="447" spans="1:2">
+      <c r="A447" t="s">
+        <v>447</v>
+      </c>
+      <c r="B447" s="1">
+        <v>113.2785343433585</v>
+      </c>
+    </row>
+    <row r="448" spans="1:2">
+      <c r="A448" t="s">
+        <v>448</v>
+      </c>
+      <c r="B448" s="1">
+        <v>113.2774058256504</v>
+      </c>
+    </row>
+    <row r="449" spans="1:2">
+      <c r="A449" t="s">
+        <v>449</v>
+      </c>
+      <c r="B449" s="1">
+        <v>113.2727436354069</v>
+      </c>
+    </row>
+    <row r="450" spans="1:2">
+      <c r="A450" t="s">
+        <v>450</v>
+      </c>
+      <c r="B450" s="1">
+        <v>113.2530026115553</v>
+      </c>
+    </row>
+    <row r="451" spans="1:2">
+      <c r="A451" t="s">
+        <v>451</v>
+      </c>
+      <c r="B451" s="1">
+        <v>113.2151237461861</v>
+      </c>
+    </row>
+    <row r="452" spans="1:2">
+      <c r="A452" t="s">
+        <v>452</v>
+      </c>
+      <c r="B452" s="1">
+        <v>113.2129037481244</v>
+      </c>
+    </row>
+    <row r="453" spans="1:2">
+      <c r="A453" t="s">
+        <v>453</v>
+      </c>
+      <c r="B453" s="1">
+        <v>113.2120324687699</v>
+      </c>
+    </row>
+    <row r="454" spans="1:2">
+      <c r="A454" t="s">
+        <v>454</v>
+      </c>
+      <c r="B454" s="1">
+        <v>113.211970020346</v>
+      </c>
+    </row>
+    <row r="455" spans="1:2">
+      <c r="A455" t="s">
+        <v>455</v>
+      </c>
+      <c r="B455" s="1">
+        <v>113.2002522856803</v>
+      </c>
+    </row>
+    <row r="456" spans="1:2">
+      <c r="A456" t="s">
+        <v>456</v>
+      </c>
+      <c r="B456" s="1">
+        <v>113.1408907402909</v>
+      </c>
+    </row>
+    <row r="457" spans="1:2">
+      <c r="A457" t="s">
+        <v>457</v>
+      </c>
+      <c r="B457" s="1">
+        <v>113.1353480525381</v>
+      </c>
+    </row>
+    <row r="458" spans="1:2">
+      <c r="A458" t="s">
+        <v>458</v>
+      </c>
+      <c r="B458" s="1">
+        <v>113.128095689576</v>
+      </c>
+    </row>
+    <row r="459" spans="1:2">
+      <c r="A459" t="s">
+        <v>459</v>
+      </c>
+      <c r="B459" s="1">
+        <v>113.111105261125</v>
+      </c>
+    </row>
+    <row r="460" spans="1:2">
+      <c r="A460" t="s">
+        <v>460</v>
+      </c>
+      <c r="B460" s="1">
+        <v>113.0557967583988</v>
+      </c>
+    </row>
+    <row r="461" spans="1:2">
+      <c r="A461" t="s">
+        <v>461</v>
+      </c>
+      <c r="B461" s="1">
+        <v>113.0386243581854</v>
+      </c>
+    </row>
+    <row r="462" spans="1:2">
+      <c r="A462" t="s">
+        <v>462</v>
+      </c>
+      <c r="B462" s="1">
+        <v>113.0263970745329</v>
+      </c>
+    </row>
+    <row r="463" spans="1:2">
+      <c r="A463" t="s">
+        <v>463</v>
+      </c>
+      <c r="B463" s="1">
+        <v>113.0208378559884</v>
+      </c>
+    </row>
+    <row r="464" spans="1:2">
+      <c r="A464" t="s">
+        <v>464</v>
+      </c>
+      <c r="B464" s="1">
+        <v>113.0056820733351</v>
+      </c>
+    </row>
+    <row r="465" spans="1:2">
+      <c r="A465" t="s">
+        <v>465</v>
+      </c>
+      <c r="B465" s="1">
+        <v>112.997638524304</v>
+      </c>
+    </row>
+    <row r="466" spans="1:2">
+      <c r="A466" t="s">
+        <v>466</v>
+      </c>
+      <c r="B466" s="1">
+        <v>112.9959652606525</v>
+      </c>
+    </row>
+    <row r="467" spans="1:2">
+      <c r="A467" t="s">
+        <v>467</v>
+      </c>
+      <c r="B467" s="1">
+        <v>112.9953514120438</v>
+      </c>
+    </row>
+    <row r="468" spans="1:2">
+      <c r="A468" t="s">
+        <v>468</v>
+      </c>
+      <c r="B468" s="1">
+        <v>112.9288738602858</v>
+      </c>
+    </row>
+    <row r="469" spans="1:2">
+      <c r="A469" t="s">
+        <v>469</v>
+      </c>
+      <c r="B469" s="1">
+        <v>112.8551484871203</v>
+      </c>
+    </row>
+    <row r="470" spans="1:2">
+      <c r="A470" t="s">
+        <v>470</v>
+      </c>
+      <c r="B470" s="1">
+        <v>112.8268557516504</v>
+      </c>
+    </row>
+    <row r="471" spans="1:2">
+      <c r="A471" t="s">
+        <v>471</v>
+      </c>
+      <c r="B471" s="1">
+        <v>112.8226756980466</v>
+      </c>
+    </row>
+    <row r="472" spans="1:2">
+      <c r="A472" t="s">
+        <v>472</v>
+      </c>
+      <c r="B472" s="1">
+        <v>112.8083674427615</v>
+      </c>
+    </row>
+    <row r="473" spans="1:2">
+      <c r="A473" t="s">
+        <v>473</v>
+      </c>
+      <c r="B473" s="1">
+        <v>112.8080763840722</v>
+      </c>
+    </row>
+    <row r="474" spans="1:2">
+      <c r="A474" t="s">
+        <v>474</v>
+      </c>
+      <c r="B474" s="1">
+        <v>112.8072449486699</v>
+      </c>
+    </row>
+    <row r="475" spans="1:2">
+      <c r="A475" t="s">
+        <v>475</v>
+      </c>
+      <c r="B475" s="1">
+        <v>112.8054306548381</v>
+      </c>
+    </row>
+    <row r="476" spans="1:2">
+      <c r="A476" t="s">
+        <v>476</v>
+      </c>
+      <c r="B476" s="1">
+        <v>112.8050894598995</v>
+      </c>
+    </row>
+    <row r="477" spans="1:2">
+      <c r="A477" t="s">
+        <v>477</v>
+      </c>
+      <c r="B477" s="1">
+        <v>112.7995728489312</v>
+      </c>
+    </row>
+    <row r="478" spans="1:2">
+      <c r="A478" t="s">
+        <v>478</v>
+      </c>
+      <c r="B478" s="1">
+        <v>112.7926963951675</v>
+      </c>
+    </row>
+    <row r="479" spans="1:2">
+      <c r="A479" t="s">
+        <v>479</v>
+      </c>
+      <c r="B479" s="1">
+        <v>112.7808599641692</v>
+      </c>
+    </row>
+    <row r="480" spans="1:2">
+      <c r="A480" t="s">
+        <v>480</v>
+      </c>
+      <c r="B480" s="1">
+        <v>112.7805953993746</v>
+      </c>
+    </row>
+    <row r="481" spans="1:2">
+      <c r="A481" t="s">
+        <v>481</v>
+      </c>
+      <c r="B481" s="1">
+        <v>112.7746637176459</v>
+      </c>
+    </row>
+    <row r="482" spans="1:2">
+      <c r="A482" t="s">
+        <v>482</v>
+      </c>
+      <c r="B482" s="1">
+        <v>112.6954665441004</v>
+      </c>
+    </row>
+    <row r="483" spans="1:2">
+      <c r="A483" t="s">
+        <v>483</v>
+      </c>
+      <c r="B483" s="1">
+        <v>112.6953381593454</v>
+      </c>
+    </row>
+    <row r="484" spans="1:2">
+      <c r="A484" t="s">
+        <v>484</v>
+      </c>
+      <c r="B484" s="1">
+        <v>112.6698031852092</v>
+      </c>
+    </row>
+    <row r="485" spans="1:2">
+      <c r="A485" t="s">
+        <v>485</v>
+      </c>
+      <c r="B485" s="1">
+        <v>112.6472867044426</v>
+      </c>
+    </row>
+    <row r="486" spans="1:2">
+      <c r="A486" t="s">
+        <v>486</v>
+      </c>
+      <c r="B486" s="1">
+        <v>112.6360934826494</v>
+      </c>
+    </row>
+    <row r="487" spans="1:2">
+      <c r="A487" t="s">
+        <v>487</v>
+      </c>
+      <c r="B487" s="1">
+        <v>112.6246358800362</v>
+      </c>
+    </row>
+    <row r="488" spans="1:2">
+      <c r="A488" t="s">
+        <v>488</v>
+      </c>
+      <c r="B488" s="1">
+        <v>112.6152148095978</v>
+      </c>
+    </row>
+    <row r="489" spans="1:2">
+      <c r="A489" t="s">
+        <v>489</v>
+      </c>
+      <c r="B489" s="1">
+        <v>112.6082885475082</v>
+      </c>
+    </row>
+    <row r="490" spans="1:2">
+      <c r="A490" t="s">
+        <v>490</v>
+      </c>
+      <c r="B490" s="1">
+        <v>112.6032300844741</v>
+      </c>
+    </row>
+    <row r="491" spans="1:2">
+      <c r="A491" t="s">
+        <v>491</v>
+      </c>
+      <c r="B491" s="1">
+        <v>112.5829640882694</v>
+      </c>
+    </row>
+    <row r="492" spans="1:2">
+      <c r="A492" t="s">
+        <v>492</v>
+      </c>
+      <c r="B492" s="1">
+        <v>112.5642632891174</v>
+      </c>
+    </row>
+    <row r="493" spans="1:2">
+      <c r="A493" t="s">
+        <v>493</v>
+      </c>
+      <c r="B493" s="1">
+        <v>112.5601572749383</v>
+      </c>
+    </row>
+    <row r="494" spans="1:2">
+      <c r="A494" t="s">
+        <v>494</v>
+      </c>
+      <c r="B494" s="1">
+        <v>112.5555275948092</v>
+      </c>
+    </row>
+    <row r="495" spans="1:2">
+      <c r="A495" t="s">
+        <v>495</v>
+      </c>
+      <c r="B495" s="1">
+        <v>112.4864598793526</v>
+      </c>
+    </row>
+    <row r="496" spans="1:2">
+      <c r="A496" t="s">
+        <v>496</v>
+      </c>
+      <c r="B496" s="1">
+        <v>112.468176234963</v>
+      </c>
+    </row>
+    <row r="497" spans="1:2">
+      <c r="A497" t="s">
+        <v>497</v>
+      </c>
+      <c r="B497" s="1">
+        <v>112.4556794326438</v>
+      </c>
+    </row>
+    <row r="498" spans="1:2">
+      <c r="A498" t="s">
+        <v>498</v>
+      </c>
+      <c r="B498" s="1">
+        <v>112.4469116691243</v>
+      </c>
+    </row>
+    <row r="499" spans="1:2">
+      <c r="A499" t="s">
+        <v>499</v>
+      </c>
+      <c r="B499" s="1">
+        <v>112.410696089415</v>
+      </c>
+    </row>
+    <row r="500" spans="1:2">
+      <c r="A500" t="s">
+        <v>500</v>
+      </c>
+      <c r="B500" s="1">
+        <v>112.3959527997969</v>
+      </c>
+    </row>
+    <row r="501" spans="1:2">
+      <c r="A501" t="s">
+        <v>501</v>
+      </c>
+      <c r="B501" s="1">
+        <v>112.3902285870098</v>
+      </c>
+    </row>
+    <row r="502" spans="1:2">
+      <c r="A502" t="s">
+        <v>502</v>
+      </c>
+      <c r="B502" s="1">
+        <v>112.384949898494</v>
+      </c>
+    </row>
+    <row r="503" spans="1:2">
+      <c r="A503" t="s">
+        <v>503</v>
+      </c>
+      <c r="B503" s="1">
+        <v>112.3698678917445</v>
+      </c>
+    </row>
+    <row r="504" spans="1:2">
+      <c r="A504" t="s">
+        <v>504</v>
+      </c>
+      <c r="B504" s="1">
+        <v>112.3643267795415</v>
+      </c>
+    </row>
+    <row r="505" spans="1:2">
+      <c r="A505" t="s">
+        <v>505</v>
+      </c>
+      <c r="B505" s="1">
+        <v>112.3532569803167</v>
+      </c>
+    </row>
+    <row r="506" spans="1:2">
+      <c r="A506" t="s">
+        <v>506</v>
+      </c>
+      <c r="B506" s="1">
+        <v>112.348921576405</v>
+      </c>
+    </row>
+    <row r="507" spans="1:2">
+      <c r="A507" t="s">
+        <v>507</v>
+      </c>
+      <c r="B507" s="1">
+        <v>112.3457151863544</v>
+      </c>
+    </row>
+    <row r="508" spans="1:2">
+      <c r="A508" t="s">
+        <v>508</v>
+      </c>
+      <c r="B508" s="1">
+        <v>112.3443100643494</v>
+      </c>
+    </row>
+    <row r="509" spans="1:2">
+      <c r="A509" t="s">
+        <v>509</v>
+      </c>
+      <c r="B509" s="1">
+        <v>112.3366263603164</v>
+      </c>
+    </row>
+    <row r="510" spans="1:2">
+      <c r="A510" t="s">
+        <v>510</v>
+      </c>
+      <c r="B510" s="1">
+        <v>112.3270094118785</v>
+      </c>
+    </row>
+    <row r="511" spans="1:2">
+      <c r="A511" t="s">
+        <v>511</v>
+      </c>
+      <c r="B511" s="1">
+        <v>112.3128845773402</v>
+      </c>
+    </row>
+    <row r="512" spans="1:2">
+      <c r="A512" t="s">
+        <v>512</v>
+      </c>
+      <c r="B512" s="1">
+        <v>112.3128219282962</v>
+      </c>
+    </row>
+    <row r="513" spans="1:2">
+      <c r="A513" t="s">
+        <v>513</v>
+      </c>
+      <c r="B513" s="1">
+        <v>112.2855288775107</v>
+      </c>
+    </row>
+    <row r="514" spans="1:2">
+      <c r="A514" t="s">
+        <v>514</v>
+      </c>
+      <c r="B514" s="1">
+        <v>112.2815784672865</v>
+      </c>
+    </row>
+    <row r="515" spans="1:2">
+      <c r="A515" t="s">
+        <v>515</v>
+      </c>
+      <c r="B515" s="1">
+        <v>112.2490515934971</v>
+      </c>
+    </row>
+    <row r="516" spans="1:2">
+      <c r="A516" t="s">
+        <v>516</v>
+      </c>
+      <c r="B516" s="1">
+        <v>112.1978404523026</v>
+      </c>
+    </row>
+    <row r="517" spans="1:2">
+      <c r="A517" t="s">
+        <v>517</v>
+      </c>
+      <c r="B517" s="1">
+        <v>112.1970028308614</v>
+      </c>
+    </row>
+    <row r="518" spans="1:2">
+      <c r="A518" t="s">
+        <v>518</v>
+      </c>
+      <c r="B518" s="1">
+        <v>112.1521745869466</v>
+      </c>
+    </row>
+    <row r="519" spans="1:2">
+      <c r="A519" t="s">
+        <v>519</v>
+      </c>
+      <c r="B519" s="1">
+        <v>112.151007845639</v>
+      </c>
+    </row>
+    <row r="520" spans="1:2">
+      <c r="A520" t="s">
+        <v>520</v>
+      </c>
+      <c r="B520" s="1">
+        <v>112.1400307365866</v>
+      </c>
+    </row>
+    <row r="521" spans="1:2">
+      <c r="A521" t="s">
+        <v>521</v>
+      </c>
+      <c r="B521" s="1">
+        <v>112.1231577583219</v>
+      </c>
+    </row>
+    <row r="522" spans="1:2">
+      <c r="A522" t="s">
+        <v>522</v>
+      </c>
+      <c r="B522" s="1">
+        <v>112.1159660867538</v>
+      </c>
+    </row>
+    <row r="523" spans="1:2">
+      <c r="A523" t="s">
+        <v>523</v>
+      </c>
+      <c r="B523" s="1">
+        <v>112.1075663935174</v>
+      </c>
+    </row>
+    <row r="524" spans="1:2">
+      <c r="A524" t="s">
+        <v>524</v>
+      </c>
+      <c r="B524" s="1">
+        <v>112.0916182087307</v>
+      </c>
+    </row>
+    <row r="525" spans="1:2">
+      <c r="A525" t="s">
+        <v>525</v>
+      </c>
+      <c r="B525" s="1">
+        <v>112.0859414808525</v>
+      </c>
+    </row>
+    <row r="526" spans="1:2">
+      <c r="A526" t="s">
+        <v>526</v>
+      </c>
+      <c r="B526" s="1">
+        <v>112.0857921883568</v>
+      </c>
+    </row>
+    <row r="527" spans="1:2">
+      <c r="A527" t="s">
+        <v>527</v>
+      </c>
+      <c r="B527" s="1">
+        <v>112.0639360530455</v>
+      </c>
+    </row>
+    <row r="528" spans="1:2">
+      <c r="A528" t="s">
+        <v>528</v>
+      </c>
+      <c r="B528" s="1">
+        <v>112.0487402527189</v>
+      </c>
+    </row>
+    <row r="529" spans="1:2">
+      <c r="A529" t="s">
+        <v>529</v>
+      </c>
+      <c r="B529" s="1">
+        <v>112.0338054732013</v>
+      </c>
+    </row>
+    <row r="530" spans="1:2">
+      <c r="A530" t="s">
+        <v>530</v>
+      </c>
+      <c r="B530" s="1">
+        <v>112.0129983093677</v>
+      </c>
+    </row>
+    <row r="531" spans="1:2">
+      <c r="A531" t="s">
+        <v>531</v>
+      </c>
+      <c r="B531" s="1">
+        <v>112.0120802922825</v>
+      </c>
+    </row>
+    <row r="532" spans="1:2">
+      <c r="A532" t="s">
+        <v>532</v>
+      </c>
+      <c r="B532" s="1">
+        <v>111.9887384956194</v>
+      </c>
+    </row>
+    <row r="533" spans="1:2">
+      <c r="A533" t="s">
+        <v>533</v>
+      </c>
+      <c r="B533" s="1">
+        <v>111.9768466742044</v>
+      </c>
+    </row>
+    <row r="534" spans="1:2">
+      <c r="A534" t="s">
+        <v>534</v>
+      </c>
+      <c r="B534" s="1">
+        <v>111.9405716498297</v>
+      </c>
+    </row>
+    <row r="535" spans="1:2">
+      <c r="A535" t="s">
+        <v>535</v>
+      </c>
+      <c r="B535" s="1">
+        <v>111.9383827548657</v>
+      </c>
+    </row>
+    <row r="536" spans="1:2">
+      <c r="A536" t="s">
+        <v>536</v>
+      </c>
+      <c r="B536" s="1">
+        <v>111.9379956983257</v>
+      </c>
+    </row>
+    <row r="537" spans="1:2">
+      <c r="A537" t="s">
+        <v>537</v>
+      </c>
+      <c r="B537" s="1">
+        <v>111.8896866897012</v>
+      </c>
+    </row>
+    <row r="538" spans="1:2">
+      <c r="A538" t="s">
+        <v>538</v>
+      </c>
+      <c r="B538" s="1">
+        <v>111.8876585641403</v>
+      </c>
+    </row>
+    <row r="539" spans="1:2">
+      <c r="A539" t="s">
+        <v>539</v>
+      </c>
+      <c r="B539" s="1">
+        <v>111.8644334666559</v>
+      </c>
+    </row>
+    <row r="540" spans="1:2">
+      <c r="A540" t="s">
+        <v>540</v>
+      </c>
+      <c r="B540" s="1">
+        <v>111.8624781635913</v>
+      </c>
+    </row>
+    <row r="541" spans="1:2">
+      <c r="A541" t="s">
+        <v>541</v>
+      </c>
+      <c r="B541" s="1">
+        <v>111.8588283523896</v>
+      </c>
+    </row>
+    <row r="542" spans="1:2">
+      <c r="A542" t="s">
+        <v>542</v>
+      </c>
+      <c r="B542" s="1">
+        <v>111.8583970122966</v>
+      </c>
+    </row>
+    <row r="543" spans="1:2">
+      <c r="A543" t="s">
+        <v>543</v>
+      </c>
+      <c r="B543" s="1">
+        <v>111.8531439135014</v>
+      </c>
+    </row>
+    <row r="544" spans="1:2">
+      <c r="A544" t="s">
+        <v>544</v>
+      </c>
+      <c r="B544" s="1">
+        <v>111.8492675928691</v>
+      </c>
+    </row>
+    <row r="545" spans="1:2">
+      <c r="A545" t="s">
+        <v>545</v>
+      </c>
+      <c r="B545" s="1">
+        <v>111.842918847942</v>
+      </c>
+    </row>
+    <row r="546" spans="1:2">
+      <c r="A546" t="s">
+        <v>546</v>
+      </c>
+      <c r="B546" s="1">
+        <v>111.8376019824431</v>
+      </c>
+    </row>
+    <row r="547" spans="1:2">
+      <c r="A547" t="s">
+        <v>547</v>
+      </c>
+      <c r="B547" s="1">
+        <v>111.8213091379004</v>
+      </c>
+    </row>
+    <row r="548" spans="1:2">
+      <c r="A548" t="s">
+        <v>548</v>
+      </c>
+      <c r="B548" s="1">
+        <v>111.7879643968557</v>
+      </c>
+    </row>
+    <row r="549" spans="1:2">
+      <c r="A549" t="s">
+        <v>549</v>
+      </c>
+      <c r="B549" s="1">
+        <v>111.7820122831688</v>
+      </c>
+    </row>
+    <row r="550" spans="1:2">
+      <c r="A550" t="s">
+        <v>550</v>
+      </c>
+      <c r="B550" s="1">
+        <v>111.7549387363908</v>
+      </c>
+    </row>
+    <row r="551" spans="1:2">
+      <c r="A551" t="s">
+        <v>551</v>
+      </c>
+      <c r="B551" s="1">
+        <v>111.7468591690584</v>
+      </c>
+    </row>
+    <row r="552" spans="1:2">
+      <c r="A552" t="s">
+        <v>552</v>
+      </c>
+      <c r="B552" s="1">
+        <v>111.7464032445951</v>
+      </c>
+    </row>
+    <row r="553" spans="1:2">
+      <c r="A553" t="s">
+        <v>553</v>
+      </c>
+      <c r="B553" s="1">
+        <v>111.7458994862061</v>
+      </c>
+    </row>
+    <row r="554" spans="1:2">
+      <c r="A554" t="s">
+        <v>554</v>
+      </c>
+      <c r="B554" s="1">
+        <v>111.7344277327426</v>
+      </c>
+    </row>
+    <row r="555" spans="1:2">
+      <c r="A555" t="s">
+        <v>555</v>
+      </c>
+      <c r="B555" s="1">
+        <v>111.7258374986156</v>
+      </c>
+    </row>
+    <row r="556" spans="1:2">
+      <c r="A556" t="s">
+        <v>556</v>
+      </c>
+      <c r="B556" s="1">
+        <v>111.7247420473168</v>
+      </c>
+    </row>
+    <row r="557" spans="1:2">
+      <c r="A557" t="s">
+        <v>557</v>
+      </c>
+      <c r="B557" s="1">
+        <v>111.7156936946952</v>
+      </c>
+    </row>
+    <row r="558" spans="1:2">
+      <c r="A558" t="s">
+        <v>558</v>
+      </c>
+      <c r="B558" s="1">
+        <v>111.7107901600618</v>
+      </c>
+    </row>
+    <row r="559" spans="1:2">
+      <c r="A559" t="s">
+        <v>559</v>
+      </c>
+      <c r="B559" s="1">
+        <v>111.6978440465134</v>
+      </c>
+    </row>
+    <row r="560" spans="1:2">
+      <c r="A560" t="s">
+        <v>560</v>
+      </c>
+      <c r="B560" s="1">
+        <v>111.6815605730602</v>
+      </c>
+    </row>
+    <row r="561" spans="1:2">
+      <c r="A561" t="s">
+        <v>561</v>
+      </c>
+      <c r="B561" s="1">
+        <v>111.6794838359491</v>
+      </c>
+    </row>
+    <row r="562" spans="1:2">
+      <c r="A562" t="s">
+        <v>562</v>
+      </c>
+      <c r="B562" s="1">
+        <v>111.6695845014629</v>
+      </c>
+    </row>
+    <row r="563" spans="1:2">
+      <c r="A563" t="s">
+        <v>563</v>
+      </c>
+      <c r="B563" s="1">
+        <v>111.6680930072997</v>
+      </c>
+    </row>
+    <row r="564" spans="1:2">
+      <c r="A564" t="s">
+        <v>564</v>
+      </c>
+      <c r="B564" s="1">
+        <v>111.6132855159198</v>
+      </c>
+    </row>
+    <row r="565" spans="1:2">
+      <c r="A565" t="s">
+        <v>565</v>
+      </c>
+      <c r="B565" s="1">
+        <v>111.6085888827632</v>
+      </c>
+    </row>
+    <row r="566" spans="1:2">
+      <c r="A566" t="s">
+        <v>566</v>
+      </c>
+      <c r="B566" s="1">
+        <v>111.6048342095179</v>
+      </c>
+    </row>
+    <row r="567" spans="1:2">
+      <c r="A567" t="s">
+        <v>567</v>
+      </c>
+      <c r="B567" s="1">
+        <v>111.5867564952678</v>
+      </c>
+    </row>
+    <row r="568" spans="1:2">
+      <c r="A568" t="s">
+        <v>568</v>
+      </c>
+      <c r="B568" s="1">
+        <v>111.5697791467819</v>
+      </c>
+    </row>
+    <row r="569" spans="1:2">
+      <c r="A569" t="s">
+        <v>569</v>
+      </c>
+      <c r="B569" s="1">
+        <v>111.5630895914407</v>
+      </c>
+    </row>
+    <row r="570" spans="1:2">
+      <c r="A570" t="s">
+        <v>570</v>
+      </c>
+      <c r="B570" s="1">
+        <v>111.53964546044</v>
+      </c>
+    </row>
+    <row r="571" spans="1:2">
+      <c r="A571" t="s">
+        <v>571</v>
+      </c>
+      <c r="B571" s="1">
+        <v>111.5126514028708</v>
+      </c>
+    </row>
+    <row r="572" spans="1:2">
+      <c r="A572" t="s">
+        <v>572</v>
+      </c>
+      <c r="B572" s="1">
+        <v>111.5051475720309</v>
+      </c>
+    </row>
+    <row r="573" spans="1:2">
+      <c r="A573" t="s">
+        <v>573</v>
+      </c>
+      <c r="B573" s="1">
+        <v>111.5033900370135</v>
+      </c>
+    </row>
+    <row r="574" spans="1:2">
+      <c r="A574" t="s">
+        <v>574</v>
+      </c>
+      <c r="B574" s="1">
+        <v>111.4957660784898</v>
+      </c>
+    </row>
+    <row r="575" spans="1:2">
+      <c r="A575" t="s">
+        <v>575</v>
+      </c>
+      <c r="B575" s="1">
+        <v>111.4924405476545</v>
+      </c>
+    </row>
+    <row r="576" spans="1:2">
+      <c r="A576" t="s">
+        <v>576</v>
+      </c>
+      <c r="B576" s="1">
+        <v>111.4824182189503</v>
+      </c>
+    </row>
+    <row r="577" spans="1:2">
+      <c r="A577" t="s">
+        <v>577</v>
+      </c>
+      <c r="B577" s="1">
+        <v>111.4644898205769</v>
+      </c>
+    </row>
+    <row r="578" spans="1:2">
+      <c r="A578" t="s">
+        <v>578</v>
+      </c>
+      <c r="B578" s="1">
+        <v>111.441025031537</v>
+      </c>
+    </row>
+    <row r="579" spans="1:2">
+      <c r="A579" t="s">
+        <v>579</v>
+      </c>
+      <c r="B579" s="1">
+        <v>111.4347458404243</v>
+      </c>
+    </row>
+    <row r="580" spans="1:2">
+      <c r="A580" t="s">
+        <v>580</v>
+      </c>
+      <c r="B580" s="1">
+        <v>111.3755379643997</v>
+      </c>
+    </row>
+    <row r="581" spans="1:2">
+      <c r="A581" t="s">
+        <v>581</v>
+      </c>
+      <c r="B581" s="1">
+        <v>111.3492087601791</v>
+      </c>
+    </row>
+    <row r="582" spans="1:2">
+      <c r="A582" t="s">
+        <v>582</v>
+      </c>
+      <c r="B582" s="1">
+        <v>111.3450038941153</v>
+      </c>
+    </row>
+    <row r="583" spans="1:2">
+      <c r="A583" t="s">
+        <v>583</v>
+      </c>
+      <c r="B583" s="1">
+        <v>111.3392799616006</v>
+      </c>
+    </row>
+    <row r="584" spans="1:2">
+      <c r="A584" t="s">
+        <v>584</v>
+      </c>
+      <c r="B584" s="1">
+        <v>111.2910293602445</v>
+      </c>
+    </row>
+    <row r="585" spans="1:2">
+      <c r="A585" t="s">
+        <v>585</v>
+      </c>
+      <c r="B585" s="1">
+        <v>111.2748536308625</v>
+      </c>
+    </row>
+    <row r="586" spans="1:2">
+      <c r="A586" t="s">
+        <v>586</v>
+      </c>
+      <c r="B586" s="1">
+        <v>111.2505282725821</v>
+      </c>
+    </row>
+    <row r="587" spans="1:2">
+      <c r="A587" t="s">
+        <v>587</v>
+      </c>
+      <c r="B587" s="1">
+        <v>111.2423250627122</v>
       </c>
     </row>
   </sheetData>

--- a/Screener/data/rs_rating_top_30.xlsx
+++ b/Screener/data/rs_rating_top_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="585">
   <si>
     <t>Symbol</t>
   </si>
@@ -31,1753 +31,1744 @@
     <t>AAOI</t>
   </si>
   <si>
+    <t>SGTX</t>
+  </si>
+  <si>
+    <t>CDLX</t>
+  </si>
+  <si>
+    <t>TSAT</t>
+  </si>
+  <si>
+    <t>USM</t>
+  </si>
+  <si>
     <t>TDS</t>
   </si>
   <si>
-    <t>USM</t>
-  </si>
-  <si>
-    <t>SGTX</t>
-  </si>
-  <si>
-    <t>CDLX</t>
-  </si>
-  <si>
-    <t>TSAT</t>
-  </si>
-  <si>
     <t>ADTX</t>
   </si>
   <si>
+    <t>CVNA</t>
+  </si>
+  <si>
+    <t>ML</t>
+  </si>
+  <si>
+    <t>DLO</t>
+  </si>
+  <si>
+    <t>ACMR</t>
+  </si>
+  <si>
+    <t>OLMA</t>
+  </si>
+  <si>
+    <t>CAMT</t>
+  </si>
+  <si>
+    <t>ANF</t>
+  </si>
+  <si>
+    <t>PHVS</t>
+  </si>
+  <si>
+    <t>APP</t>
+  </si>
+  <si>
+    <t>LEU</t>
+  </si>
+  <si>
+    <t>VRT</t>
+  </si>
+  <si>
+    <t>BBIO</t>
+  </si>
+  <si>
+    <t>PAY</t>
+  </si>
+  <si>
+    <t>BOOM</t>
+  </si>
+  <si>
+    <t>CPRI</t>
+  </si>
+  <si>
+    <t>ESTE</t>
+  </si>
+  <si>
+    <t>XPEV</t>
+  </si>
+  <si>
+    <t>MNSO</t>
+  </si>
+  <si>
+    <t>CLS</t>
+  </si>
+  <si>
+    <t>STRL</t>
+  </si>
+  <si>
+    <t>RETA</t>
+  </si>
+  <si>
+    <t>LMB</t>
+  </si>
+  <si>
+    <t>MNBP</t>
+  </si>
+  <si>
+    <t>UPWK</t>
+  </si>
+  <si>
+    <t>CEIX</t>
+  </si>
+  <si>
+    <t>SBOW</t>
+  </si>
+  <si>
+    <t>KRT</t>
+  </si>
+  <si>
+    <t>CSPI</t>
+  </si>
+  <si>
+    <t>URGN</t>
+  </si>
+  <si>
+    <t>AFRM</t>
+  </si>
+  <si>
+    <t>GENTF</t>
+  </si>
+  <si>
+    <t>CELH</t>
+  </si>
+  <si>
+    <t>SRDX</t>
+  </si>
+  <si>
+    <t>AEO</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>FUTU</t>
+  </si>
+  <si>
+    <t>BWMX</t>
+  </si>
+  <si>
+    <t>IONQ</t>
+  </si>
+  <si>
+    <t>VNO</t>
+  </si>
+  <si>
     <t>UPTDU</t>
   </si>
   <si>
-    <t>CVNA</t>
+    <t>X</t>
+  </si>
+  <si>
+    <t>VRTV</t>
+  </si>
+  <si>
+    <t>FSLY</t>
+  </si>
+  <si>
+    <t>WHD</t>
+  </si>
+  <si>
+    <t>IOT</t>
+  </si>
+  <si>
+    <t>MOD</t>
+  </si>
+  <si>
+    <t>DELL</t>
+  </si>
+  <si>
+    <t>RYTM</t>
+  </si>
+  <si>
+    <t>VIEW</t>
+  </si>
+  <si>
+    <t>CWCO</t>
+  </si>
+  <si>
+    <t>MMYT</t>
+  </si>
+  <si>
+    <t>GHM</t>
+  </si>
+  <si>
+    <t>AMR</t>
+  </si>
+  <si>
+    <t>PAR</t>
+  </si>
+  <si>
+    <t>PARR</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>SLG</t>
+  </si>
+  <si>
+    <t>PDD</t>
+  </si>
+  <si>
+    <t>SM</t>
+  </si>
+  <si>
+    <t>GCO</t>
+  </si>
+  <si>
+    <t>LYTS</t>
+  </si>
+  <si>
+    <t>WFRD</t>
+  </si>
+  <si>
+    <t>IESC</t>
+  </si>
+  <si>
+    <t>GAMB</t>
+  </si>
+  <si>
+    <t>KD</t>
+  </si>
+  <si>
+    <t>SENEB</t>
+  </si>
+  <si>
+    <t>YETI</t>
+  </si>
+  <si>
+    <t>COUR</t>
+  </si>
+  <si>
+    <t>FN</t>
+  </si>
+  <si>
+    <t>UBS</t>
+  </si>
+  <si>
+    <t>ESEA</t>
+  </si>
+  <si>
+    <t>NATR</t>
+  </si>
+  <si>
+    <t>RELY</t>
+  </si>
+  <si>
+    <t>FSTR</t>
+  </si>
+  <si>
+    <t>OBT</t>
+  </si>
+  <si>
+    <t>PDS</t>
+  </si>
+  <si>
+    <t>OII</t>
+  </si>
+  <si>
+    <t>NXGN</t>
+  </si>
+  <si>
+    <t>PSFE</t>
+  </si>
+  <si>
+    <t>HWKN</t>
+  </si>
+  <si>
+    <t>KDNY</t>
+  </si>
+  <si>
+    <t>INSM</t>
+  </si>
+  <si>
+    <t>HBB</t>
+  </si>
+  <si>
+    <t>CIR</t>
+  </si>
+  <si>
+    <t>TRNS</t>
+  </si>
+  <si>
+    <t>IDYA</t>
+  </si>
+  <si>
+    <t>CBAY</t>
+  </si>
+  <si>
+    <t>HOV</t>
+  </si>
+  <si>
+    <t>GTLS</t>
+  </si>
+  <si>
+    <t>FRSH</t>
+  </si>
+  <si>
+    <t>APA</t>
+  </si>
+  <si>
+    <t>NOV</t>
   </si>
   <si>
     <t>UPTD</t>
   </si>
   <si>
-    <t>ML</t>
-  </si>
-  <si>
-    <t>DLO</t>
-  </si>
-  <si>
-    <t>CAMT</t>
-  </si>
-  <si>
-    <t>PHVS</t>
-  </si>
-  <si>
-    <t>APP</t>
-  </si>
-  <si>
-    <t>BBIO</t>
-  </si>
-  <si>
-    <t>VRT</t>
-  </si>
-  <si>
-    <t>ACMR</t>
-  </si>
-  <si>
-    <t>ANF</t>
-  </si>
-  <si>
-    <t>LEU</t>
-  </si>
-  <si>
-    <t>STRL</t>
-  </si>
-  <si>
-    <t>LMB</t>
-  </si>
-  <si>
-    <t>XPEV</t>
-  </si>
-  <si>
-    <t>PAY</t>
-  </si>
-  <si>
-    <t>CLS</t>
-  </si>
-  <si>
-    <t>ESTE</t>
-  </si>
-  <si>
-    <t>CPRI</t>
-  </si>
-  <si>
-    <t>RYTM</t>
-  </si>
-  <si>
-    <t>MNSO</t>
-  </si>
-  <si>
-    <t>KRT</t>
-  </si>
-  <si>
-    <t>RETA</t>
-  </si>
-  <si>
-    <t>UPWK</t>
-  </si>
-  <si>
-    <t>URGN</t>
-  </si>
-  <si>
-    <t>SBOW</t>
-  </si>
-  <si>
-    <t>MNBP</t>
-  </si>
-  <si>
-    <t>BOOM</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>MOD</t>
-  </si>
-  <si>
-    <t>AEO</t>
-  </si>
-  <si>
-    <t>CEIX</t>
-  </si>
-  <si>
-    <t>FUTU</t>
-  </si>
-  <si>
-    <t>IESC</t>
-  </si>
-  <si>
-    <t>GCO</t>
-  </si>
-  <si>
-    <t>GENTF</t>
-  </si>
-  <si>
-    <t>CELH</t>
-  </si>
-  <si>
-    <t>SRDX</t>
+    <t>JXN</t>
+  </si>
+  <si>
+    <t>BRZE</t>
+  </si>
+  <si>
+    <t>DICE</t>
+  </si>
+  <si>
+    <t>CORT</t>
+  </si>
+  <si>
+    <t>HRB</t>
+  </si>
+  <si>
+    <t>XPO</t>
+  </si>
+  <si>
+    <t>POWL</t>
+  </si>
+  <si>
+    <t>LBRT</t>
+  </si>
+  <si>
+    <t>LLY</t>
+  </si>
+  <si>
+    <t>FTI</t>
+  </si>
+  <si>
+    <t>ARRY</t>
+  </si>
+  <si>
+    <t>TPL</t>
+  </si>
+  <si>
+    <t>CKX</t>
+  </si>
+  <si>
+    <t>HDSN</t>
+  </si>
+  <si>
+    <t>ODC</t>
+  </si>
+  <si>
+    <t>WAL</t>
+  </si>
+  <si>
+    <t>ITRN</t>
+  </si>
+  <si>
+    <t>CTRN</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>CRC</t>
+  </si>
+  <si>
+    <t>LBRDB</t>
+  </si>
+  <si>
+    <t>NBR</t>
+  </si>
+  <si>
+    <t>WMG</t>
+  </si>
+  <si>
+    <t>MTDR</t>
+  </si>
+  <si>
+    <t>EDU</t>
+  </si>
+  <si>
+    <t>MPC</t>
+  </si>
+  <si>
+    <t>TDW</t>
+  </si>
+  <si>
+    <t>CAL</t>
+  </si>
+  <si>
+    <t>ANIP</t>
+  </si>
+  <si>
+    <t>SMHI</t>
+  </si>
+  <si>
+    <t>PLCE</t>
+  </si>
+  <si>
+    <t>XPRO</t>
+  </si>
+  <si>
+    <t>BFST</t>
   </si>
   <si>
     <t>PRDO</t>
   </si>
   <si>
-    <t>BWMX</t>
-  </si>
-  <si>
-    <t>AMR</t>
-  </si>
-  <si>
-    <t>FSLY</t>
-  </si>
-  <si>
-    <t>PDD</t>
-  </si>
-  <si>
-    <t>VNO</t>
-  </si>
-  <si>
-    <t>VIEW</t>
+    <t>CNX</t>
+  </si>
+  <si>
+    <t>TWIN</t>
+  </si>
+  <si>
+    <t>STEP</t>
+  </si>
+  <si>
+    <t>AURC</t>
+  </si>
+  <si>
+    <t>CVI</t>
+  </si>
+  <si>
+    <t>SAIA</t>
+  </si>
+  <si>
+    <t>PBF</t>
+  </si>
+  <si>
+    <t>SENEA</t>
+  </si>
+  <si>
+    <t>VST</t>
+  </si>
+  <si>
+    <t>MTSI</t>
+  </si>
+  <si>
+    <t>ARGX</t>
+  </si>
+  <si>
+    <t>RH</t>
+  </si>
+  <si>
+    <t>ARCH</t>
+  </si>
+  <si>
+    <t>KEQU</t>
+  </si>
+  <si>
+    <t>RVMD</t>
+  </si>
+  <si>
+    <t>GIC</t>
+  </si>
+  <si>
+    <t>NVO</t>
+  </si>
+  <si>
+    <t>INBK</t>
+  </si>
+  <si>
+    <t>PLUS</t>
+  </si>
+  <si>
+    <t>CLMT</t>
+  </si>
+  <si>
+    <t>AEHR</t>
+  </si>
+  <si>
+    <t>PETQ</t>
+  </si>
+  <si>
+    <t>IPI</t>
+  </si>
+  <si>
+    <t>RNGR</t>
+  </si>
+  <si>
+    <t>SOVO</t>
+  </si>
+  <si>
+    <t>FTAI</t>
+  </si>
+  <si>
+    <t>TWST</t>
+  </si>
+  <si>
+    <t>BKI</t>
+  </si>
+  <si>
+    <t>LEAT</t>
+  </si>
+  <si>
+    <t>ROKU</t>
+  </si>
+  <si>
+    <t>OKTA</t>
+  </si>
+  <si>
+    <t>ELAN</t>
+  </si>
+  <si>
+    <t>FRHC</t>
+  </si>
+  <si>
+    <t>HEP</t>
+  </si>
+  <si>
+    <t>AROC</t>
+  </si>
+  <si>
+    <t>QTRX</t>
+  </si>
+  <si>
+    <t>PRA</t>
+  </si>
+  <si>
+    <t>APPF</t>
+  </si>
+  <si>
+    <t>GES</t>
   </si>
   <si>
     <t>NTRA</t>
   </si>
   <si>
-    <t>VRTV</t>
-  </si>
-  <si>
-    <t>SM</t>
-  </si>
-  <si>
-    <t>AFRM</t>
+    <t>AMNB</t>
+  </si>
+  <si>
+    <t>CVBF</t>
+  </si>
+  <si>
+    <t>ONTO</t>
+  </si>
+  <si>
+    <t>INTU</t>
+  </si>
+  <si>
+    <t>BBW</t>
+  </si>
+  <si>
+    <t>NTNX</t>
+  </si>
+  <si>
+    <t>SPLK</t>
+  </si>
+  <si>
+    <t>WLDN</t>
+  </si>
+  <si>
+    <t>RIVN</t>
+  </si>
+  <si>
+    <t>VET</t>
+  </si>
+  <si>
+    <t>GPOR</t>
+  </si>
+  <si>
+    <t>EH</t>
+  </si>
+  <si>
+    <t>ERIE</t>
+  </si>
+  <si>
+    <t>NOG</t>
+  </si>
+  <si>
+    <t>FLR</t>
+  </si>
+  <si>
+    <t>TALO</t>
+  </si>
+  <si>
+    <t>KRC</t>
+  </si>
+  <si>
+    <t>CHX</t>
+  </si>
+  <si>
+    <t>HNI</t>
+  </si>
+  <si>
+    <t>SMMF</t>
+  </si>
+  <si>
+    <t>OVV</t>
+  </si>
+  <si>
+    <t>CIVI</t>
+  </si>
+  <si>
+    <t>MUR</t>
+  </si>
+  <si>
+    <t>PBR</t>
+  </si>
+  <si>
+    <t>IIPR</t>
+  </si>
+  <si>
+    <t>DWAC</t>
+  </si>
+  <si>
+    <t>HAL</t>
+  </si>
+  <si>
+    <t>SLB</t>
+  </si>
+  <si>
+    <t>PTEN</t>
+  </si>
+  <si>
+    <t>PESI</t>
+  </si>
+  <si>
+    <t>NRP</t>
+  </si>
+  <si>
+    <t>DBRG</t>
+  </si>
+  <si>
+    <t>OLLI</t>
+  </si>
+  <si>
+    <t>EVI</t>
+  </si>
+  <si>
+    <t>AZTA</t>
+  </si>
+  <si>
+    <t>AZEK</t>
+  </si>
+  <si>
+    <t>TH</t>
+  </si>
+  <si>
+    <t>BCC</t>
+  </si>
+  <si>
+    <t>QCRH</t>
+  </si>
+  <si>
+    <t>TW</t>
+  </si>
+  <si>
+    <t>CPE</t>
+  </si>
+  <si>
+    <t>CTLT</t>
+  </si>
+  <si>
+    <t>NE</t>
+  </si>
+  <si>
+    <t>FETM</t>
+  </si>
+  <si>
+    <t>CF</t>
+  </si>
+  <si>
+    <t>NOA</t>
+  </si>
+  <si>
+    <t>CCJ</t>
+  </si>
+  <si>
+    <t>BR</t>
+  </si>
+  <si>
+    <t>SU</t>
+  </si>
+  <si>
+    <t>ENLC</t>
+  </si>
+  <si>
+    <t>CMT</t>
+  </si>
+  <si>
+    <t>PSX</t>
+  </si>
+  <si>
+    <t>ZION</t>
+  </si>
+  <si>
+    <t>ADBE</t>
+  </si>
+  <si>
+    <t>CABA</t>
+  </si>
+  <si>
+    <t>CRS</t>
+  </si>
+  <si>
+    <t>WMPN</t>
+  </si>
+  <si>
+    <t>BOH</t>
+  </si>
+  <si>
+    <t>HPK</t>
+  </si>
+  <si>
+    <t>EME</t>
+  </si>
+  <si>
+    <t>CDRE</t>
+  </si>
+  <si>
+    <t>ARVN</t>
+  </si>
+  <si>
+    <t>HOFT</t>
+  </si>
+  <si>
+    <t>SFBS</t>
+  </si>
+  <si>
+    <t>DCBO</t>
+  </si>
+  <si>
+    <t>MLKN</t>
+  </si>
+  <si>
+    <t>CXM</t>
+  </si>
+  <si>
+    <t>TIPT</t>
+  </si>
+  <si>
+    <t>ELF</t>
+  </si>
+  <si>
+    <t>CAAP</t>
+  </si>
+  <si>
+    <t>ANET</t>
+  </si>
+  <si>
+    <t>HAS</t>
+  </si>
+  <si>
+    <t>BKR</t>
+  </si>
+  <si>
+    <t>ROCK</t>
+  </si>
+  <si>
+    <t>YELP</t>
+  </si>
+  <si>
+    <t>COP</t>
+  </si>
+  <si>
+    <t>HP</t>
+  </si>
+  <si>
+    <t>AZZ</t>
+  </si>
+  <si>
+    <t>FORG</t>
+  </si>
+  <si>
+    <t>MORN</t>
+  </si>
+  <si>
+    <t>NFE</t>
+  </si>
+  <si>
+    <t>ODFL</t>
+  </si>
+  <si>
+    <t>BXP</t>
+  </si>
+  <si>
+    <t>VRNS</t>
+  </si>
+  <si>
+    <t>CAT</t>
+  </si>
+  <si>
+    <t>APO</t>
+  </si>
+  <si>
+    <t>BHWB</t>
+  </si>
+  <si>
+    <t>GPN</t>
+  </si>
+  <si>
+    <t>SPT</t>
+  </si>
+  <si>
+    <t>PRIM</t>
+  </si>
+  <si>
+    <t>SCPL</t>
+  </si>
+  <si>
+    <t>NCR</t>
+  </si>
+  <si>
+    <t>ETN</t>
+  </si>
+  <si>
+    <t>ALRM</t>
+  </si>
+  <si>
+    <t>SKYW</t>
+  </si>
+  <si>
+    <t>BCSF</t>
+  </si>
+  <si>
+    <t>OSK</t>
+  </si>
+  <si>
+    <t>ERF</t>
+  </si>
+  <si>
+    <t>BRC</t>
+  </si>
+  <si>
+    <t>TFII</t>
+  </si>
+  <si>
+    <t>BMA</t>
+  </si>
+  <si>
+    <t>SAH</t>
+  </si>
+  <si>
+    <t>RAMP</t>
+  </si>
+  <si>
+    <t>DCOM</t>
+  </si>
+  <si>
+    <t>JILL</t>
+  </si>
+  <si>
+    <t>AURCU</t>
+  </si>
+  <si>
+    <t>TRUP</t>
+  </si>
+  <si>
+    <t>HLNE</t>
+  </si>
+  <si>
+    <t>STER</t>
+  </si>
+  <si>
+    <t>DLR</t>
+  </si>
+  <si>
+    <t>NEWR</t>
+  </si>
+  <si>
+    <t>PSN</t>
+  </si>
+  <si>
+    <t>FNF</t>
+  </si>
+  <si>
+    <t>GRC</t>
+  </si>
+  <si>
+    <t>AR</t>
+  </si>
+  <si>
+    <t>BRP</t>
+  </si>
+  <si>
+    <t>HCCI</t>
+  </si>
+  <si>
+    <t>IMO</t>
+  </si>
+  <si>
+    <t>FUNC</t>
+  </si>
+  <si>
+    <t>CWAN</t>
+  </si>
+  <si>
+    <t>LII</t>
+  </si>
+  <si>
+    <t>GLOB</t>
+  </si>
+  <si>
+    <t>TWNK</t>
+  </si>
+  <si>
+    <t>MAT</t>
+  </si>
+  <si>
+    <t>LOB</t>
+  </si>
+  <si>
+    <t>BX</t>
+  </si>
+  <si>
+    <t>DK</t>
+  </si>
+  <si>
+    <t>AMPL</t>
+  </si>
+  <si>
+    <t>CVRX</t>
+  </si>
+  <si>
+    <t>NCNO</t>
+  </si>
+  <si>
+    <t>CARR</t>
+  </si>
+  <si>
+    <t>DRQ</t>
+  </si>
+  <si>
+    <t>CCOI</t>
+  </si>
+  <si>
+    <t>XRX</t>
+  </si>
+  <si>
+    <t>CDW</t>
+  </si>
+  <si>
+    <t>WIX</t>
+  </si>
+  <si>
+    <t>NTIC</t>
+  </si>
+  <si>
+    <t>CVE</t>
+  </si>
+  <si>
+    <t>BNTX</t>
+  </si>
+  <si>
+    <t>TRGP</t>
+  </si>
+  <si>
+    <t>NVDA</t>
+  </si>
+  <si>
+    <t>DMRC</t>
+  </si>
+  <si>
+    <t>VLO</t>
+  </si>
+  <si>
+    <t>AIT</t>
+  </si>
+  <si>
+    <t>WOR</t>
+  </si>
+  <si>
+    <t>CALB</t>
+  </si>
+  <si>
+    <t>QLYS</t>
+  </si>
+  <si>
+    <t>URI</t>
+  </si>
+  <si>
+    <t>CQP</t>
+  </si>
+  <si>
+    <t>NBIX</t>
+  </si>
+  <si>
+    <t>HZNP</t>
+  </si>
+  <si>
+    <t>CNQ</t>
   </si>
   <si>
     <t>DFH</t>
   </si>
   <si>
-    <t>WHD</t>
-  </si>
-  <si>
-    <t>MMYT</t>
-  </si>
-  <si>
-    <t>PARR</t>
-  </si>
-  <si>
-    <t>DELL</t>
-  </si>
-  <si>
-    <t>TPL</t>
-  </si>
-  <si>
-    <t>HOV</t>
-  </si>
-  <si>
-    <t>KD</t>
-  </si>
-  <si>
-    <t>SLG</t>
-  </si>
-  <si>
-    <t>CWCO</t>
-  </si>
-  <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>IDYA</t>
-  </si>
-  <si>
-    <t>ESEA</t>
-  </si>
-  <si>
-    <t>FN</t>
-  </si>
-  <si>
-    <t>CAL</t>
-  </si>
-  <si>
-    <t>WFRD</t>
-  </si>
-  <si>
-    <t>XPO</t>
-  </si>
-  <si>
-    <t>WLDN</t>
-  </si>
-  <si>
-    <t>PDS</t>
-  </si>
-  <si>
-    <t>EDU</t>
-  </si>
-  <si>
-    <t>YETI</t>
-  </si>
-  <si>
-    <t>HWKN</t>
-  </si>
-  <si>
-    <t>PAR</t>
-  </si>
-  <si>
-    <t>SENEB</t>
-  </si>
-  <si>
-    <t>ODC</t>
-  </si>
-  <si>
-    <t>EH</t>
-  </si>
-  <si>
-    <t>PETQ</t>
-  </si>
-  <si>
-    <t>CBAY</t>
-  </si>
-  <si>
-    <t>CORT</t>
-  </si>
-  <si>
-    <t>PSFE</t>
-  </si>
-  <si>
-    <t>OII</t>
-  </si>
-  <si>
-    <t>GAMB</t>
-  </si>
-  <si>
-    <t>LYTS</t>
-  </si>
-  <si>
-    <t>UBS</t>
-  </si>
-  <si>
-    <t>CTRN</t>
-  </si>
-  <si>
-    <t>NATR</t>
-  </si>
-  <si>
-    <t>NOV</t>
-  </si>
-  <si>
-    <t>CSPI</t>
-  </si>
-  <si>
-    <t>ANIP</t>
-  </si>
-  <si>
-    <t>IOT</t>
-  </si>
-  <si>
-    <t>RELY</t>
-  </si>
-  <si>
-    <t>OBT</t>
-  </si>
-  <si>
-    <t>GTLS</t>
-  </si>
-  <si>
-    <t>TWST</t>
-  </si>
-  <si>
-    <t>IPI</t>
-  </si>
-  <si>
-    <t>CRC</t>
-  </si>
-  <si>
-    <t>KDNY</t>
-  </si>
-  <si>
-    <t>POWL</t>
-  </si>
-  <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>CIR</t>
-  </si>
-  <si>
-    <t>JXN</t>
-  </si>
-  <si>
-    <t>FSTR</t>
-  </si>
-  <si>
-    <t>CMT</t>
-  </si>
-  <si>
-    <t>QTRX</t>
-  </si>
-  <si>
-    <t>SENEA</t>
-  </si>
-  <si>
-    <t>MTDR</t>
-  </si>
-  <si>
-    <t>WAL</t>
-  </si>
-  <si>
-    <t>SAIA</t>
-  </si>
-  <si>
-    <t>APA</t>
-  </si>
-  <si>
-    <t>GHM</t>
-  </si>
-  <si>
-    <t>IONQ</t>
-  </si>
-  <si>
-    <t>STEP</t>
-  </si>
-  <si>
-    <t>CNX</t>
-  </si>
-  <si>
-    <t>RVMD</t>
-  </si>
-  <si>
-    <t>AZEK</t>
-  </si>
-  <si>
-    <t>COUR</t>
-  </si>
-  <si>
-    <t>LLY</t>
-  </si>
-  <si>
-    <t>ELAN</t>
-  </si>
-  <si>
-    <t>BMA</t>
-  </si>
-  <si>
-    <t>DICE</t>
-  </si>
-  <si>
-    <t>NRP</t>
-  </si>
-  <si>
-    <t>AZTA</t>
-  </si>
-  <si>
-    <t>TDW</t>
-  </si>
-  <si>
-    <t>SMHI</t>
-  </si>
-  <si>
-    <t>HRB</t>
-  </si>
-  <si>
-    <t>BFST</t>
-  </si>
-  <si>
-    <t>MTSI</t>
-  </si>
-  <si>
-    <t>FRHC</t>
-  </si>
-  <si>
-    <t>AEHR</t>
-  </si>
-  <si>
-    <t>XPRO</t>
-  </si>
-  <si>
-    <t>PLCE</t>
-  </si>
-  <si>
-    <t>BOH</t>
-  </si>
-  <si>
-    <t>CVBF</t>
-  </si>
-  <si>
-    <t>BCC</t>
-  </si>
-  <si>
-    <t>CKX</t>
-  </si>
-  <si>
-    <t>INBK</t>
-  </si>
-  <si>
-    <t>ROCK</t>
-  </si>
-  <si>
-    <t>WMG</t>
-  </si>
-  <si>
-    <t>BBW</t>
-  </si>
-  <si>
-    <t>PESI</t>
-  </si>
-  <si>
-    <t>LBRDB</t>
-  </si>
-  <si>
-    <t>AMNB</t>
-  </si>
-  <si>
-    <t>GIC</t>
-  </si>
-  <si>
-    <t>SFBS</t>
-  </si>
-  <si>
-    <t>PRA</t>
-  </si>
-  <si>
-    <t>FTI</t>
-  </si>
-  <si>
-    <t>ARRY</t>
-  </si>
-  <si>
-    <t>ERIE</t>
-  </si>
-  <si>
-    <t>OVV</t>
-  </si>
-  <si>
-    <t>HDSN</t>
-  </si>
-  <si>
-    <t>GES</t>
-  </si>
-  <si>
-    <t>FTAI</t>
-  </si>
-  <si>
-    <t>CVI</t>
-  </si>
-  <si>
-    <t>NOG</t>
-  </si>
-  <si>
-    <t>TALO</t>
-  </si>
-  <si>
-    <t>MPC</t>
-  </si>
-  <si>
-    <t>FLR</t>
-  </si>
-  <si>
-    <t>HOFT</t>
+    <t>AKAM</t>
+  </si>
+  <si>
+    <t>CIGI</t>
+  </si>
+  <si>
+    <t>GGAL</t>
+  </si>
+  <si>
+    <t>AFYA</t>
+  </si>
+  <si>
+    <t>SSD</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>DPZ</t>
+  </si>
+  <si>
+    <t>SRV</t>
+  </si>
+  <si>
+    <t>ZS</t>
+  </si>
+  <si>
+    <t>WDC</t>
+  </si>
+  <si>
+    <t>NX</t>
+  </si>
+  <si>
+    <t>FLXS</t>
+  </si>
+  <si>
+    <t>PNFP</t>
+  </si>
+  <si>
+    <t>PEBK</t>
+  </si>
+  <si>
+    <t>MRO</t>
+  </si>
+  <si>
+    <t>FIX</t>
+  </si>
+  <si>
+    <t>PRMW</t>
+  </si>
+  <si>
+    <t>FANG</t>
+  </si>
+  <si>
+    <t>WSM</t>
+  </si>
+  <si>
+    <t>EOG</t>
+  </si>
+  <si>
+    <t>HIBB</t>
+  </si>
+  <si>
+    <t>TROX</t>
+  </si>
+  <si>
+    <t>GSHD</t>
+  </si>
+  <si>
+    <t>RBA</t>
+  </si>
+  <si>
+    <t>MLR</t>
+  </si>
+  <si>
+    <t>EXEL</t>
+  </si>
+  <si>
+    <t>EVR</t>
+  </si>
+  <si>
+    <t>SG</t>
+  </si>
+  <si>
+    <t>ESTC</t>
+  </si>
+  <si>
+    <t>SPOK</t>
+  </si>
+  <si>
+    <t>BKU</t>
+  </si>
+  <si>
+    <t>XP</t>
+  </si>
+  <si>
+    <t>STRT</t>
+  </si>
+  <si>
+    <t>CRK</t>
+  </si>
+  <si>
+    <t>NYT</t>
+  </si>
+  <si>
+    <t>BKNG</t>
+  </si>
+  <si>
+    <t>HES</t>
+  </si>
+  <si>
+    <t>MBWM</t>
+  </si>
+  <si>
+    <t>TCBI</t>
+  </si>
+  <si>
+    <t>EQNR</t>
+  </si>
+  <si>
+    <t>AFBI</t>
+  </si>
+  <si>
+    <t>WMS</t>
+  </si>
+  <si>
+    <t>FRPT</t>
+  </si>
+  <si>
+    <t>FLT</t>
+  </si>
+  <si>
+    <t>HOLI</t>
+  </si>
+  <si>
+    <t>MELI</t>
+  </si>
+  <si>
+    <t>KNSL</t>
+  </si>
+  <si>
+    <t>CATY</t>
+  </si>
+  <si>
+    <t>MEDP</t>
+  </si>
+  <si>
+    <t>PXD</t>
+  </si>
+  <si>
+    <t>AXON</t>
+  </si>
+  <si>
+    <t>HURN</t>
+  </si>
+  <si>
+    <t>CNOB</t>
+  </si>
+  <si>
+    <t>VAL</t>
+  </si>
+  <si>
+    <t>OC</t>
+  </si>
+  <si>
+    <t>VEL</t>
+  </si>
+  <si>
+    <t>USAC</t>
+  </si>
+  <si>
+    <t>GTLB</t>
+  </si>
+  <si>
+    <t>CEQP</t>
+  </si>
+  <si>
+    <t>FFNW</t>
+  </si>
+  <si>
+    <t>MET</t>
+  </si>
+  <si>
+    <t>KOP</t>
+  </si>
+  <si>
+    <t>BRBR</t>
+  </si>
+  <si>
+    <t>HCKT</t>
+  </si>
+  <si>
+    <t>TNET</t>
+  </si>
+  <si>
+    <t>HAYW</t>
+  </si>
+  <si>
+    <t>BEKE</t>
+  </si>
+  <si>
+    <t>JOE</t>
+  </si>
+  <si>
+    <t>RYAN</t>
+  </si>
+  <si>
+    <t>AVNW</t>
+  </si>
+  <si>
+    <t>STX</t>
+  </si>
+  <si>
+    <t>AKRO</t>
+  </si>
+  <si>
+    <t>ZGN</t>
+  </si>
+  <si>
+    <t>YY</t>
+  </si>
+  <si>
+    <t>VMW</t>
+  </si>
+  <si>
+    <t>PWSC</t>
+  </si>
+  <si>
+    <t>AGM</t>
+  </si>
+  <si>
+    <t>NLCP</t>
+  </si>
+  <si>
+    <t>BAND</t>
+  </si>
+  <si>
+    <t>PBNK</t>
+  </si>
+  <si>
+    <t>BXMT</t>
+  </si>
+  <si>
+    <t>ISTR</t>
+  </si>
+  <si>
+    <t>TEAM</t>
+  </si>
+  <si>
+    <t>NEWT</t>
+  </si>
+  <si>
+    <t>FOR</t>
+  </si>
+  <si>
+    <t>KE</t>
+  </si>
+  <si>
+    <t>AMGN</t>
+  </si>
+  <si>
+    <t>RBB</t>
+  </si>
+  <si>
+    <t>CTRA</t>
+  </si>
+  <si>
+    <t>YZCAY</t>
+  </si>
+  <si>
+    <t>ROST</t>
+  </si>
+  <si>
+    <t>BG</t>
+  </si>
+  <si>
+    <t>ACLS</t>
+  </si>
+  <si>
+    <t>MTCH</t>
+  </si>
+  <si>
+    <t>ALKT</t>
+  </si>
+  <si>
+    <t>CNXN</t>
+  </si>
+  <si>
+    <t>REX</t>
+  </si>
+  <si>
+    <t>JHX</t>
+  </si>
+  <si>
+    <t>ADP</t>
+  </si>
+  <si>
+    <t>UBP</t>
+  </si>
+  <si>
+    <t>QTWO</t>
+  </si>
+  <si>
+    <t>CSCO</t>
+  </si>
+  <si>
+    <t>NDP</t>
+  </si>
+  <si>
+    <t>LOGI</t>
+  </si>
+  <si>
+    <t>SPNS</t>
+  </si>
+  <si>
+    <t>TJX</t>
+  </si>
+  <si>
+    <t>AMWD</t>
+  </si>
+  <si>
+    <t>CAE</t>
+  </si>
+  <si>
+    <t>GRVY</t>
+  </si>
+  <si>
+    <t>XPOF</t>
+  </si>
+  <si>
+    <t>INFA</t>
+  </si>
+  <si>
+    <t>NVT</t>
+  </si>
+  <si>
+    <t>JEF</t>
+  </si>
+  <si>
+    <t>CMC</t>
+  </si>
+  <si>
+    <t>RILY</t>
+  </si>
+  <si>
+    <t>NUVL</t>
+  </si>
+  <si>
+    <t>EMR</t>
+  </si>
+  <si>
+    <t>APOG</t>
+  </si>
+  <si>
+    <t>ITT</t>
+  </si>
+  <si>
+    <t>SPFI</t>
+  </si>
+  <si>
+    <t>GBX</t>
+  </si>
+  <si>
+    <t>INTC</t>
+  </si>
+  <si>
+    <t>LULU</t>
+  </si>
+  <si>
+    <t>CSWC</t>
+  </si>
+  <si>
+    <t>ARCE</t>
+  </si>
+  <si>
+    <t>LAD</t>
+  </si>
+  <si>
+    <t>MGY</t>
+  </si>
+  <si>
+    <t>NVMI</t>
+  </si>
+  <si>
+    <t>TPX</t>
+  </si>
+  <si>
+    <t>REGN</t>
+  </si>
+  <si>
+    <t>VEEV</t>
+  </si>
+  <si>
+    <t>ABNB</t>
+  </si>
+  <si>
+    <t>CW</t>
+  </si>
+  <si>
+    <t>WWD</t>
+  </si>
+  <si>
+    <t>SF</t>
+  </si>
+  <si>
+    <t>TWI</t>
+  </si>
+  <si>
+    <t>XMTR</t>
+  </si>
+  <si>
+    <t>TM</t>
+  </si>
+  <si>
+    <t>UFPI</t>
+  </si>
+  <si>
+    <t>ESCA</t>
+  </si>
+  <si>
+    <t>CCB</t>
+  </si>
+  <si>
+    <t>ZTS</t>
+  </si>
+  <si>
+    <t>NUE</t>
+  </si>
+  <si>
+    <t>PFBC</t>
   </si>
   <si>
     <t>ASTE</t>
   </si>
   <si>
-    <t>NE</t>
-  </si>
-  <si>
-    <t>AROC</t>
-  </si>
-  <si>
-    <t>ARCH</t>
-  </si>
-  <si>
-    <t>GGAL</t>
-  </si>
-  <si>
-    <t>NBR</t>
-  </si>
-  <si>
-    <t>VST</t>
-  </si>
-  <si>
-    <t>FRSH</t>
-  </si>
-  <si>
-    <t>AURC</t>
-  </si>
-  <si>
-    <t>ARGX</t>
-  </si>
-  <si>
-    <t>MLKN</t>
-  </si>
-  <si>
-    <t>TRUP</t>
-  </si>
-  <si>
-    <t>TWIN</t>
-  </si>
-  <si>
-    <t>CRS</t>
-  </si>
-  <si>
-    <t>HNI</t>
-  </si>
-  <si>
-    <t>CHX</t>
-  </si>
-  <si>
-    <t>PLUS</t>
-  </si>
-  <si>
-    <t>GPOR</t>
-  </si>
-  <si>
-    <t>IIPR</t>
-  </si>
-  <si>
-    <t>ITRN</t>
-  </si>
-  <si>
-    <t>CIVI</t>
-  </si>
-  <si>
-    <t>CCJ</t>
-  </si>
-  <si>
-    <t>OSK</t>
-  </si>
-  <si>
-    <t>KRC</t>
-  </si>
-  <si>
-    <t>VET</t>
-  </si>
-  <si>
-    <t>LYFT</t>
-  </si>
-  <si>
-    <t>PTEN</t>
-  </si>
-  <si>
-    <t>QCRH</t>
+    <t>CZR</t>
+  </si>
+  <si>
+    <t>AEL</t>
+  </si>
+  <si>
+    <t>PINS</t>
+  </si>
+  <si>
+    <t>ET</t>
+  </si>
+  <si>
+    <t>SBFG</t>
+  </si>
+  <si>
+    <t>ALGN</t>
+  </si>
+  <si>
+    <t>ABCM</t>
+  </si>
+  <si>
+    <t>EQT</t>
+  </si>
+  <si>
+    <t>HCC</t>
+  </si>
+  <si>
+    <t>ORCL</t>
+  </si>
+  <si>
+    <t>TREX</t>
+  </si>
+  <si>
+    <t>WDAY</t>
+  </si>
+  <si>
+    <t>NWLI</t>
+  </si>
+  <si>
+    <t>WST</t>
+  </si>
+  <si>
+    <t>RCUS</t>
+  </si>
+  <si>
+    <t>PSTG</t>
+  </si>
+  <si>
+    <t>LRN</t>
+  </si>
+  <si>
+    <t>KKR</t>
+  </si>
+  <si>
+    <t>LDOS</t>
+  </si>
+  <si>
+    <t>BLD</t>
+  </si>
+  <si>
+    <t>TXT</t>
+  </si>
+  <si>
+    <t>IIIN</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>OMAB</t>
+  </si>
+  <si>
+    <t>VERX</t>
+  </si>
+  <si>
+    <t>OFIX</t>
+  </si>
+  <si>
+    <t>DAWN</t>
+  </si>
+  <si>
+    <t>IMVT</t>
+  </si>
+  <si>
+    <t>CSTL</t>
   </si>
   <si>
     <t>MHO</t>
   </si>
   <si>
-    <t>BKI</t>
-  </si>
-  <si>
-    <t>DBRG</t>
-  </si>
-  <si>
-    <t>EVI</t>
-  </si>
-  <si>
-    <t>GPN</t>
-  </si>
-  <si>
-    <t>SLB</t>
-  </si>
-  <si>
-    <t>HEP</t>
-  </si>
-  <si>
-    <t>NTNX</t>
-  </si>
-  <si>
-    <t>MUR</t>
-  </si>
-  <si>
-    <t>INTU</t>
-  </si>
-  <si>
-    <t>TIPT</t>
-  </si>
-  <si>
-    <t>HIBB</t>
-  </si>
-  <si>
-    <t>PBF</t>
-  </si>
-  <si>
-    <t>DWAC</t>
-  </si>
-  <si>
-    <t>EME</t>
-  </si>
-  <si>
-    <t>AZZ</t>
-  </si>
-  <si>
-    <t>TH</t>
-  </si>
-  <si>
-    <t>ODFL</t>
-  </si>
-  <si>
-    <t>FOR</t>
-  </si>
-  <si>
-    <t>CPE</t>
-  </si>
-  <si>
-    <t>SSD</t>
-  </si>
-  <si>
-    <t>PRIM</t>
-  </si>
-  <si>
-    <t>NXGN</t>
-  </si>
-  <si>
-    <t>NVO</t>
-  </si>
-  <si>
-    <t>URI</t>
-  </si>
-  <si>
-    <t>ONTO</t>
-  </si>
-  <si>
-    <t>W</t>
-  </si>
-  <si>
-    <t>BLD</t>
-  </si>
-  <si>
-    <t>SOVO</t>
-  </si>
-  <si>
-    <t>ZION</t>
-  </si>
-  <si>
-    <t>RH</t>
-  </si>
-  <si>
-    <t>BRZE</t>
-  </si>
-  <si>
-    <t>SPLK</t>
+    <t>JLL</t>
+  </si>
+  <si>
+    <t>CFBK</t>
+  </si>
+  <si>
+    <t>ALSN</t>
+  </si>
+  <si>
+    <t>BALY</t>
+  </si>
+  <si>
+    <t>PH</t>
+  </si>
+  <si>
+    <t>ATR</t>
+  </si>
+  <si>
+    <t>JBL</t>
+  </si>
+  <si>
+    <t>COCO</t>
+  </si>
+  <si>
+    <t>CPTP</t>
+  </si>
+  <si>
+    <t>NWS</t>
+  </si>
+  <si>
+    <t>IRM</t>
+  </si>
+  <si>
+    <t>PBAM</t>
+  </si>
+  <si>
+    <t>BY</t>
+  </si>
+  <si>
+    <t>IHG</t>
   </si>
   <si>
     <t>DLX</t>
   </si>
   <si>
-    <t>AR</t>
-  </si>
-  <si>
-    <t>WMPN</t>
-  </si>
-  <si>
-    <t>TEAM</t>
-  </si>
-  <si>
-    <t>QLYS</t>
-  </si>
-  <si>
-    <t>PSX</t>
-  </si>
-  <si>
-    <t>BCSF</t>
-  </si>
-  <si>
-    <t>APPF</t>
-  </si>
-  <si>
-    <t>TW</t>
-  </si>
-  <si>
-    <t>JOE</t>
-  </si>
-  <si>
-    <t>OLLI</t>
-  </si>
-  <si>
-    <t>ARVN</t>
-  </si>
-  <si>
-    <t>RIVN</t>
-  </si>
-  <si>
-    <t>SKYW</t>
-  </si>
-  <si>
-    <t>ETN</t>
-  </si>
-  <si>
-    <t>LBRT</t>
-  </si>
-  <si>
-    <t>ADBE</t>
-  </si>
-  <si>
-    <t>BR</t>
-  </si>
-  <si>
-    <t>NFE</t>
-  </si>
-  <si>
-    <t>DCOM</t>
-  </si>
-  <si>
-    <t>LII</t>
-  </si>
-  <si>
-    <t>CTLT</t>
-  </si>
-  <si>
-    <t>ENLC</t>
-  </si>
-  <si>
-    <t>NX</t>
-  </si>
-  <si>
-    <t>SU</t>
-  </si>
-  <si>
-    <t>FETM</t>
-  </si>
-  <si>
-    <t>CUBI</t>
-  </si>
-  <si>
-    <t>XP</t>
-  </si>
-  <si>
-    <t>ZEUS</t>
-  </si>
-  <si>
-    <t>KOP</t>
-  </si>
-  <si>
-    <t>RAMP</t>
-  </si>
-  <si>
-    <t>CLMT</t>
-  </si>
-  <si>
-    <t>DCBO</t>
-  </si>
-  <si>
-    <t>CDRE</t>
-  </si>
-  <si>
-    <t>SHEN</t>
-  </si>
-  <si>
-    <t>DWACU</t>
-  </si>
-  <si>
-    <t>BKU</t>
-  </si>
-  <si>
-    <t>IMO</t>
-  </si>
-  <si>
-    <t>BEKE</t>
-  </si>
-  <si>
-    <t>HAL</t>
-  </si>
-  <si>
-    <t>CAT</t>
-  </si>
-  <si>
-    <t>NCR</t>
-  </si>
-  <si>
-    <t>TWI</t>
-  </si>
-  <si>
-    <t>LEAT</t>
-  </si>
-  <si>
-    <t>BKR</t>
-  </si>
-  <si>
-    <t>NOA</t>
-  </si>
-  <si>
-    <t>CARR</t>
-  </si>
-  <si>
-    <t>CCOI</t>
-  </si>
-  <si>
-    <t>ELF</t>
-  </si>
-  <si>
-    <t>HPK</t>
-  </si>
-  <si>
-    <t>DLR</t>
-  </si>
-  <si>
-    <t>TROX</t>
-  </si>
-  <si>
-    <t>FLXS</t>
-  </si>
-  <si>
-    <t>UFPI</t>
-  </si>
-  <si>
-    <t>SMMF</t>
-  </si>
-  <si>
-    <t>CRK</t>
-  </si>
-  <si>
-    <t>ANET</t>
-  </si>
-  <si>
-    <t>BRP</t>
-  </si>
-  <si>
-    <t>HLNE</t>
-  </si>
-  <si>
-    <t>HAYW</t>
-  </si>
-  <si>
-    <t>OC</t>
-  </si>
-  <si>
-    <t>CNOB</t>
-  </si>
-  <si>
-    <t>VEEV</t>
-  </si>
-  <si>
-    <t>TREX</t>
-  </si>
-  <si>
-    <t>TCBI</t>
-  </si>
-  <si>
-    <t>JHX</t>
-  </si>
-  <si>
-    <t>ROKU</t>
-  </si>
-  <si>
-    <t>RILY</t>
-  </si>
-  <si>
-    <t>MBWM</t>
-  </si>
-  <si>
-    <t>YY</t>
-  </si>
-  <si>
-    <t>TFII</t>
-  </si>
-  <si>
-    <t>WOR</t>
-  </si>
-  <si>
-    <t>TPX</t>
-  </si>
-  <si>
-    <t>WMS</t>
-  </si>
-  <si>
-    <t>RBB</t>
-  </si>
-  <si>
-    <t>DRQ</t>
-  </si>
-  <si>
-    <t>RNGR</t>
-  </si>
-  <si>
-    <t>R</t>
-  </si>
-  <si>
-    <t>NVDA</t>
-  </si>
-  <si>
-    <t>PSN</t>
-  </si>
-  <si>
-    <t>MEDP</t>
-  </si>
-  <si>
-    <t>ERF</t>
-  </si>
-  <si>
-    <t>KTOS</t>
-  </si>
-  <si>
-    <t>ALRM</t>
-  </si>
-  <si>
-    <t>PBR</t>
-  </si>
-  <si>
-    <t>HCM</t>
-  </si>
-  <si>
-    <t>FORG</t>
-  </si>
-  <si>
-    <t>JILL</t>
-  </si>
-  <si>
-    <t>CW</t>
-  </si>
-  <si>
-    <t>LOB</t>
-  </si>
-  <si>
-    <t>AFYA</t>
-  </si>
-  <si>
-    <t>PRMW</t>
-  </si>
-  <si>
-    <t>STER</t>
-  </si>
-  <si>
-    <t>YELP</t>
-  </si>
-  <si>
-    <t>GBX</t>
-  </si>
-  <si>
-    <t>HAS</t>
-  </si>
-  <si>
-    <t>BHWB</t>
-  </si>
-  <si>
-    <t>SG</t>
-  </si>
-  <si>
-    <t>VRNS</t>
-  </si>
-  <si>
-    <t>TRGP</t>
-  </si>
-  <si>
-    <t>STX</t>
+    <t>SFST</t>
+  </si>
+  <si>
+    <t>CIEN</t>
+  </si>
+  <si>
+    <t>SHOP</t>
+  </si>
+  <si>
+    <t>ABR</t>
+  </si>
+  <si>
+    <t>PRO</t>
+  </si>
+  <si>
+    <t>ALV</t>
+  </si>
+  <si>
+    <t>VECO</t>
+  </si>
+  <si>
+    <t>ALRS</t>
+  </si>
+  <si>
+    <t>SCSC</t>
+  </si>
+  <si>
+    <t>FICO</t>
+  </si>
+  <si>
+    <t>DVN</t>
+  </si>
+  <si>
+    <t>FSFG</t>
+  </si>
+  <si>
+    <t>ZWS</t>
+  </si>
+  <si>
+    <t>HALO</t>
+  </si>
+  <si>
+    <t>CE</t>
+  </si>
+  <si>
+    <t>CEN</t>
+  </si>
+  <si>
+    <t>MVBF</t>
+  </si>
+  <si>
+    <t>DVAX</t>
+  </si>
+  <si>
+    <t>INDB</t>
+  </si>
+  <si>
+    <t>SITM</t>
+  </si>
+  <si>
+    <t>CHTR</t>
+  </si>
+  <si>
+    <t>BSRR</t>
+  </si>
+  <si>
+    <t>SPB</t>
+  </si>
+  <si>
+    <t>ATSG</t>
+  </si>
+  <si>
+    <t>MCB</t>
+  </si>
+  <si>
+    <t>CFST</t>
+  </si>
+  <si>
+    <t>HPE</t>
+  </si>
+  <si>
+    <t>EMO</t>
+  </si>
+  <si>
+    <t>LYB</t>
+  </si>
+  <si>
+    <t>CLW</t>
+  </si>
+  <si>
+    <t>CRWD</t>
+  </si>
+  <si>
+    <t>GBLI</t>
+  </si>
+  <si>
+    <t>IBM</t>
+  </si>
+  <si>
+    <t>OXY</t>
   </si>
   <si>
     <t>SKY</t>
   </si>
   <si>
-    <t>PNFP</t>
-  </si>
-  <si>
-    <t>TWNK</t>
-  </si>
-  <si>
-    <t>ATSG</t>
-  </si>
-  <si>
-    <t>BXP</t>
-  </si>
-  <si>
-    <t>TRNS</t>
-  </si>
-  <si>
-    <t>DVAX</t>
-  </si>
-  <si>
-    <t>VAL</t>
-  </si>
-  <si>
-    <t>CALB</t>
-  </si>
-  <si>
-    <t>SCPL</t>
-  </si>
-  <si>
-    <t>FNF</t>
-  </si>
-  <si>
-    <t>CLW</t>
-  </si>
-  <si>
-    <t>GSHD</t>
-  </si>
-  <si>
-    <t>AVNW</t>
-  </si>
-  <si>
-    <t>APOG</t>
-  </si>
-  <si>
-    <t>IMVT</t>
-  </si>
-  <si>
-    <t>CAAP</t>
-  </si>
-  <si>
-    <t>CVE</t>
-  </si>
-  <si>
-    <t>AURCU</t>
-  </si>
-  <si>
-    <t>BKNG</t>
-  </si>
-  <si>
-    <t>MAT</t>
-  </si>
-  <si>
-    <t>KNSL</t>
-  </si>
-  <si>
-    <t>NEWR</t>
-  </si>
-  <si>
-    <t>FRO</t>
-  </si>
-  <si>
-    <t>GRC</t>
-  </si>
-  <si>
-    <t>SWTX</t>
-  </si>
-  <si>
-    <t>AXON</t>
-  </si>
-  <si>
-    <t>NYT</t>
-  </si>
-  <si>
-    <t>ITT</t>
-  </si>
-  <si>
-    <t>CDW</t>
-  </si>
-  <si>
-    <t>COP</t>
-  </si>
-  <si>
-    <t>NEWT</t>
-  </si>
-  <si>
-    <t>HCCI</t>
-  </si>
-  <si>
-    <t>GFF</t>
-  </si>
-  <si>
-    <t>HALO</t>
-  </si>
-  <si>
-    <t>EVR</t>
-  </si>
-  <si>
-    <t>MLR</t>
-  </si>
-  <si>
-    <t>LI</t>
-  </si>
-  <si>
-    <t>PAM</t>
-  </si>
-  <si>
-    <t>SPOK</t>
-  </si>
-  <si>
-    <t>NBIX</t>
-  </si>
-  <si>
-    <t>SAH</t>
-  </si>
-  <si>
-    <t>CABA</t>
-  </si>
-  <si>
-    <t>NVT</t>
-  </si>
-  <si>
-    <t>VIST</t>
-  </si>
-  <si>
-    <t>AIT</t>
-  </si>
-  <si>
-    <t>AGM</t>
-  </si>
-  <si>
-    <t>AMWD</t>
-  </si>
-  <si>
-    <t>OLED</t>
-  </si>
-  <si>
-    <t>EXEL</t>
+    <t>PAA</t>
+  </si>
+  <si>
+    <t>PAGP</t>
+  </si>
+  <si>
+    <t>WK</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>PFC</t>
+  </si>
+  <si>
+    <t>ICFI</t>
+  </si>
+  <si>
+    <t>SAL</t>
+  </si>
+  <si>
+    <t>REVG</t>
+  </si>
+  <si>
+    <t>NWPX</t>
+  </si>
+  <si>
+    <t>HMC</t>
+  </si>
+  <si>
+    <t>ALPN</t>
+  </si>
+  <si>
+    <t>BSM</t>
+  </si>
+  <si>
+    <t>WEX</t>
   </si>
   <si>
     <t>MSA</t>
   </si>
   <si>
-    <t>SRV</t>
-  </si>
-  <si>
-    <t>HZNP</t>
-  </si>
-  <si>
-    <t>WIX</t>
-  </si>
-  <si>
-    <t>TNET</t>
-  </si>
-  <si>
-    <t>VLO</t>
-  </si>
-  <si>
-    <t>AMEH</t>
-  </si>
-  <si>
-    <t>TRDA</t>
-  </si>
-  <si>
-    <t>VVI</t>
-  </si>
-  <si>
-    <t>AMGN</t>
-  </si>
-  <si>
-    <t>MRO</t>
-  </si>
-  <si>
-    <t>CNQ</t>
-  </si>
-  <si>
-    <t>DPZ</t>
-  </si>
-  <si>
-    <t>ZGN</t>
-  </si>
-  <si>
-    <t>CCB</t>
-  </si>
-  <si>
-    <t>PFC</t>
+    <t>UBER</t>
+  </si>
+  <si>
+    <t>BCO</t>
+  </si>
+  <si>
+    <t>ATI</t>
+  </si>
+  <si>
+    <t>OPCH</t>
+  </si>
+  <si>
+    <t>PWR</t>
+  </si>
+  <si>
+    <t>ACAD</t>
+  </si>
+  <si>
+    <t>GOLF</t>
+  </si>
+  <si>
+    <t>AZPN</t>
+  </si>
+  <si>
+    <t>RCMT</t>
+  </si>
+  <si>
+    <t>CRAI</t>
+  </si>
+  <si>
+    <t>IBKR</t>
   </si>
   <si>
     <t>KNSA</t>
   </si>
   <si>
-    <t>PBNK</t>
-  </si>
-  <si>
-    <t>CZR</t>
-  </si>
-  <si>
-    <t>CRMT</t>
-  </si>
-  <si>
-    <t>OFIX</t>
-  </si>
-  <si>
-    <t>AKAM</t>
-  </si>
-  <si>
-    <t>EQNR</t>
-  </si>
-  <si>
-    <t>CIGI</t>
-  </si>
-  <si>
-    <t>BNTX</t>
-  </si>
-  <si>
-    <t>CQP</t>
-  </si>
-  <si>
-    <t>JLL</t>
-  </si>
-  <si>
-    <t>NTIC</t>
-  </si>
-  <si>
-    <t>NEOG</t>
-  </si>
-  <si>
-    <t>IIIN</t>
-  </si>
-  <si>
-    <t>ALKT</t>
-  </si>
-  <si>
-    <t>FANG</t>
-  </si>
-  <si>
-    <t>ALPN</t>
-  </si>
-  <si>
-    <t>BRBR</t>
-  </si>
-  <si>
-    <t>WDC</t>
-  </si>
-  <si>
-    <t>PFBC</t>
-  </si>
-  <si>
-    <t>KE</t>
-  </si>
-  <si>
-    <t>FIX</t>
-  </si>
-  <si>
-    <t>LAD</t>
-  </si>
-  <si>
-    <t>PEBK</t>
-  </si>
-  <si>
-    <t>J</t>
-  </si>
-  <si>
-    <t>VHNAU</t>
-  </si>
-  <si>
-    <t>NSIT</t>
-  </si>
-  <si>
-    <t>SCSC</t>
-  </si>
-  <si>
-    <t>BG</t>
-  </si>
-  <si>
-    <t>STRT</t>
-  </si>
-  <si>
-    <t>ATR</t>
-  </si>
-  <si>
-    <t>HP</t>
-  </si>
-  <si>
-    <t>SPNS</t>
-  </si>
-  <si>
-    <t>EQT</t>
-  </si>
-  <si>
-    <t>WSM</t>
-  </si>
-  <si>
-    <t>LAUR</t>
-  </si>
-  <si>
-    <t>FSFG</t>
-  </si>
-  <si>
-    <t>MTCH</t>
-  </si>
-  <si>
-    <t>MET</t>
-  </si>
-  <si>
-    <t>ATGE</t>
-  </si>
-  <si>
-    <t>TCOM</t>
-  </si>
-  <si>
-    <t>CVRX</t>
-  </si>
-  <si>
-    <t>CADE</t>
-  </si>
-  <si>
-    <t>ALGN</t>
-  </si>
-  <si>
-    <t>ABCB</t>
-  </si>
-  <si>
-    <t>LRN</t>
-  </si>
-  <si>
-    <t>FRPT</t>
-  </si>
-  <si>
-    <t>CMC</t>
-  </si>
-  <si>
-    <t>APO</t>
-  </si>
-  <si>
-    <t>PXD</t>
-  </si>
-  <si>
-    <t>FFNW</t>
-  </si>
-  <si>
-    <t>KSS</t>
-  </si>
-  <si>
-    <t>VECO</t>
-  </si>
-  <si>
-    <t>ADP</t>
-  </si>
-  <si>
-    <t>CPTP</t>
-  </si>
-  <si>
-    <t>GLOB</t>
-  </si>
-  <si>
-    <t>SPFI</t>
-  </si>
-  <si>
-    <t>CHTR</t>
-  </si>
-  <si>
-    <t>RYAN</t>
-  </si>
-  <si>
-    <t>ROAD</t>
-  </si>
-  <si>
-    <t>CSWI</t>
-  </si>
-  <si>
-    <t>MELI</t>
-  </si>
-  <si>
-    <t>ESCA</t>
-  </si>
-  <si>
-    <t>HES</t>
-  </si>
-  <si>
-    <t>FUNC</t>
-  </si>
-  <si>
-    <t>EBC</t>
-  </si>
-  <si>
-    <t>WST</t>
-  </si>
-  <si>
-    <t>OKTA</t>
-  </si>
-  <si>
-    <t>CNXN</t>
-  </si>
-  <si>
-    <t>JBL</t>
-  </si>
-  <si>
     <t>RPD</t>
   </si>
   <si>
-    <t>NCNO</t>
-  </si>
-  <si>
-    <t>MANU</t>
-  </si>
-  <si>
-    <t>ATI</t>
-  </si>
-  <si>
-    <t>PNR</t>
-  </si>
-  <si>
-    <t>AMPL</t>
-  </si>
-  <si>
-    <t>SIG</t>
-  </si>
-  <si>
-    <t>ABR</t>
-  </si>
-  <si>
-    <t>IBP</t>
-  </si>
-  <si>
-    <t>ICFI</t>
-  </si>
-  <si>
-    <t>CPNG</t>
-  </si>
-  <si>
-    <t>PH</t>
-  </si>
-  <si>
-    <t>OSIS</t>
-  </si>
-  <si>
-    <t>JAZZ</t>
-  </si>
-  <si>
-    <t>EMR</t>
-  </si>
-  <si>
-    <t>TJX</t>
-  </si>
-  <si>
-    <t>NLCP</t>
-  </si>
-  <si>
-    <t>TXT</t>
-  </si>
-  <si>
-    <t>ARCE</t>
-  </si>
-  <si>
-    <t>CIEN</t>
-  </si>
-  <si>
-    <t>ESTC</t>
-  </si>
-  <si>
-    <t>FLT</t>
-  </si>
-  <si>
-    <t>CXM</t>
-  </si>
-  <si>
-    <t>INDB</t>
-  </si>
-  <si>
-    <t>BY</t>
-  </si>
-  <si>
-    <t>ALSN</t>
-  </si>
-  <si>
-    <t>HURN</t>
-  </si>
-  <si>
-    <t>CTRA</t>
-  </si>
-  <si>
-    <t>WINA</t>
-  </si>
-  <si>
-    <t>CSCO</t>
-  </si>
-  <si>
-    <t>QTWO</t>
-  </si>
-  <si>
-    <t>VSEC</t>
-  </si>
-  <si>
-    <t>REVG</t>
-  </si>
-  <si>
-    <t>ANDE</t>
-  </si>
-  <si>
-    <t>CSWC</t>
-  </si>
-  <si>
-    <t>NWPX</t>
-  </si>
-  <si>
-    <t>FBP</t>
-  </si>
-  <si>
-    <t>CMPR</t>
-  </si>
-  <si>
-    <t>GBLI</t>
-  </si>
-  <si>
-    <t>TOL</t>
-  </si>
-  <si>
-    <t>BLDR</t>
-  </si>
-  <si>
-    <t>NREF</t>
-  </si>
-  <si>
-    <t>VEL</t>
-  </si>
-  <si>
-    <t>REX</t>
-  </si>
-  <si>
-    <t>ZWS</t>
-  </si>
-  <si>
-    <t>OFG</t>
-  </si>
-  <si>
-    <t>HCC</t>
-  </si>
-  <si>
-    <t>HLI</t>
-  </si>
-  <si>
-    <t>FLIC</t>
-  </si>
-  <si>
-    <t>AKRO</t>
-  </si>
-  <si>
     <t>ATKR</t>
   </si>
   <si>
-    <t>RCMT</t>
-  </si>
-  <si>
-    <t>GOLF</t>
-  </si>
-  <si>
-    <t>MCB</t>
-  </si>
-  <si>
-    <t>VICR</t>
-  </si>
-  <si>
-    <t>TS</t>
-  </si>
-  <si>
-    <t>TCPC</t>
-  </si>
-  <si>
-    <t>BLMN</t>
-  </si>
-  <si>
-    <t>CE</t>
-  </si>
-  <si>
-    <t>ZTS</t>
-  </si>
-  <si>
-    <t>VERX</t>
-  </si>
-  <si>
-    <t>CHK</t>
-  </si>
-  <si>
-    <t>NEU</t>
-  </si>
-  <si>
-    <t>USAC</t>
-  </si>
-  <si>
-    <t>AEL</t>
-  </si>
-  <si>
-    <t>IRM</t>
-  </si>
-  <si>
-    <t>ASGN</t>
-  </si>
-  <si>
-    <t>MORN</t>
-  </si>
-  <si>
-    <t>CF</t>
-  </si>
-  <si>
-    <t>REPYY</t>
-  </si>
-  <si>
-    <t>HOLI</t>
-  </si>
-  <si>
-    <t>GKOS</t>
-  </si>
-  <si>
-    <t>LDOS</t>
-  </si>
-  <si>
-    <t>NDP</t>
-  </si>
-  <si>
-    <t>BMI</t>
-  </si>
-  <si>
-    <t>RRC</t>
-  </si>
-  <si>
-    <t>HAFC</t>
-  </si>
-  <si>
-    <t>WLK</t>
-  </si>
-  <si>
-    <t>SITE</t>
-  </si>
-  <si>
-    <t>NHC</t>
-  </si>
-  <si>
-    <t>PSTG</t>
-  </si>
-  <si>
-    <t>LOPE</t>
-  </si>
-  <si>
-    <t>REGN</t>
-  </si>
-  <si>
-    <t>PAA</t>
-  </si>
-  <si>
-    <t>TEX</t>
-  </si>
-  <si>
-    <t>ROST</t>
-  </si>
-  <si>
-    <t>GHLD</t>
-  </si>
-  <si>
-    <t>NWLI</t>
-  </si>
-  <si>
-    <t>VMW</t>
-  </si>
-  <si>
-    <t>NPO</t>
-  </si>
-  <si>
-    <t>NWS</t>
-  </si>
-  <si>
-    <t>SF</t>
-  </si>
-  <si>
-    <t>WDAY</t>
-  </si>
-  <si>
-    <t>UBP</t>
-  </si>
-  <si>
-    <t>LAZ</t>
-  </si>
-  <si>
-    <t>NVMI</t>
-  </si>
-  <si>
-    <t>GRVY</t>
-  </si>
-  <si>
-    <t>PIPR</t>
-  </si>
-  <si>
-    <t>SFST</t>
-  </si>
-  <si>
-    <t>IBTX</t>
-  </si>
-  <si>
-    <t>MAR</t>
-  </si>
-  <si>
-    <t>KKR</t>
-  </si>
-  <si>
-    <t>SPB</t>
-  </si>
-  <si>
-    <t>INSW</t>
-  </si>
-  <si>
-    <t>AXSM</t>
-  </si>
-  <si>
-    <t>DKNG</t>
-  </si>
-  <si>
-    <t>PAGP</t>
-  </si>
-  <si>
-    <t>CFBK</t>
-  </si>
-  <si>
-    <t>WWD</t>
-  </si>
-  <si>
-    <t>HPE</t>
-  </si>
-  <si>
-    <t>STRS</t>
-  </si>
-  <si>
-    <t>DDS</t>
-  </si>
-  <si>
-    <t>LYB</t>
-  </si>
-  <si>
-    <t>SBFG</t>
-  </si>
-  <si>
-    <t>PATK</t>
-  </si>
-  <si>
-    <t>BWXT</t>
-  </si>
-  <si>
-    <t>CNS</t>
-  </si>
-  <si>
-    <t>SCCO</t>
-  </si>
-  <si>
-    <t>ICLR</t>
-  </si>
-  <si>
-    <t>VFC</t>
-  </si>
-  <si>
-    <t>EURN</t>
+    <t>CCK</t>
   </si>
 </sst>
 </file>
@@ -2128,7 +2119,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B587"/>
+  <dimension ref="A1:B584"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -2144,7 +2135,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1">
-        <v>367.365189127595</v>
+        <v>375.1114702149337</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2160,7 +2151,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1">
-        <v>341.8876227007241</v>
+        <v>278.1031413968787</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -2168,7 +2159,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="1">
-        <v>281.9982377747722</v>
+        <v>269.0856612119244</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -2176,7 +2167,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="1">
-        <v>278.3347514987391</v>
+        <v>237.4877676366722</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -2184,7 +2175,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="1">
-        <v>269.0856612119244</v>
+        <v>235.4505555561969</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -2192,7 +2183,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="1">
-        <v>232.1111246910582</v>
+        <v>227.1057985529521</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -2200,7 +2191,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="1">
-        <v>229.3056354874691</v>
+        <v>221.7980820481642</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -2208,7 +2199,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="1">
-        <v>224.4946559530995</v>
+        <v>203.3575479962205</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -2216,7 +2207,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="1">
-        <v>217.7896475721439</v>
+        <v>196.3475434100368</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -2224,7 +2215,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="1">
-        <v>216.4746473738084</v>
+        <v>193.8576921366997</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -2232,7 +2223,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="1">
-        <v>212.1284761913011</v>
+        <v>172.318967656227</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -2240,7 +2231,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="1">
-        <v>180.9346638752744</v>
+        <v>163.9053346227727</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -2248,7 +2239,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="1">
-        <v>169.8495911945186</v>
+        <v>162.4708089179383</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -2256,7 +2247,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="1">
-        <v>165.893637541049</v>
+        <v>161.7395734092898</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -2264,7 +2255,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="1">
-        <v>165.6254054028396</v>
+        <v>155.772077350901</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -2272,7 +2263,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="1">
-        <v>158.2716696196807</v>
+        <v>154.7626866041234</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -2280,7 +2271,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="1">
-        <v>157.8478878611776</v>
+        <v>153.7074092734149</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -2288,7 +2279,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="1">
-        <v>156.2942661247725</v>
+        <v>153.309761382723</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -2296,7 +2287,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="1">
-        <v>153.5582675059871</v>
+        <v>152.6498189539393</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -2304,7 +2295,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="1">
-        <v>152.4339128984715</v>
+        <v>152.1912085055033</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -2312,7 +2303,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="1">
-        <v>151.2519178835652</v>
+        <v>151.9178373906448</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -2320,7 +2311,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="1">
-        <v>151.2280504733532</v>
+        <v>151.3189732588958</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -2328,7 +2319,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="1">
-        <v>151.216447233269</v>
+        <v>149.593358325291</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -2336,7 +2327,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="1">
-        <v>149.6820914079164</v>
+        <v>149.1111711941948</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -2344,7 +2335,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="1">
-        <v>148.6519279352862</v>
+        <v>149.0827746816884</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -2352,7 +2343,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="1">
-        <v>148.4868335887433</v>
+        <v>147.6883772717224</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -2360,7 +2351,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="1">
-        <v>147.863406136705</v>
+        <v>146.7724323797808</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -2368,7 +2359,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="1">
-        <v>147.8050288287885</v>
+        <v>146.186511897762</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -2376,7 +2367,7 @@
         <v>31</v>
       </c>
       <c r="B31" s="1">
-        <v>147.7533404110362</v>
+        <v>145.7372516781548</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -2384,7 +2375,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="1">
-        <v>146.3594336714994</v>
+        <v>144.7577194478617</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -2392,7 +2383,7 @@
         <v>33</v>
       </c>
       <c r="B33" s="1">
-        <v>146.2610271569462</v>
+        <v>144.235711050184</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -2400,7 +2391,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="1">
-        <v>146.2477111771201</v>
+        <v>142.7967065124859</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -2408,7 +2399,7 @@
         <v>35</v>
       </c>
       <c r="B35" s="1">
-        <v>145.5016863974711</v>
+        <v>142.6762978487891</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -2416,7 +2407,7 @@
         <v>36</v>
       </c>
       <c r="B36" s="1">
-        <v>145.3517446689975</v>
+        <v>142.1340090410258</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -2424,7 +2415,7 @@
         <v>37</v>
       </c>
       <c r="B37" s="1">
-        <v>144.1438398038153</v>
+        <v>141.748272234545</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -2432,7 +2423,7 @@
         <v>38</v>
       </c>
       <c r="B38" s="1">
-        <v>143.6799140950631</v>
+        <v>141.3848479840987</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -2440,7 +2431,7 @@
         <v>39</v>
       </c>
       <c r="B39" s="1">
-        <v>142.7892212824563</v>
+        <v>140.3699006674614</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -2448,7 +2439,7 @@
         <v>40</v>
       </c>
       <c r="B40" s="1">
-        <v>142.3611793459206</v>
+        <v>140.3472449507131</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2456,7 +2447,7 @@
         <v>41</v>
       </c>
       <c r="B41" s="1">
-        <v>141.5229973515477</v>
+        <v>140.0733446210942</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2464,7 +2455,7 @@
         <v>42</v>
       </c>
       <c r="B42" s="1">
-        <v>141.414517585197</v>
+        <v>139.8257082262934</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2472,7 +2463,7 @@
         <v>43</v>
       </c>
       <c r="B43" s="1">
-        <v>141.2041648549374</v>
+        <v>139.739163366026</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2480,7 +2471,7 @@
         <v>44</v>
       </c>
       <c r="B44" s="1">
-        <v>141.1577525895082</v>
+        <v>138.6691700481375</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2488,7 +2479,7 @@
         <v>45</v>
       </c>
       <c r="B45" s="1">
-        <v>140.7682618360872</v>
+        <v>138.1012704573802</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2496,7 +2487,7 @@
         <v>46</v>
       </c>
       <c r="B46" s="1">
-        <v>140.5052586684555</v>
+        <v>137.7557014740061</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2504,7 +2495,7 @@
         <v>47</v>
       </c>
       <c r="B47" s="1">
-        <v>140.3688242188591</v>
+        <v>137.6354591170876</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2512,7 +2503,7 @@
         <v>48</v>
       </c>
       <c r="B48" s="1">
-        <v>139.9040723880485</v>
+        <v>137.0264872913963</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -2520,7 +2511,7 @@
         <v>49</v>
       </c>
       <c r="B49" s="1">
-        <v>138.7236716690947</v>
+        <v>136.9283650841972</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -2528,7 +2519,7 @@
         <v>50</v>
       </c>
       <c r="B50" s="1">
-        <v>138.1938042121476</v>
+        <v>136.592515364598</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -2536,7 +2527,7 @@
         <v>51</v>
       </c>
       <c r="B51" s="1">
-        <v>137.6919955565027</v>
+        <v>135.9143024792558</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -2544,7 +2535,7 @@
         <v>52</v>
       </c>
       <c r="B52" s="1">
-        <v>137.6161578341367</v>
+        <v>135.3661611959503</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -2552,7 +2543,7 @@
         <v>53</v>
       </c>
       <c r="B53" s="1">
-        <v>137.5964350349556</v>
+        <v>134.9622575960258</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -2560,7 +2551,7 @@
         <v>54</v>
       </c>
       <c r="B54" s="1">
-        <v>137.4266775413192</v>
+        <v>134.8175579437649</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -2568,7 +2559,7 @@
         <v>55</v>
       </c>
       <c r="B55" s="1">
-        <v>137.2468539544757</v>
+        <v>134.5466175948644</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -2576,7 +2567,7 @@
         <v>56</v>
       </c>
       <c r="B56" s="1">
-        <v>136.2565295561244</v>
+        <v>134.4900170489324</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -2584,7 +2575,7 @@
         <v>57</v>
       </c>
       <c r="B57" s="1">
-        <v>135.9091675644856</v>
+        <v>134.3666876823696</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -2592,7 +2583,7 @@
         <v>58</v>
       </c>
       <c r="B58" s="1">
-        <v>135.708294938195</v>
+        <v>134.0719503888682</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -2600,7 +2591,7 @@
         <v>59</v>
       </c>
       <c r="B59" s="1">
-        <v>135.6341139122364</v>
+        <v>133.9635376421299</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -2608,7 +2599,7 @@
         <v>60</v>
       </c>
       <c r="B60" s="1">
-        <v>134.923162845435</v>
+        <v>133.6860588607741</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -2616,7 +2607,7 @@
         <v>61</v>
       </c>
       <c r="B61" s="1">
-        <v>134.9224817494981</v>
+        <v>133.5256936523054</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -2624,7 +2615,7 @@
         <v>62</v>
       </c>
       <c r="B62" s="1">
-        <v>134.8222439040043</v>
+        <v>133.4616186941699</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -2632,7 +2623,7 @@
         <v>63</v>
       </c>
       <c r="B63" s="1">
-        <v>134.8209953642474</v>
+        <v>133.2660379777406</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -2640,7 +2631,7 @@
         <v>64</v>
       </c>
       <c r="B64" s="1">
-        <v>134.7029720623959</v>
+        <v>133.1460433028536</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -2648,7 +2639,7 @@
         <v>65</v>
       </c>
       <c r="B65" s="1">
-        <v>134.6647276734397</v>
+        <v>132.923734033801</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -2656,7 +2647,7 @@
         <v>66</v>
       </c>
       <c r="B66" s="1">
-        <v>134.0457650766354</v>
+        <v>132.4909788508001</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -2664,7 +2655,7 @@
         <v>67</v>
       </c>
       <c r="B67" s="1">
-        <v>133.7777466083522</v>
+        <v>132.4470662956684</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -2672,7 +2663,7 @@
         <v>68</v>
       </c>
       <c r="B68" s="1">
-        <v>133.661336542394</v>
+        <v>132.2723118663289</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -2680,7 +2671,7 @@
         <v>69</v>
       </c>
       <c r="B69" s="1">
-        <v>133.5750233627743</v>
+        <v>131.9362462026886</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -2688,7 +2679,7 @@
         <v>70</v>
       </c>
       <c r="B70" s="1">
-        <v>133.4729998160718</v>
+        <v>131.4495077251996</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -2696,7 +2687,7 @@
         <v>71</v>
       </c>
       <c r="B71" s="1">
-        <v>132.9176474337629</v>
+        <v>130.4271197850425</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -2704,7 +2695,7 @@
         <v>72</v>
       </c>
       <c r="B72" s="1">
-        <v>132.8527369998306</v>
+        <v>130.3556629502463</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2712,7 +2703,7 @@
         <v>73</v>
       </c>
       <c r="B73" s="1">
-        <v>132.7768379220713</v>
+        <v>130.0409343619319</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -2720,7 +2711,7 @@
         <v>74</v>
       </c>
       <c r="B74" s="1">
-        <v>132.6371590601599</v>
+        <v>129.6916129962184</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -2728,7 +2719,7 @@
         <v>75</v>
       </c>
       <c r="B75" s="1">
-        <v>132.0743204969195</v>
+        <v>129.6025849769854</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -2736,7 +2727,7 @@
         <v>76</v>
       </c>
       <c r="B76" s="1">
-        <v>131.5279893439846</v>
+        <v>129.0135505012744</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -2744,7 +2735,7 @@
         <v>77</v>
       </c>
       <c r="B77" s="1">
-        <v>131.5024906438925</v>
+        <v>128.9263869504151</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -2752,7 +2743,7 @@
         <v>78</v>
       </c>
       <c r="B78" s="1">
-        <v>131.363400383611</v>
+        <v>128.7032566168105</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -2760,7 +2751,7 @@
         <v>79</v>
       </c>
       <c r="B79" s="1">
-        <v>131.3479331523545</v>
+        <v>128.6792574647584</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -2768,7 +2759,7 @@
         <v>80</v>
       </c>
       <c r="B80" s="1">
-        <v>131.2446031928867</v>
+        <v>128.6560293926049</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -2776,7 +2767,7 @@
         <v>81</v>
       </c>
       <c r="B81" s="1">
-        <v>130.8148007927623</v>
+        <v>128.547522913765</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -2784,7 +2775,7 @@
         <v>82</v>
       </c>
       <c r="B82" s="1">
-        <v>130.7295189823975</v>
+        <v>128.2662881899239</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -2792,7 +2783,7 @@
         <v>83</v>
       </c>
       <c r="B83" s="1">
-        <v>130.6671392307618</v>
+        <v>127.9626825016984</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -2800,7 +2791,7 @@
         <v>84</v>
       </c>
       <c r="B84" s="1">
-        <v>130.2605944349812</v>
+        <v>127.9282355916076</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -2808,7 +2799,7 @@
         <v>85</v>
       </c>
       <c r="B85" s="1">
-        <v>130.0405810679477</v>
+        <v>127.9220819583094</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -2816,7 +2807,7 @@
         <v>86</v>
       </c>
       <c r="B86" s="1">
-        <v>130.033824091785</v>
+        <v>127.8291338363736</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -2824,7 +2815,7 @@
         <v>87</v>
       </c>
       <c r="B87" s="1">
-        <v>130.0037772771292</v>
+        <v>127.7765006058898</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -2832,7 +2823,7 @@
         <v>88</v>
       </c>
       <c r="B88" s="1">
-        <v>129.5837880651845</v>
+        <v>127.7172008396027</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -2840,7 +2831,7 @@
         <v>89</v>
       </c>
       <c r="B89" s="1">
-        <v>129.5666680134296</v>
+        <v>127.7151742887338</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -2848,7 +2839,7 @@
         <v>90</v>
       </c>
       <c r="B90" s="1">
-        <v>129.4427305635469</v>
+        <v>127.6277285272693</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -2856,7 +2847,7 @@
         <v>91</v>
       </c>
       <c r="B91" s="1">
-        <v>129.3100396723562</v>
+        <v>127.3983371195367</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -2864,7 +2855,7 @@
         <v>92</v>
       </c>
       <c r="B92" s="1">
-        <v>129.2571142878984</v>
+        <v>127.394654573195</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -2872,7 +2863,7 @@
         <v>93</v>
       </c>
       <c r="B93" s="1">
-        <v>129.2066536885204</v>
+        <v>127.1923400725596</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -2880,7 +2871,7 @@
         <v>94</v>
       </c>
       <c r="B94" s="1">
-        <v>129.032909483407</v>
+        <v>126.8416658119507</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -2888,7 +2879,7 @@
         <v>95</v>
       </c>
       <c r="B95" s="1">
-        <v>129.0133920079554</v>
+        <v>126.7177553827186</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -2896,7 +2887,7 @@
         <v>96</v>
       </c>
       <c r="B96" s="1">
-        <v>128.7632057633027</v>
+        <v>126.5274631205059</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -2904,7 +2895,7 @@
         <v>97</v>
       </c>
       <c r="B97" s="1">
-        <v>128.6856382568543</v>
+        <v>126.2219024602546</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -2912,7 +2903,7 @@
         <v>98</v>
       </c>
       <c r="B98" s="1">
-        <v>128.406150717161</v>
+        <v>126.0693017560299</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -2920,7 +2911,7 @@
         <v>99</v>
       </c>
       <c r="B99" s="1">
-        <v>128.2898609918281</v>
+        <v>126.0570037218695</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -2928,7 +2919,7 @@
         <v>100</v>
       </c>
       <c r="B100" s="1">
-        <v>128.2121808954344</v>
+        <v>126.0043558060006</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -2936,7 +2927,7 @@
         <v>101</v>
       </c>
       <c r="B101" s="1">
-        <v>128.2064210271663</v>
+        <v>125.8538735450671</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -2944,7 +2935,7 @@
         <v>102</v>
       </c>
       <c r="B102" s="1">
-        <v>128.1785188283537</v>
+        <v>125.715893088324</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -2952,7 +2943,7 @@
         <v>103</v>
       </c>
       <c r="B103" s="1">
-        <v>128.0456747602422</v>
+        <v>125.6040853798599</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -2960,7 +2951,7 @@
         <v>104</v>
       </c>
       <c r="B104" s="1">
-        <v>127.8531620145949</v>
+        <v>125.4054393977862</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -2968,7 +2959,7 @@
         <v>105</v>
       </c>
       <c r="B105" s="1">
-        <v>127.6916827965863</v>
+        <v>125.0726063784428</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -2976,7 +2967,7 @@
         <v>106</v>
       </c>
       <c r="B106" s="1">
-        <v>127.4356076082371</v>
+        <v>124.8637330331905</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -2984,7 +2975,7 @@
         <v>107</v>
       </c>
       <c r="B107" s="1">
-        <v>127.3983371195367</v>
+        <v>124.8126376544796</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -2992,7 +2983,7 @@
         <v>108</v>
       </c>
       <c r="B108" s="1">
-        <v>127.2324382390233</v>
+        <v>124.5731568584354</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -3000,7 +2991,7 @@
         <v>109</v>
       </c>
       <c r="B109" s="1">
-        <v>127.1985120234847</v>
+        <v>124.550467574374</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -3008,7 +2999,7 @@
         <v>110</v>
       </c>
       <c r="B110" s="1">
-        <v>127.1004573738192</v>
+        <v>124.5146387559315</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -3016,7 +3007,7 @@
         <v>111</v>
       </c>
       <c r="B111" s="1">
-        <v>126.985876548102</v>
+        <v>124.5032678030836</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -3024,7 +3015,7 @@
         <v>112</v>
       </c>
       <c r="B112" s="1">
-        <v>126.8126702840656</v>
+        <v>124.2615675856345</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -3032,7 +3023,7 @@
         <v>113</v>
       </c>
       <c r="B113" s="1">
-        <v>126.7506147376815</v>
+        <v>124.2299640559104</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -3040,7 +3031,7 @@
         <v>114</v>
       </c>
       <c r="B114" s="1">
-        <v>126.4365163530184</v>
+        <v>124.0000633677746</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -3048,7 +3039,7 @@
         <v>115</v>
       </c>
       <c r="B115" s="1">
-        <v>126.4094617770374</v>
+        <v>123.8388402249231</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -3056,7 +3047,7 @@
         <v>116</v>
       </c>
       <c r="B116" s="1">
-        <v>126.3374451950819</v>
+        <v>123.668739053599</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -3064,7 +3055,7 @@
         <v>117</v>
       </c>
       <c r="B117" s="1">
-        <v>126.2679433413379</v>
+        <v>123.5484722417994</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -3072,7 +3063,7 @@
         <v>118</v>
       </c>
       <c r="B118" s="1">
-        <v>126.173736662738</v>
+        <v>123.5458829022424</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -3080,7 +3071,7 @@
         <v>119</v>
       </c>
       <c r="B119" s="1">
-        <v>126.0895369497327</v>
+        <v>123.4368216995505</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -3088,7 +3079,7 @@
         <v>120</v>
       </c>
       <c r="B120" s="1">
-        <v>126.0333016365484</v>
+        <v>123.3862680508244</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -3096,7 +3087,7 @@
         <v>121</v>
       </c>
       <c r="B121" s="1">
-        <v>125.8892274563426</v>
+        <v>123.3848488089012</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -3104,7 +3095,7 @@
         <v>122</v>
       </c>
       <c r="B122" s="1">
-        <v>125.5863169866949</v>
+        <v>123.3279400374712</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -3112,7 +3103,7 @@
         <v>123</v>
       </c>
       <c r="B123" s="1">
-        <v>125.5312013648904</v>
+        <v>123.305271299904</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -3120,7 +3111,7 @@
         <v>124</v>
       </c>
       <c r="B124" s="1">
-        <v>125.332925221772</v>
+        <v>123.1959709835127</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -3128,7 +3119,7 @@
         <v>125</v>
       </c>
       <c r="B125" s="1">
-        <v>125.1609277827849</v>
+        <v>123.1827814337294</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -3136,7 +3127,7 @@
         <v>126</v>
       </c>
       <c r="B126" s="1">
-        <v>125.0462148447059</v>
+        <v>122.9966765267123</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -3144,7 +3135,7 @@
         <v>127</v>
       </c>
       <c r="B127" s="1">
-        <v>125.0193762936817</v>
+        <v>122.9943396630883</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -3152,7 +3143,7 @@
         <v>128</v>
       </c>
       <c r="B128" s="1">
-        <v>124.9889929642181</v>
+        <v>122.9712342230164</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -3160,7 +3151,7 @@
         <v>129</v>
       </c>
       <c r="B129" s="1">
-        <v>124.8927017652516</v>
+        <v>122.864535977188</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -3168,7 +3159,7 @@
         <v>130</v>
       </c>
       <c r="B130" s="1">
-        <v>124.8637330331905</v>
+        <v>122.7834281838096</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -3176,7 +3167,7 @@
         <v>131</v>
       </c>
       <c r="B131" s="1">
-        <v>124.7726592660137</v>
+        <v>122.5917585453112</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -3184,7 +3175,7 @@
         <v>132</v>
       </c>
       <c r="B132" s="1">
-        <v>124.7464514213292</v>
+        <v>122.5837849073224</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -3192,7 +3183,7 @@
         <v>133</v>
       </c>
       <c r="B133" s="1">
-        <v>124.6587897203242</v>
+        <v>122.5293010629016</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -3200,7 +3191,7 @@
         <v>134</v>
       </c>
       <c r="B134" s="1">
-        <v>124.6195427512572</v>
+        <v>122.5122702423444</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -3208,7 +3199,7 @@
         <v>135</v>
       </c>
       <c r="B135" s="1">
-        <v>124.5322927556025</v>
+        <v>122.4725065044887</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -3216,7 +3207,7 @@
         <v>136</v>
       </c>
       <c r="B136" s="1">
-        <v>124.4386611660897</v>
+        <v>122.4128335717883</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -3224,7 +3215,7 @@
         <v>137</v>
       </c>
       <c r="B137" s="1">
-        <v>124.4317701969513</v>
+        <v>122.2683879956044</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -3232,7 +3223,7 @@
         <v>138</v>
       </c>
       <c r="B138" s="1">
-        <v>124.2641166795534</v>
+        <v>122.141513363329</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -3240,7 +3231,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="1">
-        <v>124.1850491159853</v>
+        <v>122.1257377432336</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -3248,7 +3239,7 @@
         <v>140</v>
       </c>
       <c r="B140" s="1">
-        <v>124.0504263919983</v>
+        <v>122.056130077089</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -3256,7 +3247,7 @@
         <v>141</v>
       </c>
       <c r="B141" s="1">
-        <v>124.0438977590193</v>
+        <v>121.9957582280899</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -3264,7 +3255,7 @@
         <v>142</v>
       </c>
       <c r="B142" s="1">
-        <v>123.8657637971622</v>
+        <v>121.9780990298927</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -3272,7 +3263,7 @@
         <v>143</v>
       </c>
       <c r="B143" s="1">
-        <v>123.8106313031927</v>
+        <v>121.8255829376503</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -3280,7 +3271,7 @@
         <v>144</v>
       </c>
       <c r="B144" s="1">
-        <v>123.7486524590439</v>
+        <v>121.8215483287426</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -3288,7 +3279,7 @@
         <v>145</v>
       </c>
       <c r="B145" s="1">
-        <v>123.7058570200789</v>
+        <v>121.7831227512964</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -3296,7 +3287,7 @@
         <v>146</v>
       </c>
       <c r="B146" s="1">
-        <v>123.5423512594482</v>
+        <v>121.7710477407611</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -3304,7 +3295,7 @@
         <v>147</v>
       </c>
       <c r="B147" s="1">
-        <v>123.4081148941395</v>
+        <v>121.7074594614611</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -3312,7 +3303,7 @@
         <v>148</v>
       </c>
       <c r="B148" s="1">
-        <v>123.3742631579212</v>
+        <v>121.4045504396694</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -3320,7 +3311,7 @@
         <v>149</v>
       </c>
       <c r="B149" s="1">
-        <v>123.2843931743379</v>
+        <v>121.3931285423671</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -3328,7 +3319,7 @@
         <v>150</v>
       </c>
       <c r="B150" s="1">
-        <v>123.2174161086014</v>
+        <v>121.0492947263017</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -3336,7 +3327,7 @@
         <v>151</v>
       </c>
       <c r="B151" s="1">
-        <v>123.1959709835127</v>
+        <v>120.9292866121037</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -3344,7 +3335,7 @@
         <v>152</v>
       </c>
       <c r="B152" s="1">
-        <v>123.0638916518348</v>
+        <v>120.8860540239888</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -3352,7 +3343,7 @@
         <v>153</v>
       </c>
       <c r="B153" s="1">
-        <v>123.0465017009082</v>
+        <v>120.8851765070617</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -3360,7 +3351,7 @@
         <v>154</v>
       </c>
       <c r="B154" s="1">
-        <v>122.9648207610722</v>
+        <v>120.8849228294593</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -3368,7 +3359,7 @@
         <v>155</v>
       </c>
       <c r="B155" s="1">
-        <v>122.837436758697</v>
+        <v>120.8783791282792</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -3376,7 +3367,7 @@
         <v>156</v>
       </c>
       <c r="B156" s="1">
-        <v>122.7723346629056</v>
+        <v>120.7985765442389</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -3384,7 +3375,7 @@
         <v>157</v>
       </c>
       <c r="B157" s="1">
-        <v>122.7405259057571</v>
+        <v>120.7014645555427</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -3392,7 +3383,7 @@
         <v>158</v>
       </c>
       <c r="B158" s="1">
-        <v>122.6976085779776</v>
+        <v>120.6460449372903</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -3400,7 +3391,7 @@
         <v>159</v>
       </c>
       <c r="B159" s="1">
-        <v>122.6925101913907</v>
+        <v>120.6088363299458</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -3408,7 +3399,7 @@
         <v>160</v>
       </c>
       <c r="B160" s="1">
-        <v>122.6794025343286</v>
+        <v>120.5439467369645</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -3416,7 +3407,7 @@
         <v>161</v>
       </c>
       <c r="B161" s="1">
-        <v>122.6669422581622</v>
+        <v>120.5353654262292</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -3424,7 +3415,7 @@
         <v>162</v>
       </c>
       <c r="B162" s="1">
-        <v>122.6352002910656</v>
+        <v>120.5320213285974</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -3432,7 +3423,7 @@
         <v>163</v>
       </c>
       <c r="B163" s="1">
-        <v>122.5645534028136</v>
+        <v>120.4849248849437</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -3440,7 +3431,7 @@
         <v>164</v>
       </c>
       <c r="B164" s="1">
-        <v>122.5007832214279</v>
+        <v>120.4580947504674</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -3448,7 +3439,7 @@
         <v>165</v>
       </c>
       <c r="B165" s="1">
-        <v>122.4881458287939</v>
+        <v>120.3493494130659</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -3456,7 +3447,7 @@
         <v>166</v>
       </c>
       <c r="B166" s="1">
-        <v>122.4707961866203</v>
+        <v>120.3313382413647</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -3464,7 +3455,7 @@
         <v>167</v>
       </c>
       <c r="B167" s="1">
-        <v>122.4104087785523</v>
+        <v>120.2911771485788</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -3472,7 +3463,7 @@
         <v>168</v>
       </c>
       <c r="B168" s="1">
-        <v>122.3751230667579</v>
+        <v>120.2447359848294</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -3480,7 +3471,7 @@
         <v>169</v>
       </c>
       <c r="B169" s="1">
-        <v>122.3749542160245</v>
+        <v>120.2219904797234</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -3488,7 +3479,7 @@
         <v>170</v>
       </c>
       <c r="B170" s="1">
-        <v>122.3646873901205</v>
+        <v>120.2041449226811</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -3496,7 +3487,7 @@
         <v>171</v>
       </c>
       <c r="B171" s="1">
-        <v>122.3625055507816</v>
+        <v>120.1925422698804</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -3504,7 +3495,7 @@
         <v>172</v>
       </c>
       <c r="B172" s="1">
-        <v>122.3332484035391</v>
+        <v>120.1868234991401</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -3512,7 +3503,7 @@
         <v>173</v>
       </c>
       <c r="B173" s="1">
-        <v>122.3293545123131</v>
+        <v>120.1381950350006</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -3520,7 +3511,7 @@
         <v>174</v>
       </c>
       <c r="B174" s="1">
-        <v>122.2879690757544</v>
+        <v>119.951807175986</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -3528,7 +3519,7 @@
         <v>175</v>
       </c>
       <c r="B175" s="1">
-        <v>122.1798265065437</v>
+        <v>119.9340911340368</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -3536,7 +3527,7 @@
         <v>176</v>
       </c>
       <c r="B176" s="1">
-        <v>122.1602474375711</v>
+        <v>119.9026344942312</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -3544,7 +3535,7 @@
         <v>177</v>
       </c>
       <c r="B177" s="1">
-        <v>121.9957582280899</v>
+        <v>119.8702289670201</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -3552,7 +3543,7 @@
         <v>178</v>
       </c>
       <c r="B178" s="1">
-        <v>121.905323164701</v>
+        <v>119.7635788745506</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -3560,7 +3551,7 @@
         <v>179</v>
       </c>
       <c r="B179" s="1">
-        <v>121.7883288830511</v>
+        <v>119.6989500808227</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -3568,7 +3559,7 @@
         <v>180</v>
       </c>
       <c r="B180" s="1">
-        <v>121.7751601394658</v>
+        <v>119.6934822807318</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -3576,7 +3567,7 @@
         <v>181</v>
       </c>
       <c r="B181" s="1">
-        <v>121.7189798364885</v>
+        <v>119.6506372500036</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -3584,7 +3575,7 @@
         <v>182</v>
       </c>
       <c r="B182" s="1">
-        <v>121.6291743829991</v>
+        <v>119.6450510563285</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -3592,7 +3583,7 @@
         <v>183</v>
       </c>
       <c r="B183" s="1">
-        <v>121.5498197485869</v>
+        <v>119.5952867195704</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -3600,7 +3591,7 @@
         <v>184</v>
       </c>
       <c r="B184" s="1">
-        <v>121.4696861130258</v>
+        <v>119.5681680548279</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -3608,7 +3599,7 @@
         <v>185</v>
       </c>
       <c r="B185" s="1">
-        <v>121.4510582343672</v>
+        <v>119.5192672537667</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -3616,7 +3607,7 @@
         <v>186</v>
       </c>
       <c r="B186" s="1">
-        <v>121.3823181131021</v>
+        <v>119.5129140095953</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -3624,7 +3615,7 @@
         <v>187</v>
       </c>
       <c r="B187" s="1">
-        <v>121.3408389133216</v>
+        <v>119.5110037712802</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -3632,7 +3623,7 @@
         <v>188</v>
       </c>
       <c r="B188" s="1">
-        <v>121.1877249308588</v>
+        <v>119.4883720797105</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -3640,7 +3631,7 @@
         <v>189</v>
       </c>
       <c r="B189" s="1">
-        <v>121.008309152316</v>
+        <v>119.4804733203511</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -3648,7 +3639,7 @@
         <v>190</v>
       </c>
       <c r="B190" s="1">
-        <v>121.0047664874766</v>
+        <v>119.4339143089417</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -3656,7 +3647,7 @@
         <v>191</v>
       </c>
       <c r="B191" s="1">
-        <v>120.9896702141069</v>
+        <v>119.3759743462468</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -3664,7 +3655,7 @@
         <v>192</v>
       </c>
       <c r="B192" s="1">
-        <v>120.8618380809304</v>
+        <v>119.3612319430989</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -3672,7 +3663,7 @@
         <v>193</v>
       </c>
       <c r="B193" s="1">
-        <v>120.643971220224</v>
+        <v>119.3318846720279</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -3680,7 +3671,7 @@
         <v>194</v>
       </c>
       <c r="B194" s="1">
-        <v>120.435449966005</v>
+        <v>119.2943664740329</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -3688,7 +3679,7 @@
         <v>195</v>
       </c>
       <c r="B195" s="1">
-        <v>120.3882329248872</v>
+        <v>119.248980507479</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -3696,7 +3687,7 @@
         <v>196</v>
       </c>
       <c r="B196" s="1">
-        <v>120.3695544835843</v>
+        <v>119.2257586010744</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -3704,7 +3695,7 @@
         <v>197</v>
       </c>
       <c r="B197" s="1">
-        <v>120.3685133900473</v>
+        <v>119.1640070416278</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -3712,7 +3703,7 @@
         <v>198</v>
       </c>
       <c r="B198" s="1">
-        <v>120.3493494130659</v>
+        <v>119.0924529099815</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -3720,7 +3711,7 @@
         <v>199</v>
       </c>
       <c r="B199" s="1">
-        <v>120.3384928381095</v>
+        <v>119.0708132760417</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -3728,7 +3719,7 @@
         <v>200</v>
       </c>
       <c r="B200" s="1">
-        <v>120.3373865913415</v>
+        <v>119.0503613897663</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -3736,7 +3727,7 @@
         <v>201</v>
       </c>
       <c r="B201" s="1">
-        <v>120.3100240308019</v>
+        <v>119.0050871019621</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -3744,7 +3735,7 @@
         <v>202</v>
       </c>
       <c r="B202" s="1">
-        <v>120.2745108561388</v>
+        <v>118.8688114011477</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -3752,7 +3743,7 @@
         <v>203</v>
       </c>
       <c r="B203" s="1">
-        <v>120.2640426845117</v>
+        <v>118.8555361193658</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -3760,7 +3751,7 @@
         <v>204</v>
       </c>
       <c r="B204" s="1">
-        <v>120.2605435008535</v>
+        <v>118.8502592154174</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -3768,7 +3759,7 @@
         <v>205</v>
       </c>
       <c r="B205" s="1">
-        <v>120.2526852711057</v>
+        <v>118.776933880366</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -3776,7 +3767,7 @@
         <v>206</v>
       </c>
       <c r="B206" s="1">
-        <v>120.2186211903905</v>
+        <v>118.6349737431699</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -3784,7 +3775,7 @@
         <v>207</v>
       </c>
       <c r="B207" s="1">
-        <v>120.1565316734505</v>
+        <v>118.5966909520058</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -3792,7 +3783,7 @@
         <v>208</v>
       </c>
       <c r="B208" s="1">
-        <v>120.1490715176269</v>
+        <v>118.5105598822379</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -3800,7 +3791,7 @@
         <v>209</v>
       </c>
       <c r="B209" s="1">
-        <v>120.0916146162473</v>
+        <v>118.4733824000225</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -3808,7 +3799,7 @@
         <v>210</v>
       </c>
       <c r="B210" s="1">
-        <v>120.0240229256152</v>
+        <v>118.4654100931825</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -3816,7 +3807,7 @@
         <v>211</v>
       </c>
       <c r="B211" s="1">
-        <v>119.9977801440651</v>
+        <v>118.3832282699435</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -3824,7 +3815,7 @@
         <v>212</v>
       </c>
       <c r="B212" s="1">
-        <v>119.9928676709577</v>
+        <v>118.1907801877446</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -3832,7 +3823,7 @@
         <v>213</v>
       </c>
       <c r="B213" s="1">
-        <v>119.9685370982104</v>
+        <v>118.1401424599763</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -3840,7 +3831,7 @@
         <v>214</v>
       </c>
       <c r="B214" s="1">
-        <v>119.9313359841115</v>
+        <v>118.1140344711499</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -3848,7 +3839,7 @@
         <v>215</v>
       </c>
       <c r="B215" s="1">
-        <v>119.9012665412881</v>
+        <v>118.1046743330036</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -3856,7 +3847,7 @@
         <v>216</v>
       </c>
       <c r="B216" s="1">
-        <v>119.8763471795926</v>
+        <v>118.0557348746212</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -3864,7 +3855,7 @@
         <v>217</v>
       </c>
       <c r="B217" s="1">
-        <v>119.8222693468075</v>
+        <v>118.0431157854989</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -3872,7 +3863,7 @@
         <v>218</v>
       </c>
       <c r="B218" s="1">
-        <v>119.7536921220655</v>
+        <v>117.943677384935</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -3880,7 +3871,7 @@
         <v>219</v>
       </c>
       <c r="B219" s="1">
-        <v>119.6718655748274</v>
+        <v>117.9428974895677</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -3888,7 +3879,7 @@
         <v>220</v>
       </c>
       <c r="B220" s="1">
-        <v>119.6586098908239</v>
+        <v>117.9208461733467</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -3896,7 +3887,7 @@
         <v>221</v>
       </c>
       <c r="B221" s="1">
-        <v>119.6044701418876</v>
+        <v>117.7474988823152</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -3904,7 +3895,7 @@
         <v>222</v>
       </c>
       <c r="B222" s="1">
-        <v>119.4928547295332</v>
+        <v>117.67696045809</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -3912,7 +3903,7 @@
         <v>223</v>
       </c>
       <c r="B223" s="1">
-        <v>119.4713022427287</v>
+        <v>117.6715824445915</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -3920,7 +3911,7 @@
         <v>224</v>
       </c>
       <c r="B224" s="1">
-        <v>119.3870872101094</v>
+        <v>117.6496924178988</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -3928,7 +3919,7 @@
         <v>225</v>
       </c>
       <c r="B225" s="1">
-        <v>119.2782332371309</v>
+        <v>117.6134122834298</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -3936,7 +3927,7 @@
         <v>226</v>
       </c>
       <c r="B226" s="1">
-        <v>119.2383418487252</v>
+        <v>117.5706745442423</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -3944,7 +3935,7 @@
         <v>227</v>
       </c>
       <c r="B227" s="1">
-        <v>119.2267736841242</v>
+        <v>117.5443957243314</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -3952,7 +3943,7 @@
         <v>228</v>
       </c>
       <c r="B228" s="1">
-        <v>119.1602800750887</v>
+        <v>117.5396245810818</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -3960,7 +3951,7 @@
         <v>229</v>
       </c>
       <c r="B229" s="1">
-        <v>119.0988998710212</v>
+        <v>117.4247291262709</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -3968,7 +3959,7 @@
         <v>230</v>
       </c>
       <c r="B230" s="1">
-        <v>119.0336299063324</v>
+        <v>117.3974374679237</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -3976,7 +3967,7 @@
         <v>231</v>
       </c>
       <c r="B231" s="1">
-        <v>118.9286611999692</v>
+        <v>117.3742444753183</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -3984,7 +3975,7 @@
         <v>232</v>
       </c>
       <c r="B232" s="1">
-        <v>118.8574642875544</v>
+        <v>117.2805659918371</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -3992,7 +3983,7 @@
         <v>233</v>
       </c>
       <c r="B233" s="1">
-        <v>118.7294780529284</v>
+        <v>117.2381895982186</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -4000,7 +3991,7 @@
         <v>234</v>
       </c>
       <c r="B234" s="1">
-        <v>118.7116549987861</v>
+        <v>117.1716700084408</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -4008,7 +3999,7 @@
         <v>235</v>
       </c>
       <c r="B235" s="1">
-        <v>118.6650922277848</v>
+        <v>117.1327228515378</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -4016,7 +4007,7 @@
         <v>236</v>
       </c>
       <c r="B236" s="1">
-        <v>118.6194543334791</v>
+        <v>117.0123186602144</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -4024,7 +4015,7 @@
         <v>237</v>
       </c>
       <c r="B237" s="1">
-        <v>118.5185972011887</v>
+        <v>116.9782312562009</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -4032,7 +4023,7 @@
         <v>238</v>
       </c>
       <c r="B238" s="1">
-        <v>118.5062675489194</v>
+        <v>116.9518969308501</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -4040,7 +4031,7 @@
         <v>239</v>
       </c>
       <c r="B239" s="1">
-        <v>118.471727942547</v>
+        <v>116.9510457662572</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -4048,7 +4039,7 @@
         <v>240</v>
       </c>
       <c r="B240" s="1">
-        <v>118.4473235130647</v>
+        <v>116.8952594198103</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -4056,7 +4047,7 @@
         <v>241</v>
       </c>
       <c r="B241" s="1">
-        <v>118.4187044492172</v>
+        <v>116.8909063447194</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -4064,7 +4055,7 @@
         <v>242</v>
       </c>
       <c r="B242" s="1">
-        <v>118.4109808928197</v>
+        <v>116.8644429339833</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -4072,7 +4063,7 @@
         <v>243</v>
       </c>
       <c r="B243" s="1">
-        <v>118.336975582168</v>
+        <v>116.858725267481</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -4080,7 +4071,7 @@
         <v>244</v>
       </c>
       <c r="B244" s="1">
-        <v>118.3148450230387</v>
+        <v>116.857557352702</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -4088,7 +4079,7 @@
         <v>245</v>
       </c>
       <c r="B245" s="1">
-        <v>118.2836626612427</v>
+        <v>116.8168388307438</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -4096,7 +4087,7 @@
         <v>246</v>
       </c>
       <c r="B246" s="1">
-        <v>118.277576141401</v>
+        <v>116.633427264392</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -4104,7 +4095,7 @@
         <v>247</v>
       </c>
       <c r="B247" s="1">
-        <v>118.1961820525824</v>
+        <v>116.6197232024466</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -4112,7 +4103,7 @@
         <v>248</v>
       </c>
       <c r="B248" s="1">
-        <v>118.1703137788589</v>
+        <v>116.6156367141486</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -4120,7 +4111,7 @@
         <v>249</v>
       </c>
       <c r="B249" s="1">
-        <v>118.1544722429556</v>
+        <v>116.6016504909738</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -4128,7 +4119,7 @@
         <v>250</v>
       </c>
       <c r="B250" s="1">
-        <v>118.1377849326235</v>
+        <v>116.5326566308975</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -4136,7 +4127,7 @@
         <v>251</v>
       </c>
       <c r="B251" s="1">
-        <v>118.0402594775313</v>
+        <v>116.4615072753388</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -4144,7 +4135,7 @@
         <v>252</v>
       </c>
       <c r="B252" s="1">
-        <v>118.0272086560831</v>
+        <v>116.3854324621948</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -4152,7 +4143,7 @@
         <v>253</v>
       </c>
       <c r="B253" s="1">
-        <v>118.005893643287</v>
+        <v>116.382876266564</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -4160,7 +4151,7 @@
         <v>254</v>
       </c>
       <c r="B254" s="1">
-        <v>117.9852417999835</v>
+        <v>116.2890092798065</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -4168,7 +4159,7 @@
         <v>255</v>
       </c>
       <c r="B255" s="1">
-        <v>117.9643783027335</v>
+        <v>116.268030942691</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -4176,7 +4167,7 @@
         <v>256</v>
       </c>
       <c r="B256" s="1">
-        <v>117.9027912167108</v>
+        <v>116.2605385334144</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -4184,7 +4175,7 @@
         <v>257</v>
       </c>
       <c r="B257" s="1">
-        <v>117.8733865917665</v>
+        <v>116.1979522950865</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -4192,7 +4183,7 @@
         <v>258</v>
       </c>
       <c r="B258" s="1">
-        <v>117.8631427938996</v>
+        <v>116.1921781322511</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -4200,7 +4191,7 @@
         <v>259</v>
       </c>
       <c r="B259" s="1">
-        <v>117.8300645646352</v>
+        <v>116.1916545405791</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -4208,7 +4199,7 @@
         <v>260</v>
       </c>
       <c r="B260" s="1">
-        <v>117.7593741758366</v>
+        <v>116.1125041396258</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -4216,7 +4207,7 @@
         <v>261</v>
       </c>
       <c r="B261" s="1">
-        <v>117.7524559017542</v>
+        <v>116.1124817067065</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -4224,7 +4215,7 @@
         <v>262</v>
       </c>
       <c r="B262" s="1">
-        <v>117.6961243521119</v>
+        <v>116.0430780064358</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -4232,7 +4223,7 @@
         <v>263</v>
       </c>
       <c r="B263" s="1">
-        <v>117.6707026933316</v>
+        <v>116.0331152607371</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -4240,7 +4231,7 @@
         <v>264</v>
       </c>
       <c r="B264" s="1">
-        <v>117.6355321472581</v>
+        <v>115.9829945754496</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -4248,7 +4239,7 @@
         <v>265</v>
       </c>
       <c r="B265" s="1">
-        <v>117.6226741312743</v>
+        <v>115.9722962587194</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -4256,7 +4247,7 @@
         <v>266</v>
       </c>
       <c r="B266" s="1">
-        <v>117.6075033409853</v>
+        <v>115.9666534081664</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -4264,7 +4255,7 @@
         <v>267</v>
       </c>
       <c r="B267" s="1">
-        <v>117.598799610966</v>
+        <v>115.9645457955495</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -4272,7 +4263,7 @@
         <v>268</v>
       </c>
       <c r="B268" s="1">
-        <v>117.5711200601933</v>
+        <v>115.9493209966669</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -4280,7 +4271,7 @@
         <v>269</v>
       </c>
       <c r="B269" s="1">
-        <v>117.5348912454271</v>
+        <v>115.9451195756687</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -4288,7 +4279,7 @@
         <v>270</v>
       </c>
       <c r="B270" s="1">
-        <v>117.5191824512938</v>
+        <v>115.9161205468463</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -4296,7 +4287,7 @@
         <v>271</v>
       </c>
       <c r="B271" s="1">
-        <v>117.4925877701445</v>
+        <v>115.8520566416571</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -4304,7 +4295,7 @@
         <v>272</v>
       </c>
       <c r="B272" s="1">
-        <v>117.4865144918828</v>
+        <v>115.843489566317</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -4312,7 +4303,7 @@
         <v>273</v>
       </c>
       <c r="B273" s="1">
-        <v>117.4492994203681</v>
+        <v>115.8269607868227</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -4320,7 +4311,7 @@
         <v>274</v>
       </c>
       <c r="B274" s="1">
-        <v>117.4337446362687</v>
+        <v>115.778608031954</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -4328,7 +4319,7 @@
         <v>275</v>
       </c>
       <c r="B275" s="1">
-        <v>117.4174792500405</v>
+        <v>115.7627474825556</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -4336,7 +4327,7 @@
         <v>276</v>
       </c>
       <c r="B276" s="1">
-        <v>117.288509107901</v>
+        <v>115.7198100288349</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -4344,7 +4335,7 @@
         <v>277</v>
       </c>
       <c r="B277" s="1">
-        <v>117.2865342531691</v>
+        <v>115.6800419170936</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -4352,7 +4343,7 @@
         <v>278</v>
       </c>
       <c r="B278" s="1">
-        <v>117.2736297783211</v>
+        <v>115.6720876387399</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -4360,7 +4351,7 @@
         <v>279</v>
       </c>
       <c r="B279" s="1">
-        <v>117.2681884439967</v>
+        <v>115.6534615972661</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -4368,7 +4359,7 @@
         <v>280</v>
       </c>
       <c r="B280" s="1">
-        <v>117.25787183182</v>
+        <v>115.6016532019411</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -4376,7 +4367,7 @@
         <v>281</v>
       </c>
       <c r="B281" s="1">
-        <v>117.2536709758113</v>
+        <v>115.5430631534529</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -4384,7 +4375,7 @@
         <v>282</v>
       </c>
       <c r="B282" s="1">
-        <v>117.1867799720908</v>
+        <v>115.5041717422559</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -4392,7 +4383,7 @@
         <v>283</v>
       </c>
       <c r="B283" s="1">
-        <v>117.1784698968149</v>
+        <v>115.5003801093591</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -4400,7 +4391,7 @@
         <v>284</v>
       </c>
       <c r="B284" s="1">
-        <v>117.0992421491662</v>
+        <v>115.500275806657</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -4408,7 +4399,7 @@
         <v>285</v>
       </c>
       <c r="B285" s="1">
-        <v>117.0400744034751</v>
+        <v>115.4754871557412</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -4416,7 +4407,7 @@
         <v>286</v>
       </c>
       <c r="B286" s="1">
-        <v>117.0331529126549</v>
+        <v>115.4518208872402</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -4424,7 +4415,7 @@
         <v>287</v>
       </c>
       <c r="B287" s="1">
-        <v>117.0328298125633</v>
+        <v>115.4493879722331</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -4432,7 +4423,7 @@
         <v>288</v>
       </c>
       <c r="B288" s="1">
-        <v>117.0153215634094</v>
+        <v>115.4367081060589</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -4440,7 +4431,7 @@
         <v>289</v>
       </c>
       <c r="B289" s="1">
-        <v>117.0073665088496</v>
+        <v>115.4170716345388</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -4448,7 +4439,7 @@
         <v>290</v>
       </c>
       <c r="B290" s="1">
-        <v>117.0048362188108</v>
+        <v>115.38408478626</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -4456,7 +4447,7 @@
         <v>291</v>
       </c>
       <c r="B291" s="1">
-        <v>116.9495401710114</v>
+        <v>115.2888126185293</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -4464,7 +4455,7 @@
         <v>292</v>
       </c>
       <c r="B292" s="1">
-        <v>116.8116136601508</v>
+        <v>115.2692105369705</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -4472,7 +4463,7 @@
         <v>293</v>
       </c>
       <c r="B293" s="1">
-        <v>116.7988165487802</v>
+        <v>115.2691468518684</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -4480,7 +4471,7 @@
         <v>294</v>
       </c>
       <c r="B294" s="1">
-        <v>116.6757169941372</v>
+        <v>115.2398594456369</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -4488,7 +4479,7 @@
         <v>295</v>
       </c>
       <c r="B295" s="1">
-        <v>116.5933162781765</v>
+        <v>115.2085044084304</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -4496,7 +4487,7 @@
         <v>296</v>
       </c>
       <c r="B296" s="1">
-        <v>116.5924932858657</v>
+        <v>115.1823378380629</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -4504,7 +4495,7 @@
         <v>297</v>
       </c>
       <c r="B297" s="1">
-        <v>116.5738642845721</v>
+        <v>115.180387928908</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -4512,7 +4503,7 @@
         <v>298</v>
       </c>
       <c r="B298" s="1">
-        <v>116.5439195930108</v>
+        <v>115.0934638464888</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -4520,7 +4511,7 @@
         <v>299</v>
       </c>
       <c r="B299" s="1">
-        <v>116.511590943913</v>
+        <v>115.0829652515378</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -4528,7 +4519,7 @@
         <v>300</v>
       </c>
       <c r="B300" s="1">
-        <v>116.4769034851241</v>
+        <v>114.9750759159557</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -4536,7 +4527,7 @@
         <v>301</v>
       </c>
       <c r="B301" s="1">
-        <v>116.4746066958744</v>
+        <v>114.9733605701638</v>
       </c>
     </row>
     <row r="302" spans="1:2">
@@ -4544,7 +4535,7 @@
         <v>302</v>
       </c>
       <c r="B302" s="1">
-        <v>116.4542594480357</v>
+        <v>114.9442202473247</v>
       </c>
     </row>
     <row r="303" spans="1:2">
@@ -4552,7 +4543,7 @@
         <v>303</v>
       </c>
       <c r="B303" s="1">
-        <v>116.4454871364777</v>
+        <v>114.9161797895391</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -4560,7 +4551,7 @@
         <v>304</v>
       </c>
       <c r="B304" s="1">
-        <v>116.4245517242312</v>
+        <v>114.9024529511684</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -4568,7 +4559,7 @@
         <v>305</v>
       </c>
       <c r="B305" s="1">
-        <v>116.4165237175696</v>
+        <v>114.8710226533359</v>
       </c>
     </row>
     <row r="306" spans="1:2">
@@ -4576,7 +4567,7 @@
         <v>306</v>
       </c>
       <c r="B306" s="1">
-        <v>116.3912257732237</v>
+        <v>114.864023123281</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -4584,7 +4575,7 @@
         <v>307</v>
       </c>
       <c r="B307" s="1">
-        <v>116.3886222876035</v>
+        <v>114.8565047621045</v>
       </c>
     </row>
     <row r="308" spans="1:2">
@@ -4592,7 +4583,7 @@
         <v>308</v>
       </c>
       <c r="B308" s="1">
-        <v>116.3693774519284</v>
+        <v>114.8545989349276</v>
       </c>
     </row>
     <row r="309" spans="1:2">
@@ -4600,7 +4591,7 @@
         <v>309</v>
       </c>
       <c r="B309" s="1">
-        <v>116.3647686115201</v>
+        <v>114.8538532862419</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -4608,7 +4599,7 @@
         <v>310</v>
       </c>
       <c r="B310" s="1">
-        <v>116.3647527767874</v>
+        <v>114.768979160267</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -4616,7 +4607,7 @@
         <v>311</v>
       </c>
       <c r="B311" s="1">
-        <v>116.3431058011608</v>
+        <v>114.7617023277887</v>
       </c>
     </row>
     <row r="312" spans="1:2">
@@ -4624,7 +4615,7 @@
         <v>312</v>
       </c>
       <c r="B312" s="1">
-        <v>116.310780960434</v>
+        <v>114.7570429511111</v>
       </c>
     </row>
     <row r="313" spans="1:2">
@@ -4632,7 +4623,7 @@
         <v>313</v>
       </c>
       <c r="B313" s="1">
-        <v>116.2992564404179</v>
+        <v>114.6978091864908</v>
       </c>
     </row>
     <row r="314" spans="1:2">
@@ -4640,7 +4631,7 @@
         <v>314</v>
       </c>
       <c r="B314" s="1">
-        <v>116.2750377510557</v>
+        <v>114.6814818977464</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -4648,7 +4639,7 @@
         <v>315</v>
       </c>
       <c r="B315" s="1">
-        <v>116.2741934198886</v>
+        <v>114.625602233593</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -4656,7 +4647,7 @@
         <v>316</v>
       </c>
       <c r="B316" s="1">
-        <v>116.2605385334144</v>
+        <v>114.5353032382575</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -4664,7 +4655,7 @@
         <v>317</v>
       </c>
       <c r="B317" s="1">
-        <v>116.2268005133823</v>
+        <v>114.5255065526479</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -4672,7 +4663,7 @@
         <v>318</v>
       </c>
       <c r="B318" s="1">
-        <v>116.2121541975533</v>
+        <v>114.5055846481308</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -4680,7 +4671,7 @@
         <v>319</v>
       </c>
       <c r="B319" s="1">
-        <v>116.1566942381423</v>
+        <v>114.4873184299715</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -4688,7 +4679,7 @@
         <v>320</v>
       </c>
       <c r="B320" s="1">
-        <v>116.1234239537334</v>
+        <v>114.4448222350753</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -4696,7 +4687,7 @@
         <v>321</v>
       </c>
       <c r="B321" s="1">
-        <v>116.0863017640522</v>
+        <v>114.3977758852331</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -4704,7 +4695,7 @@
         <v>322</v>
       </c>
       <c r="B322" s="1">
-        <v>116.064485437522</v>
+        <v>114.3882955992435</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -4712,7 +4703,7 @@
         <v>323</v>
       </c>
       <c r="B323" s="1">
-        <v>116.0536691214113</v>
+        <v>114.3859788713332</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -4720,7 +4711,7 @@
         <v>324</v>
       </c>
       <c r="B324" s="1">
-        <v>116.0270618051872</v>
+        <v>114.3534518475678</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -4728,7 +4719,7 @@
         <v>325</v>
       </c>
       <c r="B325" s="1">
-        <v>116.0257302432735</v>
+        <v>114.3423280345419</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -4736,7 +4727,7 @@
         <v>326</v>
       </c>
       <c r="B326" s="1">
-        <v>115.9829945754496</v>
+        <v>114.3193520538651</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -4744,7 +4735,7 @@
         <v>327</v>
       </c>
       <c r="B327" s="1">
-        <v>115.9799778672907</v>
+        <v>114.3155489448717</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -4752,7 +4743,7 @@
         <v>328</v>
       </c>
       <c r="B328" s="1">
-        <v>115.9742635580621</v>
+        <v>114.3124467868761</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -4760,7 +4751,7 @@
         <v>329</v>
       </c>
       <c r="B329" s="1">
-        <v>115.9366396933145</v>
+        <v>114.3080018517291</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -4768,7 +4759,7 @@
         <v>330</v>
       </c>
       <c r="B330" s="1">
-        <v>115.9268081560374</v>
+        <v>114.2170511446275</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -4776,7 +4767,7 @@
         <v>331</v>
       </c>
       <c r="B331" s="1">
-        <v>115.899793485406</v>
+        <v>114.2098149455189</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -4784,7 +4775,7 @@
         <v>332</v>
       </c>
       <c r="B332" s="1">
-        <v>115.8919818365401</v>
+        <v>114.1820770137675</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -4792,7 +4783,7 @@
         <v>333</v>
       </c>
       <c r="B333" s="1">
-        <v>115.8154043423834</v>
+        <v>114.1794999310647</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -4800,7 +4791,7 @@
         <v>334</v>
       </c>
       <c r="B334" s="1">
-        <v>115.8109764972475</v>
+        <v>114.1636824277203</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -4808,7 +4799,7 @@
         <v>335</v>
       </c>
       <c r="B335" s="1">
-        <v>115.8023675086408</v>
+        <v>114.1229065024675</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -4816,7 +4807,7 @@
         <v>336</v>
       </c>
       <c r="B336" s="1">
-        <v>115.7912257506566</v>
+        <v>113.9636893109596</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -4824,7 +4815,7 @@
         <v>337</v>
       </c>
       <c r="B337" s="1">
-        <v>115.729582886662</v>
+        <v>113.9515709890118</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -4832,7 +4823,7 @@
         <v>338</v>
       </c>
       <c r="B338" s="1">
-        <v>115.7278961334804</v>
+        <v>113.9503907097606</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -4840,7 +4831,7 @@
         <v>339</v>
       </c>
       <c r="B339" s="1">
-        <v>115.684378083185</v>
+        <v>113.8968717584467</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -4848,7 +4839,7 @@
         <v>340</v>
       </c>
       <c r="B340" s="1">
-        <v>115.6716788739994</v>
+        <v>113.8807607649167</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -4856,7 +4847,7 @@
         <v>341</v>
       </c>
       <c r="B341" s="1">
-        <v>115.6372181286432</v>
+        <v>113.8720462882493</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -4864,7 +4855,7 @@
         <v>342</v>
       </c>
       <c r="B342" s="1">
-        <v>115.6357996275238</v>
+        <v>113.8100646037707</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -4872,7 +4863,7 @@
         <v>343</v>
       </c>
       <c r="B343" s="1">
-        <v>115.6129790736528</v>
+        <v>113.7917679626832</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -4880,7 +4871,7 @@
         <v>344</v>
       </c>
       <c r="B344" s="1">
-        <v>115.6113095594524</v>
+        <v>113.7704414508826</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -4888,7 +4879,7 @@
         <v>345</v>
       </c>
       <c r="B345" s="1">
-        <v>115.5888648314188</v>
+        <v>113.7699290906702</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -4896,7 +4887,7 @@
         <v>346</v>
       </c>
       <c r="B346" s="1">
-        <v>115.5550352520424</v>
+        <v>113.7582275669103</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -4904,7 +4895,7 @@
         <v>347</v>
       </c>
       <c r="B347" s="1">
-        <v>115.5280994413831</v>
+        <v>113.7205418097709</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -4912,7 +4903,7 @@
         <v>348</v>
       </c>
       <c r="B348" s="1">
-        <v>115.5210501673947</v>
+        <v>113.6820263325407</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -4920,7 +4911,7 @@
         <v>349</v>
       </c>
       <c r="B349" s="1">
-        <v>115.5003801093591</v>
+        <v>113.6425830590473</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -4928,7 +4919,7 @@
         <v>350</v>
       </c>
       <c r="B350" s="1">
-        <v>115.4665201295584</v>
+        <v>113.6092722074203</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -4936,7 +4927,7 @@
         <v>351</v>
       </c>
       <c r="B351" s="1">
-        <v>115.4250451934093</v>
+        <v>113.6087846639947</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -4944,7 +4935,7 @@
         <v>352</v>
       </c>
       <c r="B352" s="1">
-        <v>115.4153233904614</v>
+        <v>113.5893747209949</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -4952,7 +4943,7 @@
         <v>353</v>
       </c>
       <c r="B353" s="1">
-        <v>115.3998101822904</v>
+        <v>113.5797531984293</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -4960,7 +4951,7 @@
         <v>354</v>
       </c>
       <c r="B354" s="1">
-        <v>115.3851862437931</v>
+        <v>113.5415262736801</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -4968,7 +4959,7 @@
         <v>355</v>
       </c>
       <c r="B355" s="1">
-        <v>115.3631416617868</v>
+        <v>113.5315874225522</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -4976,7 +4967,7 @@
         <v>356</v>
       </c>
       <c r="B356" s="1">
-        <v>115.3587316413947</v>
+        <v>113.4919108473272</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -4984,7 +4975,7 @@
         <v>357</v>
       </c>
       <c r="B357" s="1">
-        <v>115.3525981039435</v>
+        <v>113.4870382298329</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -4992,7 +4983,7 @@
         <v>358</v>
       </c>
       <c r="B358" s="1">
-        <v>115.3081852139851</v>
+        <v>113.4814859339978</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -5000,7 +4991,7 @@
         <v>359</v>
       </c>
       <c r="B359" s="1">
-        <v>115.2794261145728</v>
+        <v>113.4518073348962</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -5008,7 +4999,7 @@
         <v>360</v>
       </c>
       <c r="B360" s="1">
-        <v>115.2773652471783</v>
+        <v>113.4320288869306</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -5016,7 +5007,7 @@
         <v>361</v>
       </c>
       <c r="B361" s="1">
-        <v>115.2636180149678</v>
+        <v>113.4014922160046</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -5024,7 +5015,7 @@
         <v>362</v>
       </c>
       <c r="B362" s="1">
-        <v>115.2538928913416</v>
+        <v>113.3864653041412</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -5032,7 +5023,7 @@
         <v>363</v>
       </c>
       <c r="B363" s="1">
-        <v>115.1903761933153</v>
+        <v>113.3750730006433</v>
       </c>
     </row>
     <row r="364" spans="1:2">
@@ -5040,7 +5031,7 @@
         <v>364</v>
       </c>
       <c r="B364" s="1">
-        <v>115.1696839244146</v>
+        <v>113.3742150501396</v>
       </c>
     </row>
     <row r="365" spans="1:2">
@@ -5048,7 +5039,7 @@
         <v>365</v>
       </c>
       <c r="B365" s="1">
-        <v>115.1274428452386</v>
+        <v>113.3545865855622</v>
       </c>
     </row>
     <row r="366" spans="1:2">
@@ -5056,7 +5047,7 @@
         <v>366</v>
       </c>
       <c r="B366" s="1">
-        <v>115.1221143390295</v>
+        <v>113.3399407874823</v>
       </c>
     </row>
     <row r="367" spans="1:2">
@@ -5064,7 +5055,7 @@
         <v>367</v>
       </c>
       <c r="B367" s="1">
-        <v>115.0977036481678</v>
+        <v>113.3068489672445</v>
       </c>
     </row>
     <row r="368" spans="1:2">
@@ -5072,7 +5063,7 @@
         <v>368</v>
       </c>
       <c r="B368" s="1">
-        <v>115.079370153855</v>
+        <v>113.3016125501963</v>
       </c>
     </row>
     <row r="369" spans="1:2">
@@ -5080,7 +5071,7 @@
         <v>369</v>
       </c>
       <c r="B369" s="1">
-        <v>115.0639465926794</v>
+        <v>113.2697630246735</v>
       </c>
     </row>
     <row r="370" spans="1:2">
@@ -5088,7 +5079,7 @@
         <v>370</v>
       </c>
       <c r="B370" s="1">
-        <v>115.0637869299111</v>
+        <v>113.1768390297304</v>
       </c>
     </row>
     <row r="371" spans="1:2">
@@ -5096,7 +5087,7 @@
         <v>371</v>
       </c>
       <c r="B371" s="1">
-        <v>115.0408035656555</v>
+        <v>113.1299850873466</v>
       </c>
     </row>
     <row r="372" spans="1:2">
@@ -5104,7 +5095,7 @@
         <v>372</v>
       </c>
       <c r="B372" s="1">
-        <v>115.0402222808909</v>
+        <v>113.1107463905785</v>
       </c>
     </row>
     <row r="373" spans="1:2">
@@ -5112,7 +5103,7 @@
         <v>373</v>
       </c>
       <c r="B373" s="1">
-        <v>115.0163544358535</v>
+        <v>113.0979928285179</v>
       </c>
     </row>
     <row r="374" spans="1:2">
@@ -5120,7 +5111,7 @@
         <v>374</v>
       </c>
       <c r="B374" s="1">
-        <v>115.0064649477844</v>
+        <v>113.0671583810362</v>
       </c>
     </row>
     <row r="375" spans="1:2">
@@ -5128,7 +5119,7 @@
         <v>375</v>
       </c>
       <c r="B375" s="1">
-        <v>114.9764016377146</v>
+        <v>113.0435595734874</v>
       </c>
     </row>
     <row r="376" spans="1:2">
@@ -5136,7 +5127,7 @@
         <v>376</v>
       </c>
       <c r="B376" s="1">
-        <v>114.9571788090878</v>
+        <v>113.021929548779</v>
       </c>
     </row>
     <row r="377" spans="1:2">
@@ -5144,7 +5135,7 @@
         <v>377</v>
       </c>
       <c r="B377" s="1">
-        <v>114.9423250127247</v>
+        <v>113.0212732398084</v>
       </c>
     </row>
     <row r="378" spans="1:2">
@@ -5152,7 +5143,7 @@
         <v>378</v>
       </c>
       <c r="B378" s="1">
-        <v>114.9272316375727</v>
+        <v>113.0105067321413</v>
       </c>
     </row>
     <row r="379" spans="1:2">
@@ -5160,7 +5151,7 @@
         <v>379</v>
       </c>
       <c r="B379" s="1">
-        <v>114.9176529871134</v>
+        <v>112.9934904391229</v>
       </c>
     </row>
     <row r="380" spans="1:2">
@@ -5168,7 +5159,7 @@
         <v>380</v>
       </c>
       <c r="B380" s="1">
-        <v>114.8601100230053</v>
+        <v>112.9739909157207</v>
       </c>
     </row>
     <row r="381" spans="1:2">
@@ -5176,7 +5167,7 @@
         <v>381</v>
       </c>
       <c r="B381" s="1">
-        <v>114.8253947608493</v>
+        <v>112.9705647744464</v>
       </c>
     </row>
     <row r="382" spans="1:2">
@@ -5184,7 +5175,7 @@
         <v>382</v>
       </c>
       <c r="B382" s="1">
-        <v>114.7432750225324</v>
+        <v>112.9457939716762</v>
       </c>
     </row>
     <row r="383" spans="1:2">
@@ -5192,7 +5183,7 @@
         <v>383</v>
       </c>
       <c r="B383" s="1">
-        <v>114.7313601677314</v>
+        <v>112.9063589707042</v>
       </c>
     </row>
     <row r="384" spans="1:2">
@@ -5200,7 +5191,7 @@
         <v>384</v>
       </c>
       <c r="B384" s="1">
-        <v>114.7149191505637</v>
+        <v>112.8750921922828</v>
       </c>
     </row>
     <row r="385" spans="1:2">
@@ -5208,7 +5199,7 @@
         <v>385</v>
       </c>
       <c r="B385" s="1">
-        <v>114.7087121075753</v>
+        <v>112.8708503064408</v>
       </c>
     </row>
     <row r="386" spans="1:2">
@@ -5216,7 +5207,7 @@
         <v>386</v>
       </c>
       <c r="B386" s="1">
-        <v>114.6770005910024</v>
+        <v>112.864976222954</v>
       </c>
     </row>
     <row r="387" spans="1:2">
@@ -5224,7 +5215,7 @@
         <v>387</v>
       </c>
       <c r="B387" s="1">
-        <v>114.6297653762043</v>
+        <v>112.8012182701268</v>
       </c>
     </row>
     <row r="388" spans="1:2">
@@ -5232,7 +5223,7 @@
         <v>388</v>
       </c>
       <c r="B388" s="1">
-        <v>114.5972058077659</v>
+        <v>112.7874510499713</v>
       </c>
     </row>
     <row r="389" spans="1:2">
@@ -5240,7 +5231,7 @@
         <v>389</v>
       </c>
       <c r="B389" s="1">
-        <v>114.5857754313303</v>
+        <v>112.781497292838</v>
       </c>
     </row>
     <row r="390" spans="1:2">
@@ -5248,7 +5239,7 @@
         <v>390</v>
       </c>
       <c r="B390" s="1">
-        <v>114.5597511901854</v>
+        <v>112.7584244338045</v>
       </c>
     </row>
     <row r="391" spans="1:2">
@@ -5256,7 +5247,7 @@
         <v>391</v>
       </c>
       <c r="B391" s="1">
-        <v>114.5588641484246</v>
+        <v>112.7405069398716</v>
       </c>
     </row>
     <row r="392" spans="1:2">
@@ -5264,7 +5255,7 @@
         <v>392</v>
       </c>
       <c r="B392" s="1">
-        <v>114.517912181153</v>
+        <v>112.6820185520036</v>
       </c>
     </row>
     <row r="393" spans="1:2">
@@ -5272,7 +5263,7 @@
         <v>393</v>
       </c>
       <c r="B393" s="1">
-        <v>114.482830604689</v>
+        <v>112.6697368942012</v>
       </c>
     </row>
     <row r="394" spans="1:2">
@@ -5280,7 +5271,7 @@
         <v>394</v>
       </c>
       <c r="B394" s="1">
-        <v>114.4644116400549</v>
+        <v>112.6554698571502</v>
       </c>
     </row>
     <row r="395" spans="1:2">
@@ -5288,7 +5279,7 @@
         <v>395</v>
       </c>
       <c r="B395" s="1">
-        <v>114.4565939691257</v>
+        <v>112.6278690355218</v>
       </c>
     </row>
     <row r="396" spans="1:2">
@@ -5296,7 +5287,7 @@
         <v>396</v>
       </c>
       <c r="B396" s="1">
-        <v>114.4427984334927</v>
+        <v>112.5545133339437</v>
       </c>
     </row>
     <row r="397" spans="1:2">
@@ -5304,7 +5295,7 @@
         <v>397</v>
       </c>
       <c r="B397" s="1">
-        <v>114.3949854515352</v>
+        <v>112.5260791233148</v>
       </c>
     </row>
     <row r="398" spans="1:2">
@@ -5312,7 +5303,7 @@
         <v>398</v>
       </c>
       <c r="B398" s="1">
-        <v>114.3888748811229</v>
+        <v>112.5246298446732</v>
       </c>
     </row>
     <row r="399" spans="1:2">
@@ -5320,7 +5311,7 @@
         <v>399</v>
       </c>
       <c r="B399" s="1">
-        <v>114.3815528132307</v>
+        <v>112.5215119173003</v>
       </c>
     </row>
     <row r="400" spans="1:2">
@@ -5328,7 +5319,7 @@
         <v>400</v>
       </c>
       <c r="B400" s="1">
-        <v>114.3756109003018</v>
+        <v>112.5017555794293</v>
       </c>
     </row>
     <row r="401" spans="1:2">
@@ -5336,7 +5327,7 @@
         <v>401</v>
       </c>
       <c r="B401" s="1">
-        <v>114.3574320555643</v>
+        <v>112.4977302313818</v>
       </c>
     </row>
     <row r="402" spans="1:2">
@@ -5344,7 +5335,7 @@
         <v>402</v>
       </c>
       <c r="B402" s="1">
-        <v>114.3564374712188</v>
+        <v>112.4188568951149</v>
       </c>
     </row>
     <row r="403" spans="1:2">
@@ -5352,7 +5343,7 @@
         <v>403</v>
       </c>
       <c r="B403" s="1">
-        <v>114.3141929954747</v>
+        <v>112.4055714093083</v>
       </c>
     </row>
     <row r="404" spans="1:2">
@@ -5360,7 +5351,7 @@
         <v>404</v>
       </c>
       <c r="B404" s="1">
-        <v>114.3040014365724</v>
+        <v>112.3599233015308</v>
       </c>
     </row>
     <row r="405" spans="1:2">
@@ -5368,7 +5359,7 @@
         <v>405</v>
       </c>
       <c r="B405" s="1">
-        <v>114.2985190877281</v>
+        <v>112.3578011958594</v>
       </c>
     </row>
     <row r="406" spans="1:2">
@@ -5376,7 +5367,7 @@
         <v>406</v>
       </c>
       <c r="B406" s="1">
-        <v>114.2657118378897</v>
+        <v>112.2470661813295</v>
       </c>
     </row>
     <row r="407" spans="1:2">
@@ -5384,7 +5375,7 @@
         <v>407</v>
       </c>
       <c r="B407" s="1">
-        <v>114.2543180731323</v>
+        <v>112.1733629636517</v>
       </c>
     </row>
     <row r="408" spans="1:2">
@@ -5392,7 +5383,7 @@
         <v>408</v>
       </c>
       <c r="B408" s="1">
-        <v>114.104583901422</v>
+        <v>112.0903099124958</v>
       </c>
     </row>
     <row r="409" spans="1:2">
@@ -5400,7 +5391,7 @@
         <v>409</v>
       </c>
       <c r="B409" s="1">
-        <v>114.1035981217257</v>
+        <v>112.0887132008511</v>
       </c>
     </row>
     <row r="410" spans="1:2">
@@ -5408,7 +5399,7 @@
         <v>410</v>
       </c>
       <c r="B410" s="1">
-        <v>114.0994714581257</v>
+        <v>112.0796774656803</v>
       </c>
     </row>
     <row r="411" spans="1:2">
@@ -5416,7 +5407,7 @@
         <v>411</v>
       </c>
       <c r="B411" s="1">
-        <v>113.9989110009225</v>
+        <v>112.0472947121338</v>
       </c>
     </row>
     <row r="412" spans="1:2">
@@ -5424,7 +5415,7 @@
         <v>412</v>
       </c>
       <c r="B412" s="1">
-        <v>113.9803143474116</v>
+        <v>112.0367448855218</v>
       </c>
     </row>
     <row r="413" spans="1:2">
@@ -5432,7 +5423,7 @@
         <v>413</v>
       </c>
       <c r="B413" s="1">
-        <v>113.957388697597</v>
+        <v>112.0276045407015</v>
       </c>
     </row>
     <row r="414" spans="1:2">
@@ -5440,7 +5431,7 @@
         <v>414</v>
       </c>
       <c r="B414" s="1">
-        <v>113.9249755349999</v>
+        <v>111.9841922015535</v>
       </c>
     </row>
     <row r="415" spans="1:2">
@@ -5448,7 +5439,7 @@
         <v>415</v>
       </c>
       <c r="B415" s="1">
-        <v>113.9005311461096</v>
+        <v>111.9811530908105</v>
       </c>
     </row>
     <row r="416" spans="1:2">
@@ -5456,7 +5447,7 @@
         <v>416</v>
       </c>
       <c r="B416" s="1">
-        <v>113.8842515408951</v>
+        <v>111.9655290410685</v>
       </c>
     </row>
     <row r="417" spans="1:2">
@@ -5464,7 +5455,7 @@
         <v>417</v>
       </c>
       <c r="B417" s="1">
-        <v>113.8591780298825</v>
+        <v>111.9641537675884</v>
       </c>
     </row>
     <row r="418" spans="1:2">
@@ -5472,7 +5463,7 @@
         <v>418</v>
       </c>
       <c r="B418" s="1">
-        <v>113.8389167067161</v>
+        <v>111.9474569876734</v>
       </c>
     </row>
     <row r="419" spans="1:2">
@@ -5480,7 +5471,7 @@
         <v>419</v>
       </c>
       <c r="B419" s="1">
-        <v>113.8269434446479</v>
+        <v>111.9417499070087</v>
       </c>
     </row>
     <row r="420" spans="1:2">
@@ -5488,7 +5479,7 @@
         <v>420</v>
       </c>
       <c r="B420" s="1">
-        <v>113.7680631008233</v>
+        <v>111.9211730844742</v>
       </c>
     </row>
     <row r="421" spans="1:2">
@@ -5496,7 +5487,7 @@
         <v>421</v>
       </c>
       <c r="B421" s="1">
-        <v>113.7233926848544</v>
+        <v>111.8430665860972</v>
       </c>
     </row>
     <row r="422" spans="1:2">
@@ -5504,7 +5495,7 @@
         <v>422</v>
       </c>
       <c r="B422" s="1">
-        <v>113.7123024576222</v>
+        <v>111.8333865576678</v>
       </c>
     </row>
     <row r="423" spans="1:2">
@@ -5512,7 +5503,7 @@
         <v>423</v>
       </c>
       <c r="B423" s="1">
-        <v>113.7078981686206</v>
+        <v>111.8279835005284</v>
       </c>
     </row>
     <row r="424" spans="1:2">
@@ -5520,7 +5511,7 @@
         <v>424</v>
       </c>
       <c r="B424" s="1">
-        <v>113.7000092587665</v>
+        <v>111.8050729230983</v>
       </c>
     </row>
     <row r="425" spans="1:2">
@@ -5528,7 +5519,7 @@
         <v>425</v>
       </c>
       <c r="B425" s="1">
-        <v>113.6743383101207</v>
+        <v>111.7891244732288</v>
       </c>
     </row>
     <row r="426" spans="1:2">
@@ -5536,7 +5527,7 @@
         <v>426</v>
       </c>
       <c r="B426" s="1">
-        <v>113.6028206946431</v>
+        <v>111.7870640704791</v>
       </c>
     </row>
     <row r="427" spans="1:2">
@@ -5544,7 +5535,7 @@
         <v>427</v>
       </c>
       <c r="B427" s="1">
-        <v>113.5953034503218</v>
+        <v>111.7747235046988</v>
       </c>
     </row>
     <row r="428" spans="1:2">
@@ -5552,7 +5543,7 @@
         <v>428</v>
       </c>
       <c r="B428" s="1">
-        <v>113.5836059180706</v>
+        <v>111.7107908921084</v>
       </c>
     </row>
     <row r="429" spans="1:2">
@@ -5560,7 +5551,7 @@
         <v>429</v>
       </c>
       <c r="B429" s="1">
-        <v>113.5664541178336</v>
+        <v>111.7013619995717</v>
       </c>
     </row>
     <row r="430" spans="1:2">
@@ -5568,7 +5559,7 @@
         <v>430</v>
       </c>
       <c r="B430" s="1">
-        <v>113.555086567314</v>
+        <v>111.6815605730602</v>
       </c>
     </row>
     <row r="431" spans="1:2">
@@ -5576,7 +5567,7 @@
         <v>431</v>
       </c>
       <c r="B431" s="1">
-        <v>113.5360148789063</v>
+        <v>111.6667565583979</v>
       </c>
     </row>
     <row r="432" spans="1:2">
@@ -5584,7 +5575,7 @@
         <v>432</v>
       </c>
       <c r="B432" s="1">
-        <v>113.5245088394541</v>
+        <v>111.665236865504</v>
       </c>
     </row>
     <row r="433" spans="1:2">
@@ -5592,7 +5583,7 @@
         <v>433</v>
       </c>
       <c r="B433" s="1">
-        <v>113.5205033235612</v>
+        <v>111.6462114087996</v>
       </c>
     </row>
     <row r="434" spans="1:2">
@@ -5600,7 +5591,7 @@
         <v>434</v>
       </c>
       <c r="B434" s="1">
-        <v>113.517107509522</v>
+        <v>111.6440569833447</v>
       </c>
     </row>
     <row r="435" spans="1:2">
@@ -5608,7 +5599,7 @@
         <v>435</v>
       </c>
       <c r="B435" s="1">
-        <v>113.4612356483266</v>
+        <v>111.6386449223728</v>
       </c>
     </row>
     <row r="436" spans="1:2">
@@ -5616,7 +5607,7 @@
         <v>436</v>
       </c>
       <c r="B436" s="1">
-        <v>113.4156210683079</v>
+        <v>111.6276826529042</v>
       </c>
     </row>
     <row r="437" spans="1:2">
@@ -5624,7 +5615,7 @@
         <v>437</v>
       </c>
       <c r="B437" s="1">
-        <v>113.4089094099393</v>
+        <v>111.6002853417085</v>
       </c>
     </row>
     <row r="438" spans="1:2">
@@ -5632,7 +5623,7 @@
         <v>438</v>
       </c>
       <c r="B438" s="1">
-        <v>113.4081453695192</v>
+        <v>111.5662438033215</v>
       </c>
     </row>
     <row r="439" spans="1:2">
@@ -5640,7 +5631,7 @@
         <v>439</v>
       </c>
       <c r="B439" s="1">
-        <v>113.375991445644</v>
+        <v>111.5645952675452</v>
       </c>
     </row>
     <row r="440" spans="1:2">
@@ -5648,7 +5639,7 @@
         <v>440</v>
       </c>
       <c r="B440" s="1">
-        <v>113.3744686091094</v>
+        <v>111.5399514108824</v>
       </c>
     </row>
     <row r="441" spans="1:2">
@@ -5656,7 +5647,7 @@
         <v>441</v>
       </c>
       <c r="B441" s="1">
-        <v>113.3484311955397</v>
+        <v>111.5191713722998</v>
       </c>
     </row>
     <row r="442" spans="1:2">
@@ -5664,7 +5655,7 @@
         <v>442</v>
       </c>
       <c r="B442" s="1">
-        <v>113.3300754726304</v>
+        <v>111.5191564559184</v>
       </c>
     </row>
     <row r="443" spans="1:2">
@@ -5672,7 +5663,7 @@
         <v>443</v>
       </c>
       <c r="B443" s="1">
-        <v>113.3190319966095</v>
+        <v>111.4889045253819</v>
       </c>
     </row>
     <row r="444" spans="1:2">
@@ -5680,7 +5671,7 @@
         <v>444</v>
       </c>
       <c r="B444" s="1">
-        <v>113.3106512740437</v>
+        <v>111.4642592610156</v>
       </c>
     </row>
     <row r="445" spans="1:2">
@@ -5688,7 +5679,7 @@
         <v>445</v>
       </c>
       <c r="B445" s="1">
-        <v>113.2829856832555</v>
+        <v>111.4625868093828</v>
       </c>
     </row>
     <row r="446" spans="1:2">
@@ -5696,7 +5687,7 @@
         <v>446</v>
       </c>
       <c r="B446" s="1">
-        <v>113.2806950489124</v>
+        <v>111.4399504152108</v>
       </c>
     </row>
     <row r="447" spans="1:2">
@@ -5704,7 +5695,7 @@
         <v>447</v>
       </c>
       <c r="B447" s="1">
-        <v>113.2785343433585</v>
+        <v>111.4263440305055</v>
       </c>
     </row>
     <row r="448" spans="1:2">
@@ -5712,7 +5703,7 @@
         <v>448</v>
       </c>
       <c r="B448" s="1">
-        <v>113.2774058256504</v>
+        <v>111.3634372218093</v>
       </c>
     </row>
     <row r="449" spans="1:2">
@@ -5720,7 +5711,7 @@
         <v>449</v>
       </c>
       <c r="B449" s="1">
-        <v>113.2727436354069</v>
+        <v>111.3605574039551</v>
       </c>
     </row>
     <row r="450" spans="1:2">
@@ -5728,7 +5719,7 @@
         <v>450</v>
       </c>
       <c r="B450" s="1">
-        <v>113.2530026115553</v>
+        <v>111.343443453215</v>
       </c>
     </row>
     <row r="451" spans="1:2">
@@ -5736,7 +5727,7 @@
         <v>451</v>
       </c>
       <c r="B451" s="1">
-        <v>113.2151237461861</v>
+        <v>111.3298383767798</v>
       </c>
     </row>
     <row r="452" spans="1:2">
@@ -5744,7 +5735,7 @@
         <v>452</v>
       </c>
       <c r="B452" s="1">
-        <v>113.2129037481244</v>
+        <v>111.2894649545238</v>
       </c>
     </row>
     <row r="453" spans="1:2">
@@ -5752,7 +5743,7 @@
         <v>453</v>
       </c>
       <c r="B453" s="1">
-        <v>113.2120324687699</v>
+        <v>111.2689912838221</v>
       </c>
     </row>
     <row r="454" spans="1:2">
@@ -5760,7 +5751,7 @@
         <v>454</v>
       </c>
       <c r="B454" s="1">
-        <v>113.211970020346</v>
+        <v>111.2311484420166</v>
       </c>
     </row>
     <row r="455" spans="1:2">
@@ -5768,7 +5759,7 @@
         <v>455</v>
       </c>
       <c r="B455" s="1">
-        <v>113.2002522856803</v>
+        <v>111.2303752910315</v>
       </c>
     </row>
     <row r="456" spans="1:2">
@@ -5776,7 +5767,7 @@
         <v>456</v>
       </c>
       <c r="B456" s="1">
-        <v>113.1408907402909</v>
+        <v>111.2204826876524</v>
       </c>
     </row>
     <row r="457" spans="1:2">
@@ -5784,7 +5775,7 @@
         <v>457</v>
       </c>
       <c r="B457" s="1">
-        <v>113.1353480525381</v>
+        <v>111.1880452394977</v>
       </c>
     </row>
     <row r="458" spans="1:2">
@@ -5792,7 +5783,7 @@
         <v>458</v>
       </c>
       <c r="B458" s="1">
-        <v>113.128095689576</v>
+        <v>111.1344834423018</v>
       </c>
     </row>
     <row r="459" spans="1:2">
@@ -5800,7 +5791,7 @@
         <v>459</v>
       </c>
       <c r="B459" s="1">
-        <v>113.111105261125</v>
+        <v>111.1048664718788</v>
       </c>
     </row>
     <row r="460" spans="1:2">
@@ -5808,7 +5799,7 @@
         <v>460</v>
       </c>
       <c r="B460" s="1">
-        <v>113.0557967583988</v>
+        <v>111.1028015449521</v>
       </c>
     </row>
     <row r="461" spans="1:2">
@@ -5816,7 +5807,7 @@
         <v>461</v>
       </c>
       <c r="B461" s="1">
-        <v>113.0386243581854</v>
+        <v>111.0978413927624</v>
       </c>
     </row>
     <row r="462" spans="1:2">
@@ -5824,7 +5815,7 @@
         <v>462</v>
       </c>
       <c r="B462" s="1">
-        <v>113.0263970745329</v>
+        <v>111.0787578786531</v>
       </c>
     </row>
     <row r="463" spans="1:2">
@@ -5832,7 +5823,7 @@
         <v>463</v>
       </c>
       <c r="B463" s="1">
-        <v>113.0208378559884</v>
+        <v>111.0749499421903</v>
       </c>
     </row>
     <row r="464" spans="1:2">
@@ -5840,7 +5831,7 @@
         <v>464</v>
       </c>
       <c r="B464" s="1">
-        <v>113.0056820733351</v>
+        <v>111.0591478064843</v>
       </c>
     </row>
     <row r="465" spans="1:2">
@@ -5848,7 +5839,7 @@
         <v>465</v>
       </c>
       <c r="B465" s="1">
-        <v>112.997638524304</v>
+        <v>111.0304283964173</v>
       </c>
     </row>
     <row r="466" spans="1:2">
@@ -5856,7 +5847,7 @@
         <v>466</v>
       </c>
       <c r="B466" s="1">
-        <v>112.9959652606525</v>
+        <v>111.0242818316931</v>
       </c>
     </row>
     <row r="467" spans="1:2">
@@ -5864,7 +5855,7 @@
         <v>467</v>
       </c>
       <c r="B467" s="1">
-        <v>112.9953514120438</v>
+        <v>110.9836243456158</v>
       </c>
     </row>
     <row r="468" spans="1:2">
@@ -5872,7 +5863,7 @@
         <v>468</v>
       </c>
       <c r="B468" s="1">
-        <v>112.9288738602858</v>
+        <v>110.974265662175</v>
       </c>
     </row>
     <row r="469" spans="1:2">
@@ -5880,7 +5871,7 @@
         <v>469</v>
       </c>
       <c r="B469" s="1">
-        <v>112.8551484871203</v>
+        <v>110.9719971503796</v>
       </c>
     </row>
     <row r="470" spans="1:2">
@@ -5888,7 +5879,7 @@
         <v>470</v>
       </c>
       <c r="B470" s="1">
-        <v>112.8268557516504</v>
+        <v>110.9504824578858</v>
       </c>
     </row>
     <row r="471" spans="1:2">
@@ -5896,7 +5887,7 @@
         <v>471</v>
       </c>
       <c r="B471" s="1">
-        <v>112.8226756980466</v>
+        <v>110.9456092718837</v>
       </c>
     </row>
     <row r="472" spans="1:2">
@@ -5904,7 +5895,7 @@
         <v>472</v>
       </c>
       <c r="B472" s="1">
-        <v>112.8083674427615</v>
+        <v>110.9415426098986</v>
       </c>
     </row>
     <row r="473" spans="1:2">
@@ -5912,7 +5903,7 @@
         <v>473</v>
       </c>
       <c r="B473" s="1">
-        <v>112.8080763840722</v>
+        <v>110.9350503540384</v>
       </c>
     </row>
     <row r="474" spans="1:2">
@@ -5920,7 +5911,7 @@
         <v>474</v>
       </c>
       <c r="B474" s="1">
-        <v>112.8072449486699</v>
+        <v>110.9335281300582</v>
       </c>
     </row>
     <row r="475" spans="1:2">
@@ -5928,7 +5919,7 @@
         <v>475</v>
       </c>
       <c r="B475" s="1">
-        <v>112.8054306548381</v>
+        <v>110.9020851282824</v>
       </c>
     </row>
     <row r="476" spans="1:2">
@@ -5936,7 +5927,7 @@
         <v>476</v>
       </c>
       <c r="B476" s="1">
-        <v>112.8050894598995</v>
+        <v>110.8905587982093</v>
       </c>
     </row>
     <row r="477" spans="1:2">
@@ -5944,7 +5935,7 @@
         <v>477</v>
       </c>
       <c r="B477" s="1">
-        <v>112.7995728489312</v>
+        <v>110.8901229469722</v>
       </c>
     </row>
     <row r="478" spans="1:2">
@@ -5952,7 +5943,7 @@
         <v>478</v>
       </c>
       <c r="B478" s="1">
-        <v>112.7926963951675</v>
+        <v>110.8860018183997</v>
       </c>
     </row>
     <row r="479" spans="1:2">
@@ -5960,7 +5951,7 @@
         <v>479</v>
       </c>
       <c r="B479" s="1">
-        <v>112.7808599641692</v>
+        <v>110.8667388523876</v>
       </c>
     </row>
     <row r="480" spans="1:2">
@@ -5968,7 +5959,7 @@
         <v>480</v>
       </c>
       <c r="B480" s="1">
-        <v>112.7805953993746</v>
+        <v>110.8664373544406</v>
       </c>
     </row>
     <row r="481" spans="1:2">
@@ -5976,7 +5967,7 @@
         <v>481</v>
       </c>
       <c r="B481" s="1">
-        <v>112.7746637176459</v>
+        <v>110.8392651697646</v>
       </c>
     </row>
     <row r="482" spans="1:2">
@@ -5984,7 +5975,7 @@
         <v>482</v>
       </c>
       <c r="B482" s="1">
-        <v>112.6954665441004</v>
+        <v>110.7837736971148</v>
       </c>
     </row>
     <row r="483" spans="1:2">
@@ -5992,7 +5983,7 @@
         <v>483</v>
       </c>
       <c r="B483" s="1">
-        <v>112.6953381593454</v>
+        <v>110.7617053269088</v>
       </c>
     </row>
     <row r="484" spans="1:2">
@@ -6000,7 +5991,7 @@
         <v>484</v>
       </c>
       <c r="B484" s="1">
-        <v>112.6698031852092</v>
+        <v>110.7382290366048</v>
       </c>
     </row>
     <row r="485" spans="1:2">
@@ -6008,7 +5999,7 @@
         <v>485</v>
       </c>
       <c r="B485" s="1">
-        <v>112.6472867044426</v>
+        <v>110.7370589880919</v>
       </c>
     </row>
     <row r="486" spans="1:2">
@@ -6016,7 +6007,7 @@
         <v>486</v>
       </c>
       <c r="B486" s="1">
-        <v>112.6360934826494</v>
+        <v>110.7368011746634</v>
       </c>
     </row>
     <row r="487" spans="1:2">
@@ -6024,7 +6015,7 @@
         <v>487</v>
       </c>
       <c r="B487" s="1">
-        <v>112.6246358800362</v>
+        <v>110.7320930842152</v>
       </c>
     </row>
     <row r="488" spans="1:2">
@@ -6032,7 +6023,7 @@
         <v>488</v>
       </c>
       <c r="B488" s="1">
-        <v>112.6152148095978</v>
+        <v>110.7245272047157</v>
       </c>
     </row>
     <row r="489" spans="1:2">
@@ -6040,7 +6031,7 @@
         <v>489</v>
       </c>
       <c r="B489" s="1">
-        <v>112.6082885475082</v>
+        <v>110.6623636529369</v>
       </c>
     </row>
     <row r="490" spans="1:2">
@@ -6048,7 +6039,7 @@
         <v>490</v>
       </c>
       <c r="B490" s="1">
-        <v>112.6032300844741</v>
+        <v>110.6594125959147</v>
       </c>
     </row>
     <row r="491" spans="1:2">
@@ -6056,7 +6047,7 @@
         <v>491</v>
       </c>
       <c r="B491" s="1">
-        <v>112.5829640882694</v>
+        <v>110.6129416638319</v>
       </c>
     </row>
     <row r="492" spans="1:2">
@@ -6064,7 +6055,7 @@
         <v>492</v>
       </c>
       <c r="B492" s="1">
-        <v>112.5642632891174</v>
+        <v>110.6081253723408</v>
       </c>
     </row>
     <row r="493" spans="1:2">
@@ -6072,7 +6063,7 @@
         <v>493</v>
       </c>
       <c r="B493" s="1">
-        <v>112.5601572749383</v>
+        <v>110.597995096775</v>
       </c>
     </row>
     <row r="494" spans="1:2">
@@ -6080,7 +6071,7 @@
         <v>494</v>
       </c>
       <c r="B494" s="1">
-        <v>112.5555275948092</v>
+        <v>110.5506618692471</v>
       </c>
     </row>
     <row r="495" spans="1:2">
@@ -6088,7 +6079,7 @@
         <v>495</v>
       </c>
       <c r="B495" s="1">
-        <v>112.4864598793526</v>
+        <v>110.5406240510881</v>
       </c>
     </row>
     <row r="496" spans="1:2">
@@ -6096,7 +6087,7 @@
         <v>496</v>
       </c>
       <c r="B496" s="1">
-        <v>112.468176234963</v>
+        <v>110.5260545543667</v>
       </c>
     </row>
     <row r="497" spans="1:2">
@@ -6104,7 +6095,7 @@
         <v>497</v>
       </c>
       <c r="B497" s="1">
-        <v>112.4556794326438</v>
+        <v>110.525934178046</v>
       </c>
     </row>
     <row r="498" spans="1:2">
@@ -6112,7 +6103,7 @@
         <v>498</v>
       </c>
       <c r="B498" s="1">
-        <v>112.4469116691243</v>
+        <v>110.523508849652</v>
       </c>
     </row>
     <row r="499" spans="1:2">
@@ -6120,7 +6111,7 @@
         <v>499</v>
       </c>
       <c r="B499" s="1">
-        <v>112.410696089415</v>
+        <v>110.5035937672356</v>
       </c>
     </row>
     <row r="500" spans="1:2">
@@ -6128,7 +6119,7 @@
         <v>500</v>
       </c>
       <c r="B500" s="1">
-        <v>112.3959527997969</v>
+        <v>110.4919689212437</v>
       </c>
     </row>
     <row r="501" spans="1:2">
@@ -6136,7 +6127,7 @@
         <v>501</v>
       </c>
       <c r="B501" s="1">
-        <v>112.3902285870098</v>
+        <v>110.4757513415723</v>
       </c>
     </row>
     <row r="502" spans="1:2">
@@ -6144,7 +6135,7 @@
         <v>502</v>
       </c>
       <c r="B502" s="1">
-        <v>112.384949898494</v>
+        <v>110.4613574428434</v>
       </c>
     </row>
     <row r="503" spans="1:2">
@@ -6152,7 +6143,7 @@
         <v>503</v>
       </c>
       <c r="B503" s="1">
-        <v>112.3698678917445</v>
+        <v>110.4598423644712</v>
       </c>
     </row>
     <row r="504" spans="1:2">
@@ -6160,7 +6151,7 @@
         <v>504</v>
       </c>
       <c r="B504" s="1">
-        <v>112.3643267795415</v>
+        <v>110.458566273889</v>
       </c>
     </row>
     <row r="505" spans="1:2">
@@ -6168,7 +6159,7 @@
         <v>505</v>
       </c>
       <c r="B505" s="1">
-        <v>112.3532569803167</v>
+        <v>110.4201618048906</v>
       </c>
     </row>
     <row r="506" spans="1:2">
@@ -6176,7 +6167,7 @@
         <v>506</v>
       </c>
       <c r="B506" s="1">
-        <v>112.348921576405</v>
+        <v>110.4183549601192</v>
       </c>
     </row>
     <row r="507" spans="1:2">
@@ -6184,7 +6175,7 @@
         <v>507</v>
       </c>
       <c r="B507" s="1">
-        <v>112.3457151863544</v>
+        <v>110.4140409524949</v>
       </c>
     </row>
     <row r="508" spans="1:2">
@@ -6192,7 +6183,7 @@
         <v>508</v>
       </c>
       <c r="B508" s="1">
-        <v>112.3443100643494</v>
+        <v>110.3765088937218</v>
       </c>
     </row>
     <row r="509" spans="1:2">
@@ -6200,7 +6191,7 @@
         <v>509</v>
       </c>
       <c r="B509" s="1">
-        <v>112.3366263603164</v>
+        <v>110.3141831741127</v>
       </c>
     </row>
     <row r="510" spans="1:2">
@@ -6208,7 +6199,7 @@
         <v>510</v>
       </c>
       <c r="B510" s="1">
-        <v>112.3270094118785</v>
+        <v>110.3135797146082</v>
       </c>
     </row>
     <row r="511" spans="1:2">
@@ -6216,7 +6207,7 @@
         <v>511</v>
       </c>
       <c r="B511" s="1">
-        <v>112.3128845773402</v>
+        <v>110.3012788709462</v>
       </c>
     </row>
     <row r="512" spans="1:2">
@@ -6224,7 +6215,7 @@
         <v>512</v>
       </c>
       <c r="B512" s="1">
-        <v>112.3128219282962</v>
+        <v>110.2921803094427</v>
       </c>
     </row>
     <row r="513" spans="1:2">
@@ -6232,7 +6223,7 @@
         <v>513</v>
       </c>
       <c r="B513" s="1">
-        <v>112.2855288775107</v>
+        <v>110.2803456888579</v>
       </c>
     </row>
     <row r="514" spans="1:2">
@@ -6240,7 +6231,7 @@
         <v>514</v>
       </c>
       <c r="B514" s="1">
-        <v>112.2815784672865</v>
+        <v>110.2753960504142</v>
       </c>
     </row>
     <row r="515" spans="1:2">
@@ -6248,7 +6239,7 @@
         <v>515</v>
       </c>
       <c r="B515" s="1">
-        <v>112.2490515934971</v>
+        <v>110.2684807741144</v>
       </c>
     </row>
     <row r="516" spans="1:2">
@@ -6256,7 +6247,7 @@
         <v>516</v>
       </c>
       <c r="B516" s="1">
-        <v>112.1978404523026</v>
+        <v>110.2656046364245</v>
       </c>
     </row>
     <row r="517" spans="1:2">
@@ -6264,7 +6255,7 @@
         <v>517</v>
       </c>
       <c r="B517" s="1">
-        <v>112.1970028308614</v>
+        <v>110.2499551158725</v>
       </c>
     </row>
     <row r="518" spans="1:2">
@@ -6272,7 +6263,7 @@
         <v>518</v>
       </c>
       <c r="B518" s="1">
-        <v>112.1521745869466</v>
+        <v>110.2261411800788</v>
       </c>
     </row>
     <row r="519" spans="1:2">
@@ -6280,7 +6271,7 @@
         <v>519</v>
       </c>
       <c r="B519" s="1">
-        <v>112.151007845639</v>
+        <v>110.2148758948391</v>
       </c>
     </row>
     <row r="520" spans="1:2">
@@ -6288,7 +6279,7 @@
         <v>520</v>
       </c>
       <c r="B520" s="1">
-        <v>112.1400307365866</v>
+        <v>110.2032452853311</v>
       </c>
     </row>
     <row r="521" spans="1:2">
@@ -6296,7 +6287,7 @@
         <v>521</v>
       </c>
       <c r="B521" s="1">
-        <v>112.1231577583219</v>
+        <v>110.1679607677053</v>
       </c>
     </row>
     <row r="522" spans="1:2">
@@ -6304,7 +6295,7 @@
         <v>522</v>
       </c>
       <c r="B522" s="1">
-        <v>112.1159660867538</v>
+        <v>110.1625086463855</v>
       </c>
     </row>
     <row r="523" spans="1:2">
@@ -6312,7 +6303,7 @@
         <v>523</v>
       </c>
       <c r="B523" s="1">
-        <v>112.1075663935174</v>
+        <v>110.1370235907132</v>
       </c>
     </row>
     <row r="524" spans="1:2">
@@ -6320,7 +6311,7 @@
         <v>524</v>
       </c>
       <c r="B524" s="1">
-        <v>112.0916182087307</v>
+        <v>110.1356800789254</v>
       </c>
     </row>
     <row r="525" spans="1:2">
@@ -6328,7 +6319,7 @@
         <v>525</v>
       </c>
       <c r="B525" s="1">
-        <v>112.0859414808525</v>
+        <v>110.1275730909162</v>
       </c>
     </row>
     <row r="526" spans="1:2">
@@ -6336,7 +6327,7 @@
         <v>526</v>
       </c>
       <c r="B526" s="1">
-        <v>112.0857921883568</v>
+        <v>110.0777445200306</v>
       </c>
     </row>
     <row r="527" spans="1:2">
@@ -6344,7 +6335,7 @@
         <v>527</v>
       </c>
       <c r="B527" s="1">
-        <v>112.0639360530455</v>
+        <v>110.066737366849</v>
       </c>
     </row>
     <row r="528" spans="1:2">
@@ -6352,7 +6343,7 @@
         <v>528</v>
       </c>
       <c r="B528" s="1">
-        <v>112.0487402527189</v>
+        <v>110.040370961887</v>
       </c>
     </row>
     <row r="529" spans="1:2">
@@ -6360,7 +6351,7 @@
         <v>529</v>
       </c>
       <c r="B529" s="1">
-        <v>112.0338054732013</v>
+        <v>110.037368410155</v>
       </c>
     </row>
     <row r="530" spans="1:2">
@@ -6368,7 +6359,7 @@
         <v>530</v>
       </c>
       <c r="B530" s="1">
-        <v>112.0129983093677</v>
+        <v>110.0364135124085</v>
       </c>
     </row>
     <row r="531" spans="1:2">
@@ -6376,7 +6367,7 @@
         <v>531</v>
       </c>
       <c r="B531" s="1">
-        <v>112.0120802922825</v>
+        <v>110.0256434449092</v>
       </c>
     </row>
     <row r="532" spans="1:2">
@@ -6384,7 +6375,7 @@
         <v>532</v>
       </c>
       <c r="B532" s="1">
-        <v>111.9887384956194</v>
+        <v>110.0095934308315</v>
       </c>
     </row>
     <row r="533" spans="1:2">
@@ -6392,7 +6383,7 @@
         <v>533</v>
       </c>
       <c r="B533" s="1">
-        <v>111.9768466742044</v>
+        <v>110.0035211138072</v>
       </c>
     </row>
     <row r="534" spans="1:2">
@@ -6400,7 +6391,7 @@
         <v>534</v>
       </c>
       <c r="B534" s="1">
-        <v>111.9405716498297</v>
+        <v>109.9945957317712</v>
       </c>
     </row>
     <row r="535" spans="1:2">
@@ -6408,7 +6399,7 @@
         <v>535</v>
       </c>
       <c r="B535" s="1">
-        <v>111.9383827548657</v>
+        <v>109.9783702006586</v>
       </c>
     </row>
     <row r="536" spans="1:2">
@@ -6416,7 +6407,7 @@
         <v>536</v>
       </c>
       <c r="B536" s="1">
-        <v>111.9379956983257</v>
+        <v>109.8858233427937</v>
       </c>
     </row>
     <row r="537" spans="1:2">
@@ -6424,7 +6415,7 @@
         <v>537</v>
       </c>
       <c r="B537" s="1">
-        <v>111.8896866897012</v>
+        <v>109.8824174234363</v>
       </c>
     </row>
     <row r="538" spans="1:2">
@@ -6432,7 +6423,7 @@
         <v>538</v>
       </c>
       <c r="B538" s="1">
-        <v>111.8876585641403</v>
+        <v>109.8714941742311</v>
       </c>
     </row>
     <row r="539" spans="1:2">
@@ -6440,7 +6431,7 @@
         <v>539</v>
       </c>
       <c r="B539" s="1">
-        <v>111.8644334666559</v>
+        <v>109.8616056292941</v>
       </c>
     </row>
     <row r="540" spans="1:2">
@@ -6448,7 +6439,7 @@
         <v>540</v>
       </c>
       <c r="B540" s="1">
-        <v>111.8624781635913</v>
+        <v>109.84123527149</v>
       </c>
     </row>
     <row r="541" spans="1:2">
@@ -6456,7 +6447,7 @@
         <v>541</v>
       </c>
       <c r="B541" s="1">
-        <v>111.8588283523896</v>
+        <v>109.8361003286507</v>
       </c>
     </row>
     <row r="542" spans="1:2">
@@ -6464,7 +6455,7 @@
         <v>542</v>
       </c>
       <c r="B542" s="1">
-        <v>111.8583970122966</v>
+        <v>109.8284418759077</v>
       </c>
     </row>
     <row r="543" spans="1:2">
@@ -6472,7 +6463,7 @@
         <v>543</v>
       </c>
       <c r="B543" s="1">
-        <v>111.8531439135014</v>
+        <v>109.7869898061481</v>
       </c>
     </row>
     <row r="544" spans="1:2">
@@ -6480,7 +6471,7 @@
         <v>544</v>
       </c>
       <c r="B544" s="1">
-        <v>111.8492675928691</v>
+        <v>109.7800178201886</v>
       </c>
     </row>
     <row r="545" spans="1:2">
@@ -6488,7 +6479,7 @@
         <v>545</v>
       </c>
       <c r="B545" s="1">
-        <v>111.842918847942</v>
+        <v>109.761019416448</v>
       </c>
     </row>
     <row r="546" spans="1:2">
@@ -6496,7 +6487,7 @@
         <v>546</v>
       </c>
       <c r="B546" s="1">
-        <v>111.8376019824431</v>
+        <v>109.7506604320164</v>
       </c>
     </row>
     <row r="547" spans="1:2">
@@ -6504,7 +6495,7 @@
         <v>547</v>
       </c>
       <c r="B547" s="1">
-        <v>111.8213091379004</v>
+        <v>109.7506561749608</v>
       </c>
     </row>
     <row r="548" spans="1:2">
@@ -6512,7 +6503,7 @@
         <v>548</v>
       </c>
       <c r="B548" s="1">
-        <v>111.7879643968557</v>
+        <v>109.747452827778</v>
       </c>
     </row>
     <row r="549" spans="1:2">
@@ -6520,7 +6511,7 @@
         <v>549</v>
       </c>
       <c r="B549" s="1">
-        <v>111.7820122831688</v>
+        <v>109.7201981434137</v>
       </c>
     </row>
     <row r="550" spans="1:2">
@@ -6528,7 +6519,7 @@
         <v>550</v>
       </c>
       <c r="B550" s="1">
-        <v>111.7549387363908</v>
+        <v>109.7143145682061</v>
       </c>
     </row>
     <row r="551" spans="1:2">
@@ -6536,7 +6527,7 @@
         <v>551</v>
       </c>
       <c r="B551" s="1">
-        <v>111.7468591690584</v>
+        <v>109.6795196714069</v>
       </c>
     </row>
     <row r="552" spans="1:2">
@@ -6544,7 +6535,7 @@
         <v>552</v>
       </c>
       <c r="B552" s="1">
-        <v>111.7464032445951</v>
+        <v>109.6641338240729</v>
       </c>
     </row>
     <row r="553" spans="1:2">
@@ -6552,7 +6543,7 @@
         <v>553</v>
       </c>
       <c r="B553" s="1">
-        <v>111.7458994862061</v>
+        <v>109.6617475098228</v>
       </c>
     </row>
     <row r="554" spans="1:2">
@@ -6560,7 +6551,7 @@
         <v>554</v>
       </c>
       <c r="B554" s="1">
-        <v>111.7344277327426</v>
+        <v>109.6518463622194</v>
       </c>
     </row>
     <row r="555" spans="1:2">
@@ -6568,7 +6559,7 @@
         <v>555</v>
       </c>
       <c r="B555" s="1">
-        <v>111.7258374986156</v>
+        <v>109.6493562471646</v>
       </c>
     </row>
     <row r="556" spans="1:2">
@@ -6576,7 +6567,7 @@
         <v>556</v>
       </c>
       <c r="B556" s="1">
-        <v>111.7247420473168</v>
+        <v>109.6424099290982</v>
       </c>
     </row>
     <row r="557" spans="1:2">
@@ -6584,7 +6575,7 @@
         <v>557</v>
       </c>
       <c r="B557" s="1">
-        <v>111.7156936946952</v>
+        <v>109.641514909358</v>
       </c>
     </row>
     <row r="558" spans="1:2">
@@ -6592,7 +6583,7 @@
         <v>558</v>
       </c>
       <c r="B558" s="1">
-        <v>111.7107901600618</v>
+        <v>109.6284397724228</v>
       </c>
     </row>
     <row r="559" spans="1:2">
@@ -6600,7 +6591,7 @@
         <v>559</v>
       </c>
       <c r="B559" s="1">
-        <v>111.6978440465134</v>
+        <v>109.6243189401015</v>
       </c>
     </row>
     <row r="560" spans="1:2">
@@ -6608,7 +6599,7 @@
         <v>560</v>
       </c>
       <c r="B560" s="1">
-        <v>111.6815605730602</v>
+        <v>109.6227178780777</v>
       </c>
     </row>
     <row r="561" spans="1:2">
@@ -6616,7 +6607,7 @@
         <v>561</v>
       </c>
       <c r="B561" s="1">
-        <v>111.6794838359491</v>
+        <v>109.5846884369591</v>
       </c>
     </row>
     <row r="562" spans="1:2">
@@ -6624,7 +6615,7 @@
         <v>562</v>
       </c>
       <c r="B562" s="1">
-        <v>111.6695845014629</v>
+        <v>109.5531210596935</v>
       </c>
     </row>
     <row r="563" spans="1:2">
@@ -6632,7 +6623,7 @@
         <v>563</v>
       </c>
       <c r="B563" s="1">
-        <v>111.6680930072997</v>
+        <v>109.5480203199324</v>
       </c>
     </row>
     <row r="564" spans="1:2">
@@ -6640,7 +6631,7 @@
         <v>564</v>
       </c>
       <c r="B564" s="1">
-        <v>111.6132855159198</v>
+        <v>109.5296514749531</v>
       </c>
     </row>
     <row r="565" spans="1:2">
@@ -6648,7 +6639,7 @@
         <v>565</v>
       </c>
       <c r="B565" s="1">
-        <v>111.6085888827632</v>
+        <v>109.527662097683</v>
       </c>
     </row>
     <row r="566" spans="1:2">
@@ -6656,7 +6647,7 @@
         <v>566</v>
       </c>
       <c r="B566" s="1">
-        <v>111.6048342095179</v>
+        <v>109.5251396062057</v>
       </c>
     </row>
     <row r="567" spans="1:2">
@@ -6664,7 +6655,7 @@
         <v>567</v>
       </c>
       <c r="B567" s="1">
-        <v>111.5867564952678</v>
+        <v>109.5004770502124</v>
       </c>
     </row>
     <row r="568" spans="1:2">
@@ -6672,7 +6663,7 @@
         <v>568</v>
       </c>
       <c r="B568" s="1">
-        <v>111.5697791467819</v>
+        <v>109.4954302649639</v>
       </c>
     </row>
     <row r="569" spans="1:2">
@@ -6680,7 +6671,7 @@
         <v>569</v>
       </c>
       <c r="B569" s="1">
-        <v>111.5630895914407</v>
+        <v>109.4861258928097</v>
       </c>
     </row>
     <row r="570" spans="1:2">
@@ -6688,7 +6679,7 @@
         <v>570</v>
       </c>
       <c r="B570" s="1">
-        <v>111.53964546044</v>
+        <v>109.4720677197201</v>
       </c>
     </row>
     <row r="571" spans="1:2">
@@ -6696,7 +6687,7 @@
         <v>571</v>
       </c>
       <c r="B571" s="1">
-        <v>111.5126514028708</v>
+        <v>109.4357545820059</v>
       </c>
     </row>
     <row r="572" spans="1:2">
@@ -6704,7 +6695,7 @@
         <v>572</v>
       </c>
       <c r="B572" s="1">
-        <v>111.5051475720309</v>
+        <v>109.4099818466432</v>
       </c>
     </row>
     <row r="573" spans="1:2">
@@ -6712,7 +6703,7 @@
         <v>573</v>
       </c>
       <c r="B573" s="1">
-        <v>111.5033900370135</v>
+        <v>109.401226379313</v>
       </c>
     </row>
     <row r="574" spans="1:2">
@@ -6720,7 +6711,7 @@
         <v>574</v>
       </c>
       <c r="B574" s="1">
-        <v>111.4957660784898</v>
+        <v>109.4006575237557</v>
       </c>
     </row>
     <row r="575" spans="1:2">
@@ -6728,7 +6719,7 @@
         <v>575</v>
       </c>
       <c r="B575" s="1">
-        <v>111.4924405476545</v>
+        <v>109.3999938996119</v>
       </c>
     </row>
     <row r="576" spans="1:2">
@@ -6736,7 +6727,7 @@
         <v>576</v>
       </c>
       <c r="B576" s="1">
-        <v>111.4824182189503</v>
+        <v>109.3761037423567</v>
       </c>
     </row>
     <row r="577" spans="1:2">
@@ -6744,7 +6735,7 @@
         <v>577</v>
       </c>
       <c r="B577" s="1">
-        <v>111.4644898205769</v>
+        <v>109.3697931931148</v>
       </c>
     </row>
     <row r="578" spans="1:2">
@@ -6752,7 +6743,7 @@
         <v>578</v>
       </c>
       <c r="B578" s="1">
-        <v>111.441025031537</v>
+        <v>109.368917134021</v>
       </c>
     </row>
     <row r="579" spans="1:2">
@@ -6760,7 +6751,7 @@
         <v>579</v>
       </c>
       <c r="B579" s="1">
-        <v>111.4347458404243</v>
+        <v>109.3672262308889</v>
       </c>
     </row>
     <row r="580" spans="1:2">
@@ -6768,7 +6759,7 @@
         <v>580</v>
       </c>
       <c r="B580" s="1">
-        <v>111.3755379643997</v>
+        <v>109.3540994037386</v>
       </c>
     </row>
     <row r="581" spans="1:2">
@@ -6776,7 +6767,7 @@
         <v>581</v>
       </c>
       <c r="B581" s="1">
-        <v>111.3492087601791</v>
+        <v>109.3514721004242</v>
       </c>
     </row>
     <row r="582" spans="1:2">
@@ -6784,7 +6775,7 @@
         <v>582</v>
       </c>
       <c r="B582" s="1">
-        <v>111.3450038941153</v>
+        <v>109.333593362642</v>
       </c>
     </row>
     <row r="583" spans="1:2">
@@ -6792,7 +6783,7 @@
         <v>583</v>
       </c>
       <c r="B583" s="1">
-        <v>111.3392799616006</v>
+        <v>109.3188730584058</v>
       </c>
     </row>
     <row r="584" spans="1:2">
@@ -6800,31 +6791,7 @@
         <v>584</v>
       </c>
       <c r="B584" s="1">
-        <v>111.2910293602445</v>
-      </c>
-    </row>
-    <row r="585" spans="1:2">
-      <c r="A585" t="s">
-        <v>585</v>
-      </c>
-      <c r="B585" s="1">
-        <v>111.2748536308625</v>
-      </c>
-    </row>
-    <row r="586" spans="1:2">
-      <c r="A586" t="s">
-        <v>586</v>
-      </c>
-      <c r="B586" s="1">
-        <v>111.2505282725821</v>
-      </c>
-    </row>
-    <row r="587" spans="1:2">
-      <c r="A587" t="s">
-        <v>587</v>
-      </c>
-      <c r="B587" s="1">
-        <v>111.2423250627122</v>
+        <v>109.2983121759433</v>
       </c>
     </row>
   </sheetData>

--- a/Screener/data/rs_rating_top_30.xlsx
+++ b/Screener/data/rs_rating_top_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="577">
   <si>
     <t>Symbol</t>
   </si>
@@ -28,9 +28,6 @@
     <t>EDTXU</t>
   </si>
   <si>
-    <t>AAOI</t>
-  </si>
-  <si>
     <t>SGTX</t>
   </si>
   <si>
@@ -46,34 +43,46 @@
     <t>TDS</t>
   </si>
   <si>
+    <t>CVNA</t>
+  </si>
+  <si>
+    <t>ML</t>
+  </si>
+  <si>
     <t>ADTX</t>
   </si>
   <si>
-    <t>CVNA</t>
-  </si>
-  <si>
-    <t>ML</t>
-  </si>
-  <si>
     <t>DLO</t>
   </si>
   <si>
+    <t>CAMT</t>
+  </si>
+  <si>
+    <t>PHVS</t>
+  </si>
+  <si>
     <t>ACMR</t>
   </si>
   <si>
-    <t>OLMA</t>
-  </si>
-  <si>
-    <t>CAMT</t>
+    <t>IONQ</t>
+  </si>
+  <si>
+    <t>APP</t>
+  </si>
+  <si>
+    <t>PAY</t>
+  </si>
+  <si>
+    <t>MNSO</t>
   </si>
   <si>
     <t>ANF</t>
   </si>
   <si>
-    <t>PHVS</t>
-  </si>
-  <si>
-    <t>APP</t>
+    <t>BOOM</t>
+  </si>
+  <si>
+    <t>BBIO</t>
   </si>
   <si>
     <t>LEU</t>
@@ -82,1693 +91,1660 @@
     <t>VRT</t>
   </si>
   <si>
-    <t>BBIO</t>
-  </si>
-  <si>
-    <t>PAY</t>
-  </si>
-  <si>
-    <t>BOOM</t>
-  </si>
-  <si>
     <t>CPRI</t>
   </si>
   <si>
+    <t>XPEV</t>
+  </si>
+  <si>
     <t>ESTE</t>
   </si>
   <si>
-    <t>XPEV</t>
-  </si>
-  <si>
-    <t>MNSO</t>
+    <t>CSPI</t>
+  </si>
+  <si>
+    <t>AFRM</t>
   </si>
   <si>
     <t>CLS</t>
   </si>
   <si>
+    <t>MNBP</t>
+  </si>
+  <si>
+    <t>KRT</t>
+  </si>
+  <si>
+    <t>CWCO</t>
+  </si>
+  <si>
+    <t>NXGN</t>
+  </si>
+  <si>
+    <t>FUTU</t>
+  </si>
+  <si>
     <t>STRL</t>
   </si>
   <si>
+    <t>SRDX</t>
+  </si>
+  <si>
+    <t>UPWK</t>
+  </si>
+  <si>
     <t>RETA</t>
   </si>
   <si>
     <t>LMB</t>
   </si>
   <si>
-    <t>MNBP</t>
-  </si>
-  <si>
-    <t>UPWK</t>
+    <t>CELH</t>
+  </si>
+  <si>
+    <t>GENTF</t>
+  </si>
+  <si>
+    <t>URGN</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>SBOW</t>
   </si>
   <si>
     <t>CEIX</t>
   </si>
   <si>
-    <t>SBOW</t>
-  </si>
-  <si>
-    <t>KRT</t>
-  </si>
-  <si>
-    <t>CSPI</t>
-  </si>
-  <si>
-    <t>URGN</t>
-  </si>
-  <si>
-    <t>AFRM</t>
-  </si>
-  <si>
-    <t>GENTF</t>
-  </si>
-  <si>
-    <t>CELH</t>
-  </si>
-  <si>
-    <t>SRDX</t>
+    <t>PDD</t>
+  </si>
+  <si>
+    <t>DELL</t>
+  </si>
+  <si>
+    <t>VNO</t>
+  </si>
+  <si>
+    <t>UPTDU</t>
+  </si>
+  <si>
+    <t>AMR</t>
+  </si>
+  <si>
+    <t>FSLY</t>
   </si>
   <si>
     <t>AEO</t>
   </si>
   <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>FUTU</t>
+    <t>VIEW</t>
   </si>
   <si>
     <t>BWMX</t>
   </si>
   <si>
-    <t>IONQ</t>
-  </si>
-  <si>
-    <t>VNO</t>
-  </si>
-  <si>
-    <t>UPTDU</t>
-  </si>
-  <si>
     <t>X</t>
   </si>
   <si>
+    <t>KD</t>
+  </si>
+  <si>
+    <t>WHD</t>
+  </si>
+  <si>
+    <t>RYTM</t>
+  </si>
+  <si>
+    <t>MMYT</t>
+  </si>
+  <si>
+    <t>COUR</t>
+  </si>
+  <si>
+    <t>PAR</t>
+  </si>
+  <si>
+    <t>SM</t>
+  </si>
+  <si>
+    <t>PARR</t>
+  </si>
+  <si>
+    <t>WFRD</t>
+  </si>
+  <si>
+    <t>SLG</t>
+  </si>
+  <si>
+    <t>TRNS</t>
+  </si>
+  <si>
+    <t>IESC</t>
+  </si>
+  <si>
+    <t>FRSH</t>
+  </si>
+  <si>
+    <t>OII</t>
+  </si>
+  <si>
+    <t>HOV</t>
+  </si>
+  <si>
+    <t>ESEA</t>
+  </si>
+  <si>
+    <t>MOD</t>
+  </si>
+  <si>
+    <t>INSM</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>FSTR</t>
+  </si>
+  <si>
+    <t>HWKN</t>
+  </si>
+  <si>
+    <t>KDNY</t>
+  </si>
+  <si>
+    <t>GCO</t>
+  </si>
+  <si>
+    <t>PDS</t>
+  </si>
+  <si>
+    <t>LYTS</t>
+  </si>
+  <si>
     <t>VRTV</t>
   </si>
   <si>
-    <t>FSLY</t>
-  </si>
-  <si>
-    <t>WHD</t>
+    <t>RELY</t>
+  </si>
+  <si>
+    <t>CBAY</t>
+  </si>
+  <si>
+    <t>GAMB</t>
+  </si>
+  <si>
+    <t>FTI</t>
+  </si>
+  <si>
+    <t>CORT</t>
+  </si>
+  <si>
+    <t>UBS</t>
+  </si>
+  <si>
+    <t>PSFE</t>
+  </si>
+  <si>
+    <t>FN</t>
+  </si>
+  <si>
+    <t>BRZE</t>
+  </si>
+  <si>
+    <t>QTRX</t>
+  </si>
+  <si>
+    <t>DWAC</t>
+  </si>
+  <si>
+    <t>DICE</t>
+  </si>
+  <si>
+    <t>TWST</t>
   </si>
   <si>
     <t>IOT</t>
   </si>
   <si>
-    <t>MOD</t>
-  </si>
-  <si>
-    <t>DELL</t>
-  </si>
-  <si>
-    <t>RYTM</t>
-  </si>
-  <si>
-    <t>VIEW</t>
-  </si>
-  <si>
-    <t>CWCO</t>
-  </si>
-  <si>
-    <t>MMYT</t>
+    <t>IDYA</t>
+  </si>
+  <si>
+    <t>TPL</t>
+  </si>
+  <si>
+    <t>ARRY</t>
+  </si>
+  <si>
+    <t>JXN</t>
+  </si>
+  <si>
+    <t>ROKU</t>
+  </si>
+  <si>
+    <t>GTLS</t>
+  </si>
+  <si>
+    <t>NATR</t>
+  </si>
+  <si>
+    <t>AEHR</t>
+  </si>
+  <si>
+    <t>LLY</t>
+  </si>
+  <si>
+    <t>NOV</t>
+  </si>
+  <si>
+    <t>LBRT</t>
+  </si>
+  <si>
+    <t>WMG</t>
+  </si>
+  <si>
+    <t>YETI</t>
+  </si>
+  <si>
+    <t>POWL</t>
+  </si>
+  <si>
+    <t>SENEB</t>
   </si>
   <si>
     <t>GHM</t>
   </si>
   <si>
-    <t>AMR</t>
-  </si>
-  <si>
-    <t>PAR</t>
-  </si>
-  <si>
-    <t>PARR</t>
-  </si>
-  <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>SLG</t>
-  </si>
-  <si>
-    <t>PDD</t>
-  </si>
-  <si>
-    <t>SM</t>
-  </si>
-  <si>
-    <t>GCO</t>
-  </si>
-  <si>
-    <t>LYTS</t>
-  </si>
-  <si>
-    <t>WFRD</t>
-  </si>
-  <si>
-    <t>IESC</t>
-  </si>
-  <si>
-    <t>GAMB</t>
-  </si>
-  <si>
-    <t>KD</t>
-  </si>
-  <si>
-    <t>SENEB</t>
-  </si>
-  <si>
-    <t>YETI</t>
-  </si>
-  <si>
-    <t>COUR</t>
-  </si>
-  <si>
-    <t>FN</t>
-  </si>
-  <si>
-    <t>UBS</t>
-  </si>
-  <si>
-    <t>ESEA</t>
-  </si>
-  <si>
-    <t>NATR</t>
-  </si>
-  <si>
-    <t>RELY</t>
-  </si>
-  <si>
-    <t>FSTR</t>
+    <t>CKX</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>RVMD</t>
+  </si>
+  <si>
+    <t>MPC</t>
   </si>
   <si>
     <t>OBT</t>
   </si>
   <si>
-    <t>PDS</t>
-  </si>
-  <si>
-    <t>OII</t>
-  </si>
-  <si>
-    <t>NXGN</t>
-  </si>
-  <si>
-    <t>PSFE</t>
-  </si>
-  <si>
-    <t>HWKN</t>
-  </si>
-  <si>
-    <t>KDNY</t>
-  </si>
-  <si>
-    <t>INSM</t>
-  </si>
-  <si>
-    <t>HBB</t>
+    <t>SAIA</t>
+  </si>
+  <si>
+    <t>MTSI</t>
+  </si>
+  <si>
+    <t>MTDR</t>
+  </si>
+  <si>
+    <t>APA</t>
+  </si>
+  <si>
+    <t>VST</t>
   </si>
   <si>
     <t>CIR</t>
   </si>
   <si>
-    <t>TRNS</t>
-  </si>
-  <si>
-    <t>IDYA</t>
-  </si>
-  <si>
-    <t>CBAY</t>
-  </si>
-  <si>
-    <t>HOV</t>
-  </si>
-  <si>
-    <t>GTLS</t>
-  </si>
-  <si>
-    <t>FRSH</t>
-  </si>
-  <si>
-    <t>APA</t>
-  </si>
-  <si>
-    <t>NOV</t>
+    <t>ARGX</t>
+  </si>
+  <si>
+    <t>AURC</t>
+  </si>
+  <si>
+    <t>HRB</t>
+  </si>
+  <si>
+    <t>ITRN</t>
+  </si>
+  <si>
+    <t>XPO</t>
+  </si>
+  <si>
+    <t>XPRO</t>
+  </si>
+  <si>
+    <t>STEP</t>
+  </si>
+  <si>
+    <t>OKTA</t>
+  </si>
+  <si>
+    <t>TDW</t>
+  </si>
+  <si>
+    <t>ESTC</t>
+  </si>
+  <si>
+    <t>DWACU</t>
+  </si>
+  <si>
+    <t>CNX</t>
+  </si>
+  <si>
+    <t>CRC</t>
+  </si>
+  <si>
+    <t>AMPL</t>
+  </si>
+  <si>
+    <t>SPLK</t>
+  </si>
+  <si>
+    <t>NVO</t>
+  </si>
+  <si>
+    <t>LEAT</t>
+  </si>
+  <si>
+    <t>SMHI</t>
+  </si>
+  <si>
+    <t>JILL</t>
+  </si>
+  <si>
+    <t>EDU</t>
+  </si>
+  <si>
+    <t>BKI</t>
+  </si>
+  <si>
+    <t>PBR</t>
+  </si>
+  <si>
+    <t>TWIN</t>
+  </si>
+  <si>
+    <t>HEP</t>
+  </si>
+  <si>
+    <t>NBR</t>
+  </si>
+  <si>
+    <t>PBF</t>
+  </si>
+  <si>
+    <t>NTNX</t>
+  </si>
+  <si>
+    <t>ODC</t>
+  </si>
+  <si>
+    <t>NOG</t>
+  </si>
+  <si>
+    <t>CLMT</t>
+  </si>
+  <si>
+    <t>PLUS</t>
+  </si>
+  <si>
+    <t>ANIP</t>
+  </si>
+  <si>
+    <t>CAL</t>
+  </si>
+  <si>
+    <t>MORN</t>
+  </si>
+  <si>
+    <t>ARCH</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>SLB</t>
+  </si>
+  <si>
+    <t>CABA</t>
+  </si>
+  <si>
+    <t>FRHC</t>
+  </si>
+  <si>
+    <t>IIPR</t>
+  </si>
+  <si>
+    <t>RIVN</t>
+  </si>
+  <si>
+    <t>INTU</t>
+  </si>
+  <si>
+    <t>CVI</t>
+  </si>
+  <si>
+    <t>EVI</t>
+  </si>
+  <si>
+    <t>CHX</t>
+  </si>
+  <si>
+    <t>CTRN</t>
+  </si>
+  <si>
+    <t>CWAN</t>
+  </si>
+  <si>
+    <t>AROC</t>
+  </si>
+  <si>
+    <t>ONTO</t>
+  </si>
+  <si>
+    <t>CPE</t>
+  </si>
+  <si>
+    <t>PRDO</t>
+  </si>
+  <si>
+    <t>NRP</t>
+  </si>
+  <si>
+    <t>VET</t>
+  </si>
+  <si>
+    <t>NTRA</t>
+  </si>
+  <si>
+    <t>CCJ</t>
+  </si>
+  <si>
+    <t>HAL</t>
+  </si>
+  <si>
+    <t>ANET</t>
+  </si>
+  <si>
+    <t>CIVI</t>
+  </si>
+  <si>
+    <t>FTAI</t>
+  </si>
+  <si>
+    <t>SU</t>
+  </si>
+  <si>
+    <t>FETM</t>
+  </si>
+  <si>
+    <t>ERIE</t>
+  </si>
+  <si>
+    <t>AVAV</t>
+  </si>
+  <si>
+    <t>RNGR</t>
+  </si>
+  <si>
+    <t>GPOR</t>
+  </si>
+  <si>
+    <t>GES</t>
+  </si>
+  <si>
+    <t>GIC</t>
+  </si>
+  <si>
+    <t>CXM</t>
+  </si>
+  <si>
+    <t>NOA</t>
+  </si>
+  <si>
+    <t>MUR</t>
+  </si>
+  <si>
+    <t>YZCAY</t>
+  </si>
+  <si>
+    <t>BFST</t>
+  </si>
+  <si>
+    <t>HNI</t>
+  </si>
+  <si>
+    <t>KRC</t>
+  </si>
+  <si>
+    <t>TALO</t>
+  </si>
+  <si>
+    <t>AZTA</t>
+  </si>
+  <si>
+    <t>CTLT</t>
+  </si>
+  <si>
+    <t>CMT</t>
+  </si>
+  <si>
+    <t>PRA</t>
+  </si>
+  <si>
+    <t>OVV</t>
+  </si>
+  <si>
+    <t>DFH</t>
+  </si>
+  <si>
+    <t>YY</t>
+  </si>
+  <si>
+    <t>WIX</t>
+  </si>
+  <si>
+    <t>COP</t>
+  </si>
+  <si>
+    <t>IMO</t>
+  </si>
+  <si>
+    <t>GGAL</t>
   </si>
   <si>
     <t>UPTD</t>
   </si>
   <si>
-    <t>JXN</t>
-  </si>
-  <si>
-    <t>BRZE</t>
-  </si>
-  <si>
-    <t>DICE</t>
-  </si>
-  <si>
-    <t>CORT</t>
-  </si>
-  <si>
-    <t>HRB</t>
-  </si>
-  <si>
-    <t>XPO</t>
-  </si>
-  <si>
-    <t>POWL</t>
-  </si>
-  <si>
-    <t>LBRT</t>
-  </si>
-  <si>
-    <t>LLY</t>
-  </si>
-  <si>
-    <t>FTI</t>
-  </si>
-  <si>
-    <t>ARRY</t>
-  </si>
-  <si>
-    <t>TPL</t>
-  </si>
-  <si>
-    <t>CKX</t>
-  </si>
-  <si>
-    <t>HDSN</t>
-  </si>
-  <si>
-    <t>ODC</t>
+    <t>WMPN</t>
+  </si>
+  <si>
+    <t>PETQ</t>
+  </si>
+  <si>
+    <t>KEQU</t>
+  </si>
+  <si>
+    <t>HOFT</t>
+  </si>
+  <si>
+    <t>HAS</t>
+  </si>
+  <si>
+    <t>FORG</t>
+  </si>
+  <si>
+    <t>BNTX</t>
+  </si>
+  <si>
+    <t>ADBE</t>
+  </si